--- a/docs/【DIGITAL OJT】WBS.xlsx
+++ b/docs/【DIGITAL OJT】WBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIGITALOJT\digital-ojt-development-cause-DroneInventorySystem\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:101_{3D5407B4-7265-4445-A563-A6173EB729B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E09BF70-A580-4C8A-8B5F-1D7882CA578A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13950" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16005" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -1193,7 +1193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1307,13 +1307,74 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1322,46 +1383,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1370,22 +1398,10 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1406,6 +1422,24 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1415,76 +1449,43 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2091,120 +2092,120 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="J3" s="136">
+      <c r="J3" s="97">
         <v>2024</v>
       </c>
-      <c r="K3" s="137"/>
-      <c r="L3" s="137"/>
-      <c r="M3" s="137"/>
-      <c r="N3" s="137"/>
-      <c r="O3" s="137"/>
-      <c r="P3" s="137"/>
-      <c r="Q3" s="137"/>
-      <c r="R3" s="137"/>
-      <c r="S3" s="137"/>
-      <c r="T3" s="137"/>
-      <c r="U3" s="137"/>
-      <c r="V3" s="137"/>
-      <c r="W3" s="137"/>
-      <c r="X3" s="137"/>
-      <c r="Y3" s="137"/>
-      <c r="Z3" s="137"/>
-      <c r="AA3" s="137"/>
-      <c r="AB3" s="137"/>
-      <c r="AC3" s="137"/>
-      <c r="AD3" s="137"/>
-      <c r="AE3" s="137"/>
-      <c r="AF3" s="137"/>
-      <c r="AG3" s="137"/>
-      <c r="AH3" s="137"/>
-      <c r="AI3" s="137"/>
-      <c r="AJ3" s="137"/>
-      <c r="AK3" s="137"/>
-      <c r="AL3" s="137"/>
-      <c r="AM3" s="137"/>
-      <c r="AN3" s="137"/>
-      <c r="AO3" s="137"/>
-      <c r="AP3" s="137"/>
-      <c r="AQ3" s="137"/>
-      <c r="AR3" s="137"/>
-      <c r="AS3" s="137"/>
-      <c r="AT3" s="137"/>
-      <c r="AU3" s="137"/>
-      <c r="AV3" s="137"/>
-      <c r="AW3" s="137"/>
-      <c r="AX3" s="137"/>
-      <c r="AY3" s="137"/>
-      <c r="AZ3" s="137"/>
-      <c r="BA3" s="137"/>
-      <c r="BB3" s="137"/>
-      <c r="BC3" s="137"/>
-      <c r="BD3" s="137"/>
-      <c r="BE3" s="137"/>
-      <c r="BF3" s="137"/>
-      <c r="BG3" s="137"/>
-      <c r="BH3" s="137"/>
-      <c r="BI3" s="137"/>
-      <c r="BJ3" s="137"/>
-      <c r="BK3" s="137"/>
-      <c r="BL3" s="137"/>
-      <c r="BM3" s="137"/>
-      <c r="BN3" s="137"/>
-      <c r="BO3" s="137"/>
-      <c r="BP3" s="137"/>
-      <c r="BQ3" s="137"/>
-      <c r="BR3" s="137"/>
-      <c r="BS3" s="137"/>
-      <c r="BT3" s="137"/>
-      <c r="BU3" s="137"/>
-      <c r="BV3" s="137"/>
-      <c r="BW3" s="137"/>
-      <c r="BX3" s="137"/>
-      <c r="BY3" s="137"/>
-      <c r="BZ3" s="137"/>
-      <c r="CA3" s="137"/>
-      <c r="CB3" s="137"/>
-      <c r="CC3" s="137"/>
-      <c r="CD3" s="137"/>
-      <c r="CE3" s="137"/>
-      <c r="CF3" s="137"/>
-      <c r="CG3" s="137"/>
-      <c r="CH3" s="137"/>
-      <c r="CI3" s="137"/>
-      <c r="CJ3" s="138"/>
-      <c r="CK3" s="136">
+      <c r="K3" s="98"/>
+      <c r="L3" s="98"/>
+      <c r="M3" s="98"/>
+      <c r="N3" s="98"/>
+      <c r="O3" s="98"/>
+      <c r="P3" s="98"/>
+      <c r="Q3" s="98"/>
+      <c r="R3" s="98"/>
+      <c r="S3" s="98"/>
+      <c r="T3" s="98"/>
+      <c r="U3" s="98"/>
+      <c r="V3" s="98"/>
+      <c r="W3" s="98"/>
+      <c r="X3" s="98"/>
+      <c r="Y3" s="98"/>
+      <c r="Z3" s="98"/>
+      <c r="AA3" s="98"/>
+      <c r="AB3" s="98"/>
+      <c r="AC3" s="98"/>
+      <c r="AD3" s="98"/>
+      <c r="AE3" s="98"/>
+      <c r="AF3" s="98"/>
+      <c r="AG3" s="98"/>
+      <c r="AH3" s="98"/>
+      <c r="AI3" s="98"/>
+      <c r="AJ3" s="98"/>
+      <c r="AK3" s="98"/>
+      <c r="AL3" s="98"/>
+      <c r="AM3" s="98"/>
+      <c r="AN3" s="98"/>
+      <c r="AO3" s="98"/>
+      <c r="AP3" s="98"/>
+      <c r="AQ3" s="98"/>
+      <c r="AR3" s="98"/>
+      <c r="AS3" s="98"/>
+      <c r="AT3" s="98"/>
+      <c r="AU3" s="98"/>
+      <c r="AV3" s="98"/>
+      <c r="AW3" s="98"/>
+      <c r="AX3" s="98"/>
+      <c r="AY3" s="98"/>
+      <c r="AZ3" s="98"/>
+      <c r="BA3" s="98"/>
+      <c r="BB3" s="98"/>
+      <c r="BC3" s="98"/>
+      <c r="BD3" s="98"/>
+      <c r="BE3" s="98"/>
+      <c r="BF3" s="98"/>
+      <c r="BG3" s="98"/>
+      <c r="BH3" s="98"/>
+      <c r="BI3" s="98"/>
+      <c r="BJ3" s="98"/>
+      <c r="BK3" s="98"/>
+      <c r="BL3" s="98"/>
+      <c r="BM3" s="98"/>
+      <c r="BN3" s="98"/>
+      <c r="BO3" s="98"/>
+      <c r="BP3" s="98"/>
+      <c r="BQ3" s="98"/>
+      <c r="BR3" s="98"/>
+      <c r="BS3" s="98"/>
+      <c r="BT3" s="98"/>
+      <c r="BU3" s="98"/>
+      <c r="BV3" s="98"/>
+      <c r="BW3" s="98"/>
+      <c r="BX3" s="98"/>
+      <c r="BY3" s="98"/>
+      <c r="BZ3" s="98"/>
+      <c r="CA3" s="98"/>
+      <c r="CB3" s="98"/>
+      <c r="CC3" s="98"/>
+      <c r="CD3" s="98"/>
+      <c r="CE3" s="98"/>
+      <c r="CF3" s="98"/>
+      <c r="CG3" s="98"/>
+      <c r="CH3" s="98"/>
+      <c r="CI3" s="98"/>
+      <c r="CJ3" s="99"/>
+      <c r="CK3" s="97">
         <v>2025</v>
       </c>
-      <c r="CL3" s="137"/>
-      <c r="CM3" s="137"/>
-      <c r="CN3" s="137"/>
-      <c r="CO3" s="137"/>
-      <c r="CP3" s="137"/>
-      <c r="CQ3" s="137"/>
-      <c r="CR3" s="137"/>
-      <c r="CS3" s="137"/>
-      <c r="CT3" s="137"/>
-      <c r="CU3" s="137"/>
-      <c r="CV3" s="137"/>
-      <c r="CW3" s="137"/>
-      <c r="CX3" s="137"/>
-      <c r="CY3" s="137"/>
-      <c r="CZ3" s="137"/>
-      <c r="DA3" s="137"/>
-      <c r="DB3" s="137"/>
-      <c r="DC3" s="137"/>
-      <c r="DD3" s="137"/>
-      <c r="DE3" s="137"/>
-      <c r="DF3" s="137"/>
-      <c r="DG3" s="137"/>
-      <c r="DH3" s="137"/>
-      <c r="DI3" s="137"/>
-      <c r="DJ3" s="137"/>
-      <c r="DK3" s="137"/>
-      <c r="DL3" s="137"/>
-      <c r="DM3" s="137"/>
-      <c r="DN3" s="137"/>
-      <c r="DO3" s="138"/>
+      <c r="CL3" s="98"/>
+      <c r="CM3" s="98"/>
+      <c r="CN3" s="98"/>
+      <c r="CO3" s="98"/>
+      <c r="CP3" s="98"/>
+      <c r="CQ3" s="98"/>
+      <c r="CR3" s="98"/>
+      <c r="CS3" s="98"/>
+      <c r="CT3" s="98"/>
+      <c r="CU3" s="98"/>
+      <c r="CV3" s="98"/>
+      <c r="CW3" s="98"/>
+      <c r="CX3" s="98"/>
+      <c r="CY3" s="98"/>
+      <c r="CZ3" s="98"/>
+      <c r="DA3" s="98"/>
+      <c r="DB3" s="98"/>
+      <c r="DC3" s="98"/>
+      <c r="DD3" s="98"/>
+      <c r="DE3" s="98"/>
+      <c r="DF3" s="98"/>
+      <c r="DG3" s="98"/>
+      <c r="DH3" s="98"/>
+      <c r="DI3" s="98"/>
+      <c r="DJ3" s="98"/>
+      <c r="DK3" s="98"/>
+      <c r="DL3" s="98"/>
+      <c r="DM3" s="98"/>
+      <c r="DN3" s="98"/>
+      <c r="DO3" s="99"/>
       <c r="DP3" s="1"/>
     </row>
     <row r="4" spans="1:120" ht="18" customHeight="1">
@@ -2219,124 +2220,124 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="J4" s="136">
+      <c r="J4" s="97">
         <v>10</v>
       </c>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137"/>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137"/>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137"/>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137"/>
-      <c r="V4" s="137"/>
-      <c r="W4" s="137"/>
-      <c r="X4" s="137"/>
-      <c r="Y4" s="137"/>
-      <c r="Z4" s="137"/>
-      <c r="AA4" s="138"/>
-      <c r="AB4" s="136">
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="98"/>
+      <c r="P4" s="98"/>
+      <c r="Q4" s="98"/>
+      <c r="R4" s="98"/>
+      <c r="S4" s="98"/>
+      <c r="T4" s="98"/>
+      <c r="U4" s="98"/>
+      <c r="V4" s="98"/>
+      <c r="W4" s="98"/>
+      <c r="X4" s="98"/>
+      <c r="Y4" s="98"/>
+      <c r="Z4" s="98"/>
+      <c r="AA4" s="99"/>
+      <c r="AB4" s="97">
         <v>11</v>
       </c>
-      <c r="AC4" s="137"/>
-      <c r="AD4" s="137"/>
-      <c r="AE4" s="137"/>
-      <c r="AF4" s="137"/>
-      <c r="AG4" s="137"/>
-      <c r="AH4" s="137"/>
-      <c r="AI4" s="137"/>
-      <c r="AJ4" s="137"/>
-      <c r="AK4" s="137"/>
-      <c r="AL4" s="137"/>
-      <c r="AM4" s="137"/>
-      <c r="AN4" s="137"/>
-      <c r="AO4" s="137"/>
-      <c r="AP4" s="137"/>
-      <c r="AQ4" s="137"/>
-      <c r="AR4" s="137"/>
-      <c r="AS4" s="137"/>
-      <c r="AT4" s="137"/>
-      <c r="AU4" s="137"/>
-      <c r="AV4" s="137"/>
-      <c r="AW4" s="137"/>
-      <c r="AX4" s="137"/>
-      <c r="AY4" s="137"/>
-      <c r="AZ4" s="137"/>
-      <c r="BA4" s="137"/>
-      <c r="BB4" s="137"/>
-      <c r="BC4" s="137"/>
-      <c r="BD4" s="137"/>
-      <c r="BE4" s="138"/>
-      <c r="BF4" s="136">
+      <c r="AC4" s="98"/>
+      <c r="AD4" s="98"/>
+      <c r="AE4" s="98"/>
+      <c r="AF4" s="98"/>
+      <c r="AG4" s="98"/>
+      <c r="AH4" s="98"/>
+      <c r="AI4" s="98"/>
+      <c r="AJ4" s="98"/>
+      <c r="AK4" s="98"/>
+      <c r="AL4" s="98"/>
+      <c r="AM4" s="98"/>
+      <c r="AN4" s="98"/>
+      <c r="AO4" s="98"/>
+      <c r="AP4" s="98"/>
+      <c r="AQ4" s="98"/>
+      <c r="AR4" s="98"/>
+      <c r="AS4" s="98"/>
+      <c r="AT4" s="98"/>
+      <c r="AU4" s="98"/>
+      <c r="AV4" s="98"/>
+      <c r="AW4" s="98"/>
+      <c r="AX4" s="98"/>
+      <c r="AY4" s="98"/>
+      <c r="AZ4" s="98"/>
+      <c r="BA4" s="98"/>
+      <c r="BB4" s="98"/>
+      <c r="BC4" s="98"/>
+      <c r="BD4" s="98"/>
+      <c r="BE4" s="99"/>
+      <c r="BF4" s="97">
         <v>12</v>
       </c>
-      <c r="BG4" s="137"/>
-      <c r="BH4" s="137"/>
-      <c r="BI4" s="137"/>
-      <c r="BJ4" s="137"/>
-      <c r="BK4" s="137"/>
-      <c r="BL4" s="137"/>
-      <c r="BM4" s="137"/>
-      <c r="BN4" s="137"/>
-      <c r="BO4" s="137"/>
-      <c r="BP4" s="137"/>
-      <c r="BQ4" s="137"/>
-      <c r="BR4" s="137"/>
-      <c r="BS4" s="137"/>
-      <c r="BT4" s="137"/>
-      <c r="BU4" s="137"/>
-      <c r="BV4" s="137"/>
-      <c r="BW4" s="137"/>
-      <c r="BX4" s="137"/>
-      <c r="BY4" s="137"/>
-      <c r="BZ4" s="137"/>
-      <c r="CA4" s="137"/>
-      <c r="CB4" s="137"/>
-      <c r="CC4" s="137"/>
-      <c r="CD4" s="137"/>
-      <c r="CE4" s="137"/>
-      <c r="CF4" s="137"/>
-      <c r="CG4" s="137"/>
-      <c r="CH4" s="137"/>
-      <c r="CI4" s="137"/>
-      <c r="CJ4" s="138"/>
-      <c r="CK4" s="136">
+      <c r="BG4" s="98"/>
+      <c r="BH4" s="98"/>
+      <c r="BI4" s="98"/>
+      <c r="BJ4" s="98"/>
+      <c r="BK4" s="98"/>
+      <c r="BL4" s="98"/>
+      <c r="BM4" s="98"/>
+      <c r="BN4" s="98"/>
+      <c r="BO4" s="98"/>
+      <c r="BP4" s="98"/>
+      <c r="BQ4" s="98"/>
+      <c r="BR4" s="98"/>
+      <c r="BS4" s="98"/>
+      <c r="BT4" s="98"/>
+      <c r="BU4" s="98"/>
+      <c r="BV4" s="98"/>
+      <c r="BW4" s="98"/>
+      <c r="BX4" s="98"/>
+      <c r="BY4" s="98"/>
+      <c r="BZ4" s="98"/>
+      <c r="CA4" s="98"/>
+      <c r="CB4" s="98"/>
+      <c r="CC4" s="98"/>
+      <c r="CD4" s="98"/>
+      <c r="CE4" s="98"/>
+      <c r="CF4" s="98"/>
+      <c r="CG4" s="98"/>
+      <c r="CH4" s="98"/>
+      <c r="CI4" s="98"/>
+      <c r="CJ4" s="99"/>
+      <c r="CK4" s="97">
         <v>1</v>
       </c>
-      <c r="CL4" s="137"/>
-      <c r="CM4" s="137"/>
-      <c r="CN4" s="137"/>
-      <c r="CO4" s="137"/>
-      <c r="CP4" s="137"/>
-      <c r="CQ4" s="137"/>
-      <c r="CR4" s="137"/>
-      <c r="CS4" s="137"/>
-      <c r="CT4" s="137"/>
-      <c r="CU4" s="137"/>
-      <c r="CV4" s="137"/>
-      <c r="CW4" s="137"/>
-      <c r="CX4" s="137"/>
-      <c r="CY4" s="137"/>
-      <c r="CZ4" s="137"/>
-      <c r="DA4" s="137"/>
-      <c r="DB4" s="137"/>
-      <c r="DC4" s="137"/>
-      <c r="DD4" s="137"/>
-      <c r="DE4" s="137"/>
-      <c r="DF4" s="137"/>
-      <c r="DG4" s="137"/>
-      <c r="DH4" s="137"/>
-      <c r="DI4" s="137"/>
-      <c r="DJ4" s="137"/>
-      <c r="DK4" s="137"/>
-      <c r="DL4" s="137"/>
-      <c r="DM4" s="137"/>
-      <c r="DN4" s="137"/>
-      <c r="DO4" s="138"/>
+      <c r="CL4" s="98"/>
+      <c r="CM4" s="98"/>
+      <c r="CN4" s="98"/>
+      <c r="CO4" s="98"/>
+      <c r="CP4" s="98"/>
+      <c r="CQ4" s="98"/>
+      <c r="CR4" s="98"/>
+      <c r="CS4" s="98"/>
+      <c r="CT4" s="98"/>
+      <c r="CU4" s="98"/>
+      <c r="CV4" s="98"/>
+      <c r="CW4" s="98"/>
+      <c r="CX4" s="98"/>
+      <c r="CY4" s="98"/>
+      <c r="CZ4" s="98"/>
+      <c r="DA4" s="98"/>
+      <c r="DB4" s="98"/>
+      <c r="DC4" s="98"/>
+      <c r="DD4" s="98"/>
+      <c r="DE4" s="98"/>
+      <c r="DF4" s="98"/>
+      <c r="DG4" s="98"/>
+      <c r="DH4" s="98"/>
+      <c r="DI4" s="98"/>
+      <c r="DJ4" s="98"/>
+      <c r="DK4" s="98"/>
+      <c r="DL4" s="98"/>
+      <c r="DM4" s="98"/>
+      <c r="DN4" s="98"/>
+      <c r="DO4" s="99"/>
       <c r="DP4" s="6"/>
     </row>
     <row r="5" spans="1:120" ht="18" customHeight="1">
@@ -3131,18 +3132,18 @@
     </row>
     <row r="7" spans="1:120" ht="9.75" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="139" t="s">
+      <c r="B7" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="117"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="140"/>
-      <c r="H7" s="115" t="s">
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="88"/>
+      <c r="H7" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="115" t="s">
+      <c r="I7" s="102" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="38"/>
@@ -3259,14 +3260,14 @@
     </row>
     <row r="8" spans="1:120" ht="9.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="124"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="115"/>
-      <c r="I8" s="115"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="79"/>
+      <c r="D8" s="79"/>
+      <c r="E8" s="79"/>
+      <c r="F8" s="79"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="102"/>
+      <c r="I8" s="102"/>
       <c r="J8" s="39"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
@@ -3382,15 +3383,15 @@
     <row r="9" spans="1:120" ht="9.75" customHeight="1">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
-      <c r="C9" s="141" t="s">
+      <c r="C9" s="101" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="129"/>
-      <c r="E9" s="129"/>
-      <c r="F9" s="129"/>
-      <c r="G9" s="127"/>
-      <c r="H9" s="114"/>
-      <c r="I9" s="114"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="90"/>
+      <c r="F9" s="90"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="103"/>
       <c r="J9" s="42"/>
       <c r="K9" s="42"/>
       <c r="L9" s="44"/>
@@ -3506,13 +3507,13 @@
     <row r="10" spans="1:120" ht="9.75" customHeight="1">
       <c r="A10" s="16"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="119"/>
-      <c r="D10" s="120"/>
-      <c r="E10" s="120"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="114"/>
-      <c r="I10" s="114"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="103"/>
+      <c r="I10" s="103"/>
       <c r="J10" s="46"/>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
@@ -3628,15 +3629,15 @@
     <row r="11" spans="1:120" ht="9.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="142" t="s">
+      <c r="C11" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="129"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="114"/>
-      <c r="I11" s="114"/>
+      <c r="D11" s="90"/>
+      <c r="E11" s="90"/>
+      <c r="F11" s="90"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="103"/>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
       <c r="L11" s="44"/>
@@ -3752,13 +3753,13 @@
     <row r="12" spans="1:120" ht="9.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="119"/>
-      <c r="D12" s="120"/>
-      <c r="E12" s="120"/>
-      <c r="F12" s="120"/>
-      <c r="G12" s="121"/>
-      <c r="H12" s="114"/>
-      <c r="I12" s="114"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="79"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="103"/>
+      <c r="I12" s="103"/>
       <c r="J12" s="46"/>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
@@ -3875,16 +3876,16 @@
       <c r="A13" s="1"/>
       <c r="B13" s="18"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="143" t="s">
+      <c r="D13" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="117"/>
-      <c r="F13" s="117"/>
-      <c r="G13" s="140"/>
-      <c r="H13" s="113" t="s">
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="88"/>
+      <c r="H13" s="115" t="s">
         <v>40</v>
       </c>
-      <c r="I13" s="82">
+      <c r="I13" s="106">
         <v>100</v>
       </c>
       <c r="J13" s="39"/>
@@ -4003,12 +4004,12 @@
       <c r="A14" s="1"/>
       <c r="B14" s="18"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="124"/>
-      <c r="E14" s="120"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="121"/>
-      <c r="H14" s="82"/>
-      <c r="I14" s="82"/>
+      <c r="D14" s="78"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="106"/>
+      <c r="I14" s="106"/>
       <c r="J14" s="39"/>
       <c r="K14" s="53"/>
       <c r="L14" s="15"/>
@@ -4125,16 +4126,16 @@
       <c r="A15" s="1"/>
       <c r="B15" s="18"/>
       <c r="C15" s="24"/>
-      <c r="D15" s="143" t="s">
+      <c r="D15" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="117"/>
-      <c r="F15" s="117"/>
-      <c r="G15" s="123"/>
-      <c r="H15" s="113" t="s">
+      <c r="E15" s="76"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="115" t="s">
         <v>40</v>
       </c>
-      <c r="I15" s="82">
+      <c r="I15" s="106">
         <v>100</v>
       </c>
       <c r="J15" s="14"/>
@@ -4253,12 +4254,12 @@
       <c r="A16" s="1"/>
       <c r="B16" s="18"/>
       <c r="C16" s="24"/>
-      <c r="D16" s="124"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="125"/>
-      <c r="H16" s="82"/>
-      <c r="I16" s="82"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="79"/>
+      <c r="G16" s="80"/>
+      <c r="H16" s="106"/>
+      <c r="I16" s="106"/>
       <c r="J16" s="14"/>
       <c r="K16" s="53"/>
       <c r="L16" s="15"/>
@@ -4375,16 +4376,16 @@
       <c r="A17" s="1"/>
       <c r="B17" s="18"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="143" t="s">
+      <c r="D17" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="117"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="123"/>
-      <c r="H17" s="113" t="s">
+      <c r="E17" s="76"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="115" t="s">
         <v>40</v>
       </c>
-      <c r="I17" s="82">
+      <c r="I17" s="106">
         <v>100</v>
       </c>
       <c r="J17" s="14"/>
@@ -4503,12 +4504,12 @@
       <c r="A18" s="1"/>
       <c r="B18" s="18"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="124"/>
-      <c r="E18" s="120"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="125"/>
-      <c r="H18" s="82"/>
-      <c r="I18" s="82"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="79"/>
+      <c r="F18" s="79"/>
+      <c r="G18" s="80"/>
+      <c r="H18" s="106"/>
+      <c r="I18" s="106"/>
       <c r="J18" s="14"/>
       <c r="K18" s="53"/>
       <c r="L18" s="15"/>
@@ -4625,16 +4626,16 @@
       <c r="A19" s="1"/>
       <c r="B19" s="18"/>
       <c r="C19" s="24"/>
-      <c r="D19" s="143" t="s">
+      <c r="D19" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="117"/>
-      <c r="F19" s="117"/>
-      <c r="G19" s="123"/>
-      <c r="H19" s="113" t="s">
+      <c r="E19" s="76"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="115" t="s">
         <v>40</v>
       </c>
-      <c r="I19" s="82">
+      <c r="I19" s="106">
         <v>100</v>
       </c>
       <c r="J19" s="14"/>
@@ -4753,12 +4754,12 @@
       <c r="A20" s="1"/>
       <c r="B20" s="18"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="124"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="125"/>
-      <c r="H20" s="82"/>
-      <c r="I20" s="82"/>
+      <c r="D20" s="78"/>
+      <c r="E20" s="79"/>
+      <c r="F20" s="79"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="106"/>
       <c r="J20" s="26"/>
       <c r="K20" s="54"/>
       <c r="L20" s="27"/>
@@ -4874,15 +4875,15 @@
     <row r="21" spans="1:120" ht="9.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="18"/>
-      <c r="C21" s="142" t="s">
+      <c r="C21" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="129"/>
-      <c r="E21" s="129"/>
-      <c r="F21" s="129"/>
-      <c r="G21" s="130"/>
-      <c r="H21" s="114"/>
-      <c r="I21" s="114"/>
+      <c r="D21" s="90"/>
+      <c r="E21" s="90"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="91"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="103"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="44"/>
@@ -4998,13 +4999,13 @@
     <row r="22" spans="1:120" ht="9.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="18"/>
-      <c r="C22" s="131"/>
-      <c r="D22" s="132"/>
-      <c r="E22" s="132"/>
-      <c r="F22" s="132"/>
-      <c r="G22" s="127"/>
-      <c r="H22" s="114"/>
-      <c r="I22" s="114"/>
+      <c r="C22" s="92"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="93"/>
+      <c r="F22" s="93"/>
+      <c r="G22" s="86"/>
+      <c r="H22" s="103"/>
+      <c r="I22" s="103"/>
       <c r="J22" s="46"/>
       <c r="K22" s="47"/>
       <c r="L22" s="47"/>
@@ -5121,16 +5122,16 @@
       <c r="A23" s="1"/>
       <c r="B23" s="28"/>
       <c r="C23" s="29"/>
-      <c r="D23" s="144" t="s">
+      <c r="D23" s="94" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="117"/>
-      <c r="F23" s="117"/>
-      <c r="G23" s="123"/>
-      <c r="H23" s="113" t="s">
+      <c r="E23" s="76"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="115" t="s">
         <v>46</v>
       </c>
-      <c r="I23" s="82">
+      <c r="I23" s="106">
         <v>100</v>
       </c>
       <c r="J23" s="14"/>
@@ -5249,12 +5250,12 @@
       <c r="A24" s="1"/>
       <c r="B24" s="18"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="124"/>
-      <c r="E24" s="120"/>
-      <c r="F24" s="120"/>
-      <c r="G24" s="125"/>
-      <c r="H24" s="82"/>
-      <c r="I24" s="82"/>
+      <c r="D24" s="78"/>
+      <c r="E24" s="79"/>
+      <c r="F24" s="79"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="106"/>
+      <c r="I24" s="106"/>
       <c r="J24" s="14"/>
       <c r="K24" s="15"/>
       <c r="L24" s="53"/>
@@ -5370,15 +5371,15 @@
     <row r="25" spans="1:120" ht="9.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="18"/>
-      <c r="C25" s="142" t="s">
+      <c r="C25" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="129"/>
-      <c r="E25" s="129"/>
-      <c r="F25" s="129"/>
-      <c r="G25" s="130"/>
-      <c r="H25" s="114"/>
-      <c r="I25" s="114"/>
+      <c r="D25" s="90"/>
+      <c r="E25" s="90"/>
+      <c r="F25" s="90"/>
+      <c r="G25" s="91"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="103"/>
       <c r="J25" s="42"/>
       <c r="K25" s="42"/>
       <c r="L25" s="44"/>
@@ -5494,13 +5495,13 @@
     <row r="26" spans="1:120" ht="9.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="18"/>
-      <c r="C26" s="119"/>
-      <c r="D26" s="120"/>
-      <c r="E26" s="120"/>
-      <c r="F26" s="120"/>
-      <c r="G26" s="121"/>
-      <c r="H26" s="114"/>
-      <c r="I26" s="114"/>
+      <c r="C26" s="85"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="79"/>
+      <c r="F26" s="79"/>
+      <c r="G26" s="83"/>
+      <c r="H26" s="103"/>
+      <c r="I26" s="103"/>
       <c r="J26" s="46"/>
       <c r="K26" s="47"/>
       <c r="L26" s="47"/>
@@ -5617,16 +5618,16 @@
       <c r="A27" s="1"/>
       <c r="B27" s="28"/>
       <c r="C27" s="29"/>
-      <c r="D27" s="144" t="s">
+      <c r="D27" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="117"/>
-      <c r="F27" s="117"/>
-      <c r="G27" s="123"/>
-      <c r="H27" s="113" t="s">
+      <c r="E27" s="76"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="I27" s="82">
+      <c r="I27" s="106">
         <v>100</v>
       </c>
       <c r="J27" s="14"/>
@@ -5745,12 +5746,12 @@
       <c r="A28" s="1"/>
       <c r="B28" s="28"/>
       <c r="C28" s="30"/>
-      <c r="D28" s="124"/>
-      <c r="E28" s="120"/>
-      <c r="F28" s="120"/>
-      <c r="G28" s="125"/>
-      <c r="H28" s="82"/>
-      <c r="I28" s="82"/>
+      <c r="D28" s="78"/>
+      <c r="E28" s="79"/>
+      <c r="F28" s="79"/>
+      <c r="G28" s="80"/>
+      <c r="H28" s="106"/>
+      <c r="I28" s="106"/>
       <c r="J28" s="14"/>
       <c r="K28" s="15"/>
       <c r="L28" s="15"/>
@@ -5867,16 +5868,16 @@
       <c r="A29" s="1"/>
       <c r="B29" s="28"/>
       <c r="C29" s="30"/>
-      <c r="D29" s="145" t="s">
+      <c r="D29" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="146"/>
-      <c r="F29" s="146"/>
-      <c r="G29" s="146"/>
-      <c r="H29" s="113" t="s">
+      <c r="E29" s="96"/>
+      <c r="F29" s="96"/>
+      <c r="G29" s="96"/>
+      <c r="H29" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="I29" s="82">
+      <c r="I29" s="106">
         <v>100</v>
       </c>
       <c r="J29" s="14"/>
@@ -5995,12 +5996,12 @@
       <c r="A30" s="1"/>
       <c r="B30" s="28"/>
       <c r="C30" s="31"/>
-      <c r="D30" s="124"/>
-      <c r="E30" s="120"/>
-      <c r="F30" s="120"/>
-      <c r="G30" s="120"/>
-      <c r="H30" s="82"/>
-      <c r="I30" s="82"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="79"/>
+      <c r="F30" s="79"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="106"/>
+      <c r="I30" s="106"/>
       <c r="J30" s="26"/>
       <c r="K30" s="27"/>
       <c r="L30" s="27"/>
@@ -6116,15 +6117,15 @@
     <row r="31" spans="1:120" ht="9.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="18"/>
-      <c r="C31" s="128" t="s">
+      <c r="C31" s="107" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="129"/>
-      <c r="E31" s="129"/>
-      <c r="F31" s="129"/>
-      <c r="G31" s="130"/>
-      <c r="H31" s="114"/>
-      <c r="I31" s="114"/>
+      <c r="D31" s="90"/>
+      <c r="E31" s="90"/>
+      <c r="F31" s="90"/>
+      <c r="G31" s="91"/>
+      <c r="H31" s="103"/>
+      <c r="I31" s="103"/>
       <c r="J31" s="42"/>
       <c r="K31" s="43"/>
       <c r="L31" s="44"/>
@@ -6240,13 +6241,13 @@
     <row r="32" spans="1:120" ht="9.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="18"/>
-      <c r="C32" s="131"/>
-      <c r="D32" s="132"/>
-      <c r="E32" s="132"/>
-      <c r="F32" s="132"/>
-      <c r="G32" s="127"/>
-      <c r="H32" s="114"/>
-      <c r="I32" s="114"/>
+      <c r="C32" s="92"/>
+      <c r="D32" s="93"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="93"/>
+      <c r="G32" s="86"/>
+      <c r="H32" s="103"/>
+      <c r="I32" s="103"/>
       <c r="J32" s="46"/>
       <c r="K32" s="47"/>
       <c r="L32" s="47"/>
@@ -6363,14 +6364,14 @@
       <c r="A33" s="1"/>
       <c r="B33" s="18"/>
       <c r="C33" s="32"/>
-      <c r="D33" s="133" t="s">
+      <c r="D33" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="117"/>
-      <c r="F33" s="117"/>
-      <c r="G33" s="118"/>
-      <c r="H33" s="114"/>
-      <c r="I33" s="114"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="103"/>
+      <c r="I33" s="103"/>
       <c r="J33" s="50"/>
       <c r="K33" s="51"/>
       <c r="L33" s="51"/>
@@ -6487,12 +6488,12 @@
       <c r="A34" s="1"/>
       <c r="B34" s="18"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="124"/>
-      <c r="E34" s="120"/>
-      <c r="F34" s="120"/>
-      <c r="G34" s="121"/>
-      <c r="H34" s="114"/>
-      <c r="I34" s="114"/>
+      <c r="D34" s="78"/>
+      <c r="E34" s="79"/>
+      <c r="F34" s="79"/>
+      <c r="G34" s="83"/>
+      <c r="H34" s="103"/>
+      <c r="I34" s="103"/>
       <c r="J34" s="52"/>
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
@@ -6610,15 +6611,15 @@
       <c r="B35" s="18"/>
       <c r="C35" s="1"/>
       <c r="D35" s="33"/>
-      <c r="E35" s="134" t="s">
+      <c r="E35" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="117"/>
-      <c r="G35" s="123"/>
-      <c r="H35" s="113" t="s">
+      <c r="F35" s="76"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="115" t="s">
         <v>45</v>
       </c>
-      <c r="I35" s="82">
+      <c r="I35" s="106">
         <v>100</v>
       </c>
       <c r="J35" s="14"/>
@@ -6738,11 +6739,11 @@
       <c r="B36" s="18"/>
       <c r="C36" s="1"/>
       <c r="D36" s="34"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="120"/>
-      <c r="G36" s="125"/>
-      <c r="H36" s="82"/>
-      <c r="I36" s="82"/>
+      <c r="E36" s="78"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="80"/>
+      <c r="H36" s="106"/>
+      <c r="I36" s="106"/>
       <c r="J36" s="14"/>
       <c r="K36" s="15"/>
       <c r="L36" s="15"/>
@@ -6860,15 +6861,15 @@
       <c r="B37" s="18"/>
       <c r="C37" s="1"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="134" t="s">
+      <c r="E37" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="F37" s="117"/>
-      <c r="G37" s="123"/>
-      <c r="H37" s="113" t="s">
+      <c r="F37" s="76"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="I37" s="82">
+      <c r="I37" s="106">
         <v>100</v>
       </c>
       <c r="J37" s="14"/>
@@ -6988,11 +6989,11 @@
       <c r="B38" s="18"/>
       <c r="C38" s="1"/>
       <c r="D38" s="35"/>
-      <c r="E38" s="124"/>
-      <c r="F38" s="120"/>
-      <c r="G38" s="125"/>
-      <c r="H38" s="82"/>
-      <c r="I38" s="82"/>
+      <c r="E38" s="78"/>
+      <c r="F38" s="79"/>
+      <c r="G38" s="80"/>
+      <c r="H38" s="106"/>
+      <c r="I38" s="106"/>
       <c r="J38" s="26"/>
       <c r="K38" s="27"/>
       <c r="L38" s="27"/>
@@ -7109,14 +7110,14 @@
       <c r="A39" s="1"/>
       <c r="B39" s="18"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="135" t="s">
+      <c r="D39" s="108" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="129"/>
-      <c r="F39" s="129"/>
-      <c r="G39" s="130"/>
-      <c r="H39" s="114"/>
-      <c r="I39" s="114"/>
+      <c r="E39" s="90"/>
+      <c r="F39" s="90"/>
+      <c r="G39" s="91"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="103"/>
       <c r="J39" s="50"/>
       <c r="K39" s="51"/>
       <c r="L39" s="51"/>
@@ -7233,12 +7234,12 @@
       <c r="A40" s="1"/>
       <c r="B40" s="18"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="124"/>
-      <c r="E40" s="120"/>
-      <c r="F40" s="120"/>
-      <c r="G40" s="121"/>
-      <c r="H40" s="114"/>
-      <c r="I40" s="114"/>
+      <c r="D40" s="78"/>
+      <c r="E40" s="79"/>
+      <c r="F40" s="79"/>
+      <c r="G40" s="83"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="103"/>
       <c r="J40" s="52"/>
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
@@ -7356,15 +7357,15 @@
       <c r="B41" s="18"/>
       <c r="C41" s="1"/>
       <c r="D41" s="33"/>
-      <c r="E41" s="134" t="s">
+      <c r="E41" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="117"/>
-      <c r="G41" s="123"/>
-      <c r="H41" s="113" t="s">
+      <c r="F41" s="76"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="I41" s="82">
+      <c r="I41" s="106">
         <v>100</v>
       </c>
       <c r="J41" s="14"/>
@@ -7484,11 +7485,11 @@
       <c r="B42" s="18"/>
       <c r="C42" s="1"/>
       <c r="D42" s="34"/>
-      <c r="E42" s="124"/>
-      <c r="F42" s="120"/>
-      <c r="G42" s="125"/>
-      <c r="H42" s="82"/>
-      <c r="I42" s="82"/>
+      <c r="E42" s="78"/>
+      <c r="F42" s="79"/>
+      <c r="G42" s="80"/>
+      <c r="H42" s="106"/>
+      <c r="I42" s="106"/>
       <c r="J42" s="14"/>
       <c r="K42" s="15"/>
       <c r="L42" s="15"/>
@@ -7606,15 +7607,15 @@
       <c r="B43" s="18"/>
       <c r="C43" s="1"/>
       <c r="D43" s="34"/>
-      <c r="E43" s="134" t="s">
+      <c r="E43" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="117"/>
-      <c r="G43" s="123"/>
-      <c r="H43" s="113" t="s">
+      <c r="F43" s="76"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="115" t="s">
         <v>43</v>
       </c>
-      <c r="I43" s="82">
+      <c r="I43" s="106">
         <v>100</v>
       </c>
       <c r="J43" s="14"/>
@@ -7734,11 +7735,11 @@
       <c r="B44" s="18"/>
       <c r="C44" s="1"/>
       <c r="D44" s="34"/>
-      <c r="E44" s="124"/>
-      <c r="F44" s="120"/>
-      <c r="G44" s="125"/>
-      <c r="H44" s="82"/>
-      <c r="I44" s="82"/>
+      <c r="E44" s="78"/>
+      <c r="F44" s="79"/>
+      <c r="G44" s="80"/>
+      <c r="H44" s="106"/>
+      <c r="I44" s="106"/>
       <c r="J44" s="14"/>
       <c r="K44" s="15"/>
       <c r="L44" s="15"/>
@@ -7856,15 +7857,15 @@
       <c r="B45" s="18"/>
       <c r="C45" s="1"/>
       <c r="D45" s="34"/>
-      <c r="E45" s="134" t="s">
+      <c r="E45" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="117"/>
-      <c r="G45" s="123"/>
-      <c r="H45" s="113" t="s">
+      <c r="F45" s="76"/>
+      <c r="G45" s="77"/>
+      <c r="H45" s="115" t="s">
         <v>42</v>
       </c>
-      <c r="I45" s="82">
+      <c r="I45" s="106">
         <v>100</v>
       </c>
       <c r="J45" s="14"/>
@@ -7984,11 +7985,11 @@
       <c r="B46" s="18"/>
       <c r="C46" s="1"/>
       <c r="D46" s="34"/>
-      <c r="E46" s="124"/>
-      <c r="F46" s="120"/>
-      <c r="G46" s="125"/>
-      <c r="H46" s="82"/>
-      <c r="I46" s="82"/>
+      <c r="E46" s="78"/>
+      <c r="F46" s="79"/>
+      <c r="G46" s="80"/>
+      <c r="H46" s="106"/>
+      <c r="I46" s="106"/>
       <c r="J46" s="14"/>
       <c r="K46" s="15"/>
       <c r="L46" s="15"/>
@@ -8106,15 +8107,15 @@
       <c r="B47" s="18"/>
       <c r="C47" s="1"/>
       <c r="D47" s="34"/>
-      <c r="E47" s="134" t="s">
+      <c r="E47" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="F47" s="117"/>
-      <c r="G47" s="123"/>
-      <c r="H47" s="113" t="s">
+      <c r="F47" s="76"/>
+      <c r="G47" s="77"/>
+      <c r="H47" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="I47" s="82">
+      <c r="I47" s="106">
         <v>100</v>
       </c>
       <c r="J47" s="14"/>
@@ -8234,11 +8235,11 @@
       <c r="B48" s="18"/>
       <c r="C48" s="1"/>
       <c r="D48" s="34"/>
-      <c r="E48" s="124"/>
-      <c r="F48" s="120"/>
-      <c r="G48" s="125"/>
-      <c r="H48" s="82"/>
-      <c r="I48" s="82"/>
+      <c r="E48" s="78"/>
+      <c r="F48" s="79"/>
+      <c r="G48" s="80"/>
+      <c r="H48" s="106"/>
+      <c r="I48" s="106"/>
       <c r="J48" s="14"/>
       <c r="K48" s="15"/>
       <c r="L48" s="15"/>
@@ -8356,15 +8357,15 @@
       <c r="B49" s="18"/>
       <c r="C49" s="1"/>
       <c r="D49" s="34"/>
-      <c r="E49" s="134" t="s">
+      <c r="E49" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="117"/>
-      <c r="G49" s="123"/>
-      <c r="H49" s="113" t="s">
+      <c r="F49" s="76"/>
+      <c r="G49" s="77"/>
+      <c r="H49" s="115" t="s">
         <v>50</v>
       </c>
-      <c r="I49" s="82">
+      <c r="I49" s="106">
         <v>100</v>
       </c>
       <c r="J49" s="14"/>
@@ -8484,11 +8485,11 @@
       <c r="B50" s="18"/>
       <c r="C50" s="1"/>
       <c r="D50" s="34"/>
-      <c r="E50" s="124"/>
-      <c r="F50" s="120"/>
-      <c r="G50" s="125"/>
-      <c r="H50" s="82"/>
-      <c r="I50" s="82"/>
+      <c r="E50" s="78"/>
+      <c r="F50" s="79"/>
+      <c r="G50" s="80"/>
+      <c r="H50" s="106"/>
+      <c r="I50" s="106"/>
       <c r="J50" s="14"/>
       <c r="K50" s="15"/>
       <c r="L50" s="15"/>
@@ -8606,15 +8607,15 @@
       <c r="B51" s="18"/>
       <c r="C51" s="1"/>
       <c r="D51" s="34"/>
-      <c r="E51" s="134" t="s">
+      <c r="E51" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="117"/>
-      <c r="G51" s="123"/>
-      <c r="H51" s="113" t="s">
+      <c r="F51" s="76"/>
+      <c r="G51" s="77"/>
+      <c r="H51" s="115" t="s">
         <v>47</v>
       </c>
-      <c r="I51" s="82">
+      <c r="I51" s="106">
         <v>100</v>
       </c>
       <c r="J51" s="14"/>
@@ -8734,11 +8735,11 @@
       <c r="B52" s="18"/>
       <c r="C52" s="1"/>
       <c r="D52" s="34"/>
-      <c r="E52" s="124"/>
-      <c r="F52" s="120"/>
-      <c r="G52" s="125"/>
-      <c r="H52" s="82"/>
-      <c r="I52" s="82"/>
+      <c r="E52" s="78"/>
+      <c r="F52" s="79"/>
+      <c r="G52" s="80"/>
+      <c r="H52" s="106"/>
+      <c r="I52" s="106"/>
       <c r="J52" s="26"/>
       <c r="K52" s="27"/>
       <c r="L52" s="27"/>
@@ -8855,14 +8856,14 @@
       <c r="A53" s="1"/>
       <c r="B53" s="18"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="133" t="s">
+      <c r="D53" s="81" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="117"/>
-      <c r="F53" s="117"/>
-      <c r="G53" s="118"/>
-      <c r="H53" s="114"/>
-      <c r="I53" s="114"/>
+      <c r="E53" s="76"/>
+      <c r="F53" s="76"/>
+      <c r="G53" s="82"/>
+      <c r="H53" s="103"/>
+      <c r="I53" s="103"/>
       <c r="J53" s="50"/>
       <c r="K53" s="51"/>
       <c r="L53" s="51"/>
@@ -8979,12 +8980,12 @@
       <c r="A54" s="1"/>
       <c r="B54" s="18"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="124"/>
-      <c r="E54" s="120"/>
-      <c r="F54" s="120"/>
-      <c r="G54" s="121"/>
-      <c r="H54" s="114"/>
-      <c r="I54" s="114"/>
+      <c r="D54" s="78"/>
+      <c r="E54" s="79"/>
+      <c r="F54" s="79"/>
+      <c r="G54" s="83"/>
+      <c r="H54" s="103"/>
+      <c r="I54" s="103"/>
       <c r="J54" s="52"/>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -9102,15 +9103,15 @@
       <c r="B55" s="18"/>
       <c r="C55" s="1"/>
       <c r="D55" s="34"/>
-      <c r="E55" s="134" t="s">
+      <c r="E55" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="117"/>
-      <c r="G55" s="123"/>
-      <c r="H55" s="113" t="s">
+      <c r="F55" s="76"/>
+      <c r="G55" s="77"/>
+      <c r="H55" s="115" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="82">
+      <c r="I55" s="106">
         <v>100</v>
       </c>
       <c r="J55" s="14"/>
@@ -9230,11 +9231,11 @@
       <c r="B56" s="18"/>
       <c r="C56" s="1"/>
       <c r="D56" s="34"/>
-      <c r="E56" s="124"/>
-      <c r="F56" s="120"/>
-      <c r="G56" s="125"/>
-      <c r="H56" s="82"/>
-      <c r="I56" s="82"/>
+      <c r="E56" s="78"/>
+      <c r="F56" s="79"/>
+      <c r="G56" s="80"/>
+      <c r="H56" s="106"/>
+      <c r="I56" s="106"/>
       <c r="J56" s="14"/>
       <c r="K56" s="15"/>
       <c r="L56" s="15"/>
@@ -9352,15 +9353,15 @@
       <c r="B57" s="18"/>
       <c r="C57" s="1"/>
       <c r="D57" s="34"/>
-      <c r="E57" s="134" t="s">
+      <c r="E57" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="F57" s="117"/>
-      <c r="G57" s="123"/>
-      <c r="H57" s="113" t="s">
+      <c r="F57" s="76"/>
+      <c r="G57" s="77"/>
+      <c r="H57" s="115" t="s">
         <v>51</v>
       </c>
-      <c r="I57" s="82">
+      <c r="I57" s="106">
         <v>100</v>
       </c>
       <c r="J57" s="14"/>
@@ -9480,11 +9481,11 @@
       <c r="B58" s="18"/>
       <c r="C58" s="1"/>
       <c r="D58" s="34"/>
-      <c r="E58" s="124"/>
-      <c r="F58" s="120"/>
-      <c r="G58" s="125"/>
-      <c r="H58" s="82"/>
-      <c r="I58" s="82"/>
+      <c r="E58" s="78"/>
+      <c r="F58" s="79"/>
+      <c r="G58" s="80"/>
+      <c r="H58" s="106"/>
+      <c r="I58" s="106"/>
       <c r="J58" s="14"/>
       <c r="K58" s="15"/>
       <c r="L58" s="15"/>
@@ -9602,15 +9603,15 @@
       <c r="B59" s="18"/>
       <c r="C59" s="1"/>
       <c r="D59" s="34"/>
-      <c r="E59" s="134" t="s">
+      <c r="E59" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="F59" s="117"/>
-      <c r="G59" s="123"/>
-      <c r="H59" s="113" t="s">
+      <c r="F59" s="76"/>
+      <c r="G59" s="77"/>
+      <c r="H59" s="115" t="s">
         <v>49</v>
       </c>
-      <c r="I59" s="82">
+      <c r="I59" s="106">
         <v>100</v>
       </c>
       <c r="J59" s="14"/>
@@ -9730,11 +9731,11 @@
       <c r="B60" s="18"/>
       <c r="C60" s="1"/>
       <c r="D60" s="34"/>
-      <c r="E60" s="124"/>
-      <c r="F60" s="120"/>
-      <c r="G60" s="125"/>
-      <c r="H60" s="82"/>
-      <c r="I60" s="82"/>
+      <c r="E60" s="78"/>
+      <c r="F60" s="79"/>
+      <c r="G60" s="80"/>
+      <c r="H60" s="106"/>
+      <c r="I60" s="106"/>
       <c r="J60" s="14"/>
       <c r="K60" s="15"/>
       <c r="L60" s="15"/>
@@ -9852,15 +9853,15 @@
       <c r="B61" s="18"/>
       <c r="C61" s="1"/>
       <c r="D61" s="34"/>
-      <c r="E61" s="134" t="s">
+      <c r="E61" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="F61" s="117"/>
-      <c r="G61" s="123"/>
-      <c r="H61" s="113" t="s">
+      <c r="F61" s="76"/>
+      <c r="G61" s="77"/>
+      <c r="H61" s="115" t="s">
         <v>49</v>
       </c>
-      <c r="I61" s="82">
+      <c r="I61" s="106">
         <v>100</v>
       </c>
       <c r="J61" s="14"/>
@@ -9980,11 +9981,11 @@
       <c r="B62" s="18"/>
       <c r="C62" s="1"/>
       <c r="D62" s="34"/>
-      <c r="E62" s="124"/>
-      <c r="F62" s="120"/>
-      <c r="G62" s="125"/>
-      <c r="H62" s="82"/>
-      <c r="I62" s="82"/>
+      <c r="E62" s="78"/>
+      <c r="F62" s="79"/>
+      <c r="G62" s="80"/>
+      <c r="H62" s="106"/>
+      <c r="I62" s="106"/>
       <c r="J62" s="26"/>
       <c r="K62" s="27"/>
       <c r="L62" s="27"/>
@@ -10101,14 +10102,14 @@
       <c r="A63" s="1"/>
       <c r="B63" s="18"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="133" t="s">
+      <c r="D63" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="117"/>
-      <c r="F63" s="117"/>
-      <c r="G63" s="118"/>
-      <c r="H63" s="114"/>
-      <c r="I63" s="114"/>
+      <c r="E63" s="76"/>
+      <c r="F63" s="76"/>
+      <c r="G63" s="82"/>
+      <c r="H63" s="103"/>
+      <c r="I63" s="103"/>
       <c r="J63" s="50"/>
       <c r="K63" s="51"/>
       <c r="L63" s="51"/>
@@ -10225,12 +10226,12 @@
       <c r="A64" s="1"/>
       <c r="B64" s="18"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="124"/>
-      <c r="E64" s="120"/>
-      <c r="F64" s="120"/>
-      <c r="G64" s="121"/>
-      <c r="H64" s="114"/>
-      <c r="I64" s="114"/>
+      <c r="D64" s="78"/>
+      <c r="E64" s="79"/>
+      <c r="F64" s="79"/>
+      <c r="G64" s="83"/>
+      <c r="H64" s="103"/>
+      <c r="I64" s="103"/>
       <c r="J64" s="52"/>
       <c r="K64" s="49"/>
       <c r="L64" s="49"/>
@@ -10348,15 +10349,15 @@
       <c r="B65" s="18"/>
       <c r="C65" s="1"/>
       <c r="D65" s="34"/>
-      <c r="E65" s="134" t="s">
+      <c r="E65" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="F65" s="117"/>
-      <c r="G65" s="123"/>
-      <c r="H65" s="113" t="s">
+      <c r="F65" s="76"/>
+      <c r="G65" s="77"/>
+      <c r="H65" s="115" t="s">
         <v>52</v>
       </c>
-      <c r="I65" s="82">
+      <c r="I65" s="106">
         <v>100</v>
       </c>
       <c r="J65" s="14"/>
@@ -10476,11 +10477,11 @@
       <c r="B66" s="18"/>
       <c r="C66" s="1"/>
       <c r="D66" s="34"/>
-      <c r="E66" s="124"/>
-      <c r="F66" s="120"/>
-      <c r="G66" s="125"/>
-      <c r="H66" s="82"/>
-      <c r="I66" s="82"/>
+      <c r="E66" s="78"/>
+      <c r="F66" s="79"/>
+      <c r="G66" s="80"/>
+      <c r="H66" s="106"/>
+      <c r="I66" s="106"/>
       <c r="J66" s="14"/>
       <c r="K66" s="15"/>
       <c r="L66" s="15"/>
@@ -10598,15 +10599,15 @@
       <c r="B67" s="18"/>
       <c r="C67" s="1"/>
       <c r="D67" s="34"/>
-      <c r="E67" s="134" t="s">
+      <c r="E67" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="F67" s="117"/>
-      <c r="G67" s="123"/>
-      <c r="H67" s="113" t="s">
+      <c r="F67" s="76"/>
+      <c r="G67" s="77"/>
+      <c r="H67" s="115" t="s">
         <v>53</v>
       </c>
-      <c r="I67" s="82">
+      <c r="I67" s="106">
         <v>100</v>
       </c>
       <c r="J67" s="14"/>
@@ -10726,11 +10727,11 @@
       <c r="B68" s="18"/>
       <c r="C68" s="1"/>
       <c r="D68" s="34"/>
-      <c r="E68" s="124"/>
-      <c r="F68" s="120"/>
-      <c r="G68" s="125"/>
-      <c r="H68" s="82"/>
-      <c r="I68" s="82"/>
+      <c r="E68" s="78"/>
+      <c r="F68" s="79"/>
+      <c r="G68" s="80"/>
+      <c r="H68" s="106"/>
+      <c r="I68" s="106"/>
       <c r="J68" s="14"/>
       <c r="K68" s="15"/>
       <c r="L68" s="15"/>
@@ -10848,15 +10849,15 @@
       <c r="B69" s="18"/>
       <c r="C69" s="1"/>
       <c r="D69" s="34"/>
-      <c r="E69" s="134" t="s">
+      <c r="E69" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="F69" s="117"/>
-      <c r="G69" s="123"/>
-      <c r="H69" s="113" t="s">
+      <c r="F69" s="76"/>
+      <c r="G69" s="77"/>
+      <c r="H69" s="115" t="s">
         <v>54</v>
       </c>
-      <c r="I69" s="82">
+      <c r="I69" s="106">
         <v>100</v>
       </c>
       <c r="J69" s="14"/>
@@ -10976,11 +10977,11 @@
       <c r="B70" s="18"/>
       <c r="C70" s="1"/>
       <c r="D70" s="34"/>
-      <c r="E70" s="124"/>
-      <c r="F70" s="120"/>
-      <c r="G70" s="125"/>
-      <c r="H70" s="82"/>
-      <c r="I70" s="82"/>
+      <c r="E70" s="78"/>
+      <c r="F70" s="79"/>
+      <c r="G70" s="80"/>
+      <c r="H70" s="106"/>
+      <c r="I70" s="106"/>
       <c r="J70" s="14"/>
       <c r="K70" s="15"/>
       <c r="L70" s="15"/>
@@ -11098,15 +11099,15 @@
       <c r="B71" s="18"/>
       <c r="C71" s="1"/>
       <c r="D71" s="34"/>
-      <c r="E71" s="134" t="s">
+      <c r="E71" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="F71" s="117"/>
-      <c r="G71" s="123"/>
-      <c r="H71" s="113" t="s">
+      <c r="F71" s="76"/>
+      <c r="G71" s="77"/>
+      <c r="H71" s="115" t="s">
         <v>55</v>
       </c>
-      <c r="I71" s="82"/>
+      <c r="I71" s="106"/>
       <c r="J71" s="14"/>
       <c r="K71" s="15"/>
       <c r="L71" s="15"/>
@@ -11224,11 +11225,11 @@
       <c r="B72" s="18"/>
       <c r="C72" s="1"/>
       <c r="D72" s="35"/>
-      <c r="E72" s="124"/>
-      <c r="F72" s="120"/>
-      <c r="G72" s="125"/>
-      <c r="H72" s="82"/>
-      <c r="I72" s="82"/>
+      <c r="E72" s="78"/>
+      <c r="F72" s="79"/>
+      <c r="G72" s="80"/>
+      <c r="H72" s="106"/>
+      <c r="I72" s="106"/>
       <c r="J72" s="26"/>
       <c r="K72" s="27"/>
       <c r="L72" s="27"/>
@@ -11260,7 +11261,7 @@
       <c r="AL72" s="27"/>
       <c r="AM72" s="27"/>
       <c r="AN72" s="27"/>
-      <c r="AO72" s="27"/>
+      <c r="AO72" s="58"/>
       <c r="AP72" s="27"/>
       <c r="AQ72" s="27"/>
       <c r="AR72" s="27"/>
@@ -11344,17 +11345,17 @@
     <row r="73" spans="1:120" ht="9.75" customHeight="1">
       <c r="A73" s="16"/>
       <c r="B73" s="36"/>
-      <c r="C73" s="116" t="s">
+      <c r="C73" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="D73" s="117"/>
-      <c r="E73" s="117"/>
-      <c r="F73" s="117"/>
-      <c r="G73" s="118"/>
-      <c r="H73" s="113" t="s">
+      <c r="D73" s="76"/>
+      <c r="E73" s="76"/>
+      <c r="F73" s="76"/>
+      <c r="G73" s="82"/>
+      <c r="H73" s="115" t="s">
         <v>55</v>
       </c>
-      <c r="I73" s="82"/>
+      <c r="I73" s="106"/>
       <c r="J73" s="19"/>
       <c r="K73" s="20"/>
       <c r="L73" s="20"/>
@@ -11470,13 +11471,13 @@
     <row r="74" spans="1:120" ht="9.75" customHeight="1">
       <c r="A74" s="16"/>
       <c r="B74" s="36"/>
-      <c r="C74" s="119"/>
-      <c r="D74" s="120"/>
-      <c r="E74" s="120"/>
-      <c r="F74" s="120"/>
-      <c r="G74" s="121"/>
-      <c r="H74" s="82"/>
-      <c r="I74" s="82"/>
+      <c r="C74" s="85"/>
+      <c r="D74" s="79"/>
+      <c r="E74" s="79"/>
+      <c r="F74" s="79"/>
+      <c r="G74" s="83"/>
+      <c r="H74" s="106"/>
+      <c r="I74" s="106"/>
       <c r="J74" s="19"/>
       <c r="K74" s="20"/>
       <c r="L74" s="20"/>
@@ -11508,7 +11509,7 @@
       <c r="AL74" s="20"/>
       <c r="AM74" s="20"/>
       <c r="AN74" s="20"/>
-      <c r="AO74" s="20"/>
+      <c r="AO74" s="147"/>
       <c r="AP74" s="20"/>
       <c r="AQ74" s="21"/>
       <c r="AR74" s="21"/>
@@ -11592,17 +11593,17 @@
     <row r="75" spans="1:120" ht="9.75" customHeight="1">
       <c r="A75" s="16"/>
       <c r="B75" s="36"/>
-      <c r="C75" s="116" t="s">
+      <c r="C75" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="D75" s="117"/>
-      <c r="E75" s="117"/>
-      <c r="F75" s="117"/>
-      <c r="G75" s="118"/>
-      <c r="H75" s="113" t="s">
+      <c r="D75" s="76"/>
+      <c r="E75" s="76"/>
+      <c r="F75" s="76"/>
+      <c r="G75" s="82"/>
+      <c r="H75" s="115" t="s">
         <v>58</v>
       </c>
-      <c r="I75" s="82"/>
+      <c r="I75" s="106"/>
       <c r="J75" s="19"/>
       <c r="K75" s="20"/>
       <c r="L75" s="20"/>
@@ -11718,13 +11719,13 @@
     <row r="76" spans="1:120" ht="9.75" customHeight="1">
       <c r="A76" s="16"/>
       <c r="B76" s="36"/>
-      <c r="C76" s="119"/>
-      <c r="D76" s="127"/>
-      <c r="E76" s="127"/>
-      <c r="F76" s="127"/>
-      <c r="G76" s="127"/>
-      <c r="H76" s="82"/>
-      <c r="I76" s="82"/>
+      <c r="C76" s="85"/>
+      <c r="D76" s="86"/>
+      <c r="E76" s="86"/>
+      <c r="F76" s="86"/>
+      <c r="G76" s="86"/>
+      <c r="H76" s="106"/>
+      <c r="I76" s="106"/>
       <c r="J76" s="19"/>
       <c r="K76" s="20"/>
       <c r="L76" s="20"/>
@@ -11841,14 +11842,14 @@
       <c r="A77" s="16"/>
       <c r="B77" s="36"/>
       <c r="C77" s="60"/>
-      <c r="D77" s="102" t="s">
+      <c r="D77" s="120" t="s">
         <v>59</v>
       </c>
-      <c r="E77" s="103"/>
-      <c r="F77" s="103"/>
-      <c r="G77" s="104"/>
-      <c r="H77" s="94"/>
-      <c r="I77" s="111"/>
+      <c r="E77" s="121"/>
+      <c r="F77" s="121"/>
+      <c r="G77" s="122"/>
+      <c r="H77" s="116"/>
+      <c r="I77" s="109"/>
       <c r="J77" s="63"/>
       <c r="K77" s="64"/>
       <c r="L77" s="64"/>
@@ -11965,12 +11966,12 @@
       <c r="A78" s="16"/>
       <c r="B78" s="36"/>
       <c r="C78" s="60"/>
-      <c r="D78" s="105"/>
-      <c r="E78" s="106"/>
-      <c r="F78" s="106"/>
-      <c r="G78" s="107"/>
-      <c r="H78" s="95"/>
-      <c r="I78" s="112"/>
+      <c r="D78" s="123"/>
+      <c r="E78" s="124"/>
+      <c r="F78" s="124"/>
+      <c r="G78" s="125"/>
+      <c r="H78" s="117"/>
+      <c r="I78" s="110"/>
       <c r="J78" s="63"/>
       <c r="K78" s="64"/>
       <c r="L78" s="64"/>
@@ -12086,13 +12087,13 @@
     <row r="79" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A79" s="16"/>
       <c r="B79" s="74"/>
-      <c r="C79" s="80" t="s">
+      <c r="C79" s="141" t="s">
         <v>68</v>
       </c>
-      <c r="D79" s="80"/>
-      <c r="E79" s="80"/>
-      <c r="F79" s="80"/>
-      <c r="G79" s="80"/>
+      <c r="D79" s="141"/>
+      <c r="E79" s="141"/>
+      <c r="F79" s="141"/>
+      <c r="G79" s="141"/>
       <c r="H79" s="67"/>
       <c r="I79" s="68"/>
       <c r="J79" s="63"/>
@@ -12210,11 +12211,11 @@
     <row r="80" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A80" s="16"/>
       <c r="B80" s="74"/>
-      <c r="C80" s="80"/>
-      <c r="D80" s="80"/>
-      <c r="E80" s="80"/>
-      <c r="F80" s="80"/>
-      <c r="G80" s="80"/>
+      <c r="C80" s="141"/>
+      <c r="D80" s="141"/>
+      <c r="E80" s="141"/>
+      <c r="F80" s="141"/>
+      <c r="G80" s="141"/>
       <c r="H80" s="67"/>
       <c r="I80" s="68"/>
       <c r="J80" s="63"/>
@@ -12334,15 +12335,15 @@
       <c r="B81" s="36"/>
       <c r="C81" s="60"/>
       <c r="D81" s="72"/>
-      <c r="E81" s="98" t="s">
+      <c r="E81" s="126" t="s">
         <v>60</v>
       </c>
-      <c r="F81" s="98"/>
-      <c r="G81" s="98"/>
-      <c r="H81" s="76">
+      <c r="F81" s="126"/>
+      <c r="G81" s="126"/>
+      <c r="H81" s="118">
         <v>45611</v>
       </c>
-      <c r="I81" s="78"/>
+      <c r="I81" s="111"/>
       <c r="J81" s="19"/>
       <c r="K81" s="20"/>
       <c r="L81" s="20"/>
@@ -12460,11 +12461,11 @@
       <c r="B82" s="36"/>
       <c r="C82" s="60"/>
       <c r="D82" s="72"/>
-      <c r="E82" s="75"/>
-      <c r="F82" s="75"/>
-      <c r="G82" s="75"/>
-      <c r="H82" s="77"/>
-      <c r="I82" s="79"/>
+      <c r="E82" s="127"/>
+      <c r="F82" s="127"/>
+      <c r="G82" s="127"/>
+      <c r="H82" s="119"/>
+      <c r="I82" s="112"/>
       <c r="J82" s="19"/>
       <c r="K82" s="20"/>
       <c r="L82" s="20"/>
@@ -12582,15 +12583,15 @@
       <c r="B83" s="36"/>
       <c r="C83" s="60"/>
       <c r="D83" s="72"/>
-      <c r="E83" s="75" t="s">
+      <c r="E83" s="127" t="s">
         <v>61</v>
       </c>
-      <c r="F83" s="75"/>
-      <c r="G83" s="75"/>
-      <c r="H83" s="76">
+      <c r="F83" s="127"/>
+      <c r="G83" s="127"/>
+      <c r="H83" s="118">
         <v>45614</v>
       </c>
-      <c r="I83" s="78"/>
+      <c r="I83" s="111"/>
       <c r="J83" s="19"/>
       <c r="K83" s="20"/>
       <c r="L83" s="20"/>
@@ -12708,11 +12709,11 @@
       <c r="B84" s="36"/>
       <c r="C84" s="60"/>
       <c r="D84" s="72"/>
-      <c r="E84" s="75"/>
-      <c r="F84" s="75"/>
-      <c r="G84" s="75"/>
-      <c r="H84" s="77"/>
-      <c r="I84" s="79"/>
+      <c r="E84" s="127"/>
+      <c r="F84" s="127"/>
+      <c r="G84" s="127"/>
+      <c r="H84" s="119"/>
+      <c r="I84" s="112"/>
       <c r="J84" s="19"/>
       <c r="K84" s="20"/>
       <c r="L84" s="20"/>
@@ -12830,15 +12831,15 @@
       <c r="B85" s="36"/>
       <c r="C85" s="60"/>
       <c r="D85" s="72"/>
-      <c r="E85" s="75" t="s">
+      <c r="E85" s="127" t="s">
         <v>62</v>
       </c>
-      <c r="F85" s="75"/>
-      <c r="G85" s="75"/>
-      <c r="H85" s="76">
+      <c r="F85" s="127"/>
+      <c r="G85" s="127"/>
+      <c r="H85" s="118">
         <v>45615</v>
       </c>
-      <c r="I85" s="78"/>
+      <c r="I85" s="111"/>
       <c r="J85" s="19"/>
       <c r="K85" s="20"/>
       <c r="L85" s="20"/>
@@ -12956,11 +12957,11 @@
       <c r="B86" s="36"/>
       <c r="C86" s="60"/>
       <c r="D86" s="72"/>
-      <c r="E86" s="96"/>
-      <c r="F86" s="96"/>
-      <c r="G86" s="96"/>
-      <c r="H86" s="77"/>
-      <c r="I86" s="79"/>
+      <c r="E86" s="128"/>
+      <c r="F86" s="128"/>
+      <c r="G86" s="128"/>
+      <c r="H86" s="119"/>
+      <c r="I86" s="112"/>
       <c r="J86" s="19"/>
       <c r="K86" s="20"/>
       <c r="L86" s="20"/>
@@ -13078,15 +13079,15 @@
       <c r="B87" s="36"/>
       <c r="C87" s="60"/>
       <c r="D87" s="72"/>
-      <c r="E87" s="83" t="s">
+      <c r="E87" s="129" t="s">
         <v>73</v>
       </c>
-      <c r="F87" s="84"/>
-      <c r="G87" s="85"/>
-      <c r="H87" s="81">
+      <c r="F87" s="130"/>
+      <c r="G87" s="131"/>
+      <c r="H87" s="142">
         <v>45617</v>
       </c>
-      <c r="I87" s="82"/>
+      <c r="I87" s="106"/>
       <c r="J87" s="62"/>
       <c r="K87" s="20"/>
       <c r="L87" s="20"/>
@@ -13204,11 +13205,11 @@
       <c r="B88" s="36"/>
       <c r="C88" s="60"/>
       <c r="D88" s="72"/>
-      <c r="E88" s="108"/>
-      <c r="F88" s="109"/>
-      <c r="G88" s="110"/>
-      <c r="H88" s="81"/>
-      <c r="I88" s="82"/>
+      <c r="E88" s="132"/>
+      <c r="F88" s="133"/>
+      <c r="G88" s="134"/>
+      <c r="H88" s="142"/>
+      <c r="I88" s="106"/>
       <c r="J88" s="62"/>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -13324,15 +13325,15 @@
     <row r="89" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A89" s="16"/>
       <c r="B89" s="74"/>
-      <c r="C89" s="80" t="s">
+      <c r="C89" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="D89" s="80"/>
-      <c r="E89" s="80"/>
-      <c r="F89" s="80"/>
-      <c r="G89" s="80"/>
-      <c r="H89" s="89"/>
-      <c r="I89" s="90"/>
+      <c r="D89" s="141"/>
+      <c r="E89" s="141"/>
+      <c r="F89" s="141"/>
+      <c r="G89" s="141"/>
+      <c r="H89" s="137"/>
+      <c r="I89" s="138"/>
       <c r="J89" s="66"/>
       <c r="K89" s="64"/>
       <c r="L89" s="64"/>
@@ -13448,13 +13449,13 @@
     <row r="90" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A90" s="16"/>
       <c r="B90" s="74"/>
-      <c r="C90" s="80"/>
-      <c r="D90" s="80"/>
-      <c r="E90" s="80"/>
-      <c r="F90" s="80"/>
-      <c r="G90" s="80"/>
-      <c r="H90" s="89"/>
-      <c r="I90" s="90"/>
+      <c r="C90" s="141"/>
+      <c r="D90" s="141"/>
+      <c r="E90" s="141"/>
+      <c r="F90" s="141"/>
+      <c r="G90" s="141"/>
+      <c r="H90" s="137"/>
+      <c r="I90" s="138"/>
       <c r="J90" s="66"/>
       <c r="K90" s="64"/>
       <c r="L90" s="64"/>
@@ -13572,15 +13573,15 @@
       <c r="B91" s="36"/>
       <c r="C91" s="60"/>
       <c r="D91" s="72"/>
-      <c r="E91" s="98" t="s">
+      <c r="E91" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="F91" s="98"/>
-      <c r="G91" s="98"/>
-      <c r="H91" s="76">
+      <c r="F91" s="126"/>
+      <c r="G91" s="126"/>
+      <c r="H91" s="118">
         <v>45616</v>
       </c>
-      <c r="I91" s="78"/>
+      <c r="I91" s="111"/>
       <c r="J91" s="19"/>
       <c r="K91" s="20"/>
       <c r="L91" s="20"/>
@@ -13698,11 +13699,11 @@
       <c r="B92" s="36"/>
       <c r="C92" s="60"/>
       <c r="D92" s="72"/>
-      <c r="E92" s="75"/>
-      <c r="F92" s="75"/>
-      <c r="G92" s="75"/>
-      <c r="H92" s="77"/>
-      <c r="I92" s="79"/>
+      <c r="E92" s="127"/>
+      <c r="F92" s="127"/>
+      <c r="G92" s="127"/>
+      <c r="H92" s="119"/>
+      <c r="I92" s="112"/>
       <c r="J92" s="19"/>
       <c r="K92" s="20"/>
       <c r="L92" s="20"/>
@@ -13820,15 +13821,15 @@
       <c r="B93" s="36"/>
       <c r="C93" s="60"/>
       <c r="D93" s="72"/>
-      <c r="E93" s="75" t="s">
+      <c r="E93" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="F93" s="75"/>
-      <c r="G93" s="75"/>
-      <c r="H93" s="76">
+      <c r="F93" s="127"/>
+      <c r="G93" s="127"/>
+      <c r="H93" s="118">
         <v>45617</v>
       </c>
-      <c r="I93" s="78"/>
+      <c r="I93" s="111"/>
       <c r="J93" s="19"/>
       <c r="K93" s="20"/>
       <c r="L93" s="20"/>
@@ -13946,11 +13947,11 @@
       <c r="B94" s="36"/>
       <c r="C94" s="60"/>
       <c r="D94" s="72"/>
-      <c r="E94" s="75"/>
-      <c r="F94" s="75"/>
-      <c r="G94" s="75"/>
-      <c r="H94" s="77"/>
-      <c r="I94" s="79"/>
+      <c r="E94" s="127"/>
+      <c r="F94" s="127"/>
+      <c r="G94" s="127"/>
+      <c r="H94" s="119"/>
+      <c r="I94" s="112"/>
       <c r="J94" s="19"/>
       <c r="K94" s="20"/>
       <c r="L94" s="20"/>
@@ -14068,15 +14069,15 @@
       <c r="B95" s="36"/>
       <c r="C95" s="60"/>
       <c r="D95" s="72"/>
-      <c r="E95" s="75" t="s">
+      <c r="E95" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="F95" s="75"/>
-      <c r="G95" s="75"/>
-      <c r="H95" s="76">
+      <c r="F95" s="127"/>
+      <c r="G95" s="127"/>
+      <c r="H95" s="118">
         <v>45618</v>
       </c>
-      <c r="I95" s="78"/>
+      <c r="I95" s="111"/>
       <c r="J95" s="19"/>
       <c r="K95" s="20"/>
       <c r="L95" s="20"/>
@@ -14194,11 +14195,11 @@
       <c r="B96" s="36"/>
       <c r="C96" s="60"/>
       <c r="D96" s="72"/>
-      <c r="E96" s="75"/>
-      <c r="F96" s="75"/>
-      <c r="G96" s="75"/>
-      <c r="H96" s="77"/>
-      <c r="I96" s="79"/>
+      <c r="E96" s="127"/>
+      <c r="F96" s="127"/>
+      <c r="G96" s="127"/>
+      <c r="H96" s="119"/>
+      <c r="I96" s="112"/>
       <c r="J96" s="19"/>
       <c r="K96" s="20"/>
       <c r="L96" s="20"/>
@@ -14316,15 +14317,15 @@
       <c r="B97" s="36"/>
       <c r="C97" s="60"/>
       <c r="D97" s="72"/>
-      <c r="E97" s="75" t="s">
+      <c r="E97" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="F97" s="75"/>
-      <c r="G97" s="75"/>
-      <c r="H97" s="76">
+      <c r="F97" s="127"/>
+      <c r="G97" s="127"/>
+      <c r="H97" s="118">
         <v>45621</v>
       </c>
-      <c r="I97" s="78"/>
+      <c r="I97" s="111"/>
       <c r="J97" s="19"/>
       <c r="K97" s="20"/>
       <c r="L97" s="20"/>
@@ -14442,11 +14443,11 @@
       <c r="B98" s="36"/>
       <c r="C98" s="60"/>
       <c r="D98" s="72"/>
-      <c r="E98" s="75"/>
-      <c r="F98" s="75"/>
-      <c r="G98" s="75"/>
-      <c r="H98" s="77"/>
-      <c r="I98" s="79"/>
+      <c r="E98" s="127"/>
+      <c r="F98" s="127"/>
+      <c r="G98" s="127"/>
+      <c r="H98" s="119"/>
+      <c r="I98" s="112"/>
       <c r="J98" s="19"/>
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
@@ -14564,15 +14565,15 @@
       <c r="B99" s="36"/>
       <c r="C99" s="60"/>
       <c r="D99" s="72"/>
-      <c r="E99" s="75" t="s">
+      <c r="E99" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="F99" s="75"/>
-      <c r="G99" s="75"/>
-      <c r="H99" s="76">
+      <c r="F99" s="127"/>
+      <c r="G99" s="127"/>
+      <c r="H99" s="118">
         <v>45622</v>
       </c>
-      <c r="I99" s="78"/>
+      <c r="I99" s="111"/>
       <c r="J99" s="19"/>
       <c r="K99" s="20"/>
       <c r="L99" s="20"/>
@@ -14690,11 +14691,11 @@
       <c r="B100" s="36"/>
       <c r="C100" s="60"/>
       <c r="D100" s="72"/>
-      <c r="E100" s="96"/>
-      <c r="F100" s="96"/>
-      <c r="G100" s="96"/>
-      <c r="H100" s="77"/>
-      <c r="I100" s="79"/>
+      <c r="E100" s="128"/>
+      <c r="F100" s="128"/>
+      <c r="G100" s="128"/>
+      <c r="H100" s="119"/>
+      <c r="I100" s="112"/>
       <c r="J100" s="19"/>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -14812,15 +14813,15 @@
       <c r="B101" s="36"/>
       <c r="C101" s="60"/>
       <c r="D101" s="72"/>
-      <c r="E101" s="83" t="s">
+      <c r="E101" s="129" t="s">
         <v>73</v>
       </c>
-      <c r="F101" s="84"/>
-      <c r="G101" s="85"/>
-      <c r="H101" s="76">
+      <c r="F101" s="130"/>
+      <c r="G101" s="131"/>
+      <c r="H101" s="118">
         <v>45623</v>
       </c>
-      <c r="I101" s="82"/>
+      <c r="I101" s="106"/>
       <c r="J101" s="62"/>
       <c r="K101" s="20"/>
       <c r="L101" s="20"/>
@@ -14938,11 +14939,11 @@
       <c r="B102" s="36"/>
       <c r="C102" s="60"/>
       <c r="D102" s="73"/>
-      <c r="E102" s="86"/>
-      <c r="F102" s="87"/>
-      <c r="G102" s="88"/>
-      <c r="H102" s="77"/>
-      <c r="I102" s="82"/>
+      <c r="E102" s="143"/>
+      <c r="F102" s="144"/>
+      <c r="G102" s="145"/>
+      <c r="H102" s="119"/>
+      <c r="I102" s="106"/>
       <c r="J102" s="62"/>
       <c r="K102" s="20"/>
       <c r="L102" s="20"/>
@@ -15059,14 +15060,14 @@
       <c r="A103" s="16"/>
       <c r="B103" s="36"/>
       <c r="C103" s="60"/>
-      <c r="D103" s="97" t="s">
+      <c r="D103" s="135" t="s">
         <v>70</v>
       </c>
-      <c r="E103" s="97"/>
-      <c r="F103" s="97"/>
-      <c r="G103" s="97"/>
-      <c r="H103" s="89"/>
-      <c r="I103" s="90"/>
+      <c r="E103" s="135"/>
+      <c r="F103" s="135"/>
+      <c r="G103" s="135"/>
+      <c r="H103" s="137"/>
+      <c r="I103" s="138"/>
       <c r="J103" s="66"/>
       <c r="K103" s="64"/>
       <c r="L103" s="64"/>
@@ -15183,12 +15184,12 @@
       <c r="A104" s="16"/>
       <c r="B104" s="36"/>
       <c r="C104" s="60"/>
-      <c r="D104" s="99"/>
-      <c r="E104" s="99"/>
-      <c r="F104" s="99"/>
-      <c r="G104" s="99"/>
-      <c r="H104" s="89"/>
-      <c r="I104" s="90"/>
+      <c r="D104" s="136"/>
+      <c r="E104" s="136"/>
+      <c r="F104" s="136"/>
+      <c r="G104" s="136"/>
+      <c r="H104" s="137"/>
+      <c r="I104" s="138"/>
       <c r="J104" s="66"/>
       <c r="K104" s="64"/>
       <c r="L104" s="64"/>
@@ -15304,15 +15305,15 @@
     <row r="105" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A105" s="16"/>
       <c r="B105" s="74"/>
-      <c r="C105" s="80" t="s">
+      <c r="C105" s="141" t="s">
         <v>68</v>
       </c>
-      <c r="D105" s="80"/>
-      <c r="E105" s="80"/>
-      <c r="F105" s="80"/>
-      <c r="G105" s="80"/>
-      <c r="H105" s="89"/>
-      <c r="I105" s="90"/>
+      <c r="D105" s="141"/>
+      <c r="E105" s="141"/>
+      <c r="F105" s="141"/>
+      <c r="G105" s="141"/>
+      <c r="H105" s="137"/>
+      <c r="I105" s="138"/>
       <c r="J105" s="66"/>
       <c r="K105" s="64"/>
       <c r="L105" s="64"/>
@@ -15428,13 +15429,13 @@
     <row r="106" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A106" s="16"/>
       <c r="B106" s="74"/>
-      <c r="C106" s="80"/>
-      <c r="D106" s="80"/>
-      <c r="E106" s="80"/>
-      <c r="F106" s="80"/>
-      <c r="G106" s="80"/>
-      <c r="H106" s="89"/>
-      <c r="I106" s="90"/>
+      <c r="C106" s="141"/>
+      <c r="D106" s="141"/>
+      <c r="E106" s="141"/>
+      <c r="F106" s="141"/>
+      <c r="G106" s="141"/>
+      <c r="H106" s="137"/>
+      <c r="I106" s="138"/>
       <c r="J106" s="66"/>
       <c r="K106" s="64"/>
       <c r="L106" s="64"/>
@@ -15552,15 +15553,15 @@
       <c r="B107" s="36"/>
       <c r="C107" s="60"/>
       <c r="D107" s="72"/>
-      <c r="E107" s="98" t="s">
+      <c r="E107" s="126" t="s">
         <v>60</v>
       </c>
-      <c r="F107" s="98"/>
-      <c r="G107" s="98"/>
-      <c r="H107" s="76">
+      <c r="F107" s="126"/>
+      <c r="G107" s="126"/>
+      <c r="H107" s="118">
         <v>45625</v>
       </c>
-      <c r="I107" s="100"/>
+      <c r="I107" s="113"/>
       <c r="J107" s="62"/>
       <c r="K107" s="20"/>
       <c r="L107" s="20"/>
@@ -15678,11 +15679,11 @@
       <c r="B108" s="36"/>
       <c r="C108" s="60"/>
       <c r="D108" s="72"/>
-      <c r="E108" s="75"/>
-      <c r="F108" s="75"/>
-      <c r="G108" s="75"/>
-      <c r="H108" s="77"/>
-      <c r="I108" s="101"/>
+      <c r="E108" s="127"/>
+      <c r="F108" s="127"/>
+      <c r="G108" s="127"/>
+      <c r="H108" s="119"/>
+      <c r="I108" s="114"/>
       <c r="J108" s="62"/>
       <c r="K108" s="20"/>
       <c r="L108" s="20"/>
@@ -15800,15 +15801,15 @@
       <c r="B109" s="36"/>
       <c r="C109" s="60"/>
       <c r="D109" s="72"/>
-      <c r="E109" s="75" t="s">
+      <c r="E109" s="127" t="s">
         <v>61</v>
       </c>
-      <c r="F109" s="75"/>
-      <c r="G109" s="75"/>
-      <c r="H109" s="76">
+      <c r="F109" s="127"/>
+      <c r="G109" s="127"/>
+      <c r="H109" s="118">
         <v>45629</v>
       </c>
-      <c r="I109" s="100"/>
+      <c r="I109" s="113"/>
       <c r="J109" s="62"/>
       <c r="K109" s="20"/>
       <c r="L109" s="20"/>
@@ -15926,11 +15927,11 @@
       <c r="B110" s="36"/>
       <c r="C110" s="60"/>
       <c r="D110" s="72"/>
-      <c r="E110" s="75"/>
-      <c r="F110" s="75"/>
-      <c r="G110" s="75"/>
-      <c r="H110" s="77"/>
-      <c r="I110" s="101"/>
+      <c r="E110" s="127"/>
+      <c r="F110" s="127"/>
+      <c r="G110" s="127"/>
+      <c r="H110" s="119"/>
+      <c r="I110" s="114"/>
       <c r="J110" s="62"/>
       <c r="K110" s="20"/>
       <c r="L110" s="20"/>
@@ -16048,15 +16049,15 @@
       <c r="B111" s="36"/>
       <c r="C111" s="60"/>
       <c r="D111" s="72"/>
-      <c r="E111" s="75" t="s">
+      <c r="E111" s="127" t="s">
         <v>62</v>
       </c>
-      <c r="F111" s="75"/>
-      <c r="G111" s="75"/>
-      <c r="H111" s="76">
+      <c r="F111" s="127"/>
+      <c r="G111" s="127"/>
+      <c r="H111" s="118">
         <v>45631</v>
       </c>
-      <c r="I111" s="100"/>
+      <c r="I111" s="113"/>
       <c r="J111" s="62"/>
       <c r="K111" s="20"/>
       <c r="L111" s="20"/>
@@ -16174,11 +16175,11 @@
       <c r="B112" s="36"/>
       <c r="C112" s="60"/>
       <c r="D112" s="72"/>
-      <c r="E112" s="96"/>
-      <c r="F112" s="96"/>
-      <c r="G112" s="96"/>
-      <c r="H112" s="77"/>
-      <c r="I112" s="101"/>
+      <c r="E112" s="128"/>
+      <c r="F112" s="128"/>
+      <c r="G112" s="128"/>
+      <c r="H112" s="119"/>
+      <c r="I112" s="114"/>
       <c r="J112" s="62"/>
       <c r="K112" s="20"/>
       <c r="L112" s="20"/>
@@ -16296,15 +16297,15 @@
       <c r="B113" s="36"/>
       <c r="C113" s="60"/>
       <c r="D113" s="72"/>
-      <c r="E113" s="75" t="s">
+      <c r="E113" s="127" t="s">
         <v>73</v>
       </c>
-      <c r="F113" s="75"/>
-      <c r="G113" s="75"/>
-      <c r="H113" s="81">
+      <c r="F113" s="127"/>
+      <c r="G113" s="127"/>
+      <c r="H113" s="142">
         <v>45630</v>
       </c>
-      <c r="I113" s="82"/>
+      <c r="I113" s="106"/>
       <c r="J113" s="62"/>
       <c r="K113" s="20"/>
       <c r="L113" s="20"/>
@@ -16422,11 +16423,11 @@
       <c r="B114" s="36"/>
       <c r="C114" s="60"/>
       <c r="D114" s="73"/>
-      <c r="E114" s="75"/>
-      <c r="F114" s="75"/>
-      <c r="G114" s="75"/>
-      <c r="H114" s="81"/>
-      <c r="I114" s="82"/>
+      <c r="E114" s="127"/>
+      <c r="F114" s="127"/>
+      <c r="G114" s="127"/>
+      <c r="H114" s="142"/>
+      <c r="I114" s="106"/>
       <c r="J114" s="62"/>
       <c r="K114" s="20"/>
       <c r="L114" s="20"/>
@@ -16543,14 +16544,14 @@
       <c r="A115" s="16"/>
       <c r="B115" s="36"/>
       <c r="C115" s="60"/>
-      <c r="D115" s="97" t="s">
+      <c r="D115" s="135" t="s">
         <v>71</v>
       </c>
-      <c r="E115" s="97"/>
-      <c r="F115" s="97"/>
-      <c r="G115" s="97"/>
-      <c r="H115" s="92"/>
-      <c r="I115" s="111"/>
+      <c r="E115" s="135"/>
+      <c r="F115" s="135"/>
+      <c r="G115" s="135"/>
+      <c r="H115" s="139"/>
+      <c r="I115" s="109"/>
       <c r="J115" s="63"/>
       <c r="K115" s="64"/>
       <c r="L115" s="64"/>
@@ -16667,12 +16668,12 @@
       <c r="A116" s="16"/>
       <c r="B116" s="36"/>
       <c r="C116" s="60"/>
-      <c r="D116" s="97"/>
-      <c r="E116" s="97"/>
-      <c r="F116" s="97"/>
-      <c r="G116" s="97"/>
-      <c r="H116" s="93"/>
-      <c r="I116" s="112"/>
+      <c r="D116" s="135"/>
+      <c r="E116" s="135"/>
+      <c r="F116" s="135"/>
+      <c r="G116" s="135"/>
+      <c r="H116" s="140"/>
+      <c r="I116" s="110"/>
       <c r="J116" s="63"/>
       <c r="K116" s="64"/>
       <c r="L116" s="64"/>
@@ -16790,15 +16791,15 @@
       <c r="B117" s="36"/>
       <c r="C117" s="60"/>
       <c r="D117" s="71"/>
-      <c r="E117" s="98" t="s">
+      <c r="E117" s="126" t="s">
         <v>72</v>
       </c>
-      <c r="F117" s="98"/>
-      <c r="G117" s="98"/>
-      <c r="H117" s="76">
+      <c r="F117" s="126"/>
+      <c r="G117" s="126"/>
+      <c r="H117" s="118">
         <v>45632</v>
       </c>
-      <c r="I117" s="78"/>
+      <c r="I117" s="111"/>
       <c r="J117" s="19"/>
       <c r="K117" s="20"/>
       <c r="L117" s="20"/>
@@ -16916,11 +16917,11 @@
       <c r="B118" s="36"/>
       <c r="C118" s="60"/>
       <c r="D118" s="73"/>
-      <c r="E118" s="96"/>
-      <c r="F118" s="96"/>
-      <c r="G118" s="96"/>
-      <c r="H118" s="77"/>
-      <c r="I118" s="79"/>
+      <c r="E118" s="128"/>
+      <c r="F118" s="128"/>
+      <c r="G118" s="128"/>
+      <c r="H118" s="119"/>
+      <c r="I118" s="112"/>
       <c r="J118" s="19"/>
       <c r="K118" s="20"/>
       <c r="L118" s="20"/>
@@ -17037,14 +17038,14 @@
       <c r="A119" s="16"/>
       <c r="B119" s="36"/>
       <c r="C119" s="60"/>
-      <c r="D119" s="97" t="s">
+      <c r="D119" s="135" t="s">
         <v>70</v>
       </c>
-      <c r="E119" s="97"/>
-      <c r="F119" s="97"/>
-      <c r="G119" s="97"/>
-      <c r="H119" s="92"/>
-      <c r="I119" s="111"/>
+      <c r="E119" s="135"/>
+      <c r="F119" s="135"/>
+      <c r="G119" s="135"/>
+      <c r="H119" s="139"/>
+      <c r="I119" s="109"/>
       <c r="J119" s="63"/>
       <c r="K119" s="64"/>
       <c r="L119" s="64"/>
@@ -17161,12 +17162,12 @@
       <c r="A120" s="16"/>
       <c r="B120" s="36"/>
       <c r="C120" s="60"/>
-      <c r="D120" s="99"/>
-      <c r="E120" s="99"/>
-      <c r="F120" s="99"/>
-      <c r="G120" s="99"/>
-      <c r="H120" s="93"/>
-      <c r="I120" s="112"/>
+      <c r="D120" s="136"/>
+      <c r="E120" s="136"/>
+      <c r="F120" s="136"/>
+      <c r="G120" s="136"/>
+      <c r="H120" s="140"/>
+      <c r="I120" s="110"/>
       <c r="J120" s="63"/>
       <c r="K120" s="64"/>
       <c r="L120" s="64"/>
@@ -17282,15 +17283,15 @@
     <row r="121" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A121" s="16"/>
       <c r="B121" s="74"/>
-      <c r="C121" s="80" t="s">
+      <c r="C121" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="D121" s="80"/>
-      <c r="E121" s="80"/>
-      <c r="F121" s="80"/>
-      <c r="G121" s="80"/>
-      <c r="H121" s="92"/>
-      <c r="I121" s="111"/>
+      <c r="D121" s="141"/>
+      <c r="E121" s="141"/>
+      <c r="F121" s="141"/>
+      <c r="G121" s="141"/>
+      <c r="H121" s="139"/>
+      <c r="I121" s="109"/>
       <c r="J121" s="63"/>
       <c r="K121" s="64"/>
       <c r="L121" s="64"/>
@@ -17406,13 +17407,13 @@
     <row r="122" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A122" s="16"/>
       <c r="B122" s="74"/>
-      <c r="C122" s="80"/>
-      <c r="D122" s="80"/>
-      <c r="E122" s="80"/>
-      <c r="F122" s="80"/>
-      <c r="G122" s="80"/>
-      <c r="H122" s="93"/>
-      <c r="I122" s="112"/>
+      <c r="C122" s="141"/>
+      <c r="D122" s="141"/>
+      <c r="E122" s="141"/>
+      <c r="F122" s="141"/>
+      <c r="G122" s="141"/>
+      <c r="H122" s="140"/>
+      <c r="I122" s="110"/>
       <c r="J122" s="63"/>
       <c r="K122" s="64"/>
       <c r="L122" s="64"/>
@@ -17530,15 +17531,15 @@
       <c r="B123" s="36"/>
       <c r="C123" s="60"/>
       <c r="D123" s="72"/>
-      <c r="E123" s="98" t="s">
+      <c r="E123" s="126" t="s">
         <v>63</v>
       </c>
-      <c r="F123" s="98"/>
-      <c r="G123" s="98"/>
-      <c r="H123" s="76">
+      <c r="F123" s="126"/>
+      <c r="G123" s="126"/>
+      <c r="H123" s="118">
         <v>45636</v>
       </c>
-      <c r="I123" s="78"/>
+      <c r="I123" s="111"/>
       <c r="J123" s="19"/>
       <c r="K123" s="20"/>
       <c r="L123" s="20"/>
@@ -17656,11 +17657,11 @@
       <c r="B124" s="36"/>
       <c r="C124" s="60"/>
       <c r="D124" s="72"/>
-      <c r="E124" s="75"/>
-      <c r="F124" s="75"/>
-      <c r="G124" s="75"/>
-      <c r="H124" s="77"/>
-      <c r="I124" s="79"/>
+      <c r="E124" s="127"/>
+      <c r="F124" s="127"/>
+      <c r="G124" s="127"/>
+      <c r="H124" s="119"/>
+      <c r="I124" s="112"/>
       <c r="J124" s="19"/>
       <c r="K124" s="20"/>
       <c r="L124" s="20"/>
@@ -17778,15 +17779,15 @@
       <c r="B125" s="36"/>
       <c r="C125" s="60"/>
       <c r="D125" s="72"/>
-      <c r="E125" s="75" t="s">
+      <c r="E125" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="F125" s="75"/>
-      <c r="G125" s="75"/>
-      <c r="H125" s="76">
+      <c r="F125" s="127"/>
+      <c r="G125" s="127"/>
+      <c r="H125" s="118">
         <v>45637</v>
       </c>
-      <c r="I125" s="78"/>
+      <c r="I125" s="111"/>
       <c r="J125" s="19"/>
       <c r="K125" s="20"/>
       <c r="L125" s="20"/>
@@ -17904,11 +17905,11 @@
       <c r="B126" s="36"/>
       <c r="C126" s="60"/>
       <c r="D126" s="72"/>
-      <c r="E126" s="75"/>
-      <c r="F126" s="75"/>
-      <c r="G126" s="75"/>
-      <c r="H126" s="77"/>
-      <c r="I126" s="79"/>
+      <c r="E126" s="127"/>
+      <c r="F126" s="127"/>
+      <c r="G126" s="127"/>
+      <c r="H126" s="119"/>
+      <c r="I126" s="112"/>
       <c r="J126" s="19"/>
       <c r="K126" s="20"/>
       <c r="L126" s="20"/>
@@ -18026,15 +18027,15 @@
       <c r="B127" s="36"/>
       <c r="C127" s="60"/>
       <c r="D127" s="72"/>
-      <c r="E127" s="75" t="s">
+      <c r="E127" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="F127" s="75"/>
-      <c r="G127" s="75"/>
-      <c r="H127" s="91">
+      <c r="F127" s="127"/>
+      <c r="G127" s="127"/>
+      <c r="H127" s="146">
         <v>45638</v>
       </c>
-      <c r="I127" s="82"/>
+      <c r="I127" s="106"/>
       <c r="J127" s="62"/>
       <c r="K127" s="20"/>
       <c r="L127" s="20"/>
@@ -18152,11 +18153,11 @@
       <c r="B128" s="36"/>
       <c r="C128" s="60"/>
       <c r="D128" s="72"/>
-      <c r="E128" s="75"/>
-      <c r="F128" s="75"/>
-      <c r="G128" s="75"/>
-      <c r="H128" s="91"/>
-      <c r="I128" s="82"/>
+      <c r="E128" s="127"/>
+      <c r="F128" s="127"/>
+      <c r="G128" s="127"/>
+      <c r="H128" s="146"/>
+      <c r="I128" s="106"/>
       <c r="J128" s="62"/>
       <c r="K128" s="20"/>
       <c r="L128" s="20"/>
@@ -18274,15 +18275,15 @@
       <c r="B129" s="36"/>
       <c r="C129" s="60"/>
       <c r="D129" s="72"/>
-      <c r="E129" s="75" t="s">
+      <c r="E129" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="F129" s="75"/>
-      <c r="G129" s="75"/>
-      <c r="H129" s="81">
+      <c r="F129" s="127"/>
+      <c r="G129" s="127"/>
+      <c r="H129" s="142">
         <v>45639</v>
       </c>
-      <c r="I129" s="82"/>
+      <c r="I129" s="106"/>
       <c r="J129" s="62"/>
       <c r="K129" s="20"/>
       <c r="L129" s="20"/>
@@ -18400,11 +18401,11 @@
       <c r="B130" s="36"/>
       <c r="C130" s="60"/>
       <c r="D130" s="72"/>
-      <c r="E130" s="75"/>
-      <c r="F130" s="75"/>
-      <c r="G130" s="75"/>
-      <c r="H130" s="81"/>
-      <c r="I130" s="82"/>
+      <c r="E130" s="127"/>
+      <c r="F130" s="127"/>
+      <c r="G130" s="127"/>
+      <c r="H130" s="142"/>
+      <c r="I130" s="106"/>
       <c r="J130" s="62"/>
       <c r="K130" s="20"/>
       <c r="L130" s="20"/>
@@ -18522,15 +18523,15 @@
       <c r="B131" s="36"/>
       <c r="C131" s="60"/>
       <c r="D131" s="72"/>
-      <c r="E131" s="75" t="s">
+      <c r="E131" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="F131" s="75"/>
-      <c r="G131" s="75"/>
-      <c r="H131" s="76">
+      <c r="F131" s="127"/>
+      <c r="G131" s="127"/>
+      <c r="H131" s="118">
         <v>45642</v>
       </c>
-      <c r="I131" s="78"/>
+      <c r="I131" s="111"/>
       <c r="J131" s="19"/>
       <c r="K131" s="20"/>
       <c r="L131" s="20"/>
@@ -18648,11 +18649,11 @@
       <c r="B132" s="36"/>
       <c r="C132" s="60"/>
       <c r="D132" s="72"/>
-      <c r="E132" s="96"/>
-      <c r="F132" s="96"/>
-      <c r="G132" s="96"/>
-      <c r="H132" s="77"/>
-      <c r="I132" s="79"/>
+      <c r="E132" s="128"/>
+      <c r="F132" s="128"/>
+      <c r="G132" s="128"/>
+      <c r="H132" s="119"/>
+      <c r="I132" s="112"/>
       <c r="J132" s="19"/>
       <c r="K132" s="20"/>
       <c r="L132" s="20"/>
@@ -18770,15 +18771,15 @@
       <c r="B133" s="36"/>
       <c r="C133" s="60"/>
       <c r="D133" s="72"/>
-      <c r="E133" s="83" t="s">
+      <c r="E133" s="129" t="s">
         <v>73</v>
       </c>
-      <c r="F133" s="84"/>
-      <c r="G133" s="85"/>
-      <c r="H133" s="81">
+      <c r="F133" s="130"/>
+      <c r="G133" s="131"/>
+      <c r="H133" s="142">
         <v>45638</v>
       </c>
-      <c r="I133" s="82"/>
+      <c r="I133" s="106"/>
       <c r="J133" s="62"/>
       <c r="K133" s="20"/>
       <c r="L133" s="20"/>
@@ -18896,11 +18897,11 @@
       <c r="B134" s="36"/>
       <c r="C134" s="60"/>
       <c r="D134" s="73"/>
-      <c r="E134" s="86"/>
-      <c r="F134" s="87"/>
-      <c r="G134" s="88"/>
-      <c r="H134" s="81"/>
-      <c r="I134" s="82"/>
+      <c r="E134" s="143"/>
+      <c r="F134" s="144"/>
+      <c r="G134" s="145"/>
+      <c r="H134" s="142"/>
+      <c r="I134" s="106"/>
       <c r="J134" s="62"/>
       <c r="K134" s="20"/>
       <c r="L134" s="20"/>
@@ -19017,14 +19018,14 @@
       <c r="A135" s="16"/>
       <c r="B135" s="36"/>
       <c r="C135" s="60"/>
-      <c r="D135" s="97" t="s">
+      <c r="D135" s="135" t="s">
         <v>71</v>
       </c>
-      <c r="E135" s="97"/>
-      <c r="F135" s="97"/>
-      <c r="G135" s="97"/>
-      <c r="H135" s="92"/>
-      <c r="I135" s="94"/>
+      <c r="E135" s="135"/>
+      <c r="F135" s="135"/>
+      <c r="G135" s="135"/>
+      <c r="H135" s="139"/>
+      <c r="I135" s="116"/>
       <c r="J135" s="66"/>
       <c r="K135" s="64"/>
       <c r="L135" s="64"/>
@@ -19141,12 +19142,12 @@
       <c r="A136" s="16"/>
       <c r="B136" s="36"/>
       <c r="C136" s="60"/>
-      <c r="D136" s="97"/>
-      <c r="E136" s="97"/>
-      <c r="F136" s="97"/>
-      <c r="G136" s="97"/>
-      <c r="H136" s="93"/>
-      <c r="I136" s="95"/>
+      <c r="D136" s="135"/>
+      <c r="E136" s="135"/>
+      <c r="F136" s="135"/>
+      <c r="G136" s="135"/>
+      <c r="H136" s="140"/>
+      <c r="I136" s="117"/>
       <c r="J136" s="66"/>
       <c r="K136" s="64"/>
       <c r="L136" s="64"/>
@@ -19264,15 +19265,15 @@
       <c r="B137" s="36"/>
       <c r="C137" s="60"/>
       <c r="D137" s="71"/>
-      <c r="E137" s="75" t="s">
+      <c r="E137" s="127" t="s">
         <v>72</v>
       </c>
-      <c r="F137" s="75"/>
-      <c r="G137" s="75"/>
-      <c r="H137" s="76">
+      <c r="F137" s="127"/>
+      <c r="G137" s="127"/>
+      <c r="H137" s="118">
         <v>45644</v>
       </c>
-      <c r="I137" s="78"/>
+      <c r="I137" s="111"/>
       <c r="J137" s="19"/>
       <c r="K137" s="20"/>
       <c r="L137" s="20"/>
@@ -19390,11 +19391,11 @@
       <c r="B138" s="36"/>
       <c r="C138" s="60"/>
       <c r="D138" s="73"/>
-      <c r="E138" s="75"/>
-      <c r="F138" s="75"/>
-      <c r="G138" s="75"/>
-      <c r="H138" s="77"/>
-      <c r="I138" s="79"/>
+      <c r="E138" s="127"/>
+      <c r="F138" s="127"/>
+      <c r="G138" s="127"/>
+      <c r="H138" s="119"/>
+      <c r="I138" s="112"/>
       <c r="J138" s="19"/>
       <c r="K138" s="20"/>
       <c r="L138" s="20"/>
@@ -19511,16 +19512,16 @@
       <c r="A139" s="16"/>
       <c r="B139" s="36"/>
       <c r="C139" s="60"/>
-      <c r="D139" s="75"/>
-      <c r="E139" s="75" t="s">
+      <c r="D139" s="127"/>
+      <c r="E139" s="127" t="s">
         <v>73</v>
       </c>
-      <c r="F139" s="75"/>
-      <c r="G139" s="75"/>
-      <c r="H139" s="76">
+      <c r="F139" s="127"/>
+      <c r="G139" s="127"/>
+      <c r="H139" s="118">
         <v>45645</v>
       </c>
-      <c r="I139" s="78"/>
+      <c r="I139" s="111"/>
       <c r="J139" s="19"/>
       <c r="K139" s="20"/>
       <c r="L139" s="20"/>
@@ -19637,12 +19638,12 @@
       <c r="A140" s="16"/>
       <c r="B140" s="36"/>
       <c r="C140" s="60"/>
-      <c r="D140" s="75"/>
-      <c r="E140" s="75"/>
-      <c r="F140" s="75"/>
-      <c r="G140" s="75"/>
-      <c r="H140" s="77"/>
-      <c r="I140" s="79"/>
+      <c r="D140" s="127"/>
+      <c r="E140" s="127"/>
+      <c r="F140" s="127"/>
+      <c r="G140" s="127"/>
+      <c r="H140" s="119"/>
+      <c r="I140" s="112"/>
       <c r="J140" s="19"/>
       <c r="K140" s="20"/>
       <c r="L140" s="20"/>
@@ -19758,17 +19759,17 @@
     <row r="141" spans="1:120" ht="9.75" customHeight="1">
       <c r="A141" s="1"/>
       <c r="B141" s="18"/>
-      <c r="C141" s="126" t="s">
+      <c r="C141" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="D141" s="127"/>
-      <c r="E141" s="127"/>
-      <c r="F141" s="127"/>
-      <c r="G141" s="127"/>
-      <c r="H141" s="113" t="s">
+      <c r="D141" s="86"/>
+      <c r="E141" s="86"/>
+      <c r="F141" s="86"/>
+      <c r="G141" s="86"/>
+      <c r="H141" s="115" t="s">
         <v>57</v>
       </c>
-      <c r="I141" s="82"/>
+      <c r="I141" s="106"/>
       <c r="J141" s="14"/>
       <c r="K141" s="15"/>
       <c r="L141" s="15"/>
@@ -19884,13 +19885,13 @@
     <row r="142" spans="1:120" ht="9.75" customHeight="1">
       <c r="A142" s="1"/>
       <c r="B142" s="18"/>
-      <c r="C142" s="119"/>
-      <c r="D142" s="120"/>
-      <c r="E142" s="120"/>
-      <c r="F142" s="120"/>
-      <c r="G142" s="121"/>
-      <c r="H142" s="82"/>
-      <c r="I142" s="82"/>
+      <c r="C142" s="85"/>
+      <c r="D142" s="79"/>
+      <c r="E142" s="79"/>
+      <c r="F142" s="79"/>
+      <c r="G142" s="83"/>
+      <c r="H142" s="106"/>
+      <c r="I142" s="106"/>
       <c r="J142" s="14"/>
       <c r="K142" s="15"/>
       <c r="L142" s="15"/>
@@ -20005,16 +20006,16 @@
     </row>
     <row r="143" spans="1:120" ht="9.75" customHeight="1">
       <c r="A143" s="1"/>
-      <c r="B143" s="122" t="s">
+      <c r="B143" s="104" t="s">
         <v>32</v>
       </c>
-      <c r="C143" s="117"/>
-      <c r="D143" s="117"/>
-      <c r="E143" s="117"/>
-      <c r="F143" s="117"/>
-      <c r="G143" s="123"/>
-      <c r="H143" s="82"/>
-      <c r="I143" s="82"/>
+      <c r="C143" s="76"/>
+      <c r="D143" s="76"/>
+      <c r="E143" s="76"/>
+      <c r="F143" s="76"/>
+      <c r="G143" s="77"/>
+      <c r="H143" s="106"/>
+      <c r="I143" s="106"/>
       <c r="J143" s="12"/>
       <c r="K143" s="13"/>
       <c r="L143" s="13"/>
@@ -20129,14 +20130,14 @@
     </row>
     <row r="144" spans="1:120" ht="9.75" customHeight="1">
       <c r="A144" s="1"/>
-      <c r="B144" s="124"/>
-      <c r="C144" s="120"/>
-      <c r="D144" s="120"/>
-      <c r="E144" s="120"/>
-      <c r="F144" s="120"/>
-      <c r="G144" s="125"/>
-      <c r="H144" s="82"/>
-      <c r="I144" s="82"/>
+      <c r="B144" s="78"/>
+      <c r="C144" s="79"/>
+      <c r="D144" s="79"/>
+      <c r="E144" s="79"/>
+      <c r="F144" s="79"/>
+      <c r="G144" s="80"/>
+      <c r="H144" s="106"/>
+      <c r="I144" s="106"/>
       <c r="J144" s="14"/>
       <c r="K144" s="15"/>
       <c r="L144" s="15"/>
@@ -20252,17 +20253,17 @@
     <row r="145" spans="1:120" ht="9.75" customHeight="1">
       <c r="A145" s="16"/>
       <c r="B145" s="18"/>
-      <c r="C145" s="116" t="s">
+      <c r="C145" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="D145" s="117"/>
-      <c r="E145" s="117"/>
-      <c r="F145" s="117"/>
-      <c r="G145" s="118"/>
-      <c r="H145" s="113" t="s">
+      <c r="D145" s="76"/>
+      <c r="E145" s="76"/>
+      <c r="F145" s="76"/>
+      <c r="G145" s="82"/>
+      <c r="H145" s="115" t="s">
         <v>56</v>
       </c>
-      <c r="I145" s="82"/>
+      <c r="I145" s="106"/>
       <c r="J145" s="19"/>
       <c r="K145" s="20"/>
       <c r="L145" s="20"/>
@@ -20378,13 +20379,13 @@
     <row r="146" spans="1:120" ht="9.75" customHeight="1">
       <c r="A146" s="16"/>
       <c r="B146" s="37"/>
-      <c r="C146" s="119"/>
-      <c r="D146" s="120"/>
-      <c r="E146" s="120"/>
-      <c r="F146" s="120"/>
-      <c r="G146" s="121"/>
-      <c r="H146" s="82"/>
-      <c r="I146" s="82"/>
+      <c r="C146" s="85"/>
+      <c r="D146" s="79"/>
+      <c r="E146" s="79"/>
+      <c r="F146" s="79"/>
+      <c r="G146" s="83"/>
+      <c r="H146" s="106"/>
+      <c r="I146" s="106"/>
       <c r="J146" s="19"/>
       <c r="K146" s="20"/>
       <c r="L146" s="20"/>
@@ -33927,36 +33928,167 @@
     </row>
   </sheetData>
   <mergeCells count="215">
-    <mergeCell ref="E59:G60"/>
-    <mergeCell ref="E61:G62"/>
-    <mergeCell ref="D63:G64"/>
-    <mergeCell ref="E67:G68"/>
-    <mergeCell ref="E65:G66"/>
-    <mergeCell ref="E69:G70"/>
-    <mergeCell ref="E71:G72"/>
-    <mergeCell ref="C73:G74"/>
-    <mergeCell ref="C75:G76"/>
-    <mergeCell ref="D13:G14"/>
-    <mergeCell ref="D15:G16"/>
-    <mergeCell ref="D17:G18"/>
-    <mergeCell ref="D19:G20"/>
-    <mergeCell ref="C21:G22"/>
-    <mergeCell ref="D23:G24"/>
-    <mergeCell ref="C25:G26"/>
-    <mergeCell ref="D27:G28"/>
-    <mergeCell ref="D29:G30"/>
-    <mergeCell ref="J3:CJ3"/>
-    <mergeCell ref="CK3:DO3"/>
-    <mergeCell ref="J4:AA4"/>
-    <mergeCell ref="AB4:BE4"/>
-    <mergeCell ref="BF4:CJ4"/>
-    <mergeCell ref="CK4:DO4"/>
-    <mergeCell ref="B7:G8"/>
-    <mergeCell ref="C9:G10"/>
-    <mergeCell ref="C11:G12"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="E139:G140"/>
+    <mergeCell ref="D139:D140"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="I139:I140"/>
+    <mergeCell ref="C79:G80"/>
+    <mergeCell ref="C89:G90"/>
+    <mergeCell ref="C105:G106"/>
+    <mergeCell ref="C121:G122"/>
+    <mergeCell ref="H113:H114"/>
+    <mergeCell ref="I113:I114"/>
+    <mergeCell ref="E101:G102"/>
+    <mergeCell ref="H101:H102"/>
+    <mergeCell ref="I101:I102"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="H89:H90"/>
+    <mergeCell ref="I89:I90"/>
+    <mergeCell ref="H133:H134"/>
+    <mergeCell ref="I133:I134"/>
+    <mergeCell ref="E133:G134"/>
+    <mergeCell ref="H127:H128"/>
+    <mergeCell ref="I127:I128"/>
+    <mergeCell ref="I129:I130"/>
+    <mergeCell ref="H129:H130"/>
+    <mergeCell ref="H135:H136"/>
+    <mergeCell ref="I135:I136"/>
+    <mergeCell ref="E127:G128"/>
+    <mergeCell ref="E129:G130"/>
+    <mergeCell ref="E131:G132"/>
+    <mergeCell ref="D135:G136"/>
+    <mergeCell ref="E137:G138"/>
+    <mergeCell ref="E117:G118"/>
+    <mergeCell ref="E113:G114"/>
+    <mergeCell ref="E123:G124"/>
+    <mergeCell ref="E125:G126"/>
+    <mergeCell ref="D115:G116"/>
+    <mergeCell ref="D119:G120"/>
+    <mergeCell ref="H131:H132"/>
+    <mergeCell ref="I131:I132"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="I123:I124"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="I109:I110"/>
+    <mergeCell ref="H111:H112"/>
+    <mergeCell ref="I111:I112"/>
+    <mergeCell ref="D103:G104"/>
+    <mergeCell ref="E107:G108"/>
+    <mergeCell ref="E109:G110"/>
+    <mergeCell ref="E111:G112"/>
+    <mergeCell ref="H125:H126"/>
+    <mergeCell ref="I125:I126"/>
+    <mergeCell ref="H103:H104"/>
+    <mergeCell ref="I103:I104"/>
+    <mergeCell ref="H105:H106"/>
+    <mergeCell ref="I105:I106"/>
+    <mergeCell ref="H107:H108"/>
+    <mergeCell ref="H115:H116"/>
+    <mergeCell ref="I115:I116"/>
+    <mergeCell ref="H117:H118"/>
+    <mergeCell ref="I117:I118"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="I119:I120"/>
+    <mergeCell ref="H121:H122"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="H123:H124"/>
+    <mergeCell ref="D77:G78"/>
+    <mergeCell ref="E81:G82"/>
+    <mergeCell ref="E83:G84"/>
+    <mergeCell ref="E85:G86"/>
+    <mergeCell ref="E91:G92"/>
+    <mergeCell ref="E93:G94"/>
+    <mergeCell ref="E95:G96"/>
+    <mergeCell ref="E97:G98"/>
+    <mergeCell ref="E99:G100"/>
+    <mergeCell ref="E87:G88"/>
+    <mergeCell ref="H75:H76"/>
+    <mergeCell ref="H141:H142"/>
+    <mergeCell ref="H145:H146"/>
+    <mergeCell ref="H143:H144"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="H59:H60"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="H77:H78"/>
+    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="H93:H94"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="I145:I146"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="I141:I142"/>
+    <mergeCell ref="I143:I144"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="I85:I86"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="I93:I94"/>
+    <mergeCell ref="I95:I96"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="I107:I108"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I67:I68"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="I51:I52"/>
     <mergeCell ref="C145:G146"/>
     <mergeCell ref="B143:G144"/>
     <mergeCell ref="C141:G142"/>
@@ -33981,167 +34113,36 @@
     <mergeCell ref="E55:G56"/>
     <mergeCell ref="E57:G58"/>
     <mergeCell ref="I53:I54"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="I141:I142"/>
-    <mergeCell ref="I143:I144"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="I85:I86"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="I93:I94"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="I107:I108"/>
-    <mergeCell ref="I145:I146"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="H75:H76"/>
-    <mergeCell ref="H141:H142"/>
-    <mergeCell ref="H145:H146"/>
-    <mergeCell ref="H143:H144"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="H67:H68"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H59:H60"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="H77:H78"/>
-    <mergeCell ref="H81:H82"/>
-    <mergeCell ref="H83:H84"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="H93:H94"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="D77:G78"/>
-    <mergeCell ref="E81:G82"/>
-    <mergeCell ref="E83:G84"/>
-    <mergeCell ref="E85:G86"/>
-    <mergeCell ref="E91:G92"/>
-    <mergeCell ref="E93:G94"/>
-    <mergeCell ref="E95:G96"/>
-    <mergeCell ref="E97:G98"/>
-    <mergeCell ref="E99:G100"/>
-    <mergeCell ref="E87:G88"/>
-    <mergeCell ref="H109:H110"/>
-    <mergeCell ref="I109:I110"/>
-    <mergeCell ref="H111:H112"/>
-    <mergeCell ref="I111:I112"/>
-    <mergeCell ref="D103:G104"/>
-    <mergeCell ref="E107:G108"/>
-    <mergeCell ref="E109:G110"/>
-    <mergeCell ref="E111:G112"/>
-    <mergeCell ref="H125:H126"/>
-    <mergeCell ref="I125:I126"/>
-    <mergeCell ref="H103:H104"/>
-    <mergeCell ref="I103:I104"/>
-    <mergeCell ref="H105:H106"/>
-    <mergeCell ref="I105:I106"/>
-    <mergeCell ref="H107:H108"/>
-    <mergeCell ref="H115:H116"/>
-    <mergeCell ref="I115:I116"/>
-    <mergeCell ref="H117:H118"/>
-    <mergeCell ref="I117:I118"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="I119:I120"/>
-    <mergeCell ref="H121:H122"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="H123:H124"/>
-    <mergeCell ref="H135:H136"/>
-    <mergeCell ref="I135:I136"/>
-    <mergeCell ref="E127:G128"/>
-    <mergeCell ref="E129:G130"/>
-    <mergeCell ref="E131:G132"/>
-    <mergeCell ref="D135:G136"/>
-    <mergeCell ref="E137:G138"/>
-    <mergeCell ref="E117:G118"/>
-    <mergeCell ref="E113:G114"/>
-    <mergeCell ref="E123:G124"/>
-    <mergeCell ref="E125:G126"/>
-    <mergeCell ref="D115:G116"/>
-    <mergeCell ref="D119:G120"/>
-    <mergeCell ref="H131:H132"/>
-    <mergeCell ref="I131:I132"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="I123:I124"/>
-    <mergeCell ref="E139:G140"/>
-    <mergeCell ref="D139:D140"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="I139:I140"/>
-    <mergeCell ref="C79:G80"/>
-    <mergeCell ref="C89:G90"/>
-    <mergeCell ref="C105:G106"/>
-    <mergeCell ref="C121:G122"/>
-    <mergeCell ref="H113:H114"/>
-    <mergeCell ref="I113:I114"/>
-    <mergeCell ref="E101:G102"/>
-    <mergeCell ref="H101:H102"/>
-    <mergeCell ref="I101:I102"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="H89:H90"/>
-    <mergeCell ref="I89:I90"/>
-    <mergeCell ref="H133:H134"/>
-    <mergeCell ref="I133:I134"/>
-    <mergeCell ref="E133:G134"/>
-    <mergeCell ref="H127:H128"/>
-    <mergeCell ref="I127:I128"/>
-    <mergeCell ref="I129:I130"/>
-    <mergeCell ref="H129:H130"/>
+    <mergeCell ref="J3:CJ3"/>
+    <mergeCell ref="CK3:DO3"/>
+    <mergeCell ref="J4:AA4"/>
+    <mergeCell ref="AB4:BE4"/>
+    <mergeCell ref="BF4:CJ4"/>
+    <mergeCell ref="CK4:DO4"/>
+    <mergeCell ref="B7:G8"/>
+    <mergeCell ref="C9:G10"/>
+    <mergeCell ref="C11:G12"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="D13:G14"/>
+    <mergeCell ref="D15:G16"/>
+    <mergeCell ref="D17:G18"/>
+    <mergeCell ref="D19:G20"/>
+    <mergeCell ref="C21:G22"/>
+    <mergeCell ref="D23:G24"/>
+    <mergeCell ref="C25:G26"/>
+    <mergeCell ref="D27:G28"/>
+    <mergeCell ref="D29:G30"/>
+    <mergeCell ref="E59:G60"/>
+    <mergeCell ref="E61:G62"/>
+    <mergeCell ref="D63:G64"/>
+    <mergeCell ref="E67:G68"/>
+    <mergeCell ref="E65:G66"/>
+    <mergeCell ref="E69:G70"/>
+    <mergeCell ref="E71:G72"/>
+    <mergeCell ref="C73:G74"/>
+    <mergeCell ref="C75:G76"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <conditionalFormatting sqref="J7">
@@ -34225,6 +34226,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/【DIGITAL OJT】WBS.xlsx
+++ b/docs/【DIGITAL OJT】WBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIGITALOJT\digital-ojt-development-cause-DroneInventorySystem\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB8087AD-BC94-4670-B340-347849E1A727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84453921-19C4-4841-A2FC-4D251C096DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13095" yWindow="-16395" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16905" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -1460,16 +1460,34 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1478,25 +1496,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1505,7 +1514,28 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1514,7 +1544,10 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1523,145 +1556,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1671,13 +1565,53 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1703,27 +1637,93 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2330,120 +2330,120 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="J3" s="154">
+      <c r="J3" s="144">
         <v>2024</v>
       </c>
-      <c r="K3" s="155"/>
-      <c r="L3" s="155"/>
-      <c r="M3" s="155"/>
-      <c r="N3" s="155"/>
-      <c r="O3" s="155"/>
-      <c r="P3" s="155"/>
-      <c r="Q3" s="155"/>
-      <c r="R3" s="155"/>
-      <c r="S3" s="155"/>
-      <c r="T3" s="155"/>
-      <c r="U3" s="155"/>
-      <c r="V3" s="155"/>
-      <c r="W3" s="155"/>
-      <c r="X3" s="155"/>
-      <c r="Y3" s="155"/>
-      <c r="Z3" s="155"/>
-      <c r="AA3" s="155"/>
-      <c r="AB3" s="155"/>
-      <c r="AC3" s="155"/>
-      <c r="AD3" s="155"/>
-      <c r="AE3" s="155"/>
-      <c r="AF3" s="155"/>
-      <c r="AG3" s="155"/>
-      <c r="AH3" s="155"/>
-      <c r="AI3" s="155"/>
-      <c r="AJ3" s="155"/>
-      <c r="AK3" s="155"/>
-      <c r="AL3" s="155"/>
-      <c r="AM3" s="155"/>
-      <c r="AN3" s="155"/>
-      <c r="AO3" s="155"/>
-      <c r="AP3" s="155"/>
-      <c r="AQ3" s="155"/>
-      <c r="AR3" s="155"/>
-      <c r="AS3" s="155"/>
-      <c r="AT3" s="155"/>
-      <c r="AU3" s="155"/>
-      <c r="AV3" s="155"/>
-      <c r="AW3" s="155"/>
-      <c r="AX3" s="155"/>
-      <c r="AY3" s="155"/>
-      <c r="AZ3" s="155"/>
-      <c r="BA3" s="155"/>
-      <c r="BB3" s="155"/>
-      <c r="BC3" s="155"/>
-      <c r="BD3" s="155"/>
-      <c r="BE3" s="155"/>
-      <c r="BF3" s="155"/>
-      <c r="BG3" s="155"/>
-      <c r="BH3" s="155"/>
-      <c r="BI3" s="155"/>
-      <c r="BJ3" s="155"/>
-      <c r="BK3" s="155"/>
-      <c r="BL3" s="155"/>
-      <c r="BM3" s="155"/>
-      <c r="BN3" s="155"/>
-      <c r="BO3" s="155"/>
-      <c r="BP3" s="155"/>
-      <c r="BQ3" s="155"/>
-      <c r="BR3" s="155"/>
-      <c r="BS3" s="155"/>
-      <c r="BT3" s="155"/>
-      <c r="BU3" s="155"/>
-      <c r="BV3" s="155"/>
-      <c r="BW3" s="155"/>
-      <c r="BX3" s="155"/>
-      <c r="BY3" s="155"/>
-      <c r="BZ3" s="155"/>
-      <c r="CA3" s="155"/>
-      <c r="CB3" s="155"/>
-      <c r="CC3" s="155"/>
-      <c r="CD3" s="155"/>
-      <c r="CE3" s="155"/>
-      <c r="CF3" s="155"/>
-      <c r="CG3" s="155"/>
-      <c r="CH3" s="155"/>
-      <c r="CI3" s="155"/>
-      <c r="CJ3" s="156"/>
-      <c r="CK3" s="154">
+      <c r="K3" s="145"/>
+      <c r="L3" s="145"/>
+      <c r="M3" s="145"/>
+      <c r="N3" s="145"/>
+      <c r="O3" s="145"/>
+      <c r="P3" s="145"/>
+      <c r="Q3" s="145"/>
+      <c r="R3" s="145"/>
+      <c r="S3" s="145"/>
+      <c r="T3" s="145"/>
+      <c r="U3" s="145"/>
+      <c r="V3" s="145"/>
+      <c r="W3" s="145"/>
+      <c r="X3" s="145"/>
+      <c r="Y3" s="145"/>
+      <c r="Z3" s="145"/>
+      <c r="AA3" s="145"/>
+      <c r="AB3" s="145"/>
+      <c r="AC3" s="145"/>
+      <c r="AD3" s="145"/>
+      <c r="AE3" s="145"/>
+      <c r="AF3" s="145"/>
+      <c r="AG3" s="145"/>
+      <c r="AH3" s="145"/>
+      <c r="AI3" s="145"/>
+      <c r="AJ3" s="145"/>
+      <c r="AK3" s="145"/>
+      <c r="AL3" s="145"/>
+      <c r="AM3" s="145"/>
+      <c r="AN3" s="145"/>
+      <c r="AO3" s="145"/>
+      <c r="AP3" s="145"/>
+      <c r="AQ3" s="145"/>
+      <c r="AR3" s="145"/>
+      <c r="AS3" s="145"/>
+      <c r="AT3" s="145"/>
+      <c r="AU3" s="145"/>
+      <c r="AV3" s="145"/>
+      <c r="AW3" s="145"/>
+      <c r="AX3" s="145"/>
+      <c r="AY3" s="145"/>
+      <c r="AZ3" s="145"/>
+      <c r="BA3" s="145"/>
+      <c r="BB3" s="145"/>
+      <c r="BC3" s="145"/>
+      <c r="BD3" s="145"/>
+      <c r="BE3" s="145"/>
+      <c r="BF3" s="145"/>
+      <c r="BG3" s="145"/>
+      <c r="BH3" s="145"/>
+      <c r="BI3" s="145"/>
+      <c r="BJ3" s="145"/>
+      <c r="BK3" s="145"/>
+      <c r="BL3" s="145"/>
+      <c r="BM3" s="145"/>
+      <c r="BN3" s="145"/>
+      <c r="BO3" s="145"/>
+      <c r="BP3" s="145"/>
+      <c r="BQ3" s="145"/>
+      <c r="BR3" s="145"/>
+      <c r="BS3" s="145"/>
+      <c r="BT3" s="145"/>
+      <c r="BU3" s="145"/>
+      <c r="BV3" s="145"/>
+      <c r="BW3" s="145"/>
+      <c r="BX3" s="145"/>
+      <c r="BY3" s="145"/>
+      <c r="BZ3" s="145"/>
+      <c r="CA3" s="145"/>
+      <c r="CB3" s="145"/>
+      <c r="CC3" s="145"/>
+      <c r="CD3" s="145"/>
+      <c r="CE3" s="145"/>
+      <c r="CF3" s="145"/>
+      <c r="CG3" s="145"/>
+      <c r="CH3" s="145"/>
+      <c r="CI3" s="145"/>
+      <c r="CJ3" s="146"/>
+      <c r="CK3" s="144">
         <v>2025</v>
       </c>
-      <c r="CL3" s="155"/>
-      <c r="CM3" s="155"/>
-      <c r="CN3" s="155"/>
-      <c r="CO3" s="155"/>
-      <c r="CP3" s="155"/>
-      <c r="CQ3" s="155"/>
-      <c r="CR3" s="155"/>
-      <c r="CS3" s="155"/>
-      <c r="CT3" s="155"/>
-      <c r="CU3" s="155"/>
-      <c r="CV3" s="155"/>
-      <c r="CW3" s="155"/>
-      <c r="CX3" s="155"/>
-      <c r="CY3" s="155"/>
-      <c r="CZ3" s="155"/>
-      <c r="DA3" s="155"/>
-      <c r="DB3" s="155"/>
-      <c r="DC3" s="155"/>
-      <c r="DD3" s="155"/>
-      <c r="DE3" s="155"/>
-      <c r="DF3" s="155"/>
-      <c r="DG3" s="155"/>
-      <c r="DH3" s="155"/>
-      <c r="DI3" s="155"/>
-      <c r="DJ3" s="155"/>
-      <c r="DK3" s="155"/>
-      <c r="DL3" s="155"/>
-      <c r="DM3" s="155"/>
-      <c r="DN3" s="155"/>
-      <c r="DO3" s="156"/>
+      <c r="CL3" s="145"/>
+      <c r="CM3" s="145"/>
+      <c r="CN3" s="145"/>
+      <c r="CO3" s="145"/>
+      <c r="CP3" s="145"/>
+      <c r="CQ3" s="145"/>
+      <c r="CR3" s="145"/>
+      <c r="CS3" s="145"/>
+      <c r="CT3" s="145"/>
+      <c r="CU3" s="145"/>
+      <c r="CV3" s="145"/>
+      <c r="CW3" s="145"/>
+      <c r="CX3" s="145"/>
+      <c r="CY3" s="145"/>
+      <c r="CZ3" s="145"/>
+      <c r="DA3" s="145"/>
+      <c r="DB3" s="145"/>
+      <c r="DC3" s="145"/>
+      <c r="DD3" s="145"/>
+      <c r="DE3" s="145"/>
+      <c r="DF3" s="145"/>
+      <c r="DG3" s="145"/>
+      <c r="DH3" s="145"/>
+      <c r="DI3" s="145"/>
+      <c r="DJ3" s="145"/>
+      <c r="DK3" s="145"/>
+      <c r="DL3" s="145"/>
+      <c r="DM3" s="145"/>
+      <c r="DN3" s="145"/>
+      <c r="DO3" s="146"/>
       <c r="DP3" s="1"/>
     </row>
     <row r="4" spans="1:120" ht="18" customHeight="1">
@@ -2458,124 +2458,124 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="J4" s="154">
+      <c r="J4" s="144">
         <v>10</v>
       </c>
-      <c r="K4" s="155"/>
-      <c r="L4" s="155"/>
-      <c r="M4" s="155"/>
-      <c r="N4" s="155"/>
-      <c r="O4" s="155"/>
-      <c r="P4" s="155"/>
-      <c r="Q4" s="155"/>
-      <c r="R4" s="155"/>
-      <c r="S4" s="155"/>
-      <c r="T4" s="155"/>
-      <c r="U4" s="155"/>
-      <c r="V4" s="155"/>
-      <c r="W4" s="155"/>
-      <c r="X4" s="155"/>
-      <c r="Y4" s="155"/>
-      <c r="Z4" s="155"/>
-      <c r="AA4" s="156"/>
-      <c r="AB4" s="154">
+      <c r="K4" s="145"/>
+      <c r="L4" s="145"/>
+      <c r="M4" s="145"/>
+      <c r="N4" s="145"/>
+      <c r="O4" s="145"/>
+      <c r="P4" s="145"/>
+      <c r="Q4" s="145"/>
+      <c r="R4" s="145"/>
+      <c r="S4" s="145"/>
+      <c r="T4" s="145"/>
+      <c r="U4" s="145"/>
+      <c r="V4" s="145"/>
+      <c r="W4" s="145"/>
+      <c r="X4" s="145"/>
+      <c r="Y4" s="145"/>
+      <c r="Z4" s="145"/>
+      <c r="AA4" s="146"/>
+      <c r="AB4" s="144">
         <v>11</v>
       </c>
-      <c r="AC4" s="155"/>
-      <c r="AD4" s="155"/>
-      <c r="AE4" s="155"/>
-      <c r="AF4" s="155"/>
-      <c r="AG4" s="155"/>
-      <c r="AH4" s="155"/>
-      <c r="AI4" s="155"/>
-      <c r="AJ4" s="155"/>
-      <c r="AK4" s="155"/>
-      <c r="AL4" s="155"/>
-      <c r="AM4" s="155"/>
-      <c r="AN4" s="155"/>
-      <c r="AO4" s="155"/>
-      <c r="AP4" s="155"/>
-      <c r="AQ4" s="155"/>
-      <c r="AR4" s="155"/>
-      <c r="AS4" s="155"/>
-      <c r="AT4" s="155"/>
-      <c r="AU4" s="155"/>
-      <c r="AV4" s="155"/>
-      <c r="AW4" s="155"/>
-      <c r="AX4" s="155"/>
-      <c r="AY4" s="155"/>
-      <c r="AZ4" s="155"/>
-      <c r="BA4" s="155"/>
-      <c r="BB4" s="155"/>
-      <c r="BC4" s="155"/>
-      <c r="BD4" s="155"/>
-      <c r="BE4" s="156"/>
-      <c r="BF4" s="154">
+      <c r="AC4" s="145"/>
+      <c r="AD4" s="145"/>
+      <c r="AE4" s="145"/>
+      <c r="AF4" s="145"/>
+      <c r="AG4" s="145"/>
+      <c r="AH4" s="145"/>
+      <c r="AI4" s="145"/>
+      <c r="AJ4" s="145"/>
+      <c r="AK4" s="145"/>
+      <c r="AL4" s="145"/>
+      <c r="AM4" s="145"/>
+      <c r="AN4" s="145"/>
+      <c r="AO4" s="145"/>
+      <c r="AP4" s="145"/>
+      <c r="AQ4" s="145"/>
+      <c r="AR4" s="145"/>
+      <c r="AS4" s="145"/>
+      <c r="AT4" s="145"/>
+      <c r="AU4" s="145"/>
+      <c r="AV4" s="145"/>
+      <c r="AW4" s="145"/>
+      <c r="AX4" s="145"/>
+      <c r="AY4" s="145"/>
+      <c r="AZ4" s="145"/>
+      <c r="BA4" s="145"/>
+      <c r="BB4" s="145"/>
+      <c r="BC4" s="145"/>
+      <c r="BD4" s="145"/>
+      <c r="BE4" s="146"/>
+      <c r="BF4" s="144">
         <v>12</v>
       </c>
-      <c r="BG4" s="155"/>
-      <c r="BH4" s="155"/>
-      <c r="BI4" s="155"/>
-      <c r="BJ4" s="155"/>
-      <c r="BK4" s="155"/>
-      <c r="BL4" s="155"/>
-      <c r="BM4" s="155"/>
-      <c r="BN4" s="155"/>
-      <c r="BO4" s="155"/>
-      <c r="BP4" s="155"/>
-      <c r="BQ4" s="155"/>
-      <c r="BR4" s="155"/>
-      <c r="BS4" s="155"/>
-      <c r="BT4" s="155"/>
-      <c r="BU4" s="155"/>
-      <c r="BV4" s="155"/>
-      <c r="BW4" s="155"/>
-      <c r="BX4" s="155"/>
-      <c r="BY4" s="155"/>
-      <c r="BZ4" s="155"/>
-      <c r="CA4" s="155"/>
-      <c r="CB4" s="155"/>
-      <c r="CC4" s="155"/>
-      <c r="CD4" s="155"/>
-      <c r="CE4" s="155"/>
-      <c r="CF4" s="155"/>
-      <c r="CG4" s="155"/>
-      <c r="CH4" s="155"/>
-      <c r="CI4" s="155"/>
-      <c r="CJ4" s="156"/>
-      <c r="CK4" s="154">
+      <c r="BG4" s="145"/>
+      <c r="BH4" s="145"/>
+      <c r="BI4" s="145"/>
+      <c r="BJ4" s="145"/>
+      <c r="BK4" s="145"/>
+      <c r="BL4" s="145"/>
+      <c r="BM4" s="145"/>
+      <c r="BN4" s="145"/>
+      <c r="BO4" s="145"/>
+      <c r="BP4" s="145"/>
+      <c r="BQ4" s="145"/>
+      <c r="BR4" s="145"/>
+      <c r="BS4" s="145"/>
+      <c r="BT4" s="145"/>
+      <c r="BU4" s="145"/>
+      <c r="BV4" s="145"/>
+      <c r="BW4" s="145"/>
+      <c r="BX4" s="145"/>
+      <c r="BY4" s="145"/>
+      <c r="BZ4" s="145"/>
+      <c r="CA4" s="145"/>
+      <c r="CB4" s="145"/>
+      <c r="CC4" s="145"/>
+      <c r="CD4" s="145"/>
+      <c r="CE4" s="145"/>
+      <c r="CF4" s="145"/>
+      <c r="CG4" s="145"/>
+      <c r="CH4" s="145"/>
+      <c r="CI4" s="145"/>
+      <c r="CJ4" s="146"/>
+      <c r="CK4" s="144">
         <v>1</v>
       </c>
-      <c r="CL4" s="155"/>
-      <c r="CM4" s="155"/>
-      <c r="CN4" s="155"/>
-      <c r="CO4" s="155"/>
-      <c r="CP4" s="155"/>
-      <c r="CQ4" s="155"/>
-      <c r="CR4" s="155"/>
-      <c r="CS4" s="155"/>
-      <c r="CT4" s="155"/>
-      <c r="CU4" s="155"/>
-      <c r="CV4" s="155"/>
-      <c r="CW4" s="155"/>
-      <c r="CX4" s="155"/>
-      <c r="CY4" s="155"/>
-      <c r="CZ4" s="155"/>
-      <c r="DA4" s="155"/>
-      <c r="DB4" s="155"/>
-      <c r="DC4" s="155"/>
-      <c r="DD4" s="155"/>
-      <c r="DE4" s="155"/>
-      <c r="DF4" s="155"/>
-      <c r="DG4" s="155"/>
-      <c r="DH4" s="155"/>
-      <c r="DI4" s="155"/>
-      <c r="DJ4" s="155"/>
-      <c r="DK4" s="155"/>
-      <c r="DL4" s="155"/>
-      <c r="DM4" s="155"/>
-      <c r="DN4" s="155"/>
-      <c r="DO4" s="156"/>
+      <c r="CL4" s="145"/>
+      <c r="CM4" s="145"/>
+      <c r="CN4" s="145"/>
+      <c r="CO4" s="145"/>
+      <c r="CP4" s="145"/>
+      <c r="CQ4" s="145"/>
+      <c r="CR4" s="145"/>
+      <c r="CS4" s="145"/>
+      <c r="CT4" s="145"/>
+      <c r="CU4" s="145"/>
+      <c r="CV4" s="145"/>
+      <c r="CW4" s="145"/>
+      <c r="CX4" s="145"/>
+      <c r="CY4" s="145"/>
+      <c r="CZ4" s="145"/>
+      <c r="DA4" s="145"/>
+      <c r="DB4" s="145"/>
+      <c r="DC4" s="145"/>
+      <c r="DD4" s="145"/>
+      <c r="DE4" s="145"/>
+      <c r="DF4" s="145"/>
+      <c r="DG4" s="145"/>
+      <c r="DH4" s="145"/>
+      <c r="DI4" s="145"/>
+      <c r="DJ4" s="145"/>
+      <c r="DK4" s="145"/>
+      <c r="DL4" s="145"/>
+      <c r="DM4" s="145"/>
+      <c r="DN4" s="145"/>
+      <c r="DO4" s="146"/>
       <c r="DP4" s="6"/>
     </row>
     <row r="5" spans="1:120" ht="18" customHeight="1">
@@ -3370,18 +3370,18 @@
     </row>
     <row r="7" spans="1:120" ht="9.75" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="157" t="s">
+      <c r="B7" s="147" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="137"/>
-      <c r="D7" s="137"/>
-      <c r="E7" s="137"/>
-      <c r="F7" s="137"/>
-      <c r="G7" s="158"/>
-      <c r="H7" s="135" t="s">
+      <c r="C7" s="123"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="123"/>
+      <c r="F7" s="123"/>
+      <c r="G7" s="135"/>
+      <c r="H7" s="149" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="135" t="s">
+      <c r="I7" s="149" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="38"/>
@@ -3498,14 +3498,14 @@
     </row>
     <row r="8" spans="1:120" ht="9.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="143"/>
-      <c r="C8" s="140"/>
-      <c r="D8" s="140"/>
-      <c r="E8" s="140"/>
-      <c r="F8" s="140"/>
-      <c r="G8" s="141"/>
-      <c r="H8" s="135"/>
-      <c r="I8" s="135"/>
+      <c r="B8" s="125"/>
+      <c r="C8" s="126"/>
+      <c r="D8" s="126"/>
+      <c r="E8" s="126"/>
+      <c r="F8" s="126"/>
+      <c r="G8" s="130"/>
+      <c r="H8" s="149"/>
+      <c r="I8" s="149"/>
       <c r="J8" s="39"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
@@ -3621,15 +3621,15 @@
     <row r="9" spans="1:120" ht="9.75" customHeight="1">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
-      <c r="C9" s="159" t="s">
+      <c r="C9" s="148" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="147"/>
-      <c r="E9" s="147"/>
-      <c r="F9" s="147"/>
-      <c r="G9" s="145"/>
-      <c r="H9" s="132"/>
-      <c r="I9" s="132"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="137"/>
+      <c r="F9" s="137"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="150"/>
+      <c r="I9" s="150"/>
       <c r="J9" s="42"/>
       <c r="K9" s="42"/>
       <c r="L9" s="44"/>
@@ -3745,13 +3745,13 @@
     <row r="10" spans="1:120" ht="9.75" customHeight="1">
       <c r="A10" s="16"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="139"/>
-      <c r="D10" s="140"/>
-      <c r="E10" s="140"/>
-      <c r="F10" s="140"/>
-      <c r="G10" s="141"/>
-      <c r="H10" s="132"/>
-      <c r="I10" s="132"/>
+      <c r="C10" s="132"/>
+      <c r="D10" s="126"/>
+      <c r="E10" s="126"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="130"/>
+      <c r="H10" s="150"/>
+      <c r="I10" s="150"/>
       <c r="J10" s="46"/>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
@@ -3867,15 +3867,15 @@
     <row r="11" spans="1:120" ht="9.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="160" t="s">
+      <c r="C11" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="147"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="147"/>
-      <c r="G11" s="145"/>
-      <c r="H11" s="132"/>
-      <c r="I11" s="132"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="137"/>
+      <c r="G11" s="133"/>
+      <c r="H11" s="150"/>
+      <c r="I11" s="150"/>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
       <c r="L11" s="44"/>
@@ -3991,13 +3991,13 @@
     <row r="12" spans="1:120" ht="9.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="139"/>
-      <c r="D12" s="140"/>
-      <c r="E12" s="140"/>
-      <c r="F12" s="140"/>
-      <c r="G12" s="141"/>
-      <c r="H12" s="132"/>
-      <c r="I12" s="132"/>
+      <c r="C12" s="132"/>
+      <c r="D12" s="126"/>
+      <c r="E12" s="126"/>
+      <c r="F12" s="126"/>
+      <c r="G12" s="130"/>
+      <c r="H12" s="150"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="46"/>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
@@ -4114,16 +4114,16 @@
       <c r="A13" s="1"/>
       <c r="B13" s="18"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="161" t="s">
+      <c r="D13" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="137"/>
-      <c r="F13" s="137"/>
-      <c r="G13" s="158"/>
-      <c r="H13" s="131" t="s">
+      <c r="E13" s="123"/>
+      <c r="F13" s="123"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="166" t="s">
         <v>40</v>
       </c>
-      <c r="I13" s="99">
+      <c r="I13" s="104">
         <v>100</v>
       </c>
       <c r="J13" s="39"/>
@@ -4242,12 +4242,12 @@
       <c r="A14" s="1"/>
       <c r="B14" s="18"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="143"/>
-      <c r="E14" s="140"/>
-      <c r="F14" s="140"/>
-      <c r="G14" s="141"/>
-      <c r="H14" s="99"/>
-      <c r="I14" s="99"/>
+      <c r="D14" s="125"/>
+      <c r="E14" s="126"/>
+      <c r="F14" s="126"/>
+      <c r="G14" s="130"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="104"/>
       <c r="J14" s="39"/>
       <c r="K14" s="53"/>
       <c r="L14" s="15"/>
@@ -4364,16 +4364,16 @@
       <c r="A15" s="1"/>
       <c r="B15" s="18"/>
       <c r="C15" s="24"/>
-      <c r="D15" s="161" t="s">
+      <c r="D15" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="137"/>
-      <c r="F15" s="137"/>
-      <c r="G15" s="142"/>
-      <c r="H15" s="131" t="s">
+      <c r="E15" s="123"/>
+      <c r="F15" s="123"/>
+      <c r="G15" s="124"/>
+      <c r="H15" s="166" t="s">
         <v>40</v>
       </c>
-      <c r="I15" s="99">
+      <c r="I15" s="104">
         <v>100</v>
       </c>
       <c r="J15" s="14"/>
@@ -4492,12 +4492,12 @@
       <c r="A16" s="1"/>
       <c r="B16" s="18"/>
       <c r="C16" s="24"/>
-      <c r="D16" s="143"/>
-      <c r="E16" s="140"/>
-      <c r="F16" s="140"/>
-      <c r="G16" s="144"/>
-      <c r="H16" s="99"/>
-      <c r="I16" s="99"/>
+      <c r="D16" s="125"/>
+      <c r="E16" s="126"/>
+      <c r="F16" s="126"/>
+      <c r="G16" s="127"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="104"/>
       <c r="J16" s="14"/>
       <c r="K16" s="53"/>
       <c r="L16" s="15"/>
@@ -4614,16 +4614,16 @@
       <c r="A17" s="1"/>
       <c r="B17" s="18"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="161" t="s">
+      <c r="D17" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="137"/>
-      <c r="F17" s="137"/>
-      <c r="G17" s="142"/>
-      <c r="H17" s="131" t="s">
+      <c r="E17" s="123"/>
+      <c r="F17" s="123"/>
+      <c r="G17" s="124"/>
+      <c r="H17" s="166" t="s">
         <v>40</v>
       </c>
-      <c r="I17" s="99">
+      <c r="I17" s="104">
         <v>100</v>
       </c>
       <c r="J17" s="14"/>
@@ -4742,12 +4742,12 @@
       <c r="A18" s="1"/>
       <c r="B18" s="18"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="143"/>
-      <c r="E18" s="140"/>
-      <c r="F18" s="140"/>
-      <c r="G18" s="144"/>
-      <c r="H18" s="99"/>
-      <c r="I18" s="99"/>
+      <c r="D18" s="125"/>
+      <c r="E18" s="126"/>
+      <c r="F18" s="126"/>
+      <c r="G18" s="127"/>
+      <c r="H18" s="104"/>
+      <c r="I18" s="104"/>
       <c r="J18" s="14"/>
       <c r="K18" s="53"/>
       <c r="L18" s="15"/>
@@ -4864,16 +4864,16 @@
       <c r="A19" s="1"/>
       <c r="B19" s="18"/>
       <c r="C19" s="24"/>
-      <c r="D19" s="161" t="s">
+      <c r="D19" s="134" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="137"/>
-      <c r="F19" s="137"/>
-      <c r="G19" s="142"/>
-      <c r="H19" s="131" t="s">
+      <c r="E19" s="123"/>
+      <c r="F19" s="123"/>
+      <c r="G19" s="124"/>
+      <c r="H19" s="166" t="s">
         <v>40</v>
       </c>
-      <c r="I19" s="99">
+      <c r="I19" s="104">
         <v>100</v>
       </c>
       <c r="J19" s="14"/>
@@ -4992,12 +4992,12 @@
       <c r="A20" s="1"/>
       <c r="B20" s="18"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="143"/>
-      <c r="E20" s="140"/>
-      <c r="F20" s="140"/>
-      <c r="G20" s="144"/>
-      <c r="H20" s="99"/>
-      <c r="I20" s="99"/>
+      <c r="D20" s="125"/>
+      <c r="E20" s="126"/>
+      <c r="F20" s="126"/>
+      <c r="G20" s="127"/>
+      <c r="H20" s="104"/>
+      <c r="I20" s="104"/>
       <c r="J20" s="26"/>
       <c r="K20" s="54"/>
       <c r="L20" s="27"/>
@@ -5113,15 +5113,15 @@
     <row r="21" spans="1:120" ht="9.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="18"/>
-      <c r="C21" s="160" t="s">
+      <c r="C21" s="136" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="147"/>
-      <c r="E21" s="147"/>
-      <c r="F21" s="147"/>
-      <c r="G21" s="148"/>
-      <c r="H21" s="132"/>
-      <c r="I21" s="132"/>
+      <c r="D21" s="137"/>
+      <c r="E21" s="137"/>
+      <c r="F21" s="137"/>
+      <c r="G21" s="138"/>
+      <c r="H21" s="150"/>
+      <c r="I21" s="150"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="44"/>
@@ -5237,13 +5237,13 @@
     <row r="22" spans="1:120" ht="9.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="18"/>
-      <c r="C22" s="149"/>
-      <c r="D22" s="150"/>
-      <c r="E22" s="150"/>
-      <c r="F22" s="150"/>
-      <c r="G22" s="145"/>
-      <c r="H22" s="132"/>
-      <c r="I22" s="132"/>
+      <c r="C22" s="139"/>
+      <c r="D22" s="140"/>
+      <c r="E22" s="140"/>
+      <c r="F22" s="140"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="150"/>
+      <c r="I22" s="150"/>
       <c r="J22" s="46"/>
       <c r="K22" s="47"/>
       <c r="L22" s="47"/>
@@ -5360,16 +5360,16 @@
       <c r="A23" s="1"/>
       <c r="B23" s="28"/>
       <c r="C23" s="29"/>
-      <c r="D23" s="162" t="s">
+      <c r="D23" s="141" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="137"/>
-      <c r="F23" s="137"/>
-      <c r="G23" s="142"/>
-      <c r="H23" s="131" t="s">
+      <c r="E23" s="123"/>
+      <c r="F23" s="123"/>
+      <c r="G23" s="124"/>
+      <c r="H23" s="166" t="s">
         <v>46</v>
       </c>
-      <c r="I23" s="99">
+      <c r="I23" s="104">
         <v>100</v>
       </c>
       <c r="J23" s="14"/>
@@ -5488,12 +5488,12 @@
       <c r="A24" s="1"/>
       <c r="B24" s="18"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="143"/>
-      <c r="E24" s="140"/>
-      <c r="F24" s="140"/>
-      <c r="G24" s="144"/>
-      <c r="H24" s="99"/>
-      <c r="I24" s="99"/>
+      <c r="D24" s="125"/>
+      <c r="E24" s="126"/>
+      <c r="F24" s="126"/>
+      <c r="G24" s="127"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="104"/>
       <c r="J24" s="14"/>
       <c r="K24" s="15"/>
       <c r="L24" s="53"/>
@@ -5609,15 +5609,15 @@
     <row r="25" spans="1:120" ht="9.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="18"/>
-      <c r="C25" s="160" t="s">
+      <c r="C25" s="136" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="147"/>
-      <c r="E25" s="147"/>
-      <c r="F25" s="147"/>
-      <c r="G25" s="148"/>
-      <c r="H25" s="132"/>
-      <c r="I25" s="132"/>
+      <c r="D25" s="137"/>
+      <c r="E25" s="137"/>
+      <c r="F25" s="137"/>
+      <c r="G25" s="138"/>
+      <c r="H25" s="150"/>
+      <c r="I25" s="150"/>
       <c r="J25" s="42"/>
       <c r="K25" s="42"/>
       <c r="L25" s="44"/>
@@ -5733,13 +5733,13 @@
     <row r="26" spans="1:120" ht="9.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="18"/>
-      <c r="C26" s="139"/>
-      <c r="D26" s="140"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="140"/>
-      <c r="G26" s="141"/>
-      <c r="H26" s="132"/>
-      <c r="I26" s="132"/>
+      <c r="C26" s="132"/>
+      <c r="D26" s="126"/>
+      <c r="E26" s="126"/>
+      <c r="F26" s="126"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="150"/>
+      <c r="I26" s="150"/>
       <c r="J26" s="46"/>
       <c r="K26" s="47"/>
       <c r="L26" s="47"/>
@@ -5856,16 +5856,16 @@
       <c r="A27" s="1"/>
       <c r="B27" s="28"/>
       <c r="C27" s="29"/>
-      <c r="D27" s="162" t="s">
+      <c r="D27" s="141" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="137"/>
-      <c r="F27" s="137"/>
-      <c r="G27" s="142"/>
-      <c r="H27" s="131" t="s">
+      <c r="E27" s="123"/>
+      <c r="F27" s="123"/>
+      <c r="G27" s="124"/>
+      <c r="H27" s="166" t="s">
         <v>44</v>
       </c>
-      <c r="I27" s="99">
+      <c r="I27" s="104">
         <v>100</v>
       </c>
       <c r="J27" s="14"/>
@@ -5984,12 +5984,12 @@
       <c r="A28" s="1"/>
       <c r="B28" s="28"/>
       <c r="C28" s="30"/>
-      <c r="D28" s="143"/>
-      <c r="E28" s="140"/>
-      <c r="F28" s="140"/>
-      <c r="G28" s="144"/>
-      <c r="H28" s="99"/>
-      <c r="I28" s="99"/>
+      <c r="D28" s="125"/>
+      <c r="E28" s="126"/>
+      <c r="F28" s="126"/>
+      <c r="G28" s="127"/>
+      <c r="H28" s="104"/>
+      <c r="I28" s="104"/>
       <c r="J28" s="14"/>
       <c r="K28" s="15"/>
       <c r="L28" s="15"/>
@@ -6106,16 +6106,16 @@
       <c r="A29" s="1"/>
       <c r="B29" s="28"/>
       <c r="C29" s="30"/>
-      <c r="D29" s="163" t="s">
+      <c r="D29" s="142" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="164"/>
-      <c r="F29" s="164"/>
-      <c r="G29" s="164"/>
-      <c r="H29" s="131" t="s">
+      <c r="E29" s="143"/>
+      <c r="F29" s="143"/>
+      <c r="G29" s="143"/>
+      <c r="H29" s="166" t="s">
         <v>44</v>
       </c>
-      <c r="I29" s="99">
+      <c r="I29" s="104">
         <v>100</v>
       </c>
       <c r="J29" s="14"/>
@@ -6234,12 +6234,12 @@
       <c r="A30" s="1"/>
       <c r="B30" s="28"/>
       <c r="C30" s="31"/>
-      <c r="D30" s="143"/>
-      <c r="E30" s="140"/>
-      <c r="F30" s="140"/>
-      <c r="G30" s="140"/>
-      <c r="H30" s="99"/>
-      <c r="I30" s="99"/>
+      <c r="D30" s="125"/>
+      <c r="E30" s="126"/>
+      <c r="F30" s="126"/>
+      <c r="G30" s="126"/>
+      <c r="H30" s="104"/>
+      <c r="I30" s="104"/>
       <c r="J30" s="26"/>
       <c r="K30" s="27"/>
       <c r="L30" s="27"/>
@@ -6355,15 +6355,15 @@
     <row r="31" spans="1:120" ht="9.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="18"/>
-      <c r="C31" s="146" t="s">
+      <c r="C31" s="162" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="147"/>
-      <c r="E31" s="147"/>
-      <c r="F31" s="147"/>
-      <c r="G31" s="148"/>
-      <c r="H31" s="132"/>
-      <c r="I31" s="132"/>
+      <c r="D31" s="137"/>
+      <c r="E31" s="137"/>
+      <c r="F31" s="137"/>
+      <c r="G31" s="138"/>
+      <c r="H31" s="150"/>
+      <c r="I31" s="150"/>
       <c r="J31" s="42"/>
       <c r="K31" s="43"/>
       <c r="L31" s="44"/>
@@ -6479,13 +6479,13 @@
     <row r="32" spans="1:120" ht="9.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="18"/>
-      <c r="C32" s="149"/>
-      <c r="D32" s="150"/>
-      <c r="E32" s="150"/>
-      <c r="F32" s="150"/>
-      <c r="G32" s="145"/>
-      <c r="H32" s="132"/>
-      <c r="I32" s="132"/>
+      <c r="C32" s="139"/>
+      <c r="D32" s="140"/>
+      <c r="E32" s="140"/>
+      <c r="F32" s="140"/>
+      <c r="G32" s="133"/>
+      <c r="H32" s="150"/>
+      <c r="I32" s="150"/>
       <c r="J32" s="46"/>
       <c r="K32" s="47"/>
       <c r="L32" s="47"/>
@@ -6602,14 +6602,14 @@
       <c r="A33" s="1"/>
       <c r="B33" s="18"/>
       <c r="C33" s="32"/>
-      <c r="D33" s="151" t="s">
+      <c r="D33" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="137"/>
-      <c r="F33" s="137"/>
-      <c r="G33" s="138"/>
-      <c r="H33" s="132"/>
-      <c r="I33" s="132"/>
+      <c r="E33" s="123"/>
+      <c r="F33" s="123"/>
+      <c r="G33" s="129"/>
+      <c r="H33" s="150"/>
+      <c r="I33" s="150"/>
       <c r="J33" s="50"/>
       <c r="K33" s="51"/>
       <c r="L33" s="51"/>
@@ -6726,12 +6726,12 @@
       <c r="A34" s="1"/>
       <c r="B34" s="18"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="143"/>
-      <c r="E34" s="140"/>
-      <c r="F34" s="140"/>
-      <c r="G34" s="141"/>
-      <c r="H34" s="132"/>
-      <c r="I34" s="132"/>
+      <c r="D34" s="125"/>
+      <c r="E34" s="126"/>
+      <c r="F34" s="126"/>
+      <c r="G34" s="130"/>
+      <c r="H34" s="150"/>
+      <c r="I34" s="150"/>
       <c r="J34" s="52"/>
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
@@ -6849,15 +6849,15 @@
       <c r="B35" s="18"/>
       <c r="C35" s="1"/>
       <c r="D35" s="33"/>
-      <c r="E35" s="152" t="s">
+      <c r="E35" s="122" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="137"/>
-      <c r="G35" s="142"/>
-      <c r="H35" s="131" t="s">
+      <c r="F35" s="123"/>
+      <c r="G35" s="124"/>
+      <c r="H35" s="166" t="s">
         <v>45</v>
       </c>
-      <c r="I35" s="99">
+      <c r="I35" s="104">
         <v>100</v>
       </c>
       <c r="J35" s="14"/>
@@ -6977,11 +6977,11 @@
       <c r="B36" s="18"/>
       <c r="C36" s="1"/>
       <c r="D36" s="34"/>
-      <c r="E36" s="143"/>
-      <c r="F36" s="140"/>
-      <c r="G36" s="144"/>
-      <c r="H36" s="99"/>
-      <c r="I36" s="99"/>
+      <c r="E36" s="125"/>
+      <c r="F36" s="126"/>
+      <c r="G36" s="127"/>
+      <c r="H36" s="104"/>
+      <c r="I36" s="104"/>
       <c r="J36" s="14"/>
       <c r="K36" s="15"/>
       <c r="L36" s="15"/>
@@ -7099,15 +7099,15 @@
       <c r="B37" s="18"/>
       <c r="C37" s="1"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="152" t="s">
+      <c r="E37" s="122" t="s">
         <v>21</v>
       </c>
-      <c r="F37" s="137"/>
-      <c r="G37" s="142"/>
-      <c r="H37" s="131" t="s">
+      <c r="F37" s="123"/>
+      <c r="G37" s="124"/>
+      <c r="H37" s="166" t="s">
         <v>44</v>
       </c>
-      <c r="I37" s="99">
+      <c r="I37" s="104">
         <v>100</v>
       </c>
       <c r="J37" s="14"/>
@@ -7227,11 +7227,11 @@
       <c r="B38" s="18"/>
       <c r="C38" s="1"/>
       <c r="D38" s="35"/>
-      <c r="E38" s="143"/>
-      <c r="F38" s="140"/>
-      <c r="G38" s="144"/>
-      <c r="H38" s="99"/>
-      <c r="I38" s="99"/>
+      <c r="E38" s="125"/>
+      <c r="F38" s="126"/>
+      <c r="G38" s="127"/>
+      <c r="H38" s="104"/>
+      <c r="I38" s="104"/>
       <c r="J38" s="26"/>
       <c r="K38" s="27"/>
       <c r="L38" s="27"/>
@@ -7348,14 +7348,14 @@
       <c r="A39" s="1"/>
       <c r="B39" s="18"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="153" t="s">
+      <c r="D39" s="163" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="147"/>
-      <c r="F39" s="147"/>
-      <c r="G39" s="148"/>
-      <c r="H39" s="132"/>
-      <c r="I39" s="132"/>
+      <c r="E39" s="137"/>
+      <c r="F39" s="137"/>
+      <c r="G39" s="138"/>
+      <c r="H39" s="150"/>
+      <c r="I39" s="150"/>
       <c r="J39" s="50"/>
       <c r="K39" s="51"/>
       <c r="L39" s="51"/>
@@ -7472,12 +7472,12 @@
       <c r="A40" s="1"/>
       <c r="B40" s="18"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="143"/>
-      <c r="E40" s="140"/>
-      <c r="F40" s="140"/>
-      <c r="G40" s="141"/>
-      <c r="H40" s="132"/>
-      <c r="I40" s="132"/>
+      <c r="D40" s="125"/>
+      <c r="E40" s="126"/>
+      <c r="F40" s="126"/>
+      <c r="G40" s="130"/>
+      <c r="H40" s="150"/>
+      <c r="I40" s="150"/>
       <c r="J40" s="52"/>
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
@@ -7595,15 +7595,15 @@
       <c r="B41" s="18"/>
       <c r="C41" s="1"/>
       <c r="D41" s="33"/>
-      <c r="E41" s="152" t="s">
+      <c r="E41" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="137"/>
-      <c r="G41" s="142"/>
-      <c r="H41" s="131" t="s">
+      <c r="F41" s="123"/>
+      <c r="G41" s="124"/>
+      <c r="H41" s="166" t="s">
         <v>43</v>
       </c>
-      <c r="I41" s="99">
+      <c r="I41" s="104">
         <v>100</v>
       </c>
       <c r="J41" s="14"/>
@@ -7723,11 +7723,11 @@
       <c r="B42" s="18"/>
       <c r="C42" s="1"/>
       <c r="D42" s="34"/>
-      <c r="E42" s="143"/>
-      <c r="F42" s="140"/>
-      <c r="G42" s="144"/>
-      <c r="H42" s="99"/>
-      <c r="I42" s="99"/>
+      <c r="E42" s="125"/>
+      <c r="F42" s="126"/>
+      <c r="G42" s="127"/>
+      <c r="H42" s="104"/>
+      <c r="I42" s="104"/>
       <c r="J42" s="14"/>
       <c r="K42" s="15"/>
       <c r="L42" s="15"/>
@@ -7845,15 +7845,15 @@
       <c r="B43" s="18"/>
       <c r="C43" s="1"/>
       <c r="D43" s="34"/>
-      <c r="E43" s="152" t="s">
+      <c r="E43" s="122" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="137"/>
-      <c r="G43" s="142"/>
-      <c r="H43" s="131" t="s">
+      <c r="F43" s="123"/>
+      <c r="G43" s="124"/>
+      <c r="H43" s="166" t="s">
         <v>43</v>
       </c>
-      <c r="I43" s="99">
+      <c r="I43" s="104">
         <v>100</v>
       </c>
       <c r="J43" s="14"/>
@@ -7973,11 +7973,11 @@
       <c r="B44" s="18"/>
       <c r="C44" s="1"/>
       <c r="D44" s="34"/>
-      <c r="E44" s="143"/>
-      <c r="F44" s="140"/>
-      <c r="G44" s="144"/>
-      <c r="H44" s="99"/>
-      <c r="I44" s="99"/>
+      <c r="E44" s="125"/>
+      <c r="F44" s="126"/>
+      <c r="G44" s="127"/>
+      <c r="H44" s="104"/>
+      <c r="I44" s="104"/>
       <c r="J44" s="14"/>
       <c r="K44" s="15"/>
       <c r="L44" s="15"/>
@@ -8095,15 +8095,15 @@
       <c r="B45" s="18"/>
       <c r="C45" s="1"/>
       <c r="D45" s="34"/>
-      <c r="E45" s="152" t="s">
+      <c r="E45" s="122" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="137"/>
-      <c r="G45" s="142"/>
-      <c r="H45" s="131" t="s">
+      <c r="F45" s="123"/>
+      <c r="G45" s="124"/>
+      <c r="H45" s="166" t="s">
         <v>42</v>
       </c>
-      <c r="I45" s="99">
+      <c r="I45" s="104">
         <v>100</v>
       </c>
       <c r="J45" s="14"/>
@@ -8223,11 +8223,11 @@
       <c r="B46" s="18"/>
       <c r="C46" s="1"/>
       <c r="D46" s="34"/>
-      <c r="E46" s="143"/>
-      <c r="F46" s="140"/>
-      <c r="G46" s="144"/>
-      <c r="H46" s="99"/>
-      <c r="I46" s="99"/>
+      <c r="E46" s="125"/>
+      <c r="F46" s="126"/>
+      <c r="G46" s="127"/>
+      <c r="H46" s="104"/>
+      <c r="I46" s="104"/>
       <c r="J46" s="14"/>
       <c r="K46" s="15"/>
       <c r="L46" s="15"/>
@@ -8345,15 +8345,15 @@
       <c r="B47" s="18"/>
       <c r="C47" s="1"/>
       <c r="D47" s="34"/>
-      <c r="E47" s="152" t="s">
+      <c r="E47" s="122" t="s">
         <v>25</v>
       </c>
-      <c r="F47" s="137"/>
-      <c r="G47" s="142"/>
-      <c r="H47" s="131" t="s">
+      <c r="F47" s="123"/>
+      <c r="G47" s="124"/>
+      <c r="H47" s="166" t="s">
         <v>41</v>
       </c>
-      <c r="I47" s="99">
+      <c r="I47" s="104">
         <v>100</v>
       </c>
       <c r="J47" s="14"/>
@@ -8473,11 +8473,11 @@
       <c r="B48" s="18"/>
       <c r="C48" s="1"/>
       <c r="D48" s="34"/>
-      <c r="E48" s="143"/>
-      <c r="F48" s="140"/>
-      <c r="G48" s="144"/>
-      <c r="H48" s="99"/>
-      <c r="I48" s="99"/>
+      <c r="E48" s="125"/>
+      <c r="F48" s="126"/>
+      <c r="G48" s="127"/>
+      <c r="H48" s="104"/>
+      <c r="I48" s="104"/>
       <c r="J48" s="14"/>
       <c r="K48" s="15"/>
       <c r="L48" s="15"/>
@@ -8595,15 +8595,15 @@
       <c r="B49" s="18"/>
       <c r="C49" s="1"/>
       <c r="D49" s="34"/>
-      <c r="E49" s="152" t="s">
+      <c r="E49" s="122" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="137"/>
-      <c r="G49" s="142"/>
-      <c r="H49" s="131" t="s">
+      <c r="F49" s="123"/>
+      <c r="G49" s="124"/>
+      <c r="H49" s="166" t="s">
         <v>50</v>
       </c>
-      <c r="I49" s="99">
+      <c r="I49" s="104">
         <v>100</v>
       </c>
       <c r="J49" s="14"/>
@@ -8723,11 +8723,11 @@
       <c r="B50" s="18"/>
       <c r="C50" s="1"/>
       <c r="D50" s="34"/>
-      <c r="E50" s="143"/>
-      <c r="F50" s="140"/>
-      <c r="G50" s="144"/>
-      <c r="H50" s="99"/>
-      <c r="I50" s="99"/>
+      <c r="E50" s="125"/>
+      <c r="F50" s="126"/>
+      <c r="G50" s="127"/>
+      <c r="H50" s="104"/>
+      <c r="I50" s="104"/>
       <c r="J50" s="14"/>
       <c r="K50" s="15"/>
       <c r="L50" s="15"/>
@@ -8845,15 +8845,15 @@
       <c r="B51" s="18"/>
       <c r="C51" s="1"/>
       <c r="D51" s="34"/>
-      <c r="E51" s="152" t="s">
+      <c r="E51" s="122" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="137"/>
-      <c r="G51" s="142"/>
-      <c r="H51" s="131" t="s">
+      <c r="F51" s="123"/>
+      <c r="G51" s="124"/>
+      <c r="H51" s="166" t="s">
         <v>47</v>
       </c>
-      <c r="I51" s="99">
+      <c r="I51" s="104">
         <v>100</v>
       </c>
       <c r="J51" s="14"/>
@@ -8973,11 +8973,11 @@
       <c r="B52" s="18"/>
       <c r="C52" s="1"/>
       <c r="D52" s="34"/>
-      <c r="E52" s="143"/>
-      <c r="F52" s="140"/>
-      <c r="G52" s="144"/>
-      <c r="H52" s="99"/>
-      <c r="I52" s="99"/>
+      <c r="E52" s="125"/>
+      <c r="F52" s="126"/>
+      <c r="G52" s="127"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
       <c r="J52" s="26"/>
       <c r="K52" s="27"/>
       <c r="L52" s="27"/>
@@ -9094,14 +9094,14 @@
       <c r="A53" s="1"/>
       <c r="B53" s="18"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="151" t="s">
+      <c r="D53" s="128" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="137"/>
-      <c r="F53" s="137"/>
-      <c r="G53" s="138"/>
-      <c r="H53" s="132"/>
-      <c r="I53" s="132"/>
+      <c r="E53" s="123"/>
+      <c r="F53" s="123"/>
+      <c r="G53" s="129"/>
+      <c r="H53" s="150"/>
+      <c r="I53" s="150"/>
       <c r="J53" s="50"/>
       <c r="K53" s="51"/>
       <c r="L53" s="51"/>
@@ -9218,12 +9218,12 @@
       <c r="A54" s="1"/>
       <c r="B54" s="18"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="143"/>
-      <c r="E54" s="140"/>
-      <c r="F54" s="140"/>
-      <c r="G54" s="141"/>
-      <c r="H54" s="132"/>
-      <c r="I54" s="132"/>
+      <c r="D54" s="125"/>
+      <c r="E54" s="126"/>
+      <c r="F54" s="126"/>
+      <c r="G54" s="130"/>
+      <c r="H54" s="150"/>
+      <c r="I54" s="150"/>
       <c r="J54" s="52"/>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -9341,15 +9341,15 @@
       <c r="B55" s="18"/>
       <c r="C55" s="1"/>
       <c r="D55" s="34"/>
-      <c r="E55" s="152" t="s">
+      <c r="E55" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="137"/>
-      <c r="G55" s="142"/>
-      <c r="H55" s="131" t="s">
+      <c r="F55" s="123"/>
+      <c r="G55" s="124"/>
+      <c r="H55" s="166" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="99">
+      <c r="I55" s="104">
         <v>100</v>
       </c>
       <c r="J55" s="14"/>
@@ -9469,11 +9469,11 @@
       <c r="B56" s="18"/>
       <c r="C56" s="1"/>
       <c r="D56" s="34"/>
-      <c r="E56" s="143"/>
-      <c r="F56" s="140"/>
-      <c r="G56" s="144"/>
-      <c r="H56" s="99"/>
-      <c r="I56" s="99"/>
+      <c r="E56" s="125"/>
+      <c r="F56" s="126"/>
+      <c r="G56" s="127"/>
+      <c r="H56" s="104"/>
+      <c r="I56" s="104"/>
       <c r="J56" s="14"/>
       <c r="K56" s="15"/>
       <c r="L56" s="15"/>
@@ -9591,15 +9591,15 @@
       <c r="B57" s="18"/>
       <c r="C57" s="1"/>
       <c r="D57" s="34"/>
-      <c r="E57" s="152" t="s">
+      <c r="E57" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="F57" s="137"/>
-      <c r="G57" s="142"/>
-      <c r="H57" s="131" t="s">
+      <c r="F57" s="123"/>
+      <c r="G57" s="124"/>
+      <c r="H57" s="166" t="s">
         <v>51</v>
       </c>
-      <c r="I57" s="99">
+      <c r="I57" s="104">
         <v>100</v>
       </c>
       <c r="J57" s="14"/>
@@ -9719,11 +9719,11 @@
       <c r="B58" s="18"/>
       <c r="C58" s="1"/>
       <c r="D58" s="34"/>
-      <c r="E58" s="143"/>
-      <c r="F58" s="140"/>
-      <c r="G58" s="144"/>
-      <c r="H58" s="99"/>
-      <c r="I58" s="99"/>
+      <c r="E58" s="125"/>
+      <c r="F58" s="126"/>
+      <c r="G58" s="127"/>
+      <c r="H58" s="104"/>
+      <c r="I58" s="104"/>
       <c r="J58" s="14"/>
       <c r="K58" s="15"/>
       <c r="L58" s="15"/>
@@ -9841,15 +9841,15 @@
       <c r="B59" s="18"/>
       <c r="C59" s="1"/>
       <c r="D59" s="34"/>
-      <c r="E59" s="152" t="s">
+      <c r="E59" s="122" t="s">
         <v>26</v>
       </c>
-      <c r="F59" s="137"/>
-      <c r="G59" s="142"/>
-      <c r="H59" s="131" t="s">
+      <c r="F59" s="123"/>
+      <c r="G59" s="124"/>
+      <c r="H59" s="166" t="s">
         <v>49</v>
       </c>
-      <c r="I59" s="99">
+      <c r="I59" s="104">
         <v>100</v>
       </c>
       <c r="J59" s="14"/>
@@ -9969,11 +9969,11 @@
       <c r="B60" s="18"/>
       <c r="C60" s="1"/>
       <c r="D60" s="34"/>
-      <c r="E60" s="143"/>
-      <c r="F60" s="140"/>
-      <c r="G60" s="144"/>
-      <c r="H60" s="99"/>
-      <c r="I60" s="99"/>
+      <c r="E60" s="125"/>
+      <c r="F60" s="126"/>
+      <c r="G60" s="127"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
       <c r="J60" s="14"/>
       <c r="K60" s="15"/>
       <c r="L60" s="15"/>
@@ -9998,7 +9998,7 @@
       <c r="AE60" s="15"/>
       <c r="AF60" s="53"/>
       <c r="AG60" s="53"/>
-      <c r="AH60" s="15"/>
+      <c r="AH60" s="53"/>
       <c r="AI60" s="15"/>
       <c r="AJ60" s="15"/>
       <c r="AK60" s="15"/>
@@ -10091,15 +10091,15 @@
       <c r="B61" s="18"/>
       <c r="C61" s="1"/>
       <c r="D61" s="34"/>
-      <c r="E61" s="152" t="s">
+      <c r="E61" s="122" t="s">
         <v>21</v>
       </c>
-      <c r="F61" s="137"/>
-      <c r="G61" s="142"/>
-      <c r="H61" s="131" t="s">
+      <c r="F61" s="123"/>
+      <c r="G61" s="124"/>
+      <c r="H61" s="166" t="s">
         <v>49</v>
       </c>
-      <c r="I61" s="99">
+      <c r="I61" s="104">
         <v>100</v>
       </c>
       <c r="J61" s="14"/>
@@ -10219,11 +10219,11 @@
       <c r="B62" s="18"/>
       <c r="C62" s="1"/>
       <c r="D62" s="34"/>
-      <c r="E62" s="143"/>
-      <c r="F62" s="140"/>
-      <c r="G62" s="144"/>
-      <c r="H62" s="99"/>
-      <c r="I62" s="99"/>
+      <c r="E62" s="125"/>
+      <c r="F62" s="126"/>
+      <c r="G62" s="127"/>
+      <c r="H62" s="104"/>
+      <c r="I62" s="104"/>
       <c r="J62" s="26"/>
       <c r="K62" s="27"/>
       <c r="L62" s="27"/>
@@ -10340,14 +10340,14 @@
       <c r="A63" s="1"/>
       <c r="B63" s="18"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="151" t="s">
+      <c r="D63" s="128" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="137"/>
-      <c r="F63" s="137"/>
-      <c r="G63" s="138"/>
-      <c r="H63" s="132"/>
-      <c r="I63" s="132"/>
+      <c r="E63" s="123"/>
+      <c r="F63" s="123"/>
+      <c r="G63" s="129"/>
+      <c r="H63" s="150"/>
+      <c r="I63" s="150"/>
       <c r="J63" s="50"/>
       <c r="K63" s="51"/>
       <c r="L63" s="51"/>
@@ -10464,12 +10464,12 @@
       <c r="A64" s="1"/>
       <c r="B64" s="18"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="143"/>
-      <c r="E64" s="140"/>
-      <c r="F64" s="140"/>
-      <c r="G64" s="141"/>
-      <c r="H64" s="132"/>
-      <c r="I64" s="132"/>
+      <c r="D64" s="125"/>
+      <c r="E64" s="126"/>
+      <c r="F64" s="126"/>
+      <c r="G64" s="130"/>
+      <c r="H64" s="150"/>
+      <c r="I64" s="150"/>
       <c r="J64" s="52"/>
       <c r="K64" s="49"/>
       <c r="L64" s="49"/>
@@ -10587,15 +10587,15 @@
       <c r="B65" s="18"/>
       <c r="C65" s="1"/>
       <c r="D65" s="34"/>
-      <c r="E65" s="152" t="s">
+      <c r="E65" s="122" t="s">
         <v>35</v>
       </c>
-      <c r="F65" s="137"/>
-      <c r="G65" s="142"/>
-      <c r="H65" s="131" t="s">
+      <c r="F65" s="123"/>
+      <c r="G65" s="124"/>
+      <c r="H65" s="166" t="s">
         <v>52</v>
       </c>
-      <c r="I65" s="99">
+      <c r="I65" s="104">
         <v>100</v>
       </c>
       <c r="J65" s="14"/>
@@ -10715,11 +10715,11 @@
       <c r="B66" s="18"/>
       <c r="C66" s="1"/>
       <c r="D66" s="34"/>
-      <c r="E66" s="143"/>
-      <c r="F66" s="140"/>
-      <c r="G66" s="144"/>
-      <c r="H66" s="99"/>
-      <c r="I66" s="99"/>
+      <c r="E66" s="125"/>
+      <c r="F66" s="126"/>
+      <c r="G66" s="127"/>
+      <c r="H66" s="104"/>
+      <c r="I66" s="104"/>
       <c r="J66" s="14"/>
       <c r="K66" s="15"/>
       <c r="L66" s="15"/>
@@ -10837,15 +10837,15 @@
       <c r="B67" s="18"/>
       <c r="C67" s="1"/>
       <c r="D67" s="34"/>
-      <c r="E67" s="152" t="s">
+      <c r="E67" s="122" t="s">
         <v>26</v>
       </c>
-      <c r="F67" s="137"/>
-      <c r="G67" s="142"/>
-      <c r="H67" s="131" t="s">
+      <c r="F67" s="123"/>
+      <c r="G67" s="124"/>
+      <c r="H67" s="166" t="s">
         <v>53</v>
       </c>
-      <c r="I67" s="99">
+      <c r="I67" s="104">
         <v>100</v>
       </c>
       <c r="J67" s="14"/>
@@ -10965,11 +10965,11 @@
       <c r="B68" s="18"/>
       <c r="C68" s="1"/>
       <c r="D68" s="34"/>
-      <c r="E68" s="143"/>
-      <c r="F68" s="140"/>
-      <c r="G68" s="144"/>
-      <c r="H68" s="99"/>
-      <c r="I68" s="99"/>
+      <c r="E68" s="125"/>
+      <c r="F68" s="126"/>
+      <c r="G68" s="127"/>
+      <c r="H68" s="104"/>
+      <c r="I68" s="104"/>
       <c r="J68" s="14"/>
       <c r="K68" s="15"/>
       <c r="L68" s="15"/>
@@ -11087,15 +11087,15 @@
       <c r="B69" s="18"/>
       <c r="C69" s="1"/>
       <c r="D69" s="34"/>
-      <c r="E69" s="152" t="s">
+      <c r="E69" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="F69" s="137"/>
-      <c r="G69" s="142"/>
-      <c r="H69" s="131" t="s">
+      <c r="F69" s="123"/>
+      <c r="G69" s="124"/>
+      <c r="H69" s="166" t="s">
         <v>54</v>
       </c>
-      <c r="I69" s="99">
+      <c r="I69" s="104">
         <v>100</v>
       </c>
       <c r="J69" s="14"/>
@@ -11215,11 +11215,11 @@
       <c r="B70" s="18"/>
       <c r="C70" s="1"/>
       <c r="D70" s="34"/>
-      <c r="E70" s="143"/>
-      <c r="F70" s="140"/>
-      <c r="G70" s="144"/>
-      <c r="H70" s="99"/>
-      <c r="I70" s="99"/>
+      <c r="E70" s="125"/>
+      <c r="F70" s="126"/>
+      <c r="G70" s="127"/>
+      <c r="H70" s="104"/>
+      <c r="I70" s="104"/>
       <c r="J70" s="14"/>
       <c r="K70" s="15"/>
       <c r="L70" s="15"/>
@@ -11337,15 +11337,15 @@
       <c r="B71" s="18"/>
       <c r="C71" s="1"/>
       <c r="D71" s="34"/>
-      <c r="E71" s="152" t="s">
+      <c r="E71" s="122" t="s">
         <v>21</v>
       </c>
-      <c r="F71" s="137"/>
-      <c r="G71" s="142"/>
-      <c r="H71" s="131" t="s">
+      <c r="F71" s="123"/>
+      <c r="G71" s="124"/>
+      <c r="H71" s="166" t="s">
         <v>55</v>
       </c>
-      <c r="I71" s="99">
+      <c r="I71" s="104">
         <v>100</v>
       </c>
       <c r="J71" s="14"/>
@@ -11465,11 +11465,11 @@
       <c r="B72" s="18"/>
       <c r="C72" s="1"/>
       <c r="D72" s="35"/>
-      <c r="E72" s="143"/>
-      <c r="F72" s="140"/>
-      <c r="G72" s="144"/>
-      <c r="H72" s="99"/>
-      <c r="I72" s="99"/>
+      <c r="E72" s="125"/>
+      <c r="F72" s="126"/>
+      <c r="G72" s="127"/>
+      <c r="H72" s="104"/>
+      <c r="I72" s="104"/>
       <c r="J72" s="26"/>
       <c r="K72" s="27"/>
       <c r="L72" s="27"/>
@@ -11585,17 +11585,17 @@
     <row r="73" spans="1:120" ht="9.75" customHeight="1">
       <c r="A73" s="16"/>
       <c r="B73" s="36"/>
-      <c r="C73" s="136" t="s">
+      <c r="C73" s="131" t="s">
         <v>30</v>
       </c>
-      <c r="D73" s="137"/>
-      <c r="E73" s="137"/>
-      <c r="F73" s="137"/>
-      <c r="G73" s="138"/>
-      <c r="H73" s="131" t="s">
+      <c r="D73" s="123"/>
+      <c r="E73" s="123"/>
+      <c r="F73" s="123"/>
+      <c r="G73" s="129"/>
+      <c r="H73" s="166" t="s">
         <v>55</v>
       </c>
-      <c r="I73" s="99">
+      <c r="I73" s="104">
         <v>100</v>
       </c>
       <c r="J73" s="19"/>
@@ -11713,13 +11713,13 @@
     <row r="74" spans="1:120" ht="9.75" customHeight="1">
       <c r="A74" s="16"/>
       <c r="B74" s="36"/>
-      <c r="C74" s="139"/>
-      <c r="D74" s="140"/>
-      <c r="E74" s="140"/>
-      <c r="F74" s="140"/>
-      <c r="G74" s="141"/>
-      <c r="H74" s="99"/>
-      <c r="I74" s="99"/>
+      <c r="C74" s="132"/>
+      <c r="D74" s="126"/>
+      <c r="E74" s="126"/>
+      <c r="F74" s="126"/>
+      <c r="G74" s="130"/>
+      <c r="H74" s="104"/>
+      <c r="I74" s="104"/>
       <c r="J74" s="19"/>
       <c r="K74" s="20"/>
       <c r="L74" s="20"/>
@@ -11835,17 +11835,17 @@
     <row r="75" spans="1:120" ht="9.75" customHeight="1">
       <c r="A75" s="16"/>
       <c r="B75" s="36"/>
-      <c r="C75" s="136" t="s">
+      <c r="C75" s="131" t="s">
         <v>34</v>
       </c>
-      <c r="D75" s="137"/>
-      <c r="E75" s="137"/>
-      <c r="F75" s="137"/>
-      <c r="G75" s="138"/>
-      <c r="H75" s="131" t="s">
+      <c r="D75" s="123"/>
+      <c r="E75" s="123"/>
+      <c r="F75" s="123"/>
+      <c r="G75" s="129"/>
+      <c r="H75" s="166" t="s">
         <v>58</v>
       </c>
-      <c r="I75" s="99"/>
+      <c r="I75" s="104"/>
       <c r="J75" s="19"/>
       <c r="K75" s="20"/>
       <c r="L75" s="20"/>
@@ -11961,13 +11961,13 @@
     <row r="76" spans="1:120" ht="9.75" customHeight="1">
       <c r="A76" s="16"/>
       <c r="B76" s="36"/>
-      <c r="C76" s="145"/>
-      <c r="D76" s="145"/>
-      <c r="E76" s="145"/>
-      <c r="F76" s="145"/>
-      <c r="G76" s="145"/>
-      <c r="H76" s="99"/>
-      <c r="I76" s="99"/>
+      <c r="C76" s="133"/>
+      <c r="D76" s="133"/>
+      <c r="E76" s="133"/>
+      <c r="F76" s="133"/>
+      <c r="G76" s="133"/>
+      <c r="H76" s="104"/>
+      <c r="I76" s="104"/>
       <c r="J76" s="19"/>
       <c r="K76" s="20"/>
       <c r="L76" s="20"/>
@@ -12083,15 +12083,15 @@
     <row r="77" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A77" s="16"/>
       <c r="B77" s="71"/>
-      <c r="C77" s="120" t="s">
+      <c r="C77" s="169" t="s">
         <v>62</v>
       </c>
-      <c r="D77" s="121"/>
-      <c r="E77" s="121"/>
-      <c r="F77" s="121"/>
-      <c r="G77" s="122"/>
-      <c r="H77" s="133"/>
-      <c r="I77" s="87"/>
+      <c r="D77" s="170"/>
+      <c r="E77" s="170"/>
+      <c r="F77" s="170"/>
+      <c r="G77" s="171"/>
+      <c r="H77" s="167"/>
+      <c r="I77" s="164"/>
       <c r="J77" s="63"/>
       <c r="K77" s="64"/>
       <c r="L77" s="64"/>
@@ -12207,13 +12207,13 @@
     <row r="78" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A78" s="16"/>
       <c r="B78" s="71"/>
-      <c r="C78" s="123"/>
-      <c r="D78" s="124"/>
-      <c r="E78" s="124"/>
-      <c r="F78" s="124"/>
-      <c r="G78" s="125"/>
-      <c r="H78" s="134"/>
-      <c r="I78" s="119"/>
+      <c r="C78" s="172"/>
+      <c r="D78" s="173"/>
+      <c r="E78" s="173"/>
+      <c r="F78" s="173"/>
+      <c r="G78" s="174"/>
+      <c r="H78" s="168"/>
+      <c r="I78" s="165"/>
       <c r="J78" s="63"/>
       <c r="K78" s="64"/>
       <c r="L78" s="64"/>
@@ -12330,12 +12330,12 @@
       <c r="A79" s="16"/>
       <c r="B79" s="71"/>
       <c r="C79" s="76"/>
-      <c r="D79" s="126" t="s">
+      <c r="D79" s="107" t="s">
         <v>63</v>
       </c>
-      <c r="E79" s="112"/>
-      <c r="F79" s="112"/>
-      <c r="G79" s="113"/>
+      <c r="E79" s="108"/>
+      <c r="F79" s="108"/>
+      <c r="G79" s="109"/>
       <c r="H79" s="77"/>
       <c r="I79" s="67"/>
       <c r="J79" s="63"/>
@@ -12454,10 +12454,10 @@
       <c r="A80" s="16"/>
       <c r="B80" s="71"/>
       <c r="C80" s="76"/>
-      <c r="D80" s="127"/>
-      <c r="E80" s="114"/>
-      <c r="F80" s="114"/>
-      <c r="G80" s="115"/>
+      <c r="D80" s="110"/>
+      <c r="E80" s="111"/>
+      <c r="F80" s="111"/>
+      <c r="G80" s="112"/>
       <c r="H80" s="77"/>
       <c r="I80" s="67"/>
       <c r="J80" s="63"/>
@@ -12577,15 +12577,15 @@
       <c r="B81" s="36"/>
       <c r="C81" s="60"/>
       <c r="D81" s="70"/>
-      <c r="E81" s="94" t="s">
+      <c r="E81" s="175" t="s">
         <v>73</v>
       </c>
-      <c r="F81" s="94"/>
-      <c r="G81" s="94"/>
-      <c r="H81" s="116">
+      <c r="F81" s="175"/>
+      <c r="G81" s="175"/>
+      <c r="H81" s="95">
         <v>45611</v>
       </c>
-      <c r="I81" s="89"/>
+      <c r="I81" s="97"/>
       <c r="J81" s="19"/>
       <c r="K81" s="20"/>
       <c r="L81" s="20"/>
@@ -12703,11 +12703,11 @@
       <c r="B82" s="36"/>
       <c r="C82" s="60"/>
       <c r="D82" s="70"/>
-      <c r="E82" s="92"/>
-      <c r="F82" s="92"/>
-      <c r="G82" s="92"/>
+      <c r="E82" s="94"/>
+      <c r="F82" s="94"/>
+      <c r="G82" s="94"/>
       <c r="H82" s="96"/>
-      <c r="I82" s="90"/>
+      <c r="I82" s="98"/>
       <c r="J82" s="19"/>
       <c r="K82" s="20"/>
       <c r="L82" s="20"/>
@@ -12825,15 +12825,15 @@
       <c r="B83" s="36"/>
       <c r="C83" s="60"/>
       <c r="D83" s="70"/>
-      <c r="E83" s="92" t="s">
+      <c r="E83" s="94" t="s">
         <v>74</v>
       </c>
-      <c r="F83" s="92"/>
-      <c r="G83" s="92"/>
-      <c r="H83" s="116">
+      <c r="F83" s="94"/>
+      <c r="G83" s="94"/>
+      <c r="H83" s="95">
         <v>45615</v>
       </c>
-      <c r="I83" s="89"/>
+      <c r="I83" s="97"/>
       <c r="J83" s="19"/>
       <c r="K83" s="20"/>
       <c r="L83" s="20"/>
@@ -12951,11 +12951,11 @@
       <c r="B84" s="36"/>
       <c r="C84" s="60"/>
       <c r="D84" s="70"/>
-      <c r="E84" s="92"/>
-      <c r="F84" s="92"/>
-      <c r="G84" s="92"/>
+      <c r="E84" s="94"/>
+      <c r="F84" s="94"/>
+      <c r="G84" s="94"/>
       <c r="H84" s="96"/>
-      <c r="I84" s="90"/>
+      <c r="I84" s="98"/>
       <c r="J84" s="19"/>
       <c r="K84" s="20"/>
       <c r="L84" s="20"/>
@@ -13073,15 +13073,15 @@
       <c r="B85" s="36"/>
       <c r="C85" s="60"/>
       <c r="D85" s="70"/>
-      <c r="E85" s="100" t="s">
+      <c r="E85" s="179" t="s">
         <v>61</v>
       </c>
-      <c r="F85" s="101"/>
-      <c r="G85" s="102"/>
-      <c r="H85" s="98">
+      <c r="F85" s="113"/>
+      <c r="G85" s="114"/>
+      <c r="H85" s="103">
         <v>45617</v>
       </c>
-      <c r="I85" s="99"/>
+      <c r="I85" s="104"/>
       <c r="J85" s="62"/>
       <c r="K85" s="20"/>
       <c r="L85" s="20"/>
@@ -13199,11 +13199,11 @@
       <c r="B86" s="36"/>
       <c r="C86" s="60"/>
       <c r="D86" s="70"/>
-      <c r="E86" s="103"/>
-      <c r="F86" s="104"/>
-      <c r="G86" s="105"/>
-      <c r="H86" s="98"/>
-      <c r="I86" s="99"/>
+      <c r="E86" s="176"/>
+      <c r="F86" s="117"/>
+      <c r="G86" s="118"/>
+      <c r="H86" s="103"/>
+      <c r="I86" s="104"/>
       <c r="J86" s="62"/>
       <c r="K86" s="20"/>
       <c r="L86" s="20"/>
@@ -13319,17 +13319,17 @@
     <row r="87" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A87" s="16"/>
       <c r="B87" s="71"/>
-      <c r="C87" s="187"/>
-      <c r="D87" s="92" t="s">
+      <c r="C87" s="90"/>
+      <c r="D87" s="94" t="s">
         <v>76</v>
       </c>
-      <c r="E87" s="92"/>
-      <c r="F87" s="92"/>
-      <c r="G87" s="92"/>
-      <c r="H87" s="116">
+      <c r="E87" s="94"/>
+      <c r="F87" s="94"/>
+      <c r="G87" s="94"/>
+      <c r="H87" s="95">
         <v>45615</v>
       </c>
-      <c r="I87" s="128"/>
+      <c r="I87" s="101"/>
       <c r="J87" s="62"/>
       <c r="K87" s="20"/>
       <c r="L87" s="20"/>
@@ -13445,13 +13445,13 @@
     <row r="88" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A88" s="16"/>
       <c r="B88" s="71"/>
-      <c r="C88" s="187"/>
-      <c r="D88" s="92"/>
-      <c r="E88" s="92"/>
-      <c r="F88" s="92"/>
-      <c r="G88" s="92"/>
+      <c r="C88" s="90"/>
+      <c r="D88" s="94"/>
+      <c r="E88" s="94"/>
+      <c r="F88" s="94"/>
+      <c r="G88" s="94"/>
       <c r="H88" s="96"/>
-      <c r="I88" s="129"/>
+      <c r="I88" s="102"/>
       <c r="J88" s="62"/>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -13568,14 +13568,14 @@
       <c r="A89" s="16"/>
       <c r="B89" s="36"/>
       <c r="C89" s="79"/>
-      <c r="D89" s="126" t="s">
+      <c r="D89" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="112"/>
-      <c r="F89" s="112"/>
-      <c r="G89" s="113"/>
-      <c r="H89" s="130"/>
-      <c r="I89" s="118"/>
+      <c r="E89" s="108"/>
+      <c r="F89" s="108"/>
+      <c r="G89" s="109"/>
+      <c r="H89" s="177"/>
+      <c r="I89" s="178"/>
       <c r="J89" s="66"/>
       <c r="K89" s="64"/>
       <c r="L89" s="64"/>
@@ -13692,12 +13692,12 @@
       <c r="A90" s="16"/>
       <c r="B90" s="36"/>
       <c r="C90" s="79"/>
-      <c r="D90" s="127"/>
-      <c r="E90" s="114"/>
-      <c r="F90" s="114"/>
-      <c r="G90" s="115"/>
-      <c r="H90" s="130"/>
-      <c r="I90" s="118"/>
+      <c r="D90" s="110"/>
+      <c r="E90" s="111"/>
+      <c r="F90" s="111"/>
+      <c r="G90" s="112"/>
+      <c r="H90" s="177"/>
+      <c r="I90" s="178"/>
       <c r="J90" s="66"/>
       <c r="K90" s="64"/>
       <c r="L90" s="64"/>
@@ -13815,15 +13815,15 @@
       <c r="B91" s="36"/>
       <c r="C91" s="60"/>
       <c r="D91" s="70"/>
-      <c r="E91" s="94" t="s">
+      <c r="E91" s="175" t="s">
         <v>68</v>
       </c>
-      <c r="F91" s="94"/>
-      <c r="G91" s="94"/>
-      <c r="H91" s="116">
+      <c r="F91" s="175"/>
+      <c r="G91" s="175"/>
+      <c r="H91" s="95">
         <v>45616</v>
       </c>
-      <c r="I91" s="89"/>
+      <c r="I91" s="97"/>
       <c r="J91" s="19"/>
       <c r="K91" s="20"/>
       <c r="L91" s="20"/>
@@ -13941,11 +13941,11 @@
       <c r="B92" s="36"/>
       <c r="C92" s="60"/>
       <c r="D92" s="70"/>
-      <c r="E92" s="92"/>
-      <c r="F92" s="92"/>
-      <c r="G92" s="92"/>
+      <c r="E92" s="94"/>
+      <c r="F92" s="94"/>
+      <c r="G92" s="94"/>
       <c r="H92" s="96"/>
-      <c r="I92" s="90"/>
+      <c r="I92" s="98"/>
       <c r="J92" s="19"/>
       <c r="K92" s="20"/>
       <c r="L92" s="20"/>
@@ -14063,15 +14063,15 @@
       <c r="B93" s="36"/>
       <c r="C93" s="60"/>
       <c r="D93" s="70"/>
-      <c r="E93" s="92" t="s">
+      <c r="E93" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="F93" s="92"/>
-      <c r="G93" s="92"/>
-      <c r="H93" s="116">
+      <c r="F93" s="94"/>
+      <c r="G93" s="94"/>
+      <c r="H93" s="95">
         <v>45617</v>
       </c>
-      <c r="I93" s="89"/>
+      <c r="I93" s="97"/>
       <c r="J93" s="19"/>
       <c r="K93" s="20"/>
       <c r="L93" s="20"/>
@@ -14189,11 +14189,11 @@
       <c r="B94" s="36"/>
       <c r="C94" s="60"/>
       <c r="D94" s="70"/>
-      <c r="E94" s="92"/>
-      <c r="F94" s="92"/>
-      <c r="G94" s="92"/>
+      <c r="E94" s="94"/>
+      <c r="F94" s="94"/>
+      <c r="G94" s="94"/>
       <c r="H94" s="96"/>
-      <c r="I94" s="90"/>
+      <c r="I94" s="98"/>
       <c r="J94" s="19"/>
       <c r="K94" s="20"/>
       <c r="L94" s="20"/>
@@ -14311,15 +14311,15 @@
       <c r="B95" s="36"/>
       <c r="C95" s="60"/>
       <c r="D95" s="70"/>
-      <c r="E95" s="92" t="s">
+      <c r="E95" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="F95" s="92"/>
-      <c r="G95" s="92"/>
-      <c r="H95" s="116">
+      <c r="F95" s="94"/>
+      <c r="G95" s="94"/>
+      <c r="H95" s="95">
         <v>45618</v>
       </c>
-      <c r="I95" s="89"/>
+      <c r="I95" s="97"/>
       <c r="J95" s="19"/>
       <c r="K95" s="20"/>
       <c r="L95" s="20"/>
@@ -14437,11 +14437,11 @@
       <c r="B96" s="36"/>
       <c r="C96" s="60"/>
       <c r="D96" s="70"/>
-      <c r="E96" s="92"/>
-      <c r="F96" s="92"/>
-      <c r="G96" s="92"/>
+      <c r="E96" s="94"/>
+      <c r="F96" s="94"/>
+      <c r="G96" s="94"/>
       <c r="H96" s="96"/>
-      <c r="I96" s="90"/>
+      <c r="I96" s="98"/>
       <c r="J96" s="19"/>
       <c r="K96" s="20"/>
       <c r="L96" s="20"/>
@@ -14559,15 +14559,15 @@
       <c r="B97" s="36"/>
       <c r="C97" s="60"/>
       <c r="D97" s="70"/>
-      <c r="E97" s="92" t="s">
+      <c r="E97" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="F97" s="92"/>
-      <c r="G97" s="92"/>
-      <c r="H97" s="116">
+      <c r="F97" s="94"/>
+      <c r="G97" s="94"/>
+      <c r="H97" s="95">
         <v>45621</v>
       </c>
-      <c r="I97" s="89"/>
+      <c r="I97" s="97"/>
       <c r="J97" s="19"/>
       <c r="K97" s="20"/>
       <c r="L97" s="20"/>
@@ -14685,11 +14685,11 @@
       <c r="B98" s="36"/>
       <c r="C98" s="60"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="92"/>
-      <c r="F98" s="92"/>
-      <c r="G98" s="92"/>
+      <c r="E98" s="94"/>
+      <c r="F98" s="94"/>
+      <c r="G98" s="94"/>
       <c r="H98" s="96"/>
-      <c r="I98" s="90"/>
+      <c r="I98" s="98"/>
       <c r="J98" s="19"/>
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
@@ -14807,15 +14807,15 @@
       <c r="B99" s="36"/>
       <c r="C99" s="60"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="92" t="s">
+      <c r="E99" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="F99" s="92"/>
-      <c r="G99" s="92"/>
-      <c r="H99" s="116">
+      <c r="F99" s="94"/>
+      <c r="G99" s="94"/>
+      <c r="H99" s="95">
         <v>45622</v>
       </c>
-      <c r="I99" s="89"/>
+      <c r="I99" s="97"/>
       <c r="J99" s="19"/>
       <c r="K99" s="20"/>
       <c r="L99" s="20"/>
@@ -14933,11 +14933,11 @@
       <c r="B100" s="36"/>
       <c r="C100" s="60"/>
       <c r="D100" s="70"/>
-      <c r="E100" s="92"/>
-      <c r="F100" s="92"/>
-      <c r="G100" s="92"/>
+      <c r="E100" s="94"/>
+      <c r="F100" s="94"/>
+      <c r="G100" s="94"/>
       <c r="H100" s="96"/>
-      <c r="I100" s="90"/>
+      <c r="I100" s="98"/>
       <c r="J100" s="19"/>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -15053,17 +15053,17 @@
     <row r="101" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A101" s="16"/>
       <c r="B101" s="71"/>
-      <c r="C101" s="188"/>
+      <c r="C101" s="91"/>
       <c r="D101" s="70"/>
-      <c r="E101" s="103" t="s">
+      <c r="E101" s="176" t="s">
         <v>61</v>
       </c>
-      <c r="F101" s="104"/>
-      <c r="G101" s="105"/>
-      <c r="H101" s="116">
+      <c r="F101" s="117"/>
+      <c r="G101" s="118"/>
+      <c r="H101" s="95">
         <v>45623</v>
       </c>
-      <c r="I101" s="99"/>
+      <c r="I101" s="104"/>
       <c r="J101" s="62"/>
       <c r="K101" s="20"/>
       <c r="L101" s="20"/>
@@ -15179,13 +15179,13 @@
     <row r="102" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A102" s="16"/>
       <c r="B102" s="71"/>
-      <c r="C102" s="188"/>
+      <c r="C102" s="91"/>
       <c r="D102" s="70"/>
-      <c r="E102" s="103"/>
-      <c r="F102" s="104"/>
-      <c r="G102" s="105"/>
+      <c r="E102" s="176"/>
+      <c r="F102" s="117"/>
+      <c r="G102" s="118"/>
       <c r="H102" s="96"/>
-      <c r="I102" s="99"/>
+      <c r="I102" s="104"/>
       <c r="J102" s="62"/>
       <c r="K102" s="20"/>
       <c r="L102" s="20"/>
@@ -15301,17 +15301,17 @@
     <row r="103" spans="1:120" s="83" customFormat="1" ht="9.75" customHeight="1">
       <c r="A103" s="16"/>
       <c r="B103" s="71"/>
-      <c r="C103" s="187"/>
-      <c r="D103" s="92" t="s">
+      <c r="C103" s="90"/>
+      <c r="D103" s="94" t="s">
         <v>77</v>
       </c>
-      <c r="E103" s="92"/>
-      <c r="F103" s="92"/>
-      <c r="G103" s="92"/>
-      <c r="H103" s="116">
+      <c r="E103" s="94"/>
+      <c r="F103" s="94"/>
+      <c r="G103" s="94"/>
+      <c r="H103" s="95">
         <v>45622</v>
       </c>
-      <c r="I103" s="128"/>
+      <c r="I103" s="101"/>
       <c r="J103" s="62"/>
       <c r="K103" s="20"/>
       <c r="L103" s="20"/>
@@ -15427,13 +15427,13 @@
     <row r="104" spans="1:120" s="83" customFormat="1" ht="9.75" customHeight="1">
       <c r="A104" s="16"/>
       <c r="B104" s="71"/>
-      <c r="C104" s="187"/>
-      <c r="D104" s="92"/>
-      <c r="E104" s="92"/>
-      <c r="F104" s="92"/>
-      <c r="G104" s="92"/>
+      <c r="C104" s="90"/>
+      <c r="D104" s="94"/>
+      <c r="E104" s="94"/>
+      <c r="F104" s="94"/>
+      <c r="G104" s="94"/>
       <c r="H104" s="96"/>
-      <c r="I104" s="129"/>
+      <c r="I104" s="102"/>
       <c r="J104" s="62"/>
       <c r="K104" s="20"/>
       <c r="L104" s="20"/>
@@ -15549,15 +15549,15 @@
     <row r="105" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A105" s="16"/>
       <c r="B105" s="71"/>
-      <c r="C105" s="120" t="s">
+      <c r="C105" s="169" t="s">
         <v>64</v>
       </c>
-      <c r="D105" s="121"/>
-      <c r="E105" s="121"/>
-      <c r="F105" s="121"/>
-      <c r="G105" s="122"/>
-      <c r="H105" s="117"/>
-      <c r="I105" s="118"/>
+      <c r="D105" s="170"/>
+      <c r="E105" s="170"/>
+      <c r="F105" s="170"/>
+      <c r="G105" s="171"/>
+      <c r="H105" s="180"/>
+      <c r="I105" s="178"/>
       <c r="J105" s="66"/>
       <c r="K105" s="64"/>
       <c r="L105" s="64"/>
@@ -15673,13 +15673,13 @@
     <row r="106" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A106" s="16"/>
       <c r="B106" s="71"/>
-      <c r="C106" s="123"/>
-      <c r="D106" s="124"/>
-      <c r="E106" s="124"/>
-      <c r="F106" s="124"/>
-      <c r="G106" s="125"/>
-      <c r="H106" s="117"/>
-      <c r="I106" s="118"/>
+      <c r="C106" s="172"/>
+      <c r="D106" s="173"/>
+      <c r="E106" s="173"/>
+      <c r="F106" s="173"/>
+      <c r="G106" s="174"/>
+      <c r="H106" s="180"/>
+      <c r="I106" s="178"/>
       <c r="J106" s="66"/>
       <c r="K106" s="64"/>
       <c r="L106" s="64"/>
@@ -15796,14 +15796,14 @@
       <c r="A107" s="16"/>
       <c r="B107" s="36"/>
       <c r="C107" s="78"/>
-      <c r="D107" s="126" t="s">
+      <c r="D107" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="E107" s="112"/>
-      <c r="F107" s="112"/>
-      <c r="G107" s="113"/>
-      <c r="H107" s="117"/>
-      <c r="I107" s="118"/>
+      <c r="E107" s="108"/>
+      <c r="F107" s="108"/>
+      <c r="G107" s="109"/>
+      <c r="H107" s="180"/>
+      <c r="I107" s="178"/>
       <c r="J107" s="66"/>
       <c r="K107" s="64"/>
       <c r="L107" s="64"/>
@@ -15920,12 +15920,12 @@
       <c r="A108" s="16"/>
       <c r="B108" s="36"/>
       <c r="C108" s="76"/>
-      <c r="D108" s="127"/>
-      <c r="E108" s="114"/>
-      <c r="F108" s="114"/>
-      <c r="G108" s="115"/>
-      <c r="H108" s="117"/>
-      <c r="I108" s="118"/>
+      <c r="D108" s="110"/>
+      <c r="E108" s="111"/>
+      <c r="F108" s="111"/>
+      <c r="G108" s="112"/>
+      <c r="H108" s="180"/>
+      <c r="I108" s="178"/>
       <c r="J108" s="66"/>
       <c r="K108" s="64"/>
       <c r="L108" s="64"/>
@@ -16043,15 +16043,15 @@
       <c r="B109" s="36"/>
       <c r="C109" s="60"/>
       <c r="D109" s="70"/>
-      <c r="E109" s="94" t="s">
+      <c r="E109" s="175" t="s">
         <v>73</v>
       </c>
-      <c r="F109" s="94"/>
-      <c r="G109" s="94"/>
-      <c r="H109" s="116">
+      <c r="F109" s="175"/>
+      <c r="G109" s="175"/>
+      <c r="H109" s="95">
         <v>45624</v>
       </c>
-      <c r="I109" s="128"/>
+      <c r="I109" s="101"/>
       <c r="J109" s="62"/>
       <c r="K109" s="20"/>
       <c r="L109" s="20"/>
@@ -16169,11 +16169,11 @@
       <c r="B110" s="36"/>
       <c r="C110" s="60"/>
       <c r="D110" s="70"/>
-      <c r="E110" s="92"/>
-      <c r="F110" s="92"/>
-      <c r="G110" s="92"/>
+      <c r="E110" s="94"/>
+      <c r="F110" s="94"/>
+      <c r="G110" s="94"/>
       <c r="H110" s="96"/>
-      <c r="I110" s="129"/>
+      <c r="I110" s="102"/>
       <c r="J110" s="62"/>
       <c r="K110" s="20"/>
       <c r="L110" s="20"/>
@@ -16291,15 +16291,15 @@
       <c r="B111" s="36"/>
       <c r="C111" s="60"/>
       <c r="D111" s="70"/>
-      <c r="E111" s="92" t="s">
+      <c r="E111" s="94" t="s">
         <v>74</v>
       </c>
-      <c r="F111" s="92"/>
-      <c r="G111" s="92"/>
-      <c r="H111" s="116">
+      <c r="F111" s="94"/>
+      <c r="G111" s="94"/>
+      <c r="H111" s="95">
         <v>45625</v>
       </c>
-      <c r="I111" s="128"/>
+      <c r="I111" s="101"/>
       <c r="J111" s="62"/>
       <c r="K111" s="20"/>
       <c r="L111" s="20"/>
@@ -16417,11 +16417,11 @@
       <c r="B112" s="36"/>
       <c r="C112" s="60"/>
       <c r="D112" s="70"/>
-      <c r="E112" s="92"/>
-      <c r="F112" s="92"/>
-      <c r="G112" s="92"/>
+      <c r="E112" s="94"/>
+      <c r="F112" s="94"/>
+      <c r="G112" s="94"/>
       <c r="H112" s="96"/>
-      <c r="I112" s="129"/>
+      <c r="I112" s="102"/>
       <c r="J112" s="62"/>
       <c r="K112" s="20"/>
       <c r="L112" s="20"/>
@@ -16537,17 +16537,17 @@
     <row r="113" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A113" s="16"/>
       <c r="B113" s="71"/>
-      <c r="C113" s="188"/>
+      <c r="C113" s="91"/>
       <c r="D113" s="70"/>
-      <c r="E113" s="92" t="s">
+      <c r="E113" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="F113" s="92"/>
-      <c r="G113" s="92"/>
-      <c r="H113" s="98">
+      <c r="F113" s="94"/>
+      <c r="G113" s="94"/>
+      <c r="H113" s="103">
         <v>45630</v>
       </c>
-      <c r="I113" s="99"/>
+      <c r="I113" s="104"/>
       <c r="J113" s="62"/>
       <c r="K113" s="20"/>
       <c r="L113" s="20"/>
@@ -16663,13 +16663,13 @@
     <row r="114" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A114" s="16"/>
       <c r="B114" s="71"/>
-      <c r="C114" s="188"/>
+      <c r="C114" s="91"/>
       <c r="D114" s="70"/>
-      <c r="E114" s="111"/>
-      <c r="F114" s="111"/>
-      <c r="G114" s="111"/>
-      <c r="H114" s="116"/>
-      <c r="I114" s="128"/>
+      <c r="E114" s="190"/>
+      <c r="F114" s="190"/>
+      <c r="G114" s="190"/>
+      <c r="H114" s="95"/>
+      <c r="I114" s="101"/>
       <c r="J114" s="62"/>
       <c r="K114" s="20"/>
       <c r="L114" s="20"/>
@@ -16785,17 +16785,17 @@
     <row r="115" spans="1:120" s="83" customFormat="1" ht="9.75" customHeight="1">
       <c r="A115" s="16"/>
       <c r="B115" s="71"/>
-      <c r="C115" s="188"/>
-      <c r="D115" s="92" t="s">
+      <c r="C115" s="91"/>
+      <c r="D115" s="94" t="s">
         <v>78</v>
       </c>
-      <c r="E115" s="92"/>
-      <c r="F115" s="92"/>
-      <c r="G115" s="92"/>
-      <c r="H115" s="98">
+      <c r="E115" s="94"/>
+      <c r="F115" s="94"/>
+      <c r="G115" s="94"/>
+      <c r="H115" s="103">
         <v>45625</v>
       </c>
-      <c r="I115" s="99"/>
+      <c r="I115" s="104"/>
       <c r="J115" s="62"/>
       <c r="K115" s="20"/>
       <c r="L115" s="20"/>
@@ -16911,13 +16911,13 @@
     <row r="116" spans="1:120" s="83" customFormat="1" ht="9.75" customHeight="1">
       <c r="A116" s="16"/>
       <c r="B116" s="71"/>
-      <c r="C116" s="188"/>
-      <c r="D116" s="92"/>
-      <c r="E116" s="92"/>
-      <c r="F116" s="92"/>
-      <c r="G116" s="92"/>
-      <c r="H116" s="98"/>
-      <c r="I116" s="99"/>
+      <c r="C116" s="91"/>
+      <c r="D116" s="94"/>
+      <c r="E116" s="94"/>
+      <c r="F116" s="94"/>
+      <c r="G116" s="94"/>
+      <c r="H116" s="103"/>
+      <c r="I116" s="104"/>
       <c r="J116" s="62"/>
       <c r="K116" s="20"/>
       <c r="L116" s="20"/>
@@ -17034,14 +17034,14 @@
       <c r="A117" s="16"/>
       <c r="B117" s="36"/>
       <c r="C117" s="80"/>
-      <c r="D117" s="126" t="s">
+      <c r="D117" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="E117" s="112"/>
-      <c r="F117" s="112"/>
-      <c r="G117" s="113"/>
-      <c r="H117" s="107"/>
-      <c r="I117" s="87"/>
+      <c r="E117" s="108"/>
+      <c r="F117" s="108"/>
+      <c r="G117" s="109"/>
+      <c r="H117" s="181"/>
+      <c r="I117" s="164"/>
       <c r="J117" s="63"/>
       <c r="K117" s="64"/>
       <c r="L117" s="64"/>
@@ -17158,12 +17158,12 @@
       <c r="A118" s="16"/>
       <c r="B118" s="36"/>
       <c r="C118" s="80"/>
-      <c r="D118" s="127"/>
-      <c r="E118" s="114"/>
-      <c r="F118" s="114"/>
-      <c r="G118" s="115"/>
-      <c r="H118" s="108"/>
-      <c r="I118" s="119"/>
+      <c r="D118" s="110"/>
+      <c r="E118" s="111"/>
+      <c r="F118" s="111"/>
+      <c r="G118" s="112"/>
+      <c r="H118" s="182"/>
+      <c r="I118" s="165"/>
       <c r="J118" s="63"/>
       <c r="K118" s="64"/>
       <c r="L118" s="64"/>
@@ -17281,15 +17281,15 @@
       <c r="B119" s="36"/>
       <c r="C119" s="60"/>
       <c r="D119" s="70"/>
-      <c r="E119" s="94" t="s">
+      <c r="E119" s="175" t="s">
         <v>68</v>
       </c>
-      <c r="F119" s="94"/>
-      <c r="G119" s="94"/>
-      <c r="H119" s="116">
+      <c r="F119" s="175"/>
+      <c r="G119" s="175"/>
+      <c r="H119" s="95">
         <v>45629</v>
       </c>
-      <c r="I119" s="89"/>
+      <c r="I119" s="97"/>
       <c r="J119" s="19"/>
       <c r="K119" s="20"/>
       <c r="L119" s="20"/>
@@ -17407,11 +17407,11 @@
       <c r="B120" s="36"/>
       <c r="C120" s="60"/>
       <c r="D120" s="70"/>
-      <c r="E120" s="92"/>
-      <c r="F120" s="92"/>
-      <c r="G120" s="92"/>
+      <c r="E120" s="94"/>
+      <c r="F120" s="94"/>
+      <c r="G120" s="94"/>
       <c r="H120" s="96"/>
-      <c r="I120" s="90"/>
+      <c r="I120" s="98"/>
       <c r="J120" s="19"/>
       <c r="K120" s="20"/>
       <c r="L120" s="20"/>
@@ -17529,15 +17529,15 @@
       <c r="B121" s="36"/>
       <c r="C121" s="60"/>
       <c r="D121" s="70"/>
-      <c r="E121" s="92" t="s">
+      <c r="E121" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="F121" s="92"/>
-      <c r="G121" s="92"/>
-      <c r="H121" s="116">
+      <c r="F121" s="94"/>
+      <c r="G121" s="94"/>
+      <c r="H121" s="95">
         <v>45630</v>
       </c>
-      <c r="I121" s="89"/>
+      <c r="I121" s="97"/>
       <c r="J121" s="19"/>
       <c r="K121" s="20"/>
       <c r="L121" s="20"/>
@@ -17655,11 +17655,11 @@
       <c r="B122" s="36"/>
       <c r="C122" s="60"/>
       <c r="D122" s="70"/>
-      <c r="E122" s="92"/>
-      <c r="F122" s="92"/>
-      <c r="G122" s="92"/>
+      <c r="E122" s="94"/>
+      <c r="F122" s="94"/>
+      <c r="G122" s="94"/>
       <c r="H122" s="96"/>
-      <c r="I122" s="90"/>
+      <c r="I122" s="98"/>
       <c r="J122" s="19"/>
       <c r="K122" s="20"/>
       <c r="L122" s="20"/>
@@ -17777,15 +17777,15 @@
       <c r="B123" s="36"/>
       <c r="C123" s="60"/>
       <c r="D123" s="70"/>
-      <c r="E123" s="92" t="s">
+      <c r="E123" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="F123" s="92"/>
-      <c r="G123" s="92"/>
-      <c r="H123" s="106">
+      <c r="F123" s="94"/>
+      <c r="G123" s="94"/>
+      <c r="H123" s="189">
         <v>45631</v>
       </c>
-      <c r="I123" s="99"/>
+      <c r="I123" s="104"/>
       <c r="J123" s="62"/>
       <c r="K123" s="20"/>
       <c r="L123" s="20"/>
@@ -17903,11 +17903,11 @@
       <c r="B124" s="36"/>
       <c r="C124" s="60"/>
       <c r="D124" s="70"/>
-      <c r="E124" s="92"/>
-      <c r="F124" s="92"/>
-      <c r="G124" s="92"/>
-      <c r="H124" s="106"/>
-      <c r="I124" s="99"/>
+      <c r="E124" s="94"/>
+      <c r="F124" s="94"/>
+      <c r="G124" s="94"/>
+      <c r="H124" s="189"/>
+      <c r="I124" s="104"/>
       <c r="J124" s="62"/>
       <c r="K124" s="20"/>
       <c r="L124" s="20"/>
@@ -18025,15 +18025,15 @@
       <c r="B125" s="36"/>
       <c r="C125" s="60"/>
       <c r="D125" s="70"/>
-      <c r="E125" s="92" t="s">
+      <c r="E125" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="F125" s="92"/>
-      <c r="G125" s="92"/>
-      <c r="H125" s="98">
+      <c r="F125" s="94"/>
+      <c r="G125" s="94"/>
+      <c r="H125" s="103">
         <v>45632</v>
       </c>
-      <c r="I125" s="99"/>
+      <c r="I125" s="104"/>
       <c r="J125" s="62"/>
       <c r="K125" s="20"/>
       <c r="L125" s="20"/>
@@ -18151,11 +18151,11 @@
       <c r="B126" s="36"/>
       <c r="C126" s="60"/>
       <c r="D126" s="70"/>
-      <c r="E126" s="92"/>
-      <c r="F126" s="92"/>
-      <c r="G126" s="92"/>
-      <c r="H126" s="98"/>
-      <c r="I126" s="99"/>
+      <c r="E126" s="94"/>
+      <c r="F126" s="94"/>
+      <c r="G126" s="94"/>
+      <c r="H126" s="103"/>
+      <c r="I126" s="104"/>
       <c r="J126" s="62"/>
       <c r="K126" s="20"/>
       <c r="L126" s="20"/>
@@ -18273,15 +18273,15 @@
       <c r="B127" s="36"/>
       <c r="C127" s="60"/>
       <c r="D127" s="70"/>
-      <c r="E127" s="92" t="s">
+      <c r="E127" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="F127" s="92"/>
-      <c r="G127" s="92"/>
-      <c r="H127" s="116">
+      <c r="F127" s="94"/>
+      <c r="G127" s="94"/>
+      <c r="H127" s="95">
         <v>45635</v>
       </c>
-      <c r="I127" s="89"/>
+      <c r="I127" s="97"/>
       <c r="J127" s="19"/>
       <c r="K127" s="20"/>
       <c r="L127" s="20"/>
@@ -18399,11 +18399,11 @@
       <c r="B128" s="36"/>
       <c r="C128" s="60"/>
       <c r="D128" s="70"/>
-      <c r="E128" s="111"/>
-      <c r="F128" s="111"/>
-      <c r="G128" s="111"/>
+      <c r="E128" s="190"/>
+      <c r="F128" s="190"/>
+      <c r="G128" s="190"/>
       <c r="H128" s="96"/>
-      <c r="I128" s="90"/>
+      <c r="I128" s="98"/>
       <c r="J128" s="19"/>
       <c r="K128" s="20"/>
       <c r="L128" s="20"/>
@@ -18519,17 +18519,17 @@
     <row r="129" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A129" s="16"/>
       <c r="B129" s="71"/>
-      <c r="C129" s="188"/>
+      <c r="C129" s="91"/>
       <c r="D129" s="70"/>
-      <c r="E129" s="100" t="s">
+      <c r="E129" s="179" t="s">
         <v>61</v>
       </c>
-      <c r="F129" s="101"/>
-      <c r="G129" s="102"/>
-      <c r="H129" s="98">
+      <c r="F129" s="113"/>
+      <c r="G129" s="114"/>
+      <c r="H129" s="103">
         <v>45638</v>
       </c>
-      <c r="I129" s="99"/>
+      <c r="I129" s="104"/>
       <c r="J129" s="62"/>
       <c r="K129" s="20"/>
       <c r="L129" s="20"/>
@@ -18645,13 +18645,13 @@
     <row r="130" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A130" s="16"/>
       <c r="B130" s="71"/>
-      <c r="C130" s="188"/>
+      <c r="C130" s="91"/>
       <c r="D130" s="70"/>
-      <c r="E130" s="103"/>
-      <c r="F130" s="104"/>
-      <c r="G130" s="105"/>
-      <c r="H130" s="98"/>
-      <c r="I130" s="99"/>
+      <c r="E130" s="176"/>
+      <c r="F130" s="117"/>
+      <c r="G130" s="118"/>
+      <c r="H130" s="103"/>
+      <c r="I130" s="104"/>
       <c r="J130" s="62"/>
       <c r="K130" s="20"/>
       <c r="L130" s="20"/>
@@ -18767,17 +18767,17 @@
     <row r="131" spans="1:120" s="83" customFormat="1" ht="9.75" customHeight="1">
       <c r="A131" s="16"/>
       <c r="B131" s="71"/>
-      <c r="C131" s="188"/>
-      <c r="D131" s="92" t="s">
+      <c r="C131" s="91"/>
+      <c r="D131" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="E131" s="92"/>
-      <c r="F131" s="92"/>
-      <c r="G131" s="92"/>
-      <c r="H131" s="116">
+      <c r="E131" s="94"/>
+      <c r="F131" s="94"/>
+      <c r="G131" s="94"/>
+      <c r="H131" s="95">
         <v>45635</v>
       </c>
-      <c r="I131" s="128"/>
+      <c r="I131" s="101"/>
       <c r="J131" s="62"/>
       <c r="K131" s="20"/>
       <c r="L131" s="20"/>
@@ -18893,13 +18893,13 @@
     <row r="132" spans="1:120" s="83" customFormat="1" ht="9.75" customHeight="1">
       <c r="A132" s="16"/>
       <c r="B132" s="71"/>
-      <c r="C132" s="187"/>
-      <c r="D132" s="92"/>
-      <c r="E132" s="92"/>
-      <c r="F132" s="92"/>
-      <c r="G132" s="92"/>
+      <c r="C132" s="90"/>
+      <c r="D132" s="94"/>
+      <c r="E132" s="94"/>
+      <c r="F132" s="94"/>
+      <c r="G132" s="94"/>
       <c r="H132" s="96"/>
-      <c r="I132" s="129"/>
+      <c r="I132" s="102"/>
       <c r="J132" s="62"/>
       <c r="K132" s="20"/>
       <c r="L132" s="20"/>
@@ -19015,15 +19015,15 @@
     <row r="133" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A133" s="16"/>
       <c r="B133" s="36"/>
-      <c r="C133" s="126" t="s">
+      <c r="C133" s="107" t="s">
         <v>67</v>
       </c>
-      <c r="D133" s="112"/>
-      <c r="E133" s="112"/>
-      <c r="F133" s="112"/>
-      <c r="G133" s="113"/>
-      <c r="H133" s="107"/>
-      <c r="I133" s="109"/>
+      <c r="D133" s="108"/>
+      <c r="E133" s="108"/>
+      <c r="F133" s="108"/>
+      <c r="G133" s="109"/>
+      <c r="H133" s="181"/>
+      <c r="I133" s="99"/>
       <c r="J133" s="66"/>
       <c r="K133" s="64"/>
       <c r="L133" s="64"/>
@@ -19139,13 +19139,13 @@
     <row r="134" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A134" s="16"/>
       <c r="B134" s="36"/>
-      <c r="C134" s="127"/>
-      <c r="D134" s="114"/>
-      <c r="E134" s="114"/>
-      <c r="F134" s="114"/>
-      <c r="G134" s="115"/>
-      <c r="H134" s="108"/>
-      <c r="I134" s="110"/>
+      <c r="C134" s="110"/>
+      <c r="D134" s="111"/>
+      <c r="E134" s="111"/>
+      <c r="F134" s="111"/>
+      <c r="G134" s="112"/>
+      <c r="H134" s="182"/>
+      <c r="I134" s="100"/>
       <c r="J134" s="66"/>
       <c r="K134" s="64"/>
       <c r="L134" s="64"/>
@@ -19262,14 +19262,14 @@
       <c r="A135" s="16"/>
       <c r="B135" s="36"/>
       <c r="C135" s="60"/>
-      <c r="D135" s="126" t="s">
+      <c r="D135" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="112"/>
-      <c r="F135" s="112"/>
-      <c r="G135" s="113"/>
-      <c r="H135" s="85"/>
-      <c r="I135" s="87"/>
+      <c r="E135" s="108"/>
+      <c r="F135" s="108"/>
+      <c r="G135" s="109"/>
+      <c r="H135" s="105"/>
+      <c r="I135" s="164"/>
       <c r="J135" s="63"/>
       <c r="K135" s="64"/>
       <c r="L135" s="64"/>
@@ -19386,12 +19386,12 @@
       <c r="A136" s="16"/>
       <c r="B136" s="36"/>
       <c r="C136" s="60"/>
-      <c r="D136" s="127"/>
-      <c r="E136" s="114"/>
-      <c r="F136" s="114"/>
-      <c r="G136" s="115"/>
-      <c r="H136" s="86"/>
-      <c r="I136" s="88"/>
+      <c r="D136" s="110"/>
+      <c r="E136" s="111"/>
+      <c r="F136" s="111"/>
+      <c r="G136" s="112"/>
+      <c r="H136" s="183"/>
+      <c r="I136" s="184"/>
       <c r="J136" s="63"/>
       <c r="K136" s="64"/>
       <c r="L136" s="64"/>
@@ -19509,15 +19509,15 @@
       <c r="B137" s="36"/>
       <c r="C137" s="72"/>
       <c r="D137" s="74"/>
-      <c r="E137" s="101" t="s">
+      <c r="E137" s="113" t="s">
         <v>73</v>
       </c>
-      <c r="F137" s="101"/>
-      <c r="G137" s="102"/>
-      <c r="H137" s="116">
+      <c r="F137" s="113"/>
+      <c r="G137" s="114"/>
+      <c r="H137" s="95">
         <v>45636</v>
       </c>
-      <c r="I137" s="128"/>
+      <c r="I137" s="101"/>
       <c r="J137" s="62"/>
       <c r="K137" s="20"/>
       <c r="L137" s="20"/>
@@ -19635,11 +19635,11 @@
       <c r="B138" s="36"/>
       <c r="C138" s="72"/>
       <c r="D138" s="70"/>
-      <c r="E138" s="168"/>
-      <c r="F138" s="168"/>
-      <c r="G138" s="169"/>
+      <c r="E138" s="115"/>
+      <c r="F138" s="115"/>
+      <c r="G138" s="116"/>
       <c r="H138" s="96"/>
-      <c r="I138" s="129"/>
+      <c r="I138" s="102"/>
       <c r="J138" s="62"/>
       <c r="K138" s="20"/>
       <c r="L138" s="20"/>
@@ -19757,15 +19757,15 @@
       <c r="B139" s="36"/>
       <c r="C139" s="72"/>
       <c r="D139" s="70"/>
-      <c r="E139" s="101" t="s">
+      <c r="E139" s="113" t="s">
         <v>74</v>
       </c>
-      <c r="F139" s="101"/>
-      <c r="G139" s="102"/>
-      <c r="H139" s="116">
+      <c r="F139" s="113"/>
+      <c r="G139" s="114"/>
+      <c r="H139" s="95">
         <v>45637</v>
       </c>
-      <c r="I139" s="128"/>
+      <c r="I139" s="101"/>
       <c r="J139" s="62"/>
       <c r="K139" s="20"/>
       <c r="L139" s="20"/>
@@ -19883,11 +19883,11 @@
       <c r="B140" s="36"/>
       <c r="C140" s="72"/>
       <c r="D140" s="70"/>
-      <c r="E140" s="104"/>
-      <c r="F140" s="104"/>
-      <c r="G140" s="105"/>
+      <c r="E140" s="117"/>
+      <c r="F140" s="117"/>
+      <c r="G140" s="118"/>
       <c r="H140" s="96"/>
-      <c r="I140" s="129"/>
+      <c r="I140" s="102"/>
       <c r="J140" s="62"/>
       <c r="K140" s="20"/>
       <c r="L140" s="20"/>
@@ -20004,16 +20004,16 @@
       <c r="A141" s="16"/>
       <c r="B141" s="36"/>
       <c r="C141" s="82"/>
-      <c r="D141" s="92" t="s">
+      <c r="D141" s="94" t="s">
         <v>80</v>
       </c>
-      <c r="E141" s="92"/>
-      <c r="F141" s="92"/>
-      <c r="G141" s="92"/>
-      <c r="H141" s="116">
+      <c r="E141" s="94"/>
+      <c r="F141" s="94"/>
+      <c r="G141" s="94"/>
+      <c r="H141" s="95">
         <v>45637</v>
       </c>
-      <c r="I141" s="189"/>
+      <c r="I141" s="92"/>
       <c r="J141" s="62"/>
       <c r="K141" s="20"/>
       <c r="L141" s="20"/>
@@ -20130,12 +20130,12 @@
       <c r="A142" s="16"/>
       <c r="B142" s="36"/>
       <c r="C142" s="82"/>
-      <c r="D142" s="92"/>
-      <c r="E142" s="92"/>
-      <c r="F142" s="92"/>
-      <c r="G142" s="92"/>
+      <c r="D142" s="94"/>
+      <c r="E142" s="94"/>
+      <c r="F142" s="94"/>
+      <c r="G142" s="94"/>
       <c r="H142" s="96"/>
-      <c r="I142" s="189"/>
+      <c r="I142" s="92"/>
       <c r="J142" s="62"/>
       <c r="K142" s="20"/>
       <c r="L142" s="20"/>
@@ -20252,14 +20252,14 @@
       <c r="A143" s="16"/>
       <c r="B143" s="36"/>
       <c r="C143" s="72"/>
-      <c r="D143" s="165" t="s">
+      <c r="D143" s="119" t="s">
         <v>66</v>
       </c>
-      <c r="E143" s="166"/>
-      <c r="F143" s="166"/>
-      <c r="G143" s="167"/>
-      <c r="H143" s="85"/>
-      <c r="I143" s="109"/>
+      <c r="E143" s="120"/>
+      <c r="F143" s="120"/>
+      <c r="G143" s="121"/>
+      <c r="H143" s="105"/>
+      <c r="I143" s="99"/>
       <c r="J143" s="66"/>
       <c r="K143" s="64"/>
       <c r="L143" s="64"/>
@@ -20376,12 +20376,12 @@
       <c r="A144" s="16"/>
       <c r="B144" s="36"/>
       <c r="C144" s="72"/>
-      <c r="D144" s="127"/>
-      <c r="E144" s="114"/>
-      <c r="F144" s="114"/>
-      <c r="G144" s="115"/>
-      <c r="H144" s="170"/>
-      <c r="I144" s="110"/>
+      <c r="D144" s="110"/>
+      <c r="E144" s="111"/>
+      <c r="F144" s="111"/>
+      <c r="G144" s="112"/>
+      <c r="H144" s="106"/>
+      <c r="I144" s="100"/>
       <c r="J144" s="66"/>
       <c r="K144" s="64"/>
       <c r="L144" s="64"/>
@@ -20499,15 +20499,15 @@
       <c r="B145" s="36"/>
       <c r="C145" s="72"/>
       <c r="D145" s="74"/>
-      <c r="E145" s="101" t="s">
+      <c r="E145" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="F145" s="101"/>
-      <c r="G145" s="102"/>
-      <c r="H145" s="116">
+      <c r="F145" s="113"/>
+      <c r="G145" s="114"/>
+      <c r="H145" s="95">
         <v>45639</v>
       </c>
-      <c r="I145" s="128"/>
+      <c r="I145" s="101"/>
       <c r="J145" s="62"/>
       <c r="K145" s="20"/>
       <c r="L145" s="20"/>
@@ -20625,11 +20625,11 @@
       <c r="B146" s="36"/>
       <c r="C146" s="72"/>
       <c r="D146" s="70"/>
-      <c r="E146" s="168"/>
-      <c r="F146" s="168"/>
-      <c r="G146" s="169"/>
+      <c r="E146" s="115"/>
+      <c r="F146" s="115"/>
+      <c r="G146" s="116"/>
       <c r="H146" s="96"/>
-      <c r="I146" s="129"/>
+      <c r="I146" s="102"/>
       <c r="J146" s="62"/>
       <c r="K146" s="20"/>
       <c r="L146" s="20"/>
@@ -20747,15 +20747,15 @@
       <c r="B147" s="36"/>
       <c r="C147" s="72"/>
       <c r="D147" s="70"/>
-      <c r="E147" s="101" t="s">
+      <c r="E147" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="F147" s="101"/>
-      <c r="G147" s="102"/>
-      <c r="H147" s="116">
+      <c r="F147" s="113"/>
+      <c r="G147" s="114"/>
+      <c r="H147" s="95">
         <v>45642</v>
       </c>
-      <c r="I147" s="128"/>
+      <c r="I147" s="101"/>
       <c r="J147" s="62"/>
       <c r="K147" s="20"/>
       <c r="L147" s="20"/>
@@ -20873,11 +20873,11 @@
       <c r="B148" s="36"/>
       <c r="C148" s="72"/>
       <c r="D148" s="70"/>
-      <c r="E148" s="168"/>
-      <c r="F148" s="168"/>
-      <c r="G148" s="169"/>
+      <c r="E148" s="115"/>
+      <c r="F148" s="115"/>
+      <c r="G148" s="116"/>
       <c r="H148" s="96"/>
-      <c r="I148" s="129"/>
+      <c r="I148" s="102"/>
       <c r="J148" s="62"/>
       <c r="K148" s="20"/>
       <c r="L148" s="20"/>
@@ -20995,15 +20995,15 @@
       <c r="B149" s="36"/>
       <c r="C149" s="72"/>
       <c r="D149" s="70"/>
-      <c r="E149" s="101" t="s">
+      <c r="E149" s="113" t="s">
         <v>70</v>
       </c>
-      <c r="F149" s="101"/>
-      <c r="G149" s="102"/>
-      <c r="H149" s="116">
+      <c r="F149" s="113"/>
+      <c r="G149" s="114"/>
+      <c r="H149" s="95">
         <v>45643</v>
       </c>
-      <c r="I149" s="128"/>
+      <c r="I149" s="101"/>
       <c r="J149" s="62"/>
       <c r="K149" s="20"/>
       <c r="L149" s="20"/>
@@ -21121,11 +21121,11 @@
       <c r="B150" s="36"/>
       <c r="C150" s="72"/>
       <c r="D150" s="70"/>
-      <c r="E150" s="168"/>
-      <c r="F150" s="168"/>
-      <c r="G150" s="169"/>
+      <c r="E150" s="115"/>
+      <c r="F150" s="115"/>
+      <c r="G150" s="116"/>
       <c r="H150" s="96"/>
-      <c r="I150" s="129"/>
+      <c r="I150" s="102"/>
       <c r="J150" s="62"/>
       <c r="K150" s="20"/>
       <c r="L150" s="20"/>
@@ -21243,15 +21243,15 @@
       <c r="B151" s="36"/>
       <c r="C151" s="72"/>
       <c r="D151" s="70"/>
-      <c r="E151" s="92" t="s">
+      <c r="E151" s="94" t="s">
         <v>75</v>
       </c>
-      <c r="F151" s="92"/>
-      <c r="G151" s="92"/>
-      <c r="H151" s="116">
+      <c r="F151" s="94"/>
+      <c r="G151" s="94"/>
+      <c r="H151" s="95">
         <v>45644</v>
       </c>
-      <c r="I151" s="128"/>
+      <c r="I151" s="101"/>
       <c r="J151" s="62"/>
       <c r="K151" s="20"/>
       <c r="L151" s="20"/>
@@ -21369,11 +21369,11 @@
       <c r="B152" s="36"/>
       <c r="C152" s="72"/>
       <c r="D152" s="70"/>
-      <c r="E152" s="92"/>
-      <c r="F152" s="92"/>
-      <c r="G152" s="92"/>
+      <c r="E152" s="94"/>
+      <c r="F152" s="94"/>
+      <c r="G152" s="94"/>
       <c r="H152" s="96"/>
-      <c r="I152" s="129"/>
+      <c r="I152" s="102"/>
       <c r="J152" s="62"/>
       <c r="K152" s="20"/>
       <c r="L152" s="20"/>
@@ -21491,15 +21491,15 @@
       <c r="B153" s="36"/>
       <c r="C153" s="72"/>
       <c r="D153" s="70"/>
-      <c r="E153" s="92" t="s">
+      <c r="E153" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="F153" s="92"/>
-      <c r="G153" s="92"/>
-      <c r="H153" s="116">
+      <c r="F153" s="94"/>
+      <c r="G153" s="94"/>
+      <c r="H153" s="95">
         <v>45644</v>
       </c>
-      <c r="I153" s="128"/>
+      <c r="I153" s="101"/>
       <c r="J153" s="62"/>
       <c r="K153" s="20"/>
       <c r="L153" s="20"/>
@@ -21617,11 +21617,11 @@
       <c r="B154" s="36"/>
       <c r="C154" s="72"/>
       <c r="D154" s="70"/>
-      <c r="E154" s="92"/>
-      <c r="F154" s="92"/>
-      <c r="G154" s="92"/>
+      <c r="E154" s="94"/>
+      <c r="F154" s="94"/>
+      <c r="G154" s="94"/>
       <c r="H154" s="96"/>
-      <c r="I154" s="129"/>
+      <c r="I154" s="102"/>
       <c r="J154" s="62"/>
       <c r="K154" s="20"/>
       <c r="L154" s="20"/>
@@ -21738,16 +21738,16 @@
       <c r="A155" s="1"/>
       <c r="B155" s="18"/>
       <c r="C155" s="60"/>
-      <c r="D155" s="93"/>
-      <c r="E155" s="91" t="s">
+      <c r="D155" s="186"/>
+      <c r="E155" s="185" t="s">
         <v>61</v>
       </c>
-      <c r="F155" s="92"/>
-      <c r="G155" s="92"/>
-      <c r="H155" s="95">
+      <c r="F155" s="94"/>
+      <c r="G155" s="94"/>
+      <c r="H155" s="187">
         <v>45645</v>
       </c>
-      <c r="I155" s="97"/>
+      <c r="I155" s="188"/>
       <c r="J155" s="19"/>
       <c r="K155" s="20"/>
       <c r="L155" s="20"/>
@@ -21864,12 +21864,12 @@
       <c r="A156" s="1"/>
       <c r="B156" s="18"/>
       <c r="C156" s="60"/>
-      <c r="D156" s="94"/>
-      <c r="E156" s="91"/>
-      <c r="F156" s="92"/>
-      <c r="G156" s="92"/>
+      <c r="D156" s="175"/>
+      <c r="E156" s="185"/>
+      <c r="F156" s="94"/>
+      <c r="G156" s="94"/>
       <c r="H156" s="96"/>
-      <c r="I156" s="90"/>
+      <c r="I156" s="98"/>
       <c r="J156" s="19"/>
       <c r="K156" s="20"/>
       <c r="L156" s="20"/>
@@ -21984,18 +21984,18 @@
     </row>
     <row r="157" spans="1:120" s="83" customFormat="1" ht="9.75" customHeight="1">
       <c r="A157" s="1"/>
-      <c r="B157" s="190"/>
-      <c r="C157" s="187"/>
-      <c r="D157" s="92" t="s">
+      <c r="B157" s="93"/>
+      <c r="C157" s="90"/>
+      <c r="D157" s="94" t="s">
         <v>81</v>
       </c>
-      <c r="E157" s="92"/>
-      <c r="F157" s="92"/>
-      <c r="G157" s="92"/>
-      <c r="H157" s="116">
+      <c r="E157" s="94"/>
+      <c r="F157" s="94"/>
+      <c r="G157" s="94"/>
+      <c r="H157" s="95">
         <v>45644</v>
       </c>
-      <c r="I157" s="89"/>
+      <c r="I157" s="97"/>
       <c r="J157" s="19"/>
       <c r="K157" s="20"/>
       <c r="L157" s="20"/>
@@ -22110,14 +22110,14 @@
     </row>
     <row r="158" spans="1:120" s="83" customFormat="1" ht="9.75" customHeight="1">
       <c r="A158" s="1"/>
-      <c r="B158" s="190"/>
-      <c r="C158" s="187"/>
-      <c r="D158" s="92"/>
-      <c r="E158" s="92"/>
-      <c r="F158" s="92"/>
-      <c r="G158" s="92"/>
+      <c r="B158" s="93"/>
+      <c r="C158" s="90"/>
+      <c r="D158" s="94"/>
+      <c r="E158" s="94"/>
+      <c r="F158" s="94"/>
+      <c r="G158" s="94"/>
       <c r="H158" s="96"/>
-      <c r="I158" s="90"/>
+      <c r="I158" s="98"/>
       <c r="J158" s="19"/>
       <c r="K158" s="20"/>
       <c r="L158" s="20"/>
@@ -22235,17 +22235,17 @@
       <c r="B159" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="C159" s="176" t="s">
+      <c r="C159" s="156" t="s">
         <v>31</v>
       </c>
-      <c r="D159" s="177"/>
-      <c r="E159" s="177"/>
-      <c r="F159" s="177"/>
-      <c r="G159" s="178"/>
-      <c r="H159" s="131" t="s">
+      <c r="D159" s="157"/>
+      <c r="E159" s="157"/>
+      <c r="F159" s="157"/>
+      <c r="G159" s="158"/>
+      <c r="H159" s="166" t="s">
         <v>57</v>
       </c>
-      <c r="I159" s="99"/>
+      <c r="I159" s="104"/>
       <c r="J159" s="14"/>
       <c r="K159" s="15"/>
       <c r="L159" s="15"/>
@@ -22360,14 +22360,14 @@
     </row>
     <row r="160" spans="1:120" ht="9.75" customHeight="1">
       <c r="A160" s="1"/>
-      <c r="B160" s="184"/>
-      <c r="C160" s="179"/>
-      <c r="D160" s="180"/>
-      <c r="E160" s="180"/>
-      <c r="F160" s="180"/>
-      <c r="G160" s="181"/>
-      <c r="H160" s="99"/>
-      <c r="I160" s="99"/>
+      <c r="B160" s="87"/>
+      <c r="C160" s="159"/>
+      <c r="D160" s="160"/>
+      <c r="E160" s="160"/>
+      <c r="F160" s="160"/>
+      <c r="G160" s="161"/>
+      <c r="H160" s="104"/>
+      <c r="I160" s="104"/>
       <c r="J160" s="14"/>
       <c r="K160" s="15"/>
       <c r="L160" s="15"/>
@@ -22483,13 +22483,13 @@
     <row r="161" spans="1:120" ht="9.75" customHeight="1">
       <c r="A161" s="16"/>
       <c r="B161" s="18"/>
-      <c r="C161" s="182"/>
-      <c r="D161" s="182"/>
-      <c r="E161" s="182"/>
-      <c r="F161" s="182"/>
-      <c r="G161" s="183"/>
-      <c r="H161" s="99"/>
-      <c r="I161" s="99"/>
+      <c r="C161" s="85"/>
+      <c r="D161" s="85"/>
+      <c r="E161" s="85"/>
+      <c r="F161" s="85"/>
+      <c r="G161" s="86"/>
+      <c r="H161" s="104"/>
+      <c r="I161" s="104"/>
       <c r="J161" s="12"/>
       <c r="K161" s="13"/>
       <c r="L161" s="13"/>
@@ -22605,13 +22605,13 @@
     <row r="162" spans="1:120" ht="9.75" customHeight="1">
       <c r="A162" s="16"/>
       <c r="B162" s="37"/>
-      <c r="C162" s="185"/>
-      <c r="D162" s="185"/>
-      <c r="E162" s="185"/>
-      <c r="F162" s="185"/>
-      <c r="G162" s="186"/>
-      <c r="H162" s="99"/>
-      <c r="I162" s="99"/>
+      <c r="C162" s="88"/>
+      <c r="D162" s="88"/>
+      <c r="E162" s="88"/>
+      <c r="F162" s="88"/>
+      <c r="G162" s="89"/>
+      <c r="H162" s="104"/>
+      <c r="I162" s="104"/>
       <c r="J162" s="14"/>
       <c r="K162" s="15"/>
       <c r="L162" s="15"/>
@@ -22727,17 +22727,17 @@
     <row r="163" spans="1:120" ht="9.75" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
-      <c r="C163" s="171" t="s">
+      <c r="C163" s="151" t="s">
         <v>33</v>
       </c>
-      <c r="D163" s="136"/>
-      <c r="E163" s="136"/>
-      <c r="F163" s="136"/>
-      <c r="G163" s="172"/>
-      <c r="H163" s="131" t="s">
+      <c r="D163" s="131"/>
+      <c r="E163" s="131"/>
+      <c r="F163" s="131"/>
+      <c r="G163" s="152"/>
+      <c r="H163" s="166" t="s">
         <v>56</v>
       </c>
-      <c r="I163" s="99"/>
+      <c r="I163" s="104"/>
       <c r="J163" s="19"/>
       <c r="K163" s="20"/>
       <c r="L163" s="20"/>
@@ -22853,13 +22853,13 @@
     <row r="164" spans="1:120" ht="9.75" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
-      <c r="C164" s="173"/>
-      <c r="D164" s="174"/>
-      <c r="E164" s="174"/>
-      <c r="F164" s="174"/>
-      <c r="G164" s="175"/>
-      <c r="H164" s="99"/>
-      <c r="I164" s="99"/>
+      <c r="C164" s="153"/>
+      <c r="D164" s="154"/>
+      <c r="E164" s="154"/>
+      <c r="F164" s="154"/>
+      <c r="G164" s="155"/>
+      <c r="H164" s="104"/>
+      <c r="I164" s="104"/>
       <c r="J164" s="19"/>
       <c r="K164" s="20"/>
       <c r="L164" s="20"/>
@@ -36398,6 +36398,222 @@
     </row>
   </sheetData>
   <mergeCells count="240">
+    <mergeCell ref="E155:G156"/>
+    <mergeCell ref="D155:D156"/>
+    <mergeCell ref="H155:H156"/>
+    <mergeCell ref="I155:I156"/>
+    <mergeCell ref="H113:H114"/>
+    <mergeCell ref="I113:I114"/>
+    <mergeCell ref="H129:H130"/>
+    <mergeCell ref="I129:I130"/>
+    <mergeCell ref="E129:G130"/>
+    <mergeCell ref="H123:H124"/>
+    <mergeCell ref="I123:I124"/>
+    <mergeCell ref="I125:I126"/>
+    <mergeCell ref="H125:H126"/>
+    <mergeCell ref="H133:H134"/>
+    <mergeCell ref="I133:I134"/>
+    <mergeCell ref="E123:G124"/>
+    <mergeCell ref="E125:G126"/>
+    <mergeCell ref="E127:G128"/>
+    <mergeCell ref="E113:G114"/>
+    <mergeCell ref="E119:G120"/>
+    <mergeCell ref="E121:G122"/>
+    <mergeCell ref="H127:H128"/>
+    <mergeCell ref="I127:I128"/>
+    <mergeCell ref="H121:H122"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="H105:H106"/>
+    <mergeCell ref="I105:I106"/>
+    <mergeCell ref="H107:H108"/>
+    <mergeCell ref="I107:I108"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="H117:H118"/>
+    <mergeCell ref="I117:I118"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="I119:I120"/>
+    <mergeCell ref="H101:H102"/>
+    <mergeCell ref="I101:I102"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="I85:I86"/>
+    <mergeCell ref="H89:H90"/>
+    <mergeCell ref="I89:I90"/>
+    <mergeCell ref="E81:G82"/>
+    <mergeCell ref="E83:G84"/>
+    <mergeCell ref="E91:G92"/>
+    <mergeCell ref="E93:G94"/>
+    <mergeCell ref="E95:G96"/>
+    <mergeCell ref="E97:G98"/>
+    <mergeCell ref="E99:G100"/>
+    <mergeCell ref="E85:G86"/>
+    <mergeCell ref="D89:G90"/>
+    <mergeCell ref="H75:H76"/>
+    <mergeCell ref="H159:H160"/>
+    <mergeCell ref="H163:H164"/>
+    <mergeCell ref="H161:H162"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="H59:H60"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="H77:H78"/>
+    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="H93:H94"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="H111:H112"/>
+    <mergeCell ref="I163:I164"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="I159:I160"/>
+    <mergeCell ref="I161:I162"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="I93:I94"/>
+    <mergeCell ref="I95:I96"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="I109:I110"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="I153:I154"/>
+    <mergeCell ref="I151:I152"/>
+    <mergeCell ref="I149:I150"/>
+    <mergeCell ref="I147:I148"/>
+    <mergeCell ref="I145:I146"/>
+    <mergeCell ref="I111:I112"/>
+    <mergeCell ref="I135:I136"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I67:I68"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="C163:G164"/>
+    <mergeCell ref="C159:G160"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="C31:G32"/>
+    <mergeCell ref="D33:G34"/>
+    <mergeCell ref="E35:G36"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="E43:G44"/>
+    <mergeCell ref="E45:G46"/>
+    <mergeCell ref="E47:G48"/>
+    <mergeCell ref="E49:G50"/>
+    <mergeCell ref="E51:G52"/>
+    <mergeCell ref="D53:G54"/>
+    <mergeCell ref="E55:G56"/>
+    <mergeCell ref="E57:G58"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="J3:CJ3"/>
+    <mergeCell ref="CK3:DO3"/>
+    <mergeCell ref="J4:AA4"/>
+    <mergeCell ref="AB4:BE4"/>
+    <mergeCell ref="BF4:CJ4"/>
+    <mergeCell ref="CK4:DO4"/>
+    <mergeCell ref="B7:G8"/>
+    <mergeCell ref="C9:G10"/>
+    <mergeCell ref="C11:G12"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="D13:G14"/>
+    <mergeCell ref="D15:G16"/>
+    <mergeCell ref="D17:G18"/>
+    <mergeCell ref="D19:G20"/>
+    <mergeCell ref="C21:G22"/>
+    <mergeCell ref="D23:G24"/>
+    <mergeCell ref="C25:G26"/>
+    <mergeCell ref="D27:G28"/>
+    <mergeCell ref="D29:G30"/>
+    <mergeCell ref="E147:G148"/>
+    <mergeCell ref="E149:G150"/>
+    <mergeCell ref="E151:G152"/>
+    <mergeCell ref="E59:G60"/>
+    <mergeCell ref="E61:G62"/>
+    <mergeCell ref="D63:G64"/>
+    <mergeCell ref="E67:G68"/>
+    <mergeCell ref="E65:G66"/>
+    <mergeCell ref="E69:G70"/>
+    <mergeCell ref="E71:G72"/>
+    <mergeCell ref="C73:G74"/>
+    <mergeCell ref="C75:G76"/>
+    <mergeCell ref="C77:G78"/>
+    <mergeCell ref="D79:G80"/>
+    <mergeCell ref="E109:G110"/>
+    <mergeCell ref="E111:G112"/>
+    <mergeCell ref="E101:G102"/>
+    <mergeCell ref="C105:G106"/>
+    <mergeCell ref="D107:G108"/>
+    <mergeCell ref="D117:G118"/>
+    <mergeCell ref="H145:H146"/>
+    <mergeCell ref="H143:H144"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="C133:G134"/>
+    <mergeCell ref="D135:G136"/>
+    <mergeCell ref="E137:G138"/>
+    <mergeCell ref="E139:G140"/>
+    <mergeCell ref="D143:G144"/>
+    <mergeCell ref="E145:G146"/>
+    <mergeCell ref="H135:H136"/>
     <mergeCell ref="D157:G158"/>
     <mergeCell ref="H157:H158"/>
     <mergeCell ref="I157:I158"/>
@@ -36422,222 +36638,6 @@
     <mergeCell ref="H151:H152"/>
     <mergeCell ref="H149:H150"/>
     <mergeCell ref="H147:H148"/>
-    <mergeCell ref="H145:H146"/>
-    <mergeCell ref="H143:H144"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="C133:G134"/>
-    <mergeCell ref="D135:G136"/>
-    <mergeCell ref="E137:G138"/>
-    <mergeCell ref="E139:G140"/>
-    <mergeCell ref="D143:G144"/>
-    <mergeCell ref="E145:G146"/>
-    <mergeCell ref="E147:G148"/>
-    <mergeCell ref="E149:G150"/>
-    <mergeCell ref="E151:G152"/>
-    <mergeCell ref="E59:G60"/>
-    <mergeCell ref="E61:G62"/>
-    <mergeCell ref="D63:G64"/>
-    <mergeCell ref="E67:G68"/>
-    <mergeCell ref="E65:G66"/>
-    <mergeCell ref="E69:G70"/>
-    <mergeCell ref="E71:G72"/>
-    <mergeCell ref="C73:G74"/>
-    <mergeCell ref="C75:G76"/>
-    <mergeCell ref="D13:G14"/>
-    <mergeCell ref="D15:G16"/>
-    <mergeCell ref="D17:G18"/>
-    <mergeCell ref="D19:G20"/>
-    <mergeCell ref="C21:G22"/>
-    <mergeCell ref="D23:G24"/>
-    <mergeCell ref="C25:G26"/>
-    <mergeCell ref="D27:G28"/>
-    <mergeCell ref="D29:G30"/>
-    <mergeCell ref="J3:CJ3"/>
-    <mergeCell ref="CK3:DO3"/>
-    <mergeCell ref="J4:AA4"/>
-    <mergeCell ref="AB4:BE4"/>
-    <mergeCell ref="BF4:CJ4"/>
-    <mergeCell ref="CK4:DO4"/>
-    <mergeCell ref="B7:G8"/>
-    <mergeCell ref="C9:G10"/>
-    <mergeCell ref="C11:G12"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="C163:G164"/>
-    <mergeCell ref="C159:G160"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="C31:G32"/>
-    <mergeCell ref="D33:G34"/>
-    <mergeCell ref="E35:G36"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="E43:G44"/>
-    <mergeCell ref="E45:G46"/>
-    <mergeCell ref="E47:G48"/>
-    <mergeCell ref="E49:G50"/>
-    <mergeCell ref="E51:G52"/>
-    <mergeCell ref="D53:G54"/>
-    <mergeCell ref="E55:G56"/>
-    <mergeCell ref="E57:G58"/>
-    <mergeCell ref="I53:I54"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="I159:I160"/>
-    <mergeCell ref="I161:I162"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="I93:I94"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="I109:I110"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="I153:I154"/>
-    <mergeCell ref="I151:I152"/>
-    <mergeCell ref="I149:I150"/>
-    <mergeCell ref="I147:I148"/>
-    <mergeCell ref="I145:I146"/>
-    <mergeCell ref="I163:I164"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="H75:H76"/>
-    <mergeCell ref="H159:H160"/>
-    <mergeCell ref="H163:H164"/>
-    <mergeCell ref="H161:H162"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="H67:H68"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H59:H60"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="H77:H78"/>
-    <mergeCell ref="H81:H82"/>
-    <mergeCell ref="H83:H84"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="H93:H94"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="C77:G78"/>
-    <mergeCell ref="D79:G80"/>
-    <mergeCell ref="H111:H112"/>
-    <mergeCell ref="I111:I112"/>
-    <mergeCell ref="E109:G110"/>
-    <mergeCell ref="E111:G112"/>
-    <mergeCell ref="E101:G102"/>
-    <mergeCell ref="H101:H102"/>
-    <mergeCell ref="I101:I102"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="I85:I86"/>
-    <mergeCell ref="H89:H90"/>
-    <mergeCell ref="I89:I90"/>
-    <mergeCell ref="E81:G82"/>
-    <mergeCell ref="E83:G84"/>
-    <mergeCell ref="E91:G92"/>
-    <mergeCell ref="E93:G94"/>
-    <mergeCell ref="E95:G96"/>
-    <mergeCell ref="E97:G98"/>
-    <mergeCell ref="E99:G100"/>
-    <mergeCell ref="E85:G86"/>
-    <mergeCell ref="C105:G106"/>
-    <mergeCell ref="D107:G108"/>
-    <mergeCell ref="D89:G90"/>
-    <mergeCell ref="D117:G118"/>
-    <mergeCell ref="H127:H128"/>
-    <mergeCell ref="I127:I128"/>
-    <mergeCell ref="H121:H122"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="H105:H106"/>
-    <mergeCell ref="I105:I106"/>
-    <mergeCell ref="H107:H108"/>
-    <mergeCell ref="I107:I108"/>
-    <mergeCell ref="H109:H110"/>
-    <mergeCell ref="H117:H118"/>
-    <mergeCell ref="I117:I118"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="H135:H136"/>
-    <mergeCell ref="I135:I136"/>
-    <mergeCell ref="I119:I120"/>
-    <mergeCell ref="E155:G156"/>
-    <mergeCell ref="D155:D156"/>
-    <mergeCell ref="H155:H156"/>
-    <mergeCell ref="I155:I156"/>
-    <mergeCell ref="H113:H114"/>
-    <mergeCell ref="I113:I114"/>
-    <mergeCell ref="H129:H130"/>
-    <mergeCell ref="I129:I130"/>
-    <mergeCell ref="E129:G130"/>
-    <mergeCell ref="H123:H124"/>
-    <mergeCell ref="I123:I124"/>
-    <mergeCell ref="I125:I126"/>
-    <mergeCell ref="H125:H126"/>
-    <mergeCell ref="H133:H134"/>
-    <mergeCell ref="I133:I134"/>
-    <mergeCell ref="E123:G124"/>
-    <mergeCell ref="E125:G126"/>
-    <mergeCell ref="E127:G128"/>
-    <mergeCell ref="E113:G114"/>
-    <mergeCell ref="E119:G120"/>
-    <mergeCell ref="E121:G122"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <conditionalFormatting sqref="J7">

--- a/docs/【DIGITAL OJT】WBS.xlsx
+++ b/docs/【DIGITAL OJT】WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIGITALOJT\digital-ojt-development-cause-DroneInventorySystem\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84453921-19C4-4841-A2FC-4D251C096DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCAC5C8C-0222-435C-ADF3-82888E70F148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16905" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1481,19 +1481,67 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1502,22 +1550,25 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1538,83 +1589,29 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1640,23 +1637,56 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1676,53 +1706,23 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2330,120 +2330,120 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="J3" s="144">
+      <c r="J3" s="165">
         <v>2024</v>
       </c>
-      <c r="K3" s="145"/>
-      <c r="L3" s="145"/>
-      <c r="M3" s="145"/>
-      <c r="N3" s="145"/>
-      <c r="O3" s="145"/>
-      <c r="P3" s="145"/>
-      <c r="Q3" s="145"/>
-      <c r="R3" s="145"/>
-      <c r="S3" s="145"/>
-      <c r="T3" s="145"/>
-      <c r="U3" s="145"/>
-      <c r="V3" s="145"/>
-      <c r="W3" s="145"/>
-      <c r="X3" s="145"/>
-      <c r="Y3" s="145"/>
-      <c r="Z3" s="145"/>
-      <c r="AA3" s="145"/>
-      <c r="AB3" s="145"/>
-      <c r="AC3" s="145"/>
-      <c r="AD3" s="145"/>
-      <c r="AE3" s="145"/>
-      <c r="AF3" s="145"/>
-      <c r="AG3" s="145"/>
-      <c r="AH3" s="145"/>
-      <c r="AI3" s="145"/>
-      <c r="AJ3" s="145"/>
-      <c r="AK3" s="145"/>
-      <c r="AL3" s="145"/>
-      <c r="AM3" s="145"/>
-      <c r="AN3" s="145"/>
-      <c r="AO3" s="145"/>
-      <c r="AP3" s="145"/>
-      <c r="AQ3" s="145"/>
-      <c r="AR3" s="145"/>
-      <c r="AS3" s="145"/>
-      <c r="AT3" s="145"/>
-      <c r="AU3" s="145"/>
-      <c r="AV3" s="145"/>
-      <c r="AW3" s="145"/>
-      <c r="AX3" s="145"/>
-      <c r="AY3" s="145"/>
-      <c r="AZ3" s="145"/>
-      <c r="BA3" s="145"/>
-      <c r="BB3" s="145"/>
-      <c r="BC3" s="145"/>
-      <c r="BD3" s="145"/>
-      <c r="BE3" s="145"/>
-      <c r="BF3" s="145"/>
-      <c r="BG3" s="145"/>
-      <c r="BH3" s="145"/>
-      <c r="BI3" s="145"/>
-      <c r="BJ3" s="145"/>
-      <c r="BK3" s="145"/>
-      <c r="BL3" s="145"/>
-      <c r="BM3" s="145"/>
-      <c r="BN3" s="145"/>
-      <c r="BO3" s="145"/>
-      <c r="BP3" s="145"/>
-      <c r="BQ3" s="145"/>
-      <c r="BR3" s="145"/>
-      <c r="BS3" s="145"/>
-      <c r="BT3" s="145"/>
-      <c r="BU3" s="145"/>
-      <c r="BV3" s="145"/>
-      <c r="BW3" s="145"/>
-      <c r="BX3" s="145"/>
-      <c r="BY3" s="145"/>
-      <c r="BZ3" s="145"/>
-      <c r="CA3" s="145"/>
-      <c r="CB3" s="145"/>
-      <c r="CC3" s="145"/>
-      <c r="CD3" s="145"/>
-      <c r="CE3" s="145"/>
-      <c r="CF3" s="145"/>
-      <c r="CG3" s="145"/>
-      <c r="CH3" s="145"/>
-      <c r="CI3" s="145"/>
-      <c r="CJ3" s="146"/>
-      <c r="CK3" s="144">
+      <c r="K3" s="166"/>
+      <c r="L3" s="166"/>
+      <c r="M3" s="166"/>
+      <c r="N3" s="166"/>
+      <c r="O3" s="166"/>
+      <c r="P3" s="166"/>
+      <c r="Q3" s="166"/>
+      <c r="R3" s="166"/>
+      <c r="S3" s="166"/>
+      <c r="T3" s="166"/>
+      <c r="U3" s="166"/>
+      <c r="V3" s="166"/>
+      <c r="W3" s="166"/>
+      <c r="X3" s="166"/>
+      <c r="Y3" s="166"/>
+      <c r="Z3" s="166"/>
+      <c r="AA3" s="166"/>
+      <c r="AB3" s="166"/>
+      <c r="AC3" s="166"/>
+      <c r="AD3" s="166"/>
+      <c r="AE3" s="166"/>
+      <c r="AF3" s="166"/>
+      <c r="AG3" s="166"/>
+      <c r="AH3" s="166"/>
+      <c r="AI3" s="166"/>
+      <c r="AJ3" s="166"/>
+      <c r="AK3" s="166"/>
+      <c r="AL3" s="166"/>
+      <c r="AM3" s="166"/>
+      <c r="AN3" s="166"/>
+      <c r="AO3" s="166"/>
+      <c r="AP3" s="166"/>
+      <c r="AQ3" s="166"/>
+      <c r="AR3" s="166"/>
+      <c r="AS3" s="166"/>
+      <c r="AT3" s="166"/>
+      <c r="AU3" s="166"/>
+      <c r="AV3" s="166"/>
+      <c r="AW3" s="166"/>
+      <c r="AX3" s="166"/>
+      <c r="AY3" s="166"/>
+      <c r="AZ3" s="166"/>
+      <c r="BA3" s="166"/>
+      <c r="BB3" s="166"/>
+      <c r="BC3" s="166"/>
+      <c r="BD3" s="166"/>
+      <c r="BE3" s="166"/>
+      <c r="BF3" s="166"/>
+      <c r="BG3" s="166"/>
+      <c r="BH3" s="166"/>
+      <c r="BI3" s="166"/>
+      <c r="BJ3" s="166"/>
+      <c r="BK3" s="166"/>
+      <c r="BL3" s="166"/>
+      <c r="BM3" s="166"/>
+      <c r="BN3" s="166"/>
+      <c r="BO3" s="166"/>
+      <c r="BP3" s="166"/>
+      <c r="BQ3" s="166"/>
+      <c r="BR3" s="166"/>
+      <c r="BS3" s="166"/>
+      <c r="BT3" s="166"/>
+      <c r="BU3" s="166"/>
+      <c r="BV3" s="166"/>
+      <c r="BW3" s="166"/>
+      <c r="BX3" s="166"/>
+      <c r="BY3" s="166"/>
+      <c r="BZ3" s="166"/>
+      <c r="CA3" s="166"/>
+      <c r="CB3" s="166"/>
+      <c r="CC3" s="166"/>
+      <c r="CD3" s="166"/>
+      <c r="CE3" s="166"/>
+      <c r="CF3" s="166"/>
+      <c r="CG3" s="166"/>
+      <c r="CH3" s="166"/>
+      <c r="CI3" s="166"/>
+      <c r="CJ3" s="167"/>
+      <c r="CK3" s="165">
         <v>2025</v>
       </c>
-      <c r="CL3" s="145"/>
-      <c r="CM3" s="145"/>
-      <c r="CN3" s="145"/>
-      <c r="CO3" s="145"/>
-      <c r="CP3" s="145"/>
-      <c r="CQ3" s="145"/>
-      <c r="CR3" s="145"/>
-      <c r="CS3" s="145"/>
-      <c r="CT3" s="145"/>
-      <c r="CU3" s="145"/>
-      <c r="CV3" s="145"/>
-      <c r="CW3" s="145"/>
-      <c r="CX3" s="145"/>
-      <c r="CY3" s="145"/>
-      <c r="CZ3" s="145"/>
-      <c r="DA3" s="145"/>
-      <c r="DB3" s="145"/>
-      <c r="DC3" s="145"/>
-      <c r="DD3" s="145"/>
-      <c r="DE3" s="145"/>
-      <c r="DF3" s="145"/>
-      <c r="DG3" s="145"/>
-      <c r="DH3" s="145"/>
-      <c r="DI3" s="145"/>
-      <c r="DJ3" s="145"/>
-      <c r="DK3" s="145"/>
-      <c r="DL3" s="145"/>
-      <c r="DM3" s="145"/>
-      <c r="DN3" s="145"/>
-      <c r="DO3" s="146"/>
+      <c r="CL3" s="166"/>
+      <c r="CM3" s="166"/>
+      <c r="CN3" s="166"/>
+      <c r="CO3" s="166"/>
+      <c r="CP3" s="166"/>
+      <c r="CQ3" s="166"/>
+      <c r="CR3" s="166"/>
+      <c r="CS3" s="166"/>
+      <c r="CT3" s="166"/>
+      <c r="CU3" s="166"/>
+      <c r="CV3" s="166"/>
+      <c r="CW3" s="166"/>
+      <c r="CX3" s="166"/>
+      <c r="CY3" s="166"/>
+      <c r="CZ3" s="166"/>
+      <c r="DA3" s="166"/>
+      <c r="DB3" s="166"/>
+      <c r="DC3" s="166"/>
+      <c r="DD3" s="166"/>
+      <c r="DE3" s="166"/>
+      <c r="DF3" s="166"/>
+      <c r="DG3" s="166"/>
+      <c r="DH3" s="166"/>
+      <c r="DI3" s="166"/>
+      <c r="DJ3" s="166"/>
+      <c r="DK3" s="166"/>
+      <c r="DL3" s="166"/>
+      <c r="DM3" s="166"/>
+      <c r="DN3" s="166"/>
+      <c r="DO3" s="167"/>
       <c r="DP3" s="1"/>
     </row>
     <row r="4" spans="1:120" ht="18" customHeight="1">
@@ -2458,124 +2458,124 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="J4" s="144">
+      <c r="J4" s="165">
         <v>10</v>
       </c>
-      <c r="K4" s="145"/>
-      <c r="L4" s="145"/>
-      <c r="M4" s="145"/>
-      <c r="N4" s="145"/>
-      <c r="O4" s="145"/>
-      <c r="P4" s="145"/>
-      <c r="Q4" s="145"/>
-      <c r="R4" s="145"/>
-      <c r="S4" s="145"/>
-      <c r="T4" s="145"/>
-      <c r="U4" s="145"/>
-      <c r="V4" s="145"/>
-      <c r="W4" s="145"/>
-      <c r="X4" s="145"/>
-      <c r="Y4" s="145"/>
-      <c r="Z4" s="145"/>
-      <c r="AA4" s="146"/>
-      <c r="AB4" s="144">
+      <c r="K4" s="166"/>
+      <c r="L4" s="166"/>
+      <c r="M4" s="166"/>
+      <c r="N4" s="166"/>
+      <c r="O4" s="166"/>
+      <c r="P4" s="166"/>
+      <c r="Q4" s="166"/>
+      <c r="R4" s="166"/>
+      <c r="S4" s="166"/>
+      <c r="T4" s="166"/>
+      <c r="U4" s="166"/>
+      <c r="V4" s="166"/>
+      <c r="W4" s="166"/>
+      <c r="X4" s="166"/>
+      <c r="Y4" s="166"/>
+      <c r="Z4" s="166"/>
+      <c r="AA4" s="167"/>
+      <c r="AB4" s="165">
         <v>11</v>
       </c>
-      <c r="AC4" s="145"/>
-      <c r="AD4" s="145"/>
-      <c r="AE4" s="145"/>
-      <c r="AF4" s="145"/>
-      <c r="AG4" s="145"/>
-      <c r="AH4" s="145"/>
-      <c r="AI4" s="145"/>
-      <c r="AJ4" s="145"/>
-      <c r="AK4" s="145"/>
-      <c r="AL4" s="145"/>
-      <c r="AM4" s="145"/>
-      <c r="AN4" s="145"/>
-      <c r="AO4" s="145"/>
-      <c r="AP4" s="145"/>
-      <c r="AQ4" s="145"/>
-      <c r="AR4" s="145"/>
-      <c r="AS4" s="145"/>
-      <c r="AT4" s="145"/>
-      <c r="AU4" s="145"/>
-      <c r="AV4" s="145"/>
-      <c r="AW4" s="145"/>
-      <c r="AX4" s="145"/>
-      <c r="AY4" s="145"/>
-      <c r="AZ4" s="145"/>
-      <c r="BA4" s="145"/>
-      <c r="BB4" s="145"/>
-      <c r="BC4" s="145"/>
-      <c r="BD4" s="145"/>
-      <c r="BE4" s="146"/>
-      <c r="BF4" s="144">
+      <c r="AC4" s="166"/>
+      <c r="AD4" s="166"/>
+      <c r="AE4" s="166"/>
+      <c r="AF4" s="166"/>
+      <c r="AG4" s="166"/>
+      <c r="AH4" s="166"/>
+      <c r="AI4" s="166"/>
+      <c r="AJ4" s="166"/>
+      <c r="AK4" s="166"/>
+      <c r="AL4" s="166"/>
+      <c r="AM4" s="166"/>
+      <c r="AN4" s="166"/>
+      <c r="AO4" s="166"/>
+      <c r="AP4" s="166"/>
+      <c r="AQ4" s="166"/>
+      <c r="AR4" s="166"/>
+      <c r="AS4" s="166"/>
+      <c r="AT4" s="166"/>
+      <c r="AU4" s="166"/>
+      <c r="AV4" s="166"/>
+      <c r="AW4" s="166"/>
+      <c r="AX4" s="166"/>
+      <c r="AY4" s="166"/>
+      <c r="AZ4" s="166"/>
+      <c r="BA4" s="166"/>
+      <c r="BB4" s="166"/>
+      <c r="BC4" s="166"/>
+      <c r="BD4" s="166"/>
+      <c r="BE4" s="167"/>
+      <c r="BF4" s="165">
         <v>12</v>
       </c>
-      <c r="BG4" s="145"/>
-      <c r="BH4" s="145"/>
-      <c r="BI4" s="145"/>
-      <c r="BJ4" s="145"/>
-      <c r="BK4" s="145"/>
-      <c r="BL4" s="145"/>
-      <c r="BM4" s="145"/>
-      <c r="BN4" s="145"/>
-      <c r="BO4" s="145"/>
-      <c r="BP4" s="145"/>
-      <c r="BQ4" s="145"/>
-      <c r="BR4" s="145"/>
-      <c r="BS4" s="145"/>
-      <c r="BT4" s="145"/>
-      <c r="BU4" s="145"/>
-      <c r="BV4" s="145"/>
-      <c r="BW4" s="145"/>
-      <c r="BX4" s="145"/>
-      <c r="BY4" s="145"/>
-      <c r="BZ4" s="145"/>
-      <c r="CA4" s="145"/>
-      <c r="CB4" s="145"/>
-      <c r="CC4" s="145"/>
-      <c r="CD4" s="145"/>
-      <c r="CE4" s="145"/>
-      <c r="CF4" s="145"/>
-      <c r="CG4" s="145"/>
-      <c r="CH4" s="145"/>
-      <c r="CI4" s="145"/>
-      <c r="CJ4" s="146"/>
-      <c r="CK4" s="144">
+      <c r="BG4" s="166"/>
+      <c r="BH4" s="166"/>
+      <c r="BI4" s="166"/>
+      <c r="BJ4" s="166"/>
+      <c r="BK4" s="166"/>
+      <c r="BL4" s="166"/>
+      <c r="BM4" s="166"/>
+      <c r="BN4" s="166"/>
+      <c r="BO4" s="166"/>
+      <c r="BP4" s="166"/>
+      <c r="BQ4" s="166"/>
+      <c r="BR4" s="166"/>
+      <c r="BS4" s="166"/>
+      <c r="BT4" s="166"/>
+      <c r="BU4" s="166"/>
+      <c r="BV4" s="166"/>
+      <c r="BW4" s="166"/>
+      <c r="BX4" s="166"/>
+      <c r="BY4" s="166"/>
+      <c r="BZ4" s="166"/>
+      <c r="CA4" s="166"/>
+      <c r="CB4" s="166"/>
+      <c r="CC4" s="166"/>
+      <c r="CD4" s="166"/>
+      <c r="CE4" s="166"/>
+      <c r="CF4" s="166"/>
+      <c r="CG4" s="166"/>
+      <c r="CH4" s="166"/>
+      <c r="CI4" s="166"/>
+      <c r="CJ4" s="167"/>
+      <c r="CK4" s="165">
         <v>1</v>
       </c>
-      <c r="CL4" s="145"/>
-      <c r="CM4" s="145"/>
-      <c r="CN4" s="145"/>
-      <c r="CO4" s="145"/>
-      <c r="CP4" s="145"/>
-      <c r="CQ4" s="145"/>
-      <c r="CR4" s="145"/>
-      <c r="CS4" s="145"/>
-      <c r="CT4" s="145"/>
-      <c r="CU4" s="145"/>
-      <c r="CV4" s="145"/>
-      <c r="CW4" s="145"/>
-      <c r="CX4" s="145"/>
-      <c r="CY4" s="145"/>
-      <c r="CZ4" s="145"/>
-      <c r="DA4" s="145"/>
-      <c r="DB4" s="145"/>
-      <c r="DC4" s="145"/>
-      <c r="DD4" s="145"/>
-      <c r="DE4" s="145"/>
-      <c r="DF4" s="145"/>
-      <c r="DG4" s="145"/>
-      <c r="DH4" s="145"/>
-      <c r="DI4" s="145"/>
-      <c r="DJ4" s="145"/>
-      <c r="DK4" s="145"/>
-      <c r="DL4" s="145"/>
-      <c r="DM4" s="145"/>
-      <c r="DN4" s="145"/>
-      <c r="DO4" s="146"/>
+      <c r="CL4" s="166"/>
+      <c r="CM4" s="166"/>
+      <c r="CN4" s="166"/>
+      <c r="CO4" s="166"/>
+      <c r="CP4" s="166"/>
+      <c r="CQ4" s="166"/>
+      <c r="CR4" s="166"/>
+      <c r="CS4" s="166"/>
+      <c r="CT4" s="166"/>
+      <c r="CU4" s="166"/>
+      <c r="CV4" s="166"/>
+      <c r="CW4" s="166"/>
+      <c r="CX4" s="166"/>
+      <c r="CY4" s="166"/>
+      <c r="CZ4" s="166"/>
+      <c r="DA4" s="166"/>
+      <c r="DB4" s="166"/>
+      <c r="DC4" s="166"/>
+      <c r="DD4" s="166"/>
+      <c r="DE4" s="166"/>
+      <c r="DF4" s="166"/>
+      <c r="DG4" s="166"/>
+      <c r="DH4" s="166"/>
+      <c r="DI4" s="166"/>
+      <c r="DJ4" s="166"/>
+      <c r="DK4" s="166"/>
+      <c r="DL4" s="166"/>
+      <c r="DM4" s="166"/>
+      <c r="DN4" s="166"/>
+      <c r="DO4" s="167"/>
       <c r="DP4" s="6"/>
     </row>
     <row r="5" spans="1:120" ht="18" customHeight="1">
@@ -3370,18 +3370,18 @@
     </row>
     <row r="7" spans="1:120" ht="9.75" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="147" t="s">
+      <c r="B7" s="168" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="135"/>
-      <c r="H7" s="149" t="s">
+      <c r="C7" s="156"/>
+      <c r="D7" s="156"/>
+      <c r="E7" s="156"/>
+      <c r="F7" s="156"/>
+      <c r="G7" s="169"/>
+      <c r="H7" s="134" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="149" t="s">
+      <c r="I7" s="134" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="38"/>
@@ -3498,14 +3498,14 @@
     </row>
     <row r="8" spans="1:120" ht="9.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="125"/>
-      <c r="C8" s="126"/>
-      <c r="D8" s="126"/>
-      <c r="E8" s="126"/>
-      <c r="F8" s="126"/>
-      <c r="G8" s="130"/>
-      <c r="H8" s="149"/>
-      <c r="I8" s="149"/>
+      <c r="B8" s="158"/>
+      <c r="C8" s="159"/>
+      <c r="D8" s="159"/>
+      <c r="E8" s="159"/>
+      <c r="F8" s="159"/>
+      <c r="G8" s="160"/>
+      <c r="H8" s="134"/>
+      <c r="I8" s="134"/>
       <c r="J8" s="39"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
@@ -3621,15 +3621,15 @@
     <row r="9" spans="1:120" ht="9.75" customHeight="1">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
-      <c r="C9" s="148" t="s">
+      <c r="C9" s="170" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="137"/>
-      <c r="E9" s="137"/>
-      <c r="F9" s="137"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="150"/>
-      <c r="I9" s="150"/>
+      <c r="D9" s="150"/>
+      <c r="E9" s="150"/>
+      <c r="F9" s="150"/>
+      <c r="G9" s="154"/>
+      <c r="H9" s="131"/>
+      <c r="I9" s="131"/>
       <c r="J9" s="42"/>
       <c r="K9" s="42"/>
       <c r="L9" s="44"/>
@@ -3745,13 +3745,13 @@
     <row r="10" spans="1:120" ht="9.75" customHeight="1">
       <c r="A10" s="16"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="132"/>
-      <c r="D10" s="126"/>
-      <c r="E10" s="126"/>
-      <c r="F10" s="126"/>
-      <c r="G10" s="130"/>
-      <c r="H10" s="150"/>
-      <c r="I10" s="150"/>
+      <c r="C10" s="171"/>
+      <c r="D10" s="159"/>
+      <c r="E10" s="159"/>
+      <c r="F10" s="159"/>
+      <c r="G10" s="160"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="131"/>
       <c r="J10" s="46"/>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
@@ -3867,15 +3867,15 @@
     <row r="11" spans="1:120" ht="9.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="136" t="s">
+      <c r="C11" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="137"/>
-      <c r="E11" s="137"/>
-      <c r="F11" s="137"/>
-      <c r="G11" s="133"/>
-      <c r="H11" s="150"/>
-      <c r="I11" s="150"/>
+      <c r="D11" s="150"/>
+      <c r="E11" s="150"/>
+      <c r="F11" s="150"/>
+      <c r="G11" s="154"/>
+      <c r="H11" s="131"/>
+      <c r="I11" s="131"/>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
       <c r="L11" s="44"/>
@@ -3991,13 +3991,13 @@
     <row r="12" spans="1:120" ht="9.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="132"/>
-      <c r="D12" s="126"/>
-      <c r="E12" s="126"/>
-      <c r="F12" s="126"/>
-      <c r="G12" s="130"/>
-      <c r="H12" s="150"/>
-      <c r="I12" s="150"/>
+      <c r="C12" s="171"/>
+      <c r="D12" s="159"/>
+      <c r="E12" s="159"/>
+      <c r="F12" s="159"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="131"/>
       <c r="J12" s="46"/>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
@@ -4114,13 +4114,13 @@
       <c r="A13" s="1"/>
       <c r="B13" s="18"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="134" t="s">
+      <c r="D13" s="173" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="123"/>
-      <c r="F13" s="123"/>
-      <c r="G13" s="135"/>
-      <c r="H13" s="166" t="s">
+      <c r="E13" s="156"/>
+      <c r="F13" s="156"/>
+      <c r="G13" s="169"/>
+      <c r="H13" s="130" t="s">
         <v>40</v>
       </c>
       <c r="I13" s="104">
@@ -4242,10 +4242,10 @@
       <c r="A14" s="1"/>
       <c r="B14" s="18"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="125"/>
-      <c r="E14" s="126"/>
-      <c r="F14" s="126"/>
-      <c r="G14" s="130"/>
+      <c r="D14" s="158"/>
+      <c r="E14" s="159"/>
+      <c r="F14" s="159"/>
+      <c r="G14" s="160"/>
       <c r="H14" s="104"/>
       <c r="I14" s="104"/>
       <c r="J14" s="39"/>
@@ -4364,13 +4364,13 @@
       <c r="A15" s="1"/>
       <c r="B15" s="18"/>
       <c r="C15" s="24"/>
-      <c r="D15" s="134" t="s">
+      <c r="D15" s="173" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="123"/>
-      <c r="F15" s="123"/>
-      <c r="G15" s="124"/>
-      <c r="H15" s="166" t="s">
+      <c r="E15" s="156"/>
+      <c r="F15" s="156"/>
+      <c r="G15" s="162"/>
+      <c r="H15" s="130" t="s">
         <v>40</v>
       </c>
       <c r="I15" s="104">
@@ -4492,10 +4492,10 @@
       <c r="A16" s="1"/>
       <c r="B16" s="18"/>
       <c r="C16" s="24"/>
-      <c r="D16" s="125"/>
-      <c r="E16" s="126"/>
-      <c r="F16" s="126"/>
-      <c r="G16" s="127"/>
+      <c r="D16" s="158"/>
+      <c r="E16" s="159"/>
+      <c r="F16" s="159"/>
+      <c r="G16" s="163"/>
       <c r="H16" s="104"/>
       <c r="I16" s="104"/>
       <c r="J16" s="14"/>
@@ -4614,13 +4614,13 @@
       <c r="A17" s="1"/>
       <c r="B17" s="18"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="134" t="s">
+      <c r="D17" s="173" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="123"/>
-      <c r="F17" s="123"/>
-      <c r="G17" s="124"/>
-      <c r="H17" s="166" t="s">
+      <c r="E17" s="156"/>
+      <c r="F17" s="156"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="130" t="s">
         <v>40</v>
       </c>
       <c r="I17" s="104">
@@ -4742,10 +4742,10 @@
       <c r="A18" s="1"/>
       <c r="B18" s="18"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="126"/>
-      <c r="F18" s="126"/>
-      <c r="G18" s="127"/>
+      <c r="D18" s="158"/>
+      <c r="E18" s="159"/>
+      <c r="F18" s="159"/>
+      <c r="G18" s="163"/>
       <c r="H18" s="104"/>
       <c r="I18" s="104"/>
       <c r="J18" s="14"/>
@@ -4864,13 +4864,13 @@
       <c r="A19" s="1"/>
       <c r="B19" s="18"/>
       <c r="C19" s="24"/>
-      <c r="D19" s="134" t="s">
+      <c r="D19" s="173" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="123"/>
-      <c r="F19" s="123"/>
-      <c r="G19" s="124"/>
-      <c r="H19" s="166" t="s">
+      <c r="E19" s="156"/>
+      <c r="F19" s="156"/>
+      <c r="G19" s="162"/>
+      <c r="H19" s="130" t="s">
         <v>40</v>
       </c>
       <c r="I19" s="104">
@@ -4992,10 +4992,10 @@
       <c r="A20" s="1"/>
       <c r="B20" s="18"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="125"/>
-      <c r="E20" s="126"/>
-      <c r="F20" s="126"/>
-      <c r="G20" s="127"/>
+      <c r="D20" s="158"/>
+      <c r="E20" s="159"/>
+      <c r="F20" s="159"/>
+      <c r="G20" s="163"/>
       <c r="H20" s="104"/>
       <c r="I20" s="104"/>
       <c r="J20" s="26"/>
@@ -5113,15 +5113,15 @@
     <row r="21" spans="1:120" ht="9.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="18"/>
-      <c r="C21" s="136" t="s">
+      <c r="C21" s="172" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="137"/>
-      <c r="E21" s="137"/>
-      <c r="F21" s="137"/>
-      <c r="G21" s="138"/>
-      <c r="H21" s="150"/>
-      <c r="I21" s="150"/>
+      <c r="D21" s="150"/>
+      <c r="E21" s="150"/>
+      <c r="F21" s="150"/>
+      <c r="G21" s="151"/>
+      <c r="H21" s="131"/>
+      <c r="I21" s="131"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="44"/>
@@ -5237,13 +5237,13 @@
     <row r="22" spans="1:120" ht="9.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="18"/>
-      <c r="C22" s="139"/>
-      <c r="D22" s="140"/>
-      <c r="E22" s="140"/>
-      <c r="F22" s="140"/>
-      <c r="G22" s="133"/>
-      <c r="H22" s="150"/>
-      <c r="I22" s="150"/>
+      <c r="C22" s="152"/>
+      <c r="D22" s="153"/>
+      <c r="E22" s="153"/>
+      <c r="F22" s="153"/>
+      <c r="G22" s="154"/>
+      <c r="H22" s="131"/>
+      <c r="I22" s="131"/>
       <c r="J22" s="46"/>
       <c r="K22" s="47"/>
       <c r="L22" s="47"/>
@@ -5360,13 +5360,13 @@
       <c r="A23" s="1"/>
       <c r="B23" s="28"/>
       <c r="C23" s="29"/>
-      <c r="D23" s="141" t="s">
+      <c r="D23" s="174" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="123"/>
-      <c r="F23" s="123"/>
-      <c r="G23" s="124"/>
-      <c r="H23" s="166" t="s">
+      <c r="E23" s="156"/>
+      <c r="F23" s="156"/>
+      <c r="G23" s="162"/>
+      <c r="H23" s="130" t="s">
         <v>46</v>
       </c>
       <c r="I23" s="104">
@@ -5488,10 +5488,10 @@
       <c r="A24" s="1"/>
       <c r="B24" s="18"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="125"/>
-      <c r="E24" s="126"/>
-      <c r="F24" s="126"/>
-      <c r="G24" s="127"/>
+      <c r="D24" s="158"/>
+      <c r="E24" s="159"/>
+      <c r="F24" s="159"/>
+      <c r="G24" s="163"/>
       <c r="H24" s="104"/>
       <c r="I24" s="104"/>
       <c r="J24" s="14"/>
@@ -5609,15 +5609,15 @@
     <row r="25" spans="1:120" ht="9.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="18"/>
-      <c r="C25" s="136" t="s">
+      <c r="C25" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="137"/>
-      <c r="E25" s="137"/>
-      <c r="F25" s="137"/>
-      <c r="G25" s="138"/>
-      <c r="H25" s="150"/>
-      <c r="I25" s="150"/>
+      <c r="D25" s="150"/>
+      <c r="E25" s="150"/>
+      <c r="F25" s="150"/>
+      <c r="G25" s="151"/>
+      <c r="H25" s="131"/>
+      <c r="I25" s="131"/>
       <c r="J25" s="42"/>
       <c r="K25" s="42"/>
       <c r="L25" s="44"/>
@@ -5733,13 +5733,13 @@
     <row r="26" spans="1:120" ht="9.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="18"/>
-      <c r="C26" s="132"/>
-      <c r="D26" s="126"/>
-      <c r="E26" s="126"/>
-      <c r="F26" s="126"/>
-      <c r="G26" s="130"/>
-      <c r="H26" s="150"/>
-      <c r="I26" s="150"/>
+      <c r="C26" s="171"/>
+      <c r="D26" s="159"/>
+      <c r="E26" s="159"/>
+      <c r="F26" s="159"/>
+      <c r="G26" s="160"/>
+      <c r="H26" s="131"/>
+      <c r="I26" s="131"/>
       <c r="J26" s="46"/>
       <c r="K26" s="47"/>
       <c r="L26" s="47"/>
@@ -5856,13 +5856,13 @@
       <c r="A27" s="1"/>
       <c r="B27" s="28"/>
       <c r="C27" s="29"/>
-      <c r="D27" s="141" t="s">
+      <c r="D27" s="174" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="123"/>
-      <c r="F27" s="123"/>
-      <c r="G27" s="124"/>
-      <c r="H27" s="166" t="s">
+      <c r="E27" s="156"/>
+      <c r="F27" s="156"/>
+      <c r="G27" s="162"/>
+      <c r="H27" s="130" t="s">
         <v>44</v>
       </c>
       <c r="I27" s="104">
@@ -5984,10 +5984,10 @@
       <c r="A28" s="1"/>
       <c r="B28" s="28"/>
       <c r="C28" s="30"/>
-      <c r="D28" s="125"/>
-      <c r="E28" s="126"/>
-      <c r="F28" s="126"/>
-      <c r="G28" s="127"/>
+      <c r="D28" s="158"/>
+      <c r="E28" s="159"/>
+      <c r="F28" s="159"/>
+      <c r="G28" s="163"/>
       <c r="H28" s="104"/>
       <c r="I28" s="104"/>
       <c r="J28" s="14"/>
@@ -6106,13 +6106,13 @@
       <c r="A29" s="1"/>
       <c r="B29" s="28"/>
       <c r="C29" s="30"/>
-      <c r="D29" s="142" t="s">
+      <c r="D29" s="175" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="143"/>
-      <c r="F29" s="143"/>
-      <c r="G29" s="143"/>
-      <c r="H29" s="166" t="s">
+      <c r="E29" s="176"/>
+      <c r="F29" s="176"/>
+      <c r="G29" s="176"/>
+      <c r="H29" s="130" t="s">
         <v>44</v>
       </c>
       <c r="I29" s="104">
@@ -6234,10 +6234,10 @@
       <c r="A30" s="1"/>
       <c r="B30" s="28"/>
       <c r="C30" s="31"/>
-      <c r="D30" s="125"/>
-      <c r="E30" s="126"/>
-      <c r="F30" s="126"/>
-      <c r="G30" s="126"/>
+      <c r="D30" s="158"/>
+      <c r="E30" s="159"/>
+      <c r="F30" s="159"/>
+      <c r="G30" s="159"/>
       <c r="H30" s="104"/>
       <c r="I30" s="104"/>
       <c r="J30" s="26"/>
@@ -6355,15 +6355,15 @@
     <row r="31" spans="1:120" ht="9.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="18"/>
-      <c r="C31" s="162" t="s">
+      <c r="C31" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="137"/>
-      <c r="E31" s="137"/>
-      <c r="F31" s="137"/>
-      <c r="G31" s="138"/>
-      <c r="H31" s="150"/>
-      <c r="I31" s="150"/>
+      <c r="D31" s="150"/>
+      <c r="E31" s="150"/>
+      <c r="F31" s="150"/>
+      <c r="G31" s="151"/>
+      <c r="H31" s="131"/>
+      <c r="I31" s="131"/>
       <c r="J31" s="42"/>
       <c r="K31" s="43"/>
       <c r="L31" s="44"/>
@@ -6479,13 +6479,13 @@
     <row r="32" spans="1:120" ht="9.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="18"/>
-      <c r="C32" s="139"/>
-      <c r="D32" s="140"/>
-      <c r="E32" s="140"/>
-      <c r="F32" s="140"/>
-      <c r="G32" s="133"/>
-      <c r="H32" s="150"/>
-      <c r="I32" s="150"/>
+      <c r="C32" s="152"/>
+      <c r="D32" s="153"/>
+      <c r="E32" s="153"/>
+      <c r="F32" s="153"/>
+      <c r="G32" s="154"/>
+      <c r="H32" s="131"/>
+      <c r="I32" s="131"/>
       <c r="J32" s="46"/>
       <c r="K32" s="47"/>
       <c r="L32" s="47"/>
@@ -6602,14 +6602,14 @@
       <c r="A33" s="1"/>
       <c r="B33" s="18"/>
       <c r="C33" s="32"/>
-      <c r="D33" s="128" t="s">
+      <c r="D33" s="155" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="123"/>
-      <c r="F33" s="123"/>
-      <c r="G33" s="129"/>
-      <c r="H33" s="150"/>
-      <c r="I33" s="150"/>
+      <c r="E33" s="156"/>
+      <c r="F33" s="156"/>
+      <c r="G33" s="157"/>
+      <c r="H33" s="131"/>
+      <c r="I33" s="131"/>
       <c r="J33" s="50"/>
       <c r="K33" s="51"/>
       <c r="L33" s="51"/>
@@ -6726,12 +6726,12 @@
       <c r="A34" s="1"/>
       <c r="B34" s="18"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="125"/>
-      <c r="E34" s="126"/>
-      <c r="F34" s="126"/>
-      <c r="G34" s="130"/>
-      <c r="H34" s="150"/>
-      <c r="I34" s="150"/>
+      <c r="D34" s="158"/>
+      <c r="E34" s="159"/>
+      <c r="F34" s="159"/>
+      <c r="G34" s="160"/>
+      <c r="H34" s="131"/>
+      <c r="I34" s="131"/>
       <c r="J34" s="52"/>
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
@@ -6849,12 +6849,12 @@
       <c r="B35" s="18"/>
       <c r="C35" s="1"/>
       <c r="D35" s="33"/>
-      <c r="E35" s="122" t="s">
+      <c r="E35" s="161" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="123"/>
-      <c r="G35" s="124"/>
-      <c r="H35" s="166" t="s">
+      <c r="F35" s="156"/>
+      <c r="G35" s="162"/>
+      <c r="H35" s="130" t="s">
         <v>45</v>
       </c>
       <c r="I35" s="104">
@@ -6977,9 +6977,9 @@
       <c r="B36" s="18"/>
       <c r="C36" s="1"/>
       <c r="D36" s="34"/>
-      <c r="E36" s="125"/>
-      <c r="F36" s="126"/>
-      <c r="G36" s="127"/>
+      <c r="E36" s="158"/>
+      <c r="F36" s="159"/>
+      <c r="G36" s="163"/>
       <c r="H36" s="104"/>
       <c r="I36" s="104"/>
       <c r="J36" s="14"/>
@@ -7099,12 +7099,12 @@
       <c r="B37" s="18"/>
       <c r="C37" s="1"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="122" t="s">
+      <c r="E37" s="161" t="s">
         <v>21</v>
       </c>
-      <c r="F37" s="123"/>
-      <c r="G37" s="124"/>
-      <c r="H37" s="166" t="s">
+      <c r="F37" s="156"/>
+      <c r="G37" s="162"/>
+      <c r="H37" s="130" t="s">
         <v>44</v>
       </c>
       <c r="I37" s="104">
@@ -7227,9 +7227,9 @@
       <c r="B38" s="18"/>
       <c r="C38" s="1"/>
       <c r="D38" s="35"/>
-      <c r="E38" s="125"/>
-      <c r="F38" s="126"/>
-      <c r="G38" s="127"/>
+      <c r="E38" s="158"/>
+      <c r="F38" s="159"/>
+      <c r="G38" s="163"/>
       <c r="H38" s="104"/>
       <c r="I38" s="104"/>
       <c r="J38" s="26"/>
@@ -7348,14 +7348,14 @@
       <c r="A39" s="1"/>
       <c r="B39" s="18"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="163" t="s">
+      <c r="D39" s="164" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="137"/>
-      <c r="F39" s="137"/>
-      <c r="G39" s="138"/>
-      <c r="H39" s="150"/>
-      <c r="I39" s="150"/>
+      <c r="E39" s="150"/>
+      <c r="F39" s="150"/>
+      <c r="G39" s="151"/>
+      <c r="H39" s="131"/>
+      <c r="I39" s="131"/>
       <c r="J39" s="50"/>
       <c r="K39" s="51"/>
       <c r="L39" s="51"/>
@@ -7472,12 +7472,12 @@
       <c r="A40" s="1"/>
       <c r="B40" s="18"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="125"/>
-      <c r="E40" s="126"/>
-      <c r="F40" s="126"/>
-      <c r="G40" s="130"/>
-      <c r="H40" s="150"/>
-      <c r="I40" s="150"/>
+      <c r="D40" s="158"/>
+      <c r="E40" s="159"/>
+      <c r="F40" s="159"/>
+      <c r="G40" s="160"/>
+      <c r="H40" s="131"/>
+      <c r="I40" s="131"/>
       <c r="J40" s="52"/>
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
@@ -7595,12 +7595,12 @@
       <c r="B41" s="18"/>
       <c r="C41" s="1"/>
       <c r="D41" s="33"/>
-      <c r="E41" s="122" t="s">
+      <c r="E41" s="161" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="123"/>
-      <c r="G41" s="124"/>
-      <c r="H41" s="166" t="s">
+      <c r="F41" s="156"/>
+      <c r="G41" s="162"/>
+      <c r="H41" s="130" t="s">
         <v>43</v>
       </c>
       <c r="I41" s="104">
@@ -7723,9 +7723,9 @@
       <c r="B42" s="18"/>
       <c r="C42" s="1"/>
       <c r="D42" s="34"/>
-      <c r="E42" s="125"/>
-      <c r="F42" s="126"/>
-      <c r="G42" s="127"/>
+      <c r="E42" s="158"/>
+      <c r="F42" s="159"/>
+      <c r="G42" s="163"/>
       <c r="H42" s="104"/>
       <c r="I42" s="104"/>
       <c r="J42" s="14"/>
@@ -7845,12 +7845,12 @@
       <c r="B43" s="18"/>
       <c r="C43" s="1"/>
       <c r="D43" s="34"/>
-      <c r="E43" s="122" t="s">
+      <c r="E43" s="161" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="123"/>
-      <c r="G43" s="124"/>
-      <c r="H43" s="166" t="s">
+      <c r="F43" s="156"/>
+      <c r="G43" s="162"/>
+      <c r="H43" s="130" t="s">
         <v>43</v>
       </c>
       <c r="I43" s="104">
@@ -7973,9 +7973,9 @@
       <c r="B44" s="18"/>
       <c r="C44" s="1"/>
       <c r="D44" s="34"/>
-      <c r="E44" s="125"/>
-      <c r="F44" s="126"/>
-      <c r="G44" s="127"/>
+      <c r="E44" s="158"/>
+      <c r="F44" s="159"/>
+      <c r="G44" s="163"/>
       <c r="H44" s="104"/>
       <c r="I44" s="104"/>
       <c r="J44" s="14"/>
@@ -8095,12 +8095,12 @@
       <c r="B45" s="18"/>
       <c r="C45" s="1"/>
       <c r="D45" s="34"/>
-      <c r="E45" s="122" t="s">
+      <c r="E45" s="161" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="123"/>
-      <c r="G45" s="124"/>
-      <c r="H45" s="166" t="s">
+      <c r="F45" s="156"/>
+      <c r="G45" s="162"/>
+      <c r="H45" s="130" t="s">
         <v>42</v>
       </c>
       <c r="I45" s="104">
@@ -8223,9 +8223,9 @@
       <c r="B46" s="18"/>
       <c r="C46" s="1"/>
       <c r="D46" s="34"/>
-      <c r="E46" s="125"/>
-      <c r="F46" s="126"/>
-      <c r="G46" s="127"/>
+      <c r="E46" s="158"/>
+      <c r="F46" s="159"/>
+      <c r="G46" s="163"/>
       <c r="H46" s="104"/>
       <c r="I46" s="104"/>
       <c r="J46" s="14"/>
@@ -8345,12 +8345,12 @@
       <c r="B47" s="18"/>
       <c r="C47" s="1"/>
       <c r="D47" s="34"/>
-      <c r="E47" s="122" t="s">
+      <c r="E47" s="161" t="s">
         <v>25</v>
       </c>
-      <c r="F47" s="123"/>
-      <c r="G47" s="124"/>
-      <c r="H47" s="166" t="s">
+      <c r="F47" s="156"/>
+      <c r="G47" s="162"/>
+      <c r="H47" s="130" t="s">
         <v>41</v>
       </c>
       <c r="I47" s="104">
@@ -8473,9 +8473,9 @@
       <c r="B48" s="18"/>
       <c r="C48" s="1"/>
       <c r="D48" s="34"/>
-      <c r="E48" s="125"/>
-      <c r="F48" s="126"/>
-      <c r="G48" s="127"/>
+      <c r="E48" s="158"/>
+      <c r="F48" s="159"/>
+      <c r="G48" s="163"/>
       <c r="H48" s="104"/>
       <c r="I48" s="104"/>
       <c r="J48" s="14"/>
@@ -8595,12 +8595,12 @@
       <c r="B49" s="18"/>
       <c r="C49" s="1"/>
       <c r="D49" s="34"/>
-      <c r="E49" s="122" t="s">
+      <c r="E49" s="161" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="123"/>
-      <c r="G49" s="124"/>
-      <c r="H49" s="166" t="s">
+      <c r="F49" s="156"/>
+      <c r="G49" s="162"/>
+      <c r="H49" s="130" t="s">
         <v>50</v>
       </c>
       <c r="I49" s="104">
@@ -8723,9 +8723,9 @@
       <c r="B50" s="18"/>
       <c r="C50" s="1"/>
       <c r="D50" s="34"/>
-      <c r="E50" s="125"/>
-      <c r="F50" s="126"/>
-      <c r="G50" s="127"/>
+      <c r="E50" s="158"/>
+      <c r="F50" s="159"/>
+      <c r="G50" s="163"/>
       <c r="H50" s="104"/>
       <c r="I50" s="104"/>
       <c r="J50" s="14"/>
@@ -8845,12 +8845,12 @@
       <c r="B51" s="18"/>
       <c r="C51" s="1"/>
       <c r="D51" s="34"/>
-      <c r="E51" s="122" t="s">
+      <c r="E51" s="161" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="123"/>
-      <c r="G51" s="124"/>
-      <c r="H51" s="166" t="s">
+      <c r="F51" s="156"/>
+      <c r="G51" s="162"/>
+      <c r="H51" s="130" t="s">
         <v>47</v>
       </c>
       <c r="I51" s="104">
@@ -8973,9 +8973,9 @@
       <c r="B52" s="18"/>
       <c r="C52" s="1"/>
       <c r="D52" s="34"/>
-      <c r="E52" s="125"/>
-      <c r="F52" s="126"/>
-      <c r="G52" s="127"/>
+      <c r="E52" s="158"/>
+      <c r="F52" s="159"/>
+      <c r="G52" s="163"/>
       <c r="H52" s="104"/>
       <c r="I52" s="104"/>
       <c r="J52" s="26"/>
@@ -9094,14 +9094,14 @@
       <c r="A53" s="1"/>
       <c r="B53" s="18"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="128" t="s">
+      <c r="D53" s="155" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="123"/>
-      <c r="F53" s="123"/>
-      <c r="G53" s="129"/>
-      <c r="H53" s="150"/>
-      <c r="I53" s="150"/>
+      <c r="E53" s="156"/>
+      <c r="F53" s="156"/>
+      <c r="G53" s="157"/>
+      <c r="H53" s="131"/>
+      <c r="I53" s="131"/>
       <c r="J53" s="50"/>
       <c r="K53" s="51"/>
       <c r="L53" s="51"/>
@@ -9218,12 +9218,12 @@
       <c r="A54" s="1"/>
       <c r="B54" s="18"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="125"/>
-      <c r="E54" s="126"/>
-      <c r="F54" s="126"/>
-      <c r="G54" s="130"/>
-      <c r="H54" s="150"/>
-      <c r="I54" s="150"/>
+      <c r="D54" s="158"/>
+      <c r="E54" s="159"/>
+      <c r="F54" s="159"/>
+      <c r="G54" s="160"/>
+      <c r="H54" s="131"/>
+      <c r="I54" s="131"/>
       <c r="J54" s="52"/>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -9341,12 +9341,12 @@
       <c r="B55" s="18"/>
       <c r="C55" s="1"/>
       <c r="D55" s="34"/>
-      <c r="E55" s="122" t="s">
+      <c r="E55" s="161" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="123"/>
-      <c r="G55" s="124"/>
-      <c r="H55" s="166" t="s">
+      <c r="F55" s="156"/>
+      <c r="G55" s="162"/>
+      <c r="H55" s="130" t="s">
         <v>48</v>
       </c>
       <c r="I55" s="104">
@@ -9469,9 +9469,9 @@
       <c r="B56" s="18"/>
       <c r="C56" s="1"/>
       <c r="D56" s="34"/>
-      <c r="E56" s="125"/>
-      <c r="F56" s="126"/>
-      <c r="G56" s="127"/>
+      <c r="E56" s="158"/>
+      <c r="F56" s="159"/>
+      <c r="G56" s="163"/>
       <c r="H56" s="104"/>
       <c r="I56" s="104"/>
       <c r="J56" s="14"/>
@@ -9591,12 +9591,12 @@
       <c r="B57" s="18"/>
       <c r="C57" s="1"/>
       <c r="D57" s="34"/>
-      <c r="E57" s="122" t="s">
+      <c r="E57" s="161" t="s">
         <v>29</v>
       </c>
-      <c r="F57" s="123"/>
-      <c r="G57" s="124"/>
-      <c r="H57" s="166" t="s">
+      <c r="F57" s="156"/>
+      <c r="G57" s="162"/>
+      <c r="H57" s="130" t="s">
         <v>51</v>
       </c>
       <c r="I57" s="104">
@@ -9719,9 +9719,9 @@
       <c r="B58" s="18"/>
       <c r="C58" s="1"/>
       <c r="D58" s="34"/>
-      <c r="E58" s="125"/>
-      <c r="F58" s="126"/>
-      <c r="G58" s="127"/>
+      <c r="E58" s="158"/>
+      <c r="F58" s="159"/>
+      <c r="G58" s="163"/>
       <c r="H58" s="104"/>
       <c r="I58" s="104"/>
       <c r="J58" s="14"/>
@@ -9841,12 +9841,12 @@
       <c r="B59" s="18"/>
       <c r="C59" s="1"/>
       <c r="D59" s="34"/>
-      <c r="E59" s="122" t="s">
+      <c r="E59" s="161" t="s">
         <v>26</v>
       </c>
-      <c r="F59" s="123"/>
-      <c r="G59" s="124"/>
-      <c r="H59" s="166" t="s">
+      <c r="F59" s="156"/>
+      <c r="G59" s="162"/>
+      <c r="H59" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I59" s="104">
@@ -9969,9 +9969,9 @@
       <c r="B60" s="18"/>
       <c r="C60" s="1"/>
       <c r="D60" s="34"/>
-      <c r="E60" s="125"/>
-      <c r="F60" s="126"/>
-      <c r="G60" s="127"/>
+      <c r="E60" s="158"/>
+      <c r="F60" s="159"/>
+      <c r="G60" s="163"/>
       <c r="H60" s="104"/>
       <c r="I60" s="104"/>
       <c r="J60" s="14"/>
@@ -10091,12 +10091,12 @@
       <c r="B61" s="18"/>
       <c r="C61" s="1"/>
       <c r="D61" s="34"/>
-      <c r="E61" s="122" t="s">
+      <c r="E61" s="161" t="s">
         <v>21</v>
       </c>
-      <c r="F61" s="123"/>
-      <c r="G61" s="124"/>
-      <c r="H61" s="166" t="s">
+      <c r="F61" s="156"/>
+      <c r="G61" s="162"/>
+      <c r="H61" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I61" s="104">
@@ -10219,9 +10219,9 @@
       <c r="B62" s="18"/>
       <c r="C62" s="1"/>
       <c r="D62" s="34"/>
-      <c r="E62" s="125"/>
-      <c r="F62" s="126"/>
-      <c r="G62" s="127"/>
+      <c r="E62" s="158"/>
+      <c r="F62" s="159"/>
+      <c r="G62" s="163"/>
       <c r="H62" s="104"/>
       <c r="I62" s="104"/>
       <c r="J62" s="26"/>
@@ -10340,14 +10340,14 @@
       <c r="A63" s="1"/>
       <c r="B63" s="18"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="128" t="s">
+      <c r="D63" s="155" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="123"/>
-      <c r="F63" s="123"/>
-      <c r="G63" s="129"/>
-      <c r="H63" s="150"/>
-      <c r="I63" s="150"/>
+      <c r="E63" s="156"/>
+      <c r="F63" s="156"/>
+      <c r="G63" s="157"/>
+      <c r="H63" s="131"/>
+      <c r="I63" s="131"/>
       <c r="J63" s="50"/>
       <c r="K63" s="51"/>
       <c r="L63" s="51"/>
@@ -10464,12 +10464,12 @@
       <c r="A64" s="1"/>
       <c r="B64" s="18"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="125"/>
-      <c r="E64" s="126"/>
-      <c r="F64" s="126"/>
-      <c r="G64" s="130"/>
-      <c r="H64" s="150"/>
-      <c r="I64" s="150"/>
+      <c r="D64" s="158"/>
+      <c r="E64" s="159"/>
+      <c r="F64" s="159"/>
+      <c r="G64" s="160"/>
+      <c r="H64" s="131"/>
+      <c r="I64" s="131"/>
       <c r="J64" s="52"/>
       <c r="K64" s="49"/>
       <c r="L64" s="49"/>
@@ -10587,12 +10587,12 @@
       <c r="B65" s="18"/>
       <c r="C65" s="1"/>
       <c r="D65" s="34"/>
-      <c r="E65" s="122" t="s">
+      <c r="E65" s="161" t="s">
         <v>35</v>
       </c>
-      <c r="F65" s="123"/>
-      <c r="G65" s="124"/>
-      <c r="H65" s="166" t="s">
+      <c r="F65" s="156"/>
+      <c r="G65" s="162"/>
+      <c r="H65" s="130" t="s">
         <v>52</v>
       </c>
       <c r="I65" s="104">
@@ -10715,9 +10715,9 @@
       <c r="B66" s="18"/>
       <c r="C66" s="1"/>
       <c r="D66" s="34"/>
-      <c r="E66" s="125"/>
-      <c r="F66" s="126"/>
-      <c r="G66" s="127"/>
+      <c r="E66" s="158"/>
+      <c r="F66" s="159"/>
+      <c r="G66" s="163"/>
       <c r="H66" s="104"/>
       <c r="I66" s="104"/>
       <c r="J66" s="14"/>
@@ -10837,12 +10837,12 @@
       <c r="B67" s="18"/>
       <c r="C67" s="1"/>
       <c r="D67" s="34"/>
-      <c r="E67" s="122" t="s">
+      <c r="E67" s="161" t="s">
         <v>26</v>
       </c>
-      <c r="F67" s="123"/>
-      <c r="G67" s="124"/>
-      <c r="H67" s="166" t="s">
+      <c r="F67" s="156"/>
+      <c r="G67" s="162"/>
+      <c r="H67" s="130" t="s">
         <v>53</v>
       </c>
       <c r="I67" s="104">
@@ -10965,9 +10965,9 @@
       <c r="B68" s="18"/>
       <c r="C68" s="1"/>
       <c r="D68" s="34"/>
-      <c r="E68" s="125"/>
-      <c r="F68" s="126"/>
-      <c r="G68" s="127"/>
+      <c r="E68" s="158"/>
+      <c r="F68" s="159"/>
+      <c r="G68" s="163"/>
       <c r="H68" s="104"/>
       <c r="I68" s="104"/>
       <c r="J68" s="14"/>
@@ -11087,12 +11087,12 @@
       <c r="B69" s="18"/>
       <c r="C69" s="1"/>
       <c r="D69" s="34"/>
-      <c r="E69" s="122" t="s">
+      <c r="E69" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="F69" s="123"/>
-      <c r="G69" s="124"/>
-      <c r="H69" s="166" t="s">
+      <c r="F69" s="156"/>
+      <c r="G69" s="162"/>
+      <c r="H69" s="130" t="s">
         <v>54</v>
       </c>
       <c r="I69" s="104">
@@ -11215,9 +11215,9 @@
       <c r="B70" s="18"/>
       <c r="C70" s="1"/>
       <c r="D70" s="34"/>
-      <c r="E70" s="125"/>
-      <c r="F70" s="126"/>
-      <c r="G70" s="127"/>
+      <c r="E70" s="158"/>
+      <c r="F70" s="159"/>
+      <c r="G70" s="163"/>
       <c r="H70" s="104"/>
       <c r="I70" s="104"/>
       <c r="J70" s="14"/>
@@ -11337,12 +11337,12 @@
       <c r="B71" s="18"/>
       <c r="C71" s="1"/>
       <c r="D71" s="34"/>
-      <c r="E71" s="122" t="s">
+      <c r="E71" s="161" t="s">
         <v>21</v>
       </c>
-      <c r="F71" s="123"/>
-      <c r="G71" s="124"/>
-      <c r="H71" s="166" t="s">
+      <c r="F71" s="156"/>
+      <c r="G71" s="162"/>
+      <c r="H71" s="130" t="s">
         <v>55</v>
       </c>
       <c r="I71" s="104">
@@ -11465,9 +11465,9 @@
       <c r="B72" s="18"/>
       <c r="C72" s="1"/>
       <c r="D72" s="35"/>
-      <c r="E72" s="125"/>
-      <c r="F72" s="126"/>
-      <c r="G72" s="127"/>
+      <c r="E72" s="158"/>
+      <c r="F72" s="159"/>
+      <c r="G72" s="163"/>
       <c r="H72" s="104"/>
       <c r="I72" s="104"/>
       <c r="J72" s="26"/>
@@ -11585,14 +11585,14 @@
     <row r="73" spans="1:120" ht="9.75" customHeight="1">
       <c r="A73" s="16"/>
       <c r="B73" s="36"/>
-      <c r="C73" s="131" t="s">
+      <c r="C73" s="138" t="s">
         <v>30</v>
       </c>
-      <c r="D73" s="123"/>
-      <c r="E73" s="123"/>
-      <c r="F73" s="123"/>
-      <c r="G73" s="129"/>
-      <c r="H73" s="166" t="s">
+      <c r="D73" s="156"/>
+      <c r="E73" s="156"/>
+      <c r="F73" s="156"/>
+      <c r="G73" s="157"/>
+      <c r="H73" s="130" t="s">
         <v>55</v>
       </c>
       <c r="I73" s="104">
@@ -11713,11 +11713,11 @@
     <row r="74" spans="1:120" ht="9.75" customHeight="1">
       <c r="A74" s="16"/>
       <c r="B74" s="36"/>
-      <c r="C74" s="132"/>
-      <c r="D74" s="126"/>
-      <c r="E74" s="126"/>
-      <c r="F74" s="126"/>
-      <c r="G74" s="130"/>
+      <c r="C74" s="171"/>
+      <c r="D74" s="159"/>
+      <c r="E74" s="159"/>
+      <c r="F74" s="159"/>
+      <c r="G74" s="160"/>
       <c r="H74" s="104"/>
       <c r="I74" s="104"/>
       <c r="J74" s="19"/>
@@ -11835,14 +11835,14 @@
     <row r="75" spans="1:120" ht="9.75" customHeight="1">
       <c r="A75" s="16"/>
       <c r="B75" s="36"/>
-      <c r="C75" s="131" t="s">
+      <c r="C75" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="D75" s="123"/>
-      <c r="E75" s="123"/>
-      <c r="F75" s="123"/>
-      <c r="G75" s="129"/>
-      <c r="H75" s="166" t="s">
+      <c r="D75" s="156"/>
+      <c r="E75" s="156"/>
+      <c r="F75" s="156"/>
+      <c r="G75" s="157"/>
+      <c r="H75" s="130" t="s">
         <v>58</v>
       </c>
       <c r="I75" s="104"/>
@@ -11961,11 +11961,11 @@
     <row r="76" spans="1:120" ht="9.75" customHeight="1">
       <c r="A76" s="16"/>
       <c r="B76" s="36"/>
-      <c r="C76" s="133"/>
-      <c r="D76" s="133"/>
-      <c r="E76" s="133"/>
-      <c r="F76" s="133"/>
-      <c r="G76" s="133"/>
+      <c r="C76" s="154"/>
+      <c r="D76" s="154"/>
+      <c r="E76" s="154"/>
+      <c r="F76" s="154"/>
+      <c r="G76" s="154"/>
       <c r="H76" s="104"/>
       <c r="I76" s="104"/>
       <c r="J76" s="19"/>
@@ -12083,15 +12083,15 @@
     <row r="77" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A77" s="16"/>
       <c r="B77" s="71"/>
-      <c r="C77" s="169" t="s">
+      <c r="C77" s="179" t="s">
         <v>62</v>
       </c>
-      <c r="D77" s="170"/>
-      <c r="E77" s="170"/>
-      <c r="F77" s="170"/>
-      <c r="G77" s="171"/>
-      <c r="H77" s="167"/>
-      <c r="I77" s="164"/>
+      <c r="D77" s="180"/>
+      <c r="E77" s="180"/>
+      <c r="F77" s="180"/>
+      <c r="G77" s="181"/>
+      <c r="H77" s="132"/>
+      <c r="I77" s="121"/>
       <c r="J77" s="63"/>
       <c r="K77" s="64"/>
       <c r="L77" s="64"/>
@@ -12207,13 +12207,13 @@
     <row r="78" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A78" s="16"/>
       <c r="B78" s="71"/>
-      <c r="C78" s="172"/>
-      <c r="D78" s="173"/>
-      <c r="E78" s="173"/>
-      <c r="F78" s="173"/>
-      <c r="G78" s="174"/>
-      <c r="H78" s="168"/>
-      <c r="I78" s="165"/>
+      <c r="C78" s="182"/>
+      <c r="D78" s="183"/>
+      <c r="E78" s="183"/>
+      <c r="F78" s="183"/>
+      <c r="G78" s="184"/>
+      <c r="H78" s="133"/>
+      <c r="I78" s="122"/>
       <c r="J78" s="63"/>
       <c r="K78" s="64"/>
       <c r="L78" s="64"/>
@@ -12330,12 +12330,12 @@
       <c r="A79" s="16"/>
       <c r="B79" s="71"/>
       <c r="C79" s="76"/>
-      <c r="D79" s="107" t="s">
+      <c r="D79" s="124" t="s">
         <v>63</v>
       </c>
-      <c r="E79" s="108"/>
-      <c r="F79" s="108"/>
-      <c r="G79" s="109"/>
+      <c r="E79" s="125"/>
+      <c r="F79" s="125"/>
+      <c r="G79" s="126"/>
       <c r="H79" s="77"/>
       <c r="I79" s="67"/>
       <c r="J79" s="63"/>
@@ -12454,10 +12454,10 @@
       <c r="A80" s="16"/>
       <c r="B80" s="71"/>
       <c r="C80" s="76"/>
-      <c r="D80" s="110"/>
-      <c r="E80" s="111"/>
-      <c r="F80" s="111"/>
-      <c r="G80" s="112"/>
+      <c r="D80" s="127"/>
+      <c r="E80" s="128"/>
+      <c r="F80" s="128"/>
+      <c r="G80" s="129"/>
       <c r="H80" s="77"/>
       <c r="I80" s="67"/>
       <c r="J80" s="63"/>
@@ -12577,15 +12577,17 @@
       <c r="B81" s="36"/>
       <c r="C81" s="60"/>
       <c r="D81" s="70"/>
-      <c r="E81" s="175" t="s">
+      <c r="E81" s="97" t="s">
         <v>73</v>
       </c>
-      <c r="F81" s="175"/>
-      <c r="G81" s="175"/>
-      <c r="H81" s="95">
+      <c r="F81" s="97"/>
+      <c r="G81" s="97"/>
+      <c r="H81" s="103">
         <v>45611</v>
       </c>
-      <c r="I81" s="97"/>
+      <c r="I81" s="118">
+        <v>100</v>
+      </c>
       <c r="J81" s="19"/>
       <c r="K81" s="20"/>
       <c r="L81" s="20"/>
@@ -12703,11 +12705,11 @@
       <c r="B82" s="36"/>
       <c r="C82" s="60"/>
       <c r="D82" s="70"/>
-      <c r="E82" s="94"/>
-      <c r="F82" s="94"/>
-      <c r="G82" s="94"/>
-      <c r="H82" s="96"/>
-      <c r="I82" s="98"/>
+      <c r="E82" s="95"/>
+      <c r="F82" s="95"/>
+      <c r="G82" s="95"/>
+      <c r="H82" s="99"/>
+      <c r="I82" s="101"/>
       <c r="J82" s="19"/>
       <c r="K82" s="20"/>
       <c r="L82" s="20"/>
@@ -12740,7 +12742,7 @@
       <c r="AM82" s="20"/>
       <c r="AN82" s="20"/>
       <c r="AO82" s="20"/>
-      <c r="AP82" s="20"/>
+      <c r="AP82" s="75"/>
       <c r="AQ82" s="21"/>
       <c r="AR82" s="21"/>
       <c r="AS82" s="20"/>
@@ -12825,15 +12827,17 @@
       <c r="B83" s="36"/>
       <c r="C83" s="60"/>
       <c r="D83" s="70"/>
-      <c r="E83" s="94" t="s">
+      <c r="E83" s="95" t="s">
         <v>74</v>
       </c>
-      <c r="F83" s="94"/>
-      <c r="G83" s="94"/>
-      <c r="H83" s="95">
+      <c r="F83" s="95"/>
+      <c r="G83" s="95"/>
+      <c r="H83" s="103">
         <v>45615</v>
       </c>
-      <c r="I83" s="97"/>
+      <c r="I83" s="118">
+        <v>100</v>
+      </c>
       <c r="J83" s="19"/>
       <c r="K83" s="20"/>
       <c r="L83" s="20"/>
@@ -12951,11 +12955,11 @@
       <c r="B84" s="36"/>
       <c r="C84" s="60"/>
       <c r="D84" s="70"/>
-      <c r="E84" s="94"/>
-      <c r="F84" s="94"/>
-      <c r="G84" s="94"/>
-      <c r="H84" s="96"/>
-      <c r="I84" s="98"/>
+      <c r="E84" s="95"/>
+      <c r="F84" s="95"/>
+      <c r="G84" s="95"/>
+      <c r="H84" s="99"/>
+      <c r="I84" s="101"/>
       <c r="J84" s="19"/>
       <c r="K84" s="20"/>
       <c r="L84" s="20"/>
@@ -12991,8 +12995,8 @@
       <c r="AP84" s="20"/>
       <c r="AQ84" s="21"/>
       <c r="AR84" s="21"/>
-      <c r="AS84" s="20"/>
-      <c r="AT84" s="69"/>
+      <c r="AS84" s="75"/>
+      <c r="AT84" s="75"/>
       <c r="AU84" s="69"/>
       <c r="AV84" s="69"/>
       <c r="AW84" s="20"/>
@@ -13073,15 +13077,17 @@
       <c r="B85" s="36"/>
       <c r="C85" s="60"/>
       <c r="D85" s="70"/>
-      <c r="E85" s="179" t="s">
+      <c r="E85" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="F85" s="113"/>
-      <c r="G85" s="114"/>
-      <c r="H85" s="103">
+      <c r="F85" s="107"/>
+      <c r="G85" s="108"/>
+      <c r="H85" s="102">
         <v>45617</v>
       </c>
-      <c r="I85" s="104"/>
+      <c r="I85" s="118">
+        <v>100</v>
+      </c>
       <c r="J85" s="62"/>
       <c r="K85" s="20"/>
       <c r="L85" s="20"/>
@@ -13199,11 +13205,11 @@
       <c r="B86" s="36"/>
       <c r="C86" s="60"/>
       <c r="D86" s="70"/>
-      <c r="E86" s="176"/>
-      <c r="F86" s="117"/>
-      <c r="G86" s="118"/>
-      <c r="H86" s="103"/>
-      <c r="I86" s="104"/>
+      <c r="E86" s="109"/>
+      <c r="F86" s="110"/>
+      <c r="G86" s="111"/>
+      <c r="H86" s="102"/>
+      <c r="I86" s="101"/>
       <c r="J86" s="62"/>
       <c r="K86" s="20"/>
       <c r="L86" s="20"/>
@@ -13320,16 +13326,18 @@
       <c r="A87" s="16"/>
       <c r="B87" s="71"/>
       <c r="C87" s="90"/>
-      <c r="D87" s="94" t="s">
+      <c r="D87" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E87" s="94"/>
-      <c r="F87" s="94"/>
-      <c r="G87" s="94"/>
-      <c r="H87" s="95">
+      <c r="E87" s="95"/>
+      <c r="F87" s="95"/>
+      <c r="G87" s="95"/>
+      <c r="H87" s="103">
         <v>45615</v>
       </c>
-      <c r="I87" s="101"/>
+      <c r="I87" s="118">
+        <v>100</v>
+      </c>
       <c r="J87" s="62"/>
       <c r="K87" s="20"/>
       <c r="L87" s="20"/>
@@ -13446,12 +13454,12 @@
       <c r="A88" s="16"/>
       <c r="B88" s="71"/>
       <c r="C88" s="90"/>
-      <c r="D88" s="94"/>
-      <c r="E88" s="94"/>
-      <c r="F88" s="94"/>
-      <c r="G88" s="94"/>
-      <c r="H88" s="96"/>
-      <c r="I88" s="102"/>
+      <c r="D88" s="95"/>
+      <c r="E88" s="95"/>
+      <c r="F88" s="95"/>
+      <c r="G88" s="95"/>
+      <c r="H88" s="99"/>
+      <c r="I88" s="101"/>
       <c r="J88" s="62"/>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -13568,14 +13576,14 @@
       <c r="A89" s="16"/>
       <c r="B89" s="36"/>
       <c r="C89" s="79"/>
-      <c r="D89" s="107" t="s">
+      <c r="D89" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="108"/>
-      <c r="F89" s="108"/>
-      <c r="G89" s="109"/>
-      <c r="H89" s="177"/>
-      <c r="I89" s="178"/>
+      <c r="E89" s="125"/>
+      <c r="F89" s="125"/>
+      <c r="G89" s="126"/>
+      <c r="H89" s="123"/>
+      <c r="I89" s="120"/>
       <c r="J89" s="66"/>
       <c r="K89" s="64"/>
       <c r="L89" s="64"/>
@@ -13692,12 +13700,12 @@
       <c r="A90" s="16"/>
       <c r="B90" s="36"/>
       <c r="C90" s="79"/>
-      <c r="D90" s="110"/>
-      <c r="E90" s="111"/>
-      <c r="F90" s="111"/>
-      <c r="G90" s="112"/>
-      <c r="H90" s="177"/>
-      <c r="I90" s="178"/>
+      <c r="D90" s="127"/>
+      <c r="E90" s="128"/>
+      <c r="F90" s="128"/>
+      <c r="G90" s="129"/>
+      <c r="H90" s="123"/>
+      <c r="I90" s="120"/>
       <c r="J90" s="66"/>
       <c r="K90" s="64"/>
       <c r="L90" s="64"/>
@@ -13815,15 +13823,15 @@
       <c r="B91" s="36"/>
       <c r="C91" s="60"/>
       <c r="D91" s="70"/>
-      <c r="E91" s="175" t="s">
+      <c r="E91" s="97" t="s">
         <v>68</v>
       </c>
-      <c r="F91" s="175"/>
-      <c r="G91" s="175"/>
-      <c r="H91" s="95">
+      <c r="F91" s="97"/>
+      <c r="G91" s="97"/>
+      <c r="H91" s="103">
         <v>45616</v>
       </c>
-      <c r="I91" s="97"/>
+      <c r="I91" s="118"/>
       <c r="J91" s="19"/>
       <c r="K91" s="20"/>
       <c r="L91" s="20"/>
@@ -13941,11 +13949,11 @@
       <c r="B92" s="36"/>
       <c r="C92" s="60"/>
       <c r="D92" s="70"/>
-      <c r="E92" s="94"/>
-      <c r="F92" s="94"/>
-      <c r="G92" s="94"/>
-      <c r="H92" s="96"/>
-      <c r="I92" s="98"/>
+      <c r="E92" s="95"/>
+      <c r="F92" s="95"/>
+      <c r="G92" s="95"/>
+      <c r="H92" s="99"/>
+      <c r="I92" s="101"/>
       <c r="J92" s="19"/>
       <c r="K92" s="20"/>
       <c r="L92" s="20"/>
@@ -14063,15 +14071,15 @@
       <c r="B93" s="36"/>
       <c r="C93" s="60"/>
       <c r="D93" s="70"/>
-      <c r="E93" s="94" t="s">
+      <c r="E93" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="F93" s="94"/>
-      <c r="G93" s="94"/>
-      <c r="H93" s="95">
+      <c r="F93" s="95"/>
+      <c r="G93" s="95"/>
+      <c r="H93" s="103">
         <v>45617</v>
       </c>
-      <c r="I93" s="97"/>
+      <c r="I93" s="118"/>
       <c r="J93" s="19"/>
       <c r="K93" s="20"/>
       <c r="L93" s="20"/>
@@ -14189,11 +14197,11 @@
       <c r="B94" s="36"/>
       <c r="C94" s="60"/>
       <c r="D94" s="70"/>
-      <c r="E94" s="94"/>
-      <c r="F94" s="94"/>
-      <c r="G94" s="94"/>
-      <c r="H94" s="96"/>
-      <c r="I94" s="98"/>
+      <c r="E94" s="95"/>
+      <c r="F94" s="95"/>
+      <c r="G94" s="95"/>
+      <c r="H94" s="99"/>
+      <c r="I94" s="101"/>
       <c r="J94" s="19"/>
       <c r="K94" s="20"/>
       <c r="L94" s="20"/>
@@ -14311,15 +14319,15 @@
       <c r="B95" s="36"/>
       <c r="C95" s="60"/>
       <c r="D95" s="70"/>
-      <c r="E95" s="94" t="s">
+      <c r="E95" s="95" t="s">
         <v>70</v>
       </c>
-      <c r="F95" s="94"/>
-      <c r="G95" s="94"/>
-      <c r="H95" s="95">
+      <c r="F95" s="95"/>
+      <c r="G95" s="95"/>
+      <c r="H95" s="103">
         <v>45618</v>
       </c>
-      <c r="I95" s="97"/>
+      <c r="I95" s="118"/>
       <c r="J95" s="19"/>
       <c r="K95" s="20"/>
       <c r="L95" s="20"/>
@@ -14437,11 +14445,11 @@
       <c r="B96" s="36"/>
       <c r="C96" s="60"/>
       <c r="D96" s="70"/>
-      <c r="E96" s="94"/>
-      <c r="F96" s="94"/>
-      <c r="G96" s="94"/>
-      <c r="H96" s="96"/>
-      <c r="I96" s="98"/>
+      <c r="E96" s="95"/>
+      <c r="F96" s="95"/>
+      <c r="G96" s="95"/>
+      <c r="H96" s="99"/>
+      <c r="I96" s="101"/>
       <c r="J96" s="19"/>
       <c r="K96" s="20"/>
       <c r="L96" s="20"/>
@@ -14559,15 +14567,15 @@
       <c r="B97" s="36"/>
       <c r="C97" s="60"/>
       <c r="D97" s="70"/>
-      <c r="E97" s="94" t="s">
+      <c r="E97" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="F97" s="94"/>
-      <c r="G97" s="94"/>
-      <c r="H97" s="95">
+      <c r="F97" s="95"/>
+      <c r="G97" s="95"/>
+      <c r="H97" s="103">
         <v>45621</v>
       </c>
-      <c r="I97" s="97"/>
+      <c r="I97" s="118"/>
       <c r="J97" s="19"/>
       <c r="K97" s="20"/>
       <c r="L97" s="20"/>
@@ -14685,11 +14693,11 @@
       <c r="B98" s="36"/>
       <c r="C98" s="60"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="94"/>
-      <c r="F98" s="94"/>
-      <c r="G98" s="94"/>
-      <c r="H98" s="96"/>
-      <c r="I98" s="98"/>
+      <c r="E98" s="95"/>
+      <c r="F98" s="95"/>
+      <c r="G98" s="95"/>
+      <c r="H98" s="99"/>
+      <c r="I98" s="101"/>
       <c r="J98" s="19"/>
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
@@ -14807,15 +14815,15 @@
       <c r="B99" s="36"/>
       <c r="C99" s="60"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="94" t="s">
+      <c r="E99" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="F99" s="94"/>
-      <c r="G99" s="94"/>
-      <c r="H99" s="95">
+      <c r="F99" s="95"/>
+      <c r="G99" s="95"/>
+      <c r="H99" s="103">
         <v>45622</v>
       </c>
-      <c r="I99" s="97"/>
+      <c r="I99" s="118"/>
       <c r="J99" s="19"/>
       <c r="K99" s="20"/>
       <c r="L99" s="20"/>
@@ -14933,11 +14941,11 @@
       <c r="B100" s="36"/>
       <c r="C100" s="60"/>
       <c r="D100" s="70"/>
-      <c r="E100" s="94"/>
-      <c r="F100" s="94"/>
-      <c r="G100" s="94"/>
-      <c r="H100" s="96"/>
-      <c r="I100" s="98"/>
+      <c r="E100" s="95"/>
+      <c r="F100" s="95"/>
+      <c r="G100" s="95"/>
+      <c r="H100" s="99"/>
+      <c r="I100" s="101"/>
       <c r="J100" s="19"/>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -15055,12 +15063,12 @@
       <c r="B101" s="71"/>
       <c r="C101" s="91"/>
       <c r="D101" s="70"/>
-      <c r="E101" s="176" t="s">
+      <c r="E101" s="109" t="s">
         <v>61</v>
       </c>
-      <c r="F101" s="117"/>
-      <c r="G101" s="118"/>
-      <c r="H101" s="95">
+      <c r="F101" s="110"/>
+      <c r="G101" s="111"/>
+      <c r="H101" s="103">
         <v>45623</v>
       </c>
       <c r="I101" s="104"/>
@@ -15181,10 +15189,10 @@
       <c r="B102" s="71"/>
       <c r="C102" s="91"/>
       <c r="D102" s="70"/>
-      <c r="E102" s="176"/>
-      <c r="F102" s="117"/>
-      <c r="G102" s="118"/>
-      <c r="H102" s="96"/>
+      <c r="E102" s="109"/>
+      <c r="F102" s="110"/>
+      <c r="G102" s="111"/>
+      <c r="H102" s="99"/>
       <c r="I102" s="104"/>
       <c r="J102" s="62"/>
       <c r="K102" s="20"/>
@@ -15302,16 +15310,16 @@
       <c r="A103" s="16"/>
       <c r="B103" s="71"/>
       <c r="C103" s="90"/>
-      <c r="D103" s="94" t="s">
+      <c r="D103" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="E103" s="94"/>
-      <c r="F103" s="94"/>
-      <c r="G103" s="94"/>
-      <c r="H103" s="95">
+      <c r="E103" s="95"/>
+      <c r="F103" s="95"/>
+      <c r="G103" s="95"/>
+      <c r="H103" s="103">
         <v>45622</v>
       </c>
-      <c r="I103" s="101"/>
+      <c r="I103" s="105"/>
       <c r="J103" s="62"/>
       <c r="K103" s="20"/>
       <c r="L103" s="20"/>
@@ -15428,12 +15436,12 @@
       <c r="A104" s="16"/>
       <c r="B104" s="71"/>
       <c r="C104" s="90"/>
-      <c r="D104" s="94"/>
-      <c r="E104" s="94"/>
-      <c r="F104" s="94"/>
-      <c r="G104" s="94"/>
-      <c r="H104" s="96"/>
-      <c r="I104" s="102"/>
+      <c r="D104" s="95"/>
+      <c r="E104" s="95"/>
+      <c r="F104" s="95"/>
+      <c r="G104" s="95"/>
+      <c r="H104" s="99"/>
+      <c r="I104" s="135"/>
       <c r="J104" s="62"/>
       <c r="K104" s="20"/>
       <c r="L104" s="20"/>
@@ -15549,15 +15557,15 @@
     <row r="105" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A105" s="16"/>
       <c r="B105" s="71"/>
-      <c r="C105" s="169" t="s">
+      <c r="C105" s="179" t="s">
         <v>64</v>
       </c>
-      <c r="D105" s="170"/>
-      <c r="E105" s="170"/>
-      <c r="F105" s="170"/>
-      <c r="G105" s="171"/>
-      <c r="H105" s="180"/>
-      <c r="I105" s="178"/>
+      <c r="D105" s="180"/>
+      <c r="E105" s="180"/>
+      <c r="F105" s="180"/>
+      <c r="G105" s="181"/>
+      <c r="H105" s="119"/>
+      <c r="I105" s="120"/>
       <c r="J105" s="66"/>
       <c r="K105" s="64"/>
       <c r="L105" s="64"/>
@@ -15673,13 +15681,13 @@
     <row r="106" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A106" s="16"/>
       <c r="B106" s="71"/>
-      <c r="C106" s="172"/>
-      <c r="D106" s="173"/>
-      <c r="E106" s="173"/>
-      <c r="F106" s="173"/>
-      <c r="G106" s="174"/>
-      <c r="H106" s="180"/>
-      <c r="I106" s="178"/>
+      <c r="C106" s="182"/>
+      <c r="D106" s="183"/>
+      <c r="E106" s="183"/>
+      <c r="F106" s="183"/>
+      <c r="G106" s="184"/>
+      <c r="H106" s="119"/>
+      <c r="I106" s="120"/>
       <c r="J106" s="66"/>
       <c r="K106" s="64"/>
       <c r="L106" s="64"/>
@@ -15796,14 +15804,14 @@
       <c r="A107" s="16"/>
       <c r="B107" s="36"/>
       <c r="C107" s="78"/>
-      <c r="D107" s="107" t="s">
+      <c r="D107" s="124" t="s">
         <v>59</v>
       </c>
-      <c r="E107" s="108"/>
-      <c r="F107" s="108"/>
-      <c r="G107" s="109"/>
-      <c r="H107" s="180"/>
-      <c r="I107" s="178"/>
+      <c r="E107" s="125"/>
+      <c r="F107" s="125"/>
+      <c r="G107" s="126"/>
+      <c r="H107" s="119"/>
+      <c r="I107" s="120"/>
       <c r="J107" s="66"/>
       <c r="K107" s="64"/>
       <c r="L107" s="64"/>
@@ -15920,12 +15928,12 @@
       <c r="A108" s="16"/>
       <c r="B108" s="36"/>
       <c r="C108" s="76"/>
-      <c r="D108" s="110"/>
-      <c r="E108" s="111"/>
-      <c r="F108" s="111"/>
-      <c r="G108" s="112"/>
-      <c r="H108" s="180"/>
-      <c r="I108" s="178"/>
+      <c r="D108" s="127"/>
+      <c r="E108" s="128"/>
+      <c r="F108" s="128"/>
+      <c r="G108" s="129"/>
+      <c r="H108" s="119"/>
+      <c r="I108" s="120"/>
       <c r="J108" s="66"/>
       <c r="K108" s="64"/>
       <c r="L108" s="64"/>
@@ -16043,15 +16051,15 @@
       <c r="B109" s="36"/>
       <c r="C109" s="60"/>
       <c r="D109" s="70"/>
-      <c r="E109" s="175" t="s">
+      <c r="E109" s="97" t="s">
         <v>73</v>
       </c>
-      <c r="F109" s="175"/>
-      <c r="G109" s="175"/>
-      <c r="H109" s="95">
+      <c r="F109" s="97"/>
+      <c r="G109" s="97"/>
+      <c r="H109" s="103">
         <v>45624</v>
       </c>
-      <c r="I109" s="101"/>
+      <c r="I109" s="105"/>
       <c r="J109" s="62"/>
       <c r="K109" s="20"/>
       <c r="L109" s="20"/>
@@ -16169,11 +16177,11 @@
       <c r="B110" s="36"/>
       <c r="C110" s="60"/>
       <c r="D110" s="70"/>
-      <c r="E110" s="94"/>
-      <c r="F110" s="94"/>
-      <c r="G110" s="94"/>
-      <c r="H110" s="96"/>
-      <c r="I110" s="102"/>
+      <c r="E110" s="95"/>
+      <c r="F110" s="95"/>
+      <c r="G110" s="95"/>
+      <c r="H110" s="99"/>
+      <c r="I110" s="135"/>
       <c r="J110" s="62"/>
       <c r="K110" s="20"/>
       <c r="L110" s="20"/>
@@ -16291,15 +16299,15 @@
       <c r="B111" s="36"/>
       <c r="C111" s="60"/>
       <c r="D111" s="70"/>
-      <c r="E111" s="94" t="s">
+      <c r="E111" s="95" t="s">
         <v>74</v>
       </c>
-      <c r="F111" s="94"/>
-      <c r="G111" s="94"/>
-      <c r="H111" s="95">
+      <c r="F111" s="95"/>
+      <c r="G111" s="95"/>
+      <c r="H111" s="103">
         <v>45625</v>
       </c>
-      <c r="I111" s="101"/>
+      <c r="I111" s="105"/>
       <c r="J111" s="62"/>
       <c r="K111" s="20"/>
       <c r="L111" s="20"/>
@@ -16417,11 +16425,11 @@
       <c r="B112" s="36"/>
       <c r="C112" s="60"/>
       <c r="D112" s="70"/>
-      <c r="E112" s="94"/>
-      <c r="F112" s="94"/>
-      <c r="G112" s="94"/>
-      <c r="H112" s="96"/>
-      <c r="I112" s="102"/>
+      <c r="E112" s="95"/>
+      <c r="F112" s="95"/>
+      <c r="G112" s="95"/>
+      <c r="H112" s="99"/>
+      <c r="I112" s="135"/>
       <c r="J112" s="62"/>
       <c r="K112" s="20"/>
       <c r="L112" s="20"/>
@@ -16539,12 +16547,12 @@
       <c r="B113" s="71"/>
       <c r="C113" s="91"/>
       <c r="D113" s="70"/>
-      <c r="E113" s="94" t="s">
+      <c r="E113" s="95" t="s">
         <v>61</v>
       </c>
-      <c r="F113" s="94"/>
-      <c r="G113" s="94"/>
-      <c r="H113" s="103">
+      <c r="F113" s="95"/>
+      <c r="G113" s="95"/>
+      <c r="H113" s="102">
         <v>45630</v>
       </c>
       <c r="I113" s="104"/>
@@ -16665,11 +16673,11 @@
       <c r="B114" s="71"/>
       <c r="C114" s="91"/>
       <c r="D114" s="70"/>
-      <c r="E114" s="190"/>
-      <c r="F114" s="190"/>
-      <c r="G114" s="190"/>
-      <c r="H114" s="95"/>
-      <c r="I114" s="101"/>
+      <c r="E114" s="117"/>
+      <c r="F114" s="117"/>
+      <c r="G114" s="117"/>
+      <c r="H114" s="103"/>
+      <c r="I114" s="105"/>
       <c r="J114" s="62"/>
       <c r="K114" s="20"/>
       <c r="L114" s="20"/>
@@ -16786,13 +16794,13 @@
       <c r="A115" s="16"/>
       <c r="B115" s="71"/>
       <c r="C115" s="91"/>
-      <c r="D115" s="94" t="s">
+      <c r="D115" s="95" t="s">
         <v>78</v>
       </c>
-      <c r="E115" s="94"/>
-      <c r="F115" s="94"/>
-      <c r="G115" s="94"/>
-      <c r="H115" s="103">
+      <c r="E115" s="95"/>
+      <c r="F115" s="95"/>
+      <c r="G115" s="95"/>
+      <c r="H115" s="102">
         <v>45625</v>
       </c>
       <c r="I115" s="104"/>
@@ -16912,11 +16920,11 @@
       <c r="A116" s="16"/>
       <c r="B116" s="71"/>
       <c r="C116" s="91"/>
-      <c r="D116" s="94"/>
-      <c r="E116" s="94"/>
-      <c r="F116" s="94"/>
-      <c r="G116" s="94"/>
-      <c r="H116" s="103"/>
+      <c r="D116" s="95"/>
+      <c r="E116" s="95"/>
+      <c r="F116" s="95"/>
+      <c r="G116" s="95"/>
+      <c r="H116" s="102"/>
       <c r="I116" s="104"/>
       <c r="J116" s="62"/>
       <c r="K116" s="20"/>
@@ -17034,14 +17042,14 @@
       <c r="A117" s="16"/>
       <c r="B117" s="36"/>
       <c r="C117" s="80"/>
-      <c r="D117" s="107" t="s">
+      <c r="D117" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="E117" s="108"/>
-      <c r="F117" s="108"/>
-      <c r="G117" s="109"/>
-      <c r="H117" s="181"/>
-      <c r="I117" s="164"/>
+      <c r="E117" s="125"/>
+      <c r="F117" s="125"/>
+      <c r="G117" s="126"/>
+      <c r="H117" s="113"/>
+      <c r="I117" s="121"/>
       <c r="J117" s="63"/>
       <c r="K117" s="64"/>
       <c r="L117" s="64"/>
@@ -17158,12 +17166,12 @@
       <c r="A118" s="16"/>
       <c r="B118" s="36"/>
       <c r="C118" s="80"/>
-      <c r="D118" s="110"/>
-      <c r="E118" s="111"/>
-      <c r="F118" s="111"/>
-      <c r="G118" s="112"/>
-      <c r="H118" s="182"/>
-      <c r="I118" s="165"/>
+      <c r="D118" s="127"/>
+      <c r="E118" s="128"/>
+      <c r="F118" s="128"/>
+      <c r="G118" s="129"/>
+      <c r="H118" s="114"/>
+      <c r="I118" s="122"/>
       <c r="J118" s="63"/>
       <c r="K118" s="64"/>
       <c r="L118" s="64"/>
@@ -17281,15 +17289,15 @@
       <c r="B119" s="36"/>
       <c r="C119" s="60"/>
       <c r="D119" s="70"/>
-      <c r="E119" s="175" t="s">
+      <c r="E119" s="97" t="s">
         <v>68</v>
       </c>
-      <c r="F119" s="175"/>
-      <c r="G119" s="175"/>
-      <c r="H119" s="95">
+      <c r="F119" s="97"/>
+      <c r="G119" s="97"/>
+      <c r="H119" s="103">
         <v>45629</v>
       </c>
-      <c r="I119" s="97"/>
+      <c r="I119" s="118"/>
       <c r="J119" s="19"/>
       <c r="K119" s="20"/>
       <c r="L119" s="20"/>
@@ -17407,11 +17415,11 @@
       <c r="B120" s="36"/>
       <c r="C120" s="60"/>
       <c r="D120" s="70"/>
-      <c r="E120" s="94"/>
-      <c r="F120" s="94"/>
-      <c r="G120" s="94"/>
-      <c r="H120" s="96"/>
-      <c r="I120" s="98"/>
+      <c r="E120" s="95"/>
+      <c r="F120" s="95"/>
+      <c r="G120" s="95"/>
+      <c r="H120" s="99"/>
+      <c r="I120" s="101"/>
       <c r="J120" s="19"/>
       <c r="K120" s="20"/>
       <c r="L120" s="20"/>
@@ -17529,15 +17537,15 @@
       <c r="B121" s="36"/>
       <c r="C121" s="60"/>
       <c r="D121" s="70"/>
-      <c r="E121" s="94" t="s">
+      <c r="E121" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="F121" s="94"/>
-      <c r="G121" s="94"/>
-      <c r="H121" s="95">
+      <c r="F121" s="95"/>
+      <c r="G121" s="95"/>
+      <c r="H121" s="103">
         <v>45630</v>
       </c>
-      <c r="I121" s="97"/>
+      <c r="I121" s="118"/>
       <c r="J121" s="19"/>
       <c r="K121" s="20"/>
       <c r="L121" s="20"/>
@@ -17655,11 +17663,11 @@
       <c r="B122" s="36"/>
       <c r="C122" s="60"/>
       <c r="D122" s="70"/>
-      <c r="E122" s="94"/>
-      <c r="F122" s="94"/>
-      <c r="G122" s="94"/>
-      <c r="H122" s="96"/>
-      <c r="I122" s="98"/>
+      <c r="E122" s="95"/>
+      <c r="F122" s="95"/>
+      <c r="G122" s="95"/>
+      <c r="H122" s="99"/>
+      <c r="I122" s="101"/>
       <c r="J122" s="19"/>
       <c r="K122" s="20"/>
       <c r="L122" s="20"/>
@@ -17777,12 +17785,12 @@
       <c r="B123" s="36"/>
       <c r="C123" s="60"/>
       <c r="D123" s="70"/>
-      <c r="E123" s="94" t="s">
+      <c r="E123" s="95" t="s">
         <v>70</v>
       </c>
-      <c r="F123" s="94"/>
-      <c r="G123" s="94"/>
-      <c r="H123" s="189">
+      <c r="F123" s="95"/>
+      <c r="G123" s="95"/>
+      <c r="H123" s="112">
         <v>45631</v>
       </c>
       <c r="I123" s="104"/>
@@ -17903,10 +17911,10 @@
       <c r="B124" s="36"/>
       <c r="C124" s="60"/>
       <c r="D124" s="70"/>
-      <c r="E124" s="94"/>
-      <c r="F124" s="94"/>
-      <c r="G124" s="94"/>
-      <c r="H124" s="189"/>
+      <c r="E124" s="95"/>
+      <c r="F124" s="95"/>
+      <c r="G124" s="95"/>
+      <c r="H124" s="112"/>
       <c r="I124" s="104"/>
       <c r="J124" s="62"/>
       <c r="K124" s="20"/>
@@ -18025,12 +18033,12 @@
       <c r="B125" s="36"/>
       <c r="C125" s="60"/>
       <c r="D125" s="70"/>
-      <c r="E125" s="94" t="s">
+      <c r="E125" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="F125" s="94"/>
-      <c r="G125" s="94"/>
-      <c r="H125" s="103">
+      <c r="F125" s="95"/>
+      <c r="G125" s="95"/>
+      <c r="H125" s="102">
         <v>45632</v>
       </c>
       <c r="I125" s="104"/>
@@ -18151,10 +18159,10 @@
       <c r="B126" s="36"/>
       <c r="C126" s="60"/>
       <c r="D126" s="70"/>
-      <c r="E126" s="94"/>
-      <c r="F126" s="94"/>
-      <c r="G126" s="94"/>
-      <c r="H126" s="103"/>
+      <c r="E126" s="95"/>
+      <c r="F126" s="95"/>
+      <c r="G126" s="95"/>
+      <c r="H126" s="102"/>
       <c r="I126" s="104"/>
       <c r="J126" s="62"/>
       <c r="K126" s="20"/>
@@ -18273,15 +18281,15 @@
       <c r="B127" s="36"/>
       <c r="C127" s="60"/>
       <c r="D127" s="70"/>
-      <c r="E127" s="94" t="s">
+      <c r="E127" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="F127" s="94"/>
-      <c r="G127" s="94"/>
-      <c r="H127" s="95">
+      <c r="F127" s="95"/>
+      <c r="G127" s="95"/>
+      <c r="H127" s="103">
         <v>45635</v>
       </c>
-      <c r="I127" s="97"/>
+      <c r="I127" s="118"/>
       <c r="J127" s="19"/>
       <c r="K127" s="20"/>
       <c r="L127" s="20"/>
@@ -18399,11 +18407,11 @@
       <c r="B128" s="36"/>
       <c r="C128" s="60"/>
       <c r="D128" s="70"/>
-      <c r="E128" s="190"/>
-      <c r="F128" s="190"/>
-      <c r="G128" s="190"/>
-      <c r="H128" s="96"/>
-      <c r="I128" s="98"/>
+      <c r="E128" s="117"/>
+      <c r="F128" s="117"/>
+      <c r="G128" s="117"/>
+      <c r="H128" s="99"/>
+      <c r="I128" s="101"/>
       <c r="J128" s="19"/>
       <c r="K128" s="20"/>
       <c r="L128" s="20"/>
@@ -18521,12 +18529,12 @@
       <c r="B129" s="71"/>
       <c r="C129" s="91"/>
       <c r="D129" s="70"/>
-      <c r="E129" s="179" t="s">
+      <c r="E129" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="F129" s="113"/>
-      <c r="G129" s="114"/>
-      <c r="H129" s="103">
+      <c r="F129" s="107"/>
+      <c r="G129" s="108"/>
+      <c r="H129" s="102">
         <v>45638</v>
       </c>
       <c r="I129" s="104"/>
@@ -18647,10 +18655,10 @@
       <c r="B130" s="71"/>
       <c r="C130" s="91"/>
       <c r="D130" s="70"/>
-      <c r="E130" s="176"/>
-      <c r="F130" s="117"/>
-      <c r="G130" s="118"/>
-      <c r="H130" s="103"/>
+      <c r="E130" s="109"/>
+      <c r="F130" s="110"/>
+      <c r="G130" s="111"/>
+      <c r="H130" s="102"/>
       <c r="I130" s="104"/>
       <c r="J130" s="62"/>
       <c r="K130" s="20"/>
@@ -18768,16 +18776,16 @@
       <c r="A131" s="16"/>
       <c r="B131" s="71"/>
       <c r="C131" s="91"/>
-      <c r="D131" s="94" t="s">
+      <c r="D131" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="E131" s="94"/>
-      <c r="F131" s="94"/>
-      <c r="G131" s="94"/>
-      <c r="H131" s="95">
+      <c r="E131" s="95"/>
+      <c r="F131" s="95"/>
+      <c r="G131" s="95"/>
+      <c r="H131" s="103">
         <v>45635</v>
       </c>
-      <c r="I131" s="101"/>
+      <c r="I131" s="105"/>
       <c r="J131" s="62"/>
       <c r="K131" s="20"/>
       <c r="L131" s="20"/>
@@ -18894,12 +18902,12 @@
       <c r="A132" s="16"/>
       <c r="B132" s="71"/>
       <c r="C132" s="90"/>
-      <c r="D132" s="94"/>
-      <c r="E132" s="94"/>
-      <c r="F132" s="94"/>
-      <c r="G132" s="94"/>
-      <c r="H132" s="96"/>
-      <c r="I132" s="102"/>
+      <c r="D132" s="95"/>
+      <c r="E132" s="95"/>
+      <c r="F132" s="95"/>
+      <c r="G132" s="95"/>
+      <c r="H132" s="99"/>
+      <c r="I132" s="135"/>
       <c r="J132" s="62"/>
       <c r="K132" s="20"/>
       <c r="L132" s="20"/>
@@ -19015,15 +19023,15 @@
     <row r="133" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A133" s="16"/>
       <c r="B133" s="36"/>
-      <c r="C133" s="107" t="s">
+      <c r="C133" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="D133" s="108"/>
-      <c r="E133" s="108"/>
-      <c r="F133" s="108"/>
-      <c r="G133" s="109"/>
-      <c r="H133" s="181"/>
-      <c r="I133" s="99"/>
+      <c r="D133" s="125"/>
+      <c r="E133" s="125"/>
+      <c r="F133" s="125"/>
+      <c r="G133" s="126"/>
+      <c r="H133" s="113"/>
+      <c r="I133" s="115"/>
       <c r="J133" s="66"/>
       <c r="K133" s="64"/>
       <c r="L133" s="64"/>
@@ -19139,13 +19147,13 @@
     <row r="134" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A134" s="16"/>
       <c r="B134" s="36"/>
-      <c r="C134" s="110"/>
-      <c r="D134" s="111"/>
-      <c r="E134" s="111"/>
-      <c r="F134" s="111"/>
-      <c r="G134" s="112"/>
-      <c r="H134" s="182"/>
-      <c r="I134" s="100"/>
+      <c r="C134" s="127"/>
+      <c r="D134" s="128"/>
+      <c r="E134" s="128"/>
+      <c r="F134" s="128"/>
+      <c r="G134" s="129"/>
+      <c r="H134" s="114"/>
+      <c r="I134" s="116"/>
       <c r="J134" s="66"/>
       <c r="K134" s="64"/>
       <c r="L134" s="64"/>
@@ -19262,14 +19270,14 @@
       <c r="A135" s="16"/>
       <c r="B135" s="36"/>
       <c r="C135" s="60"/>
-      <c r="D135" s="107" t="s">
+      <c r="D135" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="108"/>
-      <c r="F135" s="108"/>
-      <c r="G135" s="109"/>
-      <c r="H135" s="105"/>
-      <c r="I135" s="164"/>
+      <c r="E135" s="125"/>
+      <c r="F135" s="125"/>
+      <c r="G135" s="126"/>
+      <c r="H135" s="185"/>
+      <c r="I135" s="121"/>
       <c r="J135" s="63"/>
       <c r="K135" s="64"/>
       <c r="L135" s="64"/>
@@ -19386,12 +19394,12 @@
       <c r="A136" s="16"/>
       <c r="B136" s="36"/>
       <c r="C136" s="60"/>
-      <c r="D136" s="110"/>
-      <c r="E136" s="111"/>
-      <c r="F136" s="111"/>
-      <c r="G136" s="112"/>
-      <c r="H136" s="183"/>
-      <c r="I136" s="184"/>
+      <c r="D136" s="127"/>
+      <c r="E136" s="128"/>
+      <c r="F136" s="128"/>
+      <c r="G136" s="129"/>
+      <c r="H136" s="190"/>
+      <c r="I136" s="136"/>
       <c r="J136" s="63"/>
       <c r="K136" s="64"/>
       <c r="L136" s="64"/>
@@ -19509,15 +19517,15 @@
       <c r="B137" s="36"/>
       <c r="C137" s="72"/>
       <c r="D137" s="74"/>
-      <c r="E137" s="113" t="s">
+      <c r="E137" s="107" t="s">
         <v>73</v>
       </c>
-      <c r="F137" s="113"/>
-      <c r="G137" s="114"/>
-      <c r="H137" s="95">
+      <c r="F137" s="107"/>
+      <c r="G137" s="108"/>
+      <c r="H137" s="103">
         <v>45636</v>
       </c>
-      <c r="I137" s="101"/>
+      <c r="I137" s="105"/>
       <c r="J137" s="62"/>
       <c r="K137" s="20"/>
       <c r="L137" s="20"/>
@@ -19635,11 +19643,11 @@
       <c r="B138" s="36"/>
       <c r="C138" s="72"/>
       <c r="D138" s="70"/>
-      <c r="E138" s="115"/>
-      <c r="F138" s="115"/>
-      <c r="G138" s="116"/>
-      <c r="H138" s="96"/>
-      <c r="I138" s="102"/>
+      <c r="E138" s="177"/>
+      <c r="F138" s="177"/>
+      <c r="G138" s="178"/>
+      <c r="H138" s="99"/>
+      <c r="I138" s="135"/>
       <c r="J138" s="62"/>
       <c r="K138" s="20"/>
       <c r="L138" s="20"/>
@@ -19757,15 +19765,15 @@
       <c r="B139" s="36"/>
       <c r="C139" s="72"/>
       <c r="D139" s="70"/>
-      <c r="E139" s="113" t="s">
+      <c r="E139" s="107" t="s">
         <v>74</v>
       </c>
-      <c r="F139" s="113"/>
-      <c r="G139" s="114"/>
-      <c r="H139" s="95">
+      <c r="F139" s="107"/>
+      <c r="G139" s="108"/>
+      <c r="H139" s="103">
         <v>45637</v>
       </c>
-      <c r="I139" s="101"/>
+      <c r="I139" s="105"/>
       <c r="J139" s="62"/>
       <c r="K139" s="20"/>
       <c r="L139" s="20"/>
@@ -19883,11 +19891,11 @@
       <c r="B140" s="36"/>
       <c r="C140" s="72"/>
       <c r="D140" s="70"/>
-      <c r="E140" s="117"/>
-      <c r="F140" s="117"/>
-      <c r="G140" s="118"/>
-      <c r="H140" s="96"/>
-      <c r="I140" s="102"/>
+      <c r="E140" s="110"/>
+      <c r="F140" s="110"/>
+      <c r="G140" s="111"/>
+      <c r="H140" s="99"/>
+      <c r="I140" s="135"/>
       <c r="J140" s="62"/>
       <c r="K140" s="20"/>
       <c r="L140" s="20"/>
@@ -20004,13 +20012,13 @@
       <c r="A141" s="16"/>
       <c r="B141" s="36"/>
       <c r="C141" s="82"/>
-      <c r="D141" s="94" t="s">
+      <c r="D141" s="95" t="s">
         <v>80</v>
       </c>
-      <c r="E141" s="94"/>
-      <c r="F141" s="94"/>
-      <c r="G141" s="94"/>
-      <c r="H141" s="95">
+      <c r="E141" s="95"/>
+      <c r="F141" s="95"/>
+      <c r="G141" s="95"/>
+      <c r="H141" s="103">
         <v>45637</v>
       </c>
       <c r="I141" s="92"/>
@@ -20130,11 +20138,11 @@
       <c r="A142" s="16"/>
       <c r="B142" s="36"/>
       <c r="C142" s="82"/>
-      <c r="D142" s="94"/>
-      <c r="E142" s="94"/>
-      <c r="F142" s="94"/>
-      <c r="G142" s="94"/>
-      <c r="H142" s="96"/>
+      <c r="D142" s="95"/>
+      <c r="E142" s="95"/>
+      <c r="F142" s="95"/>
+      <c r="G142" s="95"/>
+      <c r="H142" s="99"/>
       <c r="I142" s="92"/>
       <c r="J142" s="62"/>
       <c r="K142" s="20"/>
@@ -20252,14 +20260,14 @@
       <c r="A143" s="16"/>
       <c r="B143" s="36"/>
       <c r="C143" s="72"/>
-      <c r="D143" s="119" t="s">
+      <c r="D143" s="187" t="s">
         <v>66</v>
       </c>
-      <c r="E143" s="120"/>
-      <c r="F143" s="120"/>
-      <c r="G143" s="121"/>
-      <c r="H143" s="105"/>
-      <c r="I143" s="99"/>
+      <c r="E143" s="188"/>
+      <c r="F143" s="188"/>
+      <c r="G143" s="189"/>
+      <c r="H143" s="185"/>
+      <c r="I143" s="115"/>
       <c r="J143" s="66"/>
       <c r="K143" s="64"/>
       <c r="L143" s="64"/>
@@ -20376,12 +20384,12 @@
       <c r="A144" s="16"/>
       <c r="B144" s="36"/>
       <c r="C144" s="72"/>
-      <c r="D144" s="110"/>
-      <c r="E144" s="111"/>
-      <c r="F144" s="111"/>
-      <c r="G144" s="112"/>
-      <c r="H144" s="106"/>
-      <c r="I144" s="100"/>
+      <c r="D144" s="127"/>
+      <c r="E144" s="128"/>
+      <c r="F144" s="128"/>
+      <c r="G144" s="129"/>
+      <c r="H144" s="186"/>
+      <c r="I144" s="116"/>
       <c r="J144" s="66"/>
       <c r="K144" s="64"/>
       <c r="L144" s="64"/>
@@ -20499,15 +20507,15 @@
       <c r="B145" s="36"/>
       <c r="C145" s="72"/>
       <c r="D145" s="74"/>
-      <c r="E145" s="113" t="s">
+      <c r="E145" s="107" t="s">
         <v>68</v>
       </c>
-      <c r="F145" s="113"/>
-      <c r="G145" s="114"/>
-      <c r="H145" s="95">
+      <c r="F145" s="107"/>
+      <c r="G145" s="108"/>
+      <c r="H145" s="103">
         <v>45639</v>
       </c>
-      <c r="I145" s="101"/>
+      <c r="I145" s="105"/>
       <c r="J145" s="62"/>
       <c r="K145" s="20"/>
       <c r="L145" s="20"/>
@@ -20625,11 +20633,11 @@
       <c r="B146" s="36"/>
       <c r="C146" s="72"/>
       <c r="D146" s="70"/>
-      <c r="E146" s="115"/>
-      <c r="F146" s="115"/>
-      <c r="G146" s="116"/>
-      <c r="H146" s="96"/>
-      <c r="I146" s="102"/>
+      <c r="E146" s="177"/>
+      <c r="F146" s="177"/>
+      <c r="G146" s="178"/>
+      <c r="H146" s="99"/>
+      <c r="I146" s="135"/>
       <c r="J146" s="62"/>
       <c r="K146" s="20"/>
       <c r="L146" s="20"/>
@@ -20747,15 +20755,15 @@
       <c r="B147" s="36"/>
       <c r="C147" s="72"/>
       <c r="D147" s="70"/>
-      <c r="E147" s="113" t="s">
+      <c r="E147" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="F147" s="113"/>
-      <c r="G147" s="114"/>
-      <c r="H147" s="95">
+      <c r="F147" s="107"/>
+      <c r="G147" s="108"/>
+      <c r="H147" s="103">
         <v>45642</v>
       </c>
-      <c r="I147" s="101"/>
+      <c r="I147" s="105"/>
       <c r="J147" s="62"/>
       <c r="K147" s="20"/>
       <c r="L147" s="20"/>
@@ -20873,11 +20881,11 @@
       <c r="B148" s="36"/>
       <c r="C148" s="72"/>
       <c r="D148" s="70"/>
-      <c r="E148" s="115"/>
-      <c r="F148" s="115"/>
-      <c r="G148" s="116"/>
-      <c r="H148" s="96"/>
-      <c r="I148" s="102"/>
+      <c r="E148" s="177"/>
+      <c r="F148" s="177"/>
+      <c r="G148" s="178"/>
+      <c r="H148" s="99"/>
+      <c r="I148" s="135"/>
       <c r="J148" s="62"/>
       <c r="K148" s="20"/>
       <c r="L148" s="20"/>
@@ -20995,15 +21003,15 @@
       <c r="B149" s="36"/>
       <c r="C149" s="72"/>
       <c r="D149" s="70"/>
-      <c r="E149" s="113" t="s">
+      <c r="E149" s="107" t="s">
         <v>70</v>
       </c>
-      <c r="F149" s="113"/>
-      <c r="G149" s="114"/>
-      <c r="H149" s="95">
+      <c r="F149" s="107"/>
+      <c r="G149" s="108"/>
+      <c r="H149" s="103">
         <v>45643</v>
       </c>
-      <c r="I149" s="101"/>
+      <c r="I149" s="105"/>
       <c r="J149" s="62"/>
       <c r="K149" s="20"/>
       <c r="L149" s="20"/>
@@ -21121,11 +21129,11 @@
       <c r="B150" s="36"/>
       <c r="C150" s="72"/>
       <c r="D150" s="70"/>
-      <c r="E150" s="115"/>
-      <c r="F150" s="115"/>
-      <c r="G150" s="116"/>
-      <c r="H150" s="96"/>
-      <c r="I150" s="102"/>
+      <c r="E150" s="177"/>
+      <c r="F150" s="177"/>
+      <c r="G150" s="178"/>
+      <c r="H150" s="99"/>
+      <c r="I150" s="135"/>
       <c r="J150" s="62"/>
       <c r="K150" s="20"/>
       <c r="L150" s="20"/>
@@ -21243,15 +21251,15 @@
       <c r="B151" s="36"/>
       <c r="C151" s="72"/>
       <c r="D151" s="70"/>
-      <c r="E151" s="94" t="s">
+      <c r="E151" s="95" t="s">
         <v>75</v>
       </c>
-      <c r="F151" s="94"/>
-      <c r="G151" s="94"/>
-      <c r="H151" s="95">
+      <c r="F151" s="95"/>
+      <c r="G151" s="95"/>
+      <c r="H151" s="103">
         <v>45644</v>
       </c>
-      <c r="I151" s="101"/>
+      <c r="I151" s="105"/>
       <c r="J151" s="62"/>
       <c r="K151" s="20"/>
       <c r="L151" s="20"/>
@@ -21369,11 +21377,11 @@
       <c r="B152" s="36"/>
       <c r="C152" s="72"/>
       <c r="D152" s="70"/>
-      <c r="E152" s="94"/>
-      <c r="F152" s="94"/>
-      <c r="G152" s="94"/>
-      <c r="H152" s="96"/>
-      <c r="I152" s="102"/>
+      <c r="E152" s="95"/>
+      <c r="F152" s="95"/>
+      <c r="G152" s="95"/>
+      <c r="H152" s="99"/>
+      <c r="I152" s="135"/>
       <c r="J152" s="62"/>
       <c r="K152" s="20"/>
       <c r="L152" s="20"/>
@@ -21491,15 +21499,15 @@
       <c r="B153" s="36"/>
       <c r="C153" s="72"/>
       <c r="D153" s="70"/>
-      <c r="E153" s="94" t="s">
+      <c r="E153" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="F153" s="94"/>
-      <c r="G153" s="94"/>
-      <c r="H153" s="95">
+      <c r="F153" s="95"/>
+      <c r="G153" s="95"/>
+      <c r="H153" s="103">
         <v>45644</v>
       </c>
-      <c r="I153" s="101"/>
+      <c r="I153" s="105"/>
       <c r="J153" s="62"/>
       <c r="K153" s="20"/>
       <c r="L153" s="20"/>
@@ -21617,11 +21625,11 @@
       <c r="B154" s="36"/>
       <c r="C154" s="72"/>
       <c r="D154" s="70"/>
-      <c r="E154" s="94"/>
-      <c r="F154" s="94"/>
-      <c r="G154" s="94"/>
-      <c r="H154" s="96"/>
-      <c r="I154" s="102"/>
+      <c r="E154" s="95"/>
+      <c r="F154" s="95"/>
+      <c r="G154" s="95"/>
+      <c r="H154" s="99"/>
+      <c r="I154" s="135"/>
       <c r="J154" s="62"/>
       <c r="K154" s="20"/>
       <c r="L154" s="20"/>
@@ -21738,16 +21746,16 @@
       <c r="A155" s="1"/>
       <c r="B155" s="18"/>
       <c r="C155" s="60"/>
-      <c r="D155" s="186"/>
-      <c r="E155" s="185" t="s">
+      <c r="D155" s="96"/>
+      <c r="E155" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="F155" s="94"/>
-      <c r="G155" s="94"/>
-      <c r="H155" s="187">
+      <c r="F155" s="95"/>
+      <c r="G155" s="95"/>
+      <c r="H155" s="98">
         <v>45645</v>
       </c>
-      <c r="I155" s="188"/>
+      <c r="I155" s="100"/>
       <c r="J155" s="19"/>
       <c r="K155" s="20"/>
       <c r="L155" s="20"/>
@@ -21864,12 +21872,12 @@
       <c r="A156" s="1"/>
       <c r="B156" s="18"/>
       <c r="C156" s="60"/>
-      <c r="D156" s="175"/>
-      <c r="E156" s="185"/>
-      <c r="F156" s="94"/>
-      <c r="G156" s="94"/>
-      <c r="H156" s="96"/>
-      <c r="I156" s="98"/>
+      <c r="D156" s="97"/>
+      <c r="E156" s="94"/>
+      <c r="F156" s="95"/>
+      <c r="G156" s="95"/>
+      <c r="H156" s="99"/>
+      <c r="I156" s="101"/>
       <c r="J156" s="19"/>
       <c r="K156" s="20"/>
       <c r="L156" s="20"/>
@@ -21986,16 +21994,16 @@
       <c r="A157" s="1"/>
       <c r="B157" s="93"/>
       <c r="C157" s="90"/>
-      <c r="D157" s="94" t="s">
+      <c r="D157" s="95" t="s">
         <v>81</v>
       </c>
-      <c r="E157" s="94"/>
-      <c r="F157" s="94"/>
-      <c r="G157" s="94"/>
-      <c r="H157" s="95">
+      <c r="E157" s="95"/>
+      <c r="F157" s="95"/>
+      <c r="G157" s="95"/>
+      <c r="H157" s="103">
         <v>45644</v>
       </c>
-      <c r="I157" s="97"/>
+      <c r="I157" s="118"/>
       <c r="J157" s="19"/>
       <c r="K157" s="20"/>
       <c r="L157" s="20"/>
@@ -22112,12 +22120,12 @@
       <c r="A158" s="1"/>
       <c r="B158" s="93"/>
       <c r="C158" s="90"/>
-      <c r="D158" s="94"/>
-      <c r="E158" s="94"/>
-      <c r="F158" s="94"/>
-      <c r="G158" s="94"/>
-      <c r="H158" s="96"/>
-      <c r="I158" s="98"/>
+      <c r="D158" s="95"/>
+      <c r="E158" s="95"/>
+      <c r="F158" s="95"/>
+      <c r="G158" s="95"/>
+      <c r="H158" s="99"/>
+      <c r="I158" s="101"/>
       <c r="J158" s="19"/>
       <c r="K158" s="20"/>
       <c r="L158" s="20"/>
@@ -22235,14 +22243,14 @@
       <c r="B159" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="C159" s="156" t="s">
+      <c r="C159" s="143" t="s">
         <v>31</v>
       </c>
-      <c r="D159" s="157"/>
-      <c r="E159" s="157"/>
-      <c r="F159" s="157"/>
-      <c r="G159" s="158"/>
-      <c r="H159" s="166" t="s">
+      <c r="D159" s="144"/>
+      <c r="E159" s="144"/>
+      <c r="F159" s="144"/>
+      <c r="G159" s="145"/>
+      <c r="H159" s="130" t="s">
         <v>57</v>
       </c>
       <c r="I159" s="104"/>
@@ -22361,11 +22369,11 @@
     <row r="160" spans="1:120" ht="9.75" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="87"/>
-      <c r="C160" s="159"/>
-      <c r="D160" s="160"/>
-      <c r="E160" s="160"/>
-      <c r="F160" s="160"/>
-      <c r="G160" s="161"/>
+      <c r="C160" s="146"/>
+      <c r="D160" s="147"/>
+      <c r="E160" s="147"/>
+      <c r="F160" s="147"/>
+      <c r="G160" s="148"/>
       <c r="H160" s="104"/>
       <c r="I160" s="104"/>
       <c r="J160" s="14"/>
@@ -22727,14 +22735,14 @@
     <row r="163" spans="1:120" ht="9.75" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
-      <c r="C163" s="151" t="s">
+      <c r="C163" s="137" t="s">
         <v>33</v>
       </c>
-      <c r="D163" s="131"/>
-      <c r="E163" s="131"/>
-      <c r="F163" s="131"/>
-      <c r="G163" s="152"/>
-      <c r="H163" s="166" t="s">
+      <c r="D163" s="138"/>
+      <c r="E163" s="138"/>
+      <c r="F163" s="138"/>
+      <c r="G163" s="139"/>
+      <c r="H163" s="130" t="s">
         <v>56</v>
       </c>
       <c r="I163" s="104"/>
@@ -22853,11 +22861,11 @@
     <row r="164" spans="1:120" ht="9.75" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
-      <c r="C164" s="153"/>
-      <c r="D164" s="154"/>
-      <c r="E164" s="154"/>
-      <c r="F164" s="154"/>
-      <c r="G164" s="155"/>
+      <c r="C164" s="140"/>
+      <c r="D164" s="141"/>
+      <c r="E164" s="141"/>
+      <c r="F164" s="141"/>
+      <c r="G164" s="142"/>
       <c r="H164" s="104"/>
       <c r="I164" s="104"/>
       <c r="J164" s="19"/>
@@ -36398,6 +36406,222 @@
     </row>
   </sheetData>
   <mergeCells count="240">
+    <mergeCell ref="D157:G158"/>
+    <mergeCell ref="H157:H158"/>
+    <mergeCell ref="I157:I158"/>
+    <mergeCell ref="H141:H142"/>
+    <mergeCell ref="I143:I144"/>
+    <mergeCell ref="I139:I140"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="H103:H104"/>
+    <mergeCell ref="I103:I104"/>
+    <mergeCell ref="H115:H116"/>
+    <mergeCell ref="I115:I116"/>
+    <mergeCell ref="D103:G104"/>
+    <mergeCell ref="D115:G116"/>
+    <mergeCell ref="D131:G132"/>
+    <mergeCell ref="H131:H132"/>
+    <mergeCell ref="I131:I132"/>
+    <mergeCell ref="D87:G88"/>
+    <mergeCell ref="D141:G142"/>
+    <mergeCell ref="E153:G154"/>
+    <mergeCell ref="H153:H154"/>
+    <mergeCell ref="H151:H152"/>
+    <mergeCell ref="H149:H150"/>
+    <mergeCell ref="H147:H148"/>
+    <mergeCell ref="H145:H146"/>
+    <mergeCell ref="H143:H144"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="C133:G134"/>
+    <mergeCell ref="D135:G136"/>
+    <mergeCell ref="E137:G138"/>
+    <mergeCell ref="E139:G140"/>
+    <mergeCell ref="D143:G144"/>
+    <mergeCell ref="E145:G146"/>
+    <mergeCell ref="H135:H136"/>
+    <mergeCell ref="E147:G148"/>
+    <mergeCell ref="E149:G150"/>
+    <mergeCell ref="E151:G152"/>
+    <mergeCell ref="E59:G60"/>
+    <mergeCell ref="E61:G62"/>
+    <mergeCell ref="D63:G64"/>
+    <mergeCell ref="E67:G68"/>
+    <mergeCell ref="E65:G66"/>
+    <mergeCell ref="E69:G70"/>
+    <mergeCell ref="E71:G72"/>
+    <mergeCell ref="C73:G74"/>
+    <mergeCell ref="C75:G76"/>
+    <mergeCell ref="C77:G78"/>
+    <mergeCell ref="D79:G80"/>
+    <mergeCell ref="E109:G110"/>
+    <mergeCell ref="E111:G112"/>
+    <mergeCell ref="E101:G102"/>
+    <mergeCell ref="C105:G106"/>
+    <mergeCell ref="D107:G108"/>
+    <mergeCell ref="D117:G118"/>
+    <mergeCell ref="D13:G14"/>
+    <mergeCell ref="D15:G16"/>
+    <mergeCell ref="D17:G18"/>
+    <mergeCell ref="D19:G20"/>
+    <mergeCell ref="C21:G22"/>
+    <mergeCell ref="D23:G24"/>
+    <mergeCell ref="C25:G26"/>
+    <mergeCell ref="D27:G28"/>
+    <mergeCell ref="D29:G30"/>
+    <mergeCell ref="J3:CJ3"/>
+    <mergeCell ref="CK3:DO3"/>
+    <mergeCell ref="J4:AA4"/>
+    <mergeCell ref="AB4:BE4"/>
+    <mergeCell ref="BF4:CJ4"/>
+    <mergeCell ref="CK4:DO4"/>
+    <mergeCell ref="B7:G8"/>
+    <mergeCell ref="C9:G10"/>
+    <mergeCell ref="C11:G12"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="C163:G164"/>
+    <mergeCell ref="C159:G160"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="C31:G32"/>
+    <mergeCell ref="D33:G34"/>
+    <mergeCell ref="E35:G36"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="E43:G44"/>
+    <mergeCell ref="E45:G46"/>
+    <mergeCell ref="E47:G48"/>
+    <mergeCell ref="E49:G50"/>
+    <mergeCell ref="E51:G52"/>
+    <mergeCell ref="D53:G54"/>
+    <mergeCell ref="E55:G56"/>
+    <mergeCell ref="E57:G58"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I67:I68"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="I159:I160"/>
+    <mergeCell ref="I161:I162"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="I93:I94"/>
+    <mergeCell ref="I95:I96"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="I109:I110"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="I153:I154"/>
+    <mergeCell ref="I151:I152"/>
+    <mergeCell ref="I149:I150"/>
+    <mergeCell ref="I147:I148"/>
+    <mergeCell ref="I145:I146"/>
+    <mergeCell ref="I111:I112"/>
+    <mergeCell ref="I135:I136"/>
+    <mergeCell ref="I163:I164"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="H75:H76"/>
+    <mergeCell ref="H159:H160"/>
+    <mergeCell ref="H163:H164"/>
+    <mergeCell ref="H161:H162"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="H59:H60"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="H77:H78"/>
+    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="H93:H94"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="H111:H112"/>
+    <mergeCell ref="H101:H102"/>
+    <mergeCell ref="I101:I102"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="I85:I86"/>
+    <mergeCell ref="H89:H90"/>
+    <mergeCell ref="I89:I90"/>
+    <mergeCell ref="E81:G82"/>
+    <mergeCell ref="E83:G84"/>
+    <mergeCell ref="E91:G92"/>
+    <mergeCell ref="E93:G94"/>
+    <mergeCell ref="E95:G96"/>
+    <mergeCell ref="E97:G98"/>
+    <mergeCell ref="E99:G100"/>
+    <mergeCell ref="E85:G86"/>
+    <mergeCell ref="D89:G90"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="H105:H106"/>
+    <mergeCell ref="I105:I106"/>
+    <mergeCell ref="H107:H108"/>
+    <mergeCell ref="I107:I108"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="H117:H118"/>
+    <mergeCell ref="I117:I118"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="I119:I120"/>
     <mergeCell ref="E155:G156"/>
     <mergeCell ref="D155:D156"/>
     <mergeCell ref="H155:H156"/>
@@ -36422,222 +36646,6 @@
     <mergeCell ref="H127:H128"/>
     <mergeCell ref="I127:I128"/>
     <mergeCell ref="H121:H122"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="H105:H106"/>
-    <mergeCell ref="I105:I106"/>
-    <mergeCell ref="H107:H108"/>
-    <mergeCell ref="I107:I108"/>
-    <mergeCell ref="H109:H110"/>
-    <mergeCell ref="H117:H118"/>
-    <mergeCell ref="I117:I118"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="I119:I120"/>
-    <mergeCell ref="H101:H102"/>
-    <mergeCell ref="I101:I102"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="I85:I86"/>
-    <mergeCell ref="H89:H90"/>
-    <mergeCell ref="I89:I90"/>
-    <mergeCell ref="E81:G82"/>
-    <mergeCell ref="E83:G84"/>
-    <mergeCell ref="E91:G92"/>
-    <mergeCell ref="E93:G94"/>
-    <mergeCell ref="E95:G96"/>
-    <mergeCell ref="E97:G98"/>
-    <mergeCell ref="E99:G100"/>
-    <mergeCell ref="E85:G86"/>
-    <mergeCell ref="D89:G90"/>
-    <mergeCell ref="H75:H76"/>
-    <mergeCell ref="H159:H160"/>
-    <mergeCell ref="H163:H164"/>
-    <mergeCell ref="H161:H162"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="H67:H68"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H59:H60"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="H77:H78"/>
-    <mergeCell ref="H81:H82"/>
-    <mergeCell ref="H83:H84"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="H93:H94"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="H111:H112"/>
-    <mergeCell ref="I163:I164"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="I159:I160"/>
-    <mergeCell ref="I161:I162"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="I93:I94"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="I109:I110"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="I153:I154"/>
-    <mergeCell ref="I151:I152"/>
-    <mergeCell ref="I149:I150"/>
-    <mergeCell ref="I147:I148"/>
-    <mergeCell ref="I145:I146"/>
-    <mergeCell ref="I111:I112"/>
-    <mergeCell ref="I135:I136"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="C163:G164"/>
-    <mergeCell ref="C159:G160"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="C31:G32"/>
-    <mergeCell ref="D33:G34"/>
-    <mergeCell ref="E35:G36"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="E43:G44"/>
-    <mergeCell ref="E45:G46"/>
-    <mergeCell ref="E47:G48"/>
-    <mergeCell ref="E49:G50"/>
-    <mergeCell ref="E51:G52"/>
-    <mergeCell ref="D53:G54"/>
-    <mergeCell ref="E55:G56"/>
-    <mergeCell ref="E57:G58"/>
-    <mergeCell ref="I53:I54"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="J3:CJ3"/>
-    <mergeCell ref="CK3:DO3"/>
-    <mergeCell ref="J4:AA4"/>
-    <mergeCell ref="AB4:BE4"/>
-    <mergeCell ref="BF4:CJ4"/>
-    <mergeCell ref="CK4:DO4"/>
-    <mergeCell ref="B7:G8"/>
-    <mergeCell ref="C9:G10"/>
-    <mergeCell ref="C11:G12"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="D13:G14"/>
-    <mergeCell ref="D15:G16"/>
-    <mergeCell ref="D17:G18"/>
-    <mergeCell ref="D19:G20"/>
-    <mergeCell ref="C21:G22"/>
-    <mergeCell ref="D23:G24"/>
-    <mergeCell ref="C25:G26"/>
-    <mergeCell ref="D27:G28"/>
-    <mergeCell ref="D29:G30"/>
-    <mergeCell ref="E147:G148"/>
-    <mergeCell ref="E149:G150"/>
-    <mergeCell ref="E151:G152"/>
-    <mergeCell ref="E59:G60"/>
-    <mergeCell ref="E61:G62"/>
-    <mergeCell ref="D63:G64"/>
-    <mergeCell ref="E67:G68"/>
-    <mergeCell ref="E65:G66"/>
-    <mergeCell ref="E69:G70"/>
-    <mergeCell ref="E71:G72"/>
-    <mergeCell ref="C73:G74"/>
-    <mergeCell ref="C75:G76"/>
-    <mergeCell ref="C77:G78"/>
-    <mergeCell ref="D79:G80"/>
-    <mergeCell ref="E109:G110"/>
-    <mergeCell ref="E111:G112"/>
-    <mergeCell ref="E101:G102"/>
-    <mergeCell ref="C105:G106"/>
-    <mergeCell ref="D107:G108"/>
-    <mergeCell ref="D117:G118"/>
-    <mergeCell ref="H145:H146"/>
-    <mergeCell ref="H143:H144"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="C133:G134"/>
-    <mergeCell ref="D135:G136"/>
-    <mergeCell ref="E137:G138"/>
-    <mergeCell ref="E139:G140"/>
-    <mergeCell ref="D143:G144"/>
-    <mergeCell ref="E145:G146"/>
-    <mergeCell ref="H135:H136"/>
-    <mergeCell ref="D157:G158"/>
-    <mergeCell ref="H157:H158"/>
-    <mergeCell ref="I157:I158"/>
-    <mergeCell ref="H141:H142"/>
-    <mergeCell ref="I143:I144"/>
-    <mergeCell ref="I139:I140"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="H103:H104"/>
-    <mergeCell ref="I103:I104"/>
-    <mergeCell ref="H115:H116"/>
-    <mergeCell ref="I115:I116"/>
-    <mergeCell ref="D103:G104"/>
-    <mergeCell ref="D115:G116"/>
-    <mergeCell ref="D131:G132"/>
-    <mergeCell ref="H131:H132"/>
-    <mergeCell ref="I131:I132"/>
-    <mergeCell ref="D87:G88"/>
-    <mergeCell ref="D141:G142"/>
-    <mergeCell ref="E153:G154"/>
-    <mergeCell ref="H153:H154"/>
-    <mergeCell ref="H151:H152"/>
-    <mergeCell ref="H149:H150"/>
-    <mergeCell ref="H147:H148"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <conditionalFormatting sqref="J7">

--- a/docs/【DIGITAL OJT】WBS.xlsx
+++ b/docs/【DIGITAL OJT】WBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIGITALOJT\digital-ojt-development-cause-DroneInventorySystem\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCAC5C8C-0222-435C-ADF3-82888E70F148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E77BC1D-D0C3-4415-B16B-D2FFB11BDC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16905" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14940" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -1481,67 +1481,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1550,25 +1502,22 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1589,29 +1538,110 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1637,92 +1667,62 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2330,120 +2330,120 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="J3" s="165">
+      <c r="J3" s="153">
         <v>2024</v>
       </c>
-      <c r="K3" s="166"/>
-      <c r="L3" s="166"/>
-      <c r="M3" s="166"/>
-      <c r="N3" s="166"/>
-      <c r="O3" s="166"/>
-      <c r="P3" s="166"/>
-      <c r="Q3" s="166"/>
-      <c r="R3" s="166"/>
-      <c r="S3" s="166"/>
-      <c r="T3" s="166"/>
-      <c r="U3" s="166"/>
-      <c r="V3" s="166"/>
-      <c r="W3" s="166"/>
-      <c r="X3" s="166"/>
-      <c r="Y3" s="166"/>
-      <c r="Z3" s="166"/>
-      <c r="AA3" s="166"/>
-      <c r="AB3" s="166"/>
-      <c r="AC3" s="166"/>
-      <c r="AD3" s="166"/>
-      <c r="AE3" s="166"/>
-      <c r="AF3" s="166"/>
-      <c r="AG3" s="166"/>
-      <c r="AH3" s="166"/>
-      <c r="AI3" s="166"/>
-      <c r="AJ3" s="166"/>
-      <c r="AK3" s="166"/>
-      <c r="AL3" s="166"/>
-      <c r="AM3" s="166"/>
-      <c r="AN3" s="166"/>
-      <c r="AO3" s="166"/>
-      <c r="AP3" s="166"/>
-      <c r="AQ3" s="166"/>
-      <c r="AR3" s="166"/>
-      <c r="AS3" s="166"/>
-      <c r="AT3" s="166"/>
-      <c r="AU3" s="166"/>
-      <c r="AV3" s="166"/>
-      <c r="AW3" s="166"/>
-      <c r="AX3" s="166"/>
-      <c r="AY3" s="166"/>
-      <c r="AZ3" s="166"/>
-      <c r="BA3" s="166"/>
-      <c r="BB3" s="166"/>
-      <c r="BC3" s="166"/>
-      <c r="BD3" s="166"/>
-      <c r="BE3" s="166"/>
-      <c r="BF3" s="166"/>
-      <c r="BG3" s="166"/>
-      <c r="BH3" s="166"/>
-      <c r="BI3" s="166"/>
-      <c r="BJ3" s="166"/>
-      <c r="BK3" s="166"/>
-      <c r="BL3" s="166"/>
-      <c r="BM3" s="166"/>
-      <c r="BN3" s="166"/>
-      <c r="BO3" s="166"/>
-      <c r="BP3" s="166"/>
-      <c r="BQ3" s="166"/>
-      <c r="BR3" s="166"/>
-      <c r="BS3" s="166"/>
-      <c r="BT3" s="166"/>
-      <c r="BU3" s="166"/>
-      <c r="BV3" s="166"/>
-      <c r="BW3" s="166"/>
-      <c r="BX3" s="166"/>
-      <c r="BY3" s="166"/>
-      <c r="BZ3" s="166"/>
-      <c r="CA3" s="166"/>
-      <c r="CB3" s="166"/>
-      <c r="CC3" s="166"/>
-      <c r="CD3" s="166"/>
-      <c r="CE3" s="166"/>
-      <c r="CF3" s="166"/>
-      <c r="CG3" s="166"/>
-      <c r="CH3" s="166"/>
-      <c r="CI3" s="166"/>
-      <c r="CJ3" s="167"/>
-      <c r="CK3" s="165">
+      <c r="K3" s="154"/>
+      <c r="L3" s="154"/>
+      <c r="M3" s="154"/>
+      <c r="N3" s="154"/>
+      <c r="O3" s="154"/>
+      <c r="P3" s="154"/>
+      <c r="Q3" s="154"/>
+      <c r="R3" s="154"/>
+      <c r="S3" s="154"/>
+      <c r="T3" s="154"/>
+      <c r="U3" s="154"/>
+      <c r="V3" s="154"/>
+      <c r="W3" s="154"/>
+      <c r="X3" s="154"/>
+      <c r="Y3" s="154"/>
+      <c r="Z3" s="154"/>
+      <c r="AA3" s="154"/>
+      <c r="AB3" s="154"/>
+      <c r="AC3" s="154"/>
+      <c r="AD3" s="154"/>
+      <c r="AE3" s="154"/>
+      <c r="AF3" s="154"/>
+      <c r="AG3" s="154"/>
+      <c r="AH3" s="154"/>
+      <c r="AI3" s="154"/>
+      <c r="AJ3" s="154"/>
+      <c r="AK3" s="154"/>
+      <c r="AL3" s="154"/>
+      <c r="AM3" s="154"/>
+      <c r="AN3" s="154"/>
+      <c r="AO3" s="154"/>
+      <c r="AP3" s="154"/>
+      <c r="AQ3" s="154"/>
+      <c r="AR3" s="154"/>
+      <c r="AS3" s="154"/>
+      <c r="AT3" s="154"/>
+      <c r="AU3" s="154"/>
+      <c r="AV3" s="154"/>
+      <c r="AW3" s="154"/>
+      <c r="AX3" s="154"/>
+      <c r="AY3" s="154"/>
+      <c r="AZ3" s="154"/>
+      <c r="BA3" s="154"/>
+      <c r="BB3" s="154"/>
+      <c r="BC3" s="154"/>
+      <c r="BD3" s="154"/>
+      <c r="BE3" s="154"/>
+      <c r="BF3" s="154"/>
+      <c r="BG3" s="154"/>
+      <c r="BH3" s="154"/>
+      <c r="BI3" s="154"/>
+      <c r="BJ3" s="154"/>
+      <c r="BK3" s="154"/>
+      <c r="BL3" s="154"/>
+      <c r="BM3" s="154"/>
+      <c r="BN3" s="154"/>
+      <c r="BO3" s="154"/>
+      <c r="BP3" s="154"/>
+      <c r="BQ3" s="154"/>
+      <c r="BR3" s="154"/>
+      <c r="BS3" s="154"/>
+      <c r="BT3" s="154"/>
+      <c r="BU3" s="154"/>
+      <c r="BV3" s="154"/>
+      <c r="BW3" s="154"/>
+      <c r="BX3" s="154"/>
+      <c r="BY3" s="154"/>
+      <c r="BZ3" s="154"/>
+      <c r="CA3" s="154"/>
+      <c r="CB3" s="154"/>
+      <c r="CC3" s="154"/>
+      <c r="CD3" s="154"/>
+      <c r="CE3" s="154"/>
+      <c r="CF3" s="154"/>
+      <c r="CG3" s="154"/>
+      <c r="CH3" s="154"/>
+      <c r="CI3" s="154"/>
+      <c r="CJ3" s="155"/>
+      <c r="CK3" s="153">
         <v>2025</v>
       </c>
-      <c r="CL3" s="166"/>
-      <c r="CM3" s="166"/>
-      <c r="CN3" s="166"/>
-      <c r="CO3" s="166"/>
-      <c r="CP3" s="166"/>
-      <c r="CQ3" s="166"/>
-      <c r="CR3" s="166"/>
-      <c r="CS3" s="166"/>
-      <c r="CT3" s="166"/>
-      <c r="CU3" s="166"/>
-      <c r="CV3" s="166"/>
-      <c r="CW3" s="166"/>
-      <c r="CX3" s="166"/>
-      <c r="CY3" s="166"/>
-      <c r="CZ3" s="166"/>
-      <c r="DA3" s="166"/>
-      <c r="DB3" s="166"/>
-      <c r="DC3" s="166"/>
-      <c r="DD3" s="166"/>
-      <c r="DE3" s="166"/>
-      <c r="DF3" s="166"/>
-      <c r="DG3" s="166"/>
-      <c r="DH3" s="166"/>
-      <c r="DI3" s="166"/>
-      <c r="DJ3" s="166"/>
-      <c r="DK3" s="166"/>
-      <c r="DL3" s="166"/>
-      <c r="DM3" s="166"/>
-      <c r="DN3" s="166"/>
-      <c r="DO3" s="167"/>
+      <c r="CL3" s="154"/>
+      <c r="CM3" s="154"/>
+      <c r="CN3" s="154"/>
+      <c r="CO3" s="154"/>
+      <c r="CP3" s="154"/>
+      <c r="CQ3" s="154"/>
+      <c r="CR3" s="154"/>
+      <c r="CS3" s="154"/>
+      <c r="CT3" s="154"/>
+      <c r="CU3" s="154"/>
+      <c r="CV3" s="154"/>
+      <c r="CW3" s="154"/>
+      <c r="CX3" s="154"/>
+      <c r="CY3" s="154"/>
+      <c r="CZ3" s="154"/>
+      <c r="DA3" s="154"/>
+      <c r="DB3" s="154"/>
+      <c r="DC3" s="154"/>
+      <c r="DD3" s="154"/>
+      <c r="DE3" s="154"/>
+      <c r="DF3" s="154"/>
+      <c r="DG3" s="154"/>
+      <c r="DH3" s="154"/>
+      <c r="DI3" s="154"/>
+      <c r="DJ3" s="154"/>
+      <c r="DK3" s="154"/>
+      <c r="DL3" s="154"/>
+      <c r="DM3" s="154"/>
+      <c r="DN3" s="154"/>
+      <c r="DO3" s="155"/>
       <c r="DP3" s="1"/>
     </row>
     <row r="4" spans="1:120" ht="18" customHeight="1">
@@ -2458,124 +2458,124 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="J4" s="165">
+      <c r="J4" s="153">
         <v>10</v>
       </c>
-      <c r="K4" s="166"/>
-      <c r="L4" s="166"/>
-      <c r="M4" s="166"/>
-      <c r="N4" s="166"/>
-      <c r="O4" s="166"/>
-      <c r="P4" s="166"/>
-      <c r="Q4" s="166"/>
-      <c r="R4" s="166"/>
-      <c r="S4" s="166"/>
-      <c r="T4" s="166"/>
-      <c r="U4" s="166"/>
-      <c r="V4" s="166"/>
-      <c r="W4" s="166"/>
-      <c r="X4" s="166"/>
-      <c r="Y4" s="166"/>
-      <c r="Z4" s="166"/>
-      <c r="AA4" s="167"/>
-      <c r="AB4" s="165">
+      <c r="K4" s="154"/>
+      <c r="L4" s="154"/>
+      <c r="M4" s="154"/>
+      <c r="N4" s="154"/>
+      <c r="O4" s="154"/>
+      <c r="P4" s="154"/>
+      <c r="Q4" s="154"/>
+      <c r="R4" s="154"/>
+      <c r="S4" s="154"/>
+      <c r="T4" s="154"/>
+      <c r="U4" s="154"/>
+      <c r="V4" s="154"/>
+      <c r="W4" s="154"/>
+      <c r="X4" s="154"/>
+      <c r="Y4" s="154"/>
+      <c r="Z4" s="154"/>
+      <c r="AA4" s="155"/>
+      <c r="AB4" s="153">
         <v>11</v>
       </c>
-      <c r="AC4" s="166"/>
-      <c r="AD4" s="166"/>
-      <c r="AE4" s="166"/>
-      <c r="AF4" s="166"/>
-      <c r="AG4" s="166"/>
-      <c r="AH4" s="166"/>
-      <c r="AI4" s="166"/>
-      <c r="AJ4" s="166"/>
-      <c r="AK4" s="166"/>
-      <c r="AL4" s="166"/>
-      <c r="AM4" s="166"/>
-      <c r="AN4" s="166"/>
-      <c r="AO4" s="166"/>
-      <c r="AP4" s="166"/>
-      <c r="AQ4" s="166"/>
-      <c r="AR4" s="166"/>
-      <c r="AS4" s="166"/>
-      <c r="AT4" s="166"/>
-      <c r="AU4" s="166"/>
-      <c r="AV4" s="166"/>
-      <c r="AW4" s="166"/>
-      <c r="AX4" s="166"/>
-      <c r="AY4" s="166"/>
-      <c r="AZ4" s="166"/>
-      <c r="BA4" s="166"/>
-      <c r="BB4" s="166"/>
-      <c r="BC4" s="166"/>
-      <c r="BD4" s="166"/>
-      <c r="BE4" s="167"/>
-      <c r="BF4" s="165">
+      <c r="AC4" s="154"/>
+      <c r="AD4" s="154"/>
+      <c r="AE4" s="154"/>
+      <c r="AF4" s="154"/>
+      <c r="AG4" s="154"/>
+      <c r="AH4" s="154"/>
+      <c r="AI4" s="154"/>
+      <c r="AJ4" s="154"/>
+      <c r="AK4" s="154"/>
+      <c r="AL4" s="154"/>
+      <c r="AM4" s="154"/>
+      <c r="AN4" s="154"/>
+      <c r="AO4" s="154"/>
+      <c r="AP4" s="154"/>
+      <c r="AQ4" s="154"/>
+      <c r="AR4" s="154"/>
+      <c r="AS4" s="154"/>
+      <c r="AT4" s="154"/>
+      <c r="AU4" s="154"/>
+      <c r="AV4" s="154"/>
+      <c r="AW4" s="154"/>
+      <c r="AX4" s="154"/>
+      <c r="AY4" s="154"/>
+      <c r="AZ4" s="154"/>
+      <c r="BA4" s="154"/>
+      <c r="BB4" s="154"/>
+      <c r="BC4" s="154"/>
+      <c r="BD4" s="154"/>
+      <c r="BE4" s="155"/>
+      <c r="BF4" s="153">
         <v>12</v>
       </c>
-      <c r="BG4" s="166"/>
-      <c r="BH4" s="166"/>
-      <c r="BI4" s="166"/>
-      <c r="BJ4" s="166"/>
-      <c r="BK4" s="166"/>
-      <c r="BL4" s="166"/>
-      <c r="BM4" s="166"/>
-      <c r="BN4" s="166"/>
-      <c r="BO4" s="166"/>
-      <c r="BP4" s="166"/>
-      <c r="BQ4" s="166"/>
-      <c r="BR4" s="166"/>
-      <c r="BS4" s="166"/>
-      <c r="BT4" s="166"/>
-      <c r="BU4" s="166"/>
-      <c r="BV4" s="166"/>
-      <c r="BW4" s="166"/>
-      <c r="BX4" s="166"/>
-      <c r="BY4" s="166"/>
-      <c r="BZ4" s="166"/>
-      <c r="CA4" s="166"/>
-      <c r="CB4" s="166"/>
-      <c r="CC4" s="166"/>
-      <c r="CD4" s="166"/>
-      <c r="CE4" s="166"/>
-      <c r="CF4" s="166"/>
-      <c r="CG4" s="166"/>
-      <c r="CH4" s="166"/>
-      <c r="CI4" s="166"/>
-      <c r="CJ4" s="167"/>
-      <c r="CK4" s="165">
+      <c r="BG4" s="154"/>
+      <c r="BH4" s="154"/>
+      <c r="BI4" s="154"/>
+      <c r="BJ4" s="154"/>
+      <c r="BK4" s="154"/>
+      <c r="BL4" s="154"/>
+      <c r="BM4" s="154"/>
+      <c r="BN4" s="154"/>
+      <c r="BO4" s="154"/>
+      <c r="BP4" s="154"/>
+      <c r="BQ4" s="154"/>
+      <c r="BR4" s="154"/>
+      <c r="BS4" s="154"/>
+      <c r="BT4" s="154"/>
+      <c r="BU4" s="154"/>
+      <c r="BV4" s="154"/>
+      <c r="BW4" s="154"/>
+      <c r="BX4" s="154"/>
+      <c r="BY4" s="154"/>
+      <c r="BZ4" s="154"/>
+      <c r="CA4" s="154"/>
+      <c r="CB4" s="154"/>
+      <c r="CC4" s="154"/>
+      <c r="CD4" s="154"/>
+      <c r="CE4" s="154"/>
+      <c r="CF4" s="154"/>
+      <c r="CG4" s="154"/>
+      <c r="CH4" s="154"/>
+      <c r="CI4" s="154"/>
+      <c r="CJ4" s="155"/>
+      <c r="CK4" s="153">
         <v>1</v>
       </c>
-      <c r="CL4" s="166"/>
-      <c r="CM4" s="166"/>
-      <c r="CN4" s="166"/>
-      <c r="CO4" s="166"/>
-      <c r="CP4" s="166"/>
-      <c r="CQ4" s="166"/>
-      <c r="CR4" s="166"/>
-      <c r="CS4" s="166"/>
-      <c r="CT4" s="166"/>
-      <c r="CU4" s="166"/>
-      <c r="CV4" s="166"/>
-      <c r="CW4" s="166"/>
-      <c r="CX4" s="166"/>
-      <c r="CY4" s="166"/>
-      <c r="CZ4" s="166"/>
-      <c r="DA4" s="166"/>
-      <c r="DB4" s="166"/>
-      <c r="DC4" s="166"/>
-      <c r="DD4" s="166"/>
-      <c r="DE4" s="166"/>
-      <c r="DF4" s="166"/>
-      <c r="DG4" s="166"/>
-      <c r="DH4" s="166"/>
-      <c r="DI4" s="166"/>
-      <c r="DJ4" s="166"/>
-      <c r="DK4" s="166"/>
-      <c r="DL4" s="166"/>
-      <c r="DM4" s="166"/>
-      <c r="DN4" s="166"/>
-      <c r="DO4" s="167"/>
+      <c r="CL4" s="154"/>
+      <c r="CM4" s="154"/>
+      <c r="CN4" s="154"/>
+      <c r="CO4" s="154"/>
+      <c r="CP4" s="154"/>
+      <c r="CQ4" s="154"/>
+      <c r="CR4" s="154"/>
+      <c r="CS4" s="154"/>
+      <c r="CT4" s="154"/>
+      <c r="CU4" s="154"/>
+      <c r="CV4" s="154"/>
+      <c r="CW4" s="154"/>
+      <c r="CX4" s="154"/>
+      <c r="CY4" s="154"/>
+      <c r="CZ4" s="154"/>
+      <c r="DA4" s="154"/>
+      <c r="DB4" s="154"/>
+      <c r="DC4" s="154"/>
+      <c r="DD4" s="154"/>
+      <c r="DE4" s="154"/>
+      <c r="DF4" s="154"/>
+      <c r="DG4" s="154"/>
+      <c r="DH4" s="154"/>
+      <c r="DI4" s="154"/>
+      <c r="DJ4" s="154"/>
+      <c r="DK4" s="154"/>
+      <c r="DL4" s="154"/>
+      <c r="DM4" s="154"/>
+      <c r="DN4" s="154"/>
+      <c r="DO4" s="155"/>
       <c r="DP4" s="6"/>
     </row>
     <row r="5" spans="1:120" ht="18" customHeight="1">
@@ -3370,18 +3370,18 @@
     </row>
     <row r="7" spans="1:120" ht="9.75" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="168" t="s">
+      <c r="B7" s="156" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="156"/>
-      <c r="D7" s="156"/>
-      <c r="E7" s="156"/>
-      <c r="F7" s="156"/>
-      <c r="G7" s="169"/>
-      <c r="H7" s="134" t="s">
+      <c r="C7" s="124"/>
+      <c r="D7" s="124"/>
+      <c r="E7" s="124"/>
+      <c r="F7" s="124"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="158" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="134" t="s">
+      <c r="I7" s="158" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="38"/>
@@ -3498,14 +3498,14 @@
     </row>
     <row r="8" spans="1:120" ht="9.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="158"/>
-      <c r="C8" s="159"/>
-      <c r="D8" s="159"/>
-      <c r="E8" s="159"/>
-      <c r="F8" s="159"/>
-      <c r="G8" s="160"/>
-      <c r="H8" s="134"/>
-      <c r="I8" s="134"/>
+      <c r="B8" s="126"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="127"/>
+      <c r="E8" s="127"/>
+      <c r="F8" s="127"/>
+      <c r="G8" s="131"/>
+      <c r="H8" s="158"/>
+      <c r="I8" s="158"/>
       <c r="J8" s="39"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
@@ -3621,15 +3621,15 @@
     <row r="9" spans="1:120" ht="9.75" customHeight="1">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
-      <c r="C9" s="170" t="s">
+      <c r="C9" s="157" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="150"/>
-      <c r="E9" s="150"/>
-      <c r="F9" s="150"/>
-      <c r="G9" s="154"/>
-      <c r="H9" s="131"/>
-      <c r="I9" s="131"/>
+      <c r="D9" s="146"/>
+      <c r="E9" s="146"/>
+      <c r="F9" s="146"/>
+      <c r="G9" s="134"/>
+      <c r="H9" s="159"/>
+      <c r="I9" s="159"/>
       <c r="J9" s="42"/>
       <c r="K9" s="42"/>
       <c r="L9" s="44"/>
@@ -3745,13 +3745,13 @@
     <row r="10" spans="1:120" ht="9.75" customHeight="1">
       <c r="A10" s="16"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="171"/>
-      <c r="D10" s="159"/>
-      <c r="E10" s="159"/>
-      <c r="F10" s="159"/>
-      <c r="G10" s="160"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="131"/>
+      <c r="C10" s="133"/>
+      <c r="D10" s="127"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="131"/>
+      <c r="H10" s="159"/>
+      <c r="I10" s="159"/>
       <c r="J10" s="46"/>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
@@ -3867,15 +3867,15 @@
     <row r="11" spans="1:120" ht="9.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="172" t="s">
+      <c r="C11" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="150"/>
-      <c r="E11" s="150"/>
-      <c r="F11" s="150"/>
-      <c r="G11" s="154"/>
-      <c r="H11" s="131"/>
-      <c r="I11" s="131"/>
+      <c r="D11" s="146"/>
+      <c r="E11" s="146"/>
+      <c r="F11" s="146"/>
+      <c r="G11" s="134"/>
+      <c r="H11" s="159"/>
+      <c r="I11" s="159"/>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
       <c r="L11" s="44"/>
@@ -3991,13 +3991,13 @@
     <row r="12" spans="1:120" ht="9.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="171"/>
-      <c r="D12" s="159"/>
-      <c r="E12" s="159"/>
-      <c r="F12" s="159"/>
-      <c r="G12" s="160"/>
-      <c r="H12" s="131"/>
-      <c r="I12" s="131"/>
+      <c r="C12" s="133"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="127"/>
+      <c r="G12" s="131"/>
+      <c r="H12" s="159"/>
+      <c r="I12" s="159"/>
       <c r="J12" s="46"/>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
@@ -4114,13 +4114,13 @@
       <c r="A13" s="1"/>
       <c r="B13" s="18"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="173" t="s">
+      <c r="D13" s="143" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="156"/>
-      <c r="F13" s="156"/>
-      <c r="G13" s="169"/>
-      <c r="H13" s="130" t="s">
+      <c r="E13" s="124"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="144"/>
+      <c r="H13" s="176" t="s">
         <v>40</v>
       </c>
       <c r="I13" s="104">
@@ -4242,10 +4242,10 @@
       <c r="A14" s="1"/>
       <c r="B14" s="18"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="158"/>
-      <c r="E14" s="159"/>
-      <c r="F14" s="159"/>
-      <c r="G14" s="160"/>
+      <c r="D14" s="126"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="131"/>
       <c r="H14" s="104"/>
       <c r="I14" s="104"/>
       <c r="J14" s="39"/>
@@ -4364,13 +4364,13 @@
       <c r="A15" s="1"/>
       <c r="B15" s="18"/>
       <c r="C15" s="24"/>
-      <c r="D15" s="173" t="s">
+      <c r="D15" s="143" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="156"/>
-      <c r="F15" s="156"/>
-      <c r="G15" s="162"/>
-      <c r="H15" s="130" t="s">
+      <c r="E15" s="124"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="176" t="s">
         <v>40</v>
       </c>
       <c r="I15" s="104">
@@ -4492,10 +4492,10 @@
       <c r="A16" s="1"/>
       <c r="B16" s="18"/>
       <c r="C16" s="24"/>
-      <c r="D16" s="158"/>
-      <c r="E16" s="159"/>
-      <c r="F16" s="159"/>
-      <c r="G16" s="163"/>
+      <c r="D16" s="126"/>
+      <c r="E16" s="127"/>
+      <c r="F16" s="127"/>
+      <c r="G16" s="128"/>
       <c r="H16" s="104"/>
       <c r="I16" s="104"/>
       <c r="J16" s="14"/>
@@ -4614,13 +4614,13 @@
       <c r="A17" s="1"/>
       <c r="B17" s="18"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="173" t="s">
+      <c r="D17" s="143" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="156"/>
-      <c r="F17" s="156"/>
-      <c r="G17" s="162"/>
-      <c r="H17" s="130" t="s">
+      <c r="E17" s="124"/>
+      <c r="F17" s="124"/>
+      <c r="G17" s="125"/>
+      <c r="H17" s="176" t="s">
         <v>40</v>
       </c>
       <c r="I17" s="104">
@@ -4742,10 +4742,10 @@
       <c r="A18" s="1"/>
       <c r="B18" s="18"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="158"/>
-      <c r="E18" s="159"/>
-      <c r="F18" s="159"/>
-      <c r="G18" s="163"/>
+      <c r="D18" s="126"/>
+      <c r="E18" s="127"/>
+      <c r="F18" s="127"/>
+      <c r="G18" s="128"/>
       <c r="H18" s="104"/>
       <c r="I18" s="104"/>
       <c r="J18" s="14"/>
@@ -4864,13 +4864,13 @@
       <c r="A19" s="1"/>
       <c r="B19" s="18"/>
       <c r="C19" s="24"/>
-      <c r="D19" s="173" t="s">
+      <c r="D19" s="143" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="156"/>
-      <c r="F19" s="156"/>
-      <c r="G19" s="162"/>
-      <c r="H19" s="130" t="s">
+      <c r="E19" s="124"/>
+      <c r="F19" s="124"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="176" t="s">
         <v>40</v>
       </c>
       <c r="I19" s="104">
@@ -4992,10 +4992,10 @@
       <c r="A20" s="1"/>
       <c r="B20" s="18"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="158"/>
-      <c r="E20" s="159"/>
-      <c r="F20" s="159"/>
-      <c r="G20" s="163"/>
+      <c r="D20" s="126"/>
+      <c r="E20" s="127"/>
+      <c r="F20" s="127"/>
+      <c r="G20" s="128"/>
       <c r="H20" s="104"/>
       <c r="I20" s="104"/>
       <c r="J20" s="26"/>
@@ -5113,15 +5113,15 @@
     <row r="21" spans="1:120" ht="9.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="18"/>
-      <c r="C21" s="172" t="s">
+      <c r="C21" s="145" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="150"/>
-      <c r="E21" s="150"/>
-      <c r="F21" s="150"/>
-      <c r="G21" s="151"/>
-      <c r="H21" s="131"/>
-      <c r="I21" s="131"/>
+      <c r="D21" s="146"/>
+      <c r="E21" s="146"/>
+      <c r="F21" s="146"/>
+      <c r="G21" s="147"/>
+      <c r="H21" s="159"/>
+      <c r="I21" s="159"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="44"/>
@@ -5237,13 +5237,13 @@
     <row r="22" spans="1:120" ht="9.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="18"/>
-      <c r="C22" s="152"/>
-      <c r="D22" s="153"/>
-      <c r="E22" s="153"/>
-      <c r="F22" s="153"/>
-      <c r="G22" s="154"/>
-      <c r="H22" s="131"/>
-      <c r="I22" s="131"/>
+      <c r="C22" s="148"/>
+      <c r="D22" s="149"/>
+      <c r="E22" s="149"/>
+      <c r="F22" s="149"/>
+      <c r="G22" s="134"/>
+      <c r="H22" s="159"/>
+      <c r="I22" s="159"/>
       <c r="J22" s="46"/>
       <c r="K22" s="47"/>
       <c r="L22" s="47"/>
@@ -5360,13 +5360,13 @@
       <c r="A23" s="1"/>
       <c r="B23" s="28"/>
       <c r="C23" s="29"/>
-      <c r="D23" s="174" t="s">
+      <c r="D23" s="150" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="156"/>
-      <c r="F23" s="156"/>
-      <c r="G23" s="162"/>
-      <c r="H23" s="130" t="s">
+      <c r="E23" s="124"/>
+      <c r="F23" s="124"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="176" t="s">
         <v>46</v>
       </c>
       <c r="I23" s="104">
@@ -5488,10 +5488,10 @@
       <c r="A24" s="1"/>
       <c r="B24" s="18"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="158"/>
-      <c r="E24" s="159"/>
-      <c r="F24" s="159"/>
-      <c r="G24" s="163"/>
+      <c r="D24" s="126"/>
+      <c r="E24" s="127"/>
+      <c r="F24" s="127"/>
+      <c r="G24" s="128"/>
       <c r="H24" s="104"/>
       <c r="I24" s="104"/>
       <c r="J24" s="14"/>
@@ -5609,15 +5609,15 @@
     <row r="25" spans="1:120" ht="9.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="18"/>
-      <c r="C25" s="172" t="s">
+      <c r="C25" s="145" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="150"/>
-      <c r="E25" s="150"/>
-      <c r="F25" s="150"/>
-      <c r="G25" s="151"/>
-      <c r="H25" s="131"/>
-      <c r="I25" s="131"/>
+      <c r="D25" s="146"/>
+      <c r="E25" s="146"/>
+      <c r="F25" s="146"/>
+      <c r="G25" s="147"/>
+      <c r="H25" s="159"/>
+      <c r="I25" s="159"/>
       <c r="J25" s="42"/>
       <c r="K25" s="42"/>
       <c r="L25" s="44"/>
@@ -5733,13 +5733,13 @@
     <row r="26" spans="1:120" ht="9.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="18"/>
-      <c r="C26" s="171"/>
-      <c r="D26" s="159"/>
-      <c r="E26" s="159"/>
-      <c r="F26" s="159"/>
-      <c r="G26" s="160"/>
-      <c r="H26" s="131"/>
-      <c r="I26" s="131"/>
+      <c r="C26" s="133"/>
+      <c r="D26" s="127"/>
+      <c r="E26" s="127"/>
+      <c r="F26" s="127"/>
+      <c r="G26" s="131"/>
+      <c r="H26" s="159"/>
+      <c r="I26" s="159"/>
       <c r="J26" s="46"/>
       <c r="K26" s="47"/>
       <c r="L26" s="47"/>
@@ -5856,13 +5856,13 @@
       <c r="A27" s="1"/>
       <c r="B27" s="28"/>
       <c r="C27" s="29"/>
-      <c r="D27" s="174" t="s">
+      <c r="D27" s="150" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="156"/>
-      <c r="F27" s="156"/>
-      <c r="G27" s="162"/>
-      <c r="H27" s="130" t="s">
+      <c r="E27" s="124"/>
+      <c r="F27" s="124"/>
+      <c r="G27" s="125"/>
+      <c r="H27" s="176" t="s">
         <v>44</v>
       </c>
       <c r="I27" s="104">
@@ -5984,10 +5984,10 @@
       <c r="A28" s="1"/>
       <c r="B28" s="28"/>
       <c r="C28" s="30"/>
-      <c r="D28" s="158"/>
-      <c r="E28" s="159"/>
-      <c r="F28" s="159"/>
-      <c r="G28" s="163"/>
+      <c r="D28" s="126"/>
+      <c r="E28" s="127"/>
+      <c r="F28" s="127"/>
+      <c r="G28" s="128"/>
       <c r="H28" s="104"/>
       <c r="I28" s="104"/>
       <c r="J28" s="14"/>
@@ -6106,13 +6106,13 @@
       <c r="A29" s="1"/>
       <c r="B29" s="28"/>
       <c r="C29" s="30"/>
-      <c r="D29" s="175" t="s">
+      <c r="D29" s="151" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="176"/>
-      <c r="F29" s="176"/>
-      <c r="G29" s="176"/>
-      <c r="H29" s="130" t="s">
+      <c r="E29" s="152"/>
+      <c r="F29" s="152"/>
+      <c r="G29" s="152"/>
+      <c r="H29" s="176" t="s">
         <v>44</v>
       </c>
       <c r="I29" s="104">
@@ -6234,10 +6234,10 @@
       <c r="A30" s="1"/>
       <c r="B30" s="28"/>
       <c r="C30" s="31"/>
-      <c r="D30" s="158"/>
-      <c r="E30" s="159"/>
-      <c r="F30" s="159"/>
-      <c r="G30" s="159"/>
+      <c r="D30" s="126"/>
+      <c r="E30" s="127"/>
+      <c r="F30" s="127"/>
+      <c r="G30" s="127"/>
       <c r="H30" s="104"/>
       <c r="I30" s="104"/>
       <c r="J30" s="26"/>
@@ -6355,15 +6355,15 @@
     <row r="31" spans="1:120" ht="9.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="18"/>
-      <c r="C31" s="149" t="s">
+      <c r="C31" s="171" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="150"/>
-      <c r="E31" s="150"/>
-      <c r="F31" s="150"/>
-      <c r="G31" s="151"/>
-      <c r="H31" s="131"/>
-      <c r="I31" s="131"/>
+      <c r="D31" s="146"/>
+      <c r="E31" s="146"/>
+      <c r="F31" s="146"/>
+      <c r="G31" s="147"/>
+      <c r="H31" s="159"/>
+      <c r="I31" s="159"/>
       <c r="J31" s="42"/>
       <c r="K31" s="43"/>
       <c r="L31" s="44"/>
@@ -6479,13 +6479,13 @@
     <row r="32" spans="1:120" ht="9.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="18"/>
-      <c r="C32" s="152"/>
-      <c r="D32" s="153"/>
-      <c r="E32" s="153"/>
-      <c r="F32" s="153"/>
-      <c r="G32" s="154"/>
-      <c r="H32" s="131"/>
-      <c r="I32" s="131"/>
+      <c r="C32" s="148"/>
+      <c r="D32" s="149"/>
+      <c r="E32" s="149"/>
+      <c r="F32" s="149"/>
+      <c r="G32" s="134"/>
+      <c r="H32" s="159"/>
+      <c r="I32" s="159"/>
       <c r="J32" s="46"/>
       <c r="K32" s="47"/>
       <c r="L32" s="47"/>
@@ -6602,14 +6602,14 @@
       <c r="A33" s="1"/>
       <c r="B33" s="18"/>
       <c r="C33" s="32"/>
-      <c r="D33" s="155" t="s">
+      <c r="D33" s="129" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="156"/>
-      <c r="F33" s="156"/>
-      <c r="G33" s="157"/>
-      <c r="H33" s="131"/>
-      <c r="I33" s="131"/>
+      <c r="E33" s="124"/>
+      <c r="F33" s="124"/>
+      <c r="G33" s="130"/>
+      <c r="H33" s="159"/>
+      <c r="I33" s="159"/>
       <c r="J33" s="50"/>
       <c r="K33" s="51"/>
       <c r="L33" s="51"/>
@@ -6726,12 +6726,12 @@
       <c r="A34" s="1"/>
       <c r="B34" s="18"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="158"/>
-      <c r="E34" s="159"/>
-      <c r="F34" s="159"/>
-      <c r="G34" s="160"/>
-      <c r="H34" s="131"/>
-      <c r="I34" s="131"/>
+      <c r="D34" s="126"/>
+      <c r="E34" s="127"/>
+      <c r="F34" s="127"/>
+      <c r="G34" s="131"/>
+      <c r="H34" s="159"/>
+      <c r="I34" s="159"/>
       <c r="J34" s="52"/>
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
@@ -6849,12 +6849,12 @@
       <c r="B35" s="18"/>
       <c r="C35" s="1"/>
       <c r="D35" s="33"/>
-      <c r="E35" s="161" t="s">
+      <c r="E35" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="156"/>
-      <c r="G35" s="162"/>
-      <c r="H35" s="130" t="s">
+      <c r="F35" s="124"/>
+      <c r="G35" s="125"/>
+      <c r="H35" s="176" t="s">
         <v>45</v>
       </c>
       <c r="I35" s="104">
@@ -6977,9 +6977,9 @@
       <c r="B36" s="18"/>
       <c r="C36" s="1"/>
       <c r="D36" s="34"/>
-      <c r="E36" s="158"/>
-      <c r="F36" s="159"/>
-      <c r="G36" s="163"/>
+      <c r="E36" s="126"/>
+      <c r="F36" s="127"/>
+      <c r="G36" s="128"/>
       <c r="H36" s="104"/>
       <c r="I36" s="104"/>
       <c r="J36" s="14"/>
@@ -7099,12 +7099,12 @@
       <c r="B37" s="18"/>
       <c r="C37" s="1"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="161" t="s">
+      <c r="E37" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="F37" s="156"/>
-      <c r="G37" s="162"/>
-      <c r="H37" s="130" t="s">
+      <c r="F37" s="124"/>
+      <c r="G37" s="125"/>
+      <c r="H37" s="176" t="s">
         <v>44</v>
       </c>
       <c r="I37" s="104">
@@ -7227,9 +7227,9 @@
       <c r="B38" s="18"/>
       <c r="C38" s="1"/>
       <c r="D38" s="35"/>
-      <c r="E38" s="158"/>
-      <c r="F38" s="159"/>
-      <c r="G38" s="163"/>
+      <c r="E38" s="126"/>
+      <c r="F38" s="127"/>
+      <c r="G38" s="128"/>
       <c r="H38" s="104"/>
       <c r="I38" s="104"/>
       <c r="J38" s="26"/>
@@ -7348,14 +7348,14 @@
       <c r="A39" s="1"/>
       <c r="B39" s="18"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="164" t="s">
+      <c r="D39" s="172" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="150"/>
-      <c r="F39" s="150"/>
-      <c r="G39" s="151"/>
-      <c r="H39" s="131"/>
-      <c r="I39" s="131"/>
+      <c r="E39" s="146"/>
+      <c r="F39" s="146"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="159"/>
+      <c r="I39" s="159"/>
       <c r="J39" s="50"/>
       <c r="K39" s="51"/>
       <c r="L39" s="51"/>
@@ -7472,12 +7472,12 @@
       <c r="A40" s="1"/>
       <c r="B40" s="18"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="158"/>
-      <c r="E40" s="159"/>
-      <c r="F40" s="159"/>
-      <c r="G40" s="160"/>
-      <c r="H40" s="131"/>
-      <c r="I40" s="131"/>
+      <c r="D40" s="126"/>
+      <c r="E40" s="127"/>
+      <c r="F40" s="127"/>
+      <c r="G40" s="131"/>
+      <c r="H40" s="159"/>
+      <c r="I40" s="159"/>
       <c r="J40" s="52"/>
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
@@ -7595,12 +7595,12 @@
       <c r="B41" s="18"/>
       <c r="C41" s="1"/>
       <c r="D41" s="33"/>
-      <c r="E41" s="161" t="s">
+      <c r="E41" s="123" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="156"/>
-      <c r="G41" s="162"/>
-      <c r="H41" s="130" t="s">
+      <c r="F41" s="124"/>
+      <c r="G41" s="125"/>
+      <c r="H41" s="176" t="s">
         <v>43</v>
       </c>
       <c r="I41" s="104">
@@ -7723,9 +7723,9 @@
       <c r="B42" s="18"/>
       <c r="C42" s="1"/>
       <c r="D42" s="34"/>
-      <c r="E42" s="158"/>
-      <c r="F42" s="159"/>
-      <c r="G42" s="163"/>
+      <c r="E42" s="126"/>
+      <c r="F42" s="127"/>
+      <c r="G42" s="128"/>
       <c r="H42" s="104"/>
       <c r="I42" s="104"/>
       <c r="J42" s="14"/>
@@ -7845,12 +7845,12 @@
       <c r="B43" s="18"/>
       <c r="C43" s="1"/>
       <c r="D43" s="34"/>
-      <c r="E43" s="161" t="s">
+      <c r="E43" s="123" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="156"/>
-      <c r="G43" s="162"/>
-      <c r="H43" s="130" t="s">
+      <c r="F43" s="124"/>
+      <c r="G43" s="125"/>
+      <c r="H43" s="176" t="s">
         <v>43</v>
       </c>
       <c r="I43" s="104">
@@ -7973,9 +7973,9 @@
       <c r="B44" s="18"/>
       <c r="C44" s="1"/>
       <c r="D44" s="34"/>
-      <c r="E44" s="158"/>
-      <c r="F44" s="159"/>
-      <c r="G44" s="163"/>
+      <c r="E44" s="126"/>
+      <c r="F44" s="127"/>
+      <c r="G44" s="128"/>
       <c r="H44" s="104"/>
       <c r="I44" s="104"/>
       <c r="J44" s="14"/>
@@ -8095,12 +8095,12 @@
       <c r="B45" s="18"/>
       <c r="C45" s="1"/>
       <c r="D45" s="34"/>
-      <c r="E45" s="161" t="s">
+      <c r="E45" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="156"/>
-      <c r="G45" s="162"/>
-      <c r="H45" s="130" t="s">
+      <c r="F45" s="124"/>
+      <c r="G45" s="125"/>
+      <c r="H45" s="176" t="s">
         <v>42</v>
       </c>
       <c r="I45" s="104">
@@ -8223,9 +8223,9 @@
       <c r="B46" s="18"/>
       <c r="C46" s="1"/>
       <c r="D46" s="34"/>
-      <c r="E46" s="158"/>
-      <c r="F46" s="159"/>
-      <c r="G46" s="163"/>
+      <c r="E46" s="126"/>
+      <c r="F46" s="127"/>
+      <c r="G46" s="128"/>
       <c r="H46" s="104"/>
       <c r="I46" s="104"/>
       <c r="J46" s="14"/>
@@ -8345,12 +8345,12 @@
       <c r="B47" s="18"/>
       <c r="C47" s="1"/>
       <c r="D47" s="34"/>
-      <c r="E47" s="161" t="s">
+      <c r="E47" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="F47" s="156"/>
-      <c r="G47" s="162"/>
-      <c r="H47" s="130" t="s">
+      <c r="F47" s="124"/>
+      <c r="G47" s="125"/>
+      <c r="H47" s="176" t="s">
         <v>41</v>
       </c>
       <c r="I47" s="104">
@@ -8473,9 +8473,9 @@
       <c r="B48" s="18"/>
       <c r="C48" s="1"/>
       <c r="D48" s="34"/>
-      <c r="E48" s="158"/>
-      <c r="F48" s="159"/>
-      <c r="G48" s="163"/>
+      <c r="E48" s="126"/>
+      <c r="F48" s="127"/>
+      <c r="G48" s="128"/>
       <c r="H48" s="104"/>
       <c r="I48" s="104"/>
       <c r="J48" s="14"/>
@@ -8595,12 +8595,12 @@
       <c r="B49" s="18"/>
       <c r="C49" s="1"/>
       <c r="D49" s="34"/>
-      <c r="E49" s="161" t="s">
+      <c r="E49" s="123" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="156"/>
-      <c r="G49" s="162"/>
-      <c r="H49" s="130" t="s">
+      <c r="F49" s="124"/>
+      <c r="G49" s="125"/>
+      <c r="H49" s="176" t="s">
         <v>50</v>
       </c>
       <c r="I49" s="104">
@@ -8723,9 +8723,9 @@
       <c r="B50" s="18"/>
       <c r="C50" s="1"/>
       <c r="D50" s="34"/>
-      <c r="E50" s="158"/>
-      <c r="F50" s="159"/>
-      <c r="G50" s="163"/>
+      <c r="E50" s="126"/>
+      <c r="F50" s="127"/>
+      <c r="G50" s="128"/>
       <c r="H50" s="104"/>
       <c r="I50" s="104"/>
       <c r="J50" s="14"/>
@@ -8845,12 +8845,12 @@
       <c r="B51" s="18"/>
       <c r="C51" s="1"/>
       <c r="D51" s="34"/>
-      <c r="E51" s="161" t="s">
+      <c r="E51" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="156"/>
-      <c r="G51" s="162"/>
-      <c r="H51" s="130" t="s">
+      <c r="F51" s="124"/>
+      <c r="G51" s="125"/>
+      <c r="H51" s="176" t="s">
         <v>47</v>
       </c>
       <c r="I51" s="104">
@@ -8973,9 +8973,9 @@
       <c r="B52" s="18"/>
       <c r="C52" s="1"/>
       <c r="D52" s="34"/>
-      <c r="E52" s="158"/>
-      <c r="F52" s="159"/>
-      <c r="G52" s="163"/>
+      <c r="E52" s="126"/>
+      <c r="F52" s="127"/>
+      <c r="G52" s="128"/>
       <c r="H52" s="104"/>
       <c r="I52" s="104"/>
       <c r="J52" s="26"/>
@@ -9094,14 +9094,14 @@
       <c r="A53" s="1"/>
       <c r="B53" s="18"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="155" t="s">
+      <c r="D53" s="129" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="156"/>
-      <c r="F53" s="156"/>
-      <c r="G53" s="157"/>
-      <c r="H53" s="131"/>
-      <c r="I53" s="131"/>
+      <c r="E53" s="124"/>
+      <c r="F53" s="124"/>
+      <c r="G53" s="130"/>
+      <c r="H53" s="159"/>
+      <c r="I53" s="159"/>
       <c r="J53" s="50"/>
       <c r="K53" s="51"/>
       <c r="L53" s="51"/>
@@ -9218,12 +9218,12 @@
       <c r="A54" s="1"/>
       <c r="B54" s="18"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="158"/>
-      <c r="E54" s="159"/>
-      <c r="F54" s="159"/>
-      <c r="G54" s="160"/>
-      <c r="H54" s="131"/>
-      <c r="I54" s="131"/>
+      <c r="D54" s="126"/>
+      <c r="E54" s="127"/>
+      <c r="F54" s="127"/>
+      <c r="G54" s="131"/>
+      <c r="H54" s="159"/>
+      <c r="I54" s="159"/>
       <c r="J54" s="52"/>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -9341,12 +9341,12 @@
       <c r="B55" s="18"/>
       <c r="C55" s="1"/>
       <c r="D55" s="34"/>
-      <c r="E55" s="161" t="s">
+      <c r="E55" s="123" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="156"/>
-      <c r="G55" s="162"/>
-      <c r="H55" s="130" t="s">
+      <c r="F55" s="124"/>
+      <c r="G55" s="125"/>
+      <c r="H55" s="176" t="s">
         <v>48</v>
       </c>
       <c r="I55" s="104">
@@ -9469,9 +9469,9 @@
       <c r="B56" s="18"/>
       <c r="C56" s="1"/>
       <c r="D56" s="34"/>
-      <c r="E56" s="158"/>
-      <c r="F56" s="159"/>
-      <c r="G56" s="163"/>
+      <c r="E56" s="126"/>
+      <c r="F56" s="127"/>
+      <c r="G56" s="128"/>
       <c r="H56" s="104"/>
       <c r="I56" s="104"/>
       <c r="J56" s="14"/>
@@ -9591,12 +9591,12 @@
       <c r="B57" s="18"/>
       <c r="C57" s="1"/>
       <c r="D57" s="34"/>
-      <c r="E57" s="161" t="s">
+      <c r="E57" s="123" t="s">
         <v>29</v>
       </c>
-      <c r="F57" s="156"/>
-      <c r="G57" s="162"/>
-      <c r="H57" s="130" t="s">
+      <c r="F57" s="124"/>
+      <c r="G57" s="125"/>
+      <c r="H57" s="176" t="s">
         <v>51</v>
       </c>
       <c r="I57" s="104">
@@ -9719,9 +9719,9 @@
       <c r="B58" s="18"/>
       <c r="C58" s="1"/>
       <c r="D58" s="34"/>
-      <c r="E58" s="158"/>
-      <c r="F58" s="159"/>
-      <c r="G58" s="163"/>
+      <c r="E58" s="126"/>
+      <c r="F58" s="127"/>
+      <c r="G58" s="128"/>
       <c r="H58" s="104"/>
       <c r="I58" s="104"/>
       <c r="J58" s="14"/>
@@ -9841,12 +9841,12 @@
       <c r="B59" s="18"/>
       <c r="C59" s="1"/>
       <c r="D59" s="34"/>
-      <c r="E59" s="161" t="s">
+      <c r="E59" s="123" t="s">
         <v>26</v>
       </c>
-      <c r="F59" s="156"/>
-      <c r="G59" s="162"/>
-      <c r="H59" s="130" t="s">
+      <c r="F59" s="124"/>
+      <c r="G59" s="125"/>
+      <c r="H59" s="176" t="s">
         <v>49</v>
       </c>
       <c r="I59" s="104">
@@ -9969,9 +9969,9 @@
       <c r="B60" s="18"/>
       <c r="C60" s="1"/>
       <c r="D60" s="34"/>
-      <c r="E60" s="158"/>
-      <c r="F60" s="159"/>
-      <c r="G60" s="163"/>
+      <c r="E60" s="126"/>
+      <c r="F60" s="127"/>
+      <c r="G60" s="128"/>
       <c r="H60" s="104"/>
       <c r="I60" s="104"/>
       <c r="J60" s="14"/>
@@ -10091,12 +10091,12 @@
       <c r="B61" s="18"/>
       <c r="C61" s="1"/>
       <c r="D61" s="34"/>
-      <c r="E61" s="161" t="s">
+      <c r="E61" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="F61" s="156"/>
-      <c r="G61" s="162"/>
-      <c r="H61" s="130" t="s">
+      <c r="F61" s="124"/>
+      <c r="G61" s="125"/>
+      <c r="H61" s="176" t="s">
         <v>49</v>
       </c>
       <c r="I61" s="104">
@@ -10219,9 +10219,9 @@
       <c r="B62" s="18"/>
       <c r="C62" s="1"/>
       <c r="D62" s="34"/>
-      <c r="E62" s="158"/>
-      <c r="F62" s="159"/>
-      <c r="G62" s="163"/>
+      <c r="E62" s="126"/>
+      <c r="F62" s="127"/>
+      <c r="G62" s="128"/>
       <c r="H62" s="104"/>
       <c r="I62" s="104"/>
       <c r="J62" s="26"/>
@@ -10340,14 +10340,14 @@
       <c r="A63" s="1"/>
       <c r="B63" s="18"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="155" t="s">
+      <c r="D63" s="129" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="156"/>
-      <c r="F63" s="156"/>
-      <c r="G63" s="157"/>
-      <c r="H63" s="131"/>
-      <c r="I63" s="131"/>
+      <c r="E63" s="124"/>
+      <c r="F63" s="124"/>
+      <c r="G63" s="130"/>
+      <c r="H63" s="159"/>
+      <c r="I63" s="159"/>
       <c r="J63" s="50"/>
       <c r="K63" s="51"/>
       <c r="L63" s="51"/>
@@ -10464,12 +10464,12 @@
       <c r="A64" s="1"/>
       <c r="B64" s="18"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="158"/>
-      <c r="E64" s="159"/>
-      <c r="F64" s="159"/>
-      <c r="G64" s="160"/>
-      <c r="H64" s="131"/>
-      <c r="I64" s="131"/>
+      <c r="D64" s="126"/>
+      <c r="E64" s="127"/>
+      <c r="F64" s="127"/>
+      <c r="G64" s="131"/>
+      <c r="H64" s="159"/>
+      <c r="I64" s="159"/>
       <c r="J64" s="52"/>
       <c r="K64" s="49"/>
       <c r="L64" s="49"/>
@@ -10587,12 +10587,12 @@
       <c r="B65" s="18"/>
       <c r="C65" s="1"/>
       <c r="D65" s="34"/>
-      <c r="E65" s="161" t="s">
+      <c r="E65" s="123" t="s">
         <v>35</v>
       </c>
-      <c r="F65" s="156"/>
-      <c r="G65" s="162"/>
-      <c r="H65" s="130" t="s">
+      <c r="F65" s="124"/>
+      <c r="G65" s="125"/>
+      <c r="H65" s="176" t="s">
         <v>52</v>
       </c>
       <c r="I65" s="104">
@@ -10715,9 +10715,9 @@
       <c r="B66" s="18"/>
       <c r="C66" s="1"/>
       <c r="D66" s="34"/>
-      <c r="E66" s="158"/>
-      <c r="F66" s="159"/>
-      <c r="G66" s="163"/>
+      <c r="E66" s="126"/>
+      <c r="F66" s="127"/>
+      <c r="G66" s="128"/>
       <c r="H66" s="104"/>
       <c r="I66" s="104"/>
       <c r="J66" s="14"/>
@@ -10837,12 +10837,12 @@
       <c r="B67" s="18"/>
       <c r="C67" s="1"/>
       <c r="D67" s="34"/>
-      <c r="E67" s="161" t="s">
+      <c r="E67" s="123" t="s">
         <v>26</v>
       </c>
-      <c r="F67" s="156"/>
-      <c r="G67" s="162"/>
-      <c r="H67" s="130" t="s">
+      <c r="F67" s="124"/>
+      <c r="G67" s="125"/>
+      <c r="H67" s="176" t="s">
         <v>53</v>
       </c>
       <c r="I67" s="104">
@@ -10965,9 +10965,9 @@
       <c r="B68" s="18"/>
       <c r="C68" s="1"/>
       <c r="D68" s="34"/>
-      <c r="E68" s="158"/>
-      <c r="F68" s="159"/>
-      <c r="G68" s="163"/>
+      <c r="E68" s="126"/>
+      <c r="F68" s="127"/>
+      <c r="G68" s="128"/>
       <c r="H68" s="104"/>
       <c r="I68" s="104"/>
       <c r="J68" s="14"/>
@@ -11087,12 +11087,12 @@
       <c r="B69" s="18"/>
       <c r="C69" s="1"/>
       <c r="D69" s="34"/>
-      <c r="E69" s="161" t="s">
+      <c r="E69" s="123" t="s">
         <v>36</v>
       </c>
-      <c r="F69" s="156"/>
-      <c r="G69" s="162"/>
-      <c r="H69" s="130" t="s">
+      <c r="F69" s="124"/>
+      <c r="G69" s="125"/>
+      <c r="H69" s="176" t="s">
         <v>54</v>
       </c>
       <c r="I69" s="104">
@@ -11215,9 +11215,9 @@
       <c r="B70" s="18"/>
       <c r="C70" s="1"/>
       <c r="D70" s="34"/>
-      <c r="E70" s="158"/>
-      <c r="F70" s="159"/>
-      <c r="G70" s="163"/>
+      <c r="E70" s="126"/>
+      <c r="F70" s="127"/>
+      <c r="G70" s="128"/>
       <c r="H70" s="104"/>
       <c r="I70" s="104"/>
       <c r="J70" s="14"/>
@@ -11337,12 +11337,12 @@
       <c r="B71" s="18"/>
       <c r="C71" s="1"/>
       <c r="D71" s="34"/>
-      <c r="E71" s="161" t="s">
+      <c r="E71" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="F71" s="156"/>
-      <c r="G71" s="162"/>
-      <c r="H71" s="130" t="s">
+      <c r="F71" s="124"/>
+      <c r="G71" s="125"/>
+      <c r="H71" s="176" t="s">
         <v>55</v>
       </c>
       <c r="I71" s="104">
@@ -11465,9 +11465,9 @@
       <c r="B72" s="18"/>
       <c r="C72" s="1"/>
       <c r="D72" s="35"/>
-      <c r="E72" s="158"/>
-      <c r="F72" s="159"/>
-      <c r="G72" s="163"/>
+      <c r="E72" s="126"/>
+      <c r="F72" s="127"/>
+      <c r="G72" s="128"/>
       <c r="H72" s="104"/>
       <c r="I72" s="104"/>
       <c r="J72" s="26"/>
@@ -11585,14 +11585,14 @@
     <row r="73" spans="1:120" ht="9.75" customHeight="1">
       <c r="A73" s="16"/>
       <c r="B73" s="36"/>
-      <c r="C73" s="138" t="s">
+      <c r="C73" s="132" t="s">
         <v>30</v>
       </c>
-      <c r="D73" s="156"/>
-      <c r="E73" s="156"/>
-      <c r="F73" s="156"/>
-      <c r="G73" s="157"/>
-      <c r="H73" s="130" t="s">
+      <c r="D73" s="124"/>
+      <c r="E73" s="124"/>
+      <c r="F73" s="124"/>
+      <c r="G73" s="130"/>
+      <c r="H73" s="176" t="s">
         <v>55</v>
       </c>
       <c r="I73" s="104">
@@ -11713,11 +11713,11 @@
     <row r="74" spans="1:120" ht="9.75" customHeight="1">
       <c r="A74" s="16"/>
       <c r="B74" s="36"/>
-      <c r="C74" s="171"/>
-      <c r="D74" s="159"/>
-      <c r="E74" s="159"/>
-      <c r="F74" s="159"/>
-      <c r="G74" s="160"/>
+      <c r="C74" s="133"/>
+      <c r="D74" s="127"/>
+      <c r="E74" s="127"/>
+      <c r="F74" s="127"/>
+      <c r="G74" s="131"/>
       <c r="H74" s="104"/>
       <c r="I74" s="104"/>
       <c r="J74" s="19"/>
@@ -11835,14 +11835,14 @@
     <row r="75" spans="1:120" ht="9.75" customHeight="1">
       <c r="A75" s="16"/>
       <c r="B75" s="36"/>
-      <c r="C75" s="138" t="s">
+      <c r="C75" s="132" t="s">
         <v>34</v>
       </c>
-      <c r="D75" s="156"/>
-      <c r="E75" s="156"/>
-      <c r="F75" s="156"/>
-      <c r="G75" s="157"/>
-      <c r="H75" s="130" t="s">
+      <c r="D75" s="124"/>
+      <c r="E75" s="124"/>
+      <c r="F75" s="124"/>
+      <c r="G75" s="130"/>
+      <c r="H75" s="176" t="s">
         <v>58</v>
       </c>
       <c r="I75" s="104"/>
@@ -11961,11 +11961,11 @@
     <row r="76" spans="1:120" ht="9.75" customHeight="1">
       <c r="A76" s="16"/>
       <c r="B76" s="36"/>
-      <c r="C76" s="154"/>
-      <c r="D76" s="154"/>
-      <c r="E76" s="154"/>
-      <c r="F76" s="154"/>
-      <c r="G76" s="154"/>
+      <c r="C76" s="134"/>
+      <c r="D76" s="134"/>
+      <c r="E76" s="134"/>
+      <c r="F76" s="134"/>
+      <c r="G76" s="134"/>
       <c r="H76" s="104"/>
       <c r="I76" s="104"/>
       <c r="J76" s="19"/>
@@ -12083,15 +12083,15 @@
     <row r="77" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A77" s="16"/>
       <c r="B77" s="71"/>
-      <c r="C77" s="179" t="s">
+      <c r="C77" s="135" t="s">
         <v>62</v>
       </c>
-      <c r="D77" s="180"/>
-      <c r="E77" s="180"/>
-      <c r="F77" s="180"/>
-      <c r="G77" s="181"/>
-      <c r="H77" s="132"/>
-      <c r="I77" s="121"/>
+      <c r="D77" s="136"/>
+      <c r="E77" s="136"/>
+      <c r="F77" s="136"/>
+      <c r="G77" s="137"/>
+      <c r="H77" s="177"/>
+      <c r="I77" s="173"/>
       <c r="J77" s="63"/>
       <c r="K77" s="64"/>
       <c r="L77" s="64"/>
@@ -12207,13 +12207,13 @@
     <row r="78" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A78" s="16"/>
       <c r="B78" s="71"/>
-      <c r="C78" s="182"/>
-      <c r="D78" s="183"/>
-      <c r="E78" s="183"/>
-      <c r="F78" s="183"/>
-      <c r="G78" s="184"/>
-      <c r="H78" s="133"/>
-      <c r="I78" s="122"/>
+      <c r="C78" s="138"/>
+      <c r="D78" s="139"/>
+      <c r="E78" s="139"/>
+      <c r="F78" s="139"/>
+      <c r="G78" s="140"/>
+      <c r="H78" s="178"/>
+      <c r="I78" s="174"/>
       <c r="J78" s="63"/>
       <c r="K78" s="64"/>
       <c r="L78" s="64"/>
@@ -12330,12 +12330,12 @@
       <c r="A79" s="16"/>
       <c r="B79" s="71"/>
       <c r="C79" s="76"/>
-      <c r="D79" s="124" t="s">
+      <c r="D79" s="107" t="s">
         <v>63</v>
       </c>
-      <c r="E79" s="125"/>
-      <c r="F79" s="125"/>
-      <c r="G79" s="126"/>
+      <c r="E79" s="108"/>
+      <c r="F79" s="108"/>
+      <c r="G79" s="109"/>
       <c r="H79" s="77"/>
       <c r="I79" s="67"/>
       <c r="J79" s="63"/>
@@ -12454,10 +12454,10 @@
       <c r="A80" s="16"/>
       <c r="B80" s="71"/>
       <c r="C80" s="76"/>
-      <c r="D80" s="127"/>
-      <c r="E80" s="128"/>
-      <c r="F80" s="128"/>
-      <c r="G80" s="129"/>
+      <c r="D80" s="110"/>
+      <c r="E80" s="111"/>
+      <c r="F80" s="111"/>
+      <c r="G80" s="112"/>
       <c r="H80" s="77"/>
       <c r="I80" s="67"/>
       <c r="J80" s="63"/>
@@ -12577,15 +12577,15 @@
       <c r="B81" s="36"/>
       <c r="C81" s="60"/>
       <c r="D81" s="70"/>
-      <c r="E81" s="97" t="s">
+      <c r="E81" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="F81" s="97"/>
-      <c r="G81" s="97"/>
-      <c r="H81" s="103">
+      <c r="F81" s="141"/>
+      <c r="G81" s="141"/>
+      <c r="H81" s="95">
         <v>45611</v>
       </c>
-      <c r="I81" s="118">
+      <c r="I81" s="97">
         <v>100</v>
       </c>
       <c r="J81" s="19"/>
@@ -12705,11 +12705,11 @@
       <c r="B82" s="36"/>
       <c r="C82" s="60"/>
       <c r="D82" s="70"/>
-      <c r="E82" s="95"/>
-      <c r="F82" s="95"/>
-      <c r="G82" s="95"/>
-      <c r="H82" s="99"/>
-      <c r="I82" s="101"/>
+      <c r="E82" s="94"/>
+      <c r="F82" s="94"/>
+      <c r="G82" s="94"/>
+      <c r="H82" s="96"/>
+      <c r="I82" s="98"/>
       <c r="J82" s="19"/>
       <c r="K82" s="20"/>
       <c r="L82" s="20"/>
@@ -12827,15 +12827,15 @@
       <c r="B83" s="36"/>
       <c r="C83" s="60"/>
       <c r="D83" s="70"/>
-      <c r="E83" s="95" t="s">
+      <c r="E83" s="94" t="s">
         <v>74</v>
       </c>
-      <c r="F83" s="95"/>
-      <c r="G83" s="95"/>
-      <c r="H83" s="103">
+      <c r="F83" s="94"/>
+      <c r="G83" s="94"/>
+      <c r="H83" s="95">
         <v>45615</v>
       </c>
-      <c r="I83" s="118">
+      <c r="I83" s="97">
         <v>100</v>
       </c>
       <c r="J83" s="19"/>
@@ -12955,11 +12955,11 @@
       <c r="B84" s="36"/>
       <c r="C84" s="60"/>
       <c r="D84" s="70"/>
-      <c r="E84" s="95"/>
-      <c r="F84" s="95"/>
-      <c r="G84" s="95"/>
-      <c r="H84" s="99"/>
-      <c r="I84" s="101"/>
+      <c r="E84" s="94"/>
+      <c r="F84" s="94"/>
+      <c r="G84" s="94"/>
+      <c r="H84" s="96"/>
+      <c r="I84" s="98"/>
       <c r="J84" s="19"/>
       <c r="K84" s="20"/>
       <c r="L84" s="20"/>
@@ -13077,15 +13077,15 @@
       <c r="B85" s="36"/>
       <c r="C85" s="60"/>
       <c r="D85" s="70"/>
-      <c r="E85" s="106" t="s">
+      <c r="E85" s="181" t="s">
         <v>61</v>
       </c>
-      <c r="F85" s="107"/>
-      <c r="G85" s="108"/>
-      <c r="H85" s="102">
+      <c r="F85" s="113"/>
+      <c r="G85" s="114"/>
+      <c r="H85" s="103">
         <v>45617</v>
       </c>
-      <c r="I85" s="118">
+      <c r="I85" s="97">
         <v>100</v>
       </c>
       <c r="J85" s="62"/>
@@ -13205,11 +13205,11 @@
       <c r="B86" s="36"/>
       <c r="C86" s="60"/>
       <c r="D86" s="70"/>
-      <c r="E86" s="109"/>
-      <c r="F86" s="110"/>
-      <c r="G86" s="111"/>
-      <c r="H86" s="102"/>
-      <c r="I86" s="101"/>
+      <c r="E86" s="142"/>
+      <c r="F86" s="117"/>
+      <c r="G86" s="118"/>
+      <c r="H86" s="103"/>
+      <c r="I86" s="98"/>
       <c r="J86" s="62"/>
       <c r="K86" s="20"/>
       <c r="L86" s="20"/>
@@ -13248,7 +13248,7 @@
       <c r="AS86" s="20"/>
       <c r="AT86" s="20"/>
       <c r="AU86" s="20"/>
-      <c r="AV86" s="20"/>
+      <c r="AV86" s="75"/>
       <c r="AW86" s="20"/>
       <c r="AX86" s="21"/>
       <c r="AY86" s="21"/>
@@ -13326,16 +13326,16 @@
       <c r="A87" s="16"/>
       <c r="B87" s="71"/>
       <c r="C87" s="90"/>
-      <c r="D87" s="95" t="s">
+      <c r="D87" s="94" t="s">
         <v>76</v>
       </c>
-      <c r="E87" s="95"/>
-      <c r="F87" s="95"/>
-      <c r="G87" s="95"/>
-      <c r="H87" s="103">
+      <c r="E87" s="94"/>
+      <c r="F87" s="94"/>
+      <c r="G87" s="94"/>
+      <c r="H87" s="95">
         <v>45615</v>
       </c>
-      <c r="I87" s="118">
+      <c r="I87" s="97">
         <v>100</v>
       </c>
       <c r="J87" s="62"/>
@@ -13454,12 +13454,12 @@
       <c r="A88" s="16"/>
       <c r="B88" s="71"/>
       <c r="C88" s="90"/>
-      <c r="D88" s="95"/>
-      <c r="E88" s="95"/>
-      <c r="F88" s="95"/>
-      <c r="G88" s="95"/>
-      <c r="H88" s="99"/>
-      <c r="I88" s="101"/>
+      <c r="D88" s="94"/>
+      <c r="E88" s="94"/>
+      <c r="F88" s="94"/>
+      <c r="G88" s="94"/>
+      <c r="H88" s="96"/>
+      <c r="I88" s="98"/>
       <c r="J88" s="62"/>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -13576,14 +13576,14 @@
       <c r="A89" s="16"/>
       <c r="B89" s="36"/>
       <c r="C89" s="79"/>
-      <c r="D89" s="124" t="s">
+      <c r="D89" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="125"/>
-      <c r="F89" s="125"/>
-      <c r="G89" s="126"/>
-      <c r="H89" s="123"/>
-      <c r="I89" s="120"/>
+      <c r="E89" s="108"/>
+      <c r="F89" s="108"/>
+      <c r="G89" s="109"/>
+      <c r="H89" s="179"/>
+      <c r="I89" s="180"/>
       <c r="J89" s="66"/>
       <c r="K89" s="64"/>
       <c r="L89" s="64"/>
@@ -13700,12 +13700,12 @@
       <c r="A90" s="16"/>
       <c r="B90" s="36"/>
       <c r="C90" s="79"/>
-      <c r="D90" s="127"/>
-      <c r="E90" s="128"/>
-      <c r="F90" s="128"/>
-      <c r="G90" s="129"/>
-      <c r="H90" s="123"/>
-      <c r="I90" s="120"/>
+      <c r="D90" s="110"/>
+      <c r="E90" s="111"/>
+      <c r="F90" s="111"/>
+      <c r="G90" s="112"/>
+      <c r="H90" s="179"/>
+      <c r="I90" s="180"/>
       <c r="J90" s="66"/>
       <c r="K90" s="64"/>
       <c r="L90" s="64"/>
@@ -13823,15 +13823,15 @@
       <c r="B91" s="36"/>
       <c r="C91" s="60"/>
       <c r="D91" s="70"/>
-      <c r="E91" s="97" t="s">
+      <c r="E91" s="141" t="s">
         <v>68</v>
       </c>
-      <c r="F91" s="97"/>
-      <c r="G91" s="97"/>
-      <c r="H91" s="103">
+      <c r="F91" s="141"/>
+      <c r="G91" s="141"/>
+      <c r="H91" s="95">
         <v>45616</v>
       </c>
-      <c r="I91" s="118"/>
+      <c r="I91" s="97"/>
       <c r="J91" s="19"/>
       <c r="K91" s="20"/>
       <c r="L91" s="20"/>
@@ -13949,11 +13949,11 @@
       <c r="B92" s="36"/>
       <c r="C92" s="60"/>
       <c r="D92" s="70"/>
-      <c r="E92" s="95"/>
-      <c r="F92" s="95"/>
-      <c r="G92" s="95"/>
-      <c r="H92" s="99"/>
-      <c r="I92" s="101"/>
+      <c r="E92" s="94"/>
+      <c r="F92" s="94"/>
+      <c r="G92" s="94"/>
+      <c r="H92" s="96"/>
+      <c r="I92" s="98"/>
       <c r="J92" s="19"/>
       <c r="K92" s="20"/>
       <c r="L92" s="20"/>
@@ -14071,15 +14071,15 @@
       <c r="B93" s="36"/>
       <c r="C93" s="60"/>
       <c r="D93" s="70"/>
-      <c r="E93" s="95" t="s">
+      <c r="E93" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="F93" s="95"/>
-      <c r="G93" s="95"/>
-      <c r="H93" s="103">
+      <c r="F93" s="94"/>
+      <c r="G93" s="94"/>
+      <c r="H93" s="95">
         <v>45617</v>
       </c>
-      <c r="I93" s="118"/>
+      <c r="I93" s="97"/>
       <c r="J93" s="19"/>
       <c r="K93" s="20"/>
       <c r="L93" s="20"/>
@@ -14197,11 +14197,11 @@
       <c r="B94" s="36"/>
       <c r="C94" s="60"/>
       <c r="D94" s="70"/>
-      <c r="E94" s="95"/>
-      <c r="F94" s="95"/>
-      <c r="G94" s="95"/>
-      <c r="H94" s="99"/>
-      <c r="I94" s="101"/>
+      <c r="E94" s="94"/>
+      <c r="F94" s="94"/>
+      <c r="G94" s="94"/>
+      <c r="H94" s="96"/>
+      <c r="I94" s="98"/>
       <c r="J94" s="19"/>
       <c r="K94" s="20"/>
       <c r="L94" s="20"/>
@@ -14319,15 +14319,15 @@
       <c r="B95" s="36"/>
       <c r="C95" s="60"/>
       <c r="D95" s="70"/>
-      <c r="E95" s="95" t="s">
+      <c r="E95" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="F95" s="95"/>
-      <c r="G95" s="95"/>
-      <c r="H95" s="103">
+      <c r="F95" s="94"/>
+      <c r="G95" s="94"/>
+      <c r="H95" s="95">
         <v>45618</v>
       </c>
-      <c r="I95" s="118"/>
+      <c r="I95" s="97"/>
       <c r="J95" s="19"/>
       <c r="K95" s="20"/>
       <c r="L95" s="20"/>
@@ -14445,11 +14445,11 @@
       <c r="B96" s="36"/>
       <c r="C96" s="60"/>
       <c r="D96" s="70"/>
-      <c r="E96" s="95"/>
-      <c r="F96" s="95"/>
-      <c r="G96" s="95"/>
-      <c r="H96" s="99"/>
-      <c r="I96" s="101"/>
+      <c r="E96" s="94"/>
+      <c r="F96" s="94"/>
+      <c r="G96" s="94"/>
+      <c r="H96" s="96"/>
+      <c r="I96" s="98"/>
       <c r="J96" s="19"/>
       <c r="K96" s="20"/>
       <c r="L96" s="20"/>
@@ -14567,15 +14567,15 @@
       <c r="B97" s="36"/>
       <c r="C97" s="60"/>
       <c r="D97" s="70"/>
-      <c r="E97" s="95" t="s">
+      <c r="E97" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="F97" s="95"/>
-      <c r="G97" s="95"/>
-      <c r="H97" s="103">
+      <c r="F97" s="94"/>
+      <c r="G97" s="94"/>
+      <c r="H97" s="95">
         <v>45621</v>
       </c>
-      <c r="I97" s="118"/>
+      <c r="I97" s="97"/>
       <c r="J97" s="19"/>
       <c r="K97" s="20"/>
       <c r="L97" s="20"/>
@@ -14693,11 +14693,11 @@
       <c r="B98" s="36"/>
       <c r="C98" s="60"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="95"/>
-      <c r="F98" s="95"/>
-      <c r="G98" s="95"/>
-      <c r="H98" s="99"/>
-      <c r="I98" s="101"/>
+      <c r="E98" s="94"/>
+      <c r="F98" s="94"/>
+      <c r="G98" s="94"/>
+      <c r="H98" s="96"/>
+      <c r="I98" s="98"/>
       <c r="J98" s="19"/>
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
@@ -14815,15 +14815,15 @@
       <c r="B99" s="36"/>
       <c r="C99" s="60"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="95" t="s">
+      <c r="E99" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="F99" s="95"/>
-      <c r="G99" s="95"/>
-      <c r="H99" s="103">
+      <c r="F99" s="94"/>
+      <c r="G99" s="94"/>
+      <c r="H99" s="95">
         <v>45622</v>
       </c>
-      <c r="I99" s="118"/>
+      <c r="I99" s="97"/>
       <c r="J99" s="19"/>
       <c r="K99" s="20"/>
       <c r="L99" s="20"/>
@@ -14941,11 +14941,11 @@
       <c r="B100" s="36"/>
       <c r="C100" s="60"/>
       <c r="D100" s="70"/>
-      <c r="E100" s="95"/>
-      <c r="F100" s="95"/>
-      <c r="G100" s="95"/>
-      <c r="H100" s="99"/>
-      <c r="I100" s="101"/>
+      <c r="E100" s="94"/>
+      <c r="F100" s="94"/>
+      <c r="G100" s="94"/>
+      <c r="H100" s="96"/>
+      <c r="I100" s="98"/>
       <c r="J100" s="19"/>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -15063,12 +15063,12 @@
       <c r="B101" s="71"/>
       <c r="C101" s="91"/>
       <c r="D101" s="70"/>
-      <c r="E101" s="109" t="s">
+      <c r="E101" s="142" t="s">
         <v>61</v>
       </c>
-      <c r="F101" s="110"/>
-      <c r="G101" s="111"/>
-      <c r="H101" s="103">
+      <c r="F101" s="117"/>
+      <c r="G101" s="118"/>
+      <c r="H101" s="95">
         <v>45623</v>
       </c>
       <c r="I101" s="104"/>
@@ -15189,10 +15189,10 @@
       <c r="B102" s="71"/>
       <c r="C102" s="91"/>
       <c r="D102" s="70"/>
-      <c r="E102" s="109"/>
-      <c r="F102" s="110"/>
-      <c r="G102" s="111"/>
-      <c r="H102" s="99"/>
+      <c r="E102" s="142"/>
+      <c r="F102" s="117"/>
+      <c r="G102" s="118"/>
+      <c r="H102" s="96"/>
       <c r="I102" s="104"/>
       <c r="J102" s="62"/>
       <c r="K102" s="20"/>
@@ -15310,16 +15310,16 @@
       <c r="A103" s="16"/>
       <c r="B103" s="71"/>
       <c r="C103" s="90"/>
-      <c r="D103" s="95" t="s">
+      <c r="D103" s="94" t="s">
         <v>77</v>
       </c>
-      <c r="E103" s="95"/>
-      <c r="F103" s="95"/>
-      <c r="G103" s="95"/>
-      <c r="H103" s="103">
+      <c r="E103" s="94"/>
+      <c r="F103" s="94"/>
+      <c r="G103" s="94"/>
+      <c r="H103" s="95">
         <v>45622</v>
       </c>
-      <c r="I103" s="105"/>
+      <c r="I103" s="101"/>
       <c r="J103" s="62"/>
       <c r="K103" s="20"/>
       <c r="L103" s="20"/>
@@ -15436,12 +15436,12 @@
       <c r="A104" s="16"/>
       <c r="B104" s="71"/>
       <c r="C104" s="90"/>
-      <c r="D104" s="95"/>
-      <c r="E104" s="95"/>
-      <c r="F104" s="95"/>
-      <c r="G104" s="95"/>
-      <c r="H104" s="99"/>
-      <c r="I104" s="135"/>
+      <c r="D104" s="94"/>
+      <c r="E104" s="94"/>
+      <c r="F104" s="94"/>
+      <c r="G104" s="94"/>
+      <c r="H104" s="96"/>
+      <c r="I104" s="102"/>
       <c r="J104" s="62"/>
       <c r="K104" s="20"/>
       <c r="L104" s="20"/>
@@ -15557,15 +15557,15 @@
     <row r="105" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A105" s="16"/>
       <c r="B105" s="71"/>
-      <c r="C105" s="179" t="s">
+      <c r="C105" s="135" t="s">
         <v>64</v>
       </c>
-      <c r="D105" s="180"/>
-      <c r="E105" s="180"/>
-      <c r="F105" s="180"/>
-      <c r="G105" s="181"/>
-      <c r="H105" s="119"/>
-      <c r="I105" s="120"/>
+      <c r="D105" s="136"/>
+      <c r="E105" s="136"/>
+      <c r="F105" s="136"/>
+      <c r="G105" s="137"/>
+      <c r="H105" s="182"/>
+      <c r="I105" s="180"/>
       <c r="J105" s="66"/>
       <c r="K105" s="64"/>
       <c r="L105" s="64"/>
@@ -15681,13 +15681,13 @@
     <row r="106" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A106" s="16"/>
       <c r="B106" s="71"/>
-      <c r="C106" s="182"/>
-      <c r="D106" s="183"/>
-      <c r="E106" s="183"/>
-      <c r="F106" s="183"/>
-      <c r="G106" s="184"/>
-      <c r="H106" s="119"/>
-      <c r="I106" s="120"/>
+      <c r="C106" s="138"/>
+      <c r="D106" s="139"/>
+      <c r="E106" s="139"/>
+      <c r="F106" s="139"/>
+      <c r="G106" s="140"/>
+      <c r="H106" s="182"/>
+      <c r="I106" s="180"/>
       <c r="J106" s="66"/>
       <c r="K106" s="64"/>
       <c r="L106" s="64"/>
@@ -15804,14 +15804,14 @@
       <c r="A107" s="16"/>
       <c r="B107" s="36"/>
       <c r="C107" s="78"/>
-      <c r="D107" s="124" t="s">
+      <c r="D107" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="E107" s="125"/>
-      <c r="F107" s="125"/>
-      <c r="G107" s="126"/>
-      <c r="H107" s="119"/>
-      <c r="I107" s="120"/>
+      <c r="E107" s="108"/>
+      <c r="F107" s="108"/>
+      <c r="G107" s="109"/>
+      <c r="H107" s="182"/>
+      <c r="I107" s="180"/>
       <c r="J107" s="66"/>
       <c r="K107" s="64"/>
       <c r="L107" s="64"/>
@@ -15928,12 +15928,12 @@
       <c r="A108" s="16"/>
       <c r="B108" s="36"/>
       <c r="C108" s="76"/>
-      <c r="D108" s="127"/>
-      <c r="E108" s="128"/>
-      <c r="F108" s="128"/>
-      <c r="G108" s="129"/>
-      <c r="H108" s="119"/>
-      <c r="I108" s="120"/>
+      <c r="D108" s="110"/>
+      <c r="E108" s="111"/>
+      <c r="F108" s="111"/>
+      <c r="G108" s="112"/>
+      <c r="H108" s="182"/>
+      <c r="I108" s="180"/>
       <c r="J108" s="66"/>
       <c r="K108" s="64"/>
       <c r="L108" s="64"/>
@@ -16051,15 +16051,15 @@
       <c r="B109" s="36"/>
       <c r="C109" s="60"/>
       <c r="D109" s="70"/>
-      <c r="E109" s="97" t="s">
+      <c r="E109" s="141" t="s">
         <v>73</v>
       </c>
-      <c r="F109" s="97"/>
-      <c r="G109" s="97"/>
-      <c r="H109" s="103">
+      <c r="F109" s="141"/>
+      <c r="G109" s="141"/>
+      <c r="H109" s="95">
         <v>45624</v>
       </c>
-      <c r="I109" s="105"/>
+      <c r="I109" s="101"/>
       <c r="J109" s="62"/>
       <c r="K109" s="20"/>
       <c r="L109" s="20"/>
@@ -16177,11 +16177,11 @@
       <c r="B110" s="36"/>
       <c r="C110" s="60"/>
       <c r="D110" s="70"/>
-      <c r="E110" s="95"/>
-      <c r="F110" s="95"/>
-      <c r="G110" s="95"/>
-      <c r="H110" s="99"/>
-      <c r="I110" s="135"/>
+      <c r="E110" s="94"/>
+      <c r="F110" s="94"/>
+      <c r="G110" s="94"/>
+      <c r="H110" s="96"/>
+      <c r="I110" s="102"/>
       <c r="J110" s="62"/>
       <c r="K110" s="20"/>
       <c r="L110" s="20"/>
@@ -16299,15 +16299,15 @@
       <c r="B111" s="36"/>
       <c r="C111" s="60"/>
       <c r="D111" s="70"/>
-      <c r="E111" s="95" t="s">
+      <c r="E111" s="94" t="s">
         <v>74</v>
       </c>
-      <c r="F111" s="95"/>
-      <c r="G111" s="95"/>
-      <c r="H111" s="103">
+      <c r="F111" s="94"/>
+      <c r="G111" s="94"/>
+      <c r="H111" s="95">
         <v>45625</v>
       </c>
-      <c r="I111" s="105"/>
+      <c r="I111" s="101"/>
       <c r="J111" s="62"/>
       <c r="K111" s="20"/>
       <c r="L111" s="20"/>
@@ -16425,11 +16425,11 @@
       <c r="B112" s="36"/>
       <c r="C112" s="60"/>
       <c r="D112" s="70"/>
-      <c r="E112" s="95"/>
-      <c r="F112" s="95"/>
-      <c r="G112" s="95"/>
-      <c r="H112" s="99"/>
-      <c r="I112" s="135"/>
+      <c r="E112" s="94"/>
+      <c r="F112" s="94"/>
+      <c r="G112" s="94"/>
+      <c r="H112" s="96"/>
+      <c r="I112" s="102"/>
       <c r="J112" s="62"/>
       <c r="K112" s="20"/>
       <c r="L112" s="20"/>
@@ -16547,12 +16547,12 @@
       <c r="B113" s="71"/>
       <c r="C113" s="91"/>
       <c r="D113" s="70"/>
-      <c r="E113" s="95" t="s">
+      <c r="E113" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="F113" s="95"/>
-      <c r="G113" s="95"/>
-      <c r="H113" s="102">
+      <c r="F113" s="94"/>
+      <c r="G113" s="94"/>
+      <c r="H113" s="103">
         <v>45630</v>
       </c>
       <c r="I113" s="104"/>
@@ -16673,11 +16673,11 @@
       <c r="B114" s="71"/>
       <c r="C114" s="91"/>
       <c r="D114" s="70"/>
-      <c r="E114" s="117"/>
-      <c r="F114" s="117"/>
-      <c r="G114" s="117"/>
-      <c r="H114" s="103"/>
-      <c r="I114" s="105"/>
+      <c r="E114" s="190"/>
+      <c r="F114" s="190"/>
+      <c r="G114" s="190"/>
+      <c r="H114" s="95"/>
+      <c r="I114" s="101"/>
       <c r="J114" s="62"/>
       <c r="K114" s="20"/>
       <c r="L114" s="20"/>
@@ -16794,13 +16794,13 @@
       <c r="A115" s="16"/>
       <c r="B115" s="71"/>
       <c r="C115" s="91"/>
-      <c r="D115" s="95" t="s">
+      <c r="D115" s="94" t="s">
         <v>78</v>
       </c>
-      <c r="E115" s="95"/>
-      <c r="F115" s="95"/>
-      <c r="G115" s="95"/>
-      <c r="H115" s="102">
+      <c r="E115" s="94"/>
+      <c r="F115" s="94"/>
+      <c r="G115" s="94"/>
+      <c r="H115" s="103">
         <v>45625</v>
       </c>
       <c r="I115" s="104"/>
@@ -16920,11 +16920,11 @@
       <c r="A116" s="16"/>
       <c r="B116" s="71"/>
       <c r="C116" s="91"/>
-      <c r="D116" s="95"/>
-      <c r="E116" s="95"/>
-      <c r="F116" s="95"/>
-      <c r="G116" s="95"/>
-      <c r="H116" s="102"/>
+      <c r="D116" s="94"/>
+      <c r="E116" s="94"/>
+      <c r="F116" s="94"/>
+      <c r="G116" s="94"/>
+      <c r="H116" s="103"/>
       <c r="I116" s="104"/>
       <c r="J116" s="62"/>
       <c r="K116" s="20"/>
@@ -17042,14 +17042,14 @@
       <c r="A117" s="16"/>
       <c r="B117" s="36"/>
       <c r="C117" s="80"/>
-      <c r="D117" s="124" t="s">
+      <c r="D117" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="E117" s="125"/>
-      <c r="F117" s="125"/>
-      <c r="G117" s="126"/>
-      <c r="H117" s="113"/>
-      <c r="I117" s="121"/>
+      <c r="E117" s="108"/>
+      <c r="F117" s="108"/>
+      <c r="G117" s="109"/>
+      <c r="H117" s="183"/>
+      <c r="I117" s="173"/>
       <c r="J117" s="63"/>
       <c r="K117" s="64"/>
       <c r="L117" s="64"/>
@@ -17166,12 +17166,12 @@
       <c r="A118" s="16"/>
       <c r="B118" s="36"/>
       <c r="C118" s="80"/>
-      <c r="D118" s="127"/>
-      <c r="E118" s="128"/>
-      <c r="F118" s="128"/>
-      <c r="G118" s="129"/>
-      <c r="H118" s="114"/>
-      <c r="I118" s="122"/>
+      <c r="D118" s="110"/>
+      <c r="E118" s="111"/>
+      <c r="F118" s="111"/>
+      <c r="G118" s="112"/>
+      <c r="H118" s="184"/>
+      <c r="I118" s="174"/>
       <c r="J118" s="63"/>
       <c r="K118" s="64"/>
       <c r="L118" s="64"/>
@@ -17289,15 +17289,15 @@
       <c r="B119" s="36"/>
       <c r="C119" s="60"/>
       <c r="D119" s="70"/>
-      <c r="E119" s="97" t="s">
+      <c r="E119" s="141" t="s">
         <v>68</v>
       </c>
-      <c r="F119" s="97"/>
-      <c r="G119" s="97"/>
-      <c r="H119" s="103">
+      <c r="F119" s="141"/>
+      <c r="G119" s="141"/>
+      <c r="H119" s="95">
         <v>45629</v>
       </c>
-      <c r="I119" s="118"/>
+      <c r="I119" s="97"/>
       <c r="J119" s="19"/>
       <c r="K119" s="20"/>
       <c r="L119" s="20"/>
@@ -17415,11 +17415,11 @@
       <c r="B120" s="36"/>
       <c r="C120" s="60"/>
       <c r="D120" s="70"/>
-      <c r="E120" s="95"/>
-      <c r="F120" s="95"/>
-      <c r="G120" s="95"/>
-      <c r="H120" s="99"/>
-      <c r="I120" s="101"/>
+      <c r="E120" s="94"/>
+      <c r="F120" s="94"/>
+      <c r="G120" s="94"/>
+      <c r="H120" s="96"/>
+      <c r="I120" s="98"/>
       <c r="J120" s="19"/>
       <c r="K120" s="20"/>
       <c r="L120" s="20"/>
@@ -17537,15 +17537,15 @@
       <c r="B121" s="36"/>
       <c r="C121" s="60"/>
       <c r="D121" s="70"/>
-      <c r="E121" s="95" t="s">
+      <c r="E121" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="F121" s="95"/>
-      <c r="G121" s="95"/>
-      <c r="H121" s="103">
+      <c r="F121" s="94"/>
+      <c r="G121" s="94"/>
+      <c r="H121" s="95">
         <v>45630</v>
       </c>
-      <c r="I121" s="118"/>
+      <c r="I121" s="97"/>
       <c r="J121" s="19"/>
       <c r="K121" s="20"/>
       <c r="L121" s="20"/>
@@ -17663,11 +17663,11 @@
       <c r="B122" s="36"/>
       <c r="C122" s="60"/>
       <c r="D122" s="70"/>
-      <c r="E122" s="95"/>
-      <c r="F122" s="95"/>
-      <c r="G122" s="95"/>
-      <c r="H122" s="99"/>
-      <c r="I122" s="101"/>
+      <c r="E122" s="94"/>
+      <c r="F122" s="94"/>
+      <c r="G122" s="94"/>
+      <c r="H122" s="96"/>
+      <c r="I122" s="98"/>
       <c r="J122" s="19"/>
       <c r="K122" s="20"/>
       <c r="L122" s="20"/>
@@ -17785,12 +17785,12 @@
       <c r="B123" s="36"/>
       <c r="C123" s="60"/>
       <c r="D123" s="70"/>
-      <c r="E123" s="95" t="s">
+      <c r="E123" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="F123" s="95"/>
-      <c r="G123" s="95"/>
-      <c r="H123" s="112">
+      <c r="F123" s="94"/>
+      <c r="G123" s="94"/>
+      <c r="H123" s="189">
         <v>45631</v>
       </c>
       <c r="I123" s="104"/>
@@ -17911,10 +17911,10 @@
       <c r="B124" s="36"/>
       <c r="C124" s="60"/>
       <c r="D124" s="70"/>
-      <c r="E124" s="95"/>
-      <c r="F124" s="95"/>
-      <c r="G124" s="95"/>
-      <c r="H124" s="112"/>
+      <c r="E124" s="94"/>
+      <c r="F124" s="94"/>
+      <c r="G124" s="94"/>
+      <c r="H124" s="189"/>
       <c r="I124" s="104"/>
       <c r="J124" s="62"/>
       <c r="K124" s="20"/>
@@ -18033,12 +18033,12 @@
       <c r="B125" s="36"/>
       <c r="C125" s="60"/>
       <c r="D125" s="70"/>
-      <c r="E125" s="95" t="s">
+      <c r="E125" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="F125" s="95"/>
-      <c r="G125" s="95"/>
-      <c r="H125" s="102">
+      <c r="F125" s="94"/>
+      <c r="G125" s="94"/>
+      <c r="H125" s="103">
         <v>45632</v>
       </c>
       <c r="I125" s="104"/>
@@ -18159,10 +18159,10 @@
       <c r="B126" s="36"/>
       <c r="C126" s="60"/>
       <c r="D126" s="70"/>
-      <c r="E126" s="95"/>
-      <c r="F126" s="95"/>
-      <c r="G126" s="95"/>
-      <c r="H126" s="102"/>
+      <c r="E126" s="94"/>
+      <c r="F126" s="94"/>
+      <c r="G126" s="94"/>
+      <c r="H126" s="103"/>
       <c r="I126" s="104"/>
       <c r="J126" s="62"/>
       <c r="K126" s="20"/>
@@ -18281,15 +18281,15 @@
       <c r="B127" s="36"/>
       <c r="C127" s="60"/>
       <c r="D127" s="70"/>
-      <c r="E127" s="95" t="s">
+      <c r="E127" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="F127" s="95"/>
-      <c r="G127" s="95"/>
-      <c r="H127" s="103">
+      <c r="F127" s="94"/>
+      <c r="G127" s="94"/>
+      <c r="H127" s="95">
         <v>45635</v>
       </c>
-      <c r="I127" s="118"/>
+      <c r="I127" s="97"/>
       <c r="J127" s="19"/>
       <c r="K127" s="20"/>
       <c r="L127" s="20"/>
@@ -18407,11 +18407,11 @@
       <c r="B128" s="36"/>
       <c r="C128" s="60"/>
       <c r="D128" s="70"/>
-      <c r="E128" s="117"/>
-      <c r="F128" s="117"/>
-      <c r="G128" s="117"/>
-      <c r="H128" s="99"/>
-      <c r="I128" s="101"/>
+      <c r="E128" s="190"/>
+      <c r="F128" s="190"/>
+      <c r="G128" s="190"/>
+      <c r="H128" s="96"/>
+      <c r="I128" s="98"/>
       <c r="J128" s="19"/>
       <c r="K128" s="20"/>
       <c r="L128" s="20"/>
@@ -18529,12 +18529,12 @@
       <c r="B129" s="71"/>
       <c r="C129" s="91"/>
       <c r="D129" s="70"/>
-      <c r="E129" s="106" t="s">
+      <c r="E129" s="181" t="s">
         <v>61</v>
       </c>
-      <c r="F129" s="107"/>
-      <c r="G129" s="108"/>
-      <c r="H129" s="102">
+      <c r="F129" s="113"/>
+      <c r="G129" s="114"/>
+      <c r="H129" s="103">
         <v>45638</v>
       </c>
       <c r="I129" s="104"/>
@@ -18655,10 +18655,10 @@
       <c r="B130" s="71"/>
       <c r="C130" s="91"/>
       <c r="D130" s="70"/>
-      <c r="E130" s="109"/>
-      <c r="F130" s="110"/>
-      <c r="G130" s="111"/>
-      <c r="H130" s="102"/>
+      <c r="E130" s="142"/>
+      <c r="F130" s="117"/>
+      <c r="G130" s="118"/>
+      <c r="H130" s="103"/>
       <c r="I130" s="104"/>
       <c r="J130" s="62"/>
       <c r="K130" s="20"/>
@@ -18776,16 +18776,16 @@
       <c r="A131" s="16"/>
       <c r="B131" s="71"/>
       <c r="C131" s="91"/>
-      <c r="D131" s="95" t="s">
+      <c r="D131" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="E131" s="95"/>
-      <c r="F131" s="95"/>
-      <c r="G131" s="95"/>
-      <c r="H131" s="103">
+      <c r="E131" s="94"/>
+      <c r="F131" s="94"/>
+      <c r="G131" s="94"/>
+      <c r="H131" s="95">
         <v>45635</v>
       </c>
-      <c r="I131" s="105"/>
+      <c r="I131" s="101"/>
       <c r="J131" s="62"/>
       <c r="K131" s="20"/>
       <c r="L131" s="20"/>
@@ -18902,12 +18902,12 @@
       <c r="A132" s="16"/>
       <c r="B132" s="71"/>
       <c r="C132" s="90"/>
-      <c r="D132" s="95"/>
-      <c r="E132" s="95"/>
-      <c r="F132" s="95"/>
-      <c r="G132" s="95"/>
-      <c r="H132" s="99"/>
-      <c r="I132" s="135"/>
+      <c r="D132" s="94"/>
+      <c r="E132" s="94"/>
+      <c r="F132" s="94"/>
+      <c r="G132" s="94"/>
+      <c r="H132" s="96"/>
+      <c r="I132" s="102"/>
       <c r="J132" s="62"/>
       <c r="K132" s="20"/>
       <c r="L132" s="20"/>
@@ -19023,15 +19023,15 @@
     <row r="133" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A133" s="16"/>
       <c r="B133" s="36"/>
-      <c r="C133" s="124" t="s">
+      <c r="C133" s="107" t="s">
         <v>67</v>
       </c>
-      <c r="D133" s="125"/>
-      <c r="E133" s="125"/>
-      <c r="F133" s="125"/>
-      <c r="G133" s="126"/>
-      <c r="H133" s="113"/>
-      <c r="I133" s="115"/>
+      <c r="D133" s="108"/>
+      <c r="E133" s="108"/>
+      <c r="F133" s="108"/>
+      <c r="G133" s="109"/>
+      <c r="H133" s="183"/>
+      <c r="I133" s="99"/>
       <c r="J133" s="66"/>
       <c r="K133" s="64"/>
       <c r="L133" s="64"/>
@@ -19147,13 +19147,13 @@
     <row r="134" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A134" s="16"/>
       <c r="B134" s="36"/>
-      <c r="C134" s="127"/>
-      <c r="D134" s="128"/>
-      <c r="E134" s="128"/>
-      <c r="F134" s="128"/>
-      <c r="G134" s="129"/>
-      <c r="H134" s="114"/>
-      <c r="I134" s="116"/>
+      <c r="C134" s="110"/>
+      <c r="D134" s="111"/>
+      <c r="E134" s="111"/>
+      <c r="F134" s="111"/>
+      <c r="G134" s="112"/>
+      <c r="H134" s="184"/>
+      <c r="I134" s="100"/>
       <c r="J134" s="66"/>
       <c r="K134" s="64"/>
       <c r="L134" s="64"/>
@@ -19270,14 +19270,14 @@
       <c r="A135" s="16"/>
       <c r="B135" s="36"/>
       <c r="C135" s="60"/>
-      <c r="D135" s="124" t="s">
+      <c r="D135" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="125"/>
-      <c r="F135" s="125"/>
-      <c r="G135" s="126"/>
-      <c r="H135" s="185"/>
-      <c r="I135" s="121"/>
+      <c r="E135" s="108"/>
+      <c r="F135" s="108"/>
+      <c r="G135" s="109"/>
+      <c r="H135" s="105"/>
+      <c r="I135" s="173"/>
       <c r="J135" s="63"/>
       <c r="K135" s="64"/>
       <c r="L135" s="64"/>
@@ -19394,12 +19394,12 @@
       <c r="A136" s="16"/>
       <c r="B136" s="36"/>
       <c r="C136" s="60"/>
-      <c r="D136" s="127"/>
-      <c r="E136" s="128"/>
-      <c r="F136" s="128"/>
-      <c r="G136" s="129"/>
-      <c r="H136" s="190"/>
-      <c r="I136" s="136"/>
+      <c r="D136" s="110"/>
+      <c r="E136" s="111"/>
+      <c r="F136" s="111"/>
+      <c r="G136" s="112"/>
+      <c r="H136" s="122"/>
+      <c r="I136" s="175"/>
       <c r="J136" s="63"/>
       <c r="K136" s="64"/>
       <c r="L136" s="64"/>
@@ -19517,15 +19517,15 @@
       <c r="B137" s="36"/>
       <c r="C137" s="72"/>
       <c r="D137" s="74"/>
-      <c r="E137" s="107" t="s">
+      <c r="E137" s="113" t="s">
         <v>73</v>
       </c>
-      <c r="F137" s="107"/>
-      <c r="G137" s="108"/>
-      <c r="H137" s="103">
+      <c r="F137" s="113"/>
+      <c r="G137" s="114"/>
+      <c r="H137" s="95">
         <v>45636</v>
       </c>
-      <c r="I137" s="105"/>
+      <c r="I137" s="101"/>
       <c r="J137" s="62"/>
       <c r="K137" s="20"/>
       <c r="L137" s="20"/>
@@ -19643,11 +19643,11 @@
       <c r="B138" s="36"/>
       <c r="C138" s="72"/>
       <c r="D138" s="70"/>
-      <c r="E138" s="177"/>
-      <c r="F138" s="177"/>
-      <c r="G138" s="178"/>
-      <c r="H138" s="99"/>
-      <c r="I138" s="135"/>
+      <c r="E138" s="115"/>
+      <c r="F138" s="115"/>
+      <c r="G138" s="116"/>
+      <c r="H138" s="96"/>
+      <c r="I138" s="102"/>
       <c r="J138" s="62"/>
       <c r="K138" s="20"/>
       <c r="L138" s="20"/>
@@ -19765,15 +19765,15 @@
       <c r="B139" s="36"/>
       <c r="C139" s="72"/>
       <c r="D139" s="70"/>
-      <c r="E139" s="107" t="s">
+      <c r="E139" s="113" t="s">
         <v>74</v>
       </c>
-      <c r="F139" s="107"/>
-      <c r="G139" s="108"/>
-      <c r="H139" s="103">
+      <c r="F139" s="113"/>
+      <c r="G139" s="114"/>
+      <c r="H139" s="95">
         <v>45637</v>
       </c>
-      <c r="I139" s="105"/>
+      <c r="I139" s="101"/>
       <c r="J139" s="62"/>
       <c r="K139" s="20"/>
       <c r="L139" s="20"/>
@@ -19891,11 +19891,11 @@
       <c r="B140" s="36"/>
       <c r="C140" s="72"/>
       <c r="D140" s="70"/>
-      <c r="E140" s="110"/>
-      <c r="F140" s="110"/>
-      <c r="G140" s="111"/>
-      <c r="H140" s="99"/>
-      <c r="I140" s="135"/>
+      <c r="E140" s="117"/>
+      <c r="F140" s="117"/>
+      <c r="G140" s="118"/>
+      <c r="H140" s="96"/>
+      <c r="I140" s="102"/>
       <c r="J140" s="62"/>
       <c r="K140" s="20"/>
       <c r="L140" s="20"/>
@@ -20012,13 +20012,13 @@
       <c r="A141" s="16"/>
       <c r="B141" s="36"/>
       <c r="C141" s="82"/>
-      <c r="D141" s="95" t="s">
+      <c r="D141" s="94" t="s">
         <v>80</v>
       </c>
-      <c r="E141" s="95"/>
-      <c r="F141" s="95"/>
-      <c r="G141" s="95"/>
-      <c r="H141" s="103">
+      <c r="E141" s="94"/>
+      <c r="F141" s="94"/>
+      <c r="G141" s="94"/>
+      <c r="H141" s="95">
         <v>45637</v>
       </c>
       <c r="I141" s="92"/>
@@ -20138,11 +20138,11 @@
       <c r="A142" s="16"/>
       <c r="B142" s="36"/>
       <c r="C142" s="82"/>
-      <c r="D142" s="95"/>
-      <c r="E142" s="95"/>
-      <c r="F142" s="95"/>
-      <c r="G142" s="95"/>
-      <c r="H142" s="99"/>
+      <c r="D142" s="94"/>
+      <c r="E142" s="94"/>
+      <c r="F142" s="94"/>
+      <c r="G142" s="94"/>
+      <c r="H142" s="96"/>
       <c r="I142" s="92"/>
       <c r="J142" s="62"/>
       <c r="K142" s="20"/>
@@ -20260,14 +20260,14 @@
       <c r="A143" s="16"/>
       <c r="B143" s="36"/>
       <c r="C143" s="72"/>
-      <c r="D143" s="187" t="s">
+      <c r="D143" s="119" t="s">
         <v>66</v>
       </c>
-      <c r="E143" s="188"/>
-      <c r="F143" s="188"/>
-      <c r="G143" s="189"/>
-      <c r="H143" s="185"/>
-      <c r="I143" s="115"/>
+      <c r="E143" s="120"/>
+      <c r="F143" s="120"/>
+      <c r="G143" s="121"/>
+      <c r="H143" s="105"/>
+      <c r="I143" s="99"/>
       <c r="J143" s="66"/>
       <c r="K143" s="64"/>
       <c r="L143" s="64"/>
@@ -20384,12 +20384,12 @@
       <c r="A144" s="16"/>
       <c r="B144" s="36"/>
       <c r="C144" s="72"/>
-      <c r="D144" s="127"/>
-      <c r="E144" s="128"/>
-      <c r="F144" s="128"/>
-      <c r="G144" s="129"/>
-      <c r="H144" s="186"/>
-      <c r="I144" s="116"/>
+      <c r="D144" s="110"/>
+      <c r="E144" s="111"/>
+      <c r="F144" s="111"/>
+      <c r="G144" s="112"/>
+      <c r="H144" s="106"/>
+      <c r="I144" s="100"/>
       <c r="J144" s="66"/>
       <c r="K144" s="64"/>
       <c r="L144" s="64"/>
@@ -20507,15 +20507,15 @@
       <c r="B145" s="36"/>
       <c r="C145" s="72"/>
       <c r="D145" s="74"/>
-      <c r="E145" s="107" t="s">
+      <c r="E145" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="F145" s="107"/>
-      <c r="G145" s="108"/>
-      <c r="H145" s="103">
+      <c r="F145" s="113"/>
+      <c r="G145" s="114"/>
+      <c r="H145" s="95">
         <v>45639</v>
       </c>
-      <c r="I145" s="105"/>
+      <c r="I145" s="101"/>
       <c r="J145" s="62"/>
       <c r="K145" s="20"/>
       <c r="L145" s="20"/>
@@ -20633,11 +20633,11 @@
       <c r="B146" s="36"/>
       <c r="C146" s="72"/>
       <c r="D146" s="70"/>
-      <c r="E146" s="177"/>
-      <c r="F146" s="177"/>
-      <c r="G146" s="178"/>
-      <c r="H146" s="99"/>
-      <c r="I146" s="135"/>
+      <c r="E146" s="115"/>
+      <c r="F146" s="115"/>
+      <c r="G146" s="116"/>
+      <c r="H146" s="96"/>
+      <c r="I146" s="102"/>
       <c r="J146" s="62"/>
       <c r="K146" s="20"/>
       <c r="L146" s="20"/>
@@ -20755,15 +20755,15 @@
       <c r="B147" s="36"/>
       <c r="C147" s="72"/>
       <c r="D147" s="70"/>
-      <c r="E147" s="107" t="s">
+      <c r="E147" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="F147" s="107"/>
-      <c r="G147" s="108"/>
-      <c r="H147" s="103">
+      <c r="F147" s="113"/>
+      <c r="G147" s="114"/>
+      <c r="H147" s="95">
         <v>45642</v>
       </c>
-      <c r="I147" s="105"/>
+      <c r="I147" s="101"/>
       <c r="J147" s="62"/>
       <c r="K147" s="20"/>
       <c r="L147" s="20"/>
@@ -20881,11 +20881,11 @@
       <c r="B148" s="36"/>
       <c r="C148" s="72"/>
       <c r="D148" s="70"/>
-      <c r="E148" s="177"/>
-      <c r="F148" s="177"/>
-      <c r="G148" s="178"/>
-      <c r="H148" s="99"/>
-      <c r="I148" s="135"/>
+      <c r="E148" s="115"/>
+      <c r="F148" s="115"/>
+      <c r="G148" s="116"/>
+      <c r="H148" s="96"/>
+      <c r="I148" s="102"/>
       <c r="J148" s="62"/>
       <c r="K148" s="20"/>
       <c r="L148" s="20"/>
@@ -21003,15 +21003,15 @@
       <c r="B149" s="36"/>
       <c r="C149" s="72"/>
       <c r="D149" s="70"/>
-      <c r="E149" s="107" t="s">
+      <c r="E149" s="113" t="s">
         <v>70</v>
       </c>
-      <c r="F149" s="107"/>
-      <c r="G149" s="108"/>
-      <c r="H149" s="103">
+      <c r="F149" s="113"/>
+      <c r="G149" s="114"/>
+      <c r="H149" s="95">
         <v>45643</v>
       </c>
-      <c r="I149" s="105"/>
+      <c r="I149" s="101"/>
       <c r="J149" s="62"/>
       <c r="K149" s="20"/>
       <c r="L149" s="20"/>
@@ -21129,11 +21129,11 @@
       <c r="B150" s="36"/>
       <c r="C150" s="72"/>
       <c r="D150" s="70"/>
-      <c r="E150" s="177"/>
-      <c r="F150" s="177"/>
-      <c r="G150" s="178"/>
-      <c r="H150" s="99"/>
-      <c r="I150" s="135"/>
+      <c r="E150" s="115"/>
+      <c r="F150" s="115"/>
+      <c r="G150" s="116"/>
+      <c r="H150" s="96"/>
+      <c r="I150" s="102"/>
       <c r="J150" s="62"/>
       <c r="K150" s="20"/>
       <c r="L150" s="20"/>
@@ -21251,15 +21251,15 @@
       <c r="B151" s="36"/>
       <c r="C151" s="72"/>
       <c r="D151" s="70"/>
-      <c r="E151" s="95" t="s">
+      <c r="E151" s="94" t="s">
         <v>75</v>
       </c>
-      <c r="F151" s="95"/>
-      <c r="G151" s="95"/>
-      <c r="H151" s="103">
+      <c r="F151" s="94"/>
+      <c r="G151" s="94"/>
+      <c r="H151" s="95">
         <v>45644</v>
       </c>
-      <c r="I151" s="105"/>
+      <c r="I151" s="101"/>
       <c r="J151" s="62"/>
       <c r="K151" s="20"/>
       <c r="L151" s="20"/>
@@ -21377,11 +21377,11 @@
       <c r="B152" s="36"/>
       <c r="C152" s="72"/>
       <c r="D152" s="70"/>
-      <c r="E152" s="95"/>
-      <c r="F152" s="95"/>
-      <c r="G152" s="95"/>
-      <c r="H152" s="99"/>
-      <c r="I152" s="135"/>
+      <c r="E152" s="94"/>
+      <c r="F152" s="94"/>
+      <c r="G152" s="94"/>
+      <c r="H152" s="96"/>
+      <c r="I152" s="102"/>
       <c r="J152" s="62"/>
       <c r="K152" s="20"/>
       <c r="L152" s="20"/>
@@ -21499,15 +21499,15 @@
       <c r="B153" s="36"/>
       <c r="C153" s="72"/>
       <c r="D153" s="70"/>
-      <c r="E153" s="95" t="s">
+      <c r="E153" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="F153" s="95"/>
-      <c r="G153" s="95"/>
-      <c r="H153" s="103">
+      <c r="F153" s="94"/>
+      <c r="G153" s="94"/>
+      <c r="H153" s="95">
         <v>45644</v>
       </c>
-      <c r="I153" s="105"/>
+      <c r="I153" s="101"/>
       <c r="J153" s="62"/>
       <c r="K153" s="20"/>
       <c r="L153" s="20"/>
@@ -21625,11 +21625,11 @@
       <c r="B154" s="36"/>
       <c r="C154" s="72"/>
       <c r="D154" s="70"/>
-      <c r="E154" s="95"/>
-      <c r="F154" s="95"/>
-      <c r="G154" s="95"/>
-      <c r="H154" s="99"/>
-      <c r="I154" s="135"/>
+      <c r="E154" s="94"/>
+      <c r="F154" s="94"/>
+      <c r="G154" s="94"/>
+      <c r="H154" s="96"/>
+      <c r="I154" s="102"/>
       <c r="J154" s="62"/>
       <c r="K154" s="20"/>
       <c r="L154" s="20"/>
@@ -21746,16 +21746,16 @@
       <c r="A155" s="1"/>
       <c r="B155" s="18"/>
       <c r="C155" s="60"/>
-      <c r="D155" s="96"/>
-      <c r="E155" s="94" t="s">
+      <c r="D155" s="186"/>
+      <c r="E155" s="185" t="s">
         <v>61</v>
       </c>
-      <c r="F155" s="95"/>
-      <c r="G155" s="95"/>
-      <c r="H155" s="98">
+      <c r="F155" s="94"/>
+      <c r="G155" s="94"/>
+      <c r="H155" s="187">
         <v>45645</v>
       </c>
-      <c r="I155" s="100"/>
+      <c r="I155" s="188"/>
       <c r="J155" s="19"/>
       <c r="K155" s="20"/>
       <c r="L155" s="20"/>
@@ -21872,12 +21872,12 @@
       <c r="A156" s="1"/>
       <c r="B156" s="18"/>
       <c r="C156" s="60"/>
-      <c r="D156" s="97"/>
-      <c r="E156" s="94"/>
-      <c r="F156" s="95"/>
-      <c r="G156" s="95"/>
-      <c r="H156" s="99"/>
-      <c r="I156" s="101"/>
+      <c r="D156" s="141"/>
+      <c r="E156" s="185"/>
+      <c r="F156" s="94"/>
+      <c r="G156" s="94"/>
+      <c r="H156" s="96"/>
+      <c r="I156" s="98"/>
       <c r="J156" s="19"/>
       <c r="K156" s="20"/>
       <c r="L156" s="20"/>
@@ -21994,16 +21994,16 @@
       <c r="A157" s="1"/>
       <c r="B157" s="93"/>
       <c r="C157" s="90"/>
-      <c r="D157" s="95" t="s">
+      <c r="D157" s="94" t="s">
         <v>81</v>
       </c>
-      <c r="E157" s="95"/>
-      <c r="F157" s="95"/>
-      <c r="G157" s="95"/>
-      <c r="H157" s="103">
+      <c r="E157" s="94"/>
+      <c r="F157" s="94"/>
+      <c r="G157" s="94"/>
+      <c r="H157" s="95">
         <v>45644</v>
       </c>
-      <c r="I157" s="118"/>
+      <c r="I157" s="97"/>
       <c r="J157" s="19"/>
       <c r="K157" s="20"/>
       <c r="L157" s="20"/>
@@ -22120,12 +22120,12 @@
       <c r="A158" s="1"/>
       <c r="B158" s="93"/>
       <c r="C158" s="90"/>
-      <c r="D158" s="95"/>
-      <c r="E158" s="95"/>
-      <c r="F158" s="95"/>
-      <c r="G158" s="95"/>
-      <c r="H158" s="99"/>
-      <c r="I158" s="101"/>
+      <c r="D158" s="94"/>
+      <c r="E158" s="94"/>
+      <c r="F158" s="94"/>
+      <c r="G158" s="94"/>
+      <c r="H158" s="96"/>
+      <c r="I158" s="98"/>
       <c r="J158" s="19"/>
       <c r="K158" s="20"/>
       <c r="L158" s="20"/>
@@ -22243,14 +22243,14 @@
       <c r="B159" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="C159" s="143" t="s">
+      <c r="C159" s="165" t="s">
         <v>31</v>
       </c>
-      <c r="D159" s="144"/>
-      <c r="E159" s="144"/>
-      <c r="F159" s="144"/>
-      <c r="G159" s="145"/>
-      <c r="H159" s="130" t="s">
+      <c r="D159" s="166"/>
+      <c r="E159" s="166"/>
+      <c r="F159" s="166"/>
+      <c r="G159" s="167"/>
+      <c r="H159" s="176" t="s">
         <v>57</v>
       </c>
       <c r="I159" s="104"/>
@@ -22369,11 +22369,11 @@
     <row r="160" spans="1:120" ht="9.75" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="87"/>
-      <c r="C160" s="146"/>
-      <c r="D160" s="147"/>
-      <c r="E160" s="147"/>
-      <c r="F160" s="147"/>
-      <c r="G160" s="148"/>
+      <c r="C160" s="168"/>
+      <c r="D160" s="169"/>
+      <c r="E160" s="169"/>
+      <c r="F160" s="169"/>
+      <c r="G160" s="170"/>
       <c r="H160" s="104"/>
       <c r="I160" s="104"/>
       <c r="J160" s="14"/>
@@ -22735,14 +22735,14 @@
     <row r="163" spans="1:120" ht="9.75" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
-      <c r="C163" s="137" t="s">
+      <c r="C163" s="160" t="s">
         <v>33</v>
       </c>
-      <c r="D163" s="138"/>
-      <c r="E163" s="138"/>
-      <c r="F163" s="138"/>
-      <c r="G163" s="139"/>
-      <c r="H163" s="130" t="s">
+      <c r="D163" s="132"/>
+      <c r="E163" s="132"/>
+      <c r="F163" s="132"/>
+      <c r="G163" s="161"/>
+      <c r="H163" s="176" t="s">
         <v>56</v>
       </c>
       <c r="I163" s="104"/>
@@ -22861,11 +22861,11 @@
     <row r="164" spans="1:120" ht="9.75" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
-      <c r="C164" s="140"/>
-      <c r="D164" s="141"/>
-      <c r="E164" s="141"/>
-      <c r="F164" s="141"/>
-      <c r="G164" s="142"/>
+      <c r="C164" s="162"/>
+      <c r="D164" s="163"/>
+      <c r="E164" s="163"/>
+      <c r="F164" s="163"/>
+      <c r="G164" s="164"/>
       <c r="H164" s="104"/>
       <c r="I164" s="104"/>
       <c r="J164" s="19"/>
@@ -36406,6 +36406,222 @@
     </row>
   </sheetData>
   <mergeCells count="240">
+    <mergeCell ref="E155:G156"/>
+    <mergeCell ref="D155:D156"/>
+    <mergeCell ref="H155:H156"/>
+    <mergeCell ref="I155:I156"/>
+    <mergeCell ref="H113:H114"/>
+    <mergeCell ref="I113:I114"/>
+    <mergeCell ref="H129:H130"/>
+    <mergeCell ref="I129:I130"/>
+    <mergeCell ref="E129:G130"/>
+    <mergeCell ref="H123:H124"/>
+    <mergeCell ref="I123:I124"/>
+    <mergeCell ref="I125:I126"/>
+    <mergeCell ref="H125:H126"/>
+    <mergeCell ref="H133:H134"/>
+    <mergeCell ref="I133:I134"/>
+    <mergeCell ref="E123:G124"/>
+    <mergeCell ref="E125:G126"/>
+    <mergeCell ref="E127:G128"/>
+    <mergeCell ref="E113:G114"/>
+    <mergeCell ref="E119:G120"/>
+    <mergeCell ref="E121:G122"/>
+    <mergeCell ref="H127:H128"/>
+    <mergeCell ref="I127:I128"/>
+    <mergeCell ref="H121:H122"/>
+    <mergeCell ref="H105:H106"/>
+    <mergeCell ref="I105:I106"/>
+    <mergeCell ref="H107:H108"/>
+    <mergeCell ref="I107:I108"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="H117:H118"/>
+    <mergeCell ref="I117:I118"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="I119:I120"/>
+    <mergeCell ref="H101:H102"/>
+    <mergeCell ref="I101:I102"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="I85:I86"/>
+    <mergeCell ref="H89:H90"/>
+    <mergeCell ref="I89:I90"/>
+    <mergeCell ref="E81:G82"/>
+    <mergeCell ref="E83:G84"/>
+    <mergeCell ref="E91:G92"/>
+    <mergeCell ref="E93:G94"/>
+    <mergeCell ref="E95:G96"/>
+    <mergeCell ref="E97:G98"/>
+    <mergeCell ref="E99:G100"/>
+    <mergeCell ref="E85:G86"/>
+    <mergeCell ref="D89:G90"/>
+    <mergeCell ref="H75:H76"/>
+    <mergeCell ref="H159:H160"/>
+    <mergeCell ref="H163:H164"/>
+    <mergeCell ref="H161:H162"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="H59:H60"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="H77:H78"/>
+    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="H93:H94"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="H111:H112"/>
+    <mergeCell ref="I163:I164"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="I159:I160"/>
+    <mergeCell ref="I161:I162"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="I93:I94"/>
+    <mergeCell ref="I95:I96"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="I109:I110"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="I153:I154"/>
+    <mergeCell ref="I151:I152"/>
+    <mergeCell ref="I149:I150"/>
+    <mergeCell ref="I147:I148"/>
+    <mergeCell ref="I145:I146"/>
+    <mergeCell ref="I111:I112"/>
+    <mergeCell ref="I135:I136"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I67:I68"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="C163:G164"/>
+    <mergeCell ref="C159:G160"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="C31:G32"/>
+    <mergeCell ref="D33:G34"/>
+    <mergeCell ref="E35:G36"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="E43:G44"/>
+    <mergeCell ref="E45:G46"/>
+    <mergeCell ref="E47:G48"/>
+    <mergeCell ref="E49:G50"/>
+    <mergeCell ref="E51:G52"/>
+    <mergeCell ref="D53:G54"/>
+    <mergeCell ref="E55:G56"/>
+    <mergeCell ref="E57:G58"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="J3:CJ3"/>
+    <mergeCell ref="CK3:DO3"/>
+    <mergeCell ref="J4:AA4"/>
+    <mergeCell ref="AB4:BE4"/>
+    <mergeCell ref="BF4:CJ4"/>
+    <mergeCell ref="CK4:DO4"/>
+    <mergeCell ref="B7:G8"/>
+    <mergeCell ref="C9:G10"/>
+    <mergeCell ref="C11:G12"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="D13:G14"/>
+    <mergeCell ref="D15:G16"/>
+    <mergeCell ref="D17:G18"/>
+    <mergeCell ref="D19:G20"/>
+    <mergeCell ref="C21:G22"/>
+    <mergeCell ref="D23:G24"/>
+    <mergeCell ref="C25:G26"/>
+    <mergeCell ref="D27:G28"/>
+    <mergeCell ref="D29:G30"/>
+    <mergeCell ref="E147:G148"/>
+    <mergeCell ref="E149:G150"/>
+    <mergeCell ref="E151:G152"/>
+    <mergeCell ref="E59:G60"/>
+    <mergeCell ref="E61:G62"/>
+    <mergeCell ref="D63:G64"/>
+    <mergeCell ref="E67:G68"/>
+    <mergeCell ref="E65:G66"/>
+    <mergeCell ref="E69:G70"/>
+    <mergeCell ref="E71:G72"/>
+    <mergeCell ref="C73:G74"/>
+    <mergeCell ref="C75:G76"/>
+    <mergeCell ref="C77:G78"/>
+    <mergeCell ref="D79:G80"/>
+    <mergeCell ref="E109:G110"/>
+    <mergeCell ref="E111:G112"/>
+    <mergeCell ref="E101:G102"/>
+    <mergeCell ref="C105:G106"/>
+    <mergeCell ref="D107:G108"/>
+    <mergeCell ref="D117:G118"/>
+    <mergeCell ref="H145:H146"/>
+    <mergeCell ref="H143:H144"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="C133:G134"/>
+    <mergeCell ref="D135:G136"/>
+    <mergeCell ref="E137:G138"/>
+    <mergeCell ref="E139:G140"/>
+    <mergeCell ref="D143:G144"/>
+    <mergeCell ref="E145:G146"/>
+    <mergeCell ref="H135:H136"/>
     <mergeCell ref="D157:G158"/>
     <mergeCell ref="H157:H158"/>
     <mergeCell ref="I157:I158"/>
@@ -36430,222 +36646,6 @@
     <mergeCell ref="H151:H152"/>
     <mergeCell ref="H149:H150"/>
     <mergeCell ref="H147:H148"/>
-    <mergeCell ref="H145:H146"/>
-    <mergeCell ref="H143:H144"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="C133:G134"/>
-    <mergeCell ref="D135:G136"/>
-    <mergeCell ref="E137:G138"/>
-    <mergeCell ref="E139:G140"/>
-    <mergeCell ref="D143:G144"/>
-    <mergeCell ref="E145:G146"/>
-    <mergeCell ref="H135:H136"/>
-    <mergeCell ref="E147:G148"/>
-    <mergeCell ref="E149:G150"/>
-    <mergeCell ref="E151:G152"/>
-    <mergeCell ref="E59:G60"/>
-    <mergeCell ref="E61:G62"/>
-    <mergeCell ref="D63:G64"/>
-    <mergeCell ref="E67:G68"/>
-    <mergeCell ref="E65:G66"/>
-    <mergeCell ref="E69:G70"/>
-    <mergeCell ref="E71:G72"/>
-    <mergeCell ref="C73:G74"/>
-    <mergeCell ref="C75:G76"/>
-    <mergeCell ref="C77:G78"/>
-    <mergeCell ref="D79:G80"/>
-    <mergeCell ref="E109:G110"/>
-    <mergeCell ref="E111:G112"/>
-    <mergeCell ref="E101:G102"/>
-    <mergeCell ref="C105:G106"/>
-    <mergeCell ref="D107:G108"/>
-    <mergeCell ref="D117:G118"/>
-    <mergeCell ref="D13:G14"/>
-    <mergeCell ref="D15:G16"/>
-    <mergeCell ref="D17:G18"/>
-    <mergeCell ref="D19:G20"/>
-    <mergeCell ref="C21:G22"/>
-    <mergeCell ref="D23:G24"/>
-    <mergeCell ref="C25:G26"/>
-    <mergeCell ref="D27:G28"/>
-    <mergeCell ref="D29:G30"/>
-    <mergeCell ref="J3:CJ3"/>
-    <mergeCell ref="CK3:DO3"/>
-    <mergeCell ref="J4:AA4"/>
-    <mergeCell ref="AB4:BE4"/>
-    <mergeCell ref="BF4:CJ4"/>
-    <mergeCell ref="CK4:DO4"/>
-    <mergeCell ref="B7:G8"/>
-    <mergeCell ref="C9:G10"/>
-    <mergeCell ref="C11:G12"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="C163:G164"/>
-    <mergeCell ref="C159:G160"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="C31:G32"/>
-    <mergeCell ref="D33:G34"/>
-    <mergeCell ref="E35:G36"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="E43:G44"/>
-    <mergeCell ref="E45:G46"/>
-    <mergeCell ref="E47:G48"/>
-    <mergeCell ref="E49:G50"/>
-    <mergeCell ref="E51:G52"/>
-    <mergeCell ref="D53:G54"/>
-    <mergeCell ref="E55:G56"/>
-    <mergeCell ref="E57:G58"/>
-    <mergeCell ref="I53:I54"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="I159:I160"/>
-    <mergeCell ref="I161:I162"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="I93:I94"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="I109:I110"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="I153:I154"/>
-    <mergeCell ref="I151:I152"/>
-    <mergeCell ref="I149:I150"/>
-    <mergeCell ref="I147:I148"/>
-    <mergeCell ref="I145:I146"/>
-    <mergeCell ref="I111:I112"/>
-    <mergeCell ref="I135:I136"/>
-    <mergeCell ref="I163:I164"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="H75:H76"/>
-    <mergeCell ref="H159:H160"/>
-    <mergeCell ref="H163:H164"/>
-    <mergeCell ref="H161:H162"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="H67:H68"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H59:H60"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="H77:H78"/>
-    <mergeCell ref="H81:H82"/>
-    <mergeCell ref="H83:H84"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="H93:H94"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="H111:H112"/>
-    <mergeCell ref="H101:H102"/>
-    <mergeCell ref="I101:I102"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="I85:I86"/>
-    <mergeCell ref="H89:H90"/>
-    <mergeCell ref="I89:I90"/>
-    <mergeCell ref="E81:G82"/>
-    <mergeCell ref="E83:G84"/>
-    <mergeCell ref="E91:G92"/>
-    <mergeCell ref="E93:G94"/>
-    <mergeCell ref="E95:G96"/>
-    <mergeCell ref="E97:G98"/>
-    <mergeCell ref="E99:G100"/>
-    <mergeCell ref="E85:G86"/>
-    <mergeCell ref="D89:G90"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="H105:H106"/>
-    <mergeCell ref="I105:I106"/>
-    <mergeCell ref="H107:H108"/>
-    <mergeCell ref="I107:I108"/>
-    <mergeCell ref="H109:H110"/>
-    <mergeCell ref="H117:H118"/>
-    <mergeCell ref="I117:I118"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="I119:I120"/>
-    <mergeCell ref="E155:G156"/>
-    <mergeCell ref="D155:D156"/>
-    <mergeCell ref="H155:H156"/>
-    <mergeCell ref="I155:I156"/>
-    <mergeCell ref="H113:H114"/>
-    <mergeCell ref="I113:I114"/>
-    <mergeCell ref="H129:H130"/>
-    <mergeCell ref="I129:I130"/>
-    <mergeCell ref="E129:G130"/>
-    <mergeCell ref="H123:H124"/>
-    <mergeCell ref="I123:I124"/>
-    <mergeCell ref="I125:I126"/>
-    <mergeCell ref="H125:H126"/>
-    <mergeCell ref="H133:H134"/>
-    <mergeCell ref="I133:I134"/>
-    <mergeCell ref="E123:G124"/>
-    <mergeCell ref="E125:G126"/>
-    <mergeCell ref="E127:G128"/>
-    <mergeCell ref="E113:G114"/>
-    <mergeCell ref="E119:G120"/>
-    <mergeCell ref="E121:G122"/>
-    <mergeCell ref="H127:H128"/>
-    <mergeCell ref="I127:I128"/>
-    <mergeCell ref="H121:H122"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <conditionalFormatting sqref="J7">

--- a/docs/【DIGITAL OJT】WBS.xlsx
+++ b/docs/【DIGITAL OJT】WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIGITALOJT\digital-ojt-development-cause-DroneInventorySystem\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E77BC1D-D0C3-4415-B16B-D2FFB11BDC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F0844E-5EC9-4966-9992-975F9F8D1429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14940" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1328,7 +1328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1481,19 +1481,67 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1502,22 +1550,25 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1538,110 +1589,29 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1667,63 +1637,101 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2074,7 +2082,9 @@
     <col min="1" max="7" width="5" customWidth="1"/>
     <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="119" width="3.44140625" customWidth="1"/>
+    <col min="10" max="61" width="3.44140625" customWidth="1"/>
+    <col min="62" max="63" width="3.44140625" style="197" customWidth="1"/>
+    <col min="64" max="119" width="3.44140625" customWidth="1"/>
     <col min="120" max="120" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2138,8 +2148,8 @@
       <c r="BG1" s="2"/>
       <c r="BH1" s="2"/>
       <c r="BI1" s="2"/>
-      <c r="BJ1" s="2"/>
-      <c r="BK1" s="2"/>
+      <c r="BJ1" s="198"/>
+      <c r="BK1" s="198"/>
       <c r="BL1" s="2"/>
       <c r="BM1" s="2"/>
       <c r="BN1" s="2"/>
@@ -2260,8 +2270,8 @@
       <c r="BG2" s="2"/>
       <c r="BH2" s="2"/>
       <c r="BI2" s="2"/>
-      <c r="BJ2" s="2"/>
-      <c r="BK2" s="2"/>
+      <c r="BJ2" s="198"/>
+      <c r="BK2" s="198"/>
       <c r="BL2" s="2"/>
       <c r="BM2" s="2"/>
       <c r="BN2" s="2"/>
@@ -2330,120 +2340,120 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="J3" s="153">
+      <c r="J3" s="165">
         <v>2024</v>
       </c>
-      <c r="K3" s="154"/>
-      <c r="L3" s="154"/>
-      <c r="M3" s="154"/>
-      <c r="N3" s="154"/>
-      <c r="O3" s="154"/>
-      <c r="P3" s="154"/>
-      <c r="Q3" s="154"/>
-      <c r="R3" s="154"/>
-      <c r="S3" s="154"/>
-      <c r="T3" s="154"/>
-      <c r="U3" s="154"/>
-      <c r="V3" s="154"/>
-      <c r="W3" s="154"/>
-      <c r="X3" s="154"/>
-      <c r="Y3" s="154"/>
-      <c r="Z3" s="154"/>
-      <c r="AA3" s="154"/>
-      <c r="AB3" s="154"/>
-      <c r="AC3" s="154"/>
-      <c r="AD3" s="154"/>
-      <c r="AE3" s="154"/>
-      <c r="AF3" s="154"/>
-      <c r="AG3" s="154"/>
-      <c r="AH3" s="154"/>
-      <c r="AI3" s="154"/>
-      <c r="AJ3" s="154"/>
-      <c r="AK3" s="154"/>
-      <c r="AL3" s="154"/>
-      <c r="AM3" s="154"/>
-      <c r="AN3" s="154"/>
-      <c r="AO3" s="154"/>
-      <c r="AP3" s="154"/>
-      <c r="AQ3" s="154"/>
-      <c r="AR3" s="154"/>
-      <c r="AS3" s="154"/>
-      <c r="AT3" s="154"/>
-      <c r="AU3" s="154"/>
-      <c r="AV3" s="154"/>
-      <c r="AW3" s="154"/>
-      <c r="AX3" s="154"/>
-      <c r="AY3" s="154"/>
-      <c r="AZ3" s="154"/>
-      <c r="BA3" s="154"/>
-      <c r="BB3" s="154"/>
-      <c r="BC3" s="154"/>
-      <c r="BD3" s="154"/>
-      <c r="BE3" s="154"/>
-      <c r="BF3" s="154"/>
-      <c r="BG3" s="154"/>
-      <c r="BH3" s="154"/>
-      <c r="BI3" s="154"/>
-      <c r="BJ3" s="154"/>
-      <c r="BK3" s="154"/>
-      <c r="BL3" s="154"/>
-      <c r="BM3" s="154"/>
-      <c r="BN3" s="154"/>
-      <c r="BO3" s="154"/>
-      <c r="BP3" s="154"/>
-      <c r="BQ3" s="154"/>
-      <c r="BR3" s="154"/>
-      <c r="BS3" s="154"/>
-      <c r="BT3" s="154"/>
-      <c r="BU3" s="154"/>
-      <c r="BV3" s="154"/>
-      <c r="BW3" s="154"/>
-      <c r="BX3" s="154"/>
-      <c r="BY3" s="154"/>
-      <c r="BZ3" s="154"/>
-      <c r="CA3" s="154"/>
-      <c r="CB3" s="154"/>
-      <c r="CC3" s="154"/>
-      <c r="CD3" s="154"/>
-      <c r="CE3" s="154"/>
-      <c r="CF3" s="154"/>
-      <c r="CG3" s="154"/>
-      <c r="CH3" s="154"/>
-      <c r="CI3" s="154"/>
-      <c r="CJ3" s="155"/>
-      <c r="CK3" s="153">
+      <c r="K3" s="166"/>
+      <c r="L3" s="166"/>
+      <c r="M3" s="166"/>
+      <c r="N3" s="166"/>
+      <c r="O3" s="166"/>
+      <c r="P3" s="166"/>
+      <c r="Q3" s="166"/>
+      <c r="R3" s="166"/>
+      <c r="S3" s="166"/>
+      <c r="T3" s="166"/>
+      <c r="U3" s="166"/>
+      <c r="V3" s="166"/>
+      <c r="W3" s="166"/>
+      <c r="X3" s="166"/>
+      <c r="Y3" s="166"/>
+      <c r="Z3" s="166"/>
+      <c r="AA3" s="166"/>
+      <c r="AB3" s="166"/>
+      <c r="AC3" s="166"/>
+      <c r="AD3" s="166"/>
+      <c r="AE3" s="166"/>
+      <c r="AF3" s="166"/>
+      <c r="AG3" s="166"/>
+      <c r="AH3" s="166"/>
+      <c r="AI3" s="166"/>
+      <c r="AJ3" s="166"/>
+      <c r="AK3" s="166"/>
+      <c r="AL3" s="166"/>
+      <c r="AM3" s="166"/>
+      <c r="AN3" s="166"/>
+      <c r="AO3" s="166"/>
+      <c r="AP3" s="166"/>
+      <c r="AQ3" s="166"/>
+      <c r="AR3" s="166"/>
+      <c r="AS3" s="166"/>
+      <c r="AT3" s="166"/>
+      <c r="AU3" s="166"/>
+      <c r="AV3" s="166"/>
+      <c r="AW3" s="166"/>
+      <c r="AX3" s="166"/>
+      <c r="AY3" s="166"/>
+      <c r="AZ3" s="166"/>
+      <c r="BA3" s="166"/>
+      <c r="BB3" s="166"/>
+      <c r="BC3" s="166"/>
+      <c r="BD3" s="166"/>
+      <c r="BE3" s="166"/>
+      <c r="BF3" s="166"/>
+      <c r="BG3" s="166"/>
+      <c r="BH3" s="166"/>
+      <c r="BI3" s="166"/>
+      <c r="BJ3" s="166"/>
+      <c r="BK3" s="166"/>
+      <c r="BL3" s="166"/>
+      <c r="BM3" s="166"/>
+      <c r="BN3" s="166"/>
+      <c r="BO3" s="166"/>
+      <c r="BP3" s="166"/>
+      <c r="BQ3" s="166"/>
+      <c r="BR3" s="166"/>
+      <c r="BS3" s="166"/>
+      <c r="BT3" s="166"/>
+      <c r="BU3" s="166"/>
+      <c r="BV3" s="166"/>
+      <c r="BW3" s="166"/>
+      <c r="BX3" s="166"/>
+      <c r="BY3" s="166"/>
+      <c r="BZ3" s="166"/>
+      <c r="CA3" s="166"/>
+      <c r="CB3" s="166"/>
+      <c r="CC3" s="166"/>
+      <c r="CD3" s="166"/>
+      <c r="CE3" s="166"/>
+      <c r="CF3" s="166"/>
+      <c r="CG3" s="166"/>
+      <c r="CH3" s="166"/>
+      <c r="CI3" s="166"/>
+      <c r="CJ3" s="167"/>
+      <c r="CK3" s="165">
         <v>2025</v>
       </c>
-      <c r="CL3" s="154"/>
-      <c r="CM3" s="154"/>
-      <c r="CN3" s="154"/>
-      <c r="CO3" s="154"/>
-      <c r="CP3" s="154"/>
-      <c r="CQ3" s="154"/>
-      <c r="CR3" s="154"/>
-      <c r="CS3" s="154"/>
-      <c r="CT3" s="154"/>
-      <c r="CU3" s="154"/>
-      <c r="CV3" s="154"/>
-      <c r="CW3" s="154"/>
-      <c r="CX3" s="154"/>
-      <c r="CY3" s="154"/>
-      <c r="CZ3" s="154"/>
-      <c r="DA3" s="154"/>
-      <c r="DB3" s="154"/>
-      <c r="DC3" s="154"/>
-      <c r="DD3" s="154"/>
-      <c r="DE3" s="154"/>
-      <c r="DF3" s="154"/>
-      <c r="DG3" s="154"/>
-      <c r="DH3" s="154"/>
-      <c r="DI3" s="154"/>
-      <c r="DJ3" s="154"/>
-      <c r="DK3" s="154"/>
-      <c r="DL3" s="154"/>
-      <c r="DM3" s="154"/>
-      <c r="DN3" s="154"/>
-      <c r="DO3" s="155"/>
+      <c r="CL3" s="166"/>
+      <c r="CM3" s="166"/>
+      <c r="CN3" s="166"/>
+      <c r="CO3" s="166"/>
+      <c r="CP3" s="166"/>
+      <c r="CQ3" s="166"/>
+      <c r="CR3" s="166"/>
+      <c r="CS3" s="166"/>
+      <c r="CT3" s="166"/>
+      <c r="CU3" s="166"/>
+      <c r="CV3" s="166"/>
+      <c r="CW3" s="166"/>
+      <c r="CX3" s="166"/>
+      <c r="CY3" s="166"/>
+      <c r="CZ3" s="166"/>
+      <c r="DA3" s="166"/>
+      <c r="DB3" s="166"/>
+      <c r="DC3" s="166"/>
+      <c r="DD3" s="166"/>
+      <c r="DE3" s="166"/>
+      <c r="DF3" s="166"/>
+      <c r="DG3" s="166"/>
+      <c r="DH3" s="166"/>
+      <c r="DI3" s="166"/>
+      <c r="DJ3" s="166"/>
+      <c r="DK3" s="166"/>
+      <c r="DL3" s="166"/>
+      <c r="DM3" s="166"/>
+      <c r="DN3" s="166"/>
+      <c r="DO3" s="167"/>
       <c r="DP3" s="1"/>
     </row>
     <row r="4" spans="1:120" ht="18" customHeight="1">
@@ -2458,124 +2468,124 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="J4" s="153">
+      <c r="J4" s="165">
         <v>10</v>
       </c>
-      <c r="K4" s="154"/>
-      <c r="L4" s="154"/>
-      <c r="M4" s="154"/>
-      <c r="N4" s="154"/>
-      <c r="O4" s="154"/>
-      <c r="P4" s="154"/>
-      <c r="Q4" s="154"/>
-      <c r="R4" s="154"/>
-      <c r="S4" s="154"/>
-      <c r="T4" s="154"/>
-      <c r="U4" s="154"/>
-      <c r="V4" s="154"/>
-      <c r="W4" s="154"/>
-      <c r="X4" s="154"/>
-      <c r="Y4" s="154"/>
-      <c r="Z4" s="154"/>
-      <c r="AA4" s="155"/>
-      <c r="AB4" s="153">
+      <c r="K4" s="166"/>
+      <c r="L4" s="166"/>
+      <c r="M4" s="166"/>
+      <c r="N4" s="166"/>
+      <c r="O4" s="166"/>
+      <c r="P4" s="166"/>
+      <c r="Q4" s="166"/>
+      <c r="R4" s="166"/>
+      <c r="S4" s="166"/>
+      <c r="T4" s="166"/>
+      <c r="U4" s="166"/>
+      <c r="V4" s="166"/>
+      <c r="W4" s="166"/>
+      <c r="X4" s="166"/>
+      <c r="Y4" s="166"/>
+      <c r="Z4" s="166"/>
+      <c r="AA4" s="167"/>
+      <c r="AB4" s="165">
         <v>11</v>
       </c>
-      <c r="AC4" s="154"/>
-      <c r="AD4" s="154"/>
-      <c r="AE4" s="154"/>
-      <c r="AF4" s="154"/>
-      <c r="AG4" s="154"/>
-      <c r="AH4" s="154"/>
-      <c r="AI4" s="154"/>
-      <c r="AJ4" s="154"/>
-      <c r="AK4" s="154"/>
-      <c r="AL4" s="154"/>
-      <c r="AM4" s="154"/>
-      <c r="AN4" s="154"/>
-      <c r="AO4" s="154"/>
-      <c r="AP4" s="154"/>
-      <c r="AQ4" s="154"/>
-      <c r="AR4" s="154"/>
-      <c r="AS4" s="154"/>
-      <c r="AT4" s="154"/>
-      <c r="AU4" s="154"/>
-      <c r="AV4" s="154"/>
-      <c r="AW4" s="154"/>
-      <c r="AX4" s="154"/>
-      <c r="AY4" s="154"/>
-      <c r="AZ4" s="154"/>
-      <c r="BA4" s="154"/>
-      <c r="BB4" s="154"/>
-      <c r="BC4" s="154"/>
-      <c r="BD4" s="154"/>
-      <c r="BE4" s="155"/>
-      <c r="BF4" s="153">
+      <c r="AC4" s="166"/>
+      <c r="AD4" s="166"/>
+      <c r="AE4" s="166"/>
+      <c r="AF4" s="166"/>
+      <c r="AG4" s="166"/>
+      <c r="AH4" s="166"/>
+      <c r="AI4" s="166"/>
+      <c r="AJ4" s="166"/>
+      <c r="AK4" s="166"/>
+      <c r="AL4" s="166"/>
+      <c r="AM4" s="166"/>
+      <c r="AN4" s="166"/>
+      <c r="AO4" s="166"/>
+      <c r="AP4" s="166"/>
+      <c r="AQ4" s="166"/>
+      <c r="AR4" s="166"/>
+      <c r="AS4" s="166"/>
+      <c r="AT4" s="166"/>
+      <c r="AU4" s="166"/>
+      <c r="AV4" s="166"/>
+      <c r="AW4" s="166"/>
+      <c r="AX4" s="166"/>
+      <c r="AY4" s="166"/>
+      <c r="AZ4" s="166"/>
+      <c r="BA4" s="166"/>
+      <c r="BB4" s="166"/>
+      <c r="BC4" s="166"/>
+      <c r="BD4" s="166"/>
+      <c r="BE4" s="167"/>
+      <c r="BF4" s="165">
         <v>12</v>
       </c>
-      <c r="BG4" s="154"/>
-      <c r="BH4" s="154"/>
-      <c r="BI4" s="154"/>
-      <c r="BJ4" s="154"/>
-      <c r="BK4" s="154"/>
-      <c r="BL4" s="154"/>
-      <c r="BM4" s="154"/>
-      <c r="BN4" s="154"/>
-      <c r="BO4" s="154"/>
-      <c r="BP4" s="154"/>
-      <c r="BQ4" s="154"/>
-      <c r="BR4" s="154"/>
-      <c r="BS4" s="154"/>
-      <c r="BT4" s="154"/>
-      <c r="BU4" s="154"/>
-      <c r="BV4" s="154"/>
-      <c r="BW4" s="154"/>
-      <c r="BX4" s="154"/>
-      <c r="BY4" s="154"/>
-      <c r="BZ4" s="154"/>
-      <c r="CA4" s="154"/>
-      <c r="CB4" s="154"/>
-      <c r="CC4" s="154"/>
-      <c r="CD4" s="154"/>
-      <c r="CE4" s="154"/>
-      <c r="CF4" s="154"/>
-      <c r="CG4" s="154"/>
-      <c r="CH4" s="154"/>
-      <c r="CI4" s="154"/>
-      <c r="CJ4" s="155"/>
-      <c r="CK4" s="153">
+      <c r="BG4" s="166"/>
+      <c r="BH4" s="166"/>
+      <c r="BI4" s="166"/>
+      <c r="BJ4" s="166"/>
+      <c r="BK4" s="166"/>
+      <c r="BL4" s="166"/>
+      <c r="BM4" s="166"/>
+      <c r="BN4" s="166"/>
+      <c r="BO4" s="166"/>
+      <c r="BP4" s="166"/>
+      <c r="BQ4" s="166"/>
+      <c r="BR4" s="166"/>
+      <c r="BS4" s="166"/>
+      <c r="BT4" s="166"/>
+      <c r="BU4" s="166"/>
+      <c r="BV4" s="166"/>
+      <c r="BW4" s="166"/>
+      <c r="BX4" s="166"/>
+      <c r="BY4" s="166"/>
+      <c r="BZ4" s="166"/>
+      <c r="CA4" s="166"/>
+      <c r="CB4" s="166"/>
+      <c r="CC4" s="166"/>
+      <c r="CD4" s="166"/>
+      <c r="CE4" s="166"/>
+      <c r="CF4" s="166"/>
+      <c r="CG4" s="166"/>
+      <c r="CH4" s="166"/>
+      <c r="CI4" s="166"/>
+      <c r="CJ4" s="167"/>
+      <c r="CK4" s="165">
         <v>1</v>
       </c>
-      <c r="CL4" s="154"/>
-      <c r="CM4" s="154"/>
-      <c r="CN4" s="154"/>
-      <c r="CO4" s="154"/>
-      <c r="CP4" s="154"/>
-      <c r="CQ4" s="154"/>
-      <c r="CR4" s="154"/>
-      <c r="CS4" s="154"/>
-      <c r="CT4" s="154"/>
-      <c r="CU4" s="154"/>
-      <c r="CV4" s="154"/>
-      <c r="CW4" s="154"/>
-      <c r="CX4" s="154"/>
-      <c r="CY4" s="154"/>
-      <c r="CZ4" s="154"/>
-      <c r="DA4" s="154"/>
-      <c r="DB4" s="154"/>
-      <c r="DC4" s="154"/>
-      <c r="DD4" s="154"/>
-      <c r="DE4" s="154"/>
-      <c r="DF4" s="154"/>
-      <c r="DG4" s="154"/>
-      <c r="DH4" s="154"/>
-      <c r="DI4" s="154"/>
-      <c r="DJ4" s="154"/>
-      <c r="DK4" s="154"/>
-      <c r="DL4" s="154"/>
-      <c r="DM4" s="154"/>
-      <c r="DN4" s="154"/>
-      <c r="DO4" s="155"/>
+      <c r="CL4" s="166"/>
+      <c r="CM4" s="166"/>
+      <c r="CN4" s="166"/>
+      <c r="CO4" s="166"/>
+      <c r="CP4" s="166"/>
+      <c r="CQ4" s="166"/>
+      <c r="CR4" s="166"/>
+      <c r="CS4" s="166"/>
+      <c r="CT4" s="166"/>
+      <c r="CU4" s="166"/>
+      <c r="CV4" s="166"/>
+      <c r="CW4" s="166"/>
+      <c r="CX4" s="166"/>
+      <c r="CY4" s="166"/>
+      <c r="CZ4" s="166"/>
+      <c r="DA4" s="166"/>
+      <c r="DB4" s="166"/>
+      <c r="DC4" s="166"/>
+      <c r="DD4" s="166"/>
+      <c r="DE4" s="166"/>
+      <c r="DF4" s="166"/>
+      <c r="DG4" s="166"/>
+      <c r="DH4" s="166"/>
+      <c r="DI4" s="166"/>
+      <c r="DJ4" s="166"/>
+      <c r="DK4" s="166"/>
+      <c r="DL4" s="166"/>
+      <c r="DM4" s="166"/>
+      <c r="DN4" s="166"/>
+      <c r="DO4" s="167"/>
       <c r="DP4" s="6"/>
     </row>
     <row r="5" spans="1:120" ht="18" customHeight="1">
@@ -3370,18 +3380,18 @@
     </row>
     <row r="7" spans="1:120" ht="9.75" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="156" t="s">
+      <c r="B7" s="168" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="124"/>
-      <c r="D7" s="124"/>
-      <c r="E7" s="124"/>
-      <c r="F7" s="124"/>
-      <c r="G7" s="144"/>
-      <c r="H7" s="158" t="s">
+      <c r="C7" s="156"/>
+      <c r="D7" s="156"/>
+      <c r="E7" s="156"/>
+      <c r="F7" s="156"/>
+      <c r="G7" s="169"/>
+      <c r="H7" s="134" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="158" t="s">
+      <c r="I7" s="134" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="38"/>
@@ -3436,8 +3446,8 @@
       <c r="BG7" s="13"/>
       <c r="BH7" s="13"/>
       <c r="BI7" s="13"/>
-      <c r="BJ7" s="13"/>
-      <c r="BK7" s="13"/>
+      <c r="BJ7" s="192"/>
+      <c r="BK7" s="192"/>
       <c r="BL7" s="13"/>
       <c r="BM7" s="13"/>
       <c r="BN7" s="13"/>
@@ -3498,14 +3508,14 @@
     </row>
     <row r="8" spans="1:120" ht="9.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="126"/>
-      <c r="C8" s="127"/>
-      <c r="D8" s="127"/>
-      <c r="E8" s="127"/>
-      <c r="F8" s="127"/>
-      <c r="G8" s="131"/>
-      <c r="H8" s="158"/>
-      <c r="I8" s="158"/>
+      <c r="B8" s="158"/>
+      <c r="C8" s="159"/>
+      <c r="D8" s="159"/>
+      <c r="E8" s="159"/>
+      <c r="F8" s="159"/>
+      <c r="G8" s="160"/>
+      <c r="H8" s="134"/>
+      <c r="I8" s="134"/>
       <c r="J8" s="39"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
@@ -3558,8 +3568,8 @@
       <c r="BG8" s="15"/>
       <c r="BH8" s="15"/>
       <c r="BI8" s="15"/>
-      <c r="BJ8" s="15"/>
-      <c r="BK8" s="15"/>
+      <c r="BJ8" s="193"/>
+      <c r="BK8" s="193"/>
       <c r="BL8" s="15"/>
       <c r="BM8" s="15"/>
       <c r="BN8" s="15"/>
@@ -3621,15 +3631,15 @@
     <row r="9" spans="1:120" ht="9.75" customHeight="1">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
-      <c r="C9" s="157" t="s">
+      <c r="C9" s="170" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="146"/>
-      <c r="E9" s="146"/>
-      <c r="F9" s="146"/>
-      <c r="G9" s="134"/>
-      <c r="H9" s="159"/>
-      <c r="I9" s="159"/>
+      <c r="D9" s="150"/>
+      <c r="E9" s="150"/>
+      <c r="F9" s="150"/>
+      <c r="G9" s="154"/>
+      <c r="H9" s="131"/>
+      <c r="I9" s="131"/>
       <c r="J9" s="42"/>
       <c r="K9" s="42"/>
       <c r="L9" s="44"/>
@@ -3682,8 +3692,8 @@
       <c r="BG9" s="44"/>
       <c r="BH9" s="44"/>
       <c r="BI9" s="44"/>
-      <c r="BJ9" s="44"/>
-      <c r="BK9" s="44"/>
+      <c r="BJ9" s="194"/>
+      <c r="BK9" s="194"/>
       <c r="BL9" s="45"/>
       <c r="BM9" s="45"/>
       <c r="BN9" s="44"/>
@@ -3745,13 +3755,13 @@
     <row r="10" spans="1:120" ht="9.75" customHeight="1">
       <c r="A10" s="16"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="133"/>
-      <c r="D10" s="127"/>
-      <c r="E10" s="127"/>
-      <c r="F10" s="127"/>
-      <c r="G10" s="131"/>
-      <c r="H10" s="159"/>
-      <c r="I10" s="159"/>
+      <c r="C10" s="171"/>
+      <c r="D10" s="159"/>
+      <c r="E10" s="159"/>
+      <c r="F10" s="159"/>
+      <c r="G10" s="160"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="131"/>
       <c r="J10" s="46"/>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
@@ -3804,8 +3814,8 @@
       <c r="BG10" s="47"/>
       <c r="BH10" s="47"/>
       <c r="BI10" s="47"/>
-      <c r="BJ10" s="47"/>
-      <c r="BK10" s="47"/>
+      <c r="BJ10" s="64"/>
+      <c r="BK10" s="64"/>
       <c r="BL10" s="48"/>
       <c r="BM10" s="48"/>
       <c r="BN10" s="47"/>
@@ -3867,15 +3877,15 @@
     <row r="11" spans="1:120" ht="9.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="145" t="s">
+      <c r="C11" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="146"/>
-      <c r="E11" s="146"/>
-      <c r="F11" s="146"/>
-      <c r="G11" s="134"/>
-      <c r="H11" s="159"/>
-      <c r="I11" s="159"/>
+      <c r="D11" s="150"/>
+      <c r="E11" s="150"/>
+      <c r="F11" s="150"/>
+      <c r="G11" s="154"/>
+      <c r="H11" s="131"/>
+      <c r="I11" s="131"/>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
       <c r="L11" s="44"/>
@@ -3928,8 +3938,8 @@
       <c r="BG11" s="44"/>
       <c r="BH11" s="44"/>
       <c r="BI11" s="44"/>
-      <c r="BJ11" s="44"/>
-      <c r="BK11" s="44"/>
+      <c r="BJ11" s="194"/>
+      <c r="BK11" s="194"/>
       <c r="BL11" s="45"/>
       <c r="BM11" s="45"/>
       <c r="BN11" s="44"/>
@@ -3991,13 +4001,13 @@
     <row r="12" spans="1:120" ht="9.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="133"/>
-      <c r="D12" s="127"/>
-      <c r="E12" s="127"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="131"/>
-      <c r="H12" s="159"/>
-      <c r="I12" s="159"/>
+      <c r="C12" s="171"/>
+      <c r="D12" s="159"/>
+      <c r="E12" s="159"/>
+      <c r="F12" s="159"/>
+      <c r="G12" s="160"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="131"/>
       <c r="J12" s="46"/>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
@@ -4050,8 +4060,8 @@
       <c r="BG12" s="47"/>
       <c r="BH12" s="47"/>
       <c r="BI12" s="47"/>
-      <c r="BJ12" s="47"/>
-      <c r="BK12" s="47"/>
+      <c r="BJ12" s="64"/>
+      <c r="BK12" s="64"/>
       <c r="BL12" s="48"/>
       <c r="BM12" s="48"/>
       <c r="BN12" s="47"/>
@@ -4114,13 +4124,13 @@
       <c r="A13" s="1"/>
       <c r="B13" s="18"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="143" t="s">
+      <c r="D13" s="173" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="124"/>
-      <c r="F13" s="124"/>
-      <c r="G13" s="144"/>
-      <c r="H13" s="176" t="s">
+      <c r="E13" s="156"/>
+      <c r="F13" s="156"/>
+      <c r="G13" s="169"/>
+      <c r="H13" s="130" t="s">
         <v>40</v>
       </c>
       <c r="I13" s="104">
@@ -4178,8 +4188,8 @@
       <c r="BG13" s="15"/>
       <c r="BH13" s="15"/>
       <c r="BI13" s="15"/>
-      <c r="BJ13" s="15"/>
-      <c r="BK13" s="15"/>
+      <c r="BJ13" s="193"/>
+      <c r="BK13" s="193"/>
       <c r="BL13" s="15"/>
       <c r="BM13" s="15"/>
       <c r="BN13" s="15"/>
@@ -4242,10 +4252,10 @@
       <c r="A14" s="1"/>
       <c r="B14" s="18"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="126"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="131"/>
+      <c r="D14" s="158"/>
+      <c r="E14" s="159"/>
+      <c r="F14" s="159"/>
+      <c r="G14" s="160"/>
       <c r="H14" s="104"/>
       <c r="I14" s="104"/>
       <c r="J14" s="39"/>
@@ -4300,8 +4310,8 @@
       <c r="BG14" s="15"/>
       <c r="BH14" s="15"/>
       <c r="BI14" s="15"/>
-      <c r="BJ14" s="15"/>
-      <c r="BK14" s="15"/>
+      <c r="BJ14" s="193"/>
+      <c r="BK14" s="193"/>
       <c r="BL14" s="15"/>
       <c r="BM14" s="15"/>
       <c r="BN14" s="15"/>
@@ -4364,13 +4374,13 @@
       <c r="A15" s="1"/>
       <c r="B15" s="18"/>
       <c r="C15" s="24"/>
-      <c r="D15" s="143" t="s">
+      <c r="D15" s="173" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="124"/>
-      <c r="F15" s="124"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="176" t="s">
+      <c r="E15" s="156"/>
+      <c r="F15" s="156"/>
+      <c r="G15" s="162"/>
+      <c r="H15" s="130" t="s">
         <v>40</v>
       </c>
       <c r="I15" s="104">
@@ -4428,8 +4438,8 @@
       <c r="BG15" s="15"/>
       <c r="BH15" s="15"/>
       <c r="BI15" s="15"/>
-      <c r="BJ15" s="15"/>
-      <c r="BK15" s="15"/>
+      <c r="BJ15" s="193"/>
+      <c r="BK15" s="193"/>
       <c r="BL15" s="15"/>
       <c r="BM15" s="15"/>
       <c r="BN15" s="15"/>
@@ -4492,10 +4502,10 @@
       <c r="A16" s="1"/>
       <c r="B16" s="18"/>
       <c r="C16" s="24"/>
-      <c r="D16" s="126"/>
-      <c r="E16" s="127"/>
-      <c r="F16" s="127"/>
-      <c r="G16" s="128"/>
+      <c r="D16" s="158"/>
+      <c r="E16" s="159"/>
+      <c r="F16" s="159"/>
+      <c r="G16" s="163"/>
       <c r="H16" s="104"/>
       <c r="I16" s="104"/>
       <c r="J16" s="14"/>
@@ -4550,8 +4560,8 @@
       <c r="BG16" s="15"/>
       <c r="BH16" s="15"/>
       <c r="BI16" s="15"/>
-      <c r="BJ16" s="15"/>
-      <c r="BK16" s="15"/>
+      <c r="BJ16" s="193"/>
+      <c r="BK16" s="193"/>
       <c r="BL16" s="15"/>
       <c r="BM16" s="15"/>
       <c r="BN16" s="15"/>
@@ -4614,13 +4624,13 @@
       <c r="A17" s="1"/>
       <c r="B17" s="18"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="143" t="s">
+      <c r="D17" s="173" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="124"/>
-      <c r="F17" s="124"/>
-      <c r="G17" s="125"/>
-      <c r="H17" s="176" t="s">
+      <c r="E17" s="156"/>
+      <c r="F17" s="156"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="130" t="s">
         <v>40</v>
       </c>
       <c r="I17" s="104">
@@ -4678,8 +4688,8 @@
       <c r="BG17" s="15"/>
       <c r="BH17" s="15"/>
       <c r="BI17" s="15"/>
-      <c r="BJ17" s="15"/>
-      <c r="BK17" s="15"/>
+      <c r="BJ17" s="193"/>
+      <c r="BK17" s="193"/>
       <c r="BL17" s="15"/>
       <c r="BM17" s="15"/>
       <c r="BN17" s="15"/>
@@ -4742,10 +4752,10 @@
       <c r="A18" s="1"/>
       <c r="B18" s="18"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="126"/>
-      <c r="E18" s="127"/>
-      <c r="F18" s="127"/>
-      <c r="G18" s="128"/>
+      <c r="D18" s="158"/>
+      <c r="E18" s="159"/>
+      <c r="F18" s="159"/>
+      <c r="G18" s="163"/>
       <c r="H18" s="104"/>
       <c r="I18" s="104"/>
       <c r="J18" s="14"/>
@@ -4800,8 +4810,8 @@
       <c r="BG18" s="15"/>
       <c r="BH18" s="15"/>
       <c r="BI18" s="15"/>
-      <c r="BJ18" s="15"/>
-      <c r="BK18" s="15"/>
+      <c r="BJ18" s="193"/>
+      <c r="BK18" s="193"/>
       <c r="BL18" s="15"/>
       <c r="BM18" s="15"/>
       <c r="BN18" s="15"/>
@@ -4864,13 +4874,13 @@
       <c r="A19" s="1"/>
       <c r="B19" s="18"/>
       <c r="C19" s="24"/>
-      <c r="D19" s="143" t="s">
+      <c r="D19" s="173" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="124"/>
-      <c r="F19" s="124"/>
-      <c r="G19" s="125"/>
-      <c r="H19" s="176" t="s">
+      <c r="E19" s="156"/>
+      <c r="F19" s="156"/>
+      <c r="G19" s="162"/>
+      <c r="H19" s="130" t="s">
         <v>40</v>
       </c>
       <c r="I19" s="104">
@@ -4928,8 +4938,8 @@
       <c r="BG19" s="15"/>
       <c r="BH19" s="15"/>
       <c r="BI19" s="15"/>
-      <c r="BJ19" s="15"/>
-      <c r="BK19" s="15"/>
+      <c r="BJ19" s="193"/>
+      <c r="BK19" s="193"/>
       <c r="BL19" s="15"/>
       <c r="BM19" s="15"/>
       <c r="BN19" s="15"/>
@@ -4992,10 +5002,10 @@
       <c r="A20" s="1"/>
       <c r="B20" s="18"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="126"/>
-      <c r="E20" s="127"/>
-      <c r="F20" s="127"/>
-      <c r="G20" s="128"/>
+      <c r="D20" s="158"/>
+      <c r="E20" s="159"/>
+      <c r="F20" s="159"/>
+      <c r="G20" s="163"/>
       <c r="H20" s="104"/>
       <c r="I20" s="104"/>
       <c r="J20" s="26"/>
@@ -5050,8 +5060,8 @@
       <c r="BG20" s="27"/>
       <c r="BH20" s="27"/>
       <c r="BI20" s="27"/>
-      <c r="BJ20" s="27"/>
-      <c r="BK20" s="27"/>
+      <c r="BJ20" s="195"/>
+      <c r="BK20" s="195"/>
       <c r="BL20" s="27"/>
       <c r="BM20" s="27"/>
       <c r="BN20" s="27"/>
@@ -5113,15 +5123,15 @@
     <row r="21" spans="1:120" ht="9.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="18"/>
-      <c r="C21" s="145" t="s">
+      <c r="C21" s="172" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="146"/>
-      <c r="E21" s="146"/>
-      <c r="F21" s="146"/>
-      <c r="G21" s="147"/>
-      <c r="H21" s="159"/>
-      <c r="I21" s="159"/>
+      <c r="D21" s="150"/>
+      <c r="E21" s="150"/>
+      <c r="F21" s="150"/>
+      <c r="G21" s="151"/>
+      <c r="H21" s="131"/>
+      <c r="I21" s="131"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="44"/>
@@ -5174,8 +5184,8 @@
       <c r="BG21" s="44"/>
       <c r="BH21" s="44"/>
       <c r="BI21" s="44"/>
-      <c r="BJ21" s="44"/>
-      <c r="BK21" s="44"/>
+      <c r="BJ21" s="194"/>
+      <c r="BK21" s="194"/>
       <c r="BL21" s="45"/>
       <c r="BM21" s="45"/>
       <c r="BN21" s="44"/>
@@ -5237,13 +5247,13 @@
     <row r="22" spans="1:120" ht="9.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="18"/>
-      <c r="C22" s="148"/>
-      <c r="D22" s="149"/>
-      <c r="E22" s="149"/>
-      <c r="F22" s="149"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="159"/>
-      <c r="I22" s="159"/>
+      <c r="C22" s="152"/>
+      <c r="D22" s="153"/>
+      <c r="E22" s="153"/>
+      <c r="F22" s="153"/>
+      <c r="G22" s="154"/>
+      <c r="H22" s="131"/>
+      <c r="I22" s="131"/>
       <c r="J22" s="46"/>
       <c r="K22" s="47"/>
       <c r="L22" s="47"/>
@@ -5296,8 +5306,8 @@
       <c r="BG22" s="47"/>
       <c r="BH22" s="47"/>
       <c r="BI22" s="47"/>
-      <c r="BJ22" s="47"/>
-      <c r="BK22" s="47"/>
+      <c r="BJ22" s="64"/>
+      <c r="BK22" s="64"/>
       <c r="BL22" s="48"/>
       <c r="BM22" s="48"/>
       <c r="BN22" s="47"/>
@@ -5360,13 +5370,13 @@
       <c r="A23" s="1"/>
       <c r="B23" s="28"/>
       <c r="C23" s="29"/>
-      <c r="D23" s="150" t="s">
+      <c r="D23" s="174" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="124"/>
-      <c r="F23" s="124"/>
-      <c r="G23" s="125"/>
-      <c r="H23" s="176" t="s">
+      <c r="E23" s="156"/>
+      <c r="F23" s="156"/>
+      <c r="G23" s="162"/>
+      <c r="H23" s="130" t="s">
         <v>46</v>
       </c>
       <c r="I23" s="104">
@@ -5424,8 +5434,8 @@
       <c r="BG23" s="15"/>
       <c r="BH23" s="15"/>
       <c r="BI23" s="15"/>
-      <c r="BJ23" s="15"/>
-      <c r="BK23" s="15"/>
+      <c r="BJ23" s="193"/>
+      <c r="BK23" s="193"/>
       <c r="BL23" s="15"/>
       <c r="BM23" s="15"/>
       <c r="BN23" s="15"/>
@@ -5488,10 +5498,10 @@
       <c r="A24" s="1"/>
       <c r="B24" s="18"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="126"/>
-      <c r="E24" s="127"/>
-      <c r="F24" s="127"/>
-      <c r="G24" s="128"/>
+      <c r="D24" s="158"/>
+      <c r="E24" s="159"/>
+      <c r="F24" s="159"/>
+      <c r="G24" s="163"/>
       <c r="H24" s="104"/>
       <c r="I24" s="104"/>
       <c r="J24" s="14"/>
@@ -5546,8 +5556,8 @@
       <c r="BG24" s="15"/>
       <c r="BH24" s="15"/>
       <c r="BI24" s="15"/>
-      <c r="BJ24" s="15"/>
-      <c r="BK24" s="15"/>
+      <c r="BJ24" s="193"/>
+      <c r="BK24" s="193"/>
       <c r="BL24" s="15"/>
       <c r="BM24" s="15"/>
       <c r="BN24" s="15"/>
@@ -5609,15 +5619,15 @@
     <row r="25" spans="1:120" ht="9.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="18"/>
-      <c r="C25" s="145" t="s">
+      <c r="C25" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="146"/>
-      <c r="E25" s="146"/>
-      <c r="F25" s="146"/>
-      <c r="G25" s="147"/>
-      <c r="H25" s="159"/>
-      <c r="I25" s="159"/>
+      <c r="D25" s="150"/>
+      <c r="E25" s="150"/>
+      <c r="F25" s="150"/>
+      <c r="G25" s="151"/>
+      <c r="H25" s="131"/>
+      <c r="I25" s="131"/>
       <c r="J25" s="42"/>
       <c r="K25" s="42"/>
       <c r="L25" s="44"/>
@@ -5670,8 +5680,8 @@
       <c r="BG25" s="44"/>
       <c r="BH25" s="44"/>
       <c r="BI25" s="44"/>
-      <c r="BJ25" s="44"/>
-      <c r="BK25" s="44"/>
+      <c r="BJ25" s="194"/>
+      <c r="BK25" s="194"/>
       <c r="BL25" s="45"/>
       <c r="BM25" s="45"/>
       <c r="BN25" s="44"/>
@@ -5733,13 +5743,13 @@
     <row r="26" spans="1:120" ht="9.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="18"/>
-      <c r="C26" s="133"/>
-      <c r="D26" s="127"/>
-      <c r="E26" s="127"/>
-      <c r="F26" s="127"/>
-      <c r="G26" s="131"/>
-      <c r="H26" s="159"/>
-      <c r="I26" s="159"/>
+      <c r="C26" s="171"/>
+      <c r="D26" s="159"/>
+      <c r="E26" s="159"/>
+      <c r="F26" s="159"/>
+      <c r="G26" s="160"/>
+      <c r="H26" s="131"/>
+      <c r="I26" s="131"/>
       <c r="J26" s="46"/>
       <c r="K26" s="47"/>
       <c r="L26" s="47"/>
@@ -5792,8 +5802,8 @@
       <c r="BG26" s="47"/>
       <c r="BH26" s="47"/>
       <c r="BI26" s="47"/>
-      <c r="BJ26" s="47"/>
-      <c r="BK26" s="47"/>
+      <c r="BJ26" s="64"/>
+      <c r="BK26" s="64"/>
       <c r="BL26" s="48"/>
       <c r="BM26" s="48"/>
       <c r="BN26" s="47"/>
@@ -5856,13 +5866,13 @@
       <c r="A27" s="1"/>
       <c r="B27" s="28"/>
       <c r="C27" s="29"/>
-      <c r="D27" s="150" t="s">
+      <c r="D27" s="174" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="124"/>
-      <c r="F27" s="124"/>
-      <c r="G27" s="125"/>
-      <c r="H27" s="176" t="s">
+      <c r="E27" s="156"/>
+      <c r="F27" s="156"/>
+      <c r="G27" s="162"/>
+      <c r="H27" s="130" t="s">
         <v>44</v>
       </c>
       <c r="I27" s="104">
@@ -5920,8 +5930,8 @@
       <c r="BG27" s="15"/>
       <c r="BH27" s="15"/>
       <c r="BI27" s="15"/>
-      <c r="BJ27" s="15"/>
-      <c r="BK27" s="15"/>
+      <c r="BJ27" s="193"/>
+      <c r="BK27" s="193"/>
       <c r="BL27" s="15"/>
       <c r="BM27" s="15"/>
       <c r="BN27" s="15"/>
@@ -5984,10 +5994,10 @@
       <c r="A28" s="1"/>
       <c r="B28" s="28"/>
       <c r="C28" s="30"/>
-      <c r="D28" s="126"/>
-      <c r="E28" s="127"/>
-      <c r="F28" s="127"/>
-      <c r="G28" s="128"/>
+      <c r="D28" s="158"/>
+      <c r="E28" s="159"/>
+      <c r="F28" s="159"/>
+      <c r="G28" s="163"/>
       <c r="H28" s="104"/>
       <c r="I28" s="104"/>
       <c r="J28" s="14"/>
@@ -6042,8 +6052,8 @@
       <c r="BG28" s="15"/>
       <c r="BH28" s="15"/>
       <c r="BI28" s="15"/>
-      <c r="BJ28" s="15"/>
-      <c r="BK28" s="15"/>
+      <c r="BJ28" s="193"/>
+      <c r="BK28" s="193"/>
       <c r="BL28" s="15"/>
       <c r="BM28" s="15"/>
       <c r="BN28" s="15"/>
@@ -6106,13 +6116,13 @@
       <c r="A29" s="1"/>
       <c r="B29" s="28"/>
       <c r="C29" s="30"/>
-      <c r="D29" s="151" t="s">
+      <c r="D29" s="175" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="152"/>
-      <c r="F29" s="152"/>
-      <c r="G29" s="152"/>
-      <c r="H29" s="176" t="s">
+      <c r="E29" s="176"/>
+      <c r="F29" s="176"/>
+      <c r="G29" s="176"/>
+      <c r="H29" s="130" t="s">
         <v>44</v>
       </c>
       <c r="I29" s="104">
@@ -6170,8 +6180,8 @@
       <c r="BG29" s="15"/>
       <c r="BH29" s="15"/>
       <c r="BI29" s="15"/>
-      <c r="BJ29" s="15"/>
-      <c r="BK29" s="15"/>
+      <c r="BJ29" s="193"/>
+      <c r="BK29" s="193"/>
       <c r="BL29" s="15"/>
       <c r="BM29" s="15"/>
       <c r="BN29" s="15"/>
@@ -6234,10 +6244,10 @@
       <c r="A30" s="1"/>
       <c r="B30" s="28"/>
       <c r="C30" s="31"/>
-      <c r="D30" s="126"/>
-      <c r="E30" s="127"/>
-      <c r="F30" s="127"/>
-      <c r="G30" s="127"/>
+      <c r="D30" s="158"/>
+      <c r="E30" s="159"/>
+      <c r="F30" s="159"/>
+      <c r="G30" s="159"/>
       <c r="H30" s="104"/>
       <c r="I30" s="104"/>
       <c r="J30" s="26"/>
@@ -6292,8 +6302,8 @@
       <c r="BG30" s="27"/>
       <c r="BH30" s="27"/>
       <c r="BI30" s="27"/>
-      <c r="BJ30" s="27"/>
-      <c r="BK30" s="27"/>
+      <c r="BJ30" s="195"/>
+      <c r="BK30" s="195"/>
       <c r="BL30" s="27"/>
       <c r="BM30" s="27"/>
       <c r="BN30" s="27"/>
@@ -6355,15 +6365,15 @@
     <row r="31" spans="1:120" ht="9.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="18"/>
-      <c r="C31" s="171" t="s">
+      <c r="C31" s="149" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="146"/>
-      <c r="E31" s="146"/>
-      <c r="F31" s="146"/>
-      <c r="G31" s="147"/>
-      <c r="H31" s="159"/>
-      <c r="I31" s="159"/>
+      <c r="D31" s="150"/>
+      <c r="E31" s="150"/>
+      <c r="F31" s="150"/>
+      <c r="G31" s="151"/>
+      <c r="H31" s="131"/>
+      <c r="I31" s="131"/>
       <c r="J31" s="42"/>
       <c r="K31" s="43"/>
       <c r="L31" s="44"/>
@@ -6416,8 +6426,8 @@
       <c r="BG31" s="44"/>
       <c r="BH31" s="44"/>
       <c r="BI31" s="44"/>
-      <c r="BJ31" s="44"/>
-      <c r="BK31" s="44"/>
+      <c r="BJ31" s="194"/>
+      <c r="BK31" s="194"/>
       <c r="BL31" s="45"/>
       <c r="BM31" s="45"/>
       <c r="BN31" s="44"/>
@@ -6479,13 +6489,13 @@
     <row r="32" spans="1:120" ht="9.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="18"/>
-      <c r="C32" s="148"/>
-      <c r="D32" s="149"/>
-      <c r="E32" s="149"/>
-      <c r="F32" s="149"/>
-      <c r="G32" s="134"/>
-      <c r="H32" s="159"/>
-      <c r="I32" s="159"/>
+      <c r="C32" s="152"/>
+      <c r="D32" s="153"/>
+      <c r="E32" s="153"/>
+      <c r="F32" s="153"/>
+      <c r="G32" s="154"/>
+      <c r="H32" s="131"/>
+      <c r="I32" s="131"/>
       <c r="J32" s="46"/>
       <c r="K32" s="47"/>
       <c r="L32" s="47"/>
@@ -6538,8 +6548,8 @@
       <c r="BG32" s="47"/>
       <c r="BH32" s="47"/>
       <c r="BI32" s="47"/>
-      <c r="BJ32" s="47"/>
-      <c r="BK32" s="47"/>
+      <c r="BJ32" s="64"/>
+      <c r="BK32" s="64"/>
       <c r="BL32" s="48"/>
       <c r="BM32" s="48"/>
       <c r="BN32" s="47"/>
@@ -6602,14 +6612,14 @@
       <c r="A33" s="1"/>
       <c r="B33" s="18"/>
       <c r="C33" s="32"/>
-      <c r="D33" s="129" t="s">
+      <c r="D33" s="155" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="124"/>
-      <c r="F33" s="124"/>
-      <c r="G33" s="130"/>
-      <c r="H33" s="159"/>
-      <c r="I33" s="159"/>
+      <c r="E33" s="156"/>
+      <c r="F33" s="156"/>
+      <c r="G33" s="157"/>
+      <c r="H33" s="131"/>
+      <c r="I33" s="131"/>
       <c r="J33" s="50"/>
       <c r="K33" s="51"/>
       <c r="L33" s="51"/>
@@ -6662,8 +6672,8 @@
       <c r="BG33" s="51"/>
       <c r="BH33" s="51"/>
       <c r="BI33" s="51"/>
-      <c r="BJ33" s="51"/>
-      <c r="BK33" s="51"/>
+      <c r="BJ33" s="196"/>
+      <c r="BK33" s="196"/>
       <c r="BL33" s="51"/>
       <c r="BM33" s="51"/>
       <c r="BN33" s="51"/>
@@ -6726,12 +6736,12 @@
       <c r="A34" s="1"/>
       <c r="B34" s="18"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="126"/>
-      <c r="E34" s="127"/>
-      <c r="F34" s="127"/>
-      <c r="G34" s="131"/>
-      <c r="H34" s="159"/>
-      <c r="I34" s="159"/>
+      <c r="D34" s="158"/>
+      <c r="E34" s="159"/>
+      <c r="F34" s="159"/>
+      <c r="G34" s="160"/>
+      <c r="H34" s="131"/>
+      <c r="I34" s="131"/>
       <c r="J34" s="52"/>
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
@@ -6784,8 +6794,8 @@
       <c r="BG34" s="49"/>
       <c r="BH34" s="49"/>
       <c r="BI34" s="49"/>
-      <c r="BJ34" s="49"/>
-      <c r="BK34" s="49"/>
+      <c r="BJ34" s="193"/>
+      <c r="BK34" s="193"/>
       <c r="BL34" s="49"/>
       <c r="BM34" s="49"/>
       <c r="BN34" s="49"/>
@@ -6849,12 +6859,12 @@
       <c r="B35" s="18"/>
       <c r="C35" s="1"/>
       <c r="D35" s="33"/>
-      <c r="E35" s="123" t="s">
+      <c r="E35" s="161" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="124"/>
-      <c r="G35" s="125"/>
-      <c r="H35" s="176" t="s">
+      <c r="F35" s="156"/>
+      <c r="G35" s="162"/>
+      <c r="H35" s="130" t="s">
         <v>45</v>
       </c>
       <c r="I35" s="104">
@@ -6912,8 +6922,8 @@
       <c r="BG35" s="15"/>
       <c r="BH35" s="15"/>
       <c r="BI35" s="15"/>
-      <c r="BJ35" s="15"/>
-      <c r="BK35" s="15"/>
+      <c r="BJ35" s="193"/>
+      <c r="BK35" s="193"/>
       <c r="BL35" s="15"/>
       <c r="BM35" s="15"/>
       <c r="BN35" s="15"/>
@@ -6977,9 +6987,9 @@
       <c r="B36" s="18"/>
       <c r="C36" s="1"/>
       <c r="D36" s="34"/>
-      <c r="E36" s="126"/>
-      <c r="F36" s="127"/>
-      <c r="G36" s="128"/>
+      <c r="E36" s="158"/>
+      <c r="F36" s="159"/>
+      <c r="G36" s="163"/>
       <c r="H36" s="104"/>
       <c r="I36" s="104"/>
       <c r="J36" s="14"/>
@@ -7034,8 +7044,8 @@
       <c r="BG36" s="15"/>
       <c r="BH36" s="15"/>
       <c r="BI36" s="15"/>
-      <c r="BJ36" s="15"/>
-      <c r="BK36" s="15"/>
+      <c r="BJ36" s="193"/>
+      <c r="BK36" s="193"/>
       <c r="BL36" s="15"/>
       <c r="BM36" s="15"/>
       <c r="BN36" s="15"/>
@@ -7099,12 +7109,12 @@
       <c r="B37" s="18"/>
       <c r="C37" s="1"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="123" t="s">
+      <c r="E37" s="161" t="s">
         <v>21</v>
       </c>
-      <c r="F37" s="124"/>
-      <c r="G37" s="125"/>
-      <c r="H37" s="176" t="s">
+      <c r="F37" s="156"/>
+      <c r="G37" s="162"/>
+      <c r="H37" s="130" t="s">
         <v>44</v>
       </c>
       <c r="I37" s="104">
@@ -7162,8 +7172,8 @@
       <c r="BG37" s="15"/>
       <c r="BH37" s="15"/>
       <c r="BI37" s="15"/>
-      <c r="BJ37" s="15"/>
-      <c r="BK37" s="15"/>
+      <c r="BJ37" s="193"/>
+      <c r="BK37" s="193"/>
       <c r="BL37" s="15"/>
       <c r="BM37" s="15"/>
       <c r="BN37" s="15"/>
@@ -7227,9 +7237,9 @@
       <c r="B38" s="18"/>
       <c r="C38" s="1"/>
       <c r="D38" s="35"/>
-      <c r="E38" s="126"/>
-      <c r="F38" s="127"/>
-      <c r="G38" s="128"/>
+      <c r="E38" s="158"/>
+      <c r="F38" s="159"/>
+      <c r="G38" s="163"/>
       <c r="H38" s="104"/>
       <c r="I38" s="104"/>
       <c r="J38" s="26"/>
@@ -7284,8 +7294,8 @@
       <c r="BG38" s="27"/>
       <c r="BH38" s="27"/>
       <c r="BI38" s="27"/>
-      <c r="BJ38" s="27"/>
-      <c r="BK38" s="27"/>
+      <c r="BJ38" s="195"/>
+      <c r="BK38" s="195"/>
       <c r="BL38" s="27"/>
       <c r="BM38" s="27"/>
       <c r="BN38" s="27"/>
@@ -7348,14 +7358,14 @@
       <c r="A39" s="1"/>
       <c r="B39" s="18"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="172" t="s">
+      <c r="D39" s="164" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="146"/>
-      <c r="F39" s="146"/>
-      <c r="G39" s="147"/>
-      <c r="H39" s="159"/>
-      <c r="I39" s="159"/>
+      <c r="E39" s="150"/>
+      <c r="F39" s="150"/>
+      <c r="G39" s="151"/>
+      <c r="H39" s="131"/>
+      <c r="I39" s="131"/>
       <c r="J39" s="50"/>
       <c r="K39" s="51"/>
       <c r="L39" s="51"/>
@@ -7408,8 +7418,8 @@
       <c r="BG39" s="51"/>
       <c r="BH39" s="51"/>
       <c r="BI39" s="51"/>
-      <c r="BJ39" s="51"/>
-      <c r="BK39" s="51"/>
+      <c r="BJ39" s="196"/>
+      <c r="BK39" s="196"/>
       <c r="BL39" s="51"/>
       <c r="BM39" s="51"/>
       <c r="BN39" s="51"/>
@@ -7472,12 +7482,12 @@
       <c r="A40" s="1"/>
       <c r="B40" s="18"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="126"/>
-      <c r="E40" s="127"/>
-      <c r="F40" s="127"/>
-      <c r="G40" s="131"/>
-      <c r="H40" s="159"/>
-      <c r="I40" s="159"/>
+      <c r="D40" s="158"/>
+      <c r="E40" s="159"/>
+      <c r="F40" s="159"/>
+      <c r="G40" s="160"/>
+      <c r="H40" s="131"/>
+      <c r="I40" s="131"/>
       <c r="J40" s="52"/>
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
@@ -7530,8 +7540,8 @@
       <c r="BG40" s="49"/>
       <c r="BH40" s="49"/>
       <c r="BI40" s="49"/>
-      <c r="BJ40" s="49"/>
-      <c r="BK40" s="49"/>
+      <c r="BJ40" s="193"/>
+      <c r="BK40" s="193"/>
       <c r="BL40" s="49"/>
       <c r="BM40" s="49"/>
       <c r="BN40" s="49"/>
@@ -7595,12 +7605,12 @@
       <c r="B41" s="18"/>
       <c r="C41" s="1"/>
       <c r="D41" s="33"/>
-      <c r="E41" s="123" t="s">
+      <c r="E41" s="161" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="124"/>
-      <c r="G41" s="125"/>
-      <c r="H41" s="176" t="s">
+      <c r="F41" s="156"/>
+      <c r="G41" s="162"/>
+      <c r="H41" s="130" t="s">
         <v>43</v>
       </c>
       <c r="I41" s="104">
@@ -7658,8 +7668,8 @@
       <c r="BG41" s="15"/>
       <c r="BH41" s="15"/>
       <c r="BI41" s="15"/>
-      <c r="BJ41" s="15"/>
-      <c r="BK41" s="15"/>
+      <c r="BJ41" s="193"/>
+      <c r="BK41" s="193"/>
       <c r="BL41" s="15"/>
       <c r="BM41" s="15"/>
       <c r="BN41" s="15"/>
@@ -7723,9 +7733,9 @@
       <c r="B42" s="18"/>
       <c r="C42" s="1"/>
       <c r="D42" s="34"/>
-      <c r="E42" s="126"/>
-      <c r="F42" s="127"/>
-      <c r="G42" s="128"/>
+      <c r="E42" s="158"/>
+      <c r="F42" s="159"/>
+      <c r="G42" s="163"/>
       <c r="H42" s="104"/>
       <c r="I42" s="104"/>
       <c r="J42" s="14"/>
@@ -7780,8 +7790,8 @@
       <c r="BG42" s="15"/>
       <c r="BH42" s="15"/>
       <c r="BI42" s="15"/>
-      <c r="BJ42" s="15"/>
-      <c r="BK42" s="15"/>
+      <c r="BJ42" s="193"/>
+      <c r="BK42" s="193"/>
       <c r="BL42" s="15"/>
       <c r="BM42" s="15"/>
       <c r="BN42" s="15"/>
@@ -7845,12 +7855,12 @@
       <c r="B43" s="18"/>
       <c r="C43" s="1"/>
       <c r="D43" s="34"/>
-      <c r="E43" s="123" t="s">
+      <c r="E43" s="161" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="124"/>
-      <c r="G43" s="125"/>
-      <c r="H43" s="176" t="s">
+      <c r="F43" s="156"/>
+      <c r="G43" s="162"/>
+      <c r="H43" s="130" t="s">
         <v>43</v>
       </c>
       <c r="I43" s="104">
@@ -7908,8 +7918,8 @@
       <c r="BG43" s="15"/>
       <c r="BH43" s="15"/>
       <c r="BI43" s="15"/>
-      <c r="BJ43" s="15"/>
-      <c r="BK43" s="15"/>
+      <c r="BJ43" s="193"/>
+      <c r="BK43" s="193"/>
       <c r="BL43" s="15"/>
       <c r="BM43" s="15"/>
       <c r="BN43" s="15"/>
@@ -7973,9 +7983,9 @@
       <c r="B44" s="18"/>
       <c r="C44" s="1"/>
       <c r="D44" s="34"/>
-      <c r="E44" s="126"/>
-      <c r="F44" s="127"/>
-      <c r="G44" s="128"/>
+      <c r="E44" s="158"/>
+      <c r="F44" s="159"/>
+      <c r="G44" s="163"/>
       <c r="H44" s="104"/>
       <c r="I44" s="104"/>
       <c r="J44" s="14"/>
@@ -8030,8 +8040,8 @@
       <c r="BG44" s="15"/>
       <c r="BH44" s="15"/>
       <c r="BI44" s="15"/>
-      <c r="BJ44" s="15"/>
-      <c r="BK44" s="15"/>
+      <c r="BJ44" s="193"/>
+      <c r="BK44" s="193"/>
       <c r="BL44" s="15"/>
       <c r="BM44" s="15"/>
       <c r="BN44" s="15"/>
@@ -8095,12 +8105,12 @@
       <c r="B45" s="18"/>
       <c r="C45" s="1"/>
       <c r="D45" s="34"/>
-      <c r="E45" s="123" t="s">
+      <c r="E45" s="161" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="124"/>
-      <c r="G45" s="125"/>
-      <c r="H45" s="176" t="s">
+      <c r="F45" s="156"/>
+      <c r="G45" s="162"/>
+      <c r="H45" s="130" t="s">
         <v>42</v>
       </c>
       <c r="I45" s="104">
@@ -8158,8 +8168,8 @@
       <c r="BG45" s="15"/>
       <c r="BH45" s="15"/>
       <c r="BI45" s="15"/>
-      <c r="BJ45" s="15"/>
-      <c r="BK45" s="15"/>
+      <c r="BJ45" s="193"/>
+      <c r="BK45" s="193"/>
       <c r="BL45" s="15"/>
       <c r="BM45" s="15"/>
       <c r="BN45" s="15"/>
@@ -8223,9 +8233,9 @@
       <c r="B46" s="18"/>
       <c r="C46" s="1"/>
       <c r="D46" s="34"/>
-      <c r="E46" s="126"/>
-      <c r="F46" s="127"/>
-      <c r="G46" s="128"/>
+      <c r="E46" s="158"/>
+      <c r="F46" s="159"/>
+      <c r="G46" s="163"/>
       <c r="H46" s="104"/>
       <c r="I46" s="104"/>
       <c r="J46" s="14"/>
@@ -8280,8 +8290,8 @@
       <c r="BG46" s="15"/>
       <c r="BH46" s="15"/>
       <c r="BI46" s="15"/>
-      <c r="BJ46" s="15"/>
-      <c r="BK46" s="15"/>
+      <c r="BJ46" s="193"/>
+      <c r="BK46" s="193"/>
       <c r="BL46" s="15"/>
       <c r="BM46" s="15"/>
       <c r="BN46" s="15"/>
@@ -8345,12 +8355,12 @@
       <c r="B47" s="18"/>
       <c r="C47" s="1"/>
       <c r="D47" s="34"/>
-      <c r="E47" s="123" t="s">
+      <c r="E47" s="161" t="s">
         <v>25</v>
       </c>
-      <c r="F47" s="124"/>
-      <c r="G47" s="125"/>
-      <c r="H47" s="176" t="s">
+      <c r="F47" s="156"/>
+      <c r="G47" s="162"/>
+      <c r="H47" s="130" t="s">
         <v>41</v>
       </c>
       <c r="I47" s="104">
@@ -8408,8 +8418,8 @@
       <c r="BG47" s="15"/>
       <c r="BH47" s="15"/>
       <c r="BI47" s="15"/>
-      <c r="BJ47" s="15"/>
-      <c r="BK47" s="15"/>
+      <c r="BJ47" s="193"/>
+      <c r="BK47" s="193"/>
       <c r="BL47" s="15"/>
       <c r="BM47" s="15"/>
       <c r="BN47" s="15"/>
@@ -8473,9 +8483,9 @@
       <c r="B48" s="18"/>
       <c r="C48" s="1"/>
       <c r="D48" s="34"/>
-      <c r="E48" s="126"/>
-      <c r="F48" s="127"/>
-      <c r="G48" s="128"/>
+      <c r="E48" s="158"/>
+      <c r="F48" s="159"/>
+      <c r="G48" s="163"/>
       <c r="H48" s="104"/>
       <c r="I48" s="104"/>
       <c r="J48" s="14"/>
@@ -8530,8 +8540,8 @@
       <c r="BG48" s="15"/>
       <c r="BH48" s="15"/>
       <c r="BI48" s="15"/>
-      <c r="BJ48" s="15"/>
-      <c r="BK48" s="15"/>
+      <c r="BJ48" s="193"/>
+      <c r="BK48" s="193"/>
       <c r="BL48" s="15"/>
       <c r="BM48" s="15"/>
       <c r="BN48" s="15"/>
@@ -8595,12 +8605,12 @@
       <c r="B49" s="18"/>
       <c r="C49" s="1"/>
       <c r="D49" s="34"/>
-      <c r="E49" s="123" t="s">
+      <c r="E49" s="161" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="124"/>
-      <c r="G49" s="125"/>
-      <c r="H49" s="176" t="s">
+      <c r="F49" s="156"/>
+      <c r="G49" s="162"/>
+      <c r="H49" s="130" t="s">
         <v>50</v>
       </c>
       <c r="I49" s="104">
@@ -8658,8 +8668,8 @@
       <c r="BG49" s="15"/>
       <c r="BH49" s="15"/>
       <c r="BI49" s="15"/>
-      <c r="BJ49" s="15"/>
-      <c r="BK49" s="15"/>
+      <c r="BJ49" s="193"/>
+      <c r="BK49" s="193"/>
       <c r="BL49" s="15"/>
       <c r="BM49" s="15"/>
       <c r="BN49" s="15"/>
@@ -8723,9 +8733,9 @@
       <c r="B50" s="18"/>
       <c r="C50" s="1"/>
       <c r="D50" s="34"/>
-      <c r="E50" s="126"/>
-      <c r="F50" s="127"/>
-      <c r="G50" s="128"/>
+      <c r="E50" s="158"/>
+      <c r="F50" s="159"/>
+      <c r="G50" s="163"/>
       <c r="H50" s="104"/>
       <c r="I50" s="104"/>
       <c r="J50" s="14"/>
@@ -8780,8 +8790,8 @@
       <c r="BG50" s="15"/>
       <c r="BH50" s="15"/>
       <c r="BI50" s="15"/>
-      <c r="BJ50" s="15"/>
-      <c r="BK50" s="15"/>
+      <c r="BJ50" s="193"/>
+      <c r="BK50" s="193"/>
       <c r="BL50" s="15"/>
       <c r="BM50" s="15"/>
       <c r="BN50" s="15"/>
@@ -8845,12 +8855,12 @@
       <c r="B51" s="18"/>
       <c r="C51" s="1"/>
       <c r="D51" s="34"/>
-      <c r="E51" s="123" t="s">
+      <c r="E51" s="161" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="124"/>
-      <c r="G51" s="125"/>
-      <c r="H51" s="176" t="s">
+      <c r="F51" s="156"/>
+      <c r="G51" s="162"/>
+      <c r="H51" s="130" t="s">
         <v>47</v>
       </c>
       <c r="I51" s="104">
@@ -8908,8 +8918,8 @@
       <c r="BG51" s="15"/>
       <c r="BH51" s="15"/>
       <c r="BI51" s="15"/>
-      <c r="BJ51" s="15"/>
-      <c r="BK51" s="15"/>
+      <c r="BJ51" s="193"/>
+      <c r="BK51" s="193"/>
       <c r="BL51" s="15"/>
       <c r="BM51" s="15"/>
       <c r="BN51" s="15"/>
@@ -8973,9 +8983,9 @@
       <c r="B52" s="18"/>
       <c r="C52" s="1"/>
       <c r="D52" s="34"/>
-      <c r="E52" s="126"/>
-      <c r="F52" s="127"/>
-      <c r="G52" s="128"/>
+      <c r="E52" s="158"/>
+      <c r="F52" s="159"/>
+      <c r="G52" s="163"/>
       <c r="H52" s="104"/>
       <c r="I52" s="104"/>
       <c r="J52" s="26"/>
@@ -9030,8 +9040,8 @@
       <c r="BG52" s="27"/>
       <c r="BH52" s="27"/>
       <c r="BI52" s="27"/>
-      <c r="BJ52" s="27"/>
-      <c r="BK52" s="27"/>
+      <c r="BJ52" s="195"/>
+      <c r="BK52" s="195"/>
       <c r="BL52" s="27"/>
       <c r="BM52" s="27"/>
       <c r="BN52" s="27"/>
@@ -9094,14 +9104,14 @@
       <c r="A53" s="1"/>
       <c r="B53" s="18"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="129" t="s">
+      <c r="D53" s="155" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="124"/>
-      <c r="F53" s="124"/>
-      <c r="G53" s="130"/>
-      <c r="H53" s="159"/>
-      <c r="I53" s="159"/>
+      <c r="E53" s="156"/>
+      <c r="F53" s="156"/>
+      <c r="G53" s="157"/>
+      <c r="H53" s="131"/>
+      <c r="I53" s="131"/>
       <c r="J53" s="50"/>
       <c r="K53" s="51"/>
       <c r="L53" s="51"/>
@@ -9154,8 +9164,8 @@
       <c r="BG53" s="51"/>
       <c r="BH53" s="51"/>
       <c r="BI53" s="51"/>
-      <c r="BJ53" s="51"/>
-      <c r="BK53" s="51"/>
+      <c r="BJ53" s="196"/>
+      <c r="BK53" s="196"/>
       <c r="BL53" s="51"/>
       <c r="BM53" s="51"/>
       <c r="BN53" s="51"/>
@@ -9218,12 +9228,12 @@
       <c r="A54" s="1"/>
       <c r="B54" s="18"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="126"/>
-      <c r="E54" s="127"/>
-      <c r="F54" s="127"/>
-      <c r="G54" s="131"/>
-      <c r="H54" s="159"/>
-      <c r="I54" s="159"/>
+      <c r="D54" s="158"/>
+      <c r="E54" s="159"/>
+      <c r="F54" s="159"/>
+      <c r="G54" s="160"/>
+      <c r="H54" s="131"/>
+      <c r="I54" s="131"/>
       <c r="J54" s="52"/>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -9276,8 +9286,8 @@
       <c r="BG54" s="49"/>
       <c r="BH54" s="49"/>
       <c r="BI54" s="49"/>
-      <c r="BJ54" s="49"/>
-      <c r="BK54" s="49"/>
+      <c r="BJ54" s="193"/>
+      <c r="BK54" s="193"/>
       <c r="BL54" s="49"/>
       <c r="BM54" s="49"/>
       <c r="BN54" s="49"/>
@@ -9341,12 +9351,12 @@
       <c r="B55" s="18"/>
       <c r="C55" s="1"/>
       <c r="D55" s="34"/>
-      <c r="E55" s="123" t="s">
+      <c r="E55" s="161" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="124"/>
-      <c r="G55" s="125"/>
-      <c r="H55" s="176" t="s">
+      <c r="F55" s="156"/>
+      <c r="G55" s="162"/>
+      <c r="H55" s="130" t="s">
         <v>48</v>
       </c>
       <c r="I55" s="104">
@@ -9404,8 +9414,8 @@
       <c r="BG55" s="15"/>
       <c r="BH55" s="15"/>
       <c r="BI55" s="15"/>
-      <c r="BJ55" s="15"/>
-      <c r="BK55" s="15"/>
+      <c r="BJ55" s="193"/>
+      <c r="BK55" s="193"/>
       <c r="BL55" s="15"/>
       <c r="BM55" s="15"/>
       <c r="BN55" s="15"/>
@@ -9469,9 +9479,9 @@
       <c r="B56" s="18"/>
       <c r="C56" s="1"/>
       <c r="D56" s="34"/>
-      <c r="E56" s="126"/>
-      <c r="F56" s="127"/>
-      <c r="G56" s="128"/>
+      <c r="E56" s="158"/>
+      <c r="F56" s="159"/>
+      <c r="G56" s="163"/>
       <c r="H56" s="104"/>
       <c r="I56" s="104"/>
       <c r="J56" s="14"/>
@@ -9526,8 +9536,8 @@
       <c r="BG56" s="15"/>
       <c r="BH56" s="15"/>
       <c r="BI56" s="15"/>
-      <c r="BJ56" s="15"/>
-      <c r="BK56" s="15"/>
+      <c r="BJ56" s="193"/>
+      <c r="BK56" s="193"/>
       <c r="BL56" s="15"/>
       <c r="BM56" s="15"/>
       <c r="BN56" s="15"/>
@@ -9591,12 +9601,12 @@
       <c r="B57" s="18"/>
       <c r="C57" s="1"/>
       <c r="D57" s="34"/>
-      <c r="E57" s="123" t="s">
+      <c r="E57" s="161" t="s">
         <v>29</v>
       </c>
-      <c r="F57" s="124"/>
-      <c r="G57" s="125"/>
-      <c r="H57" s="176" t="s">
+      <c r="F57" s="156"/>
+      <c r="G57" s="162"/>
+      <c r="H57" s="130" t="s">
         <v>51</v>
       </c>
       <c r="I57" s="104">
@@ -9654,8 +9664,8 @@
       <c r="BG57" s="15"/>
       <c r="BH57" s="15"/>
       <c r="BI57" s="15"/>
-      <c r="BJ57" s="15"/>
-      <c r="BK57" s="15"/>
+      <c r="BJ57" s="193"/>
+      <c r="BK57" s="193"/>
       <c r="BL57" s="15"/>
       <c r="BM57" s="15"/>
       <c r="BN57" s="15"/>
@@ -9719,9 +9729,9 @@
       <c r="B58" s="18"/>
       <c r="C58" s="1"/>
       <c r="D58" s="34"/>
-      <c r="E58" s="126"/>
-      <c r="F58" s="127"/>
-      <c r="G58" s="128"/>
+      <c r="E58" s="158"/>
+      <c r="F58" s="159"/>
+      <c r="G58" s="163"/>
       <c r="H58" s="104"/>
       <c r="I58" s="104"/>
       <c r="J58" s="14"/>
@@ -9776,8 +9786,8 @@
       <c r="BG58" s="15"/>
       <c r="BH58" s="15"/>
       <c r="BI58" s="15"/>
-      <c r="BJ58" s="15"/>
-      <c r="BK58" s="15"/>
+      <c r="BJ58" s="193"/>
+      <c r="BK58" s="193"/>
       <c r="BL58" s="15"/>
       <c r="BM58" s="15"/>
       <c r="BN58" s="15"/>
@@ -9841,12 +9851,12 @@
       <c r="B59" s="18"/>
       <c r="C59" s="1"/>
       <c r="D59" s="34"/>
-      <c r="E59" s="123" t="s">
+      <c r="E59" s="161" t="s">
         <v>26</v>
       </c>
-      <c r="F59" s="124"/>
-      <c r="G59" s="125"/>
-      <c r="H59" s="176" t="s">
+      <c r="F59" s="156"/>
+      <c r="G59" s="162"/>
+      <c r="H59" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I59" s="104">
@@ -9904,8 +9914,8 @@
       <c r="BG59" s="15"/>
       <c r="BH59" s="15"/>
       <c r="BI59" s="15"/>
-      <c r="BJ59" s="15"/>
-      <c r="BK59" s="15"/>
+      <c r="BJ59" s="193"/>
+      <c r="BK59" s="193"/>
       <c r="BL59" s="15"/>
       <c r="BM59" s="15"/>
       <c r="BN59" s="15"/>
@@ -9969,9 +9979,9 @@
       <c r="B60" s="18"/>
       <c r="C60" s="1"/>
       <c r="D60" s="34"/>
-      <c r="E60" s="126"/>
-      <c r="F60" s="127"/>
-      <c r="G60" s="128"/>
+      <c r="E60" s="158"/>
+      <c r="F60" s="159"/>
+      <c r="G60" s="163"/>
       <c r="H60" s="104"/>
       <c r="I60" s="104"/>
       <c r="J60" s="14"/>
@@ -10026,8 +10036,8 @@
       <c r="BG60" s="15"/>
       <c r="BH60" s="15"/>
       <c r="BI60" s="15"/>
-      <c r="BJ60" s="15"/>
-      <c r="BK60" s="15"/>
+      <c r="BJ60" s="193"/>
+      <c r="BK60" s="193"/>
       <c r="BL60" s="15"/>
       <c r="BM60" s="15"/>
       <c r="BN60" s="15"/>
@@ -10091,12 +10101,12 @@
       <c r="B61" s="18"/>
       <c r="C61" s="1"/>
       <c r="D61" s="34"/>
-      <c r="E61" s="123" t="s">
+      <c r="E61" s="161" t="s">
         <v>21</v>
       </c>
-      <c r="F61" s="124"/>
-      <c r="G61" s="125"/>
-      <c r="H61" s="176" t="s">
+      <c r="F61" s="156"/>
+      <c r="G61" s="162"/>
+      <c r="H61" s="130" t="s">
         <v>49</v>
       </c>
       <c r="I61" s="104">
@@ -10154,8 +10164,8 @@
       <c r="BG61" s="15"/>
       <c r="BH61" s="15"/>
       <c r="BI61" s="15"/>
-      <c r="BJ61" s="15"/>
-      <c r="BK61" s="15"/>
+      <c r="BJ61" s="193"/>
+      <c r="BK61" s="193"/>
       <c r="BL61" s="15"/>
       <c r="BM61" s="15"/>
       <c r="BN61" s="15"/>
@@ -10219,9 +10229,9 @@
       <c r="B62" s="18"/>
       <c r="C62" s="1"/>
       <c r="D62" s="34"/>
-      <c r="E62" s="126"/>
-      <c r="F62" s="127"/>
-      <c r="G62" s="128"/>
+      <c r="E62" s="158"/>
+      <c r="F62" s="159"/>
+      <c r="G62" s="163"/>
       <c r="H62" s="104"/>
       <c r="I62" s="104"/>
       <c r="J62" s="26"/>
@@ -10276,8 +10286,8 @@
       <c r="BG62" s="27"/>
       <c r="BH62" s="27"/>
       <c r="BI62" s="27"/>
-      <c r="BJ62" s="27"/>
-      <c r="BK62" s="27"/>
+      <c r="BJ62" s="195"/>
+      <c r="BK62" s="195"/>
       <c r="BL62" s="27"/>
       <c r="BM62" s="27"/>
       <c r="BN62" s="27"/>
@@ -10340,14 +10350,14 @@
       <c r="A63" s="1"/>
       <c r="B63" s="18"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="129" t="s">
+      <c r="D63" s="155" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="124"/>
-      <c r="F63" s="124"/>
-      <c r="G63" s="130"/>
-      <c r="H63" s="159"/>
-      <c r="I63" s="159"/>
+      <c r="E63" s="156"/>
+      <c r="F63" s="156"/>
+      <c r="G63" s="157"/>
+      <c r="H63" s="131"/>
+      <c r="I63" s="131"/>
       <c r="J63" s="50"/>
       <c r="K63" s="51"/>
       <c r="L63" s="51"/>
@@ -10400,8 +10410,8 @@
       <c r="BG63" s="51"/>
       <c r="BH63" s="51"/>
       <c r="BI63" s="51"/>
-      <c r="BJ63" s="51"/>
-      <c r="BK63" s="51"/>
+      <c r="BJ63" s="196"/>
+      <c r="BK63" s="196"/>
       <c r="BL63" s="51"/>
       <c r="BM63" s="51"/>
       <c r="BN63" s="51"/>
@@ -10464,12 +10474,12 @@
       <c r="A64" s="1"/>
       <c r="B64" s="18"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="126"/>
-      <c r="E64" s="127"/>
-      <c r="F64" s="127"/>
-      <c r="G64" s="131"/>
-      <c r="H64" s="159"/>
-      <c r="I64" s="159"/>
+      <c r="D64" s="158"/>
+      <c r="E64" s="159"/>
+      <c r="F64" s="159"/>
+      <c r="G64" s="160"/>
+      <c r="H64" s="131"/>
+      <c r="I64" s="131"/>
       <c r="J64" s="52"/>
       <c r="K64" s="49"/>
       <c r="L64" s="49"/>
@@ -10522,8 +10532,8 @@
       <c r="BG64" s="49"/>
       <c r="BH64" s="49"/>
       <c r="BI64" s="49"/>
-      <c r="BJ64" s="49"/>
-      <c r="BK64" s="49"/>
+      <c r="BJ64" s="193"/>
+      <c r="BK64" s="193"/>
       <c r="BL64" s="49"/>
       <c r="BM64" s="49"/>
       <c r="BN64" s="49"/>
@@ -10587,12 +10597,12 @@
       <c r="B65" s="18"/>
       <c r="C65" s="1"/>
       <c r="D65" s="34"/>
-      <c r="E65" s="123" t="s">
+      <c r="E65" s="161" t="s">
         <v>35</v>
       </c>
-      <c r="F65" s="124"/>
-      <c r="G65" s="125"/>
-      <c r="H65" s="176" t="s">
+      <c r="F65" s="156"/>
+      <c r="G65" s="162"/>
+      <c r="H65" s="130" t="s">
         <v>52</v>
       </c>
       <c r="I65" s="104">
@@ -10650,8 +10660,8 @@
       <c r="BG65" s="15"/>
       <c r="BH65" s="15"/>
       <c r="BI65" s="15"/>
-      <c r="BJ65" s="15"/>
-      <c r="BK65" s="15"/>
+      <c r="BJ65" s="193"/>
+      <c r="BK65" s="193"/>
       <c r="BL65" s="15"/>
       <c r="BM65" s="15"/>
       <c r="BN65" s="15"/>
@@ -10715,9 +10725,9 @@
       <c r="B66" s="18"/>
       <c r="C66" s="1"/>
       <c r="D66" s="34"/>
-      <c r="E66" s="126"/>
-      <c r="F66" s="127"/>
-      <c r="G66" s="128"/>
+      <c r="E66" s="158"/>
+      <c r="F66" s="159"/>
+      <c r="G66" s="163"/>
       <c r="H66" s="104"/>
       <c r="I66" s="104"/>
       <c r="J66" s="14"/>
@@ -10772,8 +10782,8 @@
       <c r="BG66" s="15"/>
       <c r="BH66" s="15"/>
       <c r="BI66" s="15"/>
-      <c r="BJ66" s="15"/>
-      <c r="BK66" s="15"/>
+      <c r="BJ66" s="193"/>
+      <c r="BK66" s="193"/>
       <c r="BL66" s="15"/>
       <c r="BM66" s="15"/>
       <c r="BN66" s="15"/>
@@ -10837,12 +10847,12 @@
       <c r="B67" s="18"/>
       <c r="C67" s="1"/>
       <c r="D67" s="34"/>
-      <c r="E67" s="123" t="s">
+      <c r="E67" s="161" t="s">
         <v>26</v>
       </c>
-      <c r="F67" s="124"/>
-      <c r="G67" s="125"/>
-      <c r="H67" s="176" t="s">
+      <c r="F67" s="156"/>
+      <c r="G67" s="162"/>
+      <c r="H67" s="130" t="s">
         <v>53</v>
       </c>
       <c r="I67" s="104">
@@ -10900,8 +10910,8 @@
       <c r="BG67" s="15"/>
       <c r="BH67" s="15"/>
       <c r="BI67" s="15"/>
-      <c r="BJ67" s="15"/>
-      <c r="BK67" s="15"/>
+      <c r="BJ67" s="193"/>
+      <c r="BK67" s="193"/>
       <c r="BL67" s="15"/>
       <c r="BM67" s="15"/>
       <c r="BN67" s="15"/>
@@ -10965,9 +10975,9 @@
       <c r="B68" s="18"/>
       <c r="C68" s="1"/>
       <c r="D68" s="34"/>
-      <c r="E68" s="126"/>
-      <c r="F68" s="127"/>
-      <c r="G68" s="128"/>
+      <c r="E68" s="158"/>
+      <c r="F68" s="159"/>
+      <c r="G68" s="163"/>
       <c r="H68" s="104"/>
       <c r="I68" s="104"/>
       <c r="J68" s="14"/>
@@ -11022,8 +11032,8 @@
       <c r="BG68" s="15"/>
       <c r="BH68" s="15"/>
       <c r="BI68" s="15"/>
-      <c r="BJ68" s="15"/>
-      <c r="BK68" s="15"/>
+      <c r="BJ68" s="193"/>
+      <c r="BK68" s="193"/>
       <c r="BL68" s="15"/>
       <c r="BM68" s="15"/>
       <c r="BN68" s="15"/>
@@ -11087,12 +11097,12 @@
       <c r="B69" s="18"/>
       <c r="C69" s="1"/>
       <c r="D69" s="34"/>
-      <c r="E69" s="123" t="s">
+      <c r="E69" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="F69" s="124"/>
-      <c r="G69" s="125"/>
-      <c r="H69" s="176" t="s">
+      <c r="F69" s="156"/>
+      <c r="G69" s="162"/>
+      <c r="H69" s="130" t="s">
         <v>54</v>
       </c>
       <c r="I69" s="104">
@@ -11150,8 +11160,8 @@
       <c r="BG69" s="15"/>
       <c r="BH69" s="15"/>
       <c r="BI69" s="15"/>
-      <c r="BJ69" s="15"/>
-      <c r="BK69" s="15"/>
+      <c r="BJ69" s="193"/>
+      <c r="BK69" s="193"/>
       <c r="BL69" s="15"/>
       <c r="BM69" s="15"/>
       <c r="BN69" s="15"/>
@@ -11215,9 +11225,9 @@
       <c r="B70" s="18"/>
       <c r="C70" s="1"/>
       <c r="D70" s="34"/>
-      <c r="E70" s="126"/>
-      <c r="F70" s="127"/>
-      <c r="G70" s="128"/>
+      <c r="E70" s="158"/>
+      <c r="F70" s="159"/>
+      <c r="G70" s="163"/>
       <c r="H70" s="104"/>
       <c r="I70" s="104"/>
       <c r="J70" s="14"/>
@@ -11272,8 +11282,8 @@
       <c r="BG70" s="15"/>
       <c r="BH70" s="15"/>
       <c r="BI70" s="15"/>
-      <c r="BJ70" s="15"/>
-      <c r="BK70" s="15"/>
+      <c r="BJ70" s="193"/>
+      <c r="BK70" s="193"/>
       <c r="BL70" s="15"/>
       <c r="BM70" s="15"/>
       <c r="BN70" s="15"/>
@@ -11337,12 +11347,12 @@
       <c r="B71" s="18"/>
       <c r="C71" s="1"/>
       <c r="D71" s="34"/>
-      <c r="E71" s="123" t="s">
+      <c r="E71" s="161" t="s">
         <v>21</v>
       </c>
-      <c r="F71" s="124"/>
-      <c r="G71" s="125"/>
-      <c r="H71" s="176" t="s">
+      <c r="F71" s="156"/>
+      <c r="G71" s="162"/>
+      <c r="H71" s="130" t="s">
         <v>55</v>
       </c>
       <c r="I71" s="104">
@@ -11400,8 +11410,8 @@
       <c r="BG71" s="15"/>
       <c r="BH71" s="15"/>
       <c r="BI71" s="15"/>
-      <c r="BJ71" s="15"/>
-      <c r="BK71" s="15"/>
+      <c r="BJ71" s="193"/>
+      <c r="BK71" s="193"/>
       <c r="BL71" s="15"/>
       <c r="BM71" s="15"/>
       <c r="BN71" s="15"/>
@@ -11465,9 +11475,9 @@
       <c r="B72" s="18"/>
       <c r="C72" s="1"/>
       <c r="D72" s="35"/>
-      <c r="E72" s="126"/>
-      <c r="F72" s="127"/>
-      <c r="G72" s="128"/>
+      <c r="E72" s="158"/>
+      <c r="F72" s="159"/>
+      <c r="G72" s="163"/>
       <c r="H72" s="104"/>
       <c r="I72" s="104"/>
       <c r="J72" s="26"/>
@@ -11522,9 +11532,9 @@
       <c r="BG72" s="27"/>
       <c r="BH72" s="27"/>
       <c r="BI72" s="27"/>
-      <c r="BJ72" s="27"/>
-      <c r="BK72" s="27"/>
-      <c r="BL72" s="27"/>
+      <c r="BJ72" s="195"/>
+      <c r="BK72" s="195"/>
+      <c r="BL72" s="195"/>
       <c r="BM72" s="27"/>
       <c r="BN72" s="27"/>
       <c r="BO72" s="27"/>
@@ -11585,14 +11595,14 @@
     <row r="73" spans="1:120" ht="9.75" customHeight="1">
       <c r="A73" s="16"/>
       <c r="B73" s="36"/>
-      <c r="C73" s="132" t="s">
+      <c r="C73" s="138" t="s">
         <v>30</v>
       </c>
-      <c r="D73" s="124"/>
-      <c r="E73" s="124"/>
-      <c r="F73" s="124"/>
-      <c r="G73" s="130"/>
-      <c r="H73" s="176" t="s">
+      <c r="D73" s="156"/>
+      <c r="E73" s="156"/>
+      <c r="F73" s="156"/>
+      <c r="G73" s="157"/>
+      <c r="H73" s="130" t="s">
         <v>55</v>
       </c>
       <c r="I73" s="104">
@@ -11650,8 +11660,8 @@
       <c r="BG73" s="20"/>
       <c r="BH73" s="20"/>
       <c r="BI73" s="20"/>
-      <c r="BJ73" s="20"/>
-      <c r="BK73" s="20"/>
+      <c r="BJ73" s="64"/>
+      <c r="BK73" s="64"/>
       <c r="BL73" s="21"/>
       <c r="BM73" s="21"/>
       <c r="BN73" s="20"/>
@@ -11713,11 +11723,11 @@
     <row r="74" spans="1:120" ht="9.75" customHeight="1">
       <c r="A74" s="16"/>
       <c r="B74" s="36"/>
-      <c r="C74" s="133"/>
-      <c r="D74" s="127"/>
-      <c r="E74" s="127"/>
-      <c r="F74" s="127"/>
-      <c r="G74" s="131"/>
+      <c r="C74" s="171"/>
+      <c r="D74" s="159"/>
+      <c r="E74" s="159"/>
+      <c r="F74" s="159"/>
+      <c r="G74" s="160"/>
       <c r="H74" s="104"/>
       <c r="I74" s="104"/>
       <c r="J74" s="19"/>
@@ -11772,8 +11782,8 @@
       <c r="BG74" s="20"/>
       <c r="BH74" s="20"/>
       <c r="BI74" s="20"/>
-      <c r="BJ74" s="20"/>
-      <c r="BK74" s="20"/>
+      <c r="BJ74" s="64"/>
+      <c r="BK74" s="64"/>
       <c r="BL74" s="21"/>
       <c r="BM74" s="21"/>
       <c r="BN74" s="20"/>
@@ -11835,14 +11845,14 @@
     <row r="75" spans="1:120" ht="9.75" customHeight="1">
       <c r="A75" s="16"/>
       <c r="B75" s="36"/>
-      <c r="C75" s="132" t="s">
+      <c r="C75" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="D75" s="124"/>
-      <c r="E75" s="124"/>
-      <c r="F75" s="124"/>
-      <c r="G75" s="130"/>
-      <c r="H75" s="176" t="s">
+      <c r="D75" s="156"/>
+      <c r="E75" s="156"/>
+      <c r="F75" s="156"/>
+      <c r="G75" s="157"/>
+      <c r="H75" s="130" t="s">
         <v>58</v>
       </c>
       <c r="I75" s="104"/>
@@ -11898,8 +11908,8 @@
       <c r="BG75" s="20"/>
       <c r="BH75" s="20"/>
       <c r="BI75" s="20"/>
-      <c r="BJ75" s="20"/>
-      <c r="BK75" s="20"/>
+      <c r="BJ75" s="64"/>
+      <c r="BK75" s="64"/>
       <c r="BL75" s="21"/>
       <c r="BM75" s="21"/>
       <c r="BN75" s="20"/>
@@ -11961,11 +11971,11 @@
     <row r="76" spans="1:120" ht="9.75" customHeight="1">
       <c r="A76" s="16"/>
       <c r="B76" s="36"/>
-      <c r="C76" s="134"/>
-      <c r="D76" s="134"/>
-      <c r="E76" s="134"/>
-      <c r="F76" s="134"/>
-      <c r="G76" s="134"/>
+      <c r="C76" s="154"/>
+      <c r="D76" s="154"/>
+      <c r="E76" s="154"/>
+      <c r="F76" s="154"/>
+      <c r="G76" s="154"/>
       <c r="H76" s="104"/>
       <c r="I76" s="104"/>
       <c r="J76" s="19"/>
@@ -12020,8 +12030,8 @@
       <c r="BG76" s="20"/>
       <c r="BH76" s="20"/>
       <c r="BI76" s="20"/>
-      <c r="BJ76" s="20"/>
-      <c r="BK76" s="20"/>
+      <c r="BJ76" s="64"/>
+      <c r="BK76" s="64"/>
       <c r="BL76" s="21"/>
       <c r="BM76" s="21"/>
       <c r="BN76" s="20"/>
@@ -12083,15 +12093,15 @@
     <row r="77" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A77" s="16"/>
       <c r="B77" s="71"/>
-      <c r="C77" s="135" t="s">
+      <c r="C77" s="179" t="s">
         <v>62</v>
       </c>
-      <c r="D77" s="136"/>
-      <c r="E77" s="136"/>
-      <c r="F77" s="136"/>
-      <c r="G77" s="137"/>
-      <c r="H77" s="177"/>
-      <c r="I77" s="173"/>
+      <c r="D77" s="180"/>
+      <c r="E77" s="180"/>
+      <c r="F77" s="180"/>
+      <c r="G77" s="181"/>
+      <c r="H77" s="132"/>
+      <c r="I77" s="121"/>
       <c r="J77" s="63"/>
       <c r="K77" s="64"/>
       <c r="L77" s="64"/>
@@ -12207,13 +12217,13 @@
     <row r="78" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A78" s="16"/>
       <c r="B78" s="71"/>
-      <c r="C78" s="138"/>
-      <c r="D78" s="139"/>
-      <c r="E78" s="139"/>
-      <c r="F78" s="139"/>
-      <c r="G78" s="140"/>
-      <c r="H78" s="178"/>
-      <c r="I78" s="174"/>
+      <c r="C78" s="182"/>
+      <c r="D78" s="183"/>
+      <c r="E78" s="183"/>
+      <c r="F78" s="183"/>
+      <c r="G78" s="184"/>
+      <c r="H78" s="133"/>
+      <c r="I78" s="122"/>
       <c r="J78" s="63"/>
       <c r="K78" s="64"/>
       <c r="L78" s="64"/>
@@ -12330,12 +12340,12 @@
       <c r="A79" s="16"/>
       <c r="B79" s="71"/>
       <c r="C79" s="76"/>
-      <c r="D79" s="107" t="s">
+      <c r="D79" s="124" t="s">
         <v>63</v>
       </c>
-      <c r="E79" s="108"/>
-      <c r="F79" s="108"/>
-      <c r="G79" s="109"/>
+      <c r="E79" s="125"/>
+      <c r="F79" s="125"/>
+      <c r="G79" s="126"/>
       <c r="H79" s="77"/>
       <c r="I79" s="67"/>
       <c r="J79" s="63"/>
@@ -12454,10 +12464,10 @@
       <c r="A80" s="16"/>
       <c r="B80" s="71"/>
       <c r="C80" s="76"/>
-      <c r="D80" s="110"/>
-      <c r="E80" s="111"/>
-      <c r="F80" s="111"/>
-      <c r="G80" s="112"/>
+      <c r="D80" s="127"/>
+      <c r="E80" s="128"/>
+      <c r="F80" s="128"/>
+      <c r="G80" s="129"/>
       <c r="H80" s="77"/>
       <c r="I80" s="67"/>
       <c r="J80" s="63"/>
@@ -12577,15 +12587,15 @@
       <c r="B81" s="36"/>
       <c r="C81" s="60"/>
       <c r="D81" s="70"/>
-      <c r="E81" s="141" t="s">
+      <c r="E81" s="97" t="s">
         <v>73</v>
       </c>
-      <c r="F81" s="141"/>
-      <c r="G81" s="141"/>
-      <c r="H81" s="95">
+      <c r="F81" s="97"/>
+      <c r="G81" s="97"/>
+      <c r="H81" s="103">
         <v>45611</v>
       </c>
-      <c r="I81" s="97">
+      <c r="I81" s="118">
         <v>100</v>
       </c>
       <c r="J81" s="19"/>
@@ -12640,8 +12650,8 @@
       <c r="BG81" s="20"/>
       <c r="BH81" s="20"/>
       <c r="BI81" s="20"/>
-      <c r="BJ81" s="20"/>
-      <c r="BK81" s="20"/>
+      <c r="BJ81" s="64"/>
+      <c r="BK81" s="64"/>
       <c r="BL81" s="21"/>
       <c r="BM81" s="21"/>
       <c r="BN81" s="20"/>
@@ -12705,11 +12715,11 @@
       <c r="B82" s="36"/>
       <c r="C82" s="60"/>
       <c r="D82" s="70"/>
-      <c r="E82" s="94"/>
-      <c r="F82" s="94"/>
-      <c r="G82" s="94"/>
-      <c r="H82" s="96"/>
-      <c r="I82" s="98"/>
+      <c r="E82" s="95"/>
+      <c r="F82" s="95"/>
+      <c r="G82" s="95"/>
+      <c r="H82" s="99"/>
+      <c r="I82" s="101"/>
       <c r="J82" s="19"/>
       <c r="K82" s="20"/>
       <c r="L82" s="20"/>
@@ -12762,8 +12772,8 @@
       <c r="BG82" s="20"/>
       <c r="BH82" s="20"/>
       <c r="BI82" s="20"/>
-      <c r="BJ82" s="20"/>
-      <c r="BK82" s="20"/>
+      <c r="BJ82" s="64"/>
+      <c r="BK82" s="64"/>
       <c r="BL82" s="21"/>
       <c r="BM82" s="21"/>
       <c r="BN82" s="20"/>
@@ -12827,15 +12837,15 @@
       <c r="B83" s="36"/>
       <c r="C83" s="60"/>
       <c r="D83" s="70"/>
-      <c r="E83" s="94" t="s">
+      <c r="E83" s="95" t="s">
         <v>74</v>
       </c>
-      <c r="F83" s="94"/>
-      <c r="G83" s="94"/>
-      <c r="H83" s="95">
+      <c r="F83" s="95"/>
+      <c r="G83" s="95"/>
+      <c r="H83" s="103">
         <v>45615</v>
       </c>
-      <c r="I83" s="97">
+      <c r="I83" s="118">
         <v>100</v>
       </c>
       <c r="J83" s="19"/>
@@ -12890,8 +12900,8 @@
       <c r="BG83" s="20"/>
       <c r="BH83" s="20"/>
       <c r="BI83" s="20"/>
-      <c r="BJ83" s="20"/>
-      <c r="BK83" s="20"/>
+      <c r="BJ83" s="64"/>
+      <c r="BK83" s="64"/>
       <c r="BL83" s="21"/>
       <c r="BM83" s="21"/>
       <c r="BN83" s="20"/>
@@ -12955,11 +12965,11 @@
       <c r="B84" s="36"/>
       <c r="C84" s="60"/>
       <c r="D84" s="70"/>
-      <c r="E84" s="94"/>
-      <c r="F84" s="94"/>
-      <c r="G84" s="94"/>
-      <c r="H84" s="96"/>
-      <c r="I84" s="98"/>
+      <c r="E84" s="95"/>
+      <c r="F84" s="95"/>
+      <c r="G84" s="95"/>
+      <c r="H84" s="99"/>
+      <c r="I84" s="101"/>
       <c r="J84" s="19"/>
       <c r="K84" s="20"/>
       <c r="L84" s="20"/>
@@ -13012,8 +13022,8 @@
       <c r="BG84" s="20"/>
       <c r="BH84" s="20"/>
       <c r="BI84" s="20"/>
-      <c r="BJ84" s="20"/>
-      <c r="BK84" s="20"/>
+      <c r="BJ84" s="64"/>
+      <c r="BK84" s="64"/>
       <c r="BL84" s="21"/>
       <c r="BM84" s="21"/>
       <c r="BN84" s="20"/>
@@ -13077,15 +13087,15 @@
       <c r="B85" s="36"/>
       <c r="C85" s="60"/>
       <c r="D85" s="70"/>
-      <c r="E85" s="181" t="s">
+      <c r="E85" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="F85" s="113"/>
-      <c r="G85" s="114"/>
-      <c r="H85" s="103">
+      <c r="F85" s="107"/>
+      <c r="G85" s="108"/>
+      <c r="H85" s="102">
         <v>45617</v>
       </c>
-      <c r="I85" s="97">
+      <c r="I85" s="118">
         <v>100</v>
       </c>
       <c r="J85" s="62"/>
@@ -13140,8 +13150,8 @@
       <c r="BG85" s="20"/>
       <c r="BH85" s="20"/>
       <c r="BI85" s="69"/>
-      <c r="BJ85" s="20"/>
-      <c r="BK85" s="20"/>
+      <c r="BJ85" s="64"/>
+      <c r="BK85" s="64"/>
       <c r="BL85" s="21"/>
       <c r="BM85" s="21"/>
       <c r="BN85" s="20"/>
@@ -13205,11 +13215,11 @@
       <c r="B86" s="36"/>
       <c r="C86" s="60"/>
       <c r="D86" s="70"/>
-      <c r="E86" s="142"/>
-      <c r="F86" s="117"/>
-      <c r="G86" s="118"/>
-      <c r="H86" s="103"/>
-      <c r="I86" s="98"/>
+      <c r="E86" s="109"/>
+      <c r="F86" s="110"/>
+      <c r="G86" s="111"/>
+      <c r="H86" s="102"/>
+      <c r="I86" s="101"/>
       <c r="J86" s="62"/>
       <c r="K86" s="20"/>
       <c r="L86" s="20"/>
@@ -13262,8 +13272,8 @@
       <c r="BG86" s="20"/>
       <c r="BH86" s="20"/>
       <c r="BI86" s="20"/>
-      <c r="BJ86" s="20"/>
-      <c r="BK86" s="20"/>
+      <c r="BJ86" s="64"/>
+      <c r="BK86" s="64"/>
       <c r="BL86" s="21"/>
       <c r="BM86" s="21"/>
       <c r="BN86" s="20"/>
@@ -13326,16 +13336,16 @@
       <c r="A87" s="16"/>
       <c r="B87" s="71"/>
       <c r="C87" s="90"/>
-      <c r="D87" s="94" t="s">
+      <c r="D87" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E87" s="94"/>
-      <c r="F87" s="94"/>
-      <c r="G87" s="94"/>
-      <c r="H87" s="95">
+      <c r="E87" s="95"/>
+      <c r="F87" s="95"/>
+      <c r="G87" s="95"/>
+      <c r="H87" s="103">
         <v>45615</v>
       </c>
-      <c r="I87" s="97">
+      <c r="I87" s="118">
         <v>100</v>
       </c>
       <c r="J87" s="62"/>
@@ -13390,8 +13400,8 @@
       <c r="BG87" s="20"/>
       <c r="BH87" s="20"/>
       <c r="BI87" s="20"/>
-      <c r="BJ87" s="20"/>
-      <c r="BK87" s="20"/>
+      <c r="BJ87" s="64"/>
+      <c r="BK87" s="64"/>
       <c r="BL87" s="21"/>
       <c r="BM87" s="21"/>
       <c r="BN87" s="20"/>
@@ -13454,12 +13464,12 @@
       <c r="A88" s="16"/>
       <c r="B88" s="71"/>
       <c r="C88" s="90"/>
-      <c r="D88" s="94"/>
-      <c r="E88" s="94"/>
-      <c r="F88" s="94"/>
-      <c r="G88" s="94"/>
-      <c r="H88" s="96"/>
-      <c r="I88" s="98"/>
+      <c r="D88" s="95"/>
+      <c r="E88" s="95"/>
+      <c r="F88" s="95"/>
+      <c r="G88" s="95"/>
+      <c r="H88" s="99"/>
+      <c r="I88" s="101"/>
       <c r="J88" s="62"/>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -13512,8 +13522,8 @@
       <c r="BG88" s="20"/>
       <c r="BH88" s="20"/>
       <c r="BI88" s="20"/>
-      <c r="BJ88" s="20"/>
-      <c r="BK88" s="20"/>
+      <c r="BJ88" s="64"/>
+      <c r="BK88" s="64"/>
       <c r="BL88" s="21"/>
       <c r="BM88" s="21"/>
       <c r="BN88" s="20"/>
@@ -13576,14 +13586,14 @@
       <c r="A89" s="16"/>
       <c r="B89" s="36"/>
       <c r="C89" s="79"/>
-      <c r="D89" s="107" t="s">
+      <c r="D89" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="108"/>
-      <c r="F89" s="108"/>
-      <c r="G89" s="109"/>
-      <c r="H89" s="179"/>
-      <c r="I89" s="180"/>
+      <c r="E89" s="125"/>
+      <c r="F89" s="125"/>
+      <c r="G89" s="126"/>
+      <c r="H89" s="123"/>
+      <c r="I89" s="120"/>
       <c r="J89" s="66"/>
       <c r="K89" s="64"/>
       <c r="L89" s="64"/>
@@ -13700,12 +13710,12 @@
       <c r="A90" s="16"/>
       <c r="B90" s="36"/>
       <c r="C90" s="79"/>
-      <c r="D90" s="110"/>
-      <c r="E90" s="111"/>
-      <c r="F90" s="111"/>
-      <c r="G90" s="112"/>
-      <c r="H90" s="179"/>
-      <c r="I90" s="180"/>
+      <c r="D90" s="127"/>
+      <c r="E90" s="128"/>
+      <c r="F90" s="128"/>
+      <c r="G90" s="129"/>
+      <c r="H90" s="123"/>
+      <c r="I90" s="120"/>
       <c r="J90" s="66"/>
       <c r="K90" s="64"/>
       <c r="L90" s="64"/>
@@ -13823,15 +13833,15 @@
       <c r="B91" s="36"/>
       <c r="C91" s="60"/>
       <c r="D91" s="70"/>
-      <c r="E91" s="141" t="s">
+      <c r="E91" s="97" t="s">
         <v>68</v>
       </c>
-      <c r="F91" s="141"/>
-      <c r="G91" s="141"/>
-      <c r="H91" s="95">
+      <c r="F91" s="97"/>
+      <c r="G91" s="97"/>
+      <c r="H91" s="103">
         <v>45616</v>
       </c>
-      <c r="I91" s="97"/>
+      <c r="I91" s="118"/>
       <c r="J91" s="19"/>
       <c r="K91" s="20"/>
       <c r="L91" s="20"/>
@@ -13884,8 +13894,8 @@
       <c r="BG91" s="20"/>
       <c r="BH91" s="20"/>
       <c r="BI91" s="20"/>
-      <c r="BJ91" s="20"/>
-      <c r="BK91" s="20"/>
+      <c r="BJ91" s="64"/>
+      <c r="BK91" s="64"/>
       <c r="BL91" s="21"/>
       <c r="BM91" s="21"/>
       <c r="BN91" s="20"/>
@@ -13949,11 +13959,11 @@
       <c r="B92" s="36"/>
       <c r="C92" s="60"/>
       <c r="D92" s="70"/>
-      <c r="E92" s="94"/>
-      <c r="F92" s="94"/>
-      <c r="G92" s="94"/>
-      <c r="H92" s="96"/>
-      <c r="I92" s="98"/>
+      <c r="E92" s="95"/>
+      <c r="F92" s="95"/>
+      <c r="G92" s="95"/>
+      <c r="H92" s="99"/>
+      <c r="I92" s="101"/>
       <c r="J92" s="19"/>
       <c r="K92" s="20"/>
       <c r="L92" s="20"/>
@@ -14006,8 +14016,8 @@
       <c r="BG92" s="20"/>
       <c r="BH92" s="20"/>
       <c r="BI92" s="20"/>
-      <c r="BJ92" s="20"/>
-      <c r="BK92" s="20"/>
+      <c r="BJ92" s="64"/>
+      <c r="BK92" s="64"/>
       <c r="BL92" s="21"/>
       <c r="BM92" s="21"/>
       <c r="BN92" s="20"/>
@@ -14071,15 +14081,15 @@
       <c r="B93" s="36"/>
       <c r="C93" s="60"/>
       <c r="D93" s="70"/>
-      <c r="E93" s="94" t="s">
+      <c r="E93" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="F93" s="94"/>
-      <c r="G93" s="94"/>
-      <c r="H93" s="95">
+      <c r="F93" s="95"/>
+      <c r="G93" s="95"/>
+      <c r="H93" s="103">
         <v>45617</v>
       </c>
-      <c r="I93" s="97"/>
+      <c r="I93" s="118"/>
       <c r="J93" s="19"/>
       <c r="K93" s="20"/>
       <c r="L93" s="20"/>
@@ -14132,8 +14142,8 @@
       <c r="BG93" s="20"/>
       <c r="BH93" s="20"/>
       <c r="BI93" s="20"/>
-      <c r="BJ93" s="20"/>
-      <c r="BK93" s="20"/>
+      <c r="BJ93" s="64"/>
+      <c r="BK93" s="64"/>
       <c r="BL93" s="21"/>
       <c r="BM93" s="21"/>
       <c r="BN93" s="20"/>
@@ -14197,11 +14207,11 @@
       <c r="B94" s="36"/>
       <c r="C94" s="60"/>
       <c r="D94" s="70"/>
-      <c r="E94" s="94"/>
-      <c r="F94" s="94"/>
-      <c r="G94" s="94"/>
-      <c r="H94" s="96"/>
-      <c r="I94" s="98"/>
+      <c r="E94" s="95"/>
+      <c r="F94" s="95"/>
+      <c r="G94" s="95"/>
+      <c r="H94" s="99"/>
+      <c r="I94" s="101"/>
       <c r="J94" s="19"/>
       <c r="K94" s="20"/>
       <c r="L94" s="20"/>
@@ -14254,8 +14264,8 @@
       <c r="BG94" s="20"/>
       <c r="BH94" s="20"/>
       <c r="BI94" s="20"/>
-      <c r="BJ94" s="20"/>
-      <c r="BK94" s="20"/>
+      <c r="BJ94" s="64"/>
+      <c r="BK94" s="64"/>
       <c r="BL94" s="21"/>
       <c r="BM94" s="21"/>
       <c r="BN94" s="20"/>
@@ -14319,15 +14329,15 @@
       <c r="B95" s="36"/>
       <c r="C95" s="60"/>
       <c r="D95" s="70"/>
-      <c r="E95" s="94" t="s">
+      <c r="E95" s="95" t="s">
         <v>70</v>
       </c>
-      <c r="F95" s="94"/>
-      <c r="G95" s="94"/>
-      <c r="H95" s="95">
+      <c r="F95" s="95"/>
+      <c r="G95" s="95"/>
+      <c r="H95" s="103">
         <v>45618</v>
       </c>
-      <c r="I95" s="97"/>
+      <c r="I95" s="118"/>
       <c r="J95" s="19"/>
       <c r="K95" s="20"/>
       <c r="L95" s="20"/>
@@ -14380,8 +14390,8 @@
       <c r="BG95" s="20"/>
       <c r="BH95" s="20"/>
       <c r="BI95" s="20"/>
-      <c r="BJ95" s="20"/>
-      <c r="BK95" s="20"/>
+      <c r="BJ95" s="64"/>
+      <c r="BK95" s="64"/>
       <c r="BL95" s="21"/>
       <c r="BM95" s="21"/>
       <c r="BN95" s="20"/>
@@ -14445,11 +14455,11 @@
       <c r="B96" s="36"/>
       <c r="C96" s="60"/>
       <c r="D96" s="70"/>
-      <c r="E96" s="94"/>
-      <c r="F96" s="94"/>
-      <c r="G96" s="94"/>
-      <c r="H96" s="96"/>
-      <c r="I96" s="98"/>
+      <c r="E96" s="95"/>
+      <c r="F96" s="95"/>
+      <c r="G96" s="95"/>
+      <c r="H96" s="99"/>
+      <c r="I96" s="101"/>
       <c r="J96" s="19"/>
       <c r="K96" s="20"/>
       <c r="L96" s="20"/>
@@ -14502,8 +14512,8 @@
       <c r="BG96" s="20"/>
       <c r="BH96" s="20"/>
       <c r="BI96" s="20"/>
-      <c r="BJ96" s="20"/>
-      <c r="BK96" s="20"/>
+      <c r="BJ96" s="64"/>
+      <c r="BK96" s="64"/>
       <c r="BL96" s="21"/>
       <c r="BM96" s="21"/>
       <c r="BN96" s="20"/>
@@ -14567,15 +14577,15 @@
       <c r="B97" s="36"/>
       <c r="C97" s="60"/>
       <c r="D97" s="70"/>
-      <c r="E97" s="94" t="s">
+      <c r="E97" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="F97" s="94"/>
-      <c r="G97" s="94"/>
-      <c r="H97" s="95">
+      <c r="F97" s="95"/>
+      <c r="G97" s="95"/>
+      <c r="H97" s="103">
         <v>45621</v>
       </c>
-      <c r="I97" s="97"/>
+      <c r="I97" s="118"/>
       <c r="J97" s="19"/>
       <c r="K97" s="20"/>
       <c r="L97" s="20"/>
@@ -14628,8 +14638,8 @@
       <c r="BG97" s="20"/>
       <c r="BH97" s="20"/>
       <c r="BI97" s="20"/>
-      <c r="BJ97" s="20"/>
-      <c r="BK97" s="20"/>
+      <c r="BJ97" s="64"/>
+      <c r="BK97" s="64"/>
       <c r="BL97" s="21"/>
       <c r="BM97" s="21"/>
       <c r="BN97" s="20"/>
@@ -14693,11 +14703,11 @@
       <c r="B98" s="36"/>
       <c r="C98" s="60"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="94"/>
-      <c r="F98" s="94"/>
-      <c r="G98" s="94"/>
-      <c r="H98" s="96"/>
-      <c r="I98" s="98"/>
+      <c r="E98" s="95"/>
+      <c r="F98" s="95"/>
+      <c r="G98" s="95"/>
+      <c r="H98" s="99"/>
+      <c r="I98" s="101"/>
       <c r="J98" s="19"/>
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
@@ -14750,8 +14760,8 @@
       <c r="BG98" s="20"/>
       <c r="BH98" s="20"/>
       <c r="BI98" s="20"/>
-      <c r="BJ98" s="20"/>
-      <c r="BK98" s="20"/>
+      <c r="BJ98" s="64"/>
+      <c r="BK98" s="64"/>
       <c r="BL98" s="21"/>
       <c r="BM98" s="21"/>
       <c r="BN98" s="20"/>
@@ -14815,15 +14825,15 @@
       <c r="B99" s="36"/>
       <c r="C99" s="60"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="94" t="s">
+      <c r="E99" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="F99" s="94"/>
-      <c r="G99" s="94"/>
-      <c r="H99" s="95">
+      <c r="F99" s="95"/>
+      <c r="G99" s="95"/>
+      <c r="H99" s="103">
         <v>45622</v>
       </c>
-      <c r="I99" s="97"/>
+      <c r="I99" s="118"/>
       <c r="J99" s="19"/>
       <c r="K99" s="20"/>
       <c r="L99" s="20"/>
@@ -14876,8 +14886,8 @@
       <c r="BG99" s="20"/>
       <c r="BH99" s="20"/>
       <c r="BI99" s="20"/>
-      <c r="BJ99" s="20"/>
-      <c r="BK99" s="20"/>
+      <c r="BJ99" s="64"/>
+      <c r="BK99" s="64"/>
       <c r="BL99" s="21"/>
       <c r="BM99" s="21"/>
       <c r="BN99" s="20"/>
@@ -14941,11 +14951,11 @@
       <c r="B100" s="36"/>
       <c r="C100" s="60"/>
       <c r="D100" s="70"/>
-      <c r="E100" s="94"/>
-      <c r="F100" s="94"/>
-      <c r="G100" s="94"/>
-      <c r="H100" s="96"/>
-      <c r="I100" s="98"/>
+      <c r="E100" s="95"/>
+      <c r="F100" s="95"/>
+      <c r="G100" s="95"/>
+      <c r="H100" s="99"/>
+      <c r="I100" s="101"/>
       <c r="J100" s="19"/>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -14998,8 +15008,8 @@
       <c r="BG100" s="20"/>
       <c r="BH100" s="20"/>
       <c r="BI100" s="20"/>
-      <c r="BJ100" s="20"/>
-      <c r="BK100" s="20"/>
+      <c r="BJ100" s="64"/>
+      <c r="BK100" s="64"/>
       <c r="BL100" s="21"/>
       <c r="BM100" s="21"/>
       <c r="BN100" s="20"/>
@@ -15063,12 +15073,12 @@
       <c r="B101" s="71"/>
       <c r="C101" s="91"/>
       <c r="D101" s="70"/>
-      <c r="E101" s="142" t="s">
+      <c r="E101" s="109" t="s">
         <v>61</v>
       </c>
-      <c r="F101" s="117"/>
-      <c r="G101" s="118"/>
-      <c r="H101" s="95">
+      <c r="F101" s="110"/>
+      <c r="G101" s="111"/>
+      <c r="H101" s="103">
         <v>45623</v>
       </c>
       <c r="I101" s="104"/>
@@ -15124,8 +15134,8 @@
       <c r="BG101" s="20"/>
       <c r="BH101" s="20"/>
       <c r="BI101" s="20"/>
-      <c r="BJ101" s="20"/>
-      <c r="BK101" s="20"/>
+      <c r="BJ101" s="64"/>
+      <c r="BK101" s="64"/>
       <c r="BL101" s="21"/>
       <c r="BM101" s="21"/>
       <c r="BN101" s="20"/>
@@ -15189,10 +15199,10 @@
       <c r="B102" s="71"/>
       <c r="C102" s="91"/>
       <c r="D102" s="70"/>
-      <c r="E102" s="142"/>
-      <c r="F102" s="117"/>
-      <c r="G102" s="118"/>
-      <c r="H102" s="96"/>
+      <c r="E102" s="109"/>
+      <c r="F102" s="110"/>
+      <c r="G102" s="111"/>
+      <c r="H102" s="99"/>
       <c r="I102" s="104"/>
       <c r="J102" s="62"/>
       <c r="K102" s="20"/>
@@ -15246,8 +15256,8 @@
       <c r="BG102" s="20"/>
       <c r="BH102" s="20"/>
       <c r="BI102" s="20"/>
-      <c r="BJ102" s="20"/>
-      <c r="BK102" s="20"/>
+      <c r="BJ102" s="64"/>
+      <c r="BK102" s="64"/>
       <c r="BL102" s="21"/>
       <c r="BM102" s="21"/>
       <c r="BN102" s="20"/>
@@ -15310,16 +15320,16 @@
       <c r="A103" s="16"/>
       <c r="B103" s="71"/>
       <c r="C103" s="90"/>
-      <c r="D103" s="94" t="s">
+      <c r="D103" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="E103" s="94"/>
-      <c r="F103" s="94"/>
-      <c r="G103" s="94"/>
-      <c r="H103" s="95">
+      <c r="E103" s="95"/>
+      <c r="F103" s="95"/>
+      <c r="G103" s="95"/>
+      <c r="H103" s="103">
         <v>45622</v>
       </c>
-      <c r="I103" s="101"/>
+      <c r="I103" s="105"/>
       <c r="J103" s="62"/>
       <c r="K103" s="20"/>
       <c r="L103" s="20"/>
@@ -15372,8 +15382,8 @@
       <c r="BG103" s="20"/>
       <c r="BH103" s="20"/>
       <c r="BI103" s="20"/>
-      <c r="BJ103" s="20"/>
-      <c r="BK103" s="20"/>
+      <c r="BJ103" s="64"/>
+      <c r="BK103" s="64"/>
       <c r="BL103" s="21"/>
       <c r="BM103" s="21"/>
       <c r="BN103" s="20"/>
@@ -15436,12 +15446,12 @@
       <c r="A104" s="16"/>
       <c r="B104" s="71"/>
       <c r="C104" s="90"/>
-      <c r="D104" s="94"/>
-      <c r="E104" s="94"/>
-      <c r="F104" s="94"/>
-      <c r="G104" s="94"/>
-      <c r="H104" s="96"/>
-      <c r="I104" s="102"/>
+      <c r="D104" s="95"/>
+      <c r="E104" s="95"/>
+      <c r="F104" s="95"/>
+      <c r="G104" s="95"/>
+      <c r="H104" s="99"/>
+      <c r="I104" s="135"/>
       <c r="J104" s="62"/>
       <c r="K104" s="20"/>
       <c r="L104" s="20"/>
@@ -15494,8 +15504,8 @@
       <c r="BG104" s="20"/>
       <c r="BH104" s="20"/>
       <c r="BI104" s="20"/>
-      <c r="BJ104" s="20"/>
-      <c r="BK104" s="20"/>
+      <c r="BJ104" s="64"/>
+      <c r="BK104" s="64"/>
       <c r="BL104" s="21"/>
       <c r="BM104" s="21"/>
       <c r="BN104" s="20"/>
@@ -15557,15 +15567,15 @@
     <row r="105" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A105" s="16"/>
       <c r="B105" s="71"/>
-      <c r="C105" s="135" t="s">
+      <c r="C105" s="179" t="s">
         <v>64</v>
       </c>
-      <c r="D105" s="136"/>
-      <c r="E105" s="136"/>
-      <c r="F105" s="136"/>
-      <c r="G105" s="137"/>
-      <c r="H105" s="182"/>
-      <c r="I105" s="180"/>
+      <c r="D105" s="180"/>
+      <c r="E105" s="180"/>
+      <c r="F105" s="180"/>
+      <c r="G105" s="181"/>
+      <c r="H105" s="119"/>
+      <c r="I105" s="120"/>
       <c r="J105" s="66"/>
       <c r="K105" s="64"/>
       <c r="L105" s="64"/>
@@ -15681,13 +15691,13 @@
     <row r="106" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A106" s="16"/>
       <c r="B106" s="71"/>
-      <c r="C106" s="138"/>
-      <c r="D106" s="139"/>
-      <c r="E106" s="139"/>
-      <c r="F106" s="139"/>
-      <c r="G106" s="140"/>
-      <c r="H106" s="182"/>
-      <c r="I106" s="180"/>
+      <c r="C106" s="182"/>
+      <c r="D106" s="183"/>
+      <c r="E106" s="183"/>
+      <c r="F106" s="183"/>
+      <c r="G106" s="184"/>
+      <c r="H106" s="119"/>
+      <c r="I106" s="120"/>
       <c r="J106" s="66"/>
       <c r="K106" s="64"/>
       <c r="L106" s="64"/>
@@ -15804,14 +15814,14 @@
       <c r="A107" s="16"/>
       <c r="B107" s="36"/>
       <c r="C107" s="78"/>
-      <c r="D107" s="107" t="s">
+      <c r="D107" s="124" t="s">
         <v>59</v>
       </c>
-      <c r="E107" s="108"/>
-      <c r="F107" s="108"/>
-      <c r="G107" s="109"/>
-      <c r="H107" s="182"/>
-      <c r="I107" s="180"/>
+      <c r="E107" s="125"/>
+      <c r="F107" s="125"/>
+      <c r="G107" s="126"/>
+      <c r="H107" s="119"/>
+      <c r="I107" s="120"/>
       <c r="J107" s="66"/>
       <c r="K107" s="64"/>
       <c r="L107" s="64"/>
@@ -15928,12 +15938,12 @@
       <c r="A108" s="16"/>
       <c r="B108" s="36"/>
       <c r="C108" s="76"/>
-      <c r="D108" s="110"/>
-      <c r="E108" s="111"/>
-      <c r="F108" s="111"/>
-      <c r="G108" s="112"/>
-      <c r="H108" s="182"/>
-      <c r="I108" s="180"/>
+      <c r="D108" s="127"/>
+      <c r="E108" s="128"/>
+      <c r="F108" s="128"/>
+      <c r="G108" s="129"/>
+      <c r="H108" s="119"/>
+      <c r="I108" s="120"/>
       <c r="J108" s="66"/>
       <c r="K108" s="64"/>
       <c r="L108" s="64"/>
@@ -16051,15 +16061,15 @@
       <c r="B109" s="36"/>
       <c r="C109" s="60"/>
       <c r="D109" s="70"/>
-      <c r="E109" s="141" t="s">
+      <c r="E109" s="97" t="s">
         <v>73</v>
       </c>
-      <c r="F109" s="141"/>
-      <c r="G109" s="141"/>
-      <c r="H109" s="95">
+      <c r="F109" s="97"/>
+      <c r="G109" s="97"/>
+      <c r="H109" s="103">
         <v>45624</v>
       </c>
-      <c r="I109" s="101"/>
+      <c r="I109" s="105"/>
       <c r="J109" s="62"/>
       <c r="K109" s="20"/>
       <c r="L109" s="20"/>
@@ -16112,8 +16122,8 @@
       <c r="BG109" s="20"/>
       <c r="BH109" s="20"/>
       <c r="BI109" s="20"/>
-      <c r="BJ109" s="20"/>
-      <c r="BK109" s="20"/>
+      <c r="BJ109" s="64"/>
+      <c r="BK109" s="64"/>
       <c r="BL109" s="21"/>
       <c r="BM109" s="21"/>
       <c r="BN109" s="20"/>
@@ -16177,11 +16187,11 @@
       <c r="B110" s="36"/>
       <c r="C110" s="60"/>
       <c r="D110" s="70"/>
-      <c r="E110" s="94"/>
-      <c r="F110" s="94"/>
-      <c r="G110" s="94"/>
-      <c r="H110" s="96"/>
-      <c r="I110" s="102"/>
+      <c r="E110" s="95"/>
+      <c r="F110" s="95"/>
+      <c r="G110" s="95"/>
+      <c r="H110" s="99"/>
+      <c r="I110" s="135"/>
       <c r="J110" s="62"/>
       <c r="K110" s="20"/>
       <c r="L110" s="20"/>
@@ -16234,8 +16244,8 @@
       <c r="BG110" s="69"/>
       <c r="BH110" s="69"/>
       <c r="BI110" s="69"/>
-      <c r="BJ110" s="69"/>
-      <c r="BK110" s="20"/>
+      <c r="BJ110" s="64"/>
+      <c r="BK110" s="64"/>
       <c r="BL110" s="21"/>
       <c r="BM110" s="21"/>
       <c r="BN110" s="20"/>
@@ -16299,15 +16309,15 @@
       <c r="B111" s="36"/>
       <c r="C111" s="60"/>
       <c r="D111" s="70"/>
-      <c r="E111" s="94" t="s">
+      <c r="E111" s="95" t="s">
         <v>74</v>
       </c>
-      <c r="F111" s="94"/>
-      <c r="G111" s="94"/>
-      <c r="H111" s="95">
+      <c r="F111" s="95"/>
+      <c r="G111" s="95"/>
+      <c r="H111" s="103">
         <v>45625</v>
       </c>
-      <c r="I111" s="101"/>
+      <c r="I111" s="105"/>
       <c r="J111" s="62"/>
       <c r="K111" s="20"/>
       <c r="L111" s="20"/>
@@ -16360,8 +16370,8 @@
       <c r="BG111" s="69"/>
       <c r="BH111" s="69"/>
       <c r="BI111" s="69"/>
-      <c r="BJ111" s="69"/>
-      <c r="BK111" s="20"/>
+      <c r="BJ111" s="64"/>
+      <c r="BK111" s="64"/>
       <c r="BL111" s="21"/>
       <c r="BM111" s="21"/>
       <c r="BN111" s="20"/>
@@ -16425,11 +16435,11 @@
       <c r="B112" s="36"/>
       <c r="C112" s="60"/>
       <c r="D112" s="70"/>
-      <c r="E112" s="94"/>
-      <c r="F112" s="94"/>
-      <c r="G112" s="94"/>
-      <c r="H112" s="96"/>
-      <c r="I112" s="102"/>
+      <c r="E112" s="95"/>
+      <c r="F112" s="95"/>
+      <c r="G112" s="95"/>
+      <c r="H112" s="99"/>
+      <c r="I112" s="135"/>
       <c r="J112" s="62"/>
       <c r="K112" s="20"/>
       <c r="L112" s="20"/>
@@ -16482,8 +16492,8 @@
       <c r="BG112" s="69"/>
       <c r="BH112" s="69"/>
       <c r="BI112" s="69"/>
-      <c r="BJ112" s="69"/>
-      <c r="BK112" s="20"/>
+      <c r="BJ112" s="64"/>
+      <c r="BK112" s="64"/>
       <c r="BL112" s="21"/>
       <c r="BM112" s="21"/>
       <c r="BN112" s="20"/>
@@ -16547,12 +16557,12 @@
       <c r="B113" s="71"/>
       <c r="C113" s="91"/>
       <c r="D113" s="70"/>
-      <c r="E113" s="94" t="s">
+      <c r="E113" s="95" t="s">
         <v>61</v>
       </c>
-      <c r="F113" s="94"/>
-      <c r="G113" s="94"/>
-      <c r="H113" s="103">
+      <c r="F113" s="95"/>
+      <c r="G113" s="95"/>
+      <c r="H113" s="102">
         <v>45630</v>
       </c>
       <c r="I113" s="104"/>
@@ -16608,8 +16618,8 @@
       <c r="BG113" s="69"/>
       <c r="BH113" s="69"/>
       <c r="BI113" s="41"/>
-      <c r="BJ113" s="69"/>
-      <c r="BK113" s="20"/>
+      <c r="BJ113" s="64"/>
+      <c r="BK113" s="64"/>
       <c r="BL113" s="21"/>
       <c r="BM113" s="21"/>
       <c r="BN113" s="20"/>
@@ -16673,11 +16683,11 @@
       <c r="B114" s="71"/>
       <c r="C114" s="91"/>
       <c r="D114" s="70"/>
-      <c r="E114" s="190"/>
-      <c r="F114" s="190"/>
-      <c r="G114" s="190"/>
-      <c r="H114" s="95"/>
-      <c r="I114" s="101"/>
+      <c r="E114" s="117"/>
+      <c r="F114" s="117"/>
+      <c r="G114" s="117"/>
+      <c r="H114" s="103"/>
+      <c r="I114" s="105"/>
       <c r="J114" s="62"/>
       <c r="K114" s="20"/>
       <c r="L114" s="20"/>
@@ -16730,8 +16740,8 @@
       <c r="BG114" s="20"/>
       <c r="BH114" s="20"/>
       <c r="BI114" s="20"/>
-      <c r="BJ114" s="20"/>
-      <c r="BK114" s="20"/>
+      <c r="BJ114" s="64"/>
+      <c r="BK114" s="64"/>
       <c r="BL114" s="21"/>
       <c r="BM114" s="21"/>
       <c r="BN114" s="20"/>
@@ -16794,13 +16804,13 @@
       <c r="A115" s="16"/>
       <c r="B115" s="71"/>
       <c r="C115" s="91"/>
-      <c r="D115" s="94" t="s">
+      <c r="D115" s="95" t="s">
         <v>78</v>
       </c>
-      <c r="E115" s="94"/>
-      <c r="F115" s="94"/>
-      <c r="G115" s="94"/>
-      <c r="H115" s="103">
+      <c r="E115" s="95"/>
+      <c r="F115" s="95"/>
+      <c r="G115" s="95"/>
+      <c r="H115" s="102">
         <v>45625</v>
       </c>
       <c r="I115" s="104"/>
@@ -16856,8 +16866,8 @@
       <c r="BG115" s="20"/>
       <c r="BH115" s="20"/>
       <c r="BI115" s="20"/>
-      <c r="BJ115" s="20"/>
-      <c r="BK115" s="20"/>
+      <c r="BJ115" s="64"/>
+      <c r="BK115" s="64"/>
       <c r="BL115" s="21"/>
       <c r="BM115" s="21"/>
       <c r="BN115" s="20"/>
@@ -16920,11 +16930,11 @@
       <c r="A116" s="16"/>
       <c r="B116" s="71"/>
       <c r="C116" s="91"/>
-      <c r="D116" s="94"/>
-      <c r="E116" s="94"/>
-      <c r="F116" s="94"/>
-      <c r="G116" s="94"/>
-      <c r="H116" s="103"/>
+      <c r="D116" s="95"/>
+      <c r="E116" s="95"/>
+      <c r="F116" s="95"/>
+      <c r="G116" s="95"/>
+      <c r="H116" s="102"/>
       <c r="I116" s="104"/>
       <c r="J116" s="62"/>
       <c r="K116" s="20"/>
@@ -16978,8 +16988,8 @@
       <c r="BG116" s="20"/>
       <c r="BH116" s="20"/>
       <c r="BI116" s="20"/>
-      <c r="BJ116" s="20"/>
-      <c r="BK116" s="20"/>
+      <c r="BJ116" s="64"/>
+      <c r="BK116" s="64"/>
       <c r="BL116" s="21"/>
       <c r="BM116" s="21"/>
       <c r="BN116" s="20"/>
@@ -17042,14 +17052,14 @@
       <c r="A117" s="16"/>
       <c r="B117" s="36"/>
       <c r="C117" s="80"/>
-      <c r="D117" s="107" t="s">
+      <c r="D117" s="124" t="s">
         <v>60</v>
       </c>
-      <c r="E117" s="108"/>
-      <c r="F117" s="108"/>
-      <c r="G117" s="109"/>
-      <c r="H117" s="183"/>
-      <c r="I117" s="173"/>
+      <c r="E117" s="125"/>
+      <c r="F117" s="125"/>
+      <c r="G117" s="126"/>
+      <c r="H117" s="113"/>
+      <c r="I117" s="121"/>
       <c r="J117" s="63"/>
       <c r="K117" s="64"/>
       <c r="L117" s="64"/>
@@ -17166,12 +17176,12 @@
       <c r="A118" s="16"/>
       <c r="B118" s="36"/>
       <c r="C118" s="80"/>
-      <c r="D118" s="110"/>
-      <c r="E118" s="111"/>
-      <c r="F118" s="111"/>
-      <c r="G118" s="112"/>
-      <c r="H118" s="184"/>
-      <c r="I118" s="174"/>
+      <c r="D118" s="127"/>
+      <c r="E118" s="128"/>
+      <c r="F118" s="128"/>
+      <c r="G118" s="129"/>
+      <c r="H118" s="114"/>
+      <c r="I118" s="122"/>
       <c r="J118" s="63"/>
       <c r="K118" s="64"/>
       <c r="L118" s="64"/>
@@ -17289,15 +17299,15 @@
       <c r="B119" s="36"/>
       <c r="C119" s="60"/>
       <c r="D119" s="70"/>
-      <c r="E119" s="141" t="s">
+      <c r="E119" s="97" t="s">
         <v>68</v>
       </c>
-      <c r="F119" s="141"/>
-      <c r="G119" s="141"/>
-      <c r="H119" s="95">
+      <c r="F119" s="97"/>
+      <c r="G119" s="97"/>
+      <c r="H119" s="103">
         <v>45629</v>
       </c>
-      <c r="I119" s="97"/>
+      <c r="I119" s="118"/>
       <c r="J119" s="19"/>
       <c r="K119" s="20"/>
       <c r="L119" s="20"/>
@@ -17350,8 +17360,8 @@
       <c r="BG119" s="41"/>
       <c r="BH119" s="41"/>
       <c r="BI119" s="20"/>
-      <c r="BJ119" s="20"/>
-      <c r="BK119" s="20"/>
+      <c r="BJ119" s="64"/>
+      <c r="BK119" s="64"/>
       <c r="BL119" s="21"/>
       <c r="BM119" s="21"/>
       <c r="BN119" s="69"/>
@@ -17415,11 +17425,11 @@
       <c r="B120" s="36"/>
       <c r="C120" s="60"/>
       <c r="D120" s="70"/>
-      <c r="E120" s="94"/>
-      <c r="F120" s="94"/>
-      <c r="G120" s="94"/>
-      <c r="H120" s="96"/>
-      <c r="I120" s="98"/>
+      <c r="E120" s="95"/>
+      <c r="F120" s="95"/>
+      <c r="G120" s="95"/>
+      <c r="H120" s="99"/>
+      <c r="I120" s="101"/>
       <c r="J120" s="19"/>
       <c r="K120" s="20"/>
       <c r="L120" s="20"/>
@@ -17472,8 +17482,8 @@
       <c r="BG120" s="20"/>
       <c r="BH120" s="20"/>
       <c r="BI120" s="20"/>
-      <c r="BJ120" s="20"/>
-      <c r="BK120" s="20"/>
+      <c r="BJ120" s="64"/>
+      <c r="BK120" s="64"/>
       <c r="BL120" s="21"/>
       <c r="BM120" s="21"/>
       <c r="BN120" s="69"/>
@@ -17537,15 +17547,15 @@
       <c r="B121" s="36"/>
       <c r="C121" s="60"/>
       <c r="D121" s="70"/>
-      <c r="E121" s="94" t="s">
+      <c r="E121" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="F121" s="94"/>
-      <c r="G121" s="94"/>
-      <c r="H121" s="95">
+      <c r="F121" s="95"/>
+      <c r="G121" s="95"/>
+      <c r="H121" s="103">
         <v>45630</v>
       </c>
-      <c r="I121" s="97"/>
+      <c r="I121" s="118"/>
       <c r="J121" s="19"/>
       <c r="K121" s="20"/>
       <c r="L121" s="20"/>
@@ -17598,8 +17608,8 @@
       <c r="BG121" s="20"/>
       <c r="BH121" s="41"/>
       <c r="BI121" s="41"/>
-      <c r="BJ121" s="20"/>
-      <c r="BK121" s="20"/>
+      <c r="BJ121" s="64"/>
+      <c r="BK121" s="64"/>
       <c r="BL121" s="21"/>
       <c r="BM121" s="21"/>
       <c r="BN121" s="69"/>
@@ -17663,11 +17673,11 @@
       <c r="B122" s="36"/>
       <c r="C122" s="60"/>
       <c r="D122" s="70"/>
-      <c r="E122" s="94"/>
-      <c r="F122" s="94"/>
-      <c r="G122" s="94"/>
-      <c r="H122" s="96"/>
-      <c r="I122" s="98"/>
+      <c r="E122" s="95"/>
+      <c r="F122" s="95"/>
+      <c r="G122" s="95"/>
+      <c r="H122" s="99"/>
+      <c r="I122" s="101"/>
       <c r="J122" s="19"/>
       <c r="K122" s="20"/>
       <c r="L122" s="20"/>
@@ -17720,8 +17730,8 @@
       <c r="BG122" s="20"/>
       <c r="BH122" s="20"/>
       <c r="BI122" s="20"/>
-      <c r="BJ122" s="20"/>
-      <c r="BK122" s="20"/>
+      <c r="BJ122" s="64"/>
+      <c r="BK122" s="64"/>
       <c r="BL122" s="21"/>
       <c r="BM122" s="21"/>
       <c r="BN122" s="69"/>
@@ -17785,12 +17795,12 @@
       <c r="B123" s="36"/>
       <c r="C123" s="60"/>
       <c r="D123" s="70"/>
-      <c r="E123" s="94" t="s">
+      <c r="E123" s="95" t="s">
         <v>70</v>
       </c>
-      <c r="F123" s="94"/>
-      <c r="G123" s="94"/>
-      <c r="H123" s="189">
+      <c r="F123" s="95"/>
+      <c r="G123" s="95"/>
+      <c r="H123" s="112">
         <v>45631</v>
       </c>
       <c r="I123" s="104"/>
@@ -17846,8 +17856,8 @@
       <c r="BG123" s="20"/>
       <c r="BH123" s="20"/>
       <c r="BI123" s="41"/>
-      <c r="BJ123" s="41"/>
-      <c r="BK123" s="20"/>
+      <c r="BJ123" s="64"/>
+      <c r="BK123" s="64"/>
       <c r="BL123" s="21"/>
       <c r="BM123" s="21"/>
       <c r="BN123" s="69"/>
@@ -17911,10 +17921,10 @@
       <c r="B124" s="36"/>
       <c r="C124" s="60"/>
       <c r="D124" s="70"/>
-      <c r="E124" s="94"/>
-      <c r="F124" s="94"/>
-      <c r="G124" s="94"/>
-      <c r="H124" s="189"/>
+      <c r="E124" s="95"/>
+      <c r="F124" s="95"/>
+      <c r="G124" s="95"/>
+      <c r="H124" s="112"/>
       <c r="I124" s="104"/>
       <c r="J124" s="62"/>
       <c r="K124" s="20"/>
@@ -17968,8 +17978,8 @@
       <c r="BG124" s="20"/>
       <c r="BH124" s="20"/>
       <c r="BI124" s="20"/>
-      <c r="BJ124" s="20"/>
-      <c r="BK124" s="20"/>
+      <c r="BJ124" s="64"/>
+      <c r="BK124" s="64"/>
       <c r="BL124" s="21"/>
       <c r="BM124" s="21"/>
       <c r="BN124" s="69"/>
@@ -18033,12 +18043,12 @@
       <c r="B125" s="36"/>
       <c r="C125" s="60"/>
       <c r="D125" s="70"/>
-      <c r="E125" s="94" t="s">
+      <c r="E125" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="F125" s="94"/>
-      <c r="G125" s="94"/>
-      <c r="H125" s="103">
+      <c r="F125" s="95"/>
+      <c r="G125" s="95"/>
+      <c r="H125" s="102">
         <v>45632</v>
       </c>
       <c r="I125" s="104"/>
@@ -18093,12 +18103,12 @@
       <c r="BF125" s="21"/>
       <c r="BG125" s="20"/>
       <c r="BH125" s="20"/>
-      <c r="BI125" s="20"/>
-      <c r="BJ125" s="41"/>
-      <c r="BK125" s="41"/>
+      <c r="BI125" s="41"/>
+      <c r="BJ125" s="64"/>
+      <c r="BK125" s="64"/>
       <c r="BL125" s="21"/>
       <c r="BM125" s="21"/>
-      <c r="BN125" s="69"/>
+      <c r="BN125" s="41"/>
       <c r="BO125" s="69"/>
       <c r="BP125" s="69"/>
       <c r="BQ125" s="69"/>
@@ -18159,10 +18169,10 @@
       <c r="B126" s="36"/>
       <c r="C126" s="60"/>
       <c r="D126" s="70"/>
-      <c r="E126" s="94"/>
-      <c r="F126" s="94"/>
-      <c r="G126" s="94"/>
-      <c r="H126" s="103"/>
+      <c r="E126" s="95"/>
+      <c r="F126" s="95"/>
+      <c r="G126" s="95"/>
+      <c r="H126" s="102"/>
       <c r="I126" s="104"/>
       <c r="J126" s="62"/>
       <c r="K126" s="20"/>
@@ -18216,8 +18226,8 @@
       <c r="BG126" s="20"/>
       <c r="BH126" s="20"/>
       <c r="BI126" s="20"/>
-      <c r="BJ126" s="20"/>
-      <c r="BK126" s="20"/>
+      <c r="BJ126" s="64"/>
+      <c r="BK126" s="64"/>
       <c r="BL126" s="21"/>
       <c r="BM126" s="21"/>
       <c r="BN126" s="69"/>
@@ -18281,15 +18291,15 @@
       <c r="B127" s="36"/>
       <c r="C127" s="60"/>
       <c r="D127" s="70"/>
-      <c r="E127" s="94" t="s">
+      <c r="E127" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="F127" s="94"/>
-      <c r="G127" s="94"/>
-      <c r="H127" s="95">
+      <c r="F127" s="95"/>
+      <c r="G127" s="95"/>
+      <c r="H127" s="103">
         <v>45635</v>
       </c>
-      <c r="I127" s="97"/>
+      <c r="I127" s="118"/>
       <c r="J127" s="19"/>
       <c r="K127" s="20"/>
       <c r="L127" s="20"/>
@@ -18342,8 +18352,8 @@
       <c r="BG127" s="20"/>
       <c r="BH127" s="20"/>
       <c r="BI127" s="20"/>
-      <c r="BJ127" s="20"/>
-      <c r="BK127" s="41"/>
+      <c r="BJ127" s="64"/>
+      <c r="BK127" s="64"/>
       <c r="BL127" s="21"/>
       <c r="BM127" s="21"/>
       <c r="BN127" s="41"/>
@@ -18407,11 +18417,11 @@
       <c r="B128" s="36"/>
       <c r="C128" s="60"/>
       <c r="D128" s="70"/>
-      <c r="E128" s="190"/>
-      <c r="F128" s="190"/>
-      <c r="G128" s="190"/>
-      <c r="H128" s="96"/>
-      <c r="I128" s="98"/>
+      <c r="E128" s="117"/>
+      <c r="F128" s="117"/>
+      <c r="G128" s="117"/>
+      <c r="H128" s="99"/>
+      <c r="I128" s="101"/>
       <c r="J128" s="19"/>
       <c r="K128" s="20"/>
       <c r="L128" s="20"/>
@@ -18464,8 +18474,8 @@
       <c r="BG128" s="20"/>
       <c r="BH128" s="20"/>
       <c r="BI128" s="20"/>
-      <c r="BJ128" s="20"/>
-      <c r="BK128" s="20"/>
+      <c r="BJ128" s="64"/>
+      <c r="BK128" s="64"/>
       <c r="BL128" s="21"/>
       <c r="BM128" s="21"/>
       <c r="BN128" s="69"/>
@@ -18529,12 +18539,12 @@
       <c r="B129" s="71"/>
       <c r="C129" s="91"/>
       <c r="D129" s="70"/>
-      <c r="E129" s="181" t="s">
+      <c r="E129" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="F129" s="113"/>
-      <c r="G129" s="114"/>
-      <c r="H129" s="103">
+      <c r="F129" s="107"/>
+      <c r="G129" s="108"/>
+      <c r="H129" s="102">
         <v>45638</v>
       </c>
       <c r="I129" s="104"/>
@@ -18590,8 +18600,8 @@
       <c r="BG129" s="20"/>
       <c r="BH129" s="20"/>
       <c r="BI129" s="20"/>
-      <c r="BJ129" s="20"/>
-      <c r="BK129" s="20"/>
+      <c r="BJ129" s="64"/>
+      <c r="BK129" s="64"/>
       <c r="BL129" s="21"/>
       <c r="BM129" s="21"/>
       <c r="BN129" s="69"/>
@@ -18655,10 +18665,10 @@
       <c r="B130" s="71"/>
       <c r="C130" s="91"/>
       <c r="D130" s="70"/>
-      <c r="E130" s="142"/>
-      <c r="F130" s="117"/>
-      <c r="G130" s="118"/>
-      <c r="H130" s="103"/>
+      <c r="E130" s="109"/>
+      <c r="F130" s="110"/>
+      <c r="G130" s="111"/>
+      <c r="H130" s="102"/>
       <c r="I130" s="104"/>
       <c r="J130" s="62"/>
       <c r="K130" s="20"/>
@@ -18712,8 +18722,8 @@
       <c r="BG130" s="20"/>
       <c r="BH130" s="20"/>
       <c r="BI130" s="20"/>
-      <c r="BJ130" s="20"/>
-      <c r="BK130" s="20"/>
+      <c r="BJ130" s="64"/>
+      <c r="BK130" s="64"/>
       <c r="BL130" s="21"/>
       <c r="BM130" s="21"/>
       <c r="BN130" s="20"/>
@@ -18776,16 +18786,16 @@
       <c r="A131" s="16"/>
       <c r="B131" s="71"/>
       <c r="C131" s="91"/>
-      <c r="D131" s="94" t="s">
+      <c r="D131" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="E131" s="94"/>
-      <c r="F131" s="94"/>
-      <c r="G131" s="94"/>
-      <c r="H131" s="95">
+      <c r="E131" s="95"/>
+      <c r="F131" s="95"/>
+      <c r="G131" s="95"/>
+      <c r="H131" s="103">
         <v>45635</v>
       </c>
-      <c r="I131" s="101"/>
+      <c r="I131" s="105"/>
       <c r="J131" s="62"/>
       <c r="K131" s="20"/>
       <c r="L131" s="20"/>
@@ -18838,8 +18848,8 @@
       <c r="BG131" s="20"/>
       <c r="BH131" s="20"/>
       <c r="BI131" s="20"/>
-      <c r="BJ131" s="20"/>
-      <c r="BK131" s="20"/>
+      <c r="BJ131" s="64"/>
+      <c r="BK131" s="64"/>
       <c r="BL131" s="21"/>
       <c r="BM131" s="21"/>
       <c r="BN131" s="20"/>
@@ -18902,12 +18912,12 @@
       <c r="A132" s="16"/>
       <c r="B132" s="71"/>
       <c r="C132" s="90"/>
-      <c r="D132" s="94"/>
-      <c r="E132" s="94"/>
-      <c r="F132" s="94"/>
-      <c r="G132" s="94"/>
-      <c r="H132" s="96"/>
-      <c r="I132" s="102"/>
+      <c r="D132" s="95"/>
+      <c r="E132" s="95"/>
+      <c r="F132" s="95"/>
+      <c r="G132" s="95"/>
+      <c r="H132" s="99"/>
+      <c r="I132" s="135"/>
       <c r="J132" s="62"/>
       <c r="K132" s="20"/>
       <c r="L132" s="20"/>
@@ -18960,8 +18970,8 @@
       <c r="BG132" s="20"/>
       <c r="BH132" s="20"/>
       <c r="BI132" s="20"/>
-      <c r="BJ132" s="20"/>
-      <c r="BK132" s="20"/>
+      <c r="BJ132" s="64"/>
+      <c r="BK132" s="64"/>
       <c r="BL132" s="21"/>
       <c r="BM132" s="21"/>
       <c r="BN132" s="20"/>
@@ -19023,15 +19033,15 @@
     <row r="133" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A133" s="16"/>
       <c r="B133" s="36"/>
-      <c r="C133" s="107" t="s">
+      <c r="C133" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="D133" s="108"/>
-      <c r="E133" s="108"/>
-      <c r="F133" s="108"/>
-      <c r="G133" s="109"/>
-      <c r="H133" s="183"/>
-      <c r="I133" s="99"/>
+      <c r="D133" s="125"/>
+      <c r="E133" s="125"/>
+      <c r="F133" s="125"/>
+      <c r="G133" s="126"/>
+      <c r="H133" s="113"/>
+      <c r="I133" s="115"/>
       <c r="J133" s="66"/>
       <c r="K133" s="64"/>
       <c r="L133" s="64"/>
@@ -19147,13 +19157,13 @@
     <row r="134" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A134" s="16"/>
       <c r="B134" s="36"/>
-      <c r="C134" s="110"/>
-      <c r="D134" s="111"/>
-      <c r="E134" s="111"/>
-      <c r="F134" s="111"/>
-      <c r="G134" s="112"/>
-      <c r="H134" s="184"/>
-      <c r="I134" s="100"/>
+      <c r="C134" s="127"/>
+      <c r="D134" s="128"/>
+      <c r="E134" s="128"/>
+      <c r="F134" s="128"/>
+      <c r="G134" s="129"/>
+      <c r="H134" s="114"/>
+      <c r="I134" s="116"/>
       <c r="J134" s="66"/>
       <c r="K134" s="64"/>
       <c r="L134" s="64"/>
@@ -19270,14 +19280,14 @@
       <c r="A135" s="16"/>
       <c r="B135" s="36"/>
       <c r="C135" s="60"/>
-      <c r="D135" s="107" t="s">
+      <c r="D135" s="124" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="108"/>
-      <c r="F135" s="108"/>
-      <c r="G135" s="109"/>
-      <c r="H135" s="105"/>
-      <c r="I135" s="173"/>
+      <c r="E135" s="125"/>
+      <c r="F135" s="125"/>
+      <c r="G135" s="126"/>
+      <c r="H135" s="185"/>
+      <c r="I135" s="121"/>
       <c r="J135" s="63"/>
       <c r="K135" s="64"/>
       <c r="L135" s="64"/>
@@ -19394,12 +19404,12 @@
       <c r="A136" s="16"/>
       <c r="B136" s="36"/>
       <c r="C136" s="60"/>
-      <c r="D136" s="110"/>
-      <c r="E136" s="111"/>
-      <c r="F136" s="111"/>
-      <c r="G136" s="112"/>
-      <c r="H136" s="122"/>
-      <c r="I136" s="175"/>
+      <c r="D136" s="127"/>
+      <c r="E136" s="128"/>
+      <c r="F136" s="128"/>
+      <c r="G136" s="129"/>
+      <c r="H136" s="190"/>
+      <c r="I136" s="136"/>
       <c r="J136" s="63"/>
       <c r="K136" s="64"/>
       <c r="L136" s="64"/>
@@ -19517,15 +19527,15 @@
       <c r="B137" s="36"/>
       <c r="C137" s="72"/>
       <c r="D137" s="74"/>
-      <c r="E137" s="113" t="s">
+      <c r="E137" s="107" t="s">
         <v>73</v>
       </c>
-      <c r="F137" s="113"/>
-      <c r="G137" s="114"/>
-      <c r="H137" s="95">
+      <c r="F137" s="107"/>
+      <c r="G137" s="108"/>
+      <c r="H137" s="103">
         <v>45636</v>
       </c>
-      <c r="I137" s="101"/>
+      <c r="I137" s="105"/>
       <c r="J137" s="62"/>
       <c r="K137" s="20"/>
       <c r="L137" s="20"/>
@@ -19578,8 +19588,8 @@
       <c r="BG137" s="20"/>
       <c r="BH137" s="20"/>
       <c r="BI137" s="20"/>
-      <c r="BJ137" s="20"/>
-      <c r="BK137" s="20"/>
+      <c r="BJ137" s="64"/>
+      <c r="BK137" s="64"/>
       <c r="BL137" s="21"/>
       <c r="BM137" s="21"/>
       <c r="BN137" s="41"/>
@@ -19643,11 +19653,11 @@
       <c r="B138" s="36"/>
       <c r="C138" s="72"/>
       <c r="D138" s="70"/>
-      <c r="E138" s="115"/>
-      <c r="F138" s="115"/>
-      <c r="G138" s="116"/>
-      <c r="H138" s="96"/>
-      <c r="I138" s="102"/>
+      <c r="E138" s="177"/>
+      <c r="F138" s="177"/>
+      <c r="G138" s="178"/>
+      <c r="H138" s="99"/>
+      <c r="I138" s="135"/>
       <c r="J138" s="62"/>
       <c r="K138" s="20"/>
       <c r="L138" s="20"/>
@@ -19700,8 +19710,8 @@
       <c r="BG138" s="20"/>
       <c r="BH138" s="20"/>
       <c r="BI138" s="20"/>
-      <c r="BJ138" s="20"/>
-      <c r="BK138" s="20"/>
+      <c r="BJ138" s="64"/>
+      <c r="BK138" s="64"/>
       <c r="BL138" s="21"/>
       <c r="BM138" s="21"/>
       <c r="BN138" s="20"/>
@@ -19765,15 +19775,15 @@
       <c r="B139" s="36"/>
       <c r="C139" s="72"/>
       <c r="D139" s="70"/>
-      <c r="E139" s="113" t="s">
+      <c r="E139" s="107" t="s">
         <v>74</v>
       </c>
-      <c r="F139" s="113"/>
-      <c r="G139" s="114"/>
-      <c r="H139" s="95">
+      <c r="F139" s="107"/>
+      <c r="G139" s="108"/>
+      <c r="H139" s="103">
         <v>45637</v>
       </c>
-      <c r="I139" s="101"/>
+      <c r="I139" s="105"/>
       <c r="J139" s="62"/>
       <c r="K139" s="20"/>
       <c r="L139" s="20"/>
@@ -19826,8 +19836,8 @@
       <c r="BG139" s="20"/>
       <c r="BH139" s="20"/>
       <c r="BI139" s="20"/>
-      <c r="BJ139" s="20"/>
-      <c r="BK139" s="20"/>
+      <c r="BJ139" s="64"/>
+      <c r="BK139" s="64"/>
       <c r="BL139" s="21"/>
       <c r="BM139" s="21"/>
       <c r="BN139" s="20"/>
@@ -19891,11 +19901,11 @@
       <c r="B140" s="36"/>
       <c r="C140" s="72"/>
       <c r="D140" s="70"/>
-      <c r="E140" s="117"/>
-      <c r="F140" s="117"/>
-      <c r="G140" s="118"/>
-      <c r="H140" s="96"/>
-      <c r="I140" s="102"/>
+      <c r="E140" s="110"/>
+      <c r="F140" s="110"/>
+      <c r="G140" s="111"/>
+      <c r="H140" s="99"/>
+      <c r="I140" s="135"/>
       <c r="J140" s="62"/>
       <c r="K140" s="20"/>
       <c r="L140" s="20"/>
@@ -19948,8 +19958,8 @@
       <c r="BG140" s="20"/>
       <c r="BH140" s="20"/>
       <c r="BI140" s="20"/>
-      <c r="BJ140" s="20"/>
-      <c r="BK140" s="20"/>
+      <c r="BJ140" s="64"/>
+      <c r="BK140" s="64"/>
       <c r="BL140" s="21"/>
       <c r="BM140" s="21"/>
       <c r="BN140" s="20"/>
@@ -20012,13 +20022,13 @@
       <c r="A141" s="16"/>
       <c r="B141" s="36"/>
       <c r="C141" s="82"/>
-      <c r="D141" s="94" t="s">
+      <c r="D141" s="95" t="s">
         <v>80</v>
       </c>
-      <c r="E141" s="94"/>
-      <c r="F141" s="94"/>
-      <c r="G141" s="94"/>
-      <c r="H141" s="95">
+      <c r="E141" s="95"/>
+      <c r="F141" s="95"/>
+      <c r="G141" s="95"/>
+      <c r="H141" s="103">
         <v>45637</v>
       </c>
       <c r="I141" s="92"/>
@@ -20074,8 +20084,8 @@
       <c r="BG141" s="20"/>
       <c r="BH141" s="20"/>
       <c r="BI141" s="20"/>
-      <c r="BJ141" s="20"/>
-      <c r="BK141" s="20"/>
+      <c r="BJ141" s="64"/>
+      <c r="BK141" s="64"/>
       <c r="BL141" s="21"/>
       <c r="BM141" s="21"/>
       <c r="BN141" s="20"/>
@@ -20138,11 +20148,11 @@
       <c r="A142" s="16"/>
       <c r="B142" s="36"/>
       <c r="C142" s="82"/>
-      <c r="D142" s="94"/>
-      <c r="E142" s="94"/>
-      <c r="F142" s="94"/>
-      <c r="G142" s="94"/>
-      <c r="H142" s="96"/>
+      <c r="D142" s="95"/>
+      <c r="E142" s="95"/>
+      <c r="F142" s="95"/>
+      <c r="G142" s="95"/>
+      <c r="H142" s="99"/>
       <c r="I142" s="92"/>
       <c r="J142" s="62"/>
       <c r="K142" s="20"/>
@@ -20196,8 +20206,8 @@
       <c r="BG142" s="20"/>
       <c r="BH142" s="20"/>
       <c r="BI142" s="20"/>
-      <c r="BJ142" s="20"/>
-      <c r="BK142" s="20"/>
+      <c r="BJ142" s="64"/>
+      <c r="BK142" s="64"/>
       <c r="BL142" s="21"/>
       <c r="BM142" s="21"/>
       <c r="BN142" s="20"/>
@@ -20260,14 +20270,14 @@
       <c r="A143" s="16"/>
       <c r="B143" s="36"/>
       <c r="C143" s="72"/>
-      <c r="D143" s="119" t="s">
+      <c r="D143" s="187" t="s">
         <v>66</v>
       </c>
-      <c r="E143" s="120"/>
-      <c r="F143" s="120"/>
-      <c r="G143" s="121"/>
-      <c r="H143" s="105"/>
-      <c r="I143" s="99"/>
+      <c r="E143" s="188"/>
+      <c r="F143" s="188"/>
+      <c r="G143" s="189"/>
+      <c r="H143" s="185"/>
+      <c r="I143" s="115"/>
       <c r="J143" s="66"/>
       <c r="K143" s="64"/>
       <c r="L143" s="64"/>
@@ -20384,12 +20394,12 @@
       <c r="A144" s="16"/>
       <c r="B144" s="36"/>
       <c r="C144" s="72"/>
-      <c r="D144" s="110"/>
-      <c r="E144" s="111"/>
-      <c r="F144" s="111"/>
-      <c r="G144" s="112"/>
-      <c r="H144" s="106"/>
-      <c r="I144" s="100"/>
+      <c r="D144" s="127"/>
+      <c r="E144" s="128"/>
+      <c r="F144" s="128"/>
+      <c r="G144" s="129"/>
+      <c r="H144" s="186"/>
+      <c r="I144" s="116"/>
       <c r="J144" s="66"/>
       <c r="K144" s="64"/>
       <c r="L144" s="64"/>
@@ -20507,15 +20517,15 @@
       <c r="B145" s="36"/>
       <c r="C145" s="72"/>
       <c r="D145" s="74"/>
-      <c r="E145" s="113" t="s">
+      <c r="E145" s="107" t="s">
         <v>68</v>
       </c>
-      <c r="F145" s="113"/>
-      <c r="G145" s="114"/>
-      <c r="H145" s="95">
+      <c r="F145" s="107"/>
+      <c r="G145" s="108"/>
+      <c r="H145" s="103">
         <v>45639</v>
       </c>
-      <c r="I145" s="101"/>
+      <c r="I145" s="105"/>
       <c r="J145" s="62"/>
       <c r="K145" s="20"/>
       <c r="L145" s="20"/>
@@ -20568,8 +20578,8 @@
       <c r="BG145" s="20"/>
       <c r="BH145" s="20"/>
       <c r="BI145" s="20"/>
-      <c r="BJ145" s="20"/>
-      <c r="BK145" s="20"/>
+      <c r="BJ145" s="64"/>
+      <c r="BK145" s="64"/>
       <c r="BL145" s="21"/>
       <c r="BM145" s="21"/>
       <c r="BN145" s="20"/>
@@ -20633,11 +20643,11 @@
       <c r="B146" s="36"/>
       <c r="C146" s="72"/>
       <c r="D146" s="70"/>
-      <c r="E146" s="115"/>
-      <c r="F146" s="115"/>
-      <c r="G146" s="116"/>
-      <c r="H146" s="96"/>
-      <c r="I146" s="102"/>
+      <c r="E146" s="177"/>
+      <c r="F146" s="177"/>
+      <c r="G146" s="178"/>
+      <c r="H146" s="99"/>
+      <c r="I146" s="135"/>
       <c r="J146" s="62"/>
       <c r="K146" s="20"/>
       <c r="L146" s="20"/>
@@ -20690,8 +20700,8 @@
       <c r="BG146" s="20"/>
       <c r="BH146" s="20"/>
       <c r="BI146" s="20"/>
-      <c r="BJ146" s="20"/>
-      <c r="BK146" s="20"/>
+      <c r="BJ146" s="64"/>
+      <c r="BK146" s="64"/>
       <c r="BL146" s="21"/>
       <c r="BM146" s="21"/>
       <c r="BN146" s="20"/>
@@ -20755,15 +20765,15 @@
       <c r="B147" s="36"/>
       <c r="C147" s="72"/>
       <c r="D147" s="70"/>
-      <c r="E147" s="113" t="s">
+      <c r="E147" s="107" t="s">
         <v>69</v>
       </c>
-      <c r="F147" s="113"/>
-      <c r="G147" s="114"/>
-      <c r="H147" s="95">
+      <c r="F147" s="107"/>
+      <c r="G147" s="108"/>
+      <c r="H147" s="103">
         <v>45642</v>
       </c>
-      <c r="I147" s="101"/>
+      <c r="I147" s="105"/>
       <c r="J147" s="62"/>
       <c r="K147" s="20"/>
       <c r="L147" s="20"/>
@@ -20816,8 +20826,8 @@
       <c r="BG147" s="20"/>
       <c r="BH147" s="20"/>
       <c r="BI147" s="20"/>
-      <c r="BJ147" s="20"/>
-      <c r="BK147" s="20"/>
+      <c r="BJ147" s="64"/>
+      <c r="BK147" s="64"/>
       <c r="BL147" s="21"/>
       <c r="BM147" s="21"/>
       <c r="BN147" s="20"/>
@@ -20881,11 +20891,11 @@
       <c r="B148" s="36"/>
       <c r="C148" s="72"/>
       <c r="D148" s="70"/>
-      <c r="E148" s="115"/>
-      <c r="F148" s="115"/>
-      <c r="G148" s="116"/>
-      <c r="H148" s="96"/>
-      <c r="I148" s="102"/>
+      <c r="E148" s="177"/>
+      <c r="F148" s="177"/>
+      <c r="G148" s="178"/>
+      <c r="H148" s="99"/>
+      <c r="I148" s="135"/>
       <c r="J148" s="62"/>
       <c r="K148" s="20"/>
       <c r="L148" s="20"/>
@@ -20938,8 +20948,8 @@
       <c r="BG148" s="20"/>
       <c r="BH148" s="20"/>
       <c r="BI148" s="20"/>
-      <c r="BJ148" s="20"/>
-      <c r="BK148" s="20"/>
+      <c r="BJ148" s="64"/>
+      <c r="BK148" s="64"/>
       <c r="BL148" s="21"/>
       <c r="BM148" s="21"/>
       <c r="BN148" s="20"/>
@@ -21003,15 +21013,15 @@
       <c r="B149" s="36"/>
       <c r="C149" s="72"/>
       <c r="D149" s="70"/>
-      <c r="E149" s="113" t="s">
+      <c r="E149" s="107" t="s">
         <v>70</v>
       </c>
-      <c r="F149" s="113"/>
-      <c r="G149" s="114"/>
-      <c r="H149" s="95">
+      <c r="F149" s="107"/>
+      <c r="G149" s="108"/>
+      <c r="H149" s="103">
         <v>45643</v>
       </c>
-      <c r="I149" s="101"/>
+      <c r="I149" s="105"/>
       <c r="J149" s="62"/>
       <c r="K149" s="20"/>
       <c r="L149" s="20"/>
@@ -21064,8 +21074,8 @@
       <c r="BG149" s="20"/>
       <c r="BH149" s="20"/>
       <c r="BI149" s="20"/>
-      <c r="BJ149" s="20"/>
-      <c r="BK149" s="20"/>
+      <c r="BJ149" s="64"/>
+      <c r="BK149" s="64"/>
       <c r="BL149" s="21"/>
       <c r="BM149" s="21"/>
       <c r="BN149" s="20"/>
@@ -21129,11 +21139,11 @@
       <c r="B150" s="36"/>
       <c r="C150" s="72"/>
       <c r="D150" s="70"/>
-      <c r="E150" s="115"/>
-      <c r="F150" s="115"/>
-      <c r="G150" s="116"/>
-      <c r="H150" s="96"/>
-      <c r="I150" s="102"/>
+      <c r="E150" s="177"/>
+      <c r="F150" s="177"/>
+      <c r="G150" s="178"/>
+      <c r="H150" s="99"/>
+      <c r="I150" s="135"/>
       <c r="J150" s="62"/>
       <c r="K150" s="20"/>
       <c r="L150" s="20"/>
@@ -21186,8 +21196,8 @@
       <c r="BG150" s="20"/>
       <c r="BH150" s="20"/>
       <c r="BI150" s="20"/>
-      <c r="BJ150" s="20"/>
-      <c r="BK150" s="20"/>
+      <c r="BJ150" s="64"/>
+      <c r="BK150" s="64"/>
       <c r="BL150" s="21"/>
       <c r="BM150" s="21"/>
       <c r="BN150" s="20"/>
@@ -21251,15 +21261,15 @@
       <c r="B151" s="36"/>
       <c r="C151" s="72"/>
       <c r="D151" s="70"/>
-      <c r="E151" s="94" t="s">
+      <c r="E151" s="95" t="s">
         <v>75</v>
       </c>
-      <c r="F151" s="94"/>
-      <c r="G151" s="94"/>
-      <c r="H151" s="95">
+      <c r="F151" s="95"/>
+      <c r="G151" s="95"/>
+      <c r="H151" s="103">
         <v>45644</v>
       </c>
-      <c r="I151" s="101"/>
+      <c r="I151" s="105"/>
       <c r="J151" s="62"/>
       <c r="K151" s="20"/>
       <c r="L151" s="20"/>
@@ -21312,8 +21322,8 @@
       <c r="BG151" s="20"/>
       <c r="BH151" s="20"/>
       <c r="BI151" s="20"/>
-      <c r="BJ151" s="20"/>
-      <c r="BK151" s="20"/>
+      <c r="BJ151" s="64"/>
+      <c r="BK151" s="64"/>
       <c r="BL151" s="21"/>
       <c r="BM151" s="21"/>
       <c r="BN151" s="20"/>
@@ -21377,11 +21387,11 @@
       <c r="B152" s="36"/>
       <c r="C152" s="72"/>
       <c r="D152" s="70"/>
-      <c r="E152" s="94"/>
-      <c r="F152" s="94"/>
-      <c r="G152" s="94"/>
-      <c r="H152" s="96"/>
-      <c r="I152" s="102"/>
+      <c r="E152" s="95"/>
+      <c r="F152" s="95"/>
+      <c r="G152" s="95"/>
+      <c r="H152" s="99"/>
+      <c r="I152" s="135"/>
       <c r="J152" s="62"/>
       <c r="K152" s="20"/>
       <c r="L152" s="20"/>
@@ -21434,8 +21444,8 @@
       <c r="BG152" s="20"/>
       <c r="BH152" s="20"/>
       <c r="BI152" s="20"/>
-      <c r="BJ152" s="20"/>
-      <c r="BK152" s="20"/>
+      <c r="BJ152" s="64"/>
+      <c r="BK152" s="64"/>
       <c r="BL152" s="21"/>
       <c r="BM152" s="21"/>
       <c r="BN152" s="20"/>
@@ -21499,15 +21509,15 @@
       <c r="B153" s="36"/>
       <c r="C153" s="72"/>
       <c r="D153" s="70"/>
-      <c r="E153" s="94" t="s">
+      <c r="E153" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="F153" s="94"/>
-      <c r="G153" s="94"/>
-      <c r="H153" s="95">
+      <c r="F153" s="95"/>
+      <c r="G153" s="95"/>
+      <c r="H153" s="103">
         <v>45644</v>
       </c>
-      <c r="I153" s="101"/>
+      <c r="I153" s="105"/>
       <c r="J153" s="62"/>
       <c r="K153" s="20"/>
       <c r="L153" s="20"/>
@@ -21560,8 +21570,8 @@
       <c r="BG153" s="20"/>
       <c r="BH153" s="20"/>
       <c r="BI153" s="20"/>
-      <c r="BJ153" s="20"/>
-      <c r="BK153" s="20"/>
+      <c r="BJ153" s="64"/>
+      <c r="BK153" s="64"/>
       <c r="BL153" s="21"/>
       <c r="BM153" s="21"/>
       <c r="BN153" s="20"/>
@@ -21625,11 +21635,11 @@
       <c r="B154" s="36"/>
       <c r="C154" s="72"/>
       <c r="D154" s="70"/>
-      <c r="E154" s="94"/>
-      <c r="F154" s="94"/>
-      <c r="G154" s="94"/>
-      <c r="H154" s="96"/>
-      <c r="I154" s="102"/>
+      <c r="E154" s="95"/>
+      <c r="F154" s="95"/>
+      <c r="G154" s="95"/>
+      <c r="H154" s="99"/>
+      <c r="I154" s="135"/>
       <c r="J154" s="62"/>
       <c r="K154" s="20"/>
       <c r="L154" s="20"/>
@@ -21682,8 +21692,8 @@
       <c r="BG154" s="20"/>
       <c r="BH154" s="20"/>
       <c r="BI154" s="20"/>
-      <c r="BJ154" s="20"/>
-      <c r="BK154" s="20"/>
+      <c r="BJ154" s="64"/>
+      <c r="BK154" s="64"/>
       <c r="BL154" s="21"/>
       <c r="BM154" s="21"/>
       <c r="BN154" s="20"/>
@@ -21746,16 +21756,16 @@
       <c r="A155" s="1"/>
       <c r="B155" s="18"/>
       <c r="C155" s="60"/>
-      <c r="D155" s="186"/>
-      <c r="E155" s="185" t="s">
+      <c r="D155" s="96"/>
+      <c r="E155" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="F155" s="94"/>
-      <c r="G155" s="94"/>
-      <c r="H155" s="187">
+      <c r="F155" s="95"/>
+      <c r="G155" s="95"/>
+      <c r="H155" s="98">
         <v>45645</v>
       </c>
-      <c r="I155" s="188"/>
+      <c r="I155" s="100"/>
       <c r="J155" s="19"/>
       <c r="K155" s="20"/>
       <c r="L155" s="20"/>
@@ -21808,8 +21818,8 @@
       <c r="BG155" s="20"/>
       <c r="BH155" s="20"/>
       <c r="BI155" s="20"/>
-      <c r="BJ155" s="20"/>
-      <c r="BK155" s="20"/>
+      <c r="BJ155" s="64"/>
+      <c r="BK155" s="64"/>
       <c r="BL155" s="21"/>
       <c r="BM155" s="21"/>
       <c r="BN155" s="20"/>
@@ -21872,12 +21882,12 @@
       <c r="A156" s="1"/>
       <c r="B156" s="18"/>
       <c r="C156" s="60"/>
-      <c r="D156" s="141"/>
-      <c r="E156" s="185"/>
-      <c r="F156" s="94"/>
-      <c r="G156" s="94"/>
-      <c r="H156" s="96"/>
-      <c r="I156" s="98"/>
+      <c r="D156" s="97"/>
+      <c r="E156" s="94"/>
+      <c r="F156" s="95"/>
+      <c r="G156" s="95"/>
+      <c r="H156" s="99"/>
+      <c r="I156" s="101"/>
       <c r="J156" s="19"/>
       <c r="K156" s="20"/>
       <c r="L156" s="20"/>
@@ -21930,8 +21940,8 @@
       <c r="BG156" s="20"/>
       <c r="BH156" s="20"/>
       <c r="BI156" s="20"/>
-      <c r="BJ156" s="20"/>
-      <c r="BK156" s="20"/>
+      <c r="BJ156" s="64"/>
+      <c r="BK156" s="64"/>
       <c r="BL156" s="21"/>
       <c r="BM156" s="21"/>
       <c r="BN156" s="20"/>
@@ -21994,16 +22004,16 @@
       <c r="A157" s="1"/>
       <c r="B157" s="93"/>
       <c r="C157" s="90"/>
-      <c r="D157" s="94" t="s">
+      <c r="D157" s="95" t="s">
         <v>81</v>
       </c>
-      <c r="E157" s="94"/>
-      <c r="F157" s="94"/>
-      <c r="G157" s="94"/>
-      <c r="H157" s="95">
+      <c r="E157" s="95"/>
+      <c r="F157" s="95"/>
+      <c r="G157" s="95"/>
+      <c r="H157" s="103">
         <v>45644</v>
       </c>
-      <c r="I157" s="97"/>
+      <c r="I157" s="118"/>
       <c r="J157" s="19"/>
       <c r="K157" s="20"/>
       <c r="L157" s="20"/>
@@ -22056,8 +22066,8 @@
       <c r="BG157" s="20"/>
       <c r="BH157" s="20"/>
       <c r="BI157" s="20"/>
-      <c r="BJ157" s="20"/>
-      <c r="BK157" s="20"/>
+      <c r="BJ157" s="64"/>
+      <c r="BK157" s="64"/>
       <c r="BL157" s="21"/>
       <c r="BM157" s="21"/>
       <c r="BN157" s="20"/>
@@ -22120,12 +22130,12 @@
       <c r="A158" s="1"/>
       <c r="B158" s="93"/>
       <c r="C158" s="90"/>
-      <c r="D158" s="94"/>
-      <c r="E158" s="94"/>
-      <c r="F158" s="94"/>
-      <c r="G158" s="94"/>
-      <c r="H158" s="96"/>
-      <c r="I158" s="98"/>
+      <c r="D158" s="95"/>
+      <c r="E158" s="95"/>
+      <c r="F158" s="95"/>
+      <c r="G158" s="95"/>
+      <c r="H158" s="99"/>
+      <c r="I158" s="101"/>
       <c r="J158" s="19"/>
       <c r="K158" s="20"/>
       <c r="L158" s="20"/>
@@ -22178,8 +22188,8 @@
       <c r="BG158" s="20"/>
       <c r="BH158" s="20"/>
       <c r="BI158" s="20"/>
-      <c r="BJ158" s="20"/>
-      <c r="BK158" s="20"/>
+      <c r="BJ158" s="64"/>
+      <c r="BK158" s="64"/>
       <c r="BL158" s="21"/>
       <c r="BM158" s="21"/>
       <c r="BN158" s="20"/>
@@ -22243,14 +22253,14 @@
       <c r="B159" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="C159" s="165" t="s">
+      <c r="C159" s="143" t="s">
         <v>31</v>
       </c>
-      <c r="D159" s="166"/>
-      <c r="E159" s="166"/>
-      <c r="F159" s="166"/>
-      <c r="G159" s="167"/>
-      <c r="H159" s="176" t="s">
+      <c r="D159" s="144"/>
+      <c r="E159" s="144"/>
+      <c r="F159" s="144"/>
+      <c r="G159" s="145"/>
+      <c r="H159" s="130" t="s">
         <v>57</v>
       </c>
       <c r="I159" s="104"/>
@@ -22306,8 +22316,8 @@
       <c r="BG159" s="15"/>
       <c r="BH159" s="15"/>
       <c r="BI159" s="15"/>
-      <c r="BJ159" s="15"/>
-      <c r="BK159" s="15"/>
+      <c r="BJ159" s="193"/>
+      <c r="BK159" s="193"/>
       <c r="BL159" s="15"/>
       <c r="BM159" s="15"/>
       <c r="BN159" s="15"/>
@@ -22369,11 +22379,11 @@
     <row r="160" spans="1:120" ht="9.75" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="87"/>
-      <c r="C160" s="168"/>
-      <c r="D160" s="169"/>
-      <c r="E160" s="169"/>
-      <c r="F160" s="169"/>
-      <c r="G160" s="170"/>
+      <c r="C160" s="146"/>
+      <c r="D160" s="147"/>
+      <c r="E160" s="147"/>
+      <c r="F160" s="147"/>
+      <c r="G160" s="148"/>
       <c r="H160" s="104"/>
       <c r="I160" s="104"/>
       <c r="J160" s="14"/>
@@ -22428,8 +22438,8 @@
       <c r="BG160" s="15"/>
       <c r="BH160" s="15"/>
       <c r="BI160" s="15"/>
-      <c r="BJ160" s="15"/>
-      <c r="BK160" s="15"/>
+      <c r="BJ160" s="193"/>
+      <c r="BK160" s="193"/>
       <c r="BL160" s="15"/>
       <c r="BM160" s="15"/>
       <c r="BN160" s="15"/>
@@ -22550,8 +22560,8 @@
       <c r="BG161" s="13"/>
       <c r="BH161" s="13"/>
       <c r="BI161" s="13"/>
-      <c r="BJ161" s="13"/>
-      <c r="BK161" s="13"/>
+      <c r="BJ161" s="192"/>
+      <c r="BK161" s="192"/>
       <c r="BL161" s="13"/>
       <c r="BM161" s="13"/>
       <c r="BN161" s="13"/>
@@ -22672,8 +22682,8 @@
       <c r="BG162" s="15"/>
       <c r="BH162" s="15"/>
       <c r="BI162" s="15"/>
-      <c r="BJ162" s="15"/>
-      <c r="BK162" s="15"/>
+      <c r="BJ162" s="193"/>
+      <c r="BK162" s="193"/>
       <c r="BL162" s="15"/>
       <c r="BM162" s="15"/>
       <c r="BN162" s="15"/>
@@ -22735,14 +22745,14 @@
     <row r="163" spans="1:120" ht="9.75" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
-      <c r="C163" s="160" t="s">
+      <c r="C163" s="137" t="s">
         <v>33</v>
       </c>
-      <c r="D163" s="132"/>
-      <c r="E163" s="132"/>
-      <c r="F163" s="132"/>
-      <c r="G163" s="161"/>
-      <c r="H163" s="176" t="s">
+      <c r="D163" s="138"/>
+      <c r="E163" s="138"/>
+      <c r="F163" s="138"/>
+      <c r="G163" s="139"/>
+      <c r="H163" s="130" t="s">
         <v>56</v>
       </c>
       <c r="I163" s="104"/>
@@ -22798,8 +22808,8 @@
       <c r="BG163" s="20"/>
       <c r="BH163" s="20"/>
       <c r="BI163" s="20"/>
-      <c r="BJ163" s="20"/>
-      <c r="BK163" s="20"/>
+      <c r="BJ163" s="64"/>
+      <c r="BK163" s="64"/>
       <c r="BL163" s="21"/>
       <c r="BM163" s="21"/>
       <c r="BN163" s="20"/>
@@ -22861,11 +22871,11 @@
     <row r="164" spans="1:120" ht="9.75" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
-      <c r="C164" s="162"/>
-      <c r="D164" s="163"/>
-      <c r="E164" s="163"/>
-      <c r="F164" s="163"/>
-      <c r="G164" s="164"/>
+      <c r="C164" s="140"/>
+      <c r="D164" s="141"/>
+      <c r="E164" s="141"/>
+      <c r="F164" s="141"/>
+      <c r="G164" s="142"/>
       <c r="H164" s="104"/>
       <c r="I164" s="104"/>
       <c r="J164" s="19"/>
@@ -22920,8 +22930,8 @@
       <c r="BG164" s="20"/>
       <c r="BH164" s="20"/>
       <c r="BI164" s="20"/>
-      <c r="BJ164" s="20"/>
-      <c r="BK164" s="20"/>
+      <c r="BJ164" s="64"/>
+      <c r="BK164" s="64"/>
       <c r="BL164" s="21"/>
       <c r="BM164" s="21"/>
       <c r="BN164" s="20"/>
@@ -23042,8 +23052,8 @@
       <c r="BG165" s="2"/>
       <c r="BH165" s="2"/>
       <c r="BI165" s="2"/>
-      <c r="BJ165" s="2"/>
-      <c r="BK165" s="2"/>
+      <c r="BJ165" s="191"/>
+      <c r="BK165" s="191"/>
       <c r="BL165" s="2"/>
       <c r="BM165" s="2"/>
       <c r="BN165" s="2"/>
@@ -23164,8 +23174,8 @@
       <c r="BG166" s="2"/>
       <c r="BH166" s="2"/>
       <c r="BI166" s="2"/>
-      <c r="BJ166" s="2"/>
-      <c r="BK166" s="2"/>
+      <c r="BJ166" s="191"/>
+      <c r="BK166" s="191"/>
       <c r="BL166" s="2"/>
       <c r="BM166" s="2"/>
       <c r="BN166" s="2"/>
@@ -23286,8 +23296,8 @@
       <c r="BG167" s="2"/>
       <c r="BH167" s="2"/>
       <c r="BI167" s="2"/>
-      <c r="BJ167" s="2"/>
-      <c r="BK167" s="2"/>
+      <c r="BJ167" s="191"/>
+      <c r="BK167" s="191"/>
       <c r="BL167" s="2"/>
       <c r="BM167" s="2"/>
       <c r="BN167" s="2"/>
@@ -23408,8 +23418,8 @@
       <c r="BG168" s="2"/>
       <c r="BH168" s="2"/>
       <c r="BI168" s="2"/>
-      <c r="BJ168" s="2"/>
-      <c r="BK168" s="2"/>
+      <c r="BJ168" s="191"/>
+      <c r="BK168" s="191"/>
       <c r="BL168" s="2"/>
       <c r="BM168" s="2"/>
       <c r="BN168" s="2"/>
@@ -23530,8 +23540,8 @@
       <c r="BG169" s="2"/>
       <c r="BH169" s="2"/>
       <c r="BI169" s="2"/>
-      <c r="BJ169" s="2"/>
-      <c r="BK169" s="2"/>
+      <c r="BJ169" s="191"/>
+      <c r="BK169" s="191"/>
       <c r="BL169" s="2"/>
       <c r="BM169" s="2"/>
       <c r="BN169" s="2"/>
@@ -23652,8 +23662,8 @@
       <c r="BG170" s="2"/>
       <c r="BH170" s="2"/>
       <c r="BI170" s="2"/>
-      <c r="BJ170" s="2"/>
-      <c r="BK170" s="2"/>
+      <c r="BJ170" s="191"/>
+      <c r="BK170" s="191"/>
       <c r="BL170" s="2"/>
       <c r="BM170" s="2"/>
       <c r="BN170" s="2"/>
@@ -23774,8 +23784,8 @@
       <c r="BG171" s="2"/>
       <c r="BH171" s="2"/>
       <c r="BI171" s="2"/>
-      <c r="BJ171" s="2"/>
-      <c r="BK171" s="2"/>
+      <c r="BJ171" s="191"/>
+      <c r="BK171" s="191"/>
       <c r="BL171" s="2"/>
       <c r="BM171" s="2"/>
       <c r="BN171" s="2"/>
@@ -23896,8 +23906,8 @@
       <c r="BG172" s="2"/>
       <c r="BH172" s="2"/>
       <c r="BI172" s="2"/>
-      <c r="BJ172" s="2"/>
-      <c r="BK172" s="2"/>
+      <c r="BJ172" s="191"/>
+      <c r="BK172" s="191"/>
       <c r="BL172" s="2"/>
       <c r="BM172" s="2"/>
       <c r="BN172" s="2"/>
@@ -24018,8 +24028,8 @@
       <c r="BG173" s="2"/>
       <c r="BH173" s="2"/>
       <c r="BI173" s="2"/>
-      <c r="BJ173" s="2"/>
-      <c r="BK173" s="2"/>
+      <c r="BJ173" s="191"/>
+      <c r="BK173" s="191"/>
       <c r="BL173" s="2"/>
       <c r="BM173" s="2"/>
       <c r="BN173" s="2"/>
@@ -24140,8 +24150,8 @@
       <c r="BG174" s="2"/>
       <c r="BH174" s="2"/>
       <c r="BI174" s="2"/>
-      <c r="BJ174" s="2"/>
-      <c r="BK174" s="2"/>
+      <c r="BJ174" s="191"/>
+      <c r="BK174" s="191"/>
       <c r="BL174" s="2"/>
       <c r="BM174" s="2"/>
       <c r="BN174" s="2"/>
@@ -24262,8 +24272,8 @@
       <c r="BG175" s="2"/>
       <c r="BH175" s="2"/>
       <c r="BI175" s="2"/>
-      <c r="BJ175" s="2"/>
-      <c r="BK175" s="2"/>
+      <c r="BJ175" s="191"/>
+      <c r="BK175" s="191"/>
       <c r="BL175" s="2"/>
       <c r="BM175" s="2"/>
       <c r="BN175" s="2"/>
@@ -24384,8 +24394,8 @@
       <c r="BG176" s="2"/>
       <c r="BH176" s="2"/>
       <c r="BI176" s="2"/>
-      <c r="BJ176" s="2"/>
-      <c r="BK176" s="2"/>
+      <c r="BJ176" s="191"/>
+      <c r="BK176" s="191"/>
       <c r="BL176" s="2"/>
       <c r="BM176" s="2"/>
       <c r="BN176" s="2"/>
@@ -24506,8 +24516,8 @@
       <c r="BG177" s="2"/>
       <c r="BH177" s="2"/>
       <c r="BI177" s="2"/>
-      <c r="BJ177" s="2"/>
-      <c r="BK177" s="2"/>
+      <c r="BJ177" s="191"/>
+      <c r="BK177" s="191"/>
       <c r="BL177" s="2"/>
       <c r="BM177" s="2"/>
       <c r="BN177" s="2"/>
@@ -24628,8 +24638,8 @@
       <c r="BG178" s="2"/>
       <c r="BH178" s="2"/>
       <c r="BI178" s="2"/>
-      <c r="BJ178" s="2"/>
-      <c r="BK178" s="2"/>
+      <c r="BJ178" s="191"/>
+      <c r="BK178" s="191"/>
       <c r="BL178" s="2"/>
       <c r="BM178" s="2"/>
       <c r="BN178" s="2"/>
@@ -24750,8 +24760,8 @@
       <c r="BG179" s="2"/>
       <c r="BH179" s="2"/>
       <c r="BI179" s="2"/>
-      <c r="BJ179" s="2"/>
-      <c r="BK179" s="2"/>
+      <c r="BJ179" s="191"/>
+      <c r="BK179" s="191"/>
       <c r="BL179" s="2"/>
       <c r="BM179" s="2"/>
       <c r="BN179" s="2"/>
@@ -24872,8 +24882,8 @@
       <c r="BG180" s="2"/>
       <c r="BH180" s="2"/>
       <c r="BI180" s="2"/>
-      <c r="BJ180" s="2"/>
-      <c r="BK180" s="2"/>
+      <c r="BJ180" s="191"/>
+      <c r="BK180" s="191"/>
       <c r="BL180" s="2"/>
       <c r="BM180" s="2"/>
       <c r="BN180" s="2"/>
@@ -24994,8 +25004,8 @@
       <c r="BG181" s="2"/>
       <c r="BH181" s="2"/>
       <c r="BI181" s="2"/>
-      <c r="BJ181" s="2"/>
-      <c r="BK181" s="2"/>
+      <c r="BJ181" s="191"/>
+      <c r="BK181" s="191"/>
       <c r="BL181" s="2"/>
       <c r="BM181" s="2"/>
       <c r="BN181" s="2"/>
@@ -25116,8 +25126,8 @@
       <c r="BG182" s="2"/>
       <c r="BH182" s="2"/>
       <c r="BI182" s="2"/>
-      <c r="BJ182" s="2"/>
-      <c r="BK182" s="2"/>
+      <c r="BJ182" s="191"/>
+      <c r="BK182" s="191"/>
       <c r="BL182" s="2"/>
       <c r="BM182" s="2"/>
       <c r="BN182" s="2"/>
@@ -25238,8 +25248,8 @@
       <c r="BG183" s="2"/>
       <c r="BH183" s="2"/>
       <c r="BI183" s="2"/>
-      <c r="BJ183" s="2"/>
-      <c r="BK183" s="2"/>
+      <c r="BJ183" s="191"/>
+      <c r="BK183" s="191"/>
       <c r="BL183" s="2"/>
       <c r="BM183" s="2"/>
       <c r="BN183" s="2"/>
@@ -25360,8 +25370,8 @@
       <c r="BG184" s="2"/>
       <c r="BH184" s="2"/>
       <c r="BI184" s="2"/>
-      <c r="BJ184" s="2"/>
-      <c r="BK184" s="2"/>
+      <c r="BJ184" s="191"/>
+      <c r="BK184" s="191"/>
       <c r="BL184" s="2"/>
       <c r="BM184" s="2"/>
       <c r="BN184" s="2"/>
@@ -25482,8 +25492,8 @@
       <c r="BG185" s="2"/>
       <c r="BH185" s="2"/>
       <c r="BI185" s="2"/>
-      <c r="BJ185" s="2"/>
-      <c r="BK185" s="2"/>
+      <c r="BJ185" s="191"/>
+      <c r="BK185" s="191"/>
       <c r="BL185" s="2"/>
       <c r="BM185" s="2"/>
       <c r="BN185" s="2"/>
@@ -25604,8 +25614,8 @@
       <c r="BG186" s="2"/>
       <c r="BH186" s="2"/>
       <c r="BI186" s="2"/>
-      <c r="BJ186" s="2"/>
-      <c r="BK186" s="2"/>
+      <c r="BJ186" s="191"/>
+      <c r="BK186" s="191"/>
       <c r="BL186" s="2"/>
       <c r="BM186" s="2"/>
       <c r="BN186" s="2"/>
@@ -25726,8 +25736,8 @@
       <c r="BG187" s="2"/>
       <c r="BH187" s="2"/>
       <c r="BI187" s="2"/>
-      <c r="BJ187" s="2"/>
-      <c r="BK187" s="2"/>
+      <c r="BJ187" s="191"/>
+      <c r="BK187" s="191"/>
       <c r="BL187" s="2"/>
       <c r="BM187" s="2"/>
       <c r="BN187" s="2"/>
@@ -25848,8 +25858,8 @@
       <c r="BG188" s="2"/>
       <c r="BH188" s="2"/>
       <c r="BI188" s="2"/>
-      <c r="BJ188" s="2"/>
-      <c r="BK188" s="2"/>
+      <c r="BJ188" s="191"/>
+      <c r="BK188" s="191"/>
       <c r="BL188" s="2"/>
       <c r="BM188" s="2"/>
       <c r="BN188" s="2"/>
@@ -25970,8 +25980,8 @@
       <c r="BG189" s="2"/>
       <c r="BH189" s="2"/>
       <c r="BI189" s="2"/>
-      <c r="BJ189" s="2"/>
-      <c r="BK189" s="2"/>
+      <c r="BJ189" s="191"/>
+      <c r="BK189" s="191"/>
       <c r="BL189" s="2"/>
       <c r="BM189" s="2"/>
       <c r="BN189" s="2"/>
@@ -26092,8 +26102,8 @@
       <c r="BG190" s="2"/>
       <c r="BH190" s="2"/>
       <c r="BI190" s="2"/>
-      <c r="BJ190" s="2"/>
-      <c r="BK190" s="2"/>
+      <c r="BJ190" s="191"/>
+      <c r="BK190" s="191"/>
       <c r="BL190" s="2"/>
       <c r="BM190" s="2"/>
       <c r="BN190" s="2"/>
@@ -26214,8 +26224,8 @@
       <c r="BG191" s="2"/>
       <c r="BH191" s="2"/>
       <c r="BI191" s="2"/>
-      <c r="BJ191" s="2"/>
-      <c r="BK191" s="2"/>
+      <c r="BJ191" s="191"/>
+      <c r="BK191" s="191"/>
       <c r="BL191" s="2"/>
       <c r="BM191" s="2"/>
       <c r="BN191" s="2"/>
@@ -26336,8 +26346,8 @@
       <c r="BG192" s="2"/>
       <c r="BH192" s="2"/>
       <c r="BI192" s="2"/>
-      <c r="BJ192" s="2"/>
-      <c r="BK192" s="2"/>
+      <c r="BJ192" s="191"/>
+      <c r="BK192" s="191"/>
       <c r="BL192" s="2"/>
       <c r="BM192" s="2"/>
       <c r="BN192" s="2"/>
@@ -26458,8 +26468,8 @@
       <c r="BG193" s="2"/>
       <c r="BH193" s="2"/>
       <c r="BI193" s="2"/>
-      <c r="BJ193" s="2"/>
-      <c r="BK193" s="2"/>
+      <c r="BJ193" s="191"/>
+      <c r="BK193" s="191"/>
       <c r="BL193" s="2"/>
       <c r="BM193" s="2"/>
       <c r="BN193" s="2"/>
@@ -26580,8 +26590,8 @@
       <c r="BG194" s="2"/>
       <c r="BH194" s="2"/>
       <c r="BI194" s="2"/>
-      <c r="BJ194" s="2"/>
-      <c r="BK194" s="2"/>
+      <c r="BJ194" s="191"/>
+      <c r="BK194" s="191"/>
       <c r="BL194" s="2"/>
       <c r="BM194" s="2"/>
       <c r="BN194" s="2"/>
@@ -26702,8 +26712,8 @@
       <c r="BG195" s="2"/>
       <c r="BH195" s="2"/>
       <c r="BI195" s="2"/>
-      <c r="BJ195" s="2"/>
-      <c r="BK195" s="2"/>
+      <c r="BJ195" s="191"/>
+      <c r="BK195" s="191"/>
       <c r="BL195" s="2"/>
       <c r="BM195" s="2"/>
       <c r="BN195" s="2"/>
@@ -26824,8 +26834,8 @@
       <c r="BG196" s="2"/>
       <c r="BH196" s="2"/>
       <c r="BI196" s="2"/>
-      <c r="BJ196" s="2"/>
-      <c r="BK196" s="2"/>
+      <c r="BJ196" s="191"/>
+      <c r="BK196" s="191"/>
       <c r="BL196" s="2"/>
       <c r="BM196" s="2"/>
       <c r="BN196" s="2"/>
@@ -26946,8 +26956,8 @@
       <c r="BG197" s="2"/>
       <c r="BH197" s="2"/>
       <c r="BI197" s="2"/>
-      <c r="BJ197" s="2"/>
-      <c r="BK197" s="2"/>
+      <c r="BJ197" s="191"/>
+      <c r="BK197" s="191"/>
       <c r="BL197" s="2"/>
       <c r="BM197" s="2"/>
       <c r="BN197" s="2"/>
@@ -27068,8 +27078,8 @@
       <c r="BG198" s="2"/>
       <c r="BH198" s="2"/>
       <c r="BI198" s="2"/>
-      <c r="BJ198" s="2"/>
-      <c r="BK198" s="2"/>
+      <c r="BJ198" s="191"/>
+      <c r="BK198" s="191"/>
       <c r="BL198" s="2"/>
       <c r="BM198" s="2"/>
       <c r="BN198" s="2"/>
@@ -27190,8 +27200,8 @@
       <c r="BG199" s="2"/>
       <c r="BH199" s="2"/>
       <c r="BI199" s="2"/>
-      <c r="BJ199" s="2"/>
-      <c r="BK199" s="2"/>
+      <c r="BJ199" s="191"/>
+      <c r="BK199" s="191"/>
       <c r="BL199" s="2"/>
       <c r="BM199" s="2"/>
       <c r="BN199" s="2"/>
@@ -27312,8 +27322,8 @@
       <c r="BG200" s="2"/>
       <c r="BH200" s="2"/>
       <c r="BI200" s="2"/>
-      <c r="BJ200" s="2"/>
-      <c r="BK200" s="2"/>
+      <c r="BJ200" s="191"/>
+      <c r="BK200" s="191"/>
       <c r="BL200" s="2"/>
       <c r="BM200" s="2"/>
       <c r="BN200" s="2"/>
@@ -27434,8 +27444,8 @@
       <c r="BG201" s="2"/>
       <c r="BH201" s="2"/>
       <c r="BI201" s="2"/>
-      <c r="BJ201" s="2"/>
-      <c r="BK201" s="2"/>
+      <c r="BJ201" s="191"/>
+      <c r="BK201" s="191"/>
       <c r="BL201" s="2"/>
       <c r="BM201" s="2"/>
       <c r="BN201" s="2"/>
@@ -27556,8 +27566,8 @@
       <c r="BG202" s="2"/>
       <c r="BH202" s="2"/>
       <c r="BI202" s="2"/>
-      <c r="BJ202" s="2"/>
-      <c r="BK202" s="2"/>
+      <c r="BJ202" s="191"/>
+      <c r="BK202" s="191"/>
       <c r="BL202" s="2"/>
       <c r="BM202" s="2"/>
       <c r="BN202" s="2"/>
@@ -27678,8 +27688,8 @@
       <c r="BG203" s="2"/>
       <c r="BH203" s="2"/>
       <c r="BI203" s="2"/>
-      <c r="BJ203" s="2"/>
-      <c r="BK203" s="2"/>
+      <c r="BJ203" s="191"/>
+      <c r="BK203" s="191"/>
       <c r="BL203" s="2"/>
       <c r="BM203" s="2"/>
       <c r="BN203" s="2"/>
@@ -27800,8 +27810,8 @@
       <c r="BG204" s="2"/>
       <c r="BH204" s="2"/>
       <c r="BI204" s="2"/>
-      <c r="BJ204" s="2"/>
-      <c r="BK204" s="2"/>
+      <c r="BJ204" s="191"/>
+      <c r="BK204" s="191"/>
       <c r="BL204" s="2"/>
       <c r="BM204" s="2"/>
       <c r="BN204" s="2"/>
@@ -27922,8 +27932,8 @@
       <c r="BG205" s="2"/>
       <c r="BH205" s="2"/>
       <c r="BI205" s="2"/>
-      <c r="BJ205" s="2"/>
-      <c r="BK205" s="2"/>
+      <c r="BJ205" s="191"/>
+      <c r="BK205" s="191"/>
       <c r="BL205" s="2"/>
       <c r="BM205" s="2"/>
       <c r="BN205" s="2"/>
@@ -28044,8 +28054,8 @@
       <c r="BG206" s="2"/>
       <c r="BH206" s="2"/>
       <c r="BI206" s="2"/>
-      <c r="BJ206" s="2"/>
-      <c r="BK206" s="2"/>
+      <c r="BJ206" s="191"/>
+      <c r="BK206" s="191"/>
       <c r="BL206" s="2"/>
       <c r="BM206" s="2"/>
       <c r="BN206" s="2"/>
@@ -28166,8 +28176,8 @@
       <c r="BG207" s="2"/>
       <c r="BH207" s="2"/>
       <c r="BI207" s="2"/>
-      <c r="BJ207" s="2"/>
-      <c r="BK207" s="2"/>
+      <c r="BJ207" s="191"/>
+      <c r="BK207" s="191"/>
       <c r="BL207" s="2"/>
       <c r="BM207" s="2"/>
       <c r="BN207" s="2"/>
@@ -28288,8 +28298,8 @@
       <c r="BG208" s="2"/>
       <c r="BH208" s="2"/>
       <c r="BI208" s="2"/>
-      <c r="BJ208" s="2"/>
-      <c r="BK208" s="2"/>
+      <c r="BJ208" s="191"/>
+      <c r="BK208" s="191"/>
       <c r="BL208" s="2"/>
       <c r="BM208" s="2"/>
       <c r="BN208" s="2"/>
@@ -28410,8 +28420,8 @@
       <c r="BG209" s="2"/>
       <c r="BH209" s="2"/>
       <c r="BI209" s="2"/>
-      <c r="BJ209" s="2"/>
-      <c r="BK209" s="2"/>
+      <c r="BJ209" s="191"/>
+      <c r="BK209" s="191"/>
       <c r="BL209" s="2"/>
       <c r="BM209" s="2"/>
       <c r="BN209" s="2"/>
@@ -28532,8 +28542,8 @@
       <c r="BG210" s="2"/>
       <c r="BH210" s="2"/>
       <c r="BI210" s="2"/>
-      <c r="BJ210" s="2"/>
-      <c r="BK210" s="2"/>
+      <c r="BJ210" s="191"/>
+      <c r="BK210" s="191"/>
       <c r="BL210" s="2"/>
       <c r="BM210" s="2"/>
       <c r="BN210" s="2"/>
@@ -28654,8 +28664,8 @@
       <c r="BG211" s="2"/>
       <c r="BH211" s="2"/>
       <c r="BI211" s="2"/>
-      <c r="BJ211" s="2"/>
-      <c r="BK211" s="2"/>
+      <c r="BJ211" s="191"/>
+      <c r="BK211" s="191"/>
       <c r="BL211" s="2"/>
       <c r="BM211" s="2"/>
       <c r="BN211" s="2"/>
@@ -28776,8 +28786,8 @@
       <c r="BG212" s="2"/>
       <c r="BH212" s="2"/>
       <c r="BI212" s="2"/>
-      <c r="BJ212" s="2"/>
-      <c r="BK212" s="2"/>
+      <c r="BJ212" s="191"/>
+      <c r="BK212" s="191"/>
       <c r="BL212" s="2"/>
       <c r="BM212" s="2"/>
       <c r="BN212" s="2"/>
@@ -28898,8 +28908,8 @@
       <c r="BG213" s="2"/>
       <c r="BH213" s="2"/>
       <c r="BI213" s="2"/>
-      <c r="BJ213" s="2"/>
-      <c r="BK213" s="2"/>
+      <c r="BJ213" s="191"/>
+      <c r="BK213" s="191"/>
       <c r="BL213" s="2"/>
       <c r="BM213" s="2"/>
       <c r="BN213" s="2"/>
@@ -29020,8 +29030,8 @@
       <c r="BG214" s="2"/>
       <c r="BH214" s="2"/>
       <c r="BI214" s="2"/>
-      <c r="BJ214" s="2"/>
-      <c r="BK214" s="2"/>
+      <c r="BJ214" s="191"/>
+      <c r="BK214" s="191"/>
       <c r="BL214" s="2"/>
       <c r="BM214" s="2"/>
       <c r="BN214" s="2"/>
@@ -29142,8 +29152,8 @@
       <c r="BG215" s="2"/>
       <c r="BH215" s="2"/>
       <c r="BI215" s="2"/>
-      <c r="BJ215" s="2"/>
-      <c r="BK215" s="2"/>
+      <c r="BJ215" s="191"/>
+      <c r="BK215" s="191"/>
       <c r="BL215" s="2"/>
       <c r="BM215" s="2"/>
       <c r="BN215" s="2"/>
@@ -29264,8 +29274,8 @@
       <c r="BG216" s="2"/>
       <c r="BH216" s="2"/>
       <c r="BI216" s="2"/>
-      <c r="BJ216" s="2"/>
-      <c r="BK216" s="2"/>
+      <c r="BJ216" s="191"/>
+      <c r="BK216" s="191"/>
       <c r="BL216" s="2"/>
       <c r="BM216" s="2"/>
       <c r="BN216" s="2"/>
@@ -29386,8 +29396,8 @@
       <c r="BG217" s="2"/>
       <c r="BH217" s="2"/>
       <c r="BI217" s="2"/>
-      <c r="BJ217" s="2"/>
-      <c r="BK217" s="2"/>
+      <c r="BJ217" s="191"/>
+      <c r="BK217" s="191"/>
       <c r="BL217" s="2"/>
       <c r="BM217" s="2"/>
       <c r="BN217" s="2"/>
@@ -29508,8 +29518,8 @@
       <c r="BG218" s="2"/>
       <c r="BH218" s="2"/>
       <c r="BI218" s="2"/>
-      <c r="BJ218" s="2"/>
-      <c r="BK218" s="2"/>
+      <c r="BJ218" s="191"/>
+      <c r="BK218" s="191"/>
       <c r="BL218" s="2"/>
       <c r="BM218" s="2"/>
       <c r="BN218" s="2"/>
@@ -29630,8 +29640,8 @@
       <c r="BG219" s="2"/>
       <c r="BH219" s="2"/>
       <c r="BI219" s="2"/>
-      <c r="BJ219" s="2"/>
-      <c r="BK219" s="2"/>
+      <c r="BJ219" s="191"/>
+      <c r="BK219" s="191"/>
       <c r="BL219" s="2"/>
       <c r="BM219" s="2"/>
       <c r="BN219" s="2"/>
@@ -29752,8 +29762,8 @@
       <c r="BG220" s="2"/>
       <c r="BH220" s="2"/>
       <c r="BI220" s="2"/>
-      <c r="BJ220" s="2"/>
-      <c r="BK220" s="2"/>
+      <c r="BJ220" s="191"/>
+      <c r="BK220" s="191"/>
       <c r="BL220" s="2"/>
       <c r="BM220" s="2"/>
       <c r="BN220" s="2"/>
@@ -29874,8 +29884,8 @@
       <c r="BG221" s="2"/>
       <c r="BH221" s="2"/>
       <c r="BI221" s="2"/>
-      <c r="BJ221" s="2"/>
-      <c r="BK221" s="2"/>
+      <c r="BJ221" s="191"/>
+      <c r="BK221" s="191"/>
       <c r="BL221" s="2"/>
       <c r="BM221" s="2"/>
       <c r="BN221" s="2"/>
@@ -29996,8 +30006,8 @@
       <c r="BG222" s="2"/>
       <c r="BH222" s="2"/>
       <c r="BI222" s="2"/>
-      <c r="BJ222" s="2"/>
-      <c r="BK222" s="2"/>
+      <c r="BJ222" s="191"/>
+      <c r="BK222" s="191"/>
       <c r="BL222" s="2"/>
       <c r="BM222" s="2"/>
       <c r="BN222" s="2"/>
@@ -30118,8 +30128,8 @@
       <c r="BG223" s="2"/>
       <c r="BH223" s="2"/>
       <c r="BI223" s="2"/>
-      <c r="BJ223" s="2"/>
-      <c r="BK223" s="2"/>
+      <c r="BJ223" s="191"/>
+      <c r="BK223" s="191"/>
       <c r="BL223" s="2"/>
       <c r="BM223" s="2"/>
       <c r="BN223" s="2"/>
@@ -30240,8 +30250,8 @@
       <c r="BG224" s="2"/>
       <c r="BH224" s="2"/>
       <c r="BI224" s="2"/>
-      <c r="BJ224" s="2"/>
-      <c r="BK224" s="2"/>
+      <c r="BJ224" s="191"/>
+      <c r="BK224" s="191"/>
       <c r="BL224" s="2"/>
       <c r="BM224" s="2"/>
       <c r="BN224" s="2"/>
@@ -30362,8 +30372,8 @@
       <c r="BG225" s="2"/>
       <c r="BH225" s="2"/>
       <c r="BI225" s="2"/>
-      <c r="BJ225" s="2"/>
-      <c r="BK225" s="2"/>
+      <c r="BJ225" s="191"/>
+      <c r="BK225" s="191"/>
       <c r="BL225" s="2"/>
       <c r="BM225" s="2"/>
       <c r="BN225" s="2"/>
@@ -30484,8 +30494,8 @@
       <c r="BG226" s="2"/>
       <c r="BH226" s="2"/>
       <c r="BI226" s="2"/>
-      <c r="BJ226" s="2"/>
-      <c r="BK226" s="2"/>
+      <c r="BJ226" s="191"/>
+      <c r="BK226" s="191"/>
       <c r="BL226" s="2"/>
       <c r="BM226" s="2"/>
       <c r="BN226" s="2"/>
@@ -30606,8 +30616,8 @@
       <c r="BG227" s="2"/>
       <c r="BH227" s="2"/>
       <c r="BI227" s="2"/>
-      <c r="BJ227" s="2"/>
-      <c r="BK227" s="2"/>
+      <c r="BJ227" s="191"/>
+      <c r="BK227" s="191"/>
       <c r="BL227" s="2"/>
       <c r="BM227" s="2"/>
       <c r="BN227" s="2"/>
@@ -30728,8 +30738,8 @@
       <c r="BG228" s="2"/>
       <c r="BH228" s="2"/>
       <c r="BI228" s="2"/>
-      <c r="BJ228" s="2"/>
-      <c r="BK228" s="2"/>
+      <c r="BJ228" s="191"/>
+      <c r="BK228" s="191"/>
       <c r="BL228" s="2"/>
       <c r="BM228" s="2"/>
       <c r="BN228" s="2"/>
@@ -30850,8 +30860,8 @@
       <c r="BG229" s="2"/>
       <c r="BH229" s="2"/>
       <c r="BI229" s="2"/>
-      <c r="BJ229" s="2"/>
-      <c r="BK229" s="2"/>
+      <c r="BJ229" s="191"/>
+      <c r="BK229" s="191"/>
       <c r="BL229" s="2"/>
       <c r="BM229" s="2"/>
       <c r="BN229" s="2"/>
@@ -30972,8 +30982,8 @@
       <c r="BG230" s="2"/>
       <c r="BH230" s="2"/>
       <c r="BI230" s="2"/>
-      <c r="BJ230" s="2"/>
-      <c r="BK230" s="2"/>
+      <c r="BJ230" s="191"/>
+      <c r="BK230" s="191"/>
       <c r="BL230" s="2"/>
       <c r="BM230" s="2"/>
       <c r="BN230" s="2"/>
@@ -31094,8 +31104,8 @@
       <c r="BG231" s="2"/>
       <c r="BH231" s="2"/>
       <c r="BI231" s="2"/>
-      <c r="BJ231" s="2"/>
-      <c r="BK231" s="2"/>
+      <c r="BJ231" s="191"/>
+      <c r="BK231" s="191"/>
       <c r="BL231" s="2"/>
       <c r="BM231" s="2"/>
       <c r="BN231" s="2"/>
@@ -31216,8 +31226,8 @@
       <c r="BG232" s="2"/>
       <c r="BH232" s="2"/>
       <c r="BI232" s="2"/>
-      <c r="BJ232" s="2"/>
-      <c r="BK232" s="2"/>
+      <c r="BJ232" s="191"/>
+      <c r="BK232" s="191"/>
       <c r="BL232" s="2"/>
       <c r="BM232" s="2"/>
       <c r="BN232" s="2"/>
@@ -31338,8 +31348,8 @@
       <c r="BG233" s="2"/>
       <c r="BH233" s="2"/>
       <c r="BI233" s="2"/>
-      <c r="BJ233" s="2"/>
-      <c r="BK233" s="2"/>
+      <c r="BJ233" s="191"/>
+      <c r="BK233" s="191"/>
       <c r="BL233" s="2"/>
       <c r="BM233" s="2"/>
       <c r="BN233" s="2"/>
@@ -31460,8 +31470,8 @@
       <c r="BG234" s="2"/>
       <c r="BH234" s="2"/>
       <c r="BI234" s="2"/>
-      <c r="BJ234" s="2"/>
-      <c r="BK234" s="2"/>
+      <c r="BJ234" s="191"/>
+      <c r="BK234" s="191"/>
       <c r="BL234" s="2"/>
       <c r="BM234" s="2"/>
       <c r="BN234" s="2"/>
@@ -31582,8 +31592,8 @@
       <c r="BG235" s="2"/>
       <c r="BH235" s="2"/>
       <c r="BI235" s="2"/>
-      <c r="BJ235" s="2"/>
-      <c r="BK235" s="2"/>
+      <c r="BJ235" s="191"/>
+      <c r="BK235" s="191"/>
       <c r="BL235" s="2"/>
       <c r="BM235" s="2"/>
       <c r="BN235" s="2"/>
@@ -31704,8 +31714,8 @@
       <c r="BG236" s="2"/>
       <c r="BH236" s="2"/>
       <c r="BI236" s="2"/>
-      <c r="BJ236" s="2"/>
-      <c r="BK236" s="2"/>
+      <c r="BJ236" s="191"/>
+      <c r="BK236" s="191"/>
       <c r="BL236" s="2"/>
       <c r="BM236" s="2"/>
       <c r="BN236" s="2"/>
@@ -31826,8 +31836,8 @@
       <c r="BG237" s="2"/>
       <c r="BH237" s="2"/>
       <c r="BI237" s="2"/>
-      <c r="BJ237" s="2"/>
-      <c r="BK237" s="2"/>
+      <c r="BJ237" s="191"/>
+      <c r="BK237" s="191"/>
       <c r="BL237" s="2"/>
       <c r="BM237" s="2"/>
       <c r="BN237" s="2"/>
@@ -31948,8 +31958,8 @@
       <c r="BG238" s="2"/>
       <c r="BH238" s="2"/>
       <c r="BI238" s="2"/>
-      <c r="BJ238" s="2"/>
-      <c r="BK238" s="2"/>
+      <c r="BJ238" s="191"/>
+      <c r="BK238" s="191"/>
       <c r="BL238" s="2"/>
       <c r="BM238" s="2"/>
       <c r="BN238" s="2"/>
@@ -32070,8 +32080,8 @@
       <c r="BG239" s="2"/>
       <c r="BH239" s="2"/>
       <c r="BI239" s="2"/>
-      <c r="BJ239" s="2"/>
-      <c r="BK239" s="2"/>
+      <c r="BJ239" s="191"/>
+      <c r="BK239" s="191"/>
       <c r="BL239" s="2"/>
       <c r="BM239" s="2"/>
       <c r="BN239" s="2"/>
@@ -32192,8 +32202,8 @@
       <c r="BG240" s="2"/>
       <c r="BH240" s="2"/>
       <c r="BI240" s="2"/>
-      <c r="BJ240" s="2"/>
-      <c r="BK240" s="2"/>
+      <c r="BJ240" s="191"/>
+      <c r="BK240" s="191"/>
       <c r="BL240" s="2"/>
       <c r="BM240" s="2"/>
       <c r="BN240" s="2"/>
@@ -32314,8 +32324,8 @@
       <c r="BG241" s="2"/>
       <c r="BH241" s="2"/>
       <c r="BI241" s="2"/>
-      <c r="BJ241" s="2"/>
-      <c r="BK241" s="2"/>
+      <c r="BJ241" s="191"/>
+      <c r="BK241" s="191"/>
       <c r="BL241" s="2"/>
       <c r="BM241" s="2"/>
       <c r="BN241" s="2"/>
@@ -32436,8 +32446,8 @@
       <c r="BG242" s="2"/>
       <c r="BH242" s="2"/>
       <c r="BI242" s="2"/>
-      <c r="BJ242" s="2"/>
-      <c r="BK242" s="2"/>
+      <c r="BJ242" s="191"/>
+      <c r="BK242" s="191"/>
       <c r="BL242" s="2"/>
       <c r="BM242" s="2"/>
       <c r="BN242" s="2"/>
@@ -32558,8 +32568,8 @@
       <c r="BG243" s="2"/>
       <c r="BH243" s="2"/>
       <c r="BI243" s="2"/>
-      <c r="BJ243" s="2"/>
-      <c r="BK243" s="2"/>
+      <c r="BJ243" s="191"/>
+      <c r="BK243" s="191"/>
       <c r="BL243" s="2"/>
       <c r="BM243" s="2"/>
       <c r="BN243" s="2"/>
@@ -32680,8 +32690,8 @@
       <c r="BG244" s="2"/>
       <c r="BH244" s="2"/>
       <c r="BI244" s="2"/>
-      <c r="BJ244" s="2"/>
-      <c r="BK244" s="2"/>
+      <c r="BJ244" s="191"/>
+      <c r="BK244" s="191"/>
       <c r="BL244" s="2"/>
       <c r="BM244" s="2"/>
       <c r="BN244" s="2"/>
@@ -32802,8 +32812,8 @@
       <c r="BG245" s="2"/>
       <c r="BH245" s="2"/>
       <c r="BI245" s="2"/>
-      <c r="BJ245" s="2"/>
-      <c r="BK245" s="2"/>
+      <c r="BJ245" s="191"/>
+      <c r="BK245" s="191"/>
       <c r="BL245" s="2"/>
       <c r="BM245" s="2"/>
       <c r="BN245" s="2"/>
@@ -32924,8 +32934,8 @@
       <c r="BG246" s="2"/>
       <c r="BH246" s="2"/>
       <c r="BI246" s="2"/>
-      <c r="BJ246" s="2"/>
-      <c r="BK246" s="2"/>
+      <c r="BJ246" s="191"/>
+      <c r="BK246" s="191"/>
       <c r="BL246" s="2"/>
       <c r="BM246" s="2"/>
       <c r="BN246" s="2"/>
@@ -33046,8 +33056,8 @@
       <c r="BG247" s="2"/>
       <c r="BH247" s="2"/>
       <c r="BI247" s="2"/>
-      <c r="BJ247" s="2"/>
-      <c r="BK247" s="2"/>
+      <c r="BJ247" s="191"/>
+      <c r="BK247" s="191"/>
       <c r="BL247" s="2"/>
       <c r="BM247" s="2"/>
       <c r="BN247" s="2"/>
@@ -33168,8 +33178,8 @@
       <c r="BG248" s="2"/>
       <c r="BH248" s="2"/>
       <c r="BI248" s="2"/>
-      <c r="BJ248" s="2"/>
-      <c r="BK248" s="2"/>
+      <c r="BJ248" s="191"/>
+      <c r="BK248" s="191"/>
       <c r="BL248" s="2"/>
       <c r="BM248" s="2"/>
       <c r="BN248" s="2"/>
@@ -33290,8 +33300,8 @@
       <c r="BG249" s="2"/>
       <c r="BH249" s="2"/>
       <c r="BI249" s="2"/>
-      <c r="BJ249" s="2"/>
-      <c r="BK249" s="2"/>
+      <c r="BJ249" s="191"/>
+      <c r="BK249" s="191"/>
       <c r="BL249" s="2"/>
       <c r="BM249" s="2"/>
       <c r="BN249" s="2"/>
@@ -33412,8 +33422,8 @@
       <c r="BG250" s="2"/>
       <c r="BH250" s="2"/>
       <c r="BI250" s="2"/>
-      <c r="BJ250" s="2"/>
-      <c r="BK250" s="2"/>
+      <c r="BJ250" s="191"/>
+      <c r="BK250" s="191"/>
       <c r="BL250" s="2"/>
       <c r="BM250" s="2"/>
       <c r="BN250" s="2"/>
@@ -33534,8 +33544,8 @@
       <c r="BG251" s="2"/>
       <c r="BH251" s="2"/>
       <c r="BI251" s="2"/>
-      <c r="BJ251" s="2"/>
-      <c r="BK251" s="2"/>
+      <c r="BJ251" s="191"/>
+      <c r="BK251" s="191"/>
       <c r="BL251" s="2"/>
       <c r="BM251" s="2"/>
       <c r="BN251" s="2"/>
@@ -33656,8 +33666,8 @@
       <c r="BG252" s="2"/>
       <c r="BH252" s="2"/>
       <c r="BI252" s="2"/>
-      <c r="BJ252" s="2"/>
-      <c r="BK252" s="2"/>
+      <c r="BJ252" s="191"/>
+      <c r="BK252" s="191"/>
       <c r="BL252" s="2"/>
       <c r="BM252" s="2"/>
       <c r="BN252" s="2"/>
@@ -33778,8 +33788,8 @@
       <c r="BG253" s="2"/>
       <c r="BH253" s="2"/>
       <c r="BI253" s="2"/>
-      <c r="BJ253" s="2"/>
-      <c r="BK253" s="2"/>
+      <c r="BJ253" s="191"/>
+      <c r="BK253" s="191"/>
       <c r="BL253" s="2"/>
       <c r="BM253" s="2"/>
       <c r="BN253" s="2"/>
@@ -33900,8 +33910,8 @@
       <c r="BG254" s="2"/>
       <c r="BH254" s="2"/>
       <c r="BI254" s="2"/>
-      <c r="BJ254" s="2"/>
-      <c r="BK254" s="2"/>
+      <c r="BJ254" s="191"/>
+      <c r="BK254" s="191"/>
       <c r="BL254" s="2"/>
       <c r="BM254" s="2"/>
       <c r="BN254" s="2"/>
@@ -34022,8 +34032,8 @@
       <c r="BG255" s="2"/>
       <c r="BH255" s="2"/>
       <c r="BI255" s="2"/>
-      <c r="BJ255" s="2"/>
-      <c r="BK255" s="2"/>
+      <c r="BJ255" s="191"/>
+      <c r="BK255" s="191"/>
       <c r="BL255" s="2"/>
       <c r="BM255" s="2"/>
       <c r="BN255" s="2"/>
@@ -34144,8 +34154,8 @@
       <c r="BG256" s="2"/>
       <c r="BH256" s="2"/>
       <c r="BI256" s="2"/>
-      <c r="BJ256" s="2"/>
-      <c r="BK256" s="2"/>
+      <c r="BJ256" s="191"/>
+      <c r="BK256" s="191"/>
       <c r="BL256" s="2"/>
       <c r="BM256" s="2"/>
       <c r="BN256" s="2"/>
@@ -34266,8 +34276,8 @@
       <c r="BG257" s="2"/>
       <c r="BH257" s="2"/>
       <c r="BI257" s="2"/>
-      <c r="BJ257" s="2"/>
-      <c r="BK257" s="2"/>
+      <c r="BJ257" s="191"/>
+      <c r="BK257" s="191"/>
       <c r="BL257" s="2"/>
       <c r="BM257" s="2"/>
       <c r="BN257" s="2"/>
@@ -34388,8 +34398,8 @@
       <c r="BG258" s="2"/>
       <c r="BH258" s="2"/>
       <c r="BI258" s="2"/>
-      <c r="BJ258" s="2"/>
-      <c r="BK258" s="2"/>
+      <c r="BJ258" s="191"/>
+      <c r="BK258" s="191"/>
       <c r="BL258" s="2"/>
       <c r="BM258" s="2"/>
       <c r="BN258" s="2"/>
@@ -34510,8 +34520,8 @@
       <c r="BG259" s="2"/>
       <c r="BH259" s="2"/>
       <c r="BI259" s="2"/>
-      <c r="BJ259" s="2"/>
-      <c r="BK259" s="2"/>
+      <c r="BJ259" s="191"/>
+      <c r="BK259" s="191"/>
       <c r="BL259" s="2"/>
       <c r="BM259" s="2"/>
       <c r="BN259" s="2"/>
@@ -34632,8 +34642,8 @@
       <c r="BG260" s="2"/>
       <c r="BH260" s="2"/>
       <c r="BI260" s="2"/>
-      <c r="BJ260" s="2"/>
-      <c r="BK260" s="2"/>
+      <c r="BJ260" s="191"/>
+      <c r="BK260" s="191"/>
       <c r="BL260" s="2"/>
       <c r="BM260" s="2"/>
       <c r="BN260" s="2"/>
@@ -34754,8 +34764,8 @@
       <c r="BG261" s="2"/>
       <c r="BH261" s="2"/>
       <c r="BI261" s="2"/>
-      <c r="BJ261" s="2"/>
-      <c r="BK261" s="2"/>
+      <c r="BJ261" s="191"/>
+      <c r="BK261" s="191"/>
       <c r="BL261" s="2"/>
       <c r="BM261" s="2"/>
       <c r="BN261" s="2"/>
@@ -34876,8 +34886,8 @@
       <c r="BG262" s="2"/>
       <c r="BH262" s="2"/>
       <c r="BI262" s="2"/>
-      <c r="BJ262" s="2"/>
-      <c r="BK262" s="2"/>
+      <c r="BJ262" s="191"/>
+      <c r="BK262" s="191"/>
       <c r="BL262" s="2"/>
       <c r="BM262" s="2"/>
       <c r="BN262" s="2"/>
@@ -34998,8 +35008,8 @@
       <c r="BG263" s="2"/>
       <c r="BH263" s="2"/>
       <c r="BI263" s="2"/>
-      <c r="BJ263" s="2"/>
-      <c r="BK263" s="2"/>
+      <c r="BJ263" s="191"/>
+      <c r="BK263" s="191"/>
       <c r="BL263" s="2"/>
       <c r="BM263" s="2"/>
       <c r="BN263" s="2"/>
@@ -35120,8 +35130,8 @@
       <c r="BG264" s="2"/>
       <c r="BH264" s="2"/>
       <c r="BI264" s="2"/>
-      <c r="BJ264" s="2"/>
-      <c r="BK264" s="2"/>
+      <c r="BJ264" s="191"/>
+      <c r="BK264" s="191"/>
       <c r="BL264" s="2"/>
       <c r="BM264" s="2"/>
       <c r="BN264" s="2"/>
@@ -35242,8 +35252,8 @@
       <c r="BG265" s="2"/>
       <c r="BH265" s="2"/>
       <c r="BI265" s="2"/>
-      <c r="BJ265" s="2"/>
-      <c r="BK265" s="2"/>
+      <c r="BJ265" s="191"/>
+      <c r="BK265" s="191"/>
       <c r="BL265" s="2"/>
       <c r="BM265" s="2"/>
       <c r="BN265" s="2"/>
@@ -35364,8 +35374,8 @@
       <c r="BG266" s="2"/>
       <c r="BH266" s="2"/>
       <c r="BI266" s="2"/>
-      <c r="BJ266" s="2"/>
-      <c r="BK266" s="2"/>
+      <c r="BJ266" s="191"/>
+      <c r="BK266" s="191"/>
       <c r="BL266" s="2"/>
       <c r="BM266" s="2"/>
       <c r="BN266" s="2"/>
@@ -35486,8 +35496,8 @@
       <c r="BG267" s="2"/>
       <c r="BH267" s="2"/>
       <c r="BI267" s="2"/>
-      <c r="BJ267" s="2"/>
-      <c r="BK267" s="2"/>
+      <c r="BJ267" s="191"/>
+      <c r="BK267" s="191"/>
       <c r="BL267" s="2"/>
       <c r="BM267" s="2"/>
       <c r="BN267" s="2"/>
@@ -35608,8 +35618,8 @@
       <c r="BG268" s="2"/>
       <c r="BH268" s="2"/>
       <c r="BI268" s="2"/>
-      <c r="BJ268" s="2"/>
-      <c r="BK268" s="2"/>
+      <c r="BJ268" s="191"/>
+      <c r="BK268" s="191"/>
       <c r="BL268" s="2"/>
       <c r="BM268" s="2"/>
       <c r="BN268" s="2"/>
@@ -35730,8 +35740,8 @@
       <c r="BG269" s="2"/>
       <c r="BH269" s="2"/>
       <c r="BI269" s="2"/>
-      <c r="BJ269" s="2"/>
-      <c r="BK269" s="2"/>
+      <c r="BJ269" s="191"/>
+      <c r="BK269" s="191"/>
       <c r="BL269" s="2"/>
       <c r="BM269" s="2"/>
       <c r="BN269" s="2"/>
@@ -35852,8 +35862,8 @@
       <c r="BG270" s="2"/>
       <c r="BH270" s="2"/>
       <c r="BI270" s="2"/>
-      <c r="BJ270" s="2"/>
-      <c r="BK270" s="2"/>
+      <c r="BJ270" s="191"/>
+      <c r="BK270" s="191"/>
       <c r="BL270" s="2"/>
       <c r="BM270" s="2"/>
       <c r="BN270" s="2"/>
@@ -35974,8 +35984,8 @@
       <c r="BG271" s="2"/>
       <c r="BH271" s="2"/>
       <c r="BI271" s="2"/>
-      <c r="BJ271" s="2"/>
-      <c r="BK271" s="2"/>
+      <c r="BJ271" s="191"/>
+      <c r="BK271" s="191"/>
       <c r="BL271" s="2"/>
       <c r="BM271" s="2"/>
       <c r="BN271" s="2"/>
@@ -36096,8 +36106,8 @@
       <c r="BG272" s="2"/>
       <c r="BH272" s="2"/>
       <c r="BI272" s="2"/>
-      <c r="BJ272" s="2"/>
-      <c r="BK272" s="2"/>
+      <c r="BJ272" s="191"/>
+      <c r="BK272" s="191"/>
       <c r="BL272" s="2"/>
       <c r="BM272" s="2"/>
       <c r="BN272" s="2"/>
@@ -36216,8 +36226,8 @@
       <c r="BG273" s="2"/>
       <c r="BH273" s="2"/>
       <c r="BI273" s="2"/>
-      <c r="BJ273" s="2"/>
-      <c r="BK273" s="2"/>
+      <c r="BJ273" s="191"/>
+      <c r="BK273" s="191"/>
       <c r="BL273" s="2"/>
       <c r="BM273" s="2"/>
       <c r="BN273" s="2"/>
@@ -36336,8 +36346,8 @@
       <c r="BG274" s="2"/>
       <c r="BH274" s="2"/>
       <c r="BI274" s="2"/>
-      <c r="BJ274" s="2"/>
-      <c r="BK274" s="2"/>
+      <c r="BJ274" s="191"/>
+      <c r="BK274" s="191"/>
       <c r="BL274" s="2"/>
       <c r="BM274" s="2"/>
       <c r="BN274" s="2"/>
@@ -36406,6 +36416,222 @@
     </row>
   </sheetData>
   <mergeCells count="240">
+    <mergeCell ref="D157:G158"/>
+    <mergeCell ref="H157:H158"/>
+    <mergeCell ref="I157:I158"/>
+    <mergeCell ref="H141:H142"/>
+    <mergeCell ref="I143:I144"/>
+    <mergeCell ref="I139:I140"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="H103:H104"/>
+    <mergeCell ref="I103:I104"/>
+    <mergeCell ref="H115:H116"/>
+    <mergeCell ref="I115:I116"/>
+    <mergeCell ref="D103:G104"/>
+    <mergeCell ref="D115:G116"/>
+    <mergeCell ref="D131:G132"/>
+    <mergeCell ref="H131:H132"/>
+    <mergeCell ref="I131:I132"/>
+    <mergeCell ref="D87:G88"/>
+    <mergeCell ref="D141:G142"/>
+    <mergeCell ref="E153:G154"/>
+    <mergeCell ref="H153:H154"/>
+    <mergeCell ref="H151:H152"/>
+    <mergeCell ref="H149:H150"/>
+    <mergeCell ref="H147:H148"/>
+    <mergeCell ref="H145:H146"/>
+    <mergeCell ref="H143:H144"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="C133:G134"/>
+    <mergeCell ref="D135:G136"/>
+    <mergeCell ref="E137:G138"/>
+    <mergeCell ref="E139:G140"/>
+    <mergeCell ref="D143:G144"/>
+    <mergeCell ref="E145:G146"/>
+    <mergeCell ref="H135:H136"/>
+    <mergeCell ref="E147:G148"/>
+    <mergeCell ref="E149:G150"/>
+    <mergeCell ref="E151:G152"/>
+    <mergeCell ref="E59:G60"/>
+    <mergeCell ref="E61:G62"/>
+    <mergeCell ref="D63:G64"/>
+    <mergeCell ref="E67:G68"/>
+    <mergeCell ref="E65:G66"/>
+    <mergeCell ref="E69:G70"/>
+    <mergeCell ref="E71:G72"/>
+    <mergeCell ref="C73:G74"/>
+    <mergeCell ref="C75:G76"/>
+    <mergeCell ref="C77:G78"/>
+    <mergeCell ref="D79:G80"/>
+    <mergeCell ref="E109:G110"/>
+    <mergeCell ref="E111:G112"/>
+    <mergeCell ref="E101:G102"/>
+    <mergeCell ref="C105:G106"/>
+    <mergeCell ref="D107:G108"/>
+    <mergeCell ref="D117:G118"/>
+    <mergeCell ref="D13:G14"/>
+    <mergeCell ref="D15:G16"/>
+    <mergeCell ref="D17:G18"/>
+    <mergeCell ref="D19:G20"/>
+    <mergeCell ref="C21:G22"/>
+    <mergeCell ref="D23:G24"/>
+    <mergeCell ref="C25:G26"/>
+    <mergeCell ref="D27:G28"/>
+    <mergeCell ref="D29:G30"/>
+    <mergeCell ref="J3:CJ3"/>
+    <mergeCell ref="CK3:DO3"/>
+    <mergeCell ref="J4:AA4"/>
+    <mergeCell ref="AB4:BE4"/>
+    <mergeCell ref="BF4:CJ4"/>
+    <mergeCell ref="CK4:DO4"/>
+    <mergeCell ref="B7:G8"/>
+    <mergeCell ref="C9:G10"/>
+    <mergeCell ref="C11:G12"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="C163:G164"/>
+    <mergeCell ref="C159:G160"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="C31:G32"/>
+    <mergeCell ref="D33:G34"/>
+    <mergeCell ref="E35:G36"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="E43:G44"/>
+    <mergeCell ref="E45:G46"/>
+    <mergeCell ref="E47:G48"/>
+    <mergeCell ref="E49:G50"/>
+    <mergeCell ref="E51:G52"/>
+    <mergeCell ref="D53:G54"/>
+    <mergeCell ref="E55:G56"/>
+    <mergeCell ref="E57:G58"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I67:I68"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="I159:I160"/>
+    <mergeCell ref="I161:I162"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="I93:I94"/>
+    <mergeCell ref="I95:I96"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="I109:I110"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="I153:I154"/>
+    <mergeCell ref="I151:I152"/>
+    <mergeCell ref="I149:I150"/>
+    <mergeCell ref="I147:I148"/>
+    <mergeCell ref="I145:I146"/>
+    <mergeCell ref="I111:I112"/>
+    <mergeCell ref="I135:I136"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="I163:I164"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="H75:H76"/>
+    <mergeCell ref="H159:H160"/>
+    <mergeCell ref="H163:H164"/>
+    <mergeCell ref="H161:H162"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="H59:H60"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="H77:H78"/>
+    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="H93:H94"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="H111:H112"/>
+    <mergeCell ref="H101:H102"/>
+    <mergeCell ref="I101:I102"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="I85:I86"/>
+    <mergeCell ref="H89:H90"/>
+    <mergeCell ref="I89:I90"/>
+    <mergeCell ref="E81:G82"/>
+    <mergeCell ref="E83:G84"/>
+    <mergeCell ref="E91:G92"/>
+    <mergeCell ref="E93:G94"/>
+    <mergeCell ref="E95:G96"/>
+    <mergeCell ref="E97:G98"/>
+    <mergeCell ref="E99:G100"/>
+    <mergeCell ref="E85:G86"/>
+    <mergeCell ref="D89:G90"/>
+    <mergeCell ref="H105:H106"/>
+    <mergeCell ref="I105:I106"/>
+    <mergeCell ref="H107:H108"/>
+    <mergeCell ref="I107:I108"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="H117:H118"/>
+    <mergeCell ref="I117:I118"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="I119:I120"/>
     <mergeCell ref="E155:G156"/>
     <mergeCell ref="D155:D156"/>
     <mergeCell ref="H155:H156"/>
@@ -36430,222 +36656,6 @@
     <mergeCell ref="H127:H128"/>
     <mergeCell ref="I127:I128"/>
     <mergeCell ref="H121:H122"/>
-    <mergeCell ref="H105:H106"/>
-    <mergeCell ref="I105:I106"/>
-    <mergeCell ref="H107:H108"/>
-    <mergeCell ref="I107:I108"/>
-    <mergeCell ref="H109:H110"/>
-    <mergeCell ref="H117:H118"/>
-    <mergeCell ref="I117:I118"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="I119:I120"/>
-    <mergeCell ref="H101:H102"/>
-    <mergeCell ref="I101:I102"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="I85:I86"/>
-    <mergeCell ref="H89:H90"/>
-    <mergeCell ref="I89:I90"/>
-    <mergeCell ref="E81:G82"/>
-    <mergeCell ref="E83:G84"/>
-    <mergeCell ref="E91:G92"/>
-    <mergeCell ref="E93:G94"/>
-    <mergeCell ref="E95:G96"/>
-    <mergeCell ref="E97:G98"/>
-    <mergeCell ref="E99:G100"/>
-    <mergeCell ref="E85:G86"/>
-    <mergeCell ref="D89:G90"/>
-    <mergeCell ref="H75:H76"/>
-    <mergeCell ref="H159:H160"/>
-    <mergeCell ref="H163:H164"/>
-    <mergeCell ref="H161:H162"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="H67:H68"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H59:H60"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="H77:H78"/>
-    <mergeCell ref="H81:H82"/>
-    <mergeCell ref="H83:H84"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="H93:H94"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="H111:H112"/>
-    <mergeCell ref="I163:I164"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="I159:I160"/>
-    <mergeCell ref="I161:I162"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="I93:I94"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="I109:I110"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="I153:I154"/>
-    <mergeCell ref="I151:I152"/>
-    <mergeCell ref="I149:I150"/>
-    <mergeCell ref="I147:I148"/>
-    <mergeCell ref="I145:I146"/>
-    <mergeCell ref="I111:I112"/>
-    <mergeCell ref="I135:I136"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="C163:G164"/>
-    <mergeCell ref="C159:G160"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="C31:G32"/>
-    <mergeCell ref="D33:G34"/>
-    <mergeCell ref="E35:G36"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="E43:G44"/>
-    <mergeCell ref="E45:G46"/>
-    <mergeCell ref="E47:G48"/>
-    <mergeCell ref="E49:G50"/>
-    <mergeCell ref="E51:G52"/>
-    <mergeCell ref="D53:G54"/>
-    <mergeCell ref="E55:G56"/>
-    <mergeCell ref="E57:G58"/>
-    <mergeCell ref="I53:I54"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="J3:CJ3"/>
-    <mergeCell ref="CK3:DO3"/>
-    <mergeCell ref="J4:AA4"/>
-    <mergeCell ref="AB4:BE4"/>
-    <mergeCell ref="BF4:CJ4"/>
-    <mergeCell ref="CK4:DO4"/>
-    <mergeCell ref="B7:G8"/>
-    <mergeCell ref="C9:G10"/>
-    <mergeCell ref="C11:G12"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="D13:G14"/>
-    <mergeCell ref="D15:G16"/>
-    <mergeCell ref="D17:G18"/>
-    <mergeCell ref="D19:G20"/>
-    <mergeCell ref="C21:G22"/>
-    <mergeCell ref="D23:G24"/>
-    <mergeCell ref="C25:G26"/>
-    <mergeCell ref="D27:G28"/>
-    <mergeCell ref="D29:G30"/>
-    <mergeCell ref="E147:G148"/>
-    <mergeCell ref="E149:G150"/>
-    <mergeCell ref="E151:G152"/>
-    <mergeCell ref="E59:G60"/>
-    <mergeCell ref="E61:G62"/>
-    <mergeCell ref="D63:G64"/>
-    <mergeCell ref="E67:G68"/>
-    <mergeCell ref="E65:G66"/>
-    <mergeCell ref="E69:G70"/>
-    <mergeCell ref="E71:G72"/>
-    <mergeCell ref="C73:G74"/>
-    <mergeCell ref="C75:G76"/>
-    <mergeCell ref="C77:G78"/>
-    <mergeCell ref="D79:G80"/>
-    <mergeCell ref="E109:G110"/>
-    <mergeCell ref="E111:G112"/>
-    <mergeCell ref="E101:G102"/>
-    <mergeCell ref="C105:G106"/>
-    <mergeCell ref="D107:G108"/>
-    <mergeCell ref="D117:G118"/>
-    <mergeCell ref="H145:H146"/>
-    <mergeCell ref="H143:H144"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="C133:G134"/>
-    <mergeCell ref="D135:G136"/>
-    <mergeCell ref="E137:G138"/>
-    <mergeCell ref="E139:G140"/>
-    <mergeCell ref="D143:G144"/>
-    <mergeCell ref="E145:G146"/>
-    <mergeCell ref="H135:H136"/>
-    <mergeCell ref="D157:G158"/>
-    <mergeCell ref="H157:H158"/>
-    <mergeCell ref="I157:I158"/>
-    <mergeCell ref="H141:H142"/>
-    <mergeCell ref="I143:I144"/>
-    <mergeCell ref="I139:I140"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="H103:H104"/>
-    <mergeCell ref="I103:I104"/>
-    <mergeCell ref="H115:H116"/>
-    <mergeCell ref="I115:I116"/>
-    <mergeCell ref="D103:G104"/>
-    <mergeCell ref="D115:G116"/>
-    <mergeCell ref="D131:G132"/>
-    <mergeCell ref="H131:H132"/>
-    <mergeCell ref="I131:I132"/>
-    <mergeCell ref="D87:G88"/>
-    <mergeCell ref="D141:G142"/>
-    <mergeCell ref="E153:G154"/>
-    <mergeCell ref="H153:H154"/>
-    <mergeCell ref="H151:H152"/>
-    <mergeCell ref="H149:H150"/>
-    <mergeCell ref="H147:H148"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <conditionalFormatting sqref="J7">

--- a/docs/【DIGITAL OJT】WBS.xlsx
+++ b/docs/【DIGITAL OJT】WBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIGITALOJT\digital-ojt-development-cause-DroneInventorySystem\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F0844E-5EC9-4966-9992-975F9F8D1429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F96B42F-D5CE-4636-A4F5-4AD97EEFDCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14940" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -1481,67 +1481,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1550,25 +1510,22 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1589,29 +1546,110 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1637,106 +1675,344 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="50">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBFBFBF"/>
+          <bgColor rgb="FFBFBFBF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2083,7 +2359,7 @@
     <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="61" width="3.44140625" customWidth="1"/>
-    <col min="62" max="63" width="3.44140625" style="197" customWidth="1"/>
+    <col min="62" max="63" width="3.44140625" style="100" customWidth="1"/>
     <col min="64" max="119" width="3.44140625" customWidth="1"/>
     <col min="120" max="120" width="5" customWidth="1"/>
   </cols>
@@ -2148,8 +2424,8 @@
       <c r="BG1" s="2"/>
       <c r="BH1" s="2"/>
       <c r="BI1" s="2"/>
-      <c r="BJ1" s="198"/>
-      <c r="BK1" s="198"/>
+      <c r="BJ1" s="101"/>
+      <c r="BK1" s="101"/>
       <c r="BL1" s="2"/>
       <c r="BM1" s="2"/>
       <c r="BN1" s="2"/>
@@ -2270,8 +2546,8 @@
       <c r="BG2" s="2"/>
       <c r="BH2" s="2"/>
       <c r="BI2" s="2"/>
-      <c r="BJ2" s="198"/>
-      <c r="BK2" s="198"/>
+      <c r="BJ2" s="101"/>
+      <c r="BK2" s="101"/>
       <c r="BL2" s="2"/>
       <c r="BM2" s="2"/>
       <c r="BN2" s="2"/>
@@ -2340,120 +2616,120 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="J3" s="165">
+      <c r="J3" s="161">
         <v>2024</v>
       </c>
-      <c r="K3" s="166"/>
-      <c r="L3" s="166"/>
-      <c r="M3" s="166"/>
-      <c r="N3" s="166"/>
-      <c r="O3" s="166"/>
-      <c r="P3" s="166"/>
-      <c r="Q3" s="166"/>
-      <c r="R3" s="166"/>
-      <c r="S3" s="166"/>
-      <c r="T3" s="166"/>
-      <c r="U3" s="166"/>
-      <c r="V3" s="166"/>
-      <c r="W3" s="166"/>
-      <c r="X3" s="166"/>
-      <c r="Y3" s="166"/>
-      <c r="Z3" s="166"/>
-      <c r="AA3" s="166"/>
-      <c r="AB3" s="166"/>
-      <c r="AC3" s="166"/>
-      <c r="AD3" s="166"/>
-      <c r="AE3" s="166"/>
-      <c r="AF3" s="166"/>
-      <c r="AG3" s="166"/>
-      <c r="AH3" s="166"/>
-      <c r="AI3" s="166"/>
-      <c r="AJ3" s="166"/>
-      <c r="AK3" s="166"/>
-      <c r="AL3" s="166"/>
-      <c r="AM3" s="166"/>
-      <c r="AN3" s="166"/>
-      <c r="AO3" s="166"/>
-      <c r="AP3" s="166"/>
-      <c r="AQ3" s="166"/>
-      <c r="AR3" s="166"/>
-      <c r="AS3" s="166"/>
-      <c r="AT3" s="166"/>
-      <c r="AU3" s="166"/>
-      <c r="AV3" s="166"/>
-      <c r="AW3" s="166"/>
-      <c r="AX3" s="166"/>
-      <c r="AY3" s="166"/>
-      <c r="AZ3" s="166"/>
-      <c r="BA3" s="166"/>
-      <c r="BB3" s="166"/>
-      <c r="BC3" s="166"/>
-      <c r="BD3" s="166"/>
-      <c r="BE3" s="166"/>
-      <c r="BF3" s="166"/>
-      <c r="BG3" s="166"/>
-      <c r="BH3" s="166"/>
-      <c r="BI3" s="166"/>
-      <c r="BJ3" s="166"/>
-      <c r="BK3" s="166"/>
-      <c r="BL3" s="166"/>
-      <c r="BM3" s="166"/>
-      <c r="BN3" s="166"/>
-      <c r="BO3" s="166"/>
-      <c r="BP3" s="166"/>
-      <c r="BQ3" s="166"/>
-      <c r="BR3" s="166"/>
-      <c r="BS3" s="166"/>
-      <c r="BT3" s="166"/>
-      <c r="BU3" s="166"/>
-      <c r="BV3" s="166"/>
-      <c r="BW3" s="166"/>
-      <c r="BX3" s="166"/>
-      <c r="BY3" s="166"/>
-      <c r="BZ3" s="166"/>
-      <c r="CA3" s="166"/>
-      <c r="CB3" s="166"/>
-      <c r="CC3" s="166"/>
-      <c r="CD3" s="166"/>
-      <c r="CE3" s="166"/>
-      <c r="CF3" s="166"/>
-      <c r="CG3" s="166"/>
-      <c r="CH3" s="166"/>
-      <c r="CI3" s="166"/>
-      <c r="CJ3" s="167"/>
-      <c r="CK3" s="165">
+      <c r="K3" s="162"/>
+      <c r="L3" s="162"/>
+      <c r="M3" s="162"/>
+      <c r="N3" s="162"/>
+      <c r="O3" s="162"/>
+      <c r="P3" s="162"/>
+      <c r="Q3" s="162"/>
+      <c r="R3" s="162"/>
+      <c r="S3" s="162"/>
+      <c r="T3" s="162"/>
+      <c r="U3" s="162"/>
+      <c r="V3" s="162"/>
+      <c r="W3" s="162"/>
+      <c r="X3" s="162"/>
+      <c r="Y3" s="162"/>
+      <c r="Z3" s="162"/>
+      <c r="AA3" s="162"/>
+      <c r="AB3" s="162"/>
+      <c r="AC3" s="162"/>
+      <c r="AD3" s="162"/>
+      <c r="AE3" s="162"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="162"/>
+      <c r="AH3" s="162"/>
+      <c r="AI3" s="162"/>
+      <c r="AJ3" s="162"/>
+      <c r="AK3" s="162"/>
+      <c r="AL3" s="162"/>
+      <c r="AM3" s="162"/>
+      <c r="AN3" s="162"/>
+      <c r="AO3" s="162"/>
+      <c r="AP3" s="162"/>
+      <c r="AQ3" s="162"/>
+      <c r="AR3" s="162"/>
+      <c r="AS3" s="162"/>
+      <c r="AT3" s="162"/>
+      <c r="AU3" s="162"/>
+      <c r="AV3" s="162"/>
+      <c r="AW3" s="162"/>
+      <c r="AX3" s="162"/>
+      <c r="AY3" s="162"/>
+      <c r="AZ3" s="162"/>
+      <c r="BA3" s="162"/>
+      <c r="BB3" s="162"/>
+      <c r="BC3" s="162"/>
+      <c r="BD3" s="162"/>
+      <c r="BE3" s="162"/>
+      <c r="BF3" s="162"/>
+      <c r="BG3" s="162"/>
+      <c r="BH3" s="162"/>
+      <c r="BI3" s="162"/>
+      <c r="BJ3" s="162"/>
+      <c r="BK3" s="162"/>
+      <c r="BL3" s="162"/>
+      <c r="BM3" s="162"/>
+      <c r="BN3" s="162"/>
+      <c r="BO3" s="162"/>
+      <c r="BP3" s="162"/>
+      <c r="BQ3" s="162"/>
+      <c r="BR3" s="162"/>
+      <c r="BS3" s="162"/>
+      <c r="BT3" s="162"/>
+      <c r="BU3" s="162"/>
+      <c r="BV3" s="162"/>
+      <c r="BW3" s="162"/>
+      <c r="BX3" s="162"/>
+      <c r="BY3" s="162"/>
+      <c r="BZ3" s="162"/>
+      <c r="CA3" s="162"/>
+      <c r="CB3" s="162"/>
+      <c r="CC3" s="162"/>
+      <c r="CD3" s="162"/>
+      <c r="CE3" s="162"/>
+      <c r="CF3" s="162"/>
+      <c r="CG3" s="162"/>
+      <c r="CH3" s="162"/>
+      <c r="CI3" s="162"/>
+      <c r="CJ3" s="163"/>
+      <c r="CK3" s="161">
         <v>2025</v>
       </c>
-      <c r="CL3" s="166"/>
-      <c r="CM3" s="166"/>
-      <c r="CN3" s="166"/>
-      <c r="CO3" s="166"/>
-      <c r="CP3" s="166"/>
-      <c r="CQ3" s="166"/>
-      <c r="CR3" s="166"/>
-      <c r="CS3" s="166"/>
-      <c r="CT3" s="166"/>
-      <c r="CU3" s="166"/>
-      <c r="CV3" s="166"/>
-      <c r="CW3" s="166"/>
-      <c r="CX3" s="166"/>
-      <c r="CY3" s="166"/>
-      <c r="CZ3" s="166"/>
-      <c r="DA3" s="166"/>
-      <c r="DB3" s="166"/>
-      <c r="DC3" s="166"/>
-      <c r="DD3" s="166"/>
-      <c r="DE3" s="166"/>
-      <c r="DF3" s="166"/>
-      <c r="DG3" s="166"/>
-      <c r="DH3" s="166"/>
-      <c r="DI3" s="166"/>
-      <c r="DJ3" s="166"/>
-      <c r="DK3" s="166"/>
-      <c r="DL3" s="166"/>
-      <c r="DM3" s="166"/>
-      <c r="DN3" s="166"/>
-      <c r="DO3" s="167"/>
+      <c r="CL3" s="162"/>
+      <c r="CM3" s="162"/>
+      <c r="CN3" s="162"/>
+      <c r="CO3" s="162"/>
+      <c r="CP3" s="162"/>
+      <c r="CQ3" s="162"/>
+      <c r="CR3" s="162"/>
+      <c r="CS3" s="162"/>
+      <c r="CT3" s="162"/>
+      <c r="CU3" s="162"/>
+      <c r="CV3" s="162"/>
+      <c r="CW3" s="162"/>
+      <c r="CX3" s="162"/>
+      <c r="CY3" s="162"/>
+      <c r="CZ3" s="162"/>
+      <c r="DA3" s="162"/>
+      <c r="DB3" s="162"/>
+      <c r="DC3" s="162"/>
+      <c r="DD3" s="162"/>
+      <c r="DE3" s="162"/>
+      <c r="DF3" s="162"/>
+      <c r="DG3" s="162"/>
+      <c r="DH3" s="162"/>
+      <c r="DI3" s="162"/>
+      <c r="DJ3" s="162"/>
+      <c r="DK3" s="162"/>
+      <c r="DL3" s="162"/>
+      <c r="DM3" s="162"/>
+      <c r="DN3" s="162"/>
+      <c r="DO3" s="163"/>
       <c r="DP3" s="1"/>
     </row>
     <row r="4" spans="1:120" ht="18" customHeight="1">
@@ -2468,124 +2744,124 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="J4" s="165">
+      <c r="J4" s="161">
         <v>10</v>
       </c>
-      <c r="K4" s="166"/>
-      <c r="L4" s="166"/>
-      <c r="M4" s="166"/>
-      <c r="N4" s="166"/>
-      <c r="O4" s="166"/>
-      <c r="P4" s="166"/>
-      <c r="Q4" s="166"/>
-      <c r="R4" s="166"/>
-      <c r="S4" s="166"/>
-      <c r="T4" s="166"/>
-      <c r="U4" s="166"/>
-      <c r="V4" s="166"/>
-      <c r="W4" s="166"/>
-      <c r="X4" s="166"/>
-      <c r="Y4" s="166"/>
-      <c r="Z4" s="166"/>
-      <c r="AA4" s="167"/>
-      <c r="AB4" s="165">
+      <c r="K4" s="162"/>
+      <c r="L4" s="162"/>
+      <c r="M4" s="162"/>
+      <c r="N4" s="162"/>
+      <c r="O4" s="162"/>
+      <c r="P4" s="162"/>
+      <c r="Q4" s="162"/>
+      <c r="R4" s="162"/>
+      <c r="S4" s="162"/>
+      <c r="T4" s="162"/>
+      <c r="U4" s="162"/>
+      <c r="V4" s="162"/>
+      <c r="W4" s="162"/>
+      <c r="X4" s="162"/>
+      <c r="Y4" s="162"/>
+      <c r="Z4" s="162"/>
+      <c r="AA4" s="163"/>
+      <c r="AB4" s="161">
         <v>11</v>
       </c>
-      <c r="AC4" s="166"/>
-      <c r="AD4" s="166"/>
-      <c r="AE4" s="166"/>
-      <c r="AF4" s="166"/>
-      <c r="AG4" s="166"/>
-      <c r="AH4" s="166"/>
-      <c r="AI4" s="166"/>
-      <c r="AJ4" s="166"/>
-      <c r="AK4" s="166"/>
-      <c r="AL4" s="166"/>
-      <c r="AM4" s="166"/>
-      <c r="AN4" s="166"/>
-      <c r="AO4" s="166"/>
-      <c r="AP4" s="166"/>
-      <c r="AQ4" s="166"/>
-      <c r="AR4" s="166"/>
-      <c r="AS4" s="166"/>
-      <c r="AT4" s="166"/>
-      <c r="AU4" s="166"/>
-      <c r="AV4" s="166"/>
-      <c r="AW4" s="166"/>
-      <c r="AX4" s="166"/>
-      <c r="AY4" s="166"/>
-      <c r="AZ4" s="166"/>
-      <c r="BA4" s="166"/>
-      <c r="BB4" s="166"/>
-      <c r="BC4" s="166"/>
-      <c r="BD4" s="166"/>
-      <c r="BE4" s="167"/>
-      <c r="BF4" s="165">
+      <c r="AC4" s="162"/>
+      <c r="AD4" s="162"/>
+      <c r="AE4" s="162"/>
+      <c r="AF4" s="162"/>
+      <c r="AG4" s="162"/>
+      <c r="AH4" s="162"/>
+      <c r="AI4" s="162"/>
+      <c r="AJ4" s="162"/>
+      <c r="AK4" s="162"/>
+      <c r="AL4" s="162"/>
+      <c r="AM4" s="162"/>
+      <c r="AN4" s="162"/>
+      <c r="AO4" s="162"/>
+      <c r="AP4" s="162"/>
+      <c r="AQ4" s="162"/>
+      <c r="AR4" s="162"/>
+      <c r="AS4" s="162"/>
+      <c r="AT4" s="162"/>
+      <c r="AU4" s="162"/>
+      <c r="AV4" s="162"/>
+      <c r="AW4" s="162"/>
+      <c r="AX4" s="162"/>
+      <c r="AY4" s="162"/>
+      <c r="AZ4" s="162"/>
+      <c r="BA4" s="162"/>
+      <c r="BB4" s="162"/>
+      <c r="BC4" s="162"/>
+      <c r="BD4" s="162"/>
+      <c r="BE4" s="163"/>
+      <c r="BF4" s="161">
         <v>12</v>
       </c>
-      <c r="BG4" s="166"/>
-      <c r="BH4" s="166"/>
-      <c r="BI4" s="166"/>
-      <c r="BJ4" s="166"/>
-      <c r="BK4" s="166"/>
-      <c r="BL4" s="166"/>
-      <c r="BM4" s="166"/>
-      <c r="BN4" s="166"/>
-      <c r="BO4" s="166"/>
-      <c r="BP4" s="166"/>
-      <c r="BQ4" s="166"/>
-      <c r="BR4" s="166"/>
-      <c r="BS4" s="166"/>
-      <c r="BT4" s="166"/>
-      <c r="BU4" s="166"/>
-      <c r="BV4" s="166"/>
-      <c r="BW4" s="166"/>
-      <c r="BX4" s="166"/>
-      <c r="BY4" s="166"/>
-      <c r="BZ4" s="166"/>
-      <c r="CA4" s="166"/>
-      <c r="CB4" s="166"/>
-      <c r="CC4" s="166"/>
-      <c r="CD4" s="166"/>
-      <c r="CE4" s="166"/>
-      <c r="CF4" s="166"/>
-      <c r="CG4" s="166"/>
-      <c r="CH4" s="166"/>
-      <c r="CI4" s="166"/>
-      <c r="CJ4" s="167"/>
-      <c r="CK4" s="165">
+      <c r="BG4" s="162"/>
+      <c r="BH4" s="162"/>
+      <c r="BI4" s="162"/>
+      <c r="BJ4" s="162"/>
+      <c r="BK4" s="162"/>
+      <c r="BL4" s="162"/>
+      <c r="BM4" s="162"/>
+      <c r="BN4" s="162"/>
+      <c r="BO4" s="162"/>
+      <c r="BP4" s="162"/>
+      <c r="BQ4" s="162"/>
+      <c r="BR4" s="162"/>
+      <c r="BS4" s="162"/>
+      <c r="BT4" s="162"/>
+      <c r="BU4" s="162"/>
+      <c r="BV4" s="162"/>
+      <c r="BW4" s="162"/>
+      <c r="BX4" s="162"/>
+      <c r="BY4" s="162"/>
+      <c r="BZ4" s="162"/>
+      <c r="CA4" s="162"/>
+      <c r="CB4" s="162"/>
+      <c r="CC4" s="162"/>
+      <c r="CD4" s="162"/>
+      <c r="CE4" s="162"/>
+      <c r="CF4" s="162"/>
+      <c r="CG4" s="162"/>
+      <c r="CH4" s="162"/>
+      <c r="CI4" s="162"/>
+      <c r="CJ4" s="163"/>
+      <c r="CK4" s="161">
         <v>1</v>
       </c>
-      <c r="CL4" s="166"/>
-      <c r="CM4" s="166"/>
-      <c r="CN4" s="166"/>
-      <c r="CO4" s="166"/>
-      <c r="CP4" s="166"/>
-      <c r="CQ4" s="166"/>
-      <c r="CR4" s="166"/>
-      <c r="CS4" s="166"/>
-      <c r="CT4" s="166"/>
-      <c r="CU4" s="166"/>
-      <c r="CV4" s="166"/>
-      <c r="CW4" s="166"/>
-      <c r="CX4" s="166"/>
-      <c r="CY4" s="166"/>
-      <c r="CZ4" s="166"/>
-      <c r="DA4" s="166"/>
-      <c r="DB4" s="166"/>
-      <c r="DC4" s="166"/>
-      <c r="DD4" s="166"/>
-      <c r="DE4" s="166"/>
-      <c r="DF4" s="166"/>
-      <c r="DG4" s="166"/>
-      <c r="DH4" s="166"/>
-      <c r="DI4" s="166"/>
-      <c r="DJ4" s="166"/>
-      <c r="DK4" s="166"/>
-      <c r="DL4" s="166"/>
-      <c r="DM4" s="166"/>
-      <c r="DN4" s="166"/>
-      <c r="DO4" s="167"/>
+      <c r="CL4" s="162"/>
+      <c r="CM4" s="162"/>
+      <c r="CN4" s="162"/>
+      <c r="CO4" s="162"/>
+      <c r="CP4" s="162"/>
+      <c r="CQ4" s="162"/>
+      <c r="CR4" s="162"/>
+      <c r="CS4" s="162"/>
+      <c r="CT4" s="162"/>
+      <c r="CU4" s="162"/>
+      <c r="CV4" s="162"/>
+      <c r="CW4" s="162"/>
+      <c r="CX4" s="162"/>
+      <c r="CY4" s="162"/>
+      <c r="CZ4" s="162"/>
+      <c r="DA4" s="162"/>
+      <c r="DB4" s="162"/>
+      <c r="DC4" s="162"/>
+      <c r="DD4" s="162"/>
+      <c r="DE4" s="162"/>
+      <c r="DF4" s="162"/>
+      <c r="DG4" s="162"/>
+      <c r="DH4" s="162"/>
+      <c r="DI4" s="162"/>
+      <c r="DJ4" s="162"/>
+      <c r="DK4" s="162"/>
+      <c r="DL4" s="162"/>
+      <c r="DM4" s="162"/>
+      <c r="DN4" s="162"/>
+      <c r="DO4" s="163"/>
       <c r="DP4" s="6"/>
     </row>
     <row r="5" spans="1:120" ht="18" customHeight="1">
@@ -3380,18 +3656,18 @@
     </row>
     <row r="7" spans="1:120" ht="9.75" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="168" t="s">
+      <c r="B7" s="164" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="156"/>
-      <c r="D7" s="156"/>
-      <c r="E7" s="156"/>
-      <c r="F7" s="156"/>
-      <c r="G7" s="169"/>
-      <c r="H7" s="134" t="s">
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="152"/>
+      <c r="H7" s="166" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="134" t="s">
+      <c r="I7" s="166" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="38"/>
@@ -3446,8 +3722,8 @@
       <c r="BG7" s="13"/>
       <c r="BH7" s="13"/>
       <c r="BI7" s="13"/>
-      <c r="BJ7" s="192"/>
-      <c r="BK7" s="192"/>
+      <c r="BJ7" s="95"/>
+      <c r="BK7" s="95"/>
       <c r="BL7" s="13"/>
       <c r="BM7" s="13"/>
       <c r="BN7" s="13"/>
@@ -3508,14 +3784,14 @@
     </row>
     <row r="8" spans="1:120" ht="9.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="158"/>
-      <c r="C8" s="159"/>
-      <c r="D8" s="159"/>
-      <c r="E8" s="159"/>
-      <c r="F8" s="159"/>
-      <c r="G8" s="160"/>
-      <c r="H8" s="134"/>
-      <c r="I8" s="134"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
+      <c r="G8" s="139"/>
+      <c r="H8" s="166"/>
+      <c r="I8" s="166"/>
       <c r="J8" s="39"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
@@ -3568,8 +3844,8 @@
       <c r="BG8" s="15"/>
       <c r="BH8" s="15"/>
       <c r="BI8" s="15"/>
-      <c r="BJ8" s="193"/>
-      <c r="BK8" s="193"/>
+      <c r="BJ8" s="96"/>
+      <c r="BK8" s="96"/>
       <c r="BL8" s="15"/>
       <c r="BM8" s="15"/>
       <c r="BN8" s="15"/>
@@ -3631,15 +3907,15 @@
     <row r="9" spans="1:120" ht="9.75" customHeight="1">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
-      <c r="C9" s="170" t="s">
+      <c r="C9" s="165" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="150"/>
-      <c r="E9" s="150"/>
-      <c r="F9" s="150"/>
-      <c r="G9" s="154"/>
-      <c r="H9" s="131"/>
-      <c r="I9" s="131"/>
+      <c r="D9" s="154"/>
+      <c r="E9" s="154"/>
+      <c r="F9" s="154"/>
+      <c r="G9" s="142"/>
+      <c r="H9" s="167"/>
+      <c r="I9" s="167"/>
       <c r="J9" s="42"/>
       <c r="K9" s="42"/>
       <c r="L9" s="44"/>
@@ -3692,8 +3968,8 @@
       <c r="BG9" s="44"/>
       <c r="BH9" s="44"/>
       <c r="BI9" s="44"/>
-      <c r="BJ9" s="194"/>
-      <c r="BK9" s="194"/>
+      <c r="BJ9" s="97"/>
+      <c r="BK9" s="97"/>
       <c r="BL9" s="45"/>
       <c r="BM9" s="45"/>
       <c r="BN9" s="44"/>
@@ -3755,13 +4031,13 @@
     <row r="10" spans="1:120" ht="9.75" customHeight="1">
       <c r="A10" s="16"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="171"/>
-      <c r="D10" s="159"/>
-      <c r="E10" s="159"/>
-      <c r="F10" s="159"/>
-      <c r="G10" s="160"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="131"/>
+      <c r="C10" s="141"/>
+      <c r="D10" s="135"/>
+      <c r="E10" s="135"/>
+      <c r="F10" s="135"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="167"/>
+      <c r="I10" s="167"/>
       <c r="J10" s="46"/>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
@@ -3877,15 +4153,15 @@
     <row r="11" spans="1:120" ht="9.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="172" t="s">
+      <c r="C11" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="150"/>
-      <c r="E11" s="150"/>
-      <c r="F11" s="150"/>
-      <c r="G11" s="154"/>
-      <c r="H11" s="131"/>
-      <c r="I11" s="131"/>
+      <c r="D11" s="154"/>
+      <c r="E11" s="154"/>
+      <c r="F11" s="154"/>
+      <c r="G11" s="142"/>
+      <c r="H11" s="167"/>
+      <c r="I11" s="167"/>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
       <c r="L11" s="44"/>
@@ -3938,8 +4214,8 @@
       <c r="BG11" s="44"/>
       <c r="BH11" s="44"/>
       <c r="BI11" s="44"/>
-      <c r="BJ11" s="194"/>
-      <c r="BK11" s="194"/>
+      <c r="BJ11" s="97"/>
+      <c r="BK11" s="97"/>
       <c r="BL11" s="45"/>
       <c r="BM11" s="45"/>
       <c r="BN11" s="44"/>
@@ -4001,13 +4277,13 @@
     <row r="12" spans="1:120" ht="9.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="171"/>
-      <c r="D12" s="159"/>
-      <c r="E12" s="159"/>
-      <c r="F12" s="159"/>
-      <c r="G12" s="160"/>
-      <c r="H12" s="131"/>
-      <c r="I12" s="131"/>
+      <c r="C12" s="141"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="135"/>
+      <c r="G12" s="139"/>
+      <c r="H12" s="167"/>
+      <c r="I12" s="167"/>
       <c r="J12" s="46"/>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
@@ -4124,16 +4400,16 @@
       <c r="A13" s="1"/>
       <c r="B13" s="18"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="173" t="s">
+      <c r="D13" s="151" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="156"/>
-      <c r="F13" s="156"/>
-      <c r="G13" s="169"/>
-      <c r="H13" s="130" t="s">
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="152"/>
+      <c r="H13" s="184" t="s">
         <v>40</v>
       </c>
-      <c r="I13" s="104">
+      <c r="I13" s="112">
         <v>100</v>
       </c>
       <c r="J13" s="39"/>
@@ -4188,8 +4464,8 @@
       <c r="BG13" s="15"/>
       <c r="BH13" s="15"/>
       <c r="BI13" s="15"/>
-      <c r="BJ13" s="193"/>
-      <c r="BK13" s="193"/>
+      <c r="BJ13" s="96"/>
+      <c r="BK13" s="96"/>
       <c r="BL13" s="15"/>
       <c r="BM13" s="15"/>
       <c r="BN13" s="15"/>
@@ -4252,12 +4528,12 @@
       <c r="A14" s="1"/>
       <c r="B14" s="18"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="158"/>
-      <c r="E14" s="159"/>
-      <c r="F14" s="159"/>
-      <c r="G14" s="160"/>
-      <c r="H14" s="104"/>
-      <c r="I14" s="104"/>
+      <c r="D14" s="134"/>
+      <c r="E14" s="135"/>
+      <c r="F14" s="135"/>
+      <c r="G14" s="139"/>
+      <c r="H14" s="112"/>
+      <c r="I14" s="112"/>
       <c r="J14" s="39"/>
       <c r="K14" s="53"/>
       <c r="L14" s="15"/>
@@ -4310,8 +4586,8 @@
       <c r="BG14" s="15"/>
       <c r="BH14" s="15"/>
       <c r="BI14" s="15"/>
-      <c r="BJ14" s="193"/>
-      <c r="BK14" s="193"/>
+      <c r="BJ14" s="96"/>
+      <c r="BK14" s="96"/>
       <c r="BL14" s="15"/>
       <c r="BM14" s="15"/>
       <c r="BN14" s="15"/>
@@ -4374,16 +4650,16 @@
       <c r="A15" s="1"/>
       <c r="B15" s="18"/>
       <c r="C15" s="24"/>
-      <c r="D15" s="173" t="s">
+      <c r="D15" s="151" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="156"/>
-      <c r="F15" s="156"/>
-      <c r="G15" s="162"/>
-      <c r="H15" s="130" t="s">
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="184" t="s">
         <v>40</v>
       </c>
-      <c r="I15" s="104">
+      <c r="I15" s="112">
         <v>100</v>
       </c>
       <c r="J15" s="14"/>
@@ -4438,8 +4714,8 @@
       <c r="BG15" s="15"/>
       <c r="BH15" s="15"/>
       <c r="BI15" s="15"/>
-      <c r="BJ15" s="193"/>
-      <c r="BK15" s="193"/>
+      <c r="BJ15" s="96"/>
+      <c r="BK15" s="96"/>
       <c r="BL15" s="15"/>
       <c r="BM15" s="15"/>
       <c r="BN15" s="15"/>
@@ -4502,12 +4778,12 @@
       <c r="A16" s="1"/>
       <c r="B16" s="18"/>
       <c r="C16" s="24"/>
-      <c r="D16" s="158"/>
-      <c r="E16" s="159"/>
-      <c r="F16" s="159"/>
-      <c r="G16" s="163"/>
-      <c r="H16" s="104"/>
-      <c r="I16" s="104"/>
+      <c r="D16" s="134"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="136"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="112"/>
       <c r="J16" s="14"/>
       <c r="K16" s="53"/>
       <c r="L16" s="15"/>
@@ -4560,8 +4836,8 @@
       <c r="BG16" s="15"/>
       <c r="BH16" s="15"/>
       <c r="BI16" s="15"/>
-      <c r="BJ16" s="193"/>
-      <c r="BK16" s="193"/>
+      <c r="BJ16" s="96"/>
+      <c r="BK16" s="96"/>
       <c r="BL16" s="15"/>
       <c r="BM16" s="15"/>
       <c r="BN16" s="15"/>
@@ -4624,16 +4900,16 @@
       <c r="A17" s="1"/>
       <c r="B17" s="18"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="173" t="s">
+      <c r="D17" s="151" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="156"/>
-      <c r="F17" s="156"/>
-      <c r="G17" s="162"/>
-      <c r="H17" s="130" t="s">
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="133"/>
+      <c r="H17" s="184" t="s">
         <v>40</v>
       </c>
-      <c r="I17" s="104">
+      <c r="I17" s="112">
         <v>100</v>
       </c>
       <c r="J17" s="14"/>
@@ -4688,8 +4964,8 @@
       <c r="BG17" s="15"/>
       <c r="BH17" s="15"/>
       <c r="BI17" s="15"/>
-      <c r="BJ17" s="193"/>
-      <c r="BK17" s="193"/>
+      <c r="BJ17" s="96"/>
+      <c r="BK17" s="96"/>
       <c r="BL17" s="15"/>
       <c r="BM17" s="15"/>
       <c r="BN17" s="15"/>
@@ -4752,12 +5028,12 @@
       <c r="A18" s="1"/>
       <c r="B18" s="18"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="158"/>
-      <c r="E18" s="159"/>
-      <c r="F18" s="159"/>
-      <c r="G18" s="163"/>
-      <c r="H18" s="104"/>
-      <c r="I18" s="104"/>
+      <c r="D18" s="134"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="136"/>
+      <c r="H18" s="112"/>
+      <c r="I18" s="112"/>
       <c r="J18" s="14"/>
       <c r="K18" s="53"/>
       <c r="L18" s="15"/>
@@ -4810,8 +5086,8 @@
       <c r="BG18" s="15"/>
       <c r="BH18" s="15"/>
       <c r="BI18" s="15"/>
-      <c r="BJ18" s="193"/>
-      <c r="BK18" s="193"/>
+      <c r="BJ18" s="96"/>
+      <c r="BK18" s="96"/>
       <c r="BL18" s="15"/>
       <c r="BM18" s="15"/>
       <c r="BN18" s="15"/>
@@ -4874,16 +5150,16 @@
       <c r="A19" s="1"/>
       <c r="B19" s="18"/>
       <c r="C19" s="24"/>
-      <c r="D19" s="173" t="s">
+      <c r="D19" s="151" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="156"/>
-      <c r="F19" s="156"/>
-      <c r="G19" s="162"/>
-      <c r="H19" s="130" t="s">
+      <c r="E19" s="132"/>
+      <c r="F19" s="132"/>
+      <c r="G19" s="133"/>
+      <c r="H19" s="184" t="s">
         <v>40</v>
       </c>
-      <c r="I19" s="104">
+      <c r="I19" s="112">
         <v>100</v>
       </c>
       <c r="J19" s="14"/>
@@ -4938,8 +5214,8 @@
       <c r="BG19" s="15"/>
       <c r="BH19" s="15"/>
       <c r="BI19" s="15"/>
-      <c r="BJ19" s="193"/>
-      <c r="BK19" s="193"/>
+      <c r="BJ19" s="96"/>
+      <c r="BK19" s="96"/>
       <c r="BL19" s="15"/>
       <c r="BM19" s="15"/>
       <c r="BN19" s="15"/>
@@ -5002,12 +5278,12 @@
       <c r="A20" s="1"/>
       <c r="B20" s="18"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="158"/>
-      <c r="E20" s="159"/>
-      <c r="F20" s="159"/>
-      <c r="G20" s="163"/>
-      <c r="H20" s="104"/>
-      <c r="I20" s="104"/>
+      <c r="D20" s="134"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="112"/>
+      <c r="I20" s="112"/>
       <c r="J20" s="26"/>
       <c r="K20" s="54"/>
       <c r="L20" s="27"/>
@@ -5060,8 +5336,8 @@
       <c r="BG20" s="27"/>
       <c r="BH20" s="27"/>
       <c r="BI20" s="27"/>
-      <c r="BJ20" s="195"/>
-      <c r="BK20" s="195"/>
+      <c r="BJ20" s="98"/>
+      <c r="BK20" s="98"/>
       <c r="BL20" s="27"/>
       <c r="BM20" s="27"/>
       <c r="BN20" s="27"/>
@@ -5123,15 +5399,15 @@
     <row r="21" spans="1:120" ht="9.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="18"/>
-      <c r="C21" s="172" t="s">
+      <c r="C21" s="153" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="150"/>
-      <c r="E21" s="150"/>
-      <c r="F21" s="150"/>
-      <c r="G21" s="151"/>
-      <c r="H21" s="131"/>
-      <c r="I21" s="131"/>
+      <c r="D21" s="154"/>
+      <c r="E21" s="154"/>
+      <c r="F21" s="154"/>
+      <c r="G21" s="155"/>
+      <c r="H21" s="167"/>
+      <c r="I21" s="167"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="44"/>
@@ -5184,8 +5460,8 @@
       <c r="BG21" s="44"/>
       <c r="BH21" s="44"/>
       <c r="BI21" s="44"/>
-      <c r="BJ21" s="194"/>
-      <c r="BK21" s="194"/>
+      <c r="BJ21" s="97"/>
+      <c r="BK21" s="97"/>
       <c r="BL21" s="45"/>
       <c r="BM21" s="45"/>
       <c r="BN21" s="44"/>
@@ -5247,13 +5523,13 @@
     <row r="22" spans="1:120" ht="9.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="18"/>
-      <c r="C22" s="152"/>
-      <c r="D22" s="153"/>
-      <c r="E22" s="153"/>
-      <c r="F22" s="153"/>
-      <c r="G22" s="154"/>
-      <c r="H22" s="131"/>
-      <c r="I22" s="131"/>
+      <c r="C22" s="156"/>
+      <c r="D22" s="157"/>
+      <c r="E22" s="157"/>
+      <c r="F22" s="157"/>
+      <c r="G22" s="142"/>
+      <c r="H22" s="167"/>
+      <c r="I22" s="167"/>
       <c r="J22" s="46"/>
       <c r="K22" s="47"/>
       <c r="L22" s="47"/>
@@ -5370,16 +5646,16 @@
       <c r="A23" s="1"/>
       <c r="B23" s="28"/>
       <c r="C23" s="29"/>
-      <c r="D23" s="174" t="s">
+      <c r="D23" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="156"/>
-      <c r="F23" s="156"/>
-      <c r="G23" s="162"/>
-      <c r="H23" s="130" t="s">
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="184" t="s">
         <v>46</v>
       </c>
-      <c r="I23" s="104">
+      <c r="I23" s="112">
         <v>100</v>
       </c>
       <c r="J23" s="14"/>
@@ -5434,8 +5710,8 @@
       <c r="BG23" s="15"/>
       <c r="BH23" s="15"/>
       <c r="BI23" s="15"/>
-      <c r="BJ23" s="193"/>
-      <c r="BK23" s="193"/>
+      <c r="BJ23" s="96"/>
+      <c r="BK23" s="96"/>
       <c r="BL23" s="15"/>
       <c r="BM23" s="15"/>
       <c r="BN23" s="15"/>
@@ -5498,12 +5774,12 @@
       <c r="A24" s="1"/>
       <c r="B24" s="18"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="158"/>
-      <c r="E24" s="159"/>
-      <c r="F24" s="159"/>
-      <c r="G24" s="163"/>
-      <c r="H24" s="104"/>
-      <c r="I24" s="104"/>
+      <c r="D24" s="134"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="136"/>
+      <c r="H24" s="112"/>
+      <c r="I24" s="112"/>
       <c r="J24" s="14"/>
       <c r="K24" s="15"/>
       <c r="L24" s="53"/>
@@ -5556,8 +5832,8 @@
       <c r="BG24" s="15"/>
       <c r="BH24" s="15"/>
       <c r="BI24" s="15"/>
-      <c r="BJ24" s="193"/>
-      <c r="BK24" s="193"/>
+      <c r="BJ24" s="96"/>
+      <c r="BK24" s="96"/>
       <c r="BL24" s="15"/>
       <c r="BM24" s="15"/>
       <c r="BN24" s="15"/>
@@ -5619,15 +5895,15 @@
     <row r="25" spans="1:120" ht="9.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="18"/>
-      <c r="C25" s="172" t="s">
+      <c r="C25" s="153" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="150"/>
-      <c r="E25" s="150"/>
-      <c r="F25" s="150"/>
-      <c r="G25" s="151"/>
-      <c r="H25" s="131"/>
-      <c r="I25" s="131"/>
+      <c r="D25" s="154"/>
+      <c r="E25" s="154"/>
+      <c r="F25" s="154"/>
+      <c r="G25" s="155"/>
+      <c r="H25" s="167"/>
+      <c r="I25" s="167"/>
       <c r="J25" s="42"/>
       <c r="K25" s="42"/>
       <c r="L25" s="44"/>
@@ -5680,8 +5956,8 @@
       <c r="BG25" s="44"/>
       <c r="BH25" s="44"/>
       <c r="BI25" s="44"/>
-      <c r="BJ25" s="194"/>
-      <c r="BK25" s="194"/>
+      <c r="BJ25" s="97"/>
+      <c r="BK25" s="97"/>
       <c r="BL25" s="45"/>
       <c r="BM25" s="45"/>
       <c r="BN25" s="44"/>
@@ -5743,13 +6019,13 @@
     <row r="26" spans="1:120" ht="9.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="18"/>
-      <c r="C26" s="171"/>
-      <c r="D26" s="159"/>
-      <c r="E26" s="159"/>
-      <c r="F26" s="159"/>
-      <c r="G26" s="160"/>
-      <c r="H26" s="131"/>
-      <c r="I26" s="131"/>
+      <c r="C26" s="141"/>
+      <c r="D26" s="135"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="135"/>
+      <c r="G26" s="139"/>
+      <c r="H26" s="167"/>
+      <c r="I26" s="167"/>
       <c r="J26" s="46"/>
       <c r="K26" s="47"/>
       <c r="L26" s="47"/>
@@ -5866,16 +6142,16 @@
       <c r="A27" s="1"/>
       <c r="B27" s="28"/>
       <c r="C27" s="29"/>
-      <c r="D27" s="174" t="s">
+      <c r="D27" s="158" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="156"/>
-      <c r="F27" s="156"/>
-      <c r="G27" s="162"/>
-      <c r="H27" s="130" t="s">
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="184" t="s">
         <v>44</v>
       </c>
-      <c r="I27" s="104">
+      <c r="I27" s="112">
         <v>100</v>
       </c>
       <c r="J27" s="14"/>
@@ -5930,8 +6206,8 @@
       <c r="BG27" s="15"/>
       <c r="BH27" s="15"/>
       <c r="BI27" s="15"/>
-      <c r="BJ27" s="193"/>
-      <c r="BK27" s="193"/>
+      <c r="BJ27" s="96"/>
+      <c r="BK27" s="96"/>
       <c r="BL27" s="15"/>
       <c r="BM27" s="15"/>
       <c r="BN27" s="15"/>
@@ -5994,12 +6270,12 @@
       <c r="A28" s="1"/>
       <c r="B28" s="28"/>
       <c r="C28" s="30"/>
-      <c r="D28" s="158"/>
-      <c r="E28" s="159"/>
-      <c r="F28" s="159"/>
-      <c r="G28" s="163"/>
-      <c r="H28" s="104"/>
-      <c r="I28" s="104"/>
+      <c r="D28" s="134"/>
+      <c r="E28" s="135"/>
+      <c r="F28" s="135"/>
+      <c r="G28" s="136"/>
+      <c r="H28" s="112"/>
+      <c r="I28" s="112"/>
       <c r="J28" s="14"/>
       <c r="K28" s="15"/>
       <c r="L28" s="15"/>
@@ -6052,8 +6328,8 @@
       <c r="BG28" s="15"/>
       <c r="BH28" s="15"/>
       <c r="BI28" s="15"/>
-      <c r="BJ28" s="193"/>
-      <c r="BK28" s="193"/>
+      <c r="BJ28" s="96"/>
+      <c r="BK28" s="96"/>
       <c r="BL28" s="15"/>
       <c r="BM28" s="15"/>
       <c r="BN28" s="15"/>
@@ -6116,16 +6392,16 @@
       <c r="A29" s="1"/>
       <c r="B29" s="28"/>
       <c r="C29" s="30"/>
-      <c r="D29" s="175" t="s">
+      <c r="D29" s="159" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="176"/>
-      <c r="F29" s="176"/>
-      <c r="G29" s="176"/>
-      <c r="H29" s="130" t="s">
+      <c r="E29" s="160"/>
+      <c r="F29" s="160"/>
+      <c r="G29" s="160"/>
+      <c r="H29" s="184" t="s">
         <v>44</v>
       </c>
-      <c r="I29" s="104">
+      <c r="I29" s="112">
         <v>100</v>
       </c>
       <c r="J29" s="14"/>
@@ -6180,8 +6456,8 @@
       <c r="BG29" s="15"/>
       <c r="BH29" s="15"/>
       <c r="BI29" s="15"/>
-      <c r="BJ29" s="193"/>
-      <c r="BK29" s="193"/>
+      <c r="BJ29" s="96"/>
+      <c r="BK29" s="96"/>
       <c r="BL29" s="15"/>
       <c r="BM29" s="15"/>
       <c r="BN29" s="15"/>
@@ -6244,12 +6520,12 @@
       <c r="A30" s="1"/>
       <c r="B30" s="28"/>
       <c r="C30" s="31"/>
-      <c r="D30" s="158"/>
-      <c r="E30" s="159"/>
-      <c r="F30" s="159"/>
-      <c r="G30" s="159"/>
-      <c r="H30" s="104"/>
-      <c r="I30" s="104"/>
+      <c r="D30" s="134"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="135"/>
+      <c r="G30" s="135"/>
+      <c r="H30" s="112"/>
+      <c r="I30" s="112"/>
       <c r="J30" s="26"/>
       <c r="K30" s="27"/>
       <c r="L30" s="27"/>
@@ -6302,8 +6578,8 @@
       <c r="BG30" s="27"/>
       <c r="BH30" s="27"/>
       <c r="BI30" s="27"/>
-      <c r="BJ30" s="195"/>
-      <c r="BK30" s="195"/>
+      <c r="BJ30" s="98"/>
+      <c r="BK30" s="98"/>
       <c r="BL30" s="27"/>
       <c r="BM30" s="27"/>
       <c r="BN30" s="27"/>
@@ -6365,15 +6641,15 @@
     <row r="31" spans="1:120" ht="9.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="18"/>
-      <c r="C31" s="149" t="s">
+      <c r="C31" s="179" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="150"/>
-      <c r="E31" s="150"/>
-      <c r="F31" s="150"/>
-      <c r="G31" s="151"/>
-      <c r="H31" s="131"/>
-      <c r="I31" s="131"/>
+      <c r="D31" s="154"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="154"/>
+      <c r="G31" s="155"/>
+      <c r="H31" s="167"/>
+      <c r="I31" s="167"/>
       <c r="J31" s="42"/>
       <c r="K31" s="43"/>
       <c r="L31" s="44"/>
@@ -6426,8 +6702,8 @@
       <c r="BG31" s="44"/>
       <c r="BH31" s="44"/>
       <c r="BI31" s="44"/>
-      <c r="BJ31" s="194"/>
-      <c r="BK31" s="194"/>
+      <c r="BJ31" s="97"/>
+      <c r="BK31" s="97"/>
       <c r="BL31" s="45"/>
       <c r="BM31" s="45"/>
       <c r="BN31" s="44"/>
@@ -6489,13 +6765,13 @@
     <row r="32" spans="1:120" ht="9.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="18"/>
-      <c r="C32" s="152"/>
-      <c r="D32" s="153"/>
-      <c r="E32" s="153"/>
-      <c r="F32" s="153"/>
-      <c r="G32" s="154"/>
-      <c r="H32" s="131"/>
-      <c r="I32" s="131"/>
+      <c r="C32" s="156"/>
+      <c r="D32" s="157"/>
+      <c r="E32" s="157"/>
+      <c r="F32" s="157"/>
+      <c r="G32" s="142"/>
+      <c r="H32" s="167"/>
+      <c r="I32" s="167"/>
       <c r="J32" s="46"/>
       <c r="K32" s="47"/>
       <c r="L32" s="47"/>
@@ -6612,14 +6888,14 @@
       <c r="A33" s="1"/>
       <c r="B33" s="18"/>
       <c r="C33" s="32"/>
-      <c r="D33" s="155" t="s">
+      <c r="D33" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="156"/>
-      <c r="F33" s="156"/>
-      <c r="G33" s="157"/>
-      <c r="H33" s="131"/>
-      <c r="I33" s="131"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="138"/>
+      <c r="H33" s="167"/>
+      <c r="I33" s="167"/>
       <c r="J33" s="50"/>
       <c r="K33" s="51"/>
       <c r="L33" s="51"/>
@@ -6672,8 +6948,8 @@
       <c r="BG33" s="51"/>
       <c r="BH33" s="51"/>
       <c r="BI33" s="51"/>
-      <c r="BJ33" s="196"/>
-      <c r="BK33" s="196"/>
+      <c r="BJ33" s="99"/>
+      <c r="BK33" s="99"/>
       <c r="BL33" s="51"/>
       <c r="BM33" s="51"/>
       <c r="BN33" s="51"/>
@@ -6736,12 +7012,12 @@
       <c r="A34" s="1"/>
       <c r="B34" s="18"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="158"/>
-      <c r="E34" s="159"/>
-      <c r="F34" s="159"/>
-      <c r="G34" s="160"/>
-      <c r="H34" s="131"/>
-      <c r="I34" s="131"/>
+      <c r="D34" s="134"/>
+      <c r="E34" s="135"/>
+      <c r="F34" s="135"/>
+      <c r="G34" s="139"/>
+      <c r="H34" s="167"/>
+      <c r="I34" s="167"/>
       <c r="J34" s="52"/>
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
@@ -6794,8 +7070,8 @@
       <c r="BG34" s="49"/>
       <c r="BH34" s="49"/>
       <c r="BI34" s="49"/>
-      <c r="BJ34" s="193"/>
-      <c r="BK34" s="193"/>
+      <c r="BJ34" s="96"/>
+      <c r="BK34" s="96"/>
       <c r="BL34" s="49"/>
       <c r="BM34" s="49"/>
       <c r="BN34" s="49"/>
@@ -6859,15 +7135,15 @@
       <c r="B35" s="18"/>
       <c r="C35" s="1"/>
       <c r="D35" s="33"/>
-      <c r="E35" s="161" t="s">
+      <c r="E35" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="156"/>
-      <c r="G35" s="162"/>
-      <c r="H35" s="130" t="s">
+      <c r="F35" s="132"/>
+      <c r="G35" s="133"/>
+      <c r="H35" s="184" t="s">
         <v>45</v>
       </c>
-      <c r="I35" s="104">
+      <c r="I35" s="112">
         <v>100</v>
       </c>
       <c r="J35" s="14"/>
@@ -6922,8 +7198,8 @@
       <c r="BG35" s="15"/>
       <c r="BH35" s="15"/>
       <c r="BI35" s="15"/>
-      <c r="BJ35" s="193"/>
-      <c r="BK35" s="193"/>
+      <c r="BJ35" s="96"/>
+      <c r="BK35" s="96"/>
       <c r="BL35" s="15"/>
       <c r="BM35" s="15"/>
       <c r="BN35" s="15"/>
@@ -6987,11 +7263,11 @@
       <c r="B36" s="18"/>
       <c r="C36" s="1"/>
       <c r="D36" s="34"/>
-      <c r="E36" s="158"/>
-      <c r="F36" s="159"/>
-      <c r="G36" s="163"/>
-      <c r="H36" s="104"/>
-      <c r="I36" s="104"/>
+      <c r="E36" s="134"/>
+      <c r="F36" s="135"/>
+      <c r="G36" s="136"/>
+      <c r="H36" s="112"/>
+      <c r="I36" s="112"/>
       <c r="J36" s="14"/>
       <c r="K36" s="15"/>
       <c r="L36" s="15"/>
@@ -7044,8 +7320,8 @@
       <c r="BG36" s="15"/>
       <c r="BH36" s="15"/>
       <c r="BI36" s="15"/>
-      <c r="BJ36" s="193"/>
-      <c r="BK36" s="193"/>
+      <c r="BJ36" s="96"/>
+      <c r="BK36" s="96"/>
       <c r="BL36" s="15"/>
       <c r="BM36" s="15"/>
       <c r="BN36" s="15"/>
@@ -7109,15 +7385,15 @@
       <c r="B37" s="18"/>
       <c r="C37" s="1"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="161" t="s">
+      <c r="E37" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F37" s="156"/>
-      <c r="G37" s="162"/>
-      <c r="H37" s="130" t="s">
+      <c r="F37" s="132"/>
+      <c r="G37" s="133"/>
+      <c r="H37" s="184" t="s">
         <v>44</v>
       </c>
-      <c r="I37" s="104">
+      <c r="I37" s="112">
         <v>100</v>
       </c>
       <c r="J37" s="14"/>
@@ -7172,8 +7448,8 @@
       <c r="BG37" s="15"/>
       <c r="BH37" s="15"/>
       <c r="BI37" s="15"/>
-      <c r="BJ37" s="193"/>
-      <c r="BK37" s="193"/>
+      <c r="BJ37" s="96"/>
+      <c r="BK37" s="96"/>
       <c r="BL37" s="15"/>
       <c r="BM37" s="15"/>
       <c r="BN37" s="15"/>
@@ -7237,11 +7513,11 @@
       <c r="B38" s="18"/>
       <c r="C38" s="1"/>
       <c r="D38" s="35"/>
-      <c r="E38" s="158"/>
-      <c r="F38" s="159"/>
-      <c r="G38" s="163"/>
-      <c r="H38" s="104"/>
-      <c r="I38" s="104"/>
+      <c r="E38" s="134"/>
+      <c r="F38" s="135"/>
+      <c r="G38" s="136"/>
+      <c r="H38" s="112"/>
+      <c r="I38" s="112"/>
       <c r="J38" s="26"/>
       <c r="K38" s="27"/>
       <c r="L38" s="27"/>
@@ -7294,8 +7570,8 @@
       <c r="BG38" s="27"/>
       <c r="BH38" s="27"/>
       <c r="BI38" s="27"/>
-      <c r="BJ38" s="195"/>
-      <c r="BK38" s="195"/>
+      <c r="BJ38" s="98"/>
+      <c r="BK38" s="98"/>
       <c r="BL38" s="27"/>
       <c r="BM38" s="27"/>
       <c r="BN38" s="27"/>
@@ -7358,14 +7634,14 @@
       <c r="A39" s="1"/>
       <c r="B39" s="18"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="164" t="s">
+      <c r="D39" s="180" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="150"/>
-      <c r="F39" s="150"/>
-      <c r="G39" s="151"/>
-      <c r="H39" s="131"/>
-      <c r="I39" s="131"/>
+      <c r="E39" s="154"/>
+      <c r="F39" s="154"/>
+      <c r="G39" s="155"/>
+      <c r="H39" s="167"/>
+      <c r="I39" s="167"/>
       <c r="J39" s="50"/>
       <c r="K39" s="51"/>
       <c r="L39" s="51"/>
@@ -7418,8 +7694,8 @@
       <c r="BG39" s="51"/>
       <c r="BH39" s="51"/>
       <c r="BI39" s="51"/>
-      <c r="BJ39" s="196"/>
-      <c r="BK39" s="196"/>
+      <c r="BJ39" s="99"/>
+      <c r="BK39" s="99"/>
       <c r="BL39" s="51"/>
       <c r="BM39" s="51"/>
       <c r="BN39" s="51"/>
@@ -7482,12 +7758,12 @@
       <c r="A40" s="1"/>
       <c r="B40" s="18"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="158"/>
-      <c r="E40" s="159"/>
-      <c r="F40" s="159"/>
-      <c r="G40" s="160"/>
-      <c r="H40" s="131"/>
-      <c r="I40" s="131"/>
+      <c r="D40" s="134"/>
+      <c r="E40" s="135"/>
+      <c r="F40" s="135"/>
+      <c r="G40" s="139"/>
+      <c r="H40" s="167"/>
+      <c r="I40" s="167"/>
       <c r="J40" s="52"/>
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
@@ -7540,8 +7816,8 @@
       <c r="BG40" s="49"/>
       <c r="BH40" s="49"/>
       <c r="BI40" s="49"/>
-      <c r="BJ40" s="193"/>
-      <c r="BK40" s="193"/>
+      <c r="BJ40" s="96"/>
+      <c r="BK40" s="96"/>
       <c r="BL40" s="49"/>
       <c r="BM40" s="49"/>
       <c r="BN40" s="49"/>
@@ -7605,15 +7881,15 @@
       <c r="B41" s="18"/>
       <c r="C41" s="1"/>
       <c r="D41" s="33"/>
-      <c r="E41" s="161" t="s">
+      <c r="E41" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="156"/>
-      <c r="G41" s="162"/>
-      <c r="H41" s="130" t="s">
+      <c r="F41" s="132"/>
+      <c r="G41" s="133"/>
+      <c r="H41" s="184" t="s">
         <v>43</v>
       </c>
-      <c r="I41" s="104">
+      <c r="I41" s="112">
         <v>100</v>
       </c>
       <c r="J41" s="14"/>
@@ -7668,8 +7944,8 @@
       <c r="BG41" s="15"/>
       <c r="BH41" s="15"/>
       <c r="BI41" s="15"/>
-      <c r="BJ41" s="193"/>
-      <c r="BK41" s="193"/>
+      <c r="BJ41" s="96"/>
+      <c r="BK41" s="96"/>
       <c r="BL41" s="15"/>
       <c r="BM41" s="15"/>
       <c r="BN41" s="15"/>
@@ -7733,11 +8009,11 @@
       <c r="B42" s="18"/>
       <c r="C42" s="1"/>
       <c r="D42" s="34"/>
-      <c r="E42" s="158"/>
-      <c r="F42" s="159"/>
-      <c r="G42" s="163"/>
-      <c r="H42" s="104"/>
-      <c r="I42" s="104"/>
+      <c r="E42" s="134"/>
+      <c r="F42" s="135"/>
+      <c r="G42" s="136"/>
+      <c r="H42" s="112"/>
+      <c r="I42" s="112"/>
       <c r="J42" s="14"/>
       <c r="K42" s="15"/>
       <c r="L42" s="15"/>
@@ -7790,8 +8066,8 @@
       <c r="BG42" s="15"/>
       <c r="BH42" s="15"/>
       <c r="BI42" s="15"/>
-      <c r="BJ42" s="193"/>
-      <c r="BK42" s="193"/>
+      <c r="BJ42" s="96"/>
+      <c r="BK42" s="96"/>
       <c r="BL42" s="15"/>
       <c r="BM42" s="15"/>
       <c r="BN42" s="15"/>
@@ -7855,15 +8131,15 @@
       <c r="B43" s="18"/>
       <c r="C43" s="1"/>
       <c r="D43" s="34"/>
-      <c r="E43" s="161" t="s">
+      <c r="E43" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="156"/>
-      <c r="G43" s="162"/>
-      <c r="H43" s="130" t="s">
+      <c r="F43" s="132"/>
+      <c r="G43" s="133"/>
+      <c r="H43" s="184" t="s">
         <v>43</v>
       </c>
-      <c r="I43" s="104">
+      <c r="I43" s="112">
         <v>100</v>
       </c>
       <c r="J43" s="14"/>
@@ -7918,8 +8194,8 @@
       <c r="BG43" s="15"/>
       <c r="BH43" s="15"/>
       <c r="BI43" s="15"/>
-      <c r="BJ43" s="193"/>
-      <c r="BK43" s="193"/>
+      <c r="BJ43" s="96"/>
+      <c r="BK43" s="96"/>
       <c r="BL43" s="15"/>
       <c r="BM43" s="15"/>
       <c r="BN43" s="15"/>
@@ -7983,11 +8259,11 @@
       <c r="B44" s="18"/>
       <c r="C44" s="1"/>
       <c r="D44" s="34"/>
-      <c r="E44" s="158"/>
-      <c r="F44" s="159"/>
-      <c r="G44" s="163"/>
-      <c r="H44" s="104"/>
-      <c r="I44" s="104"/>
+      <c r="E44" s="134"/>
+      <c r="F44" s="135"/>
+      <c r="G44" s="136"/>
+      <c r="H44" s="112"/>
+      <c r="I44" s="112"/>
       <c r="J44" s="14"/>
       <c r="K44" s="15"/>
       <c r="L44" s="15"/>
@@ -8040,8 +8316,8 @@
       <c r="BG44" s="15"/>
       <c r="BH44" s="15"/>
       <c r="BI44" s="15"/>
-      <c r="BJ44" s="193"/>
-      <c r="BK44" s="193"/>
+      <c r="BJ44" s="96"/>
+      <c r="BK44" s="96"/>
       <c r="BL44" s="15"/>
       <c r="BM44" s="15"/>
       <c r="BN44" s="15"/>
@@ -8105,15 +8381,15 @@
       <c r="B45" s="18"/>
       <c r="C45" s="1"/>
       <c r="D45" s="34"/>
-      <c r="E45" s="161" t="s">
+      <c r="E45" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="156"/>
-      <c r="G45" s="162"/>
-      <c r="H45" s="130" t="s">
+      <c r="F45" s="132"/>
+      <c r="G45" s="133"/>
+      <c r="H45" s="184" t="s">
         <v>42</v>
       </c>
-      <c r="I45" s="104">
+      <c r="I45" s="112">
         <v>100</v>
       </c>
       <c r="J45" s="14"/>
@@ -8168,8 +8444,8 @@
       <c r="BG45" s="15"/>
       <c r="BH45" s="15"/>
       <c r="BI45" s="15"/>
-      <c r="BJ45" s="193"/>
-      <c r="BK45" s="193"/>
+      <c r="BJ45" s="96"/>
+      <c r="BK45" s="96"/>
       <c r="BL45" s="15"/>
       <c r="BM45" s="15"/>
       <c r="BN45" s="15"/>
@@ -8233,11 +8509,11 @@
       <c r="B46" s="18"/>
       <c r="C46" s="1"/>
       <c r="D46" s="34"/>
-      <c r="E46" s="158"/>
-      <c r="F46" s="159"/>
-      <c r="G46" s="163"/>
-      <c r="H46" s="104"/>
-      <c r="I46" s="104"/>
+      <c r="E46" s="134"/>
+      <c r="F46" s="135"/>
+      <c r="G46" s="136"/>
+      <c r="H46" s="112"/>
+      <c r="I46" s="112"/>
       <c r="J46" s="14"/>
       <c r="K46" s="15"/>
       <c r="L46" s="15"/>
@@ -8290,8 +8566,8 @@
       <c r="BG46" s="15"/>
       <c r="BH46" s="15"/>
       <c r="BI46" s="15"/>
-      <c r="BJ46" s="193"/>
-      <c r="BK46" s="193"/>
+      <c r="BJ46" s="96"/>
+      <c r="BK46" s="96"/>
       <c r="BL46" s="15"/>
       <c r="BM46" s="15"/>
       <c r="BN46" s="15"/>
@@ -8355,15 +8631,15 @@
       <c r="B47" s="18"/>
       <c r="C47" s="1"/>
       <c r="D47" s="34"/>
-      <c r="E47" s="161" t="s">
+      <c r="E47" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="F47" s="156"/>
-      <c r="G47" s="162"/>
-      <c r="H47" s="130" t="s">
+      <c r="F47" s="132"/>
+      <c r="G47" s="133"/>
+      <c r="H47" s="184" t="s">
         <v>41</v>
       </c>
-      <c r="I47" s="104">
+      <c r="I47" s="112">
         <v>100</v>
       </c>
       <c r="J47" s="14"/>
@@ -8418,8 +8694,8 @@
       <c r="BG47" s="15"/>
       <c r="BH47" s="15"/>
       <c r="BI47" s="15"/>
-      <c r="BJ47" s="193"/>
-      <c r="BK47" s="193"/>
+      <c r="BJ47" s="96"/>
+      <c r="BK47" s="96"/>
       <c r="BL47" s="15"/>
       <c r="BM47" s="15"/>
       <c r="BN47" s="15"/>
@@ -8483,11 +8759,11 @@
       <c r="B48" s="18"/>
       <c r="C48" s="1"/>
       <c r="D48" s="34"/>
-      <c r="E48" s="158"/>
-      <c r="F48" s="159"/>
-      <c r="G48" s="163"/>
-      <c r="H48" s="104"/>
-      <c r="I48" s="104"/>
+      <c r="E48" s="134"/>
+      <c r="F48" s="135"/>
+      <c r="G48" s="136"/>
+      <c r="H48" s="112"/>
+      <c r="I48" s="112"/>
       <c r="J48" s="14"/>
       <c r="K48" s="15"/>
       <c r="L48" s="15"/>
@@ -8540,8 +8816,8 @@
       <c r="BG48" s="15"/>
       <c r="BH48" s="15"/>
       <c r="BI48" s="15"/>
-      <c r="BJ48" s="193"/>
-      <c r="BK48" s="193"/>
+      <c r="BJ48" s="96"/>
+      <c r="BK48" s="96"/>
       <c r="BL48" s="15"/>
       <c r="BM48" s="15"/>
       <c r="BN48" s="15"/>
@@ -8605,15 +8881,15 @@
       <c r="B49" s="18"/>
       <c r="C49" s="1"/>
       <c r="D49" s="34"/>
-      <c r="E49" s="161" t="s">
+      <c r="E49" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="156"/>
-      <c r="G49" s="162"/>
-      <c r="H49" s="130" t="s">
+      <c r="F49" s="132"/>
+      <c r="G49" s="133"/>
+      <c r="H49" s="184" t="s">
         <v>50</v>
       </c>
-      <c r="I49" s="104">
+      <c r="I49" s="112">
         <v>100</v>
       </c>
       <c r="J49" s="14"/>
@@ -8668,8 +8944,8 @@
       <c r="BG49" s="15"/>
       <c r="BH49" s="15"/>
       <c r="BI49" s="15"/>
-      <c r="BJ49" s="193"/>
-      <c r="BK49" s="193"/>
+      <c r="BJ49" s="96"/>
+      <c r="BK49" s="96"/>
       <c r="BL49" s="15"/>
       <c r="BM49" s="15"/>
       <c r="BN49" s="15"/>
@@ -8733,11 +9009,11 @@
       <c r="B50" s="18"/>
       <c r="C50" s="1"/>
       <c r="D50" s="34"/>
-      <c r="E50" s="158"/>
-      <c r="F50" s="159"/>
-      <c r="G50" s="163"/>
-      <c r="H50" s="104"/>
-      <c r="I50" s="104"/>
+      <c r="E50" s="134"/>
+      <c r="F50" s="135"/>
+      <c r="G50" s="136"/>
+      <c r="H50" s="112"/>
+      <c r="I50" s="112"/>
       <c r="J50" s="14"/>
       <c r="K50" s="15"/>
       <c r="L50" s="15"/>
@@ -8790,8 +9066,8 @@
       <c r="BG50" s="15"/>
       <c r="BH50" s="15"/>
       <c r="BI50" s="15"/>
-      <c r="BJ50" s="193"/>
-      <c r="BK50" s="193"/>
+      <c r="BJ50" s="96"/>
+      <c r="BK50" s="96"/>
       <c r="BL50" s="15"/>
       <c r="BM50" s="15"/>
       <c r="BN50" s="15"/>
@@ -8855,15 +9131,15 @@
       <c r="B51" s="18"/>
       <c r="C51" s="1"/>
       <c r="D51" s="34"/>
-      <c r="E51" s="161" t="s">
+      <c r="E51" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="156"/>
-      <c r="G51" s="162"/>
-      <c r="H51" s="130" t="s">
+      <c r="F51" s="132"/>
+      <c r="G51" s="133"/>
+      <c r="H51" s="184" t="s">
         <v>47</v>
       </c>
-      <c r="I51" s="104">
+      <c r="I51" s="112">
         <v>100</v>
       </c>
       <c r="J51" s="14"/>
@@ -8918,8 +9194,8 @@
       <c r="BG51" s="15"/>
       <c r="BH51" s="15"/>
       <c r="BI51" s="15"/>
-      <c r="BJ51" s="193"/>
-      <c r="BK51" s="193"/>
+      <c r="BJ51" s="96"/>
+      <c r="BK51" s="96"/>
       <c r="BL51" s="15"/>
       <c r="BM51" s="15"/>
       <c r="BN51" s="15"/>
@@ -8983,11 +9259,11 @@
       <c r="B52" s="18"/>
       <c r="C52" s="1"/>
       <c r="D52" s="34"/>
-      <c r="E52" s="158"/>
-      <c r="F52" s="159"/>
-      <c r="G52" s="163"/>
-      <c r="H52" s="104"/>
-      <c r="I52" s="104"/>
+      <c r="E52" s="134"/>
+      <c r="F52" s="135"/>
+      <c r="G52" s="136"/>
+      <c r="H52" s="112"/>
+      <c r="I52" s="112"/>
       <c r="J52" s="26"/>
       <c r="K52" s="27"/>
       <c r="L52" s="27"/>
@@ -9040,8 +9316,8 @@
       <c r="BG52" s="27"/>
       <c r="BH52" s="27"/>
       <c r="BI52" s="27"/>
-      <c r="BJ52" s="195"/>
-      <c r="BK52" s="195"/>
+      <c r="BJ52" s="98"/>
+      <c r="BK52" s="98"/>
       <c r="BL52" s="27"/>
       <c r="BM52" s="27"/>
       <c r="BN52" s="27"/>
@@ -9104,14 +9380,14 @@
       <c r="A53" s="1"/>
       <c r="B53" s="18"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="155" t="s">
+      <c r="D53" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="156"/>
-      <c r="F53" s="156"/>
-      <c r="G53" s="157"/>
-      <c r="H53" s="131"/>
-      <c r="I53" s="131"/>
+      <c r="E53" s="132"/>
+      <c r="F53" s="132"/>
+      <c r="G53" s="138"/>
+      <c r="H53" s="167"/>
+      <c r="I53" s="167"/>
       <c r="J53" s="50"/>
       <c r="K53" s="51"/>
       <c r="L53" s="51"/>
@@ -9164,8 +9440,8 @@
       <c r="BG53" s="51"/>
       <c r="BH53" s="51"/>
       <c r="BI53" s="51"/>
-      <c r="BJ53" s="196"/>
-      <c r="BK53" s="196"/>
+      <c r="BJ53" s="99"/>
+      <c r="BK53" s="99"/>
       <c r="BL53" s="51"/>
       <c r="BM53" s="51"/>
       <c r="BN53" s="51"/>
@@ -9228,12 +9504,12 @@
       <c r="A54" s="1"/>
       <c r="B54" s="18"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="158"/>
-      <c r="E54" s="159"/>
-      <c r="F54" s="159"/>
-      <c r="G54" s="160"/>
-      <c r="H54" s="131"/>
-      <c r="I54" s="131"/>
+      <c r="D54" s="134"/>
+      <c r="E54" s="135"/>
+      <c r="F54" s="135"/>
+      <c r="G54" s="139"/>
+      <c r="H54" s="167"/>
+      <c r="I54" s="167"/>
       <c r="J54" s="52"/>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -9286,8 +9562,8 @@
       <c r="BG54" s="49"/>
       <c r="BH54" s="49"/>
       <c r="BI54" s="49"/>
-      <c r="BJ54" s="193"/>
-      <c r="BK54" s="193"/>
+      <c r="BJ54" s="96"/>
+      <c r="BK54" s="96"/>
       <c r="BL54" s="49"/>
       <c r="BM54" s="49"/>
       <c r="BN54" s="49"/>
@@ -9351,15 +9627,15 @@
       <c r="B55" s="18"/>
       <c r="C55" s="1"/>
       <c r="D55" s="34"/>
-      <c r="E55" s="161" t="s">
+      <c r="E55" s="131" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="156"/>
-      <c r="G55" s="162"/>
-      <c r="H55" s="130" t="s">
+      <c r="F55" s="132"/>
+      <c r="G55" s="133"/>
+      <c r="H55" s="184" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="104">
+      <c r="I55" s="112">
         <v>100</v>
       </c>
       <c r="J55" s="14"/>
@@ -9414,8 +9690,8 @@
       <c r="BG55" s="15"/>
       <c r="BH55" s="15"/>
       <c r="BI55" s="15"/>
-      <c r="BJ55" s="193"/>
-      <c r="BK55" s="193"/>
+      <c r="BJ55" s="96"/>
+      <c r="BK55" s="96"/>
       <c r="BL55" s="15"/>
       <c r="BM55" s="15"/>
       <c r="BN55" s="15"/>
@@ -9479,11 +9755,11 @@
       <c r="B56" s="18"/>
       <c r="C56" s="1"/>
       <c r="D56" s="34"/>
-      <c r="E56" s="158"/>
-      <c r="F56" s="159"/>
-      <c r="G56" s="163"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="104"/>
+      <c r="E56" s="134"/>
+      <c r="F56" s="135"/>
+      <c r="G56" s="136"/>
+      <c r="H56" s="112"/>
+      <c r="I56" s="112"/>
       <c r="J56" s="14"/>
       <c r="K56" s="15"/>
       <c r="L56" s="15"/>
@@ -9536,8 +9812,8 @@
       <c r="BG56" s="15"/>
       <c r="BH56" s="15"/>
       <c r="BI56" s="15"/>
-      <c r="BJ56" s="193"/>
-      <c r="BK56" s="193"/>
+      <c r="BJ56" s="96"/>
+      <c r="BK56" s="96"/>
       <c r="BL56" s="15"/>
       <c r="BM56" s="15"/>
       <c r="BN56" s="15"/>
@@ -9601,15 +9877,15 @@
       <c r="B57" s="18"/>
       <c r="C57" s="1"/>
       <c r="D57" s="34"/>
-      <c r="E57" s="161" t="s">
+      <c r="E57" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="F57" s="156"/>
-      <c r="G57" s="162"/>
-      <c r="H57" s="130" t="s">
+      <c r="F57" s="132"/>
+      <c r="G57" s="133"/>
+      <c r="H57" s="184" t="s">
         <v>51</v>
       </c>
-      <c r="I57" s="104">
+      <c r="I57" s="112">
         <v>100</v>
       </c>
       <c r="J57" s="14"/>
@@ -9664,8 +9940,8 @@
       <c r="BG57" s="15"/>
       <c r="BH57" s="15"/>
       <c r="BI57" s="15"/>
-      <c r="BJ57" s="193"/>
-      <c r="BK57" s="193"/>
+      <c r="BJ57" s="96"/>
+      <c r="BK57" s="96"/>
       <c r="BL57" s="15"/>
       <c r="BM57" s="15"/>
       <c r="BN57" s="15"/>
@@ -9729,11 +10005,11 @@
       <c r="B58" s="18"/>
       <c r="C58" s="1"/>
       <c r="D58" s="34"/>
-      <c r="E58" s="158"/>
-      <c r="F58" s="159"/>
-      <c r="G58" s="163"/>
-      <c r="H58" s="104"/>
-      <c r="I58" s="104"/>
+      <c r="E58" s="134"/>
+      <c r="F58" s="135"/>
+      <c r="G58" s="136"/>
+      <c r="H58" s="112"/>
+      <c r="I58" s="112"/>
       <c r="J58" s="14"/>
       <c r="K58" s="15"/>
       <c r="L58" s="15"/>
@@ -9786,8 +10062,8 @@
       <c r="BG58" s="15"/>
       <c r="BH58" s="15"/>
       <c r="BI58" s="15"/>
-      <c r="BJ58" s="193"/>
-      <c r="BK58" s="193"/>
+      <c r="BJ58" s="96"/>
+      <c r="BK58" s="96"/>
       <c r="BL58" s="15"/>
       <c r="BM58" s="15"/>
       <c r="BN58" s="15"/>
@@ -9851,15 +10127,15 @@
       <c r="B59" s="18"/>
       <c r="C59" s="1"/>
       <c r="D59" s="34"/>
-      <c r="E59" s="161" t="s">
+      <c r="E59" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="F59" s="156"/>
-      <c r="G59" s="162"/>
-      <c r="H59" s="130" t="s">
+      <c r="F59" s="132"/>
+      <c r="G59" s="133"/>
+      <c r="H59" s="184" t="s">
         <v>49</v>
       </c>
-      <c r="I59" s="104">
+      <c r="I59" s="112">
         <v>100</v>
       </c>
       <c r="J59" s="14"/>
@@ -9914,8 +10190,8 @@
       <c r="BG59" s="15"/>
       <c r="BH59" s="15"/>
       <c r="BI59" s="15"/>
-      <c r="BJ59" s="193"/>
-      <c r="BK59" s="193"/>
+      <c r="BJ59" s="96"/>
+      <c r="BK59" s="96"/>
       <c r="BL59" s="15"/>
       <c r="BM59" s="15"/>
       <c r="BN59" s="15"/>
@@ -9979,11 +10255,11 @@
       <c r="B60" s="18"/>
       <c r="C60" s="1"/>
       <c r="D60" s="34"/>
-      <c r="E60" s="158"/>
-      <c r="F60" s="159"/>
-      <c r="G60" s="163"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="104"/>
+      <c r="E60" s="134"/>
+      <c r="F60" s="135"/>
+      <c r="G60" s="136"/>
+      <c r="H60" s="112"/>
+      <c r="I60" s="112"/>
       <c r="J60" s="14"/>
       <c r="K60" s="15"/>
       <c r="L60" s="15"/>
@@ -10036,8 +10312,8 @@
       <c r="BG60" s="15"/>
       <c r="BH60" s="15"/>
       <c r="BI60" s="15"/>
-      <c r="BJ60" s="193"/>
-      <c r="BK60" s="193"/>
+      <c r="BJ60" s="96"/>
+      <c r="BK60" s="96"/>
       <c r="BL60" s="15"/>
       <c r="BM60" s="15"/>
       <c r="BN60" s="15"/>
@@ -10101,15 +10377,15 @@
       <c r="B61" s="18"/>
       <c r="C61" s="1"/>
       <c r="D61" s="34"/>
-      <c r="E61" s="161" t="s">
+      <c r="E61" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F61" s="156"/>
-      <c r="G61" s="162"/>
-      <c r="H61" s="130" t="s">
+      <c r="F61" s="132"/>
+      <c r="G61" s="133"/>
+      <c r="H61" s="184" t="s">
         <v>49</v>
       </c>
-      <c r="I61" s="104">
+      <c r="I61" s="112">
         <v>100</v>
       </c>
       <c r="J61" s="14"/>
@@ -10164,8 +10440,8 @@
       <c r="BG61" s="15"/>
       <c r="BH61" s="15"/>
       <c r="BI61" s="15"/>
-      <c r="BJ61" s="193"/>
-      <c r="BK61" s="193"/>
+      <c r="BJ61" s="96"/>
+      <c r="BK61" s="96"/>
       <c r="BL61" s="15"/>
       <c r="BM61" s="15"/>
       <c r="BN61" s="15"/>
@@ -10229,11 +10505,11 @@
       <c r="B62" s="18"/>
       <c r="C62" s="1"/>
       <c r="D62" s="34"/>
-      <c r="E62" s="158"/>
-      <c r="F62" s="159"/>
-      <c r="G62" s="163"/>
-      <c r="H62" s="104"/>
-      <c r="I62" s="104"/>
+      <c r="E62" s="134"/>
+      <c r="F62" s="135"/>
+      <c r="G62" s="136"/>
+      <c r="H62" s="112"/>
+      <c r="I62" s="112"/>
       <c r="J62" s="26"/>
       <c r="K62" s="27"/>
       <c r="L62" s="27"/>
@@ -10286,8 +10562,8 @@
       <c r="BG62" s="27"/>
       <c r="BH62" s="27"/>
       <c r="BI62" s="27"/>
-      <c r="BJ62" s="195"/>
-      <c r="BK62" s="195"/>
+      <c r="BJ62" s="98"/>
+      <c r="BK62" s="98"/>
       <c r="BL62" s="27"/>
       <c r="BM62" s="27"/>
       <c r="BN62" s="27"/>
@@ -10350,14 +10626,14 @@
       <c r="A63" s="1"/>
       <c r="B63" s="18"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="155" t="s">
+      <c r="D63" s="137" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="156"/>
-      <c r="F63" s="156"/>
-      <c r="G63" s="157"/>
-      <c r="H63" s="131"/>
-      <c r="I63" s="131"/>
+      <c r="E63" s="132"/>
+      <c r="F63" s="132"/>
+      <c r="G63" s="138"/>
+      <c r="H63" s="167"/>
+      <c r="I63" s="167"/>
       <c r="J63" s="50"/>
       <c r="K63" s="51"/>
       <c r="L63" s="51"/>
@@ -10410,8 +10686,8 @@
       <c r="BG63" s="51"/>
       <c r="BH63" s="51"/>
       <c r="BI63" s="51"/>
-      <c r="BJ63" s="196"/>
-      <c r="BK63" s="196"/>
+      <c r="BJ63" s="99"/>
+      <c r="BK63" s="99"/>
       <c r="BL63" s="51"/>
       <c r="BM63" s="51"/>
       <c r="BN63" s="51"/>
@@ -10474,12 +10750,12 @@
       <c r="A64" s="1"/>
       <c r="B64" s="18"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="158"/>
-      <c r="E64" s="159"/>
-      <c r="F64" s="159"/>
-      <c r="G64" s="160"/>
-      <c r="H64" s="131"/>
-      <c r="I64" s="131"/>
+      <c r="D64" s="134"/>
+      <c r="E64" s="135"/>
+      <c r="F64" s="135"/>
+      <c r="G64" s="139"/>
+      <c r="H64" s="167"/>
+      <c r="I64" s="167"/>
       <c r="J64" s="52"/>
       <c r="K64" s="49"/>
       <c r="L64" s="49"/>
@@ -10532,8 +10808,8 @@
       <c r="BG64" s="49"/>
       <c r="BH64" s="49"/>
       <c r="BI64" s="49"/>
-      <c r="BJ64" s="193"/>
-      <c r="BK64" s="193"/>
+      <c r="BJ64" s="96"/>
+      <c r="BK64" s="96"/>
       <c r="BL64" s="49"/>
       <c r="BM64" s="49"/>
       <c r="BN64" s="49"/>
@@ -10597,15 +10873,15 @@
       <c r="B65" s="18"/>
       <c r="C65" s="1"/>
       <c r="D65" s="34"/>
-      <c r="E65" s="161" t="s">
+      <c r="E65" s="131" t="s">
         <v>35</v>
       </c>
-      <c r="F65" s="156"/>
-      <c r="G65" s="162"/>
-      <c r="H65" s="130" t="s">
+      <c r="F65" s="132"/>
+      <c r="G65" s="133"/>
+      <c r="H65" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="I65" s="104">
+      <c r="I65" s="112">
         <v>100</v>
       </c>
       <c r="J65" s="14"/>
@@ -10660,8 +10936,8 @@
       <c r="BG65" s="15"/>
       <c r="BH65" s="15"/>
       <c r="BI65" s="15"/>
-      <c r="BJ65" s="193"/>
-      <c r="BK65" s="193"/>
+      <c r="BJ65" s="96"/>
+      <c r="BK65" s="96"/>
       <c r="BL65" s="15"/>
       <c r="BM65" s="15"/>
       <c r="BN65" s="15"/>
@@ -10725,11 +11001,11 @@
       <c r="B66" s="18"/>
       <c r="C66" s="1"/>
       <c r="D66" s="34"/>
-      <c r="E66" s="158"/>
-      <c r="F66" s="159"/>
-      <c r="G66" s="163"/>
-      <c r="H66" s="104"/>
-      <c r="I66" s="104"/>
+      <c r="E66" s="134"/>
+      <c r="F66" s="135"/>
+      <c r="G66" s="136"/>
+      <c r="H66" s="112"/>
+      <c r="I66" s="112"/>
       <c r="J66" s="14"/>
       <c r="K66" s="15"/>
       <c r="L66" s="15"/>
@@ -10782,8 +11058,8 @@
       <c r="BG66" s="15"/>
       <c r="BH66" s="15"/>
       <c r="BI66" s="15"/>
-      <c r="BJ66" s="193"/>
-      <c r="BK66" s="193"/>
+      <c r="BJ66" s="96"/>
+      <c r="BK66" s="96"/>
       <c r="BL66" s="15"/>
       <c r="BM66" s="15"/>
       <c r="BN66" s="15"/>
@@ -10847,15 +11123,15 @@
       <c r="B67" s="18"/>
       <c r="C67" s="1"/>
       <c r="D67" s="34"/>
-      <c r="E67" s="161" t="s">
+      <c r="E67" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="F67" s="156"/>
-      <c r="G67" s="162"/>
-      <c r="H67" s="130" t="s">
+      <c r="F67" s="132"/>
+      <c r="G67" s="133"/>
+      <c r="H67" s="184" t="s">
         <v>53</v>
       </c>
-      <c r="I67" s="104">
+      <c r="I67" s="112">
         <v>100</v>
       </c>
       <c r="J67" s="14"/>
@@ -10910,8 +11186,8 @@
       <c r="BG67" s="15"/>
       <c r="BH67" s="15"/>
       <c r="BI67" s="15"/>
-      <c r="BJ67" s="193"/>
-      <c r="BK67" s="193"/>
+      <c r="BJ67" s="96"/>
+      <c r="BK67" s="96"/>
       <c r="BL67" s="15"/>
       <c r="BM67" s="15"/>
       <c r="BN67" s="15"/>
@@ -10975,11 +11251,11 @@
       <c r="B68" s="18"/>
       <c r="C68" s="1"/>
       <c r="D68" s="34"/>
-      <c r="E68" s="158"/>
-      <c r="F68" s="159"/>
-      <c r="G68" s="163"/>
-      <c r="H68" s="104"/>
-      <c r="I68" s="104"/>
+      <c r="E68" s="134"/>
+      <c r="F68" s="135"/>
+      <c r="G68" s="136"/>
+      <c r="H68" s="112"/>
+      <c r="I68" s="112"/>
       <c r="J68" s="14"/>
       <c r="K68" s="15"/>
       <c r="L68" s="15"/>
@@ -11032,8 +11308,8 @@
       <c r="BG68" s="15"/>
       <c r="BH68" s="15"/>
       <c r="BI68" s="15"/>
-      <c r="BJ68" s="193"/>
-      <c r="BK68" s="193"/>
+      <c r="BJ68" s="96"/>
+      <c r="BK68" s="96"/>
       <c r="BL68" s="15"/>
       <c r="BM68" s="15"/>
       <c r="BN68" s="15"/>
@@ -11097,15 +11373,15 @@
       <c r="B69" s="18"/>
       <c r="C69" s="1"/>
       <c r="D69" s="34"/>
-      <c r="E69" s="161" t="s">
+      <c r="E69" s="131" t="s">
         <v>36</v>
       </c>
-      <c r="F69" s="156"/>
-      <c r="G69" s="162"/>
-      <c r="H69" s="130" t="s">
+      <c r="F69" s="132"/>
+      <c r="G69" s="133"/>
+      <c r="H69" s="184" t="s">
         <v>54</v>
       </c>
-      <c r="I69" s="104">
+      <c r="I69" s="112">
         <v>100</v>
       </c>
       <c r="J69" s="14"/>
@@ -11160,8 +11436,8 @@
       <c r="BG69" s="15"/>
       <c r="BH69" s="15"/>
       <c r="BI69" s="15"/>
-      <c r="BJ69" s="193"/>
-      <c r="BK69" s="193"/>
+      <c r="BJ69" s="96"/>
+      <c r="BK69" s="96"/>
       <c r="BL69" s="15"/>
       <c r="BM69" s="15"/>
       <c r="BN69" s="15"/>
@@ -11225,11 +11501,11 @@
       <c r="B70" s="18"/>
       <c r="C70" s="1"/>
       <c r="D70" s="34"/>
-      <c r="E70" s="158"/>
-      <c r="F70" s="159"/>
-      <c r="G70" s="163"/>
-      <c r="H70" s="104"/>
-      <c r="I70" s="104"/>
+      <c r="E70" s="134"/>
+      <c r="F70" s="135"/>
+      <c r="G70" s="136"/>
+      <c r="H70" s="112"/>
+      <c r="I70" s="112"/>
       <c r="J70" s="14"/>
       <c r="K70" s="15"/>
       <c r="L70" s="15"/>
@@ -11282,8 +11558,8 @@
       <c r="BG70" s="15"/>
       <c r="BH70" s="15"/>
       <c r="BI70" s="15"/>
-      <c r="BJ70" s="193"/>
-      <c r="BK70" s="193"/>
+      <c r="BJ70" s="96"/>
+      <c r="BK70" s="96"/>
       <c r="BL70" s="15"/>
       <c r="BM70" s="15"/>
       <c r="BN70" s="15"/>
@@ -11347,15 +11623,15 @@
       <c r="B71" s="18"/>
       <c r="C71" s="1"/>
       <c r="D71" s="34"/>
-      <c r="E71" s="161" t="s">
+      <c r="E71" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F71" s="156"/>
-      <c r="G71" s="162"/>
-      <c r="H71" s="130" t="s">
+      <c r="F71" s="132"/>
+      <c r="G71" s="133"/>
+      <c r="H71" s="184" t="s">
         <v>55</v>
       </c>
-      <c r="I71" s="104">
+      <c r="I71" s="112">
         <v>100</v>
       </c>
       <c r="J71" s="14"/>
@@ -11410,8 +11686,8 @@
       <c r="BG71" s="15"/>
       <c r="BH71" s="15"/>
       <c r="BI71" s="15"/>
-      <c r="BJ71" s="193"/>
-      <c r="BK71" s="193"/>
+      <c r="BJ71" s="96"/>
+      <c r="BK71" s="96"/>
       <c r="BL71" s="15"/>
       <c r="BM71" s="15"/>
       <c r="BN71" s="15"/>
@@ -11475,11 +11751,11 @@
       <c r="B72" s="18"/>
       <c r="C72" s="1"/>
       <c r="D72" s="35"/>
-      <c r="E72" s="158"/>
-      <c r="F72" s="159"/>
-      <c r="G72" s="163"/>
-      <c r="H72" s="104"/>
-      <c r="I72" s="104"/>
+      <c r="E72" s="134"/>
+      <c r="F72" s="135"/>
+      <c r="G72" s="136"/>
+      <c r="H72" s="112"/>
+      <c r="I72" s="112"/>
       <c r="J72" s="26"/>
       <c r="K72" s="27"/>
       <c r="L72" s="27"/>
@@ -11532,9 +11808,9 @@
       <c r="BG72" s="27"/>
       <c r="BH72" s="27"/>
       <c r="BI72" s="27"/>
-      <c r="BJ72" s="195"/>
-      <c r="BK72" s="195"/>
-      <c r="BL72" s="195"/>
+      <c r="BJ72" s="98"/>
+      <c r="BK72" s="98"/>
+      <c r="BL72" s="98"/>
       <c r="BM72" s="27"/>
       <c r="BN72" s="27"/>
       <c r="BO72" s="27"/>
@@ -11595,17 +11871,17 @@
     <row r="73" spans="1:120" ht="9.75" customHeight="1">
       <c r="A73" s="16"/>
       <c r="B73" s="36"/>
-      <c r="C73" s="138" t="s">
+      <c r="C73" s="140" t="s">
         <v>30</v>
       </c>
-      <c r="D73" s="156"/>
-      <c r="E73" s="156"/>
-      <c r="F73" s="156"/>
-      <c r="G73" s="157"/>
-      <c r="H73" s="130" t="s">
+      <c r="D73" s="132"/>
+      <c r="E73" s="132"/>
+      <c r="F73" s="132"/>
+      <c r="G73" s="138"/>
+      <c r="H73" s="184" t="s">
         <v>55</v>
       </c>
-      <c r="I73" s="104">
+      <c r="I73" s="112">
         <v>100</v>
       </c>
       <c r="J73" s="19"/>
@@ -11723,13 +11999,13 @@
     <row r="74" spans="1:120" ht="9.75" customHeight="1">
       <c r="A74" s="16"/>
       <c r="B74" s="36"/>
-      <c r="C74" s="171"/>
-      <c r="D74" s="159"/>
-      <c r="E74" s="159"/>
-      <c r="F74" s="159"/>
-      <c r="G74" s="160"/>
-      <c r="H74" s="104"/>
-      <c r="I74" s="104"/>
+      <c r="C74" s="141"/>
+      <c r="D74" s="135"/>
+      <c r="E74" s="135"/>
+      <c r="F74" s="135"/>
+      <c r="G74" s="139"/>
+      <c r="H74" s="112"/>
+      <c r="I74" s="112"/>
       <c r="J74" s="19"/>
       <c r="K74" s="20"/>
       <c r="L74" s="20"/>
@@ -11845,17 +12121,17 @@
     <row r="75" spans="1:120" ht="9.75" customHeight="1">
       <c r="A75" s="16"/>
       <c r="B75" s="36"/>
-      <c r="C75" s="138" t="s">
+      <c r="C75" s="140" t="s">
         <v>34</v>
       </c>
-      <c r="D75" s="156"/>
-      <c r="E75" s="156"/>
-      <c r="F75" s="156"/>
-      <c r="G75" s="157"/>
-      <c r="H75" s="130" t="s">
+      <c r="D75" s="132"/>
+      <c r="E75" s="132"/>
+      <c r="F75" s="132"/>
+      <c r="G75" s="138"/>
+      <c r="H75" s="184" t="s">
         <v>58</v>
       </c>
-      <c r="I75" s="104"/>
+      <c r="I75" s="112"/>
       <c r="J75" s="19"/>
       <c r="K75" s="20"/>
       <c r="L75" s="20"/>
@@ -11971,13 +12247,13 @@
     <row r="76" spans="1:120" ht="9.75" customHeight="1">
       <c r="A76" s="16"/>
       <c r="B76" s="36"/>
-      <c r="C76" s="154"/>
-      <c r="D76" s="154"/>
-      <c r="E76" s="154"/>
-      <c r="F76" s="154"/>
-      <c r="G76" s="154"/>
-      <c r="H76" s="104"/>
-      <c r="I76" s="104"/>
+      <c r="C76" s="142"/>
+      <c r="D76" s="142"/>
+      <c r="E76" s="142"/>
+      <c r="F76" s="142"/>
+      <c r="G76" s="142"/>
+      <c r="H76" s="112"/>
+      <c r="I76" s="112"/>
       <c r="J76" s="19"/>
       <c r="K76" s="20"/>
       <c r="L76" s="20"/>
@@ -12093,15 +12369,15 @@
     <row r="77" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A77" s="16"/>
       <c r="B77" s="71"/>
-      <c r="C77" s="179" t="s">
+      <c r="C77" s="143" t="s">
         <v>62</v>
       </c>
-      <c r="D77" s="180"/>
-      <c r="E77" s="180"/>
-      <c r="F77" s="180"/>
-      <c r="G77" s="181"/>
-      <c r="H77" s="132"/>
-      <c r="I77" s="121"/>
+      <c r="D77" s="144"/>
+      <c r="E77" s="144"/>
+      <c r="F77" s="144"/>
+      <c r="G77" s="145"/>
+      <c r="H77" s="185"/>
+      <c r="I77" s="181"/>
       <c r="J77" s="63"/>
       <c r="K77" s="64"/>
       <c r="L77" s="64"/>
@@ -12217,13 +12493,13 @@
     <row r="78" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A78" s="16"/>
       <c r="B78" s="71"/>
-      <c r="C78" s="182"/>
-      <c r="D78" s="183"/>
-      <c r="E78" s="183"/>
-      <c r="F78" s="183"/>
-      <c r="G78" s="184"/>
-      <c r="H78" s="133"/>
-      <c r="I78" s="122"/>
+      <c r="C78" s="146"/>
+      <c r="D78" s="147"/>
+      <c r="E78" s="147"/>
+      <c r="F78" s="147"/>
+      <c r="G78" s="148"/>
+      <c r="H78" s="186"/>
+      <c r="I78" s="182"/>
       <c r="J78" s="63"/>
       <c r="K78" s="64"/>
       <c r="L78" s="64"/>
@@ -12340,12 +12616,12 @@
       <c r="A79" s="16"/>
       <c r="B79" s="71"/>
       <c r="C79" s="76"/>
-      <c r="D79" s="124" t="s">
+      <c r="D79" s="115" t="s">
         <v>63</v>
       </c>
-      <c r="E79" s="125"/>
-      <c r="F79" s="125"/>
-      <c r="G79" s="126"/>
+      <c r="E79" s="116"/>
+      <c r="F79" s="116"/>
+      <c r="G79" s="117"/>
       <c r="H79" s="77"/>
       <c r="I79" s="67"/>
       <c r="J79" s="63"/>
@@ -12464,10 +12740,10 @@
       <c r="A80" s="16"/>
       <c r="B80" s="71"/>
       <c r="C80" s="76"/>
-      <c r="D80" s="127"/>
-      <c r="E80" s="128"/>
-      <c r="F80" s="128"/>
-      <c r="G80" s="129"/>
+      <c r="D80" s="118"/>
+      <c r="E80" s="119"/>
+      <c r="F80" s="119"/>
+      <c r="G80" s="120"/>
       <c r="H80" s="77"/>
       <c r="I80" s="67"/>
       <c r="J80" s="63"/>
@@ -12587,15 +12863,15 @@
       <c r="B81" s="36"/>
       <c r="C81" s="60"/>
       <c r="D81" s="70"/>
-      <c r="E81" s="97" t="s">
+      <c r="E81" s="149" t="s">
         <v>73</v>
       </c>
-      <c r="F81" s="97"/>
-      <c r="G81" s="97"/>
+      <c r="F81" s="149"/>
+      <c r="G81" s="149"/>
       <c r="H81" s="103">
         <v>45611</v>
       </c>
-      <c r="I81" s="118">
+      <c r="I81" s="105">
         <v>100</v>
       </c>
       <c r="J81" s="19"/>
@@ -12715,11 +12991,11 @@
       <c r="B82" s="36"/>
       <c r="C82" s="60"/>
       <c r="D82" s="70"/>
-      <c r="E82" s="95"/>
-      <c r="F82" s="95"/>
-      <c r="G82" s="95"/>
-      <c r="H82" s="99"/>
-      <c r="I82" s="101"/>
+      <c r="E82" s="102"/>
+      <c r="F82" s="102"/>
+      <c r="G82" s="102"/>
+      <c r="H82" s="104"/>
+      <c r="I82" s="106"/>
       <c r="J82" s="19"/>
       <c r="K82" s="20"/>
       <c r="L82" s="20"/>
@@ -12837,15 +13113,15 @@
       <c r="B83" s="36"/>
       <c r="C83" s="60"/>
       <c r="D83" s="70"/>
-      <c r="E83" s="95" t="s">
+      <c r="E83" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="F83" s="95"/>
-      <c r="G83" s="95"/>
+      <c r="F83" s="102"/>
+      <c r="G83" s="102"/>
       <c r="H83" s="103">
         <v>45615</v>
       </c>
-      <c r="I83" s="118">
+      <c r="I83" s="105">
         <v>100</v>
       </c>
       <c r="J83" s="19"/>
@@ -12965,11 +13241,11 @@
       <c r="B84" s="36"/>
       <c r="C84" s="60"/>
       <c r="D84" s="70"/>
-      <c r="E84" s="95"/>
-      <c r="F84" s="95"/>
-      <c r="G84" s="95"/>
-      <c r="H84" s="99"/>
-      <c r="I84" s="101"/>
+      <c r="E84" s="102"/>
+      <c r="F84" s="102"/>
+      <c r="G84" s="102"/>
+      <c r="H84" s="104"/>
+      <c r="I84" s="106"/>
       <c r="J84" s="19"/>
       <c r="K84" s="20"/>
       <c r="L84" s="20"/>
@@ -13087,15 +13363,15 @@
       <c r="B85" s="36"/>
       <c r="C85" s="60"/>
       <c r="D85" s="70"/>
-      <c r="E85" s="106" t="s">
+      <c r="E85" s="189" t="s">
         <v>61</v>
       </c>
-      <c r="F85" s="107"/>
-      <c r="G85" s="108"/>
-      <c r="H85" s="102">
+      <c r="F85" s="121"/>
+      <c r="G85" s="122"/>
+      <c r="H85" s="111">
         <v>45617</v>
       </c>
-      <c r="I85" s="118">
+      <c r="I85" s="105">
         <v>100</v>
       </c>
       <c r="J85" s="62"/>
@@ -13215,11 +13491,11 @@
       <c r="B86" s="36"/>
       <c r="C86" s="60"/>
       <c r="D86" s="70"/>
-      <c r="E86" s="109"/>
-      <c r="F86" s="110"/>
-      <c r="G86" s="111"/>
-      <c r="H86" s="102"/>
-      <c r="I86" s="101"/>
+      <c r="E86" s="150"/>
+      <c r="F86" s="125"/>
+      <c r="G86" s="126"/>
+      <c r="H86" s="111"/>
+      <c r="I86" s="106"/>
       <c r="J86" s="62"/>
       <c r="K86" s="20"/>
       <c r="L86" s="20"/>
@@ -13336,16 +13612,16 @@
       <c r="A87" s="16"/>
       <c r="B87" s="71"/>
       <c r="C87" s="90"/>
-      <c r="D87" s="95" t="s">
+      <c r="D87" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="E87" s="95"/>
-      <c r="F87" s="95"/>
-      <c r="G87" s="95"/>
+      <c r="E87" s="102"/>
+      <c r="F87" s="102"/>
+      <c r="G87" s="102"/>
       <c r="H87" s="103">
         <v>45615</v>
       </c>
-      <c r="I87" s="118">
+      <c r="I87" s="105">
         <v>100</v>
       </c>
       <c r="J87" s="62"/>
@@ -13464,12 +13740,12 @@
       <c r="A88" s="16"/>
       <c r="B88" s="71"/>
       <c r="C88" s="90"/>
-      <c r="D88" s="95"/>
-      <c r="E88" s="95"/>
-      <c r="F88" s="95"/>
-      <c r="G88" s="95"/>
-      <c r="H88" s="99"/>
-      <c r="I88" s="101"/>
+      <c r="D88" s="102"/>
+      <c r="E88" s="102"/>
+      <c r="F88" s="102"/>
+      <c r="G88" s="102"/>
+      <c r="H88" s="104"/>
+      <c r="I88" s="106"/>
       <c r="J88" s="62"/>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -13586,14 +13862,14 @@
       <c r="A89" s="16"/>
       <c r="B89" s="36"/>
       <c r="C89" s="79"/>
-      <c r="D89" s="124" t="s">
+      <c r="D89" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="125"/>
-      <c r="F89" s="125"/>
-      <c r="G89" s="126"/>
-      <c r="H89" s="123"/>
-      <c r="I89" s="120"/>
+      <c r="E89" s="116"/>
+      <c r="F89" s="116"/>
+      <c r="G89" s="117"/>
+      <c r="H89" s="187"/>
+      <c r="I89" s="188"/>
       <c r="J89" s="66"/>
       <c r="K89" s="64"/>
       <c r="L89" s="64"/>
@@ -13710,12 +13986,12 @@
       <c r="A90" s="16"/>
       <c r="B90" s="36"/>
       <c r="C90" s="79"/>
-      <c r="D90" s="127"/>
-      <c r="E90" s="128"/>
-      <c r="F90" s="128"/>
-      <c r="G90" s="129"/>
-      <c r="H90" s="123"/>
-      <c r="I90" s="120"/>
+      <c r="D90" s="118"/>
+      <c r="E90" s="119"/>
+      <c r="F90" s="119"/>
+      <c r="G90" s="120"/>
+      <c r="H90" s="187"/>
+      <c r="I90" s="188"/>
       <c r="J90" s="66"/>
       <c r="K90" s="64"/>
       <c r="L90" s="64"/>
@@ -13833,15 +14109,15 @@
       <c r="B91" s="36"/>
       <c r="C91" s="60"/>
       <c r="D91" s="70"/>
-      <c r="E91" s="97" t="s">
+      <c r="E91" s="149" t="s">
         <v>68</v>
       </c>
-      <c r="F91" s="97"/>
-      <c r="G91" s="97"/>
+      <c r="F91" s="149"/>
+      <c r="G91" s="149"/>
       <c r="H91" s="103">
         <v>45616</v>
       </c>
-      <c r="I91" s="118"/>
+      <c r="I91" s="105"/>
       <c r="J91" s="19"/>
       <c r="K91" s="20"/>
       <c r="L91" s="20"/>
@@ -13959,11 +14235,11 @@
       <c r="B92" s="36"/>
       <c r="C92" s="60"/>
       <c r="D92" s="70"/>
-      <c r="E92" s="95"/>
-      <c r="F92" s="95"/>
-      <c r="G92" s="95"/>
-      <c r="H92" s="99"/>
-      <c r="I92" s="101"/>
+      <c r="E92" s="102"/>
+      <c r="F92" s="102"/>
+      <c r="G92" s="102"/>
+      <c r="H92" s="104"/>
+      <c r="I92" s="106"/>
       <c r="J92" s="19"/>
       <c r="K92" s="20"/>
       <c r="L92" s="20"/>
@@ -14081,15 +14357,15 @@
       <c r="B93" s="36"/>
       <c r="C93" s="60"/>
       <c r="D93" s="70"/>
-      <c r="E93" s="95" t="s">
+      <c r="E93" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="F93" s="95"/>
-      <c r="G93" s="95"/>
+      <c r="F93" s="102"/>
+      <c r="G93" s="102"/>
       <c r="H93" s="103">
         <v>45617</v>
       </c>
-      <c r="I93" s="118"/>
+      <c r="I93" s="105"/>
       <c r="J93" s="19"/>
       <c r="K93" s="20"/>
       <c r="L93" s="20"/>
@@ -14207,11 +14483,11 @@
       <c r="B94" s="36"/>
       <c r="C94" s="60"/>
       <c r="D94" s="70"/>
-      <c r="E94" s="95"/>
-      <c r="F94" s="95"/>
-      <c r="G94" s="95"/>
-      <c r="H94" s="99"/>
-      <c r="I94" s="101"/>
+      <c r="E94" s="102"/>
+      <c r="F94" s="102"/>
+      <c r="G94" s="102"/>
+      <c r="H94" s="104"/>
+      <c r="I94" s="106"/>
       <c r="J94" s="19"/>
       <c r="K94" s="20"/>
       <c r="L94" s="20"/>
@@ -14329,15 +14605,15 @@
       <c r="B95" s="36"/>
       <c r="C95" s="60"/>
       <c r="D95" s="70"/>
-      <c r="E95" s="95" t="s">
+      <c r="E95" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="F95" s="95"/>
-      <c r="G95" s="95"/>
+      <c r="F95" s="102"/>
+      <c r="G95" s="102"/>
       <c r="H95" s="103">
         <v>45618</v>
       </c>
-      <c r="I95" s="118"/>
+      <c r="I95" s="105"/>
       <c r="J95" s="19"/>
       <c r="K95" s="20"/>
       <c r="L95" s="20"/>
@@ -14455,11 +14731,11 @@
       <c r="B96" s="36"/>
       <c r="C96" s="60"/>
       <c r="D96" s="70"/>
-      <c r="E96" s="95"/>
-      <c r="F96" s="95"/>
-      <c r="G96" s="95"/>
-      <c r="H96" s="99"/>
-      <c r="I96" s="101"/>
+      <c r="E96" s="102"/>
+      <c r="F96" s="102"/>
+      <c r="G96" s="102"/>
+      <c r="H96" s="104"/>
+      <c r="I96" s="106"/>
       <c r="J96" s="19"/>
       <c r="K96" s="20"/>
       <c r="L96" s="20"/>
@@ -14577,15 +14853,15 @@
       <c r="B97" s="36"/>
       <c r="C97" s="60"/>
       <c r="D97" s="70"/>
-      <c r="E97" s="95" t="s">
+      <c r="E97" s="102" t="s">
         <v>71</v>
       </c>
-      <c r="F97" s="95"/>
-      <c r="G97" s="95"/>
+      <c r="F97" s="102"/>
+      <c r="G97" s="102"/>
       <c r="H97" s="103">
         <v>45621</v>
       </c>
-      <c r="I97" s="118"/>
+      <c r="I97" s="105"/>
       <c r="J97" s="19"/>
       <c r="K97" s="20"/>
       <c r="L97" s="20"/>
@@ -14703,11 +14979,11 @@
       <c r="B98" s="36"/>
       <c r="C98" s="60"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="95"/>
-      <c r="F98" s="95"/>
-      <c r="G98" s="95"/>
-      <c r="H98" s="99"/>
-      <c r="I98" s="101"/>
+      <c r="E98" s="102"/>
+      <c r="F98" s="102"/>
+      <c r="G98" s="102"/>
+      <c r="H98" s="104"/>
+      <c r="I98" s="106"/>
       <c r="J98" s="19"/>
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
@@ -14825,15 +15101,15 @@
       <c r="B99" s="36"/>
       <c r="C99" s="60"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="95" t="s">
+      <c r="E99" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="F99" s="95"/>
-      <c r="G99" s="95"/>
+      <c r="F99" s="102"/>
+      <c r="G99" s="102"/>
       <c r="H99" s="103">
         <v>45622</v>
       </c>
-      <c r="I99" s="118"/>
+      <c r="I99" s="105"/>
       <c r="J99" s="19"/>
       <c r="K99" s="20"/>
       <c r="L99" s="20"/>
@@ -14951,11 +15227,11 @@
       <c r="B100" s="36"/>
       <c r="C100" s="60"/>
       <c r="D100" s="70"/>
-      <c r="E100" s="95"/>
-      <c r="F100" s="95"/>
-      <c r="G100" s="95"/>
-      <c r="H100" s="99"/>
-      <c r="I100" s="101"/>
+      <c r="E100" s="102"/>
+      <c r="F100" s="102"/>
+      <c r="G100" s="102"/>
+      <c r="H100" s="104"/>
+      <c r="I100" s="106"/>
       <c r="J100" s="19"/>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -15073,15 +15349,15 @@
       <c r="B101" s="71"/>
       <c r="C101" s="91"/>
       <c r="D101" s="70"/>
-      <c r="E101" s="109" t="s">
+      <c r="E101" s="150" t="s">
         <v>61</v>
       </c>
-      <c r="F101" s="110"/>
-      <c r="G101" s="111"/>
+      <c r="F101" s="125"/>
+      <c r="G101" s="126"/>
       <c r="H101" s="103">
         <v>45623</v>
       </c>
-      <c r="I101" s="104"/>
+      <c r="I101" s="112"/>
       <c r="J101" s="62"/>
       <c r="K101" s="20"/>
       <c r="L101" s="20"/>
@@ -15199,11 +15475,11 @@
       <c r="B102" s="71"/>
       <c r="C102" s="91"/>
       <c r="D102" s="70"/>
-      <c r="E102" s="109"/>
-      <c r="F102" s="110"/>
-      <c r="G102" s="111"/>
-      <c r="H102" s="99"/>
-      <c r="I102" s="104"/>
+      <c r="E102" s="150"/>
+      <c r="F102" s="125"/>
+      <c r="G102" s="126"/>
+      <c r="H102" s="104"/>
+      <c r="I102" s="112"/>
       <c r="J102" s="62"/>
       <c r="K102" s="20"/>
       <c r="L102" s="20"/>
@@ -15320,16 +15596,16 @@
       <c r="A103" s="16"/>
       <c r="B103" s="71"/>
       <c r="C103" s="90"/>
-      <c r="D103" s="95" t="s">
+      <c r="D103" s="102" t="s">
         <v>77</v>
       </c>
-      <c r="E103" s="95"/>
-      <c r="F103" s="95"/>
-      <c r="G103" s="95"/>
+      <c r="E103" s="102"/>
+      <c r="F103" s="102"/>
+      <c r="G103" s="102"/>
       <c r="H103" s="103">
         <v>45622</v>
       </c>
-      <c r="I103" s="105"/>
+      <c r="I103" s="109"/>
       <c r="J103" s="62"/>
       <c r="K103" s="20"/>
       <c r="L103" s="20"/>
@@ -15446,12 +15722,12 @@
       <c r="A104" s="16"/>
       <c r="B104" s="71"/>
       <c r="C104" s="90"/>
-      <c r="D104" s="95"/>
-      <c r="E104" s="95"/>
-      <c r="F104" s="95"/>
-      <c r="G104" s="95"/>
-      <c r="H104" s="99"/>
-      <c r="I104" s="135"/>
+      <c r="D104" s="102"/>
+      <c r="E104" s="102"/>
+      <c r="F104" s="102"/>
+      <c r="G104" s="102"/>
+      <c r="H104" s="104"/>
+      <c r="I104" s="110"/>
       <c r="J104" s="62"/>
       <c r="K104" s="20"/>
       <c r="L104" s="20"/>
@@ -15567,15 +15843,15 @@
     <row r="105" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A105" s="16"/>
       <c r="B105" s="71"/>
-      <c r="C105" s="179" t="s">
+      <c r="C105" s="143" t="s">
         <v>64</v>
       </c>
-      <c r="D105" s="180"/>
-      <c r="E105" s="180"/>
-      <c r="F105" s="180"/>
-      <c r="G105" s="181"/>
-      <c r="H105" s="119"/>
-      <c r="I105" s="120"/>
+      <c r="D105" s="144"/>
+      <c r="E105" s="144"/>
+      <c r="F105" s="144"/>
+      <c r="G105" s="145"/>
+      <c r="H105" s="190"/>
+      <c r="I105" s="188"/>
       <c r="J105" s="66"/>
       <c r="K105" s="64"/>
       <c r="L105" s="64"/>
@@ -15691,13 +15967,13 @@
     <row r="106" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A106" s="16"/>
       <c r="B106" s="71"/>
-      <c r="C106" s="182"/>
-      <c r="D106" s="183"/>
-      <c r="E106" s="183"/>
-      <c r="F106" s="183"/>
-      <c r="G106" s="184"/>
-      <c r="H106" s="119"/>
-      <c r="I106" s="120"/>
+      <c r="C106" s="146"/>
+      <c r="D106" s="147"/>
+      <c r="E106" s="147"/>
+      <c r="F106" s="147"/>
+      <c r="G106" s="148"/>
+      <c r="H106" s="190"/>
+      <c r="I106" s="188"/>
       <c r="J106" s="66"/>
       <c r="K106" s="64"/>
       <c r="L106" s="64"/>
@@ -15814,14 +16090,14 @@
       <c r="A107" s="16"/>
       <c r="B107" s="36"/>
       <c r="C107" s="78"/>
-      <c r="D107" s="124" t="s">
+      <c r="D107" s="115" t="s">
         <v>59</v>
       </c>
-      <c r="E107" s="125"/>
-      <c r="F107" s="125"/>
-      <c r="G107" s="126"/>
-      <c r="H107" s="119"/>
-      <c r="I107" s="120"/>
+      <c r="E107" s="116"/>
+      <c r="F107" s="116"/>
+      <c r="G107" s="117"/>
+      <c r="H107" s="190"/>
+      <c r="I107" s="188"/>
       <c r="J107" s="66"/>
       <c r="K107" s="64"/>
       <c r="L107" s="64"/>
@@ -15938,12 +16214,12 @@
       <c r="A108" s="16"/>
       <c r="B108" s="36"/>
       <c r="C108" s="76"/>
-      <c r="D108" s="127"/>
-      <c r="E108" s="128"/>
-      <c r="F108" s="128"/>
-      <c r="G108" s="129"/>
-      <c r="H108" s="119"/>
-      <c r="I108" s="120"/>
+      <c r="D108" s="118"/>
+      <c r="E108" s="119"/>
+      <c r="F108" s="119"/>
+      <c r="G108" s="120"/>
+      <c r="H108" s="190"/>
+      <c r="I108" s="188"/>
       <c r="J108" s="66"/>
       <c r="K108" s="64"/>
       <c r="L108" s="64"/>
@@ -16061,15 +16337,15 @@
       <c r="B109" s="36"/>
       <c r="C109" s="60"/>
       <c r="D109" s="70"/>
-      <c r="E109" s="97" t="s">
+      <c r="E109" s="149" t="s">
         <v>73</v>
       </c>
-      <c r="F109" s="97"/>
-      <c r="G109" s="97"/>
+      <c r="F109" s="149"/>
+      <c r="G109" s="149"/>
       <c r="H109" s="103">
         <v>45624</v>
       </c>
-      <c r="I109" s="105"/>
+      <c r="I109" s="109"/>
       <c r="J109" s="62"/>
       <c r="K109" s="20"/>
       <c r="L109" s="20"/>
@@ -16187,11 +16463,11 @@
       <c r="B110" s="36"/>
       <c r="C110" s="60"/>
       <c r="D110" s="70"/>
-      <c r="E110" s="95"/>
-      <c r="F110" s="95"/>
-      <c r="G110" s="95"/>
-      <c r="H110" s="99"/>
-      <c r="I110" s="135"/>
+      <c r="E110" s="102"/>
+      <c r="F110" s="102"/>
+      <c r="G110" s="102"/>
+      <c r="H110" s="104"/>
+      <c r="I110" s="110"/>
       <c r="J110" s="62"/>
       <c r="K110" s="20"/>
       <c r="L110" s="20"/>
@@ -16309,15 +16585,15 @@
       <c r="B111" s="36"/>
       <c r="C111" s="60"/>
       <c r="D111" s="70"/>
-      <c r="E111" s="95" t="s">
+      <c r="E111" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="F111" s="95"/>
-      <c r="G111" s="95"/>
+      <c r="F111" s="102"/>
+      <c r="G111" s="102"/>
       <c r="H111" s="103">
         <v>45625</v>
       </c>
-      <c r="I111" s="105"/>
+      <c r="I111" s="109"/>
       <c r="J111" s="62"/>
       <c r="K111" s="20"/>
       <c r="L111" s="20"/>
@@ -16435,11 +16711,11 @@
       <c r="B112" s="36"/>
       <c r="C112" s="60"/>
       <c r="D112" s="70"/>
-      <c r="E112" s="95"/>
-      <c r="F112" s="95"/>
-      <c r="G112" s="95"/>
-      <c r="H112" s="99"/>
-      <c r="I112" s="135"/>
+      <c r="E112" s="102"/>
+      <c r="F112" s="102"/>
+      <c r="G112" s="102"/>
+      <c r="H112" s="104"/>
+      <c r="I112" s="110"/>
       <c r="J112" s="62"/>
       <c r="K112" s="20"/>
       <c r="L112" s="20"/>
@@ -16557,15 +16833,15 @@
       <c r="B113" s="71"/>
       <c r="C113" s="91"/>
       <c r="D113" s="70"/>
-      <c r="E113" s="95" t="s">
+      <c r="E113" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="F113" s="95"/>
-      <c r="G113" s="95"/>
-      <c r="H113" s="102">
+      <c r="F113" s="102"/>
+      <c r="G113" s="102"/>
+      <c r="H113" s="111">
         <v>45630</v>
       </c>
-      <c r="I113" s="104"/>
+      <c r="I113" s="112"/>
       <c r="J113" s="62"/>
       <c r="K113" s="20"/>
       <c r="L113" s="20"/>
@@ -16683,11 +16959,11 @@
       <c r="B114" s="71"/>
       <c r="C114" s="91"/>
       <c r="D114" s="70"/>
-      <c r="E114" s="117"/>
-      <c r="F114" s="117"/>
-      <c r="G114" s="117"/>
+      <c r="E114" s="198"/>
+      <c r="F114" s="198"/>
+      <c r="G114" s="198"/>
       <c r="H114" s="103"/>
-      <c r="I114" s="105"/>
+      <c r="I114" s="109"/>
       <c r="J114" s="62"/>
       <c r="K114" s="20"/>
       <c r="L114" s="20"/>
@@ -16804,16 +17080,16 @@
       <c r="A115" s="16"/>
       <c r="B115" s="71"/>
       <c r="C115" s="91"/>
-      <c r="D115" s="95" t="s">
+      <c r="D115" s="102" t="s">
         <v>78</v>
       </c>
-      <c r="E115" s="95"/>
-      <c r="F115" s="95"/>
-      <c r="G115" s="95"/>
-      <c r="H115" s="102">
+      <c r="E115" s="102"/>
+      <c r="F115" s="102"/>
+      <c r="G115" s="102"/>
+      <c r="H115" s="111">
         <v>45625</v>
       </c>
-      <c r="I115" s="104"/>
+      <c r="I115" s="112"/>
       <c r="J115" s="62"/>
       <c r="K115" s="20"/>
       <c r="L115" s="20"/>
@@ -16930,12 +17206,12 @@
       <c r="A116" s="16"/>
       <c r="B116" s="71"/>
       <c r="C116" s="91"/>
-      <c r="D116" s="95"/>
-      <c r="E116" s="95"/>
-      <c r="F116" s="95"/>
-      <c r="G116" s="95"/>
-      <c r="H116" s="102"/>
-      <c r="I116" s="104"/>
+      <c r="D116" s="102"/>
+      <c r="E116" s="102"/>
+      <c r="F116" s="102"/>
+      <c r="G116" s="102"/>
+      <c r="H116" s="111"/>
+      <c r="I116" s="112"/>
       <c r="J116" s="62"/>
       <c r="K116" s="20"/>
       <c r="L116" s="20"/>
@@ -17052,14 +17328,14 @@
       <c r="A117" s="16"/>
       <c r="B117" s="36"/>
       <c r="C117" s="80"/>
-      <c r="D117" s="124" t="s">
+      <c r="D117" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="E117" s="125"/>
-      <c r="F117" s="125"/>
-      <c r="G117" s="126"/>
-      <c r="H117" s="113"/>
-      <c r="I117" s="121"/>
+      <c r="E117" s="116"/>
+      <c r="F117" s="116"/>
+      <c r="G117" s="117"/>
+      <c r="H117" s="191"/>
+      <c r="I117" s="181"/>
       <c r="J117" s="63"/>
       <c r="K117" s="64"/>
       <c r="L117" s="64"/>
@@ -17176,12 +17452,12 @@
       <c r="A118" s="16"/>
       <c r="B118" s="36"/>
       <c r="C118" s="80"/>
-      <c r="D118" s="127"/>
-      <c r="E118" s="128"/>
-      <c r="F118" s="128"/>
-      <c r="G118" s="129"/>
-      <c r="H118" s="114"/>
-      <c r="I118" s="122"/>
+      <c r="D118" s="118"/>
+      <c r="E118" s="119"/>
+      <c r="F118" s="119"/>
+      <c r="G118" s="120"/>
+      <c r="H118" s="192"/>
+      <c r="I118" s="182"/>
       <c r="J118" s="63"/>
       <c r="K118" s="64"/>
       <c r="L118" s="64"/>
@@ -17299,15 +17575,15 @@
       <c r="B119" s="36"/>
       <c r="C119" s="60"/>
       <c r="D119" s="70"/>
-      <c r="E119" s="97" t="s">
+      <c r="E119" s="149" t="s">
         <v>68</v>
       </c>
-      <c r="F119" s="97"/>
-      <c r="G119" s="97"/>
+      <c r="F119" s="149"/>
+      <c r="G119" s="149"/>
       <c r="H119" s="103">
         <v>45629</v>
       </c>
-      <c r="I119" s="118"/>
+      <c r="I119" s="105"/>
       <c r="J119" s="19"/>
       <c r="K119" s="20"/>
       <c r="L119" s="20"/>
@@ -17425,11 +17701,11 @@
       <c r="B120" s="36"/>
       <c r="C120" s="60"/>
       <c r="D120" s="70"/>
-      <c r="E120" s="95"/>
-      <c r="F120" s="95"/>
-      <c r="G120" s="95"/>
-      <c r="H120" s="99"/>
-      <c r="I120" s="101"/>
+      <c r="E120" s="102"/>
+      <c r="F120" s="102"/>
+      <c r="G120" s="102"/>
+      <c r="H120" s="104"/>
+      <c r="I120" s="106"/>
       <c r="J120" s="19"/>
       <c r="K120" s="20"/>
       <c r="L120" s="20"/>
@@ -17547,15 +17823,15 @@
       <c r="B121" s="36"/>
       <c r="C121" s="60"/>
       <c r="D121" s="70"/>
-      <c r="E121" s="95" t="s">
+      <c r="E121" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="F121" s="95"/>
-      <c r="G121" s="95"/>
+      <c r="F121" s="102"/>
+      <c r="G121" s="102"/>
       <c r="H121" s="103">
         <v>45630</v>
       </c>
-      <c r="I121" s="118"/>
+      <c r="I121" s="105"/>
       <c r="J121" s="19"/>
       <c r="K121" s="20"/>
       <c r="L121" s="20"/>
@@ -17673,11 +17949,11 @@
       <c r="B122" s="36"/>
       <c r="C122" s="60"/>
       <c r="D122" s="70"/>
-      <c r="E122" s="95"/>
-      <c r="F122" s="95"/>
-      <c r="G122" s="95"/>
-      <c r="H122" s="99"/>
-      <c r="I122" s="101"/>
+      <c r="E122" s="102"/>
+      <c r="F122" s="102"/>
+      <c r="G122" s="102"/>
+      <c r="H122" s="104"/>
+      <c r="I122" s="106"/>
       <c r="J122" s="19"/>
       <c r="K122" s="20"/>
       <c r="L122" s="20"/>
@@ -17795,15 +18071,15 @@
       <c r="B123" s="36"/>
       <c r="C123" s="60"/>
       <c r="D123" s="70"/>
-      <c r="E123" s="95" t="s">
+      <c r="E123" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="F123" s="95"/>
-      <c r="G123" s="95"/>
-      <c r="H123" s="112">
+      <c r="F123" s="102"/>
+      <c r="G123" s="102"/>
+      <c r="H123" s="197">
         <v>45631</v>
       </c>
-      <c r="I123" s="104"/>
+      <c r="I123" s="112"/>
       <c r="J123" s="62"/>
       <c r="K123" s="20"/>
       <c r="L123" s="20"/>
@@ -17921,11 +18197,11 @@
       <c r="B124" s="36"/>
       <c r="C124" s="60"/>
       <c r="D124" s="70"/>
-      <c r="E124" s="95"/>
-      <c r="F124" s="95"/>
-      <c r="G124" s="95"/>
-      <c r="H124" s="112"/>
-      <c r="I124" s="104"/>
+      <c r="E124" s="102"/>
+      <c r="F124" s="102"/>
+      <c r="G124" s="102"/>
+      <c r="H124" s="197"/>
+      <c r="I124" s="112"/>
       <c r="J124" s="62"/>
       <c r="K124" s="20"/>
       <c r="L124" s="20"/>
@@ -18043,15 +18319,15 @@
       <c r="B125" s="36"/>
       <c r="C125" s="60"/>
       <c r="D125" s="70"/>
-      <c r="E125" s="95" t="s">
+      <c r="E125" s="102" t="s">
         <v>71</v>
       </c>
-      <c r="F125" s="95"/>
-      <c r="G125" s="95"/>
-      <c r="H125" s="102">
+      <c r="F125" s="102"/>
+      <c r="G125" s="102"/>
+      <c r="H125" s="111">
         <v>45632</v>
       </c>
-      <c r="I125" s="104"/>
+      <c r="I125" s="112"/>
       <c r="J125" s="62"/>
       <c r="K125" s="20"/>
       <c r="L125" s="20"/>
@@ -18169,11 +18445,11 @@
       <c r="B126" s="36"/>
       <c r="C126" s="60"/>
       <c r="D126" s="70"/>
-      <c r="E126" s="95"/>
-      <c r="F126" s="95"/>
-      <c r="G126" s="95"/>
-      <c r="H126" s="102"/>
-      <c r="I126" s="104"/>
+      <c r="E126" s="102"/>
+      <c r="F126" s="102"/>
+      <c r="G126" s="102"/>
+      <c r="H126" s="111"/>
+      <c r="I126" s="112"/>
       <c r="J126" s="62"/>
       <c r="K126" s="20"/>
       <c r="L126" s="20"/>
@@ -18291,15 +18567,15 @@
       <c r="B127" s="36"/>
       <c r="C127" s="60"/>
       <c r="D127" s="70"/>
-      <c r="E127" s="95" t="s">
+      <c r="E127" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="F127" s="95"/>
-      <c r="G127" s="95"/>
+      <c r="F127" s="102"/>
+      <c r="G127" s="102"/>
       <c r="H127" s="103">
         <v>45635</v>
       </c>
-      <c r="I127" s="118"/>
+      <c r="I127" s="105"/>
       <c r="J127" s="19"/>
       <c r="K127" s="20"/>
       <c r="L127" s="20"/>
@@ -18417,11 +18693,11 @@
       <c r="B128" s="36"/>
       <c r="C128" s="60"/>
       <c r="D128" s="70"/>
-      <c r="E128" s="117"/>
-      <c r="F128" s="117"/>
-      <c r="G128" s="117"/>
-      <c r="H128" s="99"/>
-      <c r="I128" s="101"/>
+      <c r="E128" s="198"/>
+      <c r="F128" s="198"/>
+      <c r="G128" s="198"/>
+      <c r="H128" s="104"/>
+      <c r="I128" s="106"/>
       <c r="J128" s="19"/>
       <c r="K128" s="20"/>
       <c r="L128" s="20"/>
@@ -18539,15 +18815,15 @@
       <c r="B129" s="71"/>
       <c r="C129" s="91"/>
       <c r="D129" s="70"/>
-      <c r="E129" s="106" t="s">
+      <c r="E129" s="189" t="s">
         <v>61</v>
       </c>
-      <c r="F129" s="107"/>
-      <c r="G129" s="108"/>
-      <c r="H129" s="102">
+      <c r="F129" s="121"/>
+      <c r="G129" s="122"/>
+      <c r="H129" s="111">
         <v>45638</v>
       </c>
-      <c r="I129" s="104"/>
+      <c r="I129" s="112"/>
       <c r="J129" s="62"/>
       <c r="K129" s="20"/>
       <c r="L129" s="20"/>
@@ -18665,11 +18941,11 @@
       <c r="B130" s="71"/>
       <c r="C130" s="91"/>
       <c r="D130" s="70"/>
-      <c r="E130" s="109"/>
-      <c r="F130" s="110"/>
-      <c r="G130" s="111"/>
-      <c r="H130" s="102"/>
-      <c r="I130" s="104"/>
+      <c r="E130" s="150"/>
+      <c r="F130" s="125"/>
+      <c r="G130" s="126"/>
+      <c r="H130" s="111"/>
+      <c r="I130" s="112"/>
       <c r="J130" s="62"/>
       <c r="K130" s="20"/>
       <c r="L130" s="20"/>
@@ -18786,16 +19062,16 @@
       <c r="A131" s="16"/>
       <c r="B131" s="71"/>
       <c r="C131" s="91"/>
-      <c r="D131" s="95" t="s">
+      <c r="D131" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="E131" s="95"/>
-      <c r="F131" s="95"/>
-      <c r="G131" s="95"/>
+      <c r="E131" s="102"/>
+      <c r="F131" s="102"/>
+      <c r="G131" s="102"/>
       <c r="H131" s="103">
         <v>45635</v>
       </c>
-      <c r="I131" s="105"/>
+      <c r="I131" s="109"/>
       <c r="J131" s="62"/>
       <c r="K131" s="20"/>
       <c r="L131" s="20"/>
@@ -18912,12 +19188,12 @@
       <c r="A132" s="16"/>
       <c r="B132" s="71"/>
       <c r="C132" s="90"/>
-      <c r="D132" s="95"/>
-      <c r="E132" s="95"/>
-      <c r="F132" s="95"/>
-      <c r="G132" s="95"/>
-      <c r="H132" s="99"/>
-      <c r="I132" s="135"/>
+      <c r="D132" s="102"/>
+      <c r="E132" s="102"/>
+      <c r="F132" s="102"/>
+      <c r="G132" s="102"/>
+      <c r="H132" s="104"/>
+      <c r="I132" s="110"/>
       <c r="J132" s="62"/>
       <c r="K132" s="20"/>
       <c r="L132" s="20"/>
@@ -19033,15 +19309,15 @@
     <row r="133" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A133" s="16"/>
       <c r="B133" s="36"/>
-      <c r="C133" s="124" t="s">
+      <c r="C133" s="115" t="s">
         <v>67</v>
       </c>
-      <c r="D133" s="125"/>
-      <c r="E133" s="125"/>
-      <c r="F133" s="125"/>
-      <c r="G133" s="126"/>
-      <c r="H133" s="113"/>
-      <c r="I133" s="115"/>
+      <c r="D133" s="116"/>
+      <c r="E133" s="116"/>
+      <c r="F133" s="116"/>
+      <c r="G133" s="117"/>
+      <c r="H133" s="191"/>
+      <c r="I133" s="107"/>
       <c r="J133" s="66"/>
       <c r="K133" s="64"/>
       <c r="L133" s="64"/>
@@ -19157,13 +19433,13 @@
     <row r="134" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A134" s="16"/>
       <c r="B134" s="36"/>
-      <c r="C134" s="127"/>
-      <c r="D134" s="128"/>
-      <c r="E134" s="128"/>
-      <c r="F134" s="128"/>
-      <c r="G134" s="129"/>
-      <c r="H134" s="114"/>
-      <c r="I134" s="116"/>
+      <c r="C134" s="118"/>
+      <c r="D134" s="119"/>
+      <c r="E134" s="119"/>
+      <c r="F134" s="119"/>
+      <c r="G134" s="120"/>
+      <c r="H134" s="192"/>
+      <c r="I134" s="108"/>
       <c r="J134" s="66"/>
       <c r="K134" s="64"/>
       <c r="L134" s="64"/>
@@ -19280,14 +19556,14 @@
       <c r="A135" s="16"/>
       <c r="B135" s="36"/>
       <c r="C135" s="60"/>
-      <c r="D135" s="124" t="s">
+      <c r="D135" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="125"/>
-      <c r="F135" s="125"/>
-      <c r="G135" s="126"/>
-      <c r="H135" s="185"/>
-      <c r="I135" s="121"/>
+      <c r="E135" s="116"/>
+      <c r="F135" s="116"/>
+      <c r="G135" s="117"/>
+      <c r="H135" s="113"/>
+      <c r="I135" s="181"/>
       <c r="J135" s="63"/>
       <c r="K135" s="64"/>
       <c r="L135" s="64"/>
@@ -19404,12 +19680,12 @@
       <c r="A136" s="16"/>
       <c r="B136" s="36"/>
       <c r="C136" s="60"/>
-      <c r="D136" s="127"/>
-      <c r="E136" s="128"/>
-      <c r="F136" s="128"/>
-      <c r="G136" s="129"/>
-      <c r="H136" s="190"/>
-      <c r="I136" s="136"/>
+      <c r="D136" s="118"/>
+      <c r="E136" s="119"/>
+      <c r="F136" s="119"/>
+      <c r="G136" s="120"/>
+      <c r="H136" s="130"/>
+      <c r="I136" s="183"/>
       <c r="J136" s="63"/>
       <c r="K136" s="64"/>
       <c r="L136" s="64"/>
@@ -19527,15 +19803,15 @@
       <c r="B137" s="36"/>
       <c r="C137" s="72"/>
       <c r="D137" s="74"/>
-      <c r="E137" s="107" t="s">
+      <c r="E137" s="121" t="s">
         <v>73</v>
       </c>
-      <c r="F137" s="107"/>
-      <c r="G137" s="108"/>
+      <c r="F137" s="121"/>
+      <c r="G137" s="122"/>
       <c r="H137" s="103">
         <v>45636</v>
       </c>
-      <c r="I137" s="105"/>
+      <c r="I137" s="109"/>
       <c r="J137" s="62"/>
       <c r="K137" s="20"/>
       <c r="L137" s="20"/>
@@ -19653,11 +19929,11 @@
       <c r="B138" s="36"/>
       <c r="C138" s="72"/>
       <c r="D138" s="70"/>
-      <c r="E138" s="177"/>
-      <c r="F138" s="177"/>
-      <c r="G138" s="178"/>
-      <c r="H138" s="99"/>
-      <c r="I138" s="135"/>
+      <c r="E138" s="123"/>
+      <c r="F138" s="123"/>
+      <c r="G138" s="124"/>
+      <c r="H138" s="104"/>
+      <c r="I138" s="110"/>
       <c r="J138" s="62"/>
       <c r="K138" s="20"/>
       <c r="L138" s="20"/>
@@ -19775,15 +20051,15 @@
       <c r="B139" s="36"/>
       <c r="C139" s="72"/>
       <c r="D139" s="70"/>
-      <c r="E139" s="107" t="s">
+      <c r="E139" s="121" t="s">
         <v>74</v>
       </c>
-      <c r="F139" s="107"/>
-      <c r="G139" s="108"/>
+      <c r="F139" s="121"/>
+      <c r="G139" s="122"/>
       <c r="H139" s="103">
         <v>45637</v>
       </c>
-      <c r="I139" s="105"/>
+      <c r="I139" s="109"/>
       <c r="J139" s="62"/>
       <c r="K139" s="20"/>
       <c r="L139" s="20"/>
@@ -19901,11 +20177,11 @@
       <c r="B140" s="36"/>
       <c r="C140" s="72"/>
       <c r="D140" s="70"/>
-      <c r="E140" s="110"/>
-      <c r="F140" s="110"/>
-      <c r="G140" s="111"/>
-      <c r="H140" s="99"/>
-      <c r="I140" s="135"/>
+      <c r="E140" s="125"/>
+      <c r="F140" s="125"/>
+      <c r="G140" s="126"/>
+      <c r="H140" s="104"/>
+      <c r="I140" s="110"/>
       <c r="J140" s="62"/>
       <c r="K140" s="20"/>
       <c r="L140" s="20"/>
@@ -20022,12 +20298,12 @@
       <c r="A141" s="16"/>
       <c r="B141" s="36"/>
       <c r="C141" s="82"/>
-      <c r="D141" s="95" t="s">
+      <c r="D141" s="102" t="s">
         <v>80</v>
       </c>
-      <c r="E141" s="95"/>
-      <c r="F141" s="95"/>
-      <c r="G141" s="95"/>
+      <c r="E141" s="102"/>
+      <c r="F141" s="102"/>
+      <c r="G141" s="102"/>
       <c r="H141" s="103">
         <v>45637</v>
       </c>
@@ -20148,11 +20424,11 @@
       <c r="A142" s="16"/>
       <c r="B142" s="36"/>
       <c r="C142" s="82"/>
-      <c r="D142" s="95"/>
-      <c r="E142" s="95"/>
-      <c r="F142" s="95"/>
-      <c r="G142" s="95"/>
-      <c r="H142" s="99"/>
+      <c r="D142" s="102"/>
+      <c r="E142" s="102"/>
+      <c r="F142" s="102"/>
+      <c r="G142" s="102"/>
+      <c r="H142" s="104"/>
       <c r="I142" s="92"/>
       <c r="J142" s="62"/>
       <c r="K142" s="20"/>
@@ -20270,14 +20546,14 @@
       <c r="A143" s="16"/>
       <c r="B143" s="36"/>
       <c r="C143" s="72"/>
-      <c r="D143" s="187" t="s">
+      <c r="D143" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="E143" s="188"/>
-      <c r="F143" s="188"/>
-      <c r="G143" s="189"/>
-      <c r="H143" s="185"/>
-      <c r="I143" s="115"/>
+      <c r="E143" s="128"/>
+      <c r="F143" s="128"/>
+      <c r="G143" s="129"/>
+      <c r="H143" s="113"/>
+      <c r="I143" s="107"/>
       <c r="J143" s="66"/>
       <c r="K143" s="64"/>
       <c r="L143" s="64"/>
@@ -20394,12 +20670,12 @@
       <c r="A144" s="16"/>
       <c r="B144" s="36"/>
       <c r="C144" s="72"/>
-      <c r="D144" s="127"/>
-      <c r="E144" s="128"/>
-      <c r="F144" s="128"/>
-      <c r="G144" s="129"/>
-      <c r="H144" s="186"/>
-      <c r="I144" s="116"/>
+      <c r="D144" s="118"/>
+      <c r="E144" s="119"/>
+      <c r="F144" s="119"/>
+      <c r="G144" s="120"/>
+      <c r="H144" s="114"/>
+      <c r="I144" s="108"/>
       <c r="J144" s="66"/>
       <c r="K144" s="64"/>
       <c r="L144" s="64"/>
@@ -20517,15 +20793,15 @@
       <c r="B145" s="36"/>
       <c r="C145" s="72"/>
       <c r="D145" s="74"/>
-      <c r="E145" s="107" t="s">
+      <c r="E145" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="F145" s="107"/>
-      <c r="G145" s="108"/>
+      <c r="F145" s="121"/>
+      <c r="G145" s="122"/>
       <c r="H145" s="103">
         <v>45639</v>
       </c>
-      <c r="I145" s="105"/>
+      <c r="I145" s="109"/>
       <c r="J145" s="62"/>
       <c r="K145" s="20"/>
       <c r="L145" s="20"/>
@@ -20643,11 +20919,11 @@
       <c r="B146" s="36"/>
       <c r="C146" s="72"/>
       <c r="D146" s="70"/>
-      <c r="E146" s="177"/>
-      <c r="F146" s="177"/>
-      <c r="G146" s="178"/>
-      <c r="H146" s="99"/>
-      <c r="I146" s="135"/>
+      <c r="E146" s="123"/>
+      <c r="F146" s="123"/>
+      <c r="G146" s="124"/>
+      <c r="H146" s="104"/>
+      <c r="I146" s="110"/>
       <c r="J146" s="62"/>
       <c r="K146" s="20"/>
       <c r="L146" s="20"/>
@@ -20765,15 +21041,15 @@
       <c r="B147" s="36"/>
       <c r="C147" s="72"/>
       <c r="D147" s="70"/>
-      <c r="E147" s="107" t="s">
+      <c r="E147" s="121" t="s">
         <v>69</v>
       </c>
-      <c r="F147" s="107"/>
-      <c r="G147" s="108"/>
+      <c r="F147" s="121"/>
+      <c r="G147" s="122"/>
       <c r="H147" s="103">
         <v>45642</v>
       </c>
-      <c r="I147" s="105"/>
+      <c r="I147" s="109"/>
       <c r="J147" s="62"/>
       <c r="K147" s="20"/>
       <c r="L147" s="20"/>
@@ -20891,11 +21167,11 @@
       <c r="B148" s="36"/>
       <c r="C148" s="72"/>
       <c r="D148" s="70"/>
-      <c r="E148" s="177"/>
-      <c r="F148" s="177"/>
-      <c r="G148" s="178"/>
-      <c r="H148" s="99"/>
-      <c r="I148" s="135"/>
+      <c r="E148" s="123"/>
+      <c r="F148" s="123"/>
+      <c r="G148" s="124"/>
+      <c r="H148" s="104"/>
+      <c r="I148" s="110"/>
       <c r="J148" s="62"/>
       <c r="K148" s="20"/>
       <c r="L148" s="20"/>
@@ -21013,15 +21289,15 @@
       <c r="B149" s="36"/>
       <c r="C149" s="72"/>
       <c r="D149" s="70"/>
-      <c r="E149" s="107" t="s">
+      <c r="E149" s="121" t="s">
         <v>70</v>
       </c>
-      <c r="F149" s="107"/>
-      <c r="G149" s="108"/>
+      <c r="F149" s="121"/>
+      <c r="G149" s="122"/>
       <c r="H149" s="103">
         <v>45643</v>
       </c>
-      <c r="I149" s="105"/>
+      <c r="I149" s="109"/>
       <c r="J149" s="62"/>
       <c r="K149" s="20"/>
       <c r="L149" s="20"/>
@@ -21139,11 +21415,11 @@
       <c r="B150" s="36"/>
       <c r="C150" s="72"/>
       <c r="D150" s="70"/>
-      <c r="E150" s="177"/>
-      <c r="F150" s="177"/>
-      <c r="G150" s="178"/>
-      <c r="H150" s="99"/>
-      <c r="I150" s="135"/>
+      <c r="E150" s="123"/>
+      <c r="F150" s="123"/>
+      <c r="G150" s="124"/>
+      <c r="H150" s="104"/>
+      <c r="I150" s="110"/>
       <c r="J150" s="62"/>
       <c r="K150" s="20"/>
       <c r="L150" s="20"/>
@@ -21261,15 +21537,15 @@
       <c r="B151" s="36"/>
       <c r="C151" s="72"/>
       <c r="D151" s="70"/>
-      <c r="E151" s="95" t="s">
+      <c r="E151" s="102" t="s">
         <v>75</v>
       </c>
-      <c r="F151" s="95"/>
-      <c r="G151" s="95"/>
+      <c r="F151" s="102"/>
+      <c r="G151" s="102"/>
       <c r="H151" s="103">
         <v>45644</v>
       </c>
-      <c r="I151" s="105"/>
+      <c r="I151" s="109"/>
       <c r="J151" s="62"/>
       <c r="K151" s="20"/>
       <c r="L151" s="20"/>
@@ -21387,11 +21663,11 @@
       <c r="B152" s="36"/>
       <c r="C152" s="72"/>
       <c r="D152" s="70"/>
-      <c r="E152" s="95"/>
-      <c r="F152" s="95"/>
-      <c r="G152" s="95"/>
-      <c r="H152" s="99"/>
-      <c r="I152" s="135"/>
+      <c r="E152" s="102"/>
+      <c r="F152" s="102"/>
+      <c r="G152" s="102"/>
+      <c r="H152" s="104"/>
+      <c r="I152" s="110"/>
       <c r="J152" s="62"/>
       <c r="K152" s="20"/>
       <c r="L152" s="20"/>
@@ -21509,15 +21785,15 @@
       <c r="B153" s="36"/>
       <c r="C153" s="72"/>
       <c r="D153" s="70"/>
-      <c r="E153" s="95" t="s">
+      <c r="E153" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="F153" s="95"/>
-      <c r="G153" s="95"/>
+      <c r="F153" s="102"/>
+      <c r="G153" s="102"/>
       <c r="H153" s="103">
         <v>45644</v>
       </c>
-      <c r="I153" s="105"/>
+      <c r="I153" s="109"/>
       <c r="J153" s="62"/>
       <c r="K153" s="20"/>
       <c r="L153" s="20"/>
@@ -21635,11 +21911,11 @@
       <c r="B154" s="36"/>
       <c r="C154" s="72"/>
       <c r="D154" s="70"/>
-      <c r="E154" s="95"/>
-      <c r="F154" s="95"/>
-      <c r="G154" s="95"/>
-      <c r="H154" s="99"/>
-      <c r="I154" s="135"/>
+      <c r="E154" s="102"/>
+      <c r="F154" s="102"/>
+      <c r="G154" s="102"/>
+      <c r="H154" s="104"/>
+      <c r="I154" s="110"/>
       <c r="J154" s="62"/>
       <c r="K154" s="20"/>
       <c r="L154" s="20"/>
@@ -21756,16 +22032,16 @@
       <c r="A155" s="1"/>
       <c r="B155" s="18"/>
       <c r="C155" s="60"/>
-      <c r="D155" s="96"/>
-      <c r="E155" s="94" t="s">
+      <c r="D155" s="194"/>
+      <c r="E155" s="193" t="s">
         <v>61</v>
       </c>
-      <c r="F155" s="95"/>
-      <c r="G155" s="95"/>
-      <c r="H155" s="98">
+      <c r="F155" s="102"/>
+      <c r="G155" s="102"/>
+      <c r="H155" s="195">
         <v>45645</v>
       </c>
-      <c r="I155" s="100"/>
+      <c r="I155" s="196"/>
       <c r="J155" s="19"/>
       <c r="K155" s="20"/>
       <c r="L155" s="20"/>
@@ -21882,12 +22158,12 @@
       <c r="A156" s="1"/>
       <c r="B156" s="18"/>
       <c r="C156" s="60"/>
-      <c r="D156" s="97"/>
-      <c r="E156" s="94"/>
-      <c r="F156" s="95"/>
-      <c r="G156" s="95"/>
-      <c r="H156" s="99"/>
-      <c r="I156" s="101"/>
+      <c r="D156" s="149"/>
+      <c r="E156" s="193"/>
+      <c r="F156" s="102"/>
+      <c r="G156" s="102"/>
+      <c r="H156" s="104"/>
+      <c r="I156" s="106"/>
       <c r="J156" s="19"/>
       <c r="K156" s="20"/>
       <c r="L156" s="20"/>
@@ -22004,16 +22280,16 @@
       <c r="A157" s="1"/>
       <c r="B157" s="93"/>
       <c r="C157" s="90"/>
-      <c r="D157" s="95" t="s">
+      <c r="D157" s="102" t="s">
         <v>81</v>
       </c>
-      <c r="E157" s="95"/>
-      <c r="F157" s="95"/>
-      <c r="G157" s="95"/>
+      <c r="E157" s="102"/>
+      <c r="F157" s="102"/>
+      <c r="G157" s="102"/>
       <c r="H157" s="103">
         <v>45644</v>
       </c>
-      <c r="I157" s="118"/>
+      <c r="I157" s="105"/>
       <c r="J157" s="19"/>
       <c r="K157" s="20"/>
       <c r="L157" s="20"/>
@@ -22130,12 +22406,12 @@
       <c r="A158" s="1"/>
       <c r="B158" s="93"/>
       <c r="C158" s="90"/>
-      <c r="D158" s="95"/>
-      <c r="E158" s="95"/>
-      <c r="F158" s="95"/>
-      <c r="G158" s="95"/>
-      <c r="H158" s="99"/>
-      <c r="I158" s="101"/>
+      <c r="D158" s="102"/>
+      <c r="E158" s="102"/>
+      <c r="F158" s="102"/>
+      <c r="G158" s="102"/>
+      <c r="H158" s="104"/>
+      <c r="I158" s="106"/>
       <c r="J158" s="19"/>
       <c r="K158" s="20"/>
       <c r="L158" s="20"/>
@@ -22253,17 +22529,17 @@
       <c r="B159" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="C159" s="143" t="s">
+      <c r="C159" s="173" t="s">
         <v>31</v>
       </c>
-      <c r="D159" s="144"/>
-      <c r="E159" s="144"/>
-      <c r="F159" s="144"/>
-      <c r="G159" s="145"/>
-      <c r="H159" s="130" t="s">
+      <c r="D159" s="174"/>
+      <c r="E159" s="174"/>
+      <c r="F159" s="174"/>
+      <c r="G159" s="175"/>
+      <c r="H159" s="184" t="s">
         <v>57</v>
       </c>
-      <c r="I159" s="104"/>
+      <c r="I159" s="112"/>
       <c r="J159" s="14"/>
       <c r="K159" s="15"/>
       <c r="L159" s="15"/>
@@ -22316,8 +22592,8 @@
       <c r="BG159" s="15"/>
       <c r="BH159" s="15"/>
       <c r="BI159" s="15"/>
-      <c r="BJ159" s="193"/>
-      <c r="BK159" s="193"/>
+      <c r="BJ159" s="96"/>
+      <c r="BK159" s="96"/>
       <c r="BL159" s="15"/>
       <c r="BM159" s="15"/>
       <c r="BN159" s="15"/>
@@ -22379,13 +22655,13 @@
     <row r="160" spans="1:120" ht="9.75" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="87"/>
-      <c r="C160" s="146"/>
-      <c r="D160" s="147"/>
-      <c r="E160" s="147"/>
-      <c r="F160" s="147"/>
-      <c r="G160" s="148"/>
-      <c r="H160" s="104"/>
-      <c r="I160" s="104"/>
+      <c r="C160" s="176"/>
+      <c r="D160" s="177"/>
+      <c r="E160" s="177"/>
+      <c r="F160" s="177"/>
+      <c r="G160" s="178"/>
+      <c r="H160" s="112"/>
+      <c r="I160" s="112"/>
       <c r="J160" s="14"/>
       <c r="K160" s="15"/>
       <c r="L160" s="15"/>
@@ -22438,8 +22714,8 @@
       <c r="BG160" s="15"/>
       <c r="BH160" s="15"/>
       <c r="BI160" s="15"/>
-      <c r="BJ160" s="193"/>
-      <c r="BK160" s="193"/>
+      <c r="BJ160" s="96"/>
+      <c r="BK160" s="96"/>
       <c r="BL160" s="15"/>
       <c r="BM160" s="15"/>
       <c r="BN160" s="15"/>
@@ -22506,8 +22782,8 @@
       <c r="E161" s="85"/>
       <c r="F161" s="85"/>
       <c r="G161" s="86"/>
-      <c r="H161" s="104"/>
-      <c r="I161" s="104"/>
+      <c r="H161" s="112"/>
+      <c r="I161" s="112"/>
       <c r="J161" s="12"/>
       <c r="K161" s="13"/>
       <c r="L161" s="13"/>
@@ -22560,8 +22836,8 @@
       <c r="BG161" s="13"/>
       <c r="BH161" s="13"/>
       <c r="BI161" s="13"/>
-      <c r="BJ161" s="192"/>
-      <c r="BK161" s="192"/>
+      <c r="BJ161" s="95"/>
+      <c r="BK161" s="95"/>
       <c r="BL161" s="13"/>
       <c r="BM161" s="13"/>
       <c r="BN161" s="13"/>
@@ -22628,8 +22904,8 @@
       <c r="E162" s="88"/>
       <c r="F162" s="88"/>
       <c r="G162" s="89"/>
-      <c r="H162" s="104"/>
-      <c r="I162" s="104"/>
+      <c r="H162" s="112"/>
+      <c r="I162" s="112"/>
       <c r="J162" s="14"/>
       <c r="K162" s="15"/>
       <c r="L162" s="15"/>
@@ -22682,8 +22958,8 @@
       <c r="BG162" s="15"/>
       <c r="BH162" s="15"/>
       <c r="BI162" s="15"/>
-      <c r="BJ162" s="193"/>
-      <c r="BK162" s="193"/>
+      <c r="BJ162" s="96"/>
+      <c r="BK162" s="96"/>
       <c r="BL162" s="15"/>
       <c r="BM162" s="15"/>
       <c r="BN162" s="15"/>
@@ -22745,17 +23021,17 @@
     <row r="163" spans="1:120" ht="9.75" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
-      <c r="C163" s="137" t="s">
+      <c r="C163" s="168" t="s">
         <v>33</v>
       </c>
-      <c r="D163" s="138"/>
-      <c r="E163" s="138"/>
-      <c r="F163" s="138"/>
-      <c r="G163" s="139"/>
-      <c r="H163" s="130" t="s">
+      <c r="D163" s="140"/>
+      <c r="E163" s="140"/>
+      <c r="F163" s="140"/>
+      <c r="G163" s="169"/>
+      <c r="H163" s="184" t="s">
         <v>56</v>
       </c>
-      <c r="I163" s="104"/>
+      <c r="I163" s="112"/>
       <c r="J163" s="19"/>
       <c r="K163" s="20"/>
       <c r="L163" s="20"/>
@@ -22871,13 +23147,13 @@
     <row r="164" spans="1:120" ht="9.75" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
-      <c r="C164" s="140"/>
-      <c r="D164" s="141"/>
-      <c r="E164" s="141"/>
-      <c r="F164" s="141"/>
-      <c r="G164" s="142"/>
-      <c r="H164" s="104"/>
-      <c r="I164" s="104"/>
+      <c r="C164" s="170"/>
+      <c r="D164" s="171"/>
+      <c r="E164" s="171"/>
+      <c r="F164" s="171"/>
+      <c r="G164" s="172"/>
+      <c r="H164" s="112"/>
+      <c r="I164" s="112"/>
       <c r="J164" s="19"/>
       <c r="K164" s="20"/>
       <c r="L164" s="20"/>
@@ -23052,8 +23328,8 @@
       <c r="BG165" s="2"/>
       <c r="BH165" s="2"/>
       <c r="BI165" s="2"/>
-      <c r="BJ165" s="191"/>
-      <c r="BK165" s="191"/>
+      <c r="BJ165" s="94"/>
+      <c r="BK165" s="94"/>
       <c r="BL165" s="2"/>
       <c r="BM165" s="2"/>
       <c r="BN165" s="2"/>
@@ -23174,8 +23450,8 @@
       <c r="BG166" s="2"/>
       <c r="BH166" s="2"/>
       <c r="BI166" s="2"/>
-      <c r="BJ166" s="191"/>
-      <c r="BK166" s="191"/>
+      <c r="BJ166" s="94"/>
+      <c r="BK166" s="94"/>
       <c r="BL166" s="2"/>
       <c r="BM166" s="2"/>
       <c r="BN166" s="2"/>
@@ -23296,8 +23572,8 @@
       <c r="BG167" s="2"/>
       <c r="BH167" s="2"/>
       <c r="BI167" s="2"/>
-      <c r="BJ167" s="191"/>
-      <c r="BK167" s="191"/>
+      <c r="BJ167" s="94"/>
+      <c r="BK167" s="94"/>
       <c r="BL167" s="2"/>
       <c r="BM167" s="2"/>
       <c r="BN167" s="2"/>
@@ -23418,8 +23694,8 @@
       <c r="BG168" s="2"/>
       <c r="BH168" s="2"/>
       <c r="BI168" s="2"/>
-      <c r="BJ168" s="191"/>
-      <c r="BK168" s="191"/>
+      <c r="BJ168" s="94"/>
+      <c r="BK168" s="94"/>
       <c r="BL168" s="2"/>
       <c r="BM168" s="2"/>
       <c r="BN168" s="2"/>
@@ -23540,8 +23816,8 @@
       <c r="BG169" s="2"/>
       <c r="BH169" s="2"/>
       <c r="BI169" s="2"/>
-      <c r="BJ169" s="191"/>
-      <c r="BK169" s="191"/>
+      <c r="BJ169" s="94"/>
+      <c r="BK169" s="94"/>
       <c r="BL169" s="2"/>
       <c r="BM169" s="2"/>
       <c r="BN169" s="2"/>
@@ -23662,8 +23938,8 @@
       <c r="BG170" s="2"/>
       <c r="BH170" s="2"/>
       <c r="BI170" s="2"/>
-      <c r="BJ170" s="191"/>
-      <c r="BK170" s="191"/>
+      <c r="BJ170" s="94"/>
+      <c r="BK170" s="94"/>
       <c r="BL170" s="2"/>
       <c r="BM170" s="2"/>
       <c r="BN170" s="2"/>
@@ -23784,8 +24060,8 @@
       <c r="BG171" s="2"/>
       <c r="BH171" s="2"/>
       <c r="BI171" s="2"/>
-      <c r="BJ171" s="191"/>
-      <c r="BK171" s="191"/>
+      <c r="BJ171" s="94"/>
+      <c r="BK171" s="94"/>
       <c r="BL171" s="2"/>
       <c r="BM171" s="2"/>
       <c r="BN171" s="2"/>
@@ -23906,8 +24182,8 @@
       <c r="BG172" s="2"/>
       <c r="BH172" s="2"/>
       <c r="BI172" s="2"/>
-      <c r="BJ172" s="191"/>
-      <c r="BK172" s="191"/>
+      <c r="BJ172" s="94"/>
+      <c r="BK172" s="94"/>
       <c r="BL172" s="2"/>
       <c r="BM172" s="2"/>
       <c r="BN172" s="2"/>
@@ -24028,8 +24304,8 @@
       <c r="BG173" s="2"/>
       <c r="BH173" s="2"/>
       <c r="BI173" s="2"/>
-      <c r="BJ173" s="191"/>
-      <c r="BK173" s="191"/>
+      <c r="BJ173" s="94"/>
+      <c r="BK173" s="94"/>
       <c r="BL173" s="2"/>
       <c r="BM173" s="2"/>
       <c r="BN173" s="2"/>
@@ -24150,8 +24426,8 @@
       <c r="BG174" s="2"/>
       <c r="BH174" s="2"/>
       <c r="BI174" s="2"/>
-      <c r="BJ174" s="191"/>
-      <c r="BK174" s="191"/>
+      <c r="BJ174" s="94"/>
+      <c r="BK174" s="94"/>
       <c r="BL174" s="2"/>
       <c r="BM174" s="2"/>
       <c r="BN174" s="2"/>
@@ -24272,8 +24548,8 @@
       <c r="BG175" s="2"/>
       <c r="BH175" s="2"/>
       <c r="BI175" s="2"/>
-      <c r="BJ175" s="191"/>
-      <c r="BK175" s="191"/>
+      <c r="BJ175" s="94"/>
+      <c r="BK175" s="94"/>
       <c r="BL175" s="2"/>
       <c r="BM175" s="2"/>
       <c r="BN175" s="2"/>
@@ -24394,8 +24670,8 @@
       <c r="BG176" s="2"/>
       <c r="BH176" s="2"/>
       <c r="BI176" s="2"/>
-      <c r="BJ176" s="191"/>
-      <c r="BK176" s="191"/>
+      <c r="BJ176" s="94"/>
+      <c r="BK176" s="94"/>
       <c r="BL176" s="2"/>
       <c r="BM176" s="2"/>
       <c r="BN176" s="2"/>
@@ -24516,8 +24792,8 @@
       <c r="BG177" s="2"/>
       <c r="BH177" s="2"/>
       <c r="BI177" s="2"/>
-      <c r="BJ177" s="191"/>
-      <c r="BK177" s="191"/>
+      <c r="BJ177" s="94"/>
+      <c r="BK177" s="94"/>
       <c r="BL177" s="2"/>
       <c r="BM177" s="2"/>
       <c r="BN177" s="2"/>
@@ -24638,8 +24914,8 @@
       <c r="BG178" s="2"/>
       <c r="BH178" s="2"/>
       <c r="BI178" s="2"/>
-      <c r="BJ178" s="191"/>
-      <c r="BK178" s="191"/>
+      <c r="BJ178" s="94"/>
+      <c r="BK178" s="94"/>
       <c r="BL178" s="2"/>
       <c r="BM178" s="2"/>
       <c r="BN178" s="2"/>
@@ -24760,8 +25036,8 @@
       <c r="BG179" s="2"/>
       <c r="BH179" s="2"/>
       <c r="BI179" s="2"/>
-      <c r="BJ179" s="191"/>
-      <c r="BK179" s="191"/>
+      <c r="BJ179" s="94"/>
+      <c r="BK179" s="94"/>
       <c r="BL179" s="2"/>
       <c r="BM179" s="2"/>
       <c r="BN179" s="2"/>
@@ -24882,8 +25158,8 @@
       <c r="BG180" s="2"/>
       <c r="BH180" s="2"/>
       <c r="BI180" s="2"/>
-      <c r="BJ180" s="191"/>
-      <c r="BK180" s="191"/>
+      <c r="BJ180" s="94"/>
+      <c r="BK180" s="94"/>
       <c r="BL180" s="2"/>
       <c r="BM180" s="2"/>
       <c r="BN180" s="2"/>
@@ -25004,8 +25280,8 @@
       <c r="BG181" s="2"/>
       <c r="BH181" s="2"/>
       <c r="BI181" s="2"/>
-      <c r="BJ181" s="191"/>
-      <c r="BK181" s="191"/>
+      <c r="BJ181" s="94"/>
+      <c r="BK181" s="94"/>
       <c r="BL181" s="2"/>
       <c r="BM181" s="2"/>
       <c r="BN181" s="2"/>
@@ -25126,8 +25402,8 @@
       <c r="BG182" s="2"/>
       <c r="BH182" s="2"/>
       <c r="BI182" s="2"/>
-      <c r="BJ182" s="191"/>
-      <c r="BK182" s="191"/>
+      <c r="BJ182" s="94"/>
+      <c r="BK182" s="94"/>
       <c r="BL182" s="2"/>
       <c r="BM182" s="2"/>
       <c r="BN182" s="2"/>
@@ -25248,8 +25524,8 @@
       <c r="BG183" s="2"/>
       <c r="BH183" s="2"/>
       <c r="BI183" s="2"/>
-      <c r="BJ183" s="191"/>
-      <c r="BK183" s="191"/>
+      <c r="BJ183" s="94"/>
+      <c r="BK183" s="94"/>
       <c r="BL183" s="2"/>
       <c r="BM183" s="2"/>
       <c r="BN183" s="2"/>
@@ -25370,8 +25646,8 @@
       <c r="BG184" s="2"/>
       <c r="BH184" s="2"/>
       <c r="BI184" s="2"/>
-      <c r="BJ184" s="191"/>
-      <c r="BK184" s="191"/>
+      <c r="BJ184" s="94"/>
+      <c r="BK184" s="94"/>
       <c r="BL184" s="2"/>
       <c r="BM184" s="2"/>
       <c r="BN184" s="2"/>
@@ -25492,8 +25768,8 @@
       <c r="BG185" s="2"/>
       <c r="BH185" s="2"/>
       <c r="BI185" s="2"/>
-      <c r="BJ185" s="191"/>
-      <c r="BK185" s="191"/>
+      <c r="BJ185" s="94"/>
+      <c r="BK185" s="94"/>
       <c r="BL185" s="2"/>
       <c r="BM185" s="2"/>
       <c r="BN185" s="2"/>
@@ -25614,8 +25890,8 @@
       <c r="BG186" s="2"/>
       <c r="BH186" s="2"/>
       <c r="BI186" s="2"/>
-      <c r="BJ186" s="191"/>
-      <c r="BK186" s="191"/>
+      <c r="BJ186" s="94"/>
+      <c r="BK186" s="94"/>
       <c r="BL186" s="2"/>
       <c r="BM186" s="2"/>
       <c r="BN186" s="2"/>
@@ -25736,8 +26012,8 @@
       <c r="BG187" s="2"/>
       <c r="BH187" s="2"/>
       <c r="BI187" s="2"/>
-      <c r="BJ187" s="191"/>
-      <c r="BK187" s="191"/>
+      <c r="BJ187" s="94"/>
+      <c r="BK187" s="94"/>
       <c r="BL187" s="2"/>
       <c r="BM187" s="2"/>
       <c r="BN187" s="2"/>
@@ -25858,8 +26134,8 @@
       <c r="BG188" s="2"/>
       <c r="BH188" s="2"/>
       <c r="BI188" s="2"/>
-      <c r="BJ188" s="191"/>
-      <c r="BK188" s="191"/>
+      <c r="BJ188" s="94"/>
+      <c r="BK188" s="94"/>
       <c r="BL188" s="2"/>
       <c r="BM188" s="2"/>
       <c r="BN188" s="2"/>
@@ -25980,8 +26256,8 @@
       <c r="BG189" s="2"/>
       <c r="BH189" s="2"/>
       <c r="BI189" s="2"/>
-      <c r="BJ189" s="191"/>
-      <c r="BK189" s="191"/>
+      <c r="BJ189" s="94"/>
+      <c r="BK189" s="94"/>
       <c r="BL189" s="2"/>
       <c r="BM189" s="2"/>
       <c r="BN189" s="2"/>
@@ -26102,8 +26378,8 @@
       <c r="BG190" s="2"/>
       <c r="BH190" s="2"/>
       <c r="BI190" s="2"/>
-      <c r="BJ190" s="191"/>
-      <c r="BK190" s="191"/>
+      <c r="BJ190" s="94"/>
+      <c r="BK190" s="94"/>
       <c r="BL190" s="2"/>
       <c r="BM190" s="2"/>
       <c r="BN190" s="2"/>
@@ -26224,8 +26500,8 @@
       <c r="BG191" s="2"/>
       <c r="BH191" s="2"/>
       <c r="BI191" s="2"/>
-      <c r="BJ191" s="191"/>
-      <c r="BK191" s="191"/>
+      <c r="BJ191" s="94"/>
+      <c r="BK191" s="94"/>
       <c r="BL191" s="2"/>
       <c r="BM191" s="2"/>
       <c r="BN191" s="2"/>
@@ -26346,8 +26622,8 @@
       <c r="BG192" s="2"/>
       <c r="BH192" s="2"/>
       <c r="BI192" s="2"/>
-      <c r="BJ192" s="191"/>
-      <c r="BK192" s="191"/>
+      <c r="BJ192" s="94"/>
+      <c r="BK192" s="94"/>
       <c r="BL192" s="2"/>
       <c r="BM192" s="2"/>
       <c r="BN192" s="2"/>
@@ -26468,8 +26744,8 @@
       <c r="BG193" s="2"/>
       <c r="BH193" s="2"/>
       <c r="BI193" s="2"/>
-      <c r="BJ193" s="191"/>
-      <c r="BK193" s="191"/>
+      <c r="BJ193" s="94"/>
+      <c r="BK193" s="94"/>
       <c r="BL193" s="2"/>
       <c r="BM193" s="2"/>
       <c r="BN193" s="2"/>
@@ -26590,8 +26866,8 @@
       <c r="BG194" s="2"/>
       <c r="BH194" s="2"/>
       <c r="BI194" s="2"/>
-      <c r="BJ194" s="191"/>
-      <c r="BK194" s="191"/>
+      <c r="BJ194" s="94"/>
+      <c r="BK194" s="94"/>
       <c r="BL194" s="2"/>
       <c r="BM194" s="2"/>
       <c r="BN194" s="2"/>
@@ -26712,8 +26988,8 @@
       <c r="BG195" s="2"/>
       <c r="BH195" s="2"/>
       <c r="BI195" s="2"/>
-      <c r="BJ195" s="191"/>
-      <c r="BK195" s="191"/>
+      <c r="BJ195" s="94"/>
+      <c r="BK195" s="94"/>
       <c r="BL195" s="2"/>
       <c r="BM195" s="2"/>
       <c r="BN195" s="2"/>
@@ -26834,8 +27110,8 @@
       <c r="BG196" s="2"/>
       <c r="BH196" s="2"/>
       <c r="BI196" s="2"/>
-      <c r="BJ196" s="191"/>
-      <c r="BK196" s="191"/>
+      <c r="BJ196" s="94"/>
+      <c r="BK196" s="94"/>
       <c r="BL196" s="2"/>
       <c r="BM196" s="2"/>
       <c r="BN196" s="2"/>
@@ -26956,8 +27232,8 @@
       <c r="BG197" s="2"/>
       <c r="BH197" s="2"/>
       <c r="BI197" s="2"/>
-      <c r="BJ197" s="191"/>
-      <c r="BK197" s="191"/>
+      <c r="BJ197" s="94"/>
+      <c r="BK197" s="94"/>
       <c r="BL197" s="2"/>
       <c r="BM197" s="2"/>
       <c r="BN197" s="2"/>
@@ -27078,8 +27354,8 @@
       <c r="BG198" s="2"/>
       <c r="BH198" s="2"/>
       <c r="BI198" s="2"/>
-      <c r="BJ198" s="191"/>
-      <c r="BK198" s="191"/>
+      <c r="BJ198" s="94"/>
+      <c r="BK198" s="94"/>
       <c r="BL198" s="2"/>
       <c r="BM198" s="2"/>
       <c r="BN198" s="2"/>
@@ -27200,8 +27476,8 @@
       <c r="BG199" s="2"/>
       <c r="BH199" s="2"/>
       <c r="BI199" s="2"/>
-      <c r="BJ199" s="191"/>
-      <c r="BK199" s="191"/>
+      <c r="BJ199" s="94"/>
+      <c r="BK199" s="94"/>
       <c r="BL199" s="2"/>
       <c r="BM199" s="2"/>
       <c r="BN199" s="2"/>
@@ -27322,8 +27598,8 @@
       <c r="BG200" s="2"/>
       <c r="BH200" s="2"/>
       <c r="BI200" s="2"/>
-      <c r="BJ200" s="191"/>
-      <c r="BK200" s="191"/>
+      <c r="BJ200" s="94"/>
+      <c r="BK200" s="94"/>
       <c r="BL200" s="2"/>
       <c r="BM200" s="2"/>
       <c r="BN200" s="2"/>
@@ -27444,8 +27720,8 @@
       <c r="BG201" s="2"/>
       <c r="BH201" s="2"/>
       <c r="BI201" s="2"/>
-      <c r="BJ201" s="191"/>
-      <c r="BK201" s="191"/>
+      <c r="BJ201" s="94"/>
+      <c r="BK201" s="94"/>
       <c r="BL201" s="2"/>
       <c r="BM201" s="2"/>
       <c r="BN201" s="2"/>
@@ -27566,8 +27842,8 @@
       <c r="BG202" s="2"/>
       <c r="BH202" s="2"/>
       <c r="BI202" s="2"/>
-      <c r="BJ202" s="191"/>
-      <c r="BK202" s="191"/>
+      <c r="BJ202" s="94"/>
+      <c r="BK202" s="94"/>
       <c r="BL202" s="2"/>
       <c r="BM202" s="2"/>
       <c r="BN202" s="2"/>
@@ -27688,8 +27964,8 @@
       <c r="BG203" s="2"/>
       <c r="BH203" s="2"/>
       <c r="BI203" s="2"/>
-      <c r="BJ203" s="191"/>
-      <c r="BK203" s="191"/>
+      <c r="BJ203" s="94"/>
+      <c r="BK203" s="94"/>
       <c r="BL203" s="2"/>
       <c r="BM203" s="2"/>
       <c r="BN203" s="2"/>
@@ -27810,8 +28086,8 @@
       <c r="BG204" s="2"/>
       <c r="BH204" s="2"/>
       <c r="BI204" s="2"/>
-      <c r="BJ204" s="191"/>
-      <c r="BK204" s="191"/>
+      <c r="BJ204" s="94"/>
+      <c r="BK204" s="94"/>
       <c r="BL204" s="2"/>
       <c r="BM204" s="2"/>
       <c r="BN204" s="2"/>
@@ -27932,8 +28208,8 @@
       <c r="BG205" s="2"/>
       <c r="BH205" s="2"/>
       <c r="BI205" s="2"/>
-      <c r="BJ205" s="191"/>
-      <c r="BK205" s="191"/>
+      <c r="BJ205" s="94"/>
+      <c r="BK205" s="94"/>
       <c r="BL205" s="2"/>
       <c r="BM205" s="2"/>
       <c r="BN205" s="2"/>
@@ -28054,8 +28330,8 @@
       <c r="BG206" s="2"/>
       <c r="BH206" s="2"/>
       <c r="BI206" s="2"/>
-      <c r="BJ206" s="191"/>
-      <c r="BK206" s="191"/>
+      <c r="BJ206" s="94"/>
+      <c r="BK206" s="94"/>
       <c r="BL206" s="2"/>
       <c r="BM206" s="2"/>
       <c r="BN206" s="2"/>
@@ -28176,8 +28452,8 @@
       <c r="BG207" s="2"/>
       <c r="BH207" s="2"/>
       <c r="BI207" s="2"/>
-      <c r="BJ207" s="191"/>
-      <c r="BK207" s="191"/>
+      <c r="BJ207" s="94"/>
+      <c r="BK207" s="94"/>
       <c r="BL207" s="2"/>
       <c r="BM207" s="2"/>
       <c r="BN207" s="2"/>
@@ -28298,8 +28574,8 @@
       <c r="BG208" s="2"/>
       <c r="BH208" s="2"/>
       <c r="BI208" s="2"/>
-      <c r="BJ208" s="191"/>
-      <c r="BK208" s="191"/>
+      <c r="BJ208" s="94"/>
+      <c r="BK208" s="94"/>
       <c r="BL208" s="2"/>
       <c r="BM208" s="2"/>
       <c r="BN208" s="2"/>
@@ -28420,8 +28696,8 @@
       <c r="BG209" s="2"/>
       <c r="BH209" s="2"/>
       <c r="BI209" s="2"/>
-      <c r="BJ209" s="191"/>
-      <c r="BK209" s="191"/>
+      <c r="BJ209" s="94"/>
+      <c r="BK209" s="94"/>
       <c r="BL209" s="2"/>
       <c r="BM209" s="2"/>
       <c r="BN209" s="2"/>
@@ -28542,8 +28818,8 @@
       <c r="BG210" s="2"/>
       <c r="BH210" s="2"/>
       <c r="BI210" s="2"/>
-      <c r="BJ210" s="191"/>
-      <c r="BK210" s="191"/>
+      <c r="BJ210" s="94"/>
+      <c r="BK210" s="94"/>
       <c r="BL210" s="2"/>
       <c r="BM210" s="2"/>
       <c r="BN210" s="2"/>
@@ -28664,8 +28940,8 @@
       <c r="BG211" s="2"/>
       <c r="BH211" s="2"/>
       <c r="BI211" s="2"/>
-      <c r="BJ211" s="191"/>
-      <c r="BK211" s="191"/>
+      <c r="BJ211" s="94"/>
+      <c r="BK211" s="94"/>
       <c r="BL211" s="2"/>
       <c r="BM211" s="2"/>
       <c r="BN211" s="2"/>
@@ -28786,8 +29062,8 @@
       <c r="BG212" s="2"/>
       <c r="BH212" s="2"/>
       <c r="BI212" s="2"/>
-      <c r="BJ212" s="191"/>
-      <c r="BK212" s="191"/>
+      <c r="BJ212" s="94"/>
+      <c r="BK212" s="94"/>
       <c r="BL212" s="2"/>
       <c r="BM212" s="2"/>
       <c r="BN212" s="2"/>
@@ -28908,8 +29184,8 @@
       <c r="BG213" s="2"/>
       <c r="BH213" s="2"/>
       <c r="BI213" s="2"/>
-      <c r="BJ213" s="191"/>
-      <c r="BK213" s="191"/>
+      <c r="BJ213" s="94"/>
+      <c r="BK213" s="94"/>
       <c r="BL213" s="2"/>
       <c r="BM213" s="2"/>
       <c r="BN213" s="2"/>
@@ -29030,8 +29306,8 @@
       <c r="BG214" s="2"/>
       <c r="BH214" s="2"/>
       <c r="BI214" s="2"/>
-      <c r="BJ214" s="191"/>
-      <c r="BK214" s="191"/>
+      <c r="BJ214" s="94"/>
+      <c r="BK214" s="94"/>
       <c r="BL214" s="2"/>
       <c r="BM214" s="2"/>
       <c r="BN214" s="2"/>
@@ -29152,8 +29428,8 @@
       <c r="BG215" s="2"/>
       <c r="BH215" s="2"/>
       <c r="BI215" s="2"/>
-      <c r="BJ215" s="191"/>
-      <c r="BK215" s="191"/>
+      <c r="BJ215" s="94"/>
+      <c r="BK215" s="94"/>
       <c r="BL215" s="2"/>
       <c r="BM215" s="2"/>
       <c r="BN215" s="2"/>
@@ -29274,8 +29550,8 @@
       <c r="BG216" s="2"/>
       <c r="BH216" s="2"/>
       <c r="BI216" s="2"/>
-      <c r="BJ216" s="191"/>
-      <c r="BK216" s="191"/>
+      <c r="BJ216" s="94"/>
+      <c r="BK216" s="94"/>
       <c r="BL216" s="2"/>
       <c r="BM216" s="2"/>
       <c r="BN216" s="2"/>
@@ -29396,8 +29672,8 @@
       <c r="BG217" s="2"/>
       <c r="BH217" s="2"/>
       <c r="BI217" s="2"/>
-      <c r="BJ217" s="191"/>
-      <c r="BK217" s="191"/>
+      <c r="BJ217" s="94"/>
+      <c r="BK217" s="94"/>
       <c r="BL217" s="2"/>
       <c r="BM217" s="2"/>
       <c r="BN217" s="2"/>
@@ -29518,8 +29794,8 @@
       <c r="BG218" s="2"/>
       <c r="BH218" s="2"/>
       <c r="BI218" s="2"/>
-      <c r="BJ218" s="191"/>
-      <c r="BK218" s="191"/>
+      <c r="BJ218" s="94"/>
+      <c r="BK218" s="94"/>
       <c r="BL218" s="2"/>
       <c r="BM218" s="2"/>
       <c r="BN218" s="2"/>
@@ -29640,8 +29916,8 @@
       <c r="BG219" s="2"/>
       <c r="BH219" s="2"/>
       <c r="BI219" s="2"/>
-      <c r="BJ219" s="191"/>
-      <c r="BK219" s="191"/>
+      <c r="BJ219" s="94"/>
+      <c r="BK219" s="94"/>
       <c r="BL219" s="2"/>
       <c r="BM219" s="2"/>
       <c r="BN219" s="2"/>
@@ -29762,8 +30038,8 @@
       <c r="BG220" s="2"/>
       <c r="BH220" s="2"/>
       <c r="BI220" s="2"/>
-      <c r="BJ220" s="191"/>
-      <c r="BK220" s="191"/>
+      <c r="BJ220" s="94"/>
+      <c r="BK220" s="94"/>
       <c r="BL220" s="2"/>
       <c r="BM220" s="2"/>
       <c r="BN220" s="2"/>
@@ -29884,8 +30160,8 @@
       <c r="BG221" s="2"/>
       <c r="BH221" s="2"/>
       <c r="BI221" s="2"/>
-      <c r="BJ221" s="191"/>
-      <c r="BK221" s="191"/>
+      <c r="BJ221" s="94"/>
+      <c r="BK221" s="94"/>
       <c r="BL221" s="2"/>
       <c r="BM221" s="2"/>
       <c r="BN221" s="2"/>
@@ -30006,8 +30282,8 @@
       <c r="BG222" s="2"/>
       <c r="BH222" s="2"/>
       <c r="BI222" s="2"/>
-      <c r="BJ222" s="191"/>
-      <c r="BK222" s="191"/>
+      <c r="BJ222" s="94"/>
+      <c r="BK222" s="94"/>
       <c r="BL222" s="2"/>
       <c r="BM222" s="2"/>
       <c r="BN222" s="2"/>
@@ -30128,8 +30404,8 @@
       <c r="BG223" s="2"/>
       <c r="BH223" s="2"/>
       <c r="BI223" s="2"/>
-      <c r="BJ223" s="191"/>
-      <c r="BK223" s="191"/>
+      <c r="BJ223" s="94"/>
+      <c r="BK223" s="94"/>
       <c r="BL223" s="2"/>
       <c r="BM223" s="2"/>
       <c r="BN223" s="2"/>
@@ -30250,8 +30526,8 @@
       <c r="BG224" s="2"/>
       <c r="BH224" s="2"/>
       <c r="BI224" s="2"/>
-      <c r="BJ224" s="191"/>
-      <c r="BK224" s="191"/>
+      <c r="BJ224" s="94"/>
+      <c r="BK224" s="94"/>
       <c r="BL224" s="2"/>
       <c r="BM224" s="2"/>
       <c r="BN224" s="2"/>
@@ -30372,8 +30648,8 @@
       <c r="BG225" s="2"/>
       <c r="BH225" s="2"/>
       <c r="BI225" s="2"/>
-      <c r="BJ225" s="191"/>
-      <c r="BK225" s="191"/>
+      <c r="BJ225" s="94"/>
+      <c r="BK225" s="94"/>
       <c r="BL225" s="2"/>
       <c r="BM225" s="2"/>
       <c r="BN225" s="2"/>
@@ -30494,8 +30770,8 @@
       <c r="BG226" s="2"/>
       <c r="BH226" s="2"/>
       <c r="BI226" s="2"/>
-      <c r="BJ226" s="191"/>
-      <c r="BK226" s="191"/>
+      <c r="BJ226" s="94"/>
+      <c r="BK226" s="94"/>
       <c r="BL226" s="2"/>
       <c r="BM226" s="2"/>
       <c r="BN226" s="2"/>
@@ -30616,8 +30892,8 @@
       <c r="BG227" s="2"/>
       <c r="BH227" s="2"/>
       <c r="BI227" s="2"/>
-      <c r="BJ227" s="191"/>
-      <c r="BK227" s="191"/>
+      <c r="BJ227" s="94"/>
+      <c r="BK227" s="94"/>
       <c r="BL227" s="2"/>
       <c r="BM227" s="2"/>
       <c r="BN227" s="2"/>
@@ -30738,8 +31014,8 @@
       <c r="BG228" s="2"/>
       <c r="BH228" s="2"/>
       <c r="BI228" s="2"/>
-      <c r="BJ228" s="191"/>
-      <c r="BK228" s="191"/>
+      <c r="BJ228" s="94"/>
+      <c r="BK228" s="94"/>
       <c r="BL228" s="2"/>
       <c r="BM228" s="2"/>
       <c r="BN228" s="2"/>
@@ -30860,8 +31136,8 @@
       <c r="BG229" s="2"/>
       <c r="BH229" s="2"/>
       <c r="BI229" s="2"/>
-      <c r="BJ229" s="191"/>
-      <c r="BK229" s="191"/>
+      <c r="BJ229" s="94"/>
+      <c r="BK229" s="94"/>
       <c r="BL229" s="2"/>
       <c r="BM229" s="2"/>
       <c r="BN229" s="2"/>
@@ -30982,8 +31258,8 @@
       <c r="BG230" s="2"/>
       <c r="BH230" s="2"/>
       <c r="BI230" s="2"/>
-      <c r="BJ230" s="191"/>
-      <c r="BK230" s="191"/>
+      <c r="BJ230" s="94"/>
+      <c r="BK230" s="94"/>
       <c r="BL230" s="2"/>
       <c r="BM230" s="2"/>
       <c r="BN230" s="2"/>
@@ -31104,8 +31380,8 @@
       <c r="BG231" s="2"/>
       <c r="BH231" s="2"/>
       <c r="BI231" s="2"/>
-      <c r="BJ231" s="191"/>
-      <c r="BK231" s="191"/>
+      <c r="BJ231" s="94"/>
+      <c r="BK231" s="94"/>
       <c r="BL231" s="2"/>
       <c r="BM231" s="2"/>
       <c r="BN231" s="2"/>
@@ -31226,8 +31502,8 @@
       <c r="BG232" s="2"/>
       <c r="BH232" s="2"/>
       <c r="BI232" s="2"/>
-      <c r="BJ232" s="191"/>
-      <c r="BK232" s="191"/>
+      <c r="BJ232" s="94"/>
+      <c r="BK232" s="94"/>
       <c r="BL232" s="2"/>
       <c r="BM232" s="2"/>
       <c r="BN232" s="2"/>
@@ -31348,8 +31624,8 @@
       <c r="BG233" s="2"/>
       <c r="BH233" s="2"/>
       <c r="BI233" s="2"/>
-      <c r="BJ233" s="191"/>
-      <c r="BK233" s="191"/>
+      <c r="BJ233" s="94"/>
+      <c r="BK233" s="94"/>
       <c r="BL233" s="2"/>
       <c r="BM233" s="2"/>
       <c r="BN233" s="2"/>
@@ -31470,8 +31746,8 @@
       <c r="BG234" s="2"/>
       <c r="BH234" s="2"/>
       <c r="BI234" s="2"/>
-      <c r="BJ234" s="191"/>
-      <c r="BK234" s="191"/>
+      <c r="BJ234" s="94"/>
+      <c r="BK234" s="94"/>
       <c r="BL234" s="2"/>
       <c r="BM234" s="2"/>
       <c r="BN234" s="2"/>
@@ -31592,8 +31868,8 @@
       <c r="BG235" s="2"/>
       <c r="BH235" s="2"/>
       <c r="BI235" s="2"/>
-      <c r="BJ235" s="191"/>
-      <c r="BK235" s="191"/>
+      <c r="BJ235" s="94"/>
+      <c r="BK235" s="94"/>
       <c r="BL235" s="2"/>
       <c r="BM235" s="2"/>
       <c r="BN235" s="2"/>
@@ -31714,8 +31990,8 @@
       <c r="BG236" s="2"/>
       <c r="BH236" s="2"/>
       <c r="BI236" s="2"/>
-      <c r="BJ236" s="191"/>
-      <c r="BK236" s="191"/>
+      <c r="BJ236" s="94"/>
+      <c r="BK236" s="94"/>
       <c r="BL236" s="2"/>
       <c r="BM236" s="2"/>
       <c r="BN236" s="2"/>
@@ -31836,8 +32112,8 @@
       <c r="BG237" s="2"/>
       <c r="BH237" s="2"/>
       <c r="BI237" s="2"/>
-      <c r="BJ237" s="191"/>
-      <c r="BK237" s="191"/>
+      <c r="BJ237" s="94"/>
+      <c r="BK237" s="94"/>
       <c r="BL237" s="2"/>
       <c r="BM237" s="2"/>
       <c r="BN237" s="2"/>
@@ -31958,8 +32234,8 @@
       <c r="BG238" s="2"/>
       <c r="BH238" s="2"/>
       <c r="BI238" s="2"/>
-      <c r="BJ238" s="191"/>
-      <c r="BK238" s="191"/>
+      <c r="BJ238" s="94"/>
+      <c r="BK238" s="94"/>
       <c r="BL238" s="2"/>
       <c r="BM238" s="2"/>
       <c r="BN238" s="2"/>
@@ -32080,8 +32356,8 @@
       <c r="BG239" s="2"/>
       <c r="BH239" s="2"/>
       <c r="BI239" s="2"/>
-      <c r="BJ239" s="191"/>
-      <c r="BK239" s="191"/>
+      <c r="BJ239" s="94"/>
+      <c r="BK239" s="94"/>
       <c r="BL239" s="2"/>
       <c r="BM239" s="2"/>
       <c r="BN239" s="2"/>
@@ -32202,8 +32478,8 @@
       <c r="BG240" s="2"/>
       <c r="BH240" s="2"/>
       <c r="BI240" s="2"/>
-      <c r="BJ240" s="191"/>
-      <c r="BK240" s="191"/>
+      <c r="BJ240" s="94"/>
+      <c r="BK240" s="94"/>
       <c r="BL240" s="2"/>
       <c r="BM240" s="2"/>
       <c r="BN240" s="2"/>
@@ -32324,8 +32600,8 @@
       <c r="BG241" s="2"/>
       <c r="BH241" s="2"/>
       <c r="BI241" s="2"/>
-      <c r="BJ241" s="191"/>
-      <c r="BK241" s="191"/>
+      <c r="BJ241" s="94"/>
+      <c r="BK241" s="94"/>
       <c r="BL241" s="2"/>
       <c r="BM241" s="2"/>
       <c r="BN241" s="2"/>
@@ -32446,8 +32722,8 @@
       <c r="BG242" s="2"/>
       <c r="BH242" s="2"/>
       <c r="BI242" s="2"/>
-      <c r="BJ242" s="191"/>
-      <c r="BK242" s="191"/>
+      <c r="BJ242" s="94"/>
+      <c r="BK242" s="94"/>
       <c r="BL242" s="2"/>
       <c r="BM242" s="2"/>
       <c r="BN242" s="2"/>
@@ -32568,8 +32844,8 @@
       <c r="BG243" s="2"/>
       <c r="BH243" s="2"/>
       <c r="BI243" s="2"/>
-      <c r="BJ243" s="191"/>
-      <c r="BK243" s="191"/>
+      <c r="BJ243" s="94"/>
+      <c r="BK243" s="94"/>
       <c r="BL243" s="2"/>
       <c r="BM243" s="2"/>
       <c r="BN243" s="2"/>
@@ -32690,8 +32966,8 @@
       <c r="BG244" s="2"/>
       <c r="BH244" s="2"/>
       <c r="BI244" s="2"/>
-      <c r="BJ244" s="191"/>
-      <c r="BK244" s="191"/>
+      <c r="BJ244" s="94"/>
+      <c r="BK244" s="94"/>
       <c r="BL244" s="2"/>
       <c r="BM244" s="2"/>
       <c r="BN244" s="2"/>
@@ -32812,8 +33088,8 @@
       <c r="BG245" s="2"/>
       <c r="BH245" s="2"/>
       <c r="BI245" s="2"/>
-      <c r="BJ245" s="191"/>
-      <c r="BK245" s="191"/>
+      <c r="BJ245" s="94"/>
+      <c r="BK245" s="94"/>
       <c r="BL245" s="2"/>
       <c r="BM245" s="2"/>
       <c r="BN245" s="2"/>
@@ -32934,8 +33210,8 @@
       <c r="BG246" s="2"/>
       <c r="BH246" s="2"/>
       <c r="BI246" s="2"/>
-      <c r="BJ246" s="191"/>
-      <c r="BK246" s="191"/>
+      <c r="BJ246" s="94"/>
+      <c r="BK246" s="94"/>
       <c r="BL246" s="2"/>
       <c r="BM246" s="2"/>
       <c r="BN246" s="2"/>
@@ -33056,8 +33332,8 @@
       <c r="BG247" s="2"/>
       <c r="BH247" s="2"/>
       <c r="BI247" s="2"/>
-      <c r="BJ247" s="191"/>
-      <c r="BK247" s="191"/>
+      <c r="BJ247" s="94"/>
+      <c r="BK247" s="94"/>
       <c r="BL247" s="2"/>
       <c r="BM247" s="2"/>
       <c r="BN247" s="2"/>
@@ -33178,8 +33454,8 @@
       <c r="BG248" s="2"/>
       <c r="BH248" s="2"/>
       <c r="BI248" s="2"/>
-      <c r="BJ248" s="191"/>
-      <c r="BK248" s="191"/>
+      <c r="BJ248" s="94"/>
+      <c r="BK248" s="94"/>
       <c r="BL248" s="2"/>
       <c r="BM248" s="2"/>
       <c r="BN248" s="2"/>
@@ -33300,8 +33576,8 @@
       <c r="BG249" s="2"/>
       <c r="BH249" s="2"/>
       <c r="BI249" s="2"/>
-      <c r="BJ249" s="191"/>
-      <c r="BK249" s="191"/>
+      <c r="BJ249" s="94"/>
+      <c r="BK249" s="94"/>
       <c r="BL249" s="2"/>
       <c r="BM249" s="2"/>
       <c r="BN249" s="2"/>
@@ -33422,8 +33698,8 @@
       <c r="BG250" s="2"/>
       <c r="BH250" s="2"/>
       <c r="BI250" s="2"/>
-      <c r="BJ250" s="191"/>
-      <c r="BK250" s="191"/>
+      <c r="BJ250" s="94"/>
+      <c r="BK250" s="94"/>
       <c r="BL250" s="2"/>
       <c r="BM250" s="2"/>
       <c r="BN250" s="2"/>
@@ -33544,8 +33820,8 @@
       <c r="BG251" s="2"/>
       <c r="BH251" s="2"/>
       <c r="BI251" s="2"/>
-      <c r="BJ251" s="191"/>
-      <c r="BK251" s="191"/>
+      <c r="BJ251" s="94"/>
+      <c r="BK251" s="94"/>
       <c r="BL251" s="2"/>
       <c r="BM251" s="2"/>
       <c r="BN251" s="2"/>
@@ -33666,8 +33942,8 @@
       <c r="BG252" s="2"/>
       <c r="BH252" s="2"/>
       <c r="BI252" s="2"/>
-      <c r="BJ252" s="191"/>
-      <c r="BK252" s="191"/>
+      <c r="BJ252" s="94"/>
+      <c r="BK252" s="94"/>
       <c r="BL252" s="2"/>
       <c r="BM252" s="2"/>
       <c r="BN252" s="2"/>
@@ -33788,8 +34064,8 @@
       <c r="BG253" s="2"/>
       <c r="BH253" s="2"/>
       <c r="BI253" s="2"/>
-      <c r="BJ253" s="191"/>
-      <c r="BK253" s="191"/>
+      <c r="BJ253" s="94"/>
+      <c r="BK253" s="94"/>
       <c r="BL253" s="2"/>
       <c r="BM253" s="2"/>
       <c r="BN253" s="2"/>
@@ -33910,8 +34186,8 @@
       <c r="BG254" s="2"/>
       <c r="BH254" s="2"/>
       <c r="BI254" s="2"/>
-      <c r="BJ254" s="191"/>
-      <c r="BK254" s="191"/>
+      <c r="BJ254" s="94"/>
+      <c r="BK254" s="94"/>
       <c r="BL254" s="2"/>
       <c r="BM254" s="2"/>
       <c r="BN254" s="2"/>
@@ -34032,8 +34308,8 @@
       <c r="BG255" s="2"/>
       <c r="BH255" s="2"/>
       <c r="BI255" s="2"/>
-      <c r="BJ255" s="191"/>
-      <c r="BK255" s="191"/>
+      <c r="BJ255" s="94"/>
+      <c r="BK255" s="94"/>
       <c r="BL255" s="2"/>
       <c r="BM255" s="2"/>
       <c r="BN255" s="2"/>
@@ -34154,8 +34430,8 @@
       <c r="BG256" s="2"/>
       <c r="BH256" s="2"/>
       <c r="BI256" s="2"/>
-      <c r="BJ256" s="191"/>
-      <c r="BK256" s="191"/>
+      <c r="BJ256" s="94"/>
+      <c r="BK256" s="94"/>
       <c r="BL256" s="2"/>
       <c r="BM256" s="2"/>
       <c r="BN256" s="2"/>
@@ -34276,8 +34552,8 @@
       <c r="BG257" s="2"/>
       <c r="BH257" s="2"/>
       <c r="BI257" s="2"/>
-      <c r="BJ257" s="191"/>
-      <c r="BK257" s="191"/>
+      <c r="BJ257" s="94"/>
+      <c r="BK257" s="94"/>
       <c r="BL257" s="2"/>
       <c r="BM257" s="2"/>
       <c r="BN257" s="2"/>
@@ -34398,8 +34674,8 @@
       <c r="BG258" s="2"/>
       <c r="BH258" s="2"/>
       <c r="BI258" s="2"/>
-      <c r="BJ258" s="191"/>
-      <c r="BK258" s="191"/>
+      <c r="BJ258" s="94"/>
+      <c r="BK258" s="94"/>
       <c r="BL258" s="2"/>
       <c r="BM258" s="2"/>
       <c r="BN258" s="2"/>
@@ -34520,8 +34796,8 @@
       <c r="BG259" s="2"/>
       <c r="BH259" s="2"/>
       <c r="BI259" s="2"/>
-      <c r="BJ259" s="191"/>
-      <c r="BK259" s="191"/>
+      <c r="BJ259" s="94"/>
+      <c r="BK259" s="94"/>
       <c r="BL259" s="2"/>
       <c r="BM259" s="2"/>
       <c r="BN259" s="2"/>
@@ -34642,8 +34918,8 @@
       <c r="BG260" s="2"/>
       <c r="BH260" s="2"/>
       <c r="BI260" s="2"/>
-      <c r="BJ260" s="191"/>
-      <c r="BK260" s="191"/>
+      <c r="BJ260" s="94"/>
+      <c r="BK260" s="94"/>
       <c r="BL260" s="2"/>
       <c r="BM260" s="2"/>
       <c r="BN260" s="2"/>
@@ -34764,8 +35040,8 @@
       <c r="BG261" s="2"/>
       <c r="BH261" s="2"/>
       <c r="BI261" s="2"/>
-      <c r="BJ261" s="191"/>
-      <c r="BK261" s="191"/>
+      <c r="BJ261" s="94"/>
+      <c r="BK261" s="94"/>
       <c r="BL261" s="2"/>
       <c r="BM261" s="2"/>
       <c r="BN261" s="2"/>
@@ -34886,8 +35162,8 @@
       <c r="BG262" s="2"/>
       <c r="BH262" s="2"/>
       <c r="BI262" s="2"/>
-      <c r="BJ262" s="191"/>
-      <c r="BK262" s="191"/>
+      <c r="BJ262" s="94"/>
+      <c r="BK262" s="94"/>
       <c r="BL262" s="2"/>
       <c r="BM262" s="2"/>
       <c r="BN262" s="2"/>
@@ -35008,8 +35284,8 @@
       <c r="BG263" s="2"/>
       <c r="BH263" s="2"/>
       <c r="BI263" s="2"/>
-      <c r="BJ263" s="191"/>
-      <c r="BK263" s="191"/>
+      <c r="BJ263" s="94"/>
+      <c r="BK263" s="94"/>
       <c r="BL263" s="2"/>
       <c r="BM263" s="2"/>
       <c r="BN263" s="2"/>
@@ -35130,8 +35406,8 @@
       <c r="BG264" s="2"/>
       <c r="BH264" s="2"/>
       <c r="BI264" s="2"/>
-      <c r="BJ264" s="191"/>
-      <c r="BK264" s="191"/>
+      <c r="BJ264" s="94"/>
+      <c r="BK264" s="94"/>
       <c r="BL264" s="2"/>
       <c r="BM264" s="2"/>
       <c r="BN264" s="2"/>
@@ -35252,8 +35528,8 @@
       <c r="BG265" s="2"/>
       <c r="BH265" s="2"/>
       <c r="BI265" s="2"/>
-      <c r="BJ265" s="191"/>
-      <c r="BK265" s="191"/>
+      <c r="BJ265" s="94"/>
+      <c r="BK265" s="94"/>
       <c r="BL265" s="2"/>
       <c r="BM265" s="2"/>
       <c r="BN265" s="2"/>
@@ -35374,8 +35650,8 @@
       <c r="BG266" s="2"/>
       <c r="BH266" s="2"/>
       <c r="BI266" s="2"/>
-      <c r="BJ266" s="191"/>
-      <c r="BK266" s="191"/>
+      <c r="BJ266" s="94"/>
+      <c r="BK266" s="94"/>
       <c r="BL266" s="2"/>
       <c r="BM266" s="2"/>
       <c r="BN266" s="2"/>
@@ -35496,8 +35772,8 @@
       <c r="BG267" s="2"/>
       <c r="BH267" s="2"/>
       <c r="BI267" s="2"/>
-      <c r="BJ267" s="191"/>
-      <c r="BK267" s="191"/>
+      <c r="BJ267" s="94"/>
+      <c r="BK267" s="94"/>
       <c r="BL267" s="2"/>
       <c r="BM267" s="2"/>
       <c r="BN267" s="2"/>
@@ -35618,8 +35894,8 @@
       <c r="BG268" s="2"/>
       <c r="BH268" s="2"/>
       <c r="BI268" s="2"/>
-      <c r="BJ268" s="191"/>
-      <c r="BK268" s="191"/>
+      <c r="BJ268" s="94"/>
+      <c r="BK268" s="94"/>
       <c r="BL268" s="2"/>
       <c r="BM268" s="2"/>
       <c r="BN268" s="2"/>
@@ -35740,8 +36016,8 @@
       <c r="BG269" s="2"/>
       <c r="BH269" s="2"/>
       <c r="BI269" s="2"/>
-      <c r="BJ269" s="191"/>
-      <c r="BK269" s="191"/>
+      <c r="BJ269" s="94"/>
+      <c r="BK269" s="94"/>
       <c r="BL269" s="2"/>
       <c r="BM269" s="2"/>
       <c r="BN269" s="2"/>
@@ -35862,8 +36138,8 @@
       <c r="BG270" s="2"/>
       <c r="BH270" s="2"/>
       <c r="BI270" s="2"/>
-      <c r="BJ270" s="191"/>
-      <c r="BK270" s="191"/>
+      <c r="BJ270" s="94"/>
+      <c r="BK270" s="94"/>
       <c r="BL270" s="2"/>
       <c r="BM270" s="2"/>
       <c r="BN270" s="2"/>
@@ -35984,8 +36260,8 @@
       <c r="BG271" s="2"/>
       <c r="BH271" s="2"/>
       <c r="BI271" s="2"/>
-      <c r="BJ271" s="191"/>
-      <c r="BK271" s="191"/>
+      <c r="BJ271" s="94"/>
+      <c r="BK271" s="94"/>
       <c r="BL271" s="2"/>
       <c r="BM271" s="2"/>
       <c r="BN271" s="2"/>
@@ -36106,8 +36382,8 @@
       <c r="BG272" s="2"/>
       <c r="BH272" s="2"/>
       <c r="BI272" s="2"/>
-      <c r="BJ272" s="191"/>
-      <c r="BK272" s="191"/>
+      <c r="BJ272" s="94"/>
+      <c r="BK272" s="94"/>
       <c r="BL272" s="2"/>
       <c r="BM272" s="2"/>
       <c r="BN272" s="2"/>
@@ -36226,8 +36502,8 @@
       <c r="BG273" s="2"/>
       <c r="BH273" s="2"/>
       <c r="BI273" s="2"/>
-      <c r="BJ273" s="191"/>
-      <c r="BK273" s="191"/>
+      <c r="BJ273" s="94"/>
+      <c r="BK273" s="94"/>
       <c r="BL273" s="2"/>
       <c r="BM273" s="2"/>
       <c r="BN273" s="2"/>
@@ -36346,8 +36622,8 @@
       <c r="BG274" s="2"/>
       <c r="BH274" s="2"/>
       <c r="BI274" s="2"/>
-      <c r="BJ274" s="191"/>
-      <c r="BK274" s="191"/>
+      <c r="BJ274" s="94"/>
+      <c r="BK274" s="94"/>
       <c r="BL274" s="2"/>
       <c r="BM274" s="2"/>
       <c r="BN274" s="2"/>
@@ -36416,6 +36692,222 @@
     </row>
   </sheetData>
   <mergeCells count="240">
+    <mergeCell ref="E155:G156"/>
+    <mergeCell ref="D155:D156"/>
+    <mergeCell ref="H155:H156"/>
+    <mergeCell ref="I155:I156"/>
+    <mergeCell ref="H113:H114"/>
+    <mergeCell ref="I113:I114"/>
+    <mergeCell ref="H129:H130"/>
+    <mergeCell ref="I129:I130"/>
+    <mergeCell ref="E129:G130"/>
+    <mergeCell ref="H123:H124"/>
+    <mergeCell ref="I123:I124"/>
+    <mergeCell ref="I125:I126"/>
+    <mergeCell ref="H125:H126"/>
+    <mergeCell ref="H133:H134"/>
+    <mergeCell ref="I133:I134"/>
+    <mergeCell ref="E123:G124"/>
+    <mergeCell ref="E125:G126"/>
+    <mergeCell ref="E127:G128"/>
+    <mergeCell ref="E113:G114"/>
+    <mergeCell ref="E119:G120"/>
+    <mergeCell ref="E121:G122"/>
+    <mergeCell ref="H127:H128"/>
+    <mergeCell ref="I127:I128"/>
+    <mergeCell ref="H121:H122"/>
+    <mergeCell ref="H105:H106"/>
+    <mergeCell ref="I105:I106"/>
+    <mergeCell ref="H107:H108"/>
+    <mergeCell ref="I107:I108"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="H117:H118"/>
+    <mergeCell ref="I117:I118"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="I119:I120"/>
+    <mergeCell ref="H101:H102"/>
+    <mergeCell ref="I101:I102"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="I85:I86"/>
+    <mergeCell ref="H89:H90"/>
+    <mergeCell ref="I89:I90"/>
+    <mergeCell ref="E81:G82"/>
+    <mergeCell ref="E83:G84"/>
+    <mergeCell ref="E91:G92"/>
+    <mergeCell ref="E93:G94"/>
+    <mergeCell ref="E95:G96"/>
+    <mergeCell ref="E97:G98"/>
+    <mergeCell ref="E99:G100"/>
+    <mergeCell ref="E85:G86"/>
+    <mergeCell ref="D89:G90"/>
+    <mergeCell ref="H75:H76"/>
+    <mergeCell ref="H159:H160"/>
+    <mergeCell ref="H163:H164"/>
+    <mergeCell ref="H161:H162"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="H59:H60"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="H77:H78"/>
+    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="H93:H94"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="H111:H112"/>
+    <mergeCell ref="I163:I164"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="I159:I160"/>
+    <mergeCell ref="I161:I162"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="I93:I94"/>
+    <mergeCell ref="I95:I96"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="I109:I110"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="I153:I154"/>
+    <mergeCell ref="I151:I152"/>
+    <mergeCell ref="I149:I150"/>
+    <mergeCell ref="I147:I148"/>
+    <mergeCell ref="I145:I146"/>
+    <mergeCell ref="I111:I112"/>
+    <mergeCell ref="I135:I136"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I67:I68"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="C163:G164"/>
+    <mergeCell ref="C159:G160"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="C31:G32"/>
+    <mergeCell ref="D33:G34"/>
+    <mergeCell ref="E35:G36"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="E43:G44"/>
+    <mergeCell ref="E45:G46"/>
+    <mergeCell ref="E47:G48"/>
+    <mergeCell ref="E49:G50"/>
+    <mergeCell ref="E51:G52"/>
+    <mergeCell ref="D53:G54"/>
+    <mergeCell ref="E55:G56"/>
+    <mergeCell ref="E57:G58"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="J3:CJ3"/>
+    <mergeCell ref="CK3:DO3"/>
+    <mergeCell ref="J4:AA4"/>
+    <mergeCell ref="AB4:BE4"/>
+    <mergeCell ref="BF4:CJ4"/>
+    <mergeCell ref="CK4:DO4"/>
+    <mergeCell ref="B7:G8"/>
+    <mergeCell ref="C9:G10"/>
+    <mergeCell ref="C11:G12"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="D13:G14"/>
+    <mergeCell ref="D15:G16"/>
+    <mergeCell ref="D17:G18"/>
+    <mergeCell ref="D19:G20"/>
+    <mergeCell ref="C21:G22"/>
+    <mergeCell ref="D23:G24"/>
+    <mergeCell ref="C25:G26"/>
+    <mergeCell ref="D27:G28"/>
+    <mergeCell ref="D29:G30"/>
+    <mergeCell ref="E147:G148"/>
+    <mergeCell ref="E149:G150"/>
+    <mergeCell ref="E151:G152"/>
+    <mergeCell ref="E59:G60"/>
+    <mergeCell ref="E61:G62"/>
+    <mergeCell ref="D63:G64"/>
+    <mergeCell ref="E67:G68"/>
+    <mergeCell ref="E65:G66"/>
+    <mergeCell ref="E69:G70"/>
+    <mergeCell ref="E71:G72"/>
+    <mergeCell ref="C73:G74"/>
+    <mergeCell ref="C75:G76"/>
+    <mergeCell ref="C77:G78"/>
+    <mergeCell ref="D79:G80"/>
+    <mergeCell ref="E109:G110"/>
+    <mergeCell ref="E111:G112"/>
+    <mergeCell ref="E101:G102"/>
+    <mergeCell ref="C105:G106"/>
+    <mergeCell ref="D107:G108"/>
+    <mergeCell ref="D117:G118"/>
+    <mergeCell ref="H145:H146"/>
+    <mergeCell ref="H143:H144"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="C133:G134"/>
+    <mergeCell ref="D135:G136"/>
+    <mergeCell ref="E137:G138"/>
+    <mergeCell ref="E139:G140"/>
+    <mergeCell ref="D143:G144"/>
+    <mergeCell ref="E145:G146"/>
+    <mergeCell ref="H135:H136"/>
     <mergeCell ref="D157:G158"/>
     <mergeCell ref="H157:H158"/>
     <mergeCell ref="I157:I158"/>
@@ -36440,302 +36932,91 @@
     <mergeCell ref="H151:H152"/>
     <mergeCell ref="H149:H150"/>
     <mergeCell ref="H147:H148"/>
-    <mergeCell ref="H145:H146"/>
-    <mergeCell ref="H143:H144"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="C133:G134"/>
-    <mergeCell ref="D135:G136"/>
-    <mergeCell ref="E137:G138"/>
-    <mergeCell ref="E139:G140"/>
-    <mergeCell ref="D143:G144"/>
-    <mergeCell ref="E145:G146"/>
-    <mergeCell ref="H135:H136"/>
-    <mergeCell ref="E147:G148"/>
-    <mergeCell ref="E149:G150"/>
-    <mergeCell ref="E151:G152"/>
-    <mergeCell ref="E59:G60"/>
-    <mergeCell ref="E61:G62"/>
-    <mergeCell ref="D63:G64"/>
-    <mergeCell ref="E67:G68"/>
-    <mergeCell ref="E65:G66"/>
-    <mergeCell ref="E69:G70"/>
-    <mergeCell ref="E71:G72"/>
-    <mergeCell ref="C73:G74"/>
-    <mergeCell ref="C75:G76"/>
-    <mergeCell ref="C77:G78"/>
-    <mergeCell ref="D79:G80"/>
-    <mergeCell ref="E109:G110"/>
-    <mergeCell ref="E111:G112"/>
-    <mergeCell ref="E101:G102"/>
-    <mergeCell ref="C105:G106"/>
-    <mergeCell ref="D107:G108"/>
-    <mergeCell ref="D117:G118"/>
-    <mergeCell ref="D13:G14"/>
-    <mergeCell ref="D15:G16"/>
-    <mergeCell ref="D17:G18"/>
-    <mergeCell ref="D19:G20"/>
-    <mergeCell ref="C21:G22"/>
-    <mergeCell ref="D23:G24"/>
-    <mergeCell ref="C25:G26"/>
-    <mergeCell ref="D27:G28"/>
-    <mergeCell ref="D29:G30"/>
-    <mergeCell ref="J3:CJ3"/>
-    <mergeCell ref="CK3:DO3"/>
-    <mergeCell ref="J4:AA4"/>
-    <mergeCell ref="AB4:BE4"/>
-    <mergeCell ref="BF4:CJ4"/>
-    <mergeCell ref="CK4:DO4"/>
-    <mergeCell ref="B7:G8"/>
-    <mergeCell ref="C9:G10"/>
-    <mergeCell ref="C11:G12"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="C163:G164"/>
-    <mergeCell ref="C159:G160"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="C31:G32"/>
-    <mergeCell ref="D33:G34"/>
-    <mergeCell ref="E35:G36"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="E43:G44"/>
-    <mergeCell ref="E45:G46"/>
-    <mergeCell ref="E47:G48"/>
-    <mergeCell ref="E49:G50"/>
-    <mergeCell ref="E51:G52"/>
-    <mergeCell ref="D53:G54"/>
-    <mergeCell ref="E55:G56"/>
-    <mergeCell ref="E57:G58"/>
-    <mergeCell ref="I53:I54"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="I159:I160"/>
-    <mergeCell ref="I161:I162"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="I93:I94"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="I109:I110"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="I153:I154"/>
-    <mergeCell ref="I151:I152"/>
-    <mergeCell ref="I149:I150"/>
-    <mergeCell ref="I147:I148"/>
-    <mergeCell ref="I145:I146"/>
-    <mergeCell ref="I111:I112"/>
-    <mergeCell ref="I135:I136"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="I163:I164"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="H75:H76"/>
-    <mergeCell ref="H159:H160"/>
-    <mergeCell ref="H163:H164"/>
-    <mergeCell ref="H161:H162"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="H67:H68"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H59:H60"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="H77:H78"/>
-    <mergeCell ref="H81:H82"/>
-    <mergeCell ref="H83:H84"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="H93:H94"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="H111:H112"/>
-    <mergeCell ref="H101:H102"/>
-    <mergeCell ref="I101:I102"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="I85:I86"/>
-    <mergeCell ref="H89:H90"/>
-    <mergeCell ref="I89:I90"/>
-    <mergeCell ref="E81:G82"/>
-    <mergeCell ref="E83:G84"/>
-    <mergeCell ref="E91:G92"/>
-    <mergeCell ref="E93:G94"/>
-    <mergeCell ref="E95:G96"/>
-    <mergeCell ref="E97:G98"/>
-    <mergeCell ref="E99:G100"/>
-    <mergeCell ref="E85:G86"/>
-    <mergeCell ref="D89:G90"/>
-    <mergeCell ref="H105:H106"/>
-    <mergeCell ref="I105:I106"/>
-    <mergeCell ref="H107:H108"/>
-    <mergeCell ref="I107:I108"/>
-    <mergeCell ref="H109:H110"/>
-    <mergeCell ref="H117:H118"/>
-    <mergeCell ref="I117:I118"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="I119:I120"/>
-    <mergeCell ref="E155:G156"/>
-    <mergeCell ref="D155:D156"/>
-    <mergeCell ref="H155:H156"/>
-    <mergeCell ref="I155:I156"/>
-    <mergeCell ref="H113:H114"/>
-    <mergeCell ref="I113:I114"/>
-    <mergeCell ref="H129:H130"/>
-    <mergeCell ref="I129:I130"/>
-    <mergeCell ref="E129:G130"/>
-    <mergeCell ref="H123:H124"/>
-    <mergeCell ref="I123:I124"/>
-    <mergeCell ref="I125:I126"/>
-    <mergeCell ref="H125:H126"/>
-    <mergeCell ref="H133:H134"/>
-    <mergeCell ref="I133:I134"/>
-    <mergeCell ref="E123:G124"/>
-    <mergeCell ref="E125:G126"/>
-    <mergeCell ref="E127:G128"/>
-    <mergeCell ref="E113:G114"/>
-    <mergeCell ref="E119:G120"/>
-    <mergeCell ref="E121:G122"/>
-    <mergeCell ref="H127:H128"/>
-    <mergeCell ref="I127:I128"/>
-    <mergeCell ref="H121:H122"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <conditionalFormatting sqref="J7">
-    <cfRule type="expression" dxfId="15" priority="14">
+    <cfRule type="expression" dxfId="33" priority="15">
       <formula>OR(J4="土", J4="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J12">
-    <cfRule type="expression" dxfId="14" priority="12">
+    <cfRule type="expression" dxfId="32" priority="13">
       <formula>OR(J6="土", J6="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J161">
-    <cfRule type="expression" dxfId="13" priority="16">
+    <cfRule type="expression" dxfId="31" priority="17">
       <formula>OR(#REF!="土", #REF!="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7:DO8 AA52:DO52 J9:Y64 AA55:DO58 Z59:DO62 J65:DO66 J137:BN137 BP137:DO137 J138:DO269 J72:DO136">
-    <cfRule type="expression" dxfId="12" priority="15">
+    <cfRule type="expression" dxfId="30" priority="16">
       <formula>OR(J$6="土", J$6="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB51:DO51 Z51:Z52 J71:AN71 AP71:DO71 Z9:DO48 Z55:Z56 Z53:DO54 Z50:DO50 AA49:DO49 J67:AL67 AO67:DO67 J68:DO70">
-    <cfRule type="expression" dxfId="11" priority="13">
+    <cfRule type="expression" dxfId="29" priority="14">
       <formula>OR(J$6="土", J$6="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA51">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="28" priority="12">
       <formula>OR(AA$6="土", AA$6="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO71">
-    <cfRule type="expression" dxfId="9" priority="10">
+    <cfRule type="expression" dxfId="27" priority="11">
       <formula>OR(AO$6="土", AO$6="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J21:J22">
-    <cfRule type="expression" dxfId="8" priority="9">
+    <cfRule type="expression" dxfId="26" priority="10">
       <formula>OR(J18="土", J18="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J25:J26">
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="25" priority="9">
       <formula>OR(J22="土", J22="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J31:J32">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="24" priority="8">
       <formula>OR(J28="土", J28="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="23" priority="7">
       <formula>OR(K22="土", K22="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="22" priority="6">
       <formula>OR(K8="土", K8="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="21" priority="5">
       <formula>OR(K6="土", K6="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z63:DO64">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="20" priority="4">
       <formula>OR(Z$6="土", Z$6="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z49">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="19" priority="3">
       <formula>OR(Z$6="土", Z$6="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM67:AN67">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="18" priority="2">
       <formula>OR(AM$6="土", AM$6="日")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:DO5">
+    <cfRule type="timePeriod" dxfId="17" priority="1" timePeriod="today">
+      <formula>FLOOR(J5,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/docs/【DIGITAL OJT】WBS.xlsx
+++ b/docs/【DIGITAL OJT】WBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIGITALOJT\digital-ojt-development-cause-DroneInventorySystem\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F96B42F-D5CE-4636-A4F5-4AD97EEFDCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7D336E-BEB3-4E9A-B1FF-CC319252A505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -1736,7 +1736,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="50">
+  <dxfs count="17">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1744,272 +1744,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFBFBFBF"/>
-          <bgColor rgb="FFBFBFBF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2353,14 +2087,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DP276"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="61" width="3.44140625" customWidth="1"/>
-    <col min="62" max="63" width="3.44140625" style="100" customWidth="1"/>
-    <col min="64" max="119" width="3.44140625" customWidth="1"/>
+    <col min="10" max="61" width="3.42578125" customWidth="1"/>
+    <col min="62" max="63" width="3.42578125" style="100" customWidth="1"/>
+    <col min="64" max="119" width="3.42578125" customWidth="1"/>
     <col min="120" max="120" width="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14277,7 +14011,7 @@
       <c r="AR92" s="21"/>
       <c r="AS92" s="20"/>
       <c r="AT92" s="20"/>
-      <c r="AU92" s="69"/>
+      <c r="AU92" s="75"/>
       <c r="AV92" s="69"/>
       <c r="AW92" s="69"/>
       <c r="AX92" s="21"/>
@@ -14526,7 +14260,7 @@
       <c r="AS94" s="20"/>
       <c r="AT94" s="20"/>
       <c r="AU94" s="69"/>
-      <c r="AV94" s="69"/>
+      <c r="AV94" s="75"/>
       <c r="AW94" s="69"/>
       <c r="AX94" s="21"/>
       <c r="AY94" s="21"/>
@@ -14775,7 +14509,7 @@
       <c r="AT96" s="20"/>
       <c r="AU96" s="20"/>
       <c r="AV96" s="20"/>
-      <c r="AW96" s="20"/>
+      <c r="AW96" s="75"/>
       <c r="AX96" s="21"/>
       <c r="AY96" s="21"/>
       <c r="AZ96" s="69"/>
@@ -15026,7 +14760,7 @@
       <c r="AW98" s="20"/>
       <c r="AX98" s="21"/>
       <c r="AY98" s="21"/>
-      <c r="AZ98" s="69"/>
+      <c r="AZ98" s="75"/>
       <c r="BA98" s="69"/>
       <c r="BB98" s="69"/>
       <c r="BC98" s="69"/>
@@ -15275,7 +15009,7 @@
       <c r="AX100" s="21"/>
       <c r="AY100" s="21"/>
       <c r="AZ100" s="69"/>
-      <c r="BA100" s="69"/>
+      <c r="BA100" s="75"/>
       <c r="BB100" s="69"/>
       <c r="BC100" s="69"/>
       <c r="BD100" s="20"/>
@@ -36935,87 +36669,87 @@
   </mergeCells>
   <phoneticPr fontId="10"/>
   <conditionalFormatting sqref="J7">
-    <cfRule type="expression" dxfId="33" priority="15">
+    <cfRule type="expression" dxfId="16" priority="15">
       <formula>OR(J4="土", J4="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J12">
-    <cfRule type="expression" dxfId="32" priority="13">
+    <cfRule type="expression" dxfId="15" priority="13">
       <formula>OR(J6="土", J6="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J161">
-    <cfRule type="expression" dxfId="31" priority="17">
+    <cfRule type="expression" dxfId="14" priority="17">
       <formula>OR(#REF!="土", #REF!="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7:DO8 AA52:DO52 J9:Y64 AA55:DO58 Z59:DO62 J65:DO66 J137:BN137 BP137:DO137 J138:DO269 J72:DO136">
-    <cfRule type="expression" dxfId="30" priority="16">
+    <cfRule type="expression" dxfId="13" priority="16">
       <formula>OR(J$6="土", J$6="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB51:DO51 Z51:Z52 J71:AN71 AP71:DO71 Z9:DO48 Z55:Z56 Z53:DO54 Z50:DO50 AA49:DO49 J67:AL67 AO67:DO67 J68:DO70">
-    <cfRule type="expression" dxfId="29" priority="14">
+    <cfRule type="expression" dxfId="12" priority="14">
       <formula>OR(J$6="土", J$6="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA51">
-    <cfRule type="expression" dxfId="28" priority="12">
+    <cfRule type="expression" dxfId="11" priority="12">
       <formula>OR(AA$6="土", AA$6="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO71">
-    <cfRule type="expression" dxfId="27" priority="11">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>OR(AO$6="土", AO$6="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J21:J22">
-    <cfRule type="expression" dxfId="26" priority="10">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>OR(J18="土", J18="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J25:J26">
-    <cfRule type="expression" dxfId="25" priority="9">
+    <cfRule type="expression" dxfId="8" priority="9">
       <formula>OR(J22="土", J22="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J31:J32">
-    <cfRule type="expression" dxfId="24" priority="8">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>OR(J28="土", J28="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="expression" dxfId="23" priority="7">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>OR(K22="土", K22="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="expression" dxfId="22" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>OR(K8="土", K8="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9">
-    <cfRule type="expression" dxfId="21" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>OR(K6="土", K6="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z63:DO64">
-    <cfRule type="expression" dxfId="20" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>OR(Z$6="土", Z$6="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z49">
-    <cfRule type="expression" dxfId="19" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>OR(Z$6="土", Z$6="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM67:AN67">
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>OR(AM$6="土", AM$6="日")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:DO5">
-    <cfRule type="timePeriod" dxfId="17" priority="1" timePeriod="today">
+    <cfRule type="timePeriod" dxfId="0" priority="1" timePeriod="today">
       <formula>FLOOR(J5,1)=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>

--- a/docs/【DIGITAL OJT】WBS.xlsx
+++ b/docs/【DIGITAL OJT】WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIGITALOJT\digital-ojt-development-cause-DroneInventorySystem\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7D336E-BEB3-4E9A-B1FF-CC319252A505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E92C0A-DA75-4357-BE19-DE0D56F102A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1489,19 +1489,67 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1510,22 +1558,25 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1546,110 +1597,29 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1675,62 +1645,92 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2350,120 +2350,120 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="J3" s="161">
+      <c r="J3" s="173">
         <v>2024</v>
       </c>
-      <c r="K3" s="162"/>
-      <c r="L3" s="162"/>
-      <c r="M3" s="162"/>
-      <c r="N3" s="162"/>
-      <c r="O3" s="162"/>
-      <c r="P3" s="162"/>
-      <c r="Q3" s="162"/>
-      <c r="R3" s="162"/>
-      <c r="S3" s="162"/>
-      <c r="T3" s="162"/>
-      <c r="U3" s="162"/>
-      <c r="V3" s="162"/>
-      <c r="W3" s="162"/>
-      <c r="X3" s="162"/>
-      <c r="Y3" s="162"/>
-      <c r="Z3" s="162"/>
-      <c r="AA3" s="162"/>
-      <c r="AB3" s="162"/>
-      <c r="AC3" s="162"/>
-      <c r="AD3" s="162"/>
-      <c r="AE3" s="162"/>
-      <c r="AF3" s="162"/>
-      <c r="AG3" s="162"/>
-      <c r="AH3" s="162"/>
-      <c r="AI3" s="162"/>
-      <c r="AJ3" s="162"/>
-      <c r="AK3" s="162"/>
-      <c r="AL3" s="162"/>
-      <c r="AM3" s="162"/>
-      <c r="AN3" s="162"/>
-      <c r="AO3" s="162"/>
-      <c r="AP3" s="162"/>
-      <c r="AQ3" s="162"/>
-      <c r="AR3" s="162"/>
-      <c r="AS3" s="162"/>
-      <c r="AT3" s="162"/>
-      <c r="AU3" s="162"/>
-      <c r="AV3" s="162"/>
-      <c r="AW3" s="162"/>
-      <c r="AX3" s="162"/>
-      <c r="AY3" s="162"/>
-      <c r="AZ3" s="162"/>
-      <c r="BA3" s="162"/>
-      <c r="BB3" s="162"/>
-      <c r="BC3" s="162"/>
-      <c r="BD3" s="162"/>
-      <c r="BE3" s="162"/>
-      <c r="BF3" s="162"/>
-      <c r="BG3" s="162"/>
-      <c r="BH3" s="162"/>
-      <c r="BI3" s="162"/>
-      <c r="BJ3" s="162"/>
-      <c r="BK3" s="162"/>
-      <c r="BL3" s="162"/>
-      <c r="BM3" s="162"/>
-      <c r="BN3" s="162"/>
-      <c r="BO3" s="162"/>
-      <c r="BP3" s="162"/>
-      <c r="BQ3" s="162"/>
-      <c r="BR3" s="162"/>
-      <c r="BS3" s="162"/>
-      <c r="BT3" s="162"/>
-      <c r="BU3" s="162"/>
-      <c r="BV3" s="162"/>
-      <c r="BW3" s="162"/>
-      <c r="BX3" s="162"/>
-      <c r="BY3" s="162"/>
-      <c r="BZ3" s="162"/>
-      <c r="CA3" s="162"/>
-      <c r="CB3" s="162"/>
-      <c r="CC3" s="162"/>
-      <c r="CD3" s="162"/>
-      <c r="CE3" s="162"/>
-      <c r="CF3" s="162"/>
-      <c r="CG3" s="162"/>
-      <c r="CH3" s="162"/>
-      <c r="CI3" s="162"/>
-      <c r="CJ3" s="163"/>
-      <c r="CK3" s="161">
+      <c r="K3" s="174"/>
+      <c r="L3" s="174"/>
+      <c r="M3" s="174"/>
+      <c r="N3" s="174"/>
+      <c r="O3" s="174"/>
+      <c r="P3" s="174"/>
+      <c r="Q3" s="174"/>
+      <c r="R3" s="174"/>
+      <c r="S3" s="174"/>
+      <c r="T3" s="174"/>
+      <c r="U3" s="174"/>
+      <c r="V3" s="174"/>
+      <c r="W3" s="174"/>
+      <c r="X3" s="174"/>
+      <c r="Y3" s="174"/>
+      <c r="Z3" s="174"/>
+      <c r="AA3" s="174"/>
+      <c r="AB3" s="174"/>
+      <c r="AC3" s="174"/>
+      <c r="AD3" s="174"/>
+      <c r="AE3" s="174"/>
+      <c r="AF3" s="174"/>
+      <c r="AG3" s="174"/>
+      <c r="AH3" s="174"/>
+      <c r="AI3" s="174"/>
+      <c r="AJ3" s="174"/>
+      <c r="AK3" s="174"/>
+      <c r="AL3" s="174"/>
+      <c r="AM3" s="174"/>
+      <c r="AN3" s="174"/>
+      <c r="AO3" s="174"/>
+      <c r="AP3" s="174"/>
+      <c r="AQ3" s="174"/>
+      <c r="AR3" s="174"/>
+      <c r="AS3" s="174"/>
+      <c r="AT3" s="174"/>
+      <c r="AU3" s="174"/>
+      <c r="AV3" s="174"/>
+      <c r="AW3" s="174"/>
+      <c r="AX3" s="174"/>
+      <c r="AY3" s="174"/>
+      <c r="AZ3" s="174"/>
+      <c r="BA3" s="174"/>
+      <c r="BB3" s="174"/>
+      <c r="BC3" s="174"/>
+      <c r="BD3" s="174"/>
+      <c r="BE3" s="174"/>
+      <c r="BF3" s="174"/>
+      <c r="BG3" s="174"/>
+      <c r="BH3" s="174"/>
+      <c r="BI3" s="174"/>
+      <c r="BJ3" s="174"/>
+      <c r="BK3" s="174"/>
+      <c r="BL3" s="174"/>
+      <c r="BM3" s="174"/>
+      <c r="BN3" s="174"/>
+      <c r="BO3" s="174"/>
+      <c r="BP3" s="174"/>
+      <c r="BQ3" s="174"/>
+      <c r="BR3" s="174"/>
+      <c r="BS3" s="174"/>
+      <c r="BT3" s="174"/>
+      <c r="BU3" s="174"/>
+      <c r="BV3" s="174"/>
+      <c r="BW3" s="174"/>
+      <c r="BX3" s="174"/>
+      <c r="BY3" s="174"/>
+      <c r="BZ3" s="174"/>
+      <c r="CA3" s="174"/>
+      <c r="CB3" s="174"/>
+      <c r="CC3" s="174"/>
+      <c r="CD3" s="174"/>
+      <c r="CE3" s="174"/>
+      <c r="CF3" s="174"/>
+      <c r="CG3" s="174"/>
+      <c r="CH3" s="174"/>
+      <c r="CI3" s="174"/>
+      <c r="CJ3" s="175"/>
+      <c r="CK3" s="173">
         <v>2025</v>
       </c>
-      <c r="CL3" s="162"/>
-      <c r="CM3" s="162"/>
-      <c r="CN3" s="162"/>
-      <c r="CO3" s="162"/>
-      <c r="CP3" s="162"/>
-      <c r="CQ3" s="162"/>
-      <c r="CR3" s="162"/>
-      <c r="CS3" s="162"/>
-      <c r="CT3" s="162"/>
-      <c r="CU3" s="162"/>
-      <c r="CV3" s="162"/>
-      <c r="CW3" s="162"/>
-      <c r="CX3" s="162"/>
-      <c r="CY3" s="162"/>
-      <c r="CZ3" s="162"/>
-      <c r="DA3" s="162"/>
-      <c r="DB3" s="162"/>
-      <c r="DC3" s="162"/>
-      <c r="DD3" s="162"/>
-      <c r="DE3" s="162"/>
-      <c r="DF3" s="162"/>
-      <c r="DG3" s="162"/>
-      <c r="DH3" s="162"/>
-      <c r="DI3" s="162"/>
-      <c r="DJ3" s="162"/>
-      <c r="DK3" s="162"/>
-      <c r="DL3" s="162"/>
-      <c r="DM3" s="162"/>
-      <c r="DN3" s="162"/>
-      <c r="DO3" s="163"/>
+      <c r="CL3" s="174"/>
+      <c r="CM3" s="174"/>
+      <c r="CN3" s="174"/>
+      <c r="CO3" s="174"/>
+      <c r="CP3" s="174"/>
+      <c r="CQ3" s="174"/>
+      <c r="CR3" s="174"/>
+      <c r="CS3" s="174"/>
+      <c r="CT3" s="174"/>
+      <c r="CU3" s="174"/>
+      <c r="CV3" s="174"/>
+      <c r="CW3" s="174"/>
+      <c r="CX3" s="174"/>
+      <c r="CY3" s="174"/>
+      <c r="CZ3" s="174"/>
+      <c r="DA3" s="174"/>
+      <c r="DB3" s="174"/>
+      <c r="DC3" s="174"/>
+      <c r="DD3" s="174"/>
+      <c r="DE3" s="174"/>
+      <c r="DF3" s="174"/>
+      <c r="DG3" s="174"/>
+      <c r="DH3" s="174"/>
+      <c r="DI3" s="174"/>
+      <c r="DJ3" s="174"/>
+      <c r="DK3" s="174"/>
+      <c r="DL3" s="174"/>
+      <c r="DM3" s="174"/>
+      <c r="DN3" s="174"/>
+      <c r="DO3" s="175"/>
       <c r="DP3" s="1"/>
     </row>
     <row r="4" spans="1:120" ht="18" customHeight="1">
@@ -2478,124 +2478,124 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="J4" s="161">
+      <c r="J4" s="173">
         <v>10</v>
       </c>
-      <c r="K4" s="162"/>
-      <c r="L4" s="162"/>
-      <c r="M4" s="162"/>
-      <c r="N4" s="162"/>
-      <c r="O4" s="162"/>
-      <c r="P4" s="162"/>
-      <c r="Q4" s="162"/>
-      <c r="R4" s="162"/>
-      <c r="S4" s="162"/>
-      <c r="T4" s="162"/>
-      <c r="U4" s="162"/>
-      <c r="V4" s="162"/>
-      <c r="W4" s="162"/>
-      <c r="X4" s="162"/>
-      <c r="Y4" s="162"/>
-      <c r="Z4" s="162"/>
-      <c r="AA4" s="163"/>
-      <c r="AB4" s="161">
+      <c r="K4" s="174"/>
+      <c r="L4" s="174"/>
+      <c r="M4" s="174"/>
+      <c r="N4" s="174"/>
+      <c r="O4" s="174"/>
+      <c r="P4" s="174"/>
+      <c r="Q4" s="174"/>
+      <c r="R4" s="174"/>
+      <c r="S4" s="174"/>
+      <c r="T4" s="174"/>
+      <c r="U4" s="174"/>
+      <c r="V4" s="174"/>
+      <c r="W4" s="174"/>
+      <c r="X4" s="174"/>
+      <c r="Y4" s="174"/>
+      <c r="Z4" s="174"/>
+      <c r="AA4" s="175"/>
+      <c r="AB4" s="173">
         <v>11</v>
       </c>
-      <c r="AC4" s="162"/>
-      <c r="AD4" s="162"/>
-      <c r="AE4" s="162"/>
-      <c r="AF4" s="162"/>
-      <c r="AG4" s="162"/>
-      <c r="AH4" s="162"/>
-      <c r="AI4" s="162"/>
-      <c r="AJ4" s="162"/>
-      <c r="AK4" s="162"/>
-      <c r="AL4" s="162"/>
-      <c r="AM4" s="162"/>
-      <c r="AN4" s="162"/>
-      <c r="AO4" s="162"/>
-      <c r="AP4" s="162"/>
-      <c r="AQ4" s="162"/>
-      <c r="AR4" s="162"/>
-      <c r="AS4" s="162"/>
-      <c r="AT4" s="162"/>
-      <c r="AU4" s="162"/>
-      <c r="AV4" s="162"/>
-      <c r="AW4" s="162"/>
-      <c r="AX4" s="162"/>
-      <c r="AY4" s="162"/>
-      <c r="AZ4" s="162"/>
-      <c r="BA4" s="162"/>
-      <c r="BB4" s="162"/>
-      <c r="BC4" s="162"/>
-      <c r="BD4" s="162"/>
-      <c r="BE4" s="163"/>
-      <c r="BF4" s="161">
+      <c r="AC4" s="174"/>
+      <c r="AD4" s="174"/>
+      <c r="AE4" s="174"/>
+      <c r="AF4" s="174"/>
+      <c r="AG4" s="174"/>
+      <c r="AH4" s="174"/>
+      <c r="AI4" s="174"/>
+      <c r="AJ4" s="174"/>
+      <c r="AK4" s="174"/>
+      <c r="AL4" s="174"/>
+      <c r="AM4" s="174"/>
+      <c r="AN4" s="174"/>
+      <c r="AO4" s="174"/>
+      <c r="AP4" s="174"/>
+      <c r="AQ4" s="174"/>
+      <c r="AR4" s="174"/>
+      <c r="AS4" s="174"/>
+      <c r="AT4" s="174"/>
+      <c r="AU4" s="174"/>
+      <c r="AV4" s="174"/>
+      <c r="AW4" s="174"/>
+      <c r="AX4" s="174"/>
+      <c r="AY4" s="174"/>
+      <c r="AZ4" s="174"/>
+      <c r="BA4" s="174"/>
+      <c r="BB4" s="174"/>
+      <c r="BC4" s="174"/>
+      <c r="BD4" s="174"/>
+      <c r="BE4" s="175"/>
+      <c r="BF4" s="173">
         <v>12</v>
       </c>
-      <c r="BG4" s="162"/>
-      <c r="BH4" s="162"/>
-      <c r="BI4" s="162"/>
-      <c r="BJ4" s="162"/>
-      <c r="BK4" s="162"/>
-      <c r="BL4" s="162"/>
-      <c r="BM4" s="162"/>
-      <c r="BN4" s="162"/>
-      <c r="BO4" s="162"/>
-      <c r="BP4" s="162"/>
-      <c r="BQ4" s="162"/>
-      <c r="BR4" s="162"/>
-      <c r="BS4" s="162"/>
-      <c r="BT4" s="162"/>
-      <c r="BU4" s="162"/>
-      <c r="BV4" s="162"/>
-      <c r="BW4" s="162"/>
-      <c r="BX4" s="162"/>
-      <c r="BY4" s="162"/>
-      <c r="BZ4" s="162"/>
-      <c r="CA4" s="162"/>
-      <c r="CB4" s="162"/>
-      <c r="CC4" s="162"/>
-      <c r="CD4" s="162"/>
-      <c r="CE4" s="162"/>
-      <c r="CF4" s="162"/>
-      <c r="CG4" s="162"/>
-      <c r="CH4" s="162"/>
-      <c r="CI4" s="162"/>
-      <c r="CJ4" s="163"/>
-      <c r="CK4" s="161">
+      <c r="BG4" s="174"/>
+      <c r="BH4" s="174"/>
+      <c r="BI4" s="174"/>
+      <c r="BJ4" s="174"/>
+      <c r="BK4" s="174"/>
+      <c r="BL4" s="174"/>
+      <c r="BM4" s="174"/>
+      <c r="BN4" s="174"/>
+      <c r="BO4" s="174"/>
+      <c r="BP4" s="174"/>
+      <c r="BQ4" s="174"/>
+      <c r="BR4" s="174"/>
+      <c r="BS4" s="174"/>
+      <c r="BT4" s="174"/>
+      <c r="BU4" s="174"/>
+      <c r="BV4" s="174"/>
+      <c r="BW4" s="174"/>
+      <c r="BX4" s="174"/>
+      <c r="BY4" s="174"/>
+      <c r="BZ4" s="174"/>
+      <c r="CA4" s="174"/>
+      <c r="CB4" s="174"/>
+      <c r="CC4" s="174"/>
+      <c r="CD4" s="174"/>
+      <c r="CE4" s="174"/>
+      <c r="CF4" s="174"/>
+      <c r="CG4" s="174"/>
+      <c r="CH4" s="174"/>
+      <c r="CI4" s="174"/>
+      <c r="CJ4" s="175"/>
+      <c r="CK4" s="173">
         <v>1</v>
       </c>
-      <c r="CL4" s="162"/>
-      <c r="CM4" s="162"/>
-      <c r="CN4" s="162"/>
-      <c r="CO4" s="162"/>
-      <c r="CP4" s="162"/>
-      <c r="CQ4" s="162"/>
-      <c r="CR4" s="162"/>
-      <c r="CS4" s="162"/>
-      <c r="CT4" s="162"/>
-      <c r="CU4" s="162"/>
-      <c r="CV4" s="162"/>
-      <c r="CW4" s="162"/>
-      <c r="CX4" s="162"/>
-      <c r="CY4" s="162"/>
-      <c r="CZ4" s="162"/>
-      <c r="DA4" s="162"/>
-      <c r="DB4" s="162"/>
-      <c r="DC4" s="162"/>
-      <c r="DD4" s="162"/>
-      <c r="DE4" s="162"/>
-      <c r="DF4" s="162"/>
-      <c r="DG4" s="162"/>
-      <c r="DH4" s="162"/>
-      <c r="DI4" s="162"/>
-      <c r="DJ4" s="162"/>
-      <c r="DK4" s="162"/>
-      <c r="DL4" s="162"/>
-      <c r="DM4" s="162"/>
-      <c r="DN4" s="162"/>
-      <c r="DO4" s="163"/>
+      <c r="CL4" s="174"/>
+      <c r="CM4" s="174"/>
+      <c r="CN4" s="174"/>
+      <c r="CO4" s="174"/>
+      <c r="CP4" s="174"/>
+      <c r="CQ4" s="174"/>
+      <c r="CR4" s="174"/>
+      <c r="CS4" s="174"/>
+      <c r="CT4" s="174"/>
+      <c r="CU4" s="174"/>
+      <c r="CV4" s="174"/>
+      <c r="CW4" s="174"/>
+      <c r="CX4" s="174"/>
+      <c r="CY4" s="174"/>
+      <c r="CZ4" s="174"/>
+      <c r="DA4" s="174"/>
+      <c r="DB4" s="174"/>
+      <c r="DC4" s="174"/>
+      <c r="DD4" s="174"/>
+      <c r="DE4" s="174"/>
+      <c r="DF4" s="174"/>
+      <c r="DG4" s="174"/>
+      <c r="DH4" s="174"/>
+      <c r="DI4" s="174"/>
+      <c r="DJ4" s="174"/>
+      <c r="DK4" s="174"/>
+      <c r="DL4" s="174"/>
+      <c r="DM4" s="174"/>
+      <c r="DN4" s="174"/>
+      <c r="DO4" s="175"/>
       <c r="DP4" s="6"/>
     </row>
     <row r="5" spans="1:120" ht="18" customHeight="1">
@@ -3390,18 +3390,18 @@
     </row>
     <row r="7" spans="1:120" ht="9.75" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="164" t="s">
+      <c r="B7" s="176" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="166" t="s">
+      <c r="C7" s="164"/>
+      <c r="D7" s="164"/>
+      <c r="E7" s="164"/>
+      <c r="F7" s="164"/>
+      <c r="G7" s="177"/>
+      <c r="H7" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="166" t="s">
+      <c r="I7" s="142" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="38"/>
@@ -3518,14 +3518,14 @@
     </row>
     <row r="8" spans="1:120" ht="9.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="134"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="135"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="135"/>
-      <c r="G8" s="139"/>
-      <c r="H8" s="166"/>
-      <c r="I8" s="166"/>
+      <c r="B8" s="166"/>
+      <c r="C8" s="167"/>
+      <c r="D8" s="167"/>
+      <c r="E8" s="167"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="168"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="142"/>
       <c r="J8" s="39"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
@@ -3641,15 +3641,15 @@
     <row r="9" spans="1:120" ht="9.75" customHeight="1">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
-      <c r="C9" s="165" t="s">
+      <c r="C9" s="178" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="154"/>
-      <c r="E9" s="154"/>
-      <c r="F9" s="154"/>
-      <c r="G9" s="142"/>
-      <c r="H9" s="167"/>
-      <c r="I9" s="167"/>
+      <c r="D9" s="158"/>
+      <c r="E9" s="158"/>
+      <c r="F9" s="158"/>
+      <c r="G9" s="162"/>
+      <c r="H9" s="139"/>
+      <c r="I9" s="139"/>
       <c r="J9" s="42"/>
       <c r="K9" s="42"/>
       <c r="L9" s="44"/>
@@ -3765,13 +3765,13 @@
     <row r="10" spans="1:120" ht="9.75" customHeight="1">
       <c r="A10" s="16"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="141"/>
-      <c r="D10" s="135"/>
-      <c r="E10" s="135"/>
-      <c r="F10" s="135"/>
-      <c r="G10" s="139"/>
-      <c r="H10" s="167"/>
-      <c r="I10" s="167"/>
+      <c r="C10" s="179"/>
+      <c r="D10" s="167"/>
+      <c r="E10" s="167"/>
+      <c r="F10" s="167"/>
+      <c r="G10" s="168"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
       <c r="J10" s="46"/>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
@@ -3887,15 +3887,15 @@
     <row r="11" spans="1:120" ht="9.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="153" t="s">
+      <c r="C11" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="154"/>
-      <c r="E11" s="154"/>
-      <c r="F11" s="154"/>
-      <c r="G11" s="142"/>
-      <c r="H11" s="167"/>
-      <c r="I11" s="167"/>
+      <c r="D11" s="158"/>
+      <c r="E11" s="158"/>
+      <c r="F11" s="158"/>
+      <c r="G11" s="162"/>
+      <c r="H11" s="139"/>
+      <c r="I11" s="139"/>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
       <c r="L11" s="44"/>
@@ -4011,13 +4011,13 @@
     <row r="12" spans="1:120" ht="9.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="141"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="135"/>
-      <c r="F12" s="135"/>
-      <c r="G12" s="139"/>
-      <c r="H12" s="167"/>
-      <c r="I12" s="167"/>
+      <c r="C12" s="179"/>
+      <c r="D12" s="167"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="167"/>
+      <c r="G12" s="168"/>
+      <c r="H12" s="139"/>
+      <c r="I12" s="139"/>
       <c r="J12" s="46"/>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
@@ -4134,13 +4134,13 @@
       <c r="A13" s="1"/>
       <c r="B13" s="18"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="151" t="s">
+      <c r="D13" s="181" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="152"/>
-      <c r="H13" s="184" t="s">
+      <c r="E13" s="164"/>
+      <c r="F13" s="164"/>
+      <c r="G13" s="177"/>
+      <c r="H13" s="138" t="s">
         <v>40</v>
       </c>
       <c r="I13" s="112">
@@ -4262,10 +4262,10 @@
       <c r="A14" s="1"/>
       <c r="B14" s="18"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="134"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="135"/>
-      <c r="G14" s="139"/>
+      <c r="D14" s="166"/>
+      <c r="E14" s="167"/>
+      <c r="F14" s="167"/>
+      <c r="G14" s="168"/>
       <c r="H14" s="112"/>
       <c r="I14" s="112"/>
       <c r="J14" s="39"/>
@@ -4384,13 +4384,13 @@
       <c r="A15" s="1"/>
       <c r="B15" s="18"/>
       <c r="C15" s="24"/>
-      <c r="D15" s="151" t="s">
+      <c r="D15" s="181" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="133"/>
-      <c r="H15" s="184" t="s">
+      <c r="E15" s="164"/>
+      <c r="F15" s="164"/>
+      <c r="G15" s="170"/>
+      <c r="H15" s="138" t="s">
         <v>40</v>
       </c>
       <c r="I15" s="112">
@@ -4512,10 +4512,10 @@
       <c r="A16" s="1"/>
       <c r="B16" s="18"/>
       <c r="C16" s="24"/>
-      <c r="D16" s="134"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="136"/>
+      <c r="D16" s="166"/>
+      <c r="E16" s="167"/>
+      <c r="F16" s="167"/>
+      <c r="G16" s="171"/>
       <c r="H16" s="112"/>
       <c r="I16" s="112"/>
       <c r="J16" s="14"/>
@@ -4634,13 +4634,13 @@
       <c r="A17" s="1"/>
       <c r="B17" s="18"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="151" t="s">
+      <c r="D17" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="132"/>
-      <c r="F17" s="132"/>
-      <c r="G17" s="133"/>
-      <c r="H17" s="184" t="s">
+      <c r="E17" s="164"/>
+      <c r="F17" s="164"/>
+      <c r="G17" s="170"/>
+      <c r="H17" s="138" t="s">
         <v>40</v>
       </c>
       <c r="I17" s="112">
@@ -4762,10 +4762,10 @@
       <c r="A18" s="1"/>
       <c r="B18" s="18"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="134"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="135"/>
-      <c r="G18" s="136"/>
+      <c r="D18" s="166"/>
+      <c r="E18" s="167"/>
+      <c r="F18" s="167"/>
+      <c r="G18" s="171"/>
       <c r="H18" s="112"/>
       <c r="I18" s="112"/>
       <c r="J18" s="14"/>
@@ -4884,13 +4884,13 @@
       <c r="A19" s="1"/>
       <c r="B19" s="18"/>
       <c r="C19" s="24"/>
-      <c r="D19" s="151" t="s">
+      <c r="D19" s="181" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="132"/>
-      <c r="F19" s="132"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="184" t="s">
+      <c r="E19" s="164"/>
+      <c r="F19" s="164"/>
+      <c r="G19" s="170"/>
+      <c r="H19" s="138" t="s">
         <v>40</v>
       </c>
       <c r="I19" s="112">
@@ -5012,10 +5012,10 @@
       <c r="A20" s="1"/>
       <c r="B20" s="18"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="134"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="135"/>
-      <c r="G20" s="136"/>
+      <c r="D20" s="166"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="167"/>
+      <c r="G20" s="171"/>
       <c r="H20" s="112"/>
       <c r="I20" s="112"/>
       <c r="J20" s="26"/>
@@ -5133,15 +5133,15 @@
     <row r="21" spans="1:120" ht="9.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="18"/>
-      <c r="C21" s="153" t="s">
+      <c r="C21" s="180" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="154"/>
-      <c r="E21" s="154"/>
-      <c r="F21" s="154"/>
-      <c r="G21" s="155"/>
-      <c r="H21" s="167"/>
-      <c r="I21" s="167"/>
+      <c r="D21" s="158"/>
+      <c r="E21" s="158"/>
+      <c r="F21" s="158"/>
+      <c r="G21" s="159"/>
+      <c r="H21" s="139"/>
+      <c r="I21" s="139"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="44"/>
@@ -5257,13 +5257,13 @@
     <row r="22" spans="1:120" ht="9.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="18"/>
-      <c r="C22" s="156"/>
-      <c r="D22" s="157"/>
-      <c r="E22" s="157"/>
-      <c r="F22" s="157"/>
-      <c r="G22" s="142"/>
-      <c r="H22" s="167"/>
-      <c r="I22" s="167"/>
+      <c r="C22" s="160"/>
+      <c r="D22" s="161"/>
+      <c r="E22" s="161"/>
+      <c r="F22" s="161"/>
+      <c r="G22" s="162"/>
+      <c r="H22" s="139"/>
+      <c r="I22" s="139"/>
       <c r="J22" s="46"/>
       <c r="K22" s="47"/>
       <c r="L22" s="47"/>
@@ -5380,13 +5380,13 @@
       <c r="A23" s="1"/>
       <c r="B23" s="28"/>
       <c r="C23" s="29"/>
-      <c r="D23" s="158" t="s">
+      <c r="D23" s="182" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="132"/>
-      <c r="F23" s="132"/>
-      <c r="G23" s="133"/>
-      <c r="H23" s="184" t="s">
+      <c r="E23" s="164"/>
+      <c r="F23" s="164"/>
+      <c r="G23" s="170"/>
+      <c r="H23" s="138" t="s">
         <v>46</v>
       </c>
       <c r="I23" s="112">
@@ -5508,10 +5508,10 @@
       <c r="A24" s="1"/>
       <c r="B24" s="18"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="134"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="135"/>
-      <c r="G24" s="136"/>
+      <c r="D24" s="166"/>
+      <c r="E24" s="167"/>
+      <c r="F24" s="167"/>
+      <c r="G24" s="171"/>
       <c r="H24" s="112"/>
       <c r="I24" s="112"/>
       <c r="J24" s="14"/>
@@ -5629,15 +5629,15 @@
     <row r="25" spans="1:120" ht="9.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="18"/>
-      <c r="C25" s="153" t="s">
+      <c r="C25" s="180" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="154"/>
-      <c r="E25" s="154"/>
-      <c r="F25" s="154"/>
-      <c r="G25" s="155"/>
-      <c r="H25" s="167"/>
-      <c r="I25" s="167"/>
+      <c r="D25" s="158"/>
+      <c r="E25" s="158"/>
+      <c r="F25" s="158"/>
+      <c r="G25" s="159"/>
+      <c r="H25" s="139"/>
+      <c r="I25" s="139"/>
       <c r="J25" s="42"/>
       <c r="K25" s="42"/>
       <c r="L25" s="44"/>
@@ -5753,13 +5753,13 @@
     <row r="26" spans="1:120" ht="9.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="18"/>
-      <c r="C26" s="141"/>
-      <c r="D26" s="135"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="135"/>
-      <c r="G26" s="139"/>
-      <c r="H26" s="167"/>
-      <c r="I26" s="167"/>
+      <c r="C26" s="179"/>
+      <c r="D26" s="167"/>
+      <c r="E26" s="167"/>
+      <c r="F26" s="167"/>
+      <c r="G26" s="168"/>
+      <c r="H26" s="139"/>
+      <c r="I26" s="139"/>
       <c r="J26" s="46"/>
       <c r="K26" s="47"/>
       <c r="L26" s="47"/>
@@ -5876,13 +5876,13 @@
       <c r="A27" s="1"/>
       <c r="B27" s="28"/>
       <c r="C27" s="29"/>
-      <c r="D27" s="158" t="s">
+      <c r="D27" s="182" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="132"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="133"/>
-      <c r="H27" s="184" t="s">
+      <c r="E27" s="164"/>
+      <c r="F27" s="164"/>
+      <c r="G27" s="170"/>
+      <c r="H27" s="138" t="s">
         <v>44</v>
       </c>
       <c r="I27" s="112">
@@ -6004,10 +6004,10 @@
       <c r="A28" s="1"/>
       <c r="B28" s="28"/>
       <c r="C28" s="30"/>
-      <c r="D28" s="134"/>
-      <c r="E28" s="135"/>
-      <c r="F28" s="135"/>
-      <c r="G28" s="136"/>
+      <c r="D28" s="166"/>
+      <c r="E28" s="167"/>
+      <c r="F28" s="167"/>
+      <c r="G28" s="171"/>
       <c r="H28" s="112"/>
       <c r="I28" s="112"/>
       <c r="J28" s="14"/>
@@ -6126,13 +6126,13 @@
       <c r="A29" s="1"/>
       <c r="B29" s="28"/>
       <c r="C29" s="30"/>
-      <c r="D29" s="159" t="s">
+      <c r="D29" s="183" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="160"/>
-      <c r="F29" s="160"/>
-      <c r="G29" s="160"/>
-      <c r="H29" s="184" t="s">
+      <c r="E29" s="184"/>
+      <c r="F29" s="184"/>
+      <c r="G29" s="184"/>
+      <c r="H29" s="138" t="s">
         <v>44</v>
       </c>
       <c r="I29" s="112">
@@ -6254,10 +6254,10 @@
       <c r="A30" s="1"/>
       <c r="B30" s="28"/>
       <c r="C30" s="31"/>
-      <c r="D30" s="134"/>
-      <c r="E30" s="135"/>
-      <c r="F30" s="135"/>
-      <c r="G30" s="135"/>
+      <c r="D30" s="166"/>
+      <c r="E30" s="167"/>
+      <c r="F30" s="167"/>
+      <c r="G30" s="167"/>
       <c r="H30" s="112"/>
       <c r="I30" s="112"/>
       <c r="J30" s="26"/>
@@ -6375,15 +6375,15 @@
     <row r="31" spans="1:120" ht="9.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="18"/>
-      <c r="C31" s="179" t="s">
+      <c r="C31" s="157" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="154"/>
-      <c r="E31" s="154"/>
-      <c r="F31" s="154"/>
-      <c r="G31" s="155"/>
-      <c r="H31" s="167"/>
-      <c r="I31" s="167"/>
+      <c r="D31" s="158"/>
+      <c r="E31" s="158"/>
+      <c r="F31" s="158"/>
+      <c r="G31" s="159"/>
+      <c r="H31" s="139"/>
+      <c r="I31" s="139"/>
       <c r="J31" s="42"/>
       <c r="K31" s="43"/>
       <c r="L31" s="44"/>
@@ -6499,13 +6499,13 @@
     <row r="32" spans="1:120" ht="9.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="18"/>
-      <c r="C32" s="156"/>
-      <c r="D32" s="157"/>
-      <c r="E32" s="157"/>
-      <c r="F32" s="157"/>
-      <c r="G32" s="142"/>
-      <c r="H32" s="167"/>
-      <c r="I32" s="167"/>
+      <c r="C32" s="160"/>
+      <c r="D32" s="161"/>
+      <c r="E32" s="161"/>
+      <c r="F32" s="161"/>
+      <c r="G32" s="162"/>
+      <c r="H32" s="139"/>
+      <c r="I32" s="139"/>
       <c r="J32" s="46"/>
       <c r="K32" s="47"/>
       <c r="L32" s="47"/>
@@ -6622,14 +6622,14 @@
       <c r="A33" s="1"/>
       <c r="B33" s="18"/>
       <c r="C33" s="32"/>
-      <c r="D33" s="137" t="s">
+      <c r="D33" s="163" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="132"/>
-      <c r="F33" s="132"/>
-      <c r="G33" s="138"/>
-      <c r="H33" s="167"/>
-      <c r="I33" s="167"/>
+      <c r="E33" s="164"/>
+      <c r="F33" s="164"/>
+      <c r="G33" s="165"/>
+      <c r="H33" s="139"/>
+      <c r="I33" s="139"/>
       <c r="J33" s="50"/>
       <c r="K33" s="51"/>
       <c r="L33" s="51"/>
@@ -6746,12 +6746,12 @@
       <c r="A34" s="1"/>
       <c r="B34" s="18"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="134"/>
-      <c r="E34" s="135"/>
-      <c r="F34" s="135"/>
-      <c r="G34" s="139"/>
-      <c r="H34" s="167"/>
-      <c r="I34" s="167"/>
+      <c r="D34" s="166"/>
+      <c r="E34" s="167"/>
+      <c r="F34" s="167"/>
+      <c r="G34" s="168"/>
+      <c r="H34" s="139"/>
+      <c r="I34" s="139"/>
       <c r="J34" s="52"/>
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
@@ -6869,12 +6869,12 @@
       <c r="B35" s="18"/>
       <c r="C35" s="1"/>
       <c r="D35" s="33"/>
-      <c r="E35" s="131" t="s">
+      <c r="E35" s="169" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="132"/>
-      <c r="G35" s="133"/>
-      <c r="H35" s="184" t="s">
+      <c r="F35" s="164"/>
+      <c r="G35" s="170"/>
+      <c r="H35" s="138" t="s">
         <v>45</v>
       </c>
       <c r="I35" s="112">
@@ -6997,9 +6997,9 @@
       <c r="B36" s="18"/>
       <c r="C36" s="1"/>
       <c r="D36" s="34"/>
-      <c r="E36" s="134"/>
-      <c r="F36" s="135"/>
-      <c r="G36" s="136"/>
+      <c r="E36" s="166"/>
+      <c r="F36" s="167"/>
+      <c r="G36" s="171"/>
       <c r="H36" s="112"/>
       <c r="I36" s="112"/>
       <c r="J36" s="14"/>
@@ -7119,12 +7119,12 @@
       <c r="B37" s="18"/>
       <c r="C37" s="1"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="131" t="s">
+      <c r="E37" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F37" s="132"/>
-      <c r="G37" s="133"/>
-      <c r="H37" s="184" t="s">
+      <c r="F37" s="164"/>
+      <c r="G37" s="170"/>
+      <c r="H37" s="138" t="s">
         <v>44</v>
       </c>
       <c r="I37" s="112">
@@ -7247,9 +7247,9 @@
       <c r="B38" s="18"/>
       <c r="C38" s="1"/>
       <c r="D38" s="35"/>
-      <c r="E38" s="134"/>
-      <c r="F38" s="135"/>
-      <c r="G38" s="136"/>
+      <c r="E38" s="166"/>
+      <c r="F38" s="167"/>
+      <c r="G38" s="171"/>
       <c r="H38" s="112"/>
       <c r="I38" s="112"/>
       <c r="J38" s="26"/>
@@ -7368,14 +7368,14 @@
       <c r="A39" s="1"/>
       <c r="B39" s="18"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="180" t="s">
+      <c r="D39" s="172" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="154"/>
-      <c r="F39" s="154"/>
-      <c r="G39" s="155"/>
-      <c r="H39" s="167"/>
-      <c r="I39" s="167"/>
+      <c r="E39" s="158"/>
+      <c r="F39" s="158"/>
+      <c r="G39" s="159"/>
+      <c r="H39" s="139"/>
+      <c r="I39" s="139"/>
       <c r="J39" s="50"/>
       <c r="K39" s="51"/>
       <c r="L39" s="51"/>
@@ -7492,12 +7492,12 @@
       <c r="A40" s="1"/>
       <c r="B40" s="18"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="134"/>
-      <c r="E40" s="135"/>
-      <c r="F40" s="135"/>
-      <c r="G40" s="139"/>
-      <c r="H40" s="167"/>
-      <c r="I40" s="167"/>
+      <c r="D40" s="166"/>
+      <c r="E40" s="167"/>
+      <c r="F40" s="167"/>
+      <c r="G40" s="168"/>
+      <c r="H40" s="139"/>
+      <c r="I40" s="139"/>
       <c r="J40" s="52"/>
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
@@ -7615,12 +7615,12 @@
       <c r="B41" s="18"/>
       <c r="C41" s="1"/>
       <c r="D41" s="33"/>
-      <c r="E41" s="131" t="s">
+      <c r="E41" s="169" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="132"/>
-      <c r="G41" s="133"/>
-      <c r="H41" s="184" t="s">
+      <c r="F41" s="164"/>
+      <c r="G41" s="170"/>
+      <c r="H41" s="138" t="s">
         <v>43</v>
       </c>
       <c r="I41" s="112">
@@ -7743,9 +7743,9 @@
       <c r="B42" s="18"/>
       <c r="C42" s="1"/>
       <c r="D42" s="34"/>
-      <c r="E42" s="134"/>
-      <c r="F42" s="135"/>
-      <c r="G42" s="136"/>
+      <c r="E42" s="166"/>
+      <c r="F42" s="167"/>
+      <c r="G42" s="171"/>
       <c r="H42" s="112"/>
       <c r="I42" s="112"/>
       <c r="J42" s="14"/>
@@ -7865,12 +7865,12 @@
       <c r="B43" s="18"/>
       <c r="C43" s="1"/>
       <c r="D43" s="34"/>
-      <c r="E43" s="131" t="s">
+      <c r="E43" s="169" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="132"/>
-      <c r="G43" s="133"/>
-      <c r="H43" s="184" t="s">
+      <c r="F43" s="164"/>
+      <c r="G43" s="170"/>
+      <c r="H43" s="138" t="s">
         <v>43</v>
       </c>
       <c r="I43" s="112">
@@ -7993,9 +7993,9 @@
       <c r="B44" s="18"/>
       <c r="C44" s="1"/>
       <c r="D44" s="34"/>
-      <c r="E44" s="134"/>
-      <c r="F44" s="135"/>
-      <c r="G44" s="136"/>
+      <c r="E44" s="166"/>
+      <c r="F44" s="167"/>
+      <c r="G44" s="171"/>
       <c r="H44" s="112"/>
       <c r="I44" s="112"/>
       <c r="J44" s="14"/>
@@ -8115,12 +8115,12 @@
       <c r="B45" s="18"/>
       <c r="C45" s="1"/>
       <c r="D45" s="34"/>
-      <c r="E45" s="131" t="s">
+      <c r="E45" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="132"/>
-      <c r="G45" s="133"/>
-      <c r="H45" s="184" t="s">
+      <c r="F45" s="164"/>
+      <c r="G45" s="170"/>
+      <c r="H45" s="138" t="s">
         <v>42</v>
       </c>
       <c r="I45" s="112">
@@ -8243,9 +8243,9 @@
       <c r="B46" s="18"/>
       <c r="C46" s="1"/>
       <c r="D46" s="34"/>
-      <c r="E46" s="134"/>
-      <c r="F46" s="135"/>
-      <c r="G46" s="136"/>
+      <c r="E46" s="166"/>
+      <c r="F46" s="167"/>
+      <c r="G46" s="171"/>
       <c r="H46" s="112"/>
       <c r="I46" s="112"/>
       <c r="J46" s="14"/>
@@ -8365,12 +8365,12 @@
       <c r="B47" s="18"/>
       <c r="C47" s="1"/>
       <c r="D47" s="34"/>
-      <c r="E47" s="131" t="s">
+      <c r="E47" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="F47" s="132"/>
-      <c r="G47" s="133"/>
-      <c r="H47" s="184" t="s">
+      <c r="F47" s="164"/>
+      <c r="G47" s="170"/>
+      <c r="H47" s="138" t="s">
         <v>41</v>
       </c>
       <c r="I47" s="112">
@@ -8493,9 +8493,9 @@
       <c r="B48" s="18"/>
       <c r="C48" s="1"/>
       <c r="D48" s="34"/>
-      <c r="E48" s="134"/>
-      <c r="F48" s="135"/>
-      <c r="G48" s="136"/>
+      <c r="E48" s="166"/>
+      <c r="F48" s="167"/>
+      <c r="G48" s="171"/>
       <c r="H48" s="112"/>
       <c r="I48" s="112"/>
       <c r="J48" s="14"/>
@@ -8615,12 +8615,12 @@
       <c r="B49" s="18"/>
       <c r="C49" s="1"/>
       <c r="D49" s="34"/>
-      <c r="E49" s="131" t="s">
+      <c r="E49" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="132"/>
-      <c r="G49" s="133"/>
-      <c r="H49" s="184" t="s">
+      <c r="F49" s="164"/>
+      <c r="G49" s="170"/>
+      <c r="H49" s="138" t="s">
         <v>50</v>
       </c>
       <c r="I49" s="112">
@@ -8743,9 +8743,9 @@
       <c r="B50" s="18"/>
       <c r="C50" s="1"/>
       <c r="D50" s="34"/>
-      <c r="E50" s="134"/>
-      <c r="F50" s="135"/>
-      <c r="G50" s="136"/>
+      <c r="E50" s="166"/>
+      <c r="F50" s="167"/>
+      <c r="G50" s="171"/>
       <c r="H50" s="112"/>
       <c r="I50" s="112"/>
       <c r="J50" s="14"/>
@@ -8865,12 +8865,12 @@
       <c r="B51" s="18"/>
       <c r="C51" s="1"/>
       <c r="D51" s="34"/>
-      <c r="E51" s="131" t="s">
+      <c r="E51" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="132"/>
-      <c r="G51" s="133"/>
-      <c r="H51" s="184" t="s">
+      <c r="F51" s="164"/>
+      <c r="G51" s="170"/>
+      <c r="H51" s="138" t="s">
         <v>47</v>
       </c>
       <c r="I51" s="112">
@@ -8993,9 +8993,9 @@
       <c r="B52" s="18"/>
       <c r="C52" s="1"/>
       <c r="D52" s="34"/>
-      <c r="E52" s="134"/>
-      <c r="F52" s="135"/>
-      <c r="G52" s="136"/>
+      <c r="E52" s="166"/>
+      <c r="F52" s="167"/>
+      <c r="G52" s="171"/>
       <c r="H52" s="112"/>
       <c r="I52" s="112"/>
       <c r="J52" s="26"/>
@@ -9114,14 +9114,14 @@
       <c r="A53" s="1"/>
       <c r="B53" s="18"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="137" t="s">
+      <c r="D53" s="163" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="132"/>
-      <c r="F53" s="132"/>
-      <c r="G53" s="138"/>
-      <c r="H53" s="167"/>
-      <c r="I53" s="167"/>
+      <c r="E53" s="164"/>
+      <c r="F53" s="164"/>
+      <c r="G53" s="165"/>
+      <c r="H53" s="139"/>
+      <c r="I53" s="139"/>
       <c r="J53" s="50"/>
       <c r="K53" s="51"/>
       <c r="L53" s="51"/>
@@ -9238,12 +9238,12 @@
       <c r="A54" s="1"/>
       <c r="B54" s="18"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="134"/>
-      <c r="E54" s="135"/>
-      <c r="F54" s="135"/>
-      <c r="G54" s="139"/>
-      <c r="H54" s="167"/>
-      <c r="I54" s="167"/>
+      <c r="D54" s="166"/>
+      <c r="E54" s="167"/>
+      <c r="F54" s="167"/>
+      <c r="G54" s="168"/>
+      <c r="H54" s="139"/>
+      <c r="I54" s="139"/>
       <c r="J54" s="52"/>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -9361,12 +9361,12 @@
       <c r="B55" s="18"/>
       <c r="C55" s="1"/>
       <c r="D55" s="34"/>
-      <c r="E55" s="131" t="s">
+      <c r="E55" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="132"/>
-      <c r="G55" s="133"/>
-      <c r="H55" s="184" t="s">
+      <c r="F55" s="164"/>
+      <c r="G55" s="170"/>
+      <c r="H55" s="138" t="s">
         <v>48</v>
       </c>
       <c r="I55" s="112">
@@ -9489,9 +9489,9 @@
       <c r="B56" s="18"/>
       <c r="C56" s="1"/>
       <c r="D56" s="34"/>
-      <c r="E56" s="134"/>
-      <c r="F56" s="135"/>
-      <c r="G56" s="136"/>
+      <c r="E56" s="166"/>
+      <c r="F56" s="167"/>
+      <c r="G56" s="171"/>
       <c r="H56" s="112"/>
       <c r="I56" s="112"/>
       <c r="J56" s="14"/>
@@ -9611,12 +9611,12 @@
       <c r="B57" s="18"/>
       <c r="C57" s="1"/>
       <c r="D57" s="34"/>
-      <c r="E57" s="131" t="s">
+      <c r="E57" s="169" t="s">
         <v>29</v>
       </c>
-      <c r="F57" s="132"/>
-      <c r="G57" s="133"/>
-      <c r="H57" s="184" t="s">
+      <c r="F57" s="164"/>
+      <c r="G57" s="170"/>
+      <c r="H57" s="138" t="s">
         <v>51</v>
       </c>
       <c r="I57" s="112">
@@ -9739,9 +9739,9 @@
       <c r="B58" s="18"/>
       <c r="C58" s="1"/>
       <c r="D58" s="34"/>
-      <c r="E58" s="134"/>
-      <c r="F58" s="135"/>
-      <c r="G58" s="136"/>
+      <c r="E58" s="166"/>
+      <c r="F58" s="167"/>
+      <c r="G58" s="171"/>
       <c r="H58" s="112"/>
       <c r="I58" s="112"/>
       <c r="J58" s="14"/>
@@ -9861,12 +9861,12 @@
       <c r="B59" s="18"/>
       <c r="C59" s="1"/>
       <c r="D59" s="34"/>
-      <c r="E59" s="131" t="s">
+      <c r="E59" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="F59" s="132"/>
-      <c r="G59" s="133"/>
-      <c r="H59" s="184" t="s">
+      <c r="F59" s="164"/>
+      <c r="G59" s="170"/>
+      <c r="H59" s="138" t="s">
         <v>49</v>
       </c>
       <c r="I59" s="112">
@@ -9989,9 +9989,9 @@
       <c r="B60" s="18"/>
       <c r="C60" s="1"/>
       <c r="D60" s="34"/>
-      <c r="E60" s="134"/>
-      <c r="F60" s="135"/>
-      <c r="G60" s="136"/>
+      <c r="E60" s="166"/>
+      <c r="F60" s="167"/>
+      <c r="G60" s="171"/>
       <c r="H60" s="112"/>
       <c r="I60" s="112"/>
       <c r="J60" s="14"/>
@@ -10111,12 +10111,12 @@
       <c r="B61" s="18"/>
       <c r="C61" s="1"/>
       <c r="D61" s="34"/>
-      <c r="E61" s="131" t="s">
+      <c r="E61" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F61" s="132"/>
-      <c r="G61" s="133"/>
-      <c r="H61" s="184" t="s">
+      <c r="F61" s="164"/>
+      <c r="G61" s="170"/>
+      <c r="H61" s="138" t="s">
         <v>49</v>
       </c>
       <c r="I61" s="112">
@@ -10239,9 +10239,9 @@
       <c r="B62" s="18"/>
       <c r="C62" s="1"/>
       <c r="D62" s="34"/>
-      <c r="E62" s="134"/>
-      <c r="F62" s="135"/>
-      <c r="G62" s="136"/>
+      <c r="E62" s="166"/>
+      <c r="F62" s="167"/>
+      <c r="G62" s="171"/>
       <c r="H62" s="112"/>
       <c r="I62" s="112"/>
       <c r="J62" s="26"/>
@@ -10360,14 +10360,14 @@
       <c r="A63" s="1"/>
       <c r="B63" s="18"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="137" t="s">
+      <c r="D63" s="163" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="132"/>
-      <c r="F63" s="132"/>
-      <c r="G63" s="138"/>
-      <c r="H63" s="167"/>
-      <c r="I63" s="167"/>
+      <c r="E63" s="164"/>
+      <c r="F63" s="164"/>
+      <c r="G63" s="165"/>
+      <c r="H63" s="139"/>
+      <c r="I63" s="139"/>
       <c r="J63" s="50"/>
       <c r="K63" s="51"/>
       <c r="L63" s="51"/>
@@ -10484,12 +10484,12 @@
       <c r="A64" s="1"/>
       <c r="B64" s="18"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="134"/>
-      <c r="E64" s="135"/>
-      <c r="F64" s="135"/>
-      <c r="G64" s="139"/>
-      <c r="H64" s="167"/>
-      <c r="I64" s="167"/>
+      <c r="D64" s="166"/>
+      <c r="E64" s="167"/>
+      <c r="F64" s="167"/>
+      <c r="G64" s="168"/>
+      <c r="H64" s="139"/>
+      <c r="I64" s="139"/>
       <c r="J64" s="52"/>
       <c r="K64" s="49"/>
       <c r="L64" s="49"/>
@@ -10607,12 +10607,12 @@
       <c r="B65" s="18"/>
       <c r="C65" s="1"/>
       <c r="D65" s="34"/>
-      <c r="E65" s="131" t="s">
+      <c r="E65" s="169" t="s">
         <v>35</v>
       </c>
-      <c r="F65" s="132"/>
-      <c r="G65" s="133"/>
-      <c r="H65" s="184" t="s">
+      <c r="F65" s="164"/>
+      <c r="G65" s="170"/>
+      <c r="H65" s="138" t="s">
         <v>52</v>
       </c>
       <c r="I65" s="112">
@@ -10735,9 +10735,9 @@
       <c r="B66" s="18"/>
       <c r="C66" s="1"/>
       <c r="D66" s="34"/>
-      <c r="E66" s="134"/>
-      <c r="F66" s="135"/>
-      <c r="G66" s="136"/>
+      <c r="E66" s="166"/>
+      <c r="F66" s="167"/>
+      <c r="G66" s="171"/>
       <c r="H66" s="112"/>
       <c r="I66" s="112"/>
       <c r="J66" s="14"/>
@@ -10857,12 +10857,12 @@
       <c r="B67" s="18"/>
       <c r="C67" s="1"/>
       <c r="D67" s="34"/>
-      <c r="E67" s="131" t="s">
+      <c r="E67" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="F67" s="132"/>
-      <c r="G67" s="133"/>
-      <c r="H67" s="184" t="s">
+      <c r="F67" s="164"/>
+      <c r="G67" s="170"/>
+      <c r="H67" s="138" t="s">
         <v>53</v>
       </c>
       <c r="I67" s="112">
@@ -10985,9 +10985,9 @@
       <c r="B68" s="18"/>
       <c r="C68" s="1"/>
       <c r="D68" s="34"/>
-      <c r="E68" s="134"/>
-      <c r="F68" s="135"/>
-      <c r="G68" s="136"/>
+      <c r="E68" s="166"/>
+      <c r="F68" s="167"/>
+      <c r="G68" s="171"/>
       <c r="H68" s="112"/>
       <c r="I68" s="112"/>
       <c r="J68" s="14"/>
@@ -11107,12 +11107,12 @@
       <c r="B69" s="18"/>
       <c r="C69" s="1"/>
       <c r="D69" s="34"/>
-      <c r="E69" s="131" t="s">
+      <c r="E69" s="169" t="s">
         <v>36</v>
       </c>
-      <c r="F69" s="132"/>
-      <c r="G69" s="133"/>
-      <c r="H69" s="184" t="s">
+      <c r="F69" s="164"/>
+      <c r="G69" s="170"/>
+      <c r="H69" s="138" t="s">
         <v>54</v>
       </c>
       <c r="I69" s="112">
@@ -11235,9 +11235,9 @@
       <c r="B70" s="18"/>
       <c r="C70" s="1"/>
       <c r="D70" s="34"/>
-      <c r="E70" s="134"/>
-      <c r="F70" s="135"/>
-      <c r="G70" s="136"/>
+      <c r="E70" s="166"/>
+      <c r="F70" s="167"/>
+      <c r="G70" s="171"/>
       <c r="H70" s="112"/>
       <c r="I70" s="112"/>
       <c r="J70" s="14"/>
@@ -11357,12 +11357,12 @@
       <c r="B71" s="18"/>
       <c r="C71" s="1"/>
       <c r="D71" s="34"/>
-      <c r="E71" s="131" t="s">
+      <c r="E71" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F71" s="132"/>
-      <c r="G71" s="133"/>
-      <c r="H71" s="184" t="s">
+      <c r="F71" s="164"/>
+      <c r="G71" s="170"/>
+      <c r="H71" s="138" t="s">
         <v>55</v>
       </c>
       <c r="I71" s="112">
@@ -11485,9 +11485,9 @@
       <c r="B72" s="18"/>
       <c r="C72" s="1"/>
       <c r="D72" s="35"/>
-      <c r="E72" s="134"/>
-      <c r="F72" s="135"/>
-      <c r="G72" s="136"/>
+      <c r="E72" s="166"/>
+      <c r="F72" s="167"/>
+      <c r="G72" s="171"/>
       <c r="H72" s="112"/>
       <c r="I72" s="112"/>
       <c r="J72" s="26"/>
@@ -11605,14 +11605,14 @@
     <row r="73" spans="1:120" ht="9.75" customHeight="1">
       <c r="A73" s="16"/>
       <c r="B73" s="36"/>
-      <c r="C73" s="140" t="s">
+      <c r="C73" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="D73" s="132"/>
-      <c r="E73" s="132"/>
-      <c r="F73" s="132"/>
-      <c r="G73" s="138"/>
-      <c r="H73" s="184" t="s">
+      <c r="D73" s="164"/>
+      <c r="E73" s="164"/>
+      <c r="F73" s="164"/>
+      <c r="G73" s="165"/>
+      <c r="H73" s="138" t="s">
         <v>55</v>
       </c>
       <c r="I73" s="112">
@@ -11733,11 +11733,11 @@
     <row r="74" spans="1:120" ht="9.75" customHeight="1">
       <c r="A74" s="16"/>
       <c r="B74" s="36"/>
-      <c r="C74" s="141"/>
-      <c r="D74" s="135"/>
-      <c r="E74" s="135"/>
-      <c r="F74" s="135"/>
-      <c r="G74" s="139"/>
+      <c r="C74" s="179"/>
+      <c r="D74" s="167"/>
+      <c r="E74" s="167"/>
+      <c r="F74" s="167"/>
+      <c r="G74" s="168"/>
       <c r="H74" s="112"/>
       <c r="I74" s="112"/>
       <c r="J74" s="19"/>
@@ -11855,14 +11855,14 @@
     <row r="75" spans="1:120" ht="9.75" customHeight="1">
       <c r="A75" s="16"/>
       <c r="B75" s="36"/>
-      <c r="C75" s="140" t="s">
+      <c r="C75" s="146" t="s">
         <v>34</v>
       </c>
-      <c r="D75" s="132"/>
-      <c r="E75" s="132"/>
-      <c r="F75" s="132"/>
-      <c r="G75" s="138"/>
-      <c r="H75" s="184" t="s">
+      <c r="D75" s="164"/>
+      <c r="E75" s="164"/>
+      <c r="F75" s="164"/>
+      <c r="G75" s="165"/>
+      <c r="H75" s="138" t="s">
         <v>58</v>
       </c>
       <c r="I75" s="112"/>
@@ -11981,11 +11981,11 @@
     <row r="76" spans="1:120" ht="9.75" customHeight="1">
       <c r="A76" s="16"/>
       <c r="B76" s="36"/>
-      <c r="C76" s="142"/>
-      <c r="D76" s="142"/>
-      <c r="E76" s="142"/>
-      <c r="F76" s="142"/>
-      <c r="G76" s="142"/>
+      <c r="C76" s="162"/>
+      <c r="D76" s="162"/>
+      <c r="E76" s="162"/>
+      <c r="F76" s="162"/>
+      <c r="G76" s="162"/>
       <c r="H76" s="112"/>
       <c r="I76" s="112"/>
       <c r="J76" s="19"/>
@@ -12103,15 +12103,15 @@
     <row r="77" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A77" s="16"/>
       <c r="B77" s="71"/>
-      <c r="C77" s="143" t="s">
+      <c r="C77" s="187" t="s">
         <v>62</v>
       </c>
-      <c r="D77" s="144"/>
-      <c r="E77" s="144"/>
-      <c r="F77" s="144"/>
-      <c r="G77" s="145"/>
-      <c r="H77" s="185"/>
-      <c r="I77" s="181"/>
+      <c r="D77" s="188"/>
+      <c r="E77" s="188"/>
+      <c r="F77" s="188"/>
+      <c r="G77" s="189"/>
+      <c r="H77" s="140"/>
+      <c r="I77" s="129"/>
       <c r="J77" s="63"/>
       <c r="K77" s="64"/>
       <c r="L77" s="64"/>
@@ -12227,13 +12227,13 @@
     <row r="78" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A78" s="16"/>
       <c r="B78" s="71"/>
-      <c r="C78" s="146"/>
-      <c r="D78" s="147"/>
-      <c r="E78" s="147"/>
-      <c r="F78" s="147"/>
-      <c r="G78" s="148"/>
-      <c r="H78" s="186"/>
-      <c r="I78" s="182"/>
+      <c r="C78" s="190"/>
+      <c r="D78" s="191"/>
+      <c r="E78" s="191"/>
+      <c r="F78" s="191"/>
+      <c r="G78" s="192"/>
+      <c r="H78" s="141"/>
+      <c r="I78" s="130"/>
       <c r="J78" s="63"/>
       <c r="K78" s="64"/>
       <c r="L78" s="64"/>
@@ -12350,12 +12350,12 @@
       <c r="A79" s="16"/>
       <c r="B79" s="71"/>
       <c r="C79" s="76"/>
-      <c r="D79" s="115" t="s">
+      <c r="D79" s="132" t="s">
         <v>63</v>
       </c>
-      <c r="E79" s="116"/>
-      <c r="F79" s="116"/>
-      <c r="G79" s="117"/>
+      <c r="E79" s="133"/>
+      <c r="F79" s="133"/>
+      <c r="G79" s="134"/>
       <c r="H79" s="77"/>
       <c r="I79" s="67"/>
       <c r="J79" s="63"/>
@@ -12474,10 +12474,10 @@
       <c r="A80" s="16"/>
       <c r="B80" s="71"/>
       <c r="C80" s="76"/>
-      <c r="D80" s="118"/>
-      <c r="E80" s="119"/>
-      <c r="F80" s="119"/>
-      <c r="G80" s="120"/>
+      <c r="D80" s="135"/>
+      <c r="E80" s="136"/>
+      <c r="F80" s="136"/>
+      <c r="G80" s="137"/>
       <c r="H80" s="77"/>
       <c r="I80" s="67"/>
       <c r="J80" s="63"/>
@@ -12597,15 +12597,15 @@
       <c r="B81" s="36"/>
       <c r="C81" s="60"/>
       <c r="D81" s="70"/>
-      <c r="E81" s="149" t="s">
+      <c r="E81" s="105" t="s">
         <v>73</v>
       </c>
-      <c r="F81" s="149"/>
-      <c r="G81" s="149"/>
-      <c r="H81" s="103">
+      <c r="F81" s="105"/>
+      <c r="G81" s="105"/>
+      <c r="H81" s="111">
         <v>45611</v>
       </c>
-      <c r="I81" s="105">
+      <c r="I81" s="126">
         <v>100</v>
       </c>
       <c r="J81" s="19"/>
@@ -12725,11 +12725,11 @@
       <c r="B82" s="36"/>
       <c r="C82" s="60"/>
       <c r="D82" s="70"/>
-      <c r="E82" s="102"/>
-      <c r="F82" s="102"/>
-      <c r="G82" s="102"/>
-      <c r="H82" s="104"/>
-      <c r="I82" s="106"/>
+      <c r="E82" s="103"/>
+      <c r="F82" s="103"/>
+      <c r="G82" s="103"/>
+      <c r="H82" s="107"/>
+      <c r="I82" s="109"/>
       <c r="J82" s="19"/>
       <c r="K82" s="20"/>
       <c r="L82" s="20"/>
@@ -12847,15 +12847,15 @@
       <c r="B83" s="36"/>
       <c r="C83" s="60"/>
       <c r="D83" s="70"/>
-      <c r="E83" s="102" t="s">
+      <c r="E83" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="F83" s="102"/>
-      <c r="G83" s="102"/>
-      <c r="H83" s="103">
+      <c r="F83" s="103"/>
+      <c r="G83" s="103"/>
+      <c r="H83" s="111">
         <v>45615</v>
       </c>
-      <c r="I83" s="105">
+      <c r="I83" s="126">
         <v>100</v>
       </c>
       <c r="J83" s="19"/>
@@ -12975,11 +12975,11 @@
       <c r="B84" s="36"/>
       <c r="C84" s="60"/>
       <c r="D84" s="70"/>
-      <c r="E84" s="102"/>
-      <c r="F84" s="102"/>
-      <c r="G84" s="102"/>
-      <c r="H84" s="104"/>
-      <c r="I84" s="106"/>
+      <c r="E84" s="103"/>
+      <c r="F84" s="103"/>
+      <c r="G84" s="103"/>
+      <c r="H84" s="107"/>
+      <c r="I84" s="109"/>
       <c r="J84" s="19"/>
       <c r="K84" s="20"/>
       <c r="L84" s="20"/>
@@ -13097,15 +13097,15 @@
       <c r="B85" s="36"/>
       <c r="C85" s="60"/>
       <c r="D85" s="70"/>
-      <c r="E85" s="189" t="s">
+      <c r="E85" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="F85" s="121"/>
-      <c r="G85" s="122"/>
-      <c r="H85" s="111">
+      <c r="F85" s="115"/>
+      <c r="G85" s="116"/>
+      <c r="H85" s="110">
         <v>45617</v>
       </c>
-      <c r="I85" s="105">
+      <c r="I85" s="126">
         <v>100</v>
       </c>
       <c r="J85" s="62"/>
@@ -13225,11 +13225,11 @@
       <c r="B86" s="36"/>
       <c r="C86" s="60"/>
       <c r="D86" s="70"/>
-      <c r="E86" s="150"/>
-      <c r="F86" s="125"/>
-      <c r="G86" s="126"/>
-      <c r="H86" s="111"/>
-      <c r="I86" s="106"/>
+      <c r="E86" s="117"/>
+      <c r="F86" s="118"/>
+      <c r="G86" s="119"/>
+      <c r="H86" s="110"/>
+      <c r="I86" s="109"/>
       <c r="J86" s="62"/>
       <c r="K86" s="20"/>
       <c r="L86" s="20"/>
@@ -13346,16 +13346,16 @@
       <c r="A87" s="16"/>
       <c r="B87" s="71"/>
       <c r="C87" s="90"/>
-      <c r="D87" s="102" t="s">
+      <c r="D87" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="E87" s="102"/>
-      <c r="F87" s="102"/>
-      <c r="G87" s="102"/>
-      <c r="H87" s="103">
+      <c r="E87" s="103"/>
+      <c r="F87" s="103"/>
+      <c r="G87" s="103"/>
+      <c r="H87" s="111">
         <v>45615</v>
       </c>
-      <c r="I87" s="105">
+      <c r="I87" s="126">
         <v>100</v>
       </c>
       <c r="J87" s="62"/>
@@ -13474,12 +13474,12 @@
       <c r="A88" s="16"/>
       <c r="B88" s="71"/>
       <c r="C88" s="90"/>
-      <c r="D88" s="102"/>
-      <c r="E88" s="102"/>
-      <c r="F88" s="102"/>
-      <c r="G88" s="102"/>
-      <c r="H88" s="104"/>
-      <c r="I88" s="106"/>
+      <c r="D88" s="103"/>
+      <c r="E88" s="103"/>
+      <c r="F88" s="103"/>
+      <c r="G88" s="103"/>
+      <c r="H88" s="107"/>
+      <c r="I88" s="109"/>
       <c r="J88" s="62"/>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -13596,14 +13596,14 @@
       <c r="A89" s="16"/>
       <c r="B89" s="36"/>
       <c r="C89" s="79"/>
-      <c r="D89" s="115" t="s">
+      <c r="D89" s="132" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="116"/>
-      <c r="F89" s="116"/>
-      <c r="G89" s="117"/>
-      <c r="H89" s="187"/>
-      <c r="I89" s="188"/>
+      <c r="E89" s="133"/>
+      <c r="F89" s="133"/>
+      <c r="G89" s="134"/>
+      <c r="H89" s="131"/>
+      <c r="I89" s="128"/>
       <c r="J89" s="66"/>
       <c r="K89" s="64"/>
       <c r="L89" s="64"/>
@@ -13720,12 +13720,12 @@
       <c r="A90" s="16"/>
       <c r="B90" s="36"/>
       <c r="C90" s="79"/>
-      <c r="D90" s="118"/>
-      <c r="E90" s="119"/>
-      <c r="F90" s="119"/>
-      <c r="G90" s="120"/>
-      <c r="H90" s="187"/>
-      <c r="I90" s="188"/>
+      <c r="D90" s="135"/>
+      <c r="E90" s="136"/>
+      <c r="F90" s="136"/>
+      <c r="G90" s="137"/>
+      <c r="H90" s="131"/>
+      <c r="I90" s="128"/>
       <c r="J90" s="66"/>
       <c r="K90" s="64"/>
       <c r="L90" s="64"/>
@@ -13843,15 +13843,17 @@
       <c r="B91" s="36"/>
       <c r="C91" s="60"/>
       <c r="D91" s="70"/>
-      <c r="E91" s="149" t="s">
+      <c r="E91" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="F91" s="149"/>
-      <c r="G91" s="149"/>
-      <c r="H91" s="103">
+      <c r="F91" s="105"/>
+      <c r="G91" s="105"/>
+      <c r="H91" s="111">
         <v>45616</v>
       </c>
-      <c r="I91" s="105"/>
+      <c r="I91" s="126">
+        <v>100</v>
+      </c>
       <c r="J91" s="19"/>
       <c r="K91" s="20"/>
       <c r="L91" s="20"/>
@@ -13969,11 +13971,11 @@
       <c r="B92" s="36"/>
       <c r="C92" s="60"/>
       <c r="D92" s="70"/>
-      <c r="E92" s="102"/>
-      <c r="F92" s="102"/>
-      <c r="G92" s="102"/>
-      <c r="H92" s="104"/>
-      <c r="I92" s="106"/>
+      <c r="E92" s="103"/>
+      <c r="F92" s="103"/>
+      <c r="G92" s="103"/>
+      <c r="H92" s="107"/>
+      <c r="I92" s="109"/>
       <c r="J92" s="19"/>
       <c r="K92" s="20"/>
       <c r="L92" s="20"/>
@@ -14091,15 +14093,17 @@
       <c r="B93" s="36"/>
       <c r="C93" s="60"/>
       <c r="D93" s="70"/>
-      <c r="E93" s="102" t="s">
+      <c r="E93" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="F93" s="102"/>
-      <c r="G93" s="102"/>
-      <c r="H93" s="103">
+      <c r="F93" s="103"/>
+      <c r="G93" s="103"/>
+      <c r="H93" s="111">
         <v>45617</v>
       </c>
-      <c r="I93" s="105"/>
+      <c r="I93" s="126">
+        <v>100</v>
+      </c>
       <c r="J93" s="19"/>
       <c r="K93" s="20"/>
       <c r="L93" s="20"/>
@@ -14217,11 +14221,11 @@
       <c r="B94" s="36"/>
       <c r="C94" s="60"/>
       <c r="D94" s="70"/>
-      <c r="E94" s="102"/>
-      <c r="F94" s="102"/>
-      <c r="G94" s="102"/>
-      <c r="H94" s="104"/>
-      <c r="I94" s="106"/>
+      <c r="E94" s="103"/>
+      <c r="F94" s="103"/>
+      <c r="G94" s="103"/>
+      <c r="H94" s="107"/>
+      <c r="I94" s="109"/>
       <c r="J94" s="19"/>
       <c r="K94" s="20"/>
       <c r="L94" s="20"/>
@@ -14339,15 +14343,17 @@
       <c r="B95" s="36"/>
       <c r="C95" s="60"/>
       <c r="D95" s="70"/>
-      <c r="E95" s="102" t="s">
+      <c r="E95" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="F95" s="102"/>
-      <c r="G95" s="102"/>
-      <c r="H95" s="103">
+      <c r="F95" s="103"/>
+      <c r="G95" s="103"/>
+      <c r="H95" s="111">
         <v>45618</v>
       </c>
-      <c r="I95" s="105"/>
+      <c r="I95" s="126">
+        <v>100</v>
+      </c>
       <c r="J95" s="19"/>
       <c r="K95" s="20"/>
       <c r="L95" s="20"/>
@@ -14465,11 +14471,11 @@
       <c r="B96" s="36"/>
       <c r="C96" s="60"/>
       <c r="D96" s="70"/>
-      <c r="E96" s="102"/>
-      <c r="F96" s="102"/>
-      <c r="G96" s="102"/>
-      <c r="H96" s="104"/>
-      <c r="I96" s="106"/>
+      <c r="E96" s="103"/>
+      <c r="F96" s="103"/>
+      <c r="G96" s="103"/>
+      <c r="H96" s="107"/>
+      <c r="I96" s="109"/>
       <c r="J96" s="19"/>
       <c r="K96" s="20"/>
       <c r="L96" s="20"/>
@@ -14587,15 +14593,17 @@
       <c r="B97" s="36"/>
       <c r="C97" s="60"/>
       <c r="D97" s="70"/>
-      <c r="E97" s="102" t="s">
+      <c r="E97" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="F97" s="102"/>
-      <c r="G97" s="102"/>
-      <c r="H97" s="103">
+      <c r="F97" s="103"/>
+      <c r="G97" s="103"/>
+      <c r="H97" s="111">
         <v>45621</v>
       </c>
-      <c r="I97" s="105"/>
+      <c r="I97" s="126">
+        <v>100</v>
+      </c>
       <c r="J97" s="19"/>
       <c r="K97" s="20"/>
       <c r="L97" s="20"/>
@@ -14713,11 +14721,11 @@
       <c r="B98" s="36"/>
       <c r="C98" s="60"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="102"/>
-      <c r="F98" s="102"/>
-      <c r="G98" s="102"/>
-      <c r="H98" s="104"/>
-      <c r="I98" s="106"/>
+      <c r="E98" s="103"/>
+      <c r="F98" s="103"/>
+      <c r="G98" s="103"/>
+      <c r="H98" s="107"/>
+      <c r="I98" s="109"/>
       <c r="J98" s="19"/>
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
@@ -14835,15 +14843,17 @@
       <c r="B99" s="36"/>
       <c r="C99" s="60"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="102" t="s">
+      <c r="E99" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="F99" s="102"/>
-      <c r="G99" s="102"/>
-      <c r="H99" s="103">
+      <c r="F99" s="103"/>
+      <c r="G99" s="103"/>
+      <c r="H99" s="111">
         <v>45622</v>
       </c>
-      <c r="I99" s="105"/>
+      <c r="I99" s="126">
+        <v>100</v>
+      </c>
       <c r="J99" s="19"/>
       <c r="K99" s="20"/>
       <c r="L99" s="20"/>
@@ -14961,11 +14971,11 @@
       <c r="B100" s="36"/>
       <c r="C100" s="60"/>
       <c r="D100" s="70"/>
-      <c r="E100" s="102"/>
-      <c r="F100" s="102"/>
-      <c r="G100" s="102"/>
-      <c r="H100" s="104"/>
-      <c r="I100" s="106"/>
+      <c r="E100" s="103"/>
+      <c r="F100" s="103"/>
+      <c r="G100" s="103"/>
+      <c r="H100" s="107"/>
+      <c r="I100" s="109"/>
       <c r="J100" s="19"/>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -15083,15 +15093,17 @@
       <c r="B101" s="71"/>
       <c r="C101" s="91"/>
       <c r="D101" s="70"/>
-      <c r="E101" s="150" t="s">
+      <c r="E101" s="117" t="s">
         <v>61</v>
       </c>
-      <c r="F101" s="125"/>
-      <c r="G101" s="126"/>
-      <c r="H101" s="103">
+      <c r="F101" s="118"/>
+      <c r="G101" s="119"/>
+      <c r="H101" s="111">
         <v>45623</v>
       </c>
-      <c r="I101" s="112"/>
+      <c r="I101" s="112">
+        <v>100</v>
+      </c>
       <c r="J101" s="62"/>
       <c r="K101" s="20"/>
       <c r="L101" s="20"/>
@@ -15209,10 +15221,10 @@
       <c r="B102" s="71"/>
       <c r="C102" s="91"/>
       <c r="D102" s="70"/>
-      <c r="E102" s="150"/>
-      <c r="F102" s="125"/>
-      <c r="G102" s="126"/>
-      <c r="H102" s="104"/>
+      <c r="E102" s="117"/>
+      <c r="F102" s="118"/>
+      <c r="G102" s="119"/>
+      <c r="H102" s="107"/>
       <c r="I102" s="112"/>
       <c r="J102" s="62"/>
       <c r="K102" s="20"/>
@@ -15330,16 +15342,18 @@
       <c r="A103" s="16"/>
       <c r="B103" s="71"/>
       <c r="C103" s="90"/>
-      <c r="D103" s="102" t="s">
+      <c r="D103" s="103" t="s">
         <v>77</v>
       </c>
-      <c r="E103" s="102"/>
-      <c r="F103" s="102"/>
-      <c r="G103" s="102"/>
-      <c r="H103" s="103">
+      <c r="E103" s="103"/>
+      <c r="F103" s="103"/>
+      <c r="G103" s="103"/>
+      <c r="H103" s="111">
         <v>45622</v>
       </c>
-      <c r="I103" s="109"/>
+      <c r="I103" s="113">
+        <v>100</v>
+      </c>
       <c r="J103" s="62"/>
       <c r="K103" s="20"/>
       <c r="L103" s="20"/>
@@ -15456,12 +15470,12 @@
       <c r="A104" s="16"/>
       <c r="B104" s="71"/>
       <c r="C104" s="90"/>
-      <c r="D104" s="102"/>
-      <c r="E104" s="102"/>
-      <c r="F104" s="102"/>
-      <c r="G104" s="102"/>
-      <c r="H104" s="104"/>
-      <c r="I104" s="110"/>
+      <c r="D104" s="103"/>
+      <c r="E104" s="103"/>
+      <c r="F104" s="103"/>
+      <c r="G104" s="103"/>
+      <c r="H104" s="107"/>
+      <c r="I104" s="143"/>
       <c r="J104" s="62"/>
       <c r="K104" s="20"/>
       <c r="L104" s="20"/>
@@ -15577,15 +15591,15 @@
     <row r="105" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A105" s="16"/>
       <c r="B105" s="71"/>
-      <c r="C105" s="143" t="s">
+      <c r="C105" s="187" t="s">
         <v>64</v>
       </c>
-      <c r="D105" s="144"/>
-      <c r="E105" s="144"/>
-      <c r="F105" s="144"/>
-      <c r="G105" s="145"/>
-      <c r="H105" s="190"/>
-      <c r="I105" s="188"/>
+      <c r="D105" s="188"/>
+      <c r="E105" s="188"/>
+      <c r="F105" s="188"/>
+      <c r="G105" s="189"/>
+      <c r="H105" s="127"/>
+      <c r="I105" s="128"/>
       <c r="J105" s="66"/>
       <c r="K105" s="64"/>
       <c r="L105" s="64"/>
@@ -15701,13 +15715,13 @@
     <row r="106" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A106" s="16"/>
       <c r="B106" s="71"/>
-      <c r="C106" s="146"/>
-      <c r="D106" s="147"/>
-      <c r="E106" s="147"/>
-      <c r="F106" s="147"/>
-      <c r="G106" s="148"/>
-      <c r="H106" s="190"/>
-      <c r="I106" s="188"/>
+      <c r="C106" s="190"/>
+      <c r="D106" s="191"/>
+      <c r="E106" s="191"/>
+      <c r="F106" s="191"/>
+      <c r="G106" s="192"/>
+      <c r="H106" s="127"/>
+      <c r="I106" s="128"/>
       <c r="J106" s="66"/>
       <c r="K106" s="64"/>
       <c r="L106" s="64"/>
@@ -15824,14 +15838,14 @@
       <c r="A107" s="16"/>
       <c r="B107" s="36"/>
       <c r="C107" s="78"/>
-      <c r="D107" s="115" t="s">
+      <c r="D107" s="132" t="s">
         <v>59</v>
       </c>
-      <c r="E107" s="116"/>
-      <c r="F107" s="116"/>
-      <c r="G107" s="117"/>
-      <c r="H107" s="190"/>
-      <c r="I107" s="188"/>
+      <c r="E107" s="133"/>
+      <c r="F107" s="133"/>
+      <c r="G107" s="134"/>
+      <c r="H107" s="127"/>
+      <c r="I107" s="128"/>
       <c r="J107" s="66"/>
       <c r="K107" s="64"/>
       <c r="L107" s="64"/>
@@ -15948,12 +15962,12 @@
       <c r="A108" s="16"/>
       <c r="B108" s="36"/>
       <c r="C108" s="76"/>
-      <c r="D108" s="118"/>
-      <c r="E108" s="119"/>
-      <c r="F108" s="119"/>
-      <c r="G108" s="120"/>
-      <c r="H108" s="190"/>
-      <c r="I108" s="188"/>
+      <c r="D108" s="135"/>
+      <c r="E108" s="136"/>
+      <c r="F108" s="136"/>
+      <c r="G108" s="137"/>
+      <c r="H108" s="127"/>
+      <c r="I108" s="128"/>
       <c r="J108" s="66"/>
       <c r="K108" s="64"/>
       <c r="L108" s="64"/>
@@ -16071,15 +16085,15 @@
       <c r="B109" s="36"/>
       <c r="C109" s="60"/>
       <c r="D109" s="70"/>
-      <c r="E109" s="149" t="s">
+      <c r="E109" s="105" t="s">
         <v>73</v>
       </c>
-      <c r="F109" s="149"/>
-      <c r="G109" s="149"/>
-      <c r="H109" s="103">
+      <c r="F109" s="105"/>
+      <c r="G109" s="105"/>
+      <c r="H109" s="111">
         <v>45624</v>
       </c>
-      <c r="I109" s="109"/>
+      <c r="I109" s="113"/>
       <c r="J109" s="62"/>
       <c r="K109" s="20"/>
       <c r="L109" s="20"/>
@@ -16197,11 +16211,11 @@
       <c r="B110" s="36"/>
       <c r="C110" s="60"/>
       <c r="D110" s="70"/>
-      <c r="E110" s="102"/>
-      <c r="F110" s="102"/>
-      <c r="G110" s="102"/>
-      <c r="H110" s="104"/>
-      <c r="I110" s="110"/>
+      <c r="E110" s="103"/>
+      <c r="F110" s="103"/>
+      <c r="G110" s="103"/>
+      <c r="H110" s="107"/>
+      <c r="I110" s="143"/>
       <c r="J110" s="62"/>
       <c r="K110" s="20"/>
       <c r="L110" s="20"/>
@@ -16319,15 +16333,15 @@
       <c r="B111" s="36"/>
       <c r="C111" s="60"/>
       <c r="D111" s="70"/>
-      <c r="E111" s="102" t="s">
+      <c r="E111" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="F111" s="102"/>
-      <c r="G111" s="102"/>
-      <c r="H111" s="103">
+      <c r="F111" s="103"/>
+      <c r="G111" s="103"/>
+      <c r="H111" s="111">
         <v>45625</v>
       </c>
-      <c r="I111" s="109"/>
+      <c r="I111" s="113"/>
       <c r="J111" s="62"/>
       <c r="K111" s="20"/>
       <c r="L111" s="20"/>
@@ -16445,11 +16459,11 @@
       <c r="B112" s="36"/>
       <c r="C112" s="60"/>
       <c r="D112" s="70"/>
-      <c r="E112" s="102"/>
-      <c r="F112" s="102"/>
-      <c r="G112" s="102"/>
-      <c r="H112" s="104"/>
-      <c r="I112" s="110"/>
+      <c r="E112" s="103"/>
+      <c r="F112" s="103"/>
+      <c r="G112" s="103"/>
+      <c r="H112" s="107"/>
+      <c r="I112" s="143"/>
       <c r="J112" s="62"/>
       <c r="K112" s="20"/>
       <c r="L112" s="20"/>
@@ -16567,12 +16581,12 @@
       <c r="B113" s="71"/>
       <c r="C113" s="91"/>
       <c r="D113" s="70"/>
-      <c r="E113" s="102" t="s">
+      <c r="E113" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="F113" s="102"/>
-      <c r="G113" s="102"/>
-      <c r="H113" s="111">
+      <c r="F113" s="103"/>
+      <c r="G113" s="103"/>
+      <c r="H113" s="110">
         <v>45630</v>
       </c>
       <c r="I113" s="112"/>
@@ -16693,11 +16707,11 @@
       <c r="B114" s="71"/>
       <c r="C114" s="91"/>
       <c r="D114" s="70"/>
-      <c r="E114" s="198"/>
-      <c r="F114" s="198"/>
-      <c r="G114" s="198"/>
-      <c r="H114" s="103"/>
-      <c r="I114" s="109"/>
+      <c r="E114" s="125"/>
+      <c r="F114" s="125"/>
+      <c r="G114" s="125"/>
+      <c r="H114" s="111"/>
+      <c r="I114" s="113"/>
       <c r="J114" s="62"/>
       <c r="K114" s="20"/>
       <c r="L114" s="20"/>
@@ -16814,13 +16828,13 @@
       <c r="A115" s="16"/>
       <c r="B115" s="71"/>
       <c r="C115" s="91"/>
-      <c r="D115" s="102" t="s">
+      <c r="D115" s="103" t="s">
         <v>78</v>
       </c>
-      <c r="E115" s="102"/>
-      <c r="F115" s="102"/>
-      <c r="G115" s="102"/>
-      <c r="H115" s="111">
+      <c r="E115" s="103"/>
+      <c r="F115" s="103"/>
+      <c r="G115" s="103"/>
+      <c r="H115" s="110">
         <v>45625</v>
       </c>
       <c r="I115" s="112"/>
@@ -16940,11 +16954,11 @@
       <c r="A116" s="16"/>
       <c r="B116" s="71"/>
       <c r="C116" s="91"/>
-      <c r="D116" s="102"/>
-      <c r="E116" s="102"/>
-      <c r="F116" s="102"/>
-      <c r="G116" s="102"/>
-      <c r="H116" s="111"/>
+      <c r="D116" s="103"/>
+      <c r="E116" s="103"/>
+      <c r="F116" s="103"/>
+      <c r="G116" s="103"/>
+      <c r="H116" s="110"/>
       <c r="I116" s="112"/>
       <c r="J116" s="62"/>
       <c r="K116" s="20"/>
@@ -17062,14 +17076,14 @@
       <c r="A117" s="16"/>
       <c r="B117" s="36"/>
       <c r="C117" s="80"/>
-      <c r="D117" s="115" t="s">
+      <c r="D117" s="132" t="s">
         <v>60</v>
       </c>
-      <c r="E117" s="116"/>
-      <c r="F117" s="116"/>
-      <c r="G117" s="117"/>
-      <c r="H117" s="191"/>
-      <c r="I117" s="181"/>
+      <c r="E117" s="133"/>
+      <c r="F117" s="133"/>
+      <c r="G117" s="134"/>
+      <c r="H117" s="121"/>
+      <c r="I117" s="129"/>
       <c r="J117" s="63"/>
       <c r="K117" s="64"/>
       <c r="L117" s="64"/>
@@ -17186,12 +17200,12 @@
       <c r="A118" s="16"/>
       <c r="B118" s="36"/>
       <c r="C118" s="80"/>
-      <c r="D118" s="118"/>
-      <c r="E118" s="119"/>
-      <c r="F118" s="119"/>
-      <c r="G118" s="120"/>
-      <c r="H118" s="192"/>
-      <c r="I118" s="182"/>
+      <c r="D118" s="135"/>
+      <c r="E118" s="136"/>
+      <c r="F118" s="136"/>
+      <c r="G118" s="137"/>
+      <c r="H118" s="122"/>
+      <c r="I118" s="130"/>
       <c r="J118" s="63"/>
       <c r="K118" s="64"/>
       <c r="L118" s="64"/>
@@ -17309,15 +17323,15 @@
       <c r="B119" s="36"/>
       <c r="C119" s="60"/>
       <c r="D119" s="70"/>
-      <c r="E119" s="149" t="s">
+      <c r="E119" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="F119" s="149"/>
-      <c r="G119" s="149"/>
-      <c r="H119" s="103">
+      <c r="F119" s="105"/>
+      <c r="G119" s="105"/>
+      <c r="H119" s="111">
         <v>45629</v>
       </c>
-      <c r="I119" s="105"/>
+      <c r="I119" s="126"/>
       <c r="J119" s="19"/>
       <c r="K119" s="20"/>
       <c r="L119" s="20"/>
@@ -17435,11 +17449,11 @@
       <c r="B120" s="36"/>
       <c r="C120" s="60"/>
       <c r="D120" s="70"/>
-      <c r="E120" s="102"/>
-      <c r="F120" s="102"/>
-      <c r="G120" s="102"/>
-      <c r="H120" s="104"/>
-      <c r="I120" s="106"/>
+      <c r="E120" s="103"/>
+      <c r="F120" s="103"/>
+      <c r="G120" s="103"/>
+      <c r="H120" s="107"/>
+      <c r="I120" s="109"/>
       <c r="J120" s="19"/>
       <c r="K120" s="20"/>
       <c r="L120" s="20"/>
@@ -17557,15 +17571,15 @@
       <c r="B121" s="36"/>
       <c r="C121" s="60"/>
       <c r="D121" s="70"/>
-      <c r="E121" s="102" t="s">
+      <c r="E121" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="F121" s="102"/>
-      <c r="G121" s="102"/>
-      <c r="H121" s="103">
+      <c r="F121" s="103"/>
+      <c r="G121" s="103"/>
+      <c r="H121" s="111">
         <v>45630</v>
       </c>
-      <c r="I121" s="105"/>
+      <c r="I121" s="126"/>
       <c r="J121" s="19"/>
       <c r="K121" s="20"/>
       <c r="L121" s="20"/>
@@ -17683,11 +17697,11 @@
       <c r="B122" s="36"/>
       <c r="C122" s="60"/>
       <c r="D122" s="70"/>
-      <c r="E122" s="102"/>
-      <c r="F122" s="102"/>
-      <c r="G122" s="102"/>
-      <c r="H122" s="104"/>
-      <c r="I122" s="106"/>
+      <c r="E122" s="103"/>
+      <c r="F122" s="103"/>
+      <c r="G122" s="103"/>
+      <c r="H122" s="107"/>
+      <c r="I122" s="109"/>
       <c r="J122" s="19"/>
       <c r="K122" s="20"/>
       <c r="L122" s="20"/>
@@ -17805,12 +17819,12 @@
       <c r="B123" s="36"/>
       <c r="C123" s="60"/>
       <c r="D123" s="70"/>
-      <c r="E123" s="102" t="s">
+      <c r="E123" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="F123" s="102"/>
-      <c r="G123" s="102"/>
-      <c r="H123" s="197">
+      <c r="F123" s="103"/>
+      <c r="G123" s="103"/>
+      <c r="H123" s="120">
         <v>45631</v>
       </c>
       <c r="I123" s="112"/>
@@ -17931,10 +17945,10 @@
       <c r="B124" s="36"/>
       <c r="C124" s="60"/>
       <c r="D124" s="70"/>
-      <c r="E124" s="102"/>
-      <c r="F124" s="102"/>
-      <c r="G124" s="102"/>
-      <c r="H124" s="197"/>
+      <c r="E124" s="103"/>
+      <c r="F124" s="103"/>
+      <c r="G124" s="103"/>
+      <c r="H124" s="120"/>
       <c r="I124" s="112"/>
       <c r="J124" s="62"/>
       <c r="K124" s="20"/>
@@ -18053,12 +18067,12 @@
       <c r="B125" s="36"/>
       <c r="C125" s="60"/>
       <c r="D125" s="70"/>
-      <c r="E125" s="102" t="s">
+      <c r="E125" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="F125" s="102"/>
-      <c r="G125" s="102"/>
-      <c r="H125" s="111">
+      <c r="F125" s="103"/>
+      <c r="G125" s="103"/>
+      <c r="H125" s="110">
         <v>45632</v>
       </c>
       <c r="I125" s="112"/>
@@ -18179,10 +18193,10 @@
       <c r="B126" s="36"/>
       <c r="C126" s="60"/>
       <c r="D126" s="70"/>
-      <c r="E126" s="102"/>
-      <c r="F126" s="102"/>
-      <c r="G126" s="102"/>
-      <c r="H126" s="111"/>
+      <c r="E126" s="103"/>
+      <c r="F126" s="103"/>
+      <c r="G126" s="103"/>
+      <c r="H126" s="110"/>
       <c r="I126" s="112"/>
       <c r="J126" s="62"/>
       <c r="K126" s="20"/>
@@ -18301,15 +18315,15 @@
       <c r="B127" s="36"/>
       <c r="C127" s="60"/>
       <c r="D127" s="70"/>
-      <c r="E127" s="102" t="s">
+      <c r="E127" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="F127" s="102"/>
-      <c r="G127" s="102"/>
-      <c r="H127" s="103">
+      <c r="F127" s="103"/>
+      <c r="G127" s="103"/>
+      <c r="H127" s="111">
         <v>45635</v>
       </c>
-      <c r="I127" s="105"/>
+      <c r="I127" s="126"/>
       <c r="J127" s="19"/>
       <c r="K127" s="20"/>
       <c r="L127" s="20"/>
@@ -18427,11 +18441,11 @@
       <c r="B128" s="36"/>
       <c r="C128" s="60"/>
       <c r="D128" s="70"/>
-      <c r="E128" s="198"/>
-      <c r="F128" s="198"/>
-      <c r="G128" s="198"/>
-      <c r="H128" s="104"/>
-      <c r="I128" s="106"/>
+      <c r="E128" s="125"/>
+      <c r="F128" s="125"/>
+      <c r="G128" s="125"/>
+      <c r="H128" s="107"/>
+      <c r="I128" s="109"/>
       <c r="J128" s="19"/>
       <c r="K128" s="20"/>
       <c r="L128" s="20"/>
@@ -18549,12 +18563,12 @@
       <c r="B129" s="71"/>
       <c r="C129" s="91"/>
       <c r="D129" s="70"/>
-      <c r="E129" s="189" t="s">
+      <c r="E129" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="F129" s="121"/>
-      <c r="G129" s="122"/>
-      <c r="H129" s="111">
+      <c r="F129" s="115"/>
+      <c r="G129" s="116"/>
+      <c r="H129" s="110">
         <v>45638</v>
       </c>
       <c r="I129" s="112"/>
@@ -18675,10 +18689,10 @@
       <c r="B130" s="71"/>
       <c r="C130" s="91"/>
       <c r="D130" s="70"/>
-      <c r="E130" s="150"/>
-      <c r="F130" s="125"/>
-      <c r="G130" s="126"/>
-      <c r="H130" s="111"/>
+      <c r="E130" s="117"/>
+      <c r="F130" s="118"/>
+      <c r="G130" s="119"/>
+      <c r="H130" s="110"/>
       <c r="I130" s="112"/>
       <c r="J130" s="62"/>
       <c r="K130" s="20"/>
@@ -18796,16 +18810,16 @@
       <c r="A131" s="16"/>
       <c r="B131" s="71"/>
       <c r="C131" s="91"/>
-      <c r="D131" s="102" t="s">
+      <c r="D131" s="103" t="s">
         <v>79</v>
       </c>
-      <c r="E131" s="102"/>
-      <c r="F131" s="102"/>
-      <c r="G131" s="102"/>
-      <c r="H131" s="103">
+      <c r="E131" s="103"/>
+      <c r="F131" s="103"/>
+      <c r="G131" s="103"/>
+      <c r="H131" s="111">
         <v>45635</v>
       </c>
-      <c r="I131" s="109"/>
+      <c r="I131" s="113"/>
       <c r="J131" s="62"/>
       <c r="K131" s="20"/>
       <c r="L131" s="20"/>
@@ -18922,12 +18936,12 @@
       <c r="A132" s="16"/>
       <c r="B132" s="71"/>
       <c r="C132" s="90"/>
-      <c r="D132" s="102"/>
-      <c r="E132" s="102"/>
-      <c r="F132" s="102"/>
-      <c r="G132" s="102"/>
-      <c r="H132" s="104"/>
-      <c r="I132" s="110"/>
+      <c r="D132" s="103"/>
+      <c r="E132" s="103"/>
+      <c r="F132" s="103"/>
+      <c r="G132" s="103"/>
+      <c r="H132" s="107"/>
+      <c r="I132" s="143"/>
       <c r="J132" s="62"/>
       <c r="K132" s="20"/>
       <c r="L132" s="20"/>
@@ -19043,15 +19057,15 @@
     <row r="133" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A133" s="16"/>
       <c r="B133" s="36"/>
-      <c r="C133" s="115" t="s">
+      <c r="C133" s="132" t="s">
         <v>67</v>
       </c>
-      <c r="D133" s="116"/>
-      <c r="E133" s="116"/>
-      <c r="F133" s="116"/>
-      <c r="G133" s="117"/>
-      <c r="H133" s="191"/>
-      <c r="I133" s="107"/>
+      <c r="D133" s="133"/>
+      <c r="E133" s="133"/>
+      <c r="F133" s="133"/>
+      <c r="G133" s="134"/>
+      <c r="H133" s="121"/>
+      <c r="I133" s="123"/>
       <c r="J133" s="66"/>
       <c r="K133" s="64"/>
       <c r="L133" s="64"/>
@@ -19167,13 +19181,13 @@
     <row r="134" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A134" s="16"/>
       <c r="B134" s="36"/>
-      <c r="C134" s="118"/>
-      <c r="D134" s="119"/>
-      <c r="E134" s="119"/>
-      <c r="F134" s="119"/>
-      <c r="G134" s="120"/>
-      <c r="H134" s="192"/>
-      <c r="I134" s="108"/>
+      <c r="C134" s="135"/>
+      <c r="D134" s="136"/>
+      <c r="E134" s="136"/>
+      <c r="F134" s="136"/>
+      <c r="G134" s="137"/>
+      <c r="H134" s="122"/>
+      <c r="I134" s="124"/>
       <c r="J134" s="66"/>
       <c r="K134" s="64"/>
       <c r="L134" s="64"/>
@@ -19290,14 +19304,14 @@
       <c r="A135" s="16"/>
       <c r="B135" s="36"/>
       <c r="C135" s="60"/>
-      <c r="D135" s="115" t="s">
+      <c r="D135" s="132" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="116"/>
-      <c r="F135" s="116"/>
-      <c r="G135" s="117"/>
-      <c r="H135" s="113"/>
-      <c r="I135" s="181"/>
+      <c r="E135" s="133"/>
+      <c r="F135" s="133"/>
+      <c r="G135" s="134"/>
+      <c r="H135" s="193"/>
+      <c r="I135" s="129"/>
       <c r="J135" s="63"/>
       <c r="K135" s="64"/>
       <c r="L135" s="64"/>
@@ -19414,12 +19428,12 @@
       <c r="A136" s="16"/>
       <c r="B136" s="36"/>
       <c r="C136" s="60"/>
-      <c r="D136" s="118"/>
-      <c r="E136" s="119"/>
-      <c r="F136" s="119"/>
-      <c r="G136" s="120"/>
-      <c r="H136" s="130"/>
-      <c r="I136" s="183"/>
+      <c r="D136" s="135"/>
+      <c r="E136" s="136"/>
+      <c r="F136" s="136"/>
+      <c r="G136" s="137"/>
+      <c r="H136" s="198"/>
+      <c r="I136" s="144"/>
       <c r="J136" s="63"/>
       <c r="K136" s="64"/>
       <c r="L136" s="64"/>
@@ -19537,15 +19551,15 @@
       <c r="B137" s="36"/>
       <c r="C137" s="72"/>
       <c r="D137" s="74"/>
-      <c r="E137" s="121" t="s">
+      <c r="E137" s="115" t="s">
         <v>73</v>
       </c>
-      <c r="F137" s="121"/>
-      <c r="G137" s="122"/>
-      <c r="H137" s="103">
+      <c r="F137" s="115"/>
+      <c r="G137" s="116"/>
+      <c r="H137" s="111">
         <v>45636</v>
       </c>
-      <c r="I137" s="109"/>
+      <c r="I137" s="113"/>
       <c r="J137" s="62"/>
       <c r="K137" s="20"/>
       <c r="L137" s="20"/>
@@ -19663,11 +19677,11 @@
       <c r="B138" s="36"/>
       <c r="C138" s="72"/>
       <c r="D138" s="70"/>
-      <c r="E138" s="123"/>
-      <c r="F138" s="123"/>
-      <c r="G138" s="124"/>
-      <c r="H138" s="104"/>
-      <c r="I138" s="110"/>
+      <c r="E138" s="185"/>
+      <c r="F138" s="185"/>
+      <c r="G138" s="186"/>
+      <c r="H138" s="107"/>
+      <c r="I138" s="143"/>
       <c r="J138" s="62"/>
       <c r="K138" s="20"/>
       <c r="L138" s="20"/>
@@ -19785,15 +19799,15 @@
       <c r="B139" s="36"/>
       <c r="C139" s="72"/>
       <c r="D139" s="70"/>
-      <c r="E139" s="121" t="s">
+      <c r="E139" s="115" t="s">
         <v>74</v>
       </c>
-      <c r="F139" s="121"/>
-      <c r="G139" s="122"/>
-      <c r="H139" s="103">
+      <c r="F139" s="115"/>
+      <c r="G139" s="116"/>
+      <c r="H139" s="111">
         <v>45637</v>
       </c>
-      <c r="I139" s="109"/>
+      <c r="I139" s="113"/>
       <c r="J139" s="62"/>
       <c r="K139" s="20"/>
       <c r="L139" s="20"/>
@@ -19911,11 +19925,11 @@
       <c r="B140" s="36"/>
       <c r="C140" s="72"/>
       <c r="D140" s="70"/>
-      <c r="E140" s="125"/>
-      <c r="F140" s="125"/>
-      <c r="G140" s="126"/>
-      <c r="H140" s="104"/>
-      <c r="I140" s="110"/>
+      <c r="E140" s="118"/>
+      <c r="F140" s="118"/>
+      <c r="G140" s="119"/>
+      <c r="H140" s="107"/>
+      <c r="I140" s="143"/>
       <c r="J140" s="62"/>
       <c r="K140" s="20"/>
       <c r="L140" s="20"/>
@@ -20032,13 +20046,13 @@
       <c r="A141" s="16"/>
       <c r="B141" s="36"/>
       <c r="C141" s="82"/>
-      <c r="D141" s="102" t="s">
+      <c r="D141" s="103" t="s">
         <v>80</v>
       </c>
-      <c r="E141" s="102"/>
-      <c r="F141" s="102"/>
-      <c r="G141" s="102"/>
-      <c r="H141" s="103">
+      <c r="E141" s="103"/>
+      <c r="F141" s="103"/>
+      <c r="G141" s="103"/>
+      <c r="H141" s="111">
         <v>45637</v>
       </c>
       <c r="I141" s="92"/>
@@ -20158,11 +20172,11 @@
       <c r="A142" s="16"/>
       <c r="B142" s="36"/>
       <c r="C142" s="82"/>
-      <c r="D142" s="102"/>
-      <c r="E142" s="102"/>
-      <c r="F142" s="102"/>
-      <c r="G142" s="102"/>
-      <c r="H142" s="104"/>
+      <c r="D142" s="103"/>
+      <c r="E142" s="103"/>
+      <c r="F142" s="103"/>
+      <c r="G142" s="103"/>
+      <c r="H142" s="107"/>
       <c r="I142" s="92"/>
       <c r="J142" s="62"/>
       <c r="K142" s="20"/>
@@ -20280,14 +20294,14 @@
       <c r="A143" s="16"/>
       <c r="B143" s="36"/>
       <c r="C143" s="72"/>
-      <c r="D143" s="127" t="s">
+      <c r="D143" s="195" t="s">
         <v>66</v>
       </c>
-      <c r="E143" s="128"/>
-      <c r="F143" s="128"/>
-      <c r="G143" s="129"/>
-      <c r="H143" s="113"/>
-      <c r="I143" s="107"/>
+      <c r="E143" s="196"/>
+      <c r="F143" s="196"/>
+      <c r="G143" s="197"/>
+      <c r="H143" s="193"/>
+      <c r="I143" s="123"/>
       <c r="J143" s="66"/>
       <c r="K143" s="64"/>
       <c r="L143" s="64"/>
@@ -20404,12 +20418,12 @@
       <c r="A144" s="16"/>
       <c r="B144" s="36"/>
       <c r="C144" s="72"/>
-      <c r="D144" s="118"/>
-      <c r="E144" s="119"/>
-      <c r="F144" s="119"/>
-      <c r="G144" s="120"/>
-      <c r="H144" s="114"/>
-      <c r="I144" s="108"/>
+      <c r="D144" s="135"/>
+      <c r="E144" s="136"/>
+      <c r="F144" s="136"/>
+      <c r="G144" s="137"/>
+      <c r="H144" s="194"/>
+      <c r="I144" s="124"/>
       <c r="J144" s="66"/>
       <c r="K144" s="64"/>
       <c r="L144" s="64"/>
@@ -20527,15 +20541,15 @@
       <c r="B145" s="36"/>
       <c r="C145" s="72"/>
       <c r="D145" s="74"/>
-      <c r="E145" s="121" t="s">
+      <c r="E145" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="F145" s="121"/>
-      <c r="G145" s="122"/>
-      <c r="H145" s="103">
+      <c r="F145" s="115"/>
+      <c r="G145" s="116"/>
+      <c r="H145" s="111">
         <v>45639</v>
       </c>
-      <c r="I145" s="109"/>
+      <c r="I145" s="113"/>
       <c r="J145" s="62"/>
       <c r="K145" s="20"/>
       <c r="L145" s="20"/>
@@ -20653,11 +20667,11 @@
       <c r="B146" s="36"/>
       <c r="C146" s="72"/>
       <c r="D146" s="70"/>
-      <c r="E146" s="123"/>
-      <c r="F146" s="123"/>
-      <c r="G146" s="124"/>
-      <c r="H146" s="104"/>
-      <c r="I146" s="110"/>
+      <c r="E146" s="185"/>
+      <c r="F146" s="185"/>
+      <c r="G146" s="186"/>
+      <c r="H146" s="107"/>
+      <c r="I146" s="143"/>
       <c r="J146" s="62"/>
       <c r="K146" s="20"/>
       <c r="L146" s="20"/>
@@ -20775,15 +20789,15 @@
       <c r="B147" s="36"/>
       <c r="C147" s="72"/>
       <c r="D147" s="70"/>
-      <c r="E147" s="121" t="s">
+      <c r="E147" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="F147" s="121"/>
-      <c r="G147" s="122"/>
-      <c r="H147" s="103">
+      <c r="F147" s="115"/>
+      <c r="G147" s="116"/>
+      <c r="H147" s="111">
         <v>45642</v>
       </c>
-      <c r="I147" s="109"/>
+      <c r="I147" s="113"/>
       <c r="J147" s="62"/>
       <c r="K147" s="20"/>
       <c r="L147" s="20"/>
@@ -20901,11 +20915,11 @@
       <c r="B148" s="36"/>
       <c r="C148" s="72"/>
       <c r="D148" s="70"/>
-      <c r="E148" s="123"/>
-      <c r="F148" s="123"/>
-      <c r="G148" s="124"/>
-      <c r="H148" s="104"/>
-      <c r="I148" s="110"/>
+      <c r="E148" s="185"/>
+      <c r="F148" s="185"/>
+      <c r="G148" s="186"/>
+      <c r="H148" s="107"/>
+      <c r="I148" s="143"/>
       <c r="J148" s="62"/>
       <c r="K148" s="20"/>
       <c r="L148" s="20"/>
@@ -21023,15 +21037,15 @@
       <c r="B149" s="36"/>
       <c r="C149" s="72"/>
       <c r="D149" s="70"/>
-      <c r="E149" s="121" t="s">
+      <c r="E149" s="115" t="s">
         <v>70</v>
       </c>
-      <c r="F149" s="121"/>
-      <c r="G149" s="122"/>
-      <c r="H149" s="103">
+      <c r="F149" s="115"/>
+      <c r="G149" s="116"/>
+      <c r="H149" s="111">
         <v>45643</v>
       </c>
-      <c r="I149" s="109"/>
+      <c r="I149" s="113"/>
       <c r="J149" s="62"/>
       <c r="K149" s="20"/>
       <c r="L149" s="20"/>
@@ -21149,11 +21163,11 @@
       <c r="B150" s="36"/>
       <c r="C150" s="72"/>
       <c r="D150" s="70"/>
-      <c r="E150" s="123"/>
-      <c r="F150" s="123"/>
-      <c r="G150" s="124"/>
-      <c r="H150" s="104"/>
-      <c r="I150" s="110"/>
+      <c r="E150" s="185"/>
+      <c r="F150" s="185"/>
+      <c r="G150" s="186"/>
+      <c r="H150" s="107"/>
+      <c r="I150" s="143"/>
       <c r="J150" s="62"/>
       <c r="K150" s="20"/>
       <c r="L150" s="20"/>
@@ -21271,15 +21285,15 @@
       <c r="B151" s="36"/>
       <c r="C151" s="72"/>
       <c r="D151" s="70"/>
-      <c r="E151" s="102" t="s">
+      <c r="E151" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="F151" s="102"/>
-      <c r="G151" s="102"/>
-      <c r="H151" s="103">
+      <c r="F151" s="103"/>
+      <c r="G151" s="103"/>
+      <c r="H151" s="111">
         <v>45644</v>
       </c>
-      <c r="I151" s="109"/>
+      <c r="I151" s="113"/>
       <c r="J151" s="62"/>
       <c r="K151" s="20"/>
       <c r="L151" s="20"/>
@@ -21397,11 +21411,11 @@
       <c r="B152" s="36"/>
       <c r="C152" s="72"/>
       <c r="D152" s="70"/>
-      <c r="E152" s="102"/>
-      <c r="F152" s="102"/>
-      <c r="G152" s="102"/>
-      <c r="H152" s="104"/>
-      <c r="I152" s="110"/>
+      <c r="E152" s="103"/>
+      <c r="F152" s="103"/>
+      <c r="G152" s="103"/>
+      <c r="H152" s="107"/>
+      <c r="I152" s="143"/>
       <c r="J152" s="62"/>
       <c r="K152" s="20"/>
       <c r="L152" s="20"/>
@@ -21519,15 +21533,15 @@
       <c r="B153" s="36"/>
       <c r="C153" s="72"/>
       <c r="D153" s="70"/>
-      <c r="E153" s="102" t="s">
+      <c r="E153" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="F153" s="102"/>
-      <c r="G153" s="102"/>
-      <c r="H153" s="103">
+      <c r="F153" s="103"/>
+      <c r="G153" s="103"/>
+      <c r="H153" s="111">
         <v>45644</v>
       </c>
-      <c r="I153" s="109"/>
+      <c r="I153" s="113"/>
       <c r="J153" s="62"/>
       <c r="K153" s="20"/>
       <c r="L153" s="20"/>
@@ -21645,11 +21659,11 @@
       <c r="B154" s="36"/>
       <c r="C154" s="72"/>
       <c r="D154" s="70"/>
-      <c r="E154" s="102"/>
-      <c r="F154" s="102"/>
-      <c r="G154" s="102"/>
-      <c r="H154" s="104"/>
-      <c r="I154" s="110"/>
+      <c r="E154" s="103"/>
+      <c r="F154" s="103"/>
+      <c r="G154" s="103"/>
+      <c r="H154" s="107"/>
+      <c r="I154" s="143"/>
       <c r="J154" s="62"/>
       <c r="K154" s="20"/>
       <c r="L154" s="20"/>
@@ -21766,16 +21780,16 @@
       <c r="A155" s="1"/>
       <c r="B155" s="18"/>
       <c r="C155" s="60"/>
-      <c r="D155" s="194"/>
-      <c r="E155" s="193" t="s">
+      <c r="D155" s="104"/>
+      <c r="E155" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="F155" s="102"/>
-      <c r="G155" s="102"/>
-      <c r="H155" s="195">
+      <c r="F155" s="103"/>
+      <c r="G155" s="103"/>
+      <c r="H155" s="106">
         <v>45645</v>
       </c>
-      <c r="I155" s="196"/>
+      <c r="I155" s="108"/>
       <c r="J155" s="19"/>
       <c r="K155" s="20"/>
       <c r="L155" s="20"/>
@@ -21892,12 +21906,12 @@
       <c r="A156" s="1"/>
       <c r="B156" s="18"/>
       <c r="C156" s="60"/>
-      <c r="D156" s="149"/>
-      <c r="E156" s="193"/>
-      <c r="F156" s="102"/>
-      <c r="G156" s="102"/>
-      <c r="H156" s="104"/>
-      <c r="I156" s="106"/>
+      <c r="D156" s="105"/>
+      <c r="E156" s="102"/>
+      <c r="F156" s="103"/>
+      <c r="G156" s="103"/>
+      <c r="H156" s="107"/>
+      <c r="I156" s="109"/>
       <c r="J156" s="19"/>
       <c r="K156" s="20"/>
       <c r="L156" s="20"/>
@@ -22014,16 +22028,16 @@
       <c r="A157" s="1"/>
       <c r="B157" s="93"/>
       <c r="C157" s="90"/>
-      <c r="D157" s="102" t="s">
+      <c r="D157" s="103" t="s">
         <v>81</v>
       </c>
-      <c r="E157" s="102"/>
-      <c r="F157" s="102"/>
-      <c r="G157" s="102"/>
-      <c r="H157" s="103">
+      <c r="E157" s="103"/>
+      <c r="F157" s="103"/>
+      <c r="G157" s="103"/>
+      <c r="H157" s="111">
         <v>45644</v>
       </c>
-      <c r="I157" s="105"/>
+      <c r="I157" s="126"/>
       <c r="J157" s="19"/>
       <c r="K157" s="20"/>
       <c r="L157" s="20"/>
@@ -22140,12 +22154,12 @@
       <c r="A158" s="1"/>
       <c r="B158" s="93"/>
       <c r="C158" s="90"/>
-      <c r="D158" s="102"/>
-      <c r="E158" s="102"/>
-      <c r="F158" s="102"/>
-      <c r="G158" s="102"/>
-      <c r="H158" s="104"/>
-      <c r="I158" s="106"/>
+      <c r="D158" s="103"/>
+      <c r="E158" s="103"/>
+      <c r="F158" s="103"/>
+      <c r="G158" s="103"/>
+      <c r="H158" s="107"/>
+      <c r="I158" s="109"/>
       <c r="J158" s="19"/>
       <c r="K158" s="20"/>
       <c r="L158" s="20"/>
@@ -22263,14 +22277,14 @@
       <c r="B159" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="C159" s="173" t="s">
+      <c r="C159" s="151" t="s">
         <v>31</v>
       </c>
-      <c r="D159" s="174"/>
-      <c r="E159" s="174"/>
-      <c r="F159" s="174"/>
-      <c r="G159" s="175"/>
-      <c r="H159" s="184" t="s">
+      <c r="D159" s="152"/>
+      <c r="E159" s="152"/>
+      <c r="F159" s="152"/>
+      <c r="G159" s="153"/>
+      <c r="H159" s="138" t="s">
         <v>57</v>
       </c>
       <c r="I159" s="112"/>
@@ -22389,11 +22403,11 @@
     <row r="160" spans="1:120" ht="9.75" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="87"/>
-      <c r="C160" s="176"/>
-      <c r="D160" s="177"/>
-      <c r="E160" s="177"/>
-      <c r="F160" s="177"/>
-      <c r="G160" s="178"/>
+      <c r="C160" s="154"/>
+      <c r="D160" s="155"/>
+      <c r="E160" s="155"/>
+      <c r="F160" s="155"/>
+      <c r="G160" s="156"/>
       <c r="H160" s="112"/>
       <c r="I160" s="112"/>
       <c r="J160" s="14"/>
@@ -22755,14 +22769,14 @@
     <row r="163" spans="1:120" ht="9.75" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
-      <c r="C163" s="168" t="s">
+      <c r="C163" s="145" t="s">
         <v>33</v>
       </c>
-      <c r="D163" s="140"/>
-      <c r="E163" s="140"/>
-      <c r="F163" s="140"/>
-      <c r="G163" s="169"/>
-      <c r="H163" s="184" t="s">
+      <c r="D163" s="146"/>
+      <c r="E163" s="146"/>
+      <c r="F163" s="146"/>
+      <c r="G163" s="147"/>
+      <c r="H163" s="138" t="s">
         <v>56</v>
       </c>
       <c r="I163" s="112"/>
@@ -22881,11 +22895,11 @@
     <row r="164" spans="1:120" ht="9.75" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
-      <c r="C164" s="170"/>
-      <c r="D164" s="171"/>
-      <c r="E164" s="171"/>
-      <c r="F164" s="171"/>
-      <c r="G164" s="172"/>
+      <c r="C164" s="148"/>
+      <c r="D164" s="149"/>
+      <c r="E164" s="149"/>
+      <c r="F164" s="149"/>
+      <c r="G164" s="150"/>
       <c r="H164" s="112"/>
       <c r="I164" s="112"/>
       <c r="J164" s="19"/>
@@ -36426,6 +36440,222 @@
     </row>
   </sheetData>
   <mergeCells count="240">
+    <mergeCell ref="D157:G158"/>
+    <mergeCell ref="H157:H158"/>
+    <mergeCell ref="I157:I158"/>
+    <mergeCell ref="H141:H142"/>
+    <mergeCell ref="I143:I144"/>
+    <mergeCell ref="I139:I140"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="H103:H104"/>
+    <mergeCell ref="I103:I104"/>
+    <mergeCell ref="H115:H116"/>
+    <mergeCell ref="I115:I116"/>
+    <mergeCell ref="D103:G104"/>
+    <mergeCell ref="D115:G116"/>
+    <mergeCell ref="D131:G132"/>
+    <mergeCell ref="H131:H132"/>
+    <mergeCell ref="I131:I132"/>
+    <mergeCell ref="D87:G88"/>
+    <mergeCell ref="D141:G142"/>
+    <mergeCell ref="E153:G154"/>
+    <mergeCell ref="H153:H154"/>
+    <mergeCell ref="H151:H152"/>
+    <mergeCell ref="H149:H150"/>
+    <mergeCell ref="H147:H148"/>
+    <mergeCell ref="H145:H146"/>
+    <mergeCell ref="H143:H144"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="C133:G134"/>
+    <mergeCell ref="D135:G136"/>
+    <mergeCell ref="E137:G138"/>
+    <mergeCell ref="E139:G140"/>
+    <mergeCell ref="D143:G144"/>
+    <mergeCell ref="E145:G146"/>
+    <mergeCell ref="H135:H136"/>
+    <mergeCell ref="E147:G148"/>
+    <mergeCell ref="E149:G150"/>
+    <mergeCell ref="E151:G152"/>
+    <mergeCell ref="E59:G60"/>
+    <mergeCell ref="E61:G62"/>
+    <mergeCell ref="D63:G64"/>
+    <mergeCell ref="E67:G68"/>
+    <mergeCell ref="E65:G66"/>
+    <mergeCell ref="E69:G70"/>
+    <mergeCell ref="E71:G72"/>
+    <mergeCell ref="C73:G74"/>
+    <mergeCell ref="C75:G76"/>
+    <mergeCell ref="C77:G78"/>
+    <mergeCell ref="D79:G80"/>
+    <mergeCell ref="E109:G110"/>
+    <mergeCell ref="E111:G112"/>
+    <mergeCell ref="E101:G102"/>
+    <mergeCell ref="C105:G106"/>
+    <mergeCell ref="D107:G108"/>
+    <mergeCell ref="D117:G118"/>
+    <mergeCell ref="D13:G14"/>
+    <mergeCell ref="D15:G16"/>
+    <mergeCell ref="D17:G18"/>
+    <mergeCell ref="D19:G20"/>
+    <mergeCell ref="C21:G22"/>
+    <mergeCell ref="D23:G24"/>
+    <mergeCell ref="C25:G26"/>
+    <mergeCell ref="D27:G28"/>
+    <mergeCell ref="D29:G30"/>
+    <mergeCell ref="J3:CJ3"/>
+    <mergeCell ref="CK3:DO3"/>
+    <mergeCell ref="J4:AA4"/>
+    <mergeCell ref="AB4:BE4"/>
+    <mergeCell ref="BF4:CJ4"/>
+    <mergeCell ref="CK4:DO4"/>
+    <mergeCell ref="B7:G8"/>
+    <mergeCell ref="C9:G10"/>
+    <mergeCell ref="C11:G12"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="C163:G164"/>
+    <mergeCell ref="C159:G160"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="C31:G32"/>
+    <mergeCell ref="D33:G34"/>
+    <mergeCell ref="E35:G36"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="E43:G44"/>
+    <mergeCell ref="E45:G46"/>
+    <mergeCell ref="E47:G48"/>
+    <mergeCell ref="E49:G50"/>
+    <mergeCell ref="E51:G52"/>
+    <mergeCell ref="D53:G54"/>
+    <mergeCell ref="E55:G56"/>
+    <mergeCell ref="E57:G58"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I67:I68"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="I159:I160"/>
+    <mergeCell ref="I161:I162"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="I93:I94"/>
+    <mergeCell ref="I95:I96"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="I109:I110"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="I153:I154"/>
+    <mergeCell ref="I151:I152"/>
+    <mergeCell ref="I149:I150"/>
+    <mergeCell ref="I147:I148"/>
+    <mergeCell ref="I145:I146"/>
+    <mergeCell ref="I111:I112"/>
+    <mergeCell ref="I135:I136"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="I163:I164"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="H75:H76"/>
+    <mergeCell ref="H159:H160"/>
+    <mergeCell ref="H163:H164"/>
+    <mergeCell ref="H161:H162"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="H59:H60"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="H77:H78"/>
+    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="H93:H94"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="H111:H112"/>
+    <mergeCell ref="H101:H102"/>
+    <mergeCell ref="I101:I102"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="I85:I86"/>
+    <mergeCell ref="H89:H90"/>
+    <mergeCell ref="I89:I90"/>
+    <mergeCell ref="E81:G82"/>
+    <mergeCell ref="E83:G84"/>
+    <mergeCell ref="E91:G92"/>
+    <mergeCell ref="E93:G94"/>
+    <mergeCell ref="E95:G96"/>
+    <mergeCell ref="E97:G98"/>
+    <mergeCell ref="E99:G100"/>
+    <mergeCell ref="E85:G86"/>
+    <mergeCell ref="D89:G90"/>
+    <mergeCell ref="H105:H106"/>
+    <mergeCell ref="I105:I106"/>
+    <mergeCell ref="H107:H108"/>
+    <mergeCell ref="I107:I108"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="H117:H118"/>
+    <mergeCell ref="I117:I118"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="I119:I120"/>
     <mergeCell ref="E155:G156"/>
     <mergeCell ref="D155:D156"/>
     <mergeCell ref="H155:H156"/>
@@ -36450,222 +36680,6 @@
     <mergeCell ref="H127:H128"/>
     <mergeCell ref="I127:I128"/>
     <mergeCell ref="H121:H122"/>
-    <mergeCell ref="H105:H106"/>
-    <mergeCell ref="I105:I106"/>
-    <mergeCell ref="H107:H108"/>
-    <mergeCell ref="I107:I108"/>
-    <mergeCell ref="H109:H110"/>
-    <mergeCell ref="H117:H118"/>
-    <mergeCell ref="I117:I118"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="I119:I120"/>
-    <mergeCell ref="H101:H102"/>
-    <mergeCell ref="I101:I102"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="I85:I86"/>
-    <mergeCell ref="H89:H90"/>
-    <mergeCell ref="I89:I90"/>
-    <mergeCell ref="E81:G82"/>
-    <mergeCell ref="E83:G84"/>
-    <mergeCell ref="E91:G92"/>
-    <mergeCell ref="E93:G94"/>
-    <mergeCell ref="E95:G96"/>
-    <mergeCell ref="E97:G98"/>
-    <mergeCell ref="E99:G100"/>
-    <mergeCell ref="E85:G86"/>
-    <mergeCell ref="D89:G90"/>
-    <mergeCell ref="H75:H76"/>
-    <mergeCell ref="H159:H160"/>
-    <mergeCell ref="H163:H164"/>
-    <mergeCell ref="H161:H162"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="H67:H68"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H59:H60"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="H77:H78"/>
-    <mergeCell ref="H81:H82"/>
-    <mergeCell ref="H83:H84"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="H93:H94"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="H111:H112"/>
-    <mergeCell ref="I163:I164"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="I159:I160"/>
-    <mergeCell ref="I161:I162"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="I93:I94"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="I109:I110"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="I153:I154"/>
-    <mergeCell ref="I151:I152"/>
-    <mergeCell ref="I149:I150"/>
-    <mergeCell ref="I147:I148"/>
-    <mergeCell ref="I145:I146"/>
-    <mergeCell ref="I111:I112"/>
-    <mergeCell ref="I135:I136"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="C163:G164"/>
-    <mergeCell ref="C159:G160"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="C31:G32"/>
-    <mergeCell ref="D33:G34"/>
-    <mergeCell ref="E35:G36"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="E43:G44"/>
-    <mergeCell ref="E45:G46"/>
-    <mergeCell ref="E47:G48"/>
-    <mergeCell ref="E49:G50"/>
-    <mergeCell ref="E51:G52"/>
-    <mergeCell ref="D53:G54"/>
-    <mergeCell ref="E55:G56"/>
-    <mergeCell ref="E57:G58"/>
-    <mergeCell ref="I53:I54"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="J3:CJ3"/>
-    <mergeCell ref="CK3:DO3"/>
-    <mergeCell ref="J4:AA4"/>
-    <mergeCell ref="AB4:BE4"/>
-    <mergeCell ref="BF4:CJ4"/>
-    <mergeCell ref="CK4:DO4"/>
-    <mergeCell ref="B7:G8"/>
-    <mergeCell ref="C9:G10"/>
-    <mergeCell ref="C11:G12"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="D13:G14"/>
-    <mergeCell ref="D15:G16"/>
-    <mergeCell ref="D17:G18"/>
-    <mergeCell ref="D19:G20"/>
-    <mergeCell ref="C21:G22"/>
-    <mergeCell ref="D23:G24"/>
-    <mergeCell ref="C25:G26"/>
-    <mergeCell ref="D27:G28"/>
-    <mergeCell ref="D29:G30"/>
-    <mergeCell ref="E147:G148"/>
-    <mergeCell ref="E149:G150"/>
-    <mergeCell ref="E151:G152"/>
-    <mergeCell ref="E59:G60"/>
-    <mergeCell ref="E61:G62"/>
-    <mergeCell ref="D63:G64"/>
-    <mergeCell ref="E67:G68"/>
-    <mergeCell ref="E65:G66"/>
-    <mergeCell ref="E69:G70"/>
-    <mergeCell ref="E71:G72"/>
-    <mergeCell ref="C73:G74"/>
-    <mergeCell ref="C75:G76"/>
-    <mergeCell ref="C77:G78"/>
-    <mergeCell ref="D79:G80"/>
-    <mergeCell ref="E109:G110"/>
-    <mergeCell ref="E111:G112"/>
-    <mergeCell ref="E101:G102"/>
-    <mergeCell ref="C105:G106"/>
-    <mergeCell ref="D107:G108"/>
-    <mergeCell ref="D117:G118"/>
-    <mergeCell ref="H145:H146"/>
-    <mergeCell ref="H143:H144"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="C133:G134"/>
-    <mergeCell ref="D135:G136"/>
-    <mergeCell ref="E137:G138"/>
-    <mergeCell ref="E139:G140"/>
-    <mergeCell ref="D143:G144"/>
-    <mergeCell ref="E145:G146"/>
-    <mergeCell ref="H135:H136"/>
-    <mergeCell ref="D157:G158"/>
-    <mergeCell ref="H157:H158"/>
-    <mergeCell ref="I157:I158"/>
-    <mergeCell ref="H141:H142"/>
-    <mergeCell ref="I143:I144"/>
-    <mergeCell ref="I139:I140"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="H103:H104"/>
-    <mergeCell ref="I103:I104"/>
-    <mergeCell ref="H115:H116"/>
-    <mergeCell ref="I115:I116"/>
-    <mergeCell ref="D103:G104"/>
-    <mergeCell ref="D115:G116"/>
-    <mergeCell ref="D131:G132"/>
-    <mergeCell ref="H131:H132"/>
-    <mergeCell ref="I131:I132"/>
-    <mergeCell ref="D87:G88"/>
-    <mergeCell ref="D141:G142"/>
-    <mergeCell ref="E153:G154"/>
-    <mergeCell ref="H153:H154"/>
-    <mergeCell ref="H151:H152"/>
-    <mergeCell ref="H149:H150"/>
-    <mergeCell ref="H147:H148"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <conditionalFormatting sqref="J7">

--- a/docs/【DIGITAL OJT】WBS.xlsx
+++ b/docs/【DIGITAL OJT】WBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIGITALOJT\digital-ojt-development-cause-DroneInventorySystem\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E92C0A-DA75-4357-BE19-DE0D56F102A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3DAEDE-6918-4F8F-9EE2-0D66A91A7FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12096" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -1489,67 +1489,19 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1558,25 +1510,22 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1597,29 +1546,110 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1645,92 +1675,62 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2350,120 +2350,120 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="J3" s="173">
+      <c r="J3" s="161">
         <v>2024</v>
       </c>
-      <c r="K3" s="174"/>
-      <c r="L3" s="174"/>
-      <c r="M3" s="174"/>
-      <c r="N3" s="174"/>
-      <c r="O3" s="174"/>
-      <c r="P3" s="174"/>
-      <c r="Q3" s="174"/>
-      <c r="R3" s="174"/>
-      <c r="S3" s="174"/>
-      <c r="T3" s="174"/>
-      <c r="U3" s="174"/>
-      <c r="V3" s="174"/>
-      <c r="W3" s="174"/>
-      <c r="X3" s="174"/>
-      <c r="Y3" s="174"/>
-      <c r="Z3" s="174"/>
-      <c r="AA3" s="174"/>
-      <c r="AB3" s="174"/>
-      <c r="AC3" s="174"/>
-      <c r="AD3" s="174"/>
-      <c r="AE3" s="174"/>
-      <c r="AF3" s="174"/>
-      <c r="AG3" s="174"/>
-      <c r="AH3" s="174"/>
-      <c r="AI3" s="174"/>
-      <c r="AJ3" s="174"/>
-      <c r="AK3" s="174"/>
-      <c r="AL3" s="174"/>
-      <c r="AM3" s="174"/>
-      <c r="AN3" s="174"/>
-      <c r="AO3" s="174"/>
-      <c r="AP3" s="174"/>
-      <c r="AQ3" s="174"/>
-      <c r="AR3" s="174"/>
-      <c r="AS3" s="174"/>
-      <c r="AT3" s="174"/>
-      <c r="AU3" s="174"/>
-      <c r="AV3" s="174"/>
-      <c r="AW3" s="174"/>
-      <c r="AX3" s="174"/>
-      <c r="AY3" s="174"/>
-      <c r="AZ3" s="174"/>
-      <c r="BA3" s="174"/>
-      <c r="BB3" s="174"/>
-      <c r="BC3" s="174"/>
-      <c r="BD3" s="174"/>
-      <c r="BE3" s="174"/>
-      <c r="BF3" s="174"/>
-      <c r="BG3" s="174"/>
-      <c r="BH3" s="174"/>
-      <c r="BI3" s="174"/>
-      <c r="BJ3" s="174"/>
-      <c r="BK3" s="174"/>
-      <c r="BL3" s="174"/>
-      <c r="BM3" s="174"/>
-      <c r="BN3" s="174"/>
-      <c r="BO3" s="174"/>
-      <c r="BP3" s="174"/>
-      <c r="BQ3" s="174"/>
-      <c r="BR3" s="174"/>
-      <c r="BS3" s="174"/>
-      <c r="BT3" s="174"/>
-      <c r="BU3" s="174"/>
-      <c r="BV3" s="174"/>
-      <c r="BW3" s="174"/>
-      <c r="BX3" s="174"/>
-      <c r="BY3" s="174"/>
-      <c r="BZ3" s="174"/>
-      <c r="CA3" s="174"/>
-      <c r="CB3" s="174"/>
-      <c r="CC3" s="174"/>
-      <c r="CD3" s="174"/>
-      <c r="CE3" s="174"/>
-      <c r="CF3" s="174"/>
-      <c r="CG3" s="174"/>
-      <c r="CH3" s="174"/>
-      <c r="CI3" s="174"/>
-      <c r="CJ3" s="175"/>
-      <c r="CK3" s="173">
+      <c r="K3" s="162"/>
+      <c r="L3" s="162"/>
+      <c r="M3" s="162"/>
+      <c r="N3" s="162"/>
+      <c r="O3" s="162"/>
+      <c r="P3" s="162"/>
+      <c r="Q3" s="162"/>
+      <c r="R3" s="162"/>
+      <c r="S3" s="162"/>
+      <c r="T3" s="162"/>
+      <c r="U3" s="162"/>
+      <c r="V3" s="162"/>
+      <c r="W3" s="162"/>
+      <c r="X3" s="162"/>
+      <c r="Y3" s="162"/>
+      <c r="Z3" s="162"/>
+      <c r="AA3" s="162"/>
+      <c r="AB3" s="162"/>
+      <c r="AC3" s="162"/>
+      <c r="AD3" s="162"/>
+      <c r="AE3" s="162"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="162"/>
+      <c r="AH3" s="162"/>
+      <c r="AI3" s="162"/>
+      <c r="AJ3" s="162"/>
+      <c r="AK3" s="162"/>
+      <c r="AL3" s="162"/>
+      <c r="AM3" s="162"/>
+      <c r="AN3" s="162"/>
+      <c r="AO3" s="162"/>
+      <c r="AP3" s="162"/>
+      <c r="AQ3" s="162"/>
+      <c r="AR3" s="162"/>
+      <c r="AS3" s="162"/>
+      <c r="AT3" s="162"/>
+      <c r="AU3" s="162"/>
+      <c r="AV3" s="162"/>
+      <c r="AW3" s="162"/>
+      <c r="AX3" s="162"/>
+      <c r="AY3" s="162"/>
+      <c r="AZ3" s="162"/>
+      <c r="BA3" s="162"/>
+      <c r="BB3" s="162"/>
+      <c r="BC3" s="162"/>
+      <c r="BD3" s="162"/>
+      <c r="BE3" s="162"/>
+      <c r="BF3" s="162"/>
+      <c r="BG3" s="162"/>
+      <c r="BH3" s="162"/>
+      <c r="BI3" s="162"/>
+      <c r="BJ3" s="162"/>
+      <c r="BK3" s="162"/>
+      <c r="BL3" s="162"/>
+      <c r="BM3" s="162"/>
+      <c r="BN3" s="162"/>
+      <c r="BO3" s="162"/>
+      <c r="BP3" s="162"/>
+      <c r="BQ3" s="162"/>
+      <c r="BR3" s="162"/>
+      <c r="BS3" s="162"/>
+      <c r="BT3" s="162"/>
+      <c r="BU3" s="162"/>
+      <c r="BV3" s="162"/>
+      <c r="BW3" s="162"/>
+      <c r="BX3" s="162"/>
+      <c r="BY3" s="162"/>
+      <c r="BZ3" s="162"/>
+      <c r="CA3" s="162"/>
+      <c r="CB3" s="162"/>
+      <c r="CC3" s="162"/>
+      <c r="CD3" s="162"/>
+      <c r="CE3" s="162"/>
+      <c r="CF3" s="162"/>
+      <c r="CG3" s="162"/>
+      <c r="CH3" s="162"/>
+      <c r="CI3" s="162"/>
+      <c r="CJ3" s="163"/>
+      <c r="CK3" s="161">
         <v>2025</v>
       </c>
-      <c r="CL3" s="174"/>
-      <c r="CM3" s="174"/>
-      <c r="CN3" s="174"/>
-      <c r="CO3" s="174"/>
-      <c r="CP3" s="174"/>
-      <c r="CQ3" s="174"/>
-      <c r="CR3" s="174"/>
-      <c r="CS3" s="174"/>
-      <c r="CT3" s="174"/>
-      <c r="CU3" s="174"/>
-      <c r="CV3" s="174"/>
-      <c r="CW3" s="174"/>
-      <c r="CX3" s="174"/>
-      <c r="CY3" s="174"/>
-      <c r="CZ3" s="174"/>
-      <c r="DA3" s="174"/>
-      <c r="DB3" s="174"/>
-      <c r="DC3" s="174"/>
-      <c r="DD3" s="174"/>
-      <c r="DE3" s="174"/>
-      <c r="DF3" s="174"/>
-      <c r="DG3" s="174"/>
-      <c r="DH3" s="174"/>
-      <c r="DI3" s="174"/>
-      <c r="DJ3" s="174"/>
-      <c r="DK3" s="174"/>
-      <c r="DL3" s="174"/>
-      <c r="DM3" s="174"/>
-      <c r="DN3" s="174"/>
-      <c r="DO3" s="175"/>
+      <c r="CL3" s="162"/>
+      <c r="CM3" s="162"/>
+      <c r="CN3" s="162"/>
+      <c r="CO3" s="162"/>
+      <c r="CP3" s="162"/>
+      <c r="CQ3" s="162"/>
+      <c r="CR3" s="162"/>
+      <c r="CS3" s="162"/>
+      <c r="CT3" s="162"/>
+      <c r="CU3" s="162"/>
+      <c r="CV3" s="162"/>
+      <c r="CW3" s="162"/>
+      <c r="CX3" s="162"/>
+      <c r="CY3" s="162"/>
+      <c r="CZ3" s="162"/>
+      <c r="DA3" s="162"/>
+      <c r="DB3" s="162"/>
+      <c r="DC3" s="162"/>
+      <c r="DD3" s="162"/>
+      <c r="DE3" s="162"/>
+      <c r="DF3" s="162"/>
+      <c r="DG3" s="162"/>
+      <c r="DH3" s="162"/>
+      <c r="DI3" s="162"/>
+      <c r="DJ3" s="162"/>
+      <c r="DK3" s="162"/>
+      <c r="DL3" s="162"/>
+      <c r="DM3" s="162"/>
+      <c r="DN3" s="162"/>
+      <c r="DO3" s="163"/>
       <c r="DP3" s="1"/>
     </row>
     <row r="4" spans="1:120" ht="18" customHeight="1">
@@ -2478,124 +2478,124 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="J4" s="173">
+      <c r="J4" s="161">
         <v>10</v>
       </c>
-      <c r="K4" s="174"/>
-      <c r="L4" s="174"/>
-      <c r="M4" s="174"/>
-      <c r="N4" s="174"/>
-      <c r="O4" s="174"/>
-      <c r="P4" s="174"/>
-      <c r="Q4" s="174"/>
-      <c r="R4" s="174"/>
-      <c r="S4" s="174"/>
-      <c r="T4" s="174"/>
-      <c r="U4" s="174"/>
-      <c r="V4" s="174"/>
-      <c r="W4" s="174"/>
-      <c r="X4" s="174"/>
-      <c r="Y4" s="174"/>
-      <c r="Z4" s="174"/>
-      <c r="AA4" s="175"/>
-      <c r="AB4" s="173">
+      <c r="K4" s="162"/>
+      <c r="L4" s="162"/>
+      <c r="M4" s="162"/>
+      <c r="N4" s="162"/>
+      <c r="O4" s="162"/>
+      <c r="P4" s="162"/>
+      <c r="Q4" s="162"/>
+      <c r="R4" s="162"/>
+      <c r="S4" s="162"/>
+      <c r="T4" s="162"/>
+      <c r="U4" s="162"/>
+      <c r="V4" s="162"/>
+      <c r="W4" s="162"/>
+      <c r="X4" s="162"/>
+      <c r="Y4" s="162"/>
+      <c r="Z4" s="162"/>
+      <c r="AA4" s="163"/>
+      <c r="AB4" s="161">
         <v>11</v>
       </c>
-      <c r="AC4" s="174"/>
-      <c r="AD4" s="174"/>
-      <c r="AE4" s="174"/>
-      <c r="AF4" s="174"/>
-      <c r="AG4" s="174"/>
-      <c r="AH4" s="174"/>
-      <c r="AI4" s="174"/>
-      <c r="AJ4" s="174"/>
-      <c r="AK4" s="174"/>
-      <c r="AL4" s="174"/>
-      <c r="AM4" s="174"/>
-      <c r="AN4" s="174"/>
-      <c r="AO4" s="174"/>
-      <c r="AP4" s="174"/>
-      <c r="AQ4" s="174"/>
-      <c r="AR4" s="174"/>
-      <c r="AS4" s="174"/>
-      <c r="AT4" s="174"/>
-      <c r="AU4" s="174"/>
-      <c r="AV4" s="174"/>
-      <c r="AW4" s="174"/>
-      <c r="AX4" s="174"/>
-      <c r="AY4" s="174"/>
-      <c r="AZ4" s="174"/>
-      <c r="BA4" s="174"/>
-      <c r="BB4" s="174"/>
-      <c r="BC4" s="174"/>
-      <c r="BD4" s="174"/>
-      <c r="BE4" s="175"/>
-      <c r="BF4" s="173">
+      <c r="AC4" s="162"/>
+      <c r="AD4" s="162"/>
+      <c r="AE4" s="162"/>
+      <c r="AF4" s="162"/>
+      <c r="AG4" s="162"/>
+      <c r="AH4" s="162"/>
+      <c r="AI4" s="162"/>
+      <c r="AJ4" s="162"/>
+      <c r="AK4" s="162"/>
+      <c r="AL4" s="162"/>
+      <c r="AM4" s="162"/>
+      <c r="AN4" s="162"/>
+      <c r="AO4" s="162"/>
+      <c r="AP4" s="162"/>
+      <c r="AQ4" s="162"/>
+      <c r="AR4" s="162"/>
+      <c r="AS4" s="162"/>
+      <c r="AT4" s="162"/>
+      <c r="AU4" s="162"/>
+      <c r="AV4" s="162"/>
+      <c r="AW4" s="162"/>
+      <c r="AX4" s="162"/>
+      <c r="AY4" s="162"/>
+      <c r="AZ4" s="162"/>
+      <c r="BA4" s="162"/>
+      <c r="BB4" s="162"/>
+      <c r="BC4" s="162"/>
+      <c r="BD4" s="162"/>
+      <c r="BE4" s="163"/>
+      <c r="BF4" s="161">
         <v>12</v>
       </c>
-      <c r="BG4" s="174"/>
-      <c r="BH4" s="174"/>
-      <c r="BI4" s="174"/>
-      <c r="BJ4" s="174"/>
-      <c r="BK4" s="174"/>
-      <c r="BL4" s="174"/>
-      <c r="BM4" s="174"/>
-      <c r="BN4" s="174"/>
-      <c r="BO4" s="174"/>
-      <c r="BP4" s="174"/>
-      <c r="BQ4" s="174"/>
-      <c r="BR4" s="174"/>
-      <c r="BS4" s="174"/>
-      <c r="BT4" s="174"/>
-      <c r="BU4" s="174"/>
-      <c r="BV4" s="174"/>
-      <c r="BW4" s="174"/>
-      <c r="BX4" s="174"/>
-      <c r="BY4" s="174"/>
-      <c r="BZ4" s="174"/>
-      <c r="CA4" s="174"/>
-      <c r="CB4" s="174"/>
-      <c r="CC4" s="174"/>
-      <c r="CD4" s="174"/>
-      <c r="CE4" s="174"/>
-      <c r="CF4" s="174"/>
-      <c r="CG4" s="174"/>
-      <c r="CH4" s="174"/>
-      <c r="CI4" s="174"/>
-      <c r="CJ4" s="175"/>
-      <c r="CK4" s="173">
+      <c r="BG4" s="162"/>
+      <c r="BH4" s="162"/>
+      <c r="BI4" s="162"/>
+      <c r="BJ4" s="162"/>
+      <c r="BK4" s="162"/>
+      <c r="BL4" s="162"/>
+      <c r="BM4" s="162"/>
+      <c r="BN4" s="162"/>
+      <c r="BO4" s="162"/>
+      <c r="BP4" s="162"/>
+      <c r="BQ4" s="162"/>
+      <c r="BR4" s="162"/>
+      <c r="BS4" s="162"/>
+      <c r="BT4" s="162"/>
+      <c r="BU4" s="162"/>
+      <c r="BV4" s="162"/>
+      <c r="BW4" s="162"/>
+      <c r="BX4" s="162"/>
+      <c r="BY4" s="162"/>
+      <c r="BZ4" s="162"/>
+      <c r="CA4" s="162"/>
+      <c r="CB4" s="162"/>
+      <c r="CC4" s="162"/>
+      <c r="CD4" s="162"/>
+      <c r="CE4" s="162"/>
+      <c r="CF4" s="162"/>
+      <c r="CG4" s="162"/>
+      <c r="CH4" s="162"/>
+      <c r="CI4" s="162"/>
+      <c r="CJ4" s="163"/>
+      <c r="CK4" s="161">
         <v>1</v>
       </c>
-      <c r="CL4" s="174"/>
-      <c r="CM4" s="174"/>
-      <c r="CN4" s="174"/>
-      <c r="CO4" s="174"/>
-      <c r="CP4" s="174"/>
-      <c r="CQ4" s="174"/>
-      <c r="CR4" s="174"/>
-      <c r="CS4" s="174"/>
-      <c r="CT4" s="174"/>
-      <c r="CU4" s="174"/>
-      <c r="CV4" s="174"/>
-      <c r="CW4" s="174"/>
-      <c r="CX4" s="174"/>
-      <c r="CY4" s="174"/>
-      <c r="CZ4" s="174"/>
-      <c r="DA4" s="174"/>
-      <c r="DB4" s="174"/>
-      <c r="DC4" s="174"/>
-      <c r="DD4" s="174"/>
-      <c r="DE4" s="174"/>
-      <c r="DF4" s="174"/>
-      <c r="DG4" s="174"/>
-      <c r="DH4" s="174"/>
-      <c r="DI4" s="174"/>
-      <c r="DJ4" s="174"/>
-      <c r="DK4" s="174"/>
-      <c r="DL4" s="174"/>
-      <c r="DM4" s="174"/>
-      <c r="DN4" s="174"/>
-      <c r="DO4" s="175"/>
+      <c r="CL4" s="162"/>
+      <c r="CM4" s="162"/>
+      <c r="CN4" s="162"/>
+      <c r="CO4" s="162"/>
+      <c r="CP4" s="162"/>
+      <c r="CQ4" s="162"/>
+      <c r="CR4" s="162"/>
+      <c r="CS4" s="162"/>
+      <c r="CT4" s="162"/>
+      <c r="CU4" s="162"/>
+      <c r="CV4" s="162"/>
+      <c r="CW4" s="162"/>
+      <c r="CX4" s="162"/>
+      <c r="CY4" s="162"/>
+      <c r="CZ4" s="162"/>
+      <c r="DA4" s="162"/>
+      <c r="DB4" s="162"/>
+      <c r="DC4" s="162"/>
+      <c r="DD4" s="162"/>
+      <c r="DE4" s="162"/>
+      <c r="DF4" s="162"/>
+      <c r="DG4" s="162"/>
+      <c r="DH4" s="162"/>
+      <c r="DI4" s="162"/>
+      <c r="DJ4" s="162"/>
+      <c r="DK4" s="162"/>
+      <c r="DL4" s="162"/>
+      <c r="DM4" s="162"/>
+      <c r="DN4" s="162"/>
+      <c r="DO4" s="163"/>
       <c r="DP4" s="6"/>
     </row>
     <row r="5" spans="1:120" ht="18" customHeight="1">
@@ -3390,18 +3390,18 @@
     </row>
     <row r="7" spans="1:120" ht="9.75" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="176" t="s">
+      <c r="B7" s="164" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="164"/>
-      <c r="D7" s="164"/>
-      <c r="E7" s="164"/>
-      <c r="F7" s="164"/>
-      <c r="G7" s="177"/>
-      <c r="H7" s="142" t="s">
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="152"/>
+      <c r="H7" s="166" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="142" t="s">
+      <c r="I7" s="166" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="38"/>
@@ -3518,14 +3518,14 @@
     </row>
     <row r="8" spans="1:120" ht="9.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="166"/>
-      <c r="C8" s="167"/>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="168"/>
-      <c r="H8" s="142"/>
-      <c r="I8" s="142"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
+      <c r="G8" s="139"/>
+      <c r="H8" s="166"/>
+      <c r="I8" s="166"/>
       <c r="J8" s="39"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
@@ -3641,15 +3641,15 @@
     <row r="9" spans="1:120" ht="9.75" customHeight="1">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
-      <c r="C9" s="178" t="s">
+      <c r="C9" s="165" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="158"/>
-      <c r="E9" s="158"/>
-      <c r="F9" s="158"/>
-      <c r="G9" s="162"/>
-      <c r="H9" s="139"/>
-      <c r="I9" s="139"/>
+      <c r="D9" s="154"/>
+      <c r="E9" s="154"/>
+      <c r="F9" s="154"/>
+      <c r="G9" s="142"/>
+      <c r="H9" s="167"/>
+      <c r="I9" s="167"/>
       <c r="J9" s="42"/>
       <c r="K9" s="42"/>
       <c r="L9" s="44"/>
@@ -3765,13 +3765,13 @@
     <row r="10" spans="1:120" ht="9.75" customHeight="1">
       <c r="A10" s="16"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="179"/>
-      <c r="D10" s="167"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="167"/>
-      <c r="G10" s="168"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="139"/>
+      <c r="C10" s="141"/>
+      <c r="D10" s="135"/>
+      <c r="E10" s="135"/>
+      <c r="F10" s="135"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="167"/>
+      <c r="I10" s="167"/>
       <c r="J10" s="46"/>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
@@ -3887,15 +3887,15 @@
     <row r="11" spans="1:120" ht="9.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="180" t="s">
+      <c r="C11" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="158"/>
-      <c r="E11" s="158"/>
-      <c r="F11" s="158"/>
-      <c r="G11" s="162"/>
-      <c r="H11" s="139"/>
-      <c r="I11" s="139"/>
+      <c r="D11" s="154"/>
+      <c r="E11" s="154"/>
+      <c r="F11" s="154"/>
+      <c r="G11" s="142"/>
+      <c r="H11" s="167"/>
+      <c r="I11" s="167"/>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
       <c r="L11" s="44"/>
@@ -4011,13 +4011,13 @@
     <row r="12" spans="1:120" ht="9.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="179"/>
-      <c r="D12" s="167"/>
-      <c r="E12" s="167"/>
-      <c r="F12" s="167"/>
-      <c r="G12" s="168"/>
-      <c r="H12" s="139"/>
-      <c r="I12" s="139"/>
+      <c r="C12" s="141"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="135"/>
+      <c r="G12" s="139"/>
+      <c r="H12" s="167"/>
+      <c r="I12" s="167"/>
       <c r="J12" s="46"/>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
@@ -4134,13 +4134,13 @@
       <c r="A13" s="1"/>
       <c r="B13" s="18"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="181" t="s">
+      <c r="D13" s="151" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="164"/>
-      <c r="F13" s="164"/>
-      <c r="G13" s="177"/>
-      <c r="H13" s="138" t="s">
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="152"/>
+      <c r="H13" s="184" t="s">
         <v>40</v>
       </c>
       <c r="I13" s="112">
@@ -4262,10 +4262,10 @@
       <c r="A14" s="1"/>
       <c r="B14" s="18"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="166"/>
-      <c r="E14" s="167"/>
-      <c r="F14" s="167"/>
-      <c r="G14" s="168"/>
+      <c r="D14" s="134"/>
+      <c r="E14" s="135"/>
+      <c r="F14" s="135"/>
+      <c r="G14" s="139"/>
       <c r="H14" s="112"/>
       <c r="I14" s="112"/>
       <c r="J14" s="39"/>
@@ -4384,13 +4384,13 @@
       <c r="A15" s="1"/>
       <c r="B15" s="18"/>
       <c r="C15" s="24"/>
-      <c r="D15" s="181" t="s">
+      <c r="D15" s="151" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="164"/>
-      <c r="F15" s="164"/>
-      <c r="G15" s="170"/>
-      <c r="H15" s="138" t="s">
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="184" t="s">
         <v>40</v>
       </c>
       <c r="I15" s="112">
@@ -4512,10 +4512,10 @@
       <c r="A16" s="1"/>
       <c r="B16" s="18"/>
       <c r="C16" s="24"/>
-      <c r="D16" s="166"/>
-      <c r="E16" s="167"/>
-      <c r="F16" s="167"/>
-      <c r="G16" s="171"/>
+      <c r="D16" s="134"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="136"/>
       <c r="H16" s="112"/>
       <c r="I16" s="112"/>
       <c r="J16" s="14"/>
@@ -4634,13 +4634,13 @@
       <c r="A17" s="1"/>
       <c r="B17" s="18"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="181" t="s">
+      <c r="D17" s="151" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="164"/>
-      <c r="F17" s="164"/>
-      <c r="G17" s="170"/>
-      <c r="H17" s="138" t="s">
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="133"/>
+      <c r="H17" s="184" t="s">
         <v>40</v>
       </c>
       <c r="I17" s="112">
@@ -4762,10 +4762,10 @@
       <c r="A18" s="1"/>
       <c r="B18" s="18"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="166"/>
-      <c r="E18" s="167"/>
-      <c r="F18" s="167"/>
-      <c r="G18" s="171"/>
+      <c r="D18" s="134"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="136"/>
       <c r="H18" s="112"/>
       <c r="I18" s="112"/>
       <c r="J18" s="14"/>
@@ -4884,13 +4884,13 @@
       <c r="A19" s="1"/>
       <c r="B19" s="18"/>
       <c r="C19" s="24"/>
-      <c r="D19" s="181" t="s">
+      <c r="D19" s="151" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="164"/>
-      <c r="F19" s="164"/>
-      <c r="G19" s="170"/>
-      <c r="H19" s="138" t="s">
+      <c r="E19" s="132"/>
+      <c r="F19" s="132"/>
+      <c r="G19" s="133"/>
+      <c r="H19" s="184" t="s">
         <v>40</v>
       </c>
       <c r="I19" s="112">
@@ -5012,10 +5012,10 @@
       <c r="A20" s="1"/>
       <c r="B20" s="18"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="166"/>
-      <c r="E20" s="167"/>
-      <c r="F20" s="167"/>
-      <c r="G20" s="171"/>
+      <c r="D20" s="134"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="136"/>
       <c r="H20" s="112"/>
       <c r="I20" s="112"/>
       <c r="J20" s="26"/>
@@ -5133,15 +5133,15 @@
     <row r="21" spans="1:120" ht="9.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="18"/>
-      <c r="C21" s="180" t="s">
+      <c r="C21" s="153" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="158"/>
-      <c r="E21" s="158"/>
-      <c r="F21" s="158"/>
-      <c r="G21" s="159"/>
-      <c r="H21" s="139"/>
-      <c r="I21" s="139"/>
+      <c r="D21" s="154"/>
+      <c r="E21" s="154"/>
+      <c r="F21" s="154"/>
+      <c r="G21" s="155"/>
+      <c r="H21" s="167"/>
+      <c r="I21" s="167"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="44"/>
@@ -5257,13 +5257,13 @@
     <row r="22" spans="1:120" ht="9.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="18"/>
-      <c r="C22" s="160"/>
-      <c r="D22" s="161"/>
-      <c r="E22" s="161"/>
-      <c r="F22" s="161"/>
-      <c r="G22" s="162"/>
-      <c r="H22" s="139"/>
-      <c r="I22" s="139"/>
+      <c r="C22" s="156"/>
+      <c r="D22" s="157"/>
+      <c r="E22" s="157"/>
+      <c r="F22" s="157"/>
+      <c r="G22" s="142"/>
+      <c r="H22" s="167"/>
+      <c r="I22" s="167"/>
       <c r="J22" s="46"/>
       <c r="K22" s="47"/>
       <c r="L22" s="47"/>
@@ -5380,13 +5380,13 @@
       <c r="A23" s="1"/>
       <c r="B23" s="28"/>
       <c r="C23" s="29"/>
-      <c r="D23" s="182" t="s">
+      <c r="D23" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="164"/>
-      <c r="F23" s="164"/>
-      <c r="G23" s="170"/>
-      <c r="H23" s="138" t="s">
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="184" t="s">
         <v>46</v>
       </c>
       <c r="I23" s="112">
@@ -5508,10 +5508,10 @@
       <c r="A24" s="1"/>
       <c r="B24" s="18"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="166"/>
-      <c r="E24" s="167"/>
-      <c r="F24" s="167"/>
-      <c r="G24" s="171"/>
+      <c r="D24" s="134"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="136"/>
       <c r="H24" s="112"/>
       <c r="I24" s="112"/>
       <c r="J24" s="14"/>
@@ -5629,15 +5629,15 @@
     <row r="25" spans="1:120" ht="9.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="18"/>
-      <c r="C25" s="180" t="s">
+      <c r="C25" s="153" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="158"/>
-      <c r="G25" s="159"/>
-      <c r="H25" s="139"/>
-      <c r="I25" s="139"/>
+      <c r="D25" s="154"/>
+      <c r="E25" s="154"/>
+      <c r="F25" s="154"/>
+      <c r="G25" s="155"/>
+      <c r="H25" s="167"/>
+      <c r="I25" s="167"/>
       <c r="J25" s="42"/>
       <c r="K25" s="42"/>
       <c r="L25" s="44"/>
@@ -5753,13 +5753,13 @@
     <row r="26" spans="1:120" ht="9.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="18"/>
-      <c r="C26" s="179"/>
-      <c r="D26" s="167"/>
-      <c r="E26" s="167"/>
-      <c r="F26" s="167"/>
-      <c r="G26" s="168"/>
-      <c r="H26" s="139"/>
-      <c r="I26" s="139"/>
+      <c r="C26" s="141"/>
+      <c r="D26" s="135"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="135"/>
+      <c r="G26" s="139"/>
+      <c r="H26" s="167"/>
+      <c r="I26" s="167"/>
       <c r="J26" s="46"/>
       <c r="K26" s="47"/>
       <c r="L26" s="47"/>
@@ -5876,13 +5876,13 @@
       <c r="A27" s="1"/>
       <c r="B27" s="28"/>
       <c r="C27" s="29"/>
-      <c r="D27" s="182" t="s">
+      <c r="D27" s="158" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="164"/>
-      <c r="F27" s="164"/>
-      <c r="G27" s="170"/>
-      <c r="H27" s="138" t="s">
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="184" t="s">
         <v>44</v>
       </c>
       <c r="I27" s="112">
@@ -6004,10 +6004,10 @@
       <c r="A28" s="1"/>
       <c r="B28" s="28"/>
       <c r="C28" s="30"/>
-      <c r="D28" s="166"/>
-      <c r="E28" s="167"/>
-      <c r="F28" s="167"/>
-      <c r="G28" s="171"/>
+      <c r="D28" s="134"/>
+      <c r="E28" s="135"/>
+      <c r="F28" s="135"/>
+      <c r="G28" s="136"/>
       <c r="H28" s="112"/>
       <c r="I28" s="112"/>
       <c r="J28" s="14"/>
@@ -6126,13 +6126,13 @@
       <c r="A29" s="1"/>
       <c r="B29" s="28"/>
       <c r="C29" s="30"/>
-      <c r="D29" s="183" t="s">
+      <c r="D29" s="159" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="184"/>
-      <c r="F29" s="184"/>
-      <c r="G29" s="184"/>
-      <c r="H29" s="138" t="s">
+      <c r="E29" s="160"/>
+      <c r="F29" s="160"/>
+      <c r="G29" s="160"/>
+      <c r="H29" s="184" t="s">
         <v>44</v>
       </c>
       <c r="I29" s="112">
@@ -6254,10 +6254,10 @@
       <c r="A30" s="1"/>
       <c r="B30" s="28"/>
       <c r="C30" s="31"/>
-      <c r="D30" s="166"/>
-      <c r="E30" s="167"/>
-      <c r="F30" s="167"/>
-      <c r="G30" s="167"/>
+      <c r="D30" s="134"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="135"/>
+      <c r="G30" s="135"/>
       <c r="H30" s="112"/>
       <c r="I30" s="112"/>
       <c r="J30" s="26"/>
@@ -6375,15 +6375,15 @@
     <row r="31" spans="1:120" ht="9.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="18"/>
-      <c r="C31" s="157" t="s">
+      <c r="C31" s="179" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="158"/>
-      <c r="E31" s="158"/>
-      <c r="F31" s="158"/>
-      <c r="G31" s="159"/>
-      <c r="H31" s="139"/>
-      <c r="I31" s="139"/>
+      <c r="D31" s="154"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="154"/>
+      <c r="G31" s="155"/>
+      <c r="H31" s="167"/>
+      <c r="I31" s="167"/>
       <c r="J31" s="42"/>
       <c r="K31" s="43"/>
       <c r="L31" s="44"/>
@@ -6499,13 +6499,13 @@
     <row r="32" spans="1:120" ht="9.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="18"/>
-      <c r="C32" s="160"/>
-      <c r="D32" s="161"/>
-      <c r="E32" s="161"/>
-      <c r="F32" s="161"/>
-      <c r="G32" s="162"/>
-      <c r="H32" s="139"/>
-      <c r="I32" s="139"/>
+      <c r="C32" s="156"/>
+      <c r="D32" s="157"/>
+      <c r="E32" s="157"/>
+      <c r="F32" s="157"/>
+      <c r="G32" s="142"/>
+      <c r="H32" s="167"/>
+      <c r="I32" s="167"/>
       <c r="J32" s="46"/>
       <c r="K32" s="47"/>
       <c r="L32" s="47"/>
@@ -6622,14 +6622,14 @@
       <c r="A33" s="1"/>
       <c r="B33" s="18"/>
       <c r="C33" s="32"/>
-      <c r="D33" s="163" t="s">
+      <c r="D33" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="164"/>
-      <c r="F33" s="164"/>
-      <c r="G33" s="165"/>
-      <c r="H33" s="139"/>
-      <c r="I33" s="139"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="138"/>
+      <c r="H33" s="167"/>
+      <c r="I33" s="167"/>
       <c r="J33" s="50"/>
       <c r="K33" s="51"/>
       <c r="L33" s="51"/>
@@ -6746,12 +6746,12 @@
       <c r="A34" s="1"/>
       <c r="B34" s="18"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="166"/>
-      <c r="E34" s="167"/>
-      <c r="F34" s="167"/>
-      <c r="G34" s="168"/>
-      <c r="H34" s="139"/>
-      <c r="I34" s="139"/>
+      <c r="D34" s="134"/>
+      <c r="E34" s="135"/>
+      <c r="F34" s="135"/>
+      <c r="G34" s="139"/>
+      <c r="H34" s="167"/>
+      <c r="I34" s="167"/>
       <c r="J34" s="52"/>
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
@@ -6869,12 +6869,12 @@
       <c r="B35" s="18"/>
       <c r="C35" s="1"/>
       <c r="D35" s="33"/>
-      <c r="E35" s="169" t="s">
+      <c r="E35" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="164"/>
-      <c r="G35" s="170"/>
-      <c r="H35" s="138" t="s">
+      <c r="F35" s="132"/>
+      <c r="G35" s="133"/>
+      <c r="H35" s="184" t="s">
         <v>45</v>
       </c>
       <c r="I35" s="112">
@@ -6997,9 +6997,9 @@
       <c r="B36" s="18"/>
       <c r="C36" s="1"/>
       <c r="D36" s="34"/>
-      <c r="E36" s="166"/>
-      <c r="F36" s="167"/>
-      <c r="G36" s="171"/>
+      <c r="E36" s="134"/>
+      <c r="F36" s="135"/>
+      <c r="G36" s="136"/>
       <c r="H36" s="112"/>
       <c r="I36" s="112"/>
       <c r="J36" s="14"/>
@@ -7119,12 +7119,12 @@
       <c r="B37" s="18"/>
       <c r="C37" s="1"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="169" t="s">
+      <c r="E37" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F37" s="164"/>
-      <c r="G37" s="170"/>
-      <c r="H37" s="138" t="s">
+      <c r="F37" s="132"/>
+      <c r="G37" s="133"/>
+      <c r="H37" s="184" t="s">
         <v>44</v>
       </c>
       <c r="I37" s="112">
@@ -7247,9 +7247,9 @@
       <c r="B38" s="18"/>
       <c r="C38" s="1"/>
       <c r="D38" s="35"/>
-      <c r="E38" s="166"/>
-      <c r="F38" s="167"/>
-      <c r="G38" s="171"/>
+      <c r="E38" s="134"/>
+      <c r="F38" s="135"/>
+      <c r="G38" s="136"/>
       <c r="H38" s="112"/>
       <c r="I38" s="112"/>
       <c r="J38" s="26"/>
@@ -7368,14 +7368,14 @@
       <c r="A39" s="1"/>
       <c r="B39" s="18"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="172" t="s">
+      <c r="D39" s="180" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="158"/>
-      <c r="F39" s="158"/>
-      <c r="G39" s="159"/>
-      <c r="H39" s="139"/>
-      <c r="I39" s="139"/>
+      <c r="E39" s="154"/>
+      <c r="F39" s="154"/>
+      <c r="G39" s="155"/>
+      <c r="H39" s="167"/>
+      <c r="I39" s="167"/>
       <c r="J39" s="50"/>
       <c r="K39" s="51"/>
       <c r="L39" s="51"/>
@@ -7492,12 +7492,12 @@
       <c r="A40" s="1"/>
       <c r="B40" s="18"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="166"/>
-      <c r="E40" s="167"/>
-      <c r="F40" s="167"/>
-      <c r="G40" s="168"/>
-      <c r="H40" s="139"/>
-      <c r="I40" s="139"/>
+      <c r="D40" s="134"/>
+      <c r="E40" s="135"/>
+      <c r="F40" s="135"/>
+      <c r="G40" s="139"/>
+      <c r="H40" s="167"/>
+      <c r="I40" s="167"/>
       <c r="J40" s="52"/>
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
@@ -7615,12 +7615,12 @@
       <c r="B41" s="18"/>
       <c r="C41" s="1"/>
       <c r="D41" s="33"/>
-      <c r="E41" s="169" t="s">
+      <c r="E41" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="164"/>
-      <c r="G41" s="170"/>
-      <c r="H41" s="138" t="s">
+      <c r="F41" s="132"/>
+      <c r="G41" s="133"/>
+      <c r="H41" s="184" t="s">
         <v>43</v>
       </c>
       <c r="I41" s="112">
@@ -7743,9 +7743,9 @@
       <c r="B42" s="18"/>
       <c r="C42" s="1"/>
       <c r="D42" s="34"/>
-      <c r="E42" s="166"/>
-      <c r="F42" s="167"/>
-      <c r="G42" s="171"/>
+      <c r="E42" s="134"/>
+      <c r="F42" s="135"/>
+      <c r="G42" s="136"/>
       <c r="H42" s="112"/>
       <c r="I42" s="112"/>
       <c r="J42" s="14"/>
@@ -7865,12 +7865,12 @@
       <c r="B43" s="18"/>
       <c r="C43" s="1"/>
       <c r="D43" s="34"/>
-      <c r="E43" s="169" t="s">
+      <c r="E43" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="164"/>
-      <c r="G43" s="170"/>
-      <c r="H43" s="138" t="s">
+      <c r="F43" s="132"/>
+      <c r="G43" s="133"/>
+      <c r="H43" s="184" t="s">
         <v>43</v>
       </c>
       <c r="I43" s="112">
@@ -7993,9 +7993,9 @@
       <c r="B44" s="18"/>
       <c r="C44" s="1"/>
       <c r="D44" s="34"/>
-      <c r="E44" s="166"/>
-      <c r="F44" s="167"/>
-      <c r="G44" s="171"/>
+      <c r="E44" s="134"/>
+      <c r="F44" s="135"/>
+      <c r="G44" s="136"/>
       <c r="H44" s="112"/>
       <c r="I44" s="112"/>
       <c r="J44" s="14"/>
@@ -8115,12 +8115,12 @@
       <c r="B45" s="18"/>
       <c r="C45" s="1"/>
       <c r="D45" s="34"/>
-      <c r="E45" s="169" t="s">
+      <c r="E45" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="164"/>
-      <c r="G45" s="170"/>
-      <c r="H45" s="138" t="s">
+      <c r="F45" s="132"/>
+      <c r="G45" s="133"/>
+      <c r="H45" s="184" t="s">
         <v>42</v>
       </c>
       <c r="I45" s="112">
@@ -8243,9 +8243,9 @@
       <c r="B46" s="18"/>
       <c r="C46" s="1"/>
       <c r="D46" s="34"/>
-      <c r="E46" s="166"/>
-      <c r="F46" s="167"/>
-      <c r="G46" s="171"/>
+      <c r="E46" s="134"/>
+      <c r="F46" s="135"/>
+      <c r="G46" s="136"/>
       <c r="H46" s="112"/>
       <c r="I46" s="112"/>
       <c r="J46" s="14"/>
@@ -8365,12 +8365,12 @@
       <c r="B47" s="18"/>
       <c r="C47" s="1"/>
       <c r="D47" s="34"/>
-      <c r="E47" s="169" t="s">
+      <c r="E47" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="F47" s="164"/>
-      <c r="G47" s="170"/>
-      <c r="H47" s="138" t="s">
+      <c r="F47" s="132"/>
+      <c r="G47" s="133"/>
+      <c r="H47" s="184" t="s">
         <v>41</v>
       </c>
       <c r="I47" s="112">
@@ -8493,9 +8493,9 @@
       <c r="B48" s="18"/>
       <c r="C48" s="1"/>
       <c r="D48" s="34"/>
-      <c r="E48" s="166"/>
-      <c r="F48" s="167"/>
-      <c r="G48" s="171"/>
+      <c r="E48" s="134"/>
+      <c r="F48" s="135"/>
+      <c r="G48" s="136"/>
       <c r="H48" s="112"/>
       <c r="I48" s="112"/>
       <c r="J48" s="14"/>
@@ -8615,12 +8615,12 @@
       <c r="B49" s="18"/>
       <c r="C49" s="1"/>
       <c r="D49" s="34"/>
-      <c r="E49" s="169" t="s">
+      <c r="E49" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="164"/>
-      <c r="G49" s="170"/>
-      <c r="H49" s="138" t="s">
+      <c r="F49" s="132"/>
+      <c r="G49" s="133"/>
+      <c r="H49" s="184" t="s">
         <v>50</v>
       </c>
       <c r="I49" s="112">
@@ -8743,9 +8743,9 @@
       <c r="B50" s="18"/>
       <c r="C50" s="1"/>
       <c r="D50" s="34"/>
-      <c r="E50" s="166"/>
-      <c r="F50" s="167"/>
-      <c r="G50" s="171"/>
+      <c r="E50" s="134"/>
+      <c r="F50" s="135"/>
+      <c r="G50" s="136"/>
       <c r="H50" s="112"/>
       <c r="I50" s="112"/>
       <c r="J50" s="14"/>
@@ -8865,12 +8865,12 @@
       <c r="B51" s="18"/>
       <c r="C51" s="1"/>
       <c r="D51" s="34"/>
-      <c r="E51" s="169" t="s">
+      <c r="E51" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="164"/>
-      <c r="G51" s="170"/>
-      <c r="H51" s="138" t="s">
+      <c r="F51" s="132"/>
+      <c r="G51" s="133"/>
+      <c r="H51" s="184" t="s">
         <v>47</v>
       </c>
       <c r="I51" s="112">
@@ -8993,9 +8993,9 @@
       <c r="B52" s="18"/>
       <c r="C52" s="1"/>
       <c r="D52" s="34"/>
-      <c r="E52" s="166"/>
-      <c r="F52" s="167"/>
-      <c r="G52" s="171"/>
+      <c r="E52" s="134"/>
+      <c r="F52" s="135"/>
+      <c r="G52" s="136"/>
       <c r="H52" s="112"/>
       <c r="I52" s="112"/>
       <c r="J52" s="26"/>
@@ -9114,14 +9114,14 @@
       <c r="A53" s="1"/>
       <c r="B53" s="18"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="163" t="s">
+      <c r="D53" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="164"/>
-      <c r="F53" s="164"/>
-      <c r="G53" s="165"/>
-      <c r="H53" s="139"/>
-      <c r="I53" s="139"/>
+      <c r="E53" s="132"/>
+      <c r="F53" s="132"/>
+      <c r="G53" s="138"/>
+      <c r="H53" s="167"/>
+      <c r="I53" s="167"/>
       <c r="J53" s="50"/>
       <c r="K53" s="51"/>
       <c r="L53" s="51"/>
@@ -9238,12 +9238,12 @@
       <c r="A54" s="1"/>
       <c r="B54" s="18"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="166"/>
-      <c r="E54" s="167"/>
-      <c r="F54" s="167"/>
-      <c r="G54" s="168"/>
-      <c r="H54" s="139"/>
-      <c r="I54" s="139"/>
+      <c r="D54" s="134"/>
+      <c r="E54" s="135"/>
+      <c r="F54" s="135"/>
+      <c r="G54" s="139"/>
+      <c r="H54" s="167"/>
+      <c r="I54" s="167"/>
       <c r="J54" s="52"/>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -9361,12 +9361,12 @@
       <c r="B55" s="18"/>
       <c r="C55" s="1"/>
       <c r="D55" s="34"/>
-      <c r="E55" s="169" t="s">
+      <c r="E55" s="131" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="164"/>
-      <c r="G55" s="170"/>
-      <c r="H55" s="138" t="s">
+      <c r="F55" s="132"/>
+      <c r="G55" s="133"/>
+      <c r="H55" s="184" t="s">
         <v>48</v>
       </c>
       <c r="I55" s="112">
@@ -9489,9 +9489,9 @@
       <c r="B56" s="18"/>
       <c r="C56" s="1"/>
       <c r="D56" s="34"/>
-      <c r="E56" s="166"/>
-      <c r="F56" s="167"/>
-      <c r="G56" s="171"/>
+      <c r="E56" s="134"/>
+      <c r="F56" s="135"/>
+      <c r="G56" s="136"/>
       <c r="H56" s="112"/>
       <c r="I56" s="112"/>
       <c r="J56" s="14"/>
@@ -9611,12 +9611,12 @@
       <c r="B57" s="18"/>
       <c r="C57" s="1"/>
       <c r="D57" s="34"/>
-      <c r="E57" s="169" t="s">
+      <c r="E57" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="F57" s="164"/>
-      <c r="G57" s="170"/>
-      <c r="H57" s="138" t="s">
+      <c r="F57" s="132"/>
+      <c r="G57" s="133"/>
+      <c r="H57" s="184" t="s">
         <v>51</v>
       </c>
       <c r="I57" s="112">
@@ -9739,9 +9739,9 @@
       <c r="B58" s="18"/>
       <c r="C58" s="1"/>
       <c r="D58" s="34"/>
-      <c r="E58" s="166"/>
-      <c r="F58" s="167"/>
-      <c r="G58" s="171"/>
+      <c r="E58" s="134"/>
+      <c r="F58" s="135"/>
+      <c r="G58" s="136"/>
       <c r="H58" s="112"/>
       <c r="I58" s="112"/>
       <c r="J58" s="14"/>
@@ -9861,12 +9861,12 @@
       <c r="B59" s="18"/>
       <c r="C59" s="1"/>
       <c r="D59" s="34"/>
-      <c r="E59" s="169" t="s">
+      <c r="E59" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="F59" s="164"/>
-      <c r="G59" s="170"/>
-      <c r="H59" s="138" t="s">
+      <c r="F59" s="132"/>
+      <c r="G59" s="133"/>
+      <c r="H59" s="184" t="s">
         <v>49</v>
       </c>
       <c r="I59" s="112">
@@ -9989,9 +9989,9 @@
       <c r="B60" s="18"/>
       <c r="C60" s="1"/>
       <c r="D60" s="34"/>
-      <c r="E60" s="166"/>
-      <c r="F60" s="167"/>
-      <c r="G60" s="171"/>
+      <c r="E60" s="134"/>
+      <c r="F60" s="135"/>
+      <c r="G60" s="136"/>
       <c r="H60" s="112"/>
       <c r="I60" s="112"/>
       <c r="J60" s="14"/>
@@ -10111,12 +10111,12 @@
       <c r="B61" s="18"/>
       <c r="C61" s="1"/>
       <c r="D61" s="34"/>
-      <c r="E61" s="169" t="s">
+      <c r="E61" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F61" s="164"/>
-      <c r="G61" s="170"/>
-      <c r="H61" s="138" t="s">
+      <c r="F61" s="132"/>
+      <c r="G61" s="133"/>
+      <c r="H61" s="184" t="s">
         <v>49</v>
       </c>
       <c r="I61" s="112">
@@ -10239,9 +10239,9 @@
       <c r="B62" s="18"/>
       <c r="C62" s="1"/>
       <c r="D62" s="34"/>
-      <c r="E62" s="166"/>
-      <c r="F62" s="167"/>
-      <c r="G62" s="171"/>
+      <c r="E62" s="134"/>
+      <c r="F62" s="135"/>
+      <c r="G62" s="136"/>
       <c r="H62" s="112"/>
       <c r="I62" s="112"/>
       <c r="J62" s="26"/>
@@ -10360,14 +10360,14 @@
       <c r="A63" s="1"/>
       <c r="B63" s="18"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="163" t="s">
+      <c r="D63" s="137" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="164"/>
-      <c r="F63" s="164"/>
-      <c r="G63" s="165"/>
-      <c r="H63" s="139"/>
-      <c r="I63" s="139"/>
+      <c r="E63" s="132"/>
+      <c r="F63" s="132"/>
+      <c r="G63" s="138"/>
+      <c r="H63" s="167"/>
+      <c r="I63" s="167"/>
       <c r="J63" s="50"/>
       <c r="K63" s="51"/>
       <c r="L63" s="51"/>
@@ -10484,12 +10484,12 @@
       <c r="A64" s="1"/>
       <c r="B64" s="18"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="166"/>
-      <c r="E64" s="167"/>
-      <c r="F64" s="167"/>
-      <c r="G64" s="168"/>
-      <c r="H64" s="139"/>
-      <c r="I64" s="139"/>
+      <c r="D64" s="134"/>
+      <c r="E64" s="135"/>
+      <c r="F64" s="135"/>
+      <c r="G64" s="139"/>
+      <c r="H64" s="167"/>
+      <c r="I64" s="167"/>
       <c r="J64" s="52"/>
       <c r="K64" s="49"/>
       <c r="L64" s="49"/>
@@ -10607,12 +10607,12 @@
       <c r="B65" s="18"/>
       <c r="C65" s="1"/>
       <c r="D65" s="34"/>
-      <c r="E65" s="169" t="s">
+      <c r="E65" s="131" t="s">
         <v>35</v>
       </c>
-      <c r="F65" s="164"/>
-      <c r="G65" s="170"/>
-      <c r="H65" s="138" t="s">
+      <c r="F65" s="132"/>
+      <c r="G65" s="133"/>
+      <c r="H65" s="184" t="s">
         <v>52</v>
       </c>
       <c r="I65" s="112">
@@ -10735,9 +10735,9 @@
       <c r="B66" s="18"/>
       <c r="C66" s="1"/>
       <c r="D66" s="34"/>
-      <c r="E66" s="166"/>
-      <c r="F66" s="167"/>
-      <c r="G66" s="171"/>
+      <c r="E66" s="134"/>
+      <c r="F66" s="135"/>
+      <c r="G66" s="136"/>
       <c r="H66" s="112"/>
       <c r="I66" s="112"/>
       <c r="J66" s="14"/>
@@ -10857,12 +10857,12 @@
       <c r="B67" s="18"/>
       <c r="C67" s="1"/>
       <c r="D67" s="34"/>
-      <c r="E67" s="169" t="s">
+      <c r="E67" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="F67" s="164"/>
-      <c r="G67" s="170"/>
-      <c r="H67" s="138" t="s">
+      <c r="F67" s="132"/>
+      <c r="G67" s="133"/>
+      <c r="H67" s="184" t="s">
         <v>53</v>
       </c>
       <c r="I67" s="112">
@@ -10985,9 +10985,9 @@
       <c r="B68" s="18"/>
       <c r="C68" s="1"/>
       <c r="D68" s="34"/>
-      <c r="E68" s="166"/>
-      <c r="F68" s="167"/>
-      <c r="G68" s="171"/>
+      <c r="E68" s="134"/>
+      <c r="F68" s="135"/>
+      <c r="G68" s="136"/>
       <c r="H68" s="112"/>
       <c r="I68" s="112"/>
       <c r="J68" s="14"/>
@@ -11107,12 +11107,12 @@
       <c r="B69" s="18"/>
       <c r="C69" s="1"/>
       <c r="D69" s="34"/>
-      <c r="E69" s="169" t="s">
+      <c r="E69" s="131" t="s">
         <v>36</v>
       </c>
-      <c r="F69" s="164"/>
-      <c r="G69" s="170"/>
-      <c r="H69" s="138" t="s">
+      <c r="F69" s="132"/>
+      <c r="G69" s="133"/>
+      <c r="H69" s="184" t="s">
         <v>54</v>
       </c>
       <c r="I69" s="112">
@@ -11235,9 +11235,9 @@
       <c r="B70" s="18"/>
       <c r="C70" s="1"/>
       <c r="D70" s="34"/>
-      <c r="E70" s="166"/>
-      <c r="F70" s="167"/>
-      <c r="G70" s="171"/>
+      <c r="E70" s="134"/>
+      <c r="F70" s="135"/>
+      <c r="G70" s="136"/>
       <c r="H70" s="112"/>
       <c r="I70" s="112"/>
       <c r="J70" s="14"/>
@@ -11357,12 +11357,12 @@
       <c r="B71" s="18"/>
       <c r="C71" s="1"/>
       <c r="D71" s="34"/>
-      <c r="E71" s="169" t="s">
+      <c r="E71" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F71" s="164"/>
-      <c r="G71" s="170"/>
-      <c r="H71" s="138" t="s">
+      <c r="F71" s="132"/>
+      <c r="G71" s="133"/>
+      <c r="H71" s="184" t="s">
         <v>55</v>
       </c>
       <c r="I71" s="112">
@@ -11485,9 +11485,9 @@
       <c r="B72" s="18"/>
       <c r="C72" s="1"/>
       <c r="D72" s="35"/>
-      <c r="E72" s="166"/>
-      <c r="F72" s="167"/>
-      <c r="G72" s="171"/>
+      <c r="E72" s="134"/>
+      <c r="F72" s="135"/>
+      <c r="G72" s="136"/>
       <c r="H72" s="112"/>
       <c r="I72" s="112"/>
       <c r="J72" s="26"/>
@@ -11605,14 +11605,14 @@
     <row r="73" spans="1:120" ht="9.75" customHeight="1">
       <c r="A73" s="16"/>
       <c r="B73" s="36"/>
-      <c r="C73" s="146" t="s">
+      <c r="C73" s="140" t="s">
         <v>30</v>
       </c>
-      <c r="D73" s="164"/>
-      <c r="E73" s="164"/>
-      <c r="F73" s="164"/>
-      <c r="G73" s="165"/>
-      <c r="H73" s="138" t="s">
+      <c r="D73" s="132"/>
+      <c r="E73" s="132"/>
+      <c r="F73" s="132"/>
+      <c r="G73" s="138"/>
+      <c r="H73" s="184" t="s">
         <v>55</v>
       </c>
       <c r="I73" s="112">
@@ -11733,11 +11733,11 @@
     <row r="74" spans="1:120" ht="9.75" customHeight="1">
       <c r="A74" s="16"/>
       <c r="B74" s="36"/>
-      <c r="C74" s="179"/>
-      <c r="D74" s="167"/>
-      <c r="E74" s="167"/>
-      <c r="F74" s="167"/>
-      <c r="G74" s="168"/>
+      <c r="C74" s="141"/>
+      <c r="D74" s="135"/>
+      <c r="E74" s="135"/>
+      <c r="F74" s="135"/>
+      <c r="G74" s="139"/>
       <c r="H74" s="112"/>
       <c r="I74" s="112"/>
       <c r="J74" s="19"/>
@@ -11855,14 +11855,14 @@
     <row r="75" spans="1:120" ht="9.75" customHeight="1">
       <c r="A75" s="16"/>
       <c r="B75" s="36"/>
-      <c r="C75" s="146" t="s">
+      <c r="C75" s="140" t="s">
         <v>34</v>
       </c>
-      <c r="D75" s="164"/>
-      <c r="E75" s="164"/>
-      <c r="F75" s="164"/>
-      <c r="G75" s="165"/>
-      <c r="H75" s="138" t="s">
+      <c r="D75" s="132"/>
+      <c r="E75" s="132"/>
+      <c r="F75" s="132"/>
+      <c r="G75" s="138"/>
+      <c r="H75" s="184" t="s">
         <v>58</v>
       </c>
       <c r="I75" s="112"/>
@@ -11981,11 +11981,11 @@
     <row r="76" spans="1:120" ht="9.75" customHeight="1">
       <c r="A76" s="16"/>
       <c r="B76" s="36"/>
-      <c r="C76" s="162"/>
-      <c r="D76" s="162"/>
-      <c r="E76" s="162"/>
-      <c r="F76" s="162"/>
-      <c r="G76" s="162"/>
+      <c r="C76" s="142"/>
+      <c r="D76" s="142"/>
+      <c r="E76" s="142"/>
+      <c r="F76" s="142"/>
+      <c r="G76" s="142"/>
       <c r="H76" s="112"/>
       <c r="I76" s="112"/>
       <c r="J76" s="19"/>
@@ -12103,15 +12103,15 @@
     <row r="77" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A77" s="16"/>
       <c r="B77" s="71"/>
-      <c r="C77" s="187" t="s">
+      <c r="C77" s="143" t="s">
         <v>62</v>
       </c>
-      <c r="D77" s="188"/>
-      <c r="E77" s="188"/>
-      <c r="F77" s="188"/>
-      <c r="G77" s="189"/>
-      <c r="H77" s="140"/>
-      <c r="I77" s="129"/>
+      <c r="D77" s="144"/>
+      <c r="E77" s="144"/>
+      <c r="F77" s="144"/>
+      <c r="G77" s="145"/>
+      <c r="H77" s="185"/>
+      <c r="I77" s="181"/>
       <c r="J77" s="63"/>
       <c r="K77" s="64"/>
       <c r="L77" s="64"/>
@@ -12227,13 +12227,13 @@
     <row r="78" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A78" s="16"/>
       <c r="B78" s="71"/>
-      <c r="C78" s="190"/>
-      <c r="D78" s="191"/>
-      <c r="E78" s="191"/>
-      <c r="F78" s="191"/>
-      <c r="G78" s="192"/>
-      <c r="H78" s="141"/>
-      <c r="I78" s="130"/>
+      <c r="C78" s="146"/>
+      <c r="D78" s="147"/>
+      <c r="E78" s="147"/>
+      <c r="F78" s="147"/>
+      <c r="G78" s="148"/>
+      <c r="H78" s="186"/>
+      <c r="I78" s="182"/>
       <c r="J78" s="63"/>
       <c r="K78" s="64"/>
       <c r="L78" s="64"/>
@@ -12350,12 +12350,12 @@
       <c r="A79" s="16"/>
       <c r="B79" s="71"/>
       <c r="C79" s="76"/>
-      <c r="D79" s="132" t="s">
+      <c r="D79" s="115" t="s">
         <v>63</v>
       </c>
-      <c r="E79" s="133"/>
-      <c r="F79" s="133"/>
-      <c r="G79" s="134"/>
+      <c r="E79" s="116"/>
+      <c r="F79" s="116"/>
+      <c r="G79" s="117"/>
       <c r="H79" s="77"/>
       <c r="I79" s="67"/>
       <c r="J79" s="63"/>
@@ -12474,10 +12474,10 @@
       <c r="A80" s="16"/>
       <c r="B80" s="71"/>
       <c r="C80" s="76"/>
-      <c r="D80" s="135"/>
-      <c r="E80" s="136"/>
-      <c r="F80" s="136"/>
-      <c r="G80" s="137"/>
+      <c r="D80" s="118"/>
+      <c r="E80" s="119"/>
+      <c r="F80" s="119"/>
+      <c r="G80" s="120"/>
       <c r="H80" s="77"/>
       <c r="I80" s="67"/>
       <c r="J80" s="63"/>
@@ -12597,15 +12597,15 @@
       <c r="B81" s="36"/>
       <c r="C81" s="60"/>
       <c r="D81" s="70"/>
-      <c r="E81" s="105" t="s">
+      <c r="E81" s="149" t="s">
         <v>73</v>
       </c>
-      <c r="F81" s="105"/>
-      <c r="G81" s="105"/>
-      <c r="H81" s="111">
+      <c r="F81" s="149"/>
+      <c r="G81" s="149"/>
+      <c r="H81" s="103">
         <v>45611</v>
       </c>
-      <c r="I81" s="126">
+      <c r="I81" s="105">
         <v>100</v>
       </c>
       <c r="J81" s="19"/>
@@ -12725,11 +12725,11 @@
       <c r="B82" s="36"/>
       <c r="C82" s="60"/>
       <c r="D82" s="70"/>
-      <c r="E82" s="103"/>
-      <c r="F82" s="103"/>
-      <c r="G82" s="103"/>
-      <c r="H82" s="107"/>
-      <c r="I82" s="109"/>
+      <c r="E82" s="102"/>
+      <c r="F82" s="102"/>
+      <c r="G82" s="102"/>
+      <c r="H82" s="104"/>
+      <c r="I82" s="106"/>
       <c r="J82" s="19"/>
       <c r="K82" s="20"/>
       <c r="L82" s="20"/>
@@ -12847,15 +12847,15 @@
       <c r="B83" s="36"/>
       <c r="C83" s="60"/>
       <c r="D83" s="70"/>
-      <c r="E83" s="103" t="s">
+      <c r="E83" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="F83" s="103"/>
-      <c r="G83" s="103"/>
-      <c r="H83" s="111">
+      <c r="F83" s="102"/>
+      <c r="G83" s="102"/>
+      <c r="H83" s="103">
         <v>45615</v>
       </c>
-      <c r="I83" s="126">
+      <c r="I83" s="105">
         <v>100</v>
       </c>
       <c r="J83" s="19"/>
@@ -12975,11 +12975,11 @@
       <c r="B84" s="36"/>
       <c r="C84" s="60"/>
       <c r="D84" s="70"/>
-      <c r="E84" s="103"/>
-      <c r="F84" s="103"/>
-      <c r="G84" s="103"/>
-      <c r="H84" s="107"/>
-      <c r="I84" s="109"/>
+      <c r="E84" s="102"/>
+      <c r="F84" s="102"/>
+      <c r="G84" s="102"/>
+      <c r="H84" s="104"/>
+      <c r="I84" s="106"/>
       <c r="J84" s="19"/>
       <c r="K84" s="20"/>
       <c r="L84" s="20"/>
@@ -13097,15 +13097,15 @@
       <c r="B85" s="36"/>
       <c r="C85" s="60"/>
       <c r="D85" s="70"/>
-      <c r="E85" s="114" t="s">
+      <c r="E85" s="189" t="s">
         <v>61</v>
       </c>
-      <c r="F85" s="115"/>
-      <c r="G85" s="116"/>
-      <c r="H85" s="110">
+      <c r="F85" s="121"/>
+      <c r="G85" s="122"/>
+      <c r="H85" s="111">
         <v>45617</v>
       </c>
-      <c r="I85" s="126">
+      <c r="I85" s="105">
         <v>100</v>
       </c>
       <c r="J85" s="62"/>
@@ -13225,11 +13225,11 @@
       <c r="B86" s="36"/>
       <c r="C86" s="60"/>
       <c r="D86" s="70"/>
-      <c r="E86" s="117"/>
-      <c r="F86" s="118"/>
-      <c r="G86" s="119"/>
-      <c r="H86" s="110"/>
-      <c r="I86" s="109"/>
+      <c r="E86" s="150"/>
+      <c r="F86" s="125"/>
+      <c r="G86" s="126"/>
+      <c r="H86" s="111"/>
+      <c r="I86" s="106"/>
       <c r="J86" s="62"/>
       <c r="K86" s="20"/>
       <c r="L86" s="20"/>
@@ -13346,16 +13346,16 @@
       <c r="A87" s="16"/>
       <c r="B87" s="71"/>
       <c r="C87" s="90"/>
-      <c r="D87" s="103" t="s">
+      <c r="D87" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="E87" s="103"/>
-      <c r="F87" s="103"/>
-      <c r="G87" s="103"/>
-      <c r="H87" s="111">
+      <c r="E87" s="102"/>
+      <c r="F87" s="102"/>
+      <c r="G87" s="102"/>
+      <c r="H87" s="103">
         <v>45615</v>
       </c>
-      <c r="I87" s="126">
+      <c r="I87" s="105">
         <v>100</v>
       </c>
       <c r="J87" s="62"/>
@@ -13474,12 +13474,12 @@
       <c r="A88" s="16"/>
       <c r="B88" s="71"/>
       <c r="C88" s="90"/>
-      <c r="D88" s="103"/>
-      <c r="E88" s="103"/>
-      <c r="F88" s="103"/>
-      <c r="G88" s="103"/>
-      <c r="H88" s="107"/>
-      <c r="I88" s="109"/>
+      <c r="D88" s="102"/>
+      <c r="E88" s="102"/>
+      <c r="F88" s="102"/>
+      <c r="G88" s="102"/>
+      <c r="H88" s="104"/>
+      <c r="I88" s="106"/>
       <c r="J88" s="62"/>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -13596,14 +13596,14 @@
       <c r="A89" s="16"/>
       <c r="B89" s="36"/>
       <c r="C89" s="79"/>
-      <c r="D89" s="132" t="s">
+      <c r="D89" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="133"/>
-      <c r="F89" s="133"/>
-      <c r="G89" s="134"/>
-      <c r="H89" s="131"/>
-      <c r="I89" s="128"/>
+      <c r="E89" s="116"/>
+      <c r="F89" s="116"/>
+      <c r="G89" s="117"/>
+      <c r="H89" s="187"/>
+      <c r="I89" s="188"/>
       <c r="J89" s="66"/>
       <c r="K89" s="64"/>
       <c r="L89" s="64"/>
@@ -13720,12 +13720,12 @@
       <c r="A90" s="16"/>
       <c r="B90" s="36"/>
       <c r="C90" s="79"/>
-      <c r="D90" s="135"/>
-      <c r="E90" s="136"/>
-      <c r="F90" s="136"/>
-      <c r="G90" s="137"/>
-      <c r="H90" s="131"/>
-      <c r="I90" s="128"/>
+      <c r="D90" s="118"/>
+      <c r="E90" s="119"/>
+      <c r="F90" s="119"/>
+      <c r="G90" s="120"/>
+      <c r="H90" s="187"/>
+      <c r="I90" s="188"/>
       <c r="J90" s="66"/>
       <c r="K90" s="64"/>
       <c r="L90" s="64"/>
@@ -13843,15 +13843,15 @@
       <c r="B91" s="36"/>
       <c r="C91" s="60"/>
       <c r="D91" s="70"/>
-      <c r="E91" s="105" t="s">
+      <c r="E91" s="149" t="s">
         <v>68</v>
       </c>
-      <c r="F91" s="105"/>
-      <c r="G91" s="105"/>
-      <c r="H91" s="111">
+      <c r="F91" s="149"/>
+      <c r="G91" s="149"/>
+      <c r="H91" s="103">
         <v>45616</v>
       </c>
-      <c r="I91" s="126">
+      <c r="I91" s="105">
         <v>100</v>
       </c>
       <c r="J91" s="19"/>
@@ -13971,11 +13971,11 @@
       <c r="B92" s="36"/>
       <c r="C92" s="60"/>
       <c r="D92" s="70"/>
-      <c r="E92" s="103"/>
-      <c r="F92" s="103"/>
-      <c r="G92" s="103"/>
-      <c r="H92" s="107"/>
-      <c r="I92" s="109"/>
+      <c r="E92" s="102"/>
+      <c r="F92" s="102"/>
+      <c r="G92" s="102"/>
+      <c r="H92" s="104"/>
+      <c r="I92" s="106"/>
       <c r="J92" s="19"/>
       <c r="K92" s="20"/>
       <c r="L92" s="20"/>
@@ -14093,15 +14093,15 @@
       <c r="B93" s="36"/>
       <c r="C93" s="60"/>
       <c r="D93" s="70"/>
-      <c r="E93" s="103" t="s">
+      <c r="E93" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="F93" s="103"/>
-      <c r="G93" s="103"/>
-      <c r="H93" s="111">
+      <c r="F93" s="102"/>
+      <c r="G93" s="102"/>
+      <c r="H93" s="103">
         <v>45617</v>
       </c>
-      <c r="I93" s="126">
+      <c r="I93" s="105">
         <v>100</v>
       </c>
       <c r="J93" s="19"/>
@@ -14221,11 +14221,11 @@
       <c r="B94" s="36"/>
       <c r="C94" s="60"/>
       <c r="D94" s="70"/>
-      <c r="E94" s="103"/>
-      <c r="F94" s="103"/>
-      <c r="G94" s="103"/>
-      <c r="H94" s="107"/>
-      <c r="I94" s="109"/>
+      <c r="E94" s="102"/>
+      <c r="F94" s="102"/>
+      <c r="G94" s="102"/>
+      <c r="H94" s="104"/>
+      <c r="I94" s="106"/>
       <c r="J94" s="19"/>
       <c r="K94" s="20"/>
       <c r="L94" s="20"/>
@@ -14343,15 +14343,15 @@
       <c r="B95" s="36"/>
       <c r="C95" s="60"/>
       <c r="D95" s="70"/>
-      <c r="E95" s="103" t="s">
+      <c r="E95" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="F95" s="103"/>
-      <c r="G95" s="103"/>
-      <c r="H95" s="111">
+      <c r="F95" s="102"/>
+      <c r="G95" s="102"/>
+      <c r="H95" s="103">
         <v>45618</v>
       </c>
-      <c r="I95" s="126">
+      <c r="I95" s="105">
         <v>100</v>
       </c>
       <c r="J95" s="19"/>
@@ -14471,11 +14471,11 @@
       <c r="B96" s="36"/>
       <c r="C96" s="60"/>
       <c r="D96" s="70"/>
-      <c r="E96" s="103"/>
-      <c r="F96" s="103"/>
-      <c r="G96" s="103"/>
-      <c r="H96" s="107"/>
-      <c r="I96" s="109"/>
+      <c r="E96" s="102"/>
+      <c r="F96" s="102"/>
+      <c r="G96" s="102"/>
+      <c r="H96" s="104"/>
+      <c r="I96" s="106"/>
       <c r="J96" s="19"/>
       <c r="K96" s="20"/>
       <c r="L96" s="20"/>
@@ -14593,15 +14593,15 @@
       <c r="B97" s="36"/>
       <c r="C97" s="60"/>
       <c r="D97" s="70"/>
-      <c r="E97" s="103" t="s">
+      <c r="E97" s="102" t="s">
         <v>71</v>
       </c>
-      <c r="F97" s="103"/>
-      <c r="G97" s="103"/>
-      <c r="H97" s="111">
+      <c r="F97" s="102"/>
+      <c r="G97" s="102"/>
+      <c r="H97" s="103">
         <v>45621</v>
       </c>
-      <c r="I97" s="126">
+      <c r="I97" s="105">
         <v>100</v>
       </c>
       <c r="J97" s="19"/>
@@ -14721,11 +14721,11 @@
       <c r="B98" s="36"/>
       <c r="C98" s="60"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="103"/>
-      <c r="F98" s="103"/>
-      <c r="G98" s="103"/>
-      <c r="H98" s="107"/>
-      <c r="I98" s="109"/>
+      <c r="E98" s="102"/>
+      <c r="F98" s="102"/>
+      <c r="G98" s="102"/>
+      <c r="H98" s="104"/>
+      <c r="I98" s="106"/>
       <c r="J98" s="19"/>
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
@@ -14843,15 +14843,15 @@
       <c r="B99" s="36"/>
       <c r="C99" s="60"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="103" t="s">
+      <c r="E99" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="F99" s="103"/>
-      <c r="G99" s="103"/>
-      <c r="H99" s="111">
+      <c r="F99" s="102"/>
+      <c r="G99" s="102"/>
+      <c r="H99" s="103">
         <v>45622</v>
       </c>
-      <c r="I99" s="126">
+      <c r="I99" s="105">
         <v>100</v>
       </c>
       <c r="J99" s="19"/>
@@ -14971,11 +14971,11 @@
       <c r="B100" s="36"/>
       <c r="C100" s="60"/>
       <c r="D100" s="70"/>
-      <c r="E100" s="103"/>
-      <c r="F100" s="103"/>
-      <c r="G100" s="103"/>
-      <c r="H100" s="107"/>
-      <c r="I100" s="109"/>
+      <c r="E100" s="102"/>
+      <c r="F100" s="102"/>
+      <c r="G100" s="102"/>
+      <c r="H100" s="104"/>
+      <c r="I100" s="106"/>
       <c r="J100" s="19"/>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -15093,12 +15093,12 @@
       <c r="B101" s="71"/>
       <c r="C101" s="91"/>
       <c r="D101" s="70"/>
-      <c r="E101" s="117" t="s">
+      <c r="E101" s="150" t="s">
         <v>61</v>
       </c>
-      <c r="F101" s="118"/>
-      <c r="G101" s="119"/>
-      <c r="H101" s="111">
+      <c r="F101" s="125"/>
+      <c r="G101" s="126"/>
+      <c r="H101" s="103">
         <v>45623</v>
       </c>
       <c r="I101" s="112">
@@ -15221,10 +15221,10 @@
       <c r="B102" s="71"/>
       <c r="C102" s="91"/>
       <c r="D102" s="70"/>
-      <c r="E102" s="117"/>
-      <c r="F102" s="118"/>
-      <c r="G102" s="119"/>
-      <c r="H102" s="107"/>
+      <c r="E102" s="150"/>
+      <c r="F102" s="125"/>
+      <c r="G102" s="126"/>
+      <c r="H102" s="104"/>
       <c r="I102" s="112"/>
       <c r="J102" s="62"/>
       <c r="K102" s="20"/>
@@ -15342,16 +15342,16 @@
       <c r="A103" s="16"/>
       <c r="B103" s="71"/>
       <c r="C103" s="90"/>
-      <c r="D103" s="103" t="s">
+      <c r="D103" s="102" t="s">
         <v>77</v>
       </c>
-      <c r="E103" s="103"/>
-      <c r="F103" s="103"/>
-      <c r="G103" s="103"/>
-      <c r="H103" s="111">
+      <c r="E103" s="102"/>
+      <c r="F103" s="102"/>
+      <c r="G103" s="102"/>
+      <c r="H103" s="103">
         <v>45622</v>
       </c>
-      <c r="I103" s="113">
+      <c r="I103" s="109">
         <v>100</v>
       </c>
       <c r="J103" s="62"/>
@@ -15470,12 +15470,12 @@
       <c r="A104" s="16"/>
       <c r="B104" s="71"/>
       <c r="C104" s="90"/>
-      <c r="D104" s="103"/>
-      <c r="E104" s="103"/>
-      <c r="F104" s="103"/>
-      <c r="G104" s="103"/>
-      <c r="H104" s="107"/>
-      <c r="I104" s="143"/>
+      <c r="D104" s="102"/>
+      <c r="E104" s="102"/>
+      <c r="F104" s="102"/>
+      <c r="G104" s="102"/>
+      <c r="H104" s="104"/>
+      <c r="I104" s="110"/>
       <c r="J104" s="62"/>
       <c r="K104" s="20"/>
       <c r="L104" s="20"/>
@@ -15591,15 +15591,15 @@
     <row r="105" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A105" s="16"/>
       <c r="B105" s="71"/>
-      <c r="C105" s="187" t="s">
+      <c r="C105" s="143" t="s">
         <v>64</v>
       </c>
-      <c r="D105" s="188"/>
-      <c r="E105" s="188"/>
-      <c r="F105" s="188"/>
-      <c r="G105" s="189"/>
-      <c r="H105" s="127"/>
-      <c r="I105" s="128"/>
+      <c r="D105" s="144"/>
+      <c r="E105" s="144"/>
+      <c r="F105" s="144"/>
+      <c r="G105" s="145"/>
+      <c r="H105" s="190"/>
+      <c r="I105" s="188"/>
       <c r="J105" s="66"/>
       <c r="K105" s="64"/>
       <c r="L105" s="64"/>
@@ -15715,13 +15715,13 @@
     <row r="106" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A106" s="16"/>
       <c r="B106" s="71"/>
-      <c r="C106" s="190"/>
-      <c r="D106" s="191"/>
-      <c r="E106" s="191"/>
-      <c r="F106" s="191"/>
-      <c r="G106" s="192"/>
-      <c r="H106" s="127"/>
-      <c r="I106" s="128"/>
+      <c r="C106" s="146"/>
+      <c r="D106" s="147"/>
+      <c r="E106" s="147"/>
+      <c r="F106" s="147"/>
+      <c r="G106" s="148"/>
+      <c r="H106" s="190"/>
+      <c r="I106" s="188"/>
       <c r="J106" s="66"/>
       <c r="K106" s="64"/>
       <c r="L106" s="64"/>
@@ -15838,14 +15838,14 @@
       <c r="A107" s="16"/>
       <c r="B107" s="36"/>
       <c r="C107" s="78"/>
-      <c r="D107" s="132" t="s">
+      <c r="D107" s="115" t="s">
         <v>59</v>
       </c>
-      <c r="E107" s="133"/>
-      <c r="F107" s="133"/>
-      <c r="G107" s="134"/>
-      <c r="H107" s="127"/>
-      <c r="I107" s="128"/>
+      <c r="E107" s="116"/>
+      <c r="F107" s="116"/>
+      <c r="G107" s="117"/>
+      <c r="H107" s="190"/>
+      <c r="I107" s="188"/>
       <c r="J107" s="66"/>
       <c r="K107" s="64"/>
       <c r="L107" s="64"/>
@@ -15962,12 +15962,12 @@
       <c r="A108" s="16"/>
       <c r="B108" s="36"/>
       <c r="C108" s="76"/>
-      <c r="D108" s="135"/>
-      <c r="E108" s="136"/>
-      <c r="F108" s="136"/>
-      <c r="G108" s="137"/>
-      <c r="H108" s="127"/>
-      <c r="I108" s="128"/>
+      <c r="D108" s="118"/>
+      <c r="E108" s="119"/>
+      <c r="F108" s="119"/>
+      <c r="G108" s="120"/>
+      <c r="H108" s="190"/>
+      <c r="I108" s="188"/>
       <c r="J108" s="66"/>
       <c r="K108" s="64"/>
       <c r="L108" s="64"/>
@@ -16085,15 +16085,17 @@
       <c r="B109" s="36"/>
       <c r="C109" s="60"/>
       <c r="D109" s="70"/>
-      <c r="E109" s="105" t="s">
+      <c r="E109" s="149" t="s">
         <v>73</v>
       </c>
-      <c r="F109" s="105"/>
-      <c r="G109" s="105"/>
-      <c r="H109" s="111">
+      <c r="F109" s="149"/>
+      <c r="G109" s="149"/>
+      <c r="H109" s="103">
         <v>45624</v>
       </c>
-      <c r="I109" s="113"/>
+      <c r="I109" s="109">
+        <v>100</v>
+      </c>
       <c r="J109" s="62"/>
       <c r="K109" s="20"/>
       <c r="L109" s="20"/>
@@ -16211,11 +16213,11 @@
       <c r="B110" s="36"/>
       <c r="C110" s="60"/>
       <c r="D110" s="70"/>
-      <c r="E110" s="103"/>
-      <c r="F110" s="103"/>
-      <c r="G110" s="103"/>
-      <c r="H110" s="107"/>
-      <c r="I110" s="143"/>
+      <c r="E110" s="102"/>
+      <c r="F110" s="102"/>
+      <c r="G110" s="102"/>
+      <c r="H110" s="104"/>
+      <c r="I110" s="110"/>
       <c r="J110" s="62"/>
       <c r="K110" s="20"/>
       <c r="L110" s="20"/>
@@ -16333,15 +16335,15 @@
       <c r="B111" s="36"/>
       <c r="C111" s="60"/>
       <c r="D111" s="70"/>
-      <c r="E111" s="103" t="s">
+      <c r="E111" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="F111" s="103"/>
-      <c r="G111" s="103"/>
-      <c r="H111" s="111">
+      <c r="F111" s="102"/>
+      <c r="G111" s="102"/>
+      <c r="H111" s="103">
         <v>45625</v>
       </c>
-      <c r="I111" s="113"/>
+      <c r="I111" s="109"/>
       <c r="J111" s="62"/>
       <c r="K111" s="20"/>
       <c r="L111" s="20"/>
@@ -16459,11 +16461,11 @@
       <c r="B112" s="36"/>
       <c r="C112" s="60"/>
       <c r="D112" s="70"/>
-      <c r="E112" s="103"/>
-      <c r="F112" s="103"/>
-      <c r="G112" s="103"/>
-      <c r="H112" s="107"/>
-      <c r="I112" s="143"/>
+      <c r="E112" s="102"/>
+      <c r="F112" s="102"/>
+      <c r="G112" s="102"/>
+      <c r="H112" s="104"/>
+      <c r="I112" s="110"/>
       <c r="J112" s="62"/>
       <c r="K112" s="20"/>
       <c r="L112" s="20"/>
@@ -16581,13 +16583,13 @@
       <c r="B113" s="71"/>
       <c r="C113" s="91"/>
       <c r="D113" s="70"/>
-      <c r="E113" s="103" t="s">
+      <c r="E113" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="F113" s="103"/>
-      <c r="G113" s="103"/>
-      <c r="H113" s="110">
-        <v>45630</v>
+      <c r="F113" s="102"/>
+      <c r="G113" s="102"/>
+      <c r="H113" s="111">
+        <v>45629</v>
       </c>
       <c r="I113" s="112"/>
       <c r="J113" s="62"/>
@@ -16707,11 +16709,11 @@
       <c r="B114" s="71"/>
       <c r="C114" s="91"/>
       <c r="D114" s="70"/>
-      <c r="E114" s="125"/>
-      <c r="F114" s="125"/>
-      <c r="G114" s="125"/>
-      <c r="H114" s="111"/>
-      <c r="I114" s="113"/>
+      <c r="E114" s="198"/>
+      <c r="F114" s="198"/>
+      <c r="G114" s="198"/>
+      <c r="H114" s="103"/>
+      <c r="I114" s="109"/>
       <c r="J114" s="62"/>
       <c r="K114" s="20"/>
       <c r="L114" s="20"/>
@@ -16828,13 +16830,13 @@
       <c r="A115" s="16"/>
       <c r="B115" s="71"/>
       <c r="C115" s="91"/>
-      <c r="D115" s="103" t="s">
+      <c r="D115" s="102" t="s">
         <v>78</v>
       </c>
-      <c r="E115" s="103"/>
-      <c r="F115" s="103"/>
-      <c r="G115" s="103"/>
-      <c r="H115" s="110">
+      <c r="E115" s="102"/>
+      <c r="F115" s="102"/>
+      <c r="G115" s="102"/>
+      <c r="H115" s="111">
         <v>45625</v>
       </c>
       <c r="I115" s="112"/>
@@ -16954,11 +16956,11 @@
       <c r="A116" s="16"/>
       <c r="B116" s="71"/>
       <c r="C116" s="91"/>
-      <c r="D116" s="103"/>
-      <c r="E116" s="103"/>
-      <c r="F116" s="103"/>
-      <c r="G116" s="103"/>
-      <c r="H116" s="110"/>
+      <c r="D116" s="102"/>
+      <c r="E116" s="102"/>
+      <c r="F116" s="102"/>
+      <c r="G116" s="102"/>
+      <c r="H116" s="111"/>
       <c r="I116" s="112"/>
       <c r="J116" s="62"/>
       <c r="K116" s="20"/>
@@ -17076,14 +17078,14 @@
       <c r="A117" s="16"/>
       <c r="B117" s="36"/>
       <c r="C117" s="80"/>
-      <c r="D117" s="132" t="s">
+      <c r="D117" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="E117" s="133"/>
-      <c r="F117" s="133"/>
-      <c r="G117" s="134"/>
-      <c r="H117" s="121"/>
-      <c r="I117" s="129"/>
+      <c r="E117" s="116"/>
+      <c r="F117" s="116"/>
+      <c r="G117" s="117"/>
+      <c r="H117" s="191"/>
+      <c r="I117" s="181"/>
       <c r="J117" s="63"/>
       <c r="K117" s="64"/>
       <c r="L117" s="64"/>
@@ -17200,12 +17202,12 @@
       <c r="A118" s="16"/>
       <c r="B118" s="36"/>
       <c r="C118" s="80"/>
-      <c r="D118" s="135"/>
-      <c r="E118" s="136"/>
-      <c r="F118" s="136"/>
-      <c r="G118" s="137"/>
-      <c r="H118" s="122"/>
-      <c r="I118" s="130"/>
+      <c r="D118" s="118"/>
+      <c r="E118" s="119"/>
+      <c r="F118" s="119"/>
+      <c r="G118" s="120"/>
+      <c r="H118" s="192"/>
+      <c r="I118" s="182"/>
       <c r="J118" s="63"/>
       <c r="K118" s="64"/>
       <c r="L118" s="64"/>
@@ -17323,15 +17325,15 @@
       <c r="B119" s="36"/>
       <c r="C119" s="60"/>
       <c r="D119" s="70"/>
-      <c r="E119" s="105" t="s">
+      <c r="E119" s="149" t="s">
         <v>68</v>
       </c>
-      <c r="F119" s="105"/>
-      <c r="G119" s="105"/>
-      <c r="H119" s="111">
+      <c r="F119" s="149"/>
+      <c r="G119" s="149"/>
+      <c r="H119" s="103">
         <v>45629</v>
       </c>
-      <c r="I119" s="126"/>
+      <c r="I119" s="105"/>
       <c r="J119" s="19"/>
       <c r="K119" s="20"/>
       <c r="L119" s="20"/>
@@ -17449,11 +17451,11 @@
       <c r="B120" s="36"/>
       <c r="C120" s="60"/>
       <c r="D120" s="70"/>
-      <c r="E120" s="103"/>
-      <c r="F120" s="103"/>
-      <c r="G120" s="103"/>
-      <c r="H120" s="107"/>
-      <c r="I120" s="109"/>
+      <c r="E120" s="102"/>
+      <c r="F120" s="102"/>
+      <c r="G120" s="102"/>
+      <c r="H120" s="104"/>
+      <c r="I120" s="106"/>
       <c r="J120" s="19"/>
       <c r="K120" s="20"/>
       <c r="L120" s="20"/>
@@ -17571,15 +17573,15 @@
       <c r="B121" s="36"/>
       <c r="C121" s="60"/>
       <c r="D121" s="70"/>
-      <c r="E121" s="103" t="s">
+      <c r="E121" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="F121" s="103"/>
-      <c r="G121" s="103"/>
-      <c r="H121" s="111">
+      <c r="F121" s="102"/>
+      <c r="G121" s="102"/>
+      <c r="H121" s="103">
         <v>45630</v>
       </c>
-      <c r="I121" s="126"/>
+      <c r="I121" s="105"/>
       <c r="J121" s="19"/>
       <c r="K121" s="20"/>
       <c r="L121" s="20"/>
@@ -17697,11 +17699,11 @@
       <c r="B122" s="36"/>
       <c r="C122" s="60"/>
       <c r="D122" s="70"/>
-      <c r="E122" s="103"/>
-      <c r="F122" s="103"/>
-      <c r="G122" s="103"/>
-      <c r="H122" s="107"/>
-      <c r="I122" s="109"/>
+      <c r="E122" s="102"/>
+      <c r="F122" s="102"/>
+      <c r="G122" s="102"/>
+      <c r="H122" s="104"/>
+      <c r="I122" s="106"/>
       <c r="J122" s="19"/>
       <c r="K122" s="20"/>
       <c r="L122" s="20"/>
@@ -17819,12 +17821,12 @@
       <c r="B123" s="36"/>
       <c r="C123" s="60"/>
       <c r="D123" s="70"/>
-      <c r="E123" s="103" t="s">
+      <c r="E123" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="F123" s="103"/>
-      <c r="G123" s="103"/>
-      <c r="H123" s="120">
+      <c r="F123" s="102"/>
+      <c r="G123" s="102"/>
+      <c r="H123" s="197">
         <v>45631</v>
       </c>
       <c r="I123" s="112"/>
@@ -17945,10 +17947,10 @@
       <c r="B124" s="36"/>
       <c r="C124" s="60"/>
       <c r="D124" s="70"/>
-      <c r="E124" s="103"/>
-      <c r="F124" s="103"/>
-      <c r="G124" s="103"/>
-      <c r="H124" s="120"/>
+      <c r="E124" s="102"/>
+      <c r="F124" s="102"/>
+      <c r="G124" s="102"/>
+      <c r="H124" s="197"/>
       <c r="I124" s="112"/>
       <c r="J124" s="62"/>
       <c r="K124" s="20"/>
@@ -18067,12 +18069,12 @@
       <c r="B125" s="36"/>
       <c r="C125" s="60"/>
       <c r="D125" s="70"/>
-      <c r="E125" s="103" t="s">
+      <c r="E125" s="102" t="s">
         <v>71</v>
       </c>
-      <c r="F125" s="103"/>
-      <c r="G125" s="103"/>
-      <c r="H125" s="110">
+      <c r="F125" s="102"/>
+      <c r="G125" s="102"/>
+      <c r="H125" s="111">
         <v>45632</v>
       </c>
       <c r="I125" s="112"/>
@@ -18193,10 +18195,10 @@
       <c r="B126" s="36"/>
       <c r="C126" s="60"/>
       <c r="D126" s="70"/>
-      <c r="E126" s="103"/>
-      <c r="F126" s="103"/>
-      <c r="G126" s="103"/>
-      <c r="H126" s="110"/>
+      <c r="E126" s="102"/>
+      <c r="F126" s="102"/>
+      <c r="G126" s="102"/>
+      <c r="H126" s="111"/>
       <c r="I126" s="112"/>
       <c r="J126" s="62"/>
       <c r="K126" s="20"/>
@@ -18315,15 +18317,15 @@
       <c r="B127" s="36"/>
       <c r="C127" s="60"/>
       <c r="D127" s="70"/>
-      <c r="E127" s="103" t="s">
+      <c r="E127" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="F127" s="103"/>
-      <c r="G127" s="103"/>
-      <c r="H127" s="111">
+      <c r="F127" s="102"/>
+      <c r="G127" s="102"/>
+      <c r="H127" s="103">
         <v>45635</v>
       </c>
-      <c r="I127" s="126"/>
+      <c r="I127" s="105"/>
       <c r="J127" s="19"/>
       <c r="K127" s="20"/>
       <c r="L127" s="20"/>
@@ -18441,11 +18443,11 @@
       <c r="B128" s="36"/>
       <c r="C128" s="60"/>
       <c r="D128" s="70"/>
-      <c r="E128" s="125"/>
-      <c r="F128" s="125"/>
-      <c r="G128" s="125"/>
-      <c r="H128" s="107"/>
-      <c r="I128" s="109"/>
+      <c r="E128" s="198"/>
+      <c r="F128" s="198"/>
+      <c r="G128" s="198"/>
+      <c r="H128" s="104"/>
+      <c r="I128" s="106"/>
       <c r="J128" s="19"/>
       <c r="K128" s="20"/>
       <c r="L128" s="20"/>
@@ -18563,12 +18565,12 @@
       <c r="B129" s="71"/>
       <c r="C129" s="91"/>
       <c r="D129" s="70"/>
-      <c r="E129" s="114" t="s">
+      <c r="E129" s="189" t="s">
         <v>61</v>
       </c>
-      <c r="F129" s="115"/>
-      <c r="G129" s="116"/>
-      <c r="H129" s="110">
+      <c r="F129" s="121"/>
+      <c r="G129" s="122"/>
+      <c r="H129" s="111">
         <v>45638</v>
       </c>
       <c r="I129" s="112"/>
@@ -18689,10 +18691,10 @@
       <c r="B130" s="71"/>
       <c r="C130" s="91"/>
       <c r="D130" s="70"/>
-      <c r="E130" s="117"/>
-      <c r="F130" s="118"/>
-      <c r="G130" s="119"/>
-      <c r="H130" s="110"/>
+      <c r="E130" s="150"/>
+      <c r="F130" s="125"/>
+      <c r="G130" s="126"/>
+      <c r="H130" s="111"/>
       <c r="I130" s="112"/>
       <c r="J130" s="62"/>
       <c r="K130" s="20"/>
@@ -18810,16 +18812,16 @@
       <c r="A131" s="16"/>
       <c r="B131" s="71"/>
       <c r="C131" s="91"/>
-      <c r="D131" s="103" t="s">
+      <c r="D131" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="E131" s="103"/>
-      <c r="F131" s="103"/>
-      <c r="G131" s="103"/>
-      <c r="H131" s="111">
+      <c r="E131" s="102"/>
+      <c r="F131" s="102"/>
+      <c r="G131" s="102"/>
+      <c r="H131" s="103">
         <v>45635</v>
       </c>
-      <c r="I131" s="113"/>
+      <c r="I131" s="109"/>
       <c r="J131" s="62"/>
       <c r="K131" s="20"/>
       <c r="L131" s="20"/>
@@ -18936,12 +18938,12 @@
       <c r="A132" s="16"/>
       <c r="B132" s="71"/>
       <c r="C132" s="90"/>
-      <c r="D132" s="103"/>
-      <c r="E132" s="103"/>
-      <c r="F132" s="103"/>
-      <c r="G132" s="103"/>
-      <c r="H132" s="107"/>
-      <c r="I132" s="143"/>
+      <c r="D132" s="102"/>
+      <c r="E132" s="102"/>
+      <c r="F132" s="102"/>
+      <c r="G132" s="102"/>
+      <c r="H132" s="104"/>
+      <c r="I132" s="110"/>
       <c r="J132" s="62"/>
       <c r="K132" s="20"/>
       <c r="L132" s="20"/>
@@ -19057,15 +19059,15 @@
     <row r="133" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A133" s="16"/>
       <c r="B133" s="36"/>
-      <c r="C133" s="132" t="s">
+      <c r="C133" s="115" t="s">
         <v>67</v>
       </c>
-      <c r="D133" s="133"/>
-      <c r="E133" s="133"/>
-      <c r="F133" s="133"/>
-      <c r="G133" s="134"/>
-      <c r="H133" s="121"/>
-      <c r="I133" s="123"/>
+      <c r="D133" s="116"/>
+      <c r="E133" s="116"/>
+      <c r="F133" s="116"/>
+      <c r="G133" s="117"/>
+      <c r="H133" s="191"/>
+      <c r="I133" s="107"/>
       <c r="J133" s="66"/>
       <c r="K133" s="64"/>
       <c r="L133" s="64"/>
@@ -19181,13 +19183,13 @@
     <row r="134" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A134" s="16"/>
       <c r="B134" s="36"/>
-      <c r="C134" s="135"/>
-      <c r="D134" s="136"/>
-      <c r="E134" s="136"/>
-      <c r="F134" s="136"/>
-      <c r="G134" s="137"/>
-      <c r="H134" s="122"/>
-      <c r="I134" s="124"/>
+      <c r="C134" s="118"/>
+      <c r="D134" s="119"/>
+      <c r="E134" s="119"/>
+      <c r="F134" s="119"/>
+      <c r="G134" s="120"/>
+      <c r="H134" s="192"/>
+      <c r="I134" s="108"/>
       <c r="J134" s="66"/>
       <c r="K134" s="64"/>
       <c r="L134" s="64"/>
@@ -19304,14 +19306,14 @@
       <c r="A135" s="16"/>
       <c r="B135" s="36"/>
       <c r="C135" s="60"/>
-      <c r="D135" s="132" t="s">
+      <c r="D135" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="133"/>
-      <c r="F135" s="133"/>
-      <c r="G135" s="134"/>
-      <c r="H135" s="193"/>
-      <c r="I135" s="129"/>
+      <c r="E135" s="116"/>
+      <c r="F135" s="116"/>
+      <c r="G135" s="117"/>
+      <c r="H135" s="113"/>
+      <c r="I135" s="181"/>
       <c r="J135" s="63"/>
       <c r="K135" s="64"/>
       <c r="L135" s="64"/>
@@ -19428,12 +19430,12 @@
       <c r="A136" s="16"/>
       <c r="B136" s="36"/>
       <c r="C136" s="60"/>
-      <c r="D136" s="135"/>
-      <c r="E136" s="136"/>
-      <c r="F136" s="136"/>
-      <c r="G136" s="137"/>
-      <c r="H136" s="198"/>
-      <c r="I136" s="144"/>
+      <c r="D136" s="118"/>
+      <c r="E136" s="119"/>
+      <c r="F136" s="119"/>
+      <c r="G136" s="120"/>
+      <c r="H136" s="130"/>
+      <c r="I136" s="183"/>
       <c r="J136" s="63"/>
       <c r="K136" s="64"/>
       <c r="L136" s="64"/>
@@ -19551,15 +19553,15 @@
       <c r="B137" s="36"/>
       <c r="C137" s="72"/>
       <c r="D137" s="74"/>
-      <c r="E137" s="115" t="s">
+      <c r="E137" s="121" t="s">
         <v>73</v>
       </c>
-      <c r="F137" s="115"/>
-      <c r="G137" s="116"/>
-      <c r="H137" s="111">
+      <c r="F137" s="121"/>
+      <c r="G137" s="122"/>
+      <c r="H137" s="103">
         <v>45636</v>
       </c>
-      <c r="I137" s="113"/>
+      <c r="I137" s="109"/>
       <c r="J137" s="62"/>
       <c r="K137" s="20"/>
       <c r="L137" s="20"/>
@@ -19677,11 +19679,11 @@
       <c r="B138" s="36"/>
       <c r="C138" s="72"/>
       <c r="D138" s="70"/>
-      <c r="E138" s="185"/>
-      <c r="F138" s="185"/>
-      <c r="G138" s="186"/>
-      <c r="H138" s="107"/>
-      <c r="I138" s="143"/>
+      <c r="E138" s="123"/>
+      <c r="F138" s="123"/>
+      <c r="G138" s="124"/>
+      <c r="H138" s="104"/>
+      <c r="I138" s="110"/>
       <c r="J138" s="62"/>
       <c r="K138" s="20"/>
       <c r="L138" s="20"/>
@@ -19799,15 +19801,15 @@
       <c r="B139" s="36"/>
       <c r="C139" s="72"/>
       <c r="D139" s="70"/>
-      <c r="E139" s="115" t="s">
+      <c r="E139" s="121" t="s">
         <v>74</v>
       </c>
-      <c r="F139" s="115"/>
-      <c r="G139" s="116"/>
-      <c r="H139" s="111">
+      <c r="F139" s="121"/>
+      <c r="G139" s="122"/>
+      <c r="H139" s="103">
         <v>45637</v>
       </c>
-      <c r="I139" s="113"/>
+      <c r="I139" s="109"/>
       <c r="J139" s="62"/>
       <c r="K139" s="20"/>
       <c r="L139" s="20"/>
@@ -19925,11 +19927,11 @@
       <c r="B140" s="36"/>
       <c r="C140" s="72"/>
       <c r="D140" s="70"/>
-      <c r="E140" s="118"/>
-      <c r="F140" s="118"/>
-      <c r="G140" s="119"/>
-      <c r="H140" s="107"/>
-      <c r="I140" s="143"/>
+      <c r="E140" s="125"/>
+      <c r="F140" s="125"/>
+      <c r="G140" s="126"/>
+      <c r="H140" s="104"/>
+      <c r="I140" s="110"/>
       <c r="J140" s="62"/>
       <c r="K140" s="20"/>
       <c r="L140" s="20"/>
@@ -20046,13 +20048,13 @@
       <c r="A141" s="16"/>
       <c r="B141" s="36"/>
       <c r="C141" s="82"/>
-      <c r="D141" s="103" t="s">
+      <c r="D141" s="102" t="s">
         <v>80</v>
       </c>
-      <c r="E141" s="103"/>
-      <c r="F141" s="103"/>
-      <c r="G141" s="103"/>
-      <c r="H141" s="111">
+      <c r="E141" s="102"/>
+      <c r="F141" s="102"/>
+      <c r="G141" s="102"/>
+      <c r="H141" s="103">
         <v>45637</v>
       </c>
       <c r="I141" s="92"/>
@@ -20172,11 +20174,11 @@
       <c r="A142" s="16"/>
       <c r="B142" s="36"/>
       <c r="C142" s="82"/>
-      <c r="D142" s="103"/>
-      <c r="E142" s="103"/>
-      <c r="F142" s="103"/>
-      <c r="G142" s="103"/>
-      <c r="H142" s="107"/>
+      <c r="D142" s="102"/>
+      <c r="E142" s="102"/>
+      <c r="F142" s="102"/>
+      <c r="G142" s="102"/>
+      <c r="H142" s="104"/>
       <c r="I142" s="92"/>
       <c r="J142" s="62"/>
       <c r="K142" s="20"/>
@@ -20294,14 +20296,14 @@
       <c r="A143" s="16"/>
       <c r="B143" s="36"/>
       <c r="C143" s="72"/>
-      <c r="D143" s="195" t="s">
+      <c r="D143" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="E143" s="196"/>
-      <c r="F143" s="196"/>
-      <c r="G143" s="197"/>
-      <c r="H143" s="193"/>
-      <c r="I143" s="123"/>
+      <c r="E143" s="128"/>
+      <c r="F143" s="128"/>
+      <c r="G143" s="129"/>
+      <c r="H143" s="113"/>
+      <c r="I143" s="107"/>
       <c r="J143" s="66"/>
       <c r="K143" s="64"/>
       <c r="L143" s="64"/>
@@ -20418,12 +20420,12 @@
       <c r="A144" s="16"/>
       <c r="B144" s="36"/>
       <c r="C144" s="72"/>
-      <c r="D144" s="135"/>
-      <c r="E144" s="136"/>
-      <c r="F144" s="136"/>
-      <c r="G144" s="137"/>
-      <c r="H144" s="194"/>
-      <c r="I144" s="124"/>
+      <c r="D144" s="118"/>
+      <c r="E144" s="119"/>
+      <c r="F144" s="119"/>
+      <c r="G144" s="120"/>
+      <c r="H144" s="114"/>
+      <c r="I144" s="108"/>
       <c r="J144" s="66"/>
       <c r="K144" s="64"/>
       <c r="L144" s="64"/>
@@ -20541,15 +20543,15 @@
       <c r="B145" s="36"/>
       <c r="C145" s="72"/>
       <c r="D145" s="74"/>
-      <c r="E145" s="115" t="s">
+      <c r="E145" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="F145" s="115"/>
-      <c r="G145" s="116"/>
-      <c r="H145" s="111">
+      <c r="F145" s="121"/>
+      <c r="G145" s="122"/>
+      <c r="H145" s="103">
         <v>45639</v>
       </c>
-      <c r="I145" s="113"/>
+      <c r="I145" s="109"/>
       <c r="J145" s="62"/>
       <c r="K145" s="20"/>
       <c r="L145" s="20"/>
@@ -20667,11 +20669,11 @@
       <c r="B146" s="36"/>
       <c r="C146" s="72"/>
       <c r="D146" s="70"/>
-      <c r="E146" s="185"/>
-      <c r="F146" s="185"/>
-      <c r="G146" s="186"/>
-      <c r="H146" s="107"/>
-      <c r="I146" s="143"/>
+      <c r="E146" s="123"/>
+      <c r="F146" s="123"/>
+      <c r="G146" s="124"/>
+      <c r="H146" s="104"/>
+      <c r="I146" s="110"/>
       <c r="J146" s="62"/>
       <c r="K146" s="20"/>
       <c r="L146" s="20"/>
@@ -20789,15 +20791,15 @@
       <c r="B147" s="36"/>
       <c r="C147" s="72"/>
       <c r="D147" s="70"/>
-      <c r="E147" s="115" t="s">
+      <c r="E147" s="121" t="s">
         <v>69</v>
       </c>
-      <c r="F147" s="115"/>
-      <c r="G147" s="116"/>
-      <c r="H147" s="111">
+      <c r="F147" s="121"/>
+      <c r="G147" s="122"/>
+      <c r="H147" s="103">
         <v>45642</v>
       </c>
-      <c r="I147" s="113"/>
+      <c r="I147" s="109"/>
       <c r="J147" s="62"/>
       <c r="K147" s="20"/>
       <c r="L147" s="20"/>
@@ -20915,11 +20917,11 @@
       <c r="B148" s="36"/>
       <c r="C148" s="72"/>
       <c r="D148" s="70"/>
-      <c r="E148" s="185"/>
-      <c r="F148" s="185"/>
-      <c r="G148" s="186"/>
-      <c r="H148" s="107"/>
-      <c r="I148" s="143"/>
+      <c r="E148" s="123"/>
+      <c r="F148" s="123"/>
+      <c r="G148" s="124"/>
+      <c r="H148" s="104"/>
+      <c r="I148" s="110"/>
       <c r="J148" s="62"/>
       <c r="K148" s="20"/>
       <c r="L148" s="20"/>
@@ -21037,15 +21039,15 @@
       <c r="B149" s="36"/>
       <c r="C149" s="72"/>
       <c r="D149" s="70"/>
-      <c r="E149" s="115" t="s">
+      <c r="E149" s="121" t="s">
         <v>70</v>
       </c>
-      <c r="F149" s="115"/>
-      <c r="G149" s="116"/>
-      <c r="H149" s="111">
+      <c r="F149" s="121"/>
+      <c r="G149" s="122"/>
+      <c r="H149" s="103">
         <v>45643</v>
       </c>
-      <c r="I149" s="113"/>
+      <c r="I149" s="109"/>
       <c r="J149" s="62"/>
       <c r="K149" s="20"/>
       <c r="L149" s="20"/>
@@ -21163,11 +21165,11 @@
       <c r="B150" s="36"/>
       <c r="C150" s="72"/>
       <c r="D150" s="70"/>
-      <c r="E150" s="185"/>
-      <c r="F150" s="185"/>
-      <c r="G150" s="186"/>
-      <c r="H150" s="107"/>
-      <c r="I150" s="143"/>
+      <c r="E150" s="123"/>
+      <c r="F150" s="123"/>
+      <c r="G150" s="124"/>
+      <c r="H150" s="104"/>
+      <c r="I150" s="110"/>
       <c r="J150" s="62"/>
       <c r="K150" s="20"/>
       <c r="L150" s="20"/>
@@ -21285,15 +21287,15 @@
       <c r="B151" s="36"/>
       <c r="C151" s="72"/>
       <c r="D151" s="70"/>
-      <c r="E151" s="103" t="s">
+      <c r="E151" s="102" t="s">
         <v>75</v>
       </c>
-      <c r="F151" s="103"/>
-      <c r="G151" s="103"/>
-      <c r="H151" s="111">
+      <c r="F151" s="102"/>
+      <c r="G151" s="102"/>
+      <c r="H151" s="103">
         <v>45644</v>
       </c>
-      <c r="I151" s="113"/>
+      <c r="I151" s="109"/>
       <c r="J151" s="62"/>
       <c r="K151" s="20"/>
       <c r="L151" s="20"/>
@@ -21411,11 +21413,11 @@
       <c r="B152" s="36"/>
       <c r="C152" s="72"/>
       <c r="D152" s="70"/>
-      <c r="E152" s="103"/>
-      <c r="F152" s="103"/>
-      <c r="G152" s="103"/>
-      <c r="H152" s="107"/>
-      <c r="I152" s="143"/>
+      <c r="E152" s="102"/>
+      <c r="F152" s="102"/>
+      <c r="G152" s="102"/>
+      <c r="H152" s="104"/>
+      <c r="I152" s="110"/>
       <c r="J152" s="62"/>
       <c r="K152" s="20"/>
       <c r="L152" s="20"/>
@@ -21533,15 +21535,15 @@
       <c r="B153" s="36"/>
       <c r="C153" s="72"/>
       <c r="D153" s="70"/>
-      <c r="E153" s="103" t="s">
+      <c r="E153" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="F153" s="103"/>
-      <c r="G153" s="103"/>
-      <c r="H153" s="111">
+      <c r="F153" s="102"/>
+      <c r="G153" s="102"/>
+      <c r="H153" s="103">
         <v>45644</v>
       </c>
-      <c r="I153" s="113"/>
+      <c r="I153" s="109"/>
       <c r="J153" s="62"/>
       <c r="K153" s="20"/>
       <c r="L153" s="20"/>
@@ -21659,11 +21661,11 @@
       <c r="B154" s="36"/>
       <c r="C154" s="72"/>
       <c r="D154" s="70"/>
-      <c r="E154" s="103"/>
-      <c r="F154" s="103"/>
-      <c r="G154" s="103"/>
-      <c r="H154" s="107"/>
-      <c r="I154" s="143"/>
+      <c r="E154" s="102"/>
+      <c r="F154" s="102"/>
+      <c r="G154" s="102"/>
+      <c r="H154" s="104"/>
+      <c r="I154" s="110"/>
       <c r="J154" s="62"/>
       <c r="K154" s="20"/>
       <c r="L154" s="20"/>
@@ -21780,16 +21782,16 @@
       <c r="A155" s="1"/>
       <c r="B155" s="18"/>
       <c r="C155" s="60"/>
-      <c r="D155" s="104"/>
-      <c r="E155" s="102" t="s">
+      <c r="D155" s="194"/>
+      <c r="E155" s="193" t="s">
         <v>61</v>
       </c>
-      <c r="F155" s="103"/>
-      <c r="G155" s="103"/>
-      <c r="H155" s="106">
+      <c r="F155" s="102"/>
+      <c r="G155" s="102"/>
+      <c r="H155" s="195">
         <v>45645</v>
       </c>
-      <c r="I155" s="108"/>
+      <c r="I155" s="196"/>
       <c r="J155" s="19"/>
       <c r="K155" s="20"/>
       <c r="L155" s="20"/>
@@ -21906,12 +21908,12 @@
       <c r="A156" s="1"/>
       <c r="B156" s="18"/>
       <c r="C156" s="60"/>
-      <c r="D156" s="105"/>
-      <c r="E156" s="102"/>
-      <c r="F156" s="103"/>
-      <c r="G156" s="103"/>
-      <c r="H156" s="107"/>
-      <c r="I156" s="109"/>
+      <c r="D156" s="149"/>
+      <c r="E156" s="193"/>
+      <c r="F156" s="102"/>
+      <c r="G156" s="102"/>
+      <c r="H156" s="104"/>
+      <c r="I156" s="106"/>
       <c r="J156" s="19"/>
       <c r="K156" s="20"/>
       <c r="L156" s="20"/>
@@ -22028,16 +22030,16 @@
       <c r="A157" s="1"/>
       <c r="B157" s="93"/>
       <c r="C157" s="90"/>
-      <c r="D157" s="103" t="s">
+      <c r="D157" s="102" t="s">
         <v>81</v>
       </c>
-      <c r="E157" s="103"/>
-      <c r="F157" s="103"/>
-      <c r="G157" s="103"/>
-      <c r="H157" s="111">
+      <c r="E157" s="102"/>
+      <c r="F157" s="102"/>
+      <c r="G157" s="102"/>
+      <c r="H157" s="103">
         <v>45644</v>
       </c>
-      <c r="I157" s="126"/>
+      <c r="I157" s="105"/>
       <c r="J157" s="19"/>
       <c r="K157" s="20"/>
       <c r="L157" s="20"/>
@@ -22154,12 +22156,12 @@
       <c r="A158" s="1"/>
       <c r="B158" s="93"/>
       <c r="C158" s="90"/>
-      <c r="D158" s="103"/>
-      <c r="E158" s="103"/>
-      <c r="F158" s="103"/>
-      <c r="G158" s="103"/>
-      <c r="H158" s="107"/>
-      <c r="I158" s="109"/>
+      <c r="D158" s="102"/>
+      <c r="E158" s="102"/>
+      <c r="F158" s="102"/>
+      <c r="G158" s="102"/>
+      <c r="H158" s="104"/>
+      <c r="I158" s="106"/>
       <c r="J158" s="19"/>
       <c r="K158" s="20"/>
       <c r="L158" s="20"/>
@@ -22277,14 +22279,14 @@
       <c r="B159" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="C159" s="151" t="s">
+      <c r="C159" s="173" t="s">
         <v>31</v>
       </c>
-      <c r="D159" s="152"/>
-      <c r="E159" s="152"/>
-      <c r="F159" s="152"/>
-      <c r="G159" s="153"/>
-      <c r="H159" s="138" t="s">
+      <c r="D159" s="174"/>
+      <c r="E159" s="174"/>
+      <c r="F159" s="174"/>
+      <c r="G159" s="175"/>
+      <c r="H159" s="184" t="s">
         <v>57</v>
       </c>
       <c r="I159" s="112"/>
@@ -22403,11 +22405,11 @@
     <row r="160" spans="1:120" ht="9.75" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="87"/>
-      <c r="C160" s="154"/>
-      <c r="D160" s="155"/>
-      <c r="E160" s="155"/>
-      <c r="F160" s="155"/>
-      <c r="G160" s="156"/>
+      <c r="C160" s="176"/>
+      <c r="D160" s="177"/>
+      <c r="E160" s="177"/>
+      <c r="F160" s="177"/>
+      <c r="G160" s="178"/>
       <c r="H160" s="112"/>
       <c r="I160" s="112"/>
       <c r="J160" s="14"/>
@@ -22769,14 +22771,14 @@
     <row r="163" spans="1:120" ht="9.75" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
-      <c r="C163" s="145" t="s">
+      <c r="C163" s="168" t="s">
         <v>33</v>
       </c>
-      <c r="D163" s="146"/>
-      <c r="E163" s="146"/>
-      <c r="F163" s="146"/>
-      <c r="G163" s="147"/>
-      <c r="H163" s="138" t="s">
+      <c r="D163" s="140"/>
+      <c r="E163" s="140"/>
+      <c r="F163" s="140"/>
+      <c r="G163" s="169"/>
+      <c r="H163" s="184" t="s">
         <v>56</v>
       </c>
       <c r="I163" s="112"/>
@@ -22895,11 +22897,11 @@
     <row r="164" spans="1:120" ht="9.75" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
-      <c r="C164" s="148"/>
-      <c r="D164" s="149"/>
-      <c r="E164" s="149"/>
-      <c r="F164" s="149"/>
-      <c r="G164" s="150"/>
+      <c r="C164" s="170"/>
+      <c r="D164" s="171"/>
+      <c r="E164" s="171"/>
+      <c r="F164" s="171"/>
+      <c r="G164" s="172"/>
       <c r="H164" s="112"/>
       <c r="I164" s="112"/>
       <c r="J164" s="19"/>
@@ -36440,6 +36442,222 @@
     </row>
   </sheetData>
   <mergeCells count="240">
+    <mergeCell ref="E155:G156"/>
+    <mergeCell ref="D155:D156"/>
+    <mergeCell ref="H155:H156"/>
+    <mergeCell ref="I155:I156"/>
+    <mergeCell ref="H113:H114"/>
+    <mergeCell ref="I113:I114"/>
+    <mergeCell ref="H129:H130"/>
+    <mergeCell ref="I129:I130"/>
+    <mergeCell ref="E129:G130"/>
+    <mergeCell ref="H123:H124"/>
+    <mergeCell ref="I123:I124"/>
+    <mergeCell ref="I125:I126"/>
+    <mergeCell ref="H125:H126"/>
+    <mergeCell ref="H133:H134"/>
+    <mergeCell ref="I133:I134"/>
+    <mergeCell ref="E123:G124"/>
+    <mergeCell ref="E125:G126"/>
+    <mergeCell ref="E127:G128"/>
+    <mergeCell ref="E113:G114"/>
+    <mergeCell ref="E119:G120"/>
+    <mergeCell ref="E121:G122"/>
+    <mergeCell ref="H127:H128"/>
+    <mergeCell ref="I127:I128"/>
+    <mergeCell ref="H121:H122"/>
+    <mergeCell ref="H105:H106"/>
+    <mergeCell ref="I105:I106"/>
+    <mergeCell ref="H107:H108"/>
+    <mergeCell ref="I107:I108"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="H117:H118"/>
+    <mergeCell ref="I117:I118"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="I119:I120"/>
+    <mergeCell ref="H101:H102"/>
+    <mergeCell ref="I101:I102"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="I85:I86"/>
+    <mergeCell ref="H89:H90"/>
+    <mergeCell ref="I89:I90"/>
+    <mergeCell ref="E81:G82"/>
+    <mergeCell ref="E83:G84"/>
+    <mergeCell ref="E91:G92"/>
+    <mergeCell ref="E93:G94"/>
+    <mergeCell ref="E95:G96"/>
+    <mergeCell ref="E97:G98"/>
+    <mergeCell ref="E99:G100"/>
+    <mergeCell ref="E85:G86"/>
+    <mergeCell ref="D89:G90"/>
+    <mergeCell ref="H75:H76"/>
+    <mergeCell ref="H159:H160"/>
+    <mergeCell ref="H163:H164"/>
+    <mergeCell ref="H161:H162"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="H59:H60"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="H77:H78"/>
+    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="H93:H94"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="H111:H112"/>
+    <mergeCell ref="I163:I164"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="I159:I160"/>
+    <mergeCell ref="I161:I162"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="I93:I94"/>
+    <mergeCell ref="I95:I96"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="I109:I110"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="I153:I154"/>
+    <mergeCell ref="I151:I152"/>
+    <mergeCell ref="I149:I150"/>
+    <mergeCell ref="I147:I148"/>
+    <mergeCell ref="I145:I146"/>
+    <mergeCell ref="I111:I112"/>
+    <mergeCell ref="I135:I136"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I67:I68"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="C163:G164"/>
+    <mergeCell ref="C159:G160"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="C31:G32"/>
+    <mergeCell ref="D33:G34"/>
+    <mergeCell ref="E35:G36"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="E43:G44"/>
+    <mergeCell ref="E45:G46"/>
+    <mergeCell ref="E47:G48"/>
+    <mergeCell ref="E49:G50"/>
+    <mergeCell ref="E51:G52"/>
+    <mergeCell ref="D53:G54"/>
+    <mergeCell ref="E55:G56"/>
+    <mergeCell ref="E57:G58"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="J3:CJ3"/>
+    <mergeCell ref="CK3:DO3"/>
+    <mergeCell ref="J4:AA4"/>
+    <mergeCell ref="AB4:BE4"/>
+    <mergeCell ref="BF4:CJ4"/>
+    <mergeCell ref="CK4:DO4"/>
+    <mergeCell ref="B7:G8"/>
+    <mergeCell ref="C9:G10"/>
+    <mergeCell ref="C11:G12"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="D13:G14"/>
+    <mergeCell ref="D15:G16"/>
+    <mergeCell ref="D17:G18"/>
+    <mergeCell ref="D19:G20"/>
+    <mergeCell ref="C21:G22"/>
+    <mergeCell ref="D23:G24"/>
+    <mergeCell ref="C25:G26"/>
+    <mergeCell ref="D27:G28"/>
+    <mergeCell ref="D29:G30"/>
+    <mergeCell ref="E147:G148"/>
+    <mergeCell ref="E149:G150"/>
+    <mergeCell ref="E151:G152"/>
+    <mergeCell ref="E59:G60"/>
+    <mergeCell ref="E61:G62"/>
+    <mergeCell ref="D63:G64"/>
+    <mergeCell ref="E67:G68"/>
+    <mergeCell ref="E65:G66"/>
+    <mergeCell ref="E69:G70"/>
+    <mergeCell ref="E71:G72"/>
+    <mergeCell ref="C73:G74"/>
+    <mergeCell ref="C75:G76"/>
+    <mergeCell ref="C77:G78"/>
+    <mergeCell ref="D79:G80"/>
+    <mergeCell ref="E109:G110"/>
+    <mergeCell ref="E111:G112"/>
+    <mergeCell ref="E101:G102"/>
+    <mergeCell ref="C105:G106"/>
+    <mergeCell ref="D107:G108"/>
+    <mergeCell ref="D117:G118"/>
+    <mergeCell ref="H145:H146"/>
+    <mergeCell ref="H143:H144"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="C133:G134"/>
+    <mergeCell ref="D135:G136"/>
+    <mergeCell ref="E137:G138"/>
+    <mergeCell ref="E139:G140"/>
+    <mergeCell ref="D143:G144"/>
+    <mergeCell ref="E145:G146"/>
+    <mergeCell ref="H135:H136"/>
     <mergeCell ref="D157:G158"/>
     <mergeCell ref="H157:H158"/>
     <mergeCell ref="I157:I158"/>
@@ -36464,222 +36682,6 @@
     <mergeCell ref="H151:H152"/>
     <mergeCell ref="H149:H150"/>
     <mergeCell ref="H147:H148"/>
-    <mergeCell ref="H145:H146"/>
-    <mergeCell ref="H143:H144"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="C133:G134"/>
-    <mergeCell ref="D135:G136"/>
-    <mergeCell ref="E137:G138"/>
-    <mergeCell ref="E139:G140"/>
-    <mergeCell ref="D143:G144"/>
-    <mergeCell ref="E145:G146"/>
-    <mergeCell ref="H135:H136"/>
-    <mergeCell ref="E147:G148"/>
-    <mergeCell ref="E149:G150"/>
-    <mergeCell ref="E151:G152"/>
-    <mergeCell ref="E59:G60"/>
-    <mergeCell ref="E61:G62"/>
-    <mergeCell ref="D63:G64"/>
-    <mergeCell ref="E67:G68"/>
-    <mergeCell ref="E65:G66"/>
-    <mergeCell ref="E69:G70"/>
-    <mergeCell ref="E71:G72"/>
-    <mergeCell ref="C73:G74"/>
-    <mergeCell ref="C75:G76"/>
-    <mergeCell ref="C77:G78"/>
-    <mergeCell ref="D79:G80"/>
-    <mergeCell ref="E109:G110"/>
-    <mergeCell ref="E111:G112"/>
-    <mergeCell ref="E101:G102"/>
-    <mergeCell ref="C105:G106"/>
-    <mergeCell ref="D107:G108"/>
-    <mergeCell ref="D117:G118"/>
-    <mergeCell ref="D13:G14"/>
-    <mergeCell ref="D15:G16"/>
-    <mergeCell ref="D17:G18"/>
-    <mergeCell ref="D19:G20"/>
-    <mergeCell ref="C21:G22"/>
-    <mergeCell ref="D23:G24"/>
-    <mergeCell ref="C25:G26"/>
-    <mergeCell ref="D27:G28"/>
-    <mergeCell ref="D29:G30"/>
-    <mergeCell ref="J3:CJ3"/>
-    <mergeCell ref="CK3:DO3"/>
-    <mergeCell ref="J4:AA4"/>
-    <mergeCell ref="AB4:BE4"/>
-    <mergeCell ref="BF4:CJ4"/>
-    <mergeCell ref="CK4:DO4"/>
-    <mergeCell ref="B7:G8"/>
-    <mergeCell ref="C9:G10"/>
-    <mergeCell ref="C11:G12"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="C163:G164"/>
-    <mergeCell ref="C159:G160"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="C31:G32"/>
-    <mergeCell ref="D33:G34"/>
-    <mergeCell ref="E35:G36"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="E43:G44"/>
-    <mergeCell ref="E45:G46"/>
-    <mergeCell ref="E47:G48"/>
-    <mergeCell ref="E49:G50"/>
-    <mergeCell ref="E51:G52"/>
-    <mergeCell ref="D53:G54"/>
-    <mergeCell ref="E55:G56"/>
-    <mergeCell ref="E57:G58"/>
-    <mergeCell ref="I53:I54"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="I159:I160"/>
-    <mergeCell ref="I161:I162"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="I93:I94"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="I109:I110"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="I153:I154"/>
-    <mergeCell ref="I151:I152"/>
-    <mergeCell ref="I149:I150"/>
-    <mergeCell ref="I147:I148"/>
-    <mergeCell ref="I145:I146"/>
-    <mergeCell ref="I111:I112"/>
-    <mergeCell ref="I135:I136"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="I163:I164"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="H75:H76"/>
-    <mergeCell ref="H159:H160"/>
-    <mergeCell ref="H163:H164"/>
-    <mergeCell ref="H161:H162"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="H67:H68"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H59:H60"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="H77:H78"/>
-    <mergeCell ref="H81:H82"/>
-    <mergeCell ref="H83:H84"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="H93:H94"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="H111:H112"/>
-    <mergeCell ref="H101:H102"/>
-    <mergeCell ref="I101:I102"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="I85:I86"/>
-    <mergeCell ref="H89:H90"/>
-    <mergeCell ref="I89:I90"/>
-    <mergeCell ref="E81:G82"/>
-    <mergeCell ref="E83:G84"/>
-    <mergeCell ref="E91:G92"/>
-    <mergeCell ref="E93:G94"/>
-    <mergeCell ref="E95:G96"/>
-    <mergeCell ref="E97:G98"/>
-    <mergeCell ref="E99:G100"/>
-    <mergeCell ref="E85:G86"/>
-    <mergeCell ref="D89:G90"/>
-    <mergeCell ref="H105:H106"/>
-    <mergeCell ref="I105:I106"/>
-    <mergeCell ref="H107:H108"/>
-    <mergeCell ref="I107:I108"/>
-    <mergeCell ref="H109:H110"/>
-    <mergeCell ref="H117:H118"/>
-    <mergeCell ref="I117:I118"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="I119:I120"/>
-    <mergeCell ref="E155:G156"/>
-    <mergeCell ref="D155:D156"/>
-    <mergeCell ref="H155:H156"/>
-    <mergeCell ref="I155:I156"/>
-    <mergeCell ref="H113:H114"/>
-    <mergeCell ref="I113:I114"/>
-    <mergeCell ref="H129:H130"/>
-    <mergeCell ref="I129:I130"/>
-    <mergeCell ref="E129:G130"/>
-    <mergeCell ref="H123:H124"/>
-    <mergeCell ref="I123:I124"/>
-    <mergeCell ref="I125:I126"/>
-    <mergeCell ref="H125:H126"/>
-    <mergeCell ref="H133:H134"/>
-    <mergeCell ref="I133:I134"/>
-    <mergeCell ref="E123:G124"/>
-    <mergeCell ref="E125:G126"/>
-    <mergeCell ref="E127:G128"/>
-    <mergeCell ref="E113:G114"/>
-    <mergeCell ref="E119:G120"/>
-    <mergeCell ref="E121:G122"/>
-    <mergeCell ref="H127:H128"/>
-    <mergeCell ref="I127:I128"/>
-    <mergeCell ref="H121:H122"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <conditionalFormatting sqref="J7">

--- a/docs/【DIGITAL OJT】WBS.xlsx
+++ b/docs/【DIGITAL OJT】WBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIGITALOJT\digital-ojt-development-cause-DroneInventorySystem\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3DAEDE-6918-4F8F-9EE2-0D66A91A7FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD42851F-DA13-42A4-8BC9-CFC4E68F8D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12096" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -1489,19 +1489,67 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1510,22 +1558,25 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1546,110 +1597,29 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1675,62 +1645,92 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2350,120 +2350,120 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="J3" s="161">
+      <c r="J3" s="173">
         <v>2024</v>
       </c>
-      <c r="K3" s="162"/>
-      <c r="L3" s="162"/>
-      <c r="M3" s="162"/>
-      <c r="N3" s="162"/>
-      <c r="O3" s="162"/>
-      <c r="P3" s="162"/>
-      <c r="Q3" s="162"/>
-      <c r="R3" s="162"/>
-      <c r="S3" s="162"/>
-      <c r="T3" s="162"/>
-      <c r="U3" s="162"/>
-      <c r="V3" s="162"/>
-      <c r="W3" s="162"/>
-      <c r="X3" s="162"/>
-      <c r="Y3" s="162"/>
-      <c r="Z3" s="162"/>
-      <c r="AA3" s="162"/>
-      <c r="AB3" s="162"/>
-      <c r="AC3" s="162"/>
-      <c r="AD3" s="162"/>
-      <c r="AE3" s="162"/>
-      <c r="AF3" s="162"/>
-      <c r="AG3" s="162"/>
-      <c r="AH3" s="162"/>
-      <c r="AI3" s="162"/>
-      <c r="AJ3" s="162"/>
-      <c r="AK3" s="162"/>
-      <c r="AL3" s="162"/>
-      <c r="AM3" s="162"/>
-      <c r="AN3" s="162"/>
-      <c r="AO3" s="162"/>
-      <c r="AP3" s="162"/>
-      <c r="AQ3" s="162"/>
-      <c r="AR3" s="162"/>
-      <c r="AS3" s="162"/>
-      <c r="AT3" s="162"/>
-      <c r="AU3" s="162"/>
-      <c r="AV3" s="162"/>
-      <c r="AW3" s="162"/>
-      <c r="AX3" s="162"/>
-      <c r="AY3" s="162"/>
-      <c r="AZ3" s="162"/>
-      <c r="BA3" s="162"/>
-      <c r="BB3" s="162"/>
-      <c r="BC3" s="162"/>
-      <c r="BD3" s="162"/>
-      <c r="BE3" s="162"/>
-      <c r="BF3" s="162"/>
-      <c r="BG3" s="162"/>
-      <c r="BH3" s="162"/>
-      <c r="BI3" s="162"/>
-      <c r="BJ3" s="162"/>
-      <c r="BK3" s="162"/>
-      <c r="BL3" s="162"/>
-      <c r="BM3" s="162"/>
-      <c r="BN3" s="162"/>
-      <c r="BO3" s="162"/>
-      <c r="BP3" s="162"/>
-      <c r="BQ3" s="162"/>
-      <c r="BR3" s="162"/>
-      <c r="BS3" s="162"/>
-      <c r="BT3" s="162"/>
-      <c r="BU3" s="162"/>
-      <c r="BV3" s="162"/>
-      <c r="BW3" s="162"/>
-      <c r="BX3" s="162"/>
-      <c r="BY3" s="162"/>
-      <c r="BZ3" s="162"/>
-      <c r="CA3" s="162"/>
-      <c r="CB3" s="162"/>
-      <c r="CC3" s="162"/>
-      <c r="CD3" s="162"/>
-      <c r="CE3" s="162"/>
-      <c r="CF3" s="162"/>
-      <c r="CG3" s="162"/>
-      <c r="CH3" s="162"/>
-      <c r="CI3" s="162"/>
-      <c r="CJ3" s="163"/>
-      <c r="CK3" s="161">
+      <c r="K3" s="174"/>
+      <c r="L3" s="174"/>
+      <c r="M3" s="174"/>
+      <c r="N3" s="174"/>
+      <c r="O3" s="174"/>
+      <c r="P3" s="174"/>
+      <c r="Q3" s="174"/>
+      <c r="R3" s="174"/>
+      <c r="S3" s="174"/>
+      <c r="T3" s="174"/>
+      <c r="U3" s="174"/>
+      <c r="V3" s="174"/>
+      <c r="W3" s="174"/>
+      <c r="X3" s="174"/>
+      <c r="Y3" s="174"/>
+      <c r="Z3" s="174"/>
+      <c r="AA3" s="174"/>
+      <c r="AB3" s="174"/>
+      <c r="AC3" s="174"/>
+      <c r="AD3" s="174"/>
+      <c r="AE3" s="174"/>
+      <c r="AF3" s="174"/>
+      <c r="AG3" s="174"/>
+      <c r="AH3" s="174"/>
+      <c r="AI3" s="174"/>
+      <c r="AJ3" s="174"/>
+      <c r="AK3" s="174"/>
+      <c r="AL3" s="174"/>
+      <c r="AM3" s="174"/>
+      <c r="AN3" s="174"/>
+      <c r="AO3" s="174"/>
+      <c r="AP3" s="174"/>
+      <c r="AQ3" s="174"/>
+      <c r="AR3" s="174"/>
+      <c r="AS3" s="174"/>
+      <c r="AT3" s="174"/>
+      <c r="AU3" s="174"/>
+      <c r="AV3" s="174"/>
+      <c r="AW3" s="174"/>
+      <c r="AX3" s="174"/>
+      <c r="AY3" s="174"/>
+      <c r="AZ3" s="174"/>
+      <c r="BA3" s="174"/>
+      <c r="BB3" s="174"/>
+      <c r="BC3" s="174"/>
+      <c r="BD3" s="174"/>
+      <c r="BE3" s="174"/>
+      <c r="BF3" s="174"/>
+      <c r="BG3" s="174"/>
+      <c r="BH3" s="174"/>
+      <c r="BI3" s="174"/>
+      <c r="BJ3" s="174"/>
+      <c r="BK3" s="174"/>
+      <c r="BL3" s="174"/>
+      <c r="BM3" s="174"/>
+      <c r="BN3" s="174"/>
+      <c r="BO3" s="174"/>
+      <c r="BP3" s="174"/>
+      <c r="BQ3" s="174"/>
+      <c r="BR3" s="174"/>
+      <c r="BS3" s="174"/>
+      <c r="BT3" s="174"/>
+      <c r="BU3" s="174"/>
+      <c r="BV3" s="174"/>
+      <c r="BW3" s="174"/>
+      <c r="BX3" s="174"/>
+      <c r="BY3" s="174"/>
+      <c r="BZ3" s="174"/>
+      <c r="CA3" s="174"/>
+      <c r="CB3" s="174"/>
+      <c r="CC3" s="174"/>
+      <c r="CD3" s="174"/>
+      <c r="CE3" s="174"/>
+      <c r="CF3" s="174"/>
+      <c r="CG3" s="174"/>
+      <c r="CH3" s="174"/>
+      <c r="CI3" s="174"/>
+      <c r="CJ3" s="175"/>
+      <c r="CK3" s="173">
         <v>2025</v>
       </c>
-      <c r="CL3" s="162"/>
-      <c r="CM3" s="162"/>
-      <c r="CN3" s="162"/>
-      <c r="CO3" s="162"/>
-      <c r="CP3" s="162"/>
-      <c r="CQ3" s="162"/>
-      <c r="CR3" s="162"/>
-      <c r="CS3" s="162"/>
-      <c r="CT3" s="162"/>
-      <c r="CU3" s="162"/>
-      <c r="CV3" s="162"/>
-      <c r="CW3" s="162"/>
-      <c r="CX3" s="162"/>
-      <c r="CY3" s="162"/>
-      <c r="CZ3" s="162"/>
-      <c r="DA3" s="162"/>
-      <c r="DB3" s="162"/>
-      <c r="DC3" s="162"/>
-      <c r="DD3" s="162"/>
-      <c r="DE3" s="162"/>
-      <c r="DF3" s="162"/>
-      <c r="DG3" s="162"/>
-      <c r="DH3" s="162"/>
-      <c r="DI3" s="162"/>
-      <c r="DJ3" s="162"/>
-      <c r="DK3" s="162"/>
-      <c r="DL3" s="162"/>
-      <c r="DM3" s="162"/>
-      <c r="DN3" s="162"/>
-      <c r="DO3" s="163"/>
+      <c r="CL3" s="174"/>
+      <c r="CM3" s="174"/>
+      <c r="CN3" s="174"/>
+      <c r="CO3" s="174"/>
+      <c r="CP3" s="174"/>
+      <c r="CQ3" s="174"/>
+      <c r="CR3" s="174"/>
+      <c r="CS3" s="174"/>
+      <c r="CT3" s="174"/>
+      <c r="CU3" s="174"/>
+      <c r="CV3" s="174"/>
+      <c r="CW3" s="174"/>
+      <c r="CX3" s="174"/>
+      <c r="CY3" s="174"/>
+      <c r="CZ3" s="174"/>
+      <c r="DA3" s="174"/>
+      <c r="DB3" s="174"/>
+      <c r="DC3" s="174"/>
+      <c r="DD3" s="174"/>
+      <c r="DE3" s="174"/>
+      <c r="DF3" s="174"/>
+      <c r="DG3" s="174"/>
+      <c r="DH3" s="174"/>
+      <c r="DI3" s="174"/>
+      <c r="DJ3" s="174"/>
+      <c r="DK3" s="174"/>
+      <c r="DL3" s="174"/>
+      <c r="DM3" s="174"/>
+      <c r="DN3" s="174"/>
+      <c r="DO3" s="175"/>
       <c r="DP3" s="1"/>
     </row>
     <row r="4" spans="1:120" ht="18" customHeight="1">
@@ -2478,124 +2478,124 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="J4" s="161">
+      <c r="J4" s="173">
         <v>10</v>
       </c>
-      <c r="K4" s="162"/>
-      <c r="L4" s="162"/>
-      <c r="M4" s="162"/>
-      <c r="N4" s="162"/>
-      <c r="O4" s="162"/>
-      <c r="P4" s="162"/>
-      <c r="Q4" s="162"/>
-      <c r="R4" s="162"/>
-      <c r="S4" s="162"/>
-      <c r="T4" s="162"/>
-      <c r="U4" s="162"/>
-      <c r="V4" s="162"/>
-      <c r="W4" s="162"/>
-      <c r="X4" s="162"/>
-      <c r="Y4" s="162"/>
-      <c r="Z4" s="162"/>
-      <c r="AA4" s="163"/>
-      <c r="AB4" s="161">
+      <c r="K4" s="174"/>
+      <c r="L4" s="174"/>
+      <c r="M4" s="174"/>
+      <c r="N4" s="174"/>
+      <c r="O4" s="174"/>
+      <c r="P4" s="174"/>
+      <c r="Q4" s="174"/>
+      <c r="R4" s="174"/>
+      <c r="S4" s="174"/>
+      <c r="T4" s="174"/>
+      <c r="U4" s="174"/>
+      <c r="V4" s="174"/>
+      <c r="W4" s="174"/>
+      <c r="X4" s="174"/>
+      <c r="Y4" s="174"/>
+      <c r="Z4" s="174"/>
+      <c r="AA4" s="175"/>
+      <c r="AB4" s="173">
         <v>11</v>
       </c>
-      <c r="AC4" s="162"/>
-      <c r="AD4" s="162"/>
-      <c r="AE4" s="162"/>
-      <c r="AF4" s="162"/>
-      <c r="AG4" s="162"/>
-      <c r="AH4" s="162"/>
-      <c r="AI4" s="162"/>
-      <c r="AJ4" s="162"/>
-      <c r="AK4" s="162"/>
-      <c r="AL4" s="162"/>
-      <c r="AM4" s="162"/>
-      <c r="AN4" s="162"/>
-      <c r="AO4" s="162"/>
-      <c r="AP4" s="162"/>
-      <c r="AQ4" s="162"/>
-      <c r="AR4" s="162"/>
-      <c r="AS4" s="162"/>
-      <c r="AT4" s="162"/>
-      <c r="AU4" s="162"/>
-      <c r="AV4" s="162"/>
-      <c r="AW4" s="162"/>
-      <c r="AX4" s="162"/>
-      <c r="AY4" s="162"/>
-      <c r="AZ4" s="162"/>
-      <c r="BA4" s="162"/>
-      <c r="BB4" s="162"/>
-      <c r="BC4" s="162"/>
-      <c r="BD4" s="162"/>
-      <c r="BE4" s="163"/>
-      <c r="BF4" s="161">
+      <c r="AC4" s="174"/>
+      <c r="AD4" s="174"/>
+      <c r="AE4" s="174"/>
+      <c r="AF4" s="174"/>
+      <c r="AG4" s="174"/>
+      <c r="AH4" s="174"/>
+      <c r="AI4" s="174"/>
+      <c r="AJ4" s="174"/>
+      <c r="AK4" s="174"/>
+      <c r="AL4" s="174"/>
+      <c r="AM4" s="174"/>
+      <c r="AN4" s="174"/>
+      <c r="AO4" s="174"/>
+      <c r="AP4" s="174"/>
+      <c r="AQ4" s="174"/>
+      <c r="AR4" s="174"/>
+      <c r="AS4" s="174"/>
+      <c r="AT4" s="174"/>
+      <c r="AU4" s="174"/>
+      <c r="AV4" s="174"/>
+      <c r="AW4" s="174"/>
+      <c r="AX4" s="174"/>
+      <c r="AY4" s="174"/>
+      <c r="AZ4" s="174"/>
+      <c r="BA4" s="174"/>
+      <c r="BB4" s="174"/>
+      <c r="BC4" s="174"/>
+      <c r="BD4" s="174"/>
+      <c r="BE4" s="175"/>
+      <c r="BF4" s="173">
         <v>12</v>
       </c>
-      <c r="BG4" s="162"/>
-      <c r="BH4" s="162"/>
-      <c r="BI4" s="162"/>
-      <c r="BJ4" s="162"/>
-      <c r="BK4" s="162"/>
-      <c r="BL4" s="162"/>
-      <c r="BM4" s="162"/>
-      <c r="BN4" s="162"/>
-      <c r="BO4" s="162"/>
-      <c r="BP4" s="162"/>
-      <c r="BQ4" s="162"/>
-      <c r="BR4" s="162"/>
-      <c r="BS4" s="162"/>
-      <c r="BT4" s="162"/>
-      <c r="BU4" s="162"/>
-      <c r="BV4" s="162"/>
-      <c r="BW4" s="162"/>
-      <c r="BX4" s="162"/>
-      <c r="BY4" s="162"/>
-      <c r="BZ4" s="162"/>
-      <c r="CA4" s="162"/>
-      <c r="CB4" s="162"/>
-      <c r="CC4" s="162"/>
-      <c r="CD4" s="162"/>
-      <c r="CE4" s="162"/>
-      <c r="CF4" s="162"/>
-      <c r="CG4" s="162"/>
-      <c r="CH4" s="162"/>
-      <c r="CI4" s="162"/>
-      <c r="CJ4" s="163"/>
-      <c r="CK4" s="161">
+      <c r="BG4" s="174"/>
+      <c r="BH4" s="174"/>
+      <c r="BI4" s="174"/>
+      <c r="BJ4" s="174"/>
+      <c r="BK4" s="174"/>
+      <c r="BL4" s="174"/>
+      <c r="BM4" s="174"/>
+      <c r="BN4" s="174"/>
+      <c r="BO4" s="174"/>
+      <c r="BP4" s="174"/>
+      <c r="BQ4" s="174"/>
+      <c r="BR4" s="174"/>
+      <c r="BS4" s="174"/>
+      <c r="BT4" s="174"/>
+      <c r="BU4" s="174"/>
+      <c r="BV4" s="174"/>
+      <c r="BW4" s="174"/>
+      <c r="BX4" s="174"/>
+      <c r="BY4" s="174"/>
+      <c r="BZ4" s="174"/>
+      <c r="CA4" s="174"/>
+      <c r="CB4" s="174"/>
+      <c r="CC4" s="174"/>
+      <c r="CD4" s="174"/>
+      <c r="CE4" s="174"/>
+      <c r="CF4" s="174"/>
+      <c r="CG4" s="174"/>
+      <c r="CH4" s="174"/>
+      <c r="CI4" s="174"/>
+      <c r="CJ4" s="175"/>
+      <c r="CK4" s="173">
         <v>1</v>
       </c>
-      <c r="CL4" s="162"/>
-      <c r="CM4" s="162"/>
-      <c r="CN4" s="162"/>
-      <c r="CO4" s="162"/>
-      <c r="CP4" s="162"/>
-      <c r="CQ4" s="162"/>
-      <c r="CR4" s="162"/>
-      <c r="CS4" s="162"/>
-      <c r="CT4" s="162"/>
-      <c r="CU4" s="162"/>
-      <c r="CV4" s="162"/>
-      <c r="CW4" s="162"/>
-      <c r="CX4" s="162"/>
-      <c r="CY4" s="162"/>
-      <c r="CZ4" s="162"/>
-      <c r="DA4" s="162"/>
-      <c r="DB4" s="162"/>
-      <c r="DC4" s="162"/>
-      <c r="DD4" s="162"/>
-      <c r="DE4" s="162"/>
-      <c r="DF4" s="162"/>
-      <c r="DG4" s="162"/>
-      <c r="DH4" s="162"/>
-      <c r="DI4" s="162"/>
-      <c r="DJ4" s="162"/>
-      <c r="DK4" s="162"/>
-      <c r="DL4" s="162"/>
-      <c r="DM4" s="162"/>
-      <c r="DN4" s="162"/>
-      <c r="DO4" s="163"/>
+      <c r="CL4" s="174"/>
+      <c r="CM4" s="174"/>
+      <c r="CN4" s="174"/>
+      <c r="CO4" s="174"/>
+      <c r="CP4" s="174"/>
+      <c r="CQ4" s="174"/>
+      <c r="CR4" s="174"/>
+      <c r="CS4" s="174"/>
+      <c r="CT4" s="174"/>
+      <c r="CU4" s="174"/>
+      <c r="CV4" s="174"/>
+      <c r="CW4" s="174"/>
+      <c r="CX4" s="174"/>
+      <c r="CY4" s="174"/>
+      <c r="CZ4" s="174"/>
+      <c r="DA4" s="174"/>
+      <c r="DB4" s="174"/>
+      <c r="DC4" s="174"/>
+      <c r="DD4" s="174"/>
+      <c r="DE4" s="174"/>
+      <c r="DF4" s="174"/>
+      <c r="DG4" s="174"/>
+      <c r="DH4" s="174"/>
+      <c r="DI4" s="174"/>
+      <c r="DJ4" s="174"/>
+      <c r="DK4" s="174"/>
+      <c r="DL4" s="174"/>
+      <c r="DM4" s="174"/>
+      <c r="DN4" s="174"/>
+      <c r="DO4" s="175"/>
       <c r="DP4" s="6"/>
     </row>
     <row r="5" spans="1:120" ht="18" customHeight="1">
@@ -3390,18 +3390,18 @@
     </row>
     <row r="7" spans="1:120" ht="9.75" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="164" t="s">
+      <c r="B7" s="176" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="166" t="s">
+      <c r="C7" s="164"/>
+      <c r="D7" s="164"/>
+      <c r="E7" s="164"/>
+      <c r="F7" s="164"/>
+      <c r="G7" s="177"/>
+      <c r="H7" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="166" t="s">
+      <c r="I7" s="142" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="38"/>
@@ -3518,14 +3518,14 @@
     </row>
     <row r="8" spans="1:120" ht="9.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="134"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="135"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="135"/>
-      <c r="G8" s="139"/>
-      <c r="H8" s="166"/>
-      <c r="I8" s="166"/>
+      <c r="B8" s="166"/>
+      <c r="C8" s="167"/>
+      <c r="D8" s="167"/>
+      <c r="E8" s="167"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="168"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="142"/>
       <c r="J8" s="39"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
@@ -3641,15 +3641,15 @@
     <row r="9" spans="1:120" ht="9.75" customHeight="1">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
-      <c r="C9" s="165" t="s">
+      <c r="C9" s="178" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="154"/>
-      <c r="E9" s="154"/>
-      <c r="F9" s="154"/>
-      <c r="G9" s="142"/>
-      <c r="H9" s="167"/>
-      <c r="I9" s="167"/>
+      <c r="D9" s="158"/>
+      <c r="E9" s="158"/>
+      <c r="F9" s="158"/>
+      <c r="G9" s="162"/>
+      <c r="H9" s="139"/>
+      <c r="I9" s="139"/>
       <c r="J9" s="42"/>
       <c r="K9" s="42"/>
       <c r="L9" s="44"/>
@@ -3765,13 +3765,13 @@
     <row r="10" spans="1:120" ht="9.75" customHeight="1">
       <c r="A10" s="16"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="141"/>
-      <c r="D10" s="135"/>
-      <c r="E10" s="135"/>
-      <c r="F10" s="135"/>
-      <c r="G10" s="139"/>
-      <c r="H10" s="167"/>
-      <c r="I10" s="167"/>
+      <c r="C10" s="179"/>
+      <c r="D10" s="167"/>
+      <c r="E10" s="167"/>
+      <c r="F10" s="167"/>
+      <c r="G10" s="168"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
       <c r="J10" s="46"/>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
@@ -3887,15 +3887,15 @@
     <row r="11" spans="1:120" ht="9.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="153" t="s">
+      <c r="C11" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="154"/>
-      <c r="E11" s="154"/>
-      <c r="F11" s="154"/>
-      <c r="G11" s="142"/>
-      <c r="H11" s="167"/>
-      <c r="I11" s="167"/>
+      <c r="D11" s="158"/>
+      <c r="E11" s="158"/>
+      <c r="F11" s="158"/>
+      <c r="G11" s="162"/>
+      <c r="H11" s="139"/>
+      <c r="I11" s="139"/>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
       <c r="L11" s="44"/>
@@ -4011,13 +4011,13 @@
     <row r="12" spans="1:120" ht="9.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="141"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="135"/>
-      <c r="F12" s="135"/>
-      <c r="G12" s="139"/>
-      <c r="H12" s="167"/>
-      <c r="I12" s="167"/>
+      <c r="C12" s="179"/>
+      <c r="D12" s="167"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="167"/>
+      <c r="G12" s="168"/>
+      <c r="H12" s="139"/>
+      <c r="I12" s="139"/>
       <c r="J12" s="46"/>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
@@ -4134,13 +4134,13 @@
       <c r="A13" s="1"/>
       <c r="B13" s="18"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="151" t="s">
+      <c r="D13" s="181" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="152"/>
-      <c r="H13" s="184" t="s">
+      <c r="E13" s="164"/>
+      <c r="F13" s="164"/>
+      <c r="G13" s="177"/>
+      <c r="H13" s="138" t="s">
         <v>40</v>
       </c>
       <c r="I13" s="112">
@@ -4262,10 +4262,10 @@
       <c r="A14" s="1"/>
       <c r="B14" s="18"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="134"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="135"/>
-      <c r="G14" s="139"/>
+      <c r="D14" s="166"/>
+      <c r="E14" s="167"/>
+      <c r="F14" s="167"/>
+      <c r="G14" s="168"/>
       <c r="H14" s="112"/>
       <c r="I14" s="112"/>
       <c r="J14" s="39"/>
@@ -4384,13 +4384,13 @@
       <c r="A15" s="1"/>
       <c r="B15" s="18"/>
       <c r="C15" s="24"/>
-      <c r="D15" s="151" t="s">
+      <c r="D15" s="181" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="133"/>
-      <c r="H15" s="184" t="s">
+      <c r="E15" s="164"/>
+      <c r="F15" s="164"/>
+      <c r="G15" s="170"/>
+      <c r="H15" s="138" t="s">
         <v>40</v>
       </c>
       <c r="I15" s="112">
@@ -4512,10 +4512,10 @@
       <c r="A16" s="1"/>
       <c r="B16" s="18"/>
       <c r="C16" s="24"/>
-      <c r="D16" s="134"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="136"/>
+      <c r="D16" s="166"/>
+      <c r="E16" s="167"/>
+      <c r="F16" s="167"/>
+      <c r="G16" s="171"/>
       <c r="H16" s="112"/>
       <c r="I16" s="112"/>
       <c r="J16" s="14"/>
@@ -4634,13 +4634,13 @@
       <c r="A17" s="1"/>
       <c r="B17" s="18"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="151" t="s">
+      <c r="D17" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="132"/>
-      <c r="F17" s="132"/>
-      <c r="G17" s="133"/>
-      <c r="H17" s="184" t="s">
+      <c r="E17" s="164"/>
+      <c r="F17" s="164"/>
+      <c r="G17" s="170"/>
+      <c r="H17" s="138" t="s">
         <v>40</v>
       </c>
       <c r="I17" s="112">
@@ -4762,10 +4762,10 @@
       <c r="A18" s="1"/>
       <c r="B18" s="18"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="134"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="135"/>
-      <c r="G18" s="136"/>
+      <c r="D18" s="166"/>
+      <c r="E18" s="167"/>
+      <c r="F18" s="167"/>
+      <c r="G18" s="171"/>
       <c r="H18" s="112"/>
       <c r="I18" s="112"/>
       <c r="J18" s="14"/>
@@ -4884,13 +4884,13 @@
       <c r="A19" s="1"/>
       <c r="B19" s="18"/>
       <c r="C19" s="24"/>
-      <c r="D19" s="151" t="s">
+      <c r="D19" s="181" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="132"/>
-      <c r="F19" s="132"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="184" t="s">
+      <c r="E19" s="164"/>
+      <c r="F19" s="164"/>
+      <c r="G19" s="170"/>
+      <c r="H19" s="138" t="s">
         <v>40</v>
       </c>
       <c r="I19" s="112">
@@ -5012,10 +5012,10 @@
       <c r="A20" s="1"/>
       <c r="B20" s="18"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="134"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="135"/>
-      <c r="G20" s="136"/>
+      <c r="D20" s="166"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="167"/>
+      <c r="G20" s="171"/>
       <c r="H20" s="112"/>
       <c r="I20" s="112"/>
       <c r="J20" s="26"/>
@@ -5133,15 +5133,15 @@
     <row r="21" spans="1:120" ht="9.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="18"/>
-      <c r="C21" s="153" t="s">
+      <c r="C21" s="180" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="154"/>
-      <c r="E21" s="154"/>
-      <c r="F21" s="154"/>
-      <c r="G21" s="155"/>
-      <c r="H21" s="167"/>
-      <c r="I21" s="167"/>
+      <c r="D21" s="158"/>
+      <c r="E21" s="158"/>
+      <c r="F21" s="158"/>
+      <c r="G21" s="159"/>
+      <c r="H21" s="139"/>
+      <c r="I21" s="139"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="44"/>
@@ -5257,13 +5257,13 @@
     <row r="22" spans="1:120" ht="9.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="18"/>
-      <c r="C22" s="156"/>
-      <c r="D22" s="157"/>
-      <c r="E22" s="157"/>
-      <c r="F22" s="157"/>
-      <c r="G22" s="142"/>
-      <c r="H22" s="167"/>
-      <c r="I22" s="167"/>
+      <c r="C22" s="160"/>
+      <c r="D22" s="161"/>
+      <c r="E22" s="161"/>
+      <c r="F22" s="161"/>
+      <c r="G22" s="162"/>
+      <c r="H22" s="139"/>
+      <c r="I22" s="139"/>
       <c r="J22" s="46"/>
       <c r="K22" s="47"/>
       <c r="L22" s="47"/>
@@ -5380,13 +5380,13 @@
       <c r="A23" s="1"/>
       <c r="B23" s="28"/>
       <c r="C23" s="29"/>
-      <c r="D23" s="158" t="s">
+      <c r="D23" s="182" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="132"/>
-      <c r="F23" s="132"/>
-      <c r="G23" s="133"/>
-      <c r="H23" s="184" t="s">
+      <c r="E23" s="164"/>
+      <c r="F23" s="164"/>
+      <c r="G23" s="170"/>
+      <c r="H23" s="138" t="s">
         <v>46</v>
       </c>
       <c r="I23" s="112">
@@ -5508,10 +5508,10 @@
       <c r="A24" s="1"/>
       <c r="B24" s="18"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="134"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="135"/>
-      <c r="G24" s="136"/>
+      <c r="D24" s="166"/>
+      <c r="E24" s="167"/>
+      <c r="F24" s="167"/>
+      <c r="G24" s="171"/>
       <c r="H24" s="112"/>
       <c r="I24" s="112"/>
       <c r="J24" s="14"/>
@@ -5629,15 +5629,15 @@
     <row r="25" spans="1:120" ht="9.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="18"/>
-      <c r="C25" s="153" t="s">
+      <c r="C25" s="180" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="154"/>
-      <c r="E25" s="154"/>
-      <c r="F25" s="154"/>
-      <c r="G25" s="155"/>
-      <c r="H25" s="167"/>
-      <c r="I25" s="167"/>
+      <c r="D25" s="158"/>
+      <c r="E25" s="158"/>
+      <c r="F25" s="158"/>
+      <c r="G25" s="159"/>
+      <c r="H25" s="139"/>
+      <c r="I25" s="139"/>
       <c r="J25" s="42"/>
       <c r="K25" s="42"/>
       <c r="L25" s="44"/>
@@ -5753,13 +5753,13 @@
     <row r="26" spans="1:120" ht="9.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="18"/>
-      <c r="C26" s="141"/>
-      <c r="D26" s="135"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="135"/>
-      <c r="G26" s="139"/>
-      <c r="H26" s="167"/>
-      <c r="I26" s="167"/>
+      <c r="C26" s="179"/>
+      <c r="D26" s="167"/>
+      <c r="E26" s="167"/>
+      <c r="F26" s="167"/>
+      <c r="G26" s="168"/>
+      <c r="H26" s="139"/>
+      <c r="I26" s="139"/>
       <c r="J26" s="46"/>
       <c r="K26" s="47"/>
       <c r="L26" s="47"/>
@@ -5876,13 +5876,13 @@
       <c r="A27" s="1"/>
       <c r="B27" s="28"/>
       <c r="C27" s="29"/>
-      <c r="D27" s="158" t="s">
+      <c r="D27" s="182" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="132"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="133"/>
-      <c r="H27" s="184" t="s">
+      <c r="E27" s="164"/>
+      <c r="F27" s="164"/>
+      <c r="G27" s="170"/>
+      <c r="H27" s="138" t="s">
         <v>44</v>
       </c>
       <c r="I27" s="112">
@@ -6004,10 +6004,10 @@
       <c r="A28" s="1"/>
       <c r="B28" s="28"/>
       <c r="C28" s="30"/>
-      <c r="D28" s="134"/>
-      <c r="E28" s="135"/>
-      <c r="F28" s="135"/>
-      <c r="G28" s="136"/>
+      <c r="D28" s="166"/>
+      <c r="E28" s="167"/>
+      <c r="F28" s="167"/>
+      <c r="G28" s="171"/>
       <c r="H28" s="112"/>
       <c r="I28" s="112"/>
       <c r="J28" s="14"/>
@@ -6126,13 +6126,13 @@
       <c r="A29" s="1"/>
       <c r="B29" s="28"/>
       <c r="C29" s="30"/>
-      <c r="D29" s="159" t="s">
+      <c r="D29" s="183" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="160"/>
-      <c r="F29" s="160"/>
-      <c r="G29" s="160"/>
-      <c r="H29" s="184" t="s">
+      <c r="E29" s="184"/>
+      <c r="F29" s="184"/>
+      <c r="G29" s="184"/>
+      <c r="H29" s="138" t="s">
         <v>44</v>
       </c>
       <c r="I29" s="112">
@@ -6254,10 +6254,10 @@
       <c r="A30" s="1"/>
       <c r="B30" s="28"/>
       <c r="C30" s="31"/>
-      <c r="D30" s="134"/>
-      <c r="E30" s="135"/>
-      <c r="F30" s="135"/>
-      <c r="G30" s="135"/>
+      <c r="D30" s="166"/>
+      <c r="E30" s="167"/>
+      <c r="F30" s="167"/>
+      <c r="G30" s="167"/>
       <c r="H30" s="112"/>
       <c r="I30" s="112"/>
       <c r="J30" s="26"/>
@@ -6375,15 +6375,15 @@
     <row r="31" spans="1:120" ht="9.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="18"/>
-      <c r="C31" s="179" t="s">
+      <c r="C31" s="157" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="154"/>
-      <c r="E31" s="154"/>
-      <c r="F31" s="154"/>
-      <c r="G31" s="155"/>
-      <c r="H31" s="167"/>
-      <c r="I31" s="167"/>
+      <c r="D31" s="158"/>
+      <c r="E31" s="158"/>
+      <c r="F31" s="158"/>
+      <c r="G31" s="159"/>
+      <c r="H31" s="139"/>
+      <c r="I31" s="139"/>
       <c r="J31" s="42"/>
       <c r="K31" s="43"/>
       <c r="L31" s="44"/>
@@ -6499,13 +6499,13 @@
     <row r="32" spans="1:120" ht="9.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="18"/>
-      <c r="C32" s="156"/>
-      <c r="D32" s="157"/>
-      <c r="E32" s="157"/>
-      <c r="F32" s="157"/>
-      <c r="G32" s="142"/>
-      <c r="H32" s="167"/>
-      <c r="I32" s="167"/>
+      <c r="C32" s="160"/>
+      <c r="D32" s="161"/>
+      <c r="E32" s="161"/>
+      <c r="F32" s="161"/>
+      <c r="G32" s="162"/>
+      <c r="H32" s="139"/>
+      <c r="I32" s="139"/>
       <c r="J32" s="46"/>
       <c r="K32" s="47"/>
       <c r="L32" s="47"/>
@@ -6622,14 +6622,14 @@
       <c r="A33" s="1"/>
       <c r="B33" s="18"/>
       <c r="C33" s="32"/>
-      <c r="D33" s="137" t="s">
+      <c r="D33" s="163" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="132"/>
-      <c r="F33" s="132"/>
-      <c r="G33" s="138"/>
-      <c r="H33" s="167"/>
-      <c r="I33" s="167"/>
+      <c r="E33" s="164"/>
+      <c r="F33" s="164"/>
+      <c r="G33" s="165"/>
+      <c r="H33" s="139"/>
+      <c r="I33" s="139"/>
       <c r="J33" s="50"/>
       <c r="K33" s="51"/>
       <c r="L33" s="51"/>
@@ -6746,12 +6746,12 @@
       <c r="A34" s="1"/>
       <c r="B34" s="18"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="134"/>
-      <c r="E34" s="135"/>
-      <c r="F34" s="135"/>
-      <c r="G34" s="139"/>
-      <c r="H34" s="167"/>
-      <c r="I34" s="167"/>
+      <c r="D34" s="166"/>
+      <c r="E34" s="167"/>
+      <c r="F34" s="167"/>
+      <c r="G34" s="168"/>
+      <c r="H34" s="139"/>
+      <c r="I34" s="139"/>
       <c r="J34" s="52"/>
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
@@ -6869,12 +6869,12 @@
       <c r="B35" s="18"/>
       <c r="C35" s="1"/>
       <c r="D35" s="33"/>
-      <c r="E35" s="131" t="s">
+      <c r="E35" s="169" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="132"/>
-      <c r="G35" s="133"/>
-      <c r="H35" s="184" t="s">
+      <c r="F35" s="164"/>
+      <c r="G35" s="170"/>
+      <c r="H35" s="138" t="s">
         <v>45</v>
       </c>
       <c r="I35" s="112">
@@ -6997,9 +6997,9 @@
       <c r="B36" s="18"/>
       <c r="C36" s="1"/>
       <c r="D36" s="34"/>
-      <c r="E36" s="134"/>
-      <c r="F36" s="135"/>
-      <c r="G36" s="136"/>
+      <c r="E36" s="166"/>
+      <c r="F36" s="167"/>
+      <c r="G36" s="171"/>
       <c r="H36" s="112"/>
       <c r="I36" s="112"/>
       <c r="J36" s="14"/>
@@ -7119,12 +7119,12 @@
       <c r="B37" s="18"/>
       <c r="C37" s="1"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="131" t="s">
+      <c r="E37" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F37" s="132"/>
-      <c r="G37" s="133"/>
-      <c r="H37" s="184" t="s">
+      <c r="F37" s="164"/>
+      <c r="G37" s="170"/>
+      <c r="H37" s="138" t="s">
         <v>44</v>
       </c>
       <c r="I37" s="112">
@@ -7247,9 +7247,9 @@
       <c r="B38" s="18"/>
       <c r="C38" s="1"/>
       <c r="D38" s="35"/>
-      <c r="E38" s="134"/>
-      <c r="F38" s="135"/>
-      <c r="G38" s="136"/>
+      <c r="E38" s="166"/>
+      <c r="F38" s="167"/>
+      <c r="G38" s="171"/>
       <c r="H38" s="112"/>
       <c r="I38" s="112"/>
       <c r="J38" s="26"/>
@@ -7368,14 +7368,14 @@
       <c r="A39" s="1"/>
       <c r="B39" s="18"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="180" t="s">
+      <c r="D39" s="172" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="154"/>
-      <c r="F39" s="154"/>
-      <c r="G39" s="155"/>
-      <c r="H39" s="167"/>
-      <c r="I39" s="167"/>
+      <c r="E39" s="158"/>
+      <c r="F39" s="158"/>
+      <c r="G39" s="159"/>
+      <c r="H39" s="139"/>
+      <c r="I39" s="139"/>
       <c r="J39" s="50"/>
       <c r="K39" s="51"/>
       <c r="L39" s="51"/>
@@ -7492,12 +7492,12 @@
       <c r="A40" s="1"/>
       <c r="B40" s="18"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="134"/>
-      <c r="E40" s="135"/>
-      <c r="F40" s="135"/>
-      <c r="G40" s="139"/>
-      <c r="H40" s="167"/>
-      <c r="I40" s="167"/>
+      <c r="D40" s="166"/>
+      <c r="E40" s="167"/>
+      <c r="F40" s="167"/>
+      <c r="G40" s="168"/>
+      <c r="H40" s="139"/>
+      <c r="I40" s="139"/>
       <c r="J40" s="52"/>
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
@@ -7615,12 +7615,12 @@
       <c r="B41" s="18"/>
       <c r="C41" s="1"/>
       <c r="D41" s="33"/>
-      <c r="E41" s="131" t="s">
+      <c r="E41" s="169" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="132"/>
-      <c r="G41" s="133"/>
-      <c r="H41" s="184" t="s">
+      <c r="F41" s="164"/>
+      <c r="G41" s="170"/>
+      <c r="H41" s="138" t="s">
         <v>43</v>
       </c>
       <c r="I41" s="112">
@@ -7743,9 +7743,9 @@
       <c r="B42" s="18"/>
       <c r="C42" s="1"/>
       <c r="D42" s="34"/>
-      <c r="E42" s="134"/>
-      <c r="F42" s="135"/>
-      <c r="G42" s="136"/>
+      <c r="E42" s="166"/>
+      <c r="F42" s="167"/>
+      <c r="G42" s="171"/>
       <c r="H42" s="112"/>
       <c r="I42" s="112"/>
       <c r="J42" s="14"/>
@@ -7865,12 +7865,12 @@
       <c r="B43" s="18"/>
       <c r="C43" s="1"/>
       <c r="D43" s="34"/>
-      <c r="E43" s="131" t="s">
+      <c r="E43" s="169" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="132"/>
-      <c r="G43" s="133"/>
-      <c r="H43" s="184" t="s">
+      <c r="F43" s="164"/>
+      <c r="G43" s="170"/>
+      <c r="H43" s="138" t="s">
         <v>43</v>
       </c>
       <c r="I43" s="112">
@@ -7993,9 +7993,9 @@
       <c r="B44" s="18"/>
       <c r="C44" s="1"/>
       <c r="D44" s="34"/>
-      <c r="E44" s="134"/>
-      <c r="F44" s="135"/>
-      <c r="G44" s="136"/>
+      <c r="E44" s="166"/>
+      <c r="F44" s="167"/>
+      <c r="G44" s="171"/>
       <c r="H44" s="112"/>
       <c r="I44" s="112"/>
       <c r="J44" s="14"/>
@@ -8115,12 +8115,12 @@
       <c r="B45" s="18"/>
       <c r="C45" s="1"/>
       <c r="D45" s="34"/>
-      <c r="E45" s="131" t="s">
+      <c r="E45" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="132"/>
-      <c r="G45" s="133"/>
-      <c r="H45" s="184" t="s">
+      <c r="F45" s="164"/>
+      <c r="G45" s="170"/>
+      <c r="H45" s="138" t="s">
         <v>42</v>
       </c>
       <c r="I45" s="112">
@@ -8243,9 +8243,9 @@
       <c r="B46" s="18"/>
       <c r="C46" s="1"/>
       <c r="D46" s="34"/>
-      <c r="E46" s="134"/>
-      <c r="F46" s="135"/>
-      <c r="G46" s="136"/>
+      <c r="E46" s="166"/>
+      <c r="F46" s="167"/>
+      <c r="G46" s="171"/>
       <c r="H46" s="112"/>
       <c r="I46" s="112"/>
       <c r="J46" s="14"/>
@@ -8365,12 +8365,12 @@
       <c r="B47" s="18"/>
       <c r="C47" s="1"/>
       <c r="D47" s="34"/>
-      <c r="E47" s="131" t="s">
+      <c r="E47" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="F47" s="132"/>
-      <c r="G47" s="133"/>
-      <c r="H47" s="184" t="s">
+      <c r="F47" s="164"/>
+      <c r="G47" s="170"/>
+      <c r="H47" s="138" t="s">
         <v>41</v>
       </c>
       <c r="I47" s="112">
@@ -8493,9 +8493,9 @@
       <c r="B48" s="18"/>
       <c r="C48" s="1"/>
       <c r="D48" s="34"/>
-      <c r="E48" s="134"/>
-      <c r="F48" s="135"/>
-      <c r="G48" s="136"/>
+      <c r="E48" s="166"/>
+      <c r="F48" s="167"/>
+      <c r="G48" s="171"/>
       <c r="H48" s="112"/>
       <c r="I48" s="112"/>
       <c r="J48" s="14"/>
@@ -8615,12 +8615,12 @@
       <c r="B49" s="18"/>
       <c r="C49" s="1"/>
       <c r="D49" s="34"/>
-      <c r="E49" s="131" t="s">
+      <c r="E49" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="132"/>
-      <c r="G49" s="133"/>
-      <c r="H49" s="184" t="s">
+      <c r="F49" s="164"/>
+      <c r="G49" s="170"/>
+      <c r="H49" s="138" t="s">
         <v>50</v>
       </c>
       <c r="I49" s="112">
@@ -8743,9 +8743,9 @@
       <c r="B50" s="18"/>
       <c r="C50" s="1"/>
       <c r="D50" s="34"/>
-      <c r="E50" s="134"/>
-      <c r="F50" s="135"/>
-      <c r="G50" s="136"/>
+      <c r="E50" s="166"/>
+      <c r="F50" s="167"/>
+      <c r="G50" s="171"/>
       <c r="H50" s="112"/>
       <c r="I50" s="112"/>
       <c r="J50" s="14"/>
@@ -8865,12 +8865,12 @@
       <c r="B51" s="18"/>
       <c r="C51" s="1"/>
       <c r="D51" s="34"/>
-      <c r="E51" s="131" t="s">
+      <c r="E51" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="132"/>
-      <c r="G51" s="133"/>
-      <c r="H51" s="184" t="s">
+      <c r="F51" s="164"/>
+      <c r="G51" s="170"/>
+      <c r="H51" s="138" t="s">
         <v>47</v>
       </c>
       <c r="I51" s="112">
@@ -8993,9 +8993,9 @@
       <c r="B52" s="18"/>
       <c r="C52" s="1"/>
       <c r="D52" s="34"/>
-      <c r="E52" s="134"/>
-      <c r="F52" s="135"/>
-      <c r="G52" s="136"/>
+      <c r="E52" s="166"/>
+      <c r="F52" s="167"/>
+      <c r="G52" s="171"/>
       <c r="H52" s="112"/>
       <c r="I52" s="112"/>
       <c r="J52" s="26"/>
@@ -9114,14 +9114,14 @@
       <c r="A53" s="1"/>
       <c r="B53" s="18"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="137" t="s">
+      <c r="D53" s="163" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="132"/>
-      <c r="F53" s="132"/>
-      <c r="G53" s="138"/>
-      <c r="H53" s="167"/>
-      <c r="I53" s="167"/>
+      <c r="E53" s="164"/>
+      <c r="F53" s="164"/>
+      <c r="G53" s="165"/>
+      <c r="H53" s="139"/>
+      <c r="I53" s="139"/>
       <c r="J53" s="50"/>
       <c r="K53" s="51"/>
       <c r="L53" s="51"/>
@@ -9238,12 +9238,12 @@
       <c r="A54" s="1"/>
       <c r="B54" s="18"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="134"/>
-      <c r="E54" s="135"/>
-      <c r="F54" s="135"/>
-      <c r="G54" s="139"/>
-      <c r="H54" s="167"/>
-      <c r="I54" s="167"/>
+      <c r="D54" s="166"/>
+      <c r="E54" s="167"/>
+      <c r="F54" s="167"/>
+      <c r="G54" s="168"/>
+      <c r="H54" s="139"/>
+      <c r="I54" s="139"/>
       <c r="J54" s="52"/>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -9361,12 +9361,12 @@
       <c r="B55" s="18"/>
       <c r="C55" s="1"/>
       <c r="D55" s="34"/>
-      <c r="E55" s="131" t="s">
+      <c r="E55" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="132"/>
-      <c r="G55" s="133"/>
-      <c r="H55" s="184" t="s">
+      <c r="F55" s="164"/>
+      <c r="G55" s="170"/>
+      <c r="H55" s="138" t="s">
         <v>48</v>
       </c>
       <c r="I55" s="112">
@@ -9489,9 +9489,9 @@
       <c r="B56" s="18"/>
       <c r="C56" s="1"/>
       <c r="D56" s="34"/>
-      <c r="E56" s="134"/>
-      <c r="F56" s="135"/>
-      <c r="G56" s="136"/>
+      <c r="E56" s="166"/>
+      <c r="F56" s="167"/>
+      <c r="G56" s="171"/>
       <c r="H56" s="112"/>
       <c r="I56" s="112"/>
       <c r="J56" s="14"/>
@@ -9611,12 +9611,12 @@
       <c r="B57" s="18"/>
       <c r="C57" s="1"/>
       <c r="D57" s="34"/>
-      <c r="E57" s="131" t="s">
+      <c r="E57" s="169" t="s">
         <v>29</v>
       </c>
-      <c r="F57" s="132"/>
-      <c r="G57" s="133"/>
-      <c r="H57" s="184" t="s">
+      <c r="F57" s="164"/>
+      <c r="G57" s="170"/>
+      <c r="H57" s="138" t="s">
         <v>51</v>
       </c>
       <c r="I57" s="112">
@@ -9739,9 +9739,9 @@
       <c r="B58" s="18"/>
       <c r="C58" s="1"/>
       <c r="D58" s="34"/>
-      <c r="E58" s="134"/>
-      <c r="F58" s="135"/>
-      <c r="G58" s="136"/>
+      <c r="E58" s="166"/>
+      <c r="F58" s="167"/>
+      <c r="G58" s="171"/>
       <c r="H58" s="112"/>
       <c r="I58" s="112"/>
       <c r="J58" s="14"/>
@@ -9861,12 +9861,12 @@
       <c r="B59" s="18"/>
       <c r="C59" s="1"/>
       <c r="D59" s="34"/>
-      <c r="E59" s="131" t="s">
+      <c r="E59" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="F59" s="132"/>
-      <c r="G59" s="133"/>
-      <c r="H59" s="184" t="s">
+      <c r="F59" s="164"/>
+      <c r="G59" s="170"/>
+      <c r="H59" s="138" t="s">
         <v>49</v>
       </c>
       <c r="I59" s="112">
@@ -9989,9 +9989,9 @@
       <c r="B60" s="18"/>
       <c r="C60" s="1"/>
       <c r="D60" s="34"/>
-      <c r="E60" s="134"/>
-      <c r="F60" s="135"/>
-      <c r="G60" s="136"/>
+      <c r="E60" s="166"/>
+      <c r="F60" s="167"/>
+      <c r="G60" s="171"/>
       <c r="H60" s="112"/>
       <c r="I60" s="112"/>
       <c r="J60" s="14"/>
@@ -10111,12 +10111,12 @@
       <c r="B61" s="18"/>
       <c r="C61" s="1"/>
       <c r="D61" s="34"/>
-      <c r="E61" s="131" t="s">
+      <c r="E61" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F61" s="132"/>
-      <c r="G61" s="133"/>
-      <c r="H61" s="184" t="s">
+      <c r="F61" s="164"/>
+      <c r="G61" s="170"/>
+      <c r="H61" s="138" t="s">
         <v>49</v>
       </c>
       <c r="I61" s="112">
@@ -10239,9 +10239,9 @@
       <c r="B62" s="18"/>
       <c r="C62" s="1"/>
       <c r="D62" s="34"/>
-      <c r="E62" s="134"/>
-      <c r="F62" s="135"/>
-      <c r="G62" s="136"/>
+      <c r="E62" s="166"/>
+      <c r="F62" s="167"/>
+      <c r="G62" s="171"/>
       <c r="H62" s="112"/>
       <c r="I62" s="112"/>
       <c r="J62" s="26"/>
@@ -10360,14 +10360,14 @@
       <c r="A63" s="1"/>
       <c r="B63" s="18"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="137" t="s">
+      <c r="D63" s="163" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="132"/>
-      <c r="F63" s="132"/>
-      <c r="G63" s="138"/>
-      <c r="H63" s="167"/>
-      <c r="I63" s="167"/>
+      <c r="E63" s="164"/>
+      <c r="F63" s="164"/>
+      <c r="G63" s="165"/>
+      <c r="H63" s="139"/>
+      <c r="I63" s="139"/>
       <c r="J63" s="50"/>
       <c r="K63" s="51"/>
       <c r="L63" s="51"/>
@@ -10484,12 +10484,12 @@
       <c r="A64" s="1"/>
       <c r="B64" s="18"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="134"/>
-      <c r="E64" s="135"/>
-      <c r="F64" s="135"/>
-      <c r="G64" s="139"/>
-      <c r="H64" s="167"/>
-      <c r="I64" s="167"/>
+      <c r="D64" s="166"/>
+      <c r="E64" s="167"/>
+      <c r="F64" s="167"/>
+      <c r="G64" s="168"/>
+      <c r="H64" s="139"/>
+      <c r="I64" s="139"/>
       <c r="J64" s="52"/>
       <c r="K64" s="49"/>
       <c r="L64" s="49"/>
@@ -10607,12 +10607,12 @@
       <c r="B65" s="18"/>
       <c r="C65" s="1"/>
       <c r="D65" s="34"/>
-      <c r="E65" s="131" t="s">
+      <c r="E65" s="169" t="s">
         <v>35</v>
       </c>
-      <c r="F65" s="132"/>
-      <c r="G65" s="133"/>
-      <c r="H65" s="184" t="s">
+      <c r="F65" s="164"/>
+      <c r="G65" s="170"/>
+      <c r="H65" s="138" t="s">
         <v>52</v>
       </c>
       <c r="I65" s="112">
@@ -10735,9 +10735,9 @@
       <c r="B66" s="18"/>
       <c r="C66" s="1"/>
       <c r="D66" s="34"/>
-      <c r="E66" s="134"/>
-      <c r="F66" s="135"/>
-      <c r="G66" s="136"/>
+      <c r="E66" s="166"/>
+      <c r="F66" s="167"/>
+      <c r="G66" s="171"/>
       <c r="H66" s="112"/>
       <c r="I66" s="112"/>
       <c r="J66" s="14"/>
@@ -10857,12 +10857,12 @@
       <c r="B67" s="18"/>
       <c r="C67" s="1"/>
       <c r="D67" s="34"/>
-      <c r="E67" s="131" t="s">
+      <c r="E67" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="F67" s="132"/>
-      <c r="G67" s="133"/>
-      <c r="H67" s="184" t="s">
+      <c r="F67" s="164"/>
+      <c r="G67" s="170"/>
+      <c r="H67" s="138" t="s">
         <v>53</v>
       </c>
       <c r="I67" s="112">
@@ -10985,9 +10985,9 @@
       <c r="B68" s="18"/>
       <c r="C68" s="1"/>
       <c r="D68" s="34"/>
-      <c r="E68" s="134"/>
-      <c r="F68" s="135"/>
-      <c r="G68" s="136"/>
+      <c r="E68" s="166"/>
+      <c r="F68" s="167"/>
+      <c r="G68" s="171"/>
       <c r="H68" s="112"/>
       <c r="I68" s="112"/>
       <c r="J68" s="14"/>
@@ -11107,12 +11107,12 @@
       <c r="B69" s="18"/>
       <c r="C69" s="1"/>
       <c r="D69" s="34"/>
-      <c r="E69" s="131" t="s">
+      <c r="E69" s="169" t="s">
         <v>36</v>
       </c>
-      <c r="F69" s="132"/>
-      <c r="G69" s="133"/>
-      <c r="H69" s="184" t="s">
+      <c r="F69" s="164"/>
+      <c r="G69" s="170"/>
+      <c r="H69" s="138" t="s">
         <v>54</v>
       </c>
       <c r="I69" s="112">
@@ -11235,9 +11235,9 @@
       <c r="B70" s="18"/>
       <c r="C70" s="1"/>
       <c r="D70" s="34"/>
-      <c r="E70" s="134"/>
-      <c r="F70" s="135"/>
-      <c r="G70" s="136"/>
+      <c r="E70" s="166"/>
+      <c r="F70" s="167"/>
+      <c r="G70" s="171"/>
       <c r="H70" s="112"/>
       <c r="I70" s="112"/>
       <c r="J70" s="14"/>
@@ -11357,12 +11357,12 @@
       <c r="B71" s="18"/>
       <c r="C71" s="1"/>
       <c r="D71" s="34"/>
-      <c r="E71" s="131" t="s">
+      <c r="E71" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F71" s="132"/>
-      <c r="G71" s="133"/>
-      <c r="H71" s="184" t="s">
+      <c r="F71" s="164"/>
+      <c r="G71" s="170"/>
+      <c r="H71" s="138" t="s">
         <v>55</v>
       </c>
       <c r="I71" s="112">
@@ -11485,9 +11485,9 @@
       <c r="B72" s="18"/>
       <c r="C72" s="1"/>
       <c r="D72" s="35"/>
-      <c r="E72" s="134"/>
-      <c r="F72" s="135"/>
-      <c r="G72" s="136"/>
+      <c r="E72" s="166"/>
+      <c r="F72" s="167"/>
+      <c r="G72" s="171"/>
       <c r="H72" s="112"/>
       <c r="I72" s="112"/>
       <c r="J72" s="26"/>
@@ -11605,14 +11605,14 @@
     <row r="73" spans="1:120" ht="9.75" customHeight="1">
       <c r="A73" s="16"/>
       <c r="B73" s="36"/>
-      <c r="C73" s="140" t="s">
+      <c r="C73" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="D73" s="132"/>
-      <c r="E73" s="132"/>
-      <c r="F73" s="132"/>
-      <c r="G73" s="138"/>
-      <c r="H73" s="184" t="s">
+      <c r="D73" s="164"/>
+      <c r="E73" s="164"/>
+      <c r="F73" s="164"/>
+      <c r="G73" s="165"/>
+      <c r="H73" s="138" t="s">
         <v>55</v>
       </c>
       <c r="I73" s="112">
@@ -11733,11 +11733,11 @@
     <row r="74" spans="1:120" ht="9.75" customHeight="1">
       <c r="A74" s="16"/>
       <c r="B74" s="36"/>
-      <c r="C74" s="141"/>
-      <c r="D74" s="135"/>
-      <c r="E74" s="135"/>
-      <c r="F74" s="135"/>
-      <c r="G74" s="139"/>
+      <c r="C74" s="179"/>
+      <c r="D74" s="167"/>
+      <c r="E74" s="167"/>
+      <c r="F74" s="167"/>
+      <c r="G74" s="168"/>
       <c r="H74" s="112"/>
       <c r="I74" s="112"/>
       <c r="J74" s="19"/>
@@ -11855,14 +11855,14 @@
     <row r="75" spans="1:120" ht="9.75" customHeight="1">
       <c r="A75" s="16"/>
       <c r="B75" s="36"/>
-      <c r="C75" s="140" t="s">
+      <c r="C75" s="146" t="s">
         <v>34</v>
       </c>
-      <c r="D75" s="132"/>
-      <c r="E75" s="132"/>
-      <c r="F75" s="132"/>
-      <c r="G75" s="138"/>
-      <c r="H75" s="184" t="s">
+      <c r="D75" s="164"/>
+      <c r="E75" s="164"/>
+      <c r="F75" s="164"/>
+      <c r="G75" s="165"/>
+      <c r="H75" s="138" t="s">
         <v>58</v>
       </c>
       <c r="I75" s="112"/>
@@ -11981,11 +11981,11 @@
     <row r="76" spans="1:120" ht="9.75" customHeight="1">
       <c r="A76" s="16"/>
       <c r="B76" s="36"/>
-      <c r="C76" s="142"/>
-      <c r="D76" s="142"/>
-      <c r="E76" s="142"/>
-      <c r="F76" s="142"/>
-      <c r="G76" s="142"/>
+      <c r="C76" s="162"/>
+      <c r="D76" s="162"/>
+      <c r="E76" s="162"/>
+      <c r="F76" s="162"/>
+      <c r="G76" s="162"/>
       <c r="H76" s="112"/>
       <c r="I76" s="112"/>
       <c r="J76" s="19"/>
@@ -12103,15 +12103,15 @@
     <row r="77" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A77" s="16"/>
       <c r="B77" s="71"/>
-      <c r="C77" s="143" t="s">
+      <c r="C77" s="187" t="s">
         <v>62</v>
       </c>
-      <c r="D77" s="144"/>
-      <c r="E77" s="144"/>
-      <c r="F77" s="144"/>
-      <c r="G77" s="145"/>
-      <c r="H77" s="185"/>
-      <c r="I77" s="181"/>
+      <c r="D77" s="188"/>
+      <c r="E77" s="188"/>
+      <c r="F77" s="188"/>
+      <c r="G77" s="189"/>
+      <c r="H77" s="140"/>
+      <c r="I77" s="129"/>
       <c r="J77" s="63"/>
       <c r="K77" s="64"/>
       <c r="L77" s="64"/>
@@ -12227,13 +12227,13 @@
     <row r="78" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A78" s="16"/>
       <c r="B78" s="71"/>
-      <c r="C78" s="146"/>
-      <c r="D78" s="147"/>
-      <c r="E78" s="147"/>
-      <c r="F78" s="147"/>
-      <c r="G78" s="148"/>
-      <c r="H78" s="186"/>
-      <c r="I78" s="182"/>
+      <c r="C78" s="190"/>
+      <c r="D78" s="191"/>
+      <c r="E78" s="191"/>
+      <c r="F78" s="191"/>
+      <c r="G78" s="192"/>
+      <c r="H78" s="141"/>
+      <c r="I78" s="130"/>
       <c r="J78" s="63"/>
       <c r="K78" s="64"/>
       <c r="L78" s="64"/>
@@ -12350,12 +12350,12 @@
       <c r="A79" s="16"/>
       <c r="B79" s="71"/>
       <c r="C79" s="76"/>
-      <c r="D79" s="115" t="s">
+      <c r="D79" s="132" t="s">
         <v>63</v>
       </c>
-      <c r="E79" s="116"/>
-      <c r="F79" s="116"/>
-      <c r="G79" s="117"/>
+      <c r="E79" s="133"/>
+      <c r="F79" s="133"/>
+      <c r="G79" s="134"/>
       <c r="H79" s="77"/>
       <c r="I79" s="67"/>
       <c r="J79" s="63"/>
@@ -12474,10 +12474,10 @@
       <c r="A80" s="16"/>
       <c r="B80" s="71"/>
       <c r="C80" s="76"/>
-      <c r="D80" s="118"/>
-      <c r="E80" s="119"/>
-      <c r="F80" s="119"/>
-      <c r="G80" s="120"/>
+      <c r="D80" s="135"/>
+      <c r="E80" s="136"/>
+      <c r="F80" s="136"/>
+      <c r="G80" s="137"/>
       <c r="H80" s="77"/>
       <c r="I80" s="67"/>
       <c r="J80" s="63"/>
@@ -12597,15 +12597,15 @@
       <c r="B81" s="36"/>
       <c r="C81" s="60"/>
       <c r="D81" s="70"/>
-      <c r="E81" s="149" t="s">
+      <c r="E81" s="105" t="s">
         <v>73</v>
       </c>
-      <c r="F81" s="149"/>
-      <c r="G81" s="149"/>
-      <c r="H81" s="103">
+      <c r="F81" s="105"/>
+      <c r="G81" s="105"/>
+      <c r="H81" s="111">
         <v>45611</v>
       </c>
-      <c r="I81" s="105">
+      <c r="I81" s="126">
         <v>100</v>
       </c>
       <c r="J81" s="19"/>
@@ -12725,11 +12725,11 @@
       <c r="B82" s="36"/>
       <c r="C82" s="60"/>
       <c r="D82" s="70"/>
-      <c r="E82" s="102"/>
-      <c r="F82" s="102"/>
-      <c r="G82" s="102"/>
-      <c r="H82" s="104"/>
-      <c r="I82" s="106"/>
+      <c r="E82" s="103"/>
+      <c r="F82" s="103"/>
+      <c r="G82" s="103"/>
+      <c r="H82" s="107"/>
+      <c r="I82" s="109"/>
       <c r="J82" s="19"/>
       <c r="K82" s="20"/>
       <c r="L82" s="20"/>
@@ -12847,15 +12847,15 @@
       <c r="B83" s="36"/>
       <c r="C83" s="60"/>
       <c r="D83" s="70"/>
-      <c r="E83" s="102" t="s">
+      <c r="E83" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="F83" s="102"/>
-      <c r="G83" s="102"/>
-      <c r="H83" s="103">
+      <c r="F83" s="103"/>
+      <c r="G83" s="103"/>
+      <c r="H83" s="111">
         <v>45615</v>
       </c>
-      <c r="I83" s="105">
+      <c r="I83" s="126">
         <v>100</v>
       </c>
       <c r="J83" s="19"/>
@@ -12975,11 +12975,11 @@
       <c r="B84" s="36"/>
       <c r="C84" s="60"/>
       <c r="D84" s="70"/>
-      <c r="E84" s="102"/>
-      <c r="F84" s="102"/>
-      <c r="G84" s="102"/>
-      <c r="H84" s="104"/>
-      <c r="I84" s="106"/>
+      <c r="E84" s="103"/>
+      <c r="F84" s="103"/>
+      <c r="G84" s="103"/>
+      <c r="H84" s="107"/>
+      <c r="I84" s="109"/>
       <c r="J84" s="19"/>
       <c r="K84" s="20"/>
       <c r="L84" s="20"/>
@@ -13097,15 +13097,15 @@
       <c r="B85" s="36"/>
       <c r="C85" s="60"/>
       <c r="D85" s="70"/>
-      <c r="E85" s="189" t="s">
+      <c r="E85" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="F85" s="121"/>
-      <c r="G85" s="122"/>
-      <c r="H85" s="111">
+      <c r="F85" s="115"/>
+      <c r="G85" s="116"/>
+      <c r="H85" s="110">
         <v>45617</v>
       </c>
-      <c r="I85" s="105">
+      <c r="I85" s="126">
         <v>100</v>
       </c>
       <c r="J85" s="62"/>
@@ -13225,11 +13225,11 @@
       <c r="B86" s="36"/>
       <c r="C86" s="60"/>
       <c r="D86" s="70"/>
-      <c r="E86" s="150"/>
-      <c r="F86" s="125"/>
-      <c r="G86" s="126"/>
-      <c r="H86" s="111"/>
-      <c r="I86" s="106"/>
+      <c r="E86" s="117"/>
+      <c r="F86" s="118"/>
+      <c r="G86" s="119"/>
+      <c r="H86" s="110"/>
+      <c r="I86" s="109"/>
       <c r="J86" s="62"/>
       <c r="K86" s="20"/>
       <c r="L86" s="20"/>
@@ -13346,16 +13346,16 @@
       <c r="A87" s="16"/>
       <c r="B87" s="71"/>
       <c r="C87" s="90"/>
-      <c r="D87" s="102" t="s">
+      <c r="D87" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="E87" s="102"/>
-      <c r="F87" s="102"/>
-      <c r="G87" s="102"/>
-      <c r="H87" s="103">
+      <c r="E87" s="103"/>
+      <c r="F87" s="103"/>
+      <c r="G87" s="103"/>
+      <c r="H87" s="111">
         <v>45615</v>
       </c>
-      <c r="I87" s="105">
+      <c r="I87" s="126">
         <v>100</v>
       </c>
       <c r="J87" s="62"/>
@@ -13474,12 +13474,12 @@
       <c r="A88" s="16"/>
       <c r="B88" s="71"/>
       <c r="C88" s="90"/>
-      <c r="D88" s="102"/>
-      <c r="E88" s="102"/>
-      <c r="F88" s="102"/>
-      <c r="G88" s="102"/>
-      <c r="H88" s="104"/>
-      <c r="I88" s="106"/>
+      <c r="D88" s="103"/>
+      <c r="E88" s="103"/>
+      <c r="F88" s="103"/>
+      <c r="G88" s="103"/>
+      <c r="H88" s="107"/>
+      <c r="I88" s="109"/>
       <c r="J88" s="62"/>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -13596,14 +13596,14 @@
       <c r="A89" s="16"/>
       <c r="B89" s="36"/>
       <c r="C89" s="79"/>
-      <c r="D89" s="115" t="s">
+      <c r="D89" s="132" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="116"/>
-      <c r="F89" s="116"/>
-      <c r="G89" s="117"/>
-      <c r="H89" s="187"/>
-      <c r="I89" s="188"/>
+      <c r="E89" s="133"/>
+      <c r="F89" s="133"/>
+      <c r="G89" s="134"/>
+      <c r="H89" s="131"/>
+      <c r="I89" s="128"/>
       <c r="J89" s="66"/>
       <c r="K89" s="64"/>
       <c r="L89" s="64"/>
@@ -13720,12 +13720,12 @@
       <c r="A90" s="16"/>
       <c r="B90" s="36"/>
       <c r="C90" s="79"/>
-      <c r="D90" s="118"/>
-      <c r="E90" s="119"/>
-      <c r="F90" s="119"/>
-      <c r="G90" s="120"/>
-      <c r="H90" s="187"/>
-      <c r="I90" s="188"/>
+      <c r="D90" s="135"/>
+      <c r="E90" s="136"/>
+      <c r="F90" s="136"/>
+      <c r="G90" s="137"/>
+      <c r="H90" s="131"/>
+      <c r="I90" s="128"/>
       <c r="J90" s="66"/>
       <c r="K90" s="64"/>
       <c r="L90" s="64"/>
@@ -13843,15 +13843,15 @@
       <c r="B91" s="36"/>
       <c r="C91" s="60"/>
       <c r="D91" s="70"/>
-      <c r="E91" s="149" t="s">
+      <c r="E91" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="F91" s="149"/>
-      <c r="G91" s="149"/>
-      <c r="H91" s="103">
+      <c r="F91" s="105"/>
+      <c r="G91" s="105"/>
+      <c r="H91" s="111">
         <v>45616</v>
       </c>
-      <c r="I91" s="105">
+      <c r="I91" s="126">
         <v>100</v>
       </c>
       <c r="J91" s="19"/>
@@ -13971,11 +13971,11 @@
       <c r="B92" s="36"/>
       <c r="C92" s="60"/>
       <c r="D92" s="70"/>
-      <c r="E92" s="102"/>
-      <c r="F92" s="102"/>
-      <c r="G92" s="102"/>
-      <c r="H92" s="104"/>
-      <c r="I92" s="106"/>
+      <c r="E92" s="103"/>
+      <c r="F92" s="103"/>
+      <c r="G92" s="103"/>
+      <c r="H92" s="107"/>
+      <c r="I92" s="109"/>
       <c r="J92" s="19"/>
       <c r="K92" s="20"/>
       <c r="L92" s="20"/>
@@ -14093,15 +14093,15 @@
       <c r="B93" s="36"/>
       <c r="C93" s="60"/>
       <c r="D93" s="70"/>
-      <c r="E93" s="102" t="s">
+      <c r="E93" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="F93" s="102"/>
-      <c r="G93" s="102"/>
-      <c r="H93" s="103">
+      <c r="F93" s="103"/>
+      <c r="G93" s="103"/>
+      <c r="H93" s="111">
         <v>45617</v>
       </c>
-      <c r="I93" s="105">
+      <c r="I93" s="126">
         <v>100</v>
       </c>
       <c r="J93" s="19"/>
@@ -14221,11 +14221,11 @@
       <c r="B94" s="36"/>
       <c r="C94" s="60"/>
       <c r="D94" s="70"/>
-      <c r="E94" s="102"/>
-      <c r="F94" s="102"/>
-      <c r="G94" s="102"/>
-      <c r="H94" s="104"/>
-      <c r="I94" s="106"/>
+      <c r="E94" s="103"/>
+      <c r="F94" s="103"/>
+      <c r="G94" s="103"/>
+      <c r="H94" s="107"/>
+      <c r="I94" s="109"/>
       <c r="J94" s="19"/>
       <c r="K94" s="20"/>
       <c r="L94" s="20"/>
@@ -14343,15 +14343,15 @@
       <c r="B95" s="36"/>
       <c r="C95" s="60"/>
       <c r="D95" s="70"/>
-      <c r="E95" s="102" t="s">
+      <c r="E95" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="F95" s="102"/>
-      <c r="G95" s="102"/>
-      <c r="H95" s="103">
+      <c r="F95" s="103"/>
+      <c r="G95" s="103"/>
+      <c r="H95" s="111">
         <v>45618</v>
       </c>
-      <c r="I95" s="105">
+      <c r="I95" s="126">
         <v>100</v>
       </c>
       <c r="J95" s="19"/>
@@ -14471,11 +14471,11 @@
       <c r="B96" s="36"/>
       <c r="C96" s="60"/>
       <c r="D96" s="70"/>
-      <c r="E96" s="102"/>
-      <c r="F96" s="102"/>
-      <c r="G96" s="102"/>
-      <c r="H96" s="104"/>
-      <c r="I96" s="106"/>
+      <c r="E96" s="103"/>
+      <c r="F96" s="103"/>
+      <c r="G96" s="103"/>
+      <c r="H96" s="107"/>
+      <c r="I96" s="109"/>
       <c r="J96" s="19"/>
       <c r="K96" s="20"/>
       <c r="L96" s="20"/>
@@ -14593,15 +14593,15 @@
       <c r="B97" s="36"/>
       <c r="C97" s="60"/>
       <c r="D97" s="70"/>
-      <c r="E97" s="102" t="s">
+      <c r="E97" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="F97" s="102"/>
-      <c r="G97" s="102"/>
-      <c r="H97" s="103">
+      <c r="F97" s="103"/>
+      <c r="G97" s="103"/>
+      <c r="H97" s="111">
         <v>45621</v>
       </c>
-      <c r="I97" s="105">
+      <c r="I97" s="126">
         <v>100</v>
       </c>
       <c r="J97" s="19"/>
@@ -14721,11 +14721,11 @@
       <c r="B98" s="36"/>
       <c r="C98" s="60"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="102"/>
-      <c r="F98" s="102"/>
-      <c r="G98" s="102"/>
-      <c r="H98" s="104"/>
-      <c r="I98" s="106"/>
+      <c r="E98" s="103"/>
+      <c r="F98" s="103"/>
+      <c r="G98" s="103"/>
+      <c r="H98" s="107"/>
+      <c r="I98" s="109"/>
       <c r="J98" s="19"/>
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
@@ -14843,15 +14843,15 @@
       <c r="B99" s="36"/>
       <c r="C99" s="60"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="102" t="s">
+      <c r="E99" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="F99" s="102"/>
-      <c r="G99" s="102"/>
-      <c r="H99" s="103">
+      <c r="F99" s="103"/>
+      <c r="G99" s="103"/>
+      <c r="H99" s="111">
         <v>45622</v>
       </c>
-      <c r="I99" s="105">
+      <c r="I99" s="126">
         <v>100</v>
       </c>
       <c r="J99" s="19"/>
@@ -14971,11 +14971,11 @@
       <c r="B100" s="36"/>
       <c r="C100" s="60"/>
       <c r="D100" s="70"/>
-      <c r="E100" s="102"/>
-      <c r="F100" s="102"/>
-      <c r="G100" s="102"/>
-      <c r="H100" s="104"/>
-      <c r="I100" s="106"/>
+      <c r="E100" s="103"/>
+      <c r="F100" s="103"/>
+      <c r="G100" s="103"/>
+      <c r="H100" s="107"/>
+      <c r="I100" s="109"/>
       <c r="J100" s="19"/>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -15093,12 +15093,12 @@
       <c r="B101" s="71"/>
       <c r="C101" s="91"/>
       <c r="D101" s="70"/>
-      <c r="E101" s="150" t="s">
+      <c r="E101" s="117" t="s">
         <v>61</v>
       </c>
-      <c r="F101" s="125"/>
-      <c r="G101" s="126"/>
-      <c r="H101" s="103">
+      <c r="F101" s="118"/>
+      <c r="G101" s="119"/>
+      <c r="H101" s="111">
         <v>45623</v>
       </c>
       <c r="I101" s="112">
@@ -15221,10 +15221,10 @@
       <c r="B102" s="71"/>
       <c r="C102" s="91"/>
       <c r="D102" s="70"/>
-      <c r="E102" s="150"/>
-      <c r="F102" s="125"/>
-      <c r="G102" s="126"/>
-      <c r="H102" s="104"/>
+      <c r="E102" s="117"/>
+      <c r="F102" s="118"/>
+      <c r="G102" s="119"/>
+      <c r="H102" s="107"/>
       <c r="I102" s="112"/>
       <c r="J102" s="62"/>
       <c r="K102" s="20"/>
@@ -15342,16 +15342,16 @@
       <c r="A103" s="16"/>
       <c r="B103" s="71"/>
       <c r="C103" s="90"/>
-      <c r="D103" s="102" t="s">
+      <c r="D103" s="103" t="s">
         <v>77</v>
       </c>
-      <c r="E103" s="102"/>
-      <c r="F103" s="102"/>
-      <c r="G103" s="102"/>
-      <c r="H103" s="103">
+      <c r="E103" s="103"/>
+      <c r="F103" s="103"/>
+      <c r="G103" s="103"/>
+      <c r="H103" s="111">
         <v>45622</v>
       </c>
-      <c r="I103" s="109">
+      <c r="I103" s="113">
         <v>100</v>
       </c>
       <c r="J103" s="62"/>
@@ -15470,12 +15470,12 @@
       <c r="A104" s="16"/>
       <c r="B104" s="71"/>
       <c r="C104" s="90"/>
-      <c r="D104" s="102"/>
-      <c r="E104" s="102"/>
-      <c r="F104" s="102"/>
-      <c r="G104" s="102"/>
-      <c r="H104" s="104"/>
-      <c r="I104" s="110"/>
+      <c r="D104" s="103"/>
+      <c r="E104" s="103"/>
+      <c r="F104" s="103"/>
+      <c r="G104" s="103"/>
+      <c r="H104" s="107"/>
+      <c r="I104" s="143"/>
       <c r="J104" s="62"/>
       <c r="K104" s="20"/>
       <c r="L104" s="20"/>
@@ -15591,15 +15591,15 @@
     <row r="105" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A105" s="16"/>
       <c r="B105" s="71"/>
-      <c r="C105" s="143" t="s">
+      <c r="C105" s="187" t="s">
         <v>64</v>
       </c>
-      <c r="D105" s="144"/>
-      <c r="E105" s="144"/>
-      <c r="F105" s="144"/>
-      <c r="G105" s="145"/>
-      <c r="H105" s="190"/>
-      <c r="I105" s="188"/>
+      <c r="D105" s="188"/>
+      <c r="E105" s="188"/>
+      <c r="F105" s="188"/>
+      <c r="G105" s="189"/>
+      <c r="H105" s="127"/>
+      <c r="I105" s="128"/>
       <c r="J105" s="66"/>
       <c r="K105" s="64"/>
       <c r="L105" s="64"/>
@@ -15715,13 +15715,13 @@
     <row r="106" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A106" s="16"/>
       <c r="B106" s="71"/>
-      <c r="C106" s="146"/>
-      <c r="D106" s="147"/>
-      <c r="E106" s="147"/>
-      <c r="F106" s="147"/>
-      <c r="G106" s="148"/>
-      <c r="H106" s="190"/>
-      <c r="I106" s="188"/>
+      <c r="C106" s="190"/>
+      <c r="D106" s="191"/>
+      <c r="E106" s="191"/>
+      <c r="F106" s="191"/>
+      <c r="G106" s="192"/>
+      <c r="H106" s="127"/>
+      <c r="I106" s="128"/>
       <c r="J106" s="66"/>
       <c r="K106" s="64"/>
       <c r="L106" s="64"/>
@@ -15838,14 +15838,14 @@
       <c r="A107" s="16"/>
       <c r="B107" s="36"/>
       <c r="C107" s="78"/>
-      <c r="D107" s="115" t="s">
+      <c r="D107" s="132" t="s">
         <v>59</v>
       </c>
-      <c r="E107" s="116"/>
-      <c r="F107" s="116"/>
-      <c r="G107" s="117"/>
-      <c r="H107" s="190"/>
-      <c r="I107" s="188"/>
+      <c r="E107" s="133"/>
+      <c r="F107" s="133"/>
+      <c r="G107" s="134"/>
+      <c r="H107" s="127"/>
+      <c r="I107" s="128"/>
       <c r="J107" s="66"/>
       <c r="K107" s="64"/>
       <c r="L107" s="64"/>
@@ -15962,12 +15962,12 @@
       <c r="A108" s="16"/>
       <c r="B108" s="36"/>
       <c r="C108" s="76"/>
-      <c r="D108" s="118"/>
-      <c r="E108" s="119"/>
-      <c r="F108" s="119"/>
-      <c r="G108" s="120"/>
-      <c r="H108" s="190"/>
-      <c r="I108" s="188"/>
+      <c r="D108" s="135"/>
+      <c r="E108" s="136"/>
+      <c r="F108" s="136"/>
+      <c r="G108" s="137"/>
+      <c r="H108" s="127"/>
+      <c r="I108" s="128"/>
       <c r="J108" s="66"/>
       <c r="K108" s="64"/>
       <c r="L108" s="64"/>
@@ -16085,15 +16085,15 @@
       <c r="B109" s="36"/>
       <c r="C109" s="60"/>
       <c r="D109" s="70"/>
-      <c r="E109" s="149" t="s">
+      <c r="E109" s="105" t="s">
         <v>73</v>
       </c>
-      <c r="F109" s="149"/>
-      <c r="G109" s="149"/>
-      <c r="H109" s="103">
+      <c r="F109" s="105"/>
+      <c r="G109" s="105"/>
+      <c r="H109" s="111">
         <v>45624</v>
       </c>
-      <c r="I109" s="109">
+      <c r="I109" s="113">
         <v>100</v>
       </c>
       <c r="J109" s="62"/>
@@ -16213,11 +16213,11 @@
       <c r="B110" s="36"/>
       <c r="C110" s="60"/>
       <c r="D110" s="70"/>
-      <c r="E110" s="102"/>
-      <c r="F110" s="102"/>
-      <c r="G110" s="102"/>
-      <c r="H110" s="104"/>
-      <c r="I110" s="110"/>
+      <c r="E110" s="103"/>
+      <c r="F110" s="103"/>
+      <c r="G110" s="103"/>
+      <c r="H110" s="107"/>
+      <c r="I110" s="143"/>
       <c r="J110" s="62"/>
       <c r="K110" s="20"/>
       <c r="L110" s="20"/>
@@ -16262,8 +16262,8 @@
       <c r="AY110" s="21"/>
       <c r="AZ110" s="20"/>
       <c r="BA110" s="20"/>
-      <c r="BB110" s="69"/>
-      <c r="BC110" s="69"/>
+      <c r="BB110" s="75"/>
+      <c r="BC110" s="75"/>
       <c r="BD110" s="69"/>
       <c r="BE110" s="21"/>
       <c r="BF110" s="21"/>
@@ -16335,15 +16335,15 @@
       <c r="B111" s="36"/>
       <c r="C111" s="60"/>
       <c r="D111" s="70"/>
-      <c r="E111" s="102" t="s">
+      <c r="E111" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="F111" s="102"/>
-      <c r="G111" s="102"/>
-      <c r="H111" s="103">
+      <c r="F111" s="103"/>
+      <c r="G111" s="103"/>
+      <c r="H111" s="111">
         <v>45625</v>
       </c>
-      <c r="I111" s="109"/>
+      <c r="I111" s="113"/>
       <c r="J111" s="62"/>
       <c r="K111" s="20"/>
       <c r="L111" s="20"/>
@@ -16461,11 +16461,11 @@
       <c r="B112" s="36"/>
       <c r="C112" s="60"/>
       <c r="D112" s="70"/>
-      <c r="E112" s="102"/>
-      <c r="F112" s="102"/>
-      <c r="G112" s="102"/>
-      <c r="H112" s="104"/>
-      <c r="I112" s="110"/>
+      <c r="E112" s="103"/>
+      <c r="F112" s="103"/>
+      <c r="G112" s="103"/>
+      <c r="H112" s="107"/>
+      <c r="I112" s="143"/>
       <c r="J112" s="62"/>
       <c r="K112" s="20"/>
       <c r="L112" s="20"/>
@@ -16583,12 +16583,12 @@
       <c r="B113" s="71"/>
       <c r="C113" s="91"/>
       <c r="D113" s="70"/>
-      <c r="E113" s="102" t="s">
+      <c r="E113" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="F113" s="102"/>
-      <c r="G113" s="102"/>
-      <c r="H113" s="111">
+      <c r="F113" s="103"/>
+      <c r="G113" s="103"/>
+      <c r="H113" s="110">
         <v>45629</v>
       </c>
       <c r="I113" s="112"/>
@@ -16709,11 +16709,11 @@
       <c r="B114" s="71"/>
       <c r="C114" s="91"/>
       <c r="D114" s="70"/>
-      <c r="E114" s="198"/>
-      <c r="F114" s="198"/>
-      <c r="G114" s="198"/>
-      <c r="H114" s="103"/>
-      <c r="I114" s="109"/>
+      <c r="E114" s="125"/>
+      <c r="F114" s="125"/>
+      <c r="G114" s="125"/>
+      <c r="H114" s="111"/>
+      <c r="I114" s="113"/>
       <c r="J114" s="62"/>
       <c r="K114" s="20"/>
       <c r="L114" s="20"/>
@@ -16830,13 +16830,13 @@
       <c r="A115" s="16"/>
       <c r="B115" s="71"/>
       <c r="C115" s="91"/>
-      <c r="D115" s="102" t="s">
+      <c r="D115" s="103" t="s">
         <v>78</v>
       </c>
-      <c r="E115" s="102"/>
-      <c r="F115" s="102"/>
-      <c r="G115" s="102"/>
-      <c r="H115" s="111">
+      <c r="E115" s="103"/>
+      <c r="F115" s="103"/>
+      <c r="G115" s="103"/>
+      <c r="H115" s="110">
         <v>45625</v>
       </c>
       <c r="I115" s="112"/>
@@ -16956,11 +16956,11 @@
       <c r="A116" s="16"/>
       <c r="B116" s="71"/>
       <c r="C116" s="91"/>
-      <c r="D116" s="102"/>
-      <c r="E116" s="102"/>
-      <c r="F116" s="102"/>
-      <c r="G116" s="102"/>
-      <c r="H116" s="111"/>
+      <c r="D116" s="103"/>
+      <c r="E116" s="103"/>
+      <c r="F116" s="103"/>
+      <c r="G116" s="103"/>
+      <c r="H116" s="110"/>
       <c r="I116" s="112"/>
       <c r="J116" s="62"/>
       <c r="K116" s="20"/>
@@ -17078,14 +17078,14 @@
       <c r="A117" s="16"/>
       <c r="B117" s="36"/>
       <c r="C117" s="80"/>
-      <c r="D117" s="115" t="s">
+      <c r="D117" s="132" t="s">
         <v>60</v>
       </c>
-      <c r="E117" s="116"/>
-      <c r="F117" s="116"/>
-      <c r="G117" s="117"/>
-      <c r="H117" s="191"/>
-      <c r="I117" s="181"/>
+      <c r="E117" s="133"/>
+      <c r="F117" s="133"/>
+      <c r="G117" s="134"/>
+      <c r="H117" s="121"/>
+      <c r="I117" s="129"/>
       <c r="J117" s="63"/>
       <c r="K117" s="64"/>
       <c r="L117" s="64"/>
@@ -17202,12 +17202,12 @@
       <c r="A118" s="16"/>
       <c r="B118" s="36"/>
       <c r="C118" s="80"/>
-      <c r="D118" s="118"/>
-      <c r="E118" s="119"/>
-      <c r="F118" s="119"/>
-      <c r="G118" s="120"/>
-      <c r="H118" s="192"/>
-      <c r="I118" s="182"/>
+      <c r="D118" s="135"/>
+      <c r="E118" s="136"/>
+      <c r="F118" s="136"/>
+      <c r="G118" s="137"/>
+      <c r="H118" s="122"/>
+      <c r="I118" s="130"/>
       <c r="J118" s="63"/>
       <c r="K118" s="64"/>
       <c r="L118" s="64"/>
@@ -17325,15 +17325,17 @@
       <c r="B119" s="36"/>
       <c r="C119" s="60"/>
       <c r="D119" s="70"/>
-      <c r="E119" s="149" t="s">
+      <c r="E119" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="F119" s="149"/>
-      <c r="G119" s="149"/>
-      <c r="H119" s="103">
+      <c r="F119" s="105"/>
+      <c r="G119" s="105"/>
+      <c r="H119" s="111">
         <v>45629</v>
       </c>
-      <c r="I119" s="105"/>
+      <c r="I119" s="126">
+        <v>100</v>
+      </c>
       <c r="J119" s="19"/>
       <c r="K119" s="20"/>
       <c r="L119" s="20"/>
@@ -17451,11 +17453,11 @@
       <c r="B120" s="36"/>
       <c r="C120" s="60"/>
       <c r="D120" s="70"/>
-      <c r="E120" s="102"/>
-      <c r="F120" s="102"/>
-      <c r="G120" s="102"/>
-      <c r="H120" s="104"/>
-      <c r="I120" s="106"/>
+      <c r="E120" s="103"/>
+      <c r="F120" s="103"/>
+      <c r="G120" s="103"/>
+      <c r="H120" s="107"/>
+      <c r="I120" s="109"/>
       <c r="J120" s="19"/>
       <c r="K120" s="20"/>
       <c r="L120" s="20"/>
@@ -17505,8 +17507,8 @@
       <c r="BD120" s="20"/>
       <c r="BE120" s="21"/>
       <c r="BF120" s="21"/>
-      <c r="BG120" s="20"/>
-      <c r="BH120" s="20"/>
+      <c r="BG120" s="75"/>
+      <c r="BH120" s="75"/>
       <c r="BI120" s="20"/>
       <c r="BJ120" s="64"/>
       <c r="BK120" s="64"/>
@@ -17573,15 +17575,15 @@
       <c r="B121" s="36"/>
       <c r="C121" s="60"/>
       <c r="D121" s="70"/>
-      <c r="E121" s="102" t="s">
+      <c r="E121" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="F121" s="102"/>
-      <c r="G121" s="102"/>
-      <c r="H121" s="103">
+      <c r="F121" s="103"/>
+      <c r="G121" s="103"/>
+      <c r="H121" s="111">
         <v>45630</v>
       </c>
-      <c r="I121" s="105"/>
+      <c r="I121" s="126"/>
       <c r="J121" s="19"/>
       <c r="K121" s="20"/>
       <c r="L121" s="20"/>
@@ -17699,11 +17701,11 @@
       <c r="B122" s="36"/>
       <c r="C122" s="60"/>
       <c r="D122" s="70"/>
-      <c r="E122" s="102"/>
-      <c r="F122" s="102"/>
-      <c r="G122" s="102"/>
-      <c r="H122" s="104"/>
-      <c r="I122" s="106"/>
+      <c r="E122" s="103"/>
+      <c r="F122" s="103"/>
+      <c r="G122" s="103"/>
+      <c r="H122" s="107"/>
+      <c r="I122" s="109"/>
       <c r="J122" s="19"/>
       <c r="K122" s="20"/>
       <c r="L122" s="20"/>
@@ -17821,12 +17823,12 @@
       <c r="B123" s="36"/>
       <c r="C123" s="60"/>
       <c r="D123" s="70"/>
-      <c r="E123" s="102" t="s">
+      <c r="E123" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="F123" s="102"/>
-      <c r="G123" s="102"/>
-      <c r="H123" s="197">
+      <c r="F123" s="103"/>
+      <c r="G123" s="103"/>
+      <c r="H123" s="120">
         <v>45631</v>
       </c>
       <c r="I123" s="112"/>
@@ -17947,10 +17949,10 @@
       <c r="B124" s="36"/>
       <c r="C124" s="60"/>
       <c r="D124" s="70"/>
-      <c r="E124" s="102"/>
-      <c r="F124" s="102"/>
-      <c r="G124" s="102"/>
-      <c r="H124" s="197"/>
+      <c r="E124" s="103"/>
+      <c r="F124" s="103"/>
+      <c r="G124" s="103"/>
+      <c r="H124" s="120"/>
       <c r="I124" s="112"/>
       <c r="J124" s="62"/>
       <c r="K124" s="20"/>
@@ -18069,12 +18071,12 @@
       <c r="B125" s="36"/>
       <c r="C125" s="60"/>
       <c r="D125" s="70"/>
-      <c r="E125" s="102" t="s">
+      <c r="E125" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="F125" s="102"/>
-      <c r="G125" s="102"/>
-      <c r="H125" s="111">
+      <c r="F125" s="103"/>
+      <c r="G125" s="103"/>
+      <c r="H125" s="110">
         <v>45632</v>
       </c>
       <c r="I125" s="112"/>
@@ -18195,10 +18197,10 @@
       <c r="B126" s="36"/>
       <c r="C126" s="60"/>
       <c r="D126" s="70"/>
-      <c r="E126" s="102"/>
-      <c r="F126" s="102"/>
-      <c r="G126" s="102"/>
-      <c r="H126" s="111"/>
+      <c r="E126" s="103"/>
+      <c r="F126" s="103"/>
+      <c r="G126" s="103"/>
+      <c r="H126" s="110"/>
       <c r="I126" s="112"/>
       <c r="J126" s="62"/>
       <c r="K126" s="20"/>
@@ -18317,15 +18319,15 @@
       <c r="B127" s="36"/>
       <c r="C127" s="60"/>
       <c r="D127" s="70"/>
-      <c r="E127" s="102" t="s">
+      <c r="E127" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="F127" s="102"/>
-      <c r="G127" s="102"/>
-      <c r="H127" s="103">
+      <c r="F127" s="103"/>
+      <c r="G127" s="103"/>
+      <c r="H127" s="111">
         <v>45635</v>
       </c>
-      <c r="I127" s="105"/>
+      <c r="I127" s="126"/>
       <c r="J127" s="19"/>
       <c r="K127" s="20"/>
       <c r="L127" s="20"/>
@@ -18443,11 +18445,11 @@
       <c r="B128" s="36"/>
       <c r="C128" s="60"/>
       <c r="D128" s="70"/>
-      <c r="E128" s="198"/>
-      <c r="F128" s="198"/>
-      <c r="G128" s="198"/>
-      <c r="H128" s="104"/>
-      <c r="I128" s="106"/>
+      <c r="E128" s="125"/>
+      <c r="F128" s="125"/>
+      <c r="G128" s="125"/>
+      <c r="H128" s="107"/>
+      <c r="I128" s="109"/>
       <c r="J128" s="19"/>
       <c r="K128" s="20"/>
       <c r="L128" s="20"/>
@@ -18565,12 +18567,12 @@
       <c r="B129" s="71"/>
       <c r="C129" s="91"/>
       <c r="D129" s="70"/>
-      <c r="E129" s="189" t="s">
+      <c r="E129" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="F129" s="121"/>
-      <c r="G129" s="122"/>
-      <c r="H129" s="111">
+      <c r="F129" s="115"/>
+      <c r="G129" s="116"/>
+      <c r="H129" s="110">
         <v>45638</v>
       </c>
       <c r="I129" s="112"/>
@@ -18691,10 +18693,10 @@
       <c r="B130" s="71"/>
       <c r="C130" s="91"/>
       <c r="D130" s="70"/>
-      <c r="E130" s="150"/>
-      <c r="F130" s="125"/>
-      <c r="G130" s="126"/>
-      <c r="H130" s="111"/>
+      <c r="E130" s="117"/>
+      <c r="F130" s="118"/>
+      <c r="G130" s="119"/>
+      <c r="H130" s="110"/>
       <c r="I130" s="112"/>
       <c r="J130" s="62"/>
       <c r="K130" s="20"/>
@@ -18812,16 +18814,16 @@
       <c r="A131" s="16"/>
       <c r="B131" s="71"/>
       <c r="C131" s="91"/>
-      <c r="D131" s="102" t="s">
+      <c r="D131" s="103" t="s">
         <v>79</v>
       </c>
-      <c r="E131" s="102"/>
-      <c r="F131" s="102"/>
-      <c r="G131" s="102"/>
-      <c r="H131" s="103">
+      <c r="E131" s="103"/>
+      <c r="F131" s="103"/>
+      <c r="G131" s="103"/>
+      <c r="H131" s="111">
         <v>45635</v>
       </c>
-      <c r="I131" s="109"/>
+      <c r="I131" s="113"/>
       <c r="J131" s="62"/>
       <c r="K131" s="20"/>
       <c r="L131" s="20"/>
@@ -18938,12 +18940,12 @@
       <c r="A132" s="16"/>
       <c r="B132" s="71"/>
       <c r="C132" s="90"/>
-      <c r="D132" s="102"/>
-      <c r="E132" s="102"/>
-      <c r="F132" s="102"/>
-      <c r="G132" s="102"/>
-      <c r="H132" s="104"/>
-      <c r="I132" s="110"/>
+      <c r="D132" s="103"/>
+      <c r="E132" s="103"/>
+      <c r="F132" s="103"/>
+      <c r="G132" s="103"/>
+      <c r="H132" s="107"/>
+      <c r="I132" s="143"/>
       <c r="J132" s="62"/>
       <c r="K132" s="20"/>
       <c r="L132" s="20"/>
@@ -19059,15 +19061,15 @@
     <row r="133" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A133" s="16"/>
       <c r="B133" s="36"/>
-      <c r="C133" s="115" t="s">
+      <c r="C133" s="132" t="s">
         <v>67</v>
       </c>
-      <c r="D133" s="116"/>
-      <c r="E133" s="116"/>
-      <c r="F133" s="116"/>
-      <c r="G133" s="117"/>
-      <c r="H133" s="191"/>
-      <c r="I133" s="107"/>
+      <c r="D133" s="133"/>
+      <c r="E133" s="133"/>
+      <c r="F133" s="133"/>
+      <c r="G133" s="134"/>
+      <c r="H133" s="121"/>
+      <c r="I133" s="123"/>
       <c r="J133" s="66"/>
       <c r="K133" s="64"/>
       <c r="L133" s="64"/>
@@ -19183,13 +19185,13 @@
     <row r="134" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A134" s="16"/>
       <c r="B134" s="36"/>
-      <c r="C134" s="118"/>
-      <c r="D134" s="119"/>
-      <c r="E134" s="119"/>
-      <c r="F134" s="119"/>
-      <c r="G134" s="120"/>
-      <c r="H134" s="192"/>
-      <c r="I134" s="108"/>
+      <c r="C134" s="135"/>
+      <c r="D134" s="136"/>
+      <c r="E134" s="136"/>
+      <c r="F134" s="136"/>
+      <c r="G134" s="137"/>
+      <c r="H134" s="122"/>
+      <c r="I134" s="124"/>
       <c r="J134" s="66"/>
       <c r="K134" s="64"/>
       <c r="L134" s="64"/>
@@ -19306,14 +19308,14 @@
       <c r="A135" s="16"/>
       <c r="B135" s="36"/>
       <c r="C135" s="60"/>
-      <c r="D135" s="115" t="s">
+      <c r="D135" s="132" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="116"/>
-      <c r="F135" s="116"/>
-      <c r="G135" s="117"/>
-      <c r="H135" s="113"/>
-      <c r="I135" s="181"/>
+      <c r="E135" s="133"/>
+      <c r="F135" s="133"/>
+      <c r="G135" s="134"/>
+      <c r="H135" s="193"/>
+      <c r="I135" s="129"/>
       <c r="J135" s="63"/>
       <c r="K135" s="64"/>
       <c r="L135" s="64"/>
@@ -19430,12 +19432,12 @@
       <c r="A136" s="16"/>
       <c r="B136" s="36"/>
       <c r="C136" s="60"/>
-      <c r="D136" s="118"/>
-      <c r="E136" s="119"/>
-      <c r="F136" s="119"/>
-      <c r="G136" s="120"/>
-      <c r="H136" s="130"/>
-      <c r="I136" s="183"/>
+      <c r="D136" s="135"/>
+      <c r="E136" s="136"/>
+      <c r="F136" s="136"/>
+      <c r="G136" s="137"/>
+      <c r="H136" s="198"/>
+      <c r="I136" s="144"/>
       <c r="J136" s="63"/>
       <c r="K136" s="64"/>
       <c r="L136" s="64"/>
@@ -19553,15 +19555,15 @@
       <c r="B137" s="36"/>
       <c r="C137" s="72"/>
       <c r="D137" s="74"/>
-      <c r="E137" s="121" t="s">
+      <c r="E137" s="115" t="s">
         <v>73</v>
       </c>
-      <c r="F137" s="121"/>
-      <c r="G137" s="122"/>
-      <c r="H137" s="103">
+      <c r="F137" s="115"/>
+      <c r="G137" s="116"/>
+      <c r="H137" s="111">
         <v>45636</v>
       </c>
-      <c r="I137" s="109"/>
+      <c r="I137" s="113"/>
       <c r="J137" s="62"/>
       <c r="K137" s="20"/>
       <c r="L137" s="20"/>
@@ -19679,11 +19681,11 @@
       <c r="B138" s="36"/>
       <c r="C138" s="72"/>
       <c r="D138" s="70"/>
-      <c r="E138" s="123"/>
-      <c r="F138" s="123"/>
-      <c r="G138" s="124"/>
-      <c r="H138" s="104"/>
-      <c r="I138" s="110"/>
+      <c r="E138" s="185"/>
+      <c r="F138" s="185"/>
+      <c r="G138" s="186"/>
+      <c r="H138" s="107"/>
+      <c r="I138" s="143"/>
       <c r="J138" s="62"/>
       <c r="K138" s="20"/>
       <c r="L138" s="20"/>
@@ -19740,7 +19742,7 @@
       <c r="BK138" s="64"/>
       <c r="BL138" s="21"/>
       <c r="BM138" s="21"/>
-      <c r="BN138" s="20"/>
+      <c r="BN138" s="69"/>
       <c r="BO138" s="69"/>
       <c r="BP138" s="69"/>
       <c r="BQ138" s="69"/>
@@ -19801,15 +19803,15 @@
       <c r="B139" s="36"/>
       <c r="C139" s="72"/>
       <c r="D139" s="70"/>
-      <c r="E139" s="121" t="s">
+      <c r="E139" s="115" t="s">
         <v>74</v>
       </c>
-      <c r="F139" s="121"/>
-      <c r="G139" s="122"/>
-      <c r="H139" s="103">
+      <c r="F139" s="115"/>
+      <c r="G139" s="116"/>
+      <c r="H139" s="111">
         <v>45637</v>
       </c>
-      <c r="I139" s="109"/>
+      <c r="I139" s="113"/>
       <c r="J139" s="62"/>
       <c r="K139" s="20"/>
       <c r="L139" s="20"/>
@@ -19927,11 +19929,11 @@
       <c r="B140" s="36"/>
       <c r="C140" s="72"/>
       <c r="D140" s="70"/>
-      <c r="E140" s="125"/>
-      <c r="F140" s="125"/>
-      <c r="G140" s="126"/>
-      <c r="H140" s="104"/>
-      <c r="I140" s="110"/>
+      <c r="E140" s="118"/>
+      <c r="F140" s="118"/>
+      <c r="G140" s="119"/>
+      <c r="H140" s="107"/>
+      <c r="I140" s="143"/>
       <c r="J140" s="62"/>
       <c r="K140" s="20"/>
       <c r="L140" s="20"/>
@@ -20048,13 +20050,13 @@
       <c r="A141" s="16"/>
       <c r="B141" s="36"/>
       <c r="C141" s="82"/>
-      <c r="D141" s="102" t="s">
+      <c r="D141" s="103" t="s">
         <v>80</v>
       </c>
-      <c r="E141" s="102"/>
-      <c r="F141" s="102"/>
-      <c r="G141" s="102"/>
-      <c r="H141" s="103">
+      <c r="E141" s="103"/>
+      <c r="F141" s="103"/>
+      <c r="G141" s="103"/>
+      <c r="H141" s="111">
         <v>45637</v>
       </c>
       <c r="I141" s="92"/>
@@ -20174,11 +20176,11 @@
       <c r="A142" s="16"/>
       <c r="B142" s="36"/>
       <c r="C142" s="82"/>
-      <c r="D142" s="102"/>
-      <c r="E142" s="102"/>
-      <c r="F142" s="102"/>
-      <c r="G142" s="102"/>
-      <c r="H142" s="104"/>
+      <c r="D142" s="103"/>
+      <c r="E142" s="103"/>
+      <c r="F142" s="103"/>
+      <c r="G142" s="103"/>
+      <c r="H142" s="107"/>
       <c r="I142" s="92"/>
       <c r="J142" s="62"/>
       <c r="K142" s="20"/>
@@ -20296,14 +20298,14 @@
       <c r="A143" s="16"/>
       <c r="B143" s="36"/>
       <c r="C143" s="72"/>
-      <c r="D143" s="127" t="s">
+      <c r="D143" s="195" t="s">
         <v>66</v>
       </c>
-      <c r="E143" s="128"/>
-      <c r="F143" s="128"/>
-      <c r="G143" s="129"/>
-      <c r="H143" s="113"/>
-      <c r="I143" s="107"/>
+      <c r="E143" s="196"/>
+      <c r="F143" s="196"/>
+      <c r="G143" s="197"/>
+      <c r="H143" s="193"/>
+      <c r="I143" s="123"/>
       <c r="J143" s="66"/>
       <c r="K143" s="64"/>
       <c r="L143" s="64"/>
@@ -20420,12 +20422,12 @@
       <c r="A144" s="16"/>
       <c r="B144" s="36"/>
       <c r="C144" s="72"/>
-      <c r="D144" s="118"/>
-      <c r="E144" s="119"/>
-      <c r="F144" s="119"/>
-      <c r="G144" s="120"/>
-      <c r="H144" s="114"/>
-      <c r="I144" s="108"/>
+      <c r="D144" s="135"/>
+      <c r="E144" s="136"/>
+      <c r="F144" s="136"/>
+      <c r="G144" s="137"/>
+      <c r="H144" s="194"/>
+      <c r="I144" s="124"/>
       <c r="J144" s="66"/>
       <c r="K144" s="64"/>
       <c r="L144" s="64"/>
@@ -20543,15 +20545,15 @@
       <c r="B145" s="36"/>
       <c r="C145" s="72"/>
       <c r="D145" s="74"/>
-      <c r="E145" s="121" t="s">
+      <c r="E145" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="F145" s="121"/>
-      <c r="G145" s="122"/>
-      <c r="H145" s="103">
+      <c r="F145" s="115"/>
+      <c r="G145" s="116"/>
+      <c r="H145" s="111">
         <v>45639</v>
       </c>
-      <c r="I145" s="109"/>
+      <c r="I145" s="113"/>
       <c r="J145" s="62"/>
       <c r="K145" s="20"/>
       <c r="L145" s="20"/>
@@ -20669,11 +20671,11 @@
       <c r="B146" s="36"/>
       <c r="C146" s="72"/>
       <c r="D146" s="70"/>
-      <c r="E146" s="123"/>
-      <c r="F146" s="123"/>
-      <c r="G146" s="124"/>
-      <c r="H146" s="104"/>
-      <c r="I146" s="110"/>
+      <c r="E146" s="185"/>
+      <c r="F146" s="185"/>
+      <c r="G146" s="186"/>
+      <c r="H146" s="107"/>
+      <c r="I146" s="143"/>
       <c r="J146" s="62"/>
       <c r="K146" s="20"/>
       <c r="L146" s="20"/>
@@ -20733,8 +20735,8 @@
       <c r="BN146" s="20"/>
       <c r="BO146" s="20"/>
       <c r="BP146" s="20"/>
-      <c r="BQ146" s="20"/>
-      <c r="BR146" s="20"/>
+      <c r="BQ146" s="69"/>
+      <c r="BR146" s="69"/>
       <c r="BS146" s="21"/>
       <c r="BT146" s="21"/>
       <c r="BU146" s="20"/>
@@ -20791,15 +20793,15 @@
       <c r="B147" s="36"/>
       <c r="C147" s="72"/>
       <c r="D147" s="70"/>
-      <c r="E147" s="121" t="s">
+      <c r="E147" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="F147" s="121"/>
-      <c r="G147" s="122"/>
-      <c r="H147" s="103">
+      <c r="F147" s="115"/>
+      <c r="G147" s="116"/>
+      <c r="H147" s="111">
         <v>45642</v>
       </c>
-      <c r="I147" s="109"/>
+      <c r="I147" s="113"/>
       <c r="J147" s="62"/>
       <c r="K147" s="20"/>
       <c r="L147" s="20"/>
@@ -20917,11 +20919,11 @@
       <c r="B148" s="36"/>
       <c r="C148" s="72"/>
       <c r="D148" s="70"/>
-      <c r="E148" s="123"/>
-      <c r="F148" s="123"/>
-      <c r="G148" s="124"/>
-      <c r="H148" s="104"/>
-      <c r="I148" s="110"/>
+      <c r="E148" s="185"/>
+      <c r="F148" s="185"/>
+      <c r="G148" s="186"/>
+      <c r="H148" s="107"/>
+      <c r="I148" s="143"/>
       <c r="J148" s="62"/>
       <c r="K148" s="20"/>
       <c r="L148" s="20"/>
@@ -21039,15 +21041,15 @@
       <c r="B149" s="36"/>
       <c r="C149" s="72"/>
       <c r="D149" s="70"/>
-      <c r="E149" s="121" t="s">
+      <c r="E149" s="115" t="s">
         <v>70</v>
       </c>
-      <c r="F149" s="121"/>
-      <c r="G149" s="122"/>
-      <c r="H149" s="103">
+      <c r="F149" s="115"/>
+      <c r="G149" s="116"/>
+      <c r="H149" s="111">
         <v>45643</v>
       </c>
-      <c r="I149" s="109"/>
+      <c r="I149" s="113"/>
       <c r="J149" s="62"/>
       <c r="K149" s="20"/>
       <c r="L149" s="20"/>
@@ -21165,11 +21167,11 @@
       <c r="B150" s="36"/>
       <c r="C150" s="72"/>
       <c r="D150" s="70"/>
-      <c r="E150" s="123"/>
-      <c r="F150" s="123"/>
-      <c r="G150" s="124"/>
-      <c r="H150" s="104"/>
-      <c r="I150" s="110"/>
+      <c r="E150" s="185"/>
+      <c r="F150" s="185"/>
+      <c r="G150" s="186"/>
+      <c r="H150" s="107"/>
+      <c r="I150" s="143"/>
       <c r="J150" s="62"/>
       <c r="K150" s="20"/>
       <c r="L150" s="20"/>
@@ -21287,15 +21289,15 @@
       <c r="B151" s="36"/>
       <c r="C151" s="72"/>
       <c r="D151" s="70"/>
-      <c r="E151" s="102" t="s">
+      <c r="E151" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="F151" s="102"/>
-      <c r="G151" s="102"/>
-      <c r="H151" s="103">
+      <c r="F151" s="103"/>
+      <c r="G151" s="103"/>
+      <c r="H151" s="111">
         <v>45644</v>
       </c>
-      <c r="I151" s="109"/>
+      <c r="I151" s="113"/>
       <c r="J151" s="62"/>
       <c r="K151" s="20"/>
       <c r="L151" s="20"/>
@@ -21413,11 +21415,11 @@
       <c r="B152" s="36"/>
       <c r="C152" s="72"/>
       <c r="D152" s="70"/>
-      <c r="E152" s="102"/>
-      <c r="F152" s="102"/>
-      <c r="G152" s="102"/>
-      <c r="H152" s="104"/>
-      <c r="I152" s="110"/>
+      <c r="E152" s="103"/>
+      <c r="F152" s="103"/>
+      <c r="G152" s="103"/>
+      <c r="H152" s="107"/>
+      <c r="I152" s="143"/>
       <c r="J152" s="62"/>
       <c r="K152" s="20"/>
       <c r="L152" s="20"/>
@@ -21535,15 +21537,15 @@
       <c r="B153" s="36"/>
       <c r="C153" s="72"/>
       <c r="D153" s="70"/>
-      <c r="E153" s="102" t="s">
+      <c r="E153" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="F153" s="102"/>
-      <c r="G153" s="102"/>
-      <c r="H153" s="103">
+      <c r="F153" s="103"/>
+      <c r="G153" s="103"/>
+      <c r="H153" s="111">
         <v>45644</v>
       </c>
-      <c r="I153" s="109"/>
+      <c r="I153" s="113"/>
       <c r="J153" s="62"/>
       <c r="K153" s="20"/>
       <c r="L153" s="20"/>
@@ -21661,11 +21663,11 @@
       <c r="B154" s="36"/>
       <c r="C154" s="72"/>
       <c r="D154" s="70"/>
-      <c r="E154" s="102"/>
-      <c r="F154" s="102"/>
-      <c r="G154" s="102"/>
-      <c r="H154" s="104"/>
-      <c r="I154" s="110"/>
+      <c r="E154" s="103"/>
+      <c r="F154" s="103"/>
+      <c r="G154" s="103"/>
+      <c r="H154" s="107"/>
+      <c r="I154" s="143"/>
       <c r="J154" s="62"/>
       <c r="K154" s="20"/>
       <c r="L154" s="20"/>
@@ -21782,16 +21784,16 @@
       <c r="A155" s="1"/>
       <c r="B155" s="18"/>
       <c r="C155" s="60"/>
-      <c r="D155" s="194"/>
-      <c r="E155" s="193" t="s">
+      <c r="D155" s="104"/>
+      <c r="E155" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="F155" s="102"/>
-      <c r="G155" s="102"/>
-      <c r="H155" s="195">
+      <c r="F155" s="103"/>
+      <c r="G155" s="103"/>
+      <c r="H155" s="106">
         <v>45645</v>
       </c>
-      <c r="I155" s="196"/>
+      <c r="I155" s="108"/>
       <c r="J155" s="19"/>
       <c r="K155" s="20"/>
       <c r="L155" s="20"/>
@@ -21908,12 +21910,12 @@
       <c r="A156" s="1"/>
       <c r="B156" s="18"/>
       <c r="C156" s="60"/>
-      <c r="D156" s="149"/>
-      <c r="E156" s="193"/>
-      <c r="F156" s="102"/>
-      <c r="G156" s="102"/>
-      <c r="H156" s="104"/>
-      <c r="I156" s="106"/>
+      <c r="D156" s="105"/>
+      <c r="E156" s="102"/>
+      <c r="F156" s="103"/>
+      <c r="G156" s="103"/>
+      <c r="H156" s="107"/>
+      <c r="I156" s="109"/>
       <c r="J156" s="19"/>
       <c r="K156" s="20"/>
       <c r="L156" s="20"/>
@@ -22030,16 +22032,16 @@
       <c r="A157" s="1"/>
       <c r="B157" s="93"/>
       <c r="C157" s="90"/>
-      <c r="D157" s="102" t="s">
+      <c r="D157" s="103" t="s">
         <v>81</v>
       </c>
-      <c r="E157" s="102"/>
-      <c r="F157" s="102"/>
-      <c r="G157" s="102"/>
-      <c r="H157" s="103">
+      <c r="E157" s="103"/>
+      <c r="F157" s="103"/>
+      <c r="G157" s="103"/>
+      <c r="H157" s="111">
         <v>45644</v>
       </c>
-      <c r="I157" s="105"/>
+      <c r="I157" s="126"/>
       <c r="J157" s="19"/>
       <c r="K157" s="20"/>
       <c r="L157" s="20"/>
@@ -22156,12 +22158,12 @@
       <c r="A158" s="1"/>
       <c r="B158" s="93"/>
       <c r="C158" s="90"/>
-      <c r="D158" s="102"/>
-      <c r="E158" s="102"/>
-      <c r="F158" s="102"/>
-      <c r="G158" s="102"/>
-      <c r="H158" s="104"/>
-      <c r="I158" s="106"/>
+      <c r="D158" s="103"/>
+      <c r="E158" s="103"/>
+      <c r="F158" s="103"/>
+      <c r="G158" s="103"/>
+      <c r="H158" s="107"/>
+      <c r="I158" s="109"/>
       <c r="J158" s="19"/>
       <c r="K158" s="20"/>
       <c r="L158" s="20"/>
@@ -22279,14 +22281,14 @@
       <c r="B159" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="C159" s="173" t="s">
+      <c r="C159" s="151" t="s">
         <v>31</v>
       </c>
-      <c r="D159" s="174"/>
-      <c r="E159" s="174"/>
-      <c r="F159" s="174"/>
-      <c r="G159" s="175"/>
-      <c r="H159" s="184" t="s">
+      <c r="D159" s="152"/>
+      <c r="E159" s="152"/>
+      <c r="F159" s="152"/>
+      <c r="G159" s="153"/>
+      <c r="H159" s="138" t="s">
         <v>57</v>
       </c>
       <c r="I159" s="112"/>
@@ -22405,11 +22407,11 @@
     <row r="160" spans="1:120" ht="9.75" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="87"/>
-      <c r="C160" s="176"/>
-      <c r="D160" s="177"/>
-      <c r="E160" s="177"/>
-      <c r="F160" s="177"/>
-      <c r="G160" s="178"/>
+      <c r="C160" s="154"/>
+      <c r="D160" s="155"/>
+      <c r="E160" s="155"/>
+      <c r="F160" s="155"/>
+      <c r="G160" s="156"/>
       <c r="H160" s="112"/>
       <c r="I160" s="112"/>
       <c r="J160" s="14"/>
@@ -22771,14 +22773,14 @@
     <row r="163" spans="1:120" ht="9.75" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
-      <c r="C163" s="168" t="s">
+      <c r="C163" s="145" t="s">
         <v>33</v>
       </c>
-      <c r="D163" s="140"/>
-      <c r="E163" s="140"/>
-      <c r="F163" s="140"/>
-      <c r="G163" s="169"/>
-      <c r="H163" s="184" t="s">
+      <c r="D163" s="146"/>
+      <c r="E163" s="146"/>
+      <c r="F163" s="146"/>
+      <c r="G163" s="147"/>
+      <c r="H163" s="138" t="s">
         <v>56</v>
       </c>
       <c r="I163" s="112"/>
@@ -22897,11 +22899,11 @@
     <row r="164" spans="1:120" ht="9.75" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
-      <c r="C164" s="170"/>
-      <c r="D164" s="171"/>
-      <c r="E164" s="171"/>
-      <c r="F164" s="171"/>
-      <c r="G164" s="172"/>
+      <c r="C164" s="148"/>
+      <c r="D164" s="149"/>
+      <c r="E164" s="149"/>
+      <c r="F164" s="149"/>
+      <c r="G164" s="150"/>
       <c r="H164" s="112"/>
       <c r="I164" s="112"/>
       <c r="J164" s="19"/>
@@ -36442,6 +36444,222 @@
     </row>
   </sheetData>
   <mergeCells count="240">
+    <mergeCell ref="D157:G158"/>
+    <mergeCell ref="H157:H158"/>
+    <mergeCell ref="I157:I158"/>
+    <mergeCell ref="H141:H142"/>
+    <mergeCell ref="I143:I144"/>
+    <mergeCell ref="I139:I140"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="H103:H104"/>
+    <mergeCell ref="I103:I104"/>
+    <mergeCell ref="H115:H116"/>
+    <mergeCell ref="I115:I116"/>
+    <mergeCell ref="D103:G104"/>
+    <mergeCell ref="D115:G116"/>
+    <mergeCell ref="D131:G132"/>
+    <mergeCell ref="H131:H132"/>
+    <mergeCell ref="I131:I132"/>
+    <mergeCell ref="D87:G88"/>
+    <mergeCell ref="D141:G142"/>
+    <mergeCell ref="E153:G154"/>
+    <mergeCell ref="H153:H154"/>
+    <mergeCell ref="H151:H152"/>
+    <mergeCell ref="H149:H150"/>
+    <mergeCell ref="H147:H148"/>
+    <mergeCell ref="H145:H146"/>
+    <mergeCell ref="H143:H144"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="C133:G134"/>
+    <mergeCell ref="D135:G136"/>
+    <mergeCell ref="E137:G138"/>
+    <mergeCell ref="E139:G140"/>
+    <mergeCell ref="D143:G144"/>
+    <mergeCell ref="E145:G146"/>
+    <mergeCell ref="H135:H136"/>
+    <mergeCell ref="E147:G148"/>
+    <mergeCell ref="E149:G150"/>
+    <mergeCell ref="E151:G152"/>
+    <mergeCell ref="E59:G60"/>
+    <mergeCell ref="E61:G62"/>
+    <mergeCell ref="D63:G64"/>
+    <mergeCell ref="E67:G68"/>
+    <mergeCell ref="E65:G66"/>
+    <mergeCell ref="E69:G70"/>
+    <mergeCell ref="E71:G72"/>
+    <mergeCell ref="C73:G74"/>
+    <mergeCell ref="C75:G76"/>
+    <mergeCell ref="C77:G78"/>
+    <mergeCell ref="D79:G80"/>
+    <mergeCell ref="E109:G110"/>
+    <mergeCell ref="E111:G112"/>
+    <mergeCell ref="E101:G102"/>
+    <mergeCell ref="C105:G106"/>
+    <mergeCell ref="D107:G108"/>
+    <mergeCell ref="D117:G118"/>
+    <mergeCell ref="D13:G14"/>
+    <mergeCell ref="D15:G16"/>
+    <mergeCell ref="D17:G18"/>
+    <mergeCell ref="D19:G20"/>
+    <mergeCell ref="C21:G22"/>
+    <mergeCell ref="D23:G24"/>
+    <mergeCell ref="C25:G26"/>
+    <mergeCell ref="D27:G28"/>
+    <mergeCell ref="D29:G30"/>
+    <mergeCell ref="J3:CJ3"/>
+    <mergeCell ref="CK3:DO3"/>
+    <mergeCell ref="J4:AA4"/>
+    <mergeCell ref="AB4:BE4"/>
+    <mergeCell ref="BF4:CJ4"/>
+    <mergeCell ref="CK4:DO4"/>
+    <mergeCell ref="B7:G8"/>
+    <mergeCell ref="C9:G10"/>
+    <mergeCell ref="C11:G12"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="C163:G164"/>
+    <mergeCell ref="C159:G160"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="C31:G32"/>
+    <mergeCell ref="D33:G34"/>
+    <mergeCell ref="E35:G36"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="E43:G44"/>
+    <mergeCell ref="E45:G46"/>
+    <mergeCell ref="E47:G48"/>
+    <mergeCell ref="E49:G50"/>
+    <mergeCell ref="E51:G52"/>
+    <mergeCell ref="D53:G54"/>
+    <mergeCell ref="E55:G56"/>
+    <mergeCell ref="E57:G58"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I67:I68"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="I159:I160"/>
+    <mergeCell ref="I161:I162"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="I93:I94"/>
+    <mergeCell ref="I95:I96"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="I109:I110"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="I153:I154"/>
+    <mergeCell ref="I151:I152"/>
+    <mergeCell ref="I149:I150"/>
+    <mergeCell ref="I147:I148"/>
+    <mergeCell ref="I145:I146"/>
+    <mergeCell ref="I111:I112"/>
+    <mergeCell ref="I135:I136"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="I163:I164"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="H75:H76"/>
+    <mergeCell ref="H159:H160"/>
+    <mergeCell ref="H163:H164"/>
+    <mergeCell ref="H161:H162"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="H59:H60"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="H77:H78"/>
+    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="H93:H94"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="H111:H112"/>
+    <mergeCell ref="H101:H102"/>
+    <mergeCell ref="I101:I102"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="I85:I86"/>
+    <mergeCell ref="H89:H90"/>
+    <mergeCell ref="I89:I90"/>
+    <mergeCell ref="E81:G82"/>
+    <mergeCell ref="E83:G84"/>
+    <mergeCell ref="E91:G92"/>
+    <mergeCell ref="E93:G94"/>
+    <mergeCell ref="E95:G96"/>
+    <mergeCell ref="E97:G98"/>
+    <mergeCell ref="E99:G100"/>
+    <mergeCell ref="E85:G86"/>
+    <mergeCell ref="D89:G90"/>
+    <mergeCell ref="H105:H106"/>
+    <mergeCell ref="I105:I106"/>
+    <mergeCell ref="H107:H108"/>
+    <mergeCell ref="I107:I108"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="H117:H118"/>
+    <mergeCell ref="I117:I118"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="I119:I120"/>
     <mergeCell ref="E155:G156"/>
     <mergeCell ref="D155:D156"/>
     <mergeCell ref="H155:H156"/>
@@ -36466,222 +36684,6 @@
     <mergeCell ref="H127:H128"/>
     <mergeCell ref="I127:I128"/>
     <mergeCell ref="H121:H122"/>
-    <mergeCell ref="H105:H106"/>
-    <mergeCell ref="I105:I106"/>
-    <mergeCell ref="H107:H108"/>
-    <mergeCell ref="I107:I108"/>
-    <mergeCell ref="H109:H110"/>
-    <mergeCell ref="H117:H118"/>
-    <mergeCell ref="I117:I118"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="I119:I120"/>
-    <mergeCell ref="H101:H102"/>
-    <mergeCell ref="I101:I102"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="I85:I86"/>
-    <mergeCell ref="H89:H90"/>
-    <mergeCell ref="I89:I90"/>
-    <mergeCell ref="E81:G82"/>
-    <mergeCell ref="E83:G84"/>
-    <mergeCell ref="E91:G92"/>
-    <mergeCell ref="E93:G94"/>
-    <mergeCell ref="E95:G96"/>
-    <mergeCell ref="E97:G98"/>
-    <mergeCell ref="E99:G100"/>
-    <mergeCell ref="E85:G86"/>
-    <mergeCell ref="D89:G90"/>
-    <mergeCell ref="H75:H76"/>
-    <mergeCell ref="H159:H160"/>
-    <mergeCell ref="H163:H164"/>
-    <mergeCell ref="H161:H162"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="H67:H68"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H59:H60"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="H77:H78"/>
-    <mergeCell ref="H81:H82"/>
-    <mergeCell ref="H83:H84"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="H93:H94"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="H111:H112"/>
-    <mergeCell ref="I163:I164"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="I159:I160"/>
-    <mergeCell ref="I161:I162"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="I93:I94"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="I109:I110"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="I153:I154"/>
-    <mergeCell ref="I151:I152"/>
-    <mergeCell ref="I149:I150"/>
-    <mergeCell ref="I147:I148"/>
-    <mergeCell ref="I145:I146"/>
-    <mergeCell ref="I111:I112"/>
-    <mergeCell ref="I135:I136"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="C163:G164"/>
-    <mergeCell ref="C159:G160"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="C31:G32"/>
-    <mergeCell ref="D33:G34"/>
-    <mergeCell ref="E35:G36"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="E43:G44"/>
-    <mergeCell ref="E45:G46"/>
-    <mergeCell ref="E47:G48"/>
-    <mergeCell ref="E49:G50"/>
-    <mergeCell ref="E51:G52"/>
-    <mergeCell ref="D53:G54"/>
-    <mergeCell ref="E55:G56"/>
-    <mergeCell ref="E57:G58"/>
-    <mergeCell ref="I53:I54"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="J3:CJ3"/>
-    <mergeCell ref="CK3:DO3"/>
-    <mergeCell ref="J4:AA4"/>
-    <mergeCell ref="AB4:BE4"/>
-    <mergeCell ref="BF4:CJ4"/>
-    <mergeCell ref="CK4:DO4"/>
-    <mergeCell ref="B7:G8"/>
-    <mergeCell ref="C9:G10"/>
-    <mergeCell ref="C11:G12"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="D13:G14"/>
-    <mergeCell ref="D15:G16"/>
-    <mergeCell ref="D17:G18"/>
-    <mergeCell ref="D19:G20"/>
-    <mergeCell ref="C21:G22"/>
-    <mergeCell ref="D23:G24"/>
-    <mergeCell ref="C25:G26"/>
-    <mergeCell ref="D27:G28"/>
-    <mergeCell ref="D29:G30"/>
-    <mergeCell ref="E147:G148"/>
-    <mergeCell ref="E149:G150"/>
-    <mergeCell ref="E151:G152"/>
-    <mergeCell ref="E59:G60"/>
-    <mergeCell ref="E61:G62"/>
-    <mergeCell ref="D63:G64"/>
-    <mergeCell ref="E67:G68"/>
-    <mergeCell ref="E65:G66"/>
-    <mergeCell ref="E69:G70"/>
-    <mergeCell ref="E71:G72"/>
-    <mergeCell ref="C73:G74"/>
-    <mergeCell ref="C75:G76"/>
-    <mergeCell ref="C77:G78"/>
-    <mergeCell ref="D79:G80"/>
-    <mergeCell ref="E109:G110"/>
-    <mergeCell ref="E111:G112"/>
-    <mergeCell ref="E101:G102"/>
-    <mergeCell ref="C105:G106"/>
-    <mergeCell ref="D107:G108"/>
-    <mergeCell ref="D117:G118"/>
-    <mergeCell ref="H145:H146"/>
-    <mergeCell ref="H143:H144"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="C133:G134"/>
-    <mergeCell ref="D135:G136"/>
-    <mergeCell ref="E137:G138"/>
-    <mergeCell ref="E139:G140"/>
-    <mergeCell ref="D143:G144"/>
-    <mergeCell ref="E145:G146"/>
-    <mergeCell ref="H135:H136"/>
-    <mergeCell ref="D157:G158"/>
-    <mergeCell ref="H157:H158"/>
-    <mergeCell ref="I157:I158"/>
-    <mergeCell ref="H141:H142"/>
-    <mergeCell ref="I143:I144"/>
-    <mergeCell ref="I139:I140"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="H103:H104"/>
-    <mergeCell ref="I103:I104"/>
-    <mergeCell ref="H115:H116"/>
-    <mergeCell ref="I115:I116"/>
-    <mergeCell ref="D103:G104"/>
-    <mergeCell ref="D115:G116"/>
-    <mergeCell ref="D131:G132"/>
-    <mergeCell ref="H131:H132"/>
-    <mergeCell ref="I131:I132"/>
-    <mergeCell ref="D87:G88"/>
-    <mergeCell ref="D141:G142"/>
-    <mergeCell ref="E153:G154"/>
-    <mergeCell ref="H153:H154"/>
-    <mergeCell ref="H151:H152"/>
-    <mergeCell ref="H149:H150"/>
-    <mergeCell ref="H147:H148"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <conditionalFormatting sqref="J7">

--- a/docs/【DIGITAL OJT】WBS.xlsx
+++ b/docs/【DIGITAL OJT】WBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIGITALOJT\digital-ojt-development-cause-DroneInventorySystem\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD42851F-DA13-42A4-8BC9-CFC4E68F8D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A765BA39-78FE-45FF-BB55-1B72716B3B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -1489,67 +1489,19 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1558,25 +1510,22 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1597,29 +1546,110 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1645,92 +1675,62 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2350,120 +2350,120 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="J3" s="173">
+      <c r="J3" s="161">
         <v>2024</v>
       </c>
-      <c r="K3" s="174"/>
-      <c r="L3" s="174"/>
-      <c r="M3" s="174"/>
-      <c r="N3" s="174"/>
-      <c r="O3" s="174"/>
-      <c r="P3" s="174"/>
-      <c r="Q3" s="174"/>
-      <c r="R3" s="174"/>
-      <c r="S3" s="174"/>
-      <c r="T3" s="174"/>
-      <c r="U3" s="174"/>
-      <c r="V3" s="174"/>
-      <c r="W3" s="174"/>
-      <c r="X3" s="174"/>
-      <c r="Y3" s="174"/>
-      <c r="Z3" s="174"/>
-      <c r="AA3" s="174"/>
-      <c r="AB3" s="174"/>
-      <c r="AC3" s="174"/>
-      <c r="AD3" s="174"/>
-      <c r="AE3" s="174"/>
-      <c r="AF3" s="174"/>
-      <c r="AG3" s="174"/>
-      <c r="AH3" s="174"/>
-      <c r="AI3" s="174"/>
-      <c r="AJ3" s="174"/>
-      <c r="AK3" s="174"/>
-      <c r="AL3" s="174"/>
-      <c r="AM3" s="174"/>
-      <c r="AN3" s="174"/>
-      <c r="AO3" s="174"/>
-      <c r="AP3" s="174"/>
-      <c r="AQ3" s="174"/>
-      <c r="AR3" s="174"/>
-      <c r="AS3" s="174"/>
-      <c r="AT3" s="174"/>
-      <c r="AU3" s="174"/>
-      <c r="AV3" s="174"/>
-      <c r="AW3" s="174"/>
-      <c r="AX3" s="174"/>
-      <c r="AY3" s="174"/>
-      <c r="AZ3" s="174"/>
-      <c r="BA3" s="174"/>
-      <c r="BB3" s="174"/>
-      <c r="BC3" s="174"/>
-      <c r="BD3" s="174"/>
-      <c r="BE3" s="174"/>
-      <c r="BF3" s="174"/>
-      <c r="BG3" s="174"/>
-      <c r="BH3" s="174"/>
-      <c r="BI3" s="174"/>
-      <c r="BJ3" s="174"/>
-      <c r="BK3" s="174"/>
-      <c r="BL3" s="174"/>
-      <c r="BM3" s="174"/>
-      <c r="BN3" s="174"/>
-      <c r="BO3" s="174"/>
-      <c r="BP3" s="174"/>
-      <c r="BQ3" s="174"/>
-      <c r="BR3" s="174"/>
-      <c r="BS3" s="174"/>
-      <c r="BT3" s="174"/>
-      <c r="BU3" s="174"/>
-      <c r="BV3" s="174"/>
-      <c r="BW3" s="174"/>
-      <c r="BX3" s="174"/>
-      <c r="BY3" s="174"/>
-      <c r="BZ3" s="174"/>
-      <c r="CA3" s="174"/>
-      <c r="CB3" s="174"/>
-      <c r="CC3" s="174"/>
-      <c r="CD3" s="174"/>
-      <c r="CE3" s="174"/>
-      <c r="CF3" s="174"/>
-      <c r="CG3" s="174"/>
-      <c r="CH3" s="174"/>
-      <c r="CI3" s="174"/>
-      <c r="CJ3" s="175"/>
-      <c r="CK3" s="173">
+      <c r="K3" s="162"/>
+      <c r="L3" s="162"/>
+      <c r="M3" s="162"/>
+      <c r="N3" s="162"/>
+      <c r="O3" s="162"/>
+      <c r="P3" s="162"/>
+      <c r="Q3" s="162"/>
+      <c r="R3" s="162"/>
+      <c r="S3" s="162"/>
+      <c r="T3" s="162"/>
+      <c r="U3" s="162"/>
+      <c r="V3" s="162"/>
+      <c r="W3" s="162"/>
+      <c r="X3" s="162"/>
+      <c r="Y3" s="162"/>
+      <c r="Z3" s="162"/>
+      <c r="AA3" s="162"/>
+      <c r="AB3" s="162"/>
+      <c r="AC3" s="162"/>
+      <c r="AD3" s="162"/>
+      <c r="AE3" s="162"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="162"/>
+      <c r="AH3" s="162"/>
+      <c r="AI3" s="162"/>
+      <c r="AJ3" s="162"/>
+      <c r="AK3" s="162"/>
+      <c r="AL3" s="162"/>
+      <c r="AM3" s="162"/>
+      <c r="AN3" s="162"/>
+      <c r="AO3" s="162"/>
+      <c r="AP3" s="162"/>
+      <c r="AQ3" s="162"/>
+      <c r="AR3" s="162"/>
+      <c r="AS3" s="162"/>
+      <c r="AT3" s="162"/>
+      <c r="AU3" s="162"/>
+      <c r="AV3" s="162"/>
+      <c r="AW3" s="162"/>
+      <c r="AX3" s="162"/>
+      <c r="AY3" s="162"/>
+      <c r="AZ3" s="162"/>
+      <c r="BA3" s="162"/>
+      <c r="BB3" s="162"/>
+      <c r="BC3" s="162"/>
+      <c r="BD3" s="162"/>
+      <c r="BE3" s="162"/>
+      <c r="BF3" s="162"/>
+      <c r="BG3" s="162"/>
+      <c r="BH3" s="162"/>
+      <c r="BI3" s="162"/>
+      <c r="BJ3" s="162"/>
+      <c r="BK3" s="162"/>
+      <c r="BL3" s="162"/>
+      <c r="BM3" s="162"/>
+      <c r="BN3" s="162"/>
+      <c r="BO3" s="162"/>
+      <c r="BP3" s="162"/>
+      <c r="BQ3" s="162"/>
+      <c r="BR3" s="162"/>
+      <c r="BS3" s="162"/>
+      <c r="BT3" s="162"/>
+      <c r="BU3" s="162"/>
+      <c r="BV3" s="162"/>
+      <c r="BW3" s="162"/>
+      <c r="BX3" s="162"/>
+      <c r="BY3" s="162"/>
+      <c r="BZ3" s="162"/>
+      <c r="CA3" s="162"/>
+      <c r="CB3" s="162"/>
+      <c r="CC3" s="162"/>
+      <c r="CD3" s="162"/>
+      <c r="CE3" s="162"/>
+      <c r="CF3" s="162"/>
+      <c r="CG3" s="162"/>
+      <c r="CH3" s="162"/>
+      <c r="CI3" s="162"/>
+      <c r="CJ3" s="163"/>
+      <c r="CK3" s="161">
         <v>2025</v>
       </c>
-      <c r="CL3" s="174"/>
-      <c r="CM3" s="174"/>
-      <c r="CN3" s="174"/>
-      <c r="CO3" s="174"/>
-      <c r="CP3" s="174"/>
-      <c r="CQ3" s="174"/>
-      <c r="CR3" s="174"/>
-      <c r="CS3" s="174"/>
-      <c r="CT3" s="174"/>
-      <c r="CU3" s="174"/>
-      <c r="CV3" s="174"/>
-      <c r="CW3" s="174"/>
-      <c r="CX3" s="174"/>
-      <c r="CY3" s="174"/>
-      <c r="CZ3" s="174"/>
-      <c r="DA3" s="174"/>
-      <c r="DB3" s="174"/>
-      <c r="DC3" s="174"/>
-      <c r="DD3" s="174"/>
-      <c r="DE3" s="174"/>
-      <c r="DF3" s="174"/>
-      <c r="DG3" s="174"/>
-      <c r="DH3" s="174"/>
-      <c r="DI3" s="174"/>
-      <c r="DJ3" s="174"/>
-      <c r="DK3" s="174"/>
-      <c r="DL3" s="174"/>
-      <c r="DM3" s="174"/>
-      <c r="DN3" s="174"/>
-      <c r="DO3" s="175"/>
+      <c r="CL3" s="162"/>
+      <c r="CM3" s="162"/>
+      <c r="CN3" s="162"/>
+      <c r="CO3" s="162"/>
+      <c r="CP3" s="162"/>
+      <c r="CQ3" s="162"/>
+      <c r="CR3" s="162"/>
+      <c r="CS3" s="162"/>
+      <c r="CT3" s="162"/>
+      <c r="CU3" s="162"/>
+      <c r="CV3" s="162"/>
+      <c r="CW3" s="162"/>
+      <c r="CX3" s="162"/>
+      <c r="CY3" s="162"/>
+      <c r="CZ3" s="162"/>
+      <c r="DA3" s="162"/>
+      <c r="DB3" s="162"/>
+      <c r="DC3" s="162"/>
+      <c r="DD3" s="162"/>
+      <c r="DE3" s="162"/>
+      <c r="DF3" s="162"/>
+      <c r="DG3" s="162"/>
+      <c r="DH3" s="162"/>
+      <c r="DI3" s="162"/>
+      <c r="DJ3" s="162"/>
+      <c r="DK3" s="162"/>
+      <c r="DL3" s="162"/>
+      <c r="DM3" s="162"/>
+      <c r="DN3" s="162"/>
+      <c r="DO3" s="163"/>
       <c r="DP3" s="1"/>
     </row>
     <row r="4" spans="1:120" ht="18" customHeight="1">
@@ -2478,124 +2478,124 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="J4" s="173">
+      <c r="J4" s="161">
         <v>10</v>
       </c>
-      <c r="K4" s="174"/>
-      <c r="L4" s="174"/>
-      <c r="M4" s="174"/>
-      <c r="N4" s="174"/>
-      <c r="O4" s="174"/>
-      <c r="P4" s="174"/>
-      <c r="Q4" s="174"/>
-      <c r="R4" s="174"/>
-      <c r="S4" s="174"/>
-      <c r="T4" s="174"/>
-      <c r="U4" s="174"/>
-      <c r="V4" s="174"/>
-      <c r="W4" s="174"/>
-      <c r="X4" s="174"/>
-      <c r="Y4" s="174"/>
-      <c r="Z4" s="174"/>
-      <c r="AA4" s="175"/>
-      <c r="AB4" s="173">
+      <c r="K4" s="162"/>
+      <c r="L4" s="162"/>
+      <c r="M4" s="162"/>
+      <c r="N4" s="162"/>
+      <c r="O4" s="162"/>
+      <c r="P4" s="162"/>
+      <c r="Q4" s="162"/>
+      <c r="R4" s="162"/>
+      <c r="S4" s="162"/>
+      <c r="T4" s="162"/>
+      <c r="U4" s="162"/>
+      <c r="V4" s="162"/>
+      <c r="W4" s="162"/>
+      <c r="X4" s="162"/>
+      <c r="Y4" s="162"/>
+      <c r="Z4" s="162"/>
+      <c r="AA4" s="163"/>
+      <c r="AB4" s="161">
         <v>11</v>
       </c>
-      <c r="AC4" s="174"/>
-      <c r="AD4" s="174"/>
-      <c r="AE4" s="174"/>
-      <c r="AF4" s="174"/>
-      <c r="AG4" s="174"/>
-      <c r="AH4" s="174"/>
-      <c r="AI4" s="174"/>
-      <c r="AJ4" s="174"/>
-      <c r="AK4" s="174"/>
-      <c r="AL4" s="174"/>
-      <c r="AM4" s="174"/>
-      <c r="AN4" s="174"/>
-      <c r="AO4" s="174"/>
-      <c r="AP4" s="174"/>
-      <c r="AQ4" s="174"/>
-      <c r="AR4" s="174"/>
-      <c r="AS4" s="174"/>
-      <c r="AT4" s="174"/>
-      <c r="AU4" s="174"/>
-      <c r="AV4" s="174"/>
-      <c r="AW4" s="174"/>
-      <c r="AX4" s="174"/>
-      <c r="AY4" s="174"/>
-      <c r="AZ4" s="174"/>
-      <c r="BA4" s="174"/>
-      <c r="BB4" s="174"/>
-      <c r="BC4" s="174"/>
-      <c r="BD4" s="174"/>
-      <c r="BE4" s="175"/>
-      <c r="BF4" s="173">
+      <c r="AC4" s="162"/>
+      <c r="AD4" s="162"/>
+      <c r="AE4" s="162"/>
+      <c r="AF4" s="162"/>
+      <c r="AG4" s="162"/>
+      <c r="AH4" s="162"/>
+      <c r="AI4" s="162"/>
+      <c r="AJ4" s="162"/>
+      <c r="AK4" s="162"/>
+      <c r="AL4" s="162"/>
+      <c r="AM4" s="162"/>
+      <c r="AN4" s="162"/>
+      <c r="AO4" s="162"/>
+      <c r="AP4" s="162"/>
+      <c r="AQ4" s="162"/>
+      <c r="AR4" s="162"/>
+      <c r="AS4" s="162"/>
+      <c r="AT4" s="162"/>
+      <c r="AU4" s="162"/>
+      <c r="AV4" s="162"/>
+      <c r="AW4" s="162"/>
+      <c r="AX4" s="162"/>
+      <c r="AY4" s="162"/>
+      <c r="AZ4" s="162"/>
+      <c r="BA4" s="162"/>
+      <c r="BB4" s="162"/>
+      <c r="BC4" s="162"/>
+      <c r="BD4" s="162"/>
+      <c r="BE4" s="163"/>
+      <c r="BF4" s="161">
         <v>12</v>
       </c>
-      <c r="BG4" s="174"/>
-      <c r="BH4" s="174"/>
-      <c r="BI4" s="174"/>
-      <c r="BJ4" s="174"/>
-      <c r="BK4" s="174"/>
-      <c r="BL4" s="174"/>
-      <c r="BM4" s="174"/>
-      <c r="BN4" s="174"/>
-      <c r="BO4" s="174"/>
-      <c r="BP4" s="174"/>
-      <c r="BQ4" s="174"/>
-      <c r="BR4" s="174"/>
-      <c r="BS4" s="174"/>
-      <c r="BT4" s="174"/>
-      <c r="BU4" s="174"/>
-      <c r="BV4" s="174"/>
-      <c r="BW4" s="174"/>
-      <c r="BX4" s="174"/>
-      <c r="BY4" s="174"/>
-      <c r="BZ4" s="174"/>
-      <c r="CA4" s="174"/>
-      <c r="CB4" s="174"/>
-      <c r="CC4" s="174"/>
-      <c r="CD4" s="174"/>
-      <c r="CE4" s="174"/>
-      <c r="CF4" s="174"/>
-      <c r="CG4" s="174"/>
-      <c r="CH4" s="174"/>
-      <c r="CI4" s="174"/>
-      <c r="CJ4" s="175"/>
-      <c r="CK4" s="173">
+      <c r="BG4" s="162"/>
+      <c r="BH4" s="162"/>
+      <c r="BI4" s="162"/>
+      <c r="BJ4" s="162"/>
+      <c r="BK4" s="162"/>
+      <c r="BL4" s="162"/>
+      <c r="BM4" s="162"/>
+      <c r="BN4" s="162"/>
+      <c r="BO4" s="162"/>
+      <c r="BP4" s="162"/>
+      <c r="BQ4" s="162"/>
+      <c r="BR4" s="162"/>
+      <c r="BS4" s="162"/>
+      <c r="BT4" s="162"/>
+      <c r="BU4" s="162"/>
+      <c r="BV4" s="162"/>
+      <c r="BW4" s="162"/>
+      <c r="BX4" s="162"/>
+      <c r="BY4" s="162"/>
+      <c r="BZ4" s="162"/>
+      <c r="CA4" s="162"/>
+      <c r="CB4" s="162"/>
+      <c r="CC4" s="162"/>
+      <c r="CD4" s="162"/>
+      <c r="CE4" s="162"/>
+      <c r="CF4" s="162"/>
+      <c r="CG4" s="162"/>
+      <c r="CH4" s="162"/>
+      <c r="CI4" s="162"/>
+      <c r="CJ4" s="163"/>
+      <c r="CK4" s="161">
         <v>1</v>
       </c>
-      <c r="CL4" s="174"/>
-      <c r="CM4" s="174"/>
-      <c r="CN4" s="174"/>
-      <c r="CO4" s="174"/>
-      <c r="CP4" s="174"/>
-      <c r="CQ4" s="174"/>
-      <c r="CR4" s="174"/>
-      <c r="CS4" s="174"/>
-      <c r="CT4" s="174"/>
-      <c r="CU4" s="174"/>
-      <c r="CV4" s="174"/>
-      <c r="CW4" s="174"/>
-      <c r="CX4" s="174"/>
-      <c r="CY4" s="174"/>
-      <c r="CZ4" s="174"/>
-      <c r="DA4" s="174"/>
-      <c r="DB4" s="174"/>
-      <c r="DC4" s="174"/>
-      <c r="DD4" s="174"/>
-      <c r="DE4" s="174"/>
-      <c r="DF4" s="174"/>
-      <c r="DG4" s="174"/>
-      <c r="DH4" s="174"/>
-      <c r="DI4" s="174"/>
-      <c r="DJ4" s="174"/>
-      <c r="DK4" s="174"/>
-      <c r="DL4" s="174"/>
-      <c r="DM4" s="174"/>
-      <c r="DN4" s="174"/>
-      <c r="DO4" s="175"/>
+      <c r="CL4" s="162"/>
+      <c r="CM4" s="162"/>
+      <c r="CN4" s="162"/>
+      <c r="CO4" s="162"/>
+      <c r="CP4" s="162"/>
+      <c r="CQ4" s="162"/>
+      <c r="CR4" s="162"/>
+      <c r="CS4" s="162"/>
+      <c r="CT4" s="162"/>
+      <c r="CU4" s="162"/>
+      <c r="CV4" s="162"/>
+      <c r="CW4" s="162"/>
+      <c r="CX4" s="162"/>
+      <c r="CY4" s="162"/>
+      <c r="CZ4" s="162"/>
+      <c r="DA4" s="162"/>
+      <c r="DB4" s="162"/>
+      <c r="DC4" s="162"/>
+      <c r="DD4" s="162"/>
+      <c r="DE4" s="162"/>
+      <c r="DF4" s="162"/>
+      <c r="DG4" s="162"/>
+      <c r="DH4" s="162"/>
+      <c r="DI4" s="162"/>
+      <c r="DJ4" s="162"/>
+      <c r="DK4" s="162"/>
+      <c r="DL4" s="162"/>
+      <c r="DM4" s="162"/>
+      <c r="DN4" s="162"/>
+      <c r="DO4" s="163"/>
       <c r="DP4" s="6"/>
     </row>
     <row r="5" spans="1:120" ht="18" customHeight="1">
@@ -3390,18 +3390,18 @@
     </row>
     <row r="7" spans="1:120" ht="9.75" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="176" t="s">
+      <c r="B7" s="164" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="164"/>
-      <c r="D7" s="164"/>
-      <c r="E7" s="164"/>
-      <c r="F7" s="164"/>
-      <c r="G7" s="177"/>
-      <c r="H7" s="142" t="s">
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="152"/>
+      <c r="H7" s="166" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="142" t="s">
+      <c r="I7" s="166" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="38"/>
@@ -3518,14 +3518,14 @@
     </row>
     <row r="8" spans="1:120" ht="9.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="166"/>
-      <c r="C8" s="167"/>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="168"/>
-      <c r="H8" s="142"/>
-      <c r="I8" s="142"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
+      <c r="G8" s="139"/>
+      <c r="H8" s="166"/>
+      <c r="I8" s="166"/>
       <c r="J8" s="39"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
@@ -3641,15 +3641,15 @@
     <row r="9" spans="1:120" ht="9.75" customHeight="1">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
-      <c r="C9" s="178" t="s">
+      <c r="C9" s="165" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="158"/>
-      <c r="E9" s="158"/>
-      <c r="F9" s="158"/>
-      <c r="G9" s="162"/>
-      <c r="H9" s="139"/>
-      <c r="I9" s="139"/>
+      <c r="D9" s="154"/>
+      <c r="E9" s="154"/>
+      <c r="F9" s="154"/>
+      <c r="G9" s="142"/>
+      <c r="H9" s="167"/>
+      <c r="I9" s="167"/>
       <c r="J9" s="42"/>
       <c r="K9" s="42"/>
       <c r="L9" s="44"/>
@@ -3765,13 +3765,13 @@
     <row r="10" spans="1:120" ht="9.75" customHeight="1">
       <c r="A10" s="16"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="179"/>
-      <c r="D10" s="167"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="167"/>
-      <c r="G10" s="168"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="139"/>
+      <c r="C10" s="141"/>
+      <c r="D10" s="135"/>
+      <c r="E10" s="135"/>
+      <c r="F10" s="135"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="167"/>
+      <c r="I10" s="167"/>
       <c r="J10" s="46"/>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
@@ -3887,15 +3887,15 @@
     <row r="11" spans="1:120" ht="9.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="180" t="s">
+      <c r="C11" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="158"/>
-      <c r="E11" s="158"/>
-      <c r="F11" s="158"/>
-      <c r="G11" s="162"/>
-      <c r="H11" s="139"/>
-      <c r="I11" s="139"/>
+      <c r="D11" s="154"/>
+      <c r="E11" s="154"/>
+      <c r="F11" s="154"/>
+      <c r="G11" s="142"/>
+      <c r="H11" s="167"/>
+      <c r="I11" s="167"/>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
       <c r="L11" s="44"/>
@@ -4011,13 +4011,13 @@
     <row r="12" spans="1:120" ht="9.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="179"/>
-      <c r="D12" s="167"/>
-      <c r="E12" s="167"/>
-      <c r="F12" s="167"/>
-      <c r="G12" s="168"/>
-      <c r="H12" s="139"/>
-      <c r="I12" s="139"/>
+      <c r="C12" s="141"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="135"/>
+      <c r="G12" s="139"/>
+      <c r="H12" s="167"/>
+      <c r="I12" s="167"/>
       <c r="J12" s="46"/>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
@@ -4134,13 +4134,13 @@
       <c r="A13" s="1"/>
       <c r="B13" s="18"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="181" t="s">
+      <c r="D13" s="151" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="164"/>
-      <c r="F13" s="164"/>
-      <c r="G13" s="177"/>
-      <c r="H13" s="138" t="s">
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="152"/>
+      <c r="H13" s="184" t="s">
         <v>40</v>
       </c>
       <c r="I13" s="112">
@@ -4262,10 +4262,10 @@
       <c r="A14" s="1"/>
       <c r="B14" s="18"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="166"/>
-      <c r="E14" s="167"/>
-      <c r="F14" s="167"/>
-      <c r="G14" s="168"/>
+      <c r="D14" s="134"/>
+      <c r="E14" s="135"/>
+      <c r="F14" s="135"/>
+      <c r="G14" s="139"/>
       <c r="H14" s="112"/>
       <c r="I14" s="112"/>
       <c r="J14" s="39"/>
@@ -4384,13 +4384,13 @@
       <c r="A15" s="1"/>
       <c r="B15" s="18"/>
       <c r="C15" s="24"/>
-      <c r="D15" s="181" t="s">
+      <c r="D15" s="151" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="164"/>
-      <c r="F15" s="164"/>
-      <c r="G15" s="170"/>
-      <c r="H15" s="138" t="s">
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="184" t="s">
         <v>40</v>
       </c>
       <c r="I15" s="112">
@@ -4512,10 +4512,10 @@
       <c r="A16" s="1"/>
       <c r="B16" s="18"/>
       <c r="C16" s="24"/>
-      <c r="D16" s="166"/>
-      <c r="E16" s="167"/>
-      <c r="F16" s="167"/>
-      <c r="G16" s="171"/>
+      <c r="D16" s="134"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="136"/>
       <c r="H16" s="112"/>
       <c r="I16" s="112"/>
       <c r="J16" s="14"/>
@@ -4634,13 +4634,13 @@
       <c r="A17" s="1"/>
       <c r="B17" s="18"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="181" t="s">
+      <c r="D17" s="151" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="164"/>
-      <c r="F17" s="164"/>
-      <c r="G17" s="170"/>
-      <c r="H17" s="138" t="s">
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="133"/>
+      <c r="H17" s="184" t="s">
         <v>40</v>
       </c>
       <c r="I17" s="112">
@@ -4762,10 +4762,10 @@
       <c r="A18" s="1"/>
       <c r="B18" s="18"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="166"/>
-      <c r="E18" s="167"/>
-      <c r="F18" s="167"/>
-      <c r="G18" s="171"/>
+      <c r="D18" s="134"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="136"/>
       <c r="H18" s="112"/>
       <c r="I18" s="112"/>
       <c r="J18" s="14"/>
@@ -4884,13 +4884,13 @@
       <c r="A19" s="1"/>
       <c r="B19" s="18"/>
       <c r="C19" s="24"/>
-      <c r="D19" s="181" t="s">
+      <c r="D19" s="151" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="164"/>
-      <c r="F19" s="164"/>
-      <c r="G19" s="170"/>
-      <c r="H19" s="138" t="s">
+      <c r="E19" s="132"/>
+      <c r="F19" s="132"/>
+      <c r="G19" s="133"/>
+      <c r="H19" s="184" t="s">
         <v>40</v>
       </c>
       <c r="I19" s="112">
@@ -5012,10 +5012,10 @@
       <c r="A20" s="1"/>
       <c r="B20" s="18"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="166"/>
-      <c r="E20" s="167"/>
-      <c r="F20" s="167"/>
-      <c r="G20" s="171"/>
+      <c r="D20" s="134"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="136"/>
       <c r="H20" s="112"/>
       <c r="I20" s="112"/>
       <c r="J20" s="26"/>
@@ -5133,15 +5133,15 @@
     <row r="21" spans="1:120" ht="9.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="18"/>
-      <c r="C21" s="180" t="s">
+      <c r="C21" s="153" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="158"/>
-      <c r="E21" s="158"/>
-      <c r="F21" s="158"/>
-      <c r="G21" s="159"/>
-      <c r="H21" s="139"/>
-      <c r="I21" s="139"/>
+      <c r="D21" s="154"/>
+      <c r="E21" s="154"/>
+      <c r="F21" s="154"/>
+      <c r="G21" s="155"/>
+      <c r="H21" s="167"/>
+      <c r="I21" s="167"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="44"/>
@@ -5257,13 +5257,13 @@
     <row r="22" spans="1:120" ht="9.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="18"/>
-      <c r="C22" s="160"/>
-      <c r="D22" s="161"/>
-      <c r="E22" s="161"/>
-      <c r="F22" s="161"/>
-      <c r="G22" s="162"/>
-      <c r="H22" s="139"/>
-      <c r="I22" s="139"/>
+      <c r="C22" s="156"/>
+      <c r="D22" s="157"/>
+      <c r="E22" s="157"/>
+      <c r="F22" s="157"/>
+      <c r="G22" s="142"/>
+      <c r="H22" s="167"/>
+      <c r="I22" s="167"/>
       <c r="J22" s="46"/>
       <c r="K22" s="47"/>
       <c r="L22" s="47"/>
@@ -5380,13 +5380,13 @@
       <c r="A23" s="1"/>
       <c r="B23" s="28"/>
       <c r="C23" s="29"/>
-      <c r="D23" s="182" t="s">
+      <c r="D23" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="164"/>
-      <c r="F23" s="164"/>
-      <c r="G23" s="170"/>
-      <c r="H23" s="138" t="s">
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="184" t="s">
         <v>46</v>
       </c>
       <c r="I23" s="112">
@@ -5508,10 +5508,10 @@
       <c r="A24" s="1"/>
       <c r="B24" s="18"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="166"/>
-      <c r="E24" s="167"/>
-      <c r="F24" s="167"/>
-      <c r="G24" s="171"/>
+      <c r="D24" s="134"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="136"/>
       <c r="H24" s="112"/>
       <c r="I24" s="112"/>
       <c r="J24" s="14"/>
@@ -5629,15 +5629,15 @@
     <row r="25" spans="1:120" ht="9.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="18"/>
-      <c r="C25" s="180" t="s">
+      <c r="C25" s="153" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="158"/>
-      <c r="G25" s="159"/>
-      <c r="H25" s="139"/>
-      <c r="I25" s="139"/>
+      <c r="D25" s="154"/>
+      <c r="E25" s="154"/>
+      <c r="F25" s="154"/>
+      <c r="G25" s="155"/>
+      <c r="H25" s="167"/>
+      <c r="I25" s="167"/>
       <c r="J25" s="42"/>
       <c r="K25" s="42"/>
       <c r="L25" s="44"/>
@@ -5753,13 +5753,13 @@
     <row r="26" spans="1:120" ht="9.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="18"/>
-      <c r="C26" s="179"/>
-      <c r="D26" s="167"/>
-      <c r="E26" s="167"/>
-      <c r="F26" s="167"/>
-      <c r="G26" s="168"/>
-      <c r="H26" s="139"/>
-      <c r="I26" s="139"/>
+      <c r="C26" s="141"/>
+      <c r="D26" s="135"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="135"/>
+      <c r="G26" s="139"/>
+      <c r="H26" s="167"/>
+      <c r="I26" s="167"/>
       <c r="J26" s="46"/>
       <c r="K26" s="47"/>
       <c r="L26" s="47"/>
@@ -5876,13 +5876,13 @@
       <c r="A27" s="1"/>
       <c r="B27" s="28"/>
       <c r="C27" s="29"/>
-      <c r="D27" s="182" t="s">
+      <c r="D27" s="158" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="164"/>
-      <c r="F27" s="164"/>
-      <c r="G27" s="170"/>
-      <c r="H27" s="138" t="s">
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="184" t="s">
         <v>44</v>
       </c>
       <c r="I27" s="112">
@@ -6004,10 +6004,10 @@
       <c r="A28" s="1"/>
       <c r="B28" s="28"/>
       <c r="C28" s="30"/>
-      <c r="D28" s="166"/>
-      <c r="E28" s="167"/>
-      <c r="F28" s="167"/>
-      <c r="G28" s="171"/>
+      <c r="D28" s="134"/>
+      <c r="E28" s="135"/>
+      <c r="F28" s="135"/>
+      <c r="G28" s="136"/>
       <c r="H28" s="112"/>
       <c r="I28" s="112"/>
       <c r="J28" s="14"/>
@@ -6126,13 +6126,13 @@
       <c r="A29" s="1"/>
       <c r="B29" s="28"/>
       <c r="C29" s="30"/>
-      <c r="D29" s="183" t="s">
+      <c r="D29" s="159" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="184"/>
-      <c r="F29" s="184"/>
-      <c r="G29" s="184"/>
-      <c r="H29" s="138" t="s">
+      <c r="E29" s="160"/>
+      <c r="F29" s="160"/>
+      <c r="G29" s="160"/>
+      <c r="H29" s="184" t="s">
         <v>44</v>
       </c>
       <c r="I29" s="112">
@@ -6254,10 +6254,10 @@
       <c r="A30" s="1"/>
       <c r="B30" s="28"/>
       <c r="C30" s="31"/>
-      <c r="D30" s="166"/>
-      <c r="E30" s="167"/>
-      <c r="F30" s="167"/>
-      <c r="G30" s="167"/>
+      <c r="D30" s="134"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="135"/>
+      <c r="G30" s="135"/>
       <c r="H30" s="112"/>
       <c r="I30" s="112"/>
       <c r="J30" s="26"/>
@@ -6375,15 +6375,15 @@
     <row r="31" spans="1:120" ht="9.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="18"/>
-      <c r="C31" s="157" t="s">
+      <c r="C31" s="179" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="158"/>
-      <c r="E31" s="158"/>
-      <c r="F31" s="158"/>
-      <c r="G31" s="159"/>
-      <c r="H31" s="139"/>
-      <c r="I31" s="139"/>
+      <c r="D31" s="154"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="154"/>
+      <c r="G31" s="155"/>
+      <c r="H31" s="167"/>
+      <c r="I31" s="167"/>
       <c r="J31" s="42"/>
       <c r="K31" s="43"/>
       <c r="L31" s="44"/>
@@ -6499,13 +6499,13 @@
     <row r="32" spans="1:120" ht="9.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="18"/>
-      <c r="C32" s="160"/>
-      <c r="D32" s="161"/>
-      <c r="E32" s="161"/>
-      <c r="F32" s="161"/>
-      <c r="G32" s="162"/>
-      <c r="H32" s="139"/>
-      <c r="I32" s="139"/>
+      <c r="C32" s="156"/>
+      <c r="D32" s="157"/>
+      <c r="E32" s="157"/>
+      <c r="F32" s="157"/>
+      <c r="G32" s="142"/>
+      <c r="H32" s="167"/>
+      <c r="I32" s="167"/>
       <c r="J32" s="46"/>
       <c r="K32" s="47"/>
       <c r="L32" s="47"/>
@@ -6622,14 +6622,14 @@
       <c r="A33" s="1"/>
       <c r="B33" s="18"/>
       <c r="C33" s="32"/>
-      <c r="D33" s="163" t="s">
+      <c r="D33" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="164"/>
-      <c r="F33" s="164"/>
-      <c r="G33" s="165"/>
-      <c r="H33" s="139"/>
-      <c r="I33" s="139"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="138"/>
+      <c r="H33" s="167"/>
+      <c r="I33" s="167"/>
       <c r="J33" s="50"/>
       <c r="K33" s="51"/>
       <c r="L33" s="51"/>
@@ -6746,12 +6746,12 @@
       <c r="A34" s="1"/>
       <c r="B34" s="18"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="166"/>
-      <c r="E34" s="167"/>
-      <c r="F34" s="167"/>
-      <c r="G34" s="168"/>
-      <c r="H34" s="139"/>
-      <c r="I34" s="139"/>
+      <c r="D34" s="134"/>
+      <c r="E34" s="135"/>
+      <c r="F34" s="135"/>
+      <c r="G34" s="139"/>
+      <c r="H34" s="167"/>
+      <c r="I34" s="167"/>
       <c r="J34" s="52"/>
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
@@ -6869,12 +6869,12 @@
       <c r="B35" s="18"/>
       <c r="C35" s="1"/>
       <c r="D35" s="33"/>
-      <c r="E35" s="169" t="s">
+      <c r="E35" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="164"/>
-      <c r="G35" s="170"/>
-      <c r="H35" s="138" t="s">
+      <c r="F35" s="132"/>
+      <c r="G35" s="133"/>
+      <c r="H35" s="184" t="s">
         <v>45</v>
       </c>
       <c r="I35" s="112">
@@ -6997,9 +6997,9 @@
       <c r="B36" s="18"/>
       <c r="C36" s="1"/>
       <c r="D36" s="34"/>
-      <c r="E36" s="166"/>
-      <c r="F36" s="167"/>
-      <c r="G36" s="171"/>
+      <c r="E36" s="134"/>
+      <c r="F36" s="135"/>
+      <c r="G36" s="136"/>
       <c r="H36" s="112"/>
       <c r="I36" s="112"/>
       <c r="J36" s="14"/>
@@ -7119,12 +7119,12 @@
       <c r="B37" s="18"/>
       <c r="C37" s="1"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="169" t="s">
+      <c r="E37" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F37" s="164"/>
-      <c r="G37" s="170"/>
-      <c r="H37" s="138" t="s">
+      <c r="F37" s="132"/>
+      <c r="G37" s="133"/>
+      <c r="H37" s="184" t="s">
         <v>44</v>
       </c>
       <c r="I37" s="112">
@@ -7247,9 +7247,9 @@
       <c r="B38" s="18"/>
       <c r="C38" s="1"/>
       <c r="D38" s="35"/>
-      <c r="E38" s="166"/>
-      <c r="F38" s="167"/>
-      <c r="G38" s="171"/>
+      <c r="E38" s="134"/>
+      <c r="F38" s="135"/>
+      <c r="G38" s="136"/>
       <c r="H38" s="112"/>
       <c r="I38" s="112"/>
       <c r="J38" s="26"/>
@@ -7368,14 +7368,14 @@
       <c r="A39" s="1"/>
       <c r="B39" s="18"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="172" t="s">
+      <c r="D39" s="180" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="158"/>
-      <c r="F39" s="158"/>
-      <c r="G39" s="159"/>
-      <c r="H39" s="139"/>
-      <c r="I39" s="139"/>
+      <c r="E39" s="154"/>
+      <c r="F39" s="154"/>
+      <c r="G39" s="155"/>
+      <c r="H39" s="167"/>
+      <c r="I39" s="167"/>
       <c r="J39" s="50"/>
       <c r="K39" s="51"/>
       <c r="L39" s="51"/>
@@ -7492,12 +7492,12 @@
       <c r="A40" s="1"/>
       <c r="B40" s="18"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="166"/>
-      <c r="E40" s="167"/>
-      <c r="F40" s="167"/>
-      <c r="G40" s="168"/>
-      <c r="H40" s="139"/>
-      <c r="I40" s="139"/>
+      <c r="D40" s="134"/>
+      <c r="E40" s="135"/>
+      <c r="F40" s="135"/>
+      <c r="G40" s="139"/>
+      <c r="H40" s="167"/>
+      <c r="I40" s="167"/>
       <c r="J40" s="52"/>
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
@@ -7615,12 +7615,12 @@
       <c r="B41" s="18"/>
       <c r="C41" s="1"/>
       <c r="D41" s="33"/>
-      <c r="E41" s="169" t="s">
+      <c r="E41" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="164"/>
-      <c r="G41" s="170"/>
-      <c r="H41" s="138" t="s">
+      <c r="F41" s="132"/>
+      <c r="G41" s="133"/>
+      <c r="H41" s="184" t="s">
         <v>43</v>
       </c>
       <c r="I41" s="112">
@@ -7743,9 +7743,9 @@
       <c r="B42" s="18"/>
       <c r="C42" s="1"/>
       <c r="D42" s="34"/>
-      <c r="E42" s="166"/>
-      <c r="F42" s="167"/>
-      <c r="G42" s="171"/>
+      <c r="E42" s="134"/>
+      <c r="F42" s="135"/>
+      <c r="G42" s="136"/>
       <c r="H42" s="112"/>
       <c r="I42" s="112"/>
       <c r="J42" s="14"/>
@@ -7865,12 +7865,12 @@
       <c r="B43" s="18"/>
       <c r="C43" s="1"/>
       <c r="D43" s="34"/>
-      <c r="E43" s="169" t="s">
+      <c r="E43" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="164"/>
-      <c r="G43" s="170"/>
-      <c r="H43" s="138" t="s">
+      <c r="F43" s="132"/>
+      <c r="G43" s="133"/>
+      <c r="H43" s="184" t="s">
         <v>43</v>
       </c>
       <c r="I43" s="112">
@@ -7993,9 +7993,9 @@
       <c r="B44" s="18"/>
       <c r="C44" s="1"/>
       <c r="D44" s="34"/>
-      <c r="E44" s="166"/>
-      <c r="F44" s="167"/>
-      <c r="G44" s="171"/>
+      <c r="E44" s="134"/>
+      <c r="F44" s="135"/>
+      <c r="G44" s="136"/>
       <c r="H44" s="112"/>
       <c r="I44" s="112"/>
       <c r="J44" s="14"/>
@@ -8115,12 +8115,12 @@
       <c r="B45" s="18"/>
       <c r="C45" s="1"/>
       <c r="D45" s="34"/>
-      <c r="E45" s="169" t="s">
+      <c r="E45" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="164"/>
-      <c r="G45" s="170"/>
-      <c r="H45" s="138" t="s">
+      <c r="F45" s="132"/>
+      <c r="G45" s="133"/>
+      <c r="H45" s="184" t="s">
         <v>42</v>
       </c>
       <c r="I45" s="112">
@@ -8243,9 +8243,9 @@
       <c r="B46" s="18"/>
       <c r="C46" s="1"/>
       <c r="D46" s="34"/>
-      <c r="E46" s="166"/>
-      <c r="F46" s="167"/>
-      <c r="G46" s="171"/>
+      <c r="E46" s="134"/>
+      <c r="F46" s="135"/>
+      <c r="G46" s="136"/>
       <c r="H46" s="112"/>
       <c r="I46" s="112"/>
       <c r="J46" s="14"/>
@@ -8365,12 +8365,12 @@
       <c r="B47" s="18"/>
       <c r="C47" s="1"/>
       <c r="D47" s="34"/>
-      <c r="E47" s="169" t="s">
+      <c r="E47" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="F47" s="164"/>
-      <c r="G47" s="170"/>
-      <c r="H47" s="138" t="s">
+      <c r="F47" s="132"/>
+      <c r="G47" s="133"/>
+      <c r="H47" s="184" t="s">
         <v>41</v>
       </c>
       <c r="I47" s="112">
@@ -8493,9 +8493,9 @@
       <c r="B48" s="18"/>
       <c r="C48" s="1"/>
       <c r="D48" s="34"/>
-      <c r="E48" s="166"/>
-      <c r="F48" s="167"/>
-      <c r="G48" s="171"/>
+      <c r="E48" s="134"/>
+      <c r="F48" s="135"/>
+      <c r="G48" s="136"/>
       <c r="H48" s="112"/>
       <c r="I48" s="112"/>
       <c r="J48" s="14"/>
@@ -8615,12 +8615,12 @@
       <c r="B49" s="18"/>
       <c r="C49" s="1"/>
       <c r="D49" s="34"/>
-      <c r="E49" s="169" t="s">
+      <c r="E49" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="164"/>
-      <c r="G49" s="170"/>
-      <c r="H49" s="138" t="s">
+      <c r="F49" s="132"/>
+      <c r="G49" s="133"/>
+      <c r="H49" s="184" t="s">
         <v>50</v>
       </c>
       <c r="I49" s="112">
@@ -8743,9 +8743,9 @@
       <c r="B50" s="18"/>
       <c r="C50" s="1"/>
       <c r="D50" s="34"/>
-      <c r="E50" s="166"/>
-      <c r="F50" s="167"/>
-      <c r="G50" s="171"/>
+      <c r="E50" s="134"/>
+      <c r="F50" s="135"/>
+      <c r="G50" s="136"/>
       <c r="H50" s="112"/>
       <c r="I50" s="112"/>
       <c r="J50" s="14"/>
@@ -8865,12 +8865,12 @@
       <c r="B51" s="18"/>
       <c r="C51" s="1"/>
       <c r="D51" s="34"/>
-      <c r="E51" s="169" t="s">
+      <c r="E51" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="164"/>
-      <c r="G51" s="170"/>
-      <c r="H51" s="138" t="s">
+      <c r="F51" s="132"/>
+      <c r="G51" s="133"/>
+      <c r="H51" s="184" t="s">
         <v>47</v>
       </c>
       <c r="I51" s="112">
@@ -8993,9 +8993,9 @@
       <c r="B52" s="18"/>
       <c r="C52" s="1"/>
       <c r="D52" s="34"/>
-      <c r="E52" s="166"/>
-      <c r="F52" s="167"/>
-      <c r="G52" s="171"/>
+      <c r="E52" s="134"/>
+      <c r="F52" s="135"/>
+      <c r="G52" s="136"/>
       <c r="H52" s="112"/>
       <c r="I52" s="112"/>
       <c r="J52" s="26"/>
@@ -9114,14 +9114,14 @@
       <c r="A53" s="1"/>
       <c r="B53" s="18"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="163" t="s">
+      <c r="D53" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="164"/>
-      <c r="F53" s="164"/>
-      <c r="G53" s="165"/>
-      <c r="H53" s="139"/>
-      <c r="I53" s="139"/>
+      <c r="E53" s="132"/>
+      <c r="F53" s="132"/>
+      <c r="G53" s="138"/>
+      <c r="H53" s="167"/>
+      <c r="I53" s="167"/>
       <c r="J53" s="50"/>
       <c r="K53" s="51"/>
       <c r="L53" s="51"/>
@@ -9238,12 +9238,12 @@
       <c r="A54" s="1"/>
       <c r="B54" s="18"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="166"/>
-      <c r="E54" s="167"/>
-      <c r="F54" s="167"/>
-      <c r="G54" s="168"/>
-      <c r="H54" s="139"/>
-      <c r="I54" s="139"/>
+      <c r="D54" s="134"/>
+      <c r="E54" s="135"/>
+      <c r="F54" s="135"/>
+      <c r="G54" s="139"/>
+      <c r="H54" s="167"/>
+      <c r="I54" s="167"/>
       <c r="J54" s="52"/>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -9361,12 +9361,12 @@
       <c r="B55" s="18"/>
       <c r="C55" s="1"/>
       <c r="D55" s="34"/>
-      <c r="E55" s="169" t="s">
+      <c r="E55" s="131" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="164"/>
-      <c r="G55" s="170"/>
-      <c r="H55" s="138" t="s">
+      <c r="F55" s="132"/>
+      <c r="G55" s="133"/>
+      <c r="H55" s="184" t="s">
         <v>48</v>
       </c>
       <c r="I55" s="112">
@@ -9489,9 +9489,9 @@
       <c r="B56" s="18"/>
       <c r="C56" s="1"/>
       <c r="D56" s="34"/>
-      <c r="E56" s="166"/>
-      <c r="F56" s="167"/>
-      <c r="G56" s="171"/>
+      <c r="E56" s="134"/>
+      <c r="F56" s="135"/>
+      <c r="G56" s="136"/>
       <c r="H56" s="112"/>
       <c r="I56" s="112"/>
       <c r="J56" s="14"/>
@@ -9611,12 +9611,12 @@
       <c r="B57" s="18"/>
       <c r="C57" s="1"/>
       <c r="D57" s="34"/>
-      <c r="E57" s="169" t="s">
+      <c r="E57" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="F57" s="164"/>
-      <c r="G57" s="170"/>
-      <c r="H57" s="138" t="s">
+      <c r="F57" s="132"/>
+      <c r="G57" s="133"/>
+      <c r="H57" s="184" t="s">
         <v>51</v>
       </c>
       <c r="I57" s="112">
@@ -9739,9 +9739,9 @@
       <c r="B58" s="18"/>
       <c r="C58" s="1"/>
       <c r="D58" s="34"/>
-      <c r="E58" s="166"/>
-      <c r="F58" s="167"/>
-      <c r="G58" s="171"/>
+      <c r="E58" s="134"/>
+      <c r="F58" s="135"/>
+      <c r="G58" s="136"/>
       <c r="H58" s="112"/>
       <c r="I58" s="112"/>
       <c r="J58" s="14"/>
@@ -9861,12 +9861,12 @@
       <c r="B59" s="18"/>
       <c r="C59" s="1"/>
       <c r="D59" s="34"/>
-      <c r="E59" s="169" t="s">
+      <c r="E59" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="F59" s="164"/>
-      <c r="G59" s="170"/>
-      <c r="H59" s="138" t="s">
+      <c r="F59" s="132"/>
+      <c r="G59" s="133"/>
+      <c r="H59" s="184" t="s">
         <v>49</v>
       </c>
       <c r="I59" s="112">
@@ -9989,9 +9989,9 @@
       <c r="B60" s="18"/>
       <c r="C60" s="1"/>
       <c r="D60" s="34"/>
-      <c r="E60" s="166"/>
-      <c r="F60" s="167"/>
-      <c r="G60" s="171"/>
+      <c r="E60" s="134"/>
+      <c r="F60" s="135"/>
+      <c r="G60" s="136"/>
       <c r="H60" s="112"/>
       <c r="I60" s="112"/>
       <c r="J60" s="14"/>
@@ -10111,12 +10111,12 @@
       <c r="B61" s="18"/>
       <c r="C61" s="1"/>
       <c r="D61" s="34"/>
-      <c r="E61" s="169" t="s">
+      <c r="E61" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F61" s="164"/>
-      <c r="G61" s="170"/>
-      <c r="H61" s="138" t="s">
+      <c r="F61" s="132"/>
+      <c r="G61" s="133"/>
+      <c r="H61" s="184" t="s">
         <v>49</v>
       </c>
       <c r="I61" s="112">
@@ -10239,9 +10239,9 @@
       <c r="B62" s="18"/>
       <c r="C62" s="1"/>
       <c r="D62" s="34"/>
-      <c r="E62" s="166"/>
-      <c r="F62" s="167"/>
-      <c r="G62" s="171"/>
+      <c r="E62" s="134"/>
+      <c r="F62" s="135"/>
+      <c r="G62" s="136"/>
       <c r="H62" s="112"/>
       <c r="I62" s="112"/>
       <c r="J62" s="26"/>
@@ -10360,14 +10360,14 @@
       <c r="A63" s="1"/>
       <c r="B63" s="18"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="163" t="s">
+      <c r="D63" s="137" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="164"/>
-      <c r="F63" s="164"/>
-      <c r="G63" s="165"/>
-      <c r="H63" s="139"/>
-      <c r="I63" s="139"/>
+      <c r="E63" s="132"/>
+      <c r="F63" s="132"/>
+      <c r="G63" s="138"/>
+      <c r="H63" s="167"/>
+      <c r="I63" s="167"/>
       <c r="J63" s="50"/>
       <c r="K63" s="51"/>
       <c r="L63" s="51"/>
@@ -10484,12 +10484,12 @@
       <c r="A64" s="1"/>
       <c r="B64" s="18"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="166"/>
-      <c r="E64" s="167"/>
-      <c r="F64" s="167"/>
-      <c r="G64" s="168"/>
-      <c r="H64" s="139"/>
-      <c r="I64" s="139"/>
+      <c r="D64" s="134"/>
+      <c r="E64" s="135"/>
+      <c r="F64" s="135"/>
+      <c r="G64" s="139"/>
+      <c r="H64" s="167"/>
+      <c r="I64" s="167"/>
       <c r="J64" s="52"/>
       <c r="K64" s="49"/>
       <c r="L64" s="49"/>
@@ -10607,12 +10607,12 @@
       <c r="B65" s="18"/>
       <c r="C65" s="1"/>
       <c r="D65" s="34"/>
-      <c r="E65" s="169" t="s">
+      <c r="E65" s="131" t="s">
         <v>35</v>
       </c>
-      <c r="F65" s="164"/>
-      <c r="G65" s="170"/>
-      <c r="H65" s="138" t="s">
+      <c r="F65" s="132"/>
+      <c r="G65" s="133"/>
+      <c r="H65" s="184" t="s">
         <v>52</v>
       </c>
       <c r="I65" s="112">
@@ -10735,9 +10735,9 @@
       <c r="B66" s="18"/>
       <c r="C66" s="1"/>
       <c r="D66" s="34"/>
-      <c r="E66" s="166"/>
-      <c r="F66" s="167"/>
-      <c r="G66" s="171"/>
+      <c r="E66" s="134"/>
+      <c r="F66" s="135"/>
+      <c r="G66" s="136"/>
       <c r="H66" s="112"/>
       <c r="I66" s="112"/>
       <c r="J66" s="14"/>
@@ -10857,12 +10857,12 @@
       <c r="B67" s="18"/>
       <c r="C67" s="1"/>
       <c r="D67" s="34"/>
-      <c r="E67" s="169" t="s">
+      <c r="E67" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="F67" s="164"/>
-      <c r="G67" s="170"/>
-      <c r="H67" s="138" t="s">
+      <c r="F67" s="132"/>
+      <c r="G67" s="133"/>
+      <c r="H67" s="184" t="s">
         <v>53</v>
       </c>
       <c r="I67" s="112">
@@ -10985,9 +10985,9 @@
       <c r="B68" s="18"/>
       <c r="C68" s="1"/>
       <c r="D68" s="34"/>
-      <c r="E68" s="166"/>
-      <c r="F68" s="167"/>
-      <c r="G68" s="171"/>
+      <c r="E68" s="134"/>
+      <c r="F68" s="135"/>
+      <c r="G68" s="136"/>
       <c r="H68" s="112"/>
       <c r="I68" s="112"/>
       <c r="J68" s="14"/>
@@ -11107,12 +11107,12 @@
       <c r="B69" s="18"/>
       <c r="C69" s="1"/>
       <c r="D69" s="34"/>
-      <c r="E69" s="169" t="s">
+      <c r="E69" s="131" t="s">
         <v>36</v>
       </c>
-      <c r="F69" s="164"/>
-      <c r="G69" s="170"/>
-      <c r="H69" s="138" t="s">
+      <c r="F69" s="132"/>
+      <c r="G69" s="133"/>
+      <c r="H69" s="184" t="s">
         <v>54</v>
       </c>
       <c r="I69" s="112">
@@ -11235,9 +11235,9 @@
       <c r="B70" s="18"/>
       <c r="C70" s="1"/>
       <c r="D70" s="34"/>
-      <c r="E70" s="166"/>
-      <c r="F70" s="167"/>
-      <c r="G70" s="171"/>
+      <c r="E70" s="134"/>
+      <c r="F70" s="135"/>
+      <c r="G70" s="136"/>
       <c r="H70" s="112"/>
       <c r="I70" s="112"/>
       <c r="J70" s="14"/>
@@ -11357,12 +11357,12 @@
       <c r="B71" s="18"/>
       <c r="C71" s="1"/>
       <c r="D71" s="34"/>
-      <c r="E71" s="169" t="s">
+      <c r="E71" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F71" s="164"/>
-      <c r="G71" s="170"/>
-      <c r="H71" s="138" t="s">
+      <c r="F71" s="132"/>
+      <c r="G71" s="133"/>
+      <c r="H71" s="184" t="s">
         <v>55</v>
       </c>
       <c r="I71" s="112">
@@ -11485,9 +11485,9 @@
       <c r="B72" s="18"/>
       <c r="C72" s="1"/>
       <c r="D72" s="35"/>
-      <c r="E72" s="166"/>
-      <c r="F72" s="167"/>
-      <c r="G72" s="171"/>
+      <c r="E72" s="134"/>
+      <c r="F72" s="135"/>
+      <c r="G72" s="136"/>
       <c r="H72" s="112"/>
       <c r="I72" s="112"/>
       <c r="J72" s="26"/>
@@ -11605,14 +11605,14 @@
     <row r="73" spans="1:120" ht="9.75" customHeight="1">
       <c r="A73" s="16"/>
       <c r="B73" s="36"/>
-      <c r="C73" s="146" t="s">
+      <c r="C73" s="140" t="s">
         <v>30</v>
       </c>
-      <c r="D73" s="164"/>
-      <c r="E73" s="164"/>
-      <c r="F73" s="164"/>
-      <c r="G73" s="165"/>
-      <c r="H73" s="138" t="s">
+      <c r="D73" s="132"/>
+      <c r="E73" s="132"/>
+      <c r="F73" s="132"/>
+      <c r="G73" s="138"/>
+      <c r="H73" s="184" t="s">
         <v>55</v>
       </c>
       <c r="I73" s="112">
@@ -11733,11 +11733,11 @@
     <row r="74" spans="1:120" ht="9.75" customHeight="1">
       <c r="A74" s="16"/>
       <c r="B74" s="36"/>
-      <c r="C74" s="179"/>
-      <c r="D74" s="167"/>
-      <c r="E74" s="167"/>
-      <c r="F74" s="167"/>
-      <c r="G74" s="168"/>
+      <c r="C74" s="141"/>
+      <c r="D74" s="135"/>
+      <c r="E74" s="135"/>
+      <c r="F74" s="135"/>
+      <c r="G74" s="139"/>
       <c r="H74" s="112"/>
       <c r="I74" s="112"/>
       <c r="J74" s="19"/>
@@ -11855,14 +11855,14 @@
     <row r="75" spans="1:120" ht="9.75" customHeight="1">
       <c r="A75" s="16"/>
       <c r="B75" s="36"/>
-      <c r="C75" s="146" t="s">
+      <c r="C75" s="140" t="s">
         <v>34</v>
       </c>
-      <c r="D75" s="164"/>
-      <c r="E75" s="164"/>
-      <c r="F75" s="164"/>
-      <c r="G75" s="165"/>
-      <c r="H75" s="138" t="s">
+      <c r="D75" s="132"/>
+      <c r="E75" s="132"/>
+      <c r="F75" s="132"/>
+      <c r="G75" s="138"/>
+      <c r="H75" s="184" t="s">
         <v>58</v>
       </c>
       <c r="I75" s="112"/>
@@ -11981,11 +11981,11 @@
     <row r="76" spans="1:120" ht="9.75" customHeight="1">
       <c r="A76" s="16"/>
       <c r="B76" s="36"/>
-      <c r="C76" s="162"/>
-      <c r="D76" s="162"/>
-      <c r="E76" s="162"/>
-      <c r="F76" s="162"/>
-      <c r="G76" s="162"/>
+      <c r="C76" s="142"/>
+      <c r="D76" s="142"/>
+      <c r="E76" s="142"/>
+      <c r="F76" s="142"/>
+      <c r="G76" s="142"/>
       <c r="H76" s="112"/>
       <c r="I76" s="112"/>
       <c r="J76" s="19"/>
@@ -12103,15 +12103,15 @@
     <row r="77" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A77" s="16"/>
       <c r="B77" s="71"/>
-      <c r="C77" s="187" t="s">
+      <c r="C77" s="143" t="s">
         <v>62</v>
       </c>
-      <c r="D77" s="188"/>
-      <c r="E77" s="188"/>
-      <c r="F77" s="188"/>
-      <c r="G77" s="189"/>
-      <c r="H77" s="140"/>
-      <c r="I77" s="129"/>
+      <c r="D77" s="144"/>
+      <c r="E77" s="144"/>
+      <c r="F77" s="144"/>
+      <c r="G77" s="145"/>
+      <c r="H77" s="185"/>
+      <c r="I77" s="181"/>
       <c r="J77" s="63"/>
       <c r="K77" s="64"/>
       <c r="L77" s="64"/>
@@ -12227,13 +12227,13 @@
     <row r="78" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A78" s="16"/>
       <c r="B78" s="71"/>
-      <c r="C78" s="190"/>
-      <c r="D78" s="191"/>
-      <c r="E78" s="191"/>
-      <c r="F78" s="191"/>
-      <c r="G78" s="192"/>
-      <c r="H78" s="141"/>
-      <c r="I78" s="130"/>
+      <c r="C78" s="146"/>
+      <c r="D78" s="147"/>
+      <c r="E78" s="147"/>
+      <c r="F78" s="147"/>
+      <c r="G78" s="148"/>
+      <c r="H78" s="186"/>
+      <c r="I78" s="182"/>
       <c r="J78" s="63"/>
       <c r="K78" s="64"/>
       <c r="L78" s="64"/>
@@ -12350,12 +12350,12 @@
       <c r="A79" s="16"/>
       <c r="B79" s="71"/>
       <c r="C79" s="76"/>
-      <c r="D79" s="132" t="s">
+      <c r="D79" s="115" t="s">
         <v>63</v>
       </c>
-      <c r="E79" s="133"/>
-      <c r="F79" s="133"/>
-      <c r="G79" s="134"/>
+      <c r="E79" s="116"/>
+      <c r="F79" s="116"/>
+      <c r="G79" s="117"/>
       <c r="H79" s="77"/>
       <c r="I79" s="67"/>
       <c r="J79" s="63"/>
@@ -12474,10 +12474,10 @@
       <c r="A80" s="16"/>
       <c r="B80" s="71"/>
       <c r="C80" s="76"/>
-      <c r="D80" s="135"/>
-      <c r="E80" s="136"/>
-      <c r="F80" s="136"/>
-      <c r="G80" s="137"/>
+      <c r="D80" s="118"/>
+      <c r="E80" s="119"/>
+      <c r="F80" s="119"/>
+      <c r="G80" s="120"/>
       <c r="H80" s="77"/>
       <c r="I80" s="67"/>
       <c r="J80" s="63"/>
@@ -12597,15 +12597,15 @@
       <c r="B81" s="36"/>
       <c r="C81" s="60"/>
       <c r="D81" s="70"/>
-      <c r="E81" s="105" t="s">
+      <c r="E81" s="149" t="s">
         <v>73</v>
       </c>
-      <c r="F81" s="105"/>
-      <c r="G81" s="105"/>
-      <c r="H81" s="111">
+      <c r="F81" s="149"/>
+      <c r="G81" s="149"/>
+      <c r="H81" s="103">
         <v>45611</v>
       </c>
-      <c r="I81" s="126">
+      <c r="I81" s="105">
         <v>100</v>
       </c>
       <c r="J81" s="19"/>
@@ -12725,11 +12725,11 @@
       <c r="B82" s="36"/>
       <c r="C82" s="60"/>
       <c r="D82" s="70"/>
-      <c r="E82" s="103"/>
-      <c r="F82" s="103"/>
-      <c r="G82" s="103"/>
-      <c r="H82" s="107"/>
-      <c r="I82" s="109"/>
+      <c r="E82" s="102"/>
+      <c r="F82" s="102"/>
+      <c r="G82" s="102"/>
+      <c r="H82" s="104"/>
+      <c r="I82" s="106"/>
       <c r="J82" s="19"/>
       <c r="K82" s="20"/>
       <c r="L82" s="20"/>
@@ -12847,15 +12847,15 @@
       <c r="B83" s="36"/>
       <c r="C83" s="60"/>
       <c r="D83" s="70"/>
-      <c r="E83" s="103" t="s">
+      <c r="E83" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="F83" s="103"/>
-      <c r="G83" s="103"/>
-      <c r="H83" s="111">
+      <c r="F83" s="102"/>
+      <c r="G83" s="102"/>
+      <c r="H83" s="103">
         <v>45615</v>
       </c>
-      <c r="I83" s="126">
+      <c r="I83" s="105">
         <v>100</v>
       </c>
       <c r="J83" s="19"/>
@@ -12975,11 +12975,11 @@
       <c r="B84" s="36"/>
       <c r="C84" s="60"/>
       <c r="D84" s="70"/>
-      <c r="E84" s="103"/>
-      <c r="F84" s="103"/>
-      <c r="G84" s="103"/>
-      <c r="H84" s="107"/>
-      <c r="I84" s="109"/>
+      <c r="E84" s="102"/>
+      <c r="F84" s="102"/>
+      <c r="G84" s="102"/>
+      <c r="H84" s="104"/>
+      <c r="I84" s="106"/>
       <c r="J84" s="19"/>
       <c r="K84" s="20"/>
       <c r="L84" s="20"/>
@@ -13097,15 +13097,15 @@
       <c r="B85" s="36"/>
       <c r="C85" s="60"/>
       <c r="D85" s="70"/>
-      <c r="E85" s="114" t="s">
+      <c r="E85" s="189" t="s">
         <v>61</v>
       </c>
-      <c r="F85" s="115"/>
-      <c r="G85" s="116"/>
-      <c r="H85" s="110">
+      <c r="F85" s="121"/>
+      <c r="G85" s="122"/>
+      <c r="H85" s="111">
         <v>45617</v>
       </c>
-      <c r="I85" s="126">
+      <c r="I85" s="105">
         <v>100</v>
       </c>
       <c r="J85" s="62"/>
@@ -13225,11 +13225,11 @@
       <c r="B86" s="36"/>
       <c r="C86" s="60"/>
       <c r="D86" s="70"/>
-      <c r="E86" s="117"/>
-      <c r="F86" s="118"/>
-      <c r="G86" s="119"/>
-      <c r="H86" s="110"/>
-      <c r="I86" s="109"/>
+      <c r="E86" s="150"/>
+      <c r="F86" s="125"/>
+      <c r="G86" s="126"/>
+      <c r="H86" s="111"/>
+      <c r="I86" s="106"/>
       <c r="J86" s="62"/>
       <c r="K86" s="20"/>
       <c r="L86" s="20"/>
@@ -13346,16 +13346,16 @@
       <c r="A87" s="16"/>
       <c r="B87" s="71"/>
       <c r="C87" s="90"/>
-      <c r="D87" s="103" t="s">
+      <c r="D87" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="E87" s="103"/>
-      <c r="F87" s="103"/>
-      <c r="G87" s="103"/>
-      <c r="H87" s="111">
+      <c r="E87" s="102"/>
+      <c r="F87" s="102"/>
+      <c r="G87" s="102"/>
+      <c r="H87" s="103">
         <v>45615</v>
       </c>
-      <c r="I87" s="126">
+      <c r="I87" s="105">
         <v>100</v>
       </c>
       <c r="J87" s="62"/>
@@ -13474,12 +13474,12 @@
       <c r="A88" s="16"/>
       <c r="B88" s="71"/>
       <c r="C88" s="90"/>
-      <c r="D88" s="103"/>
-      <c r="E88" s="103"/>
-      <c r="F88" s="103"/>
-      <c r="G88" s="103"/>
-      <c r="H88" s="107"/>
-      <c r="I88" s="109"/>
+      <c r="D88" s="102"/>
+      <c r="E88" s="102"/>
+      <c r="F88" s="102"/>
+      <c r="G88" s="102"/>
+      <c r="H88" s="104"/>
+      <c r="I88" s="106"/>
       <c r="J88" s="62"/>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -13596,14 +13596,14 @@
       <c r="A89" s="16"/>
       <c r="B89" s="36"/>
       <c r="C89" s="79"/>
-      <c r="D89" s="132" t="s">
+      <c r="D89" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="133"/>
-      <c r="F89" s="133"/>
-      <c r="G89" s="134"/>
-      <c r="H89" s="131"/>
-      <c r="I89" s="128"/>
+      <c r="E89" s="116"/>
+      <c r="F89" s="116"/>
+      <c r="G89" s="117"/>
+      <c r="H89" s="187"/>
+      <c r="I89" s="188"/>
       <c r="J89" s="66"/>
       <c r="K89" s="64"/>
       <c r="L89" s="64"/>
@@ -13720,12 +13720,12 @@
       <c r="A90" s="16"/>
       <c r="B90" s="36"/>
       <c r="C90" s="79"/>
-      <c r="D90" s="135"/>
-      <c r="E90" s="136"/>
-      <c r="F90" s="136"/>
-      <c r="G90" s="137"/>
-      <c r="H90" s="131"/>
-      <c r="I90" s="128"/>
+      <c r="D90" s="118"/>
+      <c r="E90" s="119"/>
+      <c r="F90" s="119"/>
+      <c r="G90" s="120"/>
+      <c r="H90" s="187"/>
+      <c r="I90" s="188"/>
       <c r="J90" s="66"/>
       <c r="K90" s="64"/>
       <c r="L90" s="64"/>
@@ -13843,15 +13843,15 @@
       <c r="B91" s="36"/>
       <c r="C91" s="60"/>
       <c r="D91" s="70"/>
-      <c r="E91" s="105" t="s">
+      <c r="E91" s="149" t="s">
         <v>68</v>
       </c>
-      <c r="F91" s="105"/>
-      <c r="G91" s="105"/>
-      <c r="H91" s="111">
+      <c r="F91" s="149"/>
+      <c r="G91" s="149"/>
+      <c r="H91" s="103">
         <v>45616</v>
       </c>
-      <c r="I91" s="126">
+      <c r="I91" s="105">
         <v>100</v>
       </c>
       <c r="J91" s="19"/>
@@ -13971,11 +13971,11 @@
       <c r="B92" s="36"/>
       <c r="C92" s="60"/>
       <c r="D92" s="70"/>
-      <c r="E92" s="103"/>
-      <c r="F92" s="103"/>
-      <c r="G92" s="103"/>
-      <c r="H92" s="107"/>
-      <c r="I92" s="109"/>
+      <c r="E92" s="102"/>
+      <c r="F92" s="102"/>
+      <c r="G92" s="102"/>
+      <c r="H92" s="104"/>
+      <c r="I92" s="106"/>
       <c r="J92" s="19"/>
       <c r="K92" s="20"/>
       <c r="L92" s="20"/>
@@ -14093,15 +14093,15 @@
       <c r="B93" s="36"/>
       <c r="C93" s="60"/>
       <c r="D93" s="70"/>
-      <c r="E93" s="103" t="s">
+      <c r="E93" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="F93" s="103"/>
-      <c r="G93" s="103"/>
-      <c r="H93" s="111">
+      <c r="F93" s="102"/>
+      <c r="G93" s="102"/>
+      <c r="H93" s="103">
         <v>45617</v>
       </c>
-      <c r="I93" s="126">
+      <c r="I93" s="105">
         <v>100</v>
       </c>
       <c r="J93" s="19"/>
@@ -14221,11 +14221,11 @@
       <c r="B94" s="36"/>
       <c r="C94" s="60"/>
       <c r="D94" s="70"/>
-      <c r="E94" s="103"/>
-      <c r="F94" s="103"/>
-      <c r="G94" s="103"/>
-      <c r="H94" s="107"/>
-      <c r="I94" s="109"/>
+      <c r="E94" s="102"/>
+      <c r="F94" s="102"/>
+      <c r="G94" s="102"/>
+      <c r="H94" s="104"/>
+      <c r="I94" s="106"/>
       <c r="J94" s="19"/>
       <c r="K94" s="20"/>
       <c r="L94" s="20"/>
@@ -14343,15 +14343,15 @@
       <c r="B95" s="36"/>
       <c r="C95" s="60"/>
       <c r="D95" s="70"/>
-      <c r="E95" s="103" t="s">
+      <c r="E95" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="F95" s="103"/>
-      <c r="G95" s="103"/>
-      <c r="H95" s="111">
+      <c r="F95" s="102"/>
+      <c r="G95" s="102"/>
+      <c r="H95" s="103">
         <v>45618</v>
       </c>
-      <c r="I95" s="126">
+      <c r="I95" s="105">
         <v>100</v>
       </c>
       <c r="J95" s="19"/>
@@ -14471,11 +14471,11 @@
       <c r="B96" s="36"/>
       <c r="C96" s="60"/>
       <c r="D96" s="70"/>
-      <c r="E96" s="103"/>
-      <c r="F96" s="103"/>
-      <c r="G96" s="103"/>
-      <c r="H96" s="107"/>
-      <c r="I96" s="109"/>
+      <c r="E96" s="102"/>
+      <c r="F96" s="102"/>
+      <c r="G96" s="102"/>
+      <c r="H96" s="104"/>
+      <c r="I96" s="106"/>
       <c r="J96" s="19"/>
       <c r="K96" s="20"/>
       <c r="L96" s="20"/>
@@ -14593,15 +14593,15 @@
       <c r="B97" s="36"/>
       <c r="C97" s="60"/>
       <c r="D97" s="70"/>
-      <c r="E97" s="103" t="s">
+      <c r="E97" s="102" t="s">
         <v>71</v>
       </c>
-      <c r="F97" s="103"/>
-      <c r="G97" s="103"/>
-      <c r="H97" s="111">
+      <c r="F97" s="102"/>
+      <c r="G97" s="102"/>
+      <c r="H97" s="103">
         <v>45621</v>
       </c>
-      <c r="I97" s="126">
+      <c r="I97" s="105">
         <v>100</v>
       </c>
       <c r="J97" s="19"/>
@@ -14721,11 +14721,11 @@
       <c r="B98" s="36"/>
       <c r="C98" s="60"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="103"/>
-      <c r="F98" s="103"/>
-      <c r="G98" s="103"/>
-      <c r="H98" s="107"/>
-      <c r="I98" s="109"/>
+      <c r="E98" s="102"/>
+      <c r="F98" s="102"/>
+      <c r="G98" s="102"/>
+      <c r="H98" s="104"/>
+      <c r="I98" s="106"/>
       <c r="J98" s="19"/>
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
@@ -14843,15 +14843,15 @@
       <c r="B99" s="36"/>
       <c r="C99" s="60"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="103" t="s">
+      <c r="E99" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="F99" s="103"/>
-      <c r="G99" s="103"/>
-      <c r="H99" s="111">
+      <c r="F99" s="102"/>
+      <c r="G99" s="102"/>
+      <c r="H99" s="103">
         <v>45622</v>
       </c>
-      <c r="I99" s="126">
+      <c r="I99" s="105">
         <v>100</v>
       </c>
       <c r="J99" s="19"/>
@@ -14971,11 +14971,11 @@
       <c r="B100" s="36"/>
       <c r="C100" s="60"/>
       <c r="D100" s="70"/>
-      <c r="E100" s="103"/>
-      <c r="F100" s="103"/>
-      <c r="G100" s="103"/>
-      <c r="H100" s="107"/>
-      <c r="I100" s="109"/>
+      <c r="E100" s="102"/>
+      <c r="F100" s="102"/>
+      <c r="G100" s="102"/>
+      <c r="H100" s="104"/>
+      <c r="I100" s="106"/>
       <c r="J100" s="19"/>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -15093,12 +15093,12 @@
       <c r="B101" s="71"/>
       <c r="C101" s="91"/>
       <c r="D101" s="70"/>
-      <c r="E101" s="117" t="s">
+      <c r="E101" s="150" t="s">
         <v>61</v>
       </c>
-      <c r="F101" s="118"/>
-      <c r="G101" s="119"/>
-      <c r="H101" s="111">
+      <c r="F101" s="125"/>
+      <c r="G101" s="126"/>
+      <c r="H101" s="103">
         <v>45623</v>
       </c>
       <c r="I101" s="112">
@@ -15221,10 +15221,10 @@
       <c r="B102" s="71"/>
       <c r="C102" s="91"/>
       <c r="D102" s="70"/>
-      <c r="E102" s="117"/>
-      <c r="F102" s="118"/>
-      <c r="G102" s="119"/>
-      <c r="H102" s="107"/>
+      <c r="E102" s="150"/>
+      <c r="F102" s="125"/>
+      <c r="G102" s="126"/>
+      <c r="H102" s="104"/>
       <c r="I102" s="112"/>
       <c r="J102" s="62"/>
       <c r="K102" s="20"/>
@@ -15342,16 +15342,16 @@
       <c r="A103" s="16"/>
       <c r="B103" s="71"/>
       <c r="C103" s="90"/>
-      <c r="D103" s="103" t="s">
+      <c r="D103" s="102" t="s">
         <v>77</v>
       </c>
-      <c r="E103" s="103"/>
-      <c r="F103" s="103"/>
-      <c r="G103" s="103"/>
-      <c r="H103" s="111">
+      <c r="E103" s="102"/>
+      <c r="F103" s="102"/>
+      <c r="G103" s="102"/>
+      <c r="H103" s="103">
         <v>45622</v>
       </c>
-      <c r="I103" s="113">
+      <c r="I103" s="109">
         <v>100</v>
       </c>
       <c r="J103" s="62"/>
@@ -15470,12 +15470,12 @@
       <c r="A104" s="16"/>
       <c r="B104" s="71"/>
       <c r="C104" s="90"/>
-      <c r="D104" s="103"/>
-      <c r="E104" s="103"/>
-      <c r="F104" s="103"/>
-      <c r="G104" s="103"/>
-      <c r="H104" s="107"/>
-      <c r="I104" s="143"/>
+      <c r="D104" s="102"/>
+      <c r="E104" s="102"/>
+      <c r="F104" s="102"/>
+      <c r="G104" s="102"/>
+      <c r="H104" s="104"/>
+      <c r="I104" s="110"/>
       <c r="J104" s="62"/>
       <c r="K104" s="20"/>
       <c r="L104" s="20"/>
@@ -15591,15 +15591,15 @@
     <row r="105" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A105" s="16"/>
       <c r="B105" s="71"/>
-      <c r="C105" s="187" t="s">
+      <c r="C105" s="143" t="s">
         <v>64</v>
       </c>
-      <c r="D105" s="188"/>
-      <c r="E105" s="188"/>
-      <c r="F105" s="188"/>
-      <c r="G105" s="189"/>
-      <c r="H105" s="127"/>
-      <c r="I105" s="128"/>
+      <c r="D105" s="144"/>
+      <c r="E105" s="144"/>
+      <c r="F105" s="144"/>
+      <c r="G105" s="145"/>
+      <c r="H105" s="190"/>
+      <c r="I105" s="188"/>
       <c r="J105" s="66"/>
       <c r="K105" s="64"/>
       <c r="L105" s="64"/>
@@ -15715,13 +15715,13 @@
     <row r="106" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A106" s="16"/>
       <c r="B106" s="71"/>
-      <c r="C106" s="190"/>
-      <c r="D106" s="191"/>
-      <c r="E106" s="191"/>
-      <c r="F106" s="191"/>
-      <c r="G106" s="192"/>
-      <c r="H106" s="127"/>
-      <c r="I106" s="128"/>
+      <c r="C106" s="146"/>
+      <c r="D106" s="147"/>
+      <c r="E106" s="147"/>
+      <c r="F106" s="147"/>
+      <c r="G106" s="148"/>
+      <c r="H106" s="190"/>
+      <c r="I106" s="188"/>
       <c r="J106" s="66"/>
       <c r="K106" s="64"/>
       <c r="L106" s="64"/>
@@ -15838,14 +15838,14 @@
       <c r="A107" s="16"/>
       <c r="B107" s="36"/>
       <c r="C107" s="78"/>
-      <c r="D107" s="132" t="s">
+      <c r="D107" s="115" t="s">
         <v>59</v>
       </c>
-      <c r="E107" s="133"/>
-      <c r="F107" s="133"/>
-      <c r="G107" s="134"/>
-      <c r="H107" s="127"/>
-      <c r="I107" s="128"/>
+      <c r="E107" s="116"/>
+      <c r="F107" s="116"/>
+      <c r="G107" s="117"/>
+      <c r="H107" s="190"/>
+      <c r="I107" s="188"/>
       <c r="J107" s="66"/>
       <c r="K107" s="64"/>
       <c r="L107" s="64"/>
@@ -15962,12 +15962,12 @@
       <c r="A108" s="16"/>
       <c r="B108" s="36"/>
       <c r="C108" s="76"/>
-      <c r="D108" s="135"/>
-      <c r="E108" s="136"/>
-      <c r="F108" s="136"/>
-      <c r="G108" s="137"/>
-      <c r="H108" s="127"/>
-      <c r="I108" s="128"/>
+      <c r="D108" s="118"/>
+      <c r="E108" s="119"/>
+      <c r="F108" s="119"/>
+      <c r="G108" s="120"/>
+      <c r="H108" s="190"/>
+      <c r="I108" s="188"/>
       <c r="J108" s="66"/>
       <c r="K108" s="64"/>
       <c r="L108" s="64"/>
@@ -16085,15 +16085,15 @@
       <c r="B109" s="36"/>
       <c r="C109" s="60"/>
       <c r="D109" s="70"/>
-      <c r="E109" s="105" t="s">
+      <c r="E109" s="149" t="s">
         <v>73</v>
       </c>
-      <c r="F109" s="105"/>
-      <c r="G109" s="105"/>
-      <c r="H109" s="111">
+      <c r="F109" s="149"/>
+      <c r="G109" s="149"/>
+      <c r="H109" s="103">
         <v>45624</v>
       </c>
-      <c r="I109" s="113">
+      <c r="I109" s="109">
         <v>100</v>
       </c>
       <c r="J109" s="62"/>
@@ -16213,11 +16213,11 @@
       <c r="B110" s="36"/>
       <c r="C110" s="60"/>
       <c r="D110" s="70"/>
-      <c r="E110" s="103"/>
-      <c r="F110" s="103"/>
-      <c r="G110" s="103"/>
-      <c r="H110" s="107"/>
-      <c r="I110" s="143"/>
+      <c r="E110" s="102"/>
+      <c r="F110" s="102"/>
+      <c r="G110" s="102"/>
+      <c r="H110" s="104"/>
+      <c r="I110" s="110"/>
       <c r="J110" s="62"/>
       <c r="K110" s="20"/>
       <c r="L110" s="20"/>
@@ -16335,15 +16335,15 @@
       <c r="B111" s="36"/>
       <c r="C111" s="60"/>
       <c r="D111" s="70"/>
-      <c r="E111" s="103" t="s">
+      <c r="E111" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="F111" s="103"/>
-      <c r="G111" s="103"/>
-      <c r="H111" s="111">
+      <c r="F111" s="102"/>
+      <c r="G111" s="102"/>
+      <c r="H111" s="103">
         <v>45625</v>
       </c>
-      <c r="I111" s="113"/>
+      <c r="I111" s="109"/>
       <c r="J111" s="62"/>
       <c r="K111" s="20"/>
       <c r="L111" s="20"/>
@@ -16461,11 +16461,11 @@
       <c r="B112" s="36"/>
       <c r="C112" s="60"/>
       <c r="D112" s="70"/>
-      <c r="E112" s="103"/>
-      <c r="F112" s="103"/>
-      <c r="G112" s="103"/>
-      <c r="H112" s="107"/>
-      <c r="I112" s="143"/>
+      <c r="E112" s="102"/>
+      <c r="F112" s="102"/>
+      <c r="G112" s="102"/>
+      <c r="H112" s="104"/>
+      <c r="I112" s="110"/>
       <c r="J112" s="62"/>
       <c r="K112" s="20"/>
       <c r="L112" s="20"/>
@@ -16511,8 +16511,8 @@
       <c r="AZ112" s="20"/>
       <c r="BA112" s="20"/>
       <c r="BB112" s="20"/>
-      <c r="BC112" s="20"/>
-      <c r="BD112" s="20"/>
+      <c r="BC112" s="75"/>
+      <c r="BD112" s="75"/>
       <c r="BE112" s="21"/>
       <c r="BF112" s="21"/>
       <c r="BG112" s="69"/>
@@ -16583,12 +16583,12 @@
       <c r="B113" s="71"/>
       <c r="C113" s="91"/>
       <c r="D113" s="70"/>
-      <c r="E113" s="103" t="s">
+      <c r="E113" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="F113" s="103"/>
-      <c r="G113" s="103"/>
-      <c r="H113" s="110">
+      <c r="F113" s="102"/>
+      <c r="G113" s="102"/>
+      <c r="H113" s="111">
         <v>45629</v>
       </c>
       <c r="I113" s="112"/>
@@ -16709,11 +16709,11 @@
       <c r="B114" s="71"/>
       <c r="C114" s="91"/>
       <c r="D114" s="70"/>
-      <c r="E114" s="125"/>
-      <c r="F114" s="125"/>
-      <c r="G114" s="125"/>
-      <c r="H114" s="111"/>
-      <c r="I114" s="113"/>
+      <c r="E114" s="198"/>
+      <c r="F114" s="198"/>
+      <c r="G114" s="198"/>
+      <c r="H114" s="103"/>
+      <c r="I114" s="109"/>
       <c r="J114" s="62"/>
       <c r="K114" s="20"/>
       <c r="L114" s="20"/>
@@ -16830,13 +16830,13 @@
       <c r="A115" s="16"/>
       <c r="B115" s="71"/>
       <c r="C115" s="91"/>
-      <c r="D115" s="103" t="s">
+      <c r="D115" s="102" t="s">
         <v>78</v>
       </c>
-      <c r="E115" s="103"/>
-      <c r="F115" s="103"/>
-      <c r="G115" s="103"/>
-      <c r="H115" s="110">
+      <c r="E115" s="102"/>
+      <c r="F115" s="102"/>
+      <c r="G115" s="102"/>
+      <c r="H115" s="111">
         <v>45625</v>
       </c>
       <c r="I115" s="112"/>
@@ -16956,11 +16956,11 @@
       <c r="A116" s="16"/>
       <c r="B116" s="71"/>
       <c r="C116" s="91"/>
-      <c r="D116" s="103"/>
-      <c r="E116" s="103"/>
-      <c r="F116" s="103"/>
-      <c r="G116" s="103"/>
-      <c r="H116" s="110"/>
+      <c r="D116" s="102"/>
+      <c r="E116" s="102"/>
+      <c r="F116" s="102"/>
+      <c r="G116" s="102"/>
+      <c r="H116" s="111"/>
       <c r="I116" s="112"/>
       <c r="J116" s="62"/>
       <c r="K116" s="20"/>
@@ -17078,14 +17078,14 @@
       <c r="A117" s="16"/>
       <c r="B117" s="36"/>
       <c r="C117" s="80"/>
-      <c r="D117" s="132" t="s">
+      <c r="D117" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="E117" s="133"/>
-      <c r="F117" s="133"/>
-      <c r="G117" s="134"/>
-      <c r="H117" s="121"/>
-      <c r="I117" s="129"/>
+      <c r="E117" s="116"/>
+      <c r="F117" s="116"/>
+      <c r="G117" s="117"/>
+      <c r="H117" s="191"/>
+      <c r="I117" s="181"/>
       <c r="J117" s="63"/>
       <c r="K117" s="64"/>
       <c r="L117" s="64"/>
@@ -17202,12 +17202,12 @@
       <c r="A118" s="16"/>
       <c r="B118" s="36"/>
       <c r="C118" s="80"/>
-      <c r="D118" s="135"/>
-      <c r="E118" s="136"/>
-      <c r="F118" s="136"/>
-      <c r="G118" s="137"/>
-      <c r="H118" s="122"/>
-      <c r="I118" s="130"/>
+      <c r="D118" s="118"/>
+      <c r="E118" s="119"/>
+      <c r="F118" s="119"/>
+      <c r="G118" s="120"/>
+      <c r="H118" s="192"/>
+      <c r="I118" s="182"/>
       <c r="J118" s="63"/>
       <c r="K118" s="64"/>
       <c r="L118" s="64"/>
@@ -17325,15 +17325,15 @@
       <c r="B119" s="36"/>
       <c r="C119" s="60"/>
       <c r="D119" s="70"/>
-      <c r="E119" s="105" t="s">
+      <c r="E119" s="149" t="s">
         <v>68</v>
       </c>
-      <c r="F119" s="105"/>
-      <c r="G119" s="105"/>
-      <c r="H119" s="111">
+      <c r="F119" s="149"/>
+      <c r="G119" s="149"/>
+      <c r="H119" s="103">
         <v>45629</v>
       </c>
-      <c r="I119" s="126">
+      <c r="I119" s="105">
         <v>100</v>
       </c>
       <c r="J119" s="19"/>
@@ -17453,11 +17453,11 @@
       <c r="B120" s="36"/>
       <c r="C120" s="60"/>
       <c r="D120" s="70"/>
-      <c r="E120" s="103"/>
-      <c r="F120" s="103"/>
-      <c r="G120" s="103"/>
-      <c r="H120" s="107"/>
-      <c r="I120" s="109"/>
+      <c r="E120" s="102"/>
+      <c r="F120" s="102"/>
+      <c r="G120" s="102"/>
+      <c r="H120" s="104"/>
+      <c r="I120" s="106"/>
       <c r="J120" s="19"/>
       <c r="K120" s="20"/>
       <c r="L120" s="20"/>
@@ -17575,15 +17575,15 @@
       <c r="B121" s="36"/>
       <c r="C121" s="60"/>
       <c r="D121" s="70"/>
-      <c r="E121" s="103" t="s">
+      <c r="E121" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="F121" s="103"/>
-      <c r="G121" s="103"/>
-      <c r="H121" s="111">
+      <c r="F121" s="102"/>
+      <c r="G121" s="102"/>
+      <c r="H121" s="103">
         <v>45630</v>
       </c>
-      <c r="I121" s="126"/>
+      <c r="I121" s="105"/>
       <c r="J121" s="19"/>
       <c r="K121" s="20"/>
       <c r="L121" s="20"/>
@@ -17701,11 +17701,11 @@
       <c r="B122" s="36"/>
       <c r="C122" s="60"/>
       <c r="D122" s="70"/>
-      <c r="E122" s="103"/>
-      <c r="F122" s="103"/>
-      <c r="G122" s="103"/>
-      <c r="H122" s="107"/>
-      <c r="I122" s="109"/>
+      <c r="E122" s="102"/>
+      <c r="F122" s="102"/>
+      <c r="G122" s="102"/>
+      <c r="H122" s="104"/>
+      <c r="I122" s="106"/>
       <c r="J122" s="19"/>
       <c r="K122" s="20"/>
       <c r="L122" s="20"/>
@@ -17823,12 +17823,12 @@
       <c r="B123" s="36"/>
       <c r="C123" s="60"/>
       <c r="D123" s="70"/>
-      <c r="E123" s="103" t="s">
+      <c r="E123" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="F123" s="103"/>
-      <c r="G123" s="103"/>
-      <c r="H123" s="120">
+      <c r="F123" s="102"/>
+      <c r="G123" s="102"/>
+      <c r="H123" s="197">
         <v>45631</v>
       </c>
       <c r="I123" s="112"/>
@@ -17949,10 +17949,10 @@
       <c r="B124" s="36"/>
       <c r="C124" s="60"/>
       <c r="D124" s="70"/>
-      <c r="E124" s="103"/>
-      <c r="F124" s="103"/>
-      <c r="G124" s="103"/>
-      <c r="H124" s="120"/>
+      <c r="E124" s="102"/>
+      <c r="F124" s="102"/>
+      <c r="G124" s="102"/>
+      <c r="H124" s="197"/>
       <c r="I124" s="112"/>
       <c r="J124" s="62"/>
       <c r="K124" s="20"/>
@@ -18071,12 +18071,12 @@
       <c r="B125" s="36"/>
       <c r="C125" s="60"/>
       <c r="D125" s="70"/>
-      <c r="E125" s="103" t="s">
+      <c r="E125" s="102" t="s">
         <v>71</v>
       </c>
-      <c r="F125" s="103"/>
-      <c r="G125" s="103"/>
-      <c r="H125" s="110">
+      <c r="F125" s="102"/>
+      <c r="G125" s="102"/>
+      <c r="H125" s="111">
         <v>45632</v>
       </c>
       <c r="I125" s="112"/>
@@ -18197,10 +18197,10 @@
       <c r="B126" s="36"/>
       <c r="C126" s="60"/>
       <c r="D126" s="70"/>
-      <c r="E126" s="103"/>
-      <c r="F126" s="103"/>
-      <c r="G126" s="103"/>
-      <c r="H126" s="110"/>
+      <c r="E126" s="102"/>
+      <c r="F126" s="102"/>
+      <c r="G126" s="102"/>
+      <c r="H126" s="111"/>
       <c r="I126" s="112"/>
       <c r="J126" s="62"/>
       <c r="K126" s="20"/>
@@ -18319,15 +18319,15 @@
       <c r="B127" s="36"/>
       <c r="C127" s="60"/>
       <c r="D127" s="70"/>
-      <c r="E127" s="103" t="s">
+      <c r="E127" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="F127" s="103"/>
-      <c r="G127" s="103"/>
-      <c r="H127" s="111">
+      <c r="F127" s="102"/>
+      <c r="G127" s="102"/>
+      <c r="H127" s="103">
         <v>45635</v>
       </c>
-      <c r="I127" s="126"/>
+      <c r="I127" s="105"/>
       <c r="J127" s="19"/>
       <c r="K127" s="20"/>
       <c r="L127" s="20"/>
@@ -18445,11 +18445,11 @@
       <c r="B128" s="36"/>
       <c r="C128" s="60"/>
       <c r="D128" s="70"/>
-      <c r="E128" s="125"/>
-      <c r="F128" s="125"/>
-      <c r="G128" s="125"/>
-      <c r="H128" s="107"/>
-      <c r="I128" s="109"/>
+      <c r="E128" s="198"/>
+      <c r="F128" s="198"/>
+      <c r="G128" s="198"/>
+      <c r="H128" s="104"/>
+      <c r="I128" s="106"/>
       <c r="J128" s="19"/>
       <c r="K128" s="20"/>
       <c r="L128" s="20"/>
@@ -18567,12 +18567,12 @@
       <c r="B129" s="71"/>
       <c r="C129" s="91"/>
       <c r="D129" s="70"/>
-      <c r="E129" s="114" t="s">
+      <c r="E129" s="189" t="s">
         <v>61</v>
       </c>
-      <c r="F129" s="115"/>
-      <c r="G129" s="116"/>
-      <c r="H129" s="110">
+      <c r="F129" s="121"/>
+      <c r="G129" s="122"/>
+      <c r="H129" s="111">
         <v>45638</v>
       </c>
       <c r="I129" s="112"/>
@@ -18693,10 +18693,10 @@
       <c r="B130" s="71"/>
       <c r="C130" s="91"/>
       <c r="D130" s="70"/>
-      <c r="E130" s="117"/>
-      <c r="F130" s="118"/>
-      <c r="G130" s="119"/>
-      <c r="H130" s="110"/>
+      <c r="E130" s="150"/>
+      <c r="F130" s="125"/>
+      <c r="G130" s="126"/>
+      <c r="H130" s="111"/>
       <c r="I130" s="112"/>
       <c r="J130" s="62"/>
       <c r="K130" s="20"/>
@@ -18814,16 +18814,16 @@
       <c r="A131" s="16"/>
       <c r="B131" s="71"/>
       <c r="C131" s="91"/>
-      <c r="D131" s="103" t="s">
+      <c r="D131" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="E131" s="103"/>
-      <c r="F131" s="103"/>
-      <c r="G131" s="103"/>
-      <c r="H131" s="111">
+      <c r="E131" s="102"/>
+      <c r="F131" s="102"/>
+      <c r="G131" s="102"/>
+      <c r="H131" s="103">
         <v>45635</v>
       </c>
-      <c r="I131" s="113"/>
+      <c r="I131" s="109"/>
       <c r="J131" s="62"/>
       <c r="K131" s="20"/>
       <c r="L131" s="20"/>
@@ -18940,12 +18940,12 @@
       <c r="A132" s="16"/>
       <c r="B132" s="71"/>
       <c r="C132" s="90"/>
-      <c r="D132" s="103"/>
-      <c r="E132" s="103"/>
-      <c r="F132" s="103"/>
-      <c r="G132" s="103"/>
-      <c r="H132" s="107"/>
-      <c r="I132" s="143"/>
+      <c r="D132" s="102"/>
+      <c r="E132" s="102"/>
+      <c r="F132" s="102"/>
+      <c r="G132" s="102"/>
+      <c r="H132" s="104"/>
+      <c r="I132" s="110"/>
       <c r="J132" s="62"/>
       <c r="K132" s="20"/>
       <c r="L132" s="20"/>
@@ -19061,15 +19061,15 @@
     <row r="133" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A133" s="16"/>
       <c r="B133" s="36"/>
-      <c r="C133" s="132" t="s">
+      <c r="C133" s="115" t="s">
         <v>67</v>
       </c>
-      <c r="D133" s="133"/>
-      <c r="E133" s="133"/>
-      <c r="F133" s="133"/>
-      <c r="G133" s="134"/>
-      <c r="H133" s="121"/>
-      <c r="I133" s="123"/>
+      <c r="D133" s="116"/>
+      <c r="E133" s="116"/>
+      <c r="F133" s="116"/>
+      <c r="G133" s="117"/>
+      <c r="H133" s="191"/>
+      <c r="I133" s="107"/>
       <c r="J133" s="66"/>
       <c r="K133" s="64"/>
       <c r="L133" s="64"/>
@@ -19185,13 +19185,13 @@
     <row r="134" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A134" s="16"/>
       <c r="B134" s="36"/>
-      <c r="C134" s="135"/>
-      <c r="D134" s="136"/>
-      <c r="E134" s="136"/>
-      <c r="F134" s="136"/>
-      <c r="G134" s="137"/>
-      <c r="H134" s="122"/>
-      <c r="I134" s="124"/>
+      <c r="C134" s="118"/>
+      <c r="D134" s="119"/>
+      <c r="E134" s="119"/>
+      <c r="F134" s="119"/>
+      <c r="G134" s="120"/>
+      <c r="H134" s="192"/>
+      <c r="I134" s="108"/>
       <c r="J134" s="66"/>
       <c r="K134" s="64"/>
       <c r="L134" s="64"/>
@@ -19308,14 +19308,14 @@
       <c r="A135" s="16"/>
       <c r="B135" s="36"/>
       <c r="C135" s="60"/>
-      <c r="D135" s="132" t="s">
+      <c r="D135" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="133"/>
-      <c r="F135" s="133"/>
-      <c r="G135" s="134"/>
-      <c r="H135" s="193"/>
-      <c r="I135" s="129"/>
+      <c r="E135" s="116"/>
+      <c r="F135" s="116"/>
+      <c r="G135" s="117"/>
+      <c r="H135" s="113"/>
+      <c r="I135" s="181"/>
       <c r="J135" s="63"/>
       <c r="K135" s="64"/>
       <c r="L135" s="64"/>
@@ -19432,12 +19432,12 @@
       <c r="A136" s="16"/>
       <c r="B136" s="36"/>
       <c r="C136" s="60"/>
-      <c r="D136" s="135"/>
-      <c r="E136" s="136"/>
-      <c r="F136" s="136"/>
-      <c r="G136" s="137"/>
-      <c r="H136" s="198"/>
-      <c r="I136" s="144"/>
+      <c r="D136" s="118"/>
+      <c r="E136" s="119"/>
+      <c r="F136" s="119"/>
+      <c r="G136" s="120"/>
+      <c r="H136" s="130"/>
+      <c r="I136" s="183"/>
       <c r="J136" s="63"/>
       <c r="K136" s="64"/>
       <c r="L136" s="64"/>
@@ -19555,15 +19555,15 @@
       <c r="B137" s="36"/>
       <c r="C137" s="72"/>
       <c r="D137" s="74"/>
-      <c r="E137" s="115" t="s">
+      <c r="E137" s="121" t="s">
         <v>73</v>
       </c>
-      <c r="F137" s="115"/>
-      <c r="G137" s="116"/>
-      <c r="H137" s="111">
+      <c r="F137" s="121"/>
+      <c r="G137" s="122"/>
+      <c r="H137" s="103">
         <v>45636</v>
       </c>
-      <c r="I137" s="113"/>
+      <c r="I137" s="109"/>
       <c r="J137" s="62"/>
       <c r="K137" s="20"/>
       <c r="L137" s="20"/>
@@ -19681,11 +19681,11 @@
       <c r="B138" s="36"/>
       <c r="C138" s="72"/>
       <c r="D138" s="70"/>
-      <c r="E138" s="185"/>
-      <c r="F138" s="185"/>
-      <c r="G138" s="186"/>
-      <c r="H138" s="107"/>
-      <c r="I138" s="143"/>
+      <c r="E138" s="123"/>
+      <c r="F138" s="123"/>
+      <c r="G138" s="124"/>
+      <c r="H138" s="104"/>
+      <c r="I138" s="110"/>
       <c r="J138" s="62"/>
       <c r="K138" s="20"/>
       <c r="L138" s="20"/>
@@ -19803,15 +19803,15 @@
       <c r="B139" s="36"/>
       <c r="C139" s="72"/>
       <c r="D139" s="70"/>
-      <c r="E139" s="115" t="s">
+      <c r="E139" s="121" t="s">
         <v>74</v>
       </c>
-      <c r="F139" s="115"/>
-      <c r="G139" s="116"/>
-      <c r="H139" s="111">
+      <c r="F139" s="121"/>
+      <c r="G139" s="122"/>
+      <c r="H139" s="103">
         <v>45637</v>
       </c>
-      <c r="I139" s="113"/>
+      <c r="I139" s="109"/>
       <c r="J139" s="62"/>
       <c r="K139" s="20"/>
       <c r="L139" s="20"/>
@@ -19929,11 +19929,11 @@
       <c r="B140" s="36"/>
       <c r="C140" s="72"/>
       <c r="D140" s="70"/>
-      <c r="E140" s="118"/>
-      <c r="F140" s="118"/>
-      <c r="G140" s="119"/>
-      <c r="H140" s="107"/>
-      <c r="I140" s="143"/>
+      <c r="E140" s="125"/>
+      <c r="F140" s="125"/>
+      <c r="G140" s="126"/>
+      <c r="H140" s="104"/>
+      <c r="I140" s="110"/>
       <c r="J140" s="62"/>
       <c r="K140" s="20"/>
       <c r="L140" s="20"/>
@@ -20050,13 +20050,13 @@
       <c r="A141" s="16"/>
       <c r="B141" s="36"/>
       <c r="C141" s="82"/>
-      <c r="D141" s="103" t="s">
+      <c r="D141" s="102" t="s">
         <v>80</v>
       </c>
-      <c r="E141" s="103"/>
-      <c r="F141" s="103"/>
-      <c r="G141" s="103"/>
-      <c r="H141" s="111">
+      <c r="E141" s="102"/>
+      <c r="F141" s="102"/>
+      <c r="G141" s="102"/>
+      <c r="H141" s="103">
         <v>45637</v>
       </c>
       <c r="I141" s="92"/>
@@ -20176,11 +20176,11 @@
       <c r="A142" s="16"/>
       <c r="B142" s="36"/>
       <c r="C142" s="82"/>
-      <c r="D142" s="103"/>
-      <c r="E142" s="103"/>
-      <c r="F142" s="103"/>
-      <c r="G142" s="103"/>
-      <c r="H142" s="107"/>
+      <c r="D142" s="102"/>
+      <c r="E142" s="102"/>
+      <c r="F142" s="102"/>
+      <c r="G142" s="102"/>
+      <c r="H142" s="104"/>
       <c r="I142" s="92"/>
       <c r="J142" s="62"/>
       <c r="K142" s="20"/>
@@ -20298,14 +20298,14 @@
       <c r="A143" s="16"/>
       <c r="B143" s="36"/>
       <c r="C143" s="72"/>
-      <c r="D143" s="195" t="s">
+      <c r="D143" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="E143" s="196"/>
-      <c r="F143" s="196"/>
-      <c r="G143" s="197"/>
-      <c r="H143" s="193"/>
-      <c r="I143" s="123"/>
+      <c r="E143" s="128"/>
+      <c r="F143" s="128"/>
+      <c r="G143" s="129"/>
+      <c r="H143" s="113"/>
+      <c r="I143" s="107"/>
       <c r="J143" s="66"/>
       <c r="K143" s="64"/>
       <c r="L143" s="64"/>
@@ -20422,12 +20422,12 @@
       <c r="A144" s="16"/>
       <c r="B144" s="36"/>
       <c r="C144" s="72"/>
-      <c r="D144" s="135"/>
-      <c r="E144" s="136"/>
-      <c r="F144" s="136"/>
-      <c r="G144" s="137"/>
-      <c r="H144" s="194"/>
-      <c r="I144" s="124"/>
+      <c r="D144" s="118"/>
+      <c r="E144" s="119"/>
+      <c r="F144" s="119"/>
+      <c r="G144" s="120"/>
+      <c r="H144" s="114"/>
+      <c r="I144" s="108"/>
       <c r="J144" s="66"/>
       <c r="K144" s="64"/>
       <c r="L144" s="64"/>
@@ -20545,15 +20545,15 @@
       <c r="B145" s="36"/>
       <c r="C145" s="72"/>
       <c r="D145" s="74"/>
-      <c r="E145" s="115" t="s">
+      <c r="E145" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="F145" s="115"/>
-      <c r="G145" s="116"/>
-      <c r="H145" s="111">
+      <c r="F145" s="121"/>
+      <c r="G145" s="122"/>
+      <c r="H145" s="103">
         <v>45639</v>
       </c>
-      <c r="I145" s="113"/>
+      <c r="I145" s="109"/>
       <c r="J145" s="62"/>
       <c r="K145" s="20"/>
       <c r="L145" s="20"/>
@@ -20671,11 +20671,11 @@
       <c r="B146" s="36"/>
       <c r="C146" s="72"/>
       <c r="D146" s="70"/>
-      <c r="E146" s="185"/>
-      <c r="F146" s="185"/>
-      <c r="G146" s="186"/>
-      <c r="H146" s="107"/>
-      <c r="I146" s="143"/>
+      <c r="E146" s="123"/>
+      <c r="F146" s="123"/>
+      <c r="G146" s="124"/>
+      <c r="H146" s="104"/>
+      <c r="I146" s="110"/>
       <c r="J146" s="62"/>
       <c r="K146" s="20"/>
       <c r="L146" s="20"/>
@@ -20793,15 +20793,15 @@
       <c r="B147" s="36"/>
       <c r="C147" s="72"/>
       <c r="D147" s="70"/>
-      <c r="E147" s="115" t="s">
+      <c r="E147" s="121" t="s">
         <v>69</v>
       </c>
-      <c r="F147" s="115"/>
-      <c r="G147" s="116"/>
-      <c r="H147" s="111">
+      <c r="F147" s="121"/>
+      <c r="G147" s="122"/>
+      <c r="H147" s="103">
         <v>45642</v>
       </c>
-      <c r="I147" s="113"/>
+      <c r="I147" s="109"/>
       <c r="J147" s="62"/>
       <c r="K147" s="20"/>
       <c r="L147" s="20"/>
@@ -20919,11 +20919,11 @@
       <c r="B148" s="36"/>
       <c r="C148" s="72"/>
       <c r="D148" s="70"/>
-      <c r="E148" s="185"/>
-      <c r="F148" s="185"/>
-      <c r="G148" s="186"/>
-      <c r="H148" s="107"/>
-      <c r="I148" s="143"/>
+      <c r="E148" s="123"/>
+      <c r="F148" s="123"/>
+      <c r="G148" s="124"/>
+      <c r="H148" s="104"/>
+      <c r="I148" s="110"/>
       <c r="J148" s="62"/>
       <c r="K148" s="20"/>
       <c r="L148" s="20"/>
@@ -21041,15 +21041,15 @@
       <c r="B149" s="36"/>
       <c r="C149" s="72"/>
       <c r="D149" s="70"/>
-      <c r="E149" s="115" t="s">
+      <c r="E149" s="121" t="s">
         <v>70</v>
       </c>
-      <c r="F149" s="115"/>
-      <c r="G149" s="116"/>
-      <c r="H149" s="111">
+      <c r="F149" s="121"/>
+      <c r="G149" s="122"/>
+      <c r="H149" s="103">
         <v>45643</v>
       </c>
-      <c r="I149" s="113"/>
+      <c r="I149" s="109"/>
       <c r="J149" s="62"/>
       <c r="K149" s="20"/>
       <c r="L149" s="20"/>
@@ -21167,11 +21167,11 @@
       <c r="B150" s="36"/>
       <c r="C150" s="72"/>
       <c r="D150" s="70"/>
-      <c r="E150" s="185"/>
-      <c r="F150" s="185"/>
-      <c r="G150" s="186"/>
-      <c r="H150" s="107"/>
-      <c r="I150" s="143"/>
+      <c r="E150" s="123"/>
+      <c r="F150" s="123"/>
+      <c r="G150" s="124"/>
+      <c r="H150" s="104"/>
+      <c r="I150" s="110"/>
       <c r="J150" s="62"/>
       <c r="K150" s="20"/>
       <c r="L150" s="20"/>
@@ -21289,15 +21289,15 @@
       <c r="B151" s="36"/>
       <c r="C151" s="72"/>
       <c r="D151" s="70"/>
-      <c r="E151" s="103" t="s">
+      <c r="E151" s="102" t="s">
         <v>75</v>
       </c>
-      <c r="F151" s="103"/>
-      <c r="G151" s="103"/>
-      <c r="H151" s="111">
+      <c r="F151" s="102"/>
+      <c r="G151" s="102"/>
+      <c r="H151" s="103">
         <v>45644</v>
       </c>
-      <c r="I151" s="113"/>
+      <c r="I151" s="109"/>
       <c r="J151" s="62"/>
       <c r="K151" s="20"/>
       <c r="L151" s="20"/>
@@ -21415,11 +21415,11 @@
       <c r="B152" s="36"/>
       <c r="C152" s="72"/>
       <c r="D152" s="70"/>
-      <c r="E152" s="103"/>
-      <c r="F152" s="103"/>
-      <c r="G152" s="103"/>
-      <c r="H152" s="107"/>
-      <c r="I152" s="143"/>
+      <c r="E152" s="102"/>
+      <c r="F152" s="102"/>
+      <c r="G152" s="102"/>
+      <c r="H152" s="104"/>
+      <c r="I152" s="110"/>
       <c r="J152" s="62"/>
       <c r="K152" s="20"/>
       <c r="L152" s="20"/>
@@ -21537,15 +21537,15 @@
       <c r="B153" s="36"/>
       <c r="C153" s="72"/>
       <c r="D153" s="70"/>
-      <c r="E153" s="103" t="s">
+      <c r="E153" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="F153" s="103"/>
-      <c r="G153" s="103"/>
-      <c r="H153" s="111">
+      <c r="F153" s="102"/>
+      <c r="G153" s="102"/>
+      <c r="H153" s="103">
         <v>45644</v>
       </c>
-      <c r="I153" s="113"/>
+      <c r="I153" s="109"/>
       <c r="J153" s="62"/>
       <c r="K153" s="20"/>
       <c r="L153" s="20"/>
@@ -21663,11 +21663,11 @@
       <c r="B154" s="36"/>
       <c r="C154" s="72"/>
       <c r="D154" s="70"/>
-      <c r="E154" s="103"/>
-      <c r="F154" s="103"/>
-      <c r="G154" s="103"/>
-      <c r="H154" s="107"/>
-      <c r="I154" s="143"/>
+      <c r="E154" s="102"/>
+      <c r="F154" s="102"/>
+      <c r="G154" s="102"/>
+      <c r="H154" s="104"/>
+      <c r="I154" s="110"/>
       <c r="J154" s="62"/>
       <c r="K154" s="20"/>
       <c r="L154" s="20"/>
@@ -21784,16 +21784,16 @@
       <c r="A155" s="1"/>
       <c r="B155" s="18"/>
       <c r="C155" s="60"/>
-      <c r="D155" s="104"/>
-      <c r="E155" s="102" t="s">
+      <c r="D155" s="194"/>
+      <c r="E155" s="193" t="s">
         <v>61</v>
       </c>
-      <c r="F155" s="103"/>
-      <c r="G155" s="103"/>
-      <c r="H155" s="106">
+      <c r="F155" s="102"/>
+      <c r="G155" s="102"/>
+      <c r="H155" s="195">
         <v>45645</v>
       </c>
-      <c r="I155" s="108"/>
+      <c r="I155" s="196"/>
       <c r="J155" s="19"/>
       <c r="K155" s="20"/>
       <c r="L155" s="20"/>
@@ -21910,12 +21910,12 @@
       <c r="A156" s="1"/>
       <c r="B156" s="18"/>
       <c r="C156" s="60"/>
-      <c r="D156" s="105"/>
-      <c r="E156" s="102"/>
-      <c r="F156" s="103"/>
-      <c r="G156" s="103"/>
-      <c r="H156" s="107"/>
-      <c r="I156" s="109"/>
+      <c r="D156" s="149"/>
+      <c r="E156" s="193"/>
+      <c r="F156" s="102"/>
+      <c r="G156" s="102"/>
+      <c r="H156" s="104"/>
+      <c r="I156" s="106"/>
       <c r="J156" s="19"/>
       <c r="K156" s="20"/>
       <c r="L156" s="20"/>
@@ -22032,16 +22032,16 @@
       <c r="A157" s="1"/>
       <c r="B157" s="93"/>
       <c r="C157" s="90"/>
-      <c r="D157" s="103" t="s">
+      <c r="D157" s="102" t="s">
         <v>81</v>
       </c>
-      <c r="E157" s="103"/>
-      <c r="F157" s="103"/>
-      <c r="G157" s="103"/>
-      <c r="H157" s="111">
+      <c r="E157" s="102"/>
+      <c r="F157" s="102"/>
+      <c r="G157" s="102"/>
+      <c r="H157" s="103">
         <v>45644</v>
       </c>
-      <c r="I157" s="126"/>
+      <c r="I157" s="105"/>
       <c r="J157" s="19"/>
       <c r="K157" s="20"/>
       <c r="L157" s="20"/>
@@ -22158,12 +22158,12 @@
       <c r="A158" s="1"/>
       <c r="B158" s="93"/>
       <c r="C158" s="90"/>
-      <c r="D158" s="103"/>
-      <c r="E158" s="103"/>
-      <c r="F158" s="103"/>
-      <c r="G158" s="103"/>
-      <c r="H158" s="107"/>
-      <c r="I158" s="109"/>
+      <c r="D158" s="102"/>
+      <c r="E158" s="102"/>
+      <c r="F158" s="102"/>
+      <c r="G158" s="102"/>
+      <c r="H158" s="104"/>
+      <c r="I158" s="106"/>
       <c r="J158" s="19"/>
       <c r="K158" s="20"/>
       <c r="L158" s="20"/>
@@ -22281,14 +22281,14 @@
       <c r="B159" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="C159" s="151" t="s">
+      <c r="C159" s="173" t="s">
         <v>31</v>
       </c>
-      <c r="D159" s="152"/>
-      <c r="E159" s="152"/>
-      <c r="F159" s="152"/>
-      <c r="G159" s="153"/>
-      <c r="H159" s="138" t="s">
+      <c r="D159" s="174"/>
+      <c r="E159" s="174"/>
+      <c r="F159" s="174"/>
+      <c r="G159" s="175"/>
+      <c r="H159" s="184" t="s">
         <v>57</v>
       </c>
       <c r="I159" s="112"/>
@@ -22407,11 +22407,11 @@
     <row r="160" spans="1:120" ht="9.75" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="87"/>
-      <c r="C160" s="154"/>
-      <c r="D160" s="155"/>
-      <c r="E160" s="155"/>
-      <c r="F160" s="155"/>
-      <c r="G160" s="156"/>
+      <c r="C160" s="176"/>
+      <c r="D160" s="177"/>
+      <c r="E160" s="177"/>
+      <c r="F160" s="177"/>
+      <c r="G160" s="178"/>
       <c r="H160" s="112"/>
       <c r="I160" s="112"/>
       <c r="J160" s="14"/>
@@ -22773,14 +22773,14 @@
     <row r="163" spans="1:120" ht="9.75" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
-      <c r="C163" s="145" t="s">
+      <c r="C163" s="168" t="s">
         <v>33</v>
       </c>
-      <c r="D163" s="146"/>
-      <c r="E163" s="146"/>
-      <c r="F163" s="146"/>
-      <c r="G163" s="147"/>
-      <c r="H163" s="138" t="s">
+      <c r="D163" s="140"/>
+      <c r="E163" s="140"/>
+      <c r="F163" s="140"/>
+      <c r="G163" s="169"/>
+      <c r="H163" s="184" t="s">
         <v>56</v>
       </c>
       <c r="I163" s="112"/>
@@ -22899,11 +22899,11 @@
     <row r="164" spans="1:120" ht="9.75" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
-      <c r="C164" s="148"/>
-      <c r="D164" s="149"/>
-      <c r="E164" s="149"/>
-      <c r="F164" s="149"/>
-      <c r="G164" s="150"/>
+      <c r="C164" s="170"/>
+      <c r="D164" s="171"/>
+      <c r="E164" s="171"/>
+      <c r="F164" s="171"/>
+      <c r="G164" s="172"/>
       <c r="H164" s="112"/>
       <c r="I164" s="112"/>
       <c r="J164" s="19"/>
@@ -36444,6 +36444,222 @@
     </row>
   </sheetData>
   <mergeCells count="240">
+    <mergeCell ref="E155:G156"/>
+    <mergeCell ref="D155:D156"/>
+    <mergeCell ref="H155:H156"/>
+    <mergeCell ref="I155:I156"/>
+    <mergeCell ref="H113:H114"/>
+    <mergeCell ref="I113:I114"/>
+    <mergeCell ref="H129:H130"/>
+    <mergeCell ref="I129:I130"/>
+    <mergeCell ref="E129:G130"/>
+    <mergeCell ref="H123:H124"/>
+    <mergeCell ref="I123:I124"/>
+    <mergeCell ref="I125:I126"/>
+    <mergeCell ref="H125:H126"/>
+    <mergeCell ref="H133:H134"/>
+    <mergeCell ref="I133:I134"/>
+    <mergeCell ref="E123:G124"/>
+    <mergeCell ref="E125:G126"/>
+    <mergeCell ref="E127:G128"/>
+    <mergeCell ref="E113:G114"/>
+    <mergeCell ref="E119:G120"/>
+    <mergeCell ref="E121:G122"/>
+    <mergeCell ref="H127:H128"/>
+    <mergeCell ref="I127:I128"/>
+    <mergeCell ref="H121:H122"/>
+    <mergeCell ref="H105:H106"/>
+    <mergeCell ref="I105:I106"/>
+    <mergeCell ref="H107:H108"/>
+    <mergeCell ref="I107:I108"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="H117:H118"/>
+    <mergeCell ref="I117:I118"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="I119:I120"/>
+    <mergeCell ref="H101:H102"/>
+    <mergeCell ref="I101:I102"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="I85:I86"/>
+    <mergeCell ref="H89:H90"/>
+    <mergeCell ref="I89:I90"/>
+    <mergeCell ref="E81:G82"/>
+    <mergeCell ref="E83:G84"/>
+    <mergeCell ref="E91:G92"/>
+    <mergeCell ref="E93:G94"/>
+    <mergeCell ref="E95:G96"/>
+    <mergeCell ref="E97:G98"/>
+    <mergeCell ref="E99:G100"/>
+    <mergeCell ref="E85:G86"/>
+    <mergeCell ref="D89:G90"/>
+    <mergeCell ref="H75:H76"/>
+    <mergeCell ref="H159:H160"/>
+    <mergeCell ref="H163:H164"/>
+    <mergeCell ref="H161:H162"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="H59:H60"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="H77:H78"/>
+    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="H93:H94"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="H111:H112"/>
+    <mergeCell ref="I163:I164"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="I159:I160"/>
+    <mergeCell ref="I161:I162"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="I93:I94"/>
+    <mergeCell ref="I95:I96"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="I109:I110"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="I153:I154"/>
+    <mergeCell ref="I151:I152"/>
+    <mergeCell ref="I149:I150"/>
+    <mergeCell ref="I147:I148"/>
+    <mergeCell ref="I145:I146"/>
+    <mergeCell ref="I111:I112"/>
+    <mergeCell ref="I135:I136"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I67:I68"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="C163:G164"/>
+    <mergeCell ref="C159:G160"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="C31:G32"/>
+    <mergeCell ref="D33:G34"/>
+    <mergeCell ref="E35:G36"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="E43:G44"/>
+    <mergeCell ref="E45:G46"/>
+    <mergeCell ref="E47:G48"/>
+    <mergeCell ref="E49:G50"/>
+    <mergeCell ref="E51:G52"/>
+    <mergeCell ref="D53:G54"/>
+    <mergeCell ref="E55:G56"/>
+    <mergeCell ref="E57:G58"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="J3:CJ3"/>
+    <mergeCell ref="CK3:DO3"/>
+    <mergeCell ref="J4:AA4"/>
+    <mergeCell ref="AB4:BE4"/>
+    <mergeCell ref="BF4:CJ4"/>
+    <mergeCell ref="CK4:DO4"/>
+    <mergeCell ref="B7:G8"/>
+    <mergeCell ref="C9:G10"/>
+    <mergeCell ref="C11:G12"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="D13:G14"/>
+    <mergeCell ref="D15:G16"/>
+    <mergeCell ref="D17:G18"/>
+    <mergeCell ref="D19:G20"/>
+    <mergeCell ref="C21:G22"/>
+    <mergeCell ref="D23:G24"/>
+    <mergeCell ref="C25:G26"/>
+    <mergeCell ref="D27:G28"/>
+    <mergeCell ref="D29:G30"/>
+    <mergeCell ref="E147:G148"/>
+    <mergeCell ref="E149:G150"/>
+    <mergeCell ref="E151:G152"/>
+    <mergeCell ref="E59:G60"/>
+    <mergeCell ref="E61:G62"/>
+    <mergeCell ref="D63:G64"/>
+    <mergeCell ref="E67:G68"/>
+    <mergeCell ref="E65:G66"/>
+    <mergeCell ref="E69:G70"/>
+    <mergeCell ref="E71:G72"/>
+    <mergeCell ref="C73:G74"/>
+    <mergeCell ref="C75:G76"/>
+    <mergeCell ref="C77:G78"/>
+    <mergeCell ref="D79:G80"/>
+    <mergeCell ref="E109:G110"/>
+    <mergeCell ref="E111:G112"/>
+    <mergeCell ref="E101:G102"/>
+    <mergeCell ref="C105:G106"/>
+    <mergeCell ref="D107:G108"/>
+    <mergeCell ref="D117:G118"/>
+    <mergeCell ref="H145:H146"/>
+    <mergeCell ref="H143:H144"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="C133:G134"/>
+    <mergeCell ref="D135:G136"/>
+    <mergeCell ref="E137:G138"/>
+    <mergeCell ref="E139:G140"/>
+    <mergeCell ref="D143:G144"/>
+    <mergeCell ref="E145:G146"/>
+    <mergeCell ref="H135:H136"/>
     <mergeCell ref="D157:G158"/>
     <mergeCell ref="H157:H158"/>
     <mergeCell ref="I157:I158"/>
@@ -36468,222 +36684,6 @@
     <mergeCell ref="H151:H152"/>
     <mergeCell ref="H149:H150"/>
     <mergeCell ref="H147:H148"/>
-    <mergeCell ref="H145:H146"/>
-    <mergeCell ref="H143:H144"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="C133:G134"/>
-    <mergeCell ref="D135:G136"/>
-    <mergeCell ref="E137:G138"/>
-    <mergeCell ref="E139:G140"/>
-    <mergeCell ref="D143:G144"/>
-    <mergeCell ref="E145:G146"/>
-    <mergeCell ref="H135:H136"/>
-    <mergeCell ref="E147:G148"/>
-    <mergeCell ref="E149:G150"/>
-    <mergeCell ref="E151:G152"/>
-    <mergeCell ref="E59:G60"/>
-    <mergeCell ref="E61:G62"/>
-    <mergeCell ref="D63:G64"/>
-    <mergeCell ref="E67:G68"/>
-    <mergeCell ref="E65:G66"/>
-    <mergeCell ref="E69:G70"/>
-    <mergeCell ref="E71:G72"/>
-    <mergeCell ref="C73:G74"/>
-    <mergeCell ref="C75:G76"/>
-    <mergeCell ref="C77:G78"/>
-    <mergeCell ref="D79:G80"/>
-    <mergeCell ref="E109:G110"/>
-    <mergeCell ref="E111:G112"/>
-    <mergeCell ref="E101:G102"/>
-    <mergeCell ref="C105:G106"/>
-    <mergeCell ref="D107:G108"/>
-    <mergeCell ref="D117:G118"/>
-    <mergeCell ref="D13:G14"/>
-    <mergeCell ref="D15:G16"/>
-    <mergeCell ref="D17:G18"/>
-    <mergeCell ref="D19:G20"/>
-    <mergeCell ref="C21:G22"/>
-    <mergeCell ref="D23:G24"/>
-    <mergeCell ref="C25:G26"/>
-    <mergeCell ref="D27:G28"/>
-    <mergeCell ref="D29:G30"/>
-    <mergeCell ref="J3:CJ3"/>
-    <mergeCell ref="CK3:DO3"/>
-    <mergeCell ref="J4:AA4"/>
-    <mergeCell ref="AB4:BE4"/>
-    <mergeCell ref="BF4:CJ4"/>
-    <mergeCell ref="CK4:DO4"/>
-    <mergeCell ref="B7:G8"/>
-    <mergeCell ref="C9:G10"/>
-    <mergeCell ref="C11:G12"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="C163:G164"/>
-    <mergeCell ref="C159:G160"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="C31:G32"/>
-    <mergeCell ref="D33:G34"/>
-    <mergeCell ref="E35:G36"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="E43:G44"/>
-    <mergeCell ref="E45:G46"/>
-    <mergeCell ref="E47:G48"/>
-    <mergeCell ref="E49:G50"/>
-    <mergeCell ref="E51:G52"/>
-    <mergeCell ref="D53:G54"/>
-    <mergeCell ref="E55:G56"/>
-    <mergeCell ref="E57:G58"/>
-    <mergeCell ref="I53:I54"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="I159:I160"/>
-    <mergeCell ref="I161:I162"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="I93:I94"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="I109:I110"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="I153:I154"/>
-    <mergeCell ref="I151:I152"/>
-    <mergeCell ref="I149:I150"/>
-    <mergeCell ref="I147:I148"/>
-    <mergeCell ref="I145:I146"/>
-    <mergeCell ref="I111:I112"/>
-    <mergeCell ref="I135:I136"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="I163:I164"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="H75:H76"/>
-    <mergeCell ref="H159:H160"/>
-    <mergeCell ref="H163:H164"/>
-    <mergeCell ref="H161:H162"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="H67:H68"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H59:H60"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="H77:H78"/>
-    <mergeCell ref="H81:H82"/>
-    <mergeCell ref="H83:H84"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="H93:H94"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="H111:H112"/>
-    <mergeCell ref="H101:H102"/>
-    <mergeCell ref="I101:I102"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="I85:I86"/>
-    <mergeCell ref="H89:H90"/>
-    <mergeCell ref="I89:I90"/>
-    <mergeCell ref="E81:G82"/>
-    <mergeCell ref="E83:G84"/>
-    <mergeCell ref="E91:G92"/>
-    <mergeCell ref="E93:G94"/>
-    <mergeCell ref="E95:G96"/>
-    <mergeCell ref="E97:G98"/>
-    <mergeCell ref="E99:G100"/>
-    <mergeCell ref="E85:G86"/>
-    <mergeCell ref="D89:G90"/>
-    <mergeCell ref="H105:H106"/>
-    <mergeCell ref="I105:I106"/>
-    <mergeCell ref="H107:H108"/>
-    <mergeCell ref="I107:I108"/>
-    <mergeCell ref="H109:H110"/>
-    <mergeCell ref="H117:H118"/>
-    <mergeCell ref="I117:I118"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="I119:I120"/>
-    <mergeCell ref="E155:G156"/>
-    <mergeCell ref="D155:D156"/>
-    <mergeCell ref="H155:H156"/>
-    <mergeCell ref="I155:I156"/>
-    <mergeCell ref="H113:H114"/>
-    <mergeCell ref="I113:I114"/>
-    <mergeCell ref="H129:H130"/>
-    <mergeCell ref="I129:I130"/>
-    <mergeCell ref="E129:G130"/>
-    <mergeCell ref="H123:H124"/>
-    <mergeCell ref="I123:I124"/>
-    <mergeCell ref="I125:I126"/>
-    <mergeCell ref="H125:H126"/>
-    <mergeCell ref="H133:H134"/>
-    <mergeCell ref="I133:I134"/>
-    <mergeCell ref="E123:G124"/>
-    <mergeCell ref="E125:G126"/>
-    <mergeCell ref="E127:G128"/>
-    <mergeCell ref="E113:G114"/>
-    <mergeCell ref="E119:G120"/>
-    <mergeCell ref="E121:G122"/>
-    <mergeCell ref="H127:H128"/>
-    <mergeCell ref="I127:I128"/>
-    <mergeCell ref="H121:H122"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <conditionalFormatting sqref="J7">

--- a/docs/【DIGITAL OJT】WBS.xlsx
+++ b/docs/【DIGITAL OJT】WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIGITALOJT\digital-ojt-development-cause-DroneInventorySystem\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A765BA39-78FE-45FF-BB55-1B72716B3B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18E6B07-F9D4-41BB-B450-6557E9B8DF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1489,19 +1489,67 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1510,22 +1558,25 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1546,110 +1597,29 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1675,62 +1645,92 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2350,120 +2350,120 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="J3" s="161">
+      <c r="J3" s="173">
         <v>2024</v>
       </c>
-      <c r="K3" s="162"/>
-      <c r="L3" s="162"/>
-      <c r="M3" s="162"/>
-      <c r="N3" s="162"/>
-      <c r="O3" s="162"/>
-      <c r="P3" s="162"/>
-      <c r="Q3" s="162"/>
-      <c r="R3" s="162"/>
-      <c r="S3" s="162"/>
-      <c r="T3" s="162"/>
-      <c r="U3" s="162"/>
-      <c r="V3" s="162"/>
-      <c r="W3" s="162"/>
-      <c r="X3" s="162"/>
-      <c r="Y3" s="162"/>
-      <c r="Z3" s="162"/>
-      <c r="AA3" s="162"/>
-      <c r="AB3" s="162"/>
-      <c r="AC3" s="162"/>
-      <c r="AD3" s="162"/>
-      <c r="AE3" s="162"/>
-      <c r="AF3" s="162"/>
-      <c r="AG3" s="162"/>
-      <c r="AH3" s="162"/>
-      <c r="AI3" s="162"/>
-      <c r="AJ3" s="162"/>
-      <c r="AK3" s="162"/>
-      <c r="AL3" s="162"/>
-      <c r="AM3" s="162"/>
-      <c r="AN3" s="162"/>
-      <c r="AO3" s="162"/>
-      <c r="AP3" s="162"/>
-      <c r="AQ3" s="162"/>
-      <c r="AR3" s="162"/>
-      <c r="AS3" s="162"/>
-      <c r="AT3" s="162"/>
-      <c r="AU3" s="162"/>
-      <c r="AV3" s="162"/>
-      <c r="AW3" s="162"/>
-      <c r="AX3" s="162"/>
-      <c r="AY3" s="162"/>
-      <c r="AZ3" s="162"/>
-      <c r="BA3" s="162"/>
-      <c r="BB3" s="162"/>
-      <c r="BC3" s="162"/>
-      <c r="BD3" s="162"/>
-      <c r="BE3" s="162"/>
-      <c r="BF3" s="162"/>
-      <c r="BG3" s="162"/>
-      <c r="BH3" s="162"/>
-      <c r="BI3" s="162"/>
-      <c r="BJ3" s="162"/>
-      <c r="BK3" s="162"/>
-      <c r="BL3" s="162"/>
-      <c r="BM3" s="162"/>
-      <c r="BN3" s="162"/>
-      <c r="BO3" s="162"/>
-      <c r="BP3" s="162"/>
-      <c r="BQ3" s="162"/>
-      <c r="BR3" s="162"/>
-      <c r="BS3" s="162"/>
-      <c r="BT3" s="162"/>
-      <c r="BU3" s="162"/>
-      <c r="BV3" s="162"/>
-      <c r="BW3" s="162"/>
-      <c r="BX3" s="162"/>
-      <c r="BY3" s="162"/>
-      <c r="BZ3" s="162"/>
-      <c r="CA3" s="162"/>
-      <c r="CB3" s="162"/>
-      <c r="CC3" s="162"/>
-      <c r="CD3" s="162"/>
-      <c r="CE3" s="162"/>
-      <c r="CF3" s="162"/>
-      <c r="CG3" s="162"/>
-      <c r="CH3" s="162"/>
-      <c r="CI3" s="162"/>
-      <c r="CJ3" s="163"/>
-      <c r="CK3" s="161">
+      <c r="K3" s="174"/>
+      <c r="L3" s="174"/>
+      <c r="M3" s="174"/>
+      <c r="N3" s="174"/>
+      <c r="O3" s="174"/>
+      <c r="P3" s="174"/>
+      <c r="Q3" s="174"/>
+      <c r="R3" s="174"/>
+      <c r="S3" s="174"/>
+      <c r="T3" s="174"/>
+      <c r="U3" s="174"/>
+      <c r="V3" s="174"/>
+      <c r="W3" s="174"/>
+      <c r="X3" s="174"/>
+      <c r="Y3" s="174"/>
+      <c r="Z3" s="174"/>
+      <c r="AA3" s="174"/>
+      <c r="AB3" s="174"/>
+      <c r="AC3" s="174"/>
+      <c r="AD3" s="174"/>
+      <c r="AE3" s="174"/>
+      <c r="AF3" s="174"/>
+      <c r="AG3" s="174"/>
+      <c r="AH3" s="174"/>
+      <c r="AI3" s="174"/>
+      <c r="AJ3" s="174"/>
+      <c r="AK3" s="174"/>
+      <c r="AL3" s="174"/>
+      <c r="AM3" s="174"/>
+      <c r="AN3" s="174"/>
+      <c r="AO3" s="174"/>
+      <c r="AP3" s="174"/>
+      <c r="AQ3" s="174"/>
+      <c r="AR3" s="174"/>
+      <c r="AS3" s="174"/>
+      <c r="AT3" s="174"/>
+      <c r="AU3" s="174"/>
+      <c r="AV3" s="174"/>
+      <c r="AW3" s="174"/>
+      <c r="AX3" s="174"/>
+      <c r="AY3" s="174"/>
+      <c r="AZ3" s="174"/>
+      <c r="BA3" s="174"/>
+      <c r="BB3" s="174"/>
+      <c r="BC3" s="174"/>
+      <c r="BD3" s="174"/>
+      <c r="BE3" s="174"/>
+      <c r="BF3" s="174"/>
+      <c r="BG3" s="174"/>
+      <c r="BH3" s="174"/>
+      <c r="BI3" s="174"/>
+      <c r="BJ3" s="174"/>
+      <c r="BK3" s="174"/>
+      <c r="BL3" s="174"/>
+      <c r="BM3" s="174"/>
+      <c r="BN3" s="174"/>
+      <c r="BO3" s="174"/>
+      <c r="BP3" s="174"/>
+      <c r="BQ3" s="174"/>
+      <c r="BR3" s="174"/>
+      <c r="BS3" s="174"/>
+      <c r="BT3" s="174"/>
+      <c r="BU3" s="174"/>
+      <c r="BV3" s="174"/>
+      <c r="BW3" s="174"/>
+      <c r="BX3" s="174"/>
+      <c r="BY3" s="174"/>
+      <c r="BZ3" s="174"/>
+      <c r="CA3" s="174"/>
+      <c r="CB3" s="174"/>
+      <c r="CC3" s="174"/>
+      <c r="CD3" s="174"/>
+      <c r="CE3" s="174"/>
+      <c r="CF3" s="174"/>
+      <c r="CG3" s="174"/>
+      <c r="CH3" s="174"/>
+      <c r="CI3" s="174"/>
+      <c r="CJ3" s="175"/>
+      <c r="CK3" s="173">
         <v>2025</v>
       </c>
-      <c r="CL3" s="162"/>
-      <c r="CM3" s="162"/>
-      <c r="CN3" s="162"/>
-      <c r="CO3" s="162"/>
-      <c r="CP3" s="162"/>
-      <c r="CQ3" s="162"/>
-      <c r="CR3" s="162"/>
-      <c r="CS3" s="162"/>
-      <c r="CT3" s="162"/>
-      <c r="CU3" s="162"/>
-      <c r="CV3" s="162"/>
-      <c r="CW3" s="162"/>
-      <c r="CX3" s="162"/>
-      <c r="CY3" s="162"/>
-      <c r="CZ3" s="162"/>
-      <c r="DA3" s="162"/>
-      <c r="DB3" s="162"/>
-      <c r="DC3" s="162"/>
-      <c r="DD3" s="162"/>
-      <c r="DE3" s="162"/>
-      <c r="DF3" s="162"/>
-      <c r="DG3" s="162"/>
-      <c r="DH3" s="162"/>
-      <c r="DI3" s="162"/>
-      <c r="DJ3" s="162"/>
-      <c r="DK3" s="162"/>
-      <c r="DL3" s="162"/>
-      <c r="DM3" s="162"/>
-      <c r="DN3" s="162"/>
-      <c r="DO3" s="163"/>
+      <c r="CL3" s="174"/>
+      <c r="CM3" s="174"/>
+      <c r="CN3" s="174"/>
+      <c r="CO3" s="174"/>
+      <c r="CP3" s="174"/>
+      <c r="CQ3" s="174"/>
+      <c r="CR3" s="174"/>
+      <c r="CS3" s="174"/>
+      <c r="CT3" s="174"/>
+      <c r="CU3" s="174"/>
+      <c r="CV3" s="174"/>
+      <c r="CW3" s="174"/>
+      <c r="CX3" s="174"/>
+      <c r="CY3" s="174"/>
+      <c r="CZ3" s="174"/>
+      <c r="DA3" s="174"/>
+      <c r="DB3" s="174"/>
+      <c r="DC3" s="174"/>
+      <c r="DD3" s="174"/>
+      <c r="DE3" s="174"/>
+      <c r="DF3" s="174"/>
+      <c r="DG3" s="174"/>
+      <c r="DH3" s="174"/>
+      <c r="DI3" s="174"/>
+      <c r="DJ3" s="174"/>
+      <c r="DK3" s="174"/>
+      <c r="DL3" s="174"/>
+      <c r="DM3" s="174"/>
+      <c r="DN3" s="174"/>
+      <c r="DO3" s="175"/>
       <c r="DP3" s="1"/>
     </row>
     <row r="4" spans="1:120" ht="18" customHeight="1">
@@ -2478,124 +2478,124 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="J4" s="161">
+      <c r="J4" s="173">
         <v>10</v>
       </c>
-      <c r="K4" s="162"/>
-      <c r="L4" s="162"/>
-      <c r="M4" s="162"/>
-      <c r="N4" s="162"/>
-      <c r="O4" s="162"/>
-      <c r="P4" s="162"/>
-      <c r="Q4" s="162"/>
-      <c r="R4" s="162"/>
-      <c r="S4" s="162"/>
-      <c r="T4" s="162"/>
-      <c r="U4" s="162"/>
-      <c r="V4" s="162"/>
-      <c r="W4" s="162"/>
-      <c r="X4" s="162"/>
-      <c r="Y4" s="162"/>
-      <c r="Z4" s="162"/>
-      <c r="AA4" s="163"/>
-      <c r="AB4" s="161">
+      <c r="K4" s="174"/>
+      <c r="L4" s="174"/>
+      <c r="M4" s="174"/>
+      <c r="N4" s="174"/>
+      <c r="O4" s="174"/>
+      <c r="P4" s="174"/>
+      <c r="Q4" s="174"/>
+      <c r="R4" s="174"/>
+      <c r="S4" s="174"/>
+      <c r="T4" s="174"/>
+      <c r="U4" s="174"/>
+      <c r="V4" s="174"/>
+      <c r="W4" s="174"/>
+      <c r="X4" s="174"/>
+      <c r="Y4" s="174"/>
+      <c r="Z4" s="174"/>
+      <c r="AA4" s="175"/>
+      <c r="AB4" s="173">
         <v>11</v>
       </c>
-      <c r="AC4" s="162"/>
-      <c r="AD4" s="162"/>
-      <c r="AE4" s="162"/>
-      <c r="AF4" s="162"/>
-      <c r="AG4" s="162"/>
-      <c r="AH4" s="162"/>
-      <c r="AI4" s="162"/>
-      <c r="AJ4" s="162"/>
-      <c r="AK4" s="162"/>
-      <c r="AL4" s="162"/>
-      <c r="AM4" s="162"/>
-      <c r="AN4" s="162"/>
-      <c r="AO4" s="162"/>
-      <c r="AP4" s="162"/>
-      <c r="AQ4" s="162"/>
-      <c r="AR4" s="162"/>
-      <c r="AS4" s="162"/>
-      <c r="AT4" s="162"/>
-      <c r="AU4" s="162"/>
-      <c r="AV4" s="162"/>
-      <c r="AW4" s="162"/>
-      <c r="AX4" s="162"/>
-      <c r="AY4" s="162"/>
-      <c r="AZ4" s="162"/>
-      <c r="BA4" s="162"/>
-      <c r="BB4" s="162"/>
-      <c r="BC4" s="162"/>
-      <c r="BD4" s="162"/>
-      <c r="BE4" s="163"/>
-      <c r="BF4" s="161">
+      <c r="AC4" s="174"/>
+      <c r="AD4" s="174"/>
+      <c r="AE4" s="174"/>
+      <c r="AF4" s="174"/>
+      <c r="AG4" s="174"/>
+      <c r="AH4" s="174"/>
+      <c r="AI4" s="174"/>
+      <c r="AJ4" s="174"/>
+      <c r="AK4" s="174"/>
+      <c r="AL4" s="174"/>
+      <c r="AM4" s="174"/>
+      <c r="AN4" s="174"/>
+      <c r="AO4" s="174"/>
+      <c r="AP4" s="174"/>
+      <c r="AQ4" s="174"/>
+      <c r="AR4" s="174"/>
+      <c r="AS4" s="174"/>
+      <c r="AT4" s="174"/>
+      <c r="AU4" s="174"/>
+      <c r="AV4" s="174"/>
+      <c r="AW4" s="174"/>
+      <c r="AX4" s="174"/>
+      <c r="AY4" s="174"/>
+      <c r="AZ4" s="174"/>
+      <c r="BA4" s="174"/>
+      <c r="BB4" s="174"/>
+      <c r="BC4" s="174"/>
+      <c r="BD4" s="174"/>
+      <c r="BE4" s="175"/>
+      <c r="BF4" s="173">
         <v>12</v>
       </c>
-      <c r="BG4" s="162"/>
-      <c r="BH4" s="162"/>
-      <c r="BI4" s="162"/>
-      <c r="BJ4" s="162"/>
-      <c r="BK4" s="162"/>
-      <c r="BL4" s="162"/>
-      <c r="BM4" s="162"/>
-      <c r="BN4" s="162"/>
-      <c r="BO4" s="162"/>
-      <c r="BP4" s="162"/>
-      <c r="BQ4" s="162"/>
-      <c r="BR4" s="162"/>
-      <c r="BS4" s="162"/>
-      <c r="BT4" s="162"/>
-      <c r="BU4" s="162"/>
-      <c r="BV4" s="162"/>
-      <c r="BW4" s="162"/>
-      <c r="BX4" s="162"/>
-      <c r="BY4" s="162"/>
-      <c r="BZ4" s="162"/>
-      <c r="CA4" s="162"/>
-      <c r="CB4" s="162"/>
-      <c r="CC4" s="162"/>
-      <c r="CD4" s="162"/>
-      <c r="CE4" s="162"/>
-      <c r="CF4" s="162"/>
-      <c r="CG4" s="162"/>
-      <c r="CH4" s="162"/>
-      <c r="CI4" s="162"/>
-      <c r="CJ4" s="163"/>
-      <c r="CK4" s="161">
+      <c r="BG4" s="174"/>
+      <c r="BH4" s="174"/>
+      <c r="BI4" s="174"/>
+      <c r="BJ4" s="174"/>
+      <c r="BK4" s="174"/>
+      <c r="BL4" s="174"/>
+      <c r="BM4" s="174"/>
+      <c r="BN4" s="174"/>
+      <c r="BO4" s="174"/>
+      <c r="BP4" s="174"/>
+      <c r="BQ4" s="174"/>
+      <c r="BR4" s="174"/>
+      <c r="BS4" s="174"/>
+      <c r="BT4" s="174"/>
+      <c r="BU4" s="174"/>
+      <c r="BV4" s="174"/>
+      <c r="BW4" s="174"/>
+      <c r="BX4" s="174"/>
+      <c r="BY4" s="174"/>
+      <c r="BZ4" s="174"/>
+      <c r="CA4" s="174"/>
+      <c r="CB4" s="174"/>
+      <c r="CC4" s="174"/>
+      <c r="CD4" s="174"/>
+      <c r="CE4" s="174"/>
+      <c r="CF4" s="174"/>
+      <c r="CG4" s="174"/>
+      <c r="CH4" s="174"/>
+      <c r="CI4" s="174"/>
+      <c r="CJ4" s="175"/>
+      <c r="CK4" s="173">
         <v>1</v>
       </c>
-      <c r="CL4" s="162"/>
-      <c r="CM4" s="162"/>
-      <c r="CN4" s="162"/>
-      <c r="CO4" s="162"/>
-      <c r="CP4" s="162"/>
-      <c r="CQ4" s="162"/>
-      <c r="CR4" s="162"/>
-      <c r="CS4" s="162"/>
-      <c r="CT4" s="162"/>
-      <c r="CU4" s="162"/>
-      <c r="CV4" s="162"/>
-      <c r="CW4" s="162"/>
-      <c r="CX4" s="162"/>
-      <c r="CY4" s="162"/>
-      <c r="CZ4" s="162"/>
-      <c r="DA4" s="162"/>
-      <c r="DB4" s="162"/>
-      <c r="DC4" s="162"/>
-      <c r="DD4" s="162"/>
-      <c r="DE4" s="162"/>
-      <c r="DF4" s="162"/>
-      <c r="DG4" s="162"/>
-      <c r="DH4" s="162"/>
-      <c r="DI4" s="162"/>
-      <c r="DJ4" s="162"/>
-      <c r="DK4" s="162"/>
-      <c r="DL4" s="162"/>
-      <c r="DM4" s="162"/>
-      <c r="DN4" s="162"/>
-      <c r="DO4" s="163"/>
+      <c r="CL4" s="174"/>
+      <c r="CM4" s="174"/>
+      <c r="CN4" s="174"/>
+      <c r="CO4" s="174"/>
+      <c r="CP4" s="174"/>
+      <c r="CQ4" s="174"/>
+      <c r="CR4" s="174"/>
+      <c r="CS4" s="174"/>
+      <c r="CT4" s="174"/>
+      <c r="CU4" s="174"/>
+      <c r="CV4" s="174"/>
+      <c r="CW4" s="174"/>
+      <c r="CX4" s="174"/>
+      <c r="CY4" s="174"/>
+      <c r="CZ4" s="174"/>
+      <c r="DA4" s="174"/>
+      <c r="DB4" s="174"/>
+      <c r="DC4" s="174"/>
+      <c r="DD4" s="174"/>
+      <c r="DE4" s="174"/>
+      <c r="DF4" s="174"/>
+      <c r="DG4" s="174"/>
+      <c r="DH4" s="174"/>
+      <c r="DI4" s="174"/>
+      <c r="DJ4" s="174"/>
+      <c r="DK4" s="174"/>
+      <c r="DL4" s="174"/>
+      <c r="DM4" s="174"/>
+      <c r="DN4" s="174"/>
+      <c r="DO4" s="175"/>
       <c r="DP4" s="6"/>
     </row>
     <row r="5" spans="1:120" ht="18" customHeight="1">
@@ -3390,18 +3390,18 @@
     </row>
     <row r="7" spans="1:120" ht="9.75" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="164" t="s">
+      <c r="B7" s="176" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="166" t="s">
+      <c r="C7" s="164"/>
+      <c r="D7" s="164"/>
+      <c r="E7" s="164"/>
+      <c r="F7" s="164"/>
+      <c r="G7" s="177"/>
+      <c r="H7" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="166" t="s">
+      <c r="I7" s="142" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="38"/>
@@ -3518,14 +3518,14 @@
     </row>
     <row r="8" spans="1:120" ht="9.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="134"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="135"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="135"/>
-      <c r="G8" s="139"/>
-      <c r="H8" s="166"/>
-      <c r="I8" s="166"/>
+      <c r="B8" s="166"/>
+      <c r="C8" s="167"/>
+      <c r="D8" s="167"/>
+      <c r="E8" s="167"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="168"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="142"/>
       <c r="J8" s="39"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
@@ -3641,15 +3641,15 @@
     <row r="9" spans="1:120" ht="9.75" customHeight="1">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
-      <c r="C9" s="165" t="s">
+      <c r="C9" s="178" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="154"/>
-      <c r="E9" s="154"/>
-      <c r="F9" s="154"/>
-      <c r="G9" s="142"/>
-      <c r="H9" s="167"/>
-      <c r="I9" s="167"/>
+      <c r="D9" s="158"/>
+      <c r="E9" s="158"/>
+      <c r="F9" s="158"/>
+      <c r="G9" s="162"/>
+      <c r="H9" s="139"/>
+      <c r="I9" s="139"/>
       <c r="J9" s="42"/>
       <c r="K9" s="42"/>
       <c r="L9" s="44"/>
@@ -3765,13 +3765,13 @@
     <row r="10" spans="1:120" ht="9.75" customHeight="1">
       <c r="A10" s="16"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="141"/>
-      <c r="D10" s="135"/>
-      <c r="E10" s="135"/>
-      <c r="F10" s="135"/>
-      <c r="G10" s="139"/>
-      <c r="H10" s="167"/>
-      <c r="I10" s="167"/>
+      <c r="C10" s="179"/>
+      <c r="D10" s="167"/>
+      <c r="E10" s="167"/>
+      <c r="F10" s="167"/>
+      <c r="G10" s="168"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
       <c r="J10" s="46"/>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
@@ -3887,15 +3887,15 @@
     <row r="11" spans="1:120" ht="9.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="153" t="s">
+      <c r="C11" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="154"/>
-      <c r="E11" s="154"/>
-      <c r="F11" s="154"/>
-      <c r="G11" s="142"/>
-      <c r="H11" s="167"/>
-      <c r="I11" s="167"/>
+      <c r="D11" s="158"/>
+      <c r="E11" s="158"/>
+      <c r="F11" s="158"/>
+      <c r="G11" s="162"/>
+      <c r="H11" s="139"/>
+      <c r="I11" s="139"/>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
       <c r="L11" s="44"/>
@@ -4011,13 +4011,13 @@
     <row r="12" spans="1:120" ht="9.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="141"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="135"/>
-      <c r="F12" s="135"/>
-      <c r="G12" s="139"/>
-      <c r="H12" s="167"/>
-      <c r="I12" s="167"/>
+      <c r="C12" s="179"/>
+      <c r="D12" s="167"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="167"/>
+      <c r="G12" s="168"/>
+      <c r="H12" s="139"/>
+      <c r="I12" s="139"/>
       <c r="J12" s="46"/>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
@@ -4134,13 +4134,13 @@
       <c r="A13" s="1"/>
       <c r="B13" s="18"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="151" t="s">
+      <c r="D13" s="181" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="152"/>
-      <c r="H13" s="184" t="s">
+      <c r="E13" s="164"/>
+      <c r="F13" s="164"/>
+      <c r="G13" s="177"/>
+      <c r="H13" s="138" t="s">
         <v>40</v>
       </c>
       <c r="I13" s="112">
@@ -4262,10 +4262,10 @@
       <c r="A14" s="1"/>
       <c r="B14" s="18"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="134"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="135"/>
-      <c r="G14" s="139"/>
+      <c r="D14" s="166"/>
+      <c r="E14" s="167"/>
+      <c r="F14" s="167"/>
+      <c r="G14" s="168"/>
       <c r="H14" s="112"/>
       <c r="I14" s="112"/>
       <c r="J14" s="39"/>
@@ -4384,13 +4384,13 @@
       <c r="A15" s="1"/>
       <c r="B15" s="18"/>
       <c r="C15" s="24"/>
-      <c r="D15" s="151" t="s">
+      <c r="D15" s="181" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="133"/>
-      <c r="H15" s="184" t="s">
+      <c r="E15" s="164"/>
+      <c r="F15" s="164"/>
+      <c r="G15" s="170"/>
+      <c r="H15" s="138" t="s">
         <v>40</v>
       </c>
       <c r="I15" s="112">
@@ -4512,10 +4512,10 @@
       <c r="A16" s="1"/>
       <c r="B16" s="18"/>
       <c r="C16" s="24"/>
-      <c r="D16" s="134"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="136"/>
+      <c r="D16" s="166"/>
+      <c r="E16" s="167"/>
+      <c r="F16" s="167"/>
+      <c r="G16" s="171"/>
       <c r="H16" s="112"/>
       <c r="I16" s="112"/>
       <c r="J16" s="14"/>
@@ -4634,13 +4634,13 @@
       <c r="A17" s="1"/>
       <c r="B17" s="18"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="151" t="s">
+      <c r="D17" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="132"/>
-      <c r="F17" s="132"/>
-      <c r="G17" s="133"/>
-      <c r="H17" s="184" t="s">
+      <c r="E17" s="164"/>
+      <c r="F17" s="164"/>
+      <c r="G17" s="170"/>
+      <c r="H17" s="138" t="s">
         <v>40</v>
       </c>
       <c r="I17" s="112">
@@ -4762,10 +4762,10 @@
       <c r="A18" s="1"/>
       <c r="B18" s="18"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="134"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="135"/>
-      <c r="G18" s="136"/>
+      <c r="D18" s="166"/>
+      <c r="E18" s="167"/>
+      <c r="F18" s="167"/>
+      <c r="G18" s="171"/>
       <c r="H18" s="112"/>
       <c r="I18" s="112"/>
       <c r="J18" s="14"/>
@@ -4884,13 +4884,13 @@
       <c r="A19" s="1"/>
       <c r="B19" s="18"/>
       <c r="C19" s="24"/>
-      <c r="D19" s="151" t="s">
+      <c r="D19" s="181" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="132"/>
-      <c r="F19" s="132"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="184" t="s">
+      <c r="E19" s="164"/>
+      <c r="F19" s="164"/>
+      <c r="G19" s="170"/>
+      <c r="H19" s="138" t="s">
         <v>40</v>
       </c>
       <c r="I19" s="112">
@@ -5012,10 +5012,10 @@
       <c r="A20" s="1"/>
       <c r="B20" s="18"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="134"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="135"/>
-      <c r="G20" s="136"/>
+      <c r="D20" s="166"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="167"/>
+      <c r="G20" s="171"/>
       <c r="H20" s="112"/>
       <c r="I20" s="112"/>
       <c r="J20" s="26"/>
@@ -5133,15 +5133,15 @@
     <row r="21" spans="1:120" ht="9.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="18"/>
-      <c r="C21" s="153" t="s">
+      <c r="C21" s="180" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="154"/>
-      <c r="E21" s="154"/>
-      <c r="F21" s="154"/>
-      <c r="G21" s="155"/>
-      <c r="H21" s="167"/>
-      <c r="I21" s="167"/>
+      <c r="D21" s="158"/>
+      <c r="E21" s="158"/>
+      <c r="F21" s="158"/>
+      <c r="G21" s="159"/>
+      <c r="H21" s="139"/>
+      <c r="I21" s="139"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="44"/>
@@ -5257,13 +5257,13 @@
     <row r="22" spans="1:120" ht="9.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="18"/>
-      <c r="C22" s="156"/>
-      <c r="D22" s="157"/>
-      <c r="E22" s="157"/>
-      <c r="F22" s="157"/>
-      <c r="G22" s="142"/>
-      <c r="H22" s="167"/>
-      <c r="I22" s="167"/>
+      <c r="C22" s="160"/>
+      <c r="D22" s="161"/>
+      <c r="E22" s="161"/>
+      <c r="F22" s="161"/>
+      <c r="G22" s="162"/>
+      <c r="H22" s="139"/>
+      <c r="I22" s="139"/>
       <c r="J22" s="46"/>
       <c r="K22" s="47"/>
       <c r="L22" s="47"/>
@@ -5380,13 +5380,13 @@
       <c r="A23" s="1"/>
       <c r="B23" s="28"/>
       <c r="C23" s="29"/>
-      <c r="D23" s="158" t="s">
+      <c r="D23" s="182" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="132"/>
-      <c r="F23" s="132"/>
-      <c r="G23" s="133"/>
-      <c r="H23" s="184" t="s">
+      <c r="E23" s="164"/>
+      <c r="F23" s="164"/>
+      <c r="G23" s="170"/>
+      <c r="H23" s="138" t="s">
         <v>46</v>
       </c>
       <c r="I23" s="112">
@@ -5508,10 +5508,10 @@
       <c r="A24" s="1"/>
       <c r="B24" s="18"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="134"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="135"/>
-      <c r="G24" s="136"/>
+      <c r="D24" s="166"/>
+      <c r="E24" s="167"/>
+      <c r="F24" s="167"/>
+      <c r="G24" s="171"/>
       <c r="H24" s="112"/>
       <c r="I24" s="112"/>
       <c r="J24" s="14"/>
@@ -5629,15 +5629,15 @@
     <row r="25" spans="1:120" ht="9.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="18"/>
-      <c r="C25" s="153" t="s">
+      <c r="C25" s="180" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="154"/>
-      <c r="E25" s="154"/>
-      <c r="F25" s="154"/>
-      <c r="G25" s="155"/>
-      <c r="H25" s="167"/>
-      <c r="I25" s="167"/>
+      <c r="D25" s="158"/>
+      <c r="E25" s="158"/>
+      <c r="F25" s="158"/>
+      <c r="G25" s="159"/>
+      <c r="H25" s="139"/>
+      <c r="I25" s="139"/>
       <c r="J25" s="42"/>
       <c r="K25" s="42"/>
       <c r="L25" s="44"/>
@@ -5753,13 +5753,13 @@
     <row r="26" spans="1:120" ht="9.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="18"/>
-      <c r="C26" s="141"/>
-      <c r="D26" s="135"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="135"/>
-      <c r="G26" s="139"/>
-      <c r="H26" s="167"/>
-      <c r="I26" s="167"/>
+      <c r="C26" s="179"/>
+      <c r="D26" s="167"/>
+      <c r="E26" s="167"/>
+      <c r="F26" s="167"/>
+      <c r="G26" s="168"/>
+      <c r="H26" s="139"/>
+      <c r="I26" s="139"/>
       <c r="J26" s="46"/>
       <c r="K26" s="47"/>
       <c r="L26" s="47"/>
@@ -5876,13 +5876,13 @@
       <c r="A27" s="1"/>
       <c r="B27" s="28"/>
       <c r="C27" s="29"/>
-      <c r="D27" s="158" t="s">
+      <c r="D27" s="182" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="132"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="133"/>
-      <c r="H27" s="184" t="s">
+      <c r="E27" s="164"/>
+      <c r="F27" s="164"/>
+      <c r="G27" s="170"/>
+      <c r="H27" s="138" t="s">
         <v>44</v>
       </c>
       <c r="I27" s="112">
@@ -6004,10 +6004,10 @@
       <c r="A28" s="1"/>
       <c r="B28" s="28"/>
       <c r="C28" s="30"/>
-      <c r="D28" s="134"/>
-      <c r="E28" s="135"/>
-      <c r="F28" s="135"/>
-      <c r="G28" s="136"/>
+      <c r="D28" s="166"/>
+      <c r="E28" s="167"/>
+      <c r="F28" s="167"/>
+      <c r="G28" s="171"/>
       <c r="H28" s="112"/>
       <c r="I28" s="112"/>
       <c r="J28" s="14"/>
@@ -6126,13 +6126,13 @@
       <c r="A29" s="1"/>
       <c r="B29" s="28"/>
       <c r="C29" s="30"/>
-      <c r="D29" s="159" t="s">
+      <c r="D29" s="183" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="160"/>
-      <c r="F29" s="160"/>
-      <c r="G29" s="160"/>
-      <c r="H29" s="184" t="s">
+      <c r="E29" s="184"/>
+      <c r="F29" s="184"/>
+      <c r="G29" s="184"/>
+      <c r="H29" s="138" t="s">
         <v>44</v>
       </c>
       <c r="I29" s="112">
@@ -6254,10 +6254,10 @@
       <c r="A30" s="1"/>
       <c r="B30" s="28"/>
       <c r="C30" s="31"/>
-      <c r="D30" s="134"/>
-      <c r="E30" s="135"/>
-      <c r="F30" s="135"/>
-      <c r="G30" s="135"/>
+      <c r="D30" s="166"/>
+      <c r="E30" s="167"/>
+      <c r="F30" s="167"/>
+      <c r="G30" s="167"/>
       <c r="H30" s="112"/>
       <c r="I30" s="112"/>
       <c r="J30" s="26"/>
@@ -6375,15 +6375,15 @@
     <row r="31" spans="1:120" ht="9.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="18"/>
-      <c r="C31" s="179" t="s">
+      <c r="C31" s="157" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="154"/>
-      <c r="E31" s="154"/>
-      <c r="F31" s="154"/>
-      <c r="G31" s="155"/>
-      <c r="H31" s="167"/>
-      <c r="I31" s="167"/>
+      <c r="D31" s="158"/>
+      <c r="E31" s="158"/>
+      <c r="F31" s="158"/>
+      <c r="G31" s="159"/>
+      <c r="H31" s="139"/>
+      <c r="I31" s="139"/>
       <c r="J31" s="42"/>
       <c r="K31" s="43"/>
       <c r="L31" s="44"/>
@@ -6499,13 +6499,13 @@
     <row r="32" spans="1:120" ht="9.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="18"/>
-      <c r="C32" s="156"/>
-      <c r="D32" s="157"/>
-      <c r="E32" s="157"/>
-      <c r="F32" s="157"/>
-      <c r="G32" s="142"/>
-      <c r="H32" s="167"/>
-      <c r="I32" s="167"/>
+      <c r="C32" s="160"/>
+      <c r="D32" s="161"/>
+      <c r="E32" s="161"/>
+      <c r="F32" s="161"/>
+      <c r="G32" s="162"/>
+      <c r="H32" s="139"/>
+      <c r="I32" s="139"/>
       <c r="J32" s="46"/>
       <c r="K32" s="47"/>
       <c r="L32" s="47"/>
@@ -6622,14 +6622,14 @@
       <c r="A33" s="1"/>
       <c r="B33" s="18"/>
       <c r="C33" s="32"/>
-      <c r="D33" s="137" t="s">
+      <c r="D33" s="163" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="132"/>
-      <c r="F33" s="132"/>
-      <c r="G33" s="138"/>
-      <c r="H33" s="167"/>
-      <c r="I33" s="167"/>
+      <c r="E33" s="164"/>
+      <c r="F33" s="164"/>
+      <c r="G33" s="165"/>
+      <c r="H33" s="139"/>
+      <c r="I33" s="139"/>
       <c r="J33" s="50"/>
       <c r="K33" s="51"/>
       <c r="L33" s="51"/>
@@ -6746,12 +6746,12 @@
       <c r="A34" s="1"/>
       <c r="B34" s="18"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="134"/>
-      <c r="E34" s="135"/>
-      <c r="F34" s="135"/>
-      <c r="G34" s="139"/>
-      <c r="H34" s="167"/>
-      <c r="I34" s="167"/>
+      <c r="D34" s="166"/>
+      <c r="E34" s="167"/>
+      <c r="F34" s="167"/>
+      <c r="G34" s="168"/>
+      <c r="H34" s="139"/>
+      <c r="I34" s="139"/>
       <c r="J34" s="52"/>
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
@@ -6869,12 +6869,12 @@
       <c r="B35" s="18"/>
       <c r="C35" s="1"/>
       <c r="D35" s="33"/>
-      <c r="E35" s="131" t="s">
+      <c r="E35" s="169" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="132"/>
-      <c r="G35" s="133"/>
-      <c r="H35" s="184" t="s">
+      <c r="F35" s="164"/>
+      <c r="G35" s="170"/>
+      <c r="H35" s="138" t="s">
         <v>45</v>
       </c>
       <c r="I35" s="112">
@@ -6997,9 +6997,9 @@
       <c r="B36" s="18"/>
       <c r="C36" s="1"/>
       <c r="D36" s="34"/>
-      <c r="E36" s="134"/>
-      <c r="F36" s="135"/>
-      <c r="G36" s="136"/>
+      <c r="E36" s="166"/>
+      <c r="F36" s="167"/>
+      <c r="G36" s="171"/>
       <c r="H36" s="112"/>
       <c r="I36" s="112"/>
       <c r="J36" s="14"/>
@@ -7119,12 +7119,12 @@
       <c r="B37" s="18"/>
       <c r="C37" s="1"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="131" t="s">
+      <c r="E37" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F37" s="132"/>
-      <c r="G37" s="133"/>
-      <c r="H37" s="184" t="s">
+      <c r="F37" s="164"/>
+      <c r="G37" s="170"/>
+      <c r="H37" s="138" t="s">
         <v>44</v>
       </c>
       <c r="I37" s="112">
@@ -7247,9 +7247,9 @@
       <c r="B38" s="18"/>
       <c r="C38" s="1"/>
       <c r="D38" s="35"/>
-      <c r="E38" s="134"/>
-      <c r="F38" s="135"/>
-      <c r="G38" s="136"/>
+      <c r="E38" s="166"/>
+      <c r="F38" s="167"/>
+      <c r="G38" s="171"/>
       <c r="H38" s="112"/>
       <c r="I38" s="112"/>
       <c r="J38" s="26"/>
@@ -7368,14 +7368,14 @@
       <c r="A39" s="1"/>
       <c r="B39" s="18"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="180" t="s">
+      <c r="D39" s="172" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="154"/>
-      <c r="F39" s="154"/>
-      <c r="G39" s="155"/>
-      <c r="H39" s="167"/>
-      <c r="I39" s="167"/>
+      <c r="E39" s="158"/>
+      <c r="F39" s="158"/>
+      <c r="G39" s="159"/>
+      <c r="H39" s="139"/>
+      <c r="I39" s="139"/>
       <c r="J39" s="50"/>
       <c r="K39" s="51"/>
       <c r="L39" s="51"/>
@@ -7492,12 +7492,12 @@
       <c r="A40" s="1"/>
       <c r="B40" s="18"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="134"/>
-      <c r="E40" s="135"/>
-      <c r="F40" s="135"/>
-      <c r="G40" s="139"/>
-      <c r="H40" s="167"/>
-      <c r="I40" s="167"/>
+      <c r="D40" s="166"/>
+      <c r="E40" s="167"/>
+      <c r="F40" s="167"/>
+      <c r="G40" s="168"/>
+      <c r="H40" s="139"/>
+      <c r="I40" s="139"/>
       <c r="J40" s="52"/>
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
@@ -7615,12 +7615,12 @@
       <c r="B41" s="18"/>
       <c r="C41" s="1"/>
       <c r="D41" s="33"/>
-      <c r="E41" s="131" t="s">
+      <c r="E41" s="169" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="132"/>
-      <c r="G41" s="133"/>
-      <c r="H41" s="184" t="s">
+      <c r="F41" s="164"/>
+      <c r="G41" s="170"/>
+      <c r="H41" s="138" t="s">
         <v>43</v>
       </c>
       <c r="I41" s="112">
@@ -7743,9 +7743,9 @@
       <c r="B42" s="18"/>
       <c r="C42" s="1"/>
       <c r="D42" s="34"/>
-      <c r="E42" s="134"/>
-      <c r="F42" s="135"/>
-      <c r="G42" s="136"/>
+      <c r="E42" s="166"/>
+      <c r="F42" s="167"/>
+      <c r="G42" s="171"/>
       <c r="H42" s="112"/>
       <c r="I42" s="112"/>
       <c r="J42" s="14"/>
@@ -7865,12 +7865,12 @@
       <c r="B43" s="18"/>
       <c r="C43" s="1"/>
       <c r="D43" s="34"/>
-      <c r="E43" s="131" t="s">
+      <c r="E43" s="169" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="132"/>
-      <c r="G43" s="133"/>
-      <c r="H43" s="184" t="s">
+      <c r="F43" s="164"/>
+      <c r="G43" s="170"/>
+      <c r="H43" s="138" t="s">
         <v>43</v>
       </c>
       <c r="I43" s="112">
@@ -7993,9 +7993,9 @@
       <c r="B44" s="18"/>
       <c r="C44" s="1"/>
       <c r="D44" s="34"/>
-      <c r="E44" s="134"/>
-      <c r="F44" s="135"/>
-      <c r="G44" s="136"/>
+      <c r="E44" s="166"/>
+      <c r="F44" s="167"/>
+      <c r="G44" s="171"/>
       <c r="H44" s="112"/>
       <c r="I44" s="112"/>
       <c r="J44" s="14"/>
@@ -8115,12 +8115,12 @@
       <c r="B45" s="18"/>
       <c r="C45" s="1"/>
       <c r="D45" s="34"/>
-      <c r="E45" s="131" t="s">
+      <c r="E45" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="132"/>
-      <c r="G45" s="133"/>
-      <c r="H45" s="184" t="s">
+      <c r="F45" s="164"/>
+      <c r="G45" s="170"/>
+      <c r="H45" s="138" t="s">
         <v>42</v>
       </c>
       <c r="I45" s="112">
@@ -8243,9 +8243,9 @@
       <c r="B46" s="18"/>
       <c r="C46" s="1"/>
       <c r="D46" s="34"/>
-      <c r="E46" s="134"/>
-      <c r="F46" s="135"/>
-      <c r="G46" s="136"/>
+      <c r="E46" s="166"/>
+      <c r="F46" s="167"/>
+      <c r="G46" s="171"/>
       <c r="H46" s="112"/>
       <c r="I46" s="112"/>
       <c r="J46" s="14"/>
@@ -8365,12 +8365,12 @@
       <c r="B47" s="18"/>
       <c r="C47" s="1"/>
       <c r="D47" s="34"/>
-      <c r="E47" s="131" t="s">
+      <c r="E47" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="F47" s="132"/>
-      <c r="G47" s="133"/>
-      <c r="H47" s="184" t="s">
+      <c r="F47" s="164"/>
+      <c r="G47" s="170"/>
+      <c r="H47" s="138" t="s">
         <v>41</v>
       </c>
       <c r="I47" s="112">
@@ -8493,9 +8493,9 @@
       <c r="B48" s="18"/>
       <c r="C48" s="1"/>
       <c r="D48" s="34"/>
-      <c r="E48" s="134"/>
-      <c r="F48" s="135"/>
-      <c r="G48" s="136"/>
+      <c r="E48" s="166"/>
+      <c r="F48" s="167"/>
+      <c r="G48" s="171"/>
       <c r="H48" s="112"/>
       <c r="I48" s="112"/>
       <c r="J48" s="14"/>
@@ -8615,12 +8615,12 @@
       <c r="B49" s="18"/>
       <c r="C49" s="1"/>
       <c r="D49" s="34"/>
-      <c r="E49" s="131" t="s">
+      <c r="E49" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="132"/>
-      <c r="G49" s="133"/>
-      <c r="H49" s="184" t="s">
+      <c r="F49" s="164"/>
+      <c r="G49" s="170"/>
+      <c r="H49" s="138" t="s">
         <v>50</v>
       </c>
       <c r="I49" s="112">
@@ -8743,9 +8743,9 @@
       <c r="B50" s="18"/>
       <c r="C50" s="1"/>
       <c r="D50" s="34"/>
-      <c r="E50" s="134"/>
-      <c r="F50" s="135"/>
-      <c r="G50" s="136"/>
+      <c r="E50" s="166"/>
+      <c r="F50" s="167"/>
+      <c r="G50" s="171"/>
       <c r="H50" s="112"/>
       <c r="I50" s="112"/>
       <c r="J50" s="14"/>
@@ -8865,12 +8865,12 @@
       <c r="B51" s="18"/>
       <c r="C51" s="1"/>
       <c r="D51" s="34"/>
-      <c r="E51" s="131" t="s">
+      <c r="E51" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="132"/>
-      <c r="G51" s="133"/>
-      <c r="H51" s="184" t="s">
+      <c r="F51" s="164"/>
+      <c r="G51" s="170"/>
+      <c r="H51" s="138" t="s">
         <v>47</v>
       </c>
       <c r="I51" s="112">
@@ -8993,9 +8993,9 @@
       <c r="B52" s="18"/>
       <c r="C52" s="1"/>
       <c r="D52" s="34"/>
-      <c r="E52" s="134"/>
-      <c r="F52" s="135"/>
-      <c r="G52" s="136"/>
+      <c r="E52" s="166"/>
+      <c r="F52" s="167"/>
+      <c r="G52" s="171"/>
       <c r="H52" s="112"/>
       <c r="I52" s="112"/>
       <c r="J52" s="26"/>
@@ -9114,14 +9114,14 @@
       <c r="A53" s="1"/>
       <c r="B53" s="18"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="137" t="s">
+      <c r="D53" s="163" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="132"/>
-      <c r="F53" s="132"/>
-      <c r="G53" s="138"/>
-      <c r="H53" s="167"/>
-      <c r="I53" s="167"/>
+      <c r="E53" s="164"/>
+      <c r="F53" s="164"/>
+      <c r="G53" s="165"/>
+      <c r="H53" s="139"/>
+      <c r="I53" s="139"/>
       <c r="J53" s="50"/>
       <c r="K53" s="51"/>
       <c r="L53" s="51"/>
@@ -9238,12 +9238,12 @@
       <c r="A54" s="1"/>
       <c r="B54" s="18"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="134"/>
-      <c r="E54" s="135"/>
-      <c r="F54" s="135"/>
-      <c r="G54" s="139"/>
-      <c r="H54" s="167"/>
-      <c r="I54" s="167"/>
+      <c r="D54" s="166"/>
+      <c r="E54" s="167"/>
+      <c r="F54" s="167"/>
+      <c r="G54" s="168"/>
+      <c r="H54" s="139"/>
+      <c r="I54" s="139"/>
       <c r="J54" s="52"/>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -9361,12 +9361,12 @@
       <c r="B55" s="18"/>
       <c r="C55" s="1"/>
       <c r="D55" s="34"/>
-      <c r="E55" s="131" t="s">
+      <c r="E55" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="132"/>
-      <c r="G55" s="133"/>
-      <c r="H55" s="184" t="s">
+      <c r="F55" s="164"/>
+      <c r="G55" s="170"/>
+      <c r="H55" s="138" t="s">
         <v>48</v>
       </c>
       <c r="I55" s="112">
@@ -9489,9 +9489,9 @@
       <c r="B56" s="18"/>
       <c r="C56" s="1"/>
       <c r="D56" s="34"/>
-      <c r="E56" s="134"/>
-      <c r="F56" s="135"/>
-      <c r="G56" s="136"/>
+      <c r="E56" s="166"/>
+      <c r="F56" s="167"/>
+      <c r="G56" s="171"/>
       <c r="H56" s="112"/>
       <c r="I56" s="112"/>
       <c r="J56" s="14"/>
@@ -9611,12 +9611,12 @@
       <c r="B57" s="18"/>
       <c r="C57" s="1"/>
       <c r="D57" s="34"/>
-      <c r="E57" s="131" t="s">
+      <c r="E57" s="169" t="s">
         <v>29</v>
       </c>
-      <c r="F57" s="132"/>
-      <c r="G57" s="133"/>
-      <c r="H57" s="184" t="s">
+      <c r="F57" s="164"/>
+      <c r="G57" s="170"/>
+      <c r="H57" s="138" t="s">
         <v>51</v>
       </c>
       <c r="I57" s="112">
@@ -9739,9 +9739,9 @@
       <c r="B58" s="18"/>
       <c r="C58" s="1"/>
       <c r="D58" s="34"/>
-      <c r="E58" s="134"/>
-      <c r="F58" s="135"/>
-      <c r="G58" s="136"/>
+      <c r="E58" s="166"/>
+      <c r="F58" s="167"/>
+      <c r="G58" s="171"/>
       <c r="H58" s="112"/>
       <c r="I58" s="112"/>
       <c r="J58" s="14"/>
@@ -9861,12 +9861,12 @@
       <c r="B59" s="18"/>
       <c r="C59" s="1"/>
       <c r="D59" s="34"/>
-      <c r="E59" s="131" t="s">
+      <c r="E59" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="F59" s="132"/>
-      <c r="G59" s="133"/>
-      <c r="H59" s="184" t="s">
+      <c r="F59" s="164"/>
+      <c r="G59" s="170"/>
+      <c r="H59" s="138" t="s">
         <v>49</v>
       </c>
       <c r="I59" s="112">
@@ -9989,9 +9989,9 @@
       <c r="B60" s="18"/>
       <c r="C60" s="1"/>
       <c r="D60" s="34"/>
-      <c r="E60" s="134"/>
-      <c r="F60" s="135"/>
-      <c r="G60" s="136"/>
+      <c r="E60" s="166"/>
+      <c r="F60" s="167"/>
+      <c r="G60" s="171"/>
       <c r="H60" s="112"/>
       <c r="I60" s="112"/>
       <c r="J60" s="14"/>
@@ -10111,12 +10111,12 @@
       <c r="B61" s="18"/>
       <c r="C61" s="1"/>
       <c r="D61" s="34"/>
-      <c r="E61" s="131" t="s">
+      <c r="E61" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F61" s="132"/>
-      <c r="G61" s="133"/>
-      <c r="H61" s="184" t="s">
+      <c r="F61" s="164"/>
+      <c r="G61" s="170"/>
+      <c r="H61" s="138" t="s">
         <v>49</v>
       </c>
       <c r="I61" s="112">
@@ -10239,9 +10239,9 @@
       <c r="B62" s="18"/>
       <c r="C62" s="1"/>
       <c r="D62" s="34"/>
-      <c r="E62" s="134"/>
-      <c r="F62" s="135"/>
-      <c r="G62" s="136"/>
+      <c r="E62" s="166"/>
+      <c r="F62" s="167"/>
+      <c r="G62" s="171"/>
       <c r="H62" s="112"/>
       <c r="I62" s="112"/>
       <c r="J62" s="26"/>
@@ -10360,14 +10360,14 @@
       <c r="A63" s="1"/>
       <c r="B63" s="18"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="137" t="s">
+      <c r="D63" s="163" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="132"/>
-      <c r="F63" s="132"/>
-      <c r="G63" s="138"/>
-      <c r="H63" s="167"/>
-      <c r="I63" s="167"/>
+      <c r="E63" s="164"/>
+      <c r="F63" s="164"/>
+      <c r="G63" s="165"/>
+      <c r="H63" s="139"/>
+      <c r="I63" s="139"/>
       <c r="J63" s="50"/>
       <c r="K63" s="51"/>
       <c r="L63" s="51"/>
@@ -10484,12 +10484,12 @@
       <c r="A64" s="1"/>
       <c r="B64" s="18"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="134"/>
-      <c r="E64" s="135"/>
-      <c r="F64" s="135"/>
-      <c r="G64" s="139"/>
-      <c r="H64" s="167"/>
-      <c r="I64" s="167"/>
+      <c r="D64" s="166"/>
+      <c r="E64" s="167"/>
+      <c r="F64" s="167"/>
+      <c r="G64" s="168"/>
+      <c r="H64" s="139"/>
+      <c r="I64" s="139"/>
       <c r="J64" s="52"/>
       <c r="K64" s="49"/>
       <c r="L64" s="49"/>
@@ -10607,12 +10607,12 @@
       <c r="B65" s="18"/>
       <c r="C65" s="1"/>
       <c r="D65" s="34"/>
-      <c r="E65" s="131" t="s">
+      <c r="E65" s="169" t="s">
         <v>35</v>
       </c>
-      <c r="F65" s="132"/>
-      <c r="G65" s="133"/>
-      <c r="H65" s="184" t="s">
+      <c r="F65" s="164"/>
+      <c r="G65" s="170"/>
+      <c r="H65" s="138" t="s">
         <v>52</v>
       </c>
       <c r="I65" s="112">
@@ -10735,9 +10735,9 @@
       <c r="B66" s="18"/>
       <c r="C66" s="1"/>
       <c r="D66" s="34"/>
-      <c r="E66" s="134"/>
-      <c r="F66" s="135"/>
-      <c r="G66" s="136"/>
+      <c r="E66" s="166"/>
+      <c r="F66" s="167"/>
+      <c r="G66" s="171"/>
       <c r="H66" s="112"/>
       <c r="I66" s="112"/>
       <c r="J66" s="14"/>
@@ -10857,12 +10857,12 @@
       <c r="B67" s="18"/>
       <c r="C67" s="1"/>
       <c r="D67" s="34"/>
-      <c r="E67" s="131" t="s">
+      <c r="E67" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="F67" s="132"/>
-      <c r="G67" s="133"/>
-      <c r="H67" s="184" t="s">
+      <c r="F67" s="164"/>
+      <c r="G67" s="170"/>
+      <c r="H67" s="138" t="s">
         <v>53</v>
       </c>
       <c r="I67" s="112">
@@ -10985,9 +10985,9 @@
       <c r="B68" s="18"/>
       <c r="C68" s="1"/>
       <c r="D68" s="34"/>
-      <c r="E68" s="134"/>
-      <c r="F68" s="135"/>
-      <c r="G68" s="136"/>
+      <c r="E68" s="166"/>
+      <c r="F68" s="167"/>
+      <c r="G68" s="171"/>
       <c r="H68" s="112"/>
       <c r="I68" s="112"/>
       <c r="J68" s="14"/>
@@ -11107,12 +11107,12 @@
       <c r="B69" s="18"/>
       <c r="C69" s="1"/>
       <c r="D69" s="34"/>
-      <c r="E69" s="131" t="s">
+      <c r="E69" s="169" t="s">
         <v>36</v>
       </c>
-      <c r="F69" s="132"/>
-      <c r="G69" s="133"/>
-      <c r="H69" s="184" t="s">
+      <c r="F69" s="164"/>
+      <c r="G69" s="170"/>
+      <c r="H69" s="138" t="s">
         <v>54</v>
       </c>
       <c r="I69" s="112">
@@ -11235,9 +11235,9 @@
       <c r="B70" s="18"/>
       <c r="C70" s="1"/>
       <c r="D70" s="34"/>
-      <c r="E70" s="134"/>
-      <c r="F70" s="135"/>
-      <c r="G70" s="136"/>
+      <c r="E70" s="166"/>
+      <c r="F70" s="167"/>
+      <c r="G70" s="171"/>
       <c r="H70" s="112"/>
       <c r="I70" s="112"/>
       <c r="J70" s="14"/>
@@ -11357,12 +11357,12 @@
       <c r="B71" s="18"/>
       <c r="C71" s="1"/>
       <c r="D71" s="34"/>
-      <c r="E71" s="131" t="s">
+      <c r="E71" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F71" s="132"/>
-      <c r="G71" s="133"/>
-      <c r="H71" s="184" t="s">
+      <c r="F71" s="164"/>
+      <c r="G71" s="170"/>
+      <c r="H71" s="138" t="s">
         <v>55</v>
       </c>
       <c r="I71" s="112">
@@ -11485,9 +11485,9 @@
       <c r="B72" s="18"/>
       <c r="C72" s="1"/>
       <c r="D72" s="35"/>
-      <c r="E72" s="134"/>
-      <c r="F72" s="135"/>
-      <c r="G72" s="136"/>
+      <c r="E72" s="166"/>
+      <c r="F72" s="167"/>
+      <c r="G72" s="171"/>
       <c r="H72" s="112"/>
       <c r="I72" s="112"/>
       <c r="J72" s="26"/>
@@ -11605,14 +11605,14 @@
     <row r="73" spans="1:120" ht="9.75" customHeight="1">
       <c r="A73" s="16"/>
       <c r="B73" s="36"/>
-      <c r="C73" s="140" t="s">
+      <c r="C73" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="D73" s="132"/>
-      <c r="E73" s="132"/>
-      <c r="F73" s="132"/>
-      <c r="G73" s="138"/>
-      <c r="H73" s="184" t="s">
+      <c r="D73" s="164"/>
+      <c r="E73" s="164"/>
+      <c r="F73" s="164"/>
+      <c r="G73" s="165"/>
+      <c r="H73" s="138" t="s">
         <v>55</v>
       </c>
       <c r="I73" s="112">
@@ -11733,11 +11733,11 @@
     <row r="74" spans="1:120" ht="9.75" customHeight="1">
       <c r="A74" s="16"/>
       <c r="B74" s="36"/>
-      <c r="C74" s="141"/>
-      <c r="D74" s="135"/>
-      <c r="E74" s="135"/>
-      <c r="F74" s="135"/>
-      <c r="G74" s="139"/>
+      <c r="C74" s="179"/>
+      <c r="D74" s="167"/>
+      <c r="E74" s="167"/>
+      <c r="F74" s="167"/>
+      <c r="G74" s="168"/>
       <c r="H74" s="112"/>
       <c r="I74" s="112"/>
       <c r="J74" s="19"/>
@@ -11855,14 +11855,14 @@
     <row r="75" spans="1:120" ht="9.75" customHeight="1">
       <c r="A75" s="16"/>
       <c r="B75" s="36"/>
-      <c r="C75" s="140" t="s">
+      <c r="C75" s="146" t="s">
         <v>34</v>
       </c>
-      <c r="D75" s="132"/>
-      <c r="E75" s="132"/>
-      <c r="F75" s="132"/>
-      <c r="G75" s="138"/>
-      <c r="H75" s="184" t="s">
+      <c r="D75" s="164"/>
+      <c r="E75" s="164"/>
+      <c r="F75" s="164"/>
+      <c r="G75" s="165"/>
+      <c r="H75" s="138" t="s">
         <v>58</v>
       </c>
       <c r="I75" s="112"/>
@@ -11981,11 +11981,11 @@
     <row r="76" spans="1:120" ht="9.75" customHeight="1">
       <c r="A76" s="16"/>
       <c r="B76" s="36"/>
-      <c r="C76" s="142"/>
-      <c r="D76" s="142"/>
-      <c r="E76" s="142"/>
-      <c r="F76" s="142"/>
-      <c r="G76" s="142"/>
+      <c r="C76" s="162"/>
+      <c r="D76" s="162"/>
+      <c r="E76" s="162"/>
+      <c r="F76" s="162"/>
+      <c r="G76" s="162"/>
       <c r="H76" s="112"/>
       <c r="I76" s="112"/>
       <c r="J76" s="19"/>
@@ -12103,15 +12103,15 @@
     <row r="77" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A77" s="16"/>
       <c r="B77" s="71"/>
-      <c r="C77" s="143" t="s">
+      <c r="C77" s="187" t="s">
         <v>62</v>
       </c>
-      <c r="D77" s="144"/>
-      <c r="E77" s="144"/>
-      <c r="F77" s="144"/>
-      <c r="G77" s="145"/>
-      <c r="H77" s="185"/>
-      <c r="I77" s="181"/>
+      <c r="D77" s="188"/>
+      <c r="E77" s="188"/>
+      <c r="F77" s="188"/>
+      <c r="G77" s="189"/>
+      <c r="H77" s="140"/>
+      <c r="I77" s="129"/>
       <c r="J77" s="63"/>
       <c r="K77" s="64"/>
       <c r="L77" s="64"/>
@@ -12227,13 +12227,13 @@
     <row r="78" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A78" s="16"/>
       <c r="B78" s="71"/>
-      <c r="C78" s="146"/>
-      <c r="D78" s="147"/>
-      <c r="E78" s="147"/>
-      <c r="F78" s="147"/>
-      <c r="G78" s="148"/>
-      <c r="H78" s="186"/>
-      <c r="I78" s="182"/>
+      <c r="C78" s="190"/>
+      <c r="D78" s="191"/>
+      <c r="E78" s="191"/>
+      <c r="F78" s="191"/>
+      <c r="G78" s="192"/>
+      <c r="H78" s="141"/>
+      <c r="I78" s="130"/>
       <c r="J78" s="63"/>
       <c r="K78" s="64"/>
       <c r="L78" s="64"/>
@@ -12350,12 +12350,12 @@
       <c r="A79" s="16"/>
       <c r="B79" s="71"/>
       <c r="C79" s="76"/>
-      <c r="D79" s="115" t="s">
+      <c r="D79" s="132" t="s">
         <v>63</v>
       </c>
-      <c r="E79" s="116"/>
-      <c r="F79" s="116"/>
-      <c r="G79" s="117"/>
+      <c r="E79" s="133"/>
+      <c r="F79" s="133"/>
+      <c r="G79" s="134"/>
       <c r="H79" s="77"/>
       <c r="I79" s="67"/>
       <c r="J79" s="63"/>
@@ -12474,10 +12474,10 @@
       <c r="A80" s="16"/>
       <c r="B80" s="71"/>
       <c r="C80" s="76"/>
-      <c r="D80" s="118"/>
-      <c r="E80" s="119"/>
-      <c r="F80" s="119"/>
-      <c r="G80" s="120"/>
+      <c r="D80" s="135"/>
+      <c r="E80" s="136"/>
+      <c r="F80" s="136"/>
+      <c r="G80" s="137"/>
       <c r="H80" s="77"/>
       <c r="I80" s="67"/>
       <c r="J80" s="63"/>
@@ -12597,15 +12597,15 @@
       <c r="B81" s="36"/>
       <c r="C81" s="60"/>
       <c r="D81" s="70"/>
-      <c r="E81" s="149" t="s">
+      <c r="E81" s="105" t="s">
         <v>73</v>
       </c>
-      <c r="F81" s="149"/>
-      <c r="G81" s="149"/>
-      <c r="H81" s="103">
+      <c r="F81" s="105"/>
+      <c r="G81" s="105"/>
+      <c r="H81" s="111">
         <v>45611</v>
       </c>
-      <c r="I81" s="105">
+      <c r="I81" s="126">
         <v>100</v>
       </c>
       <c r="J81" s="19"/>
@@ -12725,11 +12725,11 @@
       <c r="B82" s="36"/>
       <c r="C82" s="60"/>
       <c r="D82" s="70"/>
-      <c r="E82" s="102"/>
-      <c r="F82" s="102"/>
-      <c r="G82" s="102"/>
-      <c r="H82" s="104"/>
-      <c r="I82" s="106"/>
+      <c r="E82" s="103"/>
+      <c r="F82" s="103"/>
+      <c r="G82" s="103"/>
+      <c r="H82" s="107"/>
+      <c r="I82" s="109"/>
       <c r="J82" s="19"/>
       <c r="K82" s="20"/>
       <c r="L82" s="20"/>
@@ -12847,15 +12847,15 @@
       <c r="B83" s="36"/>
       <c r="C83" s="60"/>
       <c r="D83" s="70"/>
-      <c r="E83" s="102" t="s">
+      <c r="E83" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="F83" s="102"/>
-      <c r="G83" s="102"/>
-      <c r="H83" s="103">
+      <c r="F83" s="103"/>
+      <c r="G83" s="103"/>
+      <c r="H83" s="111">
         <v>45615</v>
       </c>
-      <c r="I83" s="105">
+      <c r="I83" s="126">
         <v>100</v>
       </c>
       <c r="J83" s="19"/>
@@ -12975,11 +12975,11 @@
       <c r="B84" s="36"/>
       <c r="C84" s="60"/>
       <c r="D84" s="70"/>
-      <c r="E84" s="102"/>
-      <c r="F84" s="102"/>
-      <c r="G84" s="102"/>
-      <c r="H84" s="104"/>
-      <c r="I84" s="106"/>
+      <c r="E84" s="103"/>
+      <c r="F84" s="103"/>
+      <c r="G84" s="103"/>
+      <c r="H84" s="107"/>
+      <c r="I84" s="109"/>
       <c r="J84" s="19"/>
       <c r="K84" s="20"/>
       <c r="L84" s="20"/>
@@ -13097,15 +13097,15 @@
       <c r="B85" s="36"/>
       <c r="C85" s="60"/>
       <c r="D85" s="70"/>
-      <c r="E85" s="189" t="s">
+      <c r="E85" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="F85" s="121"/>
-      <c r="G85" s="122"/>
-      <c r="H85" s="111">
+      <c r="F85" s="115"/>
+      <c r="G85" s="116"/>
+      <c r="H85" s="110">
         <v>45617</v>
       </c>
-      <c r="I85" s="105">
+      <c r="I85" s="126">
         <v>100</v>
       </c>
       <c r="J85" s="62"/>
@@ -13225,11 +13225,11 @@
       <c r="B86" s="36"/>
       <c r="C86" s="60"/>
       <c r="D86" s="70"/>
-      <c r="E86" s="150"/>
-      <c r="F86" s="125"/>
-      <c r="G86" s="126"/>
-      <c r="H86" s="111"/>
-      <c r="I86" s="106"/>
+      <c r="E86" s="117"/>
+      <c r="F86" s="118"/>
+      <c r="G86" s="119"/>
+      <c r="H86" s="110"/>
+      <c r="I86" s="109"/>
       <c r="J86" s="62"/>
       <c r="K86" s="20"/>
       <c r="L86" s="20"/>
@@ -13346,16 +13346,16 @@
       <c r="A87" s="16"/>
       <c r="B87" s="71"/>
       <c r="C87" s="90"/>
-      <c r="D87" s="102" t="s">
+      <c r="D87" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="E87" s="102"/>
-      <c r="F87" s="102"/>
-      <c r="G87" s="102"/>
-      <c r="H87" s="103">
+      <c r="E87" s="103"/>
+      <c r="F87" s="103"/>
+      <c r="G87" s="103"/>
+      <c r="H87" s="111">
         <v>45615</v>
       </c>
-      <c r="I87" s="105">
+      <c r="I87" s="126">
         <v>100</v>
       </c>
       <c r="J87" s="62"/>
@@ -13474,12 +13474,12 @@
       <c r="A88" s="16"/>
       <c r="B88" s="71"/>
       <c r="C88" s="90"/>
-      <c r="D88" s="102"/>
-      <c r="E88" s="102"/>
-      <c r="F88" s="102"/>
-      <c r="G88" s="102"/>
-      <c r="H88" s="104"/>
-      <c r="I88" s="106"/>
+      <c r="D88" s="103"/>
+      <c r="E88" s="103"/>
+      <c r="F88" s="103"/>
+      <c r="G88" s="103"/>
+      <c r="H88" s="107"/>
+      <c r="I88" s="109"/>
       <c r="J88" s="62"/>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -13596,14 +13596,14 @@
       <c r="A89" s="16"/>
       <c r="B89" s="36"/>
       <c r="C89" s="79"/>
-      <c r="D89" s="115" t="s">
+      <c r="D89" s="132" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="116"/>
-      <c r="F89" s="116"/>
-      <c r="G89" s="117"/>
-      <c r="H89" s="187"/>
-      <c r="I89" s="188"/>
+      <c r="E89" s="133"/>
+      <c r="F89" s="133"/>
+      <c r="G89" s="134"/>
+      <c r="H89" s="131"/>
+      <c r="I89" s="128"/>
       <c r="J89" s="66"/>
       <c r="K89" s="64"/>
       <c r="L89" s="64"/>
@@ -13720,12 +13720,12 @@
       <c r="A90" s="16"/>
       <c r="B90" s="36"/>
       <c r="C90" s="79"/>
-      <c r="D90" s="118"/>
-      <c r="E90" s="119"/>
-      <c r="F90" s="119"/>
-      <c r="G90" s="120"/>
-      <c r="H90" s="187"/>
-      <c r="I90" s="188"/>
+      <c r="D90" s="135"/>
+      <c r="E90" s="136"/>
+      <c r="F90" s="136"/>
+      <c r="G90" s="137"/>
+      <c r="H90" s="131"/>
+      <c r="I90" s="128"/>
       <c r="J90" s="66"/>
       <c r="K90" s="64"/>
       <c r="L90" s="64"/>
@@ -13843,15 +13843,15 @@
       <c r="B91" s="36"/>
       <c r="C91" s="60"/>
       <c r="D91" s="70"/>
-      <c r="E91" s="149" t="s">
+      <c r="E91" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="F91" s="149"/>
-      <c r="G91" s="149"/>
-      <c r="H91" s="103">
+      <c r="F91" s="105"/>
+      <c r="G91" s="105"/>
+      <c r="H91" s="111">
         <v>45616</v>
       </c>
-      <c r="I91" s="105">
+      <c r="I91" s="126">
         <v>100</v>
       </c>
       <c r="J91" s="19"/>
@@ -13971,11 +13971,11 @@
       <c r="B92" s="36"/>
       <c r="C92" s="60"/>
       <c r="D92" s="70"/>
-      <c r="E92" s="102"/>
-      <c r="F92" s="102"/>
-      <c r="G92" s="102"/>
-      <c r="H92" s="104"/>
-      <c r="I92" s="106"/>
+      <c r="E92" s="103"/>
+      <c r="F92" s="103"/>
+      <c r="G92" s="103"/>
+      <c r="H92" s="107"/>
+      <c r="I92" s="109"/>
       <c r="J92" s="19"/>
       <c r="K92" s="20"/>
       <c r="L92" s="20"/>
@@ -14093,15 +14093,15 @@
       <c r="B93" s="36"/>
       <c r="C93" s="60"/>
       <c r="D93" s="70"/>
-      <c r="E93" s="102" t="s">
+      <c r="E93" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="F93" s="102"/>
-      <c r="G93" s="102"/>
-      <c r="H93" s="103">
+      <c r="F93" s="103"/>
+      <c r="G93" s="103"/>
+      <c r="H93" s="111">
         <v>45617</v>
       </c>
-      <c r="I93" s="105">
+      <c r="I93" s="126">
         <v>100</v>
       </c>
       <c r="J93" s="19"/>
@@ -14221,11 +14221,11 @@
       <c r="B94" s="36"/>
       <c r="C94" s="60"/>
       <c r="D94" s="70"/>
-      <c r="E94" s="102"/>
-      <c r="F94" s="102"/>
-      <c r="G94" s="102"/>
-      <c r="H94" s="104"/>
-      <c r="I94" s="106"/>
+      <c r="E94" s="103"/>
+      <c r="F94" s="103"/>
+      <c r="G94" s="103"/>
+      <c r="H94" s="107"/>
+      <c r="I94" s="109"/>
       <c r="J94" s="19"/>
       <c r="K94" s="20"/>
       <c r="L94" s="20"/>
@@ -14343,15 +14343,15 @@
       <c r="B95" s="36"/>
       <c r="C95" s="60"/>
       <c r="D95" s="70"/>
-      <c r="E95" s="102" t="s">
+      <c r="E95" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="F95" s="102"/>
-      <c r="G95" s="102"/>
-      <c r="H95" s="103">
+      <c r="F95" s="103"/>
+      <c r="G95" s="103"/>
+      <c r="H95" s="111">
         <v>45618</v>
       </c>
-      <c r="I95" s="105">
+      <c r="I95" s="126">
         <v>100</v>
       </c>
       <c r="J95" s="19"/>
@@ -14471,11 +14471,11 @@
       <c r="B96" s="36"/>
       <c r="C96" s="60"/>
       <c r="D96" s="70"/>
-      <c r="E96" s="102"/>
-      <c r="F96" s="102"/>
-      <c r="G96" s="102"/>
-      <c r="H96" s="104"/>
-      <c r="I96" s="106"/>
+      <c r="E96" s="103"/>
+      <c r="F96" s="103"/>
+      <c r="G96" s="103"/>
+      <c r="H96" s="107"/>
+      <c r="I96" s="109"/>
       <c r="J96" s="19"/>
       <c r="K96" s="20"/>
       <c r="L96" s="20"/>
@@ -14593,15 +14593,15 @@
       <c r="B97" s="36"/>
       <c r="C97" s="60"/>
       <c r="D97" s="70"/>
-      <c r="E97" s="102" t="s">
+      <c r="E97" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="F97" s="102"/>
-      <c r="G97" s="102"/>
-      <c r="H97" s="103">
+      <c r="F97" s="103"/>
+      <c r="G97" s="103"/>
+      <c r="H97" s="111">
         <v>45621</v>
       </c>
-      <c r="I97" s="105">
+      <c r="I97" s="126">
         <v>100</v>
       </c>
       <c r="J97" s="19"/>
@@ -14721,11 +14721,11 @@
       <c r="B98" s="36"/>
       <c r="C98" s="60"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="102"/>
-      <c r="F98" s="102"/>
-      <c r="G98" s="102"/>
-      <c r="H98" s="104"/>
-      <c r="I98" s="106"/>
+      <c r="E98" s="103"/>
+      <c r="F98" s="103"/>
+      <c r="G98" s="103"/>
+      <c r="H98" s="107"/>
+      <c r="I98" s="109"/>
       <c r="J98" s="19"/>
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
@@ -14843,15 +14843,15 @@
       <c r="B99" s="36"/>
       <c r="C99" s="60"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="102" t="s">
+      <c r="E99" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="F99" s="102"/>
-      <c r="G99" s="102"/>
-      <c r="H99" s="103">
+      <c r="F99" s="103"/>
+      <c r="G99" s="103"/>
+      <c r="H99" s="111">
         <v>45622</v>
       </c>
-      <c r="I99" s="105">
+      <c r="I99" s="126">
         <v>100</v>
       </c>
       <c r="J99" s="19"/>
@@ -14971,11 +14971,11 @@
       <c r="B100" s="36"/>
       <c r="C100" s="60"/>
       <c r="D100" s="70"/>
-      <c r="E100" s="102"/>
-      <c r="F100" s="102"/>
-      <c r="G100" s="102"/>
-      <c r="H100" s="104"/>
-      <c r="I100" s="106"/>
+      <c r="E100" s="103"/>
+      <c r="F100" s="103"/>
+      <c r="G100" s="103"/>
+      <c r="H100" s="107"/>
+      <c r="I100" s="109"/>
       <c r="J100" s="19"/>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -15093,12 +15093,12 @@
       <c r="B101" s="71"/>
       <c r="C101" s="91"/>
       <c r="D101" s="70"/>
-      <c r="E101" s="150" t="s">
+      <c r="E101" s="117" t="s">
         <v>61</v>
       </c>
-      <c r="F101" s="125"/>
-      <c r="G101" s="126"/>
-      <c r="H101" s="103">
+      <c r="F101" s="118"/>
+      <c r="G101" s="119"/>
+      <c r="H101" s="111">
         <v>45623</v>
       </c>
       <c r="I101" s="112">
@@ -15221,10 +15221,10 @@
       <c r="B102" s="71"/>
       <c r="C102" s="91"/>
       <c r="D102" s="70"/>
-      <c r="E102" s="150"/>
-      <c r="F102" s="125"/>
-      <c r="G102" s="126"/>
-      <c r="H102" s="104"/>
+      <c r="E102" s="117"/>
+      <c r="F102" s="118"/>
+      <c r="G102" s="119"/>
+      <c r="H102" s="107"/>
       <c r="I102" s="112"/>
       <c r="J102" s="62"/>
       <c r="K102" s="20"/>
@@ -15342,16 +15342,16 @@
       <c r="A103" s="16"/>
       <c r="B103" s="71"/>
       <c r="C103" s="90"/>
-      <c r="D103" s="102" t="s">
+      <c r="D103" s="103" t="s">
         <v>77</v>
       </c>
-      <c r="E103" s="102"/>
-      <c r="F103" s="102"/>
-      <c r="G103" s="102"/>
-      <c r="H103" s="103">
+      <c r="E103" s="103"/>
+      <c r="F103" s="103"/>
+      <c r="G103" s="103"/>
+      <c r="H103" s="111">
         <v>45622</v>
       </c>
-      <c r="I103" s="109">
+      <c r="I103" s="113">
         <v>100</v>
       </c>
       <c r="J103" s="62"/>
@@ -15470,12 +15470,12 @@
       <c r="A104" s="16"/>
       <c r="B104" s="71"/>
       <c r="C104" s="90"/>
-      <c r="D104" s="102"/>
-      <c r="E104" s="102"/>
-      <c r="F104" s="102"/>
-      <c r="G104" s="102"/>
-      <c r="H104" s="104"/>
-      <c r="I104" s="110"/>
+      <c r="D104" s="103"/>
+      <c r="E104" s="103"/>
+      <c r="F104" s="103"/>
+      <c r="G104" s="103"/>
+      <c r="H104" s="107"/>
+      <c r="I104" s="143"/>
       <c r="J104" s="62"/>
       <c r="K104" s="20"/>
       <c r="L104" s="20"/>
@@ -15591,15 +15591,15 @@
     <row r="105" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A105" s="16"/>
       <c r="B105" s="71"/>
-      <c r="C105" s="143" t="s">
+      <c r="C105" s="187" t="s">
         <v>64</v>
       </c>
-      <c r="D105" s="144"/>
-      <c r="E105" s="144"/>
-      <c r="F105" s="144"/>
-      <c r="G105" s="145"/>
-      <c r="H105" s="190"/>
-      <c r="I105" s="188"/>
+      <c r="D105" s="188"/>
+      <c r="E105" s="188"/>
+      <c r="F105" s="188"/>
+      <c r="G105" s="189"/>
+      <c r="H105" s="127"/>
+      <c r="I105" s="128"/>
       <c r="J105" s="66"/>
       <c r="K105" s="64"/>
       <c r="L105" s="64"/>
@@ -15715,13 +15715,13 @@
     <row r="106" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A106" s="16"/>
       <c r="B106" s="71"/>
-      <c r="C106" s="146"/>
-      <c r="D106" s="147"/>
-      <c r="E106" s="147"/>
-      <c r="F106" s="147"/>
-      <c r="G106" s="148"/>
-      <c r="H106" s="190"/>
-      <c r="I106" s="188"/>
+      <c r="C106" s="190"/>
+      <c r="D106" s="191"/>
+      <c r="E106" s="191"/>
+      <c r="F106" s="191"/>
+      <c r="G106" s="192"/>
+      <c r="H106" s="127"/>
+      <c r="I106" s="128"/>
       <c r="J106" s="66"/>
       <c r="K106" s="64"/>
       <c r="L106" s="64"/>
@@ -15838,14 +15838,14 @@
       <c r="A107" s="16"/>
       <c r="B107" s="36"/>
       <c r="C107" s="78"/>
-      <c r="D107" s="115" t="s">
+      <c r="D107" s="132" t="s">
         <v>59</v>
       </c>
-      <c r="E107" s="116"/>
-      <c r="F107" s="116"/>
-      <c r="G107" s="117"/>
-      <c r="H107" s="190"/>
-      <c r="I107" s="188"/>
+      <c r="E107" s="133"/>
+      <c r="F107" s="133"/>
+      <c r="G107" s="134"/>
+      <c r="H107" s="127"/>
+      <c r="I107" s="128"/>
       <c r="J107" s="66"/>
       <c r="K107" s="64"/>
       <c r="L107" s="64"/>
@@ -15962,12 +15962,12 @@
       <c r="A108" s="16"/>
       <c r="B108" s="36"/>
       <c r="C108" s="76"/>
-      <c r="D108" s="118"/>
-      <c r="E108" s="119"/>
-      <c r="F108" s="119"/>
-      <c r="G108" s="120"/>
-      <c r="H108" s="190"/>
-      <c r="I108" s="188"/>
+      <c r="D108" s="135"/>
+      <c r="E108" s="136"/>
+      <c r="F108" s="136"/>
+      <c r="G108" s="137"/>
+      <c r="H108" s="127"/>
+      <c r="I108" s="128"/>
       <c r="J108" s="66"/>
       <c r="K108" s="64"/>
       <c r="L108" s="64"/>
@@ -16085,15 +16085,15 @@
       <c r="B109" s="36"/>
       <c r="C109" s="60"/>
       <c r="D109" s="70"/>
-      <c r="E109" s="149" t="s">
+      <c r="E109" s="105" t="s">
         <v>73</v>
       </c>
-      <c r="F109" s="149"/>
-      <c r="G109" s="149"/>
-      <c r="H109" s="103">
+      <c r="F109" s="105"/>
+      <c r="G109" s="105"/>
+      <c r="H109" s="111">
         <v>45624</v>
       </c>
-      <c r="I109" s="109">
+      <c r="I109" s="113">
         <v>100</v>
       </c>
       <c r="J109" s="62"/>
@@ -16213,11 +16213,11 @@
       <c r="B110" s="36"/>
       <c r="C110" s="60"/>
       <c r="D110" s="70"/>
-      <c r="E110" s="102"/>
-      <c r="F110" s="102"/>
-      <c r="G110" s="102"/>
-      <c r="H110" s="104"/>
-      <c r="I110" s="110"/>
+      <c r="E110" s="103"/>
+      <c r="F110" s="103"/>
+      <c r="G110" s="103"/>
+      <c r="H110" s="107"/>
+      <c r="I110" s="143"/>
       <c r="J110" s="62"/>
       <c r="K110" s="20"/>
       <c r="L110" s="20"/>
@@ -16335,15 +16335,15 @@
       <c r="B111" s="36"/>
       <c r="C111" s="60"/>
       <c r="D111" s="70"/>
-      <c r="E111" s="102" t="s">
+      <c r="E111" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="F111" s="102"/>
-      <c r="G111" s="102"/>
-      <c r="H111" s="103">
+      <c r="F111" s="103"/>
+      <c r="G111" s="103"/>
+      <c r="H111" s="111">
         <v>45625</v>
       </c>
-      <c r="I111" s="109"/>
+      <c r="I111" s="113"/>
       <c r="J111" s="62"/>
       <c r="K111" s="20"/>
       <c r="L111" s="20"/>
@@ -16461,11 +16461,11 @@
       <c r="B112" s="36"/>
       <c r="C112" s="60"/>
       <c r="D112" s="70"/>
-      <c r="E112" s="102"/>
-      <c r="F112" s="102"/>
-      <c r="G112" s="102"/>
-      <c r="H112" s="104"/>
-      <c r="I112" s="110"/>
+      <c r="E112" s="103"/>
+      <c r="F112" s="103"/>
+      <c r="G112" s="103"/>
+      <c r="H112" s="107"/>
+      <c r="I112" s="143"/>
       <c r="J112" s="62"/>
       <c r="K112" s="20"/>
       <c r="L112" s="20"/>
@@ -16583,12 +16583,12 @@
       <c r="B113" s="71"/>
       <c r="C113" s="91"/>
       <c r="D113" s="70"/>
-      <c r="E113" s="102" t="s">
+      <c r="E113" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="F113" s="102"/>
-      <c r="G113" s="102"/>
-      <c r="H113" s="111">
+      <c r="F113" s="103"/>
+      <c r="G113" s="103"/>
+      <c r="H113" s="110">
         <v>45629</v>
       </c>
       <c r="I113" s="112"/>
@@ -16709,11 +16709,11 @@
       <c r="B114" s="71"/>
       <c r="C114" s="91"/>
       <c r="D114" s="70"/>
-      <c r="E114" s="198"/>
-      <c r="F114" s="198"/>
-      <c r="G114" s="198"/>
-      <c r="H114" s="103"/>
-      <c r="I114" s="109"/>
+      <c r="E114" s="125"/>
+      <c r="F114" s="125"/>
+      <c r="G114" s="125"/>
+      <c r="H114" s="111"/>
+      <c r="I114" s="113"/>
       <c r="J114" s="62"/>
       <c r="K114" s="20"/>
       <c r="L114" s="20"/>
@@ -16830,13 +16830,13 @@
       <c r="A115" s="16"/>
       <c r="B115" s="71"/>
       <c r="C115" s="91"/>
-      <c r="D115" s="102" t="s">
+      <c r="D115" s="103" t="s">
         <v>78</v>
       </c>
-      <c r="E115" s="102"/>
-      <c r="F115" s="102"/>
-      <c r="G115" s="102"/>
-      <c r="H115" s="111">
+      <c r="E115" s="103"/>
+      <c r="F115" s="103"/>
+      <c r="G115" s="103"/>
+      <c r="H115" s="110">
         <v>45625</v>
       </c>
       <c r="I115" s="112"/>
@@ -16956,11 +16956,11 @@
       <c r="A116" s="16"/>
       <c r="B116" s="71"/>
       <c r="C116" s="91"/>
-      <c r="D116" s="102"/>
-      <c r="E116" s="102"/>
-      <c r="F116" s="102"/>
-      <c r="G116" s="102"/>
-      <c r="H116" s="111"/>
+      <c r="D116" s="103"/>
+      <c r="E116" s="103"/>
+      <c r="F116" s="103"/>
+      <c r="G116" s="103"/>
+      <c r="H116" s="110"/>
       <c r="I116" s="112"/>
       <c r="J116" s="62"/>
       <c r="K116" s="20"/>
@@ -17078,14 +17078,14 @@
       <c r="A117" s="16"/>
       <c r="B117" s="36"/>
       <c r="C117" s="80"/>
-      <c r="D117" s="115" t="s">
+      <c r="D117" s="132" t="s">
         <v>60</v>
       </c>
-      <c r="E117" s="116"/>
-      <c r="F117" s="116"/>
-      <c r="G117" s="117"/>
-      <c r="H117" s="191"/>
-      <c r="I117" s="181"/>
+      <c r="E117" s="133"/>
+      <c r="F117" s="133"/>
+      <c r="G117" s="134"/>
+      <c r="H117" s="121"/>
+      <c r="I117" s="129"/>
       <c r="J117" s="63"/>
       <c r="K117" s="64"/>
       <c r="L117" s="64"/>
@@ -17202,12 +17202,12 @@
       <c r="A118" s="16"/>
       <c r="B118" s="36"/>
       <c r="C118" s="80"/>
-      <c r="D118" s="118"/>
-      <c r="E118" s="119"/>
-      <c r="F118" s="119"/>
-      <c r="G118" s="120"/>
-      <c r="H118" s="192"/>
-      <c r="I118" s="182"/>
+      <c r="D118" s="135"/>
+      <c r="E118" s="136"/>
+      <c r="F118" s="136"/>
+      <c r="G118" s="137"/>
+      <c r="H118" s="122"/>
+      <c r="I118" s="130"/>
       <c r="J118" s="63"/>
       <c r="K118" s="64"/>
       <c r="L118" s="64"/>
@@ -17325,15 +17325,15 @@
       <c r="B119" s="36"/>
       <c r="C119" s="60"/>
       <c r="D119" s="70"/>
-      <c r="E119" s="149" t="s">
+      <c r="E119" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="F119" s="149"/>
-      <c r="G119" s="149"/>
-      <c r="H119" s="103">
+      <c r="F119" s="105"/>
+      <c r="G119" s="105"/>
+      <c r="H119" s="111">
         <v>45629</v>
       </c>
-      <c r="I119" s="105">
+      <c r="I119" s="126">
         <v>100</v>
       </c>
       <c r="J119" s="19"/>
@@ -17453,11 +17453,11 @@
       <c r="B120" s="36"/>
       <c r="C120" s="60"/>
       <c r="D120" s="70"/>
-      <c r="E120" s="102"/>
-      <c r="F120" s="102"/>
-      <c r="G120" s="102"/>
-      <c r="H120" s="104"/>
-      <c r="I120" s="106"/>
+      <c r="E120" s="103"/>
+      <c r="F120" s="103"/>
+      <c r="G120" s="103"/>
+      <c r="H120" s="107"/>
+      <c r="I120" s="109"/>
       <c r="J120" s="19"/>
       <c r="K120" s="20"/>
       <c r="L120" s="20"/>
@@ -17575,15 +17575,15 @@
       <c r="B121" s="36"/>
       <c r="C121" s="60"/>
       <c r="D121" s="70"/>
-      <c r="E121" s="102" t="s">
+      <c r="E121" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="F121" s="102"/>
-      <c r="G121" s="102"/>
-      <c r="H121" s="103">
+      <c r="F121" s="103"/>
+      <c r="G121" s="103"/>
+      <c r="H121" s="111">
         <v>45630</v>
       </c>
-      <c r="I121" s="105"/>
+      <c r="I121" s="126"/>
       <c r="J121" s="19"/>
       <c r="K121" s="20"/>
       <c r="L121" s="20"/>
@@ -17701,11 +17701,11 @@
       <c r="B122" s="36"/>
       <c r="C122" s="60"/>
       <c r="D122" s="70"/>
-      <c r="E122" s="102"/>
-      <c r="F122" s="102"/>
-      <c r="G122" s="102"/>
-      <c r="H122" s="104"/>
-      <c r="I122" s="106"/>
+      <c r="E122" s="103"/>
+      <c r="F122" s="103"/>
+      <c r="G122" s="103"/>
+      <c r="H122" s="107"/>
+      <c r="I122" s="109"/>
       <c r="J122" s="19"/>
       <c r="K122" s="20"/>
       <c r="L122" s="20"/>
@@ -17756,8 +17756,8 @@
       <c r="BE122" s="21"/>
       <c r="BF122" s="21"/>
       <c r="BG122" s="20"/>
-      <c r="BH122" s="20"/>
-      <c r="BI122" s="20"/>
+      <c r="BH122" s="75"/>
+      <c r="BI122" s="75"/>
       <c r="BJ122" s="64"/>
       <c r="BK122" s="64"/>
       <c r="BL122" s="21"/>
@@ -17823,12 +17823,12 @@
       <c r="B123" s="36"/>
       <c r="C123" s="60"/>
       <c r="D123" s="70"/>
-      <c r="E123" s="102" t="s">
+      <c r="E123" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="F123" s="102"/>
-      <c r="G123" s="102"/>
-      <c r="H123" s="197">
+      <c r="F123" s="103"/>
+      <c r="G123" s="103"/>
+      <c r="H123" s="120">
         <v>45631</v>
       </c>
       <c r="I123" s="112"/>
@@ -17949,10 +17949,10 @@
       <c r="B124" s="36"/>
       <c r="C124" s="60"/>
       <c r="D124" s="70"/>
-      <c r="E124" s="102"/>
-      <c r="F124" s="102"/>
-      <c r="G124" s="102"/>
-      <c r="H124" s="197"/>
+      <c r="E124" s="103"/>
+      <c r="F124" s="103"/>
+      <c r="G124" s="103"/>
+      <c r="H124" s="120"/>
       <c r="I124" s="112"/>
       <c r="J124" s="62"/>
       <c r="K124" s="20"/>
@@ -18071,12 +18071,12 @@
       <c r="B125" s="36"/>
       <c r="C125" s="60"/>
       <c r="D125" s="70"/>
-      <c r="E125" s="102" t="s">
+      <c r="E125" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="F125" s="102"/>
-      <c r="G125" s="102"/>
-      <c r="H125" s="111">
+      <c r="F125" s="103"/>
+      <c r="G125" s="103"/>
+      <c r="H125" s="110">
         <v>45632</v>
       </c>
       <c r="I125" s="112"/>
@@ -18197,10 +18197,10 @@
       <c r="B126" s="36"/>
       <c r="C126" s="60"/>
       <c r="D126" s="70"/>
-      <c r="E126" s="102"/>
-      <c r="F126" s="102"/>
-      <c r="G126" s="102"/>
-      <c r="H126" s="111"/>
+      <c r="E126" s="103"/>
+      <c r="F126" s="103"/>
+      <c r="G126" s="103"/>
+      <c r="H126" s="110"/>
       <c r="I126" s="112"/>
       <c r="J126" s="62"/>
       <c r="K126" s="20"/>
@@ -18319,15 +18319,15 @@
       <c r="B127" s="36"/>
       <c r="C127" s="60"/>
       <c r="D127" s="70"/>
-      <c r="E127" s="102" t="s">
+      <c r="E127" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="F127" s="102"/>
-      <c r="G127" s="102"/>
-      <c r="H127" s="103">
+      <c r="F127" s="103"/>
+      <c r="G127" s="103"/>
+      <c r="H127" s="111">
         <v>45635</v>
       </c>
-      <c r="I127" s="105"/>
+      <c r="I127" s="126"/>
       <c r="J127" s="19"/>
       <c r="K127" s="20"/>
       <c r="L127" s="20"/>
@@ -18445,11 +18445,11 @@
       <c r="B128" s="36"/>
       <c r="C128" s="60"/>
       <c r="D128" s="70"/>
-      <c r="E128" s="198"/>
-      <c r="F128" s="198"/>
-      <c r="G128" s="198"/>
-      <c r="H128" s="104"/>
-      <c r="I128" s="106"/>
+      <c r="E128" s="125"/>
+      <c r="F128" s="125"/>
+      <c r="G128" s="125"/>
+      <c r="H128" s="107"/>
+      <c r="I128" s="109"/>
       <c r="J128" s="19"/>
       <c r="K128" s="20"/>
       <c r="L128" s="20"/>
@@ -18567,12 +18567,12 @@
       <c r="B129" s="71"/>
       <c r="C129" s="91"/>
       <c r="D129" s="70"/>
-      <c r="E129" s="189" t="s">
+      <c r="E129" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="F129" s="121"/>
-      <c r="G129" s="122"/>
-      <c r="H129" s="111">
+      <c r="F129" s="115"/>
+      <c r="G129" s="116"/>
+      <c r="H129" s="110">
         <v>45638</v>
       </c>
       <c r="I129" s="112"/>
@@ -18693,10 +18693,10 @@
       <c r="B130" s="71"/>
       <c r="C130" s="91"/>
       <c r="D130" s="70"/>
-      <c r="E130" s="150"/>
-      <c r="F130" s="125"/>
-      <c r="G130" s="126"/>
-      <c r="H130" s="111"/>
+      <c r="E130" s="117"/>
+      <c r="F130" s="118"/>
+      <c r="G130" s="119"/>
+      <c r="H130" s="110"/>
       <c r="I130" s="112"/>
       <c r="J130" s="62"/>
       <c r="K130" s="20"/>
@@ -18814,16 +18814,16 @@
       <c r="A131" s="16"/>
       <c r="B131" s="71"/>
       <c r="C131" s="91"/>
-      <c r="D131" s="102" t="s">
+      <c r="D131" s="103" t="s">
         <v>79</v>
       </c>
-      <c r="E131" s="102"/>
-      <c r="F131" s="102"/>
-      <c r="G131" s="102"/>
-      <c r="H131" s="103">
+      <c r="E131" s="103"/>
+      <c r="F131" s="103"/>
+      <c r="G131" s="103"/>
+      <c r="H131" s="111">
         <v>45635</v>
       </c>
-      <c r="I131" s="109"/>
+      <c r="I131" s="113"/>
       <c r="J131" s="62"/>
       <c r="K131" s="20"/>
       <c r="L131" s="20"/>
@@ -18940,12 +18940,12 @@
       <c r="A132" s="16"/>
       <c r="B132" s="71"/>
       <c r="C132" s="90"/>
-      <c r="D132" s="102"/>
-      <c r="E132" s="102"/>
-      <c r="F132" s="102"/>
-      <c r="G132" s="102"/>
-      <c r="H132" s="104"/>
-      <c r="I132" s="110"/>
+      <c r="D132" s="103"/>
+      <c r="E132" s="103"/>
+      <c r="F132" s="103"/>
+      <c r="G132" s="103"/>
+      <c r="H132" s="107"/>
+      <c r="I132" s="143"/>
       <c r="J132" s="62"/>
       <c r="K132" s="20"/>
       <c r="L132" s="20"/>
@@ -19061,15 +19061,15 @@
     <row r="133" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A133" s="16"/>
       <c r="B133" s="36"/>
-      <c r="C133" s="115" t="s">
+      <c r="C133" s="132" t="s">
         <v>67</v>
       </c>
-      <c r="D133" s="116"/>
-      <c r="E133" s="116"/>
-      <c r="F133" s="116"/>
-      <c r="G133" s="117"/>
-      <c r="H133" s="191"/>
-      <c r="I133" s="107"/>
+      <c r="D133" s="133"/>
+      <c r="E133" s="133"/>
+      <c r="F133" s="133"/>
+      <c r="G133" s="134"/>
+      <c r="H133" s="121"/>
+      <c r="I133" s="123"/>
       <c r="J133" s="66"/>
       <c r="K133" s="64"/>
       <c r="L133" s="64"/>
@@ -19185,13 +19185,13 @@
     <row r="134" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A134" s="16"/>
       <c r="B134" s="36"/>
-      <c r="C134" s="118"/>
-      <c r="D134" s="119"/>
-      <c r="E134" s="119"/>
-      <c r="F134" s="119"/>
-      <c r="G134" s="120"/>
-      <c r="H134" s="192"/>
-      <c r="I134" s="108"/>
+      <c r="C134" s="135"/>
+      <c r="D134" s="136"/>
+      <c r="E134" s="136"/>
+      <c r="F134" s="136"/>
+      <c r="G134" s="137"/>
+      <c r="H134" s="122"/>
+      <c r="I134" s="124"/>
       <c r="J134" s="66"/>
       <c r="K134" s="64"/>
       <c r="L134" s="64"/>
@@ -19308,14 +19308,14 @@
       <c r="A135" s="16"/>
       <c r="B135" s="36"/>
       <c r="C135" s="60"/>
-      <c r="D135" s="115" t="s">
+      <c r="D135" s="132" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="116"/>
-      <c r="F135" s="116"/>
-      <c r="G135" s="117"/>
-      <c r="H135" s="113"/>
-      <c r="I135" s="181"/>
+      <c r="E135" s="133"/>
+      <c r="F135" s="133"/>
+      <c r="G135" s="134"/>
+      <c r="H135" s="193"/>
+      <c r="I135" s="129"/>
       <c r="J135" s="63"/>
       <c r="K135" s="64"/>
       <c r="L135" s="64"/>
@@ -19432,12 +19432,12 @@
       <c r="A136" s="16"/>
       <c r="B136" s="36"/>
       <c r="C136" s="60"/>
-      <c r="D136" s="118"/>
-      <c r="E136" s="119"/>
-      <c r="F136" s="119"/>
-      <c r="G136" s="120"/>
-      <c r="H136" s="130"/>
-      <c r="I136" s="183"/>
+      <c r="D136" s="135"/>
+      <c r="E136" s="136"/>
+      <c r="F136" s="136"/>
+      <c r="G136" s="137"/>
+      <c r="H136" s="198"/>
+      <c r="I136" s="144"/>
       <c r="J136" s="63"/>
       <c r="K136" s="64"/>
       <c r="L136" s="64"/>
@@ -19555,15 +19555,15 @@
       <c r="B137" s="36"/>
       <c r="C137" s="72"/>
       <c r="D137" s="74"/>
-      <c r="E137" s="121" t="s">
+      <c r="E137" s="115" t="s">
         <v>73</v>
       </c>
-      <c r="F137" s="121"/>
-      <c r="G137" s="122"/>
-      <c r="H137" s="103">
+      <c r="F137" s="115"/>
+      <c r="G137" s="116"/>
+      <c r="H137" s="111">
         <v>45636</v>
       </c>
-      <c r="I137" s="109"/>
+      <c r="I137" s="113"/>
       <c r="J137" s="62"/>
       <c r="K137" s="20"/>
       <c r="L137" s="20"/>
@@ -19681,11 +19681,11 @@
       <c r="B138" s="36"/>
       <c r="C138" s="72"/>
       <c r="D138" s="70"/>
-      <c r="E138" s="123"/>
-      <c r="F138" s="123"/>
-      <c r="G138" s="124"/>
-      <c r="H138" s="104"/>
-      <c r="I138" s="110"/>
+      <c r="E138" s="185"/>
+      <c r="F138" s="185"/>
+      <c r="G138" s="186"/>
+      <c r="H138" s="107"/>
+      <c r="I138" s="143"/>
       <c r="J138" s="62"/>
       <c r="K138" s="20"/>
       <c r="L138" s="20"/>
@@ -19803,15 +19803,15 @@
       <c r="B139" s="36"/>
       <c r="C139" s="72"/>
       <c r="D139" s="70"/>
-      <c r="E139" s="121" t="s">
+      <c r="E139" s="115" t="s">
         <v>74</v>
       </c>
-      <c r="F139" s="121"/>
-      <c r="G139" s="122"/>
-      <c r="H139" s="103">
+      <c r="F139" s="115"/>
+      <c r="G139" s="116"/>
+      <c r="H139" s="111">
         <v>45637</v>
       </c>
-      <c r="I139" s="109"/>
+      <c r="I139" s="113"/>
       <c r="J139" s="62"/>
       <c r="K139" s="20"/>
       <c r="L139" s="20"/>
@@ -19929,11 +19929,11 @@
       <c r="B140" s="36"/>
       <c r="C140" s="72"/>
       <c r="D140" s="70"/>
-      <c r="E140" s="125"/>
-      <c r="F140" s="125"/>
-      <c r="G140" s="126"/>
-      <c r="H140" s="104"/>
-      <c r="I140" s="110"/>
+      <c r="E140" s="118"/>
+      <c r="F140" s="118"/>
+      <c r="G140" s="119"/>
+      <c r="H140" s="107"/>
+      <c r="I140" s="143"/>
       <c r="J140" s="62"/>
       <c r="K140" s="20"/>
       <c r="L140" s="20"/>
@@ -20050,13 +20050,13 @@
       <c r="A141" s="16"/>
       <c r="B141" s="36"/>
       <c r="C141" s="82"/>
-      <c r="D141" s="102" t="s">
+      <c r="D141" s="103" t="s">
         <v>80</v>
       </c>
-      <c r="E141" s="102"/>
-      <c r="F141" s="102"/>
-      <c r="G141" s="102"/>
-      <c r="H141" s="103">
+      <c r="E141" s="103"/>
+      <c r="F141" s="103"/>
+      <c r="G141" s="103"/>
+      <c r="H141" s="111">
         <v>45637</v>
       </c>
       <c r="I141" s="92"/>
@@ -20176,11 +20176,11 @@
       <c r="A142" s="16"/>
       <c r="B142" s="36"/>
       <c r="C142" s="82"/>
-      <c r="D142" s="102"/>
-      <c r="E142" s="102"/>
-      <c r="F142" s="102"/>
-      <c r="G142" s="102"/>
-      <c r="H142" s="104"/>
+      <c r="D142" s="103"/>
+      <c r="E142" s="103"/>
+      <c r="F142" s="103"/>
+      <c r="G142" s="103"/>
+      <c r="H142" s="107"/>
       <c r="I142" s="92"/>
       <c r="J142" s="62"/>
       <c r="K142" s="20"/>
@@ -20298,14 +20298,14 @@
       <c r="A143" s="16"/>
       <c r="B143" s="36"/>
       <c r="C143" s="72"/>
-      <c r="D143" s="127" t="s">
+      <c r="D143" s="195" t="s">
         <v>66</v>
       </c>
-      <c r="E143" s="128"/>
-      <c r="F143" s="128"/>
-      <c r="G143" s="129"/>
-      <c r="H143" s="113"/>
-      <c r="I143" s="107"/>
+      <c r="E143" s="196"/>
+      <c r="F143" s="196"/>
+      <c r="G143" s="197"/>
+      <c r="H143" s="193"/>
+      <c r="I143" s="123"/>
       <c r="J143" s="66"/>
       <c r="K143" s="64"/>
       <c r="L143" s="64"/>
@@ -20422,12 +20422,12 @@
       <c r="A144" s="16"/>
       <c r="B144" s="36"/>
       <c r="C144" s="72"/>
-      <c r="D144" s="118"/>
-      <c r="E144" s="119"/>
-      <c r="F144" s="119"/>
-      <c r="G144" s="120"/>
-      <c r="H144" s="114"/>
-      <c r="I144" s="108"/>
+      <c r="D144" s="135"/>
+      <c r="E144" s="136"/>
+      <c r="F144" s="136"/>
+      <c r="G144" s="137"/>
+      <c r="H144" s="194"/>
+      <c r="I144" s="124"/>
       <c r="J144" s="66"/>
       <c r="K144" s="64"/>
       <c r="L144" s="64"/>
@@ -20545,15 +20545,15 @@
       <c r="B145" s="36"/>
       <c r="C145" s="72"/>
       <c r="D145" s="74"/>
-      <c r="E145" s="121" t="s">
+      <c r="E145" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="F145" s="121"/>
-      <c r="G145" s="122"/>
-      <c r="H145" s="103">
+      <c r="F145" s="115"/>
+      <c r="G145" s="116"/>
+      <c r="H145" s="111">
         <v>45639</v>
       </c>
-      <c r="I145" s="109"/>
+      <c r="I145" s="113"/>
       <c r="J145" s="62"/>
       <c r="K145" s="20"/>
       <c r="L145" s="20"/>
@@ -20671,11 +20671,11 @@
       <c r="B146" s="36"/>
       <c r="C146" s="72"/>
       <c r="D146" s="70"/>
-      <c r="E146" s="123"/>
-      <c r="F146" s="123"/>
-      <c r="G146" s="124"/>
-      <c r="H146" s="104"/>
-      <c r="I146" s="110"/>
+      <c r="E146" s="185"/>
+      <c r="F146" s="185"/>
+      <c r="G146" s="186"/>
+      <c r="H146" s="107"/>
+      <c r="I146" s="143"/>
       <c r="J146" s="62"/>
       <c r="K146" s="20"/>
       <c r="L146" s="20"/>
@@ -20793,15 +20793,15 @@
       <c r="B147" s="36"/>
       <c r="C147" s="72"/>
       <c r="D147" s="70"/>
-      <c r="E147" s="121" t="s">
+      <c r="E147" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="F147" s="121"/>
-      <c r="G147" s="122"/>
-      <c r="H147" s="103">
+      <c r="F147" s="115"/>
+      <c r="G147" s="116"/>
+      <c r="H147" s="111">
         <v>45642</v>
       </c>
-      <c r="I147" s="109"/>
+      <c r="I147" s="113"/>
       <c r="J147" s="62"/>
       <c r="K147" s="20"/>
       <c r="L147" s="20"/>
@@ -20919,11 +20919,11 @@
       <c r="B148" s="36"/>
       <c r="C148" s="72"/>
       <c r="D148" s="70"/>
-      <c r="E148" s="123"/>
-      <c r="F148" s="123"/>
-      <c r="G148" s="124"/>
-      <c r="H148" s="104"/>
-      <c r="I148" s="110"/>
+      <c r="E148" s="185"/>
+      <c r="F148" s="185"/>
+      <c r="G148" s="186"/>
+      <c r="H148" s="107"/>
+      <c r="I148" s="143"/>
       <c r="J148" s="62"/>
       <c r="K148" s="20"/>
       <c r="L148" s="20"/>
@@ -21041,15 +21041,15 @@
       <c r="B149" s="36"/>
       <c r="C149" s="72"/>
       <c r="D149" s="70"/>
-      <c r="E149" s="121" t="s">
+      <c r="E149" s="115" t="s">
         <v>70</v>
       </c>
-      <c r="F149" s="121"/>
-      <c r="G149" s="122"/>
-      <c r="H149" s="103">
+      <c r="F149" s="115"/>
+      <c r="G149" s="116"/>
+      <c r="H149" s="111">
         <v>45643</v>
       </c>
-      <c r="I149" s="109"/>
+      <c r="I149" s="113"/>
       <c r="J149" s="62"/>
       <c r="K149" s="20"/>
       <c r="L149" s="20"/>
@@ -21167,11 +21167,11 @@
       <c r="B150" s="36"/>
       <c r="C150" s="72"/>
       <c r="D150" s="70"/>
-      <c r="E150" s="123"/>
-      <c r="F150" s="123"/>
-      <c r="G150" s="124"/>
-      <c r="H150" s="104"/>
-      <c r="I150" s="110"/>
+      <c r="E150" s="185"/>
+      <c r="F150" s="185"/>
+      <c r="G150" s="186"/>
+      <c r="H150" s="107"/>
+      <c r="I150" s="143"/>
       <c r="J150" s="62"/>
       <c r="K150" s="20"/>
       <c r="L150" s="20"/>
@@ -21289,15 +21289,15 @@
       <c r="B151" s="36"/>
       <c r="C151" s="72"/>
       <c r="D151" s="70"/>
-      <c r="E151" s="102" t="s">
+      <c r="E151" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="F151" s="102"/>
-      <c r="G151" s="102"/>
-      <c r="H151" s="103">
+      <c r="F151" s="103"/>
+      <c r="G151" s="103"/>
+      <c r="H151" s="111">
         <v>45644</v>
       </c>
-      <c r="I151" s="109"/>
+      <c r="I151" s="113"/>
       <c r="J151" s="62"/>
       <c r="K151" s="20"/>
       <c r="L151" s="20"/>
@@ -21415,11 +21415,11 @@
       <c r="B152" s="36"/>
       <c r="C152" s="72"/>
       <c r="D152" s="70"/>
-      <c r="E152" s="102"/>
-      <c r="F152" s="102"/>
-      <c r="G152" s="102"/>
-      <c r="H152" s="104"/>
-      <c r="I152" s="110"/>
+      <c r="E152" s="103"/>
+      <c r="F152" s="103"/>
+      <c r="G152" s="103"/>
+      <c r="H152" s="107"/>
+      <c r="I152" s="143"/>
       <c r="J152" s="62"/>
       <c r="K152" s="20"/>
       <c r="L152" s="20"/>
@@ -21537,15 +21537,15 @@
       <c r="B153" s="36"/>
       <c r="C153" s="72"/>
       <c r="D153" s="70"/>
-      <c r="E153" s="102" t="s">
+      <c r="E153" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="F153" s="102"/>
-      <c r="G153" s="102"/>
-      <c r="H153" s="103">
+      <c r="F153" s="103"/>
+      <c r="G153" s="103"/>
+      <c r="H153" s="111">
         <v>45644</v>
       </c>
-      <c r="I153" s="109"/>
+      <c r="I153" s="113"/>
       <c r="J153" s="62"/>
       <c r="K153" s="20"/>
       <c r="L153" s="20"/>
@@ -21663,11 +21663,11 @@
       <c r="B154" s="36"/>
       <c r="C154" s="72"/>
       <c r="D154" s="70"/>
-      <c r="E154" s="102"/>
-      <c r="F154" s="102"/>
-      <c r="G154" s="102"/>
-      <c r="H154" s="104"/>
-      <c r="I154" s="110"/>
+      <c r="E154" s="103"/>
+      <c r="F154" s="103"/>
+      <c r="G154" s="103"/>
+      <c r="H154" s="107"/>
+      <c r="I154" s="143"/>
       <c r="J154" s="62"/>
       <c r="K154" s="20"/>
       <c r="L154" s="20"/>
@@ -21784,16 +21784,16 @@
       <c r="A155" s="1"/>
       <c r="B155" s="18"/>
       <c r="C155" s="60"/>
-      <c r="D155" s="194"/>
-      <c r="E155" s="193" t="s">
+      <c r="D155" s="104"/>
+      <c r="E155" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="F155" s="102"/>
-      <c r="G155" s="102"/>
-      <c r="H155" s="195">
+      <c r="F155" s="103"/>
+      <c r="G155" s="103"/>
+      <c r="H155" s="106">
         <v>45645</v>
       </c>
-      <c r="I155" s="196"/>
+      <c r="I155" s="108"/>
       <c r="J155" s="19"/>
       <c r="K155" s="20"/>
       <c r="L155" s="20"/>
@@ -21910,12 +21910,12 @@
       <c r="A156" s="1"/>
       <c r="B156" s="18"/>
       <c r="C156" s="60"/>
-      <c r="D156" s="149"/>
-      <c r="E156" s="193"/>
-      <c r="F156" s="102"/>
-      <c r="G156" s="102"/>
-      <c r="H156" s="104"/>
-      <c r="I156" s="106"/>
+      <c r="D156" s="105"/>
+      <c r="E156" s="102"/>
+      <c r="F156" s="103"/>
+      <c r="G156" s="103"/>
+      <c r="H156" s="107"/>
+      <c r="I156" s="109"/>
       <c r="J156" s="19"/>
       <c r="K156" s="20"/>
       <c r="L156" s="20"/>
@@ -22032,16 +22032,16 @@
       <c r="A157" s="1"/>
       <c r="B157" s="93"/>
       <c r="C157" s="90"/>
-      <c r="D157" s="102" t="s">
+      <c r="D157" s="103" t="s">
         <v>81</v>
       </c>
-      <c r="E157" s="102"/>
-      <c r="F157" s="102"/>
-      <c r="G157" s="102"/>
-      <c r="H157" s="103">
+      <c r="E157" s="103"/>
+      <c r="F157" s="103"/>
+      <c r="G157" s="103"/>
+      <c r="H157" s="111">
         <v>45644</v>
       </c>
-      <c r="I157" s="105"/>
+      <c r="I157" s="126"/>
       <c r="J157" s="19"/>
       <c r="K157" s="20"/>
       <c r="L157" s="20"/>
@@ -22158,12 +22158,12 @@
       <c r="A158" s="1"/>
       <c r="B158" s="93"/>
       <c r="C158" s="90"/>
-      <c r="D158" s="102"/>
-      <c r="E158" s="102"/>
-      <c r="F158" s="102"/>
-      <c r="G158" s="102"/>
-      <c r="H158" s="104"/>
-      <c r="I158" s="106"/>
+      <c r="D158" s="103"/>
+      <c r="E158" s="103"/>
+      <c r="F158" s="103"/>
+      <c r="G158" s="103"/>
+      <c r="H158" s="107"/>
+      <c r="I158" s="109"/>
       <c r="J158" s="19"/>
       <c r="K158" s="20"/>
       <c r="L158" s="20"/>
@@ -22281,14 +22281,14 @@
       <c r="B159" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="C159" s="173" t="s">
+      <c r="C159" s="151" t="s">
         <v>31</v>
       </c>
-      <c r="D159" s="174"/>
-      <c r="E159" s="174"/>
-      <c r="F159" s="174"/>
-      <c r="G159" s="175"/>
-      <c r="H159" s="184" t="s">
+      <c r="D159" s="152"/>
+      <c r="E159" s="152"/>
+      <c r="F159" s="152"/>
+      <c r="G159" s="153"/>
+      <c r="H159" s="138" t="s">
         <v>57</v>
       </c>
       <c r="I159" s="112"/>
@@ -22407,11 +22407,11 @@
     <row r="160" spans="1:120" ht="9.75" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="87"/>
-      <c r="C160" s="176"/>
-      <c r="D160" s="177"/>
-      <c r="E160" s="177"/>
-      <c r="F160" s="177"/>
-      <c r="G160" s="178"/>
+      <c r="C160" s="154"/>
+      <c r="D160" s="155"/>
+      <c r="E160" s="155"/>
+      <c r="F160" s="155"/>
+      <c r="G160" s="156"/>
       <c r="H160" s="112"/>
       <c r="I160" s="112"/>
       <c r="J160" s="14"/>
@@ -22773,14 +22773,14 @@
     <row r="163" spans="1:120" ht="9.75" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
-      <c r="C163" s="168" t="s">
+      <c r="C163" s="145" t="s">
         <v>33</v>
       </c>
-      <c r="D163" s="140"/>
-      <c r="E163" s="140"/>
-      <c r="F163" s="140"/>
-      <c r="G163" s="169"/>
-      <c r="H163" s="184" t="s">
+      <c r="D163" s="146"/>
+      <c r="E163" s="146"/>
+      <c r="F163" s="146"/>
+      <c r="G163" s="147"/>
+      <c r="H163" s="138" t="s">
         <v>56</v>
       </c>
       <c r="I163" s="112"/>
@@ -22899,11 +22899,11 @@
     <row r="164" spans="1:120" ht="9.75" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
-      <c r="C164" s="170"/>
-      <c r="D164" s="171"/>
-      <c r="E164" s="171"/>
-      <c r="F164" s="171"/>
-      <c r="G164" s="172"/>
+      <c r="C164" s="148"/>
+      <c r="D164" s="149"/>
+      <c r="E164" s="149"/>
+      <c r="F164" s="149"/>
+      <c r="G164" s="150"/>
       <c r="H164" s="112"/>
       <c r="I164" s="112"/>
       <c r="J164" s="19"/>
@@ -36444,6 +36444,222 @@
     </row>
   </sheetData>
   <mergeCells count="240">
+    <mergeCell ref="D157:G158"/>
+    <mergeCell ref="H157:H158"/>
+    <mergeCell ref="I157:I158"/>
+    <mergeCell ref="H141:H142"/>
+    <mergeCell ref="I143:I144"/>
+    <mergeCell ref="I139:I140"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="H103:H104"/>
+    <mergeCell ref="I103:I104"/>
+    <mergeCell ref="H115:H116"/>
+    <mergeCell ref="I115:I116"/>
+    <mergeCell ref="D103:G104"/>
+    <mergeCell ref="D115:G116"/>
+    <mergeCell ref="D131:G132"/>
+    <mergeCell ref="H131:H132"/>
+    <mergeCell ref="I131:I132"/>
+    <mergeCell ref="D87:G88"/>
+    <mergeCell ref="D141:G142"/>
+    <mergeCell ref="E153:G154"/>
+    <mergeCell ref="H153:H154"/>
+    <mergeCell ref="H151:H152"/>
+    <mergeCell ref="H149:H150"/>
+    <mergeCell ref="H147:H148"/>
+    <mergeCell ref="H145:H146"/>
+    <mergeCell ref="H143:H144"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="C133:G134"/>
+    <mergeCell ref="D135:G136"/>
+    <mergeCell ref="E137:G138"/>
+    <mergeCell ref="E139:G140"/>
+    <mergeCell ref="D143:G144"/>
+    <mergeCell ref="E145:G146"/>
+    <mergeCell ref="H135:H136"/>
+    <mergeCell ref="E147:G148"/>
+    <mergeCell ref="E149:G150"/>
+    <mergeCell ref="E151:G152"/>
+    <mergeCell ref="E59:G60"/>
+    <mergeCell ref="E61:G62"/>
+    <mergeCell ref="D63:G64"/>
+    <mergeCell ref="E67:G68"/>
+    <mergeCell ref="E65:G66"/>
+    <mergeCell ref="E69:G70"/>
+    <mergeCell ref="E71:G72"/>
+    <mergeCell ref="C73:G74"/>
+    <mergeCell ref="C75:G76"/>
+    <mergeCell ref="C77:G78"/>
+    <mergeCell ref="D79:G80"/>
+    <mergeCell ref="E109:G110"/>
+    <mergeCell ref="E111:G112"/>
+    <mergeCell ref="E101:G102"/>
+    <mergeCell ref="C105:G106"/>
+    <mergeCell ref="D107:G108"/>
+    <mergeCell ref="D117:G118"/>
+    <mergeCell ref="D13:G14"/>
+    <mergeCell ref="D15:G16"/>
+    <mergeCell ref="D17:G18"/>
+    <mergeCell ref="D19:G20"/>
+    <mergeCell ref="C21:G22"/>
+    <mergeCell ref="D23:G24"/>
+    <mergeCell ref="C25:G26"/>
+    <mergeCell ref="D27:G28"/>
+    <mergeCell ref="D29:G30"/>
+    <mergeCell ref="J3:CJ3"/>
+    <mergeCell ref="CK3:DO3"/>
+    <mergeCell ref="J4:AA4"/>
+    <mergeCell ref="AB4:BE4"/>
+    <mergeCell ref="BF4:CJ4"/>
+    <mergeCell ref="CK4:DO4"/>
+    <mergeCell ref="B7:G8"/>
+    <mergeCell ref="C9:G10"/>
+    <mergeCell ref="C11:G12"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="C163:G164"/>
+    <mergeCell ref="C159:G160"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="C31:G32"/>
+    <mergeCell ref="D33:G34"/>
+    <mergeCell ref="E35:G36"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="E43:G44"/>
+    <mergeCell ref="E45:G46"/>
+    <mergeCell ref="E47:G48"/>
+    <mergeCell ref="E49:G50"/>
+    <mergeCell ref="E51:G52"/>
+    <mergeCell ref="D53:G54"/>
+    <mergeCell ref="E55:G56"/>
+    <mergeCell ref="E57:G58"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I67:I68"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="I159:I160"/>
+    <mergeCell ref="I161:I162"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="I93:I94"/>
+    <mergeCell ref="I95:I96"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="I109:I110"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="I153:I154"/>
+    <mergeCell ref="I151:I152"/>
+    <mergeCell ref="I149:I150"/>
+    <mergeCell ref="I147:I148"/>
+    <mergeCell ref="I145:I146"/>
+    <mergeCell ref="I111:I112"/>
+    <mergeCell ref="I135:I136"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="I163:I164"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="H75:H76"/>
+    <mergeCell ref="H159:H160"/>
+    <mergeCell ref="H163:H164"/>
+    <mergeCell ref="H161:H162"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="H59:H60"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="H77:H78"/>
+    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="H93:H94"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="H111:H112"/>
+    <mergeCell ref="H101:H102"/>
+    <mergeCell ref="I101:I102"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="I85:I86"/>
+    <mergeCell ref="H89:H90"/>
+    <mergeCell ref="I89:I90"/>
+    <mergeCell ref="E81:G82"/>
+    <mergeCell ref="E83:G84"/>
+    <mergeCell ref="E91:G92"/>
+    <mergeCell ref="E93:G94"/>
+    <mergeCell ref="E95:G96"/>
+    <mergeCell ref="E97:G98"/>
+    <mergeCell ref="E99:G100"/>
+    <mergeCell ref="E85:G86"/>
+    <mergeCell ref="D89:G90"/>
+    <mergeCell ref="H105:H106"/>
+    <mergeCell ref="I105:I106"/>
+    <mergeCell ref="H107:H108"/>
+    <mergeCell ref="I107:I108"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="H117:H118"/>
+    <mergeCell ref="I117:I118"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="I119:I120"/>
     <mergeCell ref="E155:G156"/>
     <mergeCell ref="D155:D156"/>
     <mergeCell ref="H155:H156"/>
@@ -36468,222 +36684,6 @@
     <mergeCell ref="H127:H128"/>
     <mergeCell ref="I127:I128"/>
     <mergeCell ref="H121:H122"/>
-    <mergeCell ref="H105:H106"/>
-    <mergeCell ref="I105:I106"/>
-    <mergeCell ref="H107:H108"/>
-    <mergeCell ref="I107:I108"/>
-    <mergeCell ref="H109:H110"/>
-    <mergeCell ref="H117:H118"/>
-    <mergeCell ref="I117:I118"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="I119:I120"/>
-    <mergeCell ref="H101:H102"/>
-    <mergeCell ref="I101:I102"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="I85:I86"/>
-    <mergeCell ref="H89:H90"/>
-    <mergeCell ref="I89:I90"/>
-    <mergeCell ref="E81:G82"/>
-    <mergeCell ref="E83:G84"/>
-    <mergeCell ref="E91:G92"/>
-    <mergeCell ref="E93:G94"/>
-    <mergeCell ref="E95:G96"/>
-    <mergeCell ref="E97:G98"/>
-    <mergeCell ref="E99:G100"/>
-    <mergeCell ref="E85:G86"/>
-    <mergeCell ref="D89:G90"/>
-    <mergeCell ref="H75:H76"/>
-    <mergeCell ref="H159:H160"/>
-    <mergeCell ref="H163:H164"/>
-    <mergeCell ref="H161:H162"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="H67:H68"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H59:H60"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="H77:H78"/>
-    <mergeCell ref="H81:H82"/>
-    <mergeCell ref="H83:H84"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="H93:H94"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="H111:H112"/>
-    <mergeCell ref="I163:I164"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="I159:I160"/>
-    <mergeCell ref="I161:I162"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="I93:I94"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="I109:I110"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="I153:I154"/>
-    <mergeCell ref="I151:I152"/>
-    <mergeCell ref="I149:I150"/>
-    <mergeCell ref="I147:I148"/>
-    <mergeCell ref="I145:I146"/>
-    <mergeCell ref="I111:I112"/>
-    <mergeCell ref="I135:I136"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="C163:G164"/>
-    <mergeCell ref="C159:G160"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="C31:G32"/>
-    <mergeCell ref="D33:G34"/>
-    <mergeCell ref="E35:G36"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="E43:G44"/>
-    <mergeCell ref="E45:G46"/>
-    <mergeCell ref="E47:G48"/>
-    <mergeCell ref="E49:G50"/>
-    <mergeCell ref="E51:G52"/>
-    <mergeCell ref="D53:G54"/>
-    <mergeCell ref="E55:G56"/>
-    <mergeCell ref="E57:G58"/>
-    <mergeCell ref="I53:I54"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="J3:CJ3"/>
-    <mergeCell ref="CK3:DO3"/>
-    <mergeCell ref="J4:AA4"/>
-    <mergeCell ref="AB4:BE4"/>
-    <mergeCell ref="BF4:CJ4"/>
-    <mergeCell ref="CK4:DO4"/>
-    <mergeCell ref="B7:G8"/>
-    <mergeCell ref="C9:G10"/>
-    <mergeCell ref="C11:G12"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="D13:G14"/>
-    <mergeCell ref="D15:G16"/>
-    <mergeCell ref="D17:G18"/>
-    <mergeCell ref="D19:G20"/>
-    <mergeCell ref="C21:G22"/>
-    <mergeCell ref="D23:G24"/>
-    <mergeCell ref="C25:G26"/>
-    <mergeCell ref="D27:G28"/>
-    <mergeCell ref="D29:G30"/>
-    <mergeCell ref="E147:G148"/>
-    <mergeCell ref="E149:G150"/>
-    <mergeCell ref="E151:G152"/>
-    <mergeCell ref="E59:G60"/>
-    <mergeCell ref="E61:G62"/>
-    <mergeCell ref="D63:G64"/>
-    <mergeCell ref="E67:G68"/>
-    <mergeCell ref="E65:G66"/>
-    <mergeCell ref="E69:G70"/>
-    <mergeCell ref="E71:G72"/>
-    <mergeCell ref="C73:G74"/>
-    <mergeCell ref="C75:G76"/>
-    <mergeCell ref="C77:G78"/>
-    <mergeCell ref="D79:G80"/>
-    <mergeCell ref="E109:G110"/>
-    <mergeCell ref="E111:G112"/>
-    <mergeCell ref="E101:G102"/>
-    <mergeCell ref="C105:G106"/>
-    <mergeCell ref="D107:G108"/>
-    <mergeCell ref="D117:G118"/>
-    <mergeCell ref="H145:H146"/>
-    <mergeCell ref="H143:H144"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="C133:G134"/>
-    <mergeCell ref="D135:G136"/>
-    <mergeCell ref="E137:G138"/>
-    <mergeCell ref="E139:G140"/>
-    <mergeCell ref="D143:G144"/>
-    <mergeCell ref="E145:G146"/>
-    <mergeCell ref="H135:H136"/>
-    <mergeCell ref="D157:G158"/>
-    <mergeCell ref="H157:H158"/>
-    <mergeCell ref="I157:I158"/>
-    <mergeCell ref="H141:H142"/>
-    <mergeCell ref="I143:I144"/>
-    <mergeCell ref="I139:I140"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="H103:H104"/>
-    <mergeCell ref="I103:I104"/>
-    <mergeCell ref="H115:H116"/>
-    <mergeCell ref="I115:I116"/>
-    <mergeCell ref="D103:G104"/>
-    <mergeCell ref="D115:G116"/>
-    <mergeCell ref="D131:G132"/>
-    <mergeCell ref="H131:H132"/>
-    <mergeCell ref="I131:I132"/>
-    <mergeCell ref="D87:G88"/>
-    <mergeCell ref="D141:G142"/>
-    <mergeCell ref="E153:G154"/>
-    <mergeCell ref="H153:H154"/>
-    <mergeCell ref="H151:H152"/>
-    <mergeCell ref="H149:H150"/>
-    <mergeCell ref="H147:H148"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <conditionalFormatting sqref="J7">

--- a/docs/【DIGITAL OJT】WBS.xlsx
+++ b/docs/【DIGITAL OJT】WBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIGITALOJT\digital-ojt-development-cause-DroneInventorySystem\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18E6B07-F9D4-41BB-B450-6557E9B8DF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E68E0814-A123-4CD7-A47C-8E463D9C6F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -1489,67 +1489,19 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1558,25 +1510,22 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1597,29 +1546,110 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1645,92 +1675,62 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2350,120 +2350,120 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="J3" s="173">
+      <c r="J3" s="161">
         <v>2024</v>
       </c>
-      <c r="K3" s="174"/>
-      <c r="L3" s="174"/>
-      <c r="M3" s="174"/>
-      <c r="N3" s="174"/>
-      <c r="O3" s="174"/>
-      <c r="P3" s="174"/>
-      <c r="Q3" s="174"/>
-      <c r="R3" s="174"/>
-      <c r="S3" s="174"/>
-      <c r="T3" s="174"/>
-      <c r="U3" s="174"/>
-      <c r="V3" s="174"/>
-      <c r="W3" s="174"/>
-      <c r="X3" s="174"/>
-      <c r="Y3" s="174"/>
-      <c r="Z3" s="174"/>
-      <c r="AA3" s="174"/>
-      <c r="AB3" s="174"/>
-      <c r="AC3" s="174"/>
-      <c r="AD3" s="174"/>
-      <c r="AE3" s="174"/>
-      <c r="AF3" s="174"/>
-      <c r="AG3" s="174"/>
-      <c r="AH3" s="174"/>
-      <c r="AI3" s="174"/>
-      <c r="AJ3" s="174"/>
-      <c r="AK3" s="174"/>
-      <c r="AL3" s="174"/>
-      <c r="AM3" s="174"/>
-      <c r="AN3" s="174"/>
-      <c r="AO3" s="174"/>
-      <c r="AP3" s="174"/>
-      <c r="AQ3" s="174"/>
-      <c r="AR3" s="174"/>
-      <c r="AS3" s="174"/>
-      <c r="AT3" s="174"/>
-      <c r="AU3" s="174"/>
-      <c r="AV3" s="174"/>
-      <c r="AW3" s="174"/>
-      <c r="AX3" s="174"/>
-      <c r="AY3" s="174"/>
-      <c r="AZ3" s="174"/>
-      <c r="BA3" s="174"/>
-      <c r="BB3" s="174"/>
-      <c r="BC3" s="174"/>
-      <c r="BD3" s="174"/>
-      <c r="BE3" s="174"/>
-      <c r="BF3" s="174"/>
-      <c r="BG3" s="174"/>
-      <c r="BH3" s="174"/>
-      <c r="BI3" s="174"/>
-      <c r="BJ3" s="174"/>
-      <c r="BK3" s="174"/>
-      <c r="BL3" s="174"/>
-      <c r="BM3" s="174"/>
-      <c r="BN3" s="174"/>
-      <c r="BO3" s="174"/>
-      <c r="BP3" s="174"/>
-      <c r="BQ3" s="174"/>
-      <c r="BR3" s="174"/>
-      <c r="BS3" s="174"/>
-      <c r="BT3" s="174"/>
-      <c r="BU3" s="174"/>
-      <c r="BV3" s="174"/>
-      <c r="BW3" s="174"/>
-      <c r="BX3" s="174"/>
-      <c r="BY3" s="174"/>
-      <c r="BZ3" s="174"/>
-      <c r="CA3" s="174"/>
-      <c r="CB3" s="174"/>
-      <c r="CC3" s="174"/>
-      <c r="CD3" s="174"/>
-      <c r="CE3" s="174"/>
-      <c r="CF3" s="174"/>
-      <c r="CG3" s="174"/>
-      <c r="CH3" s="174"/>
-      <c r="CI3" s="174"/>
-      <c r="CJ3" s="175"/>
-      <c r="CK3" s="173">
+      <c r="K3" s="162"/>
+      <c r="L3" s="162"/>
+      <c r="M3" s="162"/>
+      <c r="N3" s="162"/>
+      <c r="O3" s="162"/>
+      <c r="P3" s="162"/>
+      <c r="Q3" s="162"/>
+      <c r="R3" s="162"/>
+      <c r="S3" s="162"/>
+      <c r="T3" s="162"/>
+      <c r="U3" s="162"/>
+      <c r="V3" s="162"/>
+      <c r="W3" s="162"/>
+      <c r="X3" s="162"/>
+      <c r="Y3" s="162"/>
+      <c r="Z3" s="162"/>
+      <c r="AA3" s="162"/>
+      <c r="AB3" s="162"/>
+      <c r="AC3" s="162"/>
+      <c r="AD3" s="162"/>
+      <c r="AE3" s="162"/>
+      <c r="AF3" s="162"/>
+      <c r="AG3" s="162"/>
+      <c r="AH3" s="162"/>
+      <c r="AI3" s="162"/>
+      <c r="AJ3" s="162"/>
+      <c r="AK3" s="162"/>
+      <c r="AL3" s="162"/>
+      <c r="AM3" s="162"/>
+      <c r="AN3" s="162"/>
+      <c r="AO3" s="162"/>
+      <c r="AP3" s="162"/>
+      <c r="AQ3" s="162"/>
+      <c r="AR3" s="162"/>
+      <c r="AS3" s="162"/>
+      <c r="AT3" s="162"/>
+      <c r="AU3" s="162"/>
+      <c r="AV3" s="162"/>
+      <c r="AW3" s="162"/>
+      <c r="AX3" s="162"/>
+      <c r="AY3" s="162"/>
+      <c r="AZ3" s="162"/>
+      <c r="BA3" s="162"/>
+      <c r="BB3" s="162"/>
+      <c r="BC3" s="162"/>
+      <c r="BD3" s="162"/>
+      <c r="BE3" s="162"/>
+      <c r="BF3" s="162"/>
+      <c r="BG3" s="162"/>
+      <c r="BH3" s="162"/>
+      <c r="BI3" s="162"/>
+      <c r="BJ3" s="162"/>
+      <c r="BK3" s="162"/>
+      <c r="BL3" s="162"/>
+      <c r="BM3" s="162"/>
+      <c r="BN3" s="162"/>
+      <c r="BO3" s="162"/>
+      <c r="BP3" s="162"/>
+      <c r="BQ3" s="162"/>
+      <c r="BR3" s="162"/>
+      <c r="BS3" s="162"/>
+      <c r="BT3" s="162"/>
+      <c r="BU3" s="162"/>
+      <c r="BV3" s="162"/>
+      <c r="BW3" s="162"/>
+      <c r="BX3" s="162"/>
+      <c r="BY3" s="162"/>
+      <c r="BZ3" s="162"/>
+      <c r="CA3" s="162"/>
+      <c r="CB3" s="162"/>
+      <c r="CC3" s="162"/>
+      <c r="CD3" s="162"/>
+      <c r="CE3" s="162"/>
+      <c r="CF3" s="162"/>
+      <c r="CG3" s="162"/>
+      <c r="CH3" s="162"/>
+      <c r="CI3" s="162"/>
+      <c r="CJ3" s="163"/>
+      <c r="CK3" s="161">
         <v>2025</v>
       </c>
-      <c r="CL3" s="174"/>
-      <c r="CM3" s="174"/>
-      <c r="CN3" s="174"/>
-      <c r="CO3" s="174"/>
-      <c r="CP3" s="174"/>
-      <c r="CQ3" s="174"/>
-      <c r="CR3" s="174"/>
-      <c r="CS3" s="174"/>
-      <c r="CT3" s="174"/>
-      <c r="CU3" s="174"/>
-      <c r="CV3" s="174"/>
-      <c r="CW3" s="174"/>
-      <c r="CX3" s="174"/>
-      <c r="CY3" s="174"/>
-      <c r="CZ3" s="174"/>
-      <c r="DA3" s="174"/>
-      <c r="DB3" s="174"/>
-      <c r="DC3" s="174"/>
-      <c r="DD3" s="174"/>
-      <c r="DE3" s="174"/>
-      <c r="DF3" s="174"/>
-      <c r="DG3" s="174"/>
-      <c r="DH3" s="174"/>
-      <c r="DI3" s="174"/>
-      <c r="DJ3" s="174"/>
-      <c r="DK3" s="174"/>
-      <c r="DL3" s="174"/>
-      <c r="DM3" s="174"/>
-      <c r="DN3" s="174"/>
-      <c r="DO3" s="175"/>
+      <c r="CL3" s="162"/>
+      <c r="CM3" s="162"/>
+      <c r="CN3" s="162"/>
+      <c r="CO3" s="162"/>
+      <c r="CP3" s="162"/>
+      <c r="CQ3" s="162"/>
+      <c r="CR3" s="162"/>
+      <c r="CS3" s="162"/>
+      <c r="CT3" s="162"/>
+      <c r="CU3" s="162"/>
+      <c r="CV3" s="162"/>
+      <c r="CW3" s="162"/>
+      <c r="CX3" s="162"/>
+      <c r="CY3" s="162"/>
+      <c r="CZ3" s="162"/>
+      <c r="DA3" s="162"/>
+      <c r="DB3" s="162"/>
+      <c r="DC3" s="162"/>
+      <c r="DD3" s="162"/>
+      <c r="DE3" s="162"/>
+      <c r="DF3" s="162"/>
+      <c r="DG3" s="162"/>
+      <c r="DH3" s="162"/>
+      <c r="DI3" s="162"/>
+      <c r="DJ3" s="162"/>
+      <c r="DK3" s="162"/>
+      <c r="DL3" s="162"/>
+      <c r="DM3" s="162"/>
+      <c r="DN3" s="162"/>
+      <c r="DO3" s="163"/>
       <c r="DP3" s="1"/>
     </row>
     <row r="4" spans="1:120" ht="18" customHeight="1">
@@ -2478,124 +2478,124 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="J4" s="173">
+      <c r="J4" s="161">
         <v>10</v>
       </c>
-      <c r="K4" s="174"/>
-      <c r="L4" s="174"/>
-      <c r="M4" s="174"/>
-      <c r="N4" s="174"/>
-      <c r="O4" s="174"/>
-      <c r="P4" s="174"/>
-      <c r="Q4" s="174"/>
-      <c r="R4" s="174"/>
-      <c r="S4" s="174"/>
-      <c r="T4" s="174"/>
-      <c r="U4" s="174"/>
-      <c r="V4" s="174"/>
-      <c r="W4" s="174"/>
-      <c r="X4" s="174"/>
-      <c r="Y4" s="174"/>
-      <c r="Z4" s="174"/>
-      <c r="AA4" s="175"/>
-      <c r="AB4" s="173">
+      <c r="K4" s="162"/>
+      <c r="L4" s="162"/>
+      <c r="M4" s="162"/>
+      <c r="N4" s="162"/>
+      <c r="O4" s="162"/>
+      <c r="P4" s="162"/>
+      <c r="Q4" s="162"/>
+      <c r="R4" s="162"/>
+      <c r="S4" s="162"/>
+      <c r="T4" s="162"/>
+      <c r="U4" s="162"/>
+      <c r="V4" s="162"/>
+      <c r="W4" s="162"/>
+      <c r="X4" s="162"/>
+      <c r="Y4" s="162"/>
+      <c r="Z4" s="162"/>
+      <c r="AA4" s="163"/>
+      <c r="AB4" s="161">
         <v>11</v>
       </c>
-      <c r="AC4" s="174"/>
-      <c r="AD4" s="174"/>
-      <c r="AE4" s="174"/>
-      <c r="AF4" s="174"/>
-      <c r="AG4" s="174"/>
-      <c r="AH4" s="174"/>
-      <c r="AI4" s="174"/>
-      <c r="AJ4" s="174"/>
-      <c r="AK4" s="174"/>
-      <c r="AL4" s="174"/>
-      <c r="AM4" s="174"/>
-      <c r="AN4" s="174"/>
-      <c r="AO4" s="174"/>
-      <c r="AP4" s="174"/>
-      <c r="AQ4" s="174"/>
-      <c r="AR4" s="174"/>
-      <c r="AS4" s="174"/>
-      <c r="AT4" s="174"/>
-      <c r="AU4" s="174"/>
-      <c r="AV4" s="174"/>
-      <c r="AW4" s="174"/>
-      <c r="AX4" s="174"/>
-      <c r="AY4" s="174"/>
-      <c r="AZ4" s="174"/>
-      <c r="BA4" s="174"/>
-      <c r="BB4" s="174"/>
-      <c r="BC4" s="174"/>
-      <c r="BD4" s="174"/>
-      <c r="BE4" s="175"/>
-      <c r="BF4" s="173">
+      <c r="AC4" s="162"/>
+      <c r="AD4" s="162"/>
+      <c r="AE4" s="162"/>
+      <c r="AF4" s="162"/>
+      <c r="AG4" s="162"/>
+      <c r="AH4" s="162"/>
+      <c r="AI4" s="162"/>
+      <c r="AJ4" s="162"/>
+      <c r="AK4" s="162"/>
+      <c r="AL4" s="162"/>
+      <c r="AM4" s="162"/>
+      <c r="AN4" s="162"/>
+      <c r="AO4" s="162"/>
+      <c r="AP4" s="162"/>
+      <c r="AQ4" s="162"/>
+      <c r="AR4" s="162"/>
+      <c r="AS4" s="162"/>
+      <c r="AT4" s="162"/>
+      <c r="AU4" s="162"/>
+      <c r="AV4" s="162"/>
+      <c r="AW4" s="162"/>
+      <c r="AX4" s="162"/>
+      <c r="AY4" s="162"/>
+      <c r="AZ4" s="162"/>
+      <c r="BA4" s="162"/>
+      <c r="BB4" s="162"/>
+      <c r="BC4" s="162"/>
+      <c r="BD4" s="162"/>
+      <c r="BE4" s="163"/>
+      <c r="BF4" s="161">
         <v>12</v>
       </c>
-      <c r="BG4" s="174"/>
-      <c r="BH4" s="174"/>
-      <c r="BI4" s="174"/>
-      <c r="BJ4" s="174"/>
-      <c r="BK4" s="174"/>
-      <c r="BL4" s="174"/>
-      <c r="BM4" s="174"/>
-      <c r="BN4" s="174"/>
-      <c r="BO4" s="174"/>
-      <c r="BP4" s="174"/>
-      <c r="BQ4" s="174"/>
-      <c r="BR4" s="174"/>
-      <c r="BS4" s="174"/>
-      <c r="BT4" s="174"/>
-      <c r="BU4" s="174"/>
-      <c r="BV4" s="174"/>
-      <c r="BW4" s="174"/>
-      <c r="BX4" s="174"/>
-      <c r="BY4" s="174"/>
-      <c r="BZ4" s="174"/>
-      <c r="CA4" s="174"/>
-      <c r="CB4" s="174"/>
-      <c r="CC4" s="174"/>
-      <c r="CD4" s="174"/>
-      <c r="CE4" s="174"/>
-      <c r="CF4" s="174"/>
-      <c r="CG4" s="174"/>
-      <c r="CH4" s="174"/>
-      <c r="CI4" s="174"/>
-      <c r="CJ4" s="175"/>
-      <c r="CK4" s="173">
+      <c r="BG4" s="162"/>
+      <c r="BH4" s="162"/>
+      <c r="BI4" s="162"/>
+      <c r="BJ4" s="162"/>
+      <c r="BK4" s="162"/>
+      <c r="BL4" s="162"/>
+      <c r="BM4" s="162"/>
+      <c r="BN4" s="162"/>
+      <c r="BO4" s="162"/>
+      <c r="BP4" s="162"/>
+      <c r="BQ4" s="162"/>
+      <c r="BR4" s="162"/>
+      <c r="BS4" s="162"/>
+      <c r="BT4" s="162"/>
+      <c r="BU4" s="162"/>
+      <c r="BV4" s="162"/>
+      <c r="BW4" s="162"/>
+      <c r="BX4" s="162"/>
+      <c r="BY4" s="162"/>
+      <c r="BZ4" s="162"/>
+      <c r="CA4" s="162"/>
+      <c r="CB4" s="162"/>
+      <c r="CC4" s="162"/>
+      <c r="CD4" s="162"/>
+      <c r="CE4" s="162"/>
+      <c r="CF4" s="162"/>
+      <c r="CG4" s="162"/>
+      <c r="CH4" s="162"/>
+      <c r="CI4" s="162"/>
+      <c r="CJ4" s="163"/>
+      <c r="CK4" s="161">
         <v>1</v>
       </c>
-      <c r="CL4" s="174"/>
-      <c r="CM4" s="174"/>
-      <c r="CN4" s="174"/>
-      <c r="CO4" s="174"/>
-      <c r="CP4" s="174"/>
-      <c r="CQ4" s="174"/>
-      <c r="CR4" s="174"/>
-      <c r="CS4" s="174"/>
-      <c r="CT4" s="174"/>
-      <c r="CU4" s="174"/>
-      <c r="CV4" s="174"/>
-      <c r="CW4" s="174"/>
-      <c r="CX4" s="174"/>
-      <c r="CY4" s="174"/>
-      <c r="CZ4" s="174"/>
-      <c r="DA4" s="174"/>
-      <c r="DB4" s="174"/>
-      <c r="DC4" s="174"/>
-      <c r="DD4" s="174"/>
-      <c r="DE4" s="174"/>
-      <c r="DF4" s="174"/>
-      <c r="DG4" s="174"/>
-      <c r="DH4" s="174"/>
-      <c r="DI4" s="174"/>
-      <c r="DJ4" s="174"/>
-      <c r="DK4" s="174"/>
-      <c r="DL4" s="174"/>
-      <c r="DM4" s="174"/>
-      <c r="DN4" s="174"/>
-      <c r="DO4" s="175"/>
+      <c r="CL4" s="162"/>
+      <c r="CM4" s="162"/>
+      <c r="CN4" s="162"/>
+      <c r="CO4" s="162"/>
+      <c r="CP4" s="162"/>
+      <c r="CQ4" s="162"/>
+      <c r="CR4" s="162"/>
+      <c r="CS4" s="162"/>
+      <c r="CT4" s="162"/>
+      <c r="CU4" s="162"/>
+      <c r="CV4" s="162"/>
+      <c r="CW4" s="162"/>
+      <c r="CX4" s="162"/>
+      <c r="CY4" s="162"/>
+      <c r="CZ4" s="162"/>
+      <c r="DA4" s="162"/>
+      <c r="DB4" s="162"/>
+      <c r="DC4" s="162"/>
+      <c r="DD4" s="162"/>
+      <c r="DE4" s="162"/>
+      <c r="DF4" s="162"/>
+      <c r="DG4" s="162"/>
+      <c r="DH4" s="162"/>
+      <c r="DI4" s="162"/>
+      <c r="DJ4" s="162"/>
+      <c r="DK4" s="162"/>
+      <c r="DL4" s="162"/>
+      <c r="DM4" s="162"/>
+      <c r="DN4" s="162"/>
+      <c r="DO4" s="163"/>
       <c r="DP4" s="6"/>
     </row>
     <row r="5" spans="1:120" ht="18" customHeight="1">
@@ -3390,18 +3390,18 @@
     </row>
     <row r="7" spans="1:120" ht="9.75" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="176" t="s">
+      <c r="B7" s="164" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="164"/>
-      <c r="D7" s="164"/>
-      <c r="E7" s="164"/>
-      <c r="F7" s="164"/>
-      <c r="G7" s="177"/>
-      <c r="H7" s="142" t="s">
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="152"/>
+      <c r="H7" s="166" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="142" t="s">
+      <c r="I7" s="166" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="38"/>
@@ -3518,14 +3518,14 @@
     </row>
     <row r="8" spans="1:120" ht="9.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="166"/>
-      <c r="C8" s="167"/>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="168"/>
-      <c r="H8" s="142"/>
-      <c r="I8" s="142"/>
+      <c r="B8" s="134"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
+      <c r="G8" s="139"/>
+      <c r="H8" s="166"/>
+      <c r="I8" s="166"/>
       <c r="J8" s="39"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
@@ -3641,15 +3641,15 @@
     <row r="9" spans="1:120" ht="9.75" customHeight="1">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
-      <c r="C9" s="178" t="s">
+      <c r="C9" s="165" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="158"/>
-      <c r="E9" s="158"/>
-      <c r="F9" s="158"/>
-      <c r="G9" s="162"/>
-      <c r="H9" s="139"/>
-      <c r="I9" s="139"/>
+      <c r="D9" s="154"/>
+      <c r="E9" s="154"/>
+      <c r="F9" s="154"/>
+      <c r="G9" s="142"/>
+      <c r="H9" s="167"/>
+      <c r="I9" s="167"/>
       <c r="J9" s="42"/>
       <c r="K9" s="42"/>
       <c r="L9" s="44"/>
@@ -3765,13 +3765,13 @@
     <row r="10" spans="1:120" ht="9.75" customHeight="1">
       <c r="A10" s="16"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="179"/>
-      <c r="D10" s="167"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="167"/>
-      <c r="G10" s="168"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="139"/>
+      <c r="C10" s="141"/>
+      <c r="D10" s="135"/>
+      <c r="E10" s="135"/>
+      <c r="F10" s="135"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="167"/>
+      <c r="I10" s="167"/>
       <c r="J10" s="46"/>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
@@ -3887,15 +3887,15 @@
     <row r="11" spans="1:120" ht="9.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="180" t="s">
+      <c r="C11" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="158"/>
-      <c r="E11" s="158"/>
-      <c r="F11" s="158"/>
-      <c r="G11" s="162"/>
-      <c r="H11" s="139"/>
-      <c r="I11" s="139"/>
+      <c r="D11" s="154"/>
+      <c r="E11" s="154"/>
+      <c r="F11" s="154"/>
+      <c r="G11" s="142"/>
+      <c r="H11" s="167"/>
+      <c r="I11" s="167"/>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
       <c r="L11" s="44"/>
@@ -4011,13 +4011,13 @@
     <row r="12" spans="1:120" ht="9.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="179"/>
-      <c r="D12" s="167"/>
-      <c r="E12" s="167"/>
-      <c r="F12" s="167"/>
-      <c r="G12" s="168"/>
-      <c r="H12" s="139"/>
-      <c r="I12" s="139"/>
+      <c r="C12" s="141"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="135"/>
+      <c r="G12" s="139"/>
+      <c r="H12" s="167"/>
+      <c r="I12" s="167"/>
       <c r="J12" s="46"/>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
@@ -4134,13 +4134,13 @@
       <c r="A13" s="1"/>
       <c r="B13" s="18"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="181" t="s">
+      <c r="D13" s="151" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="164"/>
-      <c r="F13" s="164"/>
-      <c r="G13" s="177"/>
-      <c r="H13" s="138" t="s">
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="152"/>
+      <c r="H13" s="184" t="s">
         <v>40</v>
       </c>
       <c r="I13" s="112">
@@ -4262,10 +4262,10 @@
       <c r="A14" s="1"/>
       <c r="B14" s="18"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="166"/>
-      <c r="E14" s="167"/>
-      <c r="F14" s="167"/>
-      <c r="G14" s="168"/>
+      <c r="D14" s="134"/>
+      <c r="E14" s="135"/>
+      <c r="F14" s="135"/>
+      <c r="G14" s="139"/>
       <c r="H14" s="112"/>
       <c r="I14" s="112"/>
       <c r="J14" s="39"/>
@@ -4384,13 +4384,13 @@
       <c r="A15" s="1"/>
       <c r="B15" s="18"/>
       <c r="C15" s="24"/>
-      <c r="D15" s="181" t="s">
+      <c r="D15" s="151" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="164"/>
-      <c r="F15" s="164"/>
-      <c r="G15" s="170"/>
-      <c r="H15" s="138" t="s">
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="133"/>
+      <c r="H15" s="184" t="s">
         <v>40</v>
       </c>
       <c r="I15" s="112">
@@ -4512,10 +4512,10 @@
       <c r="A16" s="1"/>
       <c r="B16" s="18"/>
       <c r="C16" s="24"/>
-      <c r="D16" s="166"/>
-      <c r="E16" s="167"/>
-      <c r="F16" s="167"/>
-      <c r="G16" s="171"/>
+      <c r="D16" s="134"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="136"/>
       <c r="H16" s="112"/>
       <c r="I16" s="112"/>
       <c r="J16" s="14"/>
@@ -4634,13 +4634,13 @@
       <c r="A17" s="1"/>
       <c r="B17" s="18"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="181" t="s">
+      <c r="D17" s="151" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="164"/>
-      <c r="F17" s="164"/>
-      <c r="G17" s="170"/>
-      <c r="H17" s="138" t="s">
+      <c r="E17" s="132"/>
+      <c r="F17" s="132"/>
+      <c r="G17" s="133"/>
+      <c r="H17" s="184" t="s">
         <v>40</v>
       </c>
       <c r="I17" s="112">
@@ -4762,10 +4762,10 @@
       <c r="A18" s="1"/>
       <c r="B18" s="18"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="166"/>
-      <c r="E18" s="167"/>
-      <c r="F18" s="167"/>
-      <c r="G18" s="171"/>
+      <c r="D18" s="134"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="136"/>
       <c r="H18" s="112"/>
       <c r="I18" s="112"/>
       <c r="J18" s="14"/>
@@ -4884,13 +4884,13 @@
       <c r="A19" s="1"/>
       <c r="B19" s="18"/>
       <c r="C19" s="24"/>
-      <c r="D19" s="181" t="s">
+      <c r="D19" s="151" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="164"/>
-      <c r="F19" s="164"/>
-      <c r="G19" s="170"/>
-      <c r="H19" s="138" t="s">
+      <c r="E19" s="132"/>
+      <c r="F19" s="132"/>
+      <c r="G19" s="133"/>
+      <c r="H19" s="184" t="s">
         <v>40</v>
       </c>
       <c r="I19" s="112">
@@ -5012,10 +5012,10 @@
       <c r="A20" s="1"/>
       <c r="B20" s="18"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="166"/>
-      <c r="E20" s="167"/>
-      <c r="F20" s="167"/>
-      <c r="G20" s="171"/>
+      <c r="D20" s="134"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="136"/>
       <c r="H20" s="112"/>
       <c r="I20" s="112"/>
       <c r="J20" s="26"/>
@@ -5133,15 +5133,15 @@
     <row r="21" spans="1:120" ht="9.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="18"/>
-      <c r="C21" s="180" t="s">
+      <c r="C21" s="153" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="158"/>
-      <c r="E21" s="158"/>
-      <c r="F21" s="158"/>
-      <c r="G21" s="159"/>
-      <c r="H21" s="139"/>
-      <c r="I21" s="139"/>
+      <c r="D21" s="154"/>
+      <c r="E21" s="154"/>
+      <c r="F21" s="154"/>
+      <c r="G21" s="155"/>
+      <c r="H21" s="167"/>
+      <c r="I21" s="167"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="44"/>
@@ -5257,13 +5257,13 @@
     <row r="22" spans="1:120" ht="9.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="18"/>
-      <c r="C22" s="160"/>
-      <c r="D22" s="161"/>
-      <c r="E22" s="161"/>
-      <c r="F22" s="161"/>
-      <c r="G22" s="162"/>
-      <c r="H22" s="139"/>
-      <c r="I22" s="139"/>
+      <c r="C22" s="156"/>
+      <c r="D22" s="157"/>
+      <c r="E22" s="157"/>
+      <c r="F22" s="157"/>
+      <c r="G22" s="142"/>
+      <c r="H22" s="167"/>
+      <c r="I22" s="167"/>
       <c r="J22" s="46"/>
       <c r="K22" s="47"/>
       <c r="L22" s="47"/>
@@ -5380,13 +5380,13 @@
       <c r="A23" s="1"/>
       <c r="B23" s="28"/>
       <c r="C23" s="29"/>
-      <c r="D23" s="182" t="s">
+      <c r="D23" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="164"/>
-      <c r="F23" s="164"/>
-      <c r="G23" s="170"/>
-      <c r="H23" s="138" t="s">
+      <c r="E23" s="132"/>
+      <c r="F23" s="132"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="184" t="s">
         <v>46</v>
       </c>
       <c r="I23" s="112">
@@ -5508,10 +5508,10 @@
       <c r="A24" s="1"/>
       <c r="B24" s="18"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="166"/>
-      <c r="E24" s="167"/>
-      <c r="F24" s="167"/>
-      <c r="G24" s="171"/>
+      <c r="D24" s="134"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="136"/>
       <c r="H24" s="112"/>
       <c r="I24" s="112"/>
       <c r="J24" s="14"/>
@@ -5629,15 +5629,15 @@
     <row r="25" spans="1:120" ht="9.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="18"/>
-      <c r="C25" s="180" t="s">
+      <c r="C25" s="153" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="158"/>
-      <c r="G25" s="159"/>
-      <c r="H25" s="139"/>
-      <c r="I25" s="139"/>
+      <c r="D25" s="154"/>
+      <c r="E25" s="154"/>
+      <c r="F25" s="154"/>
+      <c r="G25" s="155"/>
+      <c r="H25" s="167"/>
+      <c r="I25" s="167"/>
       <c r="J25" s="42"/>
       <c r="K25" s="42"/>
       <c r="L25" s="44"/>
@@ -5753,13 +5753,13 @@
     <row r="26" spans="1:120" ht="9.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="18"/>
-      <c r="C26" s="179"/>
-      <c r="D26" s="167"/>
-      <c r="E26" s="167"/>
-      <c r="F26" s="167"/>
-      <c r="G26" s="168"/>
-      <c r="H26" s="139"/>
-      <c r="I26" s="139"/>
+      <c r="C26" s="141"/>
+      <c r="D26" s="135"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="135"/>
+      <c r="G26" s="139"/>
+      <c r="H26" s="167"/>
+      <c r="I26" s="167"/>
       <c r="J26" s="46"/>
       <c r="K26" s="47"/>
       <c r="L26" s="47"/>
@@ -5876,13 +5876,13 @@
       <c r="A27" s="1"/>
       <c r="B27" s="28"/>
       <c r="C27" s="29"/>
-      <c r="D27" s="182" t="s">
+      <c r="D27" s="158" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="164"/>
-      <c r="F27" s="164"/>
-      <c r="G27" s="170"/>
-      <c r="H27" s="138" t="s">
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="133"/>
+      <c r="H27" s="184" t="s">
         <v>44</v>
       </c>
       <c r="I27" s="112">
@@ -6004,10 +6004,10 @@
       <c r="A28" s="1"/>
       <c r="B28" s="28"/>
       <c r="C28" s="30"/>
-      <c r="D28" s="166"/>
-      <c r="E28" s="167"/>
-      <c r="F28" s="167"/>
-      <c r="G28" s="171"/>
+      <c r="D28" s="134"/>
+      <c r="E28" s="135"/>
+      <c r="F28" s="135"/>
+      <c r="G28" s="136"/>
       <c r="H28" s="112"/>
       <c r="I28" s="112"/>
       <c r="J28" s="14"/>
@@ -6126,13 +6126,13 @@
       <c r="A29" s="1"/>
       <c r="B29" s="28"/>
       <c r="C29" s="30"/>
-      <c r="D29" s="183" t="s">
+      <c r="D29" s="159" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="184"/>
-      <c r="F29" s="184"/>
-      <c r="G29" s="184"/>
-      <c r="H29" s="138" t="s">
+      <c r="E29" s="160"/>
+      <c r="F29" s="160"/>
+      <c r="G29" s="160"/>
+      <c r="H29" s="184" t="s">
         <v>44</v>
       </c>
       <c r="I29" s="112">
@@ -6254,10 +6254,10 @@
       <c r="A30" s="1"/>
       <c r="B30" s="28"/>
       <c r="C30" s="31"/>
-      <c r="D30" s="166"/>
-      <c r="E30" s="167"/>
-      <c r="F30" s="167"/>
-      <c r="G30" s="167"/>
+      <c r="D30" s="134"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="135"/>
+      <c r="G30" s="135"/>
       <c r="H30" s="112"/>
       <c r="I30" s="112"/>
       <c r="J30" s="26"/>
@@ -6375,15 +6375,15 @@
     <row r="31" spans="1:120" ht="9.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="18"/>
-      <c r="C31" s="157" t="s">
+      <c r="C31" s="179" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="158"/>
-      <c r="E31" s="158"/>
-      <c r="F31" s="158"/>
-      <c r="G31" s="159"/>
-      <c r="H31" s="139"/>
-      <c r="I31" s="139"/>
+      <c r="D31" s="154"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="154"/>
+      <c r="G31" s="155"/>
+      <c r="H31" s="167"/>
+      <c r="I31" s="167"/>
       <c r="J31" s="42"/>
       <c r="K31" s="43"/>
       <c r="L31" s="44"/>
@@ -6499,13 +6499,13 @@
     <row r="32" spans="1:120" ht="9.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="18"/>
-      <c r="C32" s="160"/>
-      <c r="D32" s="161"/>
-      <c r="E32" s="161"/>
-      <c r="F32" s="161"/>
-      <c r="G32" s="162"/>
-      <c r="H32" s="139"/>
-      <c r="I32" s="139"/>
+      <c r="C32" s="156"/>
+      <c r="D32" s="157"/>
+      <c r="E32" s="157"/>
+      <c r="F32" s="157"/>
+      <c r="G32" s="142"/>
+      <c r="H32" s="167"/>
+      <c r="I32" s="167"/>
       <c r="J32" s="46"/>
       <c r="K32" s="47"/>
       <c r="L32" s="47"/>
@@ -6622,14 +6622,14 @@
       <c r="A33" s="1"/>
       <c r="B33" s="18"/>
       <c r="C33" s="32"/>
-      <c r="D33" s="163" t="s">
+      <c r="D33" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="164"/>
-      <c r="F33" s="164"/>
-      <c r="G33" s="165"/>
-      <c r="H33" s="139"/>
-      <c r="I33" s="139"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="138"/>
+      <c r="H33" s="167"/>
+      <c r="I33" s="167"/>
       <c r="J33" s="50"/>
       <c r="K33" s="51"/>
       <c r="L33" s="51"/>
@@ -6746,12 +6746,12 @@
       <c r="A34" s="1"/>
       <c r="B34" s="18"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="166"/>
-      <c r="E34" s="167"/>
-      <c r="F34" s="167"/>
-      <c r="G34" s="168"/>
-      <c r="H34" s="139"/>
-      <c r="I34" s="139"/>
+      <c r="D34" s="134"/>
+      <c r="E34" s="135"/>
+      <c r="F34" s="135"/>
+      <c r="G34" s="139"/>
+      <c r="H34" s="167"/>
+      <c r="I34" s="167"/>
       <c r="J34" s="52"/>
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
@@ -6869,12 +6869,12 @@
       <c r="B35" s="18"/>
       <c r="C35" s="1"/>
       <c r="D35" s="33"/>
-      <c r="E35" s="169" t="s">
+      <c r="E35" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="164"/>
-      <c r="G35" s="170"/>
-      <c r="H35" s="138" t="s">
+      <c r="F35" s="132"/>
+      <c r="G35" s="133"/>
+      <c r="H35" s="184" t="s">
         <v>45</v>
       </c>
       <c r="I35" s="112">
@@ -6997,9 +6997,9 @@
       <c r="B36" s="18"/>
       <c r="C36" s="1"/>
       <c r="D36" s="34"/>
-      <c r="E36" s="166"/>
-      <c r="F36" s="167"/>
-      <c r="G36" s="171"/>
+      <c r="E36" s="134"/>
+      <c r="F36" s="135"/>
+      <c r="G36" s="136"/>
       <c r="H36" s="112"/>
       <c r="I36" s="112"/>
       <c r="J36" s="14"/>
@@ -7119,12 +7119,12 @@
       <c r="B37" s="18"/>
       <c r="C37" s="1"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="169" t="s">
+      <c r="E37" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F37" s="164"/>
-      <c r="G37" s="170"/>
-      <c r="H37" s="138" t="s">
+      <c r="F37" s="132"/>
+      <c r="G37" s="133"/>
+      <c r="H37" s="184" t="s">
         <v>44</v>
       </c>
       <c r="I37" s="112">
@@ -7247,9 +7247,9 @@
       <c r="B38" s="18"/>
       <c r="C38" s="1"/>
       <c r="D38" s="35"/>
-      <c r="E38" s="166"/>
-      <c r="F38" s="167"/>
-      <c r="G38" s="171"/>
+      <c r="E38" s="134"/>
+      <c r="F38" s="135"/>
+      <c r="G38" s="136"/>
       <c r="H38" s="112"/>
       <c r="I38" s="112"/>
       <c r="J38" s="26"/>
@@ -7368,14 +7368,14 @@
       <c r="A39" s="1"/>
       <c r="B39" s="18"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="172" t="s">
+      <c r="D39" s="180" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="158"/>
-      <c r="F39" s="158"/>
-      <c r="G39" s="159"/>
-      <c r="H39" s="139"/>
-      <c r="I39" s="139"/>
+      <c r="E39" s="154"/>
+      <c r="F39" s="154"/>
+      <c r="G39" s="155"/>
+      <c r="H39" s="167"/>
+      <c r="I39" s="167"/>
       <c r="J39" s="50"/>
       <c r="K39" s="51"/>
       <c r="L39" s="51"/>
@@ -7492,12 +7492,12 @@
       <c r="A40" s="1"/>
       <c r="B40" s="18"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="166"/>
-      <c r="E40" s="167"/>
-      <c r="F40" s="167"/>
-      <c r="G40" s="168"/>
-      <c r="H40" s="139"/>
-      <c r="I40" s="139"/>
+      <c r="D40" s="134"/>
+      <c r="E40" s="135"/>
+      <c r="F40" s="135"/>
+      <c r="G40" s="139"/>
+      <c r="H40" s="167"/>
+      <c r="I40" s="167"/>
       <c r="J40" s="52"/>
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
@@ -7615,12 +7615,12 @@
       <c r="B41" s="18"/>
       <c r="C41" s="1"/>
       <c r="D41" s="33"/>
-      <c r="E41" s="169" t="s">
+      <c r="E41" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="164"/>
-      <c r="G41" s="170"/>
-      <c r="H41" s="138" t="s">
+      <c r="F41" s="132"/>
+      <c r="G41" s="133"/>
+      <c r="H41" s="184" t="s">
         <v>43</v>
       </c>
       <c r="I41" s="112">
@@ -7743,9 +7743,9 @@
       <c r="B42" s="18"/>
       <c r="C42" s="1"/>
       <c r="D42" s="34"/>
-      <c r="E42" s="166"/>
-      <c r="F42" s="167"/>
-      <c r="G42" s="171"/>
+      <c r="E42" s="134"/>
+      <c r="F42" s="135"/>
+      <c r="G42" s="136"/>
       <c r="H42" s="112"/>
       <c r="I42" s="112"/>
       <c r="J42" s="14"/>
@@ -7865,12 +7865,12 @@
       <c r="B43" s="18"/>
       <c r="C43" s="1"/>
       <c r="D43" s="34"/>
-      <c r="E43" s="169" t="s">
+      <c r="E43" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="164"/>
-      <c r="G43" s="170"/>
-      <c r="H43" s="138" t="s">
+      <c r="F43" s="132"/>
+      <c r="G43" s="133"/>
+      <c r="H43" s="184" t="s">
         <v>43</v>
       </c>
       <c r="I43" s="112">
@@ -7993,9 +7993,9 @@
       <c r="B44" s="18"/>
       <c r="C44" s="1"/>
       <c r="D44" s="34"/>
-      <c r="E44" s="166"/>
-      <c r="F44" s="167"/>
-      <c r="G44" s="171"/>
+      <c r="E44" s="134"/>
+      <c r="F44" s="135"/>
+      <c r="G44" s="136"/>
       <c r="H44" s="112"/>
       <c r="I44" s="112"/>
       <c r="J44" s="14"/>
@@ -8115,12 +8115,12 @@
       <c r="B45" s="18"/>
       <c r="C45" s="1"/>
       <c r="D45" s="34"/>
-      <c r="E45" s="169" t="s">
+      <c r="E45" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="164"/>
-      <c r="G45" s="170"/>
-      <c r="H45" s="138" t="s">
+      <c r="F45" s="132"/>
+      <c r="G45" s="133"/>
+      <c r="H45" s="184" t="s">
         <v>42</v>
       </c>
       <c r="I45" s="112">
@@ -8243,9 +8243,9 @@
       <c r="B46" s="18"/>
       <c r="C46" s="1"/>
       <c r="D46" s="34"/>
-      <c r="E46" s="166"/>
-      <c r="F46" s="167"/>
-      <c r="G46" s="171"/>
+      <c r="E46" s="134"/>
+      <c r="F46" s="135"/>
+      <c r="G46" s="136"/>
       <c r="H46" s="112"/>
       <c r="I46" s="112"/>
       <c r="J46" s="14"/>
@@ -8365,12 +8365,12 @@
       <c r="B47" s="18"/>
       <c r="C47" s="1"/>
       <c r="D47" s="34"/>
-      <c r="E47" s="169" t="s">
+      <c r="E47" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="F47" s="164"/>
-      <c r="G47" s="170"/>
-      <c r="H47" s="138" t="s">
+      <c r="F47" s="132"/>
+      <c r="G47" s="133"/>
+      <c r="H47" s="184" t="s">
         <v>41</v>
       </c>
       <c r="I47" s="112">
@@ -8493,9 +8493,9 @@
       <c r="B48" s="18"/>
       <c r="C48" s="1"/>
       <c r="D48" s="34"/>
-      <c r="E48" s="166"/>
-      <c r="F48" s="167"/>
-      <c r="G48" s="171"/>
+      <c r="E48" s="134"/>
+      <c r="F48" s="135"/>
+      <c r="G48" s="136"/>
       <c r="H48" s="112"/>
       <c r="I48" s="112"/>
       <c r="J48" s="14"/>
@@ -8615,12 +8615,12 @@
       <c r="B49" s="18"/>
       <c r="C49" s="1"/>
       <c r="D49" s="34"/>
-      <c r="E49" s="169" t="s">
+      <c r="E49" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="164"/>
-      <c r="G49" s="170"/>
-      <c r="H49" s="138" t="s">
+      <c r="F49" s="132"/>
+      <c r="G49" s="133"/>
+      <c r="H49" s="184" t="s">
         <v>50</v>
       </c>
       <c r="I49" s="112">
@@ -8743,9 +8743,9 @@
       <c r="B50" s="18"/>
       <c r="C50" s="1"/>
       <c r="D50" s="34"/>
-      <c r="E50" s="166"/>
-      <c r="F50" s="167"/>
-      <c r="G50" s="171"/>
+      <c r="E50" s="134"/>
+      <c r="F50" s="135"/>
+      <c r="G50" s="136"/>
       <c r="H50" s="112"/>
       <c r="I50" s="112"/>
       <c r="J50" s="14"/>
@@ -8865,12 +8865,12 @@
       <c r="B51" s="18"/>
       <c r="C51" s="1"/>
       <c r="D51" s="34"/>
-      <c r="E51" s="169" t="s">
+      <c r="E51" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="164"/>
-      <c r="G51" s="170"/>
-      <c r="H51" s="138" t="s">
+      <c r="F51" s="132"/>
+      <c r="G51" s="133"/>
+      <c r="H51" s="184" t="s">
         <v>47</v>
       </c>
       <c r="I51" s="112">
@@ -8993,9 +8993,9 @@
       <c r="B52" s="18"/>
       <c r="C52" s="1"/>
       <c r="D52" s="34"/>
-      <c r="E52" s="166"/>
-      <c r="F52" s="167"/>
-      <c r="G52" s="171"/>
+      <c r="E52" s="134"/>
+      <c r="F52" s="135"/>
+      <c r="G52" s="136"/>
       <c r="H52" s="112"/>
       <c r="I52" s="112"/>
       <c r="J52" s="26"/>
@@ -9114,14 +9114,14 @@
       <c r="A53" s="1"/>
       <c r="B53" s="18"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="163" t="s">
+      <c r="D53" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="164"/>
-      <c r="F53" s="164"/>
-      <c r="G53" s="165"/>
-      <c r="H53" s="139"/>
-      <c r="I53" s="139"/>
+      <c r="E53" s="132"/>
+      <c r="F53" s="132"/>
+      <c r="G53" s="138"/>
+      <c r="H53" s="167"/>
+      <c r="I53" s="167"/>
       <c r="J53" s="50"/>
       <c r="K53" s="51"/>
       <c r="L53" s="51"/>
@@ -9238,12 +9238,12 @@
       <c r="A54" s="1"/>
       <c r="B54" s="18"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="166"/>
-      <c r="E54" s="167"/>
-      <c r="F54" s="167"/>
-      <c r="G54" s="168"/>
-      <c r="H54" s="139"/>
-      <c r="I54" s="139"/>
+      <c r="D54" s="134"/>
+      <c r="E54" s="135"/>
+      <c r="F54" s="135"/>
+      <c r="G54" s="139"/>
+      <c r="H54" s="167"/>
+      <c r="I54" s="167"/>
       <c r="J54" s="52"/>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -9361,12 +9361,12 @@
       <c r="B55" s="18"/>
       <c r="C55" s="1"/>
       <c r="D55" s="34"/>
-      <c r="E55" s="169" t="s">
+      <c r="E55" s="131" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="164"/>
-      <c r="G55" s="170"/>
-      <c r="H55" s="138" t="s">
+      <c r="F55" s="132"/>
+      <c r="G55" s="133"/>
+      <c r="H55" s="184" t="s">
         <v>48</v>
       </c>
       <c r="I55" s="112">
@@ -9489,9 +9489,9 @@
       <c r="B56" s="18"/>
       <c r="C56" s="1"/>
       <c r="D56" s="34"/>
-      <c r="E56" s="166"/>
-      <c r="F56" s="167"/>
-      <c r="G56" s="171"/>
+      <c r="E56" s="134"/>
+      <c r="F56" s="135"/>
+      <c r="G56" s="136"/>
       <c r="H56" s="112"/>
       <c r="I56" s="112"/>
       <c r="J56" s="14"/>
@@ -9611,12 +9611,12 @@
       <c r="B57" s="18"/>
       <c r="C57" s="1"/>
       <c r="D57" s="34"/>
-      <c r="E57" s="169" t="s">
+      <c r="E57" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="F57" s="164"/>
-      <c r="G57" s="170"/>
-      <c r="H57" s="138" t="s">
+      <c r="F57" s="132"/>
+      <c r="G57" s="133"/>
+      <c r="H57" s="184" t="s">
         <v>51</v>
       </c>
       <c r="I57" s="112">
@@ -9739,9 +9739,9 @@
       <c r="B58" s="18"/>
       <c r="C58" s="1"/>
       <c r="D58" s="34"/>
-      <c r="E58" s="166"/>
-      <c r="F58" s="167"/>
-      <c r="G58" s="171"/>
+      <c r="E58" s="134"/>
+      <c r="F58" s="135"/>
+      <c r="G58" s="136"/>
       <c r="H58" s="112"/>
       <c r="I58" s="112"/>
       <c r="J58" s="14"/>
@@ -9861,12 +9861,12 @@
       <c r="B59" s="18"/>
       <c r="C59" s="1"/>
       <c r="D59" s="34"/>
-      <c r="E59" s="169" t="s">
+      <c r="E59" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="F59" s="164"/>
-      <c r="G59" s="170"/>
-      <c r="H59" s="138" t="s">
+      <c r="F59" s="132"/>
+      <c r="G59" s="133"/>
+      <c r="H59" s="184" t="s">
         <v>49</v>
       </c>
       <c r="I59" s="112">
@@ -9989,9 +9989,9 @@
       <c r="B60" s="18"/>
       <c r="C60" s="1"/>
       <c r="D60" s="34"/>
-      <c r="E60" s="166"/>
-      <c r="F60" s="167"/>
-      <c r="G60" s="171"/>
+      <c r="E60" s="134"/>
+      <c r="F60" s="135"/>
+      <c r="G60" s="136"/>
       <c r="H60" s="112"/>
       <c r="I60" s="112"/>
       <c r="J60" s="14"/>
@@ -10111,12 +10111,12 @@
       <c r="B61" s="18"/>
       <c r="C61" s="1"/>
       <c r="D61" s="34"/>
-      <c r="E61" s="169" t="s">
+      <c r="E61" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F61" s="164"/>
-      <c r="G61" s="170"/>
-      <c r="H61" s="138" t="s">
+      <c r="F61" s="132"/>
+      <c r="G61" s="133"/>
+      <c r="H61" s="184" t="s">
         <v>49</v>
       </c>
       <c r="I61" s="112">
@@ -10239,9 +10239,9 @@
       <c r="B62" s="18"/>
       <c r="C62" s="1"/>
       <c r="D62" s="34"/>
-      <c r="E62" s="166"/>
-      <c r="F62" s="167"/>
-      <c r="G62" s="171"/>
+      <c r="E62" s="134"/>
+      <c r="F62" s="135"/>
+      <c r="G62" s="136"/>
       <c r="H62" s="112"/>
       <c r="I62" s="112"/>
       <c r="J62" s="26"/>
@@ -10360,14 +10360,14 @@
       <c r="A63" s="1"/>
       <c r="B63" s="18"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="163" t="s">
+      <c r="D63" s="137" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="164"/>
-      <c r="F63" s="164"/>
-      <c r="G63" s="165"/>
-      <c r="H63" s="139"/>
-      <c r="I63" s="139"/>
+      <c r="E63" s="132"/>
+      <c r="F63" s="132"/>
+      <c r="G63" s="138"/>
+      <c r="H63" s="167"/>
+      <c r="I63" s="167"/>
       <c r="J63" s="50"/>
       <c r="K63" s="51"/>
       <c r="L63" s="51"/>
@@ -10484,12 +10484,12 @@
       <c r="A64" s="1"/>
       <c r="B64" s="18"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="166"/>
-      <c r="E64" s="167"/>
-      <c r="F64" s="167"/>
-      <c r="G64" s="168"/>
-      <c r="H64" s="139"/>
-      <c r="I64" s="139"/>
+      <c r="D64" s="134"/>
+      <c r="E64" s="135"/>
+      <c r="F64" s="135"/>
+      <c r="G64" s="139"/>
+      <c r="H64" s="167"/>
+      <c r="I64" s="167"/>
       <c r="J64" s="52"/>
       <c r="K64" s="49"/>
       <c r="L64" s="49"/>
@@ -10607,12 +10607,12 @@
       <c r="B65" s="18"/>
       <c r="C65" s="1"/>
       <c r="D65" s="34"/>
-      <c r="E65" s="169" t="s">
+      <c r="E65" s="131" t="s">
         <v>35</v>
       </c>
-      <c r="F65" s="164"/>
-      <c r="G65" s="170"/>
-      <c r="H65" s="138" t="s">
+      <c r="F65" s="132"/>
+      <c r="G65" s="133"/>
+      <c r="H65" s="184" t="s">
         <v>52</v>
       </c>
       <c r="I65" s="112">
@@ -10735,9 +10735,9 @@
       <c r="B66" s="18"/>
       <c r="C66" s="1"/>
       <c r="D66" s="34"/>
-      <c r="E66" s="166"/>
-      <c r="F66" s="167"/>
-      <c r="G66" s="171"/>
+      <c r="E66" s="134"/>
+      <c r="F66" s="135"/>
+      <c r="G66" s="136"/>
       <c r="H66" s="112"/>
       <c r="I66" s="112"/>
       <c r="J66" s="14"/>
@@ -10857,12 +10857,12 @@
       <c r="B67" s="18"/>
       <c r="C67" s="1"/>
       <c r="D67" s="34"/>
-      <c r="E67" s="169" t="s">
+      <c r="E67" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="F67" s="164"/>
-      <c r="G67" s="170"/>
-      <c r="H67" s="138" t="s">
+      <c r="F67" s="132"/>
+      <c r="G67" s="133"/>
+      <c r="H67" s="184" t="s">
         <v>53</v>
       </c>
       <c r="I67" s="112">
@@ -10985,9 +10985,9 @@
       <c r="B68" s="18"/>
       <c r="C68" s="1"/>
       <c r="D68" s="34"/>
-      <c r="E68" s="166"/>
-      <c r="F68" s="167"/>
-      <c r="G68" s="171"/>
+      <c r="E68" s="134"/>
+      <c r="F68" s="135"/>
+      <c r="G68" s="136"/>
       <c r="H68" s="112"/>
       <c r="I68" s="112"/>
       <c r="J68" s="14"/>
@@ -11107,12 +11107,12 @@
       <c r="B69" s="18"/>
       <c r="C69" s="1"/>
       <c r="D69" s="34"/>
-      <c r="E69" s="169" t="s">
+      <c r="E69" s="131" t="s">
         <v>36</v>
       </c>
-      <c r="F69" s="164"/>
-      <c r="G69" s="170"/>
-      <c r="H69" s="138" t="s">
+      <c r="F69" s="132"/>
+      <c r="G69" s="133"/>
+      <c r="H69" s="184" t="s">
         <v>54</v>
       </c>
       <c r="I69" s="112">
@@ -11235,9 +11235,9 @@
       <c r="B70" s="18"/>
       <c r="C70" s="1"/>
       <c r="D70" s="34"/>
-      <c r="E70" s="166"/>
-      <c r="F70" s="167"/>
-      <c r="G70" s="171"/>
+      <c r="E70" s="134"/>
+      <c r="F70" s="135"/>
+      <c r="G70" s="136"/>
       <c r="H70" s="112"/>
       <c r="I70" s="112"/>
       <c r="J70" s="14"/>
@@ -11357,12 +11357,12 @@
       <c r="B71" s="18"/>
       <c r="C71" s="1"/>
       <c r="D71" s="34"/>
-      <c r="E71" s="169" t="s">
+      <c r="E71" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="F71" s="164"/>
-      <c r="G71" s="170"/>
-      <c r="H71" s="138" t="s">
+      <c r="F71" s="132"/>
+      <c r="G71" s="133"/>
+      <c r="H71" s="184" t="s">
         <v>55</v>
       </c>
       <c r="I71" s="112">
@@ -11485,9 +11485,9 @@
       <c r="B72" s="18"/>
       <c r="C72" s="1"/>
       <c r="D72" s="35"/>
-      <c r="E72" s="166"/>
-      <c r="F72" s="167"/>
-      <c r="G72" s="171"/>
+      <c r="E72" s="134"/>
+      <c r="F72" s="135"/>
+      <c r="G72" s="136"/>
       <c r="H72" s="112"/>
       <c r="I72" s="112"/>
       <c r="J72" s="26"/>
@@ -11605,14 +11605,14 @@
     <row r="73" spans="1:120" ht="9.75" customHeight="1">
       <c r="A73" s="16"/>
       <c r="B73" s="36"/>
-      <c r="C73" s="146" t="s">
+      <c r="C73" s="140" t="s">
         <v>30</v>
       </c>
-      <c r="D73" s="164"/>
-      <c r="E73" s="164"/>
-      <c r="F73" s="164"/>
-      <c r="G73" s="165"/>
-      <c r="H73" s="138" t="s">
+      <c r="D73" s="132"/>
+      <c r="E73" s="132"/>
+      <c r="F73" s="132"/>
+      <c r="G73" s="138"/>
+      <c r="H73" s="184" t="s">
         <v>55</v>
       </c>
       <c r="I73" s="112">
@@ -11733,11 +11733,11 @@
     <row r="74" spans="1:120" ht="9.75" customHeight="1">
       <c r="A74" s="16"/>
       <c r="B74" s="36"/>
-      <c r="C74" s="179"/>
-      <c r="D74" s="167"/>
-      <c r="E74" s="167"/>
-      <c r="F74" s="167"/>
-      <c r="G74" s="168"/>
+      <c r="C74" s="141"/>
+      <c r="D74" s="135"/>
+      <c r="E74" s="135"/>
+      <c r="F74" s="135"/>
+      <c r="G74" s="139"/>
       <c r="H74" s="112"/>
       <c r="I74" s="112"/>
       <c r="J74" s="19"/>
@@ -11855,14 +11855,14 @@
     <row r="75" spans="1:120" ht="9.75" customHeight="1">
       <c r="A75" s="16"/>
       <c r="B75" s="36"/>
-      <c r="C75" s="146" t="s">
+      <c r="C75" s="140" t="s">
         <v>34</v>
       </c>
-      <c r="D75" s="164"/>
-      <c r="E75" s="164"/>
-      <c r="F75" s="164"/>
-      <c r="G75" s="165"/>
-      <c r="H75" s="138" t="s">
+      <c r="D75" s="132"/>
+      <c r="E75" s="132"/>
+      <c r="F75" s="132"/>
+      <c r="G75" s="138"/>
+      <c r="H75" s="184" t="s">
         <v>58</v>
       </c>
       <c r="I75" s="112"/>
@@ -11981,11 +11981,11 @@
     <row r="76" spans="1:120" ht="9.75" customHeight="1">
       <c r="A76" s="16"/>
       <c r="B76" s="36"/>
-      <c r="C76" s="162"/>
-      <c r="D76" s="162"/>
-      <c r="E76" s="162"/>
-      <c r="F76" s="162"/>
-      <c r="G76" s="162"/>
+      <c r="C76" s="142"/>
+      <c r="D76" s="142"/>
+      <c r="E76" s="142"/>
+      <c r="F76" s="142"/>
+      <c r="G76" s="142"/>
       <c r="H76" s="112"/>
       <c r="I76" s="112"/>
       <c r="J76" s="19"/>
@@ -12103,15 +12103,15 @@
     <row r="77" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A77" s="16"/>
       <c r="B77" s="71"/>
-      <c r="C77" s="187" t="s">
+      <c r="C77" s="143" t="s">
         <v>62</v>
       </c>
-      <c r="D77" s="188"/>
-      <c r="E77" s="188"/>
-      <c r="F77" s="188"/>
-      <c r="G77" s="189"/>
-      <c r="H77" s="140"/>
-      <c r="I77" s="129"/>
+      <c r="D77" s="144"/>
+      <c r="E77" s="144"/>
+      <c r="F77" s="144"/>
+      <c r="G77" s="145"/>
+      <c r="H77" s="185"/>
+      <c r="I77" s="181"/>
       <c r="J77" s="63"/>
       <c r="K77" s="64"/>
       <c r="L77" s="64"/>
@@ -12227,13 +12227,13 @@
     <row r="78" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A78" s="16"/>
       <c r="B78" s="71"/>
-      <c r="C78" s="190"/>
-      <c r="D78" s="191"/>
-      <c r="E78" s="191"/>
-      <c r="F78" s="191"/>
-      <c r="G78" s="192"/>
-      <c r="H78" s="141"/>
-      <c r="I78" s="130"/>
+      <c r="C78" s="146"/>
+      <c r="D78" s="147"/>
+      <c r="E78" s="147"/>
+      <c r="F78" s="147"/>
+      <c r="G78" s="148"/>
+      <c r="H78" s="186"/>
+      <c r="I78" s="182"/>
       <c r="J78" s="63"/>
       <c r="K78" s="64"/>
       <c r="L78" s="64"/>
@@ -12350,12 +12350,12 @@
       <c r="A79" s="16"/>
       <c r="B79" s="71"/>
       <c r="C79" s="76"/>
-      <c r="D79" s="132" t="s">
+      <c r="D79" s="115" t="s">
         <v>63</v>
       </c>
-      <c r="E79" s="133"/>
-      <c r="F79" s="133"/>
-      <c r="G79" s="134"/>
+      <c r="E79" s="116"/>
+      <c r="F79" s="116"/>
+      <c r="G79" s="117"/>
       <c r="H79" s="77"/>
       <c r="I79" s="67"/>
       <c r="J79" s="63"/>
@@ -12474,10 +12474,10 @@
       <c r="A80" s="16"/>
       <c r="B80" s="71"/>
       <c r="C80" s="76"/>
-      <c r="D80" s="135"/>
-      <c r="E80" s="136"/>
-      <c r="F80" s="136"/>
-      <c r="G80" s="137"/>
+      <c r="D80" s="118"/>
+      <c r="E80" s="119"/>
+      <c r="F80" s="119"/>
+      <c r="G80" s="120"/>
       <c r="H80" s="77"/>
       <c r="I80" s="67"/>
       <c r="J80" s="63"/>
@@ -12597,15 +12597,15 @@
       <c r="B81" s="36"/>
       <c r="C81" s="60"/>
       <c r="D81" s="70"/>
-      <c r="E81" s="105" t="s">
+      <c r="E81" s="149" t="s">
         <v>73</v>
       </c>
-      <c r="F81" s="105"/>
-      <c r="G81" s="105"/>
-      <c r="H81" s="111">
+      <c r="F81" s="149"/>
+      <c r="G81" s="149"/>
+      <c r="H81" s="103">
         <v>45611</v>
       </c>
-      <c r="I81" s="126">
+      <c r="I81" s="105">
         <v>100</v>
       </c>
       <c r="J81" s="19"/>
@@ -12725,11 +12725,11 @@
       <c r="B82" s="36"/>
       <c r="C82" s="60"/>
       <c r="D82" s="70"/>
-      <c r="E82" s="103"/>
-      <c r="F82" s="103"/>
-      <c r="G82" s="103"/>
-      <c r="H82" s="107"/>
-      <c r="I82" s="109"/>
+      <c r="E82" s="102"/>
+      <c r="F82" s="102"/>
+      <c r="G82" s="102"/>
+      <c r="H82" s="104"/>
+      <c r="I82" s="106"/>
       <c r="J82" s="19"/>
       <c r="K82" s="20"/>
       <c r="L82" s="20"/>
@@ -12847,15 +12847,15 @@
       <c r="B83" s="36"/>
       <c r="C83" s="60"/>
       <c r="D83" s="70"/>
-      <c r="E83" s="103" t="s">
+      <c r="E83" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="F83" s="103"/>
-      <c r="G83" s="103"/>
-      <c r="H83" s="111">
+      <c r="F83" s="102"/>
+      <c r="G83" s="102"/>
+      <c r="H83" s="103">
         <v>45615</v>
       </c>
-      <c r="I83" s="126">
+      <c r="I83" s="105">
         <v>100</v>
       </c>
       <c r="J83" s="19"/>
@@ -12975,11 +12975,11 @@
       <c r="B84" s="36"/>
       <c r="C84" s="60"/>
       <c r="D84" s="70"/>
-      <c r="E84" s="103"/>
-      <c r="F84" s="103"/>
-      <c r="G84" s="103"/>
-      <c r="H84" s="107"/>
-      <c r="I84" s="109"/>
+      <c r="E84" s="102"/>
+      <c r="F84" s="102"/>
+      <c r="G84" s="102"/>
+      <c r="H84" s="104"/>
+      <c r="I84" s="106"/>
       <c r="J84" s="19"/>
       <c r="K84" s="20"/>
       <c r="L84" s="20"/>
@@ -13097,15 +13097,15 @@
       <c r="B85" s="36"/>
       <c r="C85" s="60"/>
       <c r="D85" s="70"/>
-      <c r="E85" s="114" t="s">
+      <c r="E85" s="189" t="s">
         <v>61</v>
       </c>
-      <c r="F85" s="115"/>
-      <c r="G85" s="116"/>
-      <c r="H85" s="110">
+      <c r="F85" s="121"/>
+      <c r="G85" s="122"/>
+      <c r="H85" s="111">
         <v>45617</v>
       </c>
-      <c r="I85" s="126">
+      <c r="I85" s="105">
         <v>100</v>
       </c>
       <c r="J85" s="62"/>
@@ -13225,11 +13225,11 @@
       <c r="B86" s="36"/>
       <c r="C86" s="60"/>
       <c r="D86" s="70"/>
-      <c r="E86" s="117"/>
-      <c r="F86" s="118"/>
-      <c r="G86" s="119"/>
-      <c r="H86" s="110"/>
-      <c r="I86" s="109"/>
+      <c r="E86" s="150"/>
+      <c r="F86" s="125"/>
+      <c r="G86" s="126"/>
+      <c r="H86" s="111"/>
+      <c r="I86" s="106"/>
       <c r="J86" s="62"/>
       <c r="K86" s="20"/>
       <c r="L86" s="20"/>
@@ -13346,16 +13346,16 @@
       <c r="A87" s="16"/>
       <c r="B87" s="71"/>
       <c r="C87" s="90"/>
-      <c r="D87" s="103" t="s">
+      <c r="D87" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="E87" s="103"/>
-      <c r="F87" s="103"/>
-      <c r="G87" s="103"/>
-      <c r="H87" s="111">
+      <c r="E87" s="102"/>
+      <c r="F87" s="102"/>
+      <c r="G87" s="102"/>
+      <c r="H87" s="103">
         <v>45615</v>
       </c>
-      <c r="I87" s="126">
+      <c r="I87" s="105">
         <v>100</v>
       </c>
       <c r="J87" s="62"/>
@@ -13474,12 +13474,12 @@
       <c r="A88" s="16"/>
       <c r="B88" s="71"/>
       <c r="C88" s="90"/>
-      <c r="D88" s="103"/>
-      <c r="E88" s="103"/>
-      <c r="F88" s="103"/>
-      <c r="G88" s="103"/>
-      <c r="H88" s="107"/>
-      <c r="I88" s="109"/>
+      <c r="D88" s="102"/>
+      <c r="E88" s="102"/>
+      <c r="F88" s="102"/>
+      <c r="G88" s="102"/>
+      <c r="H88" s="104"/>
+      <c r="I88" s="106"/>
       <c r="J88" s="62"/>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -13596,14 +13596,14 @@
       <c r="A89" s="16"/>
       <c r="B89" s="36"/>
       <c r="C89" s="79"/>
-      <c r="D89" s="132" t="s">
+      <c r="D89" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="133"/>
-      <c r="F89" s="133"/>
-      <c r="G89" s="134"/>
-      <c r="H89" s="131"/>
-      <c r="I89" s="128"/>
+      <c r="E89" s="116"/>
+      <c r="F89" s="116"/>
+      <c r="G89" s="117"/>
+      <c r="H89" s="187"/>
+      <c r="I89" s="188"/>
       <c r="J89" s="66"/>
       <c r="K89" s="64"/>
       <c r="L89" s="64"/>
@@ -13720,12 +13720,12 @@
       <c r="A90" s="16"/>
       <c r="B90" s="36"/>
       <c r="C90" s="79"/>
-      <c r="D90" s="135"/>
-      <c r="E90" s="136"/>
-      <c r="F90" s="136"/>
-      <c r="G90" s="137"/>
-      <c r="H90" s="131"/>
-      <c r="I90" s="128"/>
+      <c r="D90" s="118"/>
+      <c r="E90" s="119"/>
+      <c r="F90" s="119"/>
+      <c r="G90" s="120"/>
+      <c r="H90" s="187"/>
+      <c r="I90" s="188"/>
       <c r="J90" s="66"/>
       <c r="K90" s="64"/>
       <c r="L90" s="64"/>
@@ -13843,15 +13843,15 @@
       <c r="B91" s="36"/>
       <c r="C91" s="60"/>
       <c r="D91" s="70"/>
-      <c r="E91" s="105" t="s">
+      <c r="E91" s="149" t="s">
         <v>68</v>
       </c>
-      <c r="F91" s="105"/>
-      <c r="G91" s="105"/>
-      <c r="H91" s="111">
+      <c r="F91" s="149"/>
+      <c r="G91" s="149"/>
+      <c r="H91" s="103">
         <v>45616</v>
       </c>
-      <c r="I91" s="126">
+      <c r="I91" s="105">
         <v>100</v>
       </c>
       <c r="J91" s="19"/>
@@ -13971,11 +13971,11 @@
       <c r="B92" s="36"/>
       <c r="C92" s="60"/>
       <c r="D92" s="70"/>
-      <c r="E92" s="103"/>
-      <c r="F92" s="103"/>
-      <c r="G92" s="103"/>
-      <c r="H92" s="107"/>
-      <c r="I92" s="109"/>
+      <c r="E92" s="102"/>
+      <c r="F92" s="102"/>
+      <c r="G92" s="102"/>
+      <c r="H92" s="104"/>
+      <c r="I92" s="106"/>
       <c r="J92" s="19"/>
       <c r="K92" s="20"/>
       <c r="L92" s="20"/>
@@ -14093,15 +14093,15 @@
       <c r="B93" s="36"/>
       <c r="C93" s="60"/>
       <c r="D93" s="70"/>
-      <c r="E93" s="103" t="s">
+      <c r="E93" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="F93" s="103"/>
-      <c r="G93" s="103"/>
-      <c r="H93" s="111">
+      <c r="F93" s="102"/>
+      <c r="G93" s="102"/>
+      <c r="H93" s="103">
         <v>45617</v>
       </c>
-      <c r="I93" s="126">
+      <c r="I93" s="105">
         <v>100</v>
       </c>
       <c r="J93" s="19"/>
@@ -14221,11 +14221,11 @@
       <c r="B94" s="36"/>
       <c r="C94" s="60"/>
       <c r="D94" s="70"/>
-      <c r="E94" s="103"/>
-      <c r="F94" s="103"/>
-      <c r="G94" s="103"/>
-      <c r="H94" s="107"/>
-      <c r="I94" s="109"/>
+      <c r="E94" s="102"/>
+      <c r="F94" s="102"/>
+      <c r="G94" s="102"/>
+      <c r="H94" s="104"/>
+      <c r="I94" s="106"/>
       <c r="J94" s="19"/>
       <c r="K94" s="20"/>
       <c r="L94" s="20"/>
@@ -14343,15 +14343,15 @@
       <c r="B95" s="36"/>
       <c r="C95" s="60"/>
       <c r="D95" s="70"/>
-      <c r="E95" s="103" t="s">
+      <c r="E95" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="F95" s="103"/>
-      <c r="G95" s="103"/>
-      <c r="H95" s="111">
+      <c r="F95" s="102"/>
+      <c r="G95" s="102"/>
+      <c r="H95" s="103">
         <v>45618</v>
       </c>
-      <c r="I95" s="126">
+      <c r="I95" s="105">
         <v>100</v>
       </c>
       <c r="J95" s="19"/>
@@ -14471,11 +14471,11 @@
       <c r="B96" s="36"/>
       <c r="C96" s="60"/>
       <c r="D96" s="70"/>
-      <c r="E96" s="103"/>
-      <c r="F96" s="103"/>
-      <c r="G96" s="103"/>
-      <c r="H96" s="107"/>
-      <c r="I96" s="109"/>
+      <c r="E96" s="102"/>
+      <c r="F96" s="102"/>
+      <c r="G96" s="102"/>
+      <c r="H96" s="104"/>
+      <c r="I96" s="106"/>
       <c r="J96" s="19"/>
       <c r="K96" s="20"/>
       <c r="L96" s="20"/>
@@ -14593,15 +14593,15 @@
       <c r="B97" s="36"/>
       <c r="C97" s="60"/>
       <c r="D97" s="70"/>
-      <c r="E97" s="103" t="s">
+      <c r="E97" s="102" t="s">
         <v>71</v>
       </c>
-      <c r="F97" s="103"/>
-      <c r="G97" s="103"/>
-      <c r="H97" s="111">
+      <c r="F97" s="102"/>
+      <c r="G97" s="102"/>
+      <c r="H97" s="103">
         <v>45621</v>
       </c>
-      <c r="I97" s="126">
+      <c r="I97" s="105">
         <v>100</v>
       </c>
       <c r="J97" s="19"/>
@@ -14721,11 +14721,11 @@
       <c r="B98" s="36"/>
       <c r="C98" s="60"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="103"/>
-      <c r="F98" s="103"/>
-      <c r="G98" s="103"/>
-      <c r="H98" s="107"/>
-      <c r="I98" s="109"/>
+      <c r="E98" s="102"/>
+      <c r="F98" s="102"/>
+      <c r="G98" s="102"/>
+      <c r="H98" s="104"/>
+      <c r="I98" s="106"/>
       <c r="J98" s="19"/>
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
@@ -14843,15 +14843,15 @@
       <c r="B99" s="36"/>
       <c r="C99" s="60"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="103" t="s">
+      <c r="E99" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="F99" s="103"/>
-      <c r="G99" s="103"/>
-      <c r="H99" s="111">
+      <c r="F99" s="102"/>
+      <c r="G99" s="102"/>
+      <c r="H99" s="103">
         <v>45622</v>
       </c>
-      <c r="I99" s="126">
+      <c r="I99" s="105">
         <v>100</v>
       </c>
       <c r="J99" s="19"/>
@@ -14971,11 +14971,11 @@
       <c r="B100" s="36"/>
       <c r="C100" s="60"/>
       <c r="D100" s="70"/>
-      <c r="E100" s="103"/>
-      <c r="F100" s="103"/>
-      <c r="G100" s="103"/>
-      <c r="H100" s="107"/>
-      <c r="I100" s="109"/>
+      <c r="E100" s="102"/>
+      <c r="F100" s="102"/>
+      <c r="G100" s="102"/>
+      <c r="H100" s="104"/>
+      <c r="I100" s="106"/>
       <c r="J100" s="19"/>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -15093,12 +15093,12 @@
       <c r="B101" s="71"/>
       <c r="C101" s="91"/>
       <c r="D101" s="70"/>
-      <c r="E101" s="117" t="s">
+      <c r="E101" s="150" t="s">
         <v>61</v>
       </c>
-      <c r="F101" s="118"/>
-      <c r="G101" s="119"/>
-      <c r="H101" s="111">
+      <c r="F101" s="125"/>
+      <c r="G101" s="126"/>
+      <c r="H101" s="103">
         <v>45623</v>
       </c>
       <c r="I101" s="112">
@@ -15221,10 +15221,10 @@
       <c r="B102" s="71"/>
       <c r="C102" s="91"/>
       <c r="D102" s="70"/>
-      <c r="E102" s="117"/>
-      <c r="F102" s="118"/>
-      <c r="G102" s="119"/>
-      <c r="H102" s="107"/>
+      <c r="E102" s="150"/>
+      <c r="F102" s="125"/>
+      <c r="G102" s="126"/>
+      <c r="H102" s="104"/>
       <c r="I102" s="112"/>
       <c r="J102" s="62"/>
       <c r="K102" s="20"/>
@@ -15342,16 +15342,16 @@
       <c r="A103" s="16"/>
       <c r="B103" s="71"/>
       <c r="C103" s="90"/>
-      <c r="D103" s="103" t="s">
+      <c r="D103" s="102" t="s">
         <v>77</v>
       </c>
-      <c r="E103" s="103"/>
-      <c r="F103" s="103"/>
-      <c r="G103" s="103"/>
-      <c r="H103" s="111">
+      <c r="E103" s="102"/>
+      <c r="F103" s="102"/>
+      <c r="G103" s="102"/>
+      <c r="H103" s="103">
         <v>45622</v>
       </c>
-      <c r="I103" s="113">
+      <c r="I103" s="109">
         <v>100</v>
       </c>
       <c r="J103" s="62"/>
@@ -15470,12 +15470,12 @@
       <c r="A104" s="16"/>
       <c r="B104" s="71"/>
       <c r="C104" s="90"/>
-      <c r="D104" s="103"/>
-      <c r="E104" s="103"/>
-      <c r="F104" s="103"/>
-      <c r="G104" s="103"/>
-      <c r="H104" s="107"/>
-      <c r="I104" s="143"/>
+      <c r="D104" s="102"/>
+      <c r="E104" s="102"/>
+      <c r="F104" s="102"/>
+      <c r="G104" s="102"/>
+      <c r="H104" s="104"/>
+      <c r="I104" s="110"/>
       <c r="J104" s="62"/>
       <c r="K104" s="20"/>
       <c r="L104" s="20"/>
@@ -15591,15 +15591,15 @@
     <row r="105" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A105" s="16"/>
       <c r="B105" s="71"/>
-      <c r="C105" s="187" t="s">
+      <c r="C105" s="143" t="s">
         <v>64</v>
       </c>
-      <c r="D105" s="188"/>
-      <c r="E105" s="188"/>
-      <c r="F105" s="188"/>
-      <c r="G105" s="189"/>
-      <c r="H105" s="127"/>
-      <c r="I105" s="128"/>
+      <c r="D105" s="144"/>
+      <c r="E105" s="144"/>
+      <c r="F105" s="144"/>
+      <c r="G105" s="145"/>
+      <c r="H105" s="190"/>
+      <c r="I105" s="188"/>
       <c r="J105" s="66"/>
       <c r="K105" s="64"/>
       <c r="L105" s="64"/>
@@ -15715,13 +15715,13 @@
     <row r="106" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A106" s="16"/>
       <c r="B106" s="71"/>
-      <c r="C106" s="190"/>
-      <c r="D106" s="191"/>
-      <c r="E106" s="191"/>
-      <c r="F106" s="191"/>
-      <c r="G106" s="192"/>
-      <c r="H106" s="127"/>
-      <c r="I106" s="128"/>
+      <c r="C106" s="146"/>
+      <c r="D106" s="147"/>
+      <c r="E106" s="147"/>
+      <c r="F106" s="147"/>
+      <c r="G106" s="148"/>
+      <c r="H106" s="190"/>
+      <c r="I106" s="188"/>
       <c r="J106" s="66"/>
       <c r="K106" s="64"/>
       <c r="L106" s="64"/>
@@ -15838,14 +15838,14 @@
       <c r="A107" s="16"/>
       <c r="B107" s="36"/>
       <c r="C107" s="78"/>
-      <c r="D107" s="132" t="s">
+      <c r="D107" s="115" t="s">
         <v>59</v>
       </c>
-      <c r="E107" s="133"/>
-      <c r="F107" s="133"/>
-      <c r="G107" s="134"/>
-      <c r="H107" s="127"/>
-      <c r="I107" s="128"/>
+      <c r="E107" s="116"/>
+      <c r="F107" s="116"/>
+      <c r="G107" s="117"/>
+      <c r="H107" s="190"/>
+      <c r="I107" s="188"/>
       <c r="J107" s="66"/>
       <c r="K107" s="64"/>
       <c r="L107" s="64"/>
@@ -15962,12 +15962,12 @@
       <c r="A108" s="16"/>
       <c r="B108" s="36"/>
       <c r="C108" s="76"/>
-      <c r="D108" s="135"/>
-      <c r="E108" s="136"/>
-      <c r="F108" s="136"/>
-      <c r="G108" s="137"/>
-      <c r="H108" s="127"/>
-      <c r="I108" s="128"/>
+      <c r="D108" s="118"/>
+      <c r="E108" s="119"/>
+      <c r="F108" s="119"/>
+      <c r="G108" s="120"/>
+      <c r="H108" s="190"/>
+      <c r="I108" s="188"/>
       <c r="J108" s="66"/>
       <c r="K108" s="64"/>
       <c r="L108" s="64"/>
@@ -16085,15 +16085,15 @@
       <c r="B109" s="36"/>
       <c r="C109" s="60"/>
       <c r="D109" s="70"/>
-      <c r="E109" s="105" t="s">
+      <c r="E109" s="149" t="s">
         <v>73</v>
       </c>
-      <c r="F109" s="105"/>
-      <c r="G109" s="105"/>
-      <c r="H109" s="111">
+      <c r="F109" s="149"/>
+      <c r="G109" s="149"/>
+      <c r="H109" s="103">
         <v>45624</v>
       </c>
-      <c r="I109" s="113">
+      <c r="I109" s="109">
         <v>100</v>
       </c>
       <c r="J109" s="62"/>
@@ -16213,11 +16213,11 @@
       <c r="B110" s="36"/>
       <c r="C110" s="60"/>
       <c r="D110" s="70"/>
-      <c r="E110" s="103"/>
-      <c r="F110" s="103"/>
-      <c r="G110" s="103"/>
-      <c r="H110" s="107"/>
-      <c r="I110" s="143"/>
+      <c r="E110" s="102"/>
+      <c r="F110" s="102"/>
+      <c r="G110" s="102"/>
+      <c r="H110" s="104"/>
+      <c r="I110" s="110"/>
       <c r="J110" s="62"/>
       <c r="K110" s="20"/>
       <c r="L110" s="20"/>
@@ -16335,15 +16335,15 @@
       <c r="B111" s="36"/>
       <c r="C111" s="60"/>
       <c r="D111" s="70"/>
-      <c r="E111" s="103" t="s">
+      <c r="E111" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="F111" s="103"/>
-      <c r="G111" s="103"/>
-      <c r="H111" s="111">
+      <c r="F111" s="102"/>
+      <c r="G111" s="102"/>
+      <c r="H111" s="103">
         <v>45625</v>
       </c>
-      <c r="I111" s="113"/>
+      <c r="I111" s="109"/>
       <c r="J111" s="62"/>
       <c r="K111" s="20"/>
       <c r="L111" s="20"/>
@@ -16461,11 +16461,11 @@
       <c r="B112" s="36"/>
       <c r="C112" s="60"/>
       <c r="D112" s="70"/>
-      <c r="E112" s="103"/>
-      <c r="F112" s="103"/>
-      <c r="G112" s="103"/>
-      <c r="H112" s="107"/>
-      <c r="I112" s="143"/>
+      <c r="E112" s="102"/>
+      <c r="F112" s="102"/>
+      <c r="G112" s="102"/>
+      <c r="H112" s="104"/>
+      <c r="I112" s="110"/>
       <c r="J112" s="62"/>
       <c r="K112" s="20"/>
       <c r="L112" s="20"/>
@@ -16583,12 +16583,12 @@
       <c r="B113" s="71"/>
       <c r="C113" s="91"/>
       <c r="D113" s="70"/>
-      <c r="E113" s="103" t="s">
+      <c r="E113" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="F113" s="103"/>
-      <c r="G113" s="103"/>
-      <c r="H113" s="110">
+      <c r="F113" s="102"/>
+      <c r="G113" s="102"/>
+      <c r="H113" s="111">
         <v>45629</v>
       </c>
       <c r="I113" s="112"/>
@@ -16709,11 +16709,11 @@
       <c r="B114" s="71"/>
       <c r="C114" s="91"/>
       <c r="D114" s="70"/>
-      <c r="E114" s="125"/>
-      <c r="F114" s="125"/>
-      <c r="G114" s="125"/>
-      <c r="H114" s="111"/>
-      <c r="I114" s="113"/>
+      <c r="E114" s="198"/>
+      <c r="F114" s="198"/>
+      <c r="G114" s="198"/>
+      <c r="H114" s="103"/>
+      <c r="I114" s="109"/>
       <c r="J114" s="62"/>
       <c r="K114" s="20"/>
       <c r="L114" s="20"/>
@@ -16830,13 +16830,13 @@
       <c r="A115" s="16"/>
       <c r="B115" s="71"/>
       <c r="C115" s="91"/>
-      <c r="D115" s="103" t="s">
+      <c r="D115" s="102" t="s">
         <v>78</v>
       </c>
-      <c r="E115" s="103"/>
-      <c r="F115" s="103"/>
-      <c r="G115" s="103"/>
-      <c r="H115" s="110">
+      <c r="E115" s="102"/>
+      <c r="F115" s="102"/>
+      <c r="G115" s="102"/>
+      <c r="H115" s="111">
         <v>45625</v>
       </c>
       <c r="I115" s="112"/>
@@ -16956,11 +16956,11 @@
       <c r="A116" s="16"/>
       <c r="B116" s="71"/>
       <c r="C116" s="91"/>
-      <c r="D116" s="103"/>
-      <c r="E116" s="103"/>
-      <c r="F116" s="103"/>
-      <c r="G116" s="103"/>
-      <c r="H116" s="110"/>
+      <c r="D116" s="102"/>
+      <c r="E116" s="102"/>
+      <c r="F116" s="102"/>
+      <c r="G116" s="102"/>
+      <c r="H116" s="111"/>
       <c r="I116" s="112"/>
       <c r="J116" s="62"/>
       <c r="K116" s="20"/>
@@ -17078,14 +17078,14 @@
       <c r="A117" s="16"/>
       <c r="B117" s="36"/>
       <c r="C117" s="80"/>
-      <c r="D117" s="132" t="s">
+      <c r="D117" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="E117" s="133"/>
-      <c r="F117" s="133"/>
-      <c r="G117" s="134"/>
-      <c r="H117" s="121"/>
-      <c r="I117" s="129"/>
+      <c r="E117" s="116"/>
+      <c r="F117" s="116"/>
+      <c r="G117" s="117"/>
+      <c r="H117" s="191"/>
+      <c r="I117" s="181"/>
       <c r="J117" s="63"/>
       <c r="K117" s="64"/>
       <c r="L117" s="64"/>
@@ -17202,12 +17202,12 @@
       <c r="A118" s="16"/>
       <c r="B118" s="36"/>
       <c r="C118" s="80"/>
-      <c r="D118" s="135"/>
-      <c r="E118" s="136"/>
-      <c r="F118" s="136"/>
-      <c r="G118" s="137"/>
-      <c r="H118" s="122"/>
-      <c r="I118" s="130"/>
+      <c r="D118" s="118"/>
+      <c r="E118" s="119"/>
+      <c r="F118" s="119"/>
+      <c r="G118" s="120"/>
+      <c r="H118" s="192"/>
+      <c r="I118" s="182"/>
       <c r="J118" s="63"/>
       <c r="K118" s="64"/>
       <c r="L118" s="64"/>
@@ -17325,15 +17325,15 @@
       <c r="B119" s="36"/>
       <c r="C119" s="60"/>
       <c r="D119" s="70"/>
-      <c r="E119" s="105" t="s">
+      <c r="E119" s="149" t="s">
         <v>68</v>
       </c>
-      <c r="F119" s="105"/>
-      <c r="G119" s="105"/>
-      <c r="H119" s="111">
+      <c r="F119" s="149"/>
+      <c r="G119" s="149"/>
+      <c r="H119" s="103">
         <v>45629</v>
       </c>
-      <c r="I119" s="126">
+      <c r="I119" s="105">
         <v>100</v>
       </c>
       <c r="J119" s="19"/>
@@ -17453,11 +17453,11 @@
       <c r="B120" s="36"/>
       <c r="C120" s="60"/>
       <c r="D120" s="70"/>
-      <c r="E120" s="103"/>
-      <c r="F120" s="103"/>
-      <c r="G120" s="103"/>
-      <c r="H120" s="107"/>
-      <c r="I120" s="109"/>
+      <c r="E120" s="102"/>
+      <c r="F120" s="102"/>
+      <c r="G120" s="102"/>
+      <c r="H120" s="104"/>
+      <c r="I120" s="106"/>
       <c r="J120" s="19"/>
       <c r="K120" s="20"/>
       <c r="L120" s="20"/>
@@ -17575,15 +17575,15 @@
       <c r="B121" s="36"/>
       <c r="C121" s="60"/>
       <c r="D121" s="70"/>
-      <c r="E121" s="103" t="s">
+      <c r="E121" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="F121" s="103"/>
-      <c r="G121" s="103"/>
-      <c r="H121" s="111">
+      <c r="F121" s="102"/>
+      <c r="G121" s="102"/>
+      <c r="H121" s="103">
         <v>45630</v>
       </c>
-      <c r="I121" s="126"/>
+      <c r="I121" s="105"/>
       <c r="J121" s="19"/>
       <c r="K121" s="20"/>
       <c r="L121" s="20"/>
@@ -17701,11 +17701,11 @@
       <c r="B122" s="36"/>
       <c r="C122" s="60"/>
       <c r="D122" s="70"/>
-      <c r="E122" s="103"/>
-      <c r="F122" s="103"/>
-      <c r="G122" s="103"/>
-      <c r="H122" s="107"/>
-      <c r="I122" s="109"/>
+      <c r="E122" s="102"/>
+      <c r="F122" s="102"/>
+      <c r="G122" s="102"/>
+      <c r="H122" s="104"/>
+      <c r="I122" s="106"/>
       <c r="J122" s="19"/>
       <c r="K122" s="20"/>
       <c r="L122" s="20"/>
@@ -17823,12 +17823,12 @@
       <c r="B123" s="36"/>
       <c r="C123" s="60"/>
       <c r="D123" s="70"/>
-      <c r="E123" s="103" t="s">
+      <c r="E123" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="F123" s="103"/>
-      <c r="G123" s="103"/>
-      <c r="H123" s="120">
+      <c r="F123" s="102"/>
+      <c r="G123" s="102"/>
+      <c r="H123" s="197">
         <v>45631</v>
       </c>
       <c r="I123" s="112"/>
@@ -17949,10 +17949,10 @@
       <c r="B124" s="36"/>
       <c r="C124" s="60"/>
       <c r="D124" s="70"/>
-      <c r="E124" s="103"/>
-      <c r="F124" s="103"/>
-      <c r="G124" s="103"/>
-      <c r="H124" s="120"/>
+      <c r="E124" s="102"/>
+      <c r="F124" s="102"/>
+      <c r="G124" s="102"/>
+      <c r="H124" s="197"/>
       <c r="I124" s="112"/>
       <c r="J124" s="62"/>
       <c r="K124" s="20"/>
@@ -18005,7 +18005,7 @@
       <c r="BF124" s="21"/>
       <c r="BG124" s="20"/>
       <c r="BH124" s="20"/>
-      <c r="BI124" s="20"/>
+      <c r="BI124" s="75"/>
       <c r="BJ124" s="64"/>
       <c r="BK124" s="64"/>
       <c r="BL124" s="21"/>
@@ -18071,12 +18071,12 @@
       <c r="B125" s="36"/>
       <c r="C125" s="60"/>
       <c r="D125" s="70"/>
-      <c r="E125" s="103" t="s">
+      <c r="E125" s="102" t="s">
         <v>71</v>
       </c>
-      <c r="F125" s="103"/>
-      <c r="G125" s="103"/>
-      <c r="H125" s="110">
+      <c r="F125" s="102"/>
+      <c r="G125" s="102"/>
+      <c r="H125" s="111">
         <v>45632</v>
       </c>
       <c r="I125" s="112"/>
@@ -18197,10 +18197,10 @@
       <c r="B126" s="36"/>
       <c r="C126" s="60"/>
       <c r="D126" s="70"/>
-      <c r="E126" s="103"/>
-      <c r="F126" s="103"/>
-      <c r="G126" s="103"/>
-      <c r="H126" s="110"/>
+      <c r="E126" s="102"/>
+      <c r="F126" s="102"/>
+      <c r="G126" s="102"/>
+      <c r="H126" s="111"/>
       <c r="I126" s="112"/>
       <c r="J126" s="62"/>
       <c r="K126" s="20"/>
@@ -18319,15 +18319,15 @@
       <c r="B127" s="36"/>
       <c r="C127" s="60"/>
       <c r="D127" s="70"/>
-      <c r="E127" s="103" t="s">
+      <c r="E127" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="F127" s="103"/>
-      <c r="G127" s="103"/>
-      <c r="H127" s="111">
+      <c r="F127" s="102"/>
+      <c r="G127" s="102"/>
+      <c r="H127" s="103">
         <v>45635</v>
       </c>
-      <c r="I127" s="126"/>
+      <c r="I127" s="105"/>
       <c r="J127" s="19"/>
       <c r="K127" s="20"/>
       <c r="L127" s="20"/>
@@ -18445,11 +18445,11 @@
       <c r="B128" s="36"/>
       <c r="C128" s="60"/>
       <c r="D128" s="70"/>
-      <c r="E128" s="125"/>
-      <c r="F128" s="125"/>
-      <c r="G128" s="125"/>
-      <c r="H128" s="107"/>
-      <c r="I128" s="109"/>
+      <c r="E128" s="198"/>
+      <c r="F128" s="198"/>
+      <c r="G128" s="198"/>
+      <c r="H128" s="104"/>
+      <c r="I128" s="106"/>
       <c r="J128" s="19"/>
       <c r="K128" s="20"/>
       <c r="L128" s="20"/>
@@ -18567,12 +18567,12 @@
       <c r="B129" s="71"/>
       <c r="C129" s="91"/>
       <c r="D129" s="70"/>
-      <c r="E129" s="114" t="s">
+      <c r="E129" s="189" t="s">
         <v>61</v>
       </c>
-      <c r="F129" s="115"/>
-      <c r="G129" s="116"/>
-      <c r="H129" s="110">
+      <c r="F129" s="121"/>
+      <c r="G129" s="122"/>
+      <c r="H129" s="111">
         <v>45638</v>
       </c>
       <c r="I129" s="112"/>
@@ -18693,10 +18693,10 @@
       <c r="B130" s="71"/>
       <c r="C130" s="91"/>
       <c r="D130" s="70"/>
-      <c r="E130" s="117"/>
-      <c r="F130" s="118"/>
-      <c r="G130" s="119"/>
-      <c r="H130" s="110"/>
+      <c r="E130" s="150"/>
+      <c r="F130" s="125"/>
+      <c r="G130" s="126"/>
+      <c r="H130" s="111"/>
       <c r="I130" s="112"/>
       <c r="J130" s="62"/>
       <c r="K130" s="20"/>
@@ -18814,16 +18814,16 @@
       <c r="A131" s="16"/>
       <c r="B131" s="71"/>
       <c r="C131" s="91"/>
-      <c r="D131" s="103" t="s">
+      <c r="D131" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="E131" s="103"/>
-      <c r="F131" s="103"/>
-      <c r="G131" s="103"/>
-      <c r="H131" s="111">
+      <c r="E131" s="102"/>
+      <c r="F131" s="102"/>
+      <c r="G131" s="102"/>
+      <c r="H131" s="103">
         <v>45635</v>
       </c>
-      <c r="I131" s="113"/>
+      <c r="I131" s="109"/>
       <c r="J131" s="62"/>
       <c r="K131" s="20"/>
       <c r="L131" s="20"/>
@@ -18940,12 +18940,12 @@
       <c r="A132" s="16"/>
       <c r="B132" s="71"/>
       <c r="C132" s="90"/>
-      <c r="D132" s="103"/>
-      <c r="E132" s="103"/>
-      <c r="F132" s="103"/>
-      <c r="G132" s="103"/>
-      <c r="H132" s="107"/>
-      <c r="I132" s="143"/>
+      <c r="D132" s="102"/>
+      <c r="E132" s="102"/>
+      <c r="F132" s="102"/>
+      <c r="G132" s="102"/>
+      <c r="H132" s="104"/>
+      <c r="I132" s="110"/>
       <c r="J132" s="62"/>
       <c r="K132" s="20"/>
       <c r="L132" s="20"/>
@@ -19061,15 +19061,15 @@
     <row r="133" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A133" s="16"/>
       <c r="B133" s="36"/>
-      <c r="C133" s="132" t="s">
+      <c r="C133" s="115" t="s">
         <v>67</v>
       </c>
-      <c r="D133" s="133"/>
-      <c r="E133" s="133"/>
-      <c r="F133" s="133"/>
-      <c r="G133" s="134"/>
-      <c r="H133" s="121"/>
-      <c r="I133" s="123"/>
+      <c r="D133" s="116"/>
+      <c r="E133" s="116"/>
+      <c r="F133" s="116"/>
+      <c r="G133" s="117"/>
+      <c r="H133" s="191"/>
+      <c r="I133" s="107"/>
       <c r="J133" s="66"/>
       <c r="K133" s="64"/>
       <c r="L133" s="64"/>
@@ -19185,13 +19185,13 @@
     <row r="134" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A134" s="16"/>
       <c r="B134" s="36"/>
-      <c r="C134" s="135"/>
-      <c r="D134" s="136"/>
-      <c r="E134" s="136"/>
-      <c r="F134" s="136"/>
-      <c r="G134" s="137"/>
-      <c r="H134" s="122"/>
-      <c r="I134" s="124"/>
+      <c r="C134" s="118"/>
+      <c r="D134" s="119"/>
+      <c r="E134" s="119"/>
+      <c r="F134" s="119"/>
+      <c r="G134" s="120"/>
+      <c r="H134" s="192"/>
+      <c r="I134" s="108"/>
       <c r="J134" s="66"/>
       <c r="K134" s="64"/>
       <c r="L134" s="64"/>
@@ -19308,14 +19308,14 @@
       <c r="A135" s="16"/>
       <c r="B135" s="36"/>
       <c r="C135" s="60"/>
-      <c r="D135" s="132" t="s">
+      <c r="D135" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="133"/>
-      <c r="F135" s="133"/>
-      <c r="G135" s="134"/>
-      <c r="H135" s="193"/>
-      <c r="I135" s="129"/>
+      <c r="E135" s="116"/>
+      <c r="F135" s="116"/>
+      <c r="G135" s="117"/>
+      <c r="H135" s="113"/>
+      <c r="I135" s="181"/>
       <c r="J135" s="63"/>
       <c r="K135" s="64"/>
       <c r="L135" s="64"/>
@@ -19432,12 +19432,12 @@
       <c r="A136" s="16"/>
       <c r="B136" s="36"/>
       <c r="C136" s="60"/>
-      <c r="D136" s="135"/>
-      <c r="E136" s="136"/>
-      <c r="F136" s="136"/>
-      <c r="G136" s="137"/>
-      <c r="H136" s="198"/>
-      <c r="I136" s="144"/>
+      <c r="D136" s="118"/>
+      <c r="E136" s="119"/>
+      <c r="F136" s="119"/>
+      <c r="G136" s="120"/>
+      <c r="H136" s="130"/>
+      <c r="I136" s="183"/>
       <c r="J136" s="63"/>
       <c r="K136" s="64"/>
       <c r="L136" s="64"/>
@@ -19555,15 +19555,15 @@
       <c r="B137" s="36"/>
       <c r="C137" s="72"/>
       <c r="D137" s="74"/>
-      <c r="E137" s="115" t="s">
+      <c r="E137" s="121" t="s">
         <v>73</v>
       </c>
-      <c r="F137" s="115"/>
-      <c r="G137" s="116"/>
-      <c r="H137" s="111">
+      <c r="F137" s="121"/>
+      <c r="G137" s="122"/>
+      <c r="H137" s="103">
         <v>45636</v>
       </c>
-      <c r="I137" s="113"/>
+      <c r="I137" s="109"/>
       <c r="J137" s="62"/>
       <c r="K137" s="20"/>
       <c r="L137" s="20"/>
@@ -19681,11 +19681,11 @@
       <c r="B138" s="36"/>
       <c r="C138" s="72"/>
       <c r="D138" s="70"/>
-      <c r="E138" s="185"/>
-      <c r="F138" s="185"/>
-      <c r="G138" s="186"/>
-      <c r="H138" s="107"/>
-      <c r="I138" s="143"/>
+      <c r="E138" s="123"/>
+      <c r="F138" s="123"/>
+      <c r="G138" s="124"/>
+      <c r="H138" s="104"/>
+      <c r="I138" s="110"/>
       <c r="J138" s="62"/>
       <c r="K138" s="20"/>
       <c r="L138" s="20"/>
@@ -19803,15 +19803,15 @@
       <c r="B139" s="36"/>
       <c r="C139" s="72"/>
       <c r="D139" s="70"/>
-      <c r="E139" s="115" t="s">
+      <c r="E139" s="121" t="s">
         <v>74</v>
       </c>
-      <c r="F139" s="115"/>
-      <c r="G139" s="116"/>
-      <c r="H139" s="111">
+      <c r="F139" s="121"/>
+      <c r="G139" s="122"/>
+      <c r="H139" s="103">
         <v>45637</v>
       </c>
-      <c r="I139" s="113"/>
+      <c r="I139" s="109"/>
       <c r="J139" s="62"/>
       <c r="K139" s="20"/>
       <c r="L139" s="20"/>
@@ -19929,11 +19929,11 @@
       <c r="B140" s="36"/>
       <c r="C140" s="72"/>
       <c r="D140" s="70"/>
-      <c r="E140" s="118"/>
-      <c r="F140" s="118"/>
-      <c r="G140" s="119"/>
-      <c r="H140" s="107"/>
-      <c r="I140" s="143"/>
+      <c r="E140" s="125"/>
+      <c r="F140" s="125"/>
+      <c r="G140" s="126"/>
+      <c r="H140" s="104"/>
+      <c r="I140" s="110"/>
       <c r="J140" s="62"/>
       <c r="K140" s="20"/>
       <c r="L140" s="20"/>
@@ -20050,13 +20050,13 @@
       <c r="A141" s="16"/>
       <c r="B141" s="36"/>
       <c r="C141" s="82"/>
-      <c r="D141" s="103" t="s">
+      <c r="D141" s="102" t="s">
         <v>80</v>
       </c>
-      <c r="E141" s="103"/>
-      <c r="F141" s="103"/>
-      <c r="G141" s="103"/>
-      <c r="H141" s="111">
+      <c r="E141" s="102"/>
+      <c r="F141" s="102"/>
+      <c r="G141" s="102"/>
+      <c r="H141" s="103">
         <v>45637</v>
       </c>
       <c r="I141" s="92"/>
@@ -20176,11 +20176,11 @@
       <c r="A142" s="16"/>
       <c r="B142" s="36"/>
       <c r="C142" s="82"/>
-      <c r="D142" s="103"/>
-      <c r="E142" s="103"/>
-      <c r="F142" s="103"/>
-      <c r="G142" s="103"/>
-      <c r="H142" s="107"/>
+      <c r="D142" s="102"/>
+      <c r="E142" s="102"/>
+      <c r="F142" s="102"/>
+      <c r="G142" s="102"/>
+      <c r="H142" s="104"/>
       <c r="I142" s="92"/>
       <c r="J142" s="62"/>
       <c r="K142" s="20"/>
@@ -20298,14 +20298,14 @@
       <c r="A143" s="16"/>
       <c r="B143" s="36"/>
       <c r="C143" s="72"/>
-      <c r="D143" s="195" t="s">
+      <c r="D143" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="E143" s="196"/>
-      <c r="F143" s="196"/>
-      <c r="G143" s="197"/>
-      <c r="H143" s="193"/>
-      <c r="I143" s="123"/>
+      <c r="E143" s="128"/>
+      <c r="F143" s="128"/>
+      <c r="G143" s="129"/>
+      <c r="H143" s="113"/>
+      <c r="I143" s="107"/>
       <c r="J143" s="66"/>
       <c r="K143" s="64"/>
       <c r="L143" s="64"/>
@@ -20422,12 +20422,12 @@
       <c r="A144" s="16"/>
       <c r="B144" s="36"/>
       <c r="C144" s="72"/>
-      <c r="D144" s="135"/>
-      <c r="E144" s="136"/>
-      <c r="F144" s="136"/>
-      <c r="G144" s="137"/>
-      <c r="H144" s="194"/>
-      <c r="I144" s="124"/>
+      <c r="D144" s="118"/>
+      <c r="E144" s="119"/>
+      <c r="F144" s="119"/>
+      <c r="G144" s="120"/>
+      <c r="H144" s="114"/>
+      <c r="I144" s="108"/>
       <c r="J144" s="66"/>
       <c r="K144" s="64"/>
       <c r="L144" s="64"/>
@@ -20545,15 +20545,15 @@
       <c r="B145" s="36"/>
       <c r="C145" s="72"/>
       <c r="D145" s="74"/>
-      <c r="E145" s="115" t="s">
+      <c r="E145" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="F145" s="115"/>
-      <c r="G145" s="116"/>
-      <c r="H145" s="111">
+      <c r="F145" s="121"/>
+      <c r="G145" s="122"/>
+      <c r="H145" s="103">
         <v>45639</v>
       </c>
-      <c r="I145" s="113"/>
+      <c r="I145" s="109"/>
       <c r="J145" s="62"/>
       <c r="K145" s="20"/>
       <c r="L145" s="20"/>
@@ -20671,11 +20671,11 @@
       <c r="B146" s="36"/>
       <c r="C146" s="72"/>
       <c r="D146" s="70"/>
-      <c r="E146" s="185"/>
-      <c r="F146" s="185"/>
-      <c r="G146" s="186"/>
-      <c r="H146" s="107"/>
-      <c r="I146" s="143"/>
+      <c r="E146" s="123"/>
+      <c r="F146" s="123"/>
+      <c r="G146" s="124"/>
+      <c r="H146" s="104"/>
+      <c r="I146" s="110"/>
       <c r="J146" s="62"/>
       <c r="K146" s="20"/>
       <c r="L146" s="20"/>
@@ -20793,15 +20793,15 @@
       <c r="B147" s="36"/>
       <c r="C147" s="72"/>
       <c r="D147" s="70"/>
-      <c r="E147" s="115" t="s">
+      <c r="E147" s="121" t="s">
         <v>69</v>
       </c>
-      <c r="F147" s="115"/>
-      <c r="G147" s="116"/>
-      <c r="H147" s="111">
+      <c r="F147" s="121"/>
+      <c r="G147" s="122"/>
+      <c r="H147" s="103">
         <v>45642</v>
       </c>
-      <c r="I147" s="113"/>
+      <c r="I147" s="109"/>
       <c r="J147" s="62"/>
       <c r="K147" s="20"/>
       <c r="L147" s="20"/>
@@ -20919,11 +20919,11 @@
       <c r="B148" s="36"/>
       <c r="C148" s="72"/>
       <c r="D148" s="70"/>
-      <c r="E148" s="185"/>
-      <c r="F148" s="185"/>
-      <c r="G148" s="186"/>
-      <c r="H148" s="107"/>
-      <c r="I148" s="143"/>
+      <c r="E148" s="123"/>
+      <c r="F148" s="123"/>
+      <c r="G148" s="124"/>
+      <c r="H148" s="104"/>
+      <c r="I148" s="110"/>
       <c r="J148" s="62"/>
       <c r="K148" s="20"/>
       <c r="L148" s="20"/>
@@ -21041,15 +21041,15 @@
       <c r="B149" s="36"/>
       <c r="C149" s="72"/>
       <c r="D149" s="70"/>
-      <c r="E149" s="115" t="s">
+      <c r="E149" s="121" t="s">
         <v>70</v>
       </c>
-      <c r="F149" s="115"/>
-      <c r="G149" s="116"/>
-      <c r="H149" s="111">
+      <c r="F149" s="121"/>
+      <c r="G149" s="122"/>
+      <c r="H149" s="103">
         <v>45643</v>
       </c>
-      <c r="I149" s="113"/>
+      <c r="I149" s="109"/>
       <c r="J149" s="62"/>
       <c r="K149" s="20"/>
       <c r="L149" s="20"/>
@@ -21167,11 +21167,11 @@
       <c r="B150" s="36"/>
       <c r="C150" s="72"/>
       <c r="D150" s="70"/>
-      <c r="E150" s="185"/>
-      <c r="F150" s="185"/>
-      <c r="G150" s="186"/>
-      <c r="H150" s="107"/>
-      <c r="I150" s="143"/>
+      <c r="E150" s="123"/>
+      <c r="F150" s="123"/>
+      <c r="G150" s="124"/>
+      <c r="H150" s="104"/>
+      <c r="I150" s="110"/>
       <c r="J150" s="62"/>
       <c r="K150" s="20"/>
       <c r="L150" s="20"/>
@@ -21289,15 +21289,15 @@
       <c r="B151" s="36"/>
       <c r="C151" s="72"/>
       <c r="D151" s="70"/>
-      <c r="E151" s="103" t="s">
+      <c r="E151" s="102" t="s">
         <v>75</v>
       </c>
-      <c r="F151" s="103"/>
-      <c r="G151" s="103"/>
-      <c r="H151" s="111">
+      <c r="F151" s="102"/>
+      <c r="G151" s="102"/>
+      <c r="H151" s="103">
         <v>45644</v>
       </c>
-      <c r="I151" s="113"/>
+      <c r="I151" s="109"/>
       <c r="J151" s="62"/>
       <c r="K151" s="20"/>
       <c r="L151" s="20"/>
@@ -21415,11 +21415,11 @@
       <c r="B152" s="36"/>
       <c r="C152" s="72"/>
       <c r="D152" s="70"/>
-      <c r="E152" s="103"/>
-      <c r="F152" s="103"/>
-      <c r="G152" s="103"/>
-      <c r="H152" s="107"/>
-      <c r="I152" s="143"/>
+      <c r="E152" s="102"/>
+      <c r="F152" s="102"/>
+      <c r="G152" s="102"/>
+      <c r="H152" s="104"/>
+      <c r="I152" s="110"/>
       <c r="J152" s="62"/>
       <c r="K152" s="20"/>
       <c r="L152" s="20"/>
@@ -21537,15 +21537,15 @@
       <c r="B153" s="36"/>
       <c r="C153" s="72"/>
       <c r="D153" s="70"/>
-      <c r="E153" s="103" t="s">
+      <c r="E153" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="F153" s="103"/>
-      <c r="G153" s="103"/>
-      <c r="H153" s="111">
+      <c r="F153" s="102"/>
+      <c r="G153" s="102"/>
+      <c r="H153" s="103">
         <v>45644</v>
       </c>
-      <c r="I153" s="113"/>
+      <c r="I153" s="109"/>
       <c r="J153" s="62"/>
       <c r="K153" s="20"/>
       <c r="L153" s="20"/>
@@ -21663,11 +21663,11 @@
       <c r="B154" s="36"/>
       <c r="C154" s="72"/>
       <c r="D154" s="70"/>
-      <c r="E154" s="103"/>
-      <c r="F154" s="103"/>
-      <c r="G154" s="103"/>
-      <c r="H154" s="107"/>
-      <c r="I154" s="143"/>
+      <c r="E154" s="102"/>
+      <c r="F154" s="102"/>
+      <c r="G154" s="102"/>
+      <c r="H154" s="104"/>
+      <c r="I154" s="110"/>
       <c r="J154" s="62"/>
       <c r="K154" s="20"/>
       <c r="L154" s="20"/>
@@ -21784,16 +21784,16 @@
       <c r="A155" s="1"/>
       <c r="B155" s="18"/>
       <c r="C155" s="60"/>
-      <c r="D155" s="104"/>
-      <c r="E155" s="102" t="s">
+      <c r="D155" s="194"/>
+      <c r="E155" s="193" t="s">
         <v>61</v>
       </c>
-      <c r="F155" s="103"/>
-      <c r="G155" s="103"/>
-      <c r="H155" s="106">
+      <c r="F155" s="102"/>
+      <c r="G155" s="102"/>
+      <c r="H155" s="195">
         <v>45645</v>
       </c>
-      <c r="I155" s="108"/>
+      <c r="I155" s="196"/>
       <c r="J155" s="19"/>
       <c r="K155" s="20"/>
       <c r="L155" s="20"/>
@@ -21910,12 +21910,12 @@
       <c r="A156" s="1"/>
       <c r="B156" s="18"/>
       <c r="C156" s="60"/>
-      <c r="D156" s="105"/>
-      <c r="E156" s="102"/>
-      <c r="F156" s="103"/>
-      <c r="G156" s="103"/>
-      <c r="H156" s="107"/>
-      <c r="I156" s="109"/>
+      <c r="D156" s="149"/>
+      <c r="E156" s="193"/>
+      <c r="F156" s="102"/>
+      <c r="G156" s="102"/>
+      <c r="H156" s="104"/>
+      <c r="I156" s="106"/>
       <c r="J156" s="19"/>
       <c r="K156" s="20"/>
       <c r="L156" s="20"/>
@@ -22032,16 +22032,16 @@
       <c r="A157" s="1"/>
       <c r="B157" s="93"/>
       <c r="C157" s="90"/>
-      <c r="D157" s="103" t="s">
+      <c r="D157" s="102" t="s">
         <v>81</v>
       </c>
-      <c r="E157" s="103"/>
-      <c r="F157" s="103"/>
-      <c r="G157" s="103"/>
-      <c r="H157" s="111">
+      <c r="E157" s="102"/>
+      <c r="F157" s="102"/>
+      <c r="G157" s="102"/>
+      <c r="H157" s="103">
         <v>45644</v>
       </c>
-      <c r="I157" s="126"/>
+      <c r="I157" s="105"/>
       <c r="J157" s="19"/>
       <c r="K157" s="20"/>
       <c r="L157" s="20"/>
@@ -22158,12 +22158,12 @@
       <c r="A158" s="1"/>
       <c r="B158" s="93"/>
       <c r="C158" s="90"/>
-      <c r="D158" s="103"/>
-      <c r="E158" s="103"/>
-      <c r="F158" s="103"/>
-      <c r="G158" s="103"/>
-      <c r="H158" s="107"/>
-      <c r="I158" s="109"/>
+      <c r="D158" s="102"/>
+      <c r="E158" s="102"/>
+      <c r="F158" s="102"/>
+      <c r="G158" s="102"/>
+      <c r="H158" s="104"/>
+      <c r="I158" s="106"/>
       <c r="J158" s="19"/>
       <c r="K158" s="20"/>
       <c r="L158" s="20"/>
@@ -22281,14 +22281,14 @@
       <c r="B159" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="C159" s="151" t="s">
+      <c r="C159" s="173" t="s">
         <v>31</v>
       </c>
-      <c r="D159" s="152"/>
-      <c r="E159" s="152"/>
-      <c r="F159" s="152"/>
-      <c r="G159" s="153"/>
-      <c r="H159" s="138" t="s">
+      <c r="D159" s="174"/>
+      <c r="E159" s="174"/>
+      <c r="F159" s="174"/>
+      <c r="G159" s="175"/>
+      <c r="H159" s="184" t="s">
         <v>57</v>
       </c>
       <c r="I159" s="112"/>
@@ -22407,11 +22407,11 @@
     <row r="160" spans="1:120" ht="9.75" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="87"/>
-      <c r="C160" s="154"/>
-      <c r="D160" s="155"/>
-      <c r="E160" s="155"/>
-      <c r="F160" s="155"/>
-      <c r="G160" s="156"/>
+      <c r="C160" s="176"/>
+      <c r="D160" s="177"/>
+      <c r="E160" s="177"/>
+      <c r="F160" s="177"/>
+      <c r="G160" s="178"/>
       <c r="H160" s="112"/>
       <c r="I160" s="112"/>
       <c r="J160" s="14"/>
@@ -22773,14 +22773,14 @@
     <row r="163" spans="1:120" ht="9.75" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
-      <c r="C163" s="145" t="s">
+      <c r="C163" s="168" t="s">
         <v>33</v>
       </c>
-      <c r="D163" s="146"/>
-      <c r="E163" s="146"/>
-      <c r="F163" s="146"/>
-      <c r="G163" s="147"/>
-      <c r="H163" s="138" t="s">
+      <c r="D163" s="140"/>
+      <c r="E163" s="140"/>
+      <c r="F163" s="140"/>
+      <c r="G163" s="169"/>
+      <c r="H163" s="184" t="s">
         <v>56</v>
       </c>
       <c r="I163" s="112"/>
@@ -22899,11 +22899,11 @@
     <row r="164" spans="1:120" ht="9.75" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
-      <c r="C164" s="148"/>
-      <c r="D164" s="149"/>
-      <c r="E164" s="149"/>
-      <c r="F164" s="149"/>
-      <c r="G164" s="150"/>
+      <c r="C164" s="170"/>
+      <c r="D164" s="171"/>
+      <c r="E164" s="171"/>
+      <c r="F164" s="171"/>
+      <c r="G164" s="172"/>
       <c r="H164" s="112"/>
       <c r="I164" s="112"/>
       <c r="J164" s="19"/>
@@ -36444,6 +36444,222 @@
     </row>
   </sheetData>
   <mergeCells count="240">
+    <mergeCell ref="E155:G156"/>
+    <mergeCell ref="D155:D156"/>
+    <mergeCell ref="H155:H156"/>
+    <mergeCell ref="I155:I156"/>
+    <mergeCell ref="H113:H114"/>
+    <mergeCell ref="I113:I114"/>
+    <mergeCell ref="H129:H130"/>
+    <mergeCell ref="I129:I130"/>
+    <mergeCell ref="E129:G130"/>
+    <mergeCell ref="H123:H124"/>
+    <mergeCell ref="I123:I124"/>
+    <mergeCell ref="I125:I126"/>
+    <mergeCell ref="H125:H126"/>
+    <mergeCell ref="H133:H134"/>
+    <mergeCell ref="I133:I134"/>
+    <mergeCell ref="E123:G124"/>
+    <mergeCell ref="E125:G126"/>
+    <mergeCell ref="E127:G128"/>
+    <mergeCell ref="E113:G114"/>
+    <mergeCell ref="E119:G120"/>
+    <mergeCell ref="E121:G122"/>
+    <mergeCell ref="H127:H128"/>
+    <mergeCell ref="I127:I128"/>
+    <mergeCell ref="H121:H122"/>
+    <mergeCell ref="H105:H106"/>
+    <mergeCell ref="I105:I106"/>
+    <mergeCell ref="H107:H108"/>
+    <mergeCell ref="I107:I108"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="H117:H118"/>
+    <mergeCell ref="I117:I118"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="I119:I120"/>
+    <mergeCell ref="H101:H102"/>
+    <mergeCell ref="I101:I102"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="I85:I86"/>
+    <mergeCell ref="H89:H90"/>
+    <mergeCell ref="I89:I90"/>
+    <mergeCell ref="E81:G82"/>
+    <mergeCell ref="E83:G84"/>
+    <mergeCell ref="E91:G92"/>
+    <mergeCell ref="E93:G94"/>
+    <mergeCell ref="E95:G96"/>
+    <mergeCell ref="E97:G98"/>
+    <mergeCell ref="E99:G100"/>
+    <mergeCell ref="E85:G86"/>
+    <mergeCell ref="D89:G90"/>
+    <mergeCell ref="H75:H76"/>
+    <mergeCell ref="H159:H160"/>
+    <mergeCell ref="H163:H164"/>
+    <mergeCell ref="H161:H162"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="H59:H60"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="H77:H78"/>
+    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="H93:H94"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="H111:H112"/>
+    <mergeCell ref="I163:I164"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="I159:I160"/>
+    <mergeCell ref="I161:I162"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="I93:I94"/>
+    <mergeCell ref="I95:I96"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="I109:I110"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="I153:I154"/>
+    <mergeCell ref="I151:I152"/>
+    <mergeCell ref="I149:I150"/>
+    <mergeCell ref="I147:I148"/>
+    <mergeCell ref="I145:I146"/>
+    <mergeCell ref="I111:I112"/>
+    <mergeCell ref="I135:I136"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I67:I68"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="C163:G164"/>
+    <mergeCell ref="C159:G160"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="C31:G32"/>
+    <mergeCell ref="D33:G34"/>
+    <mergeCell ref="E35:G36"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="E43:G44"/>
+    <mergeCell ref="E45:G46"/>
+    <mergeCell ref="E47:G48"/>
+    <mergeCell ref="E49:G50"/>
+    <mergeCell ref="E51:G52"/>
+    <mergeCell ref="D53:G54"/>
+    <mergeCell ref="E55:G56"/>
+    <mergeCell ref="E57:G58"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="J3:CJ3"/>
+    <mergeCell ref="CK3:DO3"/>
+    <mergeCell ref="J4:AA4"/>
+    <mergeCell ref="AB4:BE4"/>
+    <mergeCell ref="BF4:CJ4"/>
+    <mergeCell ref="CK4:DO4"/>
+    <mergeCell ref="B7:G8"/>
+    <mergeCell ref="C9:G10"/>
+    <mergeCell ref="C11:G12"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="D13:G14"/>
+    <mergeCell ref="D15:G16"/>
+    <mergeCell ref="D17:G18"/>
+    <mergeCell ref="D19:G20"/>
+    <mergeCell ref="C21:G22"/>
+    <mergeCell ref="D23:G24"/>
+    <mergeCell ref="C25:G26"/>
+    <mergeCell ref="D27:G28"/>
+    <mergeCell ref="D29:G30"/>
+    <mergeCell ref="E147:G148"/>
+    <mergeCell ref="E149:G150"/>
+    <mergeCell ref="E151:G152"/>
+    <mergeCell ref="E59:G60"/>
+    <mergeCell ref="E61:G62"/>
+    <mergeCell ref="D63:G64"/>
+    <mergeCell ref="E67:G68"/>
+    <mergeCell ref="E65:G66"/>
+    <mergeCell ref="E69:G70"/>
+    <mergeCell ref="E71:G72"/>
+    <mergeCell ref="C73:G74"/>
+    <mergeCell ref="C75:G76"/>
+    <mergeCell ref="C77:G78"/>
+    <mergeCell ref="D79:G80"/>
+    <mergeCell ref="E109:G110"/>
+    <mergeCell ref="E111:G112"/>
+    <mergeCell ref="E101:G102"/>
+    <mergeCell ref="C105:G106"/>
+    <mergeCell ref="D107:G108"/>
+    <mergeCell ref="D117:G118"/>
+    <mergeCell ref="H145:H146"/>
+    <mergeCell ref="H143:H144"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="C133:G134"/>
+    <mergeCell ref="D135:G136"/>
+    <mergeCell ref="E137:G138"/>
+    <mergeCell ref="E139:G140"/>
+    <mergeCell ref="D143:G144"/>
+    <mergeCell ref="E145:G146"/>
+    <mergeCell ref="H135:H136"/>
     <mergeCell ref="D157:G158"/>
     <mergeCell ref="H157:H158"/>
     <mergeCell ref="I157:I158"/>
@@ -36468,222 +36684,6 @@
     <mergeCell ref="H151:H152"/>
     <mergeCell ref="H149:H150"/>
     <mergeCell ref="H147:H148"/>
-    <mergeCell ref="H145:H146"/>
-    <mergeCell ref="H143:H144"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="C133:G134"/>
-    <mergeCell ref="D135:G136"/>
-    <mergeCell ref="E137:G138"/>
-    <mergeCell ref="E139:G140"/>
-    <mergeCell ref="D143:G144"/>
-    <mergeCell ref="E145:G146"/>
-    <mergeCell ref="H135:H136"/>
-    <mergeCell ref="E147:G148"/>
-    <mergeCell ref="E149:G150"/>
-    <mergeCell ref="E151:G152"/>
-    <mergeCell ref="E59:G60"/>
-    <mergeCell ref="E61:G62"/>
-    <mergeCell ref="D63:G64"/>
-    <mergeCell ref="E67:G68"/>
-    <mergeCell ref="E65:G66"/>
-    <mergeCell ref="E69:G70"/>
-    <mergeCell ref="E71:G72"/>
-    <mergeCell ref="C73:G74"/>
-    <mergeCell ref="C75:G76"/>
-    <mergeCell ref="C77:G78"/>
-    <mergeCell ref="D79:G80"/>
-    <mergeCell ref="E109:G110"/>
-    <mergeCell ref="E111:G112"/>
-    <mergeCell ref="E101:G102"/>
-    <mergeCell ref="C105:G106"/>
-    <mergeCell ref="D107:G108"/>
-    <mergeCell ref="D117:G118"/>
-    <mergeCell ref="D13:G14"/>
-    <mergeCell ref="D15:G16"/>
-    <mergeCell ref="D17:G18"/>
-    <mergeCell ref="D19:G20"/>
-    <mergeCell ref="C21:G22"/>
-    <mergeCell ref="D23:G24"/>
-    <mergeCell ref="C25:G26"/>
-    <mergeCell ref="D27:G28"/>
-    <mergeCell ref="D29:G30"/>
-    <mergeCell ref="J3:CJ3"/>
-    <mergeCell ref="CK3:DO3"/>
-    <mergeCell ref="J4:AA4"/>
-    <mergeCell ref="AB4:BE4"/>
-    <mergeCell ref="BF4:CJ4"/>
-    <mergeCell ref="CK4:DO4"/>
-    <mergeCell ref="B7:G8"/>
-    <mergeCell ref="C9:G10"/>
-    <mergeCell ref="C11:G12"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="C163:G164"/>
-    <mergeCell ref="C159:G160"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="C31:G32"/>
-    <mergeCell ref="D33:G34"/>
-    <mergeCell ref="E35:G36"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="E43:G44"/>
-    <mergeCell ref="E45:G46"/>
-    <mergeCell ref="E47:G48"/>
-    <mergeCell ref="E49:G50"/>
-    <mergeCell ref="E51:G52"/>
-    <mergeCell ref="D53:G54"/>
-    <mergeCell ref="E55:G56"/>
-    <mergeCell ref="E57:G58"/>
-    <mergeCell ref="I53:I54"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="I159:I160"/>
-    <mergeCell ref="I161:I162"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="I93:I94"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="I109:I110"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="I153:I154"/>
-    <mergeCell ref="I151:I152"/>
-    <mergeCell ref="I149:I150"/>
-    <mergeCell ref="I147:I148"/>
-    <mergeCell ref="I145:I146"/>
-    <mergeCell ref="I111:I112"/>
-    <mergeCell ref="I135:I136"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="I163:I164"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="H75:H76"/>
-    <mergeCell ref="H159:H160"/>
-    <mergeCell ref="H163:H164"/>
-    <mergeCell ref="H161:H162"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="H67:H68"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H59:H60"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="H77:H78"/>
-    <mergeCell ref="H81:H82"/>
-    <mergeCell ref="H83:H84"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="H93:H94"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="H111:H112"/>
-    <mergeCell ref="H101:H102"/>
-    <mergeCell ref="I101:I102"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="I85:I86"/>
-    <mergeCell ref="H89:H90"/>
-    <mergeCell ref="I89:I90"/>
-    <mergeCell ref="E81:G82"/>
-    <mergeCell ref="E83:G84"/>
-    <mergeCell ref="E91:G92"/>
-    <mergeCell ref="E93:G94"/>
-    <mergeCell ref="E95:G96"/>
-    <mergeCell ref="E97:G98"/>
-    <mergeCell ref="E99:G100"/>
-    <mergeCell ref="E85:G86"/>
-    <mergeCell ref="D89:G90"/>
-    <mergeCell ref="H105:H106"/>
-    <mergeCell ref="I105:I106"/>
-    <mergeCell ref="H107:H108"/>
-    <mergeCell ref="I107:I108"/>
-    <mergeCell ref="H109:H110"/>
-    <mergeCell ref="H117:H118"/>
-    <mergeCell ref="I117:I118"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="I119:I120"/>
-    <mergeCell ref="E155:G156"/>
-    <mergeCell ref="D155:D156"/>
-    <mergeCell ref="H155:H156"/>
-    <mergeCell ref="I155:I156"/>
-    <mergeCell ref="H113:H114"/>
-    <mergeCell ref="I113:I114"/>
-    <mergeCell ref="H129:H130"/>
-    <mergeCell ref="I129:I130"/>
-    <mergeCell ref="E129:G130"/>
-    <mergeCell ref="H123:H124"/>
-    <mergeCell ref="I123:I124"/>
-    <mergeCell ref="I125:I126"/>
-    <mergeCell ref="H125:H126"/>
-    <mergeCell ref="H133:H134"/>
-    <mergeCell ref="I133:I134"/>
-    <mergeCell ref="E123:G124"/>
-    <mergeCell ref="E125:G126"/>
-    <mergeCell ref="E127:G128"/>
-    <mergeCell ref="E113:G114"/>
-    <mergeCell ref="E119:G120"/>
-    <mergeCell ref="E121:G122"/>
-    <mergeCell ref="H127:H128"/>
-    <mergeCell ref="I127:I128"/>
-    <mergeCell ref="H121:H122"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <conditionalFormatting sqref="J7">

--- a/docs/【DIGITAL OJT】WBS.xlsx
+++ b/docs/【DIGITAL OJT】WBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIGITALOJT\digital-ojt-development-cause-DroneInventorySystem\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E68E0814-A123-4CD7-A47C-8E463D9C6F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147DC62C-0102-4339-A4CB-6BDC1E85F929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -1489,19 +1489,67 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1510,22 +1558,25 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1546,110 +1597,29 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1675,62 +1645,92 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2350,120 +2350,120 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="J3" s="161">
+      <c r="J3" s="173">
         <v>2024</v>
       </c>
-      <c r="K3" s="162"/>
-      <c r="L3" s="162"/>
-      <c r="M3" s="162"/>
-      <c r="N3" s="162"/>
-      <c r="O3" s="162"/>
-      <c r="P3" s="162"/>
-      <c r="Q3" s="162"/>
-      <c r="R3" s="162"/>
-      <c r="S3" s="162"/>
-      <c r="T3" s="162"/>
-      <c r="U3" s="162"/>
-      <c r="V3" s="162"/>
-      <c r="W3" s="162"/>
-      <c r="X3" s="162"/>
-      <c r="Y3" s="162"/>
-      <c r="Z3" s="162"/>
-      <c r="AA3" s="162"/>
-      <c r="AB3" s="162"/>
-      <c r="AC3" s="162"/>
-      <c r="AD3" s="162"/>
-      <c r="AE3" s="162"/>
-      <c r="AF3" s="162"/>
-      <c r="AG3" s="162"/>
-      <c r="AH3" s="162"/>
-      <c r="AI3" s="162"/>
-      <c r="AJ3" s="162"/>
-      <c r="AK3" s="162"/>
-      <c r="AL3" s="162"/>
-      <c r="AM3" s="162"/>
-      <c r="AN3" s="162"/>
-      <c r="AO3" s="162"/>
-      <c r="AP3" s="162"/>
-      <c r="AQ3" s="162"/>
-      <c r="AR3" s="162"/>
-      <c r="AS3" s="162"/>
-      <c r="AT3" s="162"/>
-      <c r="AU3" s="162"/>
-      <c r="AV3" s="162"/>
-      <c r="AW3" s="162"/>
-      <c r="AX3" s="162"/>
-      <c r="AY3" s="162"/>
-      <c r="AZ3" s="162"/>
-      <c r="BA3" s="162"/>
-      <c r="BB3" s="162"/>
-      <c r="BC3" s="162"/>
-      <c r="BD3" s="162"/>
-      <c r="BE3" s="162"/>
-      <c r="BF3" s="162"/>
-      <c r="BG3" s="162"/>
-      <c r="BH3" s="162"/>
-      <c r="BI3" s="162"/>
-      <c r="BJ3" s="162"/>
-      <c r="BK3" s="162"/>
-      <c r="BL3" s="162"/>
-      <c r="BM3" s="162"/>
-      <c r="BN3" s="162"/>
-      <c r="BO3" s="162"/>
-      <c r="BP3" s="162"/>
-      <c r="BQ3" s="162"/>
-      <c r="BR3" s="162"/>
-      <c r="BS3" s="162"/>
-      <c r="BT3" s="162"/>
-      <c r="BU3" s="162"/>
-      <c r="BV3" s="162"/>
-      <c r="BW3" s="162"/>
-      <c r="BX3" s="162"/>
-      <c r="BY3" s="162"/>
-      <c r="BZ3" s="162"/>
-      <c r="CA3" s="162"/>
-      <c r="CB3" s="162"/>
-      <c r="CC3" s="162"/>
-      <c r="CD3" s="162"/>
-      <c r="CE3" s="162"/>
-      <c r="CF3" s="162"/>
-      <c r="CG3" s="162"/>
-      <c r="CH3" s="162"/>
-      <c r="CI3" s="162"/>
-      <c r="CJ3" s="163"/>
-      <c r="CK3" s="161">
+      <c r="K3" s="174"/>
+      <c r="L3" s="174"/>
+      <c r="M3" s="174"/>
+      <c r="N3" s="174"/>
+      <c r="O3" s="174"/>
+      <c r="P3" s="174"/>
+      <c r="Q3" s="174"/>
+      <c r="R3" s="174"/>
+      <c r="S3" s="174"/>
+      <c r="T3" s="174"/>
+      <c r="U3" s="174"/>
+      <c r="V3" s="174"/>
+      <c r="W3" s="174"/>
+      <c r="X3" s="174"/>
+      <c r="Y3" s="174"/>
+      <c r="Z3" s="174"/>
+      <c r="AA3" s="174"/>
+      <c r="AB3" s="174"/>
+      <c r="AC3" s="174"/>
+      <c r="AD3" s="174"/>
+      <c r="AE3" s="174"/>
+      <c r="AF3" s="174"/>
+      <c r="AG3" s="174"/>
+      <c r="AH3" s="174"/>
+      <c r="AI3" s="174"/>
+      <c r="AJ3" s="174"/>
+      <c r="AK3" s="174"/>
+      <c r="AL3" s="174"/>
+      <c r="AM3" s="174"/>
+      <c r="AN3" s="174"/>
+      <c r="AO3" s="174"/>
+      <c r="AP3" s="174"/>
+      <c r="AQ3" s="174"/>
+      <c r="AR3" s="174"/>
+      <c r="AS3" s="174"/>
+      <c r="AT3" s="174"/>
+      <c r="AU3" s="174"/>
+      <c r="AV3" s="174"/>
+      <c r="AW3" s="174"/>
+      <c r="AX3" s="174"/>
+      <c r="AY3" s="174"/>
+      <c r="AZ3" s="174"/>
+      <c r="BA3" s="174"/>
+      <c r="BB3" s="174"/>
+      <c r="BC3" s="174"/>
+      <c r="BD3" s="174"/>
+      <c r="BE3" s="174"/>
+      <c r="BF3" s="174"/>
+      <c r="BG3" s="174"/>
+      <c r="BH3" s="174"/>
+      <c r="BI3" s="174"/>
+      <c r="BJ3" s="174"/>
+      <c r="BK3" s="174"/>
+      <c r="BL3" s="174"/>
+      <c r="BM3" s="174"/>
+      <c r="BN3" s="174"/>
+      <c r="BO3" s="174"/>
+      <c r="BP3" s="174"/>
+      <c r="BQ3" s="174"/>
+      <c r="BR3" s="174"/>
+      <c r="BS3" s="174"/>
+      <c r="BT3" s="174"/>
+      <c r="BU3" s="174"/>
+      <c r="BV3" s="174"/>
+      <c r="BW3" s="174"/>
+      <c r="BX3" s="174"/>
+      <c r="BY3" s="174"/>
+      <c r="BZ3" s="174"/>
+      <c r="CA3" s="174"/>
+      <c r="CB3" s="174"/>
+      <c r="CC3" s="174"/>
+      <c r="CD3" s="174"/>
+      <c r="CE3" s="174"/>
+      <c r="CF3" s="174"/>
+      <c r="CG3" s="174"/>
+      <c r="CH3" s="174"/>
+      <c r="CI3" s="174"/>
+      <c r="CJ3" s="175"/>
+      <c r="CK3" s="173">
         <v>2025</v>
       </c>
-      <c r="CL3" s="162"/>
-      <c r="CM3" s="162"/>
-      <c r="CN3" s="162"/>
-      <c r="CO3" s="162"/>
-      <c r="CP3" s="162"/>
-      <c r="CQ3" s="162"/>
-      <c r="CR3" s="162"/>
-      <c r="CS3" s="162"/>
-      <c r="CT3" s="162"/>
-      <c r="CU3" s="162"/>
-      <c r="CV3" s="162"/>
-      <c r="CW3" s="162"/>
-      <c r="CX3" s="162"/>
-      <c r="CY3" s="162"/>
-      <c r="CZ3" s="162"/>
-      <c r="DA3" s="162"/>
-      <c r="DB3" s="162"/>
-      <c r="DC3" s="162"/>
-      <c r="DD3" s="162"/>
-      <c r="DE3" s="162"/>
-      <c r="DF3" s="162"/>
-      <c r="DG3" s="162"/>
-      <c r="DH3" s="162"/>
-      <c r="DI3" s="162"/>
-      <c r="DJ3" s="162"/>
-      <c r="DK3" s="162"/>
-      <c r="DL3" s="162"/>
-      <c r="DM3" s="162"/>
-      <c r="DN3" s="162"/>
-      <c r="DO3" s="163"/>
+      <c r="CL3" s="174"/>
+      <c r="CM3" s="174"/>
+      <c r="CN3" s="174"/>
+      <c r="CO3" s="174"/>
+      <c r="CP3" s="174"/>
+      <c r="CQ3" s="174"/>
+      <c r="CR3" s="174"/>
+      <c r="CS3" s="174"/>
+      <c r="CT3" s="174"/>
+      <c r="CU3" s="174"/>
+      <c r="CV3" s="174"/>
+      <c r="CW3" s="174"/>
+      <c r="CX3" s="174"/>
+      <c r="CY3" s="174"/>
+      <c r="CZ3" s="174"/>
+      <c r="DA3" s="174"/>
+      <c r="DB3" s="174"/>
+      <c r="DC3" s="174"/>
+      <c r="DD3" s="174"/>
+      <c r="DE3" s="174"/>
+      <c r="DF3" s="174"/>
+      <c r="DG3" s="174"/>
+      <c r="DH3" s="174"/>
+      <c r="DI3" s="174"/>
+      <c r="DJ3" s="174"/>
+      <c r="DK3" s="174"/>
+      <c r="DL3" s="174"/>
+      <c r="DM3" s="174"/>
+      <c r="DN3" s="174"/>
+      <c r="DO3" s="175"/>
       <c r="DP3" s="1"/>
     </row>
     <row r="4" spans="1:120" ht="18" customHeight="1">
@@ -2478,124 +2478,124 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="J4" s="161">
+      <c r="J4" s="173">
         <v>10</v>
       </c>
-      <c r="K4" s="162"/>
-      <c r="L4" s="162"/>
-      <c r="M4" s="162"/>
-      <c r="N4" s="162"/>
-      <c r="O4" s="162"/>
-      <c r="P4" s="162"/>
-      <c r="Q4" s="162"/>
-      <c r="R4" s="162"/>
-      <c r="S4" s="162"/>
-      <c r="T4" s="162"/>
-      <c r="U4" s="162"/>
-      <c r="V4" s="162"/>
-      <c r="W4" s="162"/>
-      <c r="X4" s="162"/>
-      <c r="Y4" s="162"/>
-      <c r="Z4" s="162"/>
-      <c r="AA4" s="163"/>
-      <c r="AB4" s="161">
+      <c r="K4" s="174"/>
+      <c r="L4" s="174"/>
+      <c r="M4" s="174"/>
+      <c r="N4" s="174"/>
+      <c r="O4" s="174"/>
+      <c r="P4" s="174"/>
+      <c r="Q4" s="174"/>
+      <c r="R4" s="174"/>
+      <c r="S4" s="174"/>
+      <c r="T4" s="174"/>
+      <c r="U4" s="174"/>
+      <c r="V4" s="174"/>
+      <c r="W4" s="174"/>
+      <c r="X4" s="174"/>
+      <c r="Y4" s="174"/>
+      <c r="Z4" s="174"/>
+      <c r="AA4" s="175"/>
+      <c r="AB4" s="173">
         <v>11</v>
       </c>
-      <c r="AC4" s="162"/>
-      <c r="AD4" s="162"/>
-      <c r="AE4" s="162"/>
-      <c r="AF4" s="162"/>
-      <c r="AG4" s="162"/>
-      <c r="AH4" s="162"/>
-      <c r="AI4" s="162"/>
-      <c r="AJ4" s="162"/>
-      <c r="AK4" s="162"/>
-      <c r="AL4" s="162"/>
-      <c r="AM4" s="162"/>
-      <c r="AN4" s="162"/>
-      <c r="AO4" s="162"/>
-      <c r="AP4" s="162"/>
-      <c r="AQ4" s="162"/>
-      <c r="AR4" s="162"/>
-      <c r="AS4" s="162"/>
-      <c r="AT4" s="162"/>
-      <c r="AU4" s="162"/>
-      <c r="AV4" s="162"/>
-      <c r="AW4" s="162"/>
-      <c r="AX4" s="162"/>
-      <c r="AY4" s="162"/>
-      <c r="AZ4" s="162"/>
-      <c r="BA4" s="162"/>
-      <c r="BB4" s="162"/>
-      <c r="BC4" s="162"/>
-      <c r="BD4" s="162"/>
-      <c r="BE4" s="163"/>
-      <c r="BF4" s="161">
+      <c r="AC4" s="174"/>
+      <c r="AD4" s="174"/>
+      <c r="AE4" s="174"/>
+      <c r="AF4" s="174"/>
+      <c r="AG4" s="174"/>
+      <c r="AH4" s="174"/>
+      <c r="AI4" s="174"/>
+      <c r="AJ4" s="174"/>
+      <c r="AK4" s="174"/>
+      <c r="AL4" s="174"/>
+      <c r="AM4" s="174"/>
+      <c r="AN4" s="174"/>
+      <c r="AO4" s="174"/>
+      <c r="AP4" s="174"/>
+      <c r="AQ4" s="174"/>
+      <c r="AR4" s="174"/>
+      <c r="AS4" s="174"/>
+      <c r="AT4" s="174"/>
+      <c r="AU4" s="174"/>
+      <c r="AV4" s="174"/>
+      <c r="AW4" s="174"/>
+      <c r="AX4" s="174"/>
+      <c r="AY4" s="174"/>
+      <c r="AZ4" s="174"/>
+      <c r="BA4" s="174"/>
+      <c r="BB4" s="174"/>
+      <c r="BC4" s="174"/>
+      <c r="BD4" s="174"/>
+      <c r="BE4" s="175"/>
+      <c r="BF4" s="173">
         <v>12</v>
       </c>
-      <c r="BG4" s="162"/>
-      <c r="BH4" s="162"/>
-      <c r="BI4" s="162"/>
-      <c r="BJ4" s="162"/>
-      <c r="BK4" s="162"/>
-      <c r="BL4" s="162"/>
-      <c r="BM4" s="162"/>
-      <c r="BN4" s="162"/>
-      <c r="BO4" s="162"/>
-      <c r="BP4" s="162"/>
-      <c r="BQ4" s="162"/>
-      <c r="BR4" s="162"/>
-      <c r="BS4" s="162"/>
-      <c r="BT4" s="162"/>
-      <c r="BU4" s="162"/>
-      <c r="BV4" s="162"/>
-      <c r="BW4" s="162"/>
-      <c r="BX4" s="162"/>
-      <c r="BY4" s="162"/>
-      <c r="BZ4" s="162"/>
-      <c r="CA4" s="162"/>
-      <c r="CB4" s="162"/>
-      <c r="CC4" s="162"/>
-      <c r="CD4" s="162"/>
-      <c r="CE4" s="162"/>
-      <c r="CF4" s="162"/>
-      <c r="CG4" s="162"/>
-      <c r="CH4" s="162"/>
-      <c r="CI4" s="162"/>
-      <c r="CJ4" s="163"/>
-      <c r="CK4" s="161">
+      <c r="BG4" s="174"/>
+      <c r="BH4" s="174"/>
+      <c r="BI4" s="174"/>
+      <c r="BJ4" s="174"/>
+      <c r="BK4" s="174"/>
+      <c r="BL4" s="174"/>
+      <c r="BM4" s="174"/>
+      <c r="BN4" s="174"/>
+      <c r="BO4" s="174"/>
+      <c r="BP4" s="174"/>
+      <c r="BQ4" s="174"/>
+      <c r="BR4" s="174"/>
+      <c r="BS4" s="174"/>
+      <c r="BT4" s="174"/>
+      <c r="BU4" s="174"/>
+      <c r="BV4" s="174"/>
+      <c r="BW4" s="174"/>
+      <c r="BX4" s="174"/>
+      <c r="BY4" s="174"/>
+      <c r="BZ4" s="174"/>
+      <c r="CA4" s="174"/>
+      <c r="CB4" s="174"/>
+      <c r="CC4" s="174"/>
+      <c r="CD4" s="174"/>
+      <c r="CE4" s="174"/>
+      <c r="CF4" s="174"/>
+      <c r="CG4" s="174"/>
+      <c r="CH4" s="174"/>
+      <c r="CI4" s="174"/>
+      <c r="CJ4" s="175"/>
+      <c r="CK4" s="173">
         <v>1</v>
       </c>
-      <c r="CL4" s="162"/>
-      <c r="CM4" s="162"/>
-      <c r="CN4" s="162"/>
-      <c r="CO4" s="162"/>
-      <c r="CP4" s="162"/>
-      <c r="CQ4" s="162"/>
-      <c r="CR4" s="162"/>
-      <c r="CS4" s="162"/>
-      <c r="CT4" s="162"/>
-      <c r="CU4" s="162"/>
-      <c r="CV4" s="162"/>
-      <c r="CW4" s="162"/>
-      <c r="CX4" s="162"/>
-      <c r="CY4" s="162"/>
-      <c r="CZ4" s="162"/>
-      <c r="DA4" s="162"/>
-      <c r="DB4" s="162"/>
-      <c r="DC4" s="162"/>
-      <c r="DD4" s="162"/>
-      <c r="DE4" s="162"/>
-      <c r="DF4" s="162"/>
-      <c r="DG4" s="162"/>
-      <c r="DH4" s="162"/>
-      <c r="DI4" s="162"/>
-      <c r="DJ4" s="162"/>
-      <c r="DK4" s="162"/>
-      <c r="DL4" s="162"/>
-      <c r="DM4" s="162"/>
-      <c r="DN4" s="162"/>
-      <c r="DO4" s="163"/>
+      <c r="CL4" s="174"/>
+      <c r="CM4" s="174"/>
+      <c r="CN4" s="174"/>
+      <c r="CO4" s="174"/>
+      <c r="CP4" s="174"/>
+      <c r="CQ4" s="174"/>
+      <c r="CR4" s="174"/>
+      <c r="CS4" s="174"/>
+      <c r="CT4" s="174"/>
+      <c r="CU4" s="174"/>
+      <c r="CV4" s="174"/>
+      <c r="CW4" s="174"/>
+      <c r="CX4" s="174"/>
+      <c r="CY4" s="174"/>
+      <c r="CZ4" s="174"/>
+      <c r="DA4" s="174"/>
+      <c r="DB4" s="174"/>
+      <c r="DC4" s="174"/>
+      <c r="DD4" s="174"/>
+      <c r="DE4" s="174"/>
+      <c r="DF4" s="174"/>
+      <c r="DG4" s="174"/>
+      <c r="DH4" s="174"/>
+      <c r="DI4" s="174"/>
+      <c r="DJ4" s="174"/>
+      <c r="DK4" s="174"/>
+      <c r="DL4" s="174"/>
+      <c r="DM4" s="174"/>
+      <c r="DN4" s="174"/>
+      <c r="DO4" s="175"/>
       <c r="DP4" s="6"/>
     </row>
     <row r="5" spans="1:120" ht="18" customHeight="1">
@@ -3390,18 +3390,18 @@
     </row>
     <row r="7" spans="1:120" ht="9.75" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="164" t="s">
+      <c r="B7" s="176" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="166" t="s">
+      <c r="C7" s="164"/>
+      <c r="D7" s="164"/>
+      <c r="E7" s="164"/>
+      <c r="F7" s="164"/>
+      <c r="G7" s="177"/>
+      <c r="H7" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="166" t="s">
+      <c r="I7" s="142" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="38"/>
@@ -3518,14 +3518,14 @@
     </row>
     <row r="8" spans="1:120" ht="9.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="134"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="135"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="135"/>
-      <c r="G8" s="139"/>
-      <c r="H8" s="166"/>
-      <c r="I8" s="166"/>
+      <c r="B8" s="166"/>
+      <c r="C8" s="167"/>
+      <c r="D8" s="167"/>
+      <c r="E8" s="167"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="168"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="142"/>
       <c r="J8" s="39"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
@@ -3641,15 +3641,15 @@
     <row r="9" spans="1:120" ht="9.75" customHeight="1">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
-      <c r="C9" s="165" t="s">
+      <c r="C9" s="178" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="154"/>
-      <c r="E9" s="154"/>
-      <c r="F9" s="154"/>
-      <c r="G9" s="142"/>
-      <c r="H9" s="167"/>
-      <c r="I9" s="167"/>
+      <c r="D9" s="158"/>
+      <c r="E9" s="158"/>
+      <c r="F9" s="158"/>
+      <c r="G9" s="162"/>
+      <c r="H9" s="139"/>
+      <c r="I9" s="139"/>
       <c r="J9" s="42"/>
       <c r="K9" s="42"/>
       <c r="L9" s="44"/>
@@ -3765,13 +3765,13 @@
     <row r="10" spans="1:120" ht="9.75" customHeight="1">
       <c r="A10" s="16"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="141"/>
-      <c r="D10" s="135"/>
-      <c r="E10" s="135"/>
-      <c r="F10" s="135"/>
-      <c r="G10" s="139"/>
-      <c r="H10" s="167"/>
-      <c r="I10" s="167"/>
+      <c r="C10" s="179"/>
+      <c r="D10" s="167"/>
+      <c r="E10" s="167"/>
+      <c r="F10" s="167"/>
+      <c r="G10" s="168"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
       <c r="J10" s="46"/>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
@@ -3887,15 +3887,15 @@
     <row r="11" spans="1:120" ht="9.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="153" t="s">
+      <c r="C11" s="180" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="154"/>
-      <c r="E11" s="154"/>
-      <c r="F11" s="154"/>
-      <c r="G11" s="142"/>
-      <c r="H11" s="167"/>
-      <c r="I11" s="167"/>
+      <c r="D11" s="158"/>
+      <c r="E11" s="158"/>
+      <c r="F11" s="158"/>
+      <c r="G11" s="162"/>
+      <c r="H11" s="139"/>
+      <c r="I11" s="139"/>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
       <c r="L11" s="44"/>
@@ -4011,13 +4011,13 @@
     <row r="12" spans="1:120" ht="9.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="141"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="135"/>
-      <c r="F12" s="135"/>
-      <c r="G12" s="139"/>
-      <c r="H12" s="167"/>
-      <c r="I12" s="167"/>
+      <c r="C12" s="179"/>
+      <c r="D12" s="167"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="167"/>
+      <c r="G12" s="168"/>
+      <c r="H12" s="139"/>
+      <c r="I12" s="139"/>
       <c r="J12" s="46"/>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
@@ -4134,13 +4134,13 @@
       <c r="A13" s="1"/>
       <c r="B13" s="18"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="151" t="s">
+      <c r="D13" s="181" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="152"/>
-      <c r="H13" s="184" t="s">
+      <c r="E13" s="164"/>
+      <c r="F13" s="164"/>
+      <c r="G13" s="177"/>
+      <c r="H13" s="138" t="s">
         <v>40</v>
       </c>
       <c r="I13" s="112">
@@ -4262,10 +4262,10 @@
       <c r="A14" s="1"/>
       <c r="B14" s="18"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="134"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="135"/>
-      <c r="G14" s="139"/>
+      <c r="D14" s="166"/>
+      <c r="E14" s="167"/>
+      <c r="F14" s="167"/>
+      <c r="G14" s="168"/>
       <c r="H14" s="112"/>
       <c r="I14" s="112"/>
       <c r="J14" s="39"/>
@@ -4384,13 +4384,13 @@
       <c r="A15" s="1"/>
       <c r="B15" s="18"/>
       <c r="C15" s="24"/>
-      <c r="D15" s="151" t="s">
+      <c r="D15" s="181" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="133"/>
-      <c r="H15" s="184" t="s">
+      <c r="E15" s="164"/>
+      <c r="F15" s="164"/>
+      <c r="G15" s="170"/>
+      <c r="H15" s="138" t="s">
         <v>40</v>
       </c>
       <c r="I15" s="112">
@@ -4512,10 +4512,10 @@
       <c r="A16" s="1"/>
       <c r="B16" s="18"/>
       <c r="C16" s="24"/>
-      <c r="D16" s="134"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="136"/>
+      <c r="D16" s="166"/>
+      <c r="E16" s="167"/>
+      <c r="F16" s="167"/>
+      <c r="G16" s="171"/>
       <c r="H16" s="112"/>
       <c r="I16" s="112"/>
       <c r="J16" s="14"/>
@@ -4634,13 +4634,13 @@
       <c r="A17" s="1"/>
       <c r="B17" s="18"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="151" t="s">
+      <c r="D17" s="181" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="132"/>
-      <c r="F17" s="132"/>
-      <c r="G17" s="133"/>
-      <c r="H17" s="184" t="s">
+      <c r="E17" s="164"/>
+      <c r="F17" s="164"/>
+      <c r="G17" s="170"/>
+      <c r="H17" s="138" t="s">
         <v>40</v>
       </c>
       <c r="I17" s="112">
@@ -4762,10 +4762,10 @@
       <c r="A18" s="1"/>
       <c r="B18" s="18"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="134"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="135"/>
-      <c r="G18" s="136"/>
+      <c r="D18" s="166"/>
+      <c r="E18" s="167"/>
+      <c r="F18" s="167"/>
+      <c r="G18" s="171"/>
       <c r="H18" s="112"/>
       <c r="I18" s="112"/>
       <c r="J18" s="14"/>
@@ -4884,13 +4884,13 @@
       <c r="A19" s="1"/>
       <c r="B19" s="18"/>
       <c r="C19" s="24"/>
-      <c r="D19" s="151" t="s">
+      <c r="D19" s="181" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="132"/>
-      <c r="F19" s="132"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="184" t="s">
+      <c r="E19" s="164"/>
+      <c r="F19" s="164"/>
+      <c r="G19" s="170"/>
+      <c r="H19" s="138" t="s">
         <v>40</v>
       </c>
       <c r="I19" s="112">
@@ -5012,10 +5012,10 @@
       <c r="A20" s="1"/>
       <c r="B20" s="18"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="134"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="135"/>
-      <c r="G20" s="136"/>
+      <c r="D20" s="166"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="167"/>
+      <c r="G20" s="171"/>
       <c r="H20" s="112"/>
       <c r="I20" s="112"/>
       <c r="J20" s="26"/>
@@ -5133,15 +5133,15 @@
     <row r="21" spans="1:120" ht="9.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="18"/>
-      <c r="C21" s="153" t="s">
+      <c r="C21" s="180" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="154"/>
-      <c r="E21" s="154"/>
-      <c r="F21" s="154"/>
-      <c r="G21" s="155"/>
-      <c r="H21" s="167"/>
-      <c r="I21" s="167"/>
+      <c r="D21" s="158"/>
+      <c r="E21" s="158"/>
+      <c r="F21" s="158"/>
+      <c r="G21" s="159"/>
+      <c r="H21" s="139"/>
+      <c r="I21" s="139"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="44"/>
@@ -5257,13 +5257,13 @@
     <row r="22" spans="1:120" ht="9.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="18"/>
-      <c r="C22" s="156"/>
-      <c r="D22" s="157"/>
-      <c r="E22" s="157"/>
-      <c r="F22" s="157"/>
-      <c r="G22" s="142"/>
-      <c r="H22" s="167"/>
-      <c r="I22" s="167"/>
+      <c r="C22" s="160"/>
+      <c r="D22" s="161"/>
+      <c r="E22" s="161"/>
+      <c r="F22" s="161"/>
+      <c r="G22" s="162"/>
+      <c r="H22" s="139"/>
+      <c r="I22" s="139"/>
       <c r="J22" s="46"/>
       <c r="K22" s="47"/>
       <c r="L22" s="47"/>
@@ -5380,13 +5380,13 @@
       <c r="A23" s="1"/>
       <c r="B23" s="28"/>
       <c r="C23" s="29"/>
-      <c r="D23" s="158" t="s">
+      <c r="D23" s="182" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="132"/>
-      <c r="F23" s="132"/>
-      <c r="G23" s="133"/>
-      <c r="H23" s="184" t="s">
+      <c r="E23" s="164"/>
+      <c r="F23" s="164"/>
+      <c r="G23" s="170"/>
+      <c r="H23" s="138" t="s">
         <v>46</v>
       </c>
       <c r="I23" s="112">
@@ -5508,10 +5508,10 @@
       <c r="A24" s="1"/>
       <c r="B24" s="18"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="134"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="135"/>
-      <c r="G24" s="136"/>
+      <c r="D24" s="166"/>
+      <c r="E24" s="167"/>
+      <c r="F24" s="167"/>
+      <c r="G24" s="171"/>
       <c r="H24" s="112"/>
       <c r="I24" s="112"/>
       <c r="J24" s="14"/>
@@ -5629,15 +5629,15 @@
     <row r="25" spans="1:120" ht="9.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="18"/>
-      <c r="C25" s="153" t="s">
+      <c r="C25" s="180" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="154"/>
-      <c r="E25" s="154"/>
-      <c r="F25" s="154"/>
-      <c r="G25" s="155"/>
-      <c r="H25" s="167"/>
-      <c r="I25" s="167"/>
+      <c r="D25" s="158"/>
+      <c r="E25" s="158"/>
+      <c r="F25" s="158"/>
+      <c r="G25" s="159"/>
+      <c r="H25" s="139"/>
+      <c r="I25" s="139"/>
       <c r="J25" s="42"/>
       <c r="K25" s="42"/>
       <c r="L25" s="44"/>
@@ -5753,13 +5753,13 @@
     <row r="26" spans="1:120" ht="9.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="18"/>
-      <c r="C26" s="141"/>
-      <c r="D26" s="135"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="135"/>
-      <c r="G26" s="139"/>
-      <c r="H26" s="167"/>
-      <c r="I26" s="167"/>
+      <c r="C26" s="179"/>
+      <c r="D26" s="167"/>
+      <c r="E26" s="167"/>
+      <c r="F26" s="167"/>
+      <c r="G26" s="168"/>
+      <c r="H26" s="139"/>
+      <c r="I26" s="139"/>
       <c r="J26" s="46"/>
       <c r="K26" s="47"/>
       <c r="L26" s="47"/>
@@ -5876,13 +5876,13 @@
       <c r="A27" s="1"/>
       <c r="B27" s="28"/>
       <c r="C27" s="29"/>
-      <c r="D27" s="158" t="s">
+      <c r="D27" s="182" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="132"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="133"/>
-      <c r="H27" s="184" t="s">
+      <c r="E27" s="164"/>
+      <c r="F27" s="164"/>
+      <c r="G27" s="170"/>
+      <c r="H27" s="138" t="s">
         <v>44</v>
       </c>
       <c r="I27" s="112">
@@ -6004,10 +6004,10 @@
       <c r="A28" s="1"/>
       <c r="B28" s="28"/>
       <c r="C28" s="30"/>
-      <c r="D28" s="134"/>
-      <c r="E28" s="135"/>
-      <c r="F28" s="135"/>
-      <c r="G28" s="136"/>
+      <c r="D28" s="166"/>
+      <c r="E28" s="167"/>
+      <c r="F28" s="167"/>
+      <c r="G28" s="171"/>
       <c r="H28" s="112"/>
       <c r="I28" s="112"/>
       <c r="J28" s="14"/>
@@ -6126,13 +6126,13 @@
       <c r="A29" s="1"/>
       <c r="B29" s="28"/>
       <c r="C29" s="30"/>
-      <c r="D29" s="159" t="s">
+      <c r="D29" s="183" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="160"/>
-      <c r="F29" s="160"/>
-      <c r="G29" s="160"/>
-      <c r="H29" s="184" t="s">
+      <c r="E29" s="184"/>
+      <c r="F29" s="184"/>
+      <c r="G29" s="184"/>
+      <c r="H29" s="138" t="s">
         <v>44</v>
       </c>
       <c r="I29" s="112">
@@ -6254,10 +6254,10 @@
       <c r="A30" s="1"/>
       <c r="B30" s="28"/>
       <c r="C30" s="31"/>
-      <c r="D30" s="134"/>
-      <c r="E30" s="135"/>
-      <c r="F30" s="135"/>
-      <c r="G30" s="135"/>
+      <c r="D30" s="166"/>
+      <c r="E30" s="167"/>
+      <c r="F30" s="167"/>
+      <c r="G30" s="167"/>
       <c r="H30" s="112"/>
       <c r="I30" s="112"/>
       <c r="J30" s="26"/>
@@ -6375,15 +6375,15 @@
     <row r="31" spans="1:120" ht="9.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="18"/>
-      <c r="C31" s="179" t="s">
+      <c r="C31" s="157" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="154"/>
-      <c r="E31" s="154"/>
-      <c r="F31" s="154"/>
-      <c r="G31" s="155"/>
-      <c r="H31" s="167"/>
-      <c r="I31" s="167"/>
+      <c r="D31" s="158"/>
+      <c r="E31" s="158"/>
+      <c r="F31" s="158"/>
+      <c r="G31" s="159"/>
+      <c r="H31" s="139"/>
+      <c r="I31" s="139"/>
       <c r="J31" s="42"/>
       <c r="K31" s="43"/>
       <c r="L31" s="44"/>
@@ -6499,13 +6499,13 @@
     <row r="32" spans="1:120" ht="9.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="18"/>
-      <c r="C32" s="156"/>
-      <c r="D32" s="157"/>
-      <c r="E32" s="157"/>
-      <c r="F32" s="157"/>
-      <c r="G32" s="142"/>
-      <c r="H32" s="167"/>
-      <c r="I32" s="167"/>
+      <c r="C32" s="160"/>
+      <c r="D32" s="161"/>
+      <c r="E32" s="161"/>
+      <c r="F32" s="161"/>
+      <c r="G32" s="162"/>
+      <c r="H32" s="139"/>
+      <c r="I32" s="139"/>
       <c r="J32" s="46"/>
       <c r="K32" s="47"/>
       <c r="L32" s="47"/>
@@ -6622,14 +6622,14 @@
       <c r="A33" s="1"/>
       <c r="B33" s="18"/>
       <c r="C33" s="32"/>
-      <c r="D33" s="137" t="s">
+      <c r="D33" s="163" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="132"/>
-      <c r="F33" s="132"/>
-      <c r="G33" s="138"/>
-      <c r="H33" s="167"/>
-      <c r="I33" s="167"/>
+      <c r="E33" s="164"/>
+      <c r="F33" s="164"/>
+      <c r="G33" s="165"/>
+      <c r="H33" s="139"/>
+      <c r="I33" s="139"/>
       <c r="J33" s="50"/>
       <c r="K33" s="51"/>
       <c r="L33" s="51"/>
@@ -6746,12 +6746,12 @@
       <c r="A34" s="1"/>
       <c r="B34" s="18"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="134"/>
-      <c r="E34" s="135"/>
-      <c r="F34" s="135"/>
-      <c r="G34" s="139"/>
-      <c r="H34" s="167"/>
-      <c r="I34" s="167"/>
+      <c r="D34" s="166"/>
+      <c r="E34" s="167"/>
+      <c r="F34" s="167"/>
+      <c r="G34" s="168"/>
+      <c r="H34" s="139"/>
+      <c r="I34" s="139"/>
       <c r="J34" s="52"/>
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
@@ -6869,12 +6869,12 @@
       <c r="B35" s="18"/>
       <c r="C35" s="1"/>
       <c r="D35" s="33"/>
-      <c r="E35" s="131" t="s">
+      <c r="E35" s="169" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="132"/>
-      <c r="G35" s="133"/>
-      <c r="H35" s="184" t="s">
+      <c r="F35" s="164"/>
+      <c r="G35" s="170"/>
+      <c r="H35" s="138" t="s">
         <v>45</v>
       </c>
       <c r="I35" s="112">
@@ -6997,9 +6997,9 @@
       <c r="B36" s="18"/>
       <c r="C36" s="1"/>
       <c r="D36" s="34"/>
-      <c r="E36" s="134"/>
-      <c r="F36" s="135"/>
-      <c r="G36" s="136"/>
+      <c r="E36" s="166"/>
+      <c r="F36" s="167"/>
+      <c r="G36" s="171"/>
       <c r="H36" s="112"/>
       <c r="I36" s="112"/>
       <c r="J36" s="14"/>
@@ -7119,12 +7119,12 @@
       <c r="B37" s="18"/>
       <c r="C37" s="1"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="131" t="s">
+      <c r="E37" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F37" s="132"/>
-      <c r="G37" s="133"/>
-      <c r="H37" s="184" t="s">
+      <c r="F37" s="164"/>
+      <c r="G37" s="170"/>
+      <c r="H37" s="138" t="s">
         <v>44</v>
       </c>
       <c r="I37" s="112">
@@ -7247,9 +7247,9 @@
       <c r="B38" s="18"/>
       <c r="C38" s="1"/>
       <c r="D38" s="35"/>
-      <c r="E38" s="134"/>
-      <c r="F38" s="135"/>
-      <c r="G38" s="136"/>
+      <c r="E38" s="166"/>
+      <c r="F38" s="167"/>
+      <c r="G38" s="171"/>
       <c r="H38" s="112"/>
       <c r="I38" s="112"/>
       <c r="J38" s="26"/>
@@ -7368,14 +7368,14 @@
       <c r="A39" s="1"/>
       <c r="B39" s="18"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="180" t="s">
+      <c r="D39" s="172" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="154"/>
-      <c r="F39" s="154"/>
-      <c r="G39" s="155"/>
-      <c r="H39" s="167"/>
-      <c r="I39" s="167"/>
+      <c r="E39" s="158"/>
+      <c r="F39" s="158"/>
+      <c r="G39" s="159"/>
+      <c r="H39" s="139"/>
+      <c r="I39" s="139"/>
       <c r="J39" s="50"/>
       <c r="K39" s="51"/>
       <c r="L39" s="51"/>
@@ -7492,12 +7492,12 @@
       <c r="A40" s="1"/>
       <c r="B40" s="18"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="134"/>
-      <c r="E40" s="135"/>
-      <c r="F40" s="135"/>
-      <c r="G40" s="139"/>
-      <c r="H40" s="167"/>
-      <c r="I40" s="167"/>
+      <c r="D40" s="166"/>
+      <c r="E40" s="167"/>
+      <c r="F40" s="167"/>
+      <c r="G40" s="168"/>
+      <c r="H40" s="139"/>
+      <c r="I40" s="139"/>
       <c r="J40" s="52"/>
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
@@ -7615,12 +7615,12 @@
       <c r="B41" s="18"/>
       <c r="C41" s="1"/>
       <c r="D41" s="33"/>
-      <c r="E41" s="131" t="s">
+      <c r="E41" s="169" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="132"/>
-      <c r="G41" s="133"/>
-      <c r="H41" s="184" t="s">
+      <c r="F41" s="164"/>
+      <c r="G41" s="170"/>
+      <c r="H41" s="138" t="s">
         <v>43</v>
       </c>
       <c r="I41" s="112">
@@ -7743,9 +7743,9 @@
       <c r="B42" s="18"/>
       <c r="C42" s="1"/>
       <c r="D42" s="34"/>
-      <c r="E42" s="134"/>
-      <c r="F42" s="135"/>
-      <c r="G42" s="136"/>
+      <c r="E42" s="166"/>
+      <c r="F42" s="167"/>
+      <c r="G42" s="171"/>
       <c r="H42" s="112"/>
       <c r="I42" s="112"/>
       <c r="J42" s="14"/>
@@ -7865,12 +7865,12 @@
       <c r="B43" s="18"/>
       <c r="C43" s="1"/>
       <c r="D43" s="34"/>
-      <c r="E43" s="131" t="s">
+      <c r="E43" s="169" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="132"/>
-      <c r="G43" s="133"/>
-      <c r="H43" s="184" t="s">
+      <c r="F43" s="164"/>
+      <c r="G43" s="170"/>
+      <c r="H43" s="138" t="s">
         <v>43</v>
       </c>
       <c r="I43" s="112">
@@ -7993,9 +7993,9 @@
       <c r="B44" s="18"/>
       <c r="C44" s="1"/>
       <c r="D44" s="34"/>
-      <c r="E44" s="134"/>
-      <c r="F44" s="135"/>
-      <c r="G44" s="136"/>
+      <c r="E44" s="166"/>
+      <c r="F44" s="167"/>
+      <c r="G44" s="171"/>
       <c r="H44" s="112"/>
       <c r="I44" s="112"/>
       <c r="J44" s="14"/>
@@ -8115,12 +8115,12 @@
       <c r="B45" s="18"/>
       <c r="C45" s="1"/>
       <c r="D45" s="34"/>
-      <c r="E45" s="131" t="s">
+      <c r="E45" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="132"/>
-      <c r="G45" s="133"/>
-      <c r="H45" s="184" t="s">
+      <c r="F45" s="164"/>
+      <c r="G45" s="170"/>
+      <c r="H45" s="138" t="s">
         <v>42</v>
       </c>
       <c r="I45" s="112">
@@ -8243,9 +8243,9 @@
       <c r="B46" s="18"/>
       <c r="C46" s="1"/>
       <c r="D46" s="34"/>
-      <c r="E46" s="134"/>
-      <c r="F46" s="135"/>
-      <c r="G46" s="136"/>
+      <c r="E46" s="166"/>
+      <c r="F46" s="167"/>
+      <c r="G46" s="171"/>
       <c r="H46" s="112"/>
       <c r="I46" s="112"/>
       <c r="J46" s="14"/>
@@ -8365,12 +8365,12 @@
       <c r="B47" s="18"/>
       <c r="C47" s="1"/>
       <c r="D47" s="34"/>
-      <c r="E47" s="131" t="s">
+      <c r="E47" s="169" t="s">
         <v>25</v>
       </c>
-      <c r="F47" s="132"/>
-      <c r="G47" s="133"/>
-      <c r="H47" s="184" t="s">
+      <c r="F47" s="164"/>
+      <c r="G47" s="170"/>
+      <c r="H47" s="138" t="s">
         <v>41</v>
       </c>
       <c r="I47" s="112">
@@ -8493,9 +8493,9 @@
       <c r="B48" s="18"/>
       <c r="C48" s="1"/>
       <c r="D48" s="34"/>
-      <c r="E48" s="134"/>
-      <c r="F48" s="135"/>
-      <c r="G48" s="136"/>
+      <c r="E48" s="166"/>
+      <c r="F48" s="167"/>
+      <c r="G48" s="171"/>
       <c r="H48" s="112"/>
       <c r="I48" s="112"/>
       <c r="J48" s="14"/>
@@ -8615,12 +8615,12 @@
       <c r="B49" s="18"/>
       <c r="C49" s="1"/>
       <c r="D49" s="34"/>
-      <c r="E49" s="131" t="s">
+      <c r="E49" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="132"/>
-      <c r="G49" s="133"/>
-      <c r="H49" s="184" t="s">
+      <c r="F49" s="164"/>
+      <c r="G49" s="170"/>
+      <c r="H49" s="138" t="s">
         <v>50</v>
       </c>
       <c r="I49" s="112">
@@ -8743,9 +8743,9 @@
       <c r="B50" s="18"/>
       <c r="C50" s="1"/>
       <c r="D50" s="34"/>
-      <c r="E50" s="134"/>
-      <c r="F50" s="135"/>
-      <c r="G50" s="136"/>
+      <c r="E50" s="166"/>
+      <c r="F50" s="167"/>
+      <c r="G50" s="171"/>
       <c r="H50" s="112"/>
       <c r="I50" s="112"/>
       <c r="J50" s="14"/>
@@ -8865,12 +8865,12 @@
       <c r="B51" s="18"/>
       <c r="C51" s="1"/>
       <c r="D51" s="34"/>
-      <c r="E51" s="131" t="s">
+      <c r="E51" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="132"/>
-      <c r="G51" s="133"/>
-      <c r="H51" s="184" t="s">
+      <c r="F51" s="164"/>
+      <c r="G51" s="170"/>
+      <c r="H51" s="138" t="s">
         <v>47</v>
       </c>
       <c r="I51" s="112">
@@ -8993,9 +8993,9 @@
       <c r="B52" s="18"/>
       <c r="C52" s="1"/>
       <c r="D52" s="34"/>
-      <c r="E52" s="134"/>
-      <c r="F52" s="135"/>
-      <c r="G52" s="136"/>
+      <c r="E52" s="166"/>
+      <c r="F52" s="167"/>
+      <c r="G52" s="171"/>
       <c r="H52" s="112"/>
       <c r="I52" s="112"/>
       <c r="J52" s="26"/>
@@ -9114,14 +9114,14 @@
       <c r="A53" s="1"/>
       <c r="B53" s="18"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="137" t="s">
+      <c r="D53" s="163" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="132"/>
-      <c r="F53" s="132"/>
-      <c r="G53" s="138"/>
-      <c r="H53" s="167"/>
-      <c r="I53" s="167"/>
+      <c r="E53" s="164"/>
+      <c r="F53" s="164"/>
+      <c r="G53" s="165"/>
+      <c r="H53" s="139"/>
+      <c r="I53" s="139"/>
       <c r="J53" s="50"/>
       <c r="K53" s="51"/>
       <c r="L53" s="51"/>
@@ -9238,12 +9238,12 @@
       <c r="A54" s="1"/>
       <c r="B54" s="18"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="134"/>
-      <c r="E54" s="135"/>
-      <c r="F54" s="135"/>
-      <c r="G54" s="139"/>
-      <c r="H54" s="167"/>
-      <c r="I54" s="167"/>
+      <c r="D54" s="166"/>
+      <c r="E54" s="167"/>
+      <c r="F54" s="167"/>
+      <c r="G54" s="168"/>
+      <c r="H54" s="139"/>
+      <c r="I54" s="139"/>
       <c r="J54" s="52"/>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -9361,12 +9361,12 @@
       <c r="B55" s="18"/>
       <c r="C55" s="1"/>
       <c r="D55" s="34"/>
-      <c r="E55" s="131" t="s">
+      <c r="E55" s="169" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="132"/>
-      <c r="G55" s="133"/>
-      <c r="H55" s="184" t="s">
+      <c r="F55" s="164"/>
+      <c r="G55" s="170"/>
+      <c r="H55" s="138" t="s">
         <v>48</v>
       </c>
       <c r="I55" s="112">
@@ -9489,9 +9489,9 @@
       <c r="B56" s="18"/>
       <c r="C56" s="1"/>
       <c r="D56" s="34"/>
-      <c r="E56" s="134"/>
-      <c r="F56" s="135"/>
-      <c r="G56" s="136"/>
+      <c r="E56" s="166"/>
+      <c r="F56" s="167"/>
+      <c r="G56" s="171"/>
       <c r="H56" s="112"/>
       <c r="I56" s="112"/>
       <c r="J56" s="14"/>
@@ -9611,12 +9611,12 @@
       <c r="B57" s="18"/>
       <c r="C57" s="1"/>
       <c r="D57" s="34"/>
-      <c r="E57" s="131" t="s">
+      <c r="E57" s="169" t="s">
         <v>29</v>
       </c>
-      <c r="F57" s="132"/>
-      <c r="G57" s="133"/>
-      <c r="H57" s="184" t="s">
+      <c r="F57" s="164"/>
+      <c r="G57" s="170"/>
+      <c r="H57" s="138" t="s">
         <v>51</v>
       </c>
       <c r="I57" s="112">
@@ -9739,9 +9739,9 @@
       <c r="B58" s="18"/>
       <c r="C58" s="1"/>
       <c r="D58" s="34"/>
-      <c r="E58" s="134"/>
-      <c r="F58" s="135"/>
-      <c r="G58" s="136"/>
+      <c r="E58" s="166"/>
+      <c r="F58" s="167"/>
+      <c r="G58" s="171"/>
       <c r="H58" s="112"/>
       <c r="I58" s="112"/>
       <c r="J58" s="14"/>
@@ -9861,12 +9861,12 @@
       <c r="B59" s="18"/>
       <c r="C59" s="1"/>
       <c r="D59" s="34"/>
-      <c r="E59" s="131" t="s">
+      <c r="E59" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="F59" s="132"/>
-      <c r="G59" s="133"/>
-      <c r="H59" s="184" t="s">
+      <c r="F59" s="164"/>
+      <c r="G59" s="170"/>
+      <c r="H59" s="138" t="s">
         <v>49</v>
       </c>
       <c r="I59" s="112">
@@ -9989,9 +9989,9 @@
       <c r="B60" s="18"/>
       <c r="C60" s="1"/>
       <c r="D60" s="34"/>
-      <c r="E60" s="134"/>
-      <c r="F60" s="135"/>
-      <c r="G60" s="136"/>
+      <c r="E60" s="166"/>
+      <c r="F60" s="167"/>
+      <c r="G60" s="171"/>
       <c r="H60" s="112"/>
       <c r="I60" s="112"/>
       <c r="J60" s="14"/>
@@ -10111,12 +10111,12 @@
       <c r="B61" s="18"/>
       <c r="C61" s="1"/>
       <c r="D61" s="34"/>
-      <c r="E61" s="131" t="s">
+      <c r="E61" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F61" s="132"/>
-      <c r="G61" s="133"/>
-      <c r="H61" s="184" t="s">
+      <c r="F61" s="164"/>
+      <c r="G61" s="170"/>
+      <c r="H61" s="138" t="s">
         <v>49</v>
       </c>
       <c r="I61" s="112">
@@ -10239,9 +10239,9 @@
       <c r="B62" s="18"/>
       <c r="C62" s="1"/>
       <c r="D62" s="34"/>
-      <c r="E62" s="134"/>
-      <c r="F62" s="135"/>
-      <c r="G62" s="136"/>
+      <c r="E62" s="166"/>
+      <c r="F62" s="167"/>
+      <c r="G62" s="171"/>
       <c r="H62" s="112"/>
       <c r="I62" s="112"/>
       <c r="J62" s="26"/>
@@ -10360,14 +10360,14 @@
       <c r="A63" s="1"/>
       <c r="B63" s="18"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="137" t="s">
+      <c r="D63" s="163" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="132"/>
-      <c r="F63" s="132"/>
-      <c r="G63" s="138"/>
-      <c r="H63" s="167"/>
-      <c r="I63" s="167"/>
+      <c r="E63" s="164"/>
+      <c r="F63" s="164"/>
+      <c r="G63" s="165"/>
+      <c r="H63" s="139"/>
+      <c r="I63" s="139"/>
       <c r="J63" s="50"/>
       <c r="K63" s="51"/>
       <c r="L63" s="51"/>
@@ -10484,12 +10484,12 @@
       <c r="A64" s="1"/>
       <c r="B64" s="18"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="134"/>
-      <c r="E64" s="135"/>
-      <c r="F64" s="135"/>
-      <c r="G64" s="139"/>
-      <c r="H64" s="167"/>
-      <c r="I64" s="167"/>
+      <c r="D64" s="166"/>
+      <c r="E64" s="167"/>
+      <c r="F64" s="167"/>
+      <c r="G64" s="168"/>
+      <c r="H64" s="139"/>
+      <c r="I64" s="139"/>
       <c r="J64" s="52"/>
       <c r="K64" s="49"/>
       <c r="L64" s="49"/>
@@ -10607,12 +10607,12 @@
       <c r="B65" s="18"/>
       <c r="C65" s="1"/>
       <c r="D65" s="34"/>
-      <c r="E65" s="131" t="s">
+      <c r="E65" s="169" t="s">
         <v>35</v>
       </c>
-      <c r="F65" s="132"/>
-      <c r="G65" s="133"/>
-      <c r="H65" s="184" t="s">
+      <c r="F65" s="164"/>
+      <c r="G65" s="170"/>
+      <c r="H65" s="138" t="s">
         <v>52</v>
       </c>
       <c r="I65" s="112">
@@ -10735,9 +10735,9 @@
       <c r="B66" s="18"/>
       <c r="C66" s="1"/>
       <c r="D66" s="34"/>
-      <c r="E66" s="134"/>
-      <c r="F66" s="135"/>
-      <c r="G66" s="136"/>
+      <c r="E66" s="166"/>
+      <c r="F66" s="167"/>
+      <c r="G66" s="171"/>
       <c r="H66" s="112"/>
       <c r="I66" s="112"/>
       <c r="J66" s="14"/>
@@ -10857,12 +10857,12 @@
       <c r="B67" s="18"/>
       <c r="C67" s="1"/>
       <c r="D67" s="34"/>
-      <c r="E67" s="131" t="s">
+      <c r="E67" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="F67" s="132"/>
-      <c r="G67" s="133"/>
-      <c r="H67" s="184" t="s">
+      <c r="F67" s="164"/>
+      <c r="G67" s="170"/>
+      <c r="H67" s="138" t="s">
         <v>53</v>
       </c>
       <c r="I67" s="112">
@@ -10985,9 +10985,9 @@
       <c r="B68" s="18"/>
       <c r="C68" s="1"/>
       <c r="D68" s="34"/>
-      <c r="E68" s="134"/>
-      <c r="F68" s="135"/>
-      <c r="G68" s="136"/>
+      <c r="E68" s="166"/>
+      <c r="F68" s="167"/>
+      <c r="G68" s="171"/>
       <c r="H68" s="112"/>
       <c r="I68" s="112"/>
       <c r="J68" s="14"/>
@@ -11107,12 +11107,12 @@
       <c r="B69" s="18"/>
       <c r="C69" s="1"/>
       <c r="D69" s="34"/>
-      <c r="E69" s="131" t="s">
+      <c r="E69" s="169" t="s">
         <v>36</v>
       </c>
-      <c r="F69" s="132"/>
-      <c r="G69" s="133"/>
-      <c r="H69" s="184" t="s">
+      <c r="F69" s="164"/>
+      <c r="G69" s="170"/>
+      <c r="H69" s="138" t="s">
         <v>54</v>
       </c>
       <c r="I69" s="112">
@@ -11235,9 +11235,9 @@
       <c r="B70" s="18"/>
       <c r="C70" s="1"/>
       <c r="D70" s="34"/>
-      <c r="E70" s="134"/>
-      <c r="F70" s="135"/>
-      <c r="G70" s="136"/>
+      <c r="E70" s="166"/>
+      <c r="F70" s="167"/>
+      <c r="G70" s="171"/>
       <c r="H70" s="112"/>
       <c r="I70" s="112"/>
       <c r="J70" s="14"/>
@@ -11357,12 +11357,12 @@
       <c r="B71" s="18"/>
       <c r="C71" s="1"/>
       <c r="D71" s="34"/>
-      <c r="E71" s="131" t="s">
+      <c r="E71" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="F71" s="132"/>
-      <c r="G71" s="133"/>
-      <c r="H71" s="184" t="s">
+      <c r="F71" s="164"/>
+      <c r="G71" s="170"/>
+      <c r="H71" s="138" t="s">
         <v>55</v>
       </c>
       <c r="I71" s="112">
@@ -11485,9 +11485,9 @@
       <c r="B72" s="18"/>
       <c r="C72" s="1"/>
       <c r="D72" s="35"/>
-      <c r="E72" s="134"/>
-      <c r="F72" s="135"/>
-      <c r="G72" s="136"/>
+      <c r="E72" s="166"/>
+      <c r="F72" s="167"/>
+      <c r="G72" s="171"/>
       <c r="H72" s="112"/>
       <c r="I72" s="112"/>
       <c r="J72" s="26"/>
@@ -11605,14 +11605,14 @@
     <row r="73" spans="1:120" ht="9.75" customHeight="1">
       <c r="A73" s="16"/>
       <c r="B73" s="36"/>
-      <c r="C73" s="140" t="s">
+      <c r="C73" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="D73" s="132"/>
-      <c r="E73" s="132"/>
-      <c r="F73" s="132"/>
-      <c r="G73" s="138"/>
-      <c r="H73" s="184" t="s">
+      <c r="D73" s="164"/>
+      <c r="E73" s="164"/>
+      <c r="F73" s="164"/>
+      <c r="G73" s="165"/>
+      <c r="H73" s="138" t="s">
         <v>55</v>
       </c>
       <c r="I73" s="112">
@@ -11733,11 +11733,11 @@
     <row r="74" spans="1:120" ht="9.75" customHeight="1">
       <c r="A74" s="16"/>
       <c r="B74" s="36"/>
-      <c r="C74" s="141"/>
-      <c r="D74" s="135"/>
-      <c r="E74" s="135"/>
-      <c r="F74" s="135"/>
-      <c r="G74" s="139"/>
+      <c r="C74" s="179"/>
+      <c r="D74" s="167"/>
+      <c r="E74" s="167"/>
+      <c r="F74" s="167"/>
+      <c r="G74" s="168"/>
       <c r="H74" s="112"/>
       <c r="I74" s="112"/>
       <c r="J74" s="19"/>
@@ -11855,14 +11855,14 @@
     <row r="75" spans="1:120" ht="9.75" customHeight="1">
       <c r="A75" s="16"/>
       <c r="B75" s="36"/>
-      <c r="C75" s="140" t="s">
+      <c r="C75" s="146" t="s">
         <v>34</v>
       </c>
-      <c r="D75" s="132"/>
-      <c r="E75" s="132"/>
-      <c r="F75" s="132"/>
-      <c r="G75" s="138"/>
-      <c r="H75" s="184" t="s">
+      <c r="D75" s="164"/>
+      <c r="E75" s="164"/>
+      <c r="F75" s="164"/>
+      <c r="G75" s="165"/>
+      <c r="H75" s="138" t="s">
         <v>58</v>
       </c>
       <c r="I75" s="112"/>
@@ -11981,11 +11981,11 @@
     <row r="76" spans="1:120" ht="9.75" customHeight="1">
       <c r="A76" s="16"/>
       <c r="B76" s="36"/>
-      <c r="C76" s="142"/>
-      <c r="D76" s="142"/>
-      <c r="E76" s="142"/>
-      <c r="F76" s="142"/>
-      <c r="G76" s="142"/>
+      <c r="C76" s="162"/>
+      <c r="D76" s="162"/>
+      <c r="E76" s="162"/>
+      <c r="F76" s="162"/>
+      <c r="G76" s="162"/>
       <c r="H76" s="112"/>
       <c r="I76" s="112"/>
       <c r="J76" s="19"/>
@@ -12103,15 +12103,15 @@
     <row r="77" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A77" s="16"/>
       <c r="B77" s="71"/>
-      <c r="C77" s="143" t="s">
+      <c r="C77" s="187" t="s">
         <v>62</v>
       </c>
-      <c r="D77" s="144"/>
-      <c r="E77" s="144"/>
-      <c r="F77" s="144"/>
-      <c r="G77" s="145"/>
-      <c r="H77" s="185"/>
-      <c r="I77" s="181"/>
+      <c r="D77" s="188"/>
+      <c r="E77" s="188"/>
+      <c r="F77" s="188"/>
+      <c r="G77" s="189"/>
+      <c r="H77" s="140"/>
+      <c r="I77" s="129"/>
       <c r="J77" s="63"/>
       <c r="K77" s="64"/>
       <c r="L77" s="64"/>
@@ -12227,13 +12227,13 @@
     <row r="78" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A78" s="16"/>
       <c r="B78" s="71"/>
-      <c r="C78" s="146"/>
-      <c r="D78" s="147"/>
-      <c r="E78" s="147"/>
-      <c r="F78" s="147"/>
-      <c r="G78" s="148"/>
-      <c r="H78" s="186"/>
-      <c r="I78" s="182"/>
+      <c r="C78" s="190"/>
+      <c r="D78" s="191"/>
+      <c r="E78" s="191"/>
+      <c r="F78" s="191"/>
+      <c r="G78" s="192"/>
+      <c r="H78" s="141"/>
+      <c r="I78" s="130"/>
       <c r="J78" s="63"/>
       <c r="K78" s="64"/>
       <c r="L78" s="64"/>
@@ -12350,12 +12350,12 @@
       <c r="A79" s="16"/>
       <c r="B79" s="71"/>
       <c r="C79" s="76"/>
-      <c r="D79" s="115" t="s">
+      <c r="D79" s="132" t="s">
         <v>63</v>
       </c>
-      <c r="E79" s="116"/>
-      <c r="F79" s="116"/>
-      <c r="G79" s="117"/>
+      <c r="E79" s="133"/>
+      <c r="F79" s="133"/>
+      <c r="G79" s="134"/>
       <c r="H79" s="77"/>
       <c r="I79" s="67"/>
       <c r="J79" s="63"/>
@@ -12474,10 +12474,10 @@
       <c r="A80" s="16"/>
       <c r="B80" s="71"/>
       <c r="C80" s="76"/>
-      <c r="D80" s="118"/>
-      <c r="E80" s="119"/>
-      <c r="F80" s="119"/>
-      <c r="G80" s="120"/>
+      <c r="D80" s="135"/>
+      <c r="E80" s="136"/>
+      <c r="F80" s="136"/>
+      <c r="G80" s="137"/>
       <c r="H80" s="77"/>
       <c r="I80" s="67"/>
       <c r="J80" s="63"/>
@@ -12597,15 +12597,15 @@
       <c r="B81" s="36"/>
       <c r="C81" s="60"/>
       <c r="D81" s="70"/>
-      <c r="E81" s="149" t="s">
+      <c r="E81" s="105" t="s">
         <v>73</v>
       </c>
-      <c r="F81" s="149"/>
-      <c r="G81" s="149"/>
-      <c r="H81" s="103">
+      <c r="F81" s="105"/>
+      <c r="G81" s="105"/>
+      <c r="H81" s="111">
         <v>45611</v>
       </c>
-      <c r="I81" s="105">
+      <c r="I81" s="126">
         <v>100</v>
       </c>
       <c r="J81" s="19"/>
@@ -12725,11 +12725,11 @@
       <c r="B82" s="36"/>
       <c r="C82" s="60"/>
       <c r="D82" s="70"/>
-      <c r="E82" s="102"/>
-      <c r="F82" s="102"/>
-      <c r="G82" s="102"/>
-      <c r="H82" s="104"/>
-      <c r="I82" s="106"/>
+      <c r="E82" s="103"/>
+      <c r="F82" s="103"/>
+      <c r="G82" s="103"/>
+      <c r="H82" s="107"/>
+      <c r="I82" s="109"/>
       <c r="J82" s="19"/>
       <c r="K82" s="20"/>
       <c r="L82" s="20"/>
@@ -12847,15 +12847,15 @@
       <c r="B83" s="36"/>
       <c r="C83" s="60"/>
       <c r="D83" s="70"/>
-      <c r="E83" s="102" t="s">
+      <c r="E83" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="F83" s="102"/>
-      <c r="G83" s="102"/>
-      <c r="H83" s="103">
+      <c r="F83" s="103"/>
+      <c r="G83" s="103"/>
+      <c r="H83" s="111">
         <v>45615</v>
       </c>
-      <c r="I83" s="105">
+      <c r="I83" s="126">
         <v>100</v>
       </c>
       <c r="J83" s="19"/>
@@ -12975,11 +12975,11 @@
       <c r="B84" s="36"/>
       <c r="C84" s="60"/>
       <c r="D84" s="70"/>
-      <c r="E84" s="102"/>
-      <c r="F84" s="102"/>
-      <c r="G84" s="102"/>
-      <c r="H84" s="104"/>
-      <c r="I84" s="106"/>
+      <c r="E84" s="103"/>
+      <c r="F84" s="103"/>
+      <c r="G84" s="103"/>
+      <c r="H84" s="107"/>
+      <c r="I84" s="109"/>
       <c r="J84" s="19"/>
       <c r="K84" s="20"/>
       <c r="L84" s="20"/>
@@ -13097,15 +13097,15 @@
       <c r="B85" s="36"/>
       <c r="C85" s="60"/>
       <c r="D85" s="70"/>
-      <c r="E85" s="189" t="s">
+      <c r="E85" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="F85" s="121"/>
-      <c r="G85" s="122"/>
-      <c r="H85" s="111">
+      <c r="F85" s="115"/>
+      <c r="G85" s="116"/>
+      <c r="H85" s="110">
         <v>45617</v>
       </c>
-      <c r="I85" s="105">
+      <c r="I85" s="126">
         <v>100</v>
       </c>
       <c r="J85" s="62"/>
@@ -13225,11 +13225,11 @@
       <c r="B86" s="36"/>
       <c r="C86" s="60"/>
       <c r="D86" s="70"/>
-      <c r="E86" s="150"/>
-      <c r="F86" s="125"/>
-      <c r="G86" s="126"/>
-      <c r="H86" s="111"/>
-      <c r="I86" s="106"/>
+      <c r="E86" s="117"/>
+      <c r="F86" s="118"/>
+      <c r="G86" s="119"/>
+      <c r="H86" s="110"/>
+      <c r="I86" s="109"/>
       <c r="J86" s="62"/>
       <c r="K86" s="20"/>
       <c r="L86" s="20"/>
@@ -13346,16 +13346,16 @@
       <c r="A87" s="16"/>
       <c r="B87" s="71"/>
       <c r="C87" s="90"/>
-      <c r="D87" s="102" t="s">
+      <c r="D87" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="E87" s="102"/>
-      <c r="F87" s="102"/>
-      <c r="G87" s="102"/>
-      <c r="H87" s="103">
+      <c r="E87" s="103"/>
+      <c r="F87" s="103"/>
+      <c r="G87" s="103"/>
+      <c r="H87" s="111">
         <v>45615</v>
       </c>
-      <c r="I87" s="105">
+      <c r="I87" s="126">
         <v>100</v>
       </c>
       <c r="J87" s="62"/>
@@ -13474,12 +13474,12 @@
       <c r="A88" s="16"/>
       <c r="B88" s="71"/>
       <c r="C88" s="90"/>
-      <c r="D88" s="102"/>
-      <c r="E88" s="102"/>
-      <c r="F88" s="102"/>
-      <c r="G88" s="102"/>
-      <c r="H88" s="104"/>
-      <c r="I88" s="106"/>
+      <c r="D88" s="103"/>
+      <c r="E88" s="103"/>
+      <c r="F88" s="103"/>
+      <c r="G88" s="103"/>
+      <c r="H88" s="107"/>
+      <c r="I88" s="109"/>
       <c r="J88" s="62"/>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -13596,14 +13596,14 @@
       <c r="A89" s="16"/>
       <c r="B89" s="36"/>
       <c r="C89" s="79"/>
-      <c r="D89" s="115" t="s">
+      <c r="D89" s="132" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="116"/>
-      <c r="F89" s="116"/>
-      <c r="G89" s="117"/>
-      <c r="H89" s="187"/>
-      <c r="I89" s="188"/>
+      <c r="E89" s="133"/>
+      <c r="F89" s="133"/>
+      <c r="G89" s="134"/>
+      <c r="H89" s="131"/>
+      <c r="I89" s="128"/>
       <c r="J89" s="66"/>
       <c r="K89" s="64"/>
       <c r="L89" s="64"/>
@@ -13720,12 +13720,12 @@
       <c r="A90" s="16"/>
       <c r="B90" s="36"/>
       <c r="C90" s="79"/>
-      <c r="D90" s="118"/>
-      <c r="E90" s="119"/>
-      <c r="F90" s="119"/>
-      <c r="G90" s="120"/>
-      <c r="H90" s="187"/>
-      <c r="I90" s="188"/>
+      <c r="D90" s="135"/>
+      <c r="E90" s="136"/>
+      <c r="F90" s="136"/>
+      <c r="G90" s="137"/>
+      <c r="H90" s="131"/>
+      <c r="I90" s="128"/>
       <c r="J90" s="66"/>
       <c r="K90" s="64"/>
       <c r="L90" s="64"/>
@@ -13843,15 +13843,15 @@
       <c r="B91" s="36"/>
       <c r="C91" s="60"/>
       <c r="D91" s="70"/>
-      <c r="E91" s="149" t="s">
+      <c r="E91" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="F91" s="149"/>
-      <c r="G91" s="149"/>
-      <c r="H91" s="103">
+      <c r="F91" s="105"/>
+      <c r="G91" s="105"/>
+      <c r="H91" s="111">
         <v>45616</v>
       </c>
-      <c r="I91" s="105">
+      <c r="I91" s="126">
         <v>100</v>
       </c>
       <c r="J91" s="19"/>
@@ -13971,11 +13971,11 @@
       <c r="B92" s="36"/>
       <c r="C92" s="60"/>
       <c r="D92" s="70"/>
-      <c r="E92" s="102"/>
-      <c r="F92" s="102"/>
-      <c r="G92" s="102"/>
-      <c r="H92" s="104"/>
-      <c r="I92" s="106"/>
+      <c r="E92" s="103"/>
+      <c r="F92" s="103"/>
+      <c r="G92" s="103"/>
+      <c r="H92" s="107"/>
+      <c r="I92" s="109"/>
       <c r="J92" s="19"/>
       <c r="K92" s="20"/>
       <c r="L92" s="20"/>
@@ -14093,15 +14093,15 @@
       <c r="B93" s="36"/>
       <c r="C93" s="60"/>
       <c r="D93" s="70"/>
-      <c r="E93" s="102" t="s">
+      <c r="E93" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="F93" s="102"/>
-      <c r="G93" s="102"/>
-      <c r="H93" s="103">
+      <c r="F93" s="103"/>
+      <c r="G93" s="103"/>
+      <c r="H93" s="111">
         <v>45617</v>
       </c>
-      <c r="I93" s="105">
+      <c r="I93" s="126">
         <v>100</v>
       </c>
       <c r="J93" s="19"/>
@@ -14221,11 +14221,11 @@
       <c r="B94" s="36"/>
       <c r="C94" s="60"/>
       <c r="D94" s="70"/>
-      <c r="E94" s="102"/>
-      <c r="F94" s="102"/>
-      <c r="G94" s="102"/>
-      <c r="H94" s="104"/>
-      <c r="I94" s="106"/>
+      <c r="E94" s="103"/>
+      <c r="F94" s="103"/>
+      <c r="G94" s="103"/>
+      <c r="H94" s="107"/>
+      <c r="I94" s="109"/>
       <c r="J94" s="19"/>
       <c r="K94" s="20"/>
       <c r="L94" s="20"/>
@@ -14343,15 +14343,15 @@
       <c r="B95" s="36"/>
       <c r="C95" s="60"/>
       <c r="D95" s="70"/>
-      <c r="E95" s="102" t="s">
+      <c r="E95" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="F95" s="102"/>
-      <c r="G95" s="102"/>
-      <c r="H95" s="103">
+      <c r="F95" s="103"/>
+      <c r="G95" s="103"/>
+      <c r="H95" s="111">
         <v>45618</v>
       </c>
-      <c r="I95" s="105">
+      <c r="I95" s="126">
         <v>100</v>
       </c>
       <c r="J95" s="19"/>
@@ -14471,11 +14471,11 @@
       <c r="B96" s="36"/>
       <c r="C96" s="60"/>
       <c r="D96" s="70"/>
-      <c r="E96" s="102"/>
-      <c r="F96" s="102"/>
-      <c r="G96" s="102"/>
-      <c r="H96" s="104"/>
-      <c r="I96" s="106"/>
+      <c r="E96" s="103"/>
+      <c r="F96" s="103"/>
+      <c r="G96" s="103"/>
+      <c r="H96" s="107"/>
+      <c r="I96" s="109"/>
       <c r="J96" s="19"/>
       <c r="K96" s="20"/>
       <c r="L96" s="20"/>
@@ -14593,15 +14593,15 @@
       <c r="B97" s="36"/>
       <c r="C97" s="60"/>
       <c r="D97" s="70"/>
-      <c r="E97" s="102" t="s">
+      <c r="E97" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="F97" s="102"/>
-      <c r="G97" s="102"/>
-      <c r="H97" s="103">
+      <c r="F97" s="103"/>
+      <c r="G97" s="103"/>
+      <c r="H97" s="111">
         <v>45621</v>
       </c>
-      <c r="I97" s="105">
+      <c r="I97" s="126">
         <v>100</v>
       </c>
       <c r="J97" s="19"/>
@@ -14721,11 +14721,11 @@
       <c r="B98" s="36"/>
       <c r="C98" s="60"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="102"/>
-      <c r="F98" s="102"/>
-      <c r="G98" s="102"/>
-      <c r="H98" s="104"/>
-      <c r="I98" s="106"/>
+      <c r="E98" s="103"/>
+      <c r="F98" s="103"/>
+      <c r="G98" s="103"/>
+      <c r="H98" s="107"/>
+      <c r="I98" s="109"/>
       <c r="J98" s="19"/>
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
@@ -14843,15 +14843,15 @@
       <c r="B99" s="36"/>
       <c r="C99" s="60"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="102" t="s">
+      <c r="E99" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="F99" s="102"/>
-      <c r="G99" s="102"/>
-      <c r="H99" s="103">
+      <c r="F99" s="103"/>
+      <c r="G99" s="103"/>
+      <c r="H99" s="111">
         <v>45622</v>
       </c>
-      <c r="I99" s="105">
+      <c r="I99" s="126">
         <v>100</v>
       </c>
       <c r="J99" s="19"/>
@@ -14971,11 +14971,11 @@
       <c r="B100" s="36"/>
       <c r="C100" s="60"/>
       <c r="D100" s="70"/>
-      <c r="E100" s="102"/>
-      <c r="F100" s="102"/>
-      <c r="G100" s="102"/>
-      <c r="H100" s="104"/>
-      <c r="I100" s="106"/>
+      <c r="E100" s="103"/>
+      <c r="F100" s="103"/>
+      <c r="G100" s="103"/>
+      <c r="H100" s="107"/>
+      <c r="I100" s="109"/>
       <c r="J100" s="19"/>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -15093,12 +15093,12 @@
       <c r="B101" s="71"/>
       <c r="C101" s="91"/>
       <c r="D101" s="70"/>
-      <c r="E101" s="150" t="s">
+      <c r="E101" s="117" t="s">
         <v>61</v>
       </c>
-      <c r="F101" s="125"/>
-      <c r="G101" s="126"/>
-      <c r="H101" s="103">
+      <c r="F101" s="118"/>
+      <c r="G101" s="119"/>
+      <c r="H101" s="111">
         <v>45623</v>
       </c>
       <c r="I101" s="112">
@@ -15221,10 +15221,10 @@
       <c r="B102" s="71"/>
       <c r="C102" s="91"/>
       <c r="D102" s="70"/>
-      <c r="E102" s="150"/>
-      <c r="F102" s="125"/>
-      <c r="G102" s="126"/>
-      <c r="H102" s="104"/>
+      <c r="E102" s="117"/>
+      <c r="F102" s="118"/>
+      <c r="G102" s="119"/>
+      <c r="H102" s="107"/>
       <c r="I102" s="112"/>
       <c r="J102" s="62"/>
       <c r="K102" s="20"/>
@@ -15342,16 +15342,16 @@
       <c r="A103" s="16"/>
       <c r="B103" s="71"/>
       <c r="C103" s="90"/>
-      <c r="D103" s="102" t="s">
+      <c r="D103" s="103" t="s">
         <v>77</v>
       </c>
-      <c r="E103" s="102"/>
-      <c r="F103" s="102"/>
-      <c r="G103" s="102"/>
-      <c r="H103" s="103">
+      <c r="E103" s="103"/>
+      <c r="F103" s="103"/>
+      <c r="G103" s="103"/>
+      <c r="H103" s="111">
         <v>45622</v>
       </c>
-      <c r="I103" s="109">
+      <c r="I103" s="113">
         <v>100</v>
       </c>
       <c r="J103" s="62"/>
@@ -15470,12 +15470,12 @@
       <c r="A104" s="16"/>
       <c r="B104" s="71"/>
       <c r="C104" s="90"/>
-      <c r="D104" s="102"/>
-      <c r="E104" s="102"/>
-      <c r="F104" s="102"/>
-      <c r="G104" s="102"/>
-      <c r="H104" s="104"/>
-      <c r="I104" s="110"/>
+      <c r="D104" s="103"/>
+      <c r="E104" s="103"/>
+      <c r="F104" s="103"/>
+      <c r="G104" s="103"/>
+      <c r="H104" s="107"/>
+      <c r="I104" s="143"/>
       <c r="J104" s="62"/>
       <c r="K104" s="20"/>
       <c r="L104" s="20"/>
@@ -15591,15 +15591,15 @@
     <row r="105" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A105" s="16"/>
       <c r="B105" s="71"/>
-      <c r="C105" s="143" t="s">
+      <c r="C105" s="187" t="s">
         <v>64</v>
       </c>
-      <c r="D105" s="144"/>
-      <c r="E105" s="144"/>
-      <c r="F105" s="144"/>
-      <c r="G105" s="145"/>
-      <c r="H105" s="190"/>
-      <c r="I105" s="188"/>
+      <c r="D105" s="188"/>
+      <c r="E105" s="188"/>
+      <c r="F105" s="188"/>
+      <c r="G105" s="189"/>
+      <c r="H105" s="127"/>
+      <c r="I105" s="128"/>
       <c r="J105" s="66"/>
       <c r="K105" s="64"/>
       <c r="L105" s="64"/>
@@ -15715,13 +15715,13 @@
     <row r="106" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A106" s="16"/>
       <c r="B106" s="71"/>
-      <c r="C106" s="146"/>
-      <c r="D106" s="147"/>
-      <c r="E106" s="147"/>
-      <c r="F106" s="147"/>
-      <c r="G106" s="148"/>
-      <c r="H106" s="190"/>
-      <c r="I106" s="188"/>
+      <c r="C106" s="190"/>
+      <c r="D106" s="191"/>
+      <c r="E106" s="191"/>
+      <c r="F106" s="191"/>
+      <c r="G106" s="192"/>
+      <c r="H106" s="127"/>
+      <c r="I106" s="128"/>
       <c r="J106" s="66"/>
       <c r="K106" s="64"/>
       <c r="L106" s="64"/>
@@ -15838,14 +15838,14 @@
       <c r="A107" s="16"/>
       <c r="B107" s="36"/>
       <c r="C107" s="78"/>
-      <c r="D107" s="115" t="s">
+      <c r="D107" s="132" t="s">
         <v>59</v>
       </c>
-      <c r="E107" s="116"/>
-      <c r="F107" s="116"/>
-      <c r="G107" s="117"/>
-      <c r="H107" s="190"/>
-      <c r="I107" s="188"/>
+      <c r="E107" s="133"/>
+      <c r="F107" s="133"/>
+      <c r="G107" s="134"/>
+      <c r="H107" s="127"/>
+      <c r="I107" s="128"/>
       <c r="J107" s="66"/>
       <c r="K107" s="64"/>
       <c r="L107" s="64"/>
@@ -15962,12 +15962,12 @@
       <c r="A108" s="16"/>
       <c r="B108" s="36"/>
       <c r="C108" s="76"/>
-      <c r="D108" s="118"/>
-      <c r="E108" s="119"/>
-      <c r="F108" s="119"/>
-      <c r="G108" s="120"/>
-      <c r="H108" s="190"/>
-      <c r="I108" s="188"/>
+      <c r="D108" s="135"/>
+      <c r="E108" s="136"/>
+      <c r="F108" s="136"/>
+      <c r="G108" s="137"/>
+      <c r="H108" s="127"/>
+      <c r="I108" s="128"/>
       <c r="J108" s="66"/>
       <c r="K108" s="64"/>
       <c r="L108" s="64"/>
@@ -16085,15 +16085,15 @@
       <c r="B109" s="36"/>
       <c r="C109" s="60"/>
       <c r="D109" s="70"/>
-      <c r="E109" s="149" t="s">
+      <c r="E109" s="105" t="s">
         <v>73</v>
       </c>
-      <c r="F109" s="149"/>
-      <c r="G109" s="149"/>
-      <c r="H109" s="103">
+      <c r="F109" s="105"/>
+      <c r="G109" s="105"/>
+      <c r="H109" s="111">
         <v>45624</v>
       </c>
-      <c r="I109" s="109">
+      <c r="I109" s="113">
         <v>100</v>
       </c>
       <c r="J109" s="62"/>
@@ -16213,11 +16213,11 @@
       <c r="B110" s="36"/>
       <c r="C110" s="60"/>
       <c r="D110" s="70"/>
-      <c r="E110" s="102"/>
-      <c r="F110" s="102"/>
-      <c r="G110" s="102"/>
-      <c r="H110" s="104"/>
-      <c r="I110" s="110"/>
+      <c r="E110" s="103"/>
+      <c r="F110" s="103"/>
+      <c r="G110" s="103"/>
+      <c r="H110" s="107"/>
+      <c r="I110" s="143"/>
       <c r="J110" s="62"/>
       <c r="K110" s="20"/>
       <c r="L110" s="20"/>
@@ -16335,15 +16335,17 @@
       <c r="B111" s="36"/>
       <c r="C111" s="60"/>
       <c r="D111" s="70"/>
-      <c r="E111" s="102" t="s">
+      <c r="E111" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="F111" s="102"/>
-      <c r="G111" s="102"/>
-      <c r="H111" s="103">
+      <c r="F111" s="103"/>
+      <c r="G111" s="103"/>
+      <c r="H111" s="111">
         <v>45625</v>
       </c>
-      <c r="I111" s="109"/>
+      <c r="I111" s="113">
+        <v>100</v>
+      </c>
       <c r="J111" s="62"/>
       <c r="K111" s="20"/>
       <c r="L111" s="20"/>
@@ -16461,11 +16463,11 @@
       <c r="B112" s="36"/>
       <c r="C112" s="60"/>
       <c r="D112" s="70"/>
-      <c r="E112" s="102"/>
-      <c r="F112" s="102"/>
-      <c r="G112" s="102"/>
-      <c r="H112" s="104"/>
-      <c r="I112" s="110"/>
+      <c r="E112" s="103"/>
+      <c r="F112" s="103"/>
+      <c r="G112" s="103"/>
+      <c r="H112" s="107"/>
+      <c r="I112" s="143"/>
       <c r="J112" s="62"/>
       <c r="K112" s="20"/>
       <c r="L112" s="20"/>
@@ -16583,15 +16585,17 @@
       <c r="B113" s="71"/>
       <c r="C113" s="91"/>
       <c r="D113" s="70"/>
-      <c r="E113" s="102" t="s">
+      <c r="E113" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="F113" s="102"/>
-      <c r="G113" s="102"/>
-      <c r="H113" s="111">
+      <c r="F113" s="103"/>
+      <c r="G113" s="103"/>
+      <c r="H113" s="110">
         <v>45629</v>
       </c>
-      <c r="I113" s="112"/>
+      <c r="I113" s="112">
+        <v>100</v>
+      </c>
       <c r="J113" s="62"/>
       <c r="K113" s="20"/>
       <c r="L113" s="20"/>
@@ -16709,11 +16713,11 @@
       <c r="B114" s="71"/>
       <c r="C114" s="91"/>
       <c r="D114" s="70"/>
-      <c r="E114" s="198"/>
-      <c r="F114" s="198"/>
-      <c r="G114" s="198"/>
-      <c r="H114" s="103"/>
-      <c r="I114" s="109"/>
+      <c r="E114" s="125"/>
+      <c r="F114" s="125"/>
+      <c r="G114" s="125"/>
+      <c r="H114" s="111"/>
+      <c r="I114" s="113"/>
       <c r="J114" s="62"/>
       <c r="K114" s="20"/>
       <c r="L114" s="20"/>
@@ -16830,16 +16834,18 @@
       <c r="A115" s="16"/>
       <c r="B115" s="71"/>
       <c r="C115" s="91"/>
-      <c r="D115" s="102" t="s">
+      <c r="D115" s="103" t="s">
         <v>78</v>
       </c>
-      <c r="E115" s="102"/>
-      <c r="F115" s="102"/>
-      <c r="G115" s="102"/>
-      <c r="H115" s="111">
+      <c r="E115" s="103"/>
+      <c r="F115" s="103"/>
+      <c r="G115" s="103"/>
+      <c r="H115" s="110">
         <v>45625</v>
       </c>
-      <c r="I115" s="112"/>
+      <c r="I115" s="112">
+        <v>100</v>
+      </c>
       <c r="J115" s="62"/>
       <c r="K115" s="20"/>
       <c r="L115" s="20"/>
@@ -16956,11 +16962,11 @@
       <c r="A116" s="16"/>
       <c r="B116" s="71"/>
       <c r="C116" s="91"/>
-      <c r="D116" s="102"/>
-      <c r="E116" s="102"/>
-      <c r="F116" s="102"/>
-      <c r="G116" s="102"/>
-      <c r="H116" s="111"/>
+      <c r="D116" s="103"/>
+      <c r="E116" s="103"/>
+      <c r="F116" s="103"/>
+      <c r="G116" s="103"/>
+      <c r="H116" s="110"/>
       <c r="I116" s="112"/>
       <c r="J116" s="62"/>
       <c r="K116" s="20"/>
@@ -17078,14 +17084,14 @@
       <c r="A117" s="16"/>
       <c r="B117" s="36"/>
       <c r="C117" s="80"/>
-      <c r="D117" s="115" t="s">
+      <c r="D117" s="132" t="s">
         <v>60</v>
       </c>
-      <c r="E117" s="116"/>
-      <c r="F117" s="116"/>
-      <c r="G117" s="117"/>
-      <c r="H117" s="191"/>
-      <c r="I117" s="181"/>
+      <c r="E117" s="133"/>
+      <c r="F117" s="133"/>
+      <c r="G117" s="134"/>
+      <c r="H117" s="121"/>
+      <c r="I117" s="129"/>
       <c r="J117" s="63"/>
       <c r="K117" s="64"/>
       <c r="L117" s="64"/>
@@ -17202,12 +17208,12 @@
       <c r="A118" s="16"/>
       <c r="B118" s="36"/>
       <c r="C118" s="80"/>
-      <c r="D118" s="118"/>
-      <c r="E118" s="119"/>
-      <c r="F118" s="119"/>
-      <c r="G118" s="120"/>
-      <c r="H118" s="192"/>
-      <c r="I118" s="182"/>
+      <c r="D118" s="135"/>
+      <c r="E118" s="136"/>
+      <c r="F118" s="136"/>
+      <c r="G118" s="137"/>
+      <c r="H118" s="122"/>
+      <c r="I118" s="130"/>
       <c r="J118" s="63"/>
       <c r="K118" s="64"/>
       <c r="L118" s="64"/>
@@ -17325,15 +17331,15 @@
       <c r="B119" s="36"/>
       <c r="C119" s="60"/>
       <c r="D119" s="70"/>
-      <c r="E119" s="149" t="s">
+      <c r="E119" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="F119" s="149"/>
-      <c r="G119" s="149"/>
-      <c r="H119" s="103">
+      <c r="F119" s="105"/>
+      <c r="G119" s="105"/>
+      <c r="H119" s="111">
         <v>45629</v>
       </c>
-      <c r="I119" s="105">
+      <c r="I119" s="126">
         <v>100</v>
       </c>
       <c r="J119" s="19"/>
@@ -17453,11 +17459,11 @@
       <c r="B120" s="36"/>
       <c r="C120" s="60"/>
       <c r="D120" s="70"/>
-      <c r="E120" s="102"/>
-      <c r="F120" s="102"/>
-      <c r="G120" s="102"/>
-      <c r="H120" s="104"/>
-      <c r="I120" s="106"/>
+      <c r="E120" s="103"/>
+      <c r="F120" s="103"/>
+      <c r="G120" s="103"/>
+      <c r="H120" s="107"/>
+      <c r="I120" s="109"/>
       <c r="J120" s="19"/>
       <c r="K120" s="20"/>
       <c r="L120" s="20"/>
@@ -17575,15 +17581,17 @@
       <c r="B121" s="36"/>
       <c r="C121" s="60"/>
       <c r="D121" s="70"/>
-      <c r="E121" s="102" t="s">
+      <c r="E121" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="F121" s="102"/>
-      <c r="G121" s="102"/>
-      <c r="H121" s="103">
+      <c r="F121" s="103"/>
+      <c r="G121" s="103"/>
+      <c r="H121" s="111">
         <v>45630</v>
       </c>
-      <c r="I121" s="105"/>
+      <c r="I121" s="126">
+        <v>100</v>
+      </c>
       <c r="J121" s="19"/>
       <c r="K121" s="20"/>
       <c r="L121" s="20"/>
@@ -17701,11 +17709,11 @@
       <c r="B122" s="36"/>
       <c r="C122" s="60"/>
       <c r="D122" s="70"/>
-      <c r="E122" s="102"/>
-      <c r="F122" s="102"/>
-      <c r="G122" s="102"/>
-      <c r="H122" s="104"/>
-      <c r="I122" s="106"/>
+      <c r="E122" s="103"/>
+      <c r="F122" s="103"/>
+      <c r="G122" s="103"/>
+      <c r="H122" s="107"/>
+      <c r="I122" s="109"/>
       <c r="J122" s="19"/>
       <c r="K122" s="20"/>
       <c r="L122" s="20"/>
@@ -17823,15 +17831,17 @@
       <c r="B123" s="36"/>
       <c r="C123" s="60"/>
       <c r="D123" s="70"/>
-      <c r="E123" s="102" t="s">
+      <c r="E123" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="F123" s="102"/>
-      <c r="G123" s="102"/>
-      <c r="H123" s="197">
+      <c r="F123" s="103"/>
+      <c r="G123" s="103"/>
+      <c r="H123" s="120">
         <v>45631</v>
       </c>
-      <c r="I123" s="112"/>
+      <c r="I123" s="112">
+        <v>100</v>
+      </c>
       <c r="J123" s="62"/>
       <c r="K123" s="20"/>
       <c r="L123" s="20"/>
@@ -17949,10 +17959,10 @@
       <c r="B124" s="36"/>
       <c r="C124" s="60"/>
       <c r="D124" s="70"/>
-      <c r="E124" s="102"/>
-      <c r="F124" s="102"/>
-      <c r="G124" s="102"/>
-      <c r="H124" s="197"/>
+      <c r="E124" s="103"/>
+      <c r="F124" s="103"/>
+      <c r="G124" s="103"/>
+      <c r="H124" s="120"/>
       <c r="I124" s="112"/>
       <c r="J124" s="62"/>
       <c r="K124" s="20"/>
@@ -18071,15 +18081,17 @@
       <c r="B125" s="36"/>
       <c r="C125" s="60"/>
       <c r="D125" s="70"/>
-      <c r="E125" s="102" t="s">
+      <c r="E125" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="F125" s="102"/>
-      <c r="G125" s="102"/>
-      <c r="H125" s="111">
+      <c r="F125" s="103"/>
+      <c r="G125" s="103"/>
+      <c r="H125" s="110">
         <v>45632</v>
       </c>
-      <c r="I125" s="112"/>
+      <c r="I125" s="112">
+        <v>100</v>
+      </c>
       <c r="J125" s="62"/>
       <c r="K125" s="20"/>
       <c r="L125" s="20"/>
@@ -18197,10 +18209,10 @@
       <c r="B126" s="36"/>
       <c r="C126" s="60"/>
       <c r="D126" s="70"/>
-      <c r="E126" s="102"/>
-      <c r="F126" s="102"/>
-      <c r="G126" s="102"/>
-      <c r="H126" s="111"/>
+      <c r="E126" s="103"/>
+      <c r="F126" s="103"/>
+      <c r="G126" s="103"/>
+      <c r="H126" s="110"/>
       <c r="I126" s="112"/>
       <c r="J126" s="62"/>
       <c r="K126" s="20"/>
@@ -18253,12 +18265,12 @@
       <c r="BF126" s="21"/>
       <c r="BG126" s="20"/>
       <c r="BH126" s="20"/>
-      <c r="BI126" s="20"/>
+      <c r="BI126" s="75"/>
       <c r="BJ126" s="64"/>
       <c r="BK126" s="64"/>
       <c r="BL126" s="21"/>
       <c r="BM126" s="21"/>
-      <c r="BN126" s="69"/>
+      <c r="BN126" s="75"/>
       <c r="BO126" s="69"/>
       <c r="BP126" s="69"/>
       <c r="BQ126" s="69"/>
@@ -18319,15 +18331,17 @@
       <c r="B127" s="36"/>
       <c r="C127" s="60"/>
       <c r="D127" s="70"/>
-      <c r="E127" s="102" t="s">
+      <c r="E127" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="F127" s="102"/>
-      <c r="G127" s="102"/>
-      <c r="H127" s="103">
+      <c r="F127" s="103"/>
+      <c r="G127" s="103"/>
+      <c r="H127" s="111">
         <v>45635</v>
       </c>
-      <c r="I127" s="105"/>
+      <c r="I127" s="126">
+        <v>100</v>
+      </c>
       <c r="J127" s="19"/>
       <c r="K127" s="20"/>
       <c r="L127" s="20"/>
@@ -18445,11 +18459,11 @@
       <c r="B128" s="36"/>
       <c r="C128" s="60"/>
       <c r="D128" s="70"/>
-      <c r="E128" s="198"/>
-      <c r="F128" s="198"/>
-      <c r="G128" s="198"/>
-      <c r="H128" s="104"/>
-      <c r="I128" s="106"/>
+      <c r="E128" s="125"/>
+      <c r="F128" s="125"/>
+      <c r="G128" s="125"/>
+      <c r="H128" s="107"/>
+      <c r="I128" s="109"/>
       <c r="J128" s="19"/>
       <c r="K128" s="20"/>
       <c r="L128" s="20"/>
@@ -18506,7 +18520,7 @@
       <c r="BK128" s="64"/>
       <c r="BL128" s="21"/>
       <c r="BM128" s="21"/>
-      <c r="BN128" s="69"/>
+      <c r="BN128" s="75"/>
       <c r="BO128" s="69"/>
       <c r="BP128" s="69"/>
       <c r="BQ128" s="69"/>
@@ -18567,12 +18581,12 @@
       <c r="B129" s="71"/>
       <c r="C129" s="91"/>
       <c r="D129" s="70"/>
-      <c r="E129" s="189" t="s">
+      <c r="E129" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="F129" s="121"/>
-      <c r="G129" s="122"/>
-      <c r="H129" s="111">
+      <c r="F129" s="115"/>
+      <c r="G129" s="116"/>
+      <c r="H129" s="110">
         <v>45638</v>
       </c>
       <c r="I129" s="112"/>
@@ -18693,10 +18707,10 @@
       <c r="B130" s="71"/>
       <c r="C130" s="91"/>
       <c r="D130" s="70"/>
-      <c r="E130" s="150"/>
-      <c r="F130" s="125"/>
-      <c r="G130" s="126"/>
-      <c r="H130" s="111"/>
+      <c r="E130" s="117"/>
+      <c r="F130" s="118"/>
+      <c r="G130" s="119"/>
+      <c r="H130" s="110"/>
       <c r="I130" s="112"/>
       <c r="J130" s="62"/>
       <c r="K130" s="20"/>
@@ -18814,16 +18828,16 @@
       <c r="A131" s="16"/>
       <c r="B131" s="71"/>
       <c r="C131" s="91"/>
-      <c r="D131" s="102" t="s">
+      <c r="D131" s="103" t="s">
         <v>79</v>
       </c>
-      <c r="E131" s="102"/>
-      <c r="F131" s="102"/>
-      <c r="G131" s="102"/>
-      <c r="H131" s="103">
+      <c r="E131" s="103"/>
+      <c r="F131" s="103"/>
+      <c r="G131" s="103"/>
+      <c r="H131" s="111">
         <v>45635</v>
       </c>
-      <c r="I131" s="109"/>
+      <c r="I131" s="113"/>
       <c r="J131" s="62"/>
       <c r="K131" s="20"/>
       <c r="L131" s="20"/>
@@ -18940,12 +18954,12 @@
       <c r="A132" s="16"/>
       <c r="B132" s="71"/>
       <c r="C132" s="90"/>
-      <c r="D132" s="102"/>
-      <c r="E132" s="102"/>
-      <c r="F132" s="102"/>
-      <c r="G132" s="102"/>
-      <c r="H132" s="104"/>
-      <c r="I132" s="110"/>
+      <c r="D132" s="103"/>
+      <c r="E132" s="103"/>
+      <c r="F132" s="103"/>
+      <c r="G132" s="103"/>
+      <c r="H132" s="107"/>
+      <c r="I132" s="143"/>
       <c r="J132" s="62"/>
       <c r="K132" s="20"/>
       <c r="L132" s="20"/>
@@ -19061,15 +19075,15 @@
     <row r="133" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A133" s="16"/>
       <c r="B133" s="36"/>
-      <c r="C133" s="115" t="s">
+      <c r="C133" s="132" t="s">
         <v>67</v>
       </c>
-      <c r="D133" s="116"/>
-      <c r="E133" s="116"/>
-      <c r="F133" s="116"/>
-      <c r="G133" s="117"/>
-      <c r="H133" s="191"/>
-      <c r="I133" s="107"/>
+      <c r="D133" s="133"/>
+      <c r="E133" s="133"/>
+      <c r="F133" s="133"/>
+      <c r="G133" s="134"/>
+      <c r="H133" s="121"/>
+      <c r="I133" s="123"/>
       <c r="J133" s="66"/>
       <c r="K133" s="64"/>
       <c r="L133" s="64"/>
@@ -19185,13 +19199,13 @@
     <row r="134" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A134" s="16"/>
       <c r="B134" s="36"/>
-      <c r="C134" s="118"/>
-      <c r="D134" s="119"/>
-      <c r="E134" s="119"/>
-      <c r="F134" s="119"/>
-      <c r="G134" s="120"/>
-      <c r="H134" s="192"/>
-      <c r="I134" s="108"/>
+      <c r="C134" s="135"/>
+      <c r="D134" s="136"/>
+      <c r="E134" s="136"/>
+      <c r="F134" s="136"/>
+      <c r="G134" s="137"/>
+      <c r="H134" s="122"/>
+      <c r="I134" s="124"/>
       <c r="J134" s="66"/>
       <c r="K134" s="64"/>
       <c r="L134" s="64"/>
@@ -19308,14 +19322,14 @@
       <c r="A135" s="16"/>
       <c r="B135" s="36"/>
       <c r="C135" s="60"/>
-      <c r="D135" s="115" t="s">
+      <c r="D135" s="132" t="s">
         <v>65</v>
       </c>
-      <c r="E135" s="116"/>
-      <c r="F135" s="116"/>
-      <c r="G135" s="117"/>
-      <c r="H135" s="113"/>
-      <c r="I135" s="181"/>
+      <c r="E135" s="133"/>
+      <c r="F135" s="133"/>
+      <c r="G135" s="134"/>
+      <c r="H135" s="193"/>
+      <c r="I135" s="129"/>
       <c r="J135" s="63"/>
       <c r="K135" s="64"/>
       <c r="L135" s="64"/>
@@ -19432,12 +19446,12 @@
       <c r="A136" s="16"/>
       <c r="B136" s="36"/>
       <c r="C136" s="60"/>
-      <c r="D136" s="118"/>
-      <c r="E136" s="119"/>
-      <c r="F136" s="119"/>
-      <c r="G136" s="120"/>
-      <c r="H136" s="130"/>
-      <c r="I136" s="183"/>
+      <c r="D136" s="135"/>
+      <c r="E136" s="136"/>
+      <c r="F136" s="136"/>
+      <c r="G136" s="137"/>
+      <c r="H136" s="198"/>
+      <c r="I136" s="144"/>
       <c r="J136" s="63"/>
       <c r="K136" s="64"/>
       <c r="L136" s="64"/>
@@ -19555,15 +19569,15 @@
       <c r="B137" s="36"/>
       <c r="C137" s="72"/>
       <c r="D137" s="74"/>
-      <c r="E137" s="121" t="s">
+      <c r="E137" s="115" t="s">
         <v>73</v>
       </c>
-      <c r="F137" s="121"/>
-      <c r="G137" s="122"/>
-      <c r="H137" s="103">
+      <c r="F137" s="115"/>
+      <c r="G137" s="116"/>
+      <c r="H137" s="111">
         <v>45636</v>
       </c>
-      <c r="I137" s="109"/>
+      <c r="I137" s="113"/>
       <c r="J137" s="62"/>
       <c r="K137" s="20"/>
       <c r="L137" s="20"/>
@@ -19681,11 +19695,11 @@
       <c r="B138" s="36"/>
       <c r="C138" s="72"/>
       <c r="D138" s="70"/>
-      <c r="E138" s="123"/>
-      <c r="F138" s="123"/>
-      <c r="G138" s="124"/>
-      <c r="H138" s="104"/>
-      <c r="I138" s="110"/>
+      <c r="E138" s="185"/>
+      <c r="F138" s="185"/>
+      <c r="G138" s="186"/>
+      <c r="H138" s="107"/>
+      <c r="I138" s="143"/>
       <c r="J138" s="62"/>
       <c r="K138" s="20"/>
       <c r="L138" s="20"/>
@@ -19803,15 +19817,15 @@
       <c r="B139" s="36"/>
       <c r="C139" s="72"/>
       <c r="D139" s="70"/>
-      <c r="E139" s="121" t="s">
+      <c r="E139" s="115" t="s">
         <v>74</v>
       </c>
-      <c r="F139" s="121"/>
-      <c r="G139" s="122"/>
-      <c r="H139" s="103">
+      <c r="F139" s="115"/>
+      <c r="G139" s="116"/>
+      <c r="H139" s="111">
         <v>45637</v>
       </c>
-      <c r="I139" s="109"/>
+      <c r="I139" s="113"/>
       <c r="J139" s="62"/>
       <c r="K139" s="20"/>
       <c r="L139" s="20"/>
@@ -19929,11 +19943,11 @@
       <c r="B140" s="36"/>
       <c r="C140" s="72"/>
       <c r="D140" s="70"/>
-      <c r="E140" s="125"/>
-      <c r="F140" s="125"/>
-      <c r="G140" s="126"/>
-      <c r="H140" s="104"/>
-      <c r="I140" s="110"/>
+      <c r="E140" s="118"/>
+      <c r="F140" s="118"/>
+      <c r="G140" s="119"/>
+      <c r="H140" s="107"/>
+      <c r="I140" s="143"/>
       <c r="J140" s="62"/>
       <c r="K140" s="20"/>
       <c r="L140" s="20"/>
@@ -20050,13 +20064,13 @@
       <c r="A141" s="16"/>
       <c r="B141" s="36"/>
       <c r="C141" s="82"/>
-      <c r="D141" s="102" t="s">
+      <c r="D141" s="103" t="s">
         <v>80</v>
       </c>
-      <c r="E141" s="102"/>
-      <c r="F141" s="102"/>
-      <c r="G141" s="102"/>
-      <c r="H141" s="103">
+      <c r="E141" s="103"/>
+      <c r="F141" s="103"/>
+      <c r="G141" s="103"/>
+      <c r="H141" s="111">
         <v>45637</v>
       </c>
       <c r="I141" s="92"/>
@@ -20176,11 +20190,11 @@
       <c r="A142" s="16"/>
       <c r="B142" s="36"/>
       <c r="C142" s="82"/>
-      <c r="D142" s="102"/>
-      <c r="E142" s="102"/>
-      <c r="F142" s="102"/>
-      <c r="G142" s="102"/>
-      <c r="H142" s="104"/>
+      <c r="D142" s="103"/>
+      <c r="E142" s="103"/>
+      <c r="F142" s="103"/>
+      <c r="G142" s="103"/>
+      <c r="H142" s="107"/>
       <c r="I142" s="92"/>
       <c r="J142" s="62"/>
       <c r="K142" s="20"/>
@@ -20298,14 +20312,14 @@
       <c r="A143" s="16"/>
       <c r="B143" s="36"/>
       <c r="C143" s="72"/>
-      <c r="D143" s="127" t="s">
+      <c r="D143" s="195" t="s">
         <v>66</v>
       </c>
-      <c r="E143" s="128"/>
-      <c r="F143" s="128"/>
-      <c r="G143" s="129"/>
-      <c r="H143" s="113"/>
-      <c r="I143" s="107"/>
+      <c r="E143" s="196"/>
+      <c r="F143" s="196"/>
+      <c r="G143" s="197"/>
+      <c r="H143" s="193"/>
+      <c r="I143" s="123"/>
       <c r="J143" s="66"/>
       <c r="K143" s="64"/>
       <c r="L143" s="64"/>
@@ -20422,12 +20436,12 @@
       <c r="A144" s="16"/>
       <c r="B144" s="36"/>
       <c r="C144" s="72"/>
-      <c r="D144" s="118"/>
-      <c r="E144" s="119"/>
-      <c r="F144" s="119"/>
-      <c r="G144" s="120"/>
-      <c r="H144" s="114"/>
-      <c r="I144" s="108"/>
+      <c r="D144" s="135"/>
+      <c r="E144" s="136"/>
+      <c r="F144" s="136"/>
+      <c r="G144" s="137"/>
+      <c r="H144" s="194"/>
+      <c r="I144" s="124"/>
       <c r="J144" s="66"/>
       <c r="K144" s="64"/>
       <c r="L144" s="64"/>
@@ -20545,15 +20559,15 @@
       <c r="B145" s="36"/>
       <c r="C145" s="72"/>
       <c r="D145" s="74"/>
-      <c r="E145" s="121" t="s">
+      <c r="E145" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="F145" s="121"/>
-      <c r="G145" s="122"/>
-      <c r="H145" s="103">
+      <c r="F145" s="115"/>
+      <c r="G145" s="116"/>
+      <c r="H145" s="111">
         <v>45639</v>
       </c>
-      <c r="I145" s="109"/>
+      <c r="I145" s="113"/>
       <c r="J145" s="62"/>
       <c r="K145" s="20"/>
       <c r="L145" s="20"/>
@@ -20671,11 +20685,11 @@
       <c r="B146" s="36"/>
       <c r="C146" s="72"/>
       <c r="D146" s="70"/>
-      <c r="E146" s="123"/>
-      <c r="F146" s="123"/>
-      <c r="G146" s="124"/>
-      <c r="H146" s="104"/>
-      <c r="I146" s="110"/>
+      <c r="E146" s="185"/>
+      <c r="F146" s="185"/>
+      <c r="G146" s="186"/>
+      <c r="H146" s="107"/>
+      <c r="I146" s="143"/>
       <c r="J146" s="62"/>
       <c r="K146" s="20"/>
       <c r="L146" s="20"/>
@@ -20793,15 +20807,15 @@
       <c r="B147" s="36"/>
       <c r="C147" s="72"/>
       <c r="D147" s="70"/>
-      <c r="E147" s="121" t="s">
+      <c r="E147" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="F147" s="121"/>
-      <c r="G147" s="122"/>
-      <c r="H147" s="103">
+      <c r="F147" s="115"/>
+      <c r="G147" s="116"/>
+      <c r="H147" s="111">
         <v>45642</v>
       </c>
-      <c r="I147" s="109"/>
+      <c r="I147" s="113"/>
       <c r="J147" s="62"/>
       <c r="K147" s="20"/>
       <c r="L147" s="20"/>
@@ -20919,11 +20933,11 @@
       <c r="B148" s="36"/>
       <c r="C148" s="72"/>
       <c r="D148" s="70"/>
-      <c r="E148" s="123"/>
-      <c r="F148" s="123"/>
-      <c r="G148" s="124"/>
-      <c r="H148" s="104"/>
-      <c r="I148" s="110"/>
+      <c r="E148" s="185"/>
+      <c r="F148" s="185"/>
+      <c r="G148" s="186"/>
+      <c r="H148" s="107"/>
+      <c r="I148" s="143"/>
       <c r="J148" s="62"/>
       <c r="K148" s="20"/>
       <c r="L148" s="20"/>
@@ -21041,15 +21055,15 @@
       <c r="B149" s="36"/>
       <c r="C149" s="72"/>
       <c r="D149" s="70"/>
-      <c r="E149" s="121" t="s">
+      <c r="E149" s="115" t="s">
         <v>70</v>
       </c>
-      <c r="F149" s="121"/>
-      <c r="G149" s="122"/>
-      <c r="H149" s="103">
+      <c r="F149" s="115"/>
+      <c r="G149" s="116"/>
+      <c r="H149" s="111">
         <v>45643</v>
       </c>
-      <c r="I149" s="109"/>
+      <c r="I149" s="113"/>
       <c r="J149" s="62"/>
       <c r="K149" s="20"/>
       <c r="L149" s="20"/>
@@ -21167,11 +21181,11 @@
       <c r="B150" s="36"/>
       <c r="C150" s="72"/>
       <c r="D150" s="70"/>
-      <c r="E150" s="123"/>
-      <c r="F150" s="123"/>
-      <c r="G150" s="124"/>
-      <c r="H150" s="104"/>
-      <c r="I150" s="110"/>
+      <c r="E150" s="185"/>
+      <c r="F150" s="185"/>
+      <c r="G150" s="186"/>
+      <c r="H150" s="107"/>
+      <c r="I150" s="143"/>
       <c r="J150" s="62"/>
       <c r="K150" s="20"/>
       <c r="L150" s="20"/>
@@ -21289,15 +21303,15 @@
       <c r="B151" s="36"/>
       <c r="C151" s="72"/>
       <c r="D151" s="70"/>
-      <c r="E151" s="102" t="s">
+      <c r="E151" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="F151" s="102"/>
-      <c r="G151" s="102"/>
-      <c r="H151" s="103">
+      <c r="F151" s="103"/>
+      <c r="G151" s="103"/>
+      <c r="H151" s="111">
         <v>45644</v>
       </c>
-      <c r="I151" s="109"/>
+      <c r="I151" s="113"/>
       <c r="J151" s="62"/>
       <c r="K151" s="20"/>
       <c r="L151" s="20"/>
@@ -21415,11 +21429,11 @@
       <c r="B152" s="36"/>
       <c r="C152" s="72"/>
       <c r="D152" s="70"/>
-      <c r="E152" s="102"/>
-      <c r="F152" s="102"/>
-      <c r="G152" s="102"/>
-      <c r="H152" s="104"/>
-      <c r="I152" s="110"/>
+      <c r="E152" s="103"/>
+      <c r="F152" s="103"/>
+      <c r="G152" s="103"/>
+      <c r="H152" s="107"/>
+      <c r="I152" s="143"/>
       <c r="J152" s="62"/>
       <c r="K152" s="20"/>
       <c r="L152" s="20"/>
@@ -21537,15 +21551,15 @@
       <c r="B153" s="36"/>
       <c r="C153" s="72"/>
       <c r="D153" s="70"/>
-      <c r="E153" s="102" t="s">
+      <c r="E153" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="F153" s="102"/>
-      <c r="G153" s="102"/>
-      <c r="H153" s="103">
+      <c r="F153" s="103"/>
+      <c r="G153" s="103"/>
+      <c r="H153" s="111">
         <v>45644</v>
       </c>
-      <c r="I153" s="109"/>
+      <c r="I153" s="113"/>
       <c r="J153" s="62"/>
       <c r="K153" s="20"/>
       <c r="L153" s="20"/>
@@ -21663,11 +21677,11 @@
       <c r="B154" s="36"/>
       <c r="C154" s="72"/>
       <c r="D154" s="70"/>
-      <c r="E154" s="102"/>
-      <c r="F154" s="102"/>
-      <c r="G154" s="102"/>
-      <c r="H154" s="104"/>
-      <c r="I154" s="110"/>
+      <c r="E154" s="103"/>
+      <c r="F154" s="103"/>
+      <c r="G154" s="103"/>
+      <c r="H154" s="107"/>
+      <c r="I154" s="143"/>
       <c r="J154" s="62"/>
       <c r="K154" s="20"/>
       <c r="L154" s="20"/>
@@ -21784,16 +21798,16 @@
       <c r="A155" s="1"/>
       <c r="B155" s="18"/>
       <c r="C155" s="60"/>
-      <c r="D155" s="194"/>
-      <c r="E155" s="193" t="s">
+      <c r="D155" s="104"/>
+      <c r="E155" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="F155" s="102"/>
-      <c r="G155" s="102"/>
-      <c r="H155" s="195">
+      <c r="F155" s="103"/>
+      <c r="G155" s="103"/>
+      <c r="H155" s="106">
         <v>45645</v>
       </c>
-      <c r="I155" s="196"/>
+      <c r="I155" s="108"/>
       <c r="J155" s="19"/>
       <c r="K155" s="20"/>
       <c r="L155" s="20"/>
@@ -21910,12 +21924,12 @@
       <c r="A156" s="1"/>
       <c r="B156" s="18"/>
       <c r="C156" s="60"/>
-      <c r="D156" s="149"/>
-      <c r="E156" s="193"/>
-      <c r="F156" s="102"/>
-      <c r="G156" s="102"/>
-      <c r="H156" s="104"/>
-      <c r="I156" s="106"/>
+      <c r="D156" s="105"/>
+      <c r="E156" s="102"/>
+      <c r="F156" s="103"/>
+      <c r="G156" s="103"/>
+      <c r="H156" s="107"/>
+      <c r="I156" s="109"/>
       <c r="J156" s="19"/>
       <c r="K156" s="20"/>
       <c r="L156" s="20"/>
@@ -22032,16 +22046,16 @@
       <c r="A157" s="1"/>
       <c r="B157" s="93"/>
       <c r="C157" s="90"/>
-      <c r="D157" s="102" t="s">
+      <c r="D157" s="103" t="s">
         <v>81</v>
       </c>
-      <c r="E157" s="102"/>
-      <c r="F157" s="102"/>
-      <c r="G157" s="102"/>
-      <c r="H157" s="103">
+      <c r="E157" s="103"/>
+      <c r="F157" s="103"/>
+      <c r="G157" s="103"/>
+      <c r="H157" s="111">
         <v>45644</v>
       </c>
-      <c r="I157" s="105"/>
+      <c r="I157" s="126"/>
       <c r="J157" s="19"/>
       <c r="K157" s="20"/>
       <c r="L157" s="20"/>
@@ -22158,12 +22172,12 @@
       <c r="A158" s="1"/>
       <c r="B158" s="93"/>
       <c r="C158" s="90"/>
-      <c r="D158" s="102"/>
-      <c r="E158" s="102"/>
-      <c r="F158" s="102"/>
-      <c r="G158" s="102"/>
-      <c r="H158" s="104"/>
-      <c r="I158" s="106"/>
+      <c r="D158" s="103"/>
+      <c r="E158" s="103"/>
+      <c r="F158" s="103"/>
+      <c r="G158" s="103"/>
+      <c r="H158" s="107"/>
+      <c r="I158" s="109"/>
       <c r="J158" s="19"/>
       <c r="K158" s="20"/>
       <c r="L158" s="20"/>
@@ -22281,14 +22295,14 @@
       <c r="B159" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="C159" s="173" t="s">
+      <c r="C159" s="151" t="s">
         <v>31</v>
       </c>
-      <c r="D159" s="174"/>
-      <c r="E159" s="174"/>
-      <c r="F159" s="174"/>
-      <c r="G159" s="175"/>
-      <c r="H159" s="184" t="s">
+      <c r="D159" s="152"/>
+      <c r="E159" s="152"/>
+      <c r="F159" s="152"/>
+      <c r="G159" s="153"/>
+      <c r="H159" s="138" t="s">
         <v>57</v>
       </c>
       <c r="I159" s="112"/>
@@ -22407,11 +22421,11 @@
     <row r="160" spans="1:120" ht="9.75" customHeight="1">
       <c r="A160" s="1"/>
       <c r="B160" s="87"/>
-      <c r="C160" s="176"/>
-      <c r="D160" s="177"/>
-      <c r="E160" s="177"/>
-      <c r="F160" s="177"/>
-      <c r="G160" s="178"/>
+      <c r="C160" s="154"/>
+      <c r="D160" s="155"/>
+      <c r="E160" s="155"/>
+      <c r="F160" s="155"/>
+      <c r="G160" s="156"/>
       <c r="H160" s="112"/>
       <c r="I160" s="112"/>
       <c r="J160" s="14"/>
@@ -22773,14 +22787,14 @@
     <row r="163" spans="1:120" ht="9.75" customHeight="1">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
-      <c r="C163" s="168" t="s">
+      <c r="C163" s="145" t="s">
         <v>33</v>
       </c>
-      <c r="D163" s="140"/>
-      <c r="E163" s="140"/>
-      <c r="F163" s="140"/>
-      <c r="G163" s="169"/>
-      <c r="H163" s="184" t="s">
+      <c r="D163" s="146"/>
+      <c r="E163" s="146"/>
+      <c r="F163" s="146"/>
+      <c r="G163" s="147"/>
+      <c r="H163" s="138" t="s">
         <v>56</v>
       </c>
       <c r="I163" s="112"/>
@@ -22899,11 +22913,11 @@
     <row r="164" spans="1:120" ht="9.75" customHeight="1">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
-      <c r="C164" s="170"/>
-      <c r="D164" s="171"/>
-      <c r="E164" s="171"/>
-      <c r="F164" s="171"/>
-      <c r="G164" s="172"/>
+      <c r="C164" s="148"/>
+      <c r="D164" s="149"/>
+      <c r="E164" s="149"/>
+      <c r="F164" s="149"/>
+      <c r="G164" s="150"/>
       <c r="H164" s="112"/>
       <c r="I164" s="112"/>
       <c r="J164" s="19"/>
@@ -36444,6 +36458,222 @@
     </row>
   </sheetData>
   <mergeCells count="240">
+    <mergeCell ref="D157:G158"/>
+    <mergeCell ref="H157:H158"/>
+    <mergeCell ref="I157:I158"/>
+    <mergeCell ref="H141:H142"/>
+    <mergeCell ref="I143:I144"/>
+    <mergeCell ref="I139:I140"/>
+    <mergeCell ref="H87:H88"/>
+    <mergeCell ref="I87:I88"/>
+    <mergeCell ref="H103:H104"/>
+    <mergeCell ref="I103:I104"/>
+    <mergeCell ref="H115:H116"/>
+    <mergeCell ref="I115:I116"/>
+    <mergeCell ref="D103:G104"/>
+    <mergeCell ref="D115:G116"/>
+    <mergeCell ref="D131:G132"/>
+    <mergeCell ref="H131:H132"/>
+    <mergeCell ref="I131:I132"/>
+    <mergeCell ref="D87:G88"/>
+    <mergeCell ref="D141:G142"/>
+    <mergeCell ref="E153:G154"/>
+    <mergeCell ref="H153:H154"/>
+    <mergeCell ref="H151:H152"/>
+    <mergeCell ref="H149:H150"/>
+    <mergeCell ref="H147:H148"/>
+    <mergeCell ref="H145:H146"/>
+    <mergeCell ref="H143:H144"/>
+    <mergeCell ref="H137:H138"/>
+    <mergeCell ref="H139:H140"/>
+    <mergeCell ref="C133:G134"/>
+    <mergeCell ref="D135:G136"/>
+    <mergeCell ref="E137:G138"/>
+    <mergeCell ref="E139:G140"/>
+    <mergeCell ref="D143:G144"/>
+    <mergeCell ref="E145:G146"/>
+    <mergeCell ref="H135:H136"/>
+    <mergeCell ref="E147:G148"/>
+    <mergeCell ref="E149:G150"/>
+    <mergeCell ref="E151:G152"/>
+    <mergeCell ref="E59:G60"/>
+    <mergeCell ref="E61:G62"/>
+    <mergeCell ref="D63:G64"/>
+    <mergeCell ref="E67:G68"/>
+    <mergeCell ref="E65:G66"/>
+    <mergeCell ref="E69:G70"/>
+    <mergeCell ref="E71:G72"/>
+    <mergeCell ref="C73:G74"/>
+    <mergeCell ref="C75:G76"/>
+    <mergeCell ref="C77:G78"/>
+    <mergeCell ref="D79:G80"/>
+    <mergeCell ref="E109:G110"/>
+    <mergeCell ref="E111:G112"/>
+    <mergeCell ref="E101:G102"/>
+    <mergeCell ref="C105:G106"/>
+    <mergeCell ref="D107:G108"/>
+    <mergeCell ref="D117:G118"/>
+    <mergeCell ref="D13:G14"/>
+    <mergeCell ref="D15:G16"/>
+    <mergeCell ref="D17:G18"/>
+    <mergeCell ref="D19:G20"/>
+    <mergeCell ref="C21:G22"/>
+    <mergeCell ref="D23:G24"/>
+    <mergeCell ref="C25:G26"/>
+    <mergeCell ref="D27:G28"/>
+    <mergeCell ref="D29:G30"/>
+    <mergeCell ref="J3:CJ3"/>
+    <mergeCell ref="CK3:DO3"/>
+    <mergeCell ref="J4:AA4"/>
+    <mergeCell ref="AB4:BE4"/>
+    <mergeCell ref="BF4:CJ4"/>
+    <mergeCell ref="CK4:DO4"/>
+    <mergeCell ref="B7:G8"/>
+    <mergeCell ref="C9:G10"/>
+    <mergeCell ref="C11:G12"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="C163:G164"/>
+    <mergeCell ref="C159:G160"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="C31:G32"/>
+    <mergeCell ref="D33:G34"/>
+    <mergeCell ref="E35:G36"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="E43:G44"/>
+    <mergeCell ref="E45:G46"/>
+    <mergeCell ref="E47:G48"/>
+    <mergeCell ref="E49:G50"/>
+    <mergeCell ref="E51:G52"/>
+    <mergeCell ref="D53:G54"/>
+    <mergeCell ref="E55:G56"/>
+    <mergeCell ref="E57:G58"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="I55:I56"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I65:I66"/>
+    <mergeCell ref="I67:I68"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="I71:I72"/>
+    <mergeCell ref="I73:I74"/>
+    <mergeCell ref="I57:I58"/>
+    <mergeCell ref="I59:I60"/>
+    <mergeCell ref="I61:I62"/>
+    <mergeCell ref="I63:I64"/>
+    <mergeCell ref="I75:I76"/>
+    <mergeCell ref="I159:I160"/>
+    <mergeCell ref="I161:I162"/>
+    <mergeCell ref="I77:I78"/>
+    <mergeCell ref="I81:I82"/>
+    <mergeCell ref="I83:I84"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="I93:I94"/>
+    <mergeCell ref="I95:I96"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="I99:I100"/>
+    <mergeCell ref="I109:I110"/>
+    <mergeCell ref="I137:I138"/>
+    <mergeCell ref="I153:I154"/>
+    <mergeCell ref="I151:I152"/>
+    <mergeCell ref="I149:I150"/>
+    <mergeCell ref="I147:I148"/>
+    <mergeCell ref="I145:I146"/>
+    <mergeCell ref="I111:I112"/>
+    <mergeCell ref="I135:I136"/>
+    <mergeCell ref="I121:I122"/>
+    <mergeCell ref="I163:I164"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="H75:H76"/>
+    <mergeCell ref="H159:H160"/>
+    <mergeCell ref="H163:H164"/>
+    <mergeCell ref="H161:H162"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="H67:H68"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="H71:H72"/>
+    <mergeCell ref="H73:H74"/>
+    <mergeCell ref="H57:H58"/>
+    <mergeCell ref="H59:H60"/>
+    <mergeCell ref="H61:H62"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="H77:H78"/>
+    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="H83:H84"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="H93:H94"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="H111:H112"/>
+    <mergeCell ref="H101:H102"/>
+    <mergeCell ref="I101:I102"/>
+    <mergeCell ref="H85:H86"/>
+    <mergeCell ref="I85:I86"/>
+    <mergeCell ref="H89:H90"/>
+    <mergeCell ref="I89:I90"/>
+    <mergeCell ref="E81:G82"/>
+    <mergeCell ref="E83:G84"/>
+    <mergeCell ref="E91:G92"/>
+    <mergeCell ref="E93:G94"/>
+    <mergeCell ref="E95:G96"/>
+    <mergeCell ref="E97:G98"/>
+    <mergeCell ref="E99:G100"/>
+    <mergeCell ref="E85:G86"/>
+    <mergeCell ref="D89:G90"/>
+    <mergeCell ref="H105:H106"/>
+    <mergeCell ref="I105:I106"/>
+    <mergeCell ref="H107:H108"/>
+    <mergeCell ref="I107:I108"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="H117:H118"/>
+    <mergeCell ref="I117:I118"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="I119:I120"/>
     <mergeCell ref="E155:G156"/>
     <mergeCell ref="D155:D156"/>
     <mergeCell ref="H155:H156"/>
@@ -36468,222 +36698,6 @@
     <mergeCell ref="H127:H128"/>
     <mergeCell ref="I127:I128"/>
     <mergeCell ref="H121:H122"/>
-    <mergeCell ref="H105:H106"/>
-    <mergeCell ref="I105:I106"/>
-    <mergeCell ref="H107:H108"/>
-    <mergeCell ref="I107:I108"/>
-    <mergeCell ref="H109:H110"/>
-    <mergeCell ref="H117:H118"/>
-    <mergeCell ref="I117:I118"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="I119:I120"/>
-    <mergeCell ref="H101:H102"/>
-    <mergeCell ref="I101:I102"/>
-    <mergeCell ref="H85:H86"/>
-    <mergeCell ref="I85:I86"/>
-    <mergeCell ref="H89:H90"/>
-    <mergeCell ref="I89:I90"/>
-    <mergeCell ref="E81:G82"/>
-    <mergeCell ref="E83:G84"/>
-    <mergeCell ref="E91:G92"/>
-    <mergeCell ref="E93:G94"/>
-    <mergeCell ref="E95:G96"/>
-    <mergeCell ref="E97:G98"/>
-    <mergeCell ref="E99:G100"/>
-    <mergeCell ref="E85:G86"/>
-    <mergeCell ref="D89:G90"/>
-    <mergeCell ref="H75:H76"/>
-    <mergeCell ref="H159:H160"/>
-    <mergeCell ref="H163:H164"/>
-    <mergeCell ref="H161:H162"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="H67:H68"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="H71:H72"/>
-    <mergeCell ref="H73:H74"/>
-    <mergeCell ref="H57:H58"/>
-    <mergeCell ref="H59:H60"/>
-    <mergeCell ref="H61:H62"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="H77:H78"/>
-    <mergeCell ref="H81:H82"/>
-    <mergeCell ref="H83:H84"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="H93:H94"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="H111:H112"/>
-    <mergeCell ref="I163:I164"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="H55:H56"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="I75:I76"/>
-    <mergeCell ref="I159:I160"/>
-    <mergeCell ref="I161:I162"/>
-    <mergeCell ref="I77:I78"/>
-    <mergeCell ref="I81:I82"/>
-    <mergeCell ref="I83:I84"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="I93:I94"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="I99:I100"/>
-    <mergeCell ref="I109:I110"/>
-    <mergeCell ref="I137:I138"/>
-    <mergeCell ref="I153:I154"/>
-    <mergeCell ref="I151:I152"/>
-    <mergeCell ref="I149:I150"/>
-    <mergeCell ref="I147:I148"/>
-    <mergeCell ref="I145:I146"/>
-    <mergeCell ref="I111:I112"/>
-    <mergeCell ref="I135:I136"/>
-    <mergeCell ref="I121:I122"/>
-    <mergeCell ref="I65:I66"/>
-    <mergeCell ref="I67:I68"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="I71:I72"/>
-    <mergeCell ref="I73:I74"/>
-    <mergeCell ref="I57:I58"/>
-    <mergeCell ref="I59:I60"/>
-    <mergeCell ref="I61:I62"/>
-    <mergeCell ref="I63:I64"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="C163:G164"/>
-    <mergeCell ref="C159:G160"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="C31:G32"/>
-    <mergeCell ref="D33:G34"/>
-    <mergeCell ref="E35:G36"/>
-    <mergeCell ref="E37:G38"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="E41:G42"/>
-    <mergeCell ref="E43:G44"/>
-    <mergeCell ref="E45:G46"/>
-    <mergeCell ref="E47:G48"/>
-    <mergeCell ref="E49:G50"/>
-    <mergeCell ref="E51:G52"/>
-    <mergeCell ref="D53:G54"/>
-    <mergeCell ref="E55:G56"/>
-    <mergeCell ref="E57:G58"/>
-    <mergeCell ref="I53:I54"/>
-    <mergeCell ref="I55:I56"/>
-    <mergeCell ref="J3:CJ3"/>
-    <mergeCell ref="CK3:DO3"/>
-    <mergeCell ref="J4:AA4"/>
-    <mergeCell ref="AB4:BE4"/>
-    <mergeCell ref="BF4:CJ4"/>
-    <mergeCell ref="CK4:DO4"/>
-    <mergeCell ref="B7:G8"/>
-    <mergeCell ref="C9:G10"/>
-    <mergeCell ref="C11:G12"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="D13:G14"/>
-    <mergeCell ref="D15:G16"/>
-    <mergeCell ref="D17:G18"/>
-    <mergeCell ref="D19:G20"/>
-    <mergeCell ref="C21:G22"/>
-    <mergeCell ref="D23:G24"/>
-    <mergeCell ref="C25:G26"/>
-    <mergeCell ref="D27:G28"/>
-    <mergeCell ref="D29:G30"/>
-    <mergeCell ref="E147:G148"/>
-    <mergeCell ref="E149:G150"/>
-    <mergeCell ref="E151:G152"/>
-    <mergeCell ref="E59:G60"/>
-    <mergeCell ref="E61:G62"/>
-    <mergeCell ref="D63:G64"/>
-    <mergeCell ref="E67:G68"/>
-    <mergeCell ref="E65:G66"/>
-    <mergeCell ref="E69:G70"/>
-    <mergeCell ref="E71:G72"/>
-    <mergeCell ref="C73:G74"/>
-    <mergeCell ref="C75:G76"/>
-    <mergeCell ref="C77:G78"/>
-    <mergeCell ref="D79:G80"/>
-    <mergeCell ref="E109:G110"/>
-    <mergeCell ref="E111:G112"/>
-    <mergeCell ref="E101:G102"/>
-    <mergeCell ref="C105:G106"/>
-    <mergeCell ref="D107:G108"/>
-    <mergeCell ref="D117:G118"/>
-    <mergeCell ref="H145:H146"/>
-    <mergeCell ref="H143:H144"/>
-    <mergeCell ref="H137:H138"/>
-    <mergeCell ref="H139:H140"/>
-    <mergeCell ref="C133:G134"/>
-    <mergeCell ref="D135:G136"/>
-    <mergeCell ref="E137:G138"/>
-    <mergeCell ref="E139:G140"/>
-    <mergeCell ref="D143:G144"/>
-    <mergeCell ref="E145:G146"/>
-    <mergeCell ref="H135:H136"/>
-    <mergeCell ref="D157:G158"/>
-    <mergeCell ref="H157:H158"/>
-    <mergeCell ref="I157:I158"/>
-    <mergeCell ref="H141:H142"/>
-    <mergeCell ref="I143:I144"/>
-    <mergeCell ref="I139:I140"/>
-    <mergeCell ref="H87:H88"/>
-    <mergeCell ref="I87:I88"/>
-    <mergeCell ref="H103:H104"/>
-    <mergeCell ref="I103:I104"/>
-    <mergeCell ref="H115:H116"/>
-    <mergeCell ref="I115:I116"/>
-    <mergeCell ref="D103:G104"/>
-    <mergeCell ref="D115:G116"/>
-    <mergeCell ref="D131:G132"/>
-    <mergeCell ref="H131:H132"/>
-    <mergeCell ref="I131:I132"/>
-    <mergeCell ref="D87:G88"/>
-    <mergeCell ref="D141:G142"/>
-    <mergeCell ref="E153:G154"/>
-    <mergeCell ref="H153:H154"/>
-    <mergeCell ref="H151:H152"/>
-    <mergeCell ref="H149:H150"/>
-    <mergeCell ref="H147:H148"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
   <conditionalFormatting sqref="J7">

--- a/docs/【DIGITAL OJT】WBS.xlsx
+++ b/docs/【DIGITAL OJT】WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIGITALOJT\digital-ojt-development-cause-DroneInventorySystem\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147DC62C-0102-4339-A4CB-6BDC1E85F929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6F0488-9D47-42C4-80AE-F3F69207F530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1328,7 +1328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="199">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1477,9 +1477,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1489,67 +1486,19 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="11" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1558,25 +1507,22 @@
     <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1597,29 +1543,110 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1645,92 +1672,62 @@
     <xf numFmtId="0" fontId="13" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="56" fontId="11" fillId="0" borderId="37" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="15" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="15" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2093,7 +2090,7 @@
     <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="61" width="3.42578125" customWidth="1"/>
-    <col min="62" max="63" width="3.42578125" style="100" customWidth="1"/>
+    <col min="62" max="63" width="3.42578125" style="99" customWidth="1"/>
     <col min="64" max="119" width="3.42578125" customWidth="1"/>
     <col min="120" max="120" width="5" customWidth="1"/>
   </cols>
@@ -2158,8 +2155,8 @@
       <c r="BG1" s="2"/>
       <c r="BH1" s="2"/>
       <c r="BI1" s="2"/>
-      <c r="BJ1" s="101"/>
-      <c r="BK1" s="101"/>
+      <c r="BJ1" s="100"/>
+      <c r="BK1" s="100"/>
       <c r="BL1" s="2"/>
       <c r="BM1" s="2"/>
       <c r="BN1" s="2"/>
@@ -2280,8 +2277,8 @@
       <c r="BG2" s="2"/>
       <c r="BH2" s="2"/>
       <c r="BI2" s="2"/>
-      <c r="BJ2" s="101"/>
-      <c r="BK2" s="101"/>
+      <c r="BJ2" s="100"/>
+      <c r="BK2" s="100"/>
       <c r="BL2" s="2"/>
       <c r="BM2" s="2"/>
       <c r="BN2" s="2"/>
@@ -2350,120 +2347,120 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="J3" s="173">
+      <c r="J3" s="160">
         <v>2024</v>
       </c>
-      <c r="K3" s="174"/>
-      <c r="L3" s="174"/>
-      <c r="M3" s="174"/>
-      <c r="N3" s="174"/>
-      <c r="O3" s="174"/>
-      <c r="P3" s="174"/>
-      <c r="Q3" s="174"/>
-      <c r="R3" s="174"/>
-      <c r="S3" s="174"/>
-      <c r="T3" s="174"/>
-      <c r="U3" s="174"/>
-      <c r="V3" s="174"/>
-      <c r="W3" s="174"/>
-      <c r="X3" s="174"/>
-      <c r="Y3" s="174"/>
-      <c r="Z3" s="174"/>
-      <c r="AA3" s="174"/>
-      <c r="AB3" s="174"/>
-      <c r="AC3" s="174"/>
-      <c r="AD3" s="174"/>
-      <c r="AE3" s="174"/>
-      <c r="AF3" s="174"/>
-      <c r="AG3" s="174"/>
-      <c r="AH3" s="174"/>
-      <c r="AI3" s="174"/>
-      <c r="AJ3" s="174"/>
-      <c r="AK3" s="174"/>
-      <c r="AL3" s="174"/>
-      <c r="AM3" s="174"/>
-      <c r="AN3" s="174"/>
-      <c r="AO3" s="174"/>
-      <c r="AP3" s="174"/>
-      <c r="AQ3" s="174"/>
-      <c r="AR3" s="174"/>
-      <c r="AS3" s="174"/>
-      <c r="AT3" s="174"/>
-      <c r="AU3" s="174"/>
-      <c r="AV3" s="174"/>
-      <c r="AW3" s="174"/>
-      <c r="AX3" s="174"/>
-      <c r="AY3" s="174"/>
-      <c r="AZ3" s="174"/>
-      <c r="BA3" s="174"/>
-      <c r="BB3" s="174"/>
-      <c r="BC3" s="174"/>
-      <c r="BD3" s="174"/>
-      <c r="BE3" s="174"/>
-      <c r="BF3" s="174"/>
-      <c r="BG3" s="174"/>
-      <c r="BH3" s="174"/>
-      <c r="BI3" s="174"/>
-      <c r="BJ3" s="174"/>
-      <c r="BK3" s="174"/>
-      <c r="BL3" s="174"/>
-      <c r="BM3" s="174"/>
-      <c r="BN3" s="174"/>
-      <c r="BO3" s="174"/>
-      <c r="BP3" s="174"/>
-      <c r="BQ3" s="174"/>
-      <c r="BR3" s="174"/>
-      <c r="BS3" s="174"/>
-      <c r="BT3" s="174"/>
-      <c r="BU3" s="174"/>
-      <c r="BV3" s="174"/>
-      <c r="BW3" s="174"/>
-      <c r="BX3" s="174"/>
-      <c r="BY3" s="174"/>
-      <c r="BZ3" s="174"/>
-      <c r="CA3" s="174"/>
-      <c r="CB3" s="174"/>
-      <c r="CC3" s="174"/>
-      <c r="CD3" s="174"/>
-      <c r="CE3" s="174"/>
-      <c r="CF3" s="174"/>
-      <c r="CG3" s="174"/>
-      <c r="CH3" s="174"/>
-      <c r="CI3" s="174"/>
-      <c r="CJ3" s="175"/>
-      <c r="CK3" s="173">
+      <c r="K3" s="161"/>
+      <c r="L3" s="161"/>
+      <c r="M3" s="161"/>
+      <c r="N3" s="161"/>
+      <c r="O3" s="161"/>
+      <c r="P3" s="161"/>
+      <c r="Q3" s="161"/>
+      <c r="R3" s="161"/>
+      <c r="S3" s="161"/>
+      <c r="T3" s="161"/>
+      <c r="U3" s="161"/>
+      <c r="V3" s="161"/>
+      <c r="W3" s="161"/>
+      <c r="X3" s="161"/>
+      <c r="Y3" s="161"/>
+      <c r="Z3" s="161"/>
+      <c r="AA3" s="161"/>
+      <c r="AB3" s="161"/>
+      <c r="AC3" s="161"/>
+      <c r="AD3" s="161"/>
+      <c r="AE3" s="161"/>
+      <c r="AF3" s="161"/>
+      <c r="AG3" s="161"/>
+      <c r="AH3" s="161"/>
+      <c r="AI3" s="161"/>
+      <c r="AJ3" s="161"/>
+      <c r="AK3" s="161"/>
+      <c r="AL3" s="161"/>
+      <c r="AM3" s="161"/>
+      <c r="AN3" s="161"/>
+      <c r="AO3" s="161"/>
+      <c r="AP3" s="161"/>
+      <c r="AQ3" s="161"/>
+      <c r="AR3" s="161"/>
+      <c r="AS3" s="161"/>
+      <c r="AT3" s="161"/>
+      <c r="AU3" s="161"/>
+      <c r="AV3" s="161"/>
+      <c r="AW3" s="161"/>
+      <c r="AX3" s="161"/>
+      <c r="AY3" s="161"/>
+      <c r="AZ3" s="161"/>
+      <c r="BA3" s="161"/>
+      <c r="BB3" s="161"/>
+      <c r="BC3" s="161"/>
+      <c r="BD3" s="161"/>
+      <c r="BE3" s="161"/>
+      <c r="BF3" s="161"/>
+      <c r="BG3" s="161"/>
+      <c r="BH3" s="161"/>
+      <c r="BI3" s="161"/>
+      <c r="BJ3" s="161"/>
+      <c r="BK3" s="161"/>
+      <c r="BL3" s="161"/>
+      <c r="BM3" s="161"/>
+      <c r="BN3" s="161"/>
+      <c r="BO3" s="161"/>
+      <c r="BP3" s="161"/>
+      <c r="BQ3" s="161"/>
+      <c r="BR3" s="161"/>
+      <c r="BS3" s="161"/>
+      <c r="BT3" s="161"/>
+      <c r="BU3" s="161"/>
+      <c r="BV3" s="161"/>
+      <c r="BW3" s="161"/>
+      <c r="BX3" s="161"/>
+      <c r="BY3" s="161"/>
+      <c r="BZ3" s="161"/>
+      <c r="CA3" s="161"/>
+      <c r="CB3" s="161"/>
+      <c r="CC3" s="161"/>
+      <c r="CD3" s="161"/>
+      <c r="CE3" s="161"/>
+      <c r="CF3" s="161"/>
+      <c r="CG3" s="161"/>
+      <c r="CH3" s="161"/>
+      <c r="CI3" s="161"/>
+      <c r="CJ3" s="162"/>
+      <c r="CK3" s="160">
         <v>2025</v>
       </c>
-      <c r="CL3" s="174"/>
-      <c r="CM3" s="174"/>
-      <c r="CN3" s="174"/>
-      <c r="CO3" s="174"/>
-      <c r="CP3" s="174"/>
-      <c r="CQ3" s="174"/>
-      <c r="CR3" s="174"/>
-      <c r="CS3" s="174"/>
-      <c r="CT3" s="174"/>
-      <c r="CU3" s="174"/>
-      <c r="CV3" s="174"/>
-      <c r="CW3" s="174"/>
-      <c r="CX3" s="174"/>
-      <c r="CY3" s="174"/>
-      <c r="CZ3" s="174"/>
-      <c r="DA3" s="174"/>
-      <c r="DB3" s="174"/>
-      <c r="DC3" s="174"/>
-      <c r="DD3" s="174"/>
-      <c r="DE3" s="174"/>
-      <c r="DF3" s="174"/>
-      <c r="DG3" s="174"/>
-      <c r="DH3" s="174"/>
-      <c r="DI3" s="174"/>
-      <c r="DJ3" s="174"/>
-      <c r="DK3" s="174"/>
-      <c r="DL3" s="174"/>
-      <c r="DM3" s="174"/>
-      <c r="DN3" s="174"/>
-      <c r="DO3" s="175"/>
+      <c r="CL3" s="161"/>
+      <c r="CM3" s="161"/>
+      <c r="CN3" s="161"/>
+      <c r="CO3" s="161"/>
+      <c r="CP3" s="161"/>
+      <c r="CQ3" s="161"/>
+      <c r="CR3" s="161"/>
+      <c r="CS3" s="161"/>
+      <c r="CT3" s="161"/>
+      <c r="CU3" s="161"/>
+      <c r="CV3" s="161"/>
+      <c r="CW3" s="161"/>
+      <c r="CX3" s="161"/>
+      <c r="CY3" s="161"/>
+      <c r="CZ3" s="161"/>
+      <c r="DA3" s="161"/>
+      <c r="DB3" s="161"/>
+      <c r="DC3" s="161"/>
+      <c r="DD3" s="161"/>
+      <c r="DE3" s="161"/>
+      <c r="DF3" s="161"/>
+      <c r="DG3" s="161"/>
+      <c r="DH3" s="161"/>
+      <c r="DI3" s="161"/>
+      <c r="DJ3" s="161"/>
+      <c r="DK3" s="161"/>
+      <c r="DL3" s="161"/>
+      <c r="DM3" s="161"/>
+      <c r="DN3" s="161"/>
+      <c r="DO3" s="162"/>
       <c r="DP3" s="1"/>
     </row>
     <row r="4" spans="1:120" ht="18" customHeight="1">
@@ -2478,124 +2475,124 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="J4" s="173">
+      <c r="J4" s="160">
         <v>10</v>
       </c>
-      <c r="K4" s="174"/>
-      <c r="L4" s="174"/>
-      <c r="M4" s="174"/>
-      <c r="N4" s="174"/>
-      <c r="O4" s="174"/>
-      <c r="P4" s="174"/>
-      <c r="Q4" s="174"/>
-      <c r="R4" s="174"/>
-      <c r="S4" s="174"/>
-      <c r="T4" s="174"/>
-      <c r="U4" s="174"/>
-      <c r="V4" s="174"/>
-      <c r="W4" s="174"/>
-      <c r="X4" s="174"/>
-      <c r="Y4" s="174"/>
-      <c r="Z4" s="174"/>
-      <c r="AA4" s="175"/>
-      <c r="AB4" s="173">
+      <c r="K4" s="161"/>
+      <c r="L4" s="161"/>
+      <c r="M4" s="161"/>
+      <c r="N4" s="161"/>
+      <c r="O4" s="161"/>
+      <c r="P4" s="161"/>
+      <c r="Q4" s="161"/>
+      <c r="R4" s="161"/>
+      <c r="S4" s="161"/>
+      <c r="T4" s="161"/>
+      <c r="U4" s="161"/>
+      <c r="V4" s="161"/>
+      <c r="W4" s="161"/>
+      <c r="X4" s="161"/>
+      <c r="Y4" s="161"/>
+      <c r="Z4" s="161"/>
+      <c r="AA4" s="162"/>
+      <c r="AB4" s="160">
         <v>11</v>
       </c>
-      <c r="AC4" s="174"/>
-      <c r="AD4" s="174"/>
-      <c r="AE4" s="174"/>
-      <c r="AF4" s="174"/>
-      <c r="AG4" s="174"/>
-      <c r="AH4" s="174"/>
-      <c r="AI4" s="174"/>
-      <c r="AJ4" s="174"/>
-      <c r="AK4" s="174"/>
-      <c r="AL4" s="174"/>
-      <c r="AM4" s="174"/>
-      <c r="AN4" s="174"/>
-      <c r="AO4" s="174"/>
-      <c r="AP4" s="174"/>
-      <c r="AQ4" s="174"/>
-      <c r="AR4" s="174"/>
-      <c r="AS4" s="174"/>
-      <c r="AT4" s="174"/>
-      <c r="AU4" s="174"/>
-      <c r="AV4" s="174"/>
-      <c r="AW4" s="174"/>
-      <c r="AX4" s="174"/>
-      <c r="AY4" s="174"/>
-      <c r="AZ4" s="174"/>
-      <c r="BA4" s="174"/>
-      <c r="BB4" s="174"/>
-      <c r="BC4" s="174"/>
-      <c r="BD4" s="174"/>
-      <c r="BE4" s="175"/>
-      <c r="BF4" s="173">
+      <c r="AC4" s="161"/>
+      <c r="AD4" s="161"/>
+      <c r="AE4" s="161"/>
+      <c r="AF4" s="161"/>
+      <c r="AG4" s="161"/>
+      <c r="AH4" s="161"/>
+      <c r="AI4" s="161"/>
+      <c r="AJ4" s="161"/>
+      <c r="AK4" s="161"/>
+      <c r="AL4" s="161"/>
+      <c r="AM4" s="161"/>
+      <c r="AN4" s="161"/>
+      <c r="AO4" s="161"/>
+      <c r="AP4" s="161"/>
+      <c r="AQ4" s="161"/>
+      <c r="AR4" s="161"/>
+      <c r="AS4" s="161"/>
+      <c r="AT4" s="161"/>
+      <c r="AU4" s="161"/>
+      <c r="AV4" s="161"/>
+      <c r="AW4" s="161"/>
+      <c r="AX4" s="161"/>
+      <c r="AY4" s="161"/>
+      <c r="AZ4" s="161"/>
+      <c r="BA4" s="161"/>
+      <c r="BB4" s="161"/>
+      <c r="BC4" s="161"/>
+      <c r="BD4" s="161"/>
+      <c r="BE4" s="162"/>
+      <c r="BF4" s="160">
         <v>12</v>
       </c>
-      <c r="BG4" s="174"/>
-      <c r="BH4" s="174"/>
-      <c r="BI4" s="174"/>
-      <c r="BJ4" s="174"/>
-      <c r="BK4" s="174"/>
-      <c r="BL4" s="174"/>
-      <c r="BM4" s="174"/>
-      <c r="BN4" s="174"/>
-      <c r="BO4" s="174"/>
-      <c r="BP4" s="174"/>
-      <c r="BQ4" s="174"/>
-      <c r="BR4" s="174"/>
-      <c r="BS4" s="174"/>
-      <c r="BT4" s="174"/>
-      <c r="BU4" s="174"/>
-      <c r="BV4" s="174"/>
-      <c r="BW4" s="174"/>
-      <c r="BX4" s="174"/>
-      <c r="BY4" s="174"/>
-      <c r="BZ4" s="174"/>
-      <c r="CA4" s="174"/>
-      <c r="CB4" s="174"/>
-      <c r="CC4" s="174"/>
-      <c r="CD4" s="174"/>
-      <c r="CE4" s="174"/>
-      <c r="CF4" s="174"/>
-      <c r="CG4" s="174"/>
-      <c r="CH4" s="174"/>
-      <c r="CI4" s="174"/>
-      <c r="CJ4" s="175"/>
-      <c r="CK4" s="173">
+      <c r="BG4" s="161"/>
+      <c r="BH4" s="161"/>
+      <c r="BI4" s="161"/>
+      <c r="BJ4" s="161"/>
+      <c r="BK4" s="161"/>
+      <c r="BL4" s="161"/>
+      <c r="BM4" s="161"/>
+      <c r="BN4" s="161"/>
+      <c r="BO4" s="161"/>
+      <c r="BP4" s="161"/>
+      <c r="BQ4" s="161"/>
+      <c r="BR4" s="161"/>
+      <c r="BS4" s="161"/>
+      <c r="BT4" s="161"/>
+      <c r="BU4" s="161"/>
+      <c r="BV4" s="161"/>
+      <c r="BW4" s="161"/>
+      <c r="BX4" s="161"/>
+      <c r="BY4" s="161"/>
+      <c r="BZ4" s="161"/>
+      <c r="CA4" s="161"/>
+      <c r="CB4" s="161"/>
+      <c r="CC4" s="161"/>
+      <c r="CD4" s="161"/>
+      <c r="CE4" s="161"/>
+      <c r="CF4" s="161"/>
+      <c r="CG4" s="161"/>
+      <c r="CH4" s="161"/>
+      <c r="CI4" s="161"/>
+      <c r="CJ4" s="162"/>
+      <c r="CK4" s="160">
         <v>1</v>
       </c>
-      <c r="CL4" s="174"/>
-      <c r="CM4" s="174"/>
-      <c r="CN4" s="174"/>
-      <c r="CO4" s="174"/>
-      <c r="CP4" s="174"/>
-      <c r="CQ4" s="174"/>
-      <c r="CR4" s="174"/>
-      <c r="CS4" s="174"/>
-      <c r="CT4" s="174"/>
-      <c r="CU4" s="174"/>
-      <c r="CV4" s="174"/>
-      <c r="CW4" s="174"/>
-      <c r="CX4" s="174"/>
-      <c r="CY4" s="174"/>
-      <c r="CZ4" s="174"/>
-      <c r="DA4" s="174"/>
-      <c r="DB4" s="174"/>
-      <c r="DC4" s="174"/>
-      <c r="DD4" s="174"/>
-      <c r="DE4" s="174"/>
-      <c r="DF4" s="174"/>
-      <c r="DG4" s="174"/>
-      <c r="DH4" s="174"/>
-      <c r="DI4" s="174"/>
-      <c r="DJ4" s="174"/>
-      <c r="DK4" s="174"/>
-      <c r="DL4" s="174"/>
-      <c r="DM4" s="174"/>
-      <c r="DN4" s="174"/>
-      <c r="DO4" s="175"/>
+      <c r="CL4" s="161"/>
+      <c r="CM4" s="161"/>
+      <c r="CN4" s="161"/>
+      <c r="CO4" s="161"/>
+      <c r="CP4" s="161"/>
+      <c r="CQ4" s="161"/>
+      <c r="CR4" s="161"/>
+      <c r="CS4" s="161"/>
+      <c r="CT4" s="161"/>
+      <c r="CU4" s="161"/>
+      <c r="CV4" s="161"/>
+      <c r="CW4" s="161"/>
+      <c r="CX4" s="161"/>
+      <c r="CY4" s="161"/>
+      <c r="CZ4" s="161"/>
+      <c r="DA4" s="161"/>
+      <c r="DB4" s="161"/>
+      <c r="DC4" s="161"/>
+      <c r="DD4" s="161"/>
+      <c r="DE4" s="161"/>
+      <c r="DF4" s="161"/>
+      <c r="DG4" s="161"/>
+      <c r="DH4" s="161"/>
+      <c r="DI4" s="161"/>
+      <c r="DJ4" s="161"/>
+      <c r="DK4" s="161"/>
+      <c r="DL4" s="161"/>
+      <c r="DM4" s="161"/>
+      <c r="DN4" s="161"/>
+      <c r="DO4" s="162"/>
       <c r="DP4" s="6"/>
     </row>
     <row r="5" spans="1:120" ht="18" customHeight="1">
@@ -3390,18 +3387,18 @@
     </row>
     <row r="7" spans="1:120" ht="9.75" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="176" t="s">
+      <c r="B7" s="163" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="164"/>
-      <c r="D7" s="164"/>
-      <c r="E7" s="164"/>
-      <c r="F7" s="164"/>
-      <c r="G7" s="177"/>
-      <c r="H7" s="142" t="s">
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="151"/>
+      <c r="H7" s="165" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="142" t="s">
+      <c r="I7" s="165" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="38"/>
@@ -3456,8 +3453,8 @@
       <c r="BG7" s="13"/>
       <c r="BH7" s="13"/>
       <c r="BI7" s="13"/>
-      <c r="BJ7" s="95"/>
-      <c r="BK7" s="95"/>
+      <c r="BJ7" s="94"/>
+      <c r="BK7" s="94"/>
       <c r="BL7" s="13"/>
       <c r="BM7" s="13"/>
       <c r="BN7" s="13"/>
@@ -3518,14 +3515,14 @@
     </row>
     <row r="8" spans="1:120" ht="9.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="166"/>
-      <c r="C8" s="167"/>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="168"/>
-      <c r="H8" s="142"/>
-      <c r="I8" s="142"/>
+      <c r="B8" s="133"/>
+      <c r="C8" s="134"/>
+      <c r="D8" s="134"/>
+      <c r="E8" s="134"/>
+      <c r="F8" s="134"/>
+      <c r="G8" s="138"/>
+      <c r="H8" s="165"/>
+      <c r="I8" s="165"/>
       <c r="J8" s="39"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
@@ -3578,8 +3575,8 @@
       <c r="BG8" s="15"/>
       <c r="BH8" s="15"/>
       <c r="BI8" s="15"/>
-      <c r="BJ8" s="96"/>
-      <c r="BK8" s="96"/>
+      <c r="BJ8" s="95"/>
+      <c r="BK8" s="95"/>
       <c r="BL8" s="15"/>
       <c r="BM8" s="15"/>
       <c r="BN8" s="15"/>
@@ -3641,15 +3638,15 @@
     <row r="9" spans="1:120" ht="9.75" customHeight="1">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
-      <c r="C9" s="178" t="s">
+      <c r="C9" s="164" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="158"/>
-      <c r="E9" s="158"/>
-      <c r="F9" s="158"/>
-      <c r="G9" s="162"/>
-      <c r="H9" s="139"/>
-      <c r="I9" s="139"/>
+      <c r="D9" s="153"/>
+      <c r="E9" s="153"/>
+      <c r="F9" s="153"/>
+      <c r="G9" s="141"/>
+      <c r="H9" s="166"/>
+      <c r="I9" s="166"/>
       <c r="J9" s="42"/>
       <c r="K9" s="42"/>
       <c r="L9" s="44"/>
@@ -3702,8 +3699,8 @@
       <c r="BG9" s="44"/>
       <c r="BH9" s="44"/>
       <c r="BI9" s="44"/>
-      <c r="BJ9" s="97"/>
-      <c r="BK9" s="97"/>
+      <c r="BJ9" s="96"/>
+      <c r="BK9" s="96"/>
       <c r="BL9" s="45"/>
       <c r="BM9" s="45"/>
       <c r="BN9" s="44"/>
@@ -3765,13 +3762,13 @@
     <row r="10" spans="1:120" ht="9.75" customHeight="1">
       <c r="A10" s="16"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="179"/>
-      <c r="D10" s="167"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="167"/>
-      <c r="G10" s="168"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="139"/>
+      <c r="C10" s="140"/>
+      <c r="D10" s="134"/>
+      <c r="E10" s="134"/>
+      <c r="F10" s="134"/>
+      <c r="G10" s="138"/>
+      <c r="H10" s="166"/>
+      <c r="I10" s="166"/>
       <c r="J10" s="46"/>
       <c r="K10" s="47"/>
       <c r="L10" s="47"/>
@@ -3887,15 +3884,15 @@
     <row r="11" spans="1:120" ht="9.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="180" t="s">
+      <c r="C11" s="152" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="158"/>
-      <c r="E11" s="158"/>
-      <c r="F11" s="158"/>
-      <c r="G11" s="162"/>
-      <c r="H11" s="139"/>
-      <c r="I11" s="139"/>
+      <c r="D11" s="153"/>
+      <c r="E11" s="153"/>
+      <c r="F11" s="153"/>
+      <c r="G11" s="141"/>
+      <c r="H11" s="166"/>
+      <c r="I11" s="166"/>
       <c r="J11" s="42"/>
       <c r="K11" s="42"/>
       <c r="L11" s="44"/>
@@ -3948,8 +3945,8 @@
       <c r="BG11" s="44"/>
       <c r="BH11" s="44"/>
       <c r="BI11" s="44"/>
-      <c r="BJ11" s="97"/>
-      <c r="BK11" s="97"/>
+      <c r="BJ11" s="96"/>
+      <c r="BK11" s="96"/>
       <c r="BL11" s="45"/>
       <c r="BM11" s="45"/>
       <c r="BN11" s="44"/>
@@ -4011,13 +4008,13 @@
     <row r="12" spans="1:120" ht="9.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="179"/>
-      <c r="D12" s="167"/>
-      <c r="E12" s="167"/>
-      <c r="F12" s="167"/>
-      <c r="G12" s="168"/>
-      <c r="H12" s="139"/>
-      <c r="I12" s="139"/>
+      <c r="C12" s="140"/>
+      <c r="D12" s="134"/>
+      <c r="E12" s="134"/>
+      <c r="F12" s="134"/>
+      <c r="G12" s="138"/>
+      <c r="H12" s="166"/>
+      <c r="I12" s="166"/>
       <c r="J12" s="46"/>
       <c r="K12" s="47"/>
       <c r="L12" s="47"/>
@@ -4134,16 +4131,16 @@
       <c r="A13" s="1"/>
       <c r="B13" s="18"/>
       <c r="C13" s="22"/>
-      <c r="D13" s="181" t="s">
+      <c r="D13" s="150" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="164"/>
-      <c r="F13" s="164"/>
-      <c r="G13" s="177"/>
-      <c r="H13" s="138" t="s">
+      <c r="E13" s="131"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="151"/>
+      <c r="H13" s="183" t="s">
         <v>40</v>
       </c>
-      <c r="I13" s="112">
+      <c r="I13" s="111">
         <v>100</v>
       </c>
       <c r="J13" s="39"/>
@@ -4198,8 +4195,8 @@
       <c r="BG13" s="15"/>
       <c r="BH13" s="15"/>
       <c r="BI13" s="15"/>
-      <c r="BJ13" s="96"/>
-      <c r="BK13" s="96"/>
+      <c r="BJ13" s="95"/>
+      <c r="BK13" s="95"/>
       <c r="BL13" s="15"/>
       <c r="BM13" s="15"/>
       <c r="BN13" s="15"/>
@@ -4262,12 +4259,12 @@
       <c r="A14" s="1"/>
       <c r="B14" s="18"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="166"/>
-      <c r="E14" s="167"/>
-      <c r="F14" s="167"/>
-      <c r="G14" s="168"/>
-      <c r="H14" s="112"/>
-      <c r="I14" s="112"/>
+      <c r="D14" s="133"/>
+      <c r="E14" s="134"/>
+      <c r="F14" s="134"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
       <c r="J14" s="39"/>
       <c r="K14" s="53"/>
       <c r="L14" s="15"/>
@@ -4320,8 +4317,8 @@
       <c r="BG14" s="15"/>
       <c r="BH14" s="15"/>
       <c r="BI14" s="15"/>
-      <c r="BJ14" s="96"/>
-      <c r="BK14" s="96"/>
+      <c r="BJ14" s="95"/>
+      <c r="BK14" s="95"/>
       <c r="BL14" s="15"/>
       <c r="BM14" s="15"/>
       <c r="BN14" s="15"/>
@@ -4384,16 +4381,16 @@
       <c r="A15" s="1"/>
       <c r="B15" s="18"/>
       <c r="C15" s="24"/>
-      <c r="D15" s="181" t="s">
+      <c r="D15" s="150" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="164"/>
-      <c r="F15" s="164"/>
-      <c r="G15" s="170"/>
-      <c r="H15" s="138" t="s">
+      <c r="E15" s="131"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="183" t="s">
         <v>40</v>
       </c>
-      <c r="I15" s="112">
+      <c r="I15" s="111">
         <v>100</v>
       </c>
       <c r="J15" s="14"/>
@@ -4448,8 +4445,8 @@
       <c r="BG15" s="15"/>
       <c r="BH15" s="15"/>
       <c r="BI15" s="15"/>
-      <c r="BJ15" s="96"/>
-      <c r="BK15" s="96"/>
+      <c r="BJ15" s="95"/>
+      <c r="BK15" s="95"/>
       <c r="BL15" s="15"/>
       <c r="BM15" s="15"/>
       <c r="BN15" s="15"/>
@@ -4512,12 +4509,12 @@
       <c r="A16" s="1"/>
       <c r="B16" s="18"/>
       <c r="C16" s="24"/>
-      <c r="D16" s="166"/>
-      <c r="E16" s="167"/>
-      <c r="F16" s="167"/>
-      <c r="G16" s="171"/>
-      <c r="H16" s="112"/>
-      <c r="I16" s="112"/>
+      <c r="D16" s="133"/>
+      <c r="E16" s="134"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
       <c r="J16" s="14"/>
       <c r="K16" s="53"/>
       <c r="L16" s="15"/>
@@ -4570,8 +4567,8 @@
       <c r="BG16" s="15"/>
       <c r="BH16" s="15"/>
       <c r="BI16" s="15"/>
-      <c r="BJ16" s="96"/>
-      <c r="BK16" s="96"/>
+      <c r="BJ16" s="95"/>
+      <c r="BK16" s="95"/>
       <c r="BL16" s="15"/>
       <c r="BM16" s="15"/>
       <c r="BN16" s="15"/>
@@ -4634,16 +4631,16 @@
       <c r="A17" s="1"/>
       <c r="B17" s="18"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="181" t="s">
+      <c r="D17" s="150" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="164"/>
-      <c r="F17" s="164"/>
-      <c r="G17" s="170"/>
-      <c r="H17" s="138" t="s">
+      <c r="E17" s="131"/>
+      <c r="F17" s="131"/>
+      <c r="G17" s="132"/>
+      <c r="H17" s="183" t="s">
         <v>40</v>
       </c>
-      <c r="I17" s="112">
+      <c r="I17" s="111">
         <v>100</v>
       </c>
       <c r="J17" s="14"/>
@@ -4698,8 +4695,8 @@
       <c r="BG17" s="15"/>
       <c r="BH17" s="15"/>
       <c r="BI17" s="15"/>
-      <c r="BJ17" s="96"/>
-      <c r="BK17" s="96"/>
+      <c r="BJ17" s="95"/>
+      <c r="BK17" s="95"/>
       <c r="BL17" s="15"/>
       <c r="BM17" s="15"/>
       <c r="BN17" s="15"/>
@@ -4762,12 +4759,12 @@
       <c r="A18" s="1"/>
       <c r="B18" s="18"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="166"/>
-      <c r="E18" s="167"/>
-      <c r="F18" s="167"/>
-      <c r="G18" s="171"/>
-      <c r="H18" s="112"/>
-      <c r="I18" s="112"/>
+      <c r="D18" s="133"/>
+      <c r="E18" s="134"/>
+      <c r="F18" s="134"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="111"/>
+      <c r="I18" s="111"/>
       <c r="J18" s="14"/>
       <c r="K18" s="53"/>
       <c r="L18" s="15"/>
@@ -4820,8 +4817,8 @@
       <c r="BG18" s="15"/>
       <c r="BH18" s="15"/>
       <c r="BI18" s="15"/>
-      <c r="BJ18" s="96"/>
-      <c r="BK18" s="96"/>
+      <c r="BJ18" s="95"/>
+      <c r="BK18" s="95"/>
       <c r="BL18" s="15"/>
       <c r="BM18" s="15"/>
       <c r="BN18" s="15"/>
@@ -4884,16 +4881,16 @@
       <c r="A19" s="1"/>
       <c r="B19" s="18"/>
       <c r="C19" s="24"/>
-      <c r="D19" s="181" t="s">
+      <c r="D19" s="150" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="164"/>
-      <c r="F19" s="164"/>
-      <c r="G19" s="170"/>
-      <c r="H19" s="138" t="s">
+      <c r="E19" s="131"/>
+      <c r="F19" s="131"/>
+      <c r="G19" s="132"/>
+      <c r="H19" s="183" t="s">
         <v>40</v>
       </c>
-      <c r="I19" s="112">
+      <c r="I19" s="111">
         <v>100</v>
       </c>
       <c r="J19" s="14"/>
@@ -4948,8 +4945,8 @@
       <c r="BG19" s="15"/>
       <c r="BH19" s="15"/>
       <c r="BI19" s="15"/>
-      <c r="BJ19" s="96"/>
-      <c r="BK19" s="96"/>
+      <c r="BJ19" s="95"/>
+      <c r="BK19" s="95"/>
       <c r="BL19" s="15"/>
       <c r="BM19" s="15"/>
       <c r="BN19" s="15"/>
@@ -5012,12 +5009,12 @@
       <c r="A20" s="1"/>
       <c r="B20" s="18"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="166"/>
-      <c r="E20" s="167"/>
-      <c r="F20" s="167"/>
-      <c r="G20" s="171"/>
-      <c r="H20" s="112"/>
-      <c r="I20" s="112"/>
+      <c r="D20" s="133"/>
+      <c r="E20" s="134"/>
+      <c r="F20" s="134"/>
+      <c r="G20" s="135"/>
+      <c r="H20" s="111"/>
+      <c r="I20" s="111"/>
       <c r="J20" s="26"/>
       <c r="K20" s="54"/>
       <c r="L20" s="27"/>
@@ -5070,8 +5067,8 @@
       <c r="BG20" s="27"/>
       <c r="BH20" s="27"/>
       <c r="BI20" s="27"/>
-      <c r="BJ20" s="98"/>
-      <c r="BK20" s="98"/>
+      <c r="BJ20" s="97"/>
+      <c r="BK20" s="97"/>
       <c r="BL20" s="27"/>
       <c r="BM20" s="27"/>
       <c r="BN20" s="27"/>
@@ -5133,15 +5130,15 @@
     <row r="21" spans="1:120" ht="9.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="18"/>
-      <c r="C21" s="180" t="s">
+      <c r="C21" s="152" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="158"/>
-      <c r="E21" s="158"/>
-      <c r="F21" s="158"/>
-      <c r="G21" s="159"/>
-      <c r="H21" s="139"/>
-      <c r="I21" s="139"/>
+      <c r="D21" s="153"/>
+      <c r="E21" s="153"/>
+      <c r="F21" s="153"/>
+      <c r="G21" s="154"/>
+      <c r="H21" s="166"/>
+      <c r="I21" s="166"/>
       <c r="J21" s="42"/>
       <c r="K21" s="43"/>
       <c r="L21" s="44"/>
@@ -5194,8 +5191,8 @@
       <c r="BG21" s="44"/>
       <c r="BH21" s="44"/>
       <c r="BI21" s="44"/>
-      <c r="BJ21" s="97"/>
-      <c r="BK21" s="97"/>
+      <c r="BJ21" s="96"/>
+      <c r="BK21" s="96"/>
       <c r="BL21" s="45"/>
       <c r="BM21" s="45"/>
       <c r="BN21" s="44"/>
@@ -5257,13 +5254,13 @@
     <row r="22" spans="1:120" ht="9.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="18"/>
-      <c r="C22" s="160"/>
-      <c r="D22" s="161"/>
-      <c r="E22" s="161"/>
-      <c r="F22" s="161"/>
-      <c r="G22" s="162"/>
-      <c r="H22" s="139"/>
-      <c r="I22" s="139"/>
+      <c r="C22" s="155"/>
+      <c r="D22" s="156"/>
+      <c r="E22" s="156"/>
+      <c r="F22" s="156"/>
+      <c r="G22" s="141"/>
+      <c r="H22" s="166"/>
+      <c r="I22" s="166"/>
       <c r="J22" s="46"/>
       <c r="K22" s="47"/>
       <c r="L22" s="47"/>
@@ -5380,16 +5377,16 @@
       <c r="A23" s="1"/>
       <c r="B23" s="28"/>
       <c r="C23" s="29"/>
-      <c r="D23" s="182" t="s">
+      <c r="D23" s="157" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="164"/>
-      <c r="F23" s="164"/>
-      <c r="G23" s="170"/>
-      <c r="H23" s="138" t="s">
+      <c r="E23" s="131"/>
+      <c r="F23" s="131"/>
+      <c r="G23" s="132"/>
+      <c r="H23" s="183" t="s">
         <v>46</v>
       </c>
-      <c r="I23" s="112">
+      <c r="I23" s="111">
         <v>100</v>
       </c>
       <c r="J23" s="14"/>
@@ -5444,8 +5441,8 @@
       <c r="BG23" s="15"/>
       <c r="BH23" s="15"/>
       <c r="BI23" s="15"/>
-      <c r="BJ23" s="96"/>
-      <c r="BK23" s="96"/>
+      <c r="BJ23" s="95"/>
+      <c r="BK23" s="95"/>
       <c r="BL23" s="15"/>
       <c r="BM23" s="15"/>
       <c r="BN23" s="15"/>
@@ -5508,12 +5505,12 @@
       <c r="A24" s="1"/>
       <c r="B24" s="18"/>
       <c r="C24" s="24"/>
-      <c r="D24" s="166"/>
-      <c r="E24" s="167"/>
-      <c r="F24" s="167"/>
-      <c r="G24" s="171"/>
-      <c r="H24" s="112"/>
-      <c r="I24" s="112"/>
+      <c r="D24" s="133"/>
+      <c r="E24" s="134"/>
+      <c r="F24" s="134"/>
+      <c r="G24" s="135"/>
+      <c r="H24" s="111"/>
+      <c r="I24" s="111"/>
       <c r="J24" s="14"/>
       <c r="K24" s="15"/>
       <c r="L24" s="53"/>
@@ -5566,8 +5563,8 @@
       <c r="BG24" s="15"/>
       <c r="BH24" s="15"/>
       <c r="BI24" s="15"/>
-      <c r="BJ24" s="96"/>
-      <c r="BK24" s="96"/>
+      <c r="BJ24" s="95"/>
+      <c r="BK24" s="95"/>
       <c r="BL24" s="15"/>
       <c r="BM24" s="15"/>
       <c r="BN24" s="15"/>
@@ -5629,15 +5626,15 @@
     <row r="25" spans="1:120" ht="9.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="18"/>
-      <c r="C25" s="180" t="s">
+      <c r="C25" s="152" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="158"/>
-      <c r="G25" s="159"/>
-      <c r="H25" s="139"/>
-      <c r="I25" s="139"/>
+      <c r="D25" s="153"/>
+      <c r="E25" s="153"/>
+      <c r="F25" s="153"/>
+      <c r="G25" s="154"/>
+      <c r="H25" s="166"/>
+      <c r="I25" s="166"/>
       <c r="J25" s="42"/>
       <c r="K25" s="42"/>
       <c r="L25" s="44"/>
@@ -5690,8 +5687,8 @@
       <c r="BG25" s="44"/>
       <c r="BH25" s="44"/>
       <c r="BI25" s="44"/>
-      <c r="BJ25" s="97"/>
-      <c r="BK25" s="97"/>
+      <c r="BJ25" s="96"/>
+      <c r="BK25" s="96"/>
       <c r="BL25" s="45"/>
       <c r="BM25" s="45"/>
       <c r="BN25" s="44"/>
@@ -5753,13 +5750,13 @@
     <row r="26" spans="1:120" ht="9.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="18"/>
-      <c r="C26" s="179"/>
-      <c r="D26" s="167"/>
-      <c r="E26" s="167"/>
-      <c r="F26" s="167"/>
-      <c r="G26" s="168"/>
-      <c r="H26" s="139"/>
-      <c r="I26" s="139"/>
+      <c r="C26" s="140"/>
+      <c r="D26" s="134"/>
+      <c r="E26" s="134"/>
+      <c r="F26" s="134"/>
+      <c r="G26" s="138"/>
+      <c r="H26" s="166"/>
+      <c r="I26" s="166"/>
       <c r="J26" s="46"/>
       <c r="K26" s="47"/>
       <c r="L26" s="47"/>
@@ -5876,16 +5873,16 @@
       <c r="A27" s="1"/>
       <c r="B27" s="28"/>
       <c r="C27" s="29"/>
-      <c r="D27" s="182" t="s">
+      <c r="D27" s="157" t="s">
         <v>18</v>
       </c>
-      <c r="E27" s="164"/>
-      <c r="F27" s="164"/>
-      <c r="G27" s="170"/>
-      <c r="H27" s="138" t="s">
+      <c r="E27" s="131"/>
+      <c r="F27" s="131"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="183" t="s">
         <v>44</v>
       </c>
-      <c r="I27" s="112">
+      <c r="I27" s="111">
         <v>100</v>
       </c>
       <c r="J27" s="14"/>
@@ -5940,8 +5937,8 @@
       <c r="BG27" s="15"/>
       <c r="BH27" s="15"/>
       <c r="BI27" s="15"/>
-      <c r="BJ27" s="96"/>
-      <c r="BK27" s="96"/>
+      <c r="BJ27" s="95"/>
+      <c r="BK27" s="95"/>
       <c r="BL27" s="15"/>
       <c r="BM27" s="15"/>
       <c r="BN27" s="15"/>
@@ -6004,12 +6001,12 @@
       <c r="A28" s="1"/>
       <c r="B28" s="28"/>
       <c r="C28" s="30"/>
-      <c r="D28" s="166"/>
-      <c r="E28" s="167"/>
-      <c r="F28" s="167"/>
-      <c r="G28" s="171"/>
-      <c r="H28" s="112"/>
-      <c r="I28" s="112"/>
+      <c r="D28" s="133"/>
+      <c r="E28" s="134"/>
+      <c r="F28" s="134"/>
+      <c r="G28" s="135"/>
+      <c r="H28" s="111"/>
+      <c r="I28" s="111"/>
       <c r="J28" s="14"/>
       <c r="K28" s="15"/>
       <c r="L28" s="15"/>
@@ -6062,8 +6059,8 @@
       <c r="BG28" s="15"/>
       <c r="BH28" s="15"/>
       <c r="BI28" s="15"/>
-      <c r="BJ28" s="96"/>
-      <c r="BK28" s="96"/>
+      <c r="BJ28" s="95"/>
+      <c r="BK28" s="95"/>
       <c r="BL28" s="15"/>
       <c r="BM28" s="15"/>
       <c r="BN28" s="15"/>
@@ -6126,16 +6123,16 @@
       <c r="A29" s="1"/>
       <c r="B29" s="28"/>
       <c r="C29" s="30"/>
-      <c r="D29" s="183" t="s">
+      <c r="D29" s="158" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="184"/>
-      <c r="F29" s="184"/>
-      <c r="G29" s="184"/>
-      <c r="H29" s="138" t="s">
+      <c r="E29" s="159"/>
+      <c r="F29" s="159"/>
+      <c r="G29" s="159"/>
+      <c r="H29" s="183" t="s">
         <v>44</v>
       </c>
-      <c r="I29" s="112">
+      <c r="I29" s="111">
         <v>100</v>
       </c>
       <c r="J29" s="14"/>
@@ -6190,8 +6187,8 @@
       <c r="BG29" s="15"/>
       <c r="BH29" s="15"/>
       <c r="BI29" s="15"/>
-      <c r="BJ29" s="96"/>
-      <c r="BK29" s="96"/>
+      <c r="BJ29" s="95"/>
+      <c r="BK29" s="95"/>
       <c r="BL29" s="15"/>
       <c r="BM29" s="15"/>
       <c r="BN29" s="15"/>
@@ -6254,12 +6251,12 @@
       <c r="A30" s="1"/>
       <c r="B30" s="28"/>
       <c r="C30" s="31"/>
-      <c r="D30" s="166"/>
-      <c r="E30" s="167"/>
-      <c r="F30" s="167"/>
-      <c r="G30" s="167"/>
-      <c r="H30" s="112"/>
-      <c r="I30" s="112"/>
+      <c r="D30" s="133"/>
+      <c r="E30" s="134"/>
+      <c r="F30" s="134"/>
+      <c r="G30" s="134"/>
+      <c r="H30" s="111"/>
+      <c r="I30" s="111"/>
       <c r="J30" s="26"/>
       <c r="K30" s="27"/>
       <c r="L30" s="27"/>
@@ -6312,8 +6309,8 @@
       <c r="BG30" s="27"/>
       <c r="BH30" s="27"/>
       <c r="BI30" s="27"/>
-      <c r="BJ30" s="98"/>
-      <c r="BK30" s="98"/>
+      <c r="BJ30" s="97"/>
+      <c r="BK30" s="97"/>
       <c r="BL30" s="27"/>
       <c r="BM30" s="27"/>
       <c r="BN30" s="27"/>
@@ -6375,15 +6372,15 @@
     <row r="31" spans="1:120" ht="9.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="18"/>
-      <c r="C31" s="157" t="s">
+      <c r="C31" s="178" t="s">
         <v>39</v>
       </c>
-      <c r="D31" s="158"/>
-      <c r="E31" s="158"/>
-      <c r="F31" s="158"/>
-      <c r="G31" s="159"/>
-      <c r="H31" s="139"/>
-      <c r="I31" s="139"/>
+      <c r="D31" s="153"/>
+      <c r="E31" s="153"/>
+      <c r="F31" s="153"/>
+      <c r="G31" s="154"/>
+      <c r="H31" s="166"/>
+      <c r="I31" s="166"/>
       <c r="J31" s="42"/>
       <c r="K31" s="43"/>
       <c r="L31" s="44"/>
@@ -6436,8 +6433,8 @@
       <c r="BG31" s="44"/>
       <c r="BH31" s="44"/>
       <c r="BI31" s="44"/>
-      <c r="BJ31" s="97"/>
-      <c r="BK31" s="97"/>
+      <c r="BJ31" s="96"/>
+      <c r="BK31" s="96"/>
       <c r="BL31" s="45"/>
       <c r="BM31" s="45"/>
       <c r="BN31" s="44"/>
@@ -6499,13 +6496,13 @@
     <row r="32" spans="1:120" ht="9.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="18"/>
-      <c r="C32" s="160"/>
-      <c r="D32" s="161"/>
-      <c r="E32" s="161"/>
-      <c r="F32" s="161"/>
-      <c r="G32" s="162"/>
-      <c r="H32" s="139"/>
-      <c r="I32" s="139"/>
+      <c r="C32" s="155"/>
+      <c r="D32" s="156"/>
+      <c r="E32" s="156"/>
+      <c r="F32" s="156"/>
+      <c r="G32" s="141"/>
+      <c r="H32" s="166"/>
+      <c r="I32" s="166"/>
       <c r="J32" s="46"/>
       <c r="K32" s="47"/>
       <c r="L32" s="47"/>
@@ -6622,14 +6619,14 @@
       <c r="A33" s="1"/>
       <c r="B33" s="18"/>
       <c r="C33" s="32"/>
-      <c r="D33" s="163" t="s">
+      <c r="D33" s="136" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="164"/>
-      <c r="F33" s="164"/>
-      <c r="G33" s="165"/>
-      <c r="H33" s="139"/>
-      <c r="I33" s="139"/>
+      <c r="E33" s="131"/>
+      <c r="F33" s="131"/>
+      <c r="G33" s="137"/>
+      <c r="H33" s="166"/>
+      <c r="I33" s="166"/>
       <c r="J33" s="50"/>
       <c r="K33" s="51"/>
       <c r="L33" s="51"/>
@@ -6682,8 +6679,8 @@
       <c r="BG33" s="51"/>
       <c r="BH33" s="51"/>
       <c r="BI33" s="51"/>
-      <c r="BJ33" s="99"/>
-      <c r="BK33" s="99"/>
+      <c r="BJ33" s="98"/>
+      <c r="BK33" s="98"/>
       <c r="BL33" s="51"/>
       <c r="BM33" s="51"/>
       <c r="BN33" s="51"/>
@@ -6746,12 +6743,12 @@
       <c r="A34" s="1"/>
       <c r="B34" s="18"/>
       <c r="C34" s="1"/>
-      <c r="D34" s="166"/>
-      <c r="E34" s="167"/>
-      <c r="F34" s="167"/>
-      <c r="G34" s="168"/>
-      <c r="H34" s="139"/>
-      <c r="I34" s="139"/>
+      <c r="D34" s="133"/>
+      <c r="E34" s="134"/>
+      <c r="F34" s="134"/>
+      <c r="G34" s="138"/>
+      <c r="H34" s="166"/>
+      <c r="I34" s="166"/>
       <c r="J34" s="52"/>
       <c r="K34" s="49"/>
       <c r="L34" s="49"/>
@@ -6804,8 +6801,8 @@
       <c r="BG34" s="49"/>
       <c r="BH34" s="49"/>
       <c r="BI34" s="49"/>
-      <c r="BJ34" s="96"/>
-      <c r="BK34" s="96"/>
+      <c r="BJ34" s="95"/>
+      <c r="BK34" s="95"/>
       <c r="BL34" s="49"/>
       <c r="BM34" s="49"/>
       <c r="BN34" s="49"/>
@@ -6869,15 +6866,15 @@
       <c r="B35" s="18"/>
       <c r="C35" s="1"/>
       <c r="D35" s="33"/>
-      <c r="E35" s="169" t="s">
+      <c r="E35" s="130" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="164"/>
-      <c r="G35" s="170"/>
-      <c r="H35" s="138" t="s">
+      <c r="F35" s="131"/>
+      <c r="G35" s="132"/>
+      <c r="H35" s="183" t="s">
         <v>45</v>
       </c>
-      <c r="I35" s="112">
+      <c r="I35" s="111">
         <v>100</v>
       </c>
       <c r="J35" s="14"/>
@@ -6932,8 +6929,8 @@
       <c r="BG35" s="15"/>
       <c r="BH35" s="15"/>
       <c r="BI35" s="15"/>
-      <c r="BJ35" s="96"/>
-      <c r="BK35" s="96"/>
+      <c r="BJ35" s="95"/>
+      <c r="BK35" s="95"/>
       <c r="BL35" s="15"/>
       <c r="BM35" s="15"/>
       <c r="BN35" s="15"/>
@@ -6997,11 +6994,11 @@
       <c r="B36" s="18"/>
       <c r="C36" s="1"/>
       <c r="D36" s="34"/>
-      <c r="E36" s="166"/>
-      <c r="F36" s="167"/>
-      <c r="G36" s="171"/>
-      <c r="H36" s="112"/>
-      <c r="I36" s="112"/>
+      <c r="E36" s="133"/>
+      <c r="F36" s="134"/>
+      <c r="G36" s="135"/>
+      <c r="H36" s="111"/>
+      <c r="I36" s="111"/>
       <c r="J36" s="14"/>
       <c r="K36" s="15"/>
       <c r="L36" s="15"/>
@@ -7054,8 +7051,8 @@
       <c r="BG36" s="15"/>
       <c r="BH36" s="15"/>
       <c r="BI36" s="15"/>
-      <c r="BJ36" s="96"/>
-      <c r="BK36" s="96"/>
+      <c r="BJ36" s="95"/>
+      <c r="BK36" s="95"/>
       <c r="BL36" s="15"/>
       <c r="BM36" s="15"/>
       <c r="BN36" s="15"/>
@@ -7119,15 +7116,15 @@
       <c r="B37" s="18"/>
       <c r="C37" s="1"/>
       <c r="D37" s="34"/>
-      <c r="E37" s="169" t="s">
+      <c r="E37" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="F37" s="164"/>
-      <c r="G37" s="170"/>
-      <c r="H37" s="138" t="s">
+      <c r="F37" s="131"/>
+      <c r="G37" s="132"/>
+      <c r="H37" s="183" t="s">
         <v>44</v>
       </c>
-      <c r="I37" s="112">
+      <c r="I37" s="111">
         <v>100</v>
       </c>
       <c r="J37" s="14"/>
@@ -7182,8 +7179,8 @@
       <c r="BG37" s="15"/>
       <c r="BH37" s="15"/>
       <c r="BI37" s="15"/>
-      <c r="BJ37" s="96"/>
-      <c r="BK37" s="96"/>
+      <c r="BJ37" s="95"/>
+      <c r="BK37" s="95"/>
       <c r="BL37" s="15"/>
       <c r="BM37" s="15"/>
       <c r="BN37" s="15"/>
@@ -7247,11 +7244,11 @@
       <c r="B38" s="18"/>
       <c r="C38" s="1"/>
       <c r="D38" s="35"/>
-      <c r="E38" s="166"/>
-      <c r="F38" s="167"/>
-      <c r="G38" s="171"/>
-      <c r="H38" s="112"/>
-      <c r="I38" s="112"/>
+      <c r="E38" s="133"/>
+      <c r="F38" s="134"/>
+      <c r="G38" s="135"/>
+      <c r="H38" s="111"/>
+      <c r="I38" s="111"/>
       <c r="J38" s="26"/>
       <c r="K38" s="27"/>
       <c r="L38" s="27"/>
@@ -7304,8 +7301,8 @@
       <c r="BG38" s="27"/>
       <c r="BH38" s="27"/>
       <c r="BI38" s="27"/>
-      <c r="BJ38" s="98"/>
-      <c r="BK38" s="98"/>
+      <c r="BJ38" s="97"/>
+      <c r="BK38" s="97"/>
       <c r="BL38" s="27"/>
       <c r="BM38" s="27"/>
       <c r="BN38" s="27"/>
@@ -7368,14 +7365,14 @@
       <c r="A39" s="1"/>
       <c r="B39" s="18"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="172" t="s">
+      <c r="D39" s="179" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="158"/>
-      <c r="F39" s="158"/>
-      <c r="G39" s="159"/>
-      <c r="H39" s="139"/>
-      <c r="I39" s="139"/>
+      <c r="E39" s="153"/>
+      <c r="F39" s="153"/>
+      <c r="G39" s="154"/>
+      <c r="H39" s="166"/>
+      <c r="I39" s="166"/>
       <c r="J39" s="50"/>
       <c r="K39" s="51"/>
       <c r="L39" s="51"/>
@@ -7428,8 +7425,8 @@
       <c r="BG39" s="51"/>
       <c r="BH39" s="51"/>
       <c r="BI39" s="51"/>
-      <c r="BJ39" s="99"/>
-      <c r="BK39" s="99"/>
+      <c r="BJ39" s="98"/>
+      <c r="BK39" s="98"/>
       <c r="BL39" s="51"/>
       <c r="BM39" s="51"/>
       <c r="BN39" s="51"/>
@@ -7492,12 +7489,12 @@
       <c r="A40" s="1"/>
       <c r="B40" s="18"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="166"/>
-      <c r="E40" s="167"/>
-      <c r="F40" s="167"/>
-      <c r="G40" s="168"/>
-      <c r="H40" s="139"/>
-      <c r="I40" s="139"/>
+      <c r="D40" s="133"/>
+      <c r="E40" s="134"/>
+      <c r="F40" s="134"/>
+      <c r="G40" s="138"/>
+      <c r="H40" s="166"/>
+      <c r="I40" s="166"/>
       <c r="J40" s="52"/>
       <c r="K40" s="49"/>
       <c r="L40" s="49"/>
@@ -7550,8 +7547,8 @@
       <c r="BG40" s="49"/>
       <c r="BH40" s="49"/>
       <c r="BI40" s="49"/>
-      <c r="BJ40" s="96"/>
-      <c r="BK40" s="96"/>
+      <c r="BJ40" s="95"/>
+      <c r="BK40" s="95"/>
       <c r="BL40" s="49"/>
       <c r="BM40" s="49"/>
       <c r="BN40" s="49"/>
@@ -7615,15 +7612,15 @@
       <c r="B41" s="18"/>
       <c r="C41" s="1"/>
       <c r="D41" s="33"/>
-      <c r="E41" s="169" t="s">
+      <c r="E41" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="164"/>
-      <c r="G41" s="170"/>
-      <c r="H41" s="138" t="s">
+      <c r="F41" s="131"/>
+      <c r="G41" s="132"/>
+      <c r="H41" s="183" t="s">
         <v>43</v>
       </c>
-      <c r="I41" s="112">
+      <c r="I41" s="111">
         <v>100</v>
       </c>
       <c r="J41" s="14"/>
@@ -7678,8 +7675,8 @@
       <c r="BG41" s="15"/>
       <c r="BH41" s="15"/>
       <c r="BI41" s="15"/>
-      <c r="BJ41" s="96"/>
-      <c r="BK41" s="96"/>
+      <c r="BJ41" s="95"/>
+      <c r="BK41" s="95"/>
       <c r="BL41" s="15"/>
       <c r="BM41" s="15"/>
       <c r="BN41" s="15"/>
@@ -7743,11 +7740,11 @@
       <c r="B42" s="18"/>
       <c r="C42" s="1"/>
       <c r="D42" s="34"/>
-      <c r="E42" s="166"/>
-      <c r="F42" s="167"/>
-      <c r="G42" s="171"/>
-      <c r="H42" s="112"/>
-      <c r="I42" s="112"/>
+      <c r="E42" s="133"/>
+      <c r="F42" s="134"/>
+      <c r="G42" s="135"/>
+      <c r="H42" s="111"/>
+      <c r="I42" s="111"/>
       <c r="J42" s="14"/>
       <c r="K42" s="15"/>
       <c r="L42" s="15"/>
@@ -7800,8 +7797,8 @@
       <c r="BG42" s="15"/>
       <c r="BH42" s="15"/>
       <c r="BI42" s="15"/>
-      <c r="BJ42" s="96"/>
-      <c r="BK42" s="96"/>
+      <c r="BJ42" s="95"/>
+      <c r="BK42" s="95"/>
       <c r="BL42" s="15"/>
       <c r="BM42" s="15"/>
       <c r="BN42" s="15"/>
@@ -7865,15 +7862,15 @@
       <c r="B43" s="18"/>
       <c r="C43" s="1"/>
       <c r="D43" s="34"/>
-      <c r="E43" s="169" t="s">
+      <c r="E43" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="164"/>
-      <c r="G43" s="170"/>
-      <c r="H43" s="138" t="s">
+      <c r="F43" s="131"/>
+      <c r="G43" s="132"/>
+      <c r="H43" s="183" t="s">
         <v>43</v>
       </c>
-      <c r="I43" s="112">
+      <c r="I43" s="111">
         <v>100</v>
       </c>
       <c r="J43" s="14"/>
@@ -7928,8 +7925,8 @@
       <c r="BG43" s="15"/>
       <c r="BH43" s="15"/>
       <c r="BI43" s="15"/>
-      <c r="BJ43" s="96"/>
-      <c r="BK43" s="96"/>
+      <c r="BJ43" s="95"/>
+      <c r="BK43" s="95"/>
       <c r="BL43" s="15"/>
       <c r="BM43" s="15"/>
       <c r="BN43" s="15"/>
@@ -7993,11 +7990,11 @@
       <c r="B44" s="18"/>
       <c r="C44" s="1"/>
       <c r="D44" s="34"/>
-      <c r="E44" s="166"/>
-      <c r="F44" s="167"/>
-      <c r="G44" s="171"/>
-      <c r="H44" s="112"/>
-      <c r="I44" s="112"/>
+      <c r="E44" s="133"/>
+      <c r="F44" s="134"/>
+      <c r="G44" s="135"/>
+      <c r="H44" s="111"/>
+      <c r="I44" s="111"/>
       <c r="J44" s="14"/>
       <c r="K44" s="15"/>
       <c r="L44" s="15"/>
@@ -8050,8 +8047,8 @@
       <c r="BG44" s="15"/>
       <c r="BH44" s="15"/>
       <c r="BI44" s="15"/>
-      <c r="BJ44" s="96"/>
-      <c r="BK44" s="96"/>
+      <c r="BJ44" s="95"/>
+      <c r="BK44" s="95"/>
       <c r="BL44" s="15"/>
       <c r="BM44" s="15"/>
       <c r="BN44" s="15"/>
@@ -8115,15 +8112,15 @@
       <c r="B45" s="18"/>
       <c r="C45" s="1"/>
       <c r="D45" s="34"/>
-      <c r="E45" s="169" t="s">
+      <c r="E45" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="F45" s="164"/>
-      <c r="G45" s="170"/>
-      <c r="H45" s="138" t="s">
+      <c r="F45" s="131"/>
+      <c r="G45" s="132"/>
+      <c r="H45" s="183" t="s">
         <v>42</v>
       </c>
-      <c r="I45" s="112">
+      <c r="I45" s="111">
         <v>100</v>
       </c>
       <c r="J45" s="14"/>
@@ -8178,8 +8175,8 @@
       <c r="BG45" s="15"/>
       <c r="BH45" s="15"/>
       <c r="BI45" s="15"/>
-      <c r="BJ45" s="96"/>
-      <c r="BK45" s="96"/>
+      <c r="BJ45" s="95"/>
+      <c r="BK45" s="95"/>
       <c r="BL45" s="15"/>
       <c r="BM45" s="15"/>
       <c r="BN45" s="15"/>
@@ -8243,11 +8240,11 @@
       <c r="B46" s="18"/>
       <c r="C46" s="1"/>
       <c r="D46" s="34"/>
-      <c r="E46" s="166"/>
-      <c r="F46" s="167"/>
-      <c r="G46" s="171"/>
-      <c r="H46" s="112"/>
-      <c r="I46" s="112"/>
+      <c r="E46" s="133"/>
+      <c r="F46" s="134"/>
+      <c r="G46" s="135"/>
+      <c r="H46" s="111"/>
+      <c r="I46" s="111"/>
       <c r="J46" s="14"/>
       <c r="K46" s="15"/>
       <c r="L46" s="15"/>
@@ -8300,8 +8297,8 @@
       <c r="BG46" s="15"/>
       <c r="BH46" s="15"/>
       <c r="BI46" s="15"/>
-      <c r="BJ46" s="96"/>
-      <c r="BK46" s="96"/>
+      <c r="BJ46" s="95"/>
+      <c r="BK46" s="95"/>
       <c r="BL46" s="15"/>
       <c r="BM46" s="15"/>
       <c r="BN46" s="15"/>
@@ -8365,15 +8362,15 @@
       <c r="B47" s="18"/>
       <c r="C47" s="1"/>
       <c r="D47" s="34"/>
-      <c r="E47" s="169" t="s">
+      <c r="E47" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="F47" s="164"/>
-      <c r="G47" s="170"/>
-      <c r="H47" s="138" t="s">
+      <c r="F47" s="131"/>
+      <c r="G47" s="132"/>
+      <c r="H47" s="183" t="s">
         <v>41</v>
       </c>
-      <c r="I47" s="112">
+      <c r="I47" s="111">
         <v>100</v>
       </c>
       <c r="J47" s="14"/>
@@ -8428,8 +8425,8 @@
       <c r="BG47" s="15"/>
       <c r="BH47" s="15"/>
       <c r="BI47" s="15"/>
-      <c r="BJ47" s="96"/>
-      <c r="BK47" s="96"/>
+      <c r="BJ47" s="95"/>
+      <c r="BK47" s="95"/>
       <c r="BL47" s="15"/>
       <c r="BM47" s="15"/>
       <c r="BN47" s="15"/>
@@ -8493,11 +8490,11 @@
       <c r="B48" s="18"/>
       <c r="C48" s="1"/>
       <c r="D48" s="34"/>
-      <c r="E48" s="166"/>
-      <c r="F48" s="167"/>
-      <c r="G48" s="171"/>
-      <c r="H48" s="112"/>
-      <c r="I48" s="112"/>
+      <c r="E48" s="133"/>
+      <c r="F48" s="134"/>
+      <c r="G48" s="135"/>
+      <c r="H48" s="111"/>
+      <c r="I48" s="111"/>
       <c r="J48" s="14"/>
       <c r="K48" s="15"/>
       <c r="L48" s="15"/>
@@ -8550,8 +8547,8 @@
       <c r="BG48" s="15"/>
       <c r="BH48" s="15"/>
       <c r="BI48" s="15"/>
-      <c r="BJ48" s="96"/>
-      <c r="BK48" s="96"/>
+      <c r="BJ48" s="95"/>
+      <c r="BK48" s="95"/>
       <c r="BL48" s="15"/>
       <c r="BM48" s="15"/>
       <c r="BN48" s="15"/>
@@ -8615,15 +8612,15 @@
       <c r="B49" s="18"/>
       <c r="C49" s="1"/>
       <c r="D49" s="34"/>
-      <c r="E49" s="169" t="s">
+      <c r="E49" s="130" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="164"/>
-      <c r="G49" s="170"/>
-      <c r="H49" s="138" t="s">
+      <c r="F49" s="131"/>
+      <c r="G49" s="132"/>
+      <c r="H49" s="183" t="s">
         <v>50</v>
       </c>
-      <c r="I49" s="112">
+      <c r="I49" s="111">
         <v>100</v>
       </c>
       <c r="J49" s="14"/>
@@ -8678,8 +8675,8 @@
       <c r="BG49" s="15"/>
       <c r="BH49" s="15"/>
       <c r="BI49" s="15"/>
-      <c r="BJ49" s="96"/>
-      <c r="BK49" s="96"/>
+      <c r="BJ49" s="95"/>
+      <c r="BK49" s="95"/>
       <c r="BL49" s="15"/>
       <c r="BM49" s="15"/>
       <c r="BN49" s="15"/>
@@ -8743,11 +8740,11 @@
       <c r="B50" s="18"/>
       <c r="C50" s="1"/>
       <c r="D50" s="34"/>
-      <c r="E50" s="166"/>
-      <c r="F50" s="167"/>
-      <c r="G50" s="171"/>
-      <c r="H50" s="112"/>
-      <c r="I50" s="112"/>
+      <c r="E50" s="133"/>
+      <c r="F50" s="134"/>
+      <c r="G50" s="135"/>
+      <c r="H50" s="111"/>
+      <c r="I50" s="111"/>
       <c r="J50" s="14"/>
       <c r="K50" s="15"/>
       <c r="L50" s="15"/>
@@ -8800,8 +8797,8 @@
       <c r="BG50" s="15"/>
       <c r="BH50" s="15"/>
       <c r="BI50" s="15"/>
-      <c r="BJ50" s="96"/>
-      <c r="BK50" s="96"/>
+      <c r="BJ50" s="95"/>
+      <c r="BK50" s="95"/>
       <c r="BL50" s="15"/>
       <c r="BM50" s="15"/>
       <c r="BN50" s="15"/>
@@ -8865,15 +8862,15 @@
       <c r="B51" s="18"/>
       <c r="C51" s="1"/>
       <c r="D51" s="34"/>
-      <c r="E51" s="169" t="s">
+      <c r="E51" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="164"/>
-      <c r="G51" s="170"/>
-      <c r="H51" s="138" t="s">
+      <c r="F51" s="131"/>
+      <c r="G51" s="132"/>
+      <c r="H51" s="183" t="s">
         <v>47</v>
       </c>
-      <c r="I51" s="112">
+      <c r="I51" s="111">
         <v>100</v>
       </c>
       <c r="J51" s="14"/>
@@ -8928,8 +8925,8 @@
       <c r="BG51" s="15"/>
       <c r="BH51" s="15"/>
       <c r="BI51" s="15"/>
-      <c r="BJ51" s="96"/>
-      <c r="BK51" s="96"/>
+      <c r="BJ51" s="95"/>
+      <c r="BK51" s="95"/>
       <c r="BL51" s="15"/>
       <c r="BM51" s="15"/>
       <c r="BN51" s="15"/>
@@ -8993,11 +8990,11 @@
       <c r="B52" s="18"/>
       <c r="C52" s="1"/>
       <c r="D52" s="34"/>
-      <c r="E52" s="166"/>
-      <c r="F52" s="167"/>
-      <c r="G52" s="171"/>
-      <c r="H52" s="112"/>
-      <c r="I52" s="112"/>
+      <c r="E52" s="133"/>
+      <c r="F52" s="134"/>
+      <c r="G52" s="135"/>
+      <c r="H52" s="111"/>
+      <c r="I52" s="111"/>
       <c r="J52" s="26"/>
       <c r="K52" s="27"/>
       <c r="L52" s="27"/>
@@ -9050,8 +9047,8 @@
       <c r="BG52" s="27"/>
       <c r="BH52" s="27"/>
       <c r="BI52" s="27"/>
-      <c r="BJ52" s="98"/>
-      <c r="BK52" s="98"/>
+      <c r="BJ52" s="97"/>
+      <c r="BK52" s="97"/>
       <c r="BL52" s="27"/>
       <c r="BM52" s="27"/>
       <c r="BN52" s="27"/>
@@ -9114,14 +9111,14 @@
       <c r="A53" s="1"/>
       <c r="B53" s="18"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="163" t="s">
+      <c r="D53" s="136" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="164"/>
-      <c r="F53" s="164"/>
-      <c r="G53" s="165"/>
-      <c r="H53" s="139"/>
-      <c r="I53" s="139"/>
+      <c r="E53" s="131"/>
+      <c r="F53" s="131"/>
+      <c r="G53" s="137"/>
+      <c r="H53" s="166"/>
+      <c r="I53" s="166"/>
       <c r="J53" s="50"/>
       <c r="K53" s="51"/>
       <c r="L53" s="51"/>
@@ -9174,8 +9171,8 @@
       <c r="BG53" s="51"/>
       <c r="BH53" s="51"/>
       <c r="BI53" s="51"/>
-      <c r="BJ53" s="99"/>
-      <c r="BK53" s="99"/>
+      <c r="BJ53" s="98"/>
+      <c r="BK53" s="98"/>
       <c r="BL53" s="51"/>
       <c r="BM53" s="51"/>
       <c r="BN53" s="51"/>
@@ -9238,12 +9235,12 @@
       <c r="A54" s="1"/>
       <c r="B54" s="18"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="166"/>
-      <c r="E54" s="167"/>
-      <c r="F54" s="167"/>
-      <c r="G54" s="168"/>
-      <c r="H54" s="139"/>
-      <c r="I54" s="139"/>
+      <c r="D54" s="133"/>
+      <c r="E54" s="134"/>
+      <c r="F54" s="134"/>
+      <c r="G54" s="138"/>
+      <c r="H54" s="166"/>
+      <c r="I54" s="166"/>
       <c r="J54" s="52"/>
       <c r="K54" s="49"/>
       <c r="L54" s="49"/>
@@ -9296,8 +9293,8 @@
       <c r="BG54" s="49"/>
       <c r="BH54" s="49"/>
       <c r="BI54" s="49"/>
-      <c r="BJ54" s="96"/>
-      <c r="BK54" s="96"/>
+      <c r="BJ54" s="95"/>
+      <c r="BK54" s="95"/>
       <c r="BL54" s="49"/>
       <c r="BM54" s="49"/>
       <c r="BN54" s="49"/>
@@ -9361,15 +9358,15 @@
       <c r="B55" s="18"/>
       <c r="C55" s="1"/>
       <c r="D55" s="34"/>
-      <c r="E55" s="169" t="s">
+      <c r="E55" s="130" t="s">
         <v>28</v>
       </c>
-      <c r="F55" s="164"/>
-      <c r="G55" s="170"/>
-      <c r="H55" s="138" t="s">
+      <c r="F55" s="131"/>
+      <c r="G55" s="132"/>
+      <c r="H55" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="I55" s="112">
+      <c r="I55" s="111">
         <v>100</v>
       </c>
       <c r="J55" s="14"/>
@@ -9424,8 +9421,8 @@
       <c r="BG55" s="15"/>
       <c r="BH55" s="15"/>
       <c r="BI55" s="15"/>
-      <c r="BJ55" s="96"/>
-      <c r="BK55" s="96"/>
+      <c r="BJ55" s="95"/>
+      <c r="BK55" s="95"/>
       <c r="BL55" s="15"/>
       <c r="BM55" s="15"/>
       <c r="BN55" s="15"/>
@@ -9489,11 +9486,11 @@
       <c r="B56" s="18"/>
       <c r="C56" s="1"/>
       <c r="D56" s="34"/>
-      <c r="E56" s="166"/>
-      <c r="F56" s="167"/>
-      <c r="G56" s="171"/>
-      <c r="H56" s="112"/>
-      <c r="I56" s="112"/>
+      <c r="E56" s="133"/>
+      <c r="F56" s="134"/>
+      <c r="G56" s="135"/>
+      <c r="H56" s="111"/>
+      <c r="I56" s="111"/>
       <c r="J56" s="14"/>
       <c r="K56" s="15"/>
       <c r="L56" s="15"/>
@@ -9546,8 +9543,8 @@
       <c r="BG56" s="15"/>
       <c r="BH56" s="15"/>
       <c r="BI56" s="15"/>
-      <c r="BJ56" s="96"/>
-      <c r="BK56" s="96"/>
+      <c r="BJ56" s="95"/>
+      <c r="BK56" s="95"/>
       <c r="BL56" s="15"/>
       <c r="BM56" s="15"/>
       <c r="BN56" s="15"/>
@@ -9611,15 +9608,15 @@
       <c r="B57" s="18"/>
       <c r="C57" s="1"/>
       <c r="D57" s="34"/>
-      <c r="E57" s="169" t="s">
+      <c r="E57" s="130" t="s">
         <v>29</v>
       </c>
-      <c r="F57" s="164"/>
-      <c r="G57" s="170"/>
-      <c r="H57" s="138" t="s">
+      <c r="F57" s="131"/>
+      <c r="G57" s="132"/>
+      <c r="H57" s="183" t="s">
         <v>51</v>
       </c>
-      <c r="I57" s="112">
+      <c r="I57" s="111">
         <v>100</v>
       </c>
       <c r="J57" s="14"/>
@@ -9674,8 +9671,8 @@
       <c r="BG57" s="15"/>
       <c r="BH57" s="15"/>
       <c r="BI57" s="15"/>
-      <c r="BJ57" s="96"/>
-      <c r="BK57" s="96"/>
+      <c r="BJ57" s="95"/>
+      <c r="BK57" s="95"/>
       <c r="BL57" s="15"/>
       <c r="BM57" s="15"/>
       <c r="BN57" s="15"/>
@@ -9739,11 +9736,11 @@
       <c r="B58" s="18"/>
       <c r="C58" s="1"/>
       <c r="D58" s="34"/>
-      <c r="E58" s="166"/>
-      <c r="F58" s="167"/>
-      <c r="G58" s="171"/>
-      <c r="H58" s="112"/>
-      <c r="I58" s="112"/>
+      <c r="E58" s="133"/>
+      <c r="F58" s="134"/>
+      <c r="G58" s="135"/>
+      <c r="H58" s="111"/>
+      <c r="I58" s="111"/>
       <c r="J58" s="14"/>
       <c r="K58" s="15"/>
       <c r="L58" s="15"/>
@@ -9796,8 +9793,8 @@
       <c r="BG58" s="15"/>
       <c r="BH58" s="15"/>
       <c r="BI58" s="15"/>
-      <c r="BJ58" s="96"/>
-      <c r="BK58" s="96"/>
+      <c r="BJ58" s="95"/>
+      <c r="BK58" s="95"/>
       <c r="BL58" s="15"/>
       <c r="BM58" s="15"/>
       <c r="BN58" s="15"/>
@@ -9861,15 +9858,15 @@
       <c r="B59" s="18"/>
       <c r="C59" s="1"/>
       <c r="D59" s="34"/>
-      <c r="E59" s="169" t="s">
+      <c r="E59" s="130" t="s">
         <v>26</v>
       </c>
-      <c r="F59" s="164"/>
-      <c r="G59" s="170"/>
-      <c r="H59" s="138" t="s">
+      <c r="F59" s="131"/>
+      <c r="G59" s="132"/>
+      <c r="H59" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="I59" s="112">
+      <c r="I59" s="111">
         <v>100</v>
       </c>
       <c r="J59" s="14"/>
@@ -9924,8 +9921,8 @@
       <c r="BG59" s="15"/>
       <c r="BH59" s="15"/>
       <c r="BI59" s="15"/>
-      <c r="BJ59" s="96"/>
-      <c r="BK59" s="96"/>
+      <c r="BJ59" s="95"/>
+      <c r="BK59" s="95"/>
       <c r="BL59" s="15"/>
       <c r="BM59" s="15"/>
       <c r="BN59" s="15"/>
@@ -9989,11 +9986,11 @@
       <c r="B60" s="18"/>
       <c r="C60" s="1"/>
       <c r="D60" s="34"/>
-      <c r="E60" s="166"/>
-      <c r="F60" s="167"/>
-      <c r="G60" s="171"/>
-      <c r="H60" s="112"/>
-      <c r="I60" s="112"/>
+      <c r="E60" s="133"/>
+      <c r="F60" s="134"/>
+      <c r="G60" s="135"/>
+      <c r="H60" s="111"/>
+      <c r="I60" s="111"/>
       <c r="J60" s="14"/>
       <c r="K60" s="15"/>
       <c r="L60" s="15"/>
@@ -10046,8 +10043,8 @@
       <c r="BG60" s="15"/>
       <c r="BH60" s="15"/>
       <c r="BI60" s="15"/>
-      <c r="BJ60" s="96"/>
-      <c r="BK60" s="96"/>
+      <c r="BJ60" s="95"/>
+      <c r="BK60" s="95"/>
       <c r="BL60" s="15"/>
       <c r="BM60" s="15"/>
       <c r="BN60" s="15"/>
@@ -10111,15 +10108,15 @@
       <c r="B61" s="18"/>
       <c r="C61" s="1"/>
       <c r="D61" s="34"/>
-      <c r="E61" s="169" t="s">
+      <c r="E61" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="F61" s="164"/>
-      <c r="G61" s="170"/>
-      <c r="H61" s="138" t="s">
+      <c r="F61" s="131"/>
+      <c r="G61" s="132"/>
+      <c r="H61" s="183" t="s">
         <v>49</v>
       </c>
-      <c r="I61" s="112">
+      <c r="I61" s="111">
         <v>100</v>
       </c>
       <c r="J61" s="14"/>
@@ -10174,8 +10171,8 @@
       <c r="BG61" s="15"/>
       <c r="BH61" s="15"/>
       <c r="BI61" s="15"/>
-      <c r="BJ61" s="96"/>
-      <c r="BK61" s="96"/>
+      <c r="BJ61" s="95"/>
+      <c r="BK61" s="95"/>
       <c r="BL61" s="15"/>
       <c r="BM61" s="15"/>
       <c r="BN61" s="15"/>
@@ -10239,11 +10236,11 @@
       <c r="B62" s="18"/>
       <c r="C62" s="1"/>
       <c r="D62" s="34"/>
-      <c r="E62" s="166"/>
-      <c r="F62" s="167"/>
-      <c r="G62" s="171"/>
-      <c r="H62" s="112"/>
-      <c r="I62" s="112"/>
+      <c r="E62" s="133"/>
+      <c r="F62" s="134"/>
+      <c r="G62" s="135"/>
+      <c r="H62" s="111"/>
+      <c r="I62" s="111"/>
       <c r="J62" s="26"/>
       <c r="K62" s="27"/>
       <c r="L62" s="27"/>
@@ -10296,8 +10293,8 @@
       <c r="BG62" s="27"/>
       <c r="BH62" s="27"/>
       <c r="BI62" s="27"/>
-      <c r="BJ62" s="98"/>
-      <c r="BK62" s="98"/>
+      <c r="BJ62" s="97"/>
+      <c r="BK62" s="97"/>
       <c r="BL62" s="27"/>
       <c r="BM62" s="27"/>
       <c r="BN62" s="27"/>
@@ -10360,14 +10357,14 @@
       <c r="A63" s="1"/>
       <c r="B63" s="18"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="163" t="s">
+      <c r="D63" s="136" t="s">
         <v>35</v>
       </c>
-      <c r="E63" s="164"/>
-      <c r="F63" s="164"/>
-      <c r="G63" s="165"/>
-      <c r="H63" s="139"/>
-      <c r="I63" s="139"/>
+      <c r="E63" s="131"/>
+      <c r="F63" s="131"/>
+      <c r="G63" s="137"/>
+      <c r="H63" s="166"/>
+      <c r="I63" s="166"/>
       <c r="J63" s="50"/>
       <c r="K63" s="51"/>
       <c r="L63" s="51"/>
@@ -10420,8 +10417,8 @@
       <c r="BG63" s="51"/>
       <c r="BH63" s="51"/>
       <c r="BI63" s="51"/>
-      <c r="BJ63" s="99"/>
-      <c r="BK63" s="99"/>
+      <c r="BJ63" s="98"/>
+      <c r="BK63" s="98"/>
       <c r="BL63" s="51"/>
       <c r="BM63" s="51"/>
       <c r="BN63" s="51"/>
@@ -10484,12 +10481,12 @@
       <c r="A64" s="1"/>
       <c r="B64" s="18"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="166"/>
-      <c r="E64" s="167"/>
-      <c r="F64" s="167"/>
-      <c r="G64" s="168"/>
-      <c r="H64" s="139"/>
-      <c r="I64" s="139"/>
+      <c r="D64" s="133"/>
+      <c r="E64" s="134"/>
+      <c r="F64" s="134"/>
+      <c r="G64" s="138"/>
+      <c r="H64" s="166"/>
+      <c r="I64" s="166"/>
       <c r="J64" s="52"/>
       <c r="K64" s="49"/>
       <c r="L64" s="49"/>
@@ -10542,8 +10539,8 @@
       <c r="BG64" s="49"/>
       <c r="BH64" s="49"/>
       <c r="BI64" s="49"/>
-      <c r="BJ64" s="96"/>
-      <c r="BK64" s="96"/>
+      <c r="BJ64" s="95"/>
+      <c r="BK64" s="95"/>
       <c r="BL64" s="49"/>
       <c r="BM64" s="49"/>
       <c r="BN64" s="49"/>
@@ -10607,15 +10604,15 @@
       <c r="B65" s="18"/>
       <c r="C65" s="1"/>
       <c r="D65" s="34"/>
-      <c r="E65" s="169" t="s">
+      <c r="E65" s="130" t="s">
         <v>35</v>
       </c>
-      <c r="F65" s="164"/>
-      <c r="G65" s="170"/>
-      <c r="H65" s="138" t="s">
+      <c r="F65" s="131"/>
+      <c r="G65" s="132"/>
+      <c r="H65" s="183" t="s">
         <v>52</v>
       </c>
-      <c r="I65" s="112">
+      <c r="I65" s="111">
         <v>100</v>
       </c>
       <c r="J65" s="14"/>
@@ -10670,8 +10667,8 @@
       <c r="BG65" s="15"/>
       <c r="BH65" s="15"/>
       <c r="BI65" s="15"/>
-      <c r="BJ65" s="96"/>
-      <c r="BK65" s="96"/>
+      <c r="BJ65" s="95"/>
+      <c r="BK65" s="95"/>
       <c r="BL65" s="15"/>
       <c r="BM65" s="15"/>
       <c r="BN65" s="15"/>
@@ -10735,11 +10732,11 @@
       <c r="B66" s="18"/>
       <c r="C66" s="1"/>
       <c r="D66" s="34"/>
-      <c r="E66" s="166"/>
-      <c r="F66" s="167"/>
-      <c r="G66" s="171"/>
-      <c r="H66" s="112"/>
-      <c r="I66" s="112"/>
+      <c r="E66" s="133"/>
+      <c r="F66" s="134"/>
+      <c r="G66" s="135"/>
+      <c r="H66" s="111"/>
+      <c r="I66" s="111"/>
       <c r="J66" s="14"/>
       <c r="K66" s="15"/>
       <c r="L66" s="15"/>
@@ -10792,8 +10789,8 @@
       <c r="BG66" s="15"/>
       <c r="BH66" s="15"/>
       <c r="BI66" s="15"/>
-      <c r="BJ66" s="96"/>
-      <c r="BK66" s="96"/>
+      <c r="BJ66" s="95"/>
+      <c r="BK66" s="95"/>
       <c r="BL66" s="15"/>
       <c r="BM66" s="15"/>
       <c r="BN66" s="15"/>
@@ -10857,15 +10854,15 @@
       <c r="B67" s="18"/>
       <c r="C67" s="1"/>
       <c r="D67" s="34"/>
-      <c r="E67" s="169" t="s">
+      <c r="E67" s="130" t="s">
         <v>26</v>
       </c>
-      <c r="F67" s="164"/>
-      <c r="G67" s="170"/>
-      <c r="H67" s="138" t="s">
+      <c r="F67" s="131"/>
+      <c r="G67" s="132"/>
+      <c r="H67" s="183" t="s">
         <v>53</v>
       </c>
-      <c r="I67" s="112">
+      <c r="I67" s="111">
         <v>100</v>
       </c>
       <c r="J67" s="14"/>
@@ -10920,8 +10917,8 @@
       <c r="BG67" s="15"/>
       <c r="BH67" s="15"/>
       <c r="BI67" s="15"/>
-      <c r="BJ67" s="96"/>
-      <c r="BK67" s="96"/>
+      <c r="BJ67" s="95"/>
+      <c r="BK67" s="95"/>
       <c r="BL67" s="15"/>
       <c r="BM67" s="15"/>
       <c r="BN67" s="15"/>
@@ -10985,11 +10982,11 @@
       <c r="B68" s="18"/>
       <c r="C68" s="1"/>
       <c r="D68" s="34"/>
-      <c r="E68" s="166"/>
-      <c r="F68" s="167"/>
-      <c r="G68" s="171"/>
-      <c r="H68" s="112"/>
-      <c r="I68" s="112"/>
+      <c r="E68" s="133"/>
+      <c r="F68" s="134"/>
+      <c r="G68" s="135"/>
+      <c r="H68" s="111"/>
+      <c r="I68" s="111"/>
       <c r="J68" s="14"/>
       <c r="K68" s="15"/>
       <c r="L68" s="15"/>
@@ -11042,8 +11039,8 @@
       <c r="BG68" s="15"/>
       <c r="BH68" s="15"/>
       <c r="BI68" s="15"/>
-      <c r="BJ68" s="96"/>
-      <c r="BK68" s="96"/>
+      <c r="BJ68" s="95"/>
+      <c r="BK68" s="95"/>
       <c r="BL68" s="15"/>
       <c r="BM68" s="15"/>
       <c r="BN68" s="15"/>
@@ -11107,15 +11104,15 @@
       <c r="B69" s="18"/>
       <c r="C69" s="1"/>
       <c r="D69" s="34"/>
-      <c r="E69" s="169" t="s">
+      <c r="E69" s="130" t="s">
         <v>36</v>
       </c>
-      <c r="F69" s="164"/>
-      <c r="G69" s="170"/>
-      <c r="H69" s="138" t="s">
+      <c r="F69" s="131"/>
+      <c r="G69" s="132"/>
+      <c r="H69" s="183" t="s">
         <v>54</v>
       </c>
-      <c r="I69" s="112">
+      <c r="I69" s="111">
         <v>100</v>
       </c>
       <c r="J69" s="14"/>
@@ -11170,8 +11167,8 @@
       <c r="BG69" s="15"/>
       <c r="BH69" s="15"/>
       <c r="BI69" s="15"/>
-      <c r="BJ69" s="96"/>
-      <c r="BK69" s="96"/>
+      <c r="BJ69" s="95"/>
+      <c r="BK69" s="95"/>
       <c r="BL69" s="15"/>
       <c r="BM69" s="15"/>
       <c r="BN69" s="15"/>
@@ -11235,11 +11232,11 @@
       <c r="B70" s="18"/>
       <c r="C70" s="1"/>
       <c r="D70" s="34"/>
-      <c r="E70" s="166"/>
-      <c r="F70" s="167"/>
-      <c r="G70" s="171"/>
-      <c r="H70" s="112"/>
-      <c r="I70" s="112"/>
+      <c r="E70" s="133"/>
+      <c r="F70" s="134"/>
+      <c r="G70" s="135"/>
+      <c r="H70" s="111"/>
+      <c r="I70" s="111"/>
       <c r="J70" s="14"/>
       <c r="K70" s="15"/>
       <c r="L70" s="15"/>
@@ -11292,8 +11289,8 @@
       <c r="BG70" s="15"/>
       <c r="BH70" s="15"/>
       <c r="BI70" s="15"/>
-      <c r="BJ70" s="96"/>
-      <c r="BK70" s="96"/>
+      <c r="BJ70" s="95"/>
+      <c r="BK70" s="95"/>
       <c r="BL70" s="15"/>
       <c r="BM70" s="15"/>
       <c r="BN70" s="15"/>
@@ -11357,15 +11354,15 @@
       <c r="B71" s="18"/>
       <c r="C71" s="1"/>
       <c r="D71" s="34"/>
-      <c r="E71" s="169" t="s">
+      <c r="E71" s="130" t="s">
         <v>21</v>
       </c>
-      <c r="F71" s="164"/>
-      <c r="G71" s="170"/>
-      <c r="H71" s="138" t="s">
+      <c r="F71" s="131"/>
+      <c r="G71" s="132"/>
+      <c r="H71" s="183" t="s">
         <v>55</v>
       </c>
-      <c r="I71" s="112">
+      <c r="I71" s="111">
         <v>100</v>
       </c>
       <c r="J71" s="14"/>
@@ -11420,8 +11417,8 @@
       <c r="BG71" s="15"/>
       <c r="BH71" s="15"/>
       <c r="BI71" s="15"/>
-      <c r="BJ71" s="96"/>
-      <c r="BK71" s="96"/>
+      <c r="BJ71" s="95"/>
+      <c r="BK71" s="95"/>
       <c r="BL71" s="15"/>
       <c r="BM71" s="15"/>
       <c r="BN71" s="15"/>
@@ -11485,11 +11482,11 @@
       <c r="B72" s="18"/>
       <c r="C72" s="1"/>
       <c r="D72" s="35"/>
-      <c r="E72" s="166"/>
-      <c r="F72" s="167"/>
-      <c r="G72" s="171"/>
-      <c r="H72" s="112"/>
-      <c r="I72" s="112"/>
+      <c r="E72" s="133"/>
+      <c r="F72" s="134"/>
+      <c r="G72" s="135"/>
+      <c r="H72" s="111"/>
+      <c r="I72" s="111"/>
       <c r="J72" s="26"/>
       <c r="K72" s="27"/>
       <c r="L72" s="27"/>
@@ -11542,9 +11539,9 @@
       <c r="BG72" s="27"/>
       <c r="BH72" s="27"/>
       <c r="BI72" s="27"/>
-      <c r="BJ72" s="98"/>
-      <c r="BK72" s="98"/>
-      <c r="BL72" s="98"/>
+      <c r="BJ72" s="97"/>
+      <c r="BK72" s="97"/>
+      <c r="BL72" s="97"/>
       <c r="BM72" s="27"/>
       <c r="BN72" s="27"/>
       <c r="BO72" s="27"/>
@@ -11605,17 +11602,17 @@
     <row r="73" spans="1:120" ht="9.75" customHeight="1">
       <c r="A73" s="16"/>
       <c r="B73" s="36"/>
-      <c r="C73" s="146" t="s">
+      <c r="C73" s="139" t="s">
         <v>30</v>
       </c>
-      <c r="D73" s="164"/>
-      <c r="E73" s="164"/>
-      <c r="F73" s="164"/>
-      <c r="G73" s="165"/>
-      <c r="H73" s="138" t="s">
+      <c r="D73" s="131"/>
+      <c r="E73" s="131"/>
+      <c r="F73" s="131"/>
+      <c r="G73" s="137"/>
+      <c r="H73" s="183" t="s">
         <v>55</v>
       </c>
-      <c r="I73" s="112">
+      <c r="I73" s="111">
         <v>100</v>
       </c>
       <c r="J73" s="19"/>
@@ -11733,13 +11730,13 @@
     <row r="74" spans="1:120" ht="9.75" customHeight="1">
       <c r="A74" s="16"/>
       <c r="B74" s="36"/>
-      <c r="C74" s="179"/>
-      <c r="D74" s="167"/>
-      <c r="E74" s="167"/>
-      <c r="F74" s="167"/>
-      <c r="G74" s="168"/>
-      <c r="H74" s="112"/>
-      <c r="I74" s="112"/>
+      <c r="C74" s="140"/>
+      <c r="D74" s="134"/>
+      <c r="E74" s="134"/>
+      <c r="F74" s="134"/>
+      <c r="G74" s="138"/>
+      <c r="H74" s="111"/>
+      <c r="I74" s="111"/>
       <c r="J74" s="19"/>
       <c r="K74" s="20"/>
       <c r="L74" s="20"/>
@@ -11855,17 +11852,17 @@
     <row r="75" spans="1:120" ht="9.75" customHeight="1">
       <c r="A75" s="16"/>
       <c r="B75" s="36"/>
-      <c r="C75" s="146" t="s">
+      <c r="C75" s="139" t="s">
         <v>34</v>
       </c>
-      <c r="D75" s="164"/>
-      <c r="E75" s="164"/>
-      <c r="F75" s="164"/>
-      <c r="G75" s="165"/>
-      <c r="H75" s="138" t="s">
+      <c r="D75" s="131"/>
+      <c r="E75" s="131"/>
+      <c r="F75" s="131"/>
+      <c r="G75" s="137"/>
+      <c r="H75" s="183" t="s">
         <v>58</v>
       </c>
-      <c r="I75" s="112"/>
+      <c r="I75" s="111"/>
       <c r="J75" s="19"/>
       <c r="K75" s="20"/>
       <c r="L75" s="20"/>
@@ -11981,13 +11978,13 @@
     <row r="76" spans="1:120" ht="9.75" customHeight="1">
       <c r="A76" s="16"/>
       <c r="B76" s="36"/>
-      <c r="C76" s="162"/>
-      <c r="D76" s="162"/>
-      <c r="E76" s="162"/>
-      <c r="F76" s="162"/>
-      <c r="G76" s="162"/>
-      <c r="H76" s="112"/>
-      <c r="I76" s="112"/>
+      <c r="C76" s="141"/>
+      <c r="D76" s="141"/>
+      <c r="E76" s="141"/>
+      <c r="F76" s="141"/>
+      <c r="G76" s="141"/>
+      <c r="H76" s="111"/>
+      <c r="I76" s="111"/>
       <c r="J76" s="19"/>
       <c r="K76" s="20"/>
       <c r="L76" s="20"/>
@@ -12103,15 +12100,15 @@
     <row r="77" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A77" s="16"/>
       <c r="B77" s="71"/>
-      <c r="C77" s="187" t="s">
+      <c r="C77" s="142" t="s">
         <v>62</v>
       </c>
-      <c r="D77" s="188"/>
-      <c r="E77" s="188"/>
-      <c r="F77" s="188"/>
-      <c r="G77" s="189"/>
-      <c r="H77" s="140"/>
-      <c r="I77" s="129"/>
+      <c r="D77" s="143"/>
+      <c r="E77" s="143"/>
+      <c r="F77" s="143"/>
+      <c r="G77" s="144"/>
+      <c r="H77" s="184"/>
+      <c r="I77" s="180"/>
       <c r="J77" s="63"/>
       <c r="K77" s="64"/>
       <c r="L77" s="64"/>
@@ -12227,13 +12224,13 @@
     <row r="78" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A78" s="16"/>
       <c r="B78" s="71"/>
-      <c r="C78" s="190"/>
-      <c r="D78" s="191"/>
-      <c r="E78" s="191"/>
-      <c r="F78" s="191"/>
-      <c r="G78" s="192"/>
-      <c r="H78" s="141"/>
-      <c r="I78" s="130"/>
+      <c r="C78" s="145"/>
+      <c r="D78" s="146"/>
+      <c r="E78" s="146"/>
+      <c r="F78" s="146"/>
+      <c r="G78" s="147"/>
+      <c r="H78" s="185"/>
+      <c r="I78" s="181"/>
       <c r="J78" s="63"/>
       <c r="K78" s="64"/>
       <c r="L78" s="64"/>
@@ -12350,12 +12347,12 @@
       <c r="A79" s="16"/>
       <c r="B79" s="71"/>
       <c r="C79" s="76"/>
-      <c r="D79" s="132" t="s">
+      <c r="D79" s="114" t="s">
         <v>63</v>
       </c>
-      <c r="E79" s="133"/>
-      <c r="F79" s="133"/>
-      <c r="G79" s="134"/>
+      <c r="E79" s="115"/>
+      <c r="F79" s="115"/>
+      <c r="G79" s="116"/>
       <c r="H79" s="77"/>
       <c r="I79" s="67"/>
       <c r="J79" s="63"/>
@@ -12474,10 +12471,10 @@
       <c r="A80" s="16"/>
       <c r="B80" s="71"/>
       <c r="C80" s="76"/>
-      <c r="D80" s="135"/>
-      <c r="E80" s="136"/>
-      <c r="F80" s="136"/>
-      <c r="G80" s="137"/>
+      <c r="D80" s="117"/>
+      <c r="E80" s="118"/>
+      <c r="F80" s="118"/>
+      <c r="G80" s="119"/>
       <c r="H80" s="77"/>
       <c r="I80" s="67"/>
       <c r="J80" s="63"/>
@@ -12597,15 +12594,15 @@
       <c r="B81" s="36"/>
       <c r="C81" s="60"/>
       <c r="D81" s="70"/>
-      <c r="E81" s="105" t="s">
+      <c r="E81" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="F81" s="105"/>
-      <c r="G81" s="105"/>
-      <c r="H81" s="111">
+      <c r="F81" s="148"/>
+      <c r="G81" s="148"/>
+      <c r="H81" s="102">
         <v>45611</v>
       </c>
-      <c r="I81" s="126">
+      <c r="I81" s="104">
         <v>100</v>
       </c>
       <c r="J81" s="19"/>
@@ -12725,11 +12722,11 @@
       <c r="B82" s="36"/>
       <c r="C82" s="60"/>
       <c r="D82" s="70"/>
-      <c r="E82" s="103"/>
-      <c r="F82" s="103"/>
-      <c r="G82" s="103"/>
-      <c r="H82" s="107"/>
-      <c r="I82" s="109"/>
+      <c r="E82" s="101"/>
+      <c r="F82" s="101"/>
+      <c r="G82" s="101"/>
+      <c r="H82" s="103"/>
+      <c r="I82" s="105"/>
       <c r="J82" s="19"/>
       <c r="K82" s="20"/>
       <c r="L82" s="20"/>
@@ -12847,15 +12844,15 @@
       <c r="B83" s="36"/>
       <c r="C83" s="60"/>
       <c r="D83" s="70"/>
-      <c r="E83" s="103" t="s">
+      <c r="E83" s="101" t="s">
         <v>74</v>
       </c>
-      <c r="F83" s="103"/>
-      <c r="G83" s="103"/>
-      <c r="H83" s="111">
+      <c r="F83" s="101"/>
+      <c r="G83" s="101"/>
+      <c r="H83" s="102">
         <v>45615</v>
       </c>
-      <c r="I83" s="126">
+      <c r="I83" s="104">
         <v>100</v>
       </c>
       <c r="J83" s="19"/>
@@ -12975,11 +12972,11 @@
       <c r="B84" s="36"/>
       <c r="C84" s="60"/>
       <c r="D84" s="70"/>
-      <c r="E84" s="103"/>
-      <c r="F84" s="103"/>
-      <c r="G84" s="103"/>
-      <c r="H84" s="107"/>
-      <c r="I84" s="109"/>
+      <c r="E84" s="101"/>
+      <c r="F84" s="101"/>
+      <c r="G84" s="101"/>
+      <c r="H84" s="103"/>
+      <c r="I84" s="105"/>
       <c r="J84" s="19"/>
       <c r="K84" s="20"/>
       <c r="L84" s="20"/>
@@ -13097,15 +13094,15 @@
       <c r="B85" s="36"/>
       <c r="C85" s="60"/>
       <c r="D85" s="70"/>
-      <c r="E85" s="114" t="s">
+      <c r="E85" s="188" t="s">
         <v>61</v>
       </c>
-      <c r="F85" s="115"/>
-      <c r="G85" s="116"/>
+      <c r="F85" s="120"/>
+      <c r="G85" s="121"/>
       <c r="H85" s="110">
         <v>45617</v>
       </c>
-      <c r="I85" s="126">
+      <c r="I85" s="104">
         <v>100</v>
       </c>
       <c r="J85" s="62"/>
@@ -13225,11 +13222,11 @@
       <c r="B86" s="36"/>
       <c r="C86" s="60"/>
       <c r="D86" s="70"/>
-      <c r="E86" s="117"/>
-      <c r="F86" s="118"/>
-      <c r="G86" s="119"/>
+      <c r="E86" s="149"/>
+      <c r="F86" s="124"/>
+      <c r="G86" s="125"/>
       <c r="H86" s="110"/>
-      <c r="I86" s="109"/>
+      <c r="I86" s="105"/>
       <c r="J86" s="62"/>
       <c r="K86" s="20"/>
       <c r="L86" s="20"/>
@@ -13346,16 +13343,16 @@
       <c r="A87" s="16"/>
       <c r="B87" s="71"/>
       <c r="C87" s="90"/>
-      <c r="D87" s="103" t="s">
+      <c r="D87" s="101" t="s">
         <v>76</v>
       </c>
-      <c r="E87" s="103"/>
-      <c r="F87" s="103"/>
-      <c r="G87" s="103"/>
-      <c r="H87" s="111">
+      <c r="E87" s="101"/>
+      <c r="F87" s="101"/>
+      <c r="G87" s="101"/>
+      <c r="H87" s="102">
         <v>45615</v>
       </c>
-      <c r="I87" s="126">
+      <c r="I87" s="104">
         <v>100</v>
       </c>
       <c r="J87" s="62"/>
@@ -13474,12 +13471,12 @@
       <c r="A88" s="16"/>
       <c r="B88" s="71"/>
       <c r="C88" s="90"/>
-      <c r="D88" s="103"/>
-      <c r="E88" s="103"/>
-      <c r="F88" s="103"/>
-      <c r="G88" s="103"/>
-      <c r="H88" s="107"/>
-      <c r="I88" s="109"/>
+      <c r="D88" s="101"/>
+      <c r="E88" s="101"/>
+      <c r="F88" s="101"/>
+      <c r="G88" s="101"/>
+      <c r="H88" s="103"/>
+      <c r="I88" s="105"/>
       <c r="J88" s="62"/>
       <c r="K88" s="20"/>
       <c r="L88" s="20"/>
@@ -13596,14 +13593,14 @@
       <c r="A89" s="16"/>
       <c r="B89" s="36"/>
       <c r="C89" s="79"/>
-      <c r="D89" s="132" t="s">
+      <c r="D89" s="114" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="133"/>
-      <c r="F89" s="133"/>
-      <c r="G89" s="134"/>
-      <c r="H89" s="131"/>
-      <c r="I89" s="128"/>
+      <c r="E89" s="115"/>
+      <c r="F89" s="115"/>
+      <c r="G89" s="116"/>
+      <c r="H89" s="186"/>
+      <c r="I89" s="187"/>
       <c r="J89" s="66"/>
       <c r="K89" s="64"/>
       <c r="L89" s="64"/>
@@ -13720,12 +13717,12 @@
       <c r="A90" s="16"/>
       <c r="B90" s="36"/>
       <c r="C90" s="79"/>
-      <c r="D90" s="135"/>
-      <c r="E90" s="136"/>
-      <c r="F90" s="136"/>
-      <c r="G90" s="137"/>
-      <c r="H90" s="131"/>
-      <c r="I90" s="128"/>
+      <c r="D90" s="117"/>
+      <c r="E90" s="118"/>
+      <c r="F90" s="118"/>
+      <c r="G90" s="119"/>
+      <c r="H90" s="186"/>
+      <c r="I90" s="187"/>
       <c r="J90" s="66"/>
       <c r="K90" s="64"/>
       <c r="L90" s="64"/>
@@ -13843,15 +13840,15 @@
       <c r="B91" s="36"/>
       <c r="C91" s="60"/>
       <c r="D91" s="70"/>
-      <c r="E91" s="105" t="s">
+      <c r="E91" s="148" t="s">
         <v>68</v>
       </c>
-      <c r="F91" s="105"/>
-      <c r="G91" s="105"/>
-      <c r="H91" s="111">
+      <c r="F91" s="148"/>
+      <c r="G91" s="148"/>
+      <c r="H91" s="102">
         <v>45616</v>
       </c>
-      <c r="I91" s="126">
+      <c r="I91" s="104">
         <v>100</v>
       </c>
       <c r="J91" s="19"/>
@@ -13971,11 +13968,11 @@
       <c r="B92" s="36"/>
       <c r="C92" s="60"/>
       <c r="D92" s="70"/>
-      <c r="E92" s="103"/>
-      <c r="F92" s="103"/>
-      <c r="G92" s="103"/>
-      <c r="H92" s="107"/>
-      <c r="I92" s="109"/>
+      <c r="E92" s="101"/>
+      <c r="F92" s="101"/>
+      <c r="G92" s="101"/>
+      <c r="H92" s="103"/>
+      <c r="I92" s="105"/>
       <c r="J92" s="19"/>
       <c r="K92" s="20"/>
       <c r="L92" s="20"/>
@@ -14093,15 +14090,15 @@
       <c r="B93" s="36"/>
       <c r="C93" s="60"/>
       <c r="D93" s="70"/>
-      <c r="E93" s="103" t="s">
+      <c r="E93" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="F93" s="103"/>
-      <c r="G93" s="103"/>
-      <c r="H93" s="111">
+      <c r="F93" s="101"/>
+      <c r="G93" s="101"/>
+      <c r="H93" s="102">
         <v>45617</v>
       </c>
-      <c r="I93" s="126">
+      <c r="I93" s="104">
         <v>100</v>
       </c>
       <c r="J93" s="19"/>
@@ -14221,11 +14218,11 @@
       <c r="B94" s="36"/>
       <c r="C94" s="60"/>
       <c r="D94" s="70"/>
-      <c r="E94" s="103"/>
-      <c r="F94" s="103"/>
-      <c r="G94" s="103"/>
-      <c r="H94" s="107"/>
-      <c r="I94" s="109"/>
+      <c r="E94" s="101"/>
+      <c r="F94" s="101"/>
+      <c r="G94" s="101"/>
+      <c r="H94" s="103"/>
+      <c r="I94" s="105"/>
       <c r="J94" s="19"/>
       <c r="K94" s="20"/>
       <c r="L94" s="20"/>
@@ -14343,15 +14340,15 @@
       <c r="B95" s="36"/>
       <c r="C95" s="60"/>
       <c r="D95" s="70"/>
-      <c r="E95" s="103" t="s">
+      <c r="E95" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="F95" s="103"/>
-      <c r="G95" s="103"/>
-      <c r="H95" s="111">
+      <c r="F95" s="101"/>
+      <c r="G95" s="101"/>
+      <c r="H95" s="102">
         <v>45618</v>
       </c>
-      <c r="I95" s="126">
+      <c r="I95" s="104">
         <v>100</v>
       </c>
       <c r="J95" s="19"/>
@@ -14471,11 +14468,11 @@
       <c r="B96" s="36"/>
       <c r="C96" s="60"/>
       <c r="D96" s="70"/>
-      <c r="E96" s="103"/>
-      <c r="F96" s="103"/>
-      <c r="G96" s="103"/>
-      <c r="H96" s="107"/>
-      <c r="I96" s="109"/>
+      <c r="E96" s="101"/>
+      <c r="F96" s="101"/>
+      <c r="G96" s="101"/>
+      <c r="H96" s="103"/>
+      <c r="I96" s="105"/>
       <c r="J96" s="19"/>
       <c r="K96" s="20"/>
       <c r="L96" s="20"/>
@@ -14593,15 +14590,15 @@
       <c r="B97" s="36"/>
       <c r="C97" s="60"/>
       <c r="D97" s="70"/>
-      <c r="E97" s="103" t="s">
+      <c r="E97" s="101" t="s">
         <v>71</v>
       </c>
-      <c r="F97" s="103"/>
-      <c r="G97" s="103"/>
-      <c r="H97" s="111">
+      <c r="F97" s="101"/>
+      <c r="G97" s="101"/>
+      <c r="H97" s="102">
         <v>45621</v>
       </c>
-      <c r="I97" s="126">
+      <c r="I97" s="104">
         <v>100</v>
       </c>
       <c r="J97" s="19"/>
@@ -14721,11 +14718,11 @@
       <c r="B98" s="36"/>
       <c r="C98" s="60"/>
       <c r="D98" s="70"/>
-      <c r="E98" s="103"/>
-      <c r="F98" s="103"/>
-      <c r="G98" s="103"/>
-      <c r="H98" s="107"/>
-      <c r="I98" s="109"/>
+      <c r="E98" s="101"/>
+      <c r="F98" s="101"/>
+      <c r="G98" s="101"/>
+      <c r="H98" s="103"/>
+      <c r="I98" s="105"/>
       <c r="J98" s="19"/>
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
@@ -14843,15 +14840,15 @@
       <c r="B99" s="36"/>
       <c r="C99" s="60"/>
       <c r="D99" s="70"/>
-      <c r="E99" s="103" t="s">
+      <c r="E99" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="F99" s="103"/>
-      <c r="G99" s="103"/>
-      <c r="H99" s="111">
+      <c r="F99" s="101"/>
+      <c r="G99" s="101"/>
+      <c r="H99" s="102">
         <v>45622</v>
       </c>
-      <c r="I99" s="126">
+      <c r="I99" s="104">
         <v>100</v>
       </c>
       <c r="J99" s="19"/>
@@ -14971,11 +14968,11 @@
       <c r="B100" s="36"/>
       <c r="C100" s="60"/>
       <c r="D100" s="70"/>
-      <c r="E100" s="103"/>
-      <c r="F100" s="103"/>
-      <c r="G100" s="103"/>
-      <c r="H100" s="107"/>
-      <c r="I100" s="109"/>
+      <c r="E100" s="101"/>
+      <c r="F100" s="101"/>
+      <c r="G100" s="101"/>
+      <c r="H100" s="103"/>
+      <c r="I100" s="105"/>
       <c r="J100" s="19"/>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -15093,15 +15090,15 @@
       <c r="B101" s="71"/>
       <c r="C101" s="91"/>
       <c r="D101" s="70"/>
-      <c r="E101" s="117" t="s">
+      <c r="E101" s="149" t="s">
         <v>61</v>
       </c>
-      <c r="F101" s="118"/>
-      <c r="G101" s="119"/>
-      <c r="H101" s="111">
+      <c r="F101" s="124"/>
+      <c r="G101" s="125"/>
+      <c r="H101" s="102">
         <v>45623</v>
       </c>
-      <c r="I101" s="112">
+      <c r="I101" s="111">
         <v>100</v>
       </c>
       <c r="J101" s="62"/>
@@ -15221,11 +15218,11 @@
       <c r="B102" s="71"/>
       <c r="C102" s="91"/>
       <c r="D102" s="70"/>
-      <c r="E102" s="117"/>
-      <c r="F102" s="118"/>
-      <c r="G102" s="119"/>
-      <c r="H102" s="107"/>
-      <c r="I102" s="112"/>
+      <c r="E102" s="149"/>
+      <c r="F102" s="124"/>
+      <c r="G102" s="125"/>
+      <c r="H102" s="103"/>
+      <c r="I102" s="111"/>
       <c r="J102" s="62"/>
       <c r="K102" s="20"/>
       <c r="L102" s="20"/>
@@ -15342,16 +15339,16 @@
       <c r="A103" s="16"/>
       <c r="B103" s="71"/>
       <c r="C103" s="90"/>
-      <c r="D103" s="103" t="s">
+      <c r="D103" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="E103" s="103"/>
-      <c r="F103" s="103"/>
-      <c r="G103" s="103"/>
-      <c r="H103" s="111">
+      <c r="E103" s="101"/>
+      <c r="F103" s="101"/>
+      <c r="G103" s="101"/>
+      <c r="H103" s="102">
         <v>45622</v>
       </c>
-      <c r="I103" s="113">
+      <c r="I103" s="108">
         <v>100</v>
       </c>
       <c r="J103" s="62"/>
@@ -15470,12 +15467,12 @@
       <c r="A104" s="16"/>
       <c r="B104" s="71"/>
       <c r="C104" s="90"/>
-      <c r="D104" s="103"/>
-      <c r="E104" s="103"/>
-      <c r="F104" s="103"/>
-      <c r="G104" s="103"/>
-      <c r="H104" s="107"/>
-      <c r="I104" s="143"/>
+      <c r="D104" s="101"/>
+      <c r="E104" s="101"/>
+      <c r="F104" s="101"/>
+      <c r="G104" s="101"/>
+      <c r="H104" s="103"/>
+      <c r="I104" s="109"/>
       <c r="J104" s="62"/>
       <c r="K104" s="20"/>
       <c r="L104" s="20"/>
@@ -15591,15 +15588,15 @@
     <row r="105" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A105" s="16"/>
       <c r="B105" s="71"/>
-      <c r="C105" s="187" t="s">
+      <c r="C105" s="142" t="s">
         <v>64</v>
       </c>
-      <c r="D105" s="188"/>
-      <c r="E105" s="188"/>
-      <c r="F105" s="188"/>
-      <c r="G105" s="189"/>
-      <c r="H105" s="127"/>
-      <c r="I105" s="128"/>
+      <c r="D105" s="143"/>
+      <c r="E105" s="143"/>
+      <c r="F105" s="143"/>
+      <c r="G105" s="144"/>
+      <c r="H105" s="189"/>
+      <c r="I105" s="187"/>
       <c r="J105" s="66"/>
       <c r="K105" s="64"/>
       <c r="L105" s="64"/>
@@ -15715,13 +15712,13 @@
     <row r="106" spans="1:120" s="61" customFormat="1" ht="9.75" customHeight="1">
       <c r="A106" s="16"/>
       <c r="B106" s="71"/>
-      <c r="C106" s="190"/>
-      <c r="D106" s="191"/>
-      <c r="E106" s="191"/>
-      <c r="F106" s="191"/>
-      <c r="G106" s="192"/>
-      <c r="H106" s="127"/>
-      <c r="I106" s="128"/>
+      <c r="C106" s="145"/>
+      <c r="D106" s="146"/>
+      <c r="E106" s="146"/>
+      <c r="F106" s="146"/>
+      <c r="G106" s="147"/>
+      <c r="H106" s="189"/>
+      <c r="I106" s="187"/>
       <c r="J106" s="66"/>
       <c r="K106" s="64"/>
       <c r="L106" s="64"/>
@@ -15838,14 +15835,14 @@
       <c r="A107" s="16"/>
       <c r="B107" s="36"/>
       <c r="C107" s="78"/>
-      <c r="D107" s="132" t="s">
+      <c r="D107" s="114" t="s">
         <v>59</v>
       </c>
-      <c r="E107" s="133"/>
-      <c r="F107" s="133"/>
-      <c r="G107" s="134"/>
-      <c r="H107" s="127"/>
-      <c r="I107" s="128"/>
+      <c r="E107" s="115"/>
+      <c r="F107" s="115"/>
+      <c r="G107" s="116"/>
+      <c r="H107" s="189"/>
+      <c r="I107" s="187"/>
       <c r="J107" s="66"/>
       <c r="K107" s="64"/>
       <c r="L107" s="64"/>
@@ -15962,12 +15959,12 @@
       <c r="A108" s="16"/>
       <c r="B108" s="36"/>
       <c r="C108" s="76"/>
-      <c r="D108" s="135"/>
-      <c r="E108" s="136"/>
-      <c r="F108" s="136"/>
-      <c r="G108" s="137"/>
-      <c r="H108" s="127"/>
-      <c r="I108" s="128"/>
+      <c r="D108" s="117"/>
+      <c r="E108" s="118"/>
+      <c r="F108" s="118"/>
+      <c r="G108" s="119"/>
+      <c r="H108" s="189"/>
+      <c r="I108" s="187"/>
       <c r="J108" s="66"/>
       <c r="K108" s="64"/>
       <c r="L108" s="64"/>
@@ -16085,15 +16082,15 @@
       <c r="B109" s="36"/>
       <c r="C109" s="60"/>
       <c r="D109" s="70"/>
-      <c r="E109" s="105" t="s">
+      <c r="E109" s="148" t="s">
         <v>73</v>
       </c>
-      <c r="F109" s="105"/>
-      <c r="G109" s="105"/>
-      <c r="H109" s="111">
+      <c r="F109" s="148"/>
+      <c r="G109" s="148"/>
+      <c r="H109" s="102">
         <v>45624</v>
       </c>
-      <c r="I109" s="113">
+      <c r="I109" s="108">
         <v>100</v>
       </c>
       <c r="J109" s="62"/>
@@ -16213,11 +16210,11 @@
       <c r="B110" s="36"/>
       <c r="C110" s="60"/>
       <c r="D110" s="70"/>
-      <c r="E110" s="103"/>
-      <c r="F110" s="103"/>
-      <c r="G110" s="103"/>
-      <c r="H110" s="107"/>
-      <c r="I110" s="143"/>
+      <c r="E110" s="101"/>
+      <c r="F110" s="101"/>
+      <c r="G110" s="101"/>
+      <c r="H110" s="103"/>
+      <c r="I110" s="109"/>
       <c r="J110" s="62"/>
       <c r="K110" s="20"/>
       <c r="L110" s="20"/>
@@ -16335,15 +16332,15 @@
       <c r="B111" s="36"/>
       <c r="C111" s="60"/>
       <c r="D111" s="70"/>
-      <c r="E111" s="103" t="s">
+      <c r="E111" s="101" t="s">
         <v>74</v>
       </c>
-      <c r="F111" s="103"/>
-      <c r="G111" s="103"/>
-      <c r="H111" s="111">
+      <c r="F111" s="101"/>
+      <c r="G111" s="101"/>
+      <c r="H111" s="102">
         <v>45625</v>
       </c>
-      <c r="I111" s="113">
+      <c r="I111" s="108">
         <v>100</v>
       </c>
       <c r="J111" s="62"/>
@@ -16463,11 +16460,11 @@
       <c r="B112" s="36"/>
       <c r="C112" s="60"/>
       <c r="D112" s="70"/>
-      <c r="E112" s="103"/>
-      <c r="F112" s="103"/>
-      <c r="G112" s="103"/>
-      <c r="H112" s="107"/>
-      <c r="I112" s="143"/>
+      <c r="E112" s="101"/>
+      <c r="F112" s="101"/>
+      <c r="G112" s="101"/>
+      <c r="H112" s="103"/>
+      <c r="I112" s="109"/>
       <c r="J112" s="62"/>
       <c r="K112" s="20"/>
       <c r="L112" s="20"/>
@@ -16585,15 +16582,15 @@
       <c r="B113" s="71"/>
       <c r="C113" s="91"/>
       <c r="D113" s="70"/>
-      <c r="E113" s="103" t="s">
+      <c r="E113" s="101" t="s">
         <v>61</v>
       </c>
-      <c r="F113" s="103"/>
-      <c r="G113" s="103"/>
+      <c r="F113" s="101"/>
+      <c r="G113" s="101"/>
       <c r="H113" s="110">
         <v>45629</v>
       </c>
-      <c r="I113" s="112">
+      <c r="I113" s="111">
         <v>100</v>
       </c>
       <c r="J113" s="62"/>
@@ -16713,11 +16710,11 @@
       <c r="B114" s="71"/>
       <c r="C114" s="91"/>
       <c r="D114" s="70"/>
-      <c r="E114" s="125"/>
-      <c r="F114" s="125"/>
-      <c r="G114" s="125"/>
-      <c r="H114" s="111"/>
-      <c r="I114" s="113"/>
+      <c r="E114" s="197"/>
+      <c r="F114" s="197"/>
+      <c r="G114" s="197"/>
+      <c r="H114" s="102"/>
+      <c r="I114" s="108"/>
       <c r="J114" s="62"/>
       <c r="K114" s="20"/>
       <c r="L114" s="20"/>
@@ -16834,16 +16831,16 @@
       <c r="A115" s="16"/>
       <c r="B115" s="71"/>
       <c r="C115" s="91"/>
-      <c r="D115" s="103"